--- a/TokenMeter项目总表.xlsx
+++ b/TokenMeter项目总表.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R273bfaa83b6049a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Rbc6ef8bb2639460e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R040b0abcea5b431b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R6440d552f63d4ee6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="Raf16677dbd7a4485"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="Rc1d784c2090d4389"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="Rf593c1d785cd445b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R6b7a1e7c3e3044e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="R4341405b107e4236"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R1d84b9095f3648d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R2b6cc7a070834b86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="Re3106a0d2e2d4b80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="R6a57cec12e994a8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="Rf6cef35fabc24ddd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R870d1980669b4311"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="Rb0e4008c77844b04"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="Rbc5331d93c774516"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="Rc90f2e9dd79b4bb7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R277b58ca05794dbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Rd0996dd94d3c45f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R887b18a934b54a2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="Red3b7ea71774408d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -731,8 +731,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="TMTable5" displayName="TMTable5" ref="A4:K39" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:K39"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="TMTable5" displayName="TMTable5" ref="A4:K47" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:K47"/>
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="任务编号"/>
     <x:tableColumn id="2" name="层级"/>
@@ -751,8 +751,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TMTable6" displayName="TMTable6" ref="A4:M113" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:M113"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TMTable6" displayName="TMTable6" ref="A4:M133" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:M133"/>
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="功能编号"/>
     <x:tableColumn id="2" name="用例编号"/>
@@ -794,8 +794,8 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="TMTable8" displayName="TMTable8" ref="A4:M6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:M6"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="TMTable8" displayName="TMTable8" ref="A4:M7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:M7"/>
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="发布编号"/>
     <x:tableColumn id="2" name="版本"/>
@@ -1091,8 +1091,8 @@
         <x:v>已登记用例</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:f>COUNTA('05测试用例'!B5:B113)</x:f>
-        <x:v>109</x:v>
+        <x:f>COUNTA('05测试用例'!B5:B133)</x:f>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C8" s="9" t="str">
         <x:v>包含细化用例及未来概要场景</x:v>
@@ -1115,7 +1115,7 @@
         <x:v>细化产品用例</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>67</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C10" s="9" t="str">
         <x:v>逐条结果按运行批次记录；变体在独立结果Excel列出</x:v>
@@ -1148,7 +1148,7 @@
         <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="B13" s="10" t="n">
-        <x:v>0</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C13" s="4" t="str">
         <x:v>在05测试用例筛选此状态</x:v>
@@ -1245,7 +1245,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f032e25c44a498a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb58c15311bf44e1a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1953,7 +1953,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf83fc05e890d4999"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R442989d133f3481a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2102,7 +2102,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95753fc0b9574ea2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4227ee48b2e4820"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2497,7 +2497,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc10d539c148d4de5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R416a3d7305724974"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3416,7 +3416,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6b51f9b912f4f1f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7fa85358b3444e5f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3592,10 +3592,10 @@
         <x:v>0.4.0</x:v>
       </x:c>
       <x:c r="H8" s="9" t="str">
-        <x:v>规划中</x:v>
+        <x:v>开发中</x:v>
       </x:c>
       <x:c r="I8" s="9" t="str">
-        <x:v>docs/product/README.md:21</x:v>
+        <x:v>releases/v0.4.0-20261001T040433Z/02-breakdown.md</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="42" customHeight="1">
@@ -4126,7 +4126,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R511cbb049ee44e39"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9554a7b42354ae4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5193,260 +5193,564 @@
         <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:56</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="32" customHeight="1">
+    <x:row r="33" ht="72" customHeight="1">
       <x:c r="A33" s="4" t="str">
-        <x:v>TASK-TM001-PLAN</x:v>
+        <x:v>TASK-TM004-SOURCE</x:v>
       </x:c>
       <x:c r="B33" s="4" t="str">
-        <x:v>历史分组</x:v>
+        <x:v>具体任务</x:v>
       </x:c>
       <x:c r="C33" s="4" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="D33" s="4" t="str">
+        <x:v>REQ-TM004</x:v>
+      </x:c>
+      <x:c r="E33" s="4" t="str">
+        <x:v>AC-TM004-001
+AC-TM004-002
+AC-TM004-003
+AC-TM004-004</x:v>
+      </x:c>
+      <x:c r="F33" s="4" t="str">
+        <x:v>TM-002授权句柄、项目目录</x:v>
+      </x:c>
+      <x:c r="G33" s="4" t="str">
+        <x:v>只遍历授权根下已确认的主/子日志；失权停扫、重授补扫；越界拒绝；预览与采集分别判定</x:v>
+      </x:c>
+      <x:c r="H33" s="4" t="str">
+        <x:v>TM-002授权接口及可续扫合同</x:v>
+      </x:c>
+      <x:c r="I33" s="4" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="D33" s="4" t="str">
-        <x:v>REQ-TM001</x:v>
-      </x:c>
-      <x:c r="E33" s="4" t="str">
+      <x:c r="J33" s="4" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="K33" s="4" t="str">
+        <x:v>releases/v0.4.0-20261001T040433Z/02-breakdown.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="72" customHeight="1">
+      <x:c r="A34" s="9" t="str">
+        <x:v>TASK-TM004-PARSER</x:v>
+      </x:c>
+      <x:c r="B34" s="9" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C34" s="9" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="D34" s="9" t="str">
+        <x:v>REQ-TM004</x:v>
+      </x:c>
+      <x:c r="E34" s="9" t="str">
+        <x:v>AC-TM004-001
+AC-TM004-002
+AC-TM004-003
+AC-TM004-004</x:v>
+      </x:c>
+      <x:c r="F34" s="9" t="str">
+        <x:v>版本来源明确的完整原始行</x:v>
+      </x:c>
+      <x:c r="G34" s="9" t="str">
+        <x:v>抽取usage、模型、UTC时间、主/子标志及来源标识；不保留正文</x:v>
+      </x:c>
+      <x:c r="H34" s="9" t="str">
+        <x:v>raw样本、TM-003事件合同</x:v>
+      </x:c>
+      <x:c r="I34" s="9" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="F33" s="4" t="str">
+      <x:c r="J34" s="9" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="K34" s="9" t="str">
+        <x:v>releases/v0.4.0-20261001T040433Z/02-breakdown.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="72" customHeight="1">
+      <x:c r="A35" s="4" t="str">
+        <x:v>TASK-TM004-LINEAGE</x:v>
+      </x:c>
+      <x:c r="B35" s="4" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C35" s="4" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="D35" s="4" t="str">
+        <x:v>REQ-TM004</x:v>
+      </x:c>
+      <x:c r="E35" s="4" t="str">
+        <x:v>AC-TM004-001
+AC-TM004-002
+AC-TM004-003
+AC-TM004-004</x:v>
+      </x:c>
+      <x:c r="F35" s="4" t="str">
+        <x:v>父子与fork来源证据</x:v>
+      </x:c>
+      <x:c r="G35" s="4" t="str">
+        <x:v>证实父子关系时正确归属；证实继承历史时跨会话去重；歧义诊断且不污染可信量</x:v>
+      </x:c>
+      <x:c r="H35" s="4" t="str">
+        <x:v>raw父子/fork样本、PARSER</x:v>
+      </x:c>
+      <x:c r="I35" s="4" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="G33" s="4" t="str">
-        <x:v>六文档、完整追踪、SOP 修正、基线通过</x:v>
-      </x:c>
-      <x:c r="H33" s="4" t="str">
-        <x:v>需求</x:v>
-      </x:c>
-      <x:c r="I33" s="4" t="str">
-        <x:v>TEST-TM001-GOVERNANCE</x:v>
-      </x:c>
-      <x:c r="J33" s="4" t="str">
-        <x:v>historical_group_not_minimal_task</x:v>
-      </x:c>
-      <x:c r="K33" s="4" t="str">
-        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" ht="42" customHeight="1">
-      <x:c r="A34" s="9" t="str">
-        <x:v>TASK-TM001-SERVER</x:v>
-      </x:c>
-      <x:c r="B34" s="9" t="str">
-        <x:v>历史分组</x:v>
-      </x:c>
-      <x:c r="C34" s="9" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="D34" s="9" t="str">
-        <x:v>REQ-TM001</x:v>
-      </x:c>
-      <x:c r="E34" s="9" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="F34" s="9" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="G34" s="9" t="str">
-        <x:v>FastAPI/SQLAlchemy/Alembic 工程、真实认证/权限/审计 API；随机可撤销 token 固定30天到期、不滑动，改密/重置/停用撤销旧会话</x:v>
-      </x:c>
-      <x:c r="H34" s="9" t="str">
-        <x:v>计划、数据/测试</x:v>
-      </x:c>
-      <x:c r="I34" s="9" t="str">
-        <x:v>E2E-TM001-001、E2E-TM001-002、E2E-TM001-003</x:v>
-      </x:c>
-      <x:c r="J34" s="9" t="str">
-        <x:v>historical_group_not_minimal_task</x:v>
-      </x:c>
-      <x:c r="K34" s="9" t="str">
-        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" ht="42" customHeight="1">
-      <x:c r="A35" s="4" t="str">
-        <x:v>TASK-TM001-DATA</x:v>
-      </x:c>
-      <x:c r="B35" s="4" t="str">
-        <x:v>历史分组</x:v>
-      </x:c>
-      <x:c r="C35" s="4" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="D35" s="4" t="str">
-        <x:v>REQ-TM001</x:v>
-      </x:c>
-      <x:c r="E35" s="4" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="F35" s="4" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="G35" s="4" t="str">
-        <x:v>独立测试/生产 SQLite 文件、可执行造数 SQL、生产首建管理员、回归账号/独立预期及安全重置；已有生产密码不可被重建覆盖</x:v>
-      </x:c>
-      <x:c r="H35" s="4" t="str">
-        <x:v>计划、工程骨架</x:v>
-      </x:c>
-      <x:c r="I35" s="4" t="str">
-        <x:v>TEST-TM001-SERVER、E2E-TM001-001、E2E-TM001-005</x:v>
-      </x:c>
       <x:c r="J35" s="4" t="str">
-        <x:v>historical_group_not_minimal_task</x:v>
+        <x:v>baseline_pending</x:v>
       </x:c>
       <x:c r="K35" s="4" t="str">
-        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:11</x:v>
+        <x:v>releases/v0.4.0-20261001T040433Z/02-breakdown.md</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="72" customHeight="1">
       <x:c r="A36" s="9" t="str">
+        <x:v>TASK-TM004-INCREMENTAL</x:v>
+      </x:c>
+      <x:c r="B36" s="9" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C36" s="9" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="D36" s="9" t="str">
+        <x:v>REQ-TM004</x:v>
+      </x:c>
+      <x:c r="E36" s="9" t="str">
+        <x:v>AC-TM004-001
+AC-TM004-002
+AC-TM004-003
+AC-TM004-004</x:v>
+      </x:c>
+      <x:c r="F36" s="9" t="str">
+        <x:v>追加、半行、重复片段、跨来源ID、重启</x:v>
+      </x:c>
+      <x:c r="G36" s="9" t="str">
+        <x:v>持久游标、唯一键及事务；完整行才提交；跨来源不误去重；重扫幂等</x:v>
+      </x:c>
+      <x:c r="H36" s="9" t="str">
+        <x:v>TM-003 SQLite身份合同、PARSER</x:v>
+      </x:c>
+      <x:c r="I36" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J36" s="9" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="K36" s="9" t="str">
+        <x:v>releases/v0.4.0-20261001T040433Z/02-breakdown.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="72" customHeight="1">
+      <x:c r="A37" s="4" t="str">
+        <x:v>TASK-TM004-DIAGNOSTIC</x:v>
+      </x:c>
+      <x:c r="B37" s="4" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C37" s="4" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="D37" s="4" t="str">
+        <x:v>REQ-TM004</x:v>
+      </x:c>
+      <x:c r="E37" s="4" t="str">
+        <x:v>AC-TM004-001
+AC-TM004-002
+AC-TM004-003
+AC-TM004-004</x:v>
+      </x:c>
+      <x:c r="F37" s="4" t="str">
+        <x:v>缺usage、未知格式、读取失败</x:v>
+      </x:c>
+      <x:c r="G37" s="4" t="str">
+        <x:v>UI区分可信零、未知、缺失、无授权；诊断不泄露正文或完整路径</x:v>
+      </x:c>
+      <x:c r="H37" s="4" t="str">
+        <x:v>TM-003诊断接口、PARSER</x:v>
+      </x:c>
+      <x:c r="I37" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J37" s="4" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="K37" s="4" t="str">
+        <x:v>releases/v0.4.0-20261001T040433Z/02-breakdown.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="72" customHeight="1">
+      <x:c r="A38" s="9" t="str">
+        <x:v>TASK-TM004-DATA</x:v>
+      </x:c>
+      <x:c r="B38" s="9" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C38" s="9" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="D38" s="9" t="str">
+        <x:v>REQ-TM004</x:v>
+      </x:c>
+      <x:c r="E38" s="9" t="str">
+        <x:v>AC-TM004-001
+AC-TM004-002
+AC-TM004-003
+AC-TM004-004</x:v>
+      </x:c>
+      <x:c r="F38" s="9" t="str">
+        <x:v>隔离Claude Code 2.1.126原生投影与合成反例</x:v>
+      </x:c>
+      <x:c r="G38" s="9" t="str">
+        <x:v>版本化fixture生成、追加/半行/撤权程序、独立expected及SQLite只读检查</x:v>
+      </x:c>
+      <x:c r="H38" s="9" t="str">
+        <x:v>raw来源、TM-002/003数据合同</x:v>
+      </x:c>
+      <x:c r="I38" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J38" s="9" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="K38" s="9" t="str">
+        <x:v>releases/v0.4.0-20261001T040433Z/02-breakdown.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="72" customHeight="1">
+      <x:c r="A39" s="4" t="str">
+        <x:v>TASK-TM004-E2E</x:v>
+      </x:c>
+      <x:c r="B39" s="4" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C39" s="4" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="D39" s="4" t="str">
+        <x:v>REQ-TM004</x:v>
+      </x:c>
+      <x:c r="E39" s="4" t="str">
+        <x:v>AC-TM004-001
+AC-TM004-002
+AC-TM004-003
+AC-TM004-004</x:v>
+      </x:c>
+      <x:c r="F39" s="4" t="str">
+        <x:v>最终安装App、真实服务、隔离SQLite</x:v>
+      </x:c>
+      <x:c r="G39" s="4" t="str">
+        <x:v>全部细TC绑定固定Playwright Electron测试；逐步原始记录及历史功能全量回归</x:v>
+      </x:c>
+      <x:c r="H39" s="4" t="str">
+        <x:v>SOURCE→DATA、TM-001包执行器</x:v>
+      </x:c>
+      <x:c r="I39" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J39" s="4" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="K39" s="4" t="str">
+        <x:v>releases/v0.4.0-20261001T040433Z/02-breakdown.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="72" customHeight="1">
+      <x:c r="A40" s="9" t="str">
+        <x:v>TASK-TM004-RELEASE</x:v>
+      </x:c>
+      <x:c r="B40" s="9" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C40" s="9" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="D40" s="9" t="str">
+        <x:v>REQ-TM004</x:v>
+      </x:c>
+      <x:c r="E40" s="9" t="str">
+        <x:v>AC-TM004-001
+AC-TM004-002
+AC-TM004-003
+AC-TM004-004</x:v>
+      </x:c>
+      <x:c r="F40" s="9" t="str">
+        <x:v>完整候选</x:v>
+      </x:c>
+      <x:c r="G40" s="9" t="str">
+        <x:v>文档、矩阵、总表、Changelog同步；DMG安装门禁；交总控集成</x:v>
+      </x:c>
+      <x:c r="H40" s="9" t="str">
+        <x:v>E2E与此前版本全回归</x:v>
+      </x:c>
+      <x:c r="I40" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J40" s="9" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="K40" s="9" t="str">
+        <x:v>releases/v0.4.0-20261001T040433Z/02-breakdown.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="32" customHeight="1">
+      <x:c r="A41" s="4" t="str">
+        <x:v>TASK-TM001-PLAN</x:v>
+      </x:c>
+      <x:c r="B41" s="4" t="str">
+        <x:v>历史分组</x:v>
+      </x:c>
+      <x:c r="C41" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="D41" s="4" t="str">
+        <x:v>REQ-TM001</x:v>
+      </x:c>
+      <x:c r="E41" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="F41" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="G41" s="4" t="str">
+        <x:v>六文档、完整追踪、SOP 修正、基线通过</x:v>
+      </x:c>
+      <x:c r="H41" s="4" t="str">
+        <x:v>需求</x:v>
+      </x:c>
+      <x:c r="I41" s="4" t="str">
+        <x:v>TEST-TM001-GOVERNANCE</x:v>
+      </x:c>
+      <x:c r="J41" s="4" t="str">
+        <x:v>historical_group_not_minimal_task</x:v>
+      </x:c>
+      <x:c r="K41" s="4" t="str">
+        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="42" customHeight="1">
+      <x:c r="A42" s="9" t="str">
+        <x:v>TASK-TM001-SERVER</x:v>
+      </x:c>
+      <x:c r="B42" s="9" t="str">
+        <x:v>历史分组</x:v>
+      </x:c>
+      <x:c r="C42" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="D42" s="9" t="str">
+        <x:v>REQ-TM001</x:v>
+      </x:c>
+      <x:c r="E42" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="F42" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="G42" s="9" t="str">
+        <x:v>FastAPI/SQLAlchemy/Alembic 工程、真实认证/权限/审计 API；随机可撤销 token 固定30天到期、不滑动，改密/重置/停用撤销旧会话</x:v>
+      </x:c>
+      <x:c r="H42" s="9" t="str">
+        <x:v>计划、数据/测试</x:v>
+      </x:c>
+      <x:c r="I42" s="9" t="str">
+        <x:v>E2E-TM001-001、E2E-TM001-002、E2E-TM001-003</x:v>
+      </x:c>
+      <x:c r="J42" s="9" t="str">
+        <x:v>historical_group_not_minimal_task</x:v>
+      </x:c>
+      <x:c r="K42" s="9" t="str">
+        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="42" customHeight="1">
+      <x:c r="A43" s="4" t="str">
+        <x:v>TASK-TM001-DATA</x:v>
+      </x:c>
+      <x:c r="B43" s="4" t="str">
+        <x:v>历史分组</x:v>
+      </x:c>
+      <x:c r="C43" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="D43" s="4" t="str">
+        <x:v>REQ-TM001</x:v>
+      </x:c>
+      <x:c r="E43" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="F43" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="G43" s="4" t="str">
+        <x:v>独立测试/生产 SQLite 文件、可执行造数 SQL、生产首建管理员、回归账号/独立预期及安全重置；已有生产密码不可被重建覆盖</x:v>
+      </x:c>
+      <x:c r="H43" s="4" t="str">
+        <x:v>计划、工程骨架</x:v>
+      </x:c>
+      <x:c r="I43" s="4" t="str">
+        <x:v>TEST-TM001-SERVER、E2E-TM001-001、E2E-TM001-005</x:v>
+      </x:c>
+      <x:c r="J43" s="4" t="str">
+        <x:v>historical_group_not_minimal_task</x:v>
+      </x:c>
+      <x:c r="K43" s="4" t="str">
+        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="72" customHeight="1">
+      <x:c r="A44" s="9" t="str">
         <x:v>TASK-TM001-MAC</x:v>
       </x:c>
-      <x:c r="B36" s="9" t="str">
+      <x:c r="B44" s="9" t="str">
         <x:v>历史分组</x:v>
       </x:c>
-      <x:c r="C36" s="9" t="str">
+      <x:c r="C44" s="9" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="D36" s="9" t="str">
+      <x:c r="D44" s="9" t="str">
         <x:v>REQ-TM001</x:v>
       </x:c>
-      <x:c r="E36" s="9" t="str">
+      <x:c r="E44" s="9" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="F36" s="9" t="str">
+      <x:c r="F44" s="9" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="G36" s="9" t="str">
+      <x:c r="G44" s="9" t="str">
         <x:v>Electron React/TypeScript 登录/改密/主页/管理、默认本机 API/更新源地址与配置管理页的用户覆盖持久化；默认开启可关闭的设备自动登录、按规范化 origin 隔离的受保护凭据文件与内存会话、稳定 UI 标识、Playwright Electron工程</x:v>
       </x:c>
-      <x:c r="H36" s="9" t="str">
+      <x:c r="H44" s="9" t="str">
         <x:v>API 合同、工程骨架</x:v>
       </x:c>
-      <x:c r="I36" s="9" t="str">
+      <x:c r="I44" s="9" t="str">
         <x:v>E2E-TM001-001、E2E-TM001-002、E2E-TM001-003、E2E-TM001-004、E2E-TM001-005、E2E-TM001-006</x:v>
       </x:c>
-      <x:c r="J36" s="9" t="str">
+      <x:c r="J44" s="9" t="str">
         <x:v>historical_group_not_minimal_task</x:v>
       </x:c>
-      <x:c r="K36" s="9" t="str">
+      <x:c r="K44" s="9" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:12</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" ht="57" customHeight="1">
-      <x:c r="A37" s="4" t="str">
+    <x:row r="45" ht="57" customHeight="1">
+      <x:c r="A45" s="4" t="str">
         <x:v>TASK-TM001-UPDATE</x:v>
       </x:c>
-      <x:c r="B37" s="4" t="str">
+      <x:c r="B45" s="4" t="str">
         <x:v>历史分组</x:v>
       </x:c>
-      <x:c r="C37" s="4" t="str">
+      <x:c r="C45" s="4" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="D37" s="4" t="str">
+      <x:c r="D45" s="4" t="str">
         <x:v>REQ-TM001</x:v>
       </x:c>
-      <x:c r="E37" s="4" t="str">
+      <x:c r="E45" s="4" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="F37" s="4" t="str">
+      <x:c r="F45" s="4" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="G37" s="4" t="str">
+      <x:c r="G45" s="4" t="str">
         <x:v>固定 Ed25519 公钥、同机回环更新源/签名测试包/失败包及真实更新用例；默认49177配置、URL安全校验与升级时锁定更新设置；两构建沿用经校验的同一隔离profile，升级后服务验证自动登录</x:v>
       </x:c>
-      <x:c r="H37" s="4" t="str">
+      <x:c r="H45" s="4" t="str">
         <x:v>Mac 工程</x:v>
       </x:c>
-      <x:c r="I37" s="4" t="str">
+      <x:c r="I45" s="4" t="str">
         <x:v>E2E-TM001-004</x:v>
       </x:c>
-      <x:c r="J37" s="4" t="str">
+      <x:c r="J45" s="4" t="str">
         <x:v>historical_group_not_minimal_task</x:v>
       </x:c>
-      <x:c r="K37" s="4" t="str">
+      <x:c r="K45" s="4" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:13</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="57" customHeight="1">
-      <x:c r="A38" s="9" t="str">
+    <x:row r="46" ht="57" customHeight="1">
+      <x:c r="A46" s="9" t="str">
         <x:v>TASK-TM001-RUNNER</x:v>
       </x:c>
-      <x:c r="B38" s="9" t="str">
+      <x:c r="B46" s="9" t="str">
         <x:v>历史分组</x:v>
       </x:c>
-      <x:c r="C38" s="9" t="str">
+      <x:c r="C46" s="9" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="D38" s="9" t="str">
+      <x:c r="D46" s="9" t="str">
         <x:v>REQ-TM001</x:v>
       </x:c>
-      <x:c r="E38" s="9" t="str">
+      <x:c r="E46" s="9" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="F38" s="9" t="str">
+      <x:c r="F46" s="9" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="G38" s="9" t="str">
+      <x:c r="G46" s="9" t="str">
         <x:v>本机Playwright从最终DMG安装App执行全部六例，原始JSON/trace/fixtureSQL/包摘要、父门禁复核；默认值与动态独占端口隔离测试；真实Squirrel自重启及profile、身份恢复</x:v>
       </x:c>
-      <x:c r="H38" s="9" t="str">
+      <x:c r="H46" s="9" t="str">
         <x:v>数据/桌面工程</x:v>
       </x:c>
-      <x:c r="I38" s="9" t="str">
+      <x:c r="I46" s="9" t="str">
         <x:v>E2E-TM001-001、E2E-TM001-002、E2E-TM001-003、E2E-TM001-004、E2E-TM001-005、E2E-TM001-006</x:v>
       </x:c>
-      <x:c r="J38" s="9" t="str">
+      <x:c r="J46" s="9" t="str">
         <x:v>historical_group_not_minimal_task</x:v>
       </x:c>
-      <x:c r="K38" s="9" t="str">
+      <x:c r="K46" s="9" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:14</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" ht="32" customHeight="1">
-      <x:c r="A39" s="4" t="str">
+    <x:row r="47" ht="32" customHeight="1">
+      <x:c r="A47" s="4" t="str">
         <x:v>TASK-TM001-REVIEW</x:v>
       </x:c>
-      <x:c r="B39" s="4" t="str">
+      <x:c r="B47" s="4" t="str">
         <x:v>历史分组</x:v>
       </x:c>
-      <x:c r="C39" s="4" t="str">
+      <x:c r="C47" s="4" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="D39" s="4" t="str">
+      <x:c r="D47" s="4" t="str">
         <x:v>REQ-TM001</x:v>
       </x:c>
-      <x:c r="E39" s="4" t="str">
+      <x:c r="E47" s="4" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="F39" s="4" t="str">
+      <x:c r="F47" s="4" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="G39" s="4" t="str">
+      <x:c r="G47" s="4" t="str">
         <x:v>完整回归、流程复盘、PR 与合并判定、发布阻塞记录</x:v>
       </x:c>
-      <x:c r="H39" s="4" t="str">
+      <x:c r="H47" s="4" t="str">
         <x:v>全部实现任务</x:v>
       </x:c>
-      <x:c r="I39" s="4" t="str">
+      <x:c r="I47" s="4" t="str">
         <x:v>TEST-TM001-GOVERNANCE</x:v>
       </x:c>
-      <x:c r="J39" s="4" t="str">
+      <x:c r="J47" s="4" t="str">
         <x:v>historical_group_not_minimal_task</x:v>
       </x:c>
-      <x:c r="K39" s="4" t="str">
+      <x:c r="K47" s="4" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:15</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="J5:J39">
+  <x:conditionalFormatting sqref="J5:J47">
     <x:cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="10" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="11" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37a03de48b1548e1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re12022c604784224"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9451,517 +9755,550 @@
         <x:v>尚未执行</x:v>
       </x:c>
     </x:row>
-    <x:row r="93" ht="57" customHeight="1">
+    <x:row r="93" ht="72" customHeight="1">
       <x:c r="A93" s="4" t="str">
-        <x:v>TM-005</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B93" s="4" t="str">
-        <x:v>E2E-TM005-001</x:v>
+        <x:v>TC-TM004-SOURCE-01</x:v>
       </x:c>
       <x:c r="C93" s="4" t="str">
-        <x:v>日期筛选、趋势和明细</x:v>
+        <x:v>授权根限定（TASK-TM004-SOURCE，AC-001，E2E-001）</x:v>
       </x:c>
       <x:c r="D93" s="4" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-SOURCE</x:v>
       </x:c>
       <x:c r="E93" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F93" s="4" t="str">
-        <x:v>数据集 date_ranges；date_ranges 已由 scripts/test_data.py 提供标准化语义样例，固定2026-09-29T04:00:00Z、Asia/Shanghai、seed42；13行含1重复、12唯一。需另有已验证raw输入映射和真实App导入流程，当前未实现。</x:v>
+        <x:v>用户经 TM-002 UI 只选择隔离项目A目录；目录内有 M=100/10 完整原始行，旁边未授权目录有 X=999/99。</x:v>
       </x:c>
       <x:c r="G93" s="4" t="str">
-        <x:v>独立expected中的total依次16500、110、17380、27830、31130；custom=2200。today共5条、input15000、output1500、cache1700、reasoning170，cache/reasoning不再相加；custom-start包含、custom-end排除。趋势点及明细按expected事件时间逐条核对。</x:v>
+        <x:v>UI 显示待确认，事件表无新增
+UI 显示1次 M、total110，SQLite只读见唯一M
+调用数仍1、total110
+无X读取请求且事件表无X</x:v>
       </x:c>
       <x:c r="H93" s="4" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读按来源/项目统计 M 行数与 token，总数1/110；检查 X 键不存在；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I93" s="4" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J93" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K93" s="4" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L93" s="4" t="str">
-        <x:v>docs/testing/cases/05-TM-005-usage-statistics.md:15</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:87</x:v>
       </x:c>
       <x:c r="M93" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
     </x:row>
-    <x:row r="94" ht="57" customHeight="1">
+    <x:row r="94" ht="72" customHeight="1">
       <x:c r="A94" s="9" t="str">
-        <x:v>TM-005</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B94" s="9" t="str">
-        <x:v>E2E-TM005-002</x:v>
+        <x:v>TC-TM004-SOURCE-02</x:v>
       </x:c>
       <x:c r="C94" s="9" t="str">
-        <x:v>时区、月边界与缺失值</x:v>
+        <x:v>撤权和重新授权（TASK-TM004-SOURCE，AC-004，E2E-004）</x:v>
       </x:c>
       <x:c r="D94" s="9" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-SOURCE</x:v>
       </x:c>
       <x:c r="E94" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F94" s="9" t="str">
-        <x:v>数据集 date_ranges；复用date_ranges中的2026-09-28T15:59:59Z与16:00:00Z、2026-08-30T15:59:59Z与16:00:00Z边界。另需补充覆盖缺口、已覆盖零调用日、unknown字段三类状态；当前生成器未覆盖后面三类。</x:v>
+        <x:v>已扫描 M=100/10、S=200/20；撤权期间子代理新增 N=50/5。</x:v>
       </x:c>
       <x:c r="G94" s="9" t="str">
-        <x:v>Shanghai下15:59:59Z仍属前日、16:00:00Z属次日；UTC下二者同属UTC日期。无覆盖显示缺失，真实零可显示0，unknown字段显示未知；不得互相代替。各范围expected须独立按当地日期边界列出，不调用产品查询生成。</x:v>
+        <x:v>状态显示不可读且保留total330
+仍330且诊断为读取受阻
+唯一 M/S/N、total385
+M/S/N仍为三次且total385</x:v>
       </x:c>
       <x:c r="H94" s="9" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读唯一键数3与 token总385，撤权阶段无N。重置同共用配方；TM-002失权模拟与子目录绑定待补；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I94" s="9" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J94" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K94" s="9" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L94" s="9" t="str">
-        <x:v>docs/testing/cases/05-TM-005-usage-statistics.md:32</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:91</x:v>
       </x:c>
       <x:c r="M94" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
     </x:row>
-    <x:row r="95" ht="57" customHeight="1">
+    <x:row r="95" ht="72" customHeight="1">
       <x:c r="A95" s="4" t="str">
-        <x:v>TM-006</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B95" s="4" t="str">
-        <x:v>E2E-TM006-001</x:v>
+        <x:v>TC-TM004-PARSER-01</x:v>
       </x:c>
       <x:c r="C95" s="4" t="str">
-        <x:v>Token子项与基础费用</x:v>
+        <x:v>主/子实际调用（TASK-TM004-PARSER，AC-001，E2E-001）</x:v>
       </x:c>
       <x:c r="D95" s="4" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-PARSER</x:v>
       </x:c>
       <x:c r="E95" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F95" s="4" t="str">
-        <x:v>数据集 pricing；pricing由scripts/test_data.py生成合成非计费价格。gpt-5每百万input/cache/output为USD2/0.2/8；today-gpt input1000含cache200、output100含reasoning20。价格不是厂商现价。</x:v>
+        <x:v>同一项目原始主M100/10与子S200/20，模型各自保留，父关系有原始证据。</x:v>
       </x:c>
       <x:c r="G95" s="4" t="str">
-        <x:v>单调用total=1100；费用=(800×2+200×0.2+100×8)/1000000=USD0.002440，reasoning20不另加价。today已知费用USD0.015190且有1条无价格，alice今日USD0.010090。使用Decimal/十进制独立oracle，不以界面舍入反推底层精度。</x:v>
+        <x:v>可信total110
+可信input300/output30/total330
+仍2次调用/330</x:v>
       </x:c>
       <x:c r="H95" s="4" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读两条唯一事件和模型/父项目归属；不读取正文。版本化raw和模型字段待补；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I95" s="4" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J95" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K95" s="4" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L95" s="4" t="str">
-        <x:v>docs/testing/cases/06-TM-006-cost-estimates.md:15</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:95</x:v>
       </x:c>
       <x:c r="M95" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
     </x:row>
-    <x:row r="96" ht="57" customHeight="1">
+    <x:row r="96" ht="102" customHeight="1">
       <x:c r="A96" s="9" t="str">
-        <x:v>TM-006</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B96" s="9" t="str">
-        <x:v>E2E-TM006-002</x:v>
+        <x:v>TC-TM004-PARSER-02</x:v>
       </x:c>
       <x:c r="C96" s="9" t="str">
-        <x:v>历史价格、多币种和未知费用</x:v>
+        <x:v>未知结构/缺字段（TASK-TM004-PARSER，AC-003，E2E-003）</x:v>
       </x:c>
       <x:c r="D96" s="9" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-PARSER</x:v>
       </x:c>
       <x:c r="E96" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F96" s="9" t="str">
-        <x:v>数据集 pricing_extended；pricing_extended planned：同模型在生效时点T前后各一调用，两个独立价格版本；另有USD/CNY各一模型、无价模型和订阅估算模型。必须提供价格/订阅分摊规则及手算expected后才能实现。</x:v>
+        <x:v>已支持版本完整 M100/10、未知结构 U、JSONL 原始行真正缺 usage 的 Q。</x:v>
       </x:c>
       <x:c r="G96" s="9" t="str">
-        <x:v>T前后依各自生效版本计算，历史结果不会悄悄换价；USD与CNY分组，未约定汇率不得相加；无价格显示未知而非0；订阅必须明确估算口径。具体金额oracle依待定义订阅/价格合同生成，当前不得手填PASS。</x:v>
+        <x:v>可信total110
+可信仍110且出现未知结构诊断
+可信仍110、缺usage诊断新增
+诊断可见且不显示 U/Q 为零调用</x:v>
       </x:c>
       <x:c r="H96" s="9" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读可信事件1条/110，诊断各1条；具体版本标识、缺字段schema和SQL待补。隔离负测中 API SSE 省略 usage 后 CLI 仍在原生 JSONL 写0/0，**不是** Q 的原生缺字段样本；Q 需另证来源或标明故障注入，不得把0/0回填解释成已知零；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I96" s="9" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J96" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K96" s="9" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L96" s="9" t="str">
-        <x:v>docs/testing/cases/06-TM-006-cost-estimates.md:32</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:99</x:v>
       </x:c>
       <x:c r="M96" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
     </x:row>
-    <x:row r="97" ht="57" customHeight="1">
+    <x:row r="97" ht="72" customHeight="1">
       <x:c r="A97" s="4" t="str">
-        <x:v>TM-007</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B97" s="4" t="str">
-        <x:v>E2E-TM007-001</x:v>
+        <x:v>TC-TM004-LINEAGE-01</x:v>
       </x:c>
       <x:c r="C97" s="4" t="str">
-        <x:v>离线、重启和补传幂等</x:v>
+        <x:v>子代理父项目（TASK-TM004-LINEAGE，AC-001，E2E-001）</x:v>
       </x:c>
       <x:c r="D97" s="4" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-LINEAGE</x:v>
       </x:c>
       <x:c r="E97" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F97" s="4" t="str">
-        <x:v>数据集 sync_faults；sync_faults planned；alice两个隔离设备A/B，设备A调用100/10、B调用200/20；真实FastAPI/SQLite服务，可由外部fixture断网/恢复。账号继续用隔离测试fixture。</x:v>
+        <x:v>项目A主M100/10、子S200/20，另有项目B同名会话标识但无父关系。</x:v>
       </x:c>
       <x:c r="G97" s="4" t="str">
-        <x:v>离线重启不丢队列；恢复后2唯一调用、input300/output30/total330；重复批次不再加量。客户端只在真实确认后标已同步，个人合计与对应团队子集一致。</x:v>
+        <x:v>A=110
+A=330、B=0
+A仍330
+S标为子代理且使用原模型</x:v>
       </x:c>
       <x:c r="H97" s="4" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读S的父项目键为A、事件数2；原始父链线索缺失时不得假称通过；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I97" s="4" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J97" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K97" s="4" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L97" s="4" t="str">
-        <x:v>docs/testing/cases/07-TM-007-team-sync.md:11</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:103</x:v>
       </x:c>
       <x:c r="M97" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
     </x:row>
-    <x:row r="98" ht="57" customHeight="1">
+    <x:row r="98" ht="72" customHeight="1">
       <x:c r="A98" s="9" t="str">
-        <x:v>TM-007</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B98" s="9" t="str">
-        <x:v>E2E-TM007-002</x:v>
+        <x:v>TC-TM004-LINEAGE-02</x:v>
       </x:c>
       <x:c r="C98" s="9" t="str">
-        <x:v>部分确认、中断和账号切换</x:v>
+        <x:v>fork继承和ID改写（TASK-TM004-LINEAGE，AC-002，E2E-002）</x:v>
       </x:c>
       <x:c r="D98" s="9" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-LINEAGE</x:v>
       </x:c>
       <x:c r="E98" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F98" s="9" t="str">
-        <x:v>数据集 sync_faults；准备alice的三条唯一事件A/B/C，总量各110/220/330；控制服务仅确认A后断开，B可能已提交但响应丢失，C未提交。另有bob账号。故障注入必须在真实服务外部或明确测试环境中完成，不能绕过认证。</x:v>
+        <x:v>原M100/10、fork复制或引用M但消息ID改写、fork新N50/5。</x:v>
       </x:c>
       <x:c r="G98" s="9" t="str">
-        <x:v>最终alice的A/B/C各一次、total660；响应丢失不造成B重复；bob不能承接或篡改alice既有事件归属。切换时旧队列按已批准归属策略隔离，不能默认为新登录账号。</x:v>
+        <x:v>M仅入账一次且total110
+仍110
+total165且调用数2
+仍165</x:v>
       </x:c>
       <x:c r="H98" s="9" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读可信唯一调用2/165及继承诊断/关系；待schema确定；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I98" s="9" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J98" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K98" s="9" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L98" s="9" t="str">
-        <x:v>docs/testing/cases/07-TM-007-team-sync.md:28</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:107</x:v>
       </x:c>
       <x:c r="M98" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
     </x:row>
-    <x:row r="99" ht="57" customHeight="1">
+    <x:row r="99" ht="72" customHeight="1">
       <x:c r="A99" s="4" t="str">
-        <x:v>TM-007</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B99" s="4" t="str">
-        <x:v>E2E-TM007-003</x:v>
+        <x:v>TC-TM004-INCREMENTAL-01</x:v>
       </x:c>
       <x:c r="C99" s="4" t="str">
-        <x:v>上传白名单与项目映射</x:v>
+        <x:v>半行完成（TASK-TM004-INCREMENTAL，AC-002，E2E-002）</x:v>
       </x:c>
       <x:c r="D99" s="4" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-INCREMENTAL</x:v>
       </x:c>
       <x:c r="E99" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F99" s="4" t="str">
-        <x:v>数据集 sync_faults；合成日志包含唯一正文/代码/API-key/完整路径哨兵，以及合法用量/必要去重元数据；只用假值。准备已归属项目A和未归属事件B，待sync_faults生成。</x:v>
+        <x:v>已计M+N total165，P=20/2 原始JSONL行分成两次写入。</x:v>
       </x:c>
       <x:c r="G99" s="4" t="str">
-        <x:v>网络载荷/持久服务数据均不得含正文、代码、key或完整本机路径；只有批准用量/去重字段。B可明确分配，分配不增加事件量、也不跨团队归属。</x:v>
+        <x:v>扫描后仍165、读取游标未越过半行
+扫描后total187、调用数3
+P仅入账一次且total187</x:v>
       </x:c>
       <x:c r="H99" s="4" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读P只一条，可信事件3/187，游标处于完整行末；具体游标schema待补；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I99" s="4" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J99" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K99" s="4" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L99" s="4" t="str">
-        <x:v>docs/testing/cases/07-TM-007-team-sync.md:45</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:111</x:v>
       </x:c>
       <x:c r="M99" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
     </x:row>
-    <x:row r="100" ht="57" customHeight="1">
+    <x:row r="100" ht="72" customHeight="1">
       <x:c r="A100" s="9" t="str">
-        <x:v>TM-007</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B100" s="9" t="str">
-        <x:v>E2E-TM007-004</x:v>
+        <x:v>TC-TM004-INCREMENTAL-02</x:v>
       </x:c>
       <x:c r="C100" s="9" t="str">
-        <x:v>统计越权与停用后上传</x:v>
+        <x:v>重复与事务恢复（TASK-TM004-INCREMENTAL，AC-002/004，E2E-002/004）</x:v>
       </x:c>
       <x:c r="D100" s="9" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-INCREMENTAL</x:v>
       </x:c>
       <x:c r="E100" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F100" s="9" t="str">
-        <x:v>数据集 sync_faults；alice项目A调用100/10，bob项目B调用200/20；成员alice与管理员独立会话；alice另有一条未确认调用C=50/5。sync_faults与可重建统计SQL尚未实现。</x:v>
+        <x:v>完整M100/10、重复相同片段及移动/复制文件；在扫描提交边界中断App。</x:v>
       </x:c>
       <x:c r="G100" s="9" t="str">
-        <x:v>成员无权请求被服务端拒绝，UI不显示bob的220；停用后旧会话及上传拒绝，C不能标为已确认；合法历史不能被失败上传删除。此处补足TM-001仅身份/管理接口权限的范围。</x:v>
+        <x:v>M仅入账一次且total110
+仍110
+仍唯一M/110
+total165</x:v>
       </x:c>
       <x:c r="H100" s="9" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读唯一键数2/165且游标一致；故障注入不得绕过产品事务。TM-003事务接口待补；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I100" s="9" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J100" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K100" s="9" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L100" s="9" t="str">
-        <x:v>docs/testing/cases/07-TM-007-team-sync.md:62</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:115</x:v>
       </x:c>
       <x:c r="M100" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
     </x:row>
-    <x:row r="101" ht="57" customHeight="1">
+    <x:row r="101" ht="87" customHeight="1">
       <x:c r="A101" s="4" t="str">
-        <x:v>TM-008</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B101" s="4" t="str">
-        <x:v>E2E-TM008-001</x:v>
+        <x:v>TC-TM004-DIAG-01</x:v>
       </x:c>
       <x:c r="C101" s="4" t="str">
-        <x:v>筛选一致的CSV导出</x:v>
+        <x:v>未知值不是零（TASK-TM004-DIAGNOSTIC，AC-003，E2E-003）</x:v>
       </x:c>
       <x:c r="D101" s="4" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-DIAGNOSTIC</x:v>
       </x:c>
       <x:c r="E101" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F101" s="4" t="str">
-        <x:v>数据集 export_rows；export_rows planned；两成员、两个模型、时间范围内外各有事件，独立清单明确每条ID/字段/权限。先具备TM-005/007统计和授权。</x:v>
+        <x:v>可信M100/10、U未知格式、Q的JSONL原始行缺usage，以及另有独立来源证明的有效零usage记录Z。</x:v>
       </x:c>
       <x:c r="G101" s="4" t="str">
-        <x:v>每次CSV仅包含当次筛选且授权可见记录，行数/ID/汇总等于独立清单与界面；不混入旧筛选、其他成员或范围外记录。已知/未知费用语义一致。</x:v>
+        <x:v>显示110
+显示可信110和两个不同未覆盖提示
+零值记录可见但总量仍110
+三种状态不混淆</x:v>
       </x:c>
       <x:c r="H101" s="4" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读可信M和已证实的Z，U/Q仅诊断，不以0写入；Z的原始有效性仍 baseline_pending。2.1.126 遇到畸形合成 API 缺usage会自己写0/0，不能拿该行充当Z；未经额外证据不能由0/0 raw推断上游已知零；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I101" s="4" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J101" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K101" s="4" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L101" s="4" t="str">
-        <x:v>docs/testing/cases/08-TM-008-csv-export.md:11</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:119</x:v>
       </x:c>
       <x:c r="M101" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
     </x:row>
-    <x:row r="102" ht="57" customHeight="1">
+    <x:row r="102" ht="72" customHeight="1">
       <x:c r="A102" s="9" t="str">
-        <x:v>TM-008</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B102" s="9" t="str">
-        <x:v>E2E-TM008-002</x:v>
+        <x:v>TC-TM004-DIAG-02</x:v>
       </x:c>
       <x:c r="C102" s="9" t="str">
-        <x:v>CSV转义、未知值及权限</x:v>
+        <x:v>失权提示及隐私（TASK-TM004-DIAGNOSTIC，AC-004，E2E-004）</x:v>
       </x:c>
       <x:c r="D102" s="9" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-DIAGNOSTIC</x:v>
       </x:c>
       <x:c r="E102" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F102" s="9" t="str">
-        <x:v>数据集 export_rows；export_rows需含字段 a,b、say "hi"、带实际换行的项目名、未知费用与非ASCII模型名；两成员各有可区分哨兵事件。只在隔离数据中使用。</x:v>
+        <x:v>M已入账，撤权目录含合成 prompt、代码和密钥哨兵字符串。</x:v>
       </x:c>
       <x:c r="G102" s="9" t="str">
-        <x:v>逗号、双引号、嵌入换行均round-trip一致，Unicode不损坏；未知值不写成0；他人哨兵不出现在文件。若导出失败，不能留下看似完整的半文件。</x:v>
+        <x:v>UI显示读取受阻而非零用量，保留110
+无哨兵文本及完整源路径
+受阻提示消除且M不重计</x:v>
       </x:c>
       <x:c r="H102" s="9" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读事件1/110、诊断状态与仅白名单字段；隐私哨兵由固定生成器构造，不使用真实秘密；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I102" s="9" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J102" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K102" s="9" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L102" s="9" t="str">
-        <x:v>docs/testing/cases/08-TM-008-csv-export.md:28</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:123</x:v>
       </x:c>
       <x:c r="M102" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
     </x:row>
-    <x:row r="103" ht="57" customHeight="1">
+    <x:row r="103" ht="72" customHeight="1">
       <x:c r="A103" s="4" t="str">
-        <x:v>TM-009</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B103" s="4" t="str">
-        <x:v>E2E-TM009-001</x:v>
+        <x:v>TC-TM004-DATA-01</x:v>
       </x:c>
       <x:c r="C103" s="4" t="str">
-        <x:v>80%/100%提醒幂等</x:v>
+        <x:v>原始fixture和独立oracle（TASK-TM004-DATA，AC-001–004，E2E-003）</x:v>
       </x:c>
       <x:c r="D103" s="4" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-DATA</x:v>
       </x:c>
       <x:c r="E103" s="4" t="str">
-        <x:v>产品E2E</x:v>
+        <x:v>data_fixture</x:v>
       </x:c>
       <x:c r="F103" s="4" t="str">
-        <x:v>数据集 budget_periods；budget_periods planned；独立个人、项目和团队预算分别100个合成USD单位，同周期使用量依次79→80→99→100；原始调用与价格要能精确形成这些费用。</x:v>
+        <x:v>固定版本 CLI/公开来源、隔离 CLAUDE_CONFIG_DIR、固定合成任务；禁止访问真实 ~/.claude。</x:v>
       </x:c>
       <x:c r="G103" s="4" t="str">
-        <x:v>每预算每周期80与100各最多一次，未达到不发；重扫/重启/重复上传不重发；预算仅提醒，不拦截模型调用。三层预算分别按其授权范围计算。</x:v>
+        <x:v>版本、来源、原始SHA及父子/fork证据有原件
+M/S/N/P的330、165、187、385在运行前记录
+SHA一致且SQL初态只有合成账号与零事件
+仅删除本次拥有目录且保留原始报告</x:v>
       </x:c>
       <x:c r="H103" s="4" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：本例不直接写入产品用量表；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I103" s="4" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J103" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K103" s="4" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L103" s="4" t="str">
-        <x:v>docs/testing/cases/09-TM-009-budget-alerts.md:11</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:127</x:v>
       </x:c>
       <x:c r="M103" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
     </x:row>
-    <x:row r="104" ht="57" customHeight="1">
+    <x:row r="104" ht="72" customHeight="1">
       <x:c r="A104" s="9" t="str">
-        <x:v>TM-009</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B104" s="9" t="str">
-        <x:v>E2E-TM009-002</x:v>
+        <x:v>TC-TM004-E2E-01</x:v>
       </x:c>
       <x:c r="C104" s="9" t="str">
-        <x:v>新周期、币种与通知恢复</x:v>
+        <x:v>安装包真实链路（TASK-TM004-E2E，AC-001–004，E2E-001/004）</x:v>
       </x:c>
       <x:c r="D104" s="9" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-E2E</x:v>
       </x:c>
       <x:c r="E104" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F104" s="9" t="str">
-        <x:v>数据集 budget_periods；两个币种独立预算；旧周期已发80/100阈值，参考时钟可由产品支持的测试配置推进；测试通知权限可以拒绝及恢复，不能修改用户其他App授权。</x:v>
+        <x:v>本版固定候选SHA、原DMG、TM-001–004完整必测TC清单。</x:v>
       </x:c>
       <x:c r="G104" s="9" t="str">
-        <x:v>系统拒绝不丢失应用内状态、不造成重试通知风暴；新周期独立重置，允许新一轮各阈值一次；币种分开计算。通知补发策略需在对应需求明确，不能由测试临时猜测。</x:v>
+        <x:v>仅连接本次独占服务和隔离授权根
+逐步断言UI、IPC后果和只读SQLite
+目标及历史已交付TC全部执行且无跳过/重试/失败
+结果与候选包一致且本次资源清理完成</x:v>
       </x:c>
       <x:c r="H104" s="9" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：本例不直接写入产品用量表；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I104" s="9" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J104" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K104" s="9" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L104" s="9" t="str">
-        <x:v>docs/testing/cases/09-TM-009-budget-alerts.md:28</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:131</x:v>
       </x:c>
       <x:c r="M104" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -9969,343 +10306,366 @@
     </x:row>
     <x:row r="105" ht="72" customHeight="1">
       <x:c r="A105" s="4" t="str">
-        <x:v>TM-010</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B105" s="4" t="str">
-        <x:v>E2E-TM010-001</x:v>
+        <x:v>TC-TM004-RELEASE-01</x:v>
       </x:c>
       <x:c r="C105" s="4" t="str">
-        <x:v>稳定版发现更新与数据保留</x:v>
+        <x:v>候选与证据一致（TASK-TM004-RELEASE，AC-001–004，E2E-004）</x:v>
       </x:c>
       <x:c r="D105" s="4" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-RELEASE</x:v>
       </x:c>
       <x:c r="E105" s="4" t="str">
-        <x:v>产品E2E</x:v>
+        <x:v>release_gate</x:v>
       </x:c>
       <x:c r="F105" s="4" t="str">
-        <x:v>数据集 update_packages；依赖TM-001/007；update_packages planned。需真实已分发稳定版、候选最终包及相同分发profile的签名/清单；旧版有账号设置、手动地址、统计/队列独立快照。首版无历史稳定版时使用SOP017规定的候选→受控高版，不伪称稳定升级。</x:v>
+        <x:v>同一已提交SHA/tree、DMG摘要、完整TM-001–004结果。</x:v>
       </x:c>
       <x:c r="G105" s="4" t="str">
-        <x:v>更新频率和说明可用；只有声明候选被安装，Sparkle自主重启；更新前后账号/设置/统计与快照一致，队列不丢失不重复。完整更新体验仍为未来功能，TM-001-004通过只证明最小更新路径。</x:v>
+        <x:v>SHA/tree和DMG摘要一致
+完整集合逐例PASS且清理完成，否则阻断
+Excel行和源摘要一致
+SOP-018真实PASS才进入SOP-019</x:v>
       </x:c>
       <x:c r="H105" s="4" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：本例不直接写入产品用量表；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I105" s="4" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J105" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K105" s="4" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L105" s="4" t="str">
-        <x:v>docs/testing/cases/10-TM-010-software-updates.md:11</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:135</x:v>
       </x:c>
       <x:c r="M105" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
     </x:row>
-    <x:row r="106" ht="57" customHeight="1">
+    <x:row r="106" ht="72" customHeight="1">
       <x:c r="A106" s="9" t="str">
-        <x:v>TM-010</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B106" s="9" t="str">
-        <x:v>E2E-TM010-002</x:v>
+        <x:v>TC-TM004-SOURCE-03</x:v>
       </x:c>
       <x:c r="C106" s="9" t="str">
-        <x:v>签名、网络、空间和迁移失败恢复</x:v>
+        <x:v>嵌套子代理目录（TASK-TM004-SOURCE，AC-001，E2E-001）</x:v>
       </x:c>
       <x:c r="D106" s="9" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-SOURCE</x:v>
       </x:c>
       <x:c r="E106" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F106" s="9" t="str">
-        <x:v>数据集 update_packages；对同一干净旧版分别建立四个隔离子场景：坏签名包、下载中断、受限测试卷空间不足、受控迁移失败；每个保存旧版包/DB/配置摘要。故障不能作用用户系统盘/生产库。</x:v>
+        <x:v>2.1.126 已安装二进制显示子代理路径可在 subagents/ 下继续嵌套；确切层级与父链由待取得的原始样本决定。固定数据应含项目A主M100/10、一级子S200/20、嵌套子T=50/5，以及授权根外同名文件X=999/99。</x:v>
       </x:c>
       <x:c r="G106" s="9" t="str">
-        <x:v>每个失败均不能形成半更新；原账号/统计和包的可用状态可验证。网络恢复后的成功需要完整包校验；迁移失败恢复来源与摘要明确。四个子场景全部为本case必需，不能挑一项通过。</x:v>
+        <x:v>项目A可信total385/3次调用
+不读取X
+总量和归属不变
+不猜A</x:v>
       </x:c>
       <x:c r="H106" s="9" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读事件唯一键、父项目与总量3/385；缺链变体的T不得纳入A可信聚合；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I106" s="9" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J106" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K106" s="9" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L106" s="9" t="str">
-        <x:v>docs/testing/cases/10-TM-010-software-updates.md:28</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:139</x:v>
       </x:c>
       <x:c r="M106" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
     </x:row>
-    <x:row r="107" ht="57" customHeight="1">
+    <x:row r="107" ht="72" customHeight="1">
       <x:c r="A107" s="4" t="str">
-        <x:v>TM-010</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B107" s="4" t="str">
-        <x:v>E2E-TM010-003</x:v>
+        <x:v>TC-TM004-PARSER-03</x:v>
       </x:c>
       <x:c r="C107" s="4" t="str">
-        <x:v>升级默认地址和手动覆盖</x:v>
+        <x:v>同一消息多内容块和 Agent 摘要（TASK-TM004-PARSER，AC-001，E2E-001）</x:v>
       </x:c>
       <x:c r="D107" s="4" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-PARSER</x:v>
       </x:c>
       <x:c r="E107" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F107" s="4" t="str">
-        <x:v>数据集 server_default_migration；server_default_migration planned；两套旧安装A从未设置地址、B已手动设置；候选内置一个届时确定且测试可访问的生产HTTPS默认地址。两源有独立账号/数据/会话，公钥不可随URL编辑。</x:v>
+        <x:v>同一次主调用M100/10拆为至少两个带相同 message.id 与 usage 的 assistant 内容块，另有 Agent 工具结果的 totalTokens/usage 摘要与子S200/20原始调用；本机独立结构探针已实际生成31/9双块，CLI 写两行相同 ID 和完整 usage，子代理19/6的父工具结果出现 total_tokens: 25。</x:v>
       </x:c>
       <x:c r="G107" s="4" t="str">
-        <x:v>只有无手动覆盖安装跟随新版默认；显式覆盖即使恰好等于旧默认也应按已经确定的配置来源规则处理。改变origin需重新服务认证，旧token不能跨源复用。</x:v>
+        <x:v>UI/SQLite为1次调用、total110
+可信为M+S两次、total330
+仍330</x:v>
       </x:c>
       <x:c r="H107" s="4" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读源消息调用键2个/330，父Agent汇总不能额外成为第三次调用；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I107" s="4" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J107" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K107" s="4" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L107" s="4" t="str">
-        <x:v>docs/testing/cases/10-TM-010-software-updates.md:45</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:143</x:v>
       </x:c>
       <x:c r="M107" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
     </x:row>
-    <x:row r="108" ht="57" customHeight="1">
+    <x:row r="108" ht="72" customHeight="1">
       <x:c r="A108" s="9" t="str">
-        <x:v>TM-011</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B108" s="9" t="str">
-        <x:v>E2E-TM011-001</x:v>
+        <x:v>TC-TM004-LINEAGE-03</x:v>
       </x:c>
       <x:c r="C108" s="9" t="str">
-        <x:v>SQLite迁移与中断恢复</x:v>
+        <x:v>forkedFrom 复制与改写 UUID（TASK-TM004-LINEAGE，AC-002，E2E-002）</x:v>
       </x:c>
       <x:c r="D108" s="9" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-LINEAGE</x:v>
       </x:c>
       <x:c r="E108" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F108" s="9" t="str">
-        <x:v>数据集 migration_snapshots；migration_snapshots planned；旧schema副本含固定账号/事件/队列、预计算记录数/Token/金额；候选迁移版本和明确故障点。全部作用私有临时库。</x:v>
+        <x:v>已计M100/10；分别用2.1.126真实生成的 fork 复制记录（保留 UUID）和改写 UUID 记录，依据实际 raw 的跨文件调用身份/父链判定，不能假定两者都含 forkedFrom；再追加真正新N50/5。</x:v>
       </x:c>
       <x:c r="G108" s="9" t="str">
-        <x:v>成功迁移只改变设计允许的schema/数据；账号、记录数、Token、费用/队列归属不丢。失败恢复到可启动一致状态，重复启动不重复迁移数据。不能以文件存在作为恢复成功。</x:v>
+        <x:v>M仅计一次且total110
+均仍110并在诊断/关系中可追溯原M
+total165/2次
+仍两次可信调用且total165</x:v>
       </x:c>
       <x:c r="H108" s="9" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读可信调用键2个、继承引用指向M；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I108" s="9" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J108" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K108" s="9" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L108" s="9" t="str">
-        <x:v>docs/testing/cases/11-TM-011-data-migration.md:11</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:147</x:v>
       </x:c>
       <x:c r="M108" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
     </x:row>
-    <x:row r="109" ht="57" customHeight="1">
+    <x:row r="109" ht="72" customHeight="1">
       <x:c r="A109" s="4" t="str">
-        <x:v>TM-011</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B109" s="4" t="str">
-        <x:v>E2E-TM011-002</x:v>
+        <x:v>TC-TM004-LINEAGE-04</x:v>
       </x:c>
       <x:c r="C109" s="4" t="str">
-        <x:v>未来SQLite到MySQL迁移</x:v>
+        <x:v>fork-context-ref 父链（TASK-TM004-LINEAGE，AC-002，E2E-002）</x:v>
       </x:c>
       <x:c r="D109" s="4" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-LINEAGE</x:v>
       </x:c>
       <x:c r="E109" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F109" s="4" t="str">
-        <x:v>数据集 migration_snapshots；仅后续独立版本适用；用户已确定v0.1.0继续SQLite。需要隔离源SQLite、目标MySQL、固定多成员/多项目用量快照、字符/时间/Decimal边界和独立expected。</x:v>
+        <x:v>2.1.126真实子代理 fork 记录中带 agentId,parentSessionId,parentLastUuid,contextLength；父会话存在M100/10，子代理仅新增S200/20。</x:v>
       </x:c>
       <x:c r="G109" s="4" t="str">
-        <x:v>源/目标记录数、Token、Decimal金额及权限结果一致，ID和幂等语义保持；不重复历史且旧源未被破坏。MySQL版本、字符集和迁移范围须在对应版本指定。</x:v>
+        <x:v>可信110
+可信330/2次而非440
+可信M/S两次且total330
+引用解析到M的既有调用键</x:v>
       </x:c>
       <x:c r="H109" s="4" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读M/S各一条及引用，total330；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I109" s="4" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J109" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K109" s="4" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L109" s="4" t="str">
-        <x:v>docs/testing/cases/11-TM-011-data-migration.md:28</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:151</x:v>
       </x:c>
       <x:c r="M109" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
     </x:row>
-    <x:row r="110" ht="57" customHeight="1">
+    <x:row r="110" ht="72" customHeight="1">
       <x:c r="A110" s="9" t="str">
-        <x:v>TM-011</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B110" s="9" t="str">
-        <x:v>E2E-TM011-003</x:v>
+        <x:v>TC-TM004-LINEAGE-05</x:v>
       </x:c>
       <x:c r="C110" s="9" t="str">
-        <x:v>备份恢复与旧客户端补传</x:v>
+        <x:v>缺失或矛盾父链（TASK-TM004-LINEAGE，AC-002/003，E2E-002/003）</x:v>
       </x:c>
       <x:c r="D110" s="9" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-LINEAGE</x:v>
       </x:c>
       <x:c r="E110" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F110" s="9" t="str">
-        <x:v>数据集 migration_snapshots；隔离服务已确认事件A/B与旧客户端未确认C；备份包含schema/数据/版本/摘要，另保存不在备份里的独立oracle。恢复目标必须为空且带测试标记。</x:v>
+        <x:v>在上一例的合成同构目录中分别移除引用父文件、指向不存在的 parentLastUuid、或提供无 forkedFrom 但UUID改写的复制历史；这些是测试故障注入，不能标为厂商实际输出。</x:v>
       </x:c>
       <x:c r="G110" s="9" t="str">
-        <x:v>备份能实际恢复而非只压缩成功；A/B不丢，重复补传不增加；C最终只出现一次，账号/权限符合恢复基线。队列与服务确认一致，旧客户端协议兼容。</x:v>
+        <x:v>M仅计一次且total110
+App显示未确定来源诊断，可信总量仍110、不能把不明副本计为新调用或有效零
+若真实新增S200/20可独立识别则总量330
+可信总量保持且诊断随恢复更新</x:v>
       </x:c>
       <x:c r="H110" s="9" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读未确定记录与可信M/S计数，不能借SQL灌成功；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I110" s="9" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J110" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K110" s="9" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L110" s="9" t="str">
-        <x:v>docs/testing/cases/11-TM-011-data-migration.md:45</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:155</x:v>
       </x:c>
       <x:c r="M110" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
     </x:row>
-    <x:row r="111" ht="57" customHeight="1">
+    <x:row r="111" ht="102" customHeight="1">
       <x:c r="A111" s="4" t="str">
-        <x:v>TM-011</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B111" s="4" t="str">
-        <x:v>E2E-TM011-004</x:v>
+        <x:v>TC-TM004-SOURCE-04</x:v>
       </x:c>
       <x:c r="C111" s="4" t="str">
-        <x:v>保留时间边界与未同步保护</x:v>
+        <x:v>预览截断后的可续扫覆盖（TASK-TM004-SOURCE，AC-001/004，E2E-001/004）</x:v>
       </x:c>
       <x:c r="D111" s="4" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-SOURCE</x:v>
       </x:c>
       <x:c r="E111" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F111" s="4" t="str">
-        <x:v>数据集 migration_snapshots；固定参考时间和Asia/Shanghai；本地90天/服务端365天。分别生成保留首日00:00、前一秒、前一天的已确认事件，以及同样超龄但未同步事件；具备可控时钟与独立边界oracle。</x:v>
+        <x:v>本例独占授权根，固定程序按 TM-002 已提交枚举顺序生成至少1025个普通 .jsonl 文件及足够目录项；前段有主M100/10，预览截断范围外且至少第五个256项采集页的深层 subagents/ 文件有子S50/5，其余文件没有可计量调用。另备可控制的页间撤权/恢复点。</x:v>
       </x:c>
       <x:c r="G111" s="4" t="str">
-        <x:v>保留首日00:00仍在，早一秒的已同步记录被清理；本地/服务按各自天数独立判定。未同步记录即使超龄仍保护，成功补传仅计一次；历史缺失不能显示真实0。</x:v>
+        <x:v>1000文件预览显示被截断，不声称全量
+UI 可显示已见M110，但 TM-003 coverage.scan_incomplete=1
+使用 openCandidateReadOnly(candidateToken) 读原始行；在另一次固定变体于页间撤权，下一页或打开须拒绝，cancelScan 后 scan_incomplete=1，重授后以新授权世代续扫
+可信 M+S 两调用、input150/output15/total165，scan_incomplete=0 才可显示本次覆盖完成；重启重扫总量不变</x:v>
       </x:c>
       <x:c r="H111" s="4" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读各来源事件键、聚合 (2,150,15)、游标及 coverage.scan_incomplete；中途必须为1；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I111" s="4" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J111" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K111" s="4" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L111" s="4" t="str">
-        <x:v>docs/testing/cases/11-TM-011-data-migration.md:62</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:159</x:v>
       </x:c>
       <x:c r="M111" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
     </x:row>
-    <x:row r="112" ht="57" customHeight="1">
+    <x:row r="112" ht="102" customHeight="1">
       <x:c r="A112" s="9" t="str">
-        <x:v>TM-012</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B112" s="9" t="str">
-        <x:v>E2E-TM012-001</x:v>
+        <x:v>TC-TM004-INCREMENTAL-03</x:v>
       </x:c>
       <x:c r="C112" s="9" t="str">
-        <x:v>菜单栏摘要、暂停恢复与刷新</x:v>
+        <x:v>跨工具同 ID 与 Claude 复制历史（TASK-TM004-INCREMENTAL，AC-001/002，E2E-001/002）</x:v>
       </x:c>
       <x:c r="D112" s="9" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-INCREMENTAL</x:v>
       </x:c>
       <x:c r="E112" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F112" s="9" t="str">
-        <x:v>数据集 diagnostic_states；diagnostic_states planned；已采集A=100/10；暂停期间追加B=200/20并重放A。依赖实际采集、统计和同步功能，使用专用日志目录。</x:v>
+        <x:v>同一合成主体、各自经 UI 授权的 Codex 与 Claude 隔离根。固定本地响应使 Codex 原生 payload.response_id 与 Claude 主 assistant.message.id 字面均为 shared-call-01，分别有 C=11/1 与 M=100/10；Claude 原生 --fork-session 复制M，再有独立 Agent 子调用S=200/20（新 message.id、与父同 sessionId 但带 agentId）。另以明确标记的衍生故障数据令同一 Claude message.id 出现矛盾101/10，该行不冒称 CLI 原件。</x:v>
       </x:c>
       <x:c r="G112" s="9" t="str">
-        <x:v>初始total110、暂停期间仍110，恢复后唯一A/B、total330；手动刷新与重启不重复。菜单栏与主窗口同一筛选口径；暂停状态不伪装成没有日志。</x:v>
+        <x:v>可信1次/total12
+可信2次/input111/output11/total122，跨工具同字面 ID 不冲突
+可信3次/input311/output31/total342
+可信仍3次/342，出现 identity_conflict 与覆盖不完整</x:v>
       </x:c>
       <x:c r="H112" s="9" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读同一 principal_key 下 source=codex 与 source=claude_code 各自事件数1/2、source_event_key 不同，Agent source_scope_key 与主来源可区分，复制M不多行，冲突不覆写原M；键与归属均不得存原生ID/完整路径；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I112" s="9" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J112" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K112" s="9" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L112" s="9" t="str">
-        <x:v>docs/testing/cases/12-TM-012-menu-diagnostics.md:11</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:163</x:v>
       </x:c>
       <x:c r="M112" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -10313,13 +10673,13 @@
     </x:row>
     <x:row r="113" ht="57" customHeight="1">
       <x:c r="A113" s="4" t="str">
-        <x:v>TM-012</x:v>
+        <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B113" s="4" t="str">
-        <x:v>E2E-TM012-002</x:v>
+        <x:v>E2E-TM005-001</x:v>
       </x:c>
       <x:c r="C113" s="4" t="str">
-        <x:v>诊断状态、恢复和登录启动</x:v>
+        <x:v>日期筛选、趋势和明细</x:v>
       </x:c>
       <x:c r="D113" s="4" t="str">
         <x:v>待拆解</x:v>
@@ -10328,10 +10688,10 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F113" s="4" t="str">
-        <x:v>数据集 diagnostic_states；独立子场景：已授权目录失效、真实服务不可达/恢复、测试App登录启动开关。故障作用测试目录/进程；使用已登录桌面与可自动检查的系统设置。</x:v>
+        <x:v>数据集 date_ranges；date_ranges 已由 scripts/test_data.py 提供标准化语义样例，固定2026-09-29T04:00:00Z、Asia/Shanghai、seed42；13行含1重复、12唯一。需另有已验证raw输入映射和真实App导入流程，当前未实现。</x:v>
       </x:c>
       <x:c r="G113" s="4" t="str">
-        <x:v>错误与真实目录/网络故障一致，不能用旧缓存一直显示健康；恢复后状态及时更新，未同步数据不丢。启动设置与OS登记/实际启动行为一致，测试结束恢复本次测试前状态。</x:v>
+        <x:v>独立expected中的total依次16500、110、17380、27830、31130；custom=2200。today共5条、input15000、output1500、cache1700、reasoning170，cache/reasoning不再相加；custom-start包含、custom-end排除。趋势点及明细按expected事件时间逐条核对。</x:v>
       </x:c>
       <x:c r="H113" s="4" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
@@ -10348,36 +10708,896 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L113" s="4" t="str">
-        <x:v>docs/testing/cases/12-TM-012-menu-diagnostics.md:28</x:v>
+        <x:v>docs/testing/cases/05-TM-005-usage-statistics.md:15</x:v>
       </x:c>
       <x:c r="M113" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
     </x:row>
+    <x:row r="114" ht="57" customHeight="1">
+      <x:c r="A114" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B114" s="9" t="str">
+        <x:v>E2E-TM005-002</x:v>
+      </x:c>
+      <x:c r="C114" s="9" t="str">
+        <x:v>时区、月边界与缺失值</x:v>
+      </x:c>
+      <x:c r="D114" s="9" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E114" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F114" s="9" t="str">
+        <x:v>数据集 date_ranges；复用date_ranges中的2026-09-28T15:59:59Z与16:00:00Z、2026-08-30T15:59:59Z与16:00:00Z边界。另需补充覆盖缺口、已覆盖零调用日、unknown字段三类状态；当前生成器未覆盖后面三类。</x:v>
+      </x:c>
+      <x:c r="G114" s="9" t="str">
+        <x:v>Shanghai下15:59:59Z仍属前日、16:00:00Z属次日；UTC下二者同属UTC日期。无覆盖显示缺失，真实零可显示0，unknown字段显示未知；不得互相代替。各范围expected须独立按当地日期边界列出，不调用产品查询生成。</x:v>
+      </x:c>
+      <x:c r="H114" s="9" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I114" s="9" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J114" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K114" s="9" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L114" s="9" t="str">
+        <x:v>docs/testing/cases/05-TM-005-usage-statistics.md:32</x:v>
+      </x:c>
+      <x:c r="M114" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" ht="57" customHeight="1">
+      <x:c r="A115" s="4" t="str">
+        <x:v>TM-006</x:v>
+      </x:c>
+      <x:c r="B115" s="4" t="str">
+        <x:v>E2E-TM006-001</x:v>
+      </x:c>
+      <x:c r="C115" s="4" t="str">
+        <x:v>Token子项与基础费用</x:v>
+      </x:c>
+      <x:c r="D115" s="4" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E115" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F115" s="4" t="str">
+        <x:v>数据集 pricing；pricing由scripts/test_data.py生成合成非计费价格。gpt-5每百万input/cache/output为USD2/0.2/8；today-gpt input1000含cache200、output100含reasoning20。价格不是厂商现价。</x:v>
+      </x:c>
+      <x:c r="G115" s="4" t="str">
+        <x:v>单调用total=1100；费用=(800×2+200×0.2+100×8)/1000000=USD0.002440，reasoning20不另加价。today已知费用USD0.015190且有1条无价格，alice今日USD0.010090。使用Decimal/十进制独立oracle，不以界面舍入反推底层精度。</x:v>
+      </x:c>
+      <x:c r="H115" s="4" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I115" s="4" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J115" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K115" s="4" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L115" s="4" t="str">
+        <x:v>docs/testing/cases/06-TM-006-cost-estimates.md:15</x:v>
+      </x:c>
+      <x:c r="M115" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" ht="57" customHeight="1">
+      <x:c r="A116" s="9" t="str">
+        <x:v>TM-006</x:v>
+      </x:c>
+      <x:c r="B116" s="9" t="str">
+        <x:v>E2E-TM006-002</x:v>
+      </x:c>
+      <x:c r="C116" s="9" t="str">
+        <x:v>历史价格、多币种和未知费用</x:v>
+      </x:c>
+      <x:c r="D116" s="9" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E116" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F116" s="9" t="str">
+        <x:v>数据集 pricing_extended；pricing_extended planned：同模型在生效时点T前后各一调用，两个独立价格版本；另有USD/CNY各一模型、无价模型和订阅估算模型。必须提供价格/订阅分摊规则及手算expected后才能实现。</x:v>
+      </x:c>
+      <x:c r="G116" s="9" t="str">
+        <x:v>T前后依各自生效版本计算，历史结果不会悄悄换价；USD与CNY分组，未约定汇率不得相加；无价格显示未知而非0；订阅必须明确估算口径。具体金额oracle依待定义订阅/价格合同生成，当前不得手填PASS。</x:v>
+      </x:c>
+      <x:c r="H116" s="9" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I116" s="9" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J116" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K116" s="9" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L116" s="9" t="str">
+        <x:v>docs/testing/cases/06-TM-006-cost-estimates.md:32</x:v>
+      </x:c>
+      <x:c r="M116" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" ht="57" customHeight="1">
+      <x:c r="A117" s="4" t="str">
+        <x:v>TM-007</x:v>
+      </x:c>
+      <x:c r="B117" s="4" t="str">
+        <x:v>E2E-TM007-001</x:v>
+      </x:c>
+      <x:c r="C117" s="4" t="str">
+        <x:v>离线、重启和补传幂等</x:v>
+      </x:c>
+      <x:c r="D117" s="4" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E117" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F117" s="4" t="str">
+        <x:v>数据集 sync_faults；sync_faults planned；alice两个隔离设备A/B，设备A调用100/10、B调用200/20；真实FastAPI/SQLite服务，可由外部fixture断网/恢复。账号继续用隔离测试fixture。</x:v>
+      </x:c>
+      <x:c r="G117" s="4" t="str">
+        <x:v>离线重启不丢队列；恢复后2唯一调用、input300/output30/total330；重复批次不再加量。客户端只在真实确认后标已同步，个人合计与对应团队子集一致。</x:v>
+      </x:c>
+      <x:c r="H117" s="4" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I117" s="4" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J117" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K117" s="4" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L117" s="4" t="str">
+        <x:v>docs/testing/cases/07-TM-007-team-sync.md:11</x:v>
+      </x:c>
+      <x:c r="M117" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" ht="57" customHeight="1">
+      <x:c r="A118" s="9" t="str">
+        <x:v>TM-007</x:v>
+      </x:c>
+      <x:c r="B118" s="9" t="str">
+        <x:v>E2E-TM007-002</x:v>
+      </x:c>
+      <x:c r="C118" s="9" t="str">
+        <x:v>部分确认、中断和账号切换</x:v>
+      </x:c>
+      <x:c r="D118" s="9" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E118" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F118" s="9" t="str">
+        <x:v>数据集 sync_faults；准备alice的三条唯一事件A/B/C，总量各110/220/330；控制服务仅确认A后断开，B可能已提交但响应丢失，C未提交。另有bob账号。故障注入必须在真实服务外部或明确测试环境中完成，不能绕过认证。</x:v>
+      </x:c>
+      <x:c r="G118" s="9" t="str">
+        <x:v>最终alice的A/B/C各一次、total660；响应丢失不造成B重复；bob不能承接或篡改alice既有事件归属。切换时旧队列按已批准归属策略隔离，不能默认为新登录账号。</x:v>
+      </x:c>
+      <x:c r="H118" s="9" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I118" s="9" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J118" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K118" s="9" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L118" s="9" t="str">
+        <x:v>docs/testing/cases/07-TM-007-team-sync.md:28</x:v>
+      </x:c>
+      <x:c r="M118" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" ht="57" customHeight="1">
+      <x:c r="A119" s="4" t="str">
+        <x:v>TM-007</x:v>
+      </x:c>
+      <x:c r="B119" s="4" t="str">
+        <x:v>E2E-TM007-003</x:v>
+      </x:c>
+      <x:c r="C119" s="4" t="str">
+        <x:v>上传白名单与项目映射</x:v>
+      </x:c>
+      <x:c r="D119" s="4" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E119" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F119" s="4" t="str">
+        <x:v>数据集 sync_faults；合成日志包含唯一正文/代码/API-key/完整路径哨兵，以及合法用量/必要去重元数据；只用假值。准备已归属项目A和未归属事件B，待sync_faults生成。</x:v>
+      </x:c>
+      <x:c r="G119" s="4" t="str">
+        <x:v>网络载荷/持久服务数据均不得含正文、代码、key或完整本机路径；只有批准用量/去重字段。B可明确分配，分配不增加事件量、也不跨团队归属。</x:v>
+      </x:c>
+      <x:c r="H119" s="4" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I119" s="4" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J119" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K119" s="4" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L119" s="4" t="str">
+        <x:v>docs/testing/cases/07-TM-007-team-sync.md:45</x:v>
+      </x:c>
+      <x:c r="M119" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" ht="57" customHeight="1">
+      <x:c r="A120" s="9" t="str">
+        <x:v>TM-007</x:v>
+      </x:c>
+      <x:c r="B120" s="9" t="str">
+        <x:v>E2E-TM007-004</x:v>
+      </x:c>
+      <x:c r="C120" s="9" t="str">
+        <x:v>统计越权与停用后上传</x:v>
+      </x:c>
+      <x:c r="D120" s="9" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E120" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F120" s="9" t="str">
+        <x:v>数据集 sync_faults；alice项目A调用100/10，bob项目B调用200/20；成员alice与管理员独立会话；alice另有一条未确认调用C=50/5。sync_faults与可重建统计SQL尚未实现。</x:v>
+      </x:c>
+      <x:c r="G120" s="9" t="str">
+        <x:v>成员无权请求被服务端拒绝，UI不显示bob的220；停用后旧会话及上传拒绝，C不能标为已确认；合法历史不能被失败上传删除。此处补足TM-001仅身份/管理接口权限的范围。</x:v>
+      </x:c>
+      <x:c r="H120" s="9" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I120" s="9" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J120" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K120" s="9" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L120" s="9" t="str">
+        <x:v>docs/testing/cases/07-TM-007-team-sync.md:62</x:v>
+      </x:c>
+      <x:c r="M120" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" ht="57" customHeight="1">
+      <x:c r="A121" s="4" t="str">
+        <x:v>TM-008</x:v>
+      </x:c>
+      <x:c r="B121" s="4" t="str">
+        <x:v>E2E-TM008-001</x:v>
+      </x:c>
+      <x:c r="C121" s="4" t="str">
+        <x:v>筛选一致的CSV导出</x:v>
+      </x:c>
+      <x:c r="D121" s="4" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E121" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F121" s="4" t="str">
+        <x:v>数据集 export_rows；export_rows planned；两成员、两个模型、时间范围内外各有事件，独立清单明确每条ID/字段/权限。先具备TM-005/007统计和授权。</x:v>
+      </x:c>
+      <x:c r="G121" s="4" t="str">
+        <x:v>每次CSV仅包含当次筛选且授权可见记录，行数/ID/汇总等于独立清单与界面；不混入旧筛选、其他成员或范围外记录。已知/未知费用语义一致。</x:v>
+      </x:c>
+      <x:c r="H121" s="4" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I121" s="4" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J121" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K121" s="4" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L121" s="4" t="str">
+        <x:v>docs/testing/cases/08-TM-008-csv-export.md:11</x:v>
+      </x:c>
+      <x:c r="M121" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" ht="57" customHeight="1">
+      <x:c r="A122" s="9" t="str">
+        <x:v>TM-008</x:v>
+      </x:c>
+      <x:c r="B122" s="9" t="str">
+        <x:v>E2E-TM008-002</x:v>
+      </x:c>
+      <x:c r="C122" s="9" t="str">
+        <x:v>CSV转义、未知值及权限</x:v>
+      </x:c>
+      <x:c r="D122" s="9" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E122" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F122" s="9" t="str">
+        <x:v>数据集 export_rows；export_rows需含字段 a,b、say "hi"、带实际换行的项目名、未知费用与非ASCII模型名；两成员各有可区分哨兵事件。只在隔离数据中使用。</x:v>
+      </x:c>
+      <x:c r="G122" s="9" t="str">
+        <x:v>逗号、双引号、嵌入换行均round-trip一致，Unicode不损坏；未知值不写成0；他人哨兵不出现在文件。若导出失败，不能留下看似完整的半文件。</x:v>
+      </x:c>
+      <x:c r="H122" s="9" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I122" s="9" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J122" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K122" s="9" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L122" s="9" t="str">
+        <x:v>docs/testing/cases/08-TM-008-csv-export.md:28</x:v>
+      </x:c>
+      <x:c r="M122" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" ht="57" customHeight="1">
+      <x:c r="A123" s="4" t="str">
+        <x:v>TM-009</x:v>
+      </x:c>
+      <x:c r="B123" s="4" t="str">
+        <x:v>E2E-TM009-001</x:v>
+      </x:c>
+      <x:c r="C123" s="4" t="str">
+        <x:v>80%/100%提醒幂等</x:v>
+      </x:c>
+      <x:c r="D123" s="4" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E123" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F123" s="4" t="str">
+        <x:v>数据集 budget_periods；budget_periods planned；独立个人、项目和团队预算分别100个合成USD单位，同周期使用量依次79→80→99→100；原始调用与价格要能精确形成这些费用。</x:v>
+      </x:c>
+      <x:c r="G123" s="4" t="str">
+        <x:v>每预算每周期80与100各最多一次，未达到不发；重扫/重启/重复上传不重发；预算仅提醒，不拦截模型调用。三层预算分别按其授权范围计算。</x:v>
+      </x:c>
+      <x:c r="H123" s="4" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I123" s="4" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J123" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K123" s="4" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L123" s="4" t="str">
+        <x:v>docs/testing/cases/09-TM-009-budget-alerts.md:11</x:v>
+      </x:c>
+      <x:c r="M123" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" ht="57" customHeight="1">
+      <x:c r="A124" s="9" t="str">
+        <x:v>TM-009</x:v>
+      </x:c>
+      <x:c r="B124" s="9" t="str">
+        <x:v>E2E-TM009-002</x:v>
+      </x:c>
+      <x:c r="C124" s="9" t="str">
+        <x:v>新周期、币种与通知恢复</x:v>
+      </x:c>
+      <x:c r="D124" s="9" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E124" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F124" s="9" t="str">
+        <x:v>数据集 budget_periods；两个币种独立预算；旧周期已发80/100阈值，参考时钟可由产品支持的测试配置推进；测试通知权限可以拒绝及恢复，不能修改用户其他App授权。</x:v>
+      </x:c>
+      <x:c r="G124" s="9" t="str">
+        <x:v>系统拒绝不丢失应用内状态、不造成重试通知风暴；新周期独立重置，允许新一轮各阈值一次；币种分开计算。通知补发策略需在对应需求明确，不能由测试临时猜测。</x:v>
+      </x:c>
+      <x:c r="H124" s="9" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I124" s="9" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J124" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K124" s="9" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L124" s="9" t="str">
+        <x:v>docs/testing/cases/09-TM-009-budget-alerts.md:28</x:v>
+      </x:c>
+      <x:c r="M124" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" ht="72" customHeight="1">
+      <x:c r="A125" s="4" t="str">
+        <x:v>TM-010</x:v>
+      </x:c>
+      <x:c r="B125" s="4" t="str">
+        <x:v>E2E-TM010-001</x:v>
+      </x:c>
+      <x:c r="C125" s="4" t="str">
+        <x:v>稳定版发现更新与数据保留</x:v>
+      </x:c>
+      <x:c r="D125" s="4" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E125" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F125" s="4" t="str">
+        <x:v>数据集 update_packages；依赖TM-001/007；update_packages planned。需真实已分发稳定版、候选最终包及相同分发profile的签名/清单；旧版有账号设置、手动地址、统计/队列独立快照。首版无历史稳定版时使用SOP017规定的候选→受控高版，不伪称稳定升级。</x:v>
+      </x:c>
+      <x:c r="G125" s="4" t="str">
+        <x:v>更新频率和说明可用；只有声明候选被安装，Sparkle自主重启；更新前后账号/设置/统计与快照一致，队列不丢失不重复。完整更新体验仍为未来功能，TM-001-004通过只证明最小更新路径。</x:v>
+      </x:c>
+      <x:c r="H125" s="4" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I125" s="4" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J125" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K125" s="4" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L125" s="4" t="str">
+        <x:v>docs/testing/cases/10-TM-010-software-updates.md:11</x:v>
+      </x:c>
+      <x:c r="M125" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" ht="57" customHeight="1">
+      <x:c r="A126" s="9" t="str">
+        <x:v>TM-010</x:v>
+      </x:c>
+      <x:c r="B126" s="9" t="str">
+        <x:v>E2E-TM010-002</x:v>
+      </x:c>
+      <x:c r="C126" s="9" t="str">
+        <x:v>签名、网络、空间和迁移失败恢复</x:v>
+      </x:c>
+      <x:c r="D126" s="9" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E126" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F126" s="9" t="str">
+        <x:v>数据集 update_packages；对同一干净旧版分别建立四个隔离子场景：坏签名包、下载中断、受限测试卷空间不足、受控迁移失败；每个保存旧版包/DB/配置摘要。故障不能作用用户系统盘/生产库。</x:v>
+      </x:c>
+      <x:c r="G126" s="9" t="str">
+        <x:v>每个失败均不能形成半更新；原账号/统计和包的可用状态可验证。网络恢复后的成功需要完整包校验；迁移失败恢复来源与摘要明确。四个子场景全部为本case必需，不能挑一项通过。</x:v>
+      </x:c>
+      <x:c r="H126" s="9" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I126" s="9" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J126" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K126" s="9" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L126" s="9" t="str">
+        <x:v>docs/testing/cases/10-TM-010-software-updates.md:28</x:v>
+      </x:c>
+      <x:c r="M126" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" ht="57" customHeight="1">
+      <x:c r="A127" s="4" t="str">
+        <x:v>TM-010</x:v>
+      </x:c>
+      <x:c r="B127" s="4" t="str">
+        <x:v>E2E-TM010-003</x:v>
+      </x:c>
+      <x:c r="C127" s="4" t="str">
+        <x:v>升级默认地址和手动覆盖</x:v>
+      </x:c>
+      <x:c r="D127" s="4" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E127" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F127" s="4" t="str">
+        <x:v>数据集 server_default_migration；server_default_migration planned；两套旧安装A从未设置地址、B已手动设置；候选内置一个届时确定且测试可访问的生产HTTPS默认地址。两源有独立账号/数据/会话，公钥不可随URL编辑。</x:v>
+      </x:c>
+      <x:c r="G127" s="4" t="str">
+        <x:v>只有无手动覆盖安装跟随新版默认；显式覆盖即使恰好等于旧默认也应按已经确定的配置来源规则处理。改变origin需重新服务认证，旧token不能跨源复用。</x:v>
+      </x:c>
+      <x:c r="H127" s="4" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I127" s="4" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J127" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K127" s="4" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L127" s="4" t="str">
+        <x:v>docs/testing/cases/10-TM-010-software-updates.md:45</x:v>
+      </x:c>
+      <x:c r="M127" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" ht="57" customHeight="1">
+      <x:c r="A128" s="9" t="str">
+        <x:v>TM-011</x:v>
+      </x:c>
+      <x:c r="B128" s="9" t="str">
+        <x:v>E2E-TM011-001</x:v>
+      </x:c>
+      <x:c r="C128" s="9" t="str">
+        <x:v>SQLite迁移与中断恢复</x:v>
+      </x:c>
+      <x:c r="D128" s="9" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E128" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F128" s="9" t="str">
+        <x:v>数据集 migration_snapshots；migration_snapshots planned；旧schema副本含固定账号/事件/队列、预计算记录数/Token/金额；候选迁移版本和明确故障点。全部作用私有临时库。</x:v>
+      </x:c>
+      <x:c r="G128" s="9" t="str">
+        <x:v>成功迁移只改变设计允许的schema/数据；账号、记录数、Token、费用/队列归属不丢。失败恢复到可启动一致状态，重复启动不重复迁移数据。不能以文件存在作为恢复成功。</x:v>
+      </x:c>
+      <x:c r="H128" s="9" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I128" s="9" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J128" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K128" s="9" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L128" s="9" t="str">
+        <x:v>docs/testing/cases/11-TM-011-data-migration.md:11</x:v>
+      </x:c>
+      <x:c r="M128" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" ht="57" customHeight="1">
+      <x:c r="A129" s="4" t="str">
+        <x:v>TM-011</x:v>
+      </x:c>
+      <x:c r="B129" s="4" t="str">
+        <x:v>E2E-TM011-002</x:v>
+      </x:c>
+      <x:c r="C129" s="4" t="str">
+        <x:v>未来SQLite到MySQL迁移</x:v>
+      </x:c>
+      <x:c r="D129" s="4" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E129" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F129" s="4" t="str">
+        <x:v>数据集 migration_snapshots；仅后续独立版本适用；用户已确定v0.1.0继续SQLite。需要隔离源SQLite、目标MySQL、固定多成员/多项目用量快照、字符/时间/Decimal边界和独立expected。</x:v>
+      </x:c>
+      <x:c r="G129" s="4" t="str">
+        <x:v>源/目标记录数、Token、Decimal金额及权限结果一致，ID和幂等语义保持；不重复历史且旧源未被破坏。MySQL版本、字符集和迁移范围须在对应版本指定。</x:v>
+      </x:c>
+      <x:c r="H129" s="4" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I129" s="4" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J129" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K129" s="4" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L129" s="4" t="str">
+        <x:v>docs/testing/cases/11-TM-011-data-migration.md:28</x:v>
+      </x:c>
+      <x:c r="M129" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" ht="57" customHeight="1">
+      <x:c r="A130" s="9" t="str">
+        <x:v>TM-011</x:v>
+      </x:c>
+      <x:c r="B130" s="9" t="str">
+        <x:v>E2E-TM011-003</x:v>
+      </x:c>
+      <x:c r="C130" s="9" t="str">
+        <x:v>备份恢复与旧客户端补传</x:v>
+      </x:c>
+      <x:c r="D130" s="9" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E130" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F130" s="9" t="str">
+        <x:v>数据集 migration_snapshots；隔离服务已确认事件A/B与旧客户端未确认C；备份包含schema/数据/版本/摘要，另保存不在备份里的独立oracle。恢复目标必须为空且带测试标记。</x:v>
+      </x:c>
+      <x:c r="G130" s="9" t="str">
+        <x:v>备份能实际恢复而非只压缩成功；A/B不丢，重复补传不增加；C最终只出现一次，账号/权限符合恢复基线。队列与服务确认一致，旧客户端协议兼容。</x:v>
+      </x:c>
+      <x:c r="H130" s="9" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I130" s="9" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J130" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K130" s="9" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L130" s="9" t="str">
+        <x:v>docs/testing/cases/11-TM-011-data-migration.md:45</x:v>
+      </x:c>
+      <x:c r="M130" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" ht="57" customHeight="1">
+      <x:c r="A131" s="4" t="str">
+        <x:v>TM-011</x:v>
+      </x:c>
+      <x:c r="B131" s="4" t="str">
+        <x:v>E2E-TM011-004</x:v>
+      </x:c>
+      <x:c r="C131" s="4" t="str">
+        <x:v>保留时间边界与未同步保护</x:v>
+      </x:c>
+      <x:c r="D131" s="4" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E131" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F131" s="4" t="str">
+        <x:v>数据集 migration_snapshots；固定参考时间和Asia/Shanghai；本地90天/服务端365天。分别生成保留首日00:00、前一秒、前一天的已确认事件，以及同样超龄但未同步事件；具备可控时钟与独立边界oracle。</x:v>
+      </x:c>
+      <x:c r="G131" s="4" t="str">
+        <x:v>保留首日00:00仍在，早一秒的已同步记录被清理；本地/服务按各自天数独立判定。未同步记录即使超龄仍保护，成功补传仅计一次；历史缺失不能显示真实0。</x:v>
+      </x:c>
+      <x:c r="H131" s="4" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I131" s="4" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J131" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K131" s="4" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L131" s="4" t="str">
+        <x:v>docs/testing/cases/11-TM-011-data-migration.md:62</x:v>
+      </x:c>
+      <x:c r="M131" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" ht="57" customHeight="1">
+      <x:c r="A132" s="9" t="str">
+        <x:v>TM-012</x:v>
+      </x:c>
+      <x:c r="B132" s="9" t="str">
+        <x:v>E2E-TM012-001</x:v>
+      </x:c>
+      <x:c r="C132" s="9" t="str">
+        <x:v>菜单栏摘要、暂停恢复与刷新</x:v>
+      </x:c>
+      <x:c r="D132" s="9" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E132" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F132" s="9" t="str">
+        <x:v>数据集 diagnostic_states；diagnostic_states planned；已采集A=100/10；暂停期间追加B=200/20并重放A。依赖实际采集、统计和同步功能，使用专用日志目录。</x:v>
+      </x:c>
+      <x:c r="G132" s="9" t="str">
+        <x:v>初始total110、暂停期间仍110，恢复后唯一A/B、total330；手动刷新与重启不重复。菜单栏与主窗口同一筛选口径；暂停状态不伪装成没有日志。</x:v>
+      </x:c>
+      <x:c r="H132" s="9" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I132" s="9" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J132" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K132" s="9" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L132" s="9" t="str">
+        <x:v>docs/testing/cases/12-TM-012-menu-diagnostics.md:11</x:v>
+      </x:c>
+      <x:c r="M132" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" ht="57" customHeight="1">
+      <x:c r="A133" s="4" t="str">
+        <x:v>TM-012</x:v>
+      </x:c>
+      <x:c r="B133" s="4" t="str">
+        <x:v>E2E-TM012-002</x:v>
+      </x:c>
+      <x:c r="C133" s="4" t="str">
+        <x:v>诊断状态、恢复和登录启动</x:v>
+      </x:c>
+      <x:c r="D133" s="4" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E133" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F133" s="4" t="str">
+        <x:v>数据集 diagnostic_states；独立子场景：已授权目录失效、真实服务不可达/恢复、测试App登录启动开关。故障作用测试目录/进程；使用已登录桌面与可自动检查的系统设置。</x:v>
+      </x:c>
+      <x:c r="G133" s="4" t="str">
+        <x:v>错误与真实目录/网络故障一致，不能用旧缓存一直显示健康；恢复后状态及时更新，未同步数据不丢。启动设置与OS登记/实际启动行为一致，测试结束恢复本次测试前状态。</x:v>
+      </x:c>
+      <x:c r="H133" s="4" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I133" s="4" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J133" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K133" s="4" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L133" s="4" t="str">
+        <x:v>docs/testing/cases/12-TM-012-menu-diagnostics.md:28</x:v>
+      </x:c>
+      <x:c r="M133" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G5:G113">
+  <x:conditionalFormatting sqref="G5:G133">
     <x:cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="I5:I113">
+  <x:conditionalFormatting sqref="I5:I133">
     <x:cfRule type="containsText" dxfId="15" priority="4" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="17" priority="6" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="J5:J113">
+  <x:conditionalFormatting sqref="J5:J133">
     <x:cfRule type="containsText" dxfId="18" priority="7" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="19" priority="8" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="20" priority="9" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="M5:M113">
+  <x:conditionalFormatting sqref="M5:M133">
     <x:cfRule type="containsText" dxfId="21" priority="10" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="22" priority="11" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="23" priority="12" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46d0525f2c284244"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R981c725aa33a45e0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10912,7 +12132,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R468164e844d040cc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb916c68e4f6f40e5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11064,25 +12284,66 @@
         <x:v>releases/v0.1.0-20260929T074814Z/06-iteration-record.md</x:v>
       </x:c>
     </x:row>
+    <x:row r="7" ht="42" customHeight="1">
+      <x:c r="A7" s="4" t="str">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+      <x:c r="B7" s="4" t="str">
+        <x:v>0.4.0</x:v>
+      </x:c>
+      <x:c r="C7" s="16" t="n">
+        <x:v>46296.16982638889</x:v>
+      </x:c>
+      <x:c r="D7" s="4" t="str">
+        <x:v>产品功能</x:v>
+      </x:c>
+      <x:c r="E7" s="4" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="F7" s="4" t="str">
+        <x:v>未发布</x:v>
+      </x:c>
+      <x:c r="G7" s="4" t="str">
+        <x:v>internal</x:v>
+      </x:c>
+      <x:c r="H7" s="4" t="str">
+        <x:v>dmg/&lt;release_id&gt;/：仅门禁PASS后放正式DMG</x:v>
+      </x:c>
+      <x:c r="I7" s="15" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J7" s="4" t="str">
+        <x:v>设计草案：20条细TC已登记；程序、SQL、产品E2E与发布门禁尚未完成</x:v>
+      </x:c>
+      <x:c r="K7" s="4" t="str">
+        <x:v>Claude Code 2.1.126 隔离CLI原生投影与独立oracle；非产品通过证据</x:v>
+      </x:c>
+      <x:c r="L7" s="4" t="str">
+        <x:v>releases/v0.4.0-20261001T040433Z/00-manifest.json</x:v>
+      </x:c>
+      <x:c r="M7" s="4" t="str">
+        <x:v>releases/v0.4.0-20261001T040433Z/06-iteration-record.md</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="F5:F6">
+  <x:conditionalFormatting sqref="F5:F7">
     <x:cfRule type="containsText" dxfId="30" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="31" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="32" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="J5:J6">
+  <x:conditionalFormatting sqref="J5:J7">
     <x:cfRule type="containsText" dxfId="33" priority="4" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="34" priority="5" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="35" priority="6" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="M5:M6">
+  <x:conditionalFormatting sqref="M5:M7">
     <x:cfRule type="containsText" dxfId="36" priority="7" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="37" priority="8" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="38" priority="9" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R194caa4b70474ce0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd587e9eab8ff422e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11987,7 +13248,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93cbdb1e43044101"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4ef76d0af5da48d6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TokenMeter项目总表.xlsx
+++ b/TokenMeter项目总表.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R273bfaa83b6049a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Rbc6ef8bb2639460e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R040b0abcea5b431b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R6440d552f63d4ee6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="Raf16677dbd7a4485"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="Rc1d784c2090d4389"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="Rf593c1d785cd445b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R6b7a1e7c3e3044e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="R4341405b107e4236"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R1d84b9095f3648d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R2b6cc7a070834b86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R4cccc0ad4a264356"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="R4797cc0c671342ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R7b218f9584464048"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R2d6080f09ca2464c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R17a6e08107a448e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R80d0806121a04480"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R1d83853b71cc4f58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="Ra89beec5c33e407c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Rc6b09aeb4829442b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="Rbfee68823e604397"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="Rfb7bba6be6364c78"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -816,8 +816,8 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="TMTable9" displayName="TMTable9" ref="A4:H36" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:H36"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="TMTable9" displayName="TMTable9" ref="A4:H43" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:H43"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="复盘编号"/>
     <x:tableColumn id="2" name="名称"/>
@@ -1245,7 +1245,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f032e25c44a498a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R763d9cabeb79442f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1295,7 +1295,7 @@
         <x:v>依据</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="132" customHeight="1">
+    <x:row r="5" ht="162" customHeight="1">
       <x:c r="A5" s="4" t="str">
         <x:v>SOP-000</x:v>
       </x:c>
@@ -1306,16 +1306,16 @@
         <x:v>用户改变流程要求、现有 SOP 缺步骤/判据、规范冲突，或需要迁移 SOP 编号和位置。</x:v>
       </x:c>
       <x:c r="D5" s="4" t="str">
-        <x:v>读取当前[工作索引](README.md)、[文档规范](../docs/standards/documentation.md)及受影响流程；明确规则来源和当前 release_id。其他会话先向「SOP」管理会话（thread ID 01a0f5a5-63f7-76b0-aa53-ac6befec91ef）报告修订需求，由该会话执行本 SOP。迁移前按旧有效 SOP 执行，迁移后采用本目录。</x:v>
+        <x:v>读取当前[工作索引](README.md)、[文档规范](../docs/standards/documentation.md)及受影响流程；明确规则来源和当前 release_id。其他会话先向「SOP」管理会话（thread ID 01a0f5a5-63f7-76b0-aa53-ac6befec91ef）报告修订需求，由该会话执行本 SOP。非SOP文档的唯一编写者为「文档」会话（thread ID 01a0f14b-0888-7e93-bb85-a76b419f2ba7）；迁移前按旧有效 SOP 执行，迁移后采用本目录。</x:v>
       </x:c>
       <x:c r="E5" s="4" t="str">
-        <x:v>完整 SOP 索引、独立工作 SOP、同步的规范/模板/目录，以及变更与检查记录。</x:v>
+        <x:v>完整 SOP 索引、独立工作 SOP、向文档会话交接的非SOP变更清单及其提交/检查记录；整合后关联的规范、模板和目录。</x:v>
       </x:c>
       <x:c r="F5" s="4" t="str">
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G5" s="4" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H5" s="4" t="str">
         <x:v>sop/SOP-000-maintenance.md</x:v>
@@ -1471,7 +1471,7 @@
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G11" s="4" t="n">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H11" s="4" t="str">
         <x:v>sop/SOP-006-test-plan.md</x:v>
@@ -1601,7 +1601,7 @@
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G16" s="9" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H16" s="9" t="str">
         <x:v>sop/SOP-011-test-implementation.md</x:v>
@@ -1679,7 +1679,7 @@
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G19" s="4" t="n">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H19" s="4" t="str">
         <x:v>sop/SOP-014-e2e.md</x:v>
@@ -1757,7 +1757,7 @@
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G22" s="9" t="n">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H22" s="9" t="str">
         <x:v>sop/SOP-017-package-validation.md</x:v>
@@ -1783,7 +1783,7 @@
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G23" s="4" t="n">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H23" s="4" t="str">
         <x:v>sop/SOP-018-release-gate.md</x:v>
@@ -1919,7 +1919,7 @@
         <x:v>sop/SOP-023-iteration.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="57" customHeight="1">
+    <x:row r="29" ht="117" customHeight="1">
       <x:c r="A29" s="4" t="str">
         <x:v>SOP-024</x:v>
       </x:c>
@@ -1930,7 +1930,7 @@
         <x:v>新增文档、实现/接口/命令/测试变化、状态更新、链接迁移或记录关键决定。</x:v>
       </x:c>
       <x:c r="D29" s="4" t="str">
-        <x:v>先读 [文档规范](../docs/standards/documentation.md)、适用 SOP 和当前版本；变更规范/模板结构先经 SOP-000。</x:v>
+        <x:v>先读 [文档规范](../docs/standards/documentation.md)、适用 SOP 和当前版本；变更SOP定义先由SOP会话按SOP-000处理，非SOP规范/模板由文档会话编写。其他会话提供目标文件、具体内容/依据、版本、代码或原始证据及紧急依赖；已完成但未集成的旧非SOP改动须保留并交接，不丢弃。</x:v>
       </x:c>
       <x:c r="E29" s="4" t="str">
         <x:v>合规文档、目录/链接/追踪关系、准确状态与实际检查记录。</x:v>
@@ -1939,7 +1939,7 @@
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G29" s="4" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H29" s="4" t="str">
         <x:v>sop/SOP-024-document-change.md</x:v>
@@ -1953,7 +1953,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf83fc05e890d4999"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R661b6341359a462d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2102,7 +2102,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95753fc0b9574ea2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Refacf0baad7d450b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2497,7 +2497,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc10d539c148d4de5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R163e906384534adc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3416,7 +3416,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6b51f9b912f4f1f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R970291c4378548da"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4126,7 +4126,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R511cbb049ee44e39"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3660c153b5dd4a3d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5446,7 +5446,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37a03de48b1548e1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb15f249c701f45ed"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10377,7 +10377,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46d0525f2c284244"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf492ea58d26548f4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10912,7 +10912,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R468164e844d040cc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91e619ff28294f4c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11046,13 +11046,13 @@
         <x:v>internal</x:v>
       </x:c>
       <x:c r="H6" s="9" t="str">
-        <x:v>dmg/&lt;release_id&gt;/：当前仅开发包；正式DMG门禁PASS后保存</x:v>
+        <x:v>dmg/&lt;release_id&gt;/：当前有 d2db551 同摘要 CANDIDATE-NOT-RELEASED 便捷副本；正式原名 DMG 待最终整合门禁与归档</x:v>
       </x:c>
       <x:c r="I6" s="18" t="b">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J6" s="9" t="str">
-        <x:v>Electron本机精细全量：78父用例62 PASS/9 FAIL/7 BLOCKED；38变体31 PASS/7 FAIL。开发候选未发布，未签发通行证；定向验证另存批次。</x:v>
+        <x:v>独立候选 d2db551 本机门禁 PASS，78父TC/38变体规范化全PASS，机器通行证已生成；最终 master 整合树尚未重验，未正式发布。旧3467dc1门禁FAIL原件保留。</x:v>
       </x:c>
       <x:c r="K6" s="9" t="str">
         <x:v>旧SwiftUI PR #2 已合并、历史双平台六例PASS；不继承给Electron</x:v>
@@ -11082,7 +11082,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R194caa4b70474ce0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5282f33019444cc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11979,15 +11979,197 @@
         <x:v>docs/retrospectives/2026-09-29--2026-09-30-tokenmeter.md:478</x:v>
       </x:c>
     </x:row>
+    <x:row r="37" ht="117" customHeight="1">
+      <x:c r="A37" s="4" t="str">
+        <x:v>RET-032</x:v>
+      </x:c>
+      <x:c r="B37" s="4" t="str">
+        <x:v>本机测试决定与远端保护规则冲突</x:v>
+      </x:c>
+      <x:c r="C37" s="4" t="str">
+        <x:v>用户确认完整产品测试在本机执行，Git 只管理源码；远端 master 仍要求三项旧 Actions 检查且强制 PR。手动工作流不能稳定提供同一 PR head 的所需检查，已通过的本机门禁也不能冒充远端状态。</x:v>
+      </x:c>
+      <x:c r="D37" s="4" t="str">
+        <x:v>开发总控与 SOP 会话读取保护 API、工作流触发和旧检查的 App 来源，区分本机候选验收与远端合并条件。用户再次确认只在明确多环境要求时启动 Actions 完整测试。</x:v>
+      </x:c>
+      <x:c r="E37" s="4" t="str">
+        <x:v>由 SOP 会话修订 SOP-019，并保存保护规则迁移前后快照；移除旧三项 required checks，保留 PR、管理员执行、对话解决及禁强推/删除。每次整合仍需复读当前保护和远端树，最终本地 master 候选重新运行完整适用门禁。</x:v>
+      </x:c>
+      <x:c r="F37" s="4" t="str">
+        <x:v>规范分支 PR #4/#5 已先行进入远端 master 的历史见[TM-001 版本 06](../../releases/v0.1.0-20260929T074814Z/06-iteration-record.md)；当前最终产品整合和远端发布未据此自动完成。原始快照在本机 .local/git-sync/20261001T055756Z-local-only-protection/。</x:v>
+      </x:c>
+      <x:c r="G37" s="4" t="str">
+        <x:v>验收结果、远端分支保护和分发资格各需独立证明。更换执行地点时，同时核对保护规则与工作流触发，不能只改 SOP 文字。</x:v>
+      </x:c>
+      <x:c r="H37" s="4" t="str">
+        <x:v>docs/retrospectives/2026-10-01-development-and-governance.md:5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="102" customHeight="1">
+      <x:c r="A38" s="9" t="str">
+        <x:v>RET-033</x:v>
+      </x:c>
+      <x:c r="B38" s="9" t="str">
+        <x:v>主精细报告的辅助占位与最终结果口径不同</x:v>
+      </x:c>
+      <x:c r="C38" s="9" t="str">
+        <x:v>TM-001 主精细 run 的 116 行中，11 条辅助项只是待独立程序执行的占位，原始状态 BLOCKED。把后续辅助 PASS 回写到主报告，或只看主报告判最终失败，都会丢失真实来源。</x:v>
+      </x:c>
+      <x:c r="D38" s="9" t="str">
+        <x:v>核对精细、辅助、独立审计和六组补充 E2E 的原始报告及逐例 Excel，确定每份报告的候选、包、运行顺序和覆盖范围；旧主报告不改写。</x:v>
+      </x:c>
+      <x:c r="E38" s="9" t="str">
+        <x:v>固定门禁从各来源原件独立复算最终 78 父 TC、38 变体结果，保留主 run 的 11 条原始 BLOCKED，并在 final-product-result.json 写来源与规范化状态；缺原件、错候选或错摘要均阻断。</x:v>
+      </x:c>
+      <x:c r="F38" s="9" t="str">
+        <x:v>开发包联合复核曾得到逐项 PASS，但其主 run 仍为 BLOCKED 且包未发布；独立候选 d2db551 的新门禁原件最终为 PASS，见 .local/gates/tm001-final-gate-d2db551-20261001T0904Z/。最终总控整合仍待重验。</x:v>
+      </x:c>
+      <x:c r="G38" s="9" t="str">
+        <x:v>聚合结论要保留每个来源的原始状态和身份，不能把汇总表、截图或手工标记当作源测试结果。</x:v>
+      </x:c>
+      <x:c r="H38" s="9" t="str">
+        <x:v>docs/retrospectives/2026-10-01-development-and-governance.md:17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="117" customHeight="1">
+      <x:c r="A39" s="4" t="str">
+        <x:v>RET-034</x:v>
+      </x:c>
+      <x:c r="B39" s="4" t="str">
+        <x:v>首次干净候选缺管理员本人身份旁证</x:v>
+      </x:c>
+      <x:c r="C39" s="4" t="str">
+        <x:v>候选 3467dc1 的 95 个真实精细 Playwright 入口、辅助 11/11、审计 12/12、补充六组 6/6 分项通过，但最终门禁 FAIL。补充管理员场景只有被撤销成员 /v1/me 的预期 401，没有管理员本人有效 200 的原始旁证。</x:v>
+      </x:c>
+      <x:c r="D39" s="4" t="str">
+        <x:v>保留 .local/gates/tm001-final-gate-3467dc1-20261001T0730Z/gate.json 的 FAIL，按 SOP-015 对照既定身份验收与 service audit；判断为固定测试证据缺口，未把分项 PASS 推定为产品认证完成。</x:v>
+      </x:c>
+      <x:c r="E39" s="4" t="str">
+        <x:v>在固定 E2E-003 增加真实 App 重启后的管理员会话恢复、有效 /v1/me 200 及账号/角色断言，并给缺失 200 的门禁路径加负测；冻结新候选后完整重跑。</x:v>
+      </x:c>
+      <x:c r="F39" s="4" t="str">
+        <x:v>d2db551 的 E2E-003 原始 service audit 已出现有效 200，独立本机门禁 PASS；旧 FAIL 原件未覆盖。依据[本版结果](../../releases/v0.1.0-20260929T074814Z/07-test-results.md)及新旧 .local/gates/ 原件。正式整合发布仍待总控处理。</x:v>
+      </x:c>
+      <x:c r="G39" s="4" t="str">
+        <x:v>用例通过和门禁要求的证据链是两层检查。对关键身份行为，固定程序须采到正向与撤销后的反向原件。</x:v>
+      </x:c>
+      <x:c r="H39" s="4" t="str">
+        <x:v>docs/retrospectives/2026-10-01-development-and-governance.md:29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="72" customHeight="1">
+      <x:c r="A40" s="9" t="str">
+        <x:v>RET-035</x:v>
+      </x:c>
+      <x:c r="B40" s="9" t="str">
+        <x:v>系统打开文件列表含空名称项</x:v>
+      </x:c>
+      <x:c r="C40" s="9" t="str">
+        <x:v>lsof -Fn 可能产生无名称行。升级场景的采集器把它当成空路径，后续审计会报打开文件列表不完整；若简单丢弃整个列表，又会隐藏具名文件证据。</x:v>
+      </x:c>
+      <x:c r="D40" s="9" t="str">
+        <x:v>在首次门禁 FAIL 后只读核对 E2E-004 原始列表，确认有一条空名称；对照归档校验要求，区分命令输出占位与实际具名文件路径。</x:v>
+      </x:c>
+      <x:c r="E40" s="9" t="str">
+        <x:v>固定解析器只忽略无名称条目、保留全部具名路径；003 与精细更新采集器共用规则，并增加解析单元测试。</x:v>
+      </x:c>
+      <x:c r="F40" s="9" t="str">
+        <x:v>新候选 d2db551 的 E2E-004 原件记录 125 个具名路径、零空项，完整门禁 PASS；旧候选原件仍可复查。见版本 06 和两次门禁目录。</x:v>
+      </x:c>
+      <x:c r="G40" s="9" t="str">
+        <x:v>OS 工具的文本输出需按真实语法建模。修采集器时保留可审计的有效项，并用固定反例验证。</x:v>
+      </x:c>
+      <x:c r="H40" s="9" t="str">
+        <x:v>docs/retrospectives/2026-10-01-development-and-governance.md:41</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="87" customHeight="1">
+      <x:c r="A41" s="4" t="str">
+        <x:v>RET-036</x:v>
+      </x:c>
+      <x:c r="B41" s="4" t="str">
+        <x:v>后续版本不能沿用 TM-001 固定门禁总数</x:v>
+      </x:c>
+      <x:c r="C41" s="4" t="str">
+        <x:v>SOP-011/014/018 曾把 TM-001 的 116 主行、78 父 TC、38 变体、11 辅助、12 审计和六组场景写成通用候选数量。TM-002/003 新增用例后，该固定数会遗漏新需求，或让门禁错误地以旧集合判通过。</x:v>
+      </x:c>
+      <x:c r="D41" s="4" t="str">
+        <x:v>TM-002/003 报告各自草稿集合和门禁派生 TC 的自依赖；SOP 会话逐项核对来源 release、固定候选清单和既有 TM-001 历史原件，避免改写旧报告。</x:v>
+      </x:c>
+      <x:c r="E41" s="4" t="str">
+        <x:v>SOP 独立提交 3303c0b 定义目标版本加此前已交付功能的机器清单并集，逐来源核对父/变体/辅助/场景/审计；最终 gate 自身派生 TC 在其他原件及真实升级验真后计算。本会话接管其发布和用例规范等非 SOP 附件。</x:v>
+      </x:c>
+      <x:c r="F41" s="4" t="str">
+        <x:v>规范分支结构、基线、质量与治理 198/198 检查通过；产品跨版本执行器尚未在最终整合树实测，TM-002/003 产品验收仍 BLOCKED。原始规范检查在 .local/git-sync/20261001-cross-release-sop/。</x:v>
+      </x:c>
+      <x:c r="G41" s="4" t="str">
+        <x:v>历史版本的精确数量只约束其来源原件；后续发行范围必须从已确认版本的机器清单生成，并保存来源摘要。</x:v>
+      </x:c>
+      <x:c r="H41" s="4" t="str">
+        <x:v>docs/retrospectives/2026-10-01-development-and-governance.md:53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="72" customHeight="1">
+      <x:c r="A42" s="9" t="str">
+        <x:v>RET-037</x:v>
+      </x:c>
+      <x:c r="B42" s="9" t="str">
+        <x:v>隔离 profile 不能证明 Keychain 凭据隔离</x:v>
+      </x:c>
+      <x:c r="C42" s="9" t="str">
+        <x:v>TM-002 的 safeStorage 在 macOS 涉及 Keychain。只使用独立 --user-data-dir 不能证明系统 item 与正式 App 分离，测试若误读、覆盖或清理已有凭据会污染用户环境。</x:v>
+      </x:c>
+      <x:c r="D42" s="9" t="str">
+        <x:v>总控和 SOP 会话区分浏览器 profile 与系统凭据命名空间，核对 Electron 源码仅能提供设计线索，不能替代最终 DMG 原生 item 身份证明。</x:v>
+      </x:c>
+      <x:c r="E42" s="9" t="str">
+        <x:v>在首次相关调用前，用同一最终 DMG 于隔离 macOS 测试账号或经证明独立的命名空间探查精确 service/account；要求预先不存在，记录 owner 与创建元数据，仅清理本次创建的精确 item。来源身份/密钥不可用时停读。相关规范和设计作为 TM-002/003/004 前置。</x:v>
+      </x:c>
+      <x:c r="F42" s="9" t="str">
+        <x:v>SOP 与非 SOP 设计约束已在分支形成；TM-002/003/004 尚无最终包原生探针和对应产品 E2E 原件，保持 BLOCKED。依据版本 06 及隔离规范交接。</x:v>
+      </x:c>
+      <x:c r="G42" s="9" t="str">
+        <x:v>测试隔离需覆盖操作系统共享资源，不只覆盖进程目录和 SQLite；不能从源码命名推断运行时凭据身份。</x:v>
+      </x:c>
+      <x:c r="H42" s="9" t="str">
+        <x:v>docs/retrospectives/2026-10-01-development-and-governance.md:65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="72" customHeight="1">
+      <x:c r="A43" s="4" t="str">
+        <x:v>RET-038</x:v>
+      </x:c>
+      <x:c r="B43" s="4" t="str">
+        <x:v>并发开发造成文档草稿与候选状态交叉</x:v>
+      </x:c>
+      <x:c r="C43" s="4" t="str">
+        <x:v>TM-002 至 TM-005 并行形成需求、用例、机器目录和总表草稿；个别分支含已提交或未提交文档。不同分支中的用例数量、状态和来源行号在持续变化，直接合并可能覆盖 TM-001 原始批次，或把 baseline_pending 当作产品 PASS。</x:v>
+      </x:c>
+      <x:c r="D43" s="4" t="str">
+        <x:v>用户先指定“SOP”会话统一维护 SOP，随后指定“文档”会话统一编写其余文档与 Excel。文档会话核对可见会话、分支和交接输入，保留已形成的 diff 与原始检查，按来源需求逐项审阅。</x:v>
+      </x:c>
+      <x:c r="E43" s="4" t="str">
+        <x:v>建立[会话体系](../project-sessions.md)和单一文档入口；需求会话继续代码/固定测试并交付候选、TC、原件和阻断，文档会话在独立分支维护非 SOP 文档、目录和 Excel，总控整合后重验。未核实的分支不写成已创建会话。</x:v>
+      </x:c>
+      <x:c r="F43" s="4" t="str">
+        <x:v>归口规则已通知现有核心会话，交接队列已登记；TM-002 至 TM-005 的草稿仍在核对中，严格基线或产品门禁未通过的部分不升格。此次文档提交与检查结果见版本 06。</x:v>
+      </x:c>
+      <x:c r="G43" s="4" t="str">
+        <x:v>角色归口减少并发覆盖，但每条事实仍需要候选身份、原始证据和阶段状态。Excel 更新也须遵守候选输入先提交、批次在归档后索引的时序。</x:v>
+      </x:c>
+      <x:c r="H43" s="4" t="str">
+        <x:v>docs/retrospectives/2026-10-01-development-and-governance.md:77</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="F5:F36">
+  <x:conditionalFormatting sqref="F5:F43">
     <x:cfRule type="containsText" dxfId="39" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="40" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="41" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93cbdb1e43044101"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc07fa5317a0347a6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TokenMeter项目总表.xlsx
+++ b/TokenMeter项目总表.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R4cccc0ad4a264356"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="R4797cc0c671342ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R7b218f9584464048"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R2d6080f09ca2464c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R17a6e08107a448e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R80d0806121a04480"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R1d83853b71cc4f58"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="Ra89beec5c33e407c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Rc6b09aeb4829442b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="Rbfee68823e604397"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="Rfb7bba6be6364c78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R5bcf6af7c2824aeb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="R416d93558caa47ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R3eed2723341c4efe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R11eacf0c8a6847ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="Rd6c7c534ab26465b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R3c8710592e9c49c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R1b270a2dee4346ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R0a4b3a5aa47546dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Rf888855f751947d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R32cead9b86ec4dda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R35c4bd608c694a0e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -680,9 +680,9 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TMTable2" displayName="TMTable2" ref="A4:H16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:H16"/>
-  <x:tableColumns count="8">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TMTable2" displayName="TMTable2" ref="A4:I16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:I16"/>
+  <x:tableColumns count="9">
     <x:tableColumn id="1" name="需求编号"/>
     <x:tableColumn id="2" name="功能编号"/>
     <x:tableColumn id="3" name="名称"/>
@@ -691,15 +691,16 @@
     <x:tableColumn id="6" name="验收数量"/>
     <x:tableColumn id="7" name="状态"/>
     <x:tableColumn id="8" name="依据"/>
+    <x:tableColumn id="9" name="design_source"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TMTable3" displayName="TMTable3" ref="A4:G41" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:G41"/>
-  <x:tableColumns count="7">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TMTable3" displayName="TMTable3" ref="A4:H41" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:H41"/>
+  <x:tableColumns count="8">
     <x:tableColumn id="1" name="验收编号"/>
     <x:tableColumn id="2" name="需求编号"/>
     <x:tableColumn id="3" name="功能编号"/>
@@ -707,15 +708,16 @@
     <x:tableColumn id="5" name="数据要求"/>
     <x:tableColumn id="6" name="状态"/>
     <x:tableColumn id="7" name="依据"/>
+    <x:tableColumn id="8" name="design_source"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="TMTable4" displayName="TMTable4" ref="A4:I25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:I25"/>
-  <x:tableColumns count="9">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="TMTable4" displayName="TMTable4" ref="A4:J25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:J25"/>
+  <x:tableColumns count="10">
     <x:tableColumn id="1" name="功能编号"/>
     <x:tableColumn id="2" name="层级"/>
     <x:tableColumn id="3" name="父功能"/>
@@ -725,15 +727,16 @@
     <x:tableColumn id="7" name="版本"/>
     <x:tableColumn id="8" name="状态"/>
     <x:tableColumn id="9" name="依据"/>
+    <x:tableColumn id="10" name="design_source"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="TMTable5" displayName="TMTable5" ref="A4:K39" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:K39"/>
-  <x:tableColumns count="11">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="TMTable5" displayName="TMTable5" ref="A4:L48" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:L48"/>
+  <x:tableColumns count="12">
     <x:tableColumn id="1" name="任务编号"/>
     <x:tableColumn id="2" name="层级"/>
     <x:tableColumn id="3" name="功能点编号"/>
@@ -745,15 +748,16 @@
     <x:tableColumn id="9" name="历史场景映射"/>
     <x:tableColumn id="10" name="状态"/>
     <x:tableColumn id="11" name="依据"/>
+    <x:tableColumn id="12" name="decision_source"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TMTable6" displayName="TMTable6" ref="A4:M113" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:M113"/>
-  <x:tableColumns count="13">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TMTable6" displayName="TMTable6" ref="A4:N176" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:N176"/>
+  <x:tableColumns count="14">
     <x:tableColumn id="1" name="功能编号"/>
     <x:tableColumn id="2" name="用例编号"/>
     <x:tableColumn id="3" name="测试点"/>
@@ -767,6 +771,7 @@
     <x:tableColumn id="11" name="范围"/>
     <x:tableColumn id="12" name="详细设计依据"/>
     <x:tableColumn id="13" name="最近结果批次"/>
+    <x:tableColumn id="14" name="归属版本"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -794,9 +799,9 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="TMTable8" displayName="TMTable8" ref="A4:M6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:M6"/>
-  <x:tableColumns count="13">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="TMTable8" displayName="TMTable8" ref="A4:N7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:N7"/>
+  <x:tableColumns count="14">
     <x:tableColumn id="1" name="发布编号"/>
     <x:tableColumn id="2" name="版本"/>
     <x:tableColumn id="3" name="立项时间"/>
@@ -810,6 +815,7 @@
     <x:tableColumn id="11" name="历史证据"/>
     <x:tableColumn id="12" name="依据"/>
     <x:tableColumn id="13" name="状态依据"/>
+    <x:tableColumn id="14" name="design_source"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -1091,11 +1097,11 @@
         <x:v>已登记用例</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:f>COUNTA('05测试用例'!B5:B113)</x:f>
-        <x:v>109</x:v>
+        <x:f>COUNTA('05测试用例'!B5:B176)</x:f>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="C8" s="9" t="str">
-        <x:v>包含细化用例及未来概要场景</x:v>
+        <x:v>父用例与具有稳定 ID 的变体各占一行；含未来概要场景</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="32" customHeight="1">
@@ -1115,10 +1121,10 @@
         <x:v>细化产品用例</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>67</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C10" s="9" t="str">
-        <x:v>逐条结果按运行批次记录；变体在独立结果Excel列出</x:v>
+        <x:v>逐条结果按运行批次记录；稳定变体独立列出</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="32" customHeight="1">
@@ -1126,10 +1132,10 @@
         <x:v>界面与治理检查</x:v>
       </x:c>
       <x:c r="B11" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C11" s="4" t="str">
-        <x:v>辅助检查不能替代产品E2E</x:v>
+        <x:v>辅助检查不能替代产品E2E；稳定变体独立列出</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="32" customHeight="1">
@@ -1137,7 +1143,7 @@
         <x:v>未来概要场景</x:v>
       </x:c>
       <x:c r="B12" s="11" t="n">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C12" s="9" t="str">
         <x:v>进入对应功能需求阶段后继续细化</x:v>
@@ -1148,7 +1154,7 @@
         <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="B13" s="10" t="n">
-        <x:v>0</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C13" s="4" t="str">
         <x:v>在05测试用例筛选此状态</x:v>
@@ -1245,7 +1251,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R763d9cabeb79442f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c8e4c6871c9448d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1549,7 +1555,7 @@
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G14" s="9" t="n">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H14" s="9" t="str">
         <x:v>sop/SOP-009-environment.md</x:v>
@@ -1575,7 +1581,7 @@
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G15" s="4" t="n">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H15" s="4" t="str">
         <x:v>sop/SOP-010-test-data.md</x:v>
@@ -1737,7 +1743,7 @@
         <x:v>sop/SOP-016-database-migration.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="42" customHeight="1">
+    <x:row r="22" ht="102" customHeight="1">
       <x:c r="A22" s="9" t="str">
         <x:v>SOP-017</x:v>
       </x:c>
@@ -1748,7 +1754,7 @@
         <x:v>内部本地版本准备发行或包/更新器变化。</x:v>
       </x:c>
       <x:c r="D22" s="9" t="str">
-        <x:v>007预案、013/014、真实本机GUI和稳定本地签名能力。</x:v>
+        <x:v>007预案、013/014、SOP-019在本地master固定的本版本里程碑SHA/tree、真实本机GUI和稳定本地签名能力。首版验证自身受控高版更新；后续版本真实升级另须有上一版本按SOP-018/020形成、可独立复核的本机正式稳定DMG。</x:v>
       </x:c>
       <x:c r="E22" s="9" t="str">
         <x:v>原始安装包及系统签名、安装/更新/E2E证据；根dmg/&lt;release_id&gt;/的未发布标记便捷副本及摘要核对。</x:v>
@@ -1757,13 +1763,13 @@
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G22" s="9" t="n">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H22" s="9" t="str">
         <x:v>sop/SOP-017-package-validation.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="42" customHeight="1">
+    <x:row r="23" ht="87" customHeight="1">
       <x:c r="A23" s="4" t="str">
         <x:v>SOP-018</x:v>
       </x:c>
@@ -1774,7 +1780,7 @@
         <x:v>固定最终候选准备内部本地发行。</x:v>
       </x:c>
       <x:c r="D23" s="4" t="str">
-        <x:v>013/014/017真实执行、干净候选和原始产物齐全。</x:v>
+        <x:v>013/014/017真实执行、SOP-019固定的本地master版本里程碑与其干净候选、原始产物齐全。后续版本的上一实际稳定包及真实升级证据须按SOP-017齐全；远端统一源码推送不是本机门禁的前置。</x:v>
       </x:c>
       <x:c r="E23" s="4" t="str">
         <x:v>PASS通行证或明确FAIL/BLOCKED，原始证据保持本地。</x:v>
@@ -1783,13 +1789,13 @@
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G23" s="4" t="n">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H23" s="4" t="str">
         <x:v>sop/SOP-018-release-gate.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="267" customHeight="1">
+    <x:row r="24" ht="312" customHeight="1">
       <x:c r="A24" s="9" t="str">
         <x:v>SOP-019</x:v>
       </x:c>
@@ -1797,25 +1803,25 @@
         <x:v>SOP-019 Git 版本追踪</x:v>
       </x:c>
       <x:c r="C24" s="9" t="str">
-        <x:v>需求分支达到本地集成条件，或已通过正式本机发布门禁、需要建立源码 Tag。PR 只在远端策略要求时作为受控替代路径，不再是默认集成步骤。</x:v>
+        <x:v>需求分支达到本地里程碑集成条件；某版本通过正式本机门禁、需要成为下一版本稳定升级源；或全部目标版本完成、需要统一远端源码登记与正式Tag。PR只在远端策略要求时作为受控替代路径。</x:v>
       </x:c>
       <x:c r="D24" s="9" t="str">
-        <x:v>用户已授权总控自主整合、推送和适用门禁后的发行。分支具有对应 release_id、文档基线和适用检查结果；本地与远端 master 的实际状态可核对。产品迭代/修复在远端集成前须有固定测试程序及**本地 master 最终整合提交**对应的完整产品 E2E；正式 Tag 还须 SOP-017/018 的最终包和 PASS 通行证。仅规范及其必要文档附件的独立分支可在SOP-008结构、基线和治理检查通过后先行并入源码master，但不得记为产品E2E、发布PASS、通行证或Tag；后续产品候选须以这个新基线整合并完成完整门禁。2026-10-01用户再次确认 Git 仅用于源码版本管理、本机承担产品测试，旧 Actions 必需检查已按此决定移除；其余远端保护仍须真实满足。未提交的用户改动不得覆盖或带入整合。</x:v>
+        <x:v>用户已授权总控自主整合、最终统一远端推送和适用门禁后的本机发行。分支具有对应release_id、文档基线和适用检查结果；本地与远端master的实际状态可核对。每个正式产品版本须在其**本地master固定里程碑提交**上由固定程序完成本轮与此前已交付功能的完整产品E2E、SOP-017/018最终包门禁，再按SOP-020形成可供后续升级的本机稳定包；远端源码登记不作为本机稳定包的前置，但在全部目标版本完成前保持待办。正式Tag仍须本地通行证及最终远端读回。仅规范及其必要文档附件的独立分支可在SOP-008结构、基线和治理检查通过后先行并入源码master，但不得记为产品E2E、发布PASS、通行证或Tag；后续产品候选须以新基线完成完整门禁。2026-10-01用户再次确认Git仅用于源码版本管理、本机承担产品测试，旧Actions必需检查已移除；其余远端保护仍须满足。未提交的用户改动不得覆盖或带入整合。</x:v>
       </x:c>
       <x:c r="E24" s="9" t="str">
-        <x:v>本地 master 整合与门禁记录、远端 master 读回、必要时的源码 Tag 和可查询的本地发行索引。</x:v>
+        <x:v>逐版本地master里程碑及门禁/稳定包记录、最终远端master读回与逐版源码Tag映射；本地发行索引分别显示已完成和远端待办。</x:v>
       </x:c>
       <x:c r="F24" s="9" t="str">
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G24" s="9" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H24" s="9" t="str">
         <x:v>sop/SOP-019-git-release.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="42" customHeight="1">
+    <x:row r="25" ht="72" customHeight="1">
       <x:c r="A25" s="4" t="str">
         <x:v>SOP-020</x:v>
       </x:c>
@@ -1823,19 +1829,19 @@
         <x:v>SOP-020 本地发行归档</x:v>
       </x:c>
       <x:c r="C25" s="4" t="str">
-        <x:v>本机018 PASS并完成源码追踪。</x:v>
+        <x:v>本机018 PASS，且SOP-019已固定该版本在本地master的不可变SHA/tree与来源追踪；远端master读回和正式Tag可保持待办，不冒充已完成。</x:v>
       </x:c>
       <x:c r="D25" s="4" t="str">
-        <x:v>有效通行证、原包、独立新目标目录和恢复预案。</x:v>
+        <x:v>有效通行证、同一候选原包、本地版本里程碑、独立新目标目录和恢复预案。上一版本尚无正式稳定包时，下一版本依赖真实升级的门禁继续BLOCKED。</x:v>
       </x:c>
       <x:c r="E25" s="4" t="str">
-        <x:v>本地版本归档、原件校验和、根dmg/&lt;release_id&gt;/正式安装入口与追踪。</x:v>
+        <x:v>本地版本归档、原件校验和、根dmg/&lt;release_id&gt;/正式稳定安装入口、来源SHA/tree及远端待办/后续登记收据。</x:v>
       </x:c>
       <x:c r="F25" s="4" t="str">
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G25" s="4" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H25" s="4" t="str">
         <x:v>sop/SOP-020-deployment.md</x:v>
@@ -1953,7 +1959,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R661b6341359a462d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02f8fd2b66bf4042"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2102,7 +2108,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Refacf0baad7d450b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85c0fee1613347c3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2119,6 +2125,7 @@
     <x:col min="6" max="6" width="45" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="45" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="85" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="85" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2">
@@ -2150,6 +2157,9 @@
       </x:c>
       <x:c r="H4" s="8" t="str">
         <x:v>依据</x:v>
+      </x:c>
+      <x:c r="I4" s="8" t="str">
+        <x:v>design_source</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="102" customHeight="1">
@@ -2182,8 +2192,11 @@
       <x:c r="H5" s="4" t="str">
         <x:v>docs/product/README.md:18</x:v>
       </x:c>
-    </x:row>
-    <x:row r="6" ht="42" customHeight="1">
+      <x:c r="I5" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="57" customHeight="1">
       <x:c r="A6" s="9" t="str">
         <x:v>REQ-TM002</x:v>
       </x:c>
@@ -2194,7 +2207,7 @@
         <x:v>首次授权</x:v>
       </x:c>
       <x:c r="D6" s="9" t="str">
-        <x:v>选择目录、候选文件预览、记录采集/同步意愿、拒绝/撤销/重新授权</x:v>
+        <x:v>已登录成员通过 macOS 原生目录选择器选定来源，预览选中根内候选文件；分别确认采集与未来同步意愿，App 在当前用户私有记录中加密持久保存已确认目录 locator；撤销删除记录，失效或解密失败停读，经重新选择和确认后恢复。</x:v>
       </x:c>
       <x:c r="E6" s="9" t="str">
         <x:v>AC-TM002-001
@@ -2204,10 +2217,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="G6" s="9" t="str">
-        <x:v>规划中</x:v>
+        <x:v>baseline_pending</x:v>
       </x:c>
       <x:c r="H6" s="9" t="str">
         <x:v>docs/product/README.md:19</x:v>
+      </x:c>
+      <x:c r="I6" s="9" t="str">
+        <x:v>releases/v0.2.0-20261001T034118Z/01-requirements.md:5</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="72" customHeight="1">
@@ -2238,6 +2254,9 @@
       <x:c r="H7" s="4" t="str">
         <x:v>docs/product/README.md:20</x:v>
       </x:c>
+      <x:c r="I7" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="72" customHeight="1">
       <x:c r="A8" s="9" t="str">
@@ -2267,6 +2286,9 @@
       <x:c r="H8" s="9" t="str">
         <x:v>docs/product/README.md:21</x:v>
       </x:c>
+      <x:c r="I8" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="42" customHeight="1">
       <x:c r="A9" s="4" t="str">
@@ -2294,6 +2316,9 @@
       <x:c r="H9" s="4" t="str">
         <x:v>docs/product/README.md:22</x:v>
       </x:c>
+      <x:c r="I9" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="42" customHeight="1">
       <x:c r="A10" s="9" t="str">
@@ -2320,6 +2345,9 @@
       </x:c>
       <x:c r="H10" s="9" t="str">
         <x:v>docs/product/README.md:23</x:v>
+      </x:c>
+      <x:c r="I10" s="9" t="str">
+        <x:v>未提供</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="72" customHeight="1">
@@ -2350,6 +2378,9 @@
       <x:c r="H11" s="4" t="str">
         <x:v>docs/product/README.md:24</x:v>
       </x:c>
+      <x:c r="I11" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="42" customHeight="1">
       <x:c r="A12" s="9" t="str">
@@ -2377,6 +2408,9 @@
       <x:c r="H12" s="9" t="str">
         <x:v>docs/product/README.md:25</x:v>
       </x:c>
+      <x:c r="I12" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="42" customHeight="1">
       <x:c r="A13" s="4" t="str">
@@ -2403,6 +2437,9 @@
       </x:c>
       <x:c r="H13" s="4" t="str">
         <x:v>docs/product/README.md:26</x:v>
+      </x:c>
+      <x:c r="I13" s="4" t="str">
+        <x:v>未提供</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="57" customHeight="1">
@@ -2431,6 +2468,9 @@
       </x:c>
       <x:c r="H14" s="9" t="str">
         <x:v>docs/product/README.md:27</x:v>
+      </x:c>
+      <x:c r="I14" s="9" t="str">
+        <x:v>未提供</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="72" customHeight="1">
@@ -2461,6 +2501,9 @@
       <x:c r="H15" s="4" t="str">
         <x:v>docs/product/README.md:28</x:v>
       </x:c>
+      <x:c r="I15" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" ht="42" customHeight="1">
       <x:c r="A16" s="9" t="str">
@@ -2487,6 +2530,9 @@
       </x:c>
       <x:c r="H16" s="9" t="str">
         <x:v>docs/product/README.md:29</x:v>
+      </x:c>
+      <x:c r="I16" s="9" t="str">
+        <x:v>未提供</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2497,7 +2543,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R163e906384534adc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f0aa82aa5844cbf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2513,6 +2559,7 @@
     <x:col min="5" max="5" width="45" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="45" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="85" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="85" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2">
@@ -2542,6 +2589,9 @@
       <x:c r="G4" s="8" t="str">
         <x:v>依据</x:v>
       </x:c>
+      <x:c r="H4" s="8" t="str">
+        <x:v>design_source</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="57" customHeight="1">
       <x:c r="A5" s="4" t="str">
@@ -2567,6 +2617,9 @@
       <x:c r="G5" s="4" t="str">
         <x:v>tests/acceptance.json#AC-TM001-001</x:v>
       </x:c>
+      <x:c r="H5" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="57" customHeight="1">
       <x:c r="A6" s="9" t="str">
@@ -2592,6 +2645,9 @@
       <x:c r="G6" s="9" t="str">
         <x:v>tests/acceptance.json#AC-TM001-002</x:v>
       </x:c>
+      <x:c r="H6" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="57" customHeight="1">
       <x:c r="A7" s="4" t="str">
@@ -2617,6 +2673,9 @@
       <x:c r="G7" s="4" t="str">
         <x:v>tests/acceptance.json#AC-TM001-003</x:v>
       </x:c>
+      <x:c r="H7" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="87" customHeight="1">
       <x:c r="A8" s="9" t="str">
@@ -2642,6 +2701,9 @@
       <x:c r="G8" s="9" t="str">
         <x:v>tests/acceptance.json#AC-TM001-004</x:v>
       </x:c>
+      <x:c r="H8" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="57" customHeight="1">
       <x:c r="A9" s="4" t="str">
@@ -2667,6 +2729,9 @@
       <x:c r="G9" s="4" t="str">
         <x:v>tests/acceptance.json#AC-TM001-005</x:v>
       </x:c>
+      <x:c r="H9" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="72" customHeight="1">
       <x:c r="A10" s="9" t="str">
@@ -2690,8 +2755,11 @@
       <x:c r="G10" s="9" t="str">
         <x:v>tests/acceptance.json#AC-TM001-006</x:v>
       </x:c>
-    </x:row>
-    <x:row r="11" ht="42" customHeight="1">
+      <x:c r="H10" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="147" customHeight="1">
       <x:c r="A11" s="4" t="str">
         <x:v>AC-TM002-001</x:v>
       </x:c>
@@ -2702,19 +2770,30 @@
         <x:v>TM-002</x:v>
       </x:c>
       <x:c r="D11" s="4" t="str">
-        <x:v>真实系统授权完成，只读取选定目录；确认前不开始持续扫描；选择和同意状态可在重启后恢复</x:v>
+        <x:v>已验证账号通过 macOS 原生目录选择器选定来源；App 强制只读取所选目录；确认前不持续扫描，选择和两项意愿在同一身份重启后恢复</x:v>
       </x:c>
       <x:c r="E11" s="4" t="str">
-        <x:v>不适用</x:v>
+        <x:v>native_directory_picker
+selected_root_a_b
+candidate_metadata
+consent_state
+restart_identity
+access_audit
+encrypted_private_locator
+keychain_fault_injection
+paged_candidate_scan</x:v>
       </x:c>
       <x:c r="F11" s="4" t="str">
-        <x:v>规划中</x:v>
+        <x:v>baseline_pending</x:v>
       </x:c>
       <x:c r="G11" s="4" t="str">
         <x:v>tests/acceptance.json#AC-TM002-001</x:v>
       </x:c>
-    </x:row>
-    <x:row r="12" ht="32" customHeight="1">
+      <x:c r="H11" s="4" t="str">
+        <x:v>releases/v0.2.0-20261001T034118Z/01-requirements.md:21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="102" customHeight="1">
       <x:c r="A12" s="9" t="str">
         <x:v>AC-TM002-002</x:v>
       </x:c>
@@ -2725,16 +2804,24 @@
         <x:v>TM-002</x:v>
       </x:c>
       <x:c r="D12" s="9" t="str">
-        <x:v>App 不崩溃、不继续读取失效目录；重新授权后可读取目录并恢复授权状态</x:v>
+        <x:v>用户在 App 内撤销来源或所选目录失效后，App 不崩溃并停止读取；再次通过原生目录选择器选定并明确确认后恢复读取和来源状态</x:v>
       </x:c>
       <x:c r="E12" s="9" t="str">
-        <x:v>不适用</x:v>
+        <x:v>selected_root_a_b
+access_loss
+reselect
+access_audit
+owner_cleanup
+stale_selection_and_cursor</x:v>
       </x:c>
       <x:c r="F12" s="9" t="str">
-        <x:v>规划中</x:v>
+        <x:v>baseline_pending</x:v>
       </x:c>
       <x:c r="G12" s="9" t="str">
         <x:v>tests/acceptance.json#AC-TM002-002</x:v>
+      </x:c>
+      <x:c r="H12" s="9" t="str">
+        <x:v>releases/v0.2.0-20261001T034118Z/01-requirements.md:22</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="32" customHeight="1">
@@ -2759,6 +2846,9 @@
       <x:c r="G13" s="4" t="str">
         <x:v>tests/acceptance.json#AC-TM003-001</x:v>
       </x:c>
+      <x:c r="H13" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="42" customHeight="1">
       <x:c r="A14" s="9" t="str">
@@ -2782,6 +2872,9 @@
       <x:c r="G14" s="9" t="str">
         <x:v>tests/acceptance.json#AC-TM003-002</x:v>
       </x:c>
+      <x:c r="H14" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="32" customHeight="1">
       <x:c r="A15" s="4" t="str">
@@ -2805,6 +2898,9 @@
       <x:c r="G15" s="4" t="str">
         <x:v>tests/acceptance.json#AC-TM003-003</x:v>
       </x:c>
+      <x:c r="H15" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" ht="32" customHeight="1">
       <x:c r="A16" s="9" t="str">
@@ -2828,6 +2924,9 @@
       <x:c r="G16" s="9" t="str">
         <x:v>tests/acceptance.json#AC-TM003-004</x:v>
       </x:c>
+      <x:c r="H16" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="32" customHeight="1">
       <x:c r="A17" s="4" t="str">
@@ -2851,6 +2950,9 @@
       <x:c r="G17" s="4" t="str">
         <x:v>tests/acceptance.json#AC-TM004-001</x:v>
       </x:c>
+      <x:c r="H17" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="32" customHeight="1">
       <x:c r="A18" s="9" t="str">
@@ -2874,6 +2976,9 @@
       <x:c r="G18" s="9" t="str">
         <x:v>tests/acceptance.json#AC-TM004-002</x:v>
       </x:c>
+      <x:c r="H18" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="32" customHeight="1">
       <x:c r="A19" s="4" t="str">
@@ -2897,6 +3002,9 @@
       <x:c r="G19" s="4" t="str">
         <x:v>tests/acceptance.json#AC-TM004-003</x:v>
       </x:c>
+      <x:c r="H19" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="32" customHeight="1">
       <x:c r="A20" s="9" t="str">
@@ -2920,6 +3028,9 @@
       <x:c r="G20" s="9" t="str">
         <x:v>tests/acceptance.json#AC-TM004-004</x:v>
       </x:c>
+      <x:c r="H20" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="32" customHeight="1">
       <x:c r="A21" s="4" t="str">
@@ -2943,6 +3054,9 @@
       <x:c r="G21" s="4" t="str">
         <x:v>tests/acceptance.json#AC-TM005-001</x:v>
       </x:c>
+      <x:c r="H21" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="32" customHeight="1">
       <x:c r="A22" s="9" t="str">
@@ -2966,6 +3080,9 @@
       <x:c r="G22" s="9" t="str">
         <x:v>tests/acceptance.json#AC-TM005-002</x:v>
       </x:c>
+      <x:c r="H22" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="32" customHeight="1">
       <x:c r="A23" s="4" t="str">
@@ -2988,6 +3105,9 @@
       </x:c>
       <x:c r="G23" s="4" t="str">
         <x:v>tests/acceptance.json#AC-TM006-001</x:v>
+      </x:c>
+      <x:c r="H23" s="4" t="str">
+        <x:v>未提供</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="72" customHeight="1">
@@ -3015,6 +3135,9 @@
       <x:c r="G24" s="9" t="str">
         <x:v>tests/acceptance.json#AC-TM006-002</x:v>
       </x:c>
+      <x:c r="H24" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="32" customHeight="1">
       <x:c r="A25" s="4" t="str">
@@ -3038,6 +3161,9 @@
       <x:c r="G25" s="4" t="str">
         <x:v>tests/acceptance.json#AC-TM007-001</x:v>
       </x:c>
+      <x:c r="H25" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" ht="32" customHeight="1">
       <x:c r="A26" s="9" t="str">
@@ -3061,6 +3187,9 @@
       <x:c r="G26" s="9" t="str">
         <x:v>tests/acceptance.json#AC-TM007-002</x:v>
       </x:c>
+      <x:c r="H26" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="32" customHeight="1">
       <x:c r="A27" s="4" t="str">
@@ -3084,6 +3213,9 @@
       <x:c r="G27" s="4" t="str">
         <x:v>tests/acceptance.json#AC-TM007-003</x:v>
       </x:c>
+      <x:c r="H27" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="42" customHeight="1">
       <x:c r="A28" s="9" t="str">
@@ -3107,6 +3239,9 @@
       <x:c r="G28" s="9" t="str">
         <x:v>tests/acceptance.json#AC-TM007-004</x:v>
       </x:c>
+      <x:c r="H28" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="32" customHeight="1">
       <x:c r="A29" s="4" t="str">
@@ -3130,6 +3265,9 @@
       <x:c r="G29" s="4" t="str">
         <x:v>tests/acceptance.json#AC-TM008-001</x:v>
       </x:c>
+      <x:c r="H29" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="32" customHeight="1">
       <x:c r="A30" s="9" t="str">
@@ -3153,6 +3291,9 @@
       <x:c r="G30" s="9" t="str">
         <x:v>tests/acceptance.json#AC-TM008-002</x:v>
       </x:c>
+      <x:c r="H30" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="32" customHeight="1">
       <x:c r="A31" s="4" t="str">
@@ -3176,6 +3317,9 @@
       <x:c r="G31" s="4" t="str">
         <x:v>tests/acceptance.json#AC-TM009-001</x:v>
       </x:c>
+      <x:c r="H31" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="32" customHeight="1">
       <x:c r="A32" s="9" t="str">
@@ -3199,6 +3343,9 @@
       <x:c r="G32" s="9" t="str">
         <x:v>tests/acceptance.json#AC-TM009-002</x:v>
       </x:c>
+      <x:c r="H32" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="33" ht="42" customHeight="1">
       <x:c r="A33" s="4" t="str">
@@ -3222,6 +3369,9 @@
       <x:c r="G33" s="4" t="str">
         <x:v>tests/acceptance.json#AC-TM010-001</x:v>
       </x:c>
+      <x:c r="H33" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="34" ht="32" customHeight="1">
       <x:c r="A34" s="9" t="str">
@@ -3245,6 +3395,9 @@
       <x:c r="G34" s="9" t="str">
         <x:v>tests/acceptance.json#AC-TM010-002</x:v>
       </x:c>
+      <x:c r="H34" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="35" ht="42" customHeight="1">
       <x:c r="A35" s="4" t="str">
@@ -3269,6 +3422,9 @@
       <x:c r="G35" s="4" t="str">
         <x:v>tests/acceptance.json#AC-TM010-003</x:v>
       </x:c>
+      <x:c r="H35" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" ht="32" customHeight="1">
       <x:c r="A36" s="9" t="str">
@@ -3292,6 +3448,9 @@
       <x:c r="G36" s="9" t="str">
         <x:v>tests/acceptance.json#AC-TM011-001</x:v>
       </x:c>
+      <x:c r="H36" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="37" ht="32" customHeight="1">
       <x:c r="A37" s="4" t="str">
@@ -3315,6 +3474,9 @@
       <x:c r="G37" s="4" t="str">
         <x:v>tests/acceptance.json#AC-TM011-002</x:v>
       </x:c>
+      <x:c r="H37" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="38" ht="32" customHeight="1">
       <x:c r="A38" s="9" t="str">
@@ -3338,6 +3500,9 @@
       <x:c r="G38" s="9" t="str">
         <x:v>tests/acceptance.json#AC-TM011-003</x:v>
       </x:c>
+      <x:c r="H38" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="39" ht="42" customHeight="1">
       <x:c r="A39" s="4" t="str">
@@ -3361,6 +3526,9 @@
       <x:c r="G39" s="4" t="str">
         <x:v>tests/acceptance.json#AC-TM011-004</x:v>
       </x:c>
+      <x:c r="H39" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="40" ht="32" customHeight="1">
       <x:c r="A40" s="9" t="str">
@@ -3384,6 +3552,9 @@
       <x:c r="G40" s="9" t="str">
         <x:v>tests/acceptance.json#AC-TM012-001</x:v>
       </x:c>
+      <x:c r="H40" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="41" ht="32" customHeight="1">
       <x:c r="A41" s="4" t="str">
@@ -3406,6 +3577,9 @@
       </x:c>
       <x:c r="G41" s="4" t="str">
         <x:v>tests/acceptance.json#AC-TM012-002</x:v>
+      </x:c>
+      <x:c r="H41" s="4" t="str">
+        <x:v>未提供</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3416,7 +3590,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R970291c4378548da"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5407363040844d1a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3434,6 +3608,7 @@
     <x:col min="7" max="7" width="45" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="45" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="85" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="85" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2">
@@ -3468,6 +3643,9 @@
       </x:c>
       <x:c r="I4" s="8" t="str">
         <x:v>依据</x:v>
+      </x:c>
+      <x:c r="J4" s="8" t="str">
+        <x:v>design_source</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="102" customHeight="1">
@@ -3503,8 +3681,11 @@
       <x:c r="I5" s="4" t="str">
         <x:v>docs/product/README.md:18</x:v>
       </x:c>
-    </x:row>
-    <x:row r="6" ht="42" customHeight="1">
+      <x:c r="J5" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="57" customHeight="1">
       <x:c r="A6" s="9" t="str">
         <x:v>TM-002</x:v>
       </x:c>
@@ -3518,7 +3699,7 @@
         <x:v>首次授权</x:v>
       </x:c>
       <x:c r="E6" s="9" t="str">
-        <x:v>选择目录、候选文件预览、记录采集/同步意愿、拒绝/撤销/重新授权</x:v>
+        <x:v>已登录成员通过 macOS 原生目录选择器选定来源，预览选中根内候选文件；分别确认采集与未来同步意愿，App 在当前用户私有记录中加密持久保存已确认目录 locator；撤销删除记录，失效或解密失败停读，经重新选择和确认后恢复。</x:v>
       </x:c>
       <x:c r="F6" s="9" t="str">
         <x:v>AC-TM002-001
@@ -3528,10 +3709,13 @@
         <x:v>0.2.0</x:v>
       </x:c>
       <x:c r="H6" s="9" t="str">
-        <x:v>规划中</x:v>
+        <x:v>baseline_pending</x:v>
       </x:c>
       <x:c r="I6" s="9" t="str">
         <x:v>docs/product/README.md:19</x:v>
+      </x:c>
+      <x:c r="J6" s="9" t="str">
+        <x:v>releases/v0.2.0-20261001T034118Z/01-requirements.md:13</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="72" customHeight="1">
@@ -3565,6 +3749,9 @@
       <x:c r="I7" s="4" t="str">
         <x:v>docs/product/README.md:20</x:v>
       </x:c>
+      <x:c r="J7" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="72" customHeight="1">
       <x:c r="A8" s="9" t="str">
@@ -3597,6 +3784,9 @@
       <x:c r="I8" s="9" t="str">
         <x:v>docs/product/README.md:21</x:v>
       </x:c>
+      <x:c r="J8" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="42" customHeight="1">
       <x:c r="A9" s="4" t="str">
@@ -3627,6 +3817,9 @@
       <x:c r="I9" s="4" t="str">
         <x:v>docs/product/README.md:22</x:v>
       </x:c>
+      <x:c r="J9" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="42" customHeight="1">
       <x:c r="A10" s="9" t="str">
@@ -3656,6 +3849,9 @@
       </x:c>
       <x:c r="I10" s="9" t="str">
         <x:v>docs/product/README.md:23</x:v>
+      </x:c>
+      <x:c r="J10" s="9" t="str">
+        <x:v>未提供</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="72" customHeight="1">
@@ -3689,6 +3885,9 @@
       <x:c r="I11" s="4" t="str">
         <x:v>docs/product/README.md:24</x:v>
       </x:c>
+      <x:c r="J11" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="42" customHeight="1">
       <x:c r="A12" s="9" t="str">
@@ -3719,6 +3918,9 @@
       <x:c r="I12" s="9" t="str">
         <x:v>docs/product/README.md:25</x:v>
       </x:c>
+      <x:c r="J12" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="42" customHeight="1">
       <x:c r="A13" s="4" t="str">
@@ -3748,6 +3950,9 @@
       </x:c>
       <x:c r="I13" s="4" t="str">
         <x:v>docs/product/README.md:26</x:v>
+      </x:c>
+      <x:c r="J13" s="4" t="str">
+        <x:v>未提供</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="57" customHeight="1">
@@ -3779,6 +3984,9 @@
       </x:c>
       <x:c r="I14" s="9" t="str">
         <x:v>docs/product/README.md:27</x:v>
+      </x:c>
+      <x:c r="J14" s="9" t="str">
+        <x:v>未提供</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="72" customHeight="1">
@@ -3812,6 +4020,9 @@
       <x:c r="I15" s="4" t="str">
         <x:v>docs/product/README.md:28</x:v>
       </x:c>
+      <x:c r="J15" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" ht="42" customHeight="1">
       <x:c r="A16" s="9" t="str">
@@ -3842,6 +4053,9 @@
       <x:c r="I16" s="9" t="str">
         <x:v>docs/product/README.md:29</x:v>
       </x:c>
+      <x:c r="J16" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="42" customHeight="1">
       <x:c r="A17" s="4" t="str">
@@ -3872,6 +4086,9 @@
       <x:c r="I17" s="4" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/01a-feature-points.md:7</x:v>
       </x:c>
+      <x:c r="J17" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="42" customHeight="1">
       <x:c r="A18" s="9" t="str">
@@ -3902,6 +4119,9 @@
       <x:c r="I18" s="9" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/01a-feature-points.md:8</x:v>
       </x:c>
+      <x:c r="J18" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="42" customHeight="1">
       <x:c r="A19" s="4" t="str">
@@ -3932,6 +4152,9 @@
       <x:c r="I19" s="4" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/01a-feature-points.md:9</x:v>
       </x:c>
+      <x:c r="J19" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="42" customHeight="1">
       <x:c r="A20" s="9" t="str">
@@ -3962,6 +4185,9 @@
       <x:c r="I20" s="9" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/01a-feature-points.md:10</x:v>
       </x:c>
+      <x:c r="J20" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="32" customHeight="1">
       <x:c r="A21" s="4" t="str">
@@ -3991,6 +4217,9 @@
       <x:c r="I21" s="4" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/01a-feature-points.md:11</x:v>
       </x:c>
+      <x:c r="J21" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="32" customHeight="1">
       <x:c r="A22" s="9" t="str">
@@ -4020,6 +4249,9 @@
       <x:c r="I22" s="9" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/01a-feature-points.md:12</x:v>
       </x:c>
+      <x:c r="J22" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="32" customHeight="1">
       <x:c r="A23" s="4" t="str">
@@ -4048,6 +4280,9 @@
       </x:c>
       <x:c r="I23" s="4" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/01a-feature-points.md:13</x:v>
+      </x:c>
+      <x:c r="J23" s="4" t="str">
+        <x:v>未提供</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="102" customHeight="1">
@@ -4083,6 +4318,9 @@
       <x:c r="I24" s="9" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/01a-feature-points.md:14</x:v>
       </x:c>
+      <x:c r="J24" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="102" customHeight="1">
       <x:c r="A25" s="4" t="str">
@@ -4116,6 +4354,9 @@
       </x:c>
       <x:c r="I25" s="4" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/01a-feature-points.md:15</x:v>
+      </x:c>
+      <x:c r="J25" s="4" t="str">
+        <x:v>未提供</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4126,7 +4367,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3660c153b5dd4a3d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R490ea09385ac40b6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4146,6 +4387,7 @@
     <x:col min="9" max="9" width="45" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="45" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="85" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="85" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2">
@@ -4187,6 +4429,9 @@
       <x:c r="K4" s="8" t="str">
         <x:v>依据</x:v>
       </x:c>
+      <x:c r="L4" s="8" t="str">
+        <x:v>decision_source</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="42" customHeight="1">
       <x:c r="A5" s="4" t="str">
@@ -4223,6 +4468,9 @@
       <x:c r="K5" s="4" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:29</x:v>
       </x:c>
+      <x:c r="L5" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="42" customHeight="1">
       <x:c r="A6" s="9" t="str">
@@ -4259,6 +4507,9 @@
       <x:c r="K6" s="9" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:30</x:v>
       </x:c>
+      <x:c r="L6" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="42" customHeight="1">
       <x:c r="A7" s="4" t="str">
@@ -4295,6 +4546,9 @@
       <x:c r="K7" s="4" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:31</x:v>
       </x:c>
+      <x:c r="L7" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="42" customHeight="1">
       <x:c r="A8" s="9" t="str">
@@ -4330,6 +4584,9 @@
       <x:c r="K8" s="9" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:32</x:v>
       </x:c>
+      <x:c r="L8" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="42" customHeight="1">
       <x:c r="A9" s="4" t="str">
@@ -4366,6 +4623,9 @@
       <x:c r="K9" s="4" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:33</x:v>
       </x:c>
+      <x:c r="L9" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="32" customHeight="1">
       <x:c r="A10" s="9" t="str">
@@ -4401,6 +4661,9 @@
       <x:c r="K10" s="9" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:34</x:v>
       </x:c>
+      <x:c r="L10" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="42" customHeight="1">
       <x:c r="A11" s="4" t="str">
@@ -4436,6 +4699,9 @@
       <x:c r="K11" s="4" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:35</x:v>
       </x:c>
+      <x:c r="L11" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="32" customHeight="1">
       <x:c r="A12" s="9" t="str">
@@ -4471,6 +4737,9 @@
       <x:c r="K12" s="9" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:36</x:v>
       </x:c>
+      <x:c r="L12" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="32" customHeight="1">
       <x:c r="A13" s="4" t="str">
@@ -4506,6 +4775,9 @@
       <x:c r="K13" s="4" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:37</x:v>
       </x:c>
+      <x:c r="L13" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="32" customHeight="1">
       <x:c r="A14" s="9" t="str">
@@ -4541,6 +4813,9 @@
       <x:c r="K14" s="9" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:38</x:v>
       </x:c>
+      <x:c r="L14" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="32" customHeight="1">
       <x:c r="A15" s="4" t="str">
@@ -4576,6 +4851,9 @@
       <x:c r="K15" s="4" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:39</x:v>
       </x:c>
+      <x:c r="L15" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" ht="32" customHeight="1">
       <x:c r="A16" s="9" t="str">
@@ -4611,6 +4889,9 @@
       <x:c r="K16" s="9" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:40</x:v>
       </x:c>
+      <x:c r="L16" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="42" customHeight="1">
       <x:c r="A17" s="4" t="str">
@@ -4647,6 +4928,9 @@
       <x:c r="K17" s="4" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:41</x:v>
       </x:c>
+      <x:c r="L17" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="32" customHeight="1">
       <x:c r="A18" s="9" t="str">
@@ -4682,6 +4966,9 @@
       <x:c r="K18" s="9" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:42</x:v>
       </x:c>
+      <x:c r="L18" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="57" customHeight="1">
       <x:c r="A19" s="4" t="str">
@@ -4717,6 +5004,9 @@
       <x:c r="K19" s="4" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:43</x:v>
       </x:c>
+      <x:c r="L19" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="32" customHeight="1">
       <x:c r="A20" s="9" t="str">
@@ -4752,6 +5042,9 @@
       <x:c r="K20" s="9" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:44</x:v>
       </x:c>
+      <x:c r="L20" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="32" customHeight="1">
       <x:c r="A21" s="4" t="str">
@@ -4787,6 +5080,9 @@
       <x:c r="K21" s="4" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:45</x:v>
       </x:c>
+      <x:c r="L21" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="32" customHeight="1">
       <x:c r="A22" s="9" t="str">
@@ -4822,6 +5118,9 @@
       <x:c r="K22" s="9" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:46</x:v>
       </x:c>
+      <x:c r="L22" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="42" customHeight="1">
       <x:c r="A23" s="4" t="str">
@@ -4857,6 +5156,9 @@
       <x:c r="K23" s="4" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:47</x:v>
       </x:c>
+      <x:c r="L23" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="32" customHeight="1">
       <x:c r="A24" s="9" t="str">
@@ -4892,6 +5194,9 @@
       <x:c r="K24" s="9" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:48</x:v>
       </x:c>
+      <x:c r="L24" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="32" customHeight="1">
       <x:c r="A25" s="4" t="str">
@@ -4927,6 +5232,9 @@
       <x:c r="K25" s="4" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:49</x:v>
       </x:c>
+      <x:c r="L25" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" ht="42" customHeight="1">
       <x:c r="A26" s="9" t="str">
@@ -4962,6 +5270,9 @@
       <x:c r="K26" s="9" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:50</x:v>
       </x:c>
+      <x:c r="L26" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="42" customHeight="1">
       <x:c r="A27" s="4" t="str">
@@ -4997,6 +5308,9 @@
       <x:c r="K27" s="4" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:51</x:v>
       </x:c>
+      <x:c r="L27" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="32" customHeight="1">
       <x:c r="A28" s="9" t="str">
@@ -5031,6 +5345,9 @@
       </x:c>
       <x:c r="K28" s="9" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:52</x:v>
+      </x:c>
+      <x:c r="L28" s="9" t="str">
+        <x:v>未提供</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="102" customHeight="1">
@@ -5072,6 +5389,9 @@
       <x:c r="K29" s="4" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:53</x:v>
       </x:c>
+      <x:c r="L29" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="102" customHeight="1">
       <x:c r="A30" s="9" t="str">
@@ -5112,6 +5432,9 @@
       <x:c r="K30" s="9" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:54</x:v>
       </x:c>
+      <x:c r="L30" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="102" customHeight="1">
       <x:c r="A31" s="4" t="str">
@@ -5152,6 +5475,9 @@
       <x:c r="K31" s="4" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:55</x:v>
       </x:c>
+      <x:c r="L31" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="102" customHeight="1">
       <x:c r="A32" s="9" t="str">
@@ -5192,261 +5518,639 @@
       <x:c r="K32" s="9" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:56</x:v>
       </x:c>
-    </x:row>
-    <x:row r="33" ht="32" customHeight="1">
+      <x:c r="L32" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="42" customHeight="1">
       <x:c r="A33" s="4" t="str">
-        <x:v>TASK-TM001-PLAN</x:v>
+        <x:v>TASK-TM002-PICKER</x:v>
       </x:c>
       <x:c r="B33" s="4" t="str">
-        <x:v>历史分组</x:v>
+        <x:v>具体任务</x:v>
       </x:c>
       <x:c r="C33" s="4" t="str">
+        <x:v>FP-TM002-01</x:v>
+      </x:c>
+      <x:c r="D33" s="4" t="str">
+        <x:v>REQ-TM002</x:v>
+      </x:c>
+      <x:c r="E33" s="4" t="str">
+        <x:v>AC-TM002-001</x:v>
+      </x:c>
+      <x:c r="F33" s="4" t="str">
+        <x:v>已验证的 TM-001 登录身份</x:v>
+      </x:c>
+      <x:c r="G33" s="4" t="str">
+        <x:v>通过原生目录选择器取得来源；取消不改状态；主进程只接受系统选择结果，不暴露 renderer 任意路径读取接口</x:v>
+      </x:c>
+      <x:c r="H33" s="4" t="str">
+        <x:v>TM-001 身份；主进程选择器、preload、引导 UI</x:v>
+      </x:c>
+      <x:c r="I33" s="4" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="D33" s="4" t="str">
-        <x:v>REQ-TM001</x:v>
-      </x:c>
-      <x:c r="E33" s="4" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="F33" s="4" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="G33" s="4" t="str">
-        <x:v>六文档、完整追踪、SOP 修正、基线通过</x:v>
-      </x:c>
-      <x:c r="H33" s="4" t="str">
-        <x:v>需求</x:v>
-      </x:c>
-      <x:c r="I33" s="4" t="str">
-        <x:v>TEST-TM001-GOVERNANCE</x:v>
-      </x:c>
       <x:c r="J33" s="4" t="str">
-        <x:v>historical_group_not_minimal_task</x:v>
+        <x:v>baseline_pending</x:v>
       </x:c>
       <x:c r="K33" s="4" t="str">
-        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:9</x:v>
+        <x:v>releases/v0.2.0-20261001T034118Z/02-breakdown.md:7</x:v>
+      </x:c>
+      <x:c r="L33" s="4" t="str">
+        <x:v>未提供</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="42" customHeight="1">
       <x:c r="A34" s="9" t="str">
-        <x:v>TASK-TM001-SERVER</x:v>
+        <x:v>TASK-TM002-PREVIEW</x:v>
       </x:c>
       <x:c r="B34" s="9" t="str">
-        <x:v>历史分组</x:v>
+        <x:v>具体任务</x:v>
       </x:c>
       <x:c r="C34" s="9" t="str">
+        <x:v>FP-TM002-01</x:v>
+      </x:c>
+      <x:c r="D34" s="9" t="str">
+        <x:v>REQ-TM002</x:v>
+      </x:c>
+      <x:c r="E34" s="9" t="str">
+        <x:v>AC-TM002-001</x:v>
+      </x:c>
+      <x:c r="F34" s="9" t="str">
+        <x:v>PICKER 暂选根与本版候选规则</x:v>
+      </x:c>
+      <x:c r="G34" s="9" t="str">
+        <x:v>只列相对名称、大小、时间；拒绝符号链接逸出及未选根，绝不读取正文；达到上限标明预览不完整</x:v>
+      </x:c>
+      <x:c r="H34" s="9" t="str">
+        <x:v>PICKER；主进程候选枚举和 UI</x:v>
+      </x:c>
+      <x:c r="I34" s="9" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="D34" s="9" t="str">
-        <x:v>REQ-TM001</x:v>
-      </x:c>
-      <x:c r="E34" s="9" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="F34" s="9" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="G34" s="9" t="str">
-        <x:v>FastAPI/SQLAlchemy/Alembic 工程、真实认证/权限/审计 API；随机可撤销 token 固定30天到期、不滑动，改密/重置/停用撤销旧会话</x:v>
-      </x:c>
-      <x:c r="H34" s="9" t="str">
-        <x:v>计划、数据/测试</x:v>
-      </x:c>
-      <x:c r="I34" s="9" t="str">
-        <x:v>E2E-TM001-001、E2E-TM001-002、E2E-TM001-003</x:v>
-      </x:c>
       <x:c r="J34" s="9" t="str">
-        <x:v>historical_group_not_minimal_task</x:v>
+        <x:v>baseline_pending</x:v>
       </x:c>
       <x:c r="K34" s="9" t="str">
-        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:10</x:v>
+        <x:v>releases/v0.2.0-20261001T034118Z/02-breakdown.md:8</x:v>
+      </x:c>
+      <x:c r="L34" s="9" t="str">
+        <x:v>未提供</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="42" customHeight="1">
       <x:c r="A35" s="4" t="str">
-        <x:v>TASK-TM001-DATA</x:v>
+        <x:v>TASK-TM002-CONSENT</x:v>
       </x:c>
       <x:c r="B35" s="4" t="str">
-        <x:v>历史分组</x:v>
+        <x:v>具体任务</x:v>
       </x:c>
       <x:c r="C35" s="4" t="str">
+        <x:v>FP-TM002-02</x:v>
+      </x:c>
+      <x:c r="D35" s="4" t="str">
+        <x:v>REQ-TM002</x:v>
+      </x:c>
+      <x:c r="E35" s="4" t="str">
+        <x:v>AC-TM002-001</x:v>
+      </x:c>
+      <x:c r="F35" s="4" t="str">
+        <x:v>PICKER/PREVIEW 暂选结果与用户明确意愿</x:v>
+      </x:c>
+      <x:c r="G35" s="4" t="str">
+        <x:v>分别确认采集与未来同步意愿；确认前不持续读取，本版不因同步意愿上传</x:v>
+      </x:c>
+      <x:c r="H35" s="4" t="str">
+        <x:v>PICKER、PREVIEW；UI 与主进程来源状态机</x:v>
+      </x:c>
+      <x:c r="I35" s="4" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="D35" s="4" t="str">
-        <x:v>REQ-TM001</x:v>
-      </x:c>
-      <x:c r="E35" s="4" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="F35" s="4" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="G35" s="4" t="str">
-        <x:v>独立测试/生产 SQLite 文件、可执行造数 SQL、生产首建管理员、回归账号/独立预期及安全重置；已有生产密码不可被重建覆盖</x:v>
-      </x:c>
-      <x:c r="H35" s="4" t="str">
-        <x:v>计划、工程骨架</x:v>
-      </x:c>
-      <x:c r="I35" s="4" t="str">
-        <x:v>TEST-TM001-SERVER、E2E-TM001-001、E2E-TM001-005</x:v>
-      </x:c>
       <x:c r="J35" s="4" t="str">
-        <x:v>historical_group_not_minimal_task</x:v>
+        <x:v>baseline_pending</x:v>
       </x:c>
       <x:c r="K35" s="4" t="str">
-        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:11</x:v>
+        <x:v>releases/v0.2.0-20261001T034118Z/02-breakdown.md:9</x:v>
+      </x:c>
+      <x:c r="L35" s="4" t="str">
+        <x:v>未提供</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="72" customHeight="1">
       <x:c r="A36" s="9" t="str">
-        <x:v>TASK-TM001-MAC</x:v>
+        <x:v>TASK-TM002-STORE</x:v>
       </x:c>
       <x:c r="B36" s="9" t="str">
-        <x:v>历史分组</x:v>
+        <x:v>具体任务</x:v>
       </x:c>
       <x:c r="C36" s="9" t="str">
+        <x:v>FP-TM002-02</x:v>
+      </x:c>
+      <x:c r="D36" s="9" t="str">
+        <x:v>REQ-TM002</x:v>
+      </x:c>
+      <x:c r="E36" s="9" t="str">
+        <x:v>AC-TM002-001</x:v>
+      </x:c>
+      <x:c r="F36" s="9" t="str">
+        <x:v>已确认来源、服务 origin 与真实账号</x:v>
+      </x:c>
+      <x:c r="G36" s="9" t="str">
+        <x:v>已确认目录的规范化路径以 Electron safeStorage 加密为 locator，密文写入当前用户 0700/0600 私有 sources 记录，macOS 密钥由 Keychain 保护；按服务 origin 与真实账号隔离，重启经验证恢复；未确认暂选内容不持久化，密钥不可用或解密失败停读，不回退明文。</x:v>
+      </x:c>
+      <x:c r="H36" s="9" t="str">
+        <x:v>CONSENT；受保护本地配置、safeStorage/Keychain 与状态恢复；无加密能力时安全拒绝</x:v>
+      </x:c>
+      <x:c r="I36" s="9" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="D36" s="9" t="str">
-        <x:v>REQ-TM001</x:v>
-      </x:c>
-      <x:c r="E36" s="9" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="F36" s="9" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="G36" s="9" t="str">
-        <x:v>Electron React/TypeScript 登录/改密/主页/管理、默认本机 API/更新源地址与配置管理页的用户覆盖持久化；默认开启可关闭的设备自动登录、按规范化 origin 隔离的受保护凭据文件与内存会话、稳定 UI 标识、Playwright Electron工程</x:v>
-      </x:c>
-      <x:c r="H36" s="9" t="str">
-        <x:v>API 合同、工程骨架</x:v>
-      </x:c>
-      <x:c r="I36" s="9" t="str">
-        <x:v>E2E-TM001-001、E2E-TM001-002、E2E-TM001-003、E2E-TM001-004、E2E-TM001-005、E2E-TM001-006</x:v>
-      </x:c>
       <x:c r="J36" s="9" t="str">
-        <x:v>historical_group_not_minimal_task</x:v>
+        <x:v>baseline_pending</x:v>
       </x:c>
       <x:c r="K36" s="9" t="str">
-        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:12</x:v>
+        <x:v>releases/v0.2.0-20261001T034118Z/02-breakdown.md:10</x:v>
+      </x:c>
+      <x:c r="L36" s="9" t="str">
+        <x:v>releases/v0.2.0-20261001T034118Z/01-requirements.md:32</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="57" customHeight="1">
       <x:c r="A37" s="4" t="str">
-        <x:v>TASK-TM001-UPDATE</x:v>
+        <x:v>TASK-TM002-ACCESS</x:v>
       </x:c>
       <x:c r="B37" s="4" t="str">
-        <x:v>历史分组</x:v>
+        <x:v>具体任务</x:v>
       </x:c>
       <x:c r="C37" s="4" t="str">
+        <x:v>FP-TM002-03</x:v>
+      </x:c>
+      <x:c r="D37" s="4" t="str">
+        <x:v>REQ-TM002</x:v>
+      </x:c>
+      <x:c r="E37" s="4" t="str">
+        <x:v>AC-TM002-002</x:v>
+      </x:c>
+      <x:c r="F37" s="4" t="str">
+        <x:v>已确认来源及可读取目录</x:v>
+      </x:c>
+      <x:c r="G37" s="4" t="str">
+        <x:v>后续读取经主进程受限接口；受控候选元数据刷新验证范围；App 内撤销删除 locator 并立即停读，密钥不可用、解密失败、目录不可读或根身份变化均停读；经原生选择器重新选择并确认后才恢复。</x:v>
+      </x:c>
+      <x:c r="H37" s="4" t="str">
+        <x:v>STORE；来源访问模块与 UI 状态；TM-003 后续调用</x:v>
+      </x:c>
+      <x:c r="I37" s="4" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="D37" s="4" t="str">
-        <x:v>REQ-TM001</x:v>
-      </x:c>
-      <x:c r="E37" s="4" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="F37" s="4" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="G37" s="4" t="str">
-        <x:v>固定 Ed25519 公钥、同机回环更新源/签名测试包/失败包及真实更新用例；默认49177配置、URL安全校验与升级时锁定更新设置；两构建沿用经校验的同一隔离profile，升级后服务验证自动登录</x:v>
-      </x:c>
-      <x:c r="H37" s="4" t="str">
-        <x:v>Mac 工程</x:v>
-      </x:c>
-      <x:c r="I37" s="4" t="str">
-        <x:v>E2E-TM001-004</x:v>
-      </x:c>
       <x:c r="J37" s="4" t="str">
-        <x:v>historical_group_not_minimal_task</x:v>
+        <x:v>baseline_pending</x:v>
       </x:c>
       <x:c r="K37" s="4" t="str">
-        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:13</x:v>
+        <x:v>releases/v0.2.0-20261001T034118Z/02-breakdown.md:11</x:v>
+      </x:c>
+      <x:c r="L37" s="4" t="str">
+        <x:v>releases/v0.2.0-20261001T034118Z/01-requirements.md:32</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="57" customHeight="1">
       <x:c r="A38" s="9" t="str">
+        <x:v>TASK-TM002-DATA</x:v>
+      </x:c>
+      <x:c r="B38" s="9" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C38" s="9" t="str">
+        <x:v>FP-TM002-01
+FP-TM002-02
+FP-TM002-03</x:v>
+      </x:c>
+      <x:c r="D38" s="9" t="str">
+        <x:v>REQ-TM002</x:v>
+      </x:c>
+      <x:c r="E38" s="9" t="str">
+        <x:v>AC-TM002-001
+AC-TM002-002</x:v>
+      </x:c>
+      <x:c r="F38" s="9" t="str">
+        <x:v>本轮隔离目录与独立预期值</x:v>
+      </x:c>
+      <x:c r="G38" s="9" t="str">
+        <x:v>固定合成 A/B、候选/非候选/逸出文件及确认/失效状态；只清理取得所有权的目录</x:v>
+      </x:c>
+      <x:c r="H38" s="9" t="str">
+        <x:v>SOP-010；不访问真实工具日志或生产库</x:v>
+      </x:c>
+      <x:c r="I38" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J38" s="9" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="K38" s="9" t="str">
+        <x:v>releases/v0.2.0-20261001T034118Z/02-breakdown.md:12</x:v>
+      </x:c>
+      <x:c r="L38" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="57" customHeight="1">
+      <x:c r="A39" s="4" t="str">
+        <x:v>TASK-TM002-CATALOG</x:v>
+      </x:c>
+      <x:c r="B39" s="4" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C39" s="4" t="str">
+        <x:v>FP-TM002-01
+FP-TM002-02
+FP-TM002-03</x:v>
+      </x:c>
+      <x:c r="D39" s="4" t="str">
+        <x:v>REQ-TM002</x:v>
+      </x:c>
+      <x:c r="E39" s="4" t="str">
+        <x:v>AC-TM002-001
+AC-TM002-002</x:v>
+      </x:c>
+      <x:c r="F39" s="4" t="str">
+        <x:v>本版逐条 TC 与跨版本任务归属</x:v>
+      </x:c>
+      <x:c r="G39" s="4" t="str">
+        <x:v>新 TC 关联 0.2.0 TASK，保留 0.1.0 TC 归属；目录导出及质量检查有失败回归</x:v>
+      </x:c>
+      <x:c r="H39" s="4" t="str">
+        <x:v>SOP-000/006/011；测试清单、导出和治理测试</x:v>
+      </x:c>
+      <x:c r="I39" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J39" s="4" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="K39" s="4" t="str">
+        <x:v>releases/v0.2.0-20261001T034118Z/02-breakdown.md:13</x:v>
+      </x:c>
+      <x:c r="L39" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="57" customHeight="1">
+      <x:c r="A40" s="9" t="str">
+        <x:v>TASK-TM002-RUNNER</x:v>
+      </x:c>
+      <x:c r="B40" s="9" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C40" s="9" t="str">
+        <x:v>FP-TM002-01
+FP-TM002-02
+FP-TM002-03</x:v>
+      </x:c>
+      <x:c r="D40" s="9" t="str">
+        <x:v>REQ-TM002</x:v>
+      </x:c>
+      <x:c r="E40" s="9" t="str">
+        <x:v>AC-TM002-001
+AC-TM002-002</x:v>
+      </x:c>
+      <x:c r="F40" s="9" t="str">
+        <x:v>固定用例代码、隔离服务和 SQLite</x:v>
+      </x:c>
+      <x:c r="G40" s="9" t="str">
+        <x:v>驱动安装后 App 与真实原生面板；逐 TC 自动保存步骤及读取范围证据；缺绑定或环境判 BLOCKED</x:v>
+      </x:c>
+      <x:c r="H40" s="9" t="str">
+        <x:v>SOP-011/014；Playwright spec、面板驱动和本机 runner/gate</x:v>
+      </x:c>
+      <x:c r="I40" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J40" s="9" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="K40" s="9" t="str">
+        <x:v>releases/v0.2.0-20261001T034118Z/02-breakdown.md:14</x:v>
+      </x:c>
+      <x:c r="L40" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="57" customHeight="1">
+      <x:c r="A41" s="4" t="str">
+        <x:v>TASK-TM002-DELIVERY</x:v>
+      </x:c>
+      <x:c r="B41" s="4" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C41" s="4" t="str">
+        <x:v>FP-TM002-01
+FP-TM002-02
+FP-TM002-03</x:v>
+      </x:c>
+      <x:c r="D41" s="4" t="str">
+        <x:v>REQ-TM002</x:v>
+      </x:c>
+      <x:c r="E41" s="4" t="str">
+        <x:v>AC-TM002-001
+AC-TM002-002</x:v>
+      </x:c>
+      <x:c r="F41" s="4" t="str">
+        <x:v>TM-001 与 TM-002 完整回归范围及最终候选</x:v>
+      </x:c>
+      <x:c r="G41" s="4" t="str">
+        <x:v>运行全部目标 TC 和既有完整回归，验证稳定包真实升级、最终 DMG 与本机门禁；仅原件 PASS 放行</x:v>
+      </x:c>
+      <x:c r="H41" s="4" t="str">
+        <x:v>SOP-013/014/017/018；打包、门禁与本地归档</x:v>
+      </x:c>
+      <x:c r="I41" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J41" s="4" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="K41" s="4" t="str">
+        <x:v>releases/v0.2.0-20261001T034118Z/02-breakdown.md:15</x:v>
+      </x:c>
+      <x:c r="L41" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="32" customHeight="1">
+      <x:c r="A42" s="9" t="str">
+        <x:v>TASK-TM001-PLAN</x:v>
+      </x:c>
+      <x:c r="B42" s="9" t="str">
+        <x:v>历史分组</x:v>
+      </x:c>
+      <x:c r="C42" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="D42" s="9" t="str">
+        <x:v>REQ-TM001</x:v>
+      </x:c>
+      <x:c r="E42" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="F42" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="G42" s="9" t="str">
+        <x:v>六文档、完整追踪、SOP 修正、基线通过</x:v>
+      </x:c>
+      <x:c r="H42" s="9" t="str">
+        <x:v>需求</x:v>
+      </x:c>
+      <x:c r="I42" s="9" t="str">
+        <x:v>TEST-TM001-GOVERNANCE</x:v>
+      </x:c>
+      <x:c r="J42" s="9" t="str">
+        <x:v>historical_group_not_minimal_task</x:v>
+      </x:c>
+      <x:c r="K42" s="9" t="str">
+        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:9</x:v>
+      </x:c>
+      <x:c r="L42" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="42" customHeight="1">
+      <x:c r="A43" s="4" t="str">
+        <x:v>TASK-TM001-SERVER</x:v>
+      </x:c>
+      <x:c r="B43" s="4" t="str">
+        <x:v>历史分组</x:v>
+      </x:c>
+      <x:c r="C43" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="D43" s="4" t="str">
+        <x:v>REQ-TM001</x:v>
+      </x:c>
+      <x:c r="E43" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="F43" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="G43" s="4" t="str">
+        <x:v>FastAPI/SQLAlchemy/Alembic 工程、真实认证/权限/审计 API；随机可撤销 token 固定30天到期、不滑动，改密/重置/停用撤销旧会话</x:v>
+      </x:c>
+      <x:c r="H43" s="4" t="str">
+        <x:v>计划、数据/测试</x:v>
+      </x:c>
+      <x:c r="I43" s="4" t="str">
+        <x:v>E2E-TM001-001、E2E-TM001-002、E2E-TM001-003</x:v>
+      </x:c>
+      <x:c r="J43" s="4" t="str">
+        <x:v>historical_group_not_minimal_task</x:v>
+      </x:c>
+      <x:c r="K43" s="4" t="str">
+        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:10</x:v>
+      </x:c>
+      <x:c r="L43" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="42" customHeight="1">
+      <x:c r="A44" s="9" t="str">
+        <x:v>TASK-TM001-DATA</x:v>
+      </x:c>
+      <x:c r="B44" s="9" t="str">
+        <x:v>历史分组</x:v>
+      </x:c>
+      <x:c r="C44" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="D44" s="9" t="str">
+        <x:v>REQ-TM001</x:v>
+      </x:c>
+      <x:c r="E44" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="F44" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="G44" s="9" t="str">
+        <x:v>独立测试/生产 SQLite 文件、可执行造数 SQL、生产首建管理员、回归账号/独立预期及安全重置；已有生产密码不可被重建覆盖</x:v>
+      </x:c>
+      <x:c r="H44" s="9" t="str">
+        <x:v>计划、工程骨架</x:v>
+      </x:c>
+      <x:c r="I44" s="9" t="str">
+        <x:v>TEST-TM001-SERVER、E2E-TM001-001、E2E-TM001-005</x:v>
+      </x:c>
+      <x:c r="J44" s="9" t="str">
+        <x:v>historical_group_not_minimal_task</x:v>
+      </x:c>
+      <x:c r="K44" s="9" t="str">
+        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:11</x:v>
+      </x:c>
+      <x:c r="L44" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="72" customHeight="1">
+      <x:c r="A45" s="4" t="str">
+        <x:v>TASK-TM001-MAC</x:v>
+      </x:c>
+      <x:c r="B45" s="4" t="str">
+        <x:v>历史分组</x:v>
+      </x:c>
+      <x:c r="C45" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="D45" s="4" t="str">
+        <x:v>REQ-TM001</x:v>
+      </x:c>
+      <x:c r="E45" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="F45" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="G45" s="4" t="str">
+        <x:v>Electron React/TypeScript 登录/改密/主页/管理、默认本机 API/更新源地址与配置管理页的用户覆盖持久化；默认开启可关闭的设备自动登录、按规范化 origin 隔离的受保护凭据文件与内存会话、稳定 UI 标识、Playwright Electron工程</x:v>
+      </x:c>
+      <x:c r="H45" s="4" t="str">
+        <x:v>API 合同、工程骨架</x:v>
+      </x:c>
+      <x:c r="I45" s="4" t="str">
+        <x:v>E2E-TM001-001、E2E-TM001-002、E2E-TM001-003、E2E-TM001-004、E2E-TM001-005、E2E-TM001-006</x:v>
+      </x:c>
+      <x:c r="J45" s="4" t="str">
+        <x:v>historical_group_not_minimal_task</x:v>
+      </x:c>
+      <x:c r="K45" s="4" t="str">
+        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:12</x:v>
+      </x:c>
+      <x:c r="L45" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="57" customHeight="1">
+      <x:c r="A46" s="9" t="str">
+        <x:v>TASK-TM001-UPDATE</x:v>
+      </x:c>
+      <x:c r="B46" s="9" t="str">
+        <x:v>历史分组</x:v>
+      </x:c>
+      <x:c r="C46" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="D46" s="9" t="str">
+        <x:v>REQ-TM001</x:v>
+      </x:c>
+      <x:c r="E46" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="F46" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="G46" s="9" t="str">
+        <x:v>固定 Ed25519 公钥、同机回环更新源/签名测试包/失败包及真实更新用例；默认49177配置、URL安全校验与升级时锁定更新设置；两构建沿用经校验的同一隔离profile，升级后服务验证自动登录</x:v>
+      </x:c>
+      <x:c r="H46" s="9" t="str">
+        <x:v>Mac 工程</x:v>
+      </x:c>
+      <x:c r="I46" s="9" t="str">
+        <x:v>E2E-TM001-004</x:v>
+      </x:c>
+      <x:c r="J46" s="9" t="str">
+        <x:v>historical_group_not_minimal_task</x:v>
+      </x:c>
+      <x:c r="K46" s="9" t="str">
+        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:13</x:v>
+      </x:c>
+      <x:c r="L46" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="57" customHeight="1">
+      <x:c r="A47" s="4" t="str">
         <x:v>TASK-TM001-RUNNER</x:v>
       </x:c>
-      <x:c r="B38" s="9" t="str">
+      <x:c r="B47" s="4" t="str">
         <x:v>历史分组</x:v>
       </x:c>
-      <x:c r="C38" s="9" t="str">
+      <x:c r="C47" s="4" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="D38" s="9" t="str">
+      <x:c r="D47" s="4" t="str">
         <x:v>REQ-TM001</x:v>
       </x:c>
-      <x:c r="E38" s="9" t="str">
+      <x:c r="E47" s="4" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="F38" s="9" t="str">
+      <x:c r="F47" s="4" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="G38" s="9" t="str">
+      <x:c r="G47" s="4" t="str">
         <x:v>本机Playwright从最终DMG安装App执行全部六例，原始JSON/trace/fixtureSQL/包摘要、父门禁复核；默认值与动态独占端口隔离测试；真实Squirrel自重启及profile、身份恢复</x:v>
       </x:c>
-      <x:c r="H38" s="9" t="str">
+      <x:c r="H47" s="4" t="str">
         <x:v>数据/桌面工程</x:v>
       </x:c>
-      <x:c r="I38" s="9" t="str">
+      <x:c r="I47" s="4" t="str">
         <x:v>E2E-TM001-001、E2E-TM001-002、E2E-TM001-003、E2E-TM001-004、E2E-TM001-005、E2E-TM001-006</x:v>
       </x:c>
-      <x:c r="J38" s="9" t="str">
+      <x:c r="J47" s="4" t="str">
         <x:v>historical_group_not_minimal_task</x:v>
       </x:c>
-      <x:c r="K38" s="9" t="str">
+      <x:c r="K47" s="4" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:14</x:v>
       </x:c>
-    </x:row>
-    <x:row r="39" ht="32" customHeight="1">
-      <x:c r="A39" s="4" t="str">
+      <x:c r="L47" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="32" customHeight="1">
+      <x:c r="A48" s="9" t="str">
         <x:v>TASK-TM001-REVIEW</x:v>
       </x:c>
-      <x:c r="B39" s="4" t="str">
+      <x:c r="B48" s="9" t="str">
         <x:v>历史分组</x:v>
       </x:c>
-      <x:c r="C39" s="4" t="str">
+      <x:c r="C48" s="9" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="D39" s="4" t="str">
+      <x:c r="D48" s="9" t="str">
         <x:v>REQ-TM001</x:v>
       </x:c>
-      <x:c r="E39" s="4" t="str">
+      <x:c r="E48" s="9" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="F39" s="4" t="str">
+      <x:c r="F48" s="9" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="G39" s="4" t="str">
+      <x:c r="G48" s="9" t="str">
         <x:v>完整回归、流程复盘、PR 与合并判定、发布阻塞记录</x:v>
       </x:c>
-      <x:c r="H39" s="4" t="str">
+      <x:c r="H48" s="9" t="str">
         <x:v>全部实现任务</x:v>
       </x:c>
-      <x:c r="I39" s="4" t="str">
+      <x:c r="I48" s="9" t="str">
         <x:v>TEST-TM001-GOVERNANCE</x:v>
       </x:c>
-      <x:c r="J39" s="4" t="str">
+      <x:c r="J48" s="9" t="str">
         <x:v>historical_group_not_minimal_task</x:v>
       </x:c>
-      <x:c r="K39" s="4" t="str">
+      <x:c r="K48" s="9" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:15</x:v>
       </x:c>
+      <x:c r="L48" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="J5:J39">
+  <x:conditionalFormatting sqref="J5:J48">
     <x:cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="10" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="11" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb15f249c701f45ed"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R857f4be4041d474b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5468,6 +6172,7 @@
     <x:col min="11" max="11" width="22" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="85" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="65" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="52" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2">
@@ -5515,6 +6220,9 @@
       <x:c r="M4" s="8" t="str">
         <x:v>最近结果批次</x:v>
       </x:c>
+      <x:c r="N4" s="8" t="str">
+        <x:v>归属版本</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="87" customHeight="1">
       <x:c r="A5" s="4" t="str">
@@ -5560,6 +6268,9 @@
       <x:c r="M5" s="4" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N5" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="87" customHeight="1">
       <x:c r="A6" s="9" t="str">
@@ -5604,6 +6315,9 @@
       <x:c r="M6" s="9" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N6" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="87" customHeight="1">
       <x:c r="A7" s="4" t="str">
@@ -5648,6 +6362,9 @@
       <x:c r="M7" s="4" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N7" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="87" customHeight="1">
       <x:c r="A8" s="9" t="str">
@@ -5692,6 +6409,9 @@
       <x:c r="M8" s="9" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N8" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="87" customHeight="1">
       <x:c r="A9" s="4" t="str">
@@ -5736,6 +6456,9 @@
       <x:c r="M9" s="4" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N9" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="87" customHeight="1">
       <x:c r="A10" s="9" t="str">
@@ -5780,6 +6503,9 @@
       <x:c r="M10" s="9" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N10" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="87" customHeight="1">
       <x:c r="A11" s="4" t="str">
@@ -5824,6 +6550,9 @@
       <x:c r="M11" s="4" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N11" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="87" customHeight="1">
       <x:c r="A12" s="9" t="str">
@@ -5868,6 +6597,9 @@
       <x:c r="M12" s="9" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N12" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="87" customHeight="1">
       <x:c r="A13" s="4" t="str">
@@ -5912,6 +6644,9 @@
       <x:c r="M13" s="4" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N13" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="102" customHeight="1">
       <x:c r="A14" s="9" t="str">
@@ -5956,6 +6691,9 @@
       <x:c r="M14" s="9" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N14" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="87" customHeight="1">
       <x:c r="A15" s="4" t="str">
@@ -6001,6 +6739,9 @@
       <x:c r="M15" s="4" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N15" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" ht="87" customHeight="1">
       <x:c r="A16" s="9" t="str">
@@ -6046,6 +6787,9 @@
       <x:c r="M16" s="9" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N16" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="87" customHeight="1">
       <x:c r="A17" s="4" t="str">
@@ -6090,6 +6834,9 @@
       <x:c r="M17" s="4" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N17" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="87" customHeight="1">
       <x:c r="A18" s="9" t="str">
@@ -6134,6 +6881,9 @@
       <x:c r="M18" s="9" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N18" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="102" customHeight="1">
       <x:c r="A19" s="4" t="str">
@@ -6178,6 +6928,9 @@
       <x:c r="M19" s="4" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N19" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="102" customHeight="1">
       <x:c r="A20" s="9" t="str">
@@ -6223,6 +6976,9 @@
       <x:c r="M20" s="9" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N20" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="87" customHeight="1">
       <x:c r="A21" s="4" t="str">
@@ -6267,6 +7023,9 @@
       <x:c r="M21" s="4" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N21" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="87" customHeight="1">
       <x:c r="A22" s="9" t="str">
@@ -6311,6 +7070,9 @@
       <x:c r="M22" s="9" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N22" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="102" customHeight="1">
       <x:c r="A23" s="4" t="str">
@@ -6355,6 +7117,9 @@
       <x:c r="M23" s="4" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N23" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="87" customHeight="1">
       <x:c r="A24" s="9" t="str">
@@ -6399,6 +7164,9 @@
       <x:c r="M24" s="9" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N24" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="87" customHeight="1">
       <x:c r="A25" s="4" t="str">
@@ -6443,6 +7211,9 @@
       <x:c r="M25" s="4" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N25" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" ht="87" customHeight="1">
       <x:c r="A26" s="9" t="str">
@@ -6487,6 +7258,9 @@
       <x:c r="M26" s="9" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N26" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="87" customHeight="1">
       <x:c r="A27" s="4" t="str">
@@ -6531,6 +7305,9 @@
       <x:c r="M27" s="4" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N27" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="87" customHeight="1">
       <x:c r="A28" s="9" t="str">
@@ -6575,6 +7352,9 @@
       <x:c r="M28" s="9" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N28" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="87" customHeight="1">
       <x:c r="A29" s="4" t="str">
@@ -6619,6 +7399,9 @@
       <x:c r="M29" s="4" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N29" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="87" customHeight="1">
       <x:c r="A30" s="9" t="str">
@@ -6662,6 +7445,9 @@
       </x:c>
       <x:c r="M30" s="9" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
+      </x:c>
+      <x:c r="N30" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="102" customHeight="1">
@@ -6709,6 +7495,9 @@
       <x:c r="M31" s="4" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N31" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="87" customHeight="1">
       <x:c r="A32" s="9" t="str">
@@ -6753,6 +7542,9 @@
       <x:c r="M32" s="9" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N32" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="33" ht="87" customHeight="1">
       <x:c r="A33" s="4" t="str">
@@ -6797,6 +7589,9 @@
       <x:c r="M33" s="4" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N33" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="34" ht="87" customHeight="1">
       <x:c r="A34" s="9" t="str">
@@ -6841,6 +7636,9 @@
       <x:c r="M34" s="9" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N34" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="35" ht="87" customHeight="1">
       <x:c r="A35" s="4" t="str">
@@ -6885,6 +7683,9 @@
       <x:c r="M35" s="4" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N35" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" ht="87" customHeight="1">
       <x:c r="A36" s="9" t="str">
@@ -6929,6 +7730,9 @@
       <x:c r="M36" s="9" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N36" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="37" ht="102" customHeight="1">
       <x:c r="A37" s="4" t="str">
@@ -6972,6 +7776,9 @@
       </x:c>
       <x:c r="M37" s="4" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
+      </x:c>
+      <x:c r="N37" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="72" customHeight="1">
@@ -7019,6 +7826,9 @@
       <x:c r="M38" s="9" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N38" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="39" ht="72" customHeight="1">
       <x:c r="A39" s="4" t="str">
@@ -7065,6 +7875,9 @@
       <x:c r="M39" s="4" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N39" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="40" ht="72" customHeight="1">
       <x:c r="A40" s="9" t="str">
@@ -7111,6 +7924,9 @@
       <x:c r="M40" s="9" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N40" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="41" ht="72" customHeight="1">
       <x:c r="A41" s="4" t="str">
@@ -7157,6 +7973,9 @@
       <x:c r="M41" s="4" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N41" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="42" ht="72" customHeight="1">
       <x:c r="A42" s="9" t="str">
@@ -7203,6 +8022,9 @@
       <x:c r="M42" s="9" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N42" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="43" ht="72" customHeight="1">
       <x:c r="A43" s="4" t="str">
@@ -7249,6 +8071,9 @@
       <x:c r="M43" s="4" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N43" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="44" ht="72" customHeight="1">
       <x:c r="A44" s="9" t="str">
@@ -7295,6 +8120,9 @@
       <x:c r="M44" s="9" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N44" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="45" ht="72" customHeight="1">
       <x:c r="A45" s="4" t="str">
@@ -7341,6 +8169,9 @@
       <x:c r="M45" s="4" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N45" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="46" ht="72" customHeight="1">
       <x:c r="A46" s="9" t="str">
@@ -7388,6 +8219,9 @@
       <x:c r="M46" s="9" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N46" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="47" ht="72" customHeight="1">
       <x:c r="A47" s="4" t="str">
@@ -7433,6 +8267,9 @@
       </x:c>
       <x:c r="M47" s="4" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
+      </x:c>
+      <x:c r="N47" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="87" customHeight="1">
@@ -7481,6 +8318,9 @@
       <x:c r="M48" s="9" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N48" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="49" ht="72" customHeight="1">
       <x:c r="A49" s="4" t="str">
@@ -7527,6 +8367,9 @@
       <x:c r="M49" s="4" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N49" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="50" ht="72" customHeight="1">
       <x:c r="A50" s="9" t="str">
@@ -7573,6 +8416,9 @@
       <x:c r="M50" s="9" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N50" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="51" ht="72" customHeight="1">
       <x:c r="A51" s="4" t="str">
@@ -7619,6 +8465,9 @@
       <x:c r="M51" s="4" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N51" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="52" ht="72" customHeight="1">
       <x:c r="A52" s="9" t="str">
@@ -7665,6 +8514,9 @@
       <x:c r="M52" s="9" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N52" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="53" ht="72" customHeight="1">
       <x:c r="A53" s="4" t="str">
@@ -7711,6 +8563,9 @@
       <x:c r="M53" s="4" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N53" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="54" ht="72" customHeight="1">
       <x:c r="A54" s="9" t="str">
@@ -7756,6 +8611,9 @@
       </x:c>
       <x:c r="M54" s="9" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
+      </x:c>
+      <x:c r="N54" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="87" customHeight="1">
@@ -7804,6 +8662,9 @@
       <x:c r="M55" s="4" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N55" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="56" ht="72" customHeight="1">
       <x:c r="A56" s="9" t="str">
@@ -7849,6 +8710,9 @@
       </x:c>
       <x:c r="M56" s="9" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
+      </x:c>
+      <x:c r="N56" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="102" customHeight="1">
@@ -7897,6 +8761,9 @@
       <x:c r="M57" s="4" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N57" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="58" ht="72" customHeight="1">
       <x:c r="A58" s="9" t="str">
@@ -7943,6 +8810,9 @@
       <x:c r="M58" s="9" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N58" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="59" ht="72" customHeight="1">
       <x:c r="A59" s="4" t="str">
@@ -7988,6 +8858,9 @@
       </x:c>
       <x:c r="M59" s="4" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
+      </x:c>
+      <x:c r="N59" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="87" customHeight="1">
@@ -8036,6 +8909,9 @@
       <x:c r="M60" s="9" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N60" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="61" ht="72" customHeight="1">
       <x:c r="A61" s="4" t="str">
@@ -8081,6 +8957,9 @@
       </x:c>
       <x:c r="M61" s="4" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
+      </x:c>
+      <x:c r="N61" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="87" customHeight="1">
@@ -8129,6 +9008,9 @@
       <x:c r="M62" s="9" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N62" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="63" ht="87" customHeight="1">
       <x:c r="A63" s="4" t="str">
@@ -8176,6 +9058,9 @@
       <x:c r="M63" s="4" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N63" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="64" ht="72" customHeight="1">
       <x:c r="A64" s="9" t="str">
@@ -8222,6 +9107,9 @@
       <x:c r="M64" s="9" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N64" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="65" ht="57" customHeight="1">
       <x:c r="A65" s="4" t="str">
@@ -8266,6 +9154,9 @@
       </x:c>
       <x:c r="M65" s="4" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
+      </x:c>
+      <x:c r="N65" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="72" customHeight="1">
@@ -8313,6 +9204,9 @@
       <x:c r="M66" s="9" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N66" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="67" ht="72" customHeight="1">
       <x:c r="A67" s="4" t="str">
@@ -8358,6 +9252,9 @@
       </x:c>
       <x:c r="M67" s="4" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
+      </x:c>
+      <x:c r="N67" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="102" customHeight="1">
@@ -8406,6 +9303,9 @@
       <x:c r="M68" s="9" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N68" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="69" ht="87" customHeight="1">
       <x:c r="A69" s="4" t="str">
@@ -8453,6 +9353,9 @@
       <x:c r="M69" s="4" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N69" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="70" ht="87" customHeight="1">
       <x:c r="A70" s="9" t="str">
@@ -8500,6 +9403,9 @@
       <x:c r="M70" s="9" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N70" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="71" ht="87" customHeight="1">
       <x:c r="A71" s="4" t="str">
@@ -8547,6 +9453,9 @@
       <x:c r="M71" s="4" t="str">
         <x:v>local-534748ff47cb44229183a6bd878c1674</x:v>
       </x:c>
+      <x:c r="N71" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="72" ht="57" customHeight="1">
       <x:c r="A72" s="9" t="str">
@@ -8590,6 +9499,9 @@
       <x:c r="M72" s="9" t="str">
         <x:v>aux-818fe55e1e8940e4a3196b9d03b76563</x:v>
       </x:c>
+      <x:c r="N72" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="73" ht="57" customHeight="1">
       <x:c r="A73" s="4" t="str">
@@ -8633,6 +9545,9 @@
       <x:c r="M73" s="4" t="str">
         <x:v>aux-818fe55e1e8940e4a3196b9d03b76563</x:v>
       </x:c>
+      <x:c r="N73" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="74" ht="57" customHeight="1">
       <x:c r="A74" s="9" t="str">
@@ -8676,6 +9591,9 @@
       <x:c r="M74" s="9" t="str">
         <x:v>aux-818fe55e1e8940e4a3196b9d03b76563</x:v>
       </x:c>
+      <x:c r="N74" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="75" ht="57" customHeight="1">
       <x:c r="A75" s="4" t="str">
@@ -8719,6 +9637,9 @@
       <x:c r="M75" s="4" t="str">
         <x:v>aux-818fe55e1e8940e4a3196b9d03b76563</x:v>
       </x:c>
+      <x:c r="N75" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="76" ht="57" customHeight="1">
       <x:c r="A76" s="9" t="str">
@@ -8762,6 +9683,9 @@
       <x:c r="M76" s="9" t="str">
         <x:v>aux-818fe55e1e8940e4a3196b9d03b76563</x:v>
       </x:c>
+      <x:c r="N76" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="77" ht="57" customHeight="1">
       <x:c r="A77" s="4" t="str">
@@ -8805,6 +9729,9 @@
       <x:c r="M77" s="4" t="str">
         <x:v>aux-818fe55e1e8940e4a3196b9d03b76563</x:v>
       </x:c>
+      <x:c r="N77" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="78" ht="57" customHeight="1">
       <x:c r="A78" s="9" t="str">
@@ -8848,6 +9775,9 @@
       <x:c r="M78" s="9" t="str">
         <x:v>aux-818fe55e1e8940e4a3196b9d03b76563</x:v>
       </x:c>
+      <x:c r="N78" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="79" ht="57" customHeight="1">
       <x:c r="A79" s="4" t="str">
@@ -8891,6 +9821,9 @@
       <x:c r="M79" s="4" t="str">
         <x:v>aux-818fe55e1e8940e4a3196b9d03b76563</x:v>
       </x:c>
+      <x:c r="N79" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="80" ht="57" customHeight="1">
       <x:c r="A80" s="9" t="str">
@@ -8934,6 +9867,9 @@
       <x:c r="M80" s="9" t="str">
         <x:v>aux-818fe55e1e8940e4a3196b9d03b76563</x:v>
       </x:c>
+      <x:c r="N80" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="81" ht="57" customHeight="1">
       <x:c r="A81" s="4" t="str">
@@ -8977,6 +9913,9 @@
       <x:c r="M81" s="4" t="str">
         <x:v>aux-818fe55e1e8940e4a3196b9d03b76563</x:v>
       </x:c>
+      <x:c r="N81" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="82" ht="57" customHeight="1">
       <x:c r="A82" s="9" t="str">
@@ -9020,8 +9959,11 @@
       <x:c r="M82" s="9" t="str">
         <x:v>aux-818fe55e1e8940e4a3196b9d03b76563</x:v>
       </x:c>
-    </x:row>
-    <x:row r="83" ht="72" customHeight="1">
+      <x:c r="N82" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="102" customHeight="1">
       <x:c r="A83" s="4" t="str">
         <x:v>TM-002</x:v>
       </x:c>
@@ -9029,1355 +9971,4411 @@
         <x:v>E2E-TM002-001</x:v>
       </x:c>
       <x:c r="C83" s="4" t="str">
-        <x:v>首次授权、预览与确认</x:v>
+        <x:v>选择、预览、意愿与恢复</x:v>
       </x:c>
       <x:c r="D83" s="4" t="str">
+        <x:v>TASK-TM002-PICKER
+TASK-TM002-PREVIEW
+TASK-TM002-CONSENT
+TASK-TM002-STORE</x:v>
+      </x:c>
+      <x:c r="E83" s="4" t="str">
+        <x:v>product_e2e_group</x:v>
+      </x:c>
+      <x:c r="F83" s="4" t="str">
+        <x:v>system_permissions 合成 Codex/Claude A 与通常未选 B；分别真实选择/取消、显式预览、独立意愿、重启/换账号/换 origin；SELECT-02#REPLACE_CONFIRMED 唯一例外：同账号工具从已确认 Codex A 经真实面板原子替换为 B。</x:v>
+      </x:c>
+      <x:c r="G83" s="4" t="str">
+        <x:v>逐条子TC核对真实面板、App来源范围控制、撤销/失效/恢复；不声明沙盒或TCC授权。</x:v>
+      </x:c>
+      <x:c r="H83" s="4" t="str">
+        <x:v>准备：独占动态回环服务、隔离 SQLite、seed=42 合成 Alice/Bob 与本例 A/B；场景组只汇总子TC；每条子TC独占数据和运行结果。
+变化：TM-002 无服务业务写入；仅真实 TM-001 认证可改变 sessions/audit；本机来源记录依本例步骤变化。
+核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
+      </x:c>
+      <x:c r="I83" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J83" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K83" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L83" s="4" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:23</x:v>
+      </x:c>
+      <x:c r="M83" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N83" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="102" customHeight="1">
+      <x:c r="A84" s="9" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B84" s="9" t="str">
+        <x:v>E2E-TM002-002</x:v>
+      </x:c>
+      <x:c r="C84" s="9" t="str">
+        <x:v>撤销、失效与重新选择</x:v>
+      </x:c>
+      <x:c r="D84" s="9" t="str">
+        <x:v>TASK-TM002-PICKER
+TASK-TM002-ACCESS</x:v>
+      </x:c>
+      <x:c r="E84" s="9" t="str">
+        <x:v>product_e2e_group</x:v>
+      </x:c>
+      <x:c r="F84" s="9" t="str">
+        <x:v>system_permissions自有A/B；分别用UI移除、POSIX chmod 000、同路径新inode、原生面板取消/重选构造独立输入。</x:v>
+      </x:c>
+      <x:c r="G84" s="9" t="str">
+        <x:v>逐条子TC核对真实面板、App来源范围控制、撤销/失效/恢复；不声明沙盒或TCC授权。</x:v>
+      </x:c>
+      <x:c r="H84" s="9" t="str">
+        <x:v>准备：独占动态回环服务、隔离 SQLite、seed=42 合成 Alice/Bob 与本例 A/B；场景组只汇总子TC；每条子TC独占数据和运行结果。
+变化：TM-002 无服务业务写入；仅真实 TM-001 认证可改变 sessions/audit；本机来源记录依本例步骤变化。
+核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
+      </x:c>
+      <x:c r="I84" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J84" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K84" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L84" s="9" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:227</x:v>
+      </x:c>
+      <x:c r="M84" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N84" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="117" customHeight="1">
+      <x:c r="A85" s="4" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B85" s="4" t="str">
+        <x:v>TC-TM002-SELECT-01</x:v>
+      </x:c>
+      <x:c r="C85" s="4" t="str">
+        <x:v>首次从原生面板选择 A</x:v>
+      </x:c>
+      <x:c r="D85" s="4" t="str">
+        <x:v>TASK-TM002-PICKER</x:v>
+      </x:c>
+      <x:c r="E85" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F85" s="4" t="str">
+        <x:v>全新 profile、S1 的 Alice 已真实登录且经身份验证；A/B 如共同 fixture，尚无已确认来源。实际输入为工具 codex、原生目录面板中的 A。</x:v>
+      </x:c>
+      <x:c r="G85" s="4" t="str">
+        <x:v>UI 出现等待系统选择状态；observer 见原生 showOpenDialog 被调用一次。文件 F0；网络/DB ND0。
+UI 进入待确认/可预览状态，只显示 A 的安全标签，不显示绝对路径；observer 记录面板未取消且选择标签 A。文件 FR；网络/DB ND0。
+UI 没有“已授权采集”状态；主进程尚未建立已确认来源的读取 allowlist，私有已确认 sources 记录不存在，B 无访问，A 原始文件 SHA256 与初始清单一致；网络/DB ND0。</x:v>
+      </x:c>
+      <x:c r="H85" s="4" t="str">
+        <x:v>准备：独占动态回环服务、隔离 SQLite、seed=42 合成 Alice/Bob 与本例 A/B；R；账号 SQL 及只读核对见共同 ND 定义；TM-002 不写服务 DB。独立 expected 为“暂选 A、确认记录仍无”。
+变化：TM-002 无服务业务写入；仅真实 TM-001 认证可改变 sessions/audit；本机来源记录依本例步骤变化。
+核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
+      </x:c>
+      <x:c r="I85" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J85" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K85" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L85" s="4" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:40</x:v>
+      </x:c>
+      <x:c r="M85" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N85" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="132" customHeight="1">
+      <x:c r="A86" s="9" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B86" s="9" t="str">
+        <x:v>TC-TM002-SELECT-02</x:v>
+      </x:c>
+      <x:c r="C86" s="9" t="str">
+        <x:v>面板取消保留当前来源状态</x:v>
+      </x:c>
+      <x:c r="D86" s="9" t="str">
+        <x:v>TASK-TM002-PICKER</x:v>
+      </x:c>
+      <x:c r="E86" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F86" s="9" t="str">
+        <x:v>三个独立 profile/运行：#FIRST_CANCEL 无来源且真实面板取消；#CONFIRMED_CANCEL 已确认 Codex A true/false 后再次真实面板取消；#REPLACE_CONFIRMED 同一 S1/Alice/codex 先确认 A，真实面板选择 B 并原子确认新根。</x:v>
+      </x:c>
+      <x:c r="G86" s="9" t="str">
+        <x:v>UI 保持当前引导、等待面板；observer 见 showOpenDialog 一次。文件 F0；网络/DB ND0。
+UI 返回需要选择，不显示候选/成功授权，也不崩溃；observer 见 canceled=true、空选中集合。文件 F0；网络/DB ND0。
+UI 仍为无来源；没有 sources 记录、A/B 文件操作或隐式扫描；网络/DB NDA 仅允许 /v1/me。</x:v>
+      </x:c>
+      <x:c r="H86" s="9" t="str">
+        <x:v>准备：三变体各自 R、隔离 SQLite、seed=42 合成 Alice/Bob 与 A/B；共同账号 SQL。#FIRST_CANCEL 无来源；#CONFIRMED_CANCEL 保留旧 A；#REPLACE_CONFIRMED 原子替换为 B，独立 expected 仅 B1。TM-002 无业务 DB 写入。
+变化：TM-002 无服务业务写入；仅真实 TM-001 认证可改变 sessions/audit；本机来源记录依本例步骤变化。
+核验：先执行 Q-TM002-USERS；只读比较 sessions/audit、网络 ND0/NDA、本例私有来源密文摘要与 A/B 根身份。#REPLACE_CONFIRMED 另按原子提交时间比较旧 A 停读和新 B 唯一候选；不直接向 DB 写来源状态。</x:v>
+      </x:c>
+      <x:c r="I86" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J86" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K86" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L86" s="9" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:51</x:v>
+      </x:c>
+      <x:c r="M86" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N86" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="132" customHeight="1">
+      <x:c r="A87" s="4" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B87" s="4" t="str">
+        <x:v>TC-TM002-SELECT-02#FIRST_CANCEL</x:v>
+      </x:c>
+      <x:c r="C87" s="4" t="str">
+        <x:v>面板取消保留当前来源状态 · 变体</x:v>
+      </x:c>
+      <x:c r="D87" s="4" t="str">
+        <x:v>TASK-TM002-PICKER</x:v>
+      </x:c>
+      <x:c r="E87" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F87" s="4" t="str">
+        <x:v>无来源；打开 Codex 原生目录面板并点击“取消”。</x:v>
+      </x:c>
+      <x:c r="G87" s="4" t="str">
+        <x:v>重启经 /v1/me 后仍无来源和 sources 记录，A/B 零访问。</x:v>
+      </x:c>
+      <x:c r="H87" s="4" t="str">
+        <x:v>准备：三变体各自 R、隔离 SQLite、seed=42 合成 Alice/Bob 与 A/B；共同账号 SQL。#FIRST_CANCEL 无来源；#CONFIRMED_CANCEL 保留旧 A；#REPLACE_CONFIRMED 原子替换为 B，独立 expected 仅 B1。TM-002 无业务 DB 写入。
+变化：TM-002 无服务业务写入；仅真实 TM-001 认证可改变 sessions/audit；本机来源记录依本例步骤变化。
+核验：先执行 Q-TM002-USERS；只读比较 sessions/audit、网络 ND0/NDA、本例私有来源密文摘要与 A/B 根身份。#REPLACE_CONFIRMED 另按原子提交时间比较旧 A 停读和新 B 唯一候选；不直接向 DB 写来源状态。</x:v>
+      </x:c>
+      <x:c r="I87" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J87" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K87" s="4" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L87" s="4" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:51</x:v>
+      </x:c>
+      <x:c r="M87" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N87" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="132" customHeight="1">
+      <x:c r="A88" s="9" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B88" s="9" t="str">
+        <x:v>TC-TM002-SELECT-02#CONFIRMED_CANCEL</x:v>
+      </x:c>
+      <x:c r="C88" s="9" t="str">
+        <x:v>面板取消保留当前来源状态 · 变体</x:v>
+      </x:c>
+      <x:c r="D88" s="9" t="str">
+        <x:v>TASK-TM002-PICKER</x:v>
+      </x:c>
+      <x:c r="E88" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F88" s="9" t="str">
+        <x:v>已确认 A 的 true/false 并刷新 A1/A2；“更换来源”面板点击“取消”。</x:v>
+      </x:c>
+      <x:c r="G88" s="9" t="str">
+        <x:v>旧 A confirmed_enabled、true/false、根身份与密文记录摘要不变；重启显式刷新仍仅 A1/A2，B 零访问。</x:v>
+      </x:c>
+      <x:c r="H88" s="9" t="str">
+        <x:v>准备：三变体各自 R、隔离 SQLite、seed=42 合成 Alice/Bob 与 A/B；共同账号 SQL。#FIRST_CANCEL 无来源；#CONFIRMED_CANCEL 保留旧 A；#REPLACE_CONFIRMED 原子替换为 B，独立 expected 仅 B1。TM-002 无业务 DB 写入。
+变化：TM-002 无服务业务写入；仅真实 TM-001 认证可改变 sessions/audit；本机来源记录依本例步骤变化。
+核验：先执行 Q-TM002-USERS；只读比较 sessions/audit、网络 ND0/NDA、本例私有来源密文摘要与 A/B 根身份。#REPLACE_CONFIRMED 另按原子提交时间比较旧 A 停读和新 B 唯一候选；不直接向 DB 写来源状态。</x:v>
+      </x:c>
+      <x:c r="I88" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J88" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K88" s="9" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L88" s="9" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:51</x:v>
+      </x:c>
+      <x:c r="M88" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N88" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="132" customHeight="1">
+      <x:c r="A89" s="4" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B89" s="4" t="str">
+        <x:v>TC-TM002-SELECT-02#REPLACE_CONFIRMED</x:v>
+      </x:c>
+      <x:c r="C89" s="4" t="str">
+        <x:v>面板取消保留当前来源状态 · 变体</x:v>
+      </x:c>
+      <x:c r="D89" s="4" t="str">
+        <x:v>TASK-TM002-PICKER</x:v>
+      </x:c>
+      <x:c r="E89" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F89" s="4" t="str">
+        <x:v>S1/Alice/codex 已经通过真实面板确认 A true/false 并刷新 A1/A2；再由真实面板选 B 并明确确认 true/false。</x:v>
+      </x:c>
+      <x:c r="G89" s="4" t="str">
+        <x:v>新根 B 原子确认后唯一候选为 sessions/2026/10/01/b-01.jsonl；旧 A 扫描/游标/读取能力与未提交结果失效，提交后 A 全操作零；重启仅恢复 B，服务 DB 无 TM-002 写入。</x:v>
+      </x:c>
+      <x:c r="H89" s="4" t="str">
+        <x:v>准备：三变体各自 R、隔离 SQLite、seed=42 合成 Alice/Bob 与 A/B；共同账号 SQL。#FIRST_CANCEL 无来源；#CONFIRMED_CANCEL 保留旧 A；#REPLACE_CONFIRMED 原子替换为 B，独立 expected 仅 B1。TM-002 无业务 DB 写入。
+变化：TM-002 无服务业务写入；仅真实 TM-001 认证可改变 sessions/audit；本机来源记录依本例步骤变化。
+核验：先执行 Q-TM002-USERS；只读比较 sessions/audit、网络 ND0/NDA、本例私有来源密文摘要与 A/B 根身份。#REPLACE_CONFIRMED 另按原子提交时间比较旧 A 停读和新 B 唯一候选；不直接向 DB 写来源状态。</x:v>
+      </x:c>
+      <x:c r="I89" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J89" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K89" s="4" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L89" s="4" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:51</x:v>
+      </x:c>
+      <x:c r="M89" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N89" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="132" customHeight="1">
+      <x:c r="A90" s="9" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B90" s="9" t="str">
+        <x:v>TC-TM002-SELECT-04</x:v>
+      </x:c>
+      <x:c r="C90" s="9" t="str">
+        <x:v>Claude Code 来源选择、预览、确认与恢复</x:v>
+      </x:c>
+      <x:c r="D90" s="9" t="str">
+        <x:v>TASK-TM002-PICKER
+TASK-TM002-PREVIEW
+TASK-TM002-CONSENT
+TASK-TM002-STORE</x:v>
+      </x:c>
+      <x:c r="E90" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F90" s="9" t="str">
+        <x:v>全新 profile，S1 Alice 真实登录并已验证身份；独占 Claude A 只含 C1=projects/sample/claude-01.jsonl（31 B、固定 mtime）与非候选 projects/sample/readme.txt（内容 README 加换行，共 7 B），未选 B 含 projects/sample/claude-b-01.jsonl（31 B、标记 PRIVATE_CLAUDE_B）。工具输入为 claude_code，采集=true，未来同步意愿保留默认 false；两个根均为本例合成数据。</x:v>
+      </x:c>
+      <x:c r="G90" s="9" t="str">
+        <x:v>UI 进入待确认；observer 见 showOpenDialog 一次并返回 A 标签；文件 FR、B 零访问，网络/DB ND0。
+UI 候选集合恰为 {C1}，相对路径 projects/sample/claude-01.jsonl、大小 31 B 和固定 mtime 与独立清单一致，不出现 B 的候选、完整根路径或 PRIVATE_CLAUDE_1/B；文件 FP 且正文 open/read=0，B 全操作=0；网络/DB ND0。
+UI 显示 claude_code 来源 confirmed_enabled 与 true/false；私有 sources 记录首次写入 S1/Alice/claude_code 的确认态，B 与服务 DB 不变；文件仅允许确认后的 FE，网络/DB ND0。
+UI 仍显示 claude_code、true/false，候选集合恰为 {C1}；文件 FE 只读 Claude A 元数据、B 零访问，不上传正文、路径或用量；网络/DB NDA 仅允许 /v1/me。</x:v>
+      </x:c>
+      <x:c r="H90" s="9" t="str">
+        <x:v>准备：独占动态回环服务、隔离 SQLite、seed=42 合成 Alice/Bob 与本例 A/B；R；共同账号 SQL 只准备 Alice/Bob，TM-002 无业务 DB 写入。独立 expected 为预览集合 {C1}、确认态 true/false、重启后相同来源；只验证递归 .jsonl 元数据候选，不验证 Claude Code 原始日志解析或用量。
+变化：TM-002 无服务业务写入；仅真实 TM-001 认证可改变 sessions/audit；本机来源记录依本例步骤变化。
+核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
+      </x:c>
+      <x:c r="I90" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J90" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K90" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L90" s="9" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:72</x:v>
+      </x:c>
+      <x:c r="M90" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N90" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="117" customHeight="1">
+      <x:c r="A91" s="4" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B91" s="4" t="str">
+        <x:v>TC-TM002-PREVIEW-01</x:v>
+      </x:c>
+      <x:c r="C91" s="4" t="str">
+        <x:v>只显示 A 的候选元数据</x:v>
+      </x:c>
+      <x:c r="D91" s="4" t="str">
+        <x:v>TASK-TM002-PREVIEW</x:v>
+      </x:c>
+      <x:c r="E91" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F91" s="4" t="str">
+        <x:v>S1 Alice 真实面板暂选 A，尚未确认；A 有相对路径 A1/A2 与 sessions/2026/10/01/ignore.txt，B 有 B1。递归 .jsonl 规则使 A1/A2 为候选，B1 与 ignore.txt 不在候选中。</x:v>
+      </x:c>
+      <x:c r="G91" s="4" t="str">
+        <x:v>UI 出现两个候选条目，无 b-01/ignore；文件 FP 只允许 A 的显式元数据枚举；网络/DB ND0。
+两个候选的相对名/大小/时间与独立清单一致，既不显示绝对根路径，也不显示 PRIVATE_A1/PRIVATE_A2/PRIVATE_B1；文件正文 open/read 为零；网络/DB ND0。
+仍无已确认 sources 记录，无 B 访问，A/B 文件 SHA256 不变；网络/DB ND0。</x:v>
+      </x:c>
+      <x:c r="H91" s="4" t="str">
+        <x:v>准备：独占动态回环服务、隔离 SQLite、seed=42 合成 Alice/Bob 与本例 A/B；R；共同账号 SQL；TM-002 无业务 DB 操作。独立清单恰有两个候选，相对路径 A1 和 A2，大小均 25 B、mtime=2026-10-01T00:00:00Z；显示格式未定时按可访问元数据值比较。
+变化：TM-002 无服务业务写入；仅真实 TM-001 认证可改变 sessions/audit；本机来源记录依本例步骤变化。
+核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
+      </x:c>
+      <x:c r="I91" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J91" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K91" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L91" s="4" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:84</x:v>
+      </x:c>
+      <x:c r="M91" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N91" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="117" customHeight="1">
+      <x:c r="A92" s="9" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B92" s="9" t="str">
+        <x:v>TC-TM002-PREVIEW-02</x:v>
+      </x:c>
+      <x:c r="C92" s="9" t="str">
+        <x:v>非候选文件不充当日志</x:v>
+      </x:c>
+      <x:c r="D92" s="9" t="str">
+        <x:v>TASK-TM002-PREVIEW</x:v>
+      </x:c>
+      <x:c r="E92" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F92" s="9" t="str">
+        <x:v>S1 Alice 选 A；本例 A 只生成 sessions/2026/10/01/ignore.txt（12 B），不生成 A1/A2、文件 symlink 或目录 symlink；B 仍有 B1。所有变化仅作用于运行 App 前的本例自有 fixture。</x:v>
+      </x:c>
+      <x:c r="G92" s="9" t="str">
+        <x:v>UI 为待确认；文件 FR 只允许选中 A 的根元数据校验，B 零访问；网络/DB ND0。
+UI 显示“0 个候选文件”空态并与读取失败区分；ignore.txt 与 B1 均不列入，未出现 PRIVATE_B1；文件 FP，无正文读取；网络/DB ND0。
+UI 可以显示已确认且当前无候选，非权限错误；受控刷新仍返回空集合，来源记录仅在确认后出现；文件 FE，网络/DB ND0。</x:v>
+      </x:c>
+      <x:c r="H92" s="9" t="str">
+        <x:v>准备：独占动态回环服务、隔离 SQLite、seed=42 合成 Alice/Bob 与本例 A/B；R；共同账号 SQL；TM-002 无业务 DB 操作。独立 expected 候选集合为空；需求草稿允许确认空目录等待未来文件。
+变化：TM-002 无服务业务写入；仅真实 TM-001 认证可改变 sessions/audit；本机来源记录依本例步骤变化。
+核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
+      </x:c>
+      <x:c r="I92" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J92" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K92" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L92" s="9" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:95</x:v>
+      </x:c>
+      <x:c r="M92" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N92" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="117" customHeight="1">
+      <x:c r="A93" s="4" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B93" s="4" t="str">
+        <x:v>TC-TM002-PREVIEW-03</x:v>
+      </x:c>
+      <x:c r="C93" s="4" t="str">
+        <x:v>符号链接不能逸出选中根</x:v>
+      </x:c>
+      <x:c r="D93" s="4" t="str">
+        <x:v>TASK-TM002-PREVIEW</x:v>
+      </x:c>
+      <x:c r="E93" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F93" s="4" t="str">
+        <x:v>S1 Alice 选 A；A 中同层文件 symlink sessions/2026/10/01/link-out.jsonl 与目录 symlink sessions/2026/10/01/escape 指向本例 B；A1/A2 仍存在。</x:v>
+      </x:c>
+      <x:c r="G93" s="4" t="str">
+        <x:v>UI 候选集合恰为 {A1,A2}；文件 FP 允许对 A 内链接做 lstat，但不得跟随进入 B，也不得打开目标正文；网络/DB ND0。
+UI 不含 sessions/2026/10/01/link-out.jsonl、sessions/2026/10/01/escape/b-01.jsonl 或 B1；B 的 stat/readdir/open/read 均为零，PRIVATE_B1 未出现在 UI/报告；网络/DB ND0。
+UI 候选集合仍恰为 {A1,A2}；文件 FE，B 零访问，原始文件字节不变；网络/DB ND0。</x:v>
+      </x:c>
+      <x:c r="H93" s="4" t="str">
+        <x:v>准备：独占动态回环服务、隔离 SQLite、seed=42 合成 Alice/Bob 与本例 A/B；R；共同账号 SQL；TM-002 无业务 DB 操作。独立 expected 只含 A 的两个普通文件，拒绝 symlink 与 B。
+变化：TM-002 无服务业务写入；仅真实 TM-001 认证可改变 sessions/audit；本机来源记录依本例步骤变化。
+核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
+      </x:c>
+      <x:c r="I93" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J93" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K93" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L93" s="4" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:106</x:v>
+      </x:c>
+      <x:c r="M93" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N93" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="117" customHeight="1">
+      <x:c r="A94" s="9" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B94" s="9" t="str">
+        <x:v>TC-TM002-PREVIEW-04</x:v>
+      </x:c>
+      <x:c r="C94" s="9" t="str">
+        <x:v>枚举上限与“不完整”提示</x:v>
+      </x:c>
+      <x:c r="D94" s="9" t="str">
+        <x:v>TASK-TM002-PREVIEW</x:v>
+      </x:c>
+      <x:c r="E94" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F94" s="9" t="str">
+        <x:v>每个变体各用全新 S1 Alice、A/B、profile 和 run_id，真实面板选 A；A 的具体合成树由下述变体替代普通 A1/A2，B 保留未选 B1。CANDIDATES_1001 与 ENTRIES_5001 的独立预探针须证明深度未超限、正常枚举可在 2 秒内完成，才能归因于数量上限；否则该变体 BLOCKED。只操作本例自有根；上限固定为深度 8、最多 1000 候选、最多 5000 目录项、2 秒。所有预期清单在运行前固定；不借产品输出生成答案。</x:v>
+      </x:c>
+      <x:c r="G94" s="9" t="str">
+        <x:v>UI 待确认；observer 记录真实选中 A；文件 FR；网络/DB ND0。
+UI 候选、计数与不完整提示满足本变体独立预期；文件 FP、正文零读取、B 零访问；网络/DB ND0。
+UI 不把截断当完整空集；来源未确认且未落盘；网络/DB ND0。</x:v>
+      </x:c>
+      <x:c r="H94" s="9" t="str">
+        <x:v>准备：独占动态回环服务、隔离 SQLite、seed=42 合成 Alice/Bob 与本例 A/B；每变体使用 R 与共同账号 SQL；TM-002 无业务 DB 操作。每条变体都有独立 fixture manifest/expected/清理和原始结果；真实测试路径为计划中的共同产品 spec，automated_test=null。
+变化：TM-002 无服务业务写入；仅真实 TM-001 认证可改变 sessions/audit；本机来源记录依本例步骤变化。
+核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
+      </x:c>
+      <x:c r="I94" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J94" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K94" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L94" s="9" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:117</x:v>
+      </x:c>
+      <x:c r="M94" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N94" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="117" customHeight="1">
+      <x:c r="A95" s="4" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B95" s="4" t="str">
+        <x:v>TC-TM002-PREVIEW-04#CANDIDATES_1001</x:v>
+      </x:c>
+      <x:c r="C95" s="4" t="str">
+        <x:v>枚举上限与“不完整”提示 · 变体</x:v>
+      </x:c>
+      <x:c r="D95" s="4" t="str">
+        <x:v>TASK-TM002-PREVIEW</x:v>
+      </x:c>
+      <x:c r="E95" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F95" s="4" t="str">
+        <x:v>A 根直接放 c-0000.jsonl 至 c-1000.jsonl 共 1001 个普通文件，各内容为固定 3 B 的一行空 JSON 加换行，mtime 固定；无 symlink 或其他候选。</x:v>
+      </x:c>
+      <x:c r="G95" s="4" t="str">
+        <x:v>只显示字典序前1000条 c-0000.jsonl…c-0999.jsonl、计数1000及“不完整”；c-1000.jsonl/B1均不显示，正文零读取。</x:v>
+      </x:c>
+      <x:c r="H95" s="4" t="str">
+        <x:v>准备：独占动态回环服务、隔离 SQLite、seed=42 合成 Alice/Bob 与本例 A/B；每变体使用 R 与共同账号 SQL；TM-002 无业务 DB 操作。每条变体都有独立 fixture manifest/expected/清理和原始结果；真实测试路径为计划中的共同产品 spec，automated_test=null。
+变化：TM-002 无服务业务写入；仅真实 TM-001 认证可改变 sessions/audit；本机来源记录依本例步骤变化。
+核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
+      </x:c>
+      <x:c r="I95" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J95" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K95" s="4" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L95" s="4" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:117</x:v>
+      </x:c>
+      <x:c r="M95" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N95" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="117" customHeight="1">
+      <x:c r="A96" s="9" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B96" s="9" t="str">
+        <x:v>TC-TM002-PREVIEW-04#ENTRIES_5001</x:v>
+      </x:c>
+      <x:c r="C96" s="9" t="str">
+        <x:v>枚举上限与“不完整”提示 · 变体</x:v>
+      </x:c>
+      <x:c r="D96" s="9" t="str">
+        <x:v>TASK-TM002-PREVIEW</x:v>
+      </x:c>
+      <x:c r="E96" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F96" s="9" t="str">
+        <x:v>A 根直接放 n-0000.txt 至 n-5000.txt 共 5001 个非候选普通文件，无 .jsonl 或 symlink。</x:v>
+      </x:c>
+      <x:c r="G96" s="9" t="str">
+        <x:v>检查最多5000个目录项即停止，候选可为空但须标“不完整/尚未检查全部项目”；不能显示完整的0个日志。</x:v>
+      </x:c>
+      <x:c r="H96" s="9" t="str">
+        <x:v>准备：独占动态回环服务、隔离 SQLite、seed=42 合成 Alice/Bob 与本例 A/B；每变体使用 R 与共同账号 SQL；TM-002 无业务 DB 操作。每条变体都有独立 fixture manifest/expected/清理和原始结果；真实测试路径为计划中的共同产品 spec，automated_test=null。
+变化：TM-002 无服务业务写入；仅真实 TM-001 认证可改变 sessions/audit；本机来源记录依本例步骤变化。
+核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
+      </x:c>
+      <x:c r="I96" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J96" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K96" s="9" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L96" s="9" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:117</x:v>
+      </x:c>
+      <x:c r="M96" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N96" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" ht="117" customHeight="1">
+      <x:c r="A97" s="4" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B97" s="4" t="str">
+        <x:v>TC-TM002-PREVIEW-04#DEPTH_9</x:v>
+      </x:c>
+      <x:c r="C97" s="4" t="str">
+        <x:v>枚举上限与“不完整”提示 · 变体</x:v>
+      </x:c>
+      <x:c r="D97" s="4" t="str">
+        <x:v>TASK-TM002-PREVIEW</x:v>
+      </x:c>
+      <x:c r="E97" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F97" s="4" t="str">
+        <x:v>A 中 d1/d2/d3/d4/d5/d6/d7/at8.jsonl 位于相对文件深度 8，d1/d2/d3/d4/d5/d6/d7/d8/at9.jsonl 位于深度 9，各是固定 3 B 普通文件，无 symlink。</x:v>
+      </x:c>
+      <x:c r="G97" s="4" t="str">
+        <x:v>只显示深度8相对候选并标“不完整/深度截断”；深度9文件不显示、不读正文。</x:v>
+      </x:c>
+      <x:c r="H97" s="4" t="str">
+        <x:v>准备：独占动态回环服务、隔离 SQLite、seed=42 合成 Alice/Bob 与本例 A/B；每变体使用 R 与共同账号 SQL；TM-002 无业务 DB 操作。每条变体都有独立 fixture manifest/expected/清理和原始结果；真实测试路径为计划中的共同产品 spec，automated_test=null。
+变化：TM-002 无服务业务写入；仅真实 TM-001 认证可改变 sessions/audit；本机来源记录依本例步骤变化。
+核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
+      </x:c>
+      <x:c r="I97" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J97" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K97" s="4" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L97" s="4" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:117</x:v>
+      </x:c>
+      <x:c r="M97" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N97" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="117" customHeight="1">
+      <x:c r="A98" s="9" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B98" s="9" t="str">
+        <x:v>TC-TM002-CONSENT-01</x:v>
+      </x:c>
+      <x:c r="C98" s="9" t="str">
+        <x:v>预览不启动持续读取</x:v>
+      </x:c>
+      <x:c r="D98" s="9" t="str">
+        <x:v>TASK-TM002-CONSENT</x:v>
+      </x:c>
+      <x:c r="E98" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F98" s="9" t="str">
+        <x:v>S1 Alice 已通过真实面板暂选 A 并完成一次显式预览，尚未确认；随后固定 fixture 向 A 写 a-new、B 写 b-new，观察窗口为至少一个本版约定的后台补扫周期（当前设计明确 TM-002 无后台扫描）。</x:v>
+      </x:c>
+      <x:c r="G98" s="9" t="str">
+        <x:v>UI 仍为待确认；其后文件访问应停止于 FP 的显式动作，私有 sources 记录为空；网络/DB ND0。
+UI 不自动新增 AN 或显示采集完成；该窗口内 A/B readdir/stat/open/read/watch 均为零；网络/DB ND0。
+UI 回到无来源，a-new 不自动预览；A/B 无后台读取，未确认暂选未持久化；网络/DB NDA。</x:v>
+      </x:c>
+      <x:c r="H98" s="9" t="str">
+        <x:v>准备：独占动态回环服务、隔离 SQLite、seed=42 合成 Alice/Bob 与本例 A/B；R；共同账号 SQL；TM-002 无业务 DB 操作。独立 expected：确认前无 watcher、定时重枚举或持久来源记录；已完成的那次显式预览不算持续读取。
+变化：TM-002 无服务业务写入；仅真实 TM-001 认证可改变 sessions/audit；本机来源记录依本例步骤变化。
+核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
+      </x:c>
+      <x:c r="I98" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J98" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K98" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L98" s="9" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:127</x:v>
+      </x:c>
+      <x:c r="M98" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N98" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" ht="117" customHeight="1">
+      <x:c r="A99" s="4" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B99" s="4" t="str">
+        <x:v>TC-TM002-CONSENT-02</x:v>
+      </x:c>
+      <x:c r="C99" s="4" t="str">
+        <x:v>采集开启、未来同步关闭</x:v>
+      </x:c>
+      <x:c r="D99" s="4" t="str">
+        <x:v>TASK-TM002-CONSENT</x:v>
+      </x:c>
+      <x:c r="E99" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F99" s="4" t="str">
+        <x:v>S1 Alice 真实面板选 A；采集开关=true，未来同步意愿=false；确认后才由 fixture 写 a-new/b-new。</x:v>
+      </x:c>
+      <x:c r="G99" s="4" t="str">
+        <x:v>UI 两个控件值分别为 true/false；尚无确认记录，文件仅 FP 的显式预览，网络/DB ND0。
+UI 显示已确认且采集开启、同步关闭；私有来源记录第一次出现且两布尔值分别为 true/false，主进程只为 S1/Alice/codex 的 A 建立已确认读取 allowlist，证明默认同步=false 未被确认流程改写，A 文件未改；网络/DB ND0。
+UI 候选集合恰为 {A1,A2,AN}，每条相对路径各一次，B 不出现；主进程 allowlist 决策只允许 A，文件 FE 仅 A 元数据访问，正文零读取；无上传请求，网络/DB ND0。</x:v>
+      </x:c>
+      <x:c r="H99" s="4" t="str">
+        <x:v>准备：独占动态回环服务、隔离 SQLite、seed=42 合成 Alice/Bob 与本例 A/B；R；共同账号 SQL；TM-002 无业务 DB 操作。独立 expected 为 confirmed_enabled、true/false、候选只增加 A 的 a-new。
+变化：TM-002 无服务业务写入；仅真实 TM-001 认证可改变 sessions/audit；本机来源记录依本例步骤变化。
+核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
+      </x:c>
+      <x:c r="I99" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J99" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K99" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L99" s="4" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:138</x:v>
+      </x:c>
+      <x:c r="M99" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N99" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="117" customHeight="1">
+      <x:c r="A100" s="9" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B100" s="9" t="str">
+        <x:v>TC-TM002-CONSENT-03</x:v>
+      </x:c>
+      <x:c r="C100" s="9" t="str">
+        <x:v>采集关闭时两种未来同步意愿独立保存</x:v>
+      </x:c>
+      <x:c r="D100" s="9" t="str">
+        <x:v>TASK-TM002-CONSENT</x:v>
+      </x:c>
+      <x:c r="E100" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F100" s="9" t="str">
+        <x:v>两个独立全新 profile 中 S1 Alice 真实面板选择 A：#FALSE_TRUE 采集=false/未来同步=true；#FALSE_FALSE 采集=false/未来同步=false；均为 confirmed_paused。</x:v>
+      </x:c>
+      <x:c r="G100" s="9" t="str">
+        <x:v>UI 显示已确认但采集暂停，两个开关分别为该输入；私有记录保存该变体的 false/true 或 false/false，不建立刷新能力，文件 FS，网络/DB ND0。
+UI 保持暂停、不把“未读”显示为 0 候选；主进程来源能力仍为暂停，A/B 均无后续访问、无上传，文件 FS；网络/DB ND0。受限接口拒绝调用由辅助安全用例单独验证，不以本例直接 IPC 代替真实 UI。
+UI 仍为已确认暂停且显示本变体的两个布尔值；不自动读取 A/B，也不上传；文件 FS，网络/DB NDA。</x:v>
+      </x:c>
+      <x:c r="H100" s="9" t="str">
+        <x:v>准备：两变体各自 R、隔离 SQLite、seed=42 合成 Alice/Bob 与 A/B；共同账号 SQL。独立 expected 为 confirmed_paused false/true 和 false/false，均不读、不上传。TM-002 无业务 DB 操作。
+变化：TM-002 无服务业务写入；仅真实 TM-001 认证可改变 sessions/audit；本机来源记录依本例步骤变化。
+核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
+      </x:c>
+      <x:c r="I100" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J100" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K100" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L100" s="9" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:149</x:v>
+      </x:c>
+      <x:c r="M100" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N100" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="117" customHeight="1">
+      <x:c r="A101" s="4" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B101" s="4" t="str">
+        <x:v>TC-TM002-CONSENT-03#FALSE_TRUE</x:v>
+      </x:c>
+      <x:c r="C101" s="4" t="str">
+        <x:v>采集关闭时两种未来同步意愿独立保存 · 变体</x:v>
+      </x:c>
+      <x:c r="D101" s="4" t="str">
+        <x:v>TASK-TM002-CONSENT</x:v>
+      </x:c>
+      <x:c r="E101" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F101" s="4" t="str">
+        <x:v>S1 Alice 选 A，确认采集=false、未来同步=true。</x:v>
+      </x:c>
+      <x:c r="G101" s="4" t="str">
+        <x:v>confirmed_paused false/true；刷新控件不可用，A/B 零后续读取与上传，重启仍 false/true。</x:v>
+      </x:c>
+      <x:c r="H101" s="4" t="str">
+        <x:v>准备：两变体各自 R、隔离 SQLite、seed=42 合成 Alice/Bob 与 A/B；共同账号 SQL。独立 expected 为 confirmed_paused false/true 和 false/false，均不读、不上传。TM-002 无业务 DB 操作。
+变化：TM-002 无服务业务写入；仅真实 TM-001 认证可改变 sessions/audit；本机来源记录依本例步骤变化。
+核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
+      </x:c>
+      <x:c r="I101" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J101" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K101" s="4" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L101" s="4" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:149</x:v>
+      </x:c>
+      <x:c r="M101" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N101" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" ht="117" customHeight="1">
+      <x:c r="A102" s="9" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B102" s="9" t="str">
+        <x:v>TC-TM002-CONSENT-03#FALSE_FALSE</x:v>
+      </x:c>
+      <x:c r="C102" s="9" t="str">
+        <x:v>采集关闭时两种未来同步意愿独立保存 · 变体</x:v>
+      </x:c>
+      <x:c r="D102" s="9" t="str">
+        <x:v>TASK-TM002-CONSENT</x:v>
+      </x:c>
+      <x:c r="E102" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F102" s="9" t="str">
+        <x:v>另一个独立 profile 中 S1 Alice 选 A，确认采集=false、未来同步=false。</x:v>
+      </x:c>
+      <x:c r="G102" s="9" t="str">
+        <x:v>confirmed_paused false/false；刷新控件不可用，A/B 零后续读取与上传，重启仍 false/false。</x:v>
+      </x:c>
+      <x:c r="H102" s="9" t="str">
+        <x:v>准备：两变体各自 R、隔离 SQLite、seed=42 合成 Alice/Bob 与 A/B；共同账号 SQL。独立 expected 为 confirmed_paused false/true 和 false/false，均不读、不上传。TM-002 无业务 DB 操作。
+变化：TM-002 无服务业务写入；仅真实 TM-001 认证可改变 sessions/audit；本机来源记录依本例步骤变化。
+核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
+      </x:c>
+      <x:c r="I102" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J102" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K102" s="9" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L102" s="9" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:149</x:v>
+      </x:c>
+      <x:c r="M102" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N102" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" ht="147" customHeight="1">
+      <x:c r="A103" s="4" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B103" s="4" t="str">
+        <x:v>TC-TM002-CONSENT-04</x:v>
+      </x:c>
+      <x:c r="C103" s="4" t="str">
+        <x:v>两意愿均开启，本版仍不上传</x:v>
+      </x:c>
+      <x:c r="D103" s="4" t="str">
+        <x:v>TASK-TM002-CONSENT</x:v>
+      </x:c>
+      <x:c r="E103" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F103" s="4" t="str">
+        <x:v>三个独立 profile：#BOTH_TRUE 经真实面板确认 A true/true；#TURN_SYNC_OFF 从 true/true 经产品 UI 改成 true/false；#TURN_COLLECT_OFF_ON 从 true/false 经 updateSourceConsent UI 先改 false/false，再明确改回 true/false。TM-007 上传未交付。</x:v>
+      </x:c>
+      <x:c r="G103" s="4" t="str">
+        <x:v>UI 同时显示采集开启与未来同步意愿开启；私有记录为 true/true，A 原文不变；网络/DB ND0。
+UI 候选集合恰为 {A1,A2}，文件 FE；网络只允许 TM-001 认证流量，绝无用量、目录、路径或意愿上传；服务库无 TM-002 业务写入，ND0。
+UI 仍为 true/true，受控刷新集合恰为 {A1,A2} 且只读 A 元数据，B 零访问；网络/DB NDA，仍无上传。</x:v>
+      </x:c>
+      <x:c r="H103" s="4" t="str">
+        <x:v>准备：三变体各自 R、隔离 SQLite、seed=42 合成 Alice/Bob 与 A/B；共同账号 SQL。#BOTH_TRUE expected true/true；#TURN_SYNC_OFF expected true/false；#TURN_COLLECT_OFF_ON 两次完整布尔对原子持久为 false/false 再 true/false。TM-002 无服务业务写入。
+变化：TM-002 无服务业务写入；仅真实 TM-001 认证可改变 sessions/audit；本机来源记录依本例步骤变化。
+核验：先执行 Q-TM002-USERS；对照 sessions/audit、网络 ND0/NDA 与本例私有记录的完整布尔对、根身份/密文摘要。#TURN_COLLECT_OFF_ON 另核对旧扫描代际失效和恢复后仅 A；不向 DB 写来源状态。</x:v>
+      </x:c>
+      <x:c r="I103" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J103" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K103" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L103" s="4" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:160</x:v>
+      </x:c>
+      <x:c r="M103" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N103" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" ht="147" customHeight="1">
+      <x:c r="A104" s="9" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B104" s="9" t="str">
+        <x:v>TC-TM002-CONSENT-04#BOTH_TRUE</x:v>
+      </x:c>
+      <x:c r="C104" s="9" t="str">
+        <x:v>两意愿均开启，本版仍不上传 · 变体</x:v>
+      </x:c>
+      <x:c r="D104" s="9" t="str">
+        <x:v>TASK-TM002-CONSENT</x:v>
+      </x:c>
+      <x:c r="E104" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F104" s="9" t="str">
+        <x:v>确认 A 的采集=true、未来同步=true，显式刷新并重启。</x:v>
+      </x:c>
+      <x:c r="G104" s="9" t="str">
+        <x:v>confirmed_enabled true/true；刷新和重启后仅 A1/A2，未来同步意愿不触发用量、目录或意愿上传。</x:v>
+      </x:c>
+      <x:c r="H104" s="9" t="str">
+        <x:v>准备：三变体各自 R、隔离 SQLite、seed=42 合成 Alice/Bob 与 A/B；共同账号 SQL。#BOTH_TRUE expected true/true；#TURN_SYNC_OFF expected true/false；#TURN_COLLECT_OFF_ON 两次完整布尔对原子持久为 false/false 再 true/false。TM-002 无服务业务写入。
+变化：TM-002 无服务业务写入；仅真实 TM-001 认证可改变 sessions/audit；本机来源记录依本例步骤变化。
+核验：先执行 Q-TM002-USERS；对照 sessions/audit、网络 ND0/NDA 与本例私有记录的完整布尔对、根身份/密文摘要。#TURN_COLLECT_OFF_ON 另核对旧扫描代际失效和恢复后仅 A；不向 DB 写来源状态。</x:v>
+      </x:c>
+      <x:c r="I104" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J104" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K104" s="9" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L104" s="9" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:160</x:v>
+      </x:c>
+      <x:c r="M104" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N104" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" ht="147" customHeight="1">
+      <x:c r="A105" s="4" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B105" s="4" t="str">
+        <x:v>TC-TM002-CONSENT-04#TURN_SYNC_OFF</x:v>
+      </x:c>
+      <x:c r="C105" s="4" t="str">
+        <x:v>两意愿均开启，本版仍不上传 · 变体</x:v>
+      </x:c>
+      <x:c r="D105" s="4" t="str">
+        <x:v>TASK-TM002-CONSENT</x:v>
+      </x:c>
+      <x:c r="E105" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F105" s="4" t="str">
+        <x:v>独立 profile 确认 A 的 true/true 并刷新 A1/A2，随后 UI 保存 true/false。</x:v>
+      </x:c>
+      <x:c r="G105" s="4" t="str">
+        <x:v>同一已确认 A、true/false、根身份不变；密文 locator 仍可恢复，设置动作不扫描或上传；重启后仍刷新 A1/A2。允许安全重加密使密文字节变化。</x:v>
+      </x:c>
+      <x:c r="H105" s="4" t="str">
+        <x:v>准备：三变体各自 R、隔离 SQLite、seed=42 合成 Alice/Bob 与 A/B；共同账号 SQL。#BOTH_TRUE expected true/true；#TURN_SYNC_OFF expected true/false；#TURN_COLLECT_OFF_ON 两次完整布尔对原子持久为 false/false 再 true/false。TM-002 无服务业务写入。
+变化：TM-002 无服务业务写入；仅真实 TM-001 认证可改变 sessions/audit；本机来源记录依本例步骤变化。
+核验：先执行 Q-TM002-USERS；对照 sessions/audit、网络 ND0/NDA 与本例私有记录的完整布尔对、根身份/密文摘要。#TURN_COLLECT_OFF_ON 另核对旧扫描代际失效和恢复后仅 A；不向 DB 写来源状态。</x:v>
+      </x:c>
+      <x:c r="I105" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J105" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K105" s="4" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L105" s="4" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:160</x:v>
+      </x:c>
+      <x:c r="M105" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N105" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" ht="147" customHeight="1">
+      <x:c r="A106" s="9" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B106" s="9" t="str">
+        <x:v>TC-TM002-CONSENT-04#TURN_COLLECT_OFF_ON</x:v>
+      </x:c>
+      <x:c r="C106" s="9" t="str">
+        <x:v>两意愿均开启，本版仍不上传 · 变体</x:v>
+      </x:c>
+      <x:c r="D106" s="9" t="str">
+        <x:v>TASK-TM002-CONSENT</x:v>
+      </x:c>
+      <x:c r="E106" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F106" s="9" t="str">
+        <x:v>S1/Alice 真实面板确认 A true/false 并刷新 A1/A2；产品 UI 关闭采集保持同步 false，再明确开启采集。</x:v>
+      </x:c>
+      <x:c r="G106" s="9" t="str">
+        <x:v>关闭时 confirmed_paused false/false、旧扫描与未提交结果失效、刷新不可用且 A/B 后续零访问；再次开启后 confirmed_enabled true/false 且仅 A1/A2；两次完整布尔对原子持久，无上传。</x:v>
+      </x:c>
+      <x:c r="H106" s="9" t="str">
+        <x:v>准备：三变体各自 R、隔离 SQLite、seed=42 合成 Alice/Bob 与 A/B；共同账号 SQL。#BOTH_TRUE expected true/true；#TURN_SYNC_OFF expected true/false；#TURN_COLLECT_OFF_ON 两次完整布尔对原子持久为 false/false 再 true/false。TM-002 无服务业务写入。
+变化：TM-002 无服务业务写入；仅真实 TM-001 认证可改变 sessions/audit；本机来源记录依本例步骤变化。
+核验：先执行 Q-TM002-USERS；对照 sessions/audit、网络 ND0/NDA 与本例私有记录的完整布尔对、根身份/密文摘要。#TURN_COLLECT_OFF_ON 另核对旧扫描代际失效和恢复后仅 A；不向 DB 写来源状态。</x:v>
+      </x:c>
+      <x:c r="I106" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J106" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K106" s="9" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L106" s="9" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:160</x:v>
+      </x:c>
+      <x:c r="M106" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N106" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" ht="132" customHeight="1">
+      <x:c r="A107" s="4" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B107" s="4" t="str">
+        <x:v>TC-TM002-STATE-01</x:v>
+      </x:c>
+      <x:c r="C107" s="4" t="str">
+        <x:v>同账号重启的正常恢复与损坏密文停读</x:v>
+      </x:c>
+      <x:c r="D107" s="4" t="str">
+        <x:v>TASK-TM002-STORE</x:v>
+      </x:c>
+      <x:c r="E107" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F107" s="4" t="str">
+        <x:v>两个独立全新 profile/run_id、同一候选最终 DMG 安装后 App、S1 Alice 经真实面板确认 A true/false、TM-001 自动登录。#NORMAL_RESTORE 保留健康密文；#CORRUPT_LOCATOR 关闭 App 后经 owner/UID/0600/普通文件/无链接检查，将本例 sources 记录唯一 locator 密文字段原子替换为固定 Base64 AAEC（3 字节 00 01 02）。两变体用隔离代理屏障原样转发真实 /v1/me。</x:v>
+      </x:c>
+      <x:c r="G107" s="4" t="str">
+        <x:v>UI 进程退出；来源记录存在且归属 S1/Alice，目录/文件权限符合合同，A/B 内容 SHA256 不变；网络/DB ND0。
+隔离服务屏障已截住真实 FastAPI /v1/me 响应且尚未放行时，UI 不提前展示可读取 A 的已验证态；主进程未重建可用的来源 allowlist，文件 FS，无来源访问；网络/DB NDA 只允许该身份验证请求。
+UI 恢复 A、true/false 且非 B；主进程仅重建 S1/Alice 的 A 范围，文件 FE 只枚举 A，B 零访问；网络/DB NDA，无上传。</x:v>
+      </x:c>
+      <x:c r="H107" s="4" t="str">
+        <x:v>准备：两变体各自 R、独占动态回环服务与 SQLite、seed=42 合成 Alice/Bob/A/B，执行共同账号 SQL；真实 UI 确认 A。#CORRUPT_LOCATOR 仅在 App 退出和本例记录所有权/模式核对后故意损坏自有密文字段，绝不向 DB 写来源状态。
+变化：TM-002 无服务业务写入；真实 /v1/me 可产生既有 sessions/audit 副作用。#NORMAL_RESTORE 本机密文保持可恢复；#CORRUPT_LOCATOR 本机密文故意损坏后不可恢复且无读取能力。
+核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 与真实 /v1/me、网络 NDA、本例私有记录前后摘要和 A/B 文件访问审计；损坏注入不修改服务 DB。</x:v>
+      </x:c>
+      <x:c r="I107" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J107" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K107" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L107" s="4" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:189</x:v>
+      </x:c>
+      <x:c r="M107" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N107" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" ht="132" customHeight="1">
+      <x:c r="A108" s="9" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B108" s="9" t="str">
+        <x:v>TC-TM002-STATE-01#NORMAL_RESTORE</x:v>
+      </x:c>
+      <x:c r="C108" s="9" t="str">
+        <x:v>同账号重启的正常恢复与损坏密文停读 · 变体</x:v>
+      </x:c>
+      <x:c r="D108" s="9" t="str">
+        <x:v>TASK-TM002-STORE</x:v>
+      </x:c>
+      <x:c r="E108" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F108" s="9" t="str">
+        <x:v>独立 profile 中经真实面板确认 A true/false，保留健康 0600 密文；重启时以真实 /v1/me 屏障验证身份前后。</x:v>
+      </x:c>
+      <x:c r="G108" s="9" t="str">
+        <x:v>身份未验证前停读；真实 Alice /v1/me 200 后仅 A 的 true/false 与 A1/A2 恢复，B 零访问，无上传。</x:v>
+      </x:c>
+      <x:c r="H108" s="9" t="str">
+        <x:v>准备：两变体各自 R、独占动态回环服务与 SQLite、seed=42 合成 Alice/Bob/A/B，执行共同账号 SQL；真实 UI 确认 A。#CORRUPT_LOCATOR 仅在 App 退出和本例记录所有权/模式核对后故意损坏自有密文字段，绝不向 DB 写来源状态。
+变化：TM-002 无服务业务写入；真实 /v1/me 可产生既有 sessions/audit 副作用。#NORMAL_RESTORE 本机密文保持可恢复；#CORRUPT_LOCATOR 本机密文故意损坏后不可恢复且无读取能力。
+核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 与真实 /v1/me、网络 NDA、本例私有记录前后摘要和 A/B 文件访问审计；损坏注入不修改服务 DB。</x:v>
+      </x:c>
+      <x:c r="I108" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J108" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K108" s="9" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L108" s="9" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:189</x:v>
+      </x:c>
+      <x:c r="M108" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N108" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="132" customHeight="1">
+      <x:c r="A109" s="4" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B109" s="4" t="str">
+        <x:v>TC-TM002-STATE-01#CORRUPT_LOCATOR</x:v>
+      </x:c>
+      <x:c r="C109" s="4" t="str">
+        <x:v>同账号重启的正常恢复与损坏密文停读 · 变体</x:v>
+      </x:c>
+      <x:c r="D109" s="4" t="str">
+        <x:v>TASK-TM002-STORE</x:v>
+      </x:c>
+      <x:c r="E109" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F109" s="4" t="str">
+        <x:v>另一个独立 profile 经真实面板确认 A true/false、刷新 A1/A2、退出后仅将本例 locator 密文字段改为固定 Base64 AAEC；同一最终 DMG 重启并释放真实 /v1/me，随后真实面板重选取消。</x:v>
+      </x:c>
+      <x:c r="G109" s="4" t="str">
+        <x:v>身份验证前无来源能力；损坏密文导致 needs_reselect、刷新不可用、旧 A 不恢复且 A/B 后续零访问；取消重选及再次重启仍停读，不把未读显示完整 0 个，不泄漏路径/密文。</x:v>
+      </x:c>
+      <x:c r="H109" s="4" t="str">
+        <x:v>准备：两变体各自 R、独占动态回环服务与 SQLite、seed=42 合成 Alice/Bob/A/B，执行共同账号 SQL；真实 UI 确认 A。#CORRUPT_LOCATOR 仅在 App 退出和本例记录所有权/模式核对后故意损坏自有密文字段，绝不向 DB 写来源状态。
+变化：TM-002 无服务业务写入；真实 /v1/me 可产生既有 sessions/audit 副作用。#NORMAL_RESTORE 本机密文保持可恢复；#CORRUPT_LOCATOR 本机密文故意损坏后不可恢复且无读取能力。
+核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 与真实 /v1/me、网络 NDA、本例私有记录前后摘要和 A/B 文件访问审计；损坏注入不修改服务 DB。</x:v>
+      </x:c>
+      <x:c r="I109" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J109" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K109" s="4" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L109" s="4" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:189</x:v>
+      </x:c>
+      <x:c r="M109" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N109" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="117" customHeight="1">
+      <x:c r="A110" s="9" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B110" s="9" t="str">
+        <x:v>TC-TM002-STATE-02</x:v>
+      </x:c>
+      <x:c r="C110" s="9" t="str">
+        <x:v>同服务账号隔离</x:v>
+      </x:c>
+      <x:c r="D110" s="9" t="str">
+        <x:v>TASK-TM002-STORE</x:v>
+      </x:c>
+      <x:c r="E110" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F110" s="9" t="str">
+        <x:v>S1 Alice 已确认 A，true/false；S1 Bob 是 fixture 的另一个有效成员，尚无来源。</x:v>
+      </x:c>
+      <x:c r="G110" s="9" t="str">
+        <x:v>UI 返回登录；来源页不再可访问且后续刷新被拒绝；文件 FS；网络/DB NDA 允许 logout。
+UI 显示 Bob 无来源，A 名称、意愿与候选不可见；主进程拒绝 Bob 使用 Alice 的 A 来源能力，文件 FS，A/B 无访问；网络/DB NDA 允许 login/me。
+UI 只恢复 Alice 的 A 与 true/false；文件 FE 仅 Alice 主动刷新 A 后出现，B 无访问；网络/DB NDA。</x:v>
+      </x:c>
+      <x:c r="H110" s="9" t="str">
+        <x:v>准备：独占动态回环服务、隔离 SQLite、seed=42 合成 Alice/Bob 与本例 A/B；R；共同账号 SQL 验 Alice/Bob id；账号切换造成的 sessions/audit 变化按 NDA，TM-002 无业务 DB 操作。
+变化：TM-002 无服务业务写入；仅真实 TM-001 认证可改变 sessions/audit；本机来源记录依本例步骤变化。
+核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
+      </x:c>
+      <x:c r="I110" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J110" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K110" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L110" s="9" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:205</x:v>
+      </x:c>
+      <x:c r="M110" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N110" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" ht="102" customHeight="1">
+      <x:c r="A111" s="4" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B111" s="4" t="str">
+        <x:v>TC-TM002-STATE-03</x:v>
+      </x:c>
+      <x:c r="C111" s="4" t="str">
+        <x:v>同账号不同服务 origin 隔离</x:v>
+      </x:c>
+      <x:c r="D111" s="4" t="str">
+        <x:v>TASK-TM002-STORE</x:v>
+      </x:c>
+      <x:c r="E111" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F111" s="4" t="str">
+        <x:v>S1 Alice 已确认 A，true/false；S2 为另一个动态独占回环服务与 SQLite，可登录同 id Alice，但无来源。服务地址只经 TM-001 真实配置 UI 改动。</x:v>
+      </x:c>
+      <x:c r="G111" s="4" t="str">
+        <x:v>UI 不显示 S1 的 A/意愿；来源内存能力卸载，文件 FS，A/B 无访问；网络/DB NDA 仅目标 S2 认证。
+UI 显示 S2 无来源且无法刷新 S1 的 A；主进程拒绝将 S1/Alice 的 allowlist 用于 S2/Alice，文件 FS，无 A/B 访问；网络/DB ND0。
+UI 恢复 S1 的 A/true/false，文件 FE 仅 A；S2 的库与本地来源记录不接收 S1 路径或候选；网络/DB NDA。</x:v>
+      </x:c>
+      <x:c r="H111" s="4" t="str">
+        <x:v>准备：独占动态回环服务、隔离 SQLite、seed=42 合成 Alice/Bob 与本例 A/B；R；两个隔离库分别按共同账号 SQL 核验；配置与登录副作用按 NDA，TM-002 无业务 DB 操作。
+变化：TM-002 无服务业务写入；仅真实 TM-001 认证可改变 sessions/audit；本机来源记录依本例步骤变化。
+核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
+      </x:c>
+      <x:c r="I111" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J111" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K111" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L111" s="4" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:216</x:v>
+      </x:c>
+      <x:c r="M111" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N111" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" ht="102" customHeight="1">
+      <x:c r="A112" s="9" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B112" s="9" t="str">
+        <x:v>TC-TM002-SELECT-03</x:v>
+      </x:c>
+      <x:c r="C112" s="9" t="str">
+        <x:v>失效后选择面板取消</x:v>
+      </x:c>
+      <x:c r="D112" s="9" t="str">
+        <x:v>TASK-TM002-PICKER</x:v>
+      </x:c>
+      <x:c r="E112" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F112" s="9" t="str">
+        <x:v>S1 Alice 已确认 A，采集=true/同步=false；由本例 fixture 使 A 拒读并通过受控刷新进入 needs_reselect；本例保留 A 权限拒绝状态直到观察完成。输入为重新选择面板取消。</x:v>
+      </x:c>
+      <x:c r="G112" s="9" t="str">
+        <x:v>UI 显示需重新选择而非“0 个文件”；刷新已停止，后续文件 FS；网络/DB ND0。
+observer 见真实调用及 canceled=true；UI 返回需重新选择，不显示恢复成功；文件 FS；网络/DB ND0。
+UI 仍需重新选择且拒绝刷新；旧 locator 不被重新信任，A/B 无文件访问；网络/DB ND0。</x:v>
+      </x:c>
+      <x:c r="H112" s="9" t="str">
+        <x:v>准备：独占动态回环服务、隔离 SQLite、seed=42 合成 Alice/Bob 与本例 A/B；R 最终恢复 A 0700；共同账号 SQL，TM-002 无业务 DB 操作；expected 为 needs_reselect。
+变化：TM-002 无服务业务写入；仅真实 TM-001 认证可改变 sessions/audit；本机来源记录依本例步骤变化。
+核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
+      </x:c>
+      <x:c r="I112" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J112" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K112" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L112" s="9" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:243</x:v>
+      </x:c>
+      <x:c r="M112" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N112" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" ht="102" customHeight="1">
+      <x:c r="A113" s="4" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B113" s="4" t="str">
+        <x:v>TC-TM002-ACCESS-01</x:v>
+      </x:c>
+      <x:c r="C113" s="4" t="str">
+        <x:v>用户主动撤销来源</x:v>
+      </x:c>
+      <x:c r="D113" s="4" t="str">
+        <x:v>TASK-TM002-ACCESS</x:v>
+      </x:c>
+      <x:c r="E113" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F113" s="4" t="str">
+        <x:v>S1 Alice 已确认 A，true/false，能够受控刷新；记录 A/B 内容 SHA256。输入为 UI“移除来源”确认，以此撤销 App 对 A 的来源 allowlist 记录。</x:v>
+      </x:c>
+      <x:c r="G113" s="4" t="str">
+        <x:v>UI 变为需要选择；主进程立即撤销 A 的 allowlist 能力，后续刷新被拒绝，私有记录清除该来源 locator/意愿；文件 FS；网络/DB ND0。
+UI 不恢复旧来源、不显示 a-new；主进程拒绝原来源的刷新请求，A/B 无文件读取/监听，文件 FS；网络/DB ND0。
+UI 仍无来源；A/B 内容除 fixture 新增项外保持原样，旧 locator 不复活；文件 FS；网络/DB NDA。</x:v>
+      </x:c>
+      <x:c r="H113" s="4" t="str">
+        <x:v>准备：独占动态回环服务、隔离 SQLite、seed=42 合成 Alice/Bob 与本例 A/B；R；共同账号 SQL；TM-002 无业务 DB 操作。独立 expected 为 none、旧 locator 被清除。
+变化：TM-002 无服务业务写入；仅真实 TM-001 认证可改变 sessions/audit；本机来源记录依本例步骤变化。
+核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
+      </x:c>
+      <x:c r="I113" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J113" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K113" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L113" s="4" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:254</x:v>
+      </x:c>
+      <x:c r="M113" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N113" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" ht="117" customHeight="1">
+      <x:c r="A114" s="9" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B114" s="9" t="str">
+        <x:v>TC-TM002-ACCESS-02</x:v>
+      </x:c>
+      <x:c r="C114" s="9" t="str">
+        <x:v>POSIX 拒读后停止访问</x:v>
+      </x:c>
+      <x:c r="D114" s="9" t="str">
+        <x:v>TASK-TM002-ACCESS</x:v>
+      </x:c>
+      <x:c r="E114" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F114" s="9" t="str">
+        <x:v>S1 Alice 已确认 A，true/false；fixture 确认 A 初始 0700，可正常刷新；随后将自有 A chmod 000，并先以同 uid 的独立探针确认 readdir 被 OS 拒绝。若无法造成真实拒读，例为 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="G114" s="9" t="str">
+        <x:v>UI 候选集合恰为 {A1,A2}；文件 FE 仅 A 元数据，B 无访问；网络/DB ND0。
+UI 显示需重新选择/访问失效而非“0 个文件”，登录及配置页仍响应；访问尝试得到明确拒绝，主进程标记来源失效并撤销读取能力，停止后续刷新，B 零访问；网络/DB ND0。
+UI 仍需重新选择，不显示 a-new；文件 FS，A/B 后续访问为零；网络/DB ND0。</x:v>
+      </x:c>
+      <x:c r="H114" s="9" t="str">
+        <x:v>准备：独占动态回环服务、隔离 SQLite、seed=42 合成 Alice/Bob 与本例 A/B；R 必须在 finally 恢复 A 0700 并核对 owner marker；共同账号 SQL，TM-002 无业务 DB 操作。expected 为 needs_reselect。
+变化：TM-002 无服务业务写入；仅真实 TM-001 认证可改变 sessions/audit；本机来源记录依本例步骤变化。
+核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
+      </x:c>
+      <x:c r="I114" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J114" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K114" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L114" s="9" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:265</x:v>
+      </x:c>
+      <x:c r="M114" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N114" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" ht="117" customHeight="1">
+      <x:c r="A115" s="4" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B115" s="4" t="str">
+        <x:v>TC-TM002-ACCESS-03</x:v>
+      </x:c>
+      <x:c r="C115" s="4" t="str">
+        <x:v>同路径新 inode 不继承旧授权</x:v>
+      </x:c>
+      <x:c r="D115" s="4" t="str">
+        <x:v>TASK-TM002-ACCESS</x:v>
+      </x:c>
+      <x:c r="E115" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F115" s="4" t="str">
+        <x:v>S1 Alice 已确认 A，true/false，记录根设备号与 inode；fixture 仅在自有 runRoot 中把原 A 重命名为 A-old，并在原 A 路径新建不同 inode 目录及 a-new；原 A-old 仍有 A1/A2。</x:v>
+      </x:c>
+      <x:c r="G115" s="4" t="str">
+        <x:v>UI 候选集合恰为 {A1,A2}；文件 FE，B 无访问；网络/DB ND0。
+UI 显示需重新选择，不能把新 A 的 a-new 当作既有 App 来源授权；主进程发现根身份不符后标记来源失效并撤销原 allowlist 能力，新/旧 A 均不得有候选正文读取；网络/DB ND0。
+UI 仍需重新选择，既不显示新 A 的 a-new，也不自行追踪旧 A-old；后续文件 FS；网络/DB NDA 仅允许 /v1/me。</x:v>
+      </x:c>
+      <x:c r="H115" s="4" t="str">
+        <x:v>准备：独占动态回环服务、隔离 SQLite、seed=42 合成 Alice/Bob 与本例 A/B；R 清理时分别按 owner marker 验 A-new/A-old，不能跟随链接；共同账号 SQL，TM-002 无业务 DB 操作。独立 expected 为旧根身份失效、needs_reselect。
+变化：TM-002 无服务业务写入；仅真实 TM-001 认证可改变 sessions/audit；本机来源记录依本例步骤变化。
+核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
+      </x:c>
+      <x:c r="I115" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J115" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K115" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L115" s="4" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:276</x:v>
+      </x:c>
+      <x:c r="M115" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N115" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" ht="117" customHeight="1">
+      <x:c r="A116" s="9" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B116" s="9" t="str">
+        <x:v>TC-TM002-ACCESS-04</x:v>
+      </x:c>
+      <x:c r="C116" s="9" t="str">
+        <x:v>重启后取消重新选择仍停读</x:v>
+      </x:c>
+      <x:c r="D116" s="9" t="str">
+        <x:v>TASK-TM002-ACCESS</x:v>
+      </x:c>
+      <x:c r="E116" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F116" s="9" t="str">
+        <x:v>S1 Alice 已确认 A 后由本例 chmod 000 真实拒读，刷新进入 needs_reselect；fixture 随后恢复 A 0700，重启 App。与 SELECT-03 的即时取消不同，本例验证失效状态持久化与重启后的取消。</x:v>
+      </x:c>
+      <x:c r="G116" s="9" t="str">
+        <x:v>UI 仍显示需重新选择，没有自动候选；A/B 无来源读取，文件 FS；网络/DB NDA。
+observer 记录 canceled=true；UI 仍需重新选择，旧来源不启用；文件 FS；网络/DB ND0。
+UI 拒绝旧来源刷新，不显示 a-new；A/B 后续访问为零，文件 FS；网络/DB ND0。</x:v>
+      </x:c>
+      <x:c r="H116" s="9" t="str">
+        <x:v>准备：独占动态回环服务、隔离 SQLite、seed=42 合成 Alice/Bob 与本例 A/B；R；共同账号 SQL，TM-002 无业务 DB 操作。expected 为重启后 needs_reselect，取消后仍需重新选择。
+变化：TM-002 无服务业务写入；仅真实 TM-001 认证可改变 sessions/audit；本机来源记录依本例步骤变化。
+核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
+      </x:c>
+      <x:c r="I116" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J116" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K116" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L116" s="9" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:287</x:v>
+      </x:c>
+      <x:c r="M116" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N116" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" ht="132" customHeight="1">
+      <x:c r="A117" s="4" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B117" s="4" t="str">
+        <x:v>TC-TM002-ACCESS-05</x:v>
+      </x:c>
+      <x:c r="C117" s="4" t="str">
+        <x:v>真实重新选择并确认后恢复</x:v>
+      </x:c>
+      <x:c r="D117" s="4" t="str">
+        <x:v>TASK-TM002-ACCESS</x:v>
+      </x:c>
+      <x:c r="E117" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F117" s="4" t="str">
+        <x:v>S1 Alice 曾确认 A，随后 chmod 000 拒读进入 needs_reselect；本例 fixture 恢复 A 0700 并新增 a-new，B 仍有 b-01；不直接改私有来源记录。</x:v>
+      </x:c>
+      <x:c r="G117" s="4" t="str">
+        <x:v>observer 记录新的面板调用/选中 A；UI 仅进入待确认预览，尚未恢复采集；文件 FP，B 零访问；网络/DB ND0。
+UI 转 confirmed_enabled；私有来源记录更新为本次新 locator 与 true/false，旧失效能力不再可用；文件只允许确认后的 FE；网络/DB ND0。
+UI 候选集合恰为 {A1,A2,AN}，每条相对路径各一次，未列 B；文件 FE 仅 A 元数据，无正文打开/读取或 B 访问；网络/DB ND0。
+UI 仍为 confirmed_enabled 且候选集合恰为 {A1,A2,AN}，每条相对路径各一次；文件 FE，B 无访问；网络/DB NDA。</x:v>
+      </x:c>
+      <x:c r="H117" s="4" t="str">
+        <x:v>准备：独占动态回环服务、隔离 SQLite、seed=42 合成 Alice/Bob 与本例 A/B；R；共同账号 SQL；TM-002 无业务 DB 操作。独立 expected 为新确认后候选集合 {A1,A2,AN} 每条相对路径各一次，B 零。
+变化：TM-002 无服务业务写入；仅真实 TM-001 认证可改变 sessions/audit；本机来源记录依本例步骤变化。
+核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
+      </x:c>
+      <x:c r="I117" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J117" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K117" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L117" s="4" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:298</x:v>
+      </x:c>
+      <x:c r="M117" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N117" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" ht="87" customHeight="1">
+      <x:c r="A118" s="9" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B118" s="9" t="str">
+        <x:v>TC-TM002-LIMIT-01</x:v>
+      </x:c>
+      <x:c r="C118" s="9" t="str">
+        <x:v>2 秒枚举期限的固定时钟边界</x:v>
+      </x:c>
+      <x:c r="D118" s="9" t="str">
+        <x:v>TASK-TM002-PREVIEW</x:v>
+      </x:c>
+      <x:c r="E118" s="9" t="str">
+        <x:v>单元</x:v>
+      </x:c>
+      <x:c r="F118" s="9" t="str">
+        <x:v>仅在版本化单元测试中调用同一候选枚举算法，注入固定可控的单调时钟和只返回合成元数据的 FS adapter。根 A 的 adapter 按顺序提供普通相对候选 A1、A2；时钟读取序列固定为开始 0 ms、完成 A1 时 1999 ms、尝试 A2 前 2001 ms。最大枚举期限=2000 ms，深度8/1000候选/5000目录项均未触及；不调用原生面板、不启动安装后 App，也不访问用户文件。</x:v>
+      </x:c>
+      <x:c r="G118" s="9" t="str">
+        <x:v>UI 不适用，原因是单元边界测试；adapter 首项为 A1，内容 open/read 为零，无网络/DB 操作。
+结果只含相对路径 A1、25 B 与固定 mtime；A2 未进入结果，返回 incomplete=true、reason=timeout，不返回“完整 0 个”，无网络/DB 操作。
+此结果只证明算法对 2 秒期限的反应，不能冒充真实 macOS 目录或最终包 E2E。</x:v>
+      </x:c>
+      <x:c r="H118" s="9" t="str">
+        <x:v>准备：输入 A1/A2 与时间序列写在固定测试源码；仅内存 adapter，无服务/SQLite/本机来源记录，SQL 不适用。每例新建测试结果目录并清理本例所有的内存状态；模拟 adapter 不代替原生面板与 App 主进程范围控制的产品证据。
+变化：不适用：辅助检查不写服务业务库。
+核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
+      </x:c>
+      <x:c r="I118" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J118" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K118" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L118" s="9" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:312</x:v>
+      </x:c>
+      <x:c r="M118" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N118" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" ht="147" customHeight="1">
+      <x:c r="A119" s="4" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B119" s="4" t="str">
+        <x:v>TC-TM002-STORE-01</x:v>
+      </x:c>
+      <x:c r="C119" s="4" t="str">
+        <x:v>密文恢复或原子写入失败的安全状态</x:v>
+      </x:c>
+      <x:c r="D119" s="4" t="str">
+        <x:v>TASK-TM002-STORE</x:v>
+      </x:c>
+      <x:c r="E119" s="4" t="str">
+        <x:v>安全单元</x:v>
+      </x:c>
+      <x:c r="F119" s="4" t="str">
+        <x:v>三个独立自有 0700 profile/0600 sources 密文记录、合成 S1/Alice/A/B；#KEY_UNAVAILABLE 异步密钥能力不可用；#DECRYPT_FAIL A 密文解密 Promise 拒绝；#WRITE_FAIL_KEEP_OLD 先恢复健康旧 A 且 B 加密成功，仅在本例私有 sources 原子 temp write/rename 注入固定失败。使用真实来源存储/访问代码与受控 safeStorage/文件系统故障，不访问用户 Keychain。</x:v>
+      </x:c>
+      <x:c r="G119" s="4" t="str">
+        <x:v>UI 不适用，原因是存储单元测试；A/B 未访问、无网络/DB 操作。
+返回安全错误/需重新选择，不解密或信任记录、不建立读取能力；不能尝试从普通设置、日志或记录字段取明文目录路径；A/B readdir/stat/open/read/watch 为零，无网络/DB 操作。
+不得写入明文或弱化密文记录，也不得将来源标为已确认；对原记录的保留或安全清理由版本化存储合同决定，但不得产生可读取能力；保存脱敏错误码和文件摘要，无网络/DB 操作。</x:v>
+      </x:c>
+      <x:c r="H119" s="4" t="str">
+        <x:v>准备：三变体各自自有 0700 profile/0600 sources、合成 S1/Alice/A/B；前两变体受控 safeStorage 故障，#WRITE_FAIL_KEEP_OLD B 加密成功后仅 temp write/rename 失败且预置健康旧 A 原密文字节 SHA256。无服务/SQLite，SQL 不适用。
+变化：不适用：辅助安全单元不写服务数据库。前两变体密钥/解密故障停读需重选；#WRITE_FAIL_KEEP_OLD 仅原子私有记录写入失败且旧 A 健康时，原 A 密文、意愿、根与能力不变，B 不生效。
+核验：不适用：无 DB 连接或 SQL；核对 sources 0600/密文摘要、状态与 A/B 审计。#WRITE_FAIL_KEEP_OLD 核对 B 加密已成功、故障仅在私有写入阶段、失败临时文件不可恢复，随后旧 A 再刷新 A1/A2，原记录字节 SHA 不变。</x:v>
+      </x:c>
+      <x:c r="I119" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J119" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K119" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L119" s="4" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:323</x:v>
+      </x:c>
+      <x:c r="M119" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N119" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" ht="147" customHeight="1">
+      <x:c r="A120" s="9" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B120" s="9" t="str">
+        <x:v>TC-TM002-STORE-01#KEY_UNAVAILABLE</x:v>
+      </x:c>
+      <x:c r="C120" s="9" t="str">
+        <x:v>密文恢复或原子写入失败的安全状态 · 变体</x:v>
+      </x:c>
+      <x:c r="D120" s="9" t="str">
+        <x:v>TASK-TM002-STORE</x:v>
+      </x:c>
+      <x:c r="E120" s="9" t="str">
+        <x:v>安全单元</x:v>
+      </x:c>
+      <x:c r="F120" s="9" t="str">
+        <x:v>safeStorage 异步加密能力检查不可用；已预置 0600 密文记录。</x:v>
+      </x:c>
+      <x:c r="G120" s="9" t="str">
+        <x:v>恢复需重选/安全停读，A/B readdir/stat/open/read/watch 为零；确认新暂选 A 亦不得明文落盘或进入已确认态。</x:v>
+      </x:c>
+      <x:c r="H120" s="9" t="str">
+        <x:v>准备：三变体各自自有 0700 profile/0600 sources、合成 S1/Alice/A/B；前两变体受控 safeStorage 故障，#WRITE_FAIL_KEEP_OLD B 加密成功后仅 temp write/rename 失败且预置健康旧 A 原密文字节 SHA256。无服务/SQLite，SQL 不适用。
+变化：不适用：辅助安全单元不写服务数据库。前两变体密钥/解密故障停读需重选；#WRITE_FAIL_KEEP_OLD 仅原子私有记录写入失败且旧 A 健康时，原 A 密文、意愿、根与能力不变，B 不生效。
+核验：不适用：无 DB 连接或 SQL；核对 sources 0600/密文摘要、状态与 A/B 审计。#WRITE_FAIL_KEEP_OLD 核对 B 加密已成功、故障仅在私有写入阶段、失败临时文件不可恢复，随后旧 A 再刷新 A1/A2，原记录字节 SHA 不变。</x:v>
+      </x:c>
+      <x:c r="I120" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J120" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K120" s="9" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L120" s="9" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:323</x:v>
+      </x:c>
+      <x:c r="M120" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N120" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" ht="147" customHeight="1">
+      <x:c r="A121" s="4" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B121" s="4" t="str">
+        <x:v>TC-TM002-STORE-01#DECRYPT_FAIL</x:v>
+      </x:c>
+      <x:c r="C121" s="4" t="str">
+        <x:v>密文恢复或原子写入失败的安全状态 · 变体</x:v>
+      </x:c>
+      <x:c r="D121" s="4" t="str">
+        <x:v>TASK-TM002-STORE</x:v>
+      </x:c>
+      <x:c r="E121" s="4" t="str">
+        <x:v>安全单元</x:v>
+      </x:c>
+      <x:c r="F121" s="4" t="str">
+        <x:v>safeStorage 能力可用，decryptStringAsync 对预置密文以固定错误拒绝。</x:v>
+      </x:c>
+      <x:c r="G121" s="4" t="str">
+        <x:v>恢复需重选/安全停读；受控刷新拒绝且不报告“完整 0 个候选”；A/B 零访问，记录与诊断不含路径、明文或密文。</x:v>
+      </x:c>
+      <x:c r="H121" s="4" t="str">
+        <x:v>准备：三变体各自自有 0700 profile/0600 sources、合成 S1/Alice/A/B；前两变体受控 safeStorage 故障，#WRITE_FAIL_KEEP_OLD B 加密成功后仅 temp write/rename 失败且预置健康旧 A 原密文字节 SHA256。无服务/SQLite，SQL 不适用。
+变化：不适用：辅助安全单元不写服务数据库。前两变体密钥/解密故障停读需重选；#WRITE_FAIL_KEEP_OLD 仅原子私有记录写入失败且旧 A 健康时，原 A 密文、意愿、根与能力不变，B 不生效。
+核验：不适用：无 DB 连接或 SQL；核对 sources 0600/密文摘要、状态与 A/B 审计。#WRITE_FAIL_KEEP_OLD 核对 B 加密已成功、故障仅在私有写入阶段、失败临时文件不可恢复，随后旧 A 再刷新 A1/A2，原记录字节 SHA 不变。</x:v>
+      </x:c>
+      <x:c r="I121" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J121" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K121" s="4" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L121" s="4" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:323</x:v>
+      </x:c>
+      <x:c r="M121" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N121" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" ht="147" customHeight="1">
+      <x:c r="A122" s="9" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B122" s="9" t="str">
+        <x:v>TC-TM002-STORE-01#WRITE_FAIL_KEEP_OLD</x:v>
+      </x:c>
+      <x:c r="C122" s="9" t="str">
+        <x:v>密文恢复或原子写入失败的安全状态 · 变体</x:v>
+      </x:c>
+      <x:c r="D122" s="9" t="str">
+        <x:v>TASK-TM002-STORE</x:v>
+      </x:c>
+      <x:c r="E122" s="9" t="str">
+        <x:v>安全单元</x:v>
+      </x:c>
+      <x:c r="F122" s="9" t="str">
+        <x:v>本例旧 A 已确认 true/false 且密文可解、身份/根健康；受控 provider 暂选 B，B encryptStringAsync 成功，仅私有 sources 原子 temp write/rename 注入固定失败。</x:v>
+      </x:c>
+      <x:c r="G122" s="9" t="str">
+        <x:v>新 B 私有记录提交失败且 B 不生效；旧 A 来源/意愿/能力及原密文字节 SHA 完全不变，可再次刷新 A1/A2；失败临时文件不可恢复，B 只有选择根校验、无候选或正文读取。密钥不可用应走另一个停读变体。</x:v>
+      </x:c>
+      <x:c r="H122" s="9" t="str">
+        <x:v>准备：三变体各自自有 0700 profile/0600 sources、合成 S1/Alice/A/B；前两变体受控 safeStorage 故障，#WRITE_FAIL_KEEP_OLD B 加密成功后仅 temp write/rename 失败且预置健康旧 A 原密文字节 SHA256。无服务/SQLite，SQL 不适用。
+变化：不适用：辅助安全单元不写服务数据库。前两变体密钥/解密故障停读需重选；#WRITE_FAIL_KEEP_OLD 仅原子私有记录写入失败且旧 A 健康时，原 A 密文、意愿、根与能力不变，B 不生效。
+核验：不适用：无 DB 连接或 SQL；核对 sources 0600/密文摘要、状态与 A/B 审计。#WRITE_FAIL_KEEP_OLD 核对 B 加密已成功、故障仅在私有写入阶段、失败临时文件不可恢复，随后旧 A 再刷新 A1/A2，原记录字节 SHA 不变。</x:v>
+      </x:c>
+      <x:c r="I122" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J122" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K122" s="9" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L122" s="9" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:323</x:v>
+      </x:c>
+      <x:c r="M122" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N122" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" ht="192" customHeight="1">
+      <x:c r="A123" s="4" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B123" s="4" t="str">
+        <x:v>TC-TM002-ACCESS-06</x:v>
+      </x:c>
+      <x:c r="C123" s="4" t="str">
+        <x:v>内部分页游标完整性与失效</x:v>
+      </x:c>
+      <x:c r="D123" s="4" t="str">
+        <x:v>TASK-TM002-ACCESS</x:v>
+      </x:c>
+      <x:c r="E123" s="4" t="str">
+        <x:v>单元</x:v>
+      </x:c>
+      <x:c r="F123" s="4" t="str">
+        <x:v>三个独立变体各在真实 A 中建立 1201 个普通 3 B 候选：根文件 a.jsonl、目录文件 a/x.jsonl、根文件 p-0000.jsonl 至 p-1198.jsonl 共 1199 个；B1 未选。完整相对路径 UTF-8 字节序应为 a.jsonl、a/x.jsonl、随后 p-*，不能按根目录项原始名字 a/ 与 a.jsonl 排序。S1/Alice/codex 已确认、采集=true，生产 C helper/主进程在真实 A 上分页 pageSize=256；#PAGE_COMPLETION 同样使用真实 helper。#TREE_CHANGED 首页面后在真实 A 增加 p-0000a.jsonl，须由生产 C helper/主进程拒绝旧游标并新扫 1202 条；不用 FS adapter 自报版本。</x:v>
+      </x:c>
+      <x:c r="G123" s="4" t="str">
+        <x:v>UI 不适用，原因是内部单元能力；按完整相对路径排序返回 a.jsonl,a/x.jsonl,p-0000.jsonl…p-0253.jsonl 共 256 条及受限游标，complete=false；不得按根目录项 a/、a.jsonl 的原始顺序先给 a/x.jsonl。只读 A 元数据且 B 零访问；无网络/DB 操作。
+第 2 页恰为 p-0254…p-0509，第 3 页 p-0510…p-0765，第 4 页 p-0766…p-1021，各 256 条；第 5 页 p-1022…p-1198 共 177 条。单页均不超过 256，前四页 complete=false，只有第五页 complete=true 且无后续游标；不打开正文、B 零访问，无网络/DB 操作。
+五页恰为 256/256/256/256/177；合并的 1201 个完整相对名与运行前清单逐项相同且无重漏，a.jsonl 先于 a/x.jsonl，只有末页 complete=true；B 零访问、正文 open/read=0，UI 的 1000 项预览仍不完整。；无网络/DB 操作。</x:v>
+      </x:c>
+      <x:c r="H123" s="4" t="str">
+        <x:v>准备：三变体各自 R，在真实 A 根建普通 a.jsonl、0700 a/ 内普通 a/x.jsonl，以及 p-0000.jsonl 至 p-1198.jsonl 1199 个普通文件；1201 候选均固定 3 B/mtime，B1 未选，S1/Alice/codex 来源已确认。预先按完整相对路径 UTF-8 字节序计算旧树五页边界，#PAGE_COMPLETION 与 #TREE_CHANGED 均调用真实 A 上的生产 C helper/主进程。#TREE_CHANGED 首页面后向已遍历真实 A 根新增 p-0000a.jsonl，新树 1202 条；用生产 C helper/主进程，不用 FS adapter 自报版本。无服务/SQLite，SQL 不适用。
+变化：不适用：内部只读分页不写服务数据库；#REVOKE_CURSOR 删除本机来源密文，#TREE_CHANGED 仅向本例 A 新增 p-0000a.jsonl。
+核验：不适用：无 DB 连接或 SQL；以固定完整相对路径清单比较每页、游标、complete 与 A/B 审计。旧树必须 a.jsonl 先于 a/x.jsonl，后接 p-0000…p-1198，页边界 256/256/256/256/177。#TREE_CHANGED 旧游标 invalid/incomplete；新扫描五页 256/256/256/256/178、1202 名无重漏、p-0000a 总序第 4；只据真实目录和生产 helper/主进程判断。</x:v>
+      </x:c>
+      <x:c r="I123" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J123" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K123" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L123" s="4" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:342</x:v>
+      </x:c>
+      <x:c r="M123" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N123" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" ht="192" customHeight="1">
+      <x:c r="A124" s="9" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B124" s="9" t="str">
+        <x:v>TC-TM002-ACCESS-06#PAGE_COMPLETION</x:v>
+      </x:c>
+      <x:c r="C124" s="9" t="str">
+        <x:v>内部分页游标完整性与失效 · 变体</x:v>
+      </x:c>
+      <x:c r="D124" s="9" t="str">
+        <x:v>TASK-TM002-ACCESS</x:v>
+      </x:c>
+      <x:c r="E124" s="9" t="str">
+        <x:v>单元</x:v>
+      </x:c>
+      <x:c r="F124" s="9" t="str">
+        <x:v>真实 A 内根普通 a.jsonl、目录普通 a/x.jsonl、根内 p-0000.jsonl 至 p-1198.jsonl，共 1201 个固定 3 B 候选；生产 C helper/主进程在真实 A 上内部 pageSize=256，顺序提交受限游标。</x:v>
+      </x:c>
+      <x:c r="G124" s="9" t="str">
+        <x:v>完整相对路径 UTF-8 字节序先 a.jsonl、再 a/x.jsonl、再 p-*；五页 256/256/256/256/177，边界为首页至 p-0253、第二页 p-0254…p-0509、第三页 p-0510…p-0765、第四页 p-0766…p-1021、末页 p-1022…p-1198；前四页 complete=false，末页 complete=true，1201 名无重漏。UI 1000 条预览不能因此标完整。</x:v>
+      </x:c>
+      <x:c r="H124" s="9" t="str">
+        <x:v>准备：三变体各自 R，在真实 A 根建普通 a.jsonl、0700 a/ 内普通 a/x.jsonl，以及 p-0000.jsonl 至 p-1198.jsonl 1199 个普通文件；1201 候选均固定 3 B/mtime，B1 未选，S1/Alice/codex 来源已确认。预先按完整相对路径 UTF-8 字节序计算旧树五页边界，#PAGE_COMPLETION 与 #TREE_CHANGED 均调用真实 A 上的生产 C helper/主进程。#TREE_CHANGED 首页面后向已遍历真实 A 根新增 p-0000a.jsonl，新树 1202 条；用生产 C helper/主进程，不用 FS adapter 自报版本。无服务/SQLite，SQL 不适用。
+变化：不适用：内部只读分页不写服务数据库；#REVOKE_CURSOR 删除本机来源密文，#TREE_CHANGED 仅向本例 A 新增 p-0000a.jsonl。
+核验：不适用：无 DB 连接或 SQL；以固定完整相对路径清单比较每页、游标、complete 与 A/B 审计。旧树必须 a.jsonl 先于 a/x.jsonl，后接 p-0000…p-1198，页边界 256/256/256/256/177。#TREE_CHANGED 旧游标 invalid/incomplete；新扫描五页 256/256/256/256/178、1202 名无重漏、p-0000a 总序第 4；只据真实目录和生产 helper/主进程判断。</x:v>
+      </x:c>
+      <x:c r="I124" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J124" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K124" s="9" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L124" s="9" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:342</x:v>
+      </x:c>
+      <x:c r="M124" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N124" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" ht="192" customHeight="1">
+      <x:c r="A125" s="4" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B125" s="4" t="str">
+        <x:v>TC-TM002-ACCESS-06#REVOKE_CURSOR</x:v>
+      </x:c>
+      <x:c r="C125" s="4" t="str">
+        <x:v>内部分页游标完整性与失效 · 变体</x:v>
+      </x:c>
+      <x:c r="D125" s="4" t="str">
+        <x:v>TASK-TM002-ACCESS</x:v>
+      </x:c>
+      <x:c r="E125" s="4" t="str">
+        <x:v>单元</x:v>
+      </x:c>
+      <x:c r="F125" s="4" t="str">
+        <x:v>独立真实 A 初始 1201 候选，第一页按完整相对路径给 a.jsonl,a/x.jsonl,p-0000…p-0253；得到游标后经来源状态机撤销，再提交旧游标。</x:v>
+      </x:c>
+      <x:c r="G125" s="4" t="str">
+        <x:v>第一页 a.jsonl 必须先于 a/x.jsonl；撤销后旧游标拒绝、密文删除，A/B 无后续访问或余页，不能返回 complete=true，也不能把 256 条报告完整。</x:v>
+      </x:c>
+      <x:c r="H125" s="4" t="str">
+        <x:v>准备：三变体各自 R，在真实 A 根建普通 a.jsonl、0700 a/ 内普通 a/x.jsonl，以及 p-0000.jsonl 至 p-1198.jsonl 1199 个普通文件；1201 候选均固定 3 B/mtime，B1 未选，S1/Alice/codex 来源已确认。预先按完整相对路径 UTF-8 字节序计算旧树五页边界，#PAGE_COMPLETION 与 #TREE_CHANGED 均调用真实 A 上的生产 C helper/主进程。#TREE_CHANGED 首页面后向已遍历真实 A 根新增 p-0000a.jsonl，新树 1202 条；用生产 C helper/主进程，不用 FS adapter 自报版本。无服务/SQLite，SQL 不适用。
+变化：不适用：内部只读分页不写服务数据库；#REVOKE_CURSOR 删除本机来源密文，#TREE_CHANGED 仅向本例 A 新增 p-0000a.jsonl。
+核验：不适用：无 DB 连接或 SQL；以固定完整相对路径清单比较每页、游标、complete 与 A/B 审计。旧树必须 a.jsonl 先于 a/x.jsonl，后接 p-0000…p-1198，页边界 256/256/256/256/177。#TREE_CHANGED 旧游标 invalid/incomplete；新扫描五页 256/256/256/256/178、1202 名无重漏、p-0000a 总序第 4；只据真实目录和生产 helper/主进程判断。</x:v>
+      </x:c>
+      <x:c r="I125" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J125" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K125" s="4" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L125" s="4" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:342</x:v>
+      </x:c>
+      <x:c r="M125" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N125" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" ht="192" customHeight="1">
+      <x:c r="A126" s="9" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B126" s="9" t="str">
+        <x:v>TC-TM002-ACCESS-06#TREE_CHANGED</x:v>
+      </x:c>
+      <x:c r="C126" s="9" t="str">
+        <x:v>内部分页游标完整性与失效 · 变体</x:v>
+      </x:c>
+      <x:c r="D126" s="9" t="str">
+        <x:v>TASK-TM002-ACCESS</x:v>
+      </x:c>
+      <x:c r="E126" s="9" t="str">
+        <x:v>单元</x:v>
+      </x:c>
+      <x:c r="F126" s="9" t="str">
+        <x:v>独立真实 A 初始根普通 a.jsonl、目录普通 a/x.jsonl 与 p-0000…p-1198 共 1201 候选；生产 C helper/主进程首页按完整相对路径返回前 256 后，向已遍历真实 A 根加入 p-0000a.jsonl，使其在新树总序应为第 4。</x:v>
+      </x:c>
+      <x:c r="G126" s="9" t="str">
+        <x:v>旧游标必须 invalid/incomplete，不得混页或 complete=true；新扫描按完整相对路径先 a.jsonl、a/x.jsonl、p-0000、p-0000a，随后 p-*，共 1202 名、五页 256/256/256/256/178、无重漏，仅末页 complete=true；B 零访问。</x:v>
+      </x:c>
+      <x:c r="H126" s="9" t="str">
+        <x:v>准备：三变体各自 R，在真实 A 根建普通 a.jsonl、0700 a/ 内普通 a/x.jsonl，以及 p-0000.jsonl 至 p-1198.jsonl 1199 个普通文件；1201 候选均固定 3 B/mtime，B1 未选，S1/Alice/codex 来源已确认。预先按完整相对路径 UTF-8 字节序计算旧树五页边界，#PAGE_COMPLETION 与 #TREE_CHANGED 均调用真实 A 上的生产 C helper/主进程。#TREE_CHANGED 首页面后向已遍历真实 A 根新增 p-0000a.jsonl，新树 1202 条；用生产 C helper/主进程，不用 FS adapter 自报版本。无服务/SQLite，SQL 不适用。
+变化：不适用：内部只读分页不写服务数据库；#REVOKE_CURSOR 删除本机来源密文，#TREE_CHANGED 仅向本例 A 新增 p-0000a.jsonl。
+核验：不适用：无 DB 连接或 SQL；以固定完整相对路径清单比较每页、游标、complete 与 A/B 审计。旧树必须 a.jsonl 先于 a/x.jsonl，后接 p-0000…p-1198，页边界 256/256/256/256/177。#TREE_CHANGED 旧游标 invalid/incomplete；新扫描五页 256/256/256/256/178、1202 名无重漏、p-0000a 总序第 4；只据真实目录和生产 helper/主进程判断。</x:v>
+      </x:c>
+      <x:c r="I126" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J126" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K126" s="9" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L126" s="9" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:342</x:v>
+      </x:c>
+      <x:c r="M126" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N126" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" ht="87" customHeight="1">
+      <x:c r="A127" s="4" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B127" s="4" t="str">
+        <x:v>TC-TM002-SECURITY-01</x:v>
+      </x:c>
+      <x:c r="C127" s="4" t="str">
+        <x:v>renderer 不能传任意路径</x:v>
+      </x:c>
+      <x:c r="D127" s="4" t="str">
+        <x:v>TASK-TM002-ACCESS</x:v>
+      </x:c>
+      <x:c r="E127" s="4" t="str">
+        <x:v>安全单元</x:v>
+      </x:c>
+      <x:c r="F127" s="4" t="str">
+        <x:v>七个独立变体：四个恶意 IPC 参数分别为 B 绝对路径、B 的 file:// URL、../B/sessions/2026/10/01/b-01.jsonl、伪造 selectionId 00000000-0000-4000-8000-000000000099；三个受控竞态为过期选择、撤销期间刷新、切换账号期间刷新。全部只用自有 A/B 与同一主进程业务代码。</x:v>
+      </x:c>
+      <x:c r="G127" s="4" t="str">
+        <x:v>测试 UI 不适用，原因是本例为主进程参数安全层；A/B 文件未被读取，无网络/DB 操作。
+主进程返回安全错误码，不返回内容、绝对路径或 locator；不存在 renderer 任意文件读取 API，A/B open/read=0、B 元数据访问=0；无网络/DB 操作。
+四个恶意参数变体均未确认来源、未修改 A/B 字节；分别保存脱敏错误码和文件审计，不记录路径或 token；无网络/DB 操作。</x:v>
+      </x:c>
+      <x:c r="H127" s="4" t="str">
+        <x:v>准备：七变体各自 R 与独立 A/B/profile；仅内存主进程 handler、受控异步屏障和隔离文件；无服务/DB，SQL 不适用。四恶意参数安全拒绝，三竞态过期结果不提交。
+变化：不适用：辅助检查不写服务业务库。
+核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
+      </x:c>
+      <x:c r="I127" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J127" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K127" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L127" s="4" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:361</x:v>
+      </x:c>
+      <x:c r="M127" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N127" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" ht="72" customHeight="1">
+      <x:c r="A128" s="9" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B128" s="9" t="str">
+        <x:v>TC-TM002-SECURITY-01#ABSOLUTE</x:v>
+      </x:c>
+      <x:c r="C128" s="9" t="str">
+        <x:v>renderer 不能传任意路径 · 变体</x:v>
+      </x:c>
+      <x:c r="D128" s="9" t="str">
+        <x:v>TASK-TM002-ACCESS</x:v>
+      </x:c>
+      <x:c r="E128" s="9" t="str">
+        <x:v>安全单元</x:v>
+      </x:c>
+      <x:c r="F128" s="9" t="str">
+        <x:v>renderer传B绝对路径</x:v>
+      </x:c>
+      <x:c r="G128" s="9" t="str">
+        <x:v>主进程安全拒绝，不返回内容、绝对路径或 locator；B 元数据/open/read=0，sources 无确认记录。</x:v>
+      </x:c>
+      <x:c r="H128" s="9" t="str">
+        <x:v>准备：七变体各自 R 与独立 A/B/profile；仅内存主进程 handler、受控异步屏障和隔离文件；无服务/DB，SQL 不适用。四恶意参数安全拒绝，三竞态过期结果不提交。
+变化：不适用：辅助检查不写服务业务库。
+核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
+      </x:c>
+      <x:c r="I128" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J128" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K128" s="9" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L128" s="9" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:361</x:v>
+      </x:c>
+      <x:c r="M128" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N128" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" ht="72" customHeight="1">
+      <x:c r="A129" s="4" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B129" s="4" t="str">
+        <x:v>TC-TM002-SECURITY-01#FILE_URL</x:v>
+      </x:c>
+      <x:c r="C129" s="4" t="str">
+        <x:v>renderer 不能传任意路径 · 变体</x:v>
+      </x:c>
+      <x:c r="D129" s="4" t="str">
+        <x:v>TASK-TM002-ACCESS</x:v>
+      </x:c>
+      <x:c r="E129" s="4" t="str">
+        <x:v>安全单元</x:v>
+      </x:c>
+      <x:c r="F129" s="4" t="str">
+        <x:v>renderer传指向B的file:// URL</x:v>
+      </x:c>
+      <x:c r="G129" s="4" t="str">
+        <x:v>主进程安全拒绝，不返回内容、绝对路径或 locator；B 元数据/open/read=0，sources 无确认记录。</x:v>
+      </x:c>
+      <x:c r="H129" s="4" t="str">
+        <x:v>准备：七变体各自 R 与独立 A/B/profile；仅内存主进程 handler、受控异步屏障和隔离文件；无服务/DB，SQL 不适用。四恶意参数安全拒绝，三竞态过期结果不提交。
+变化：不适用：辅助检查不写服务业务库。
+核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
+      </x:c>
+      <x:c r="I129" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J129" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K129" s="4" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L129" s="4" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:361</x:v>
+      </x:c>
+      <x:c r="M129" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N129" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" ht="72" customHeight="1">
+      <x:c r="A130" s="9" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B130" s="9" t="str">
+        <x:v>TC-TM002-SECURITY-01#DOTDOT</x:v>
+      </x:c>
+      <x:c r="C130" s="9" t="str">
+        <x:v>renderer 不能传任意路径 · 变体</x:v>
+      </x:c>
+      <x:c r="D130" s="9" t="str">
+        <x:v>TASK-TM002-ACCESS</x:v>
+      </x:c>
+      <x:c r="E130" s="9" t="str">
+        <x:v>安全单元</x:v>
+      </x:c>
+      <x:c r="F130" s="9" t="str">
+        <x:v>renderer传../B/sessions/2026/10/01/b-01.jsonl</x:v>
+      </x:c>
+      <x:c r="G130" s="9" t="str">
+        <x:v>主进程安全拒绝，不返回内容、绝对路径或 locator；B 元数据/open/read=0，sources 无确认记录。</x:v>
+      </x:c>
+      <x:c r="H130" s="9" t="str">
+        <x:v>准备：七变体各自 R 与独立 A/B/profile；仅内存主进程 handler、受控异步屏障和隔离文件；无服务/DB，SQL 不适用。四恶意参数安全拒绝，三竞态过期结果不提交。
+变化：不适用：辅助检查不写服务业务库。
+核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
+      </x:c>
+      <x:c r="I130" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J130" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K130" s="9" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L130" s="9" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:361</x:v>
+      </x:c>
+      <x:c r="M130" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N130" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" ht="72" customHeight="1">
+      <x:c r="A131" s="4" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B131" s="4" t="str">
+        <x:v>TC-TM002-SECURITY-01#TOKEN</x:v>
+      </x:c>
+      <x:c r="C131" s="4" t="str">
+        <x:v>renderer 不能传任意路径 · 变体</x:v>
+      </x:c>
+      <x:c r="D131" s="4" t="str">
+        <x:v>TASK-TM002-ACCESS</x:v>
+      </x:c>
+      <x:c r="E131" s="4" t="str">
+        <x:v>安全单元</x:v>
+      </x:c>
+      <x:c r="F131" s="4" t="str">
+        <x:v>renderer传伪造selectionId 00000000-0000-4000-8000-000000000099</x:v>
+      </x:c>
+      <x:c r="G131" s="4" t="str">
+        <x:v>主进程安全拒绝，不返回内容、绝对路径或 locator；B 元数据/open/read=0，sources 无确认记录。</x:v>
+      </x:c>
+      <x:c r="H131" s="4" t="str">
+        <x:v>准备：七变体各自 R 与独立 A/B/profile；仅内存主进程 handler、受控异步屏障和隔离文件；无服务/DB，SQL 不适用。四恶意参数安全拒绝，三竞态过期结果不提交。
+变化：不适用：辅助检查不写服务业务库。
+核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
+      </x:c>
+      <x:c r="I131" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J131" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K131" s="4" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L131" s="4" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:361</x:v>
+      </x:c>
+      <x:c r="M131" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N131" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" ht="72" customHeight="1">
+      <x:c r="A132" s="9" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B132" s="9" t="str">
+        <x:v>TC-TM002-SECURITY-01#STALE_SELECTION</x:v>
+      </x:c>
+      <x:c r="C132" s="9" t="str">
+        <x:v>renderer 不能传任意路径 · 变体</x:v>
+      </x:c>
+      <x:c r="D132" s="9" t="str">
+        <x:v>TASK-TM002-ACCESS</x:v>
+      </x:c>
+      <x:c r="E132" s="9" t="str">
+        <x:v>安全单元</x:v>
+      </x:c>
+      <x:c r="F132" s="9" t="str">
+        <x:v>Alice 无来源，选择结果停在 Promise 屏障；切至 Bob 后释放 A 结果。</x:v>
+      </x:c>
+      <x:c r="G132" s="9" t="str">
+        <x:v>旧 Alice 结果拒绝，Bob 不得建暂选/确认 A；Alice/Bob 无新增来源，A/B 零读取。</x:v>
+      </x:c>
+      <x:c r="H132" s="9" t="str">
+        <x:v>准备：七变体各自 R 与独立 A/B/profile；仅内存主进程 handler、受控异步屏障和隔离文件；无服务/DB，SQL 不适用。四恶意参数安全拒绝，三竞态过期结果不提交。
+变化：不适用：辅助检查不写服务业务库。
+核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
+      </x:c>
+      <x:c r="I132" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J132" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K132" s="9" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L132" s="9" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:361</x:v>
+      </x:c>
+      <x:c r="M132" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N132" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" ht="72" customHeight="1">
+      <x:c r="A133" s="4" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B133" s="4" t="str">
+        <x:v>TC-TM002-SECURITY-01#REVOKE_DURING_REFRESH</x:v>
+      </x:c>
+      <x:c r="C133" s="4" t="str">
+        <x:v>renderer 不能传任意路径 · 变体</x:v>
+      </x:c>
+      <x:c r="D133" s="4" t="str">
+        <x:v>TASK-TM002-ACCESS</x:v>
+      </x:c>
+      <x:c r="E133" s="4" t="str">
+        <x:v>安全单元</x:v>
+      </x:c>
+      <x:c r="F133" s="4" t="str">
+        <x:v>Alice 已确认 A true/false；首个 A 元数据读取后/提交前停住，撤销后释放。</x:v>
+      </x:c>
+      <x:c r="G133" s="4" t="str">
+        <x:v>撤销删密文和读取能力，旧 Promise 不提交候选或 complete=true；撤销后 A/B 后续操作为零。</x:v>
+      </x:c>
+      <x:c r="H133" s="4" t="str">
+        <x:v>准备：七变体各自 R 与独立 A/B/profile；仅内存主进程 handler、受控异步屏障和隔离文件；无服务/DB，SQL 不适用。四恶意参数安全拒绝，三竞态过期结果不提交。
+变化：不适用：辅助检查不写服务业务库。
+核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
+      </x:c>
+      <x:c r="I133" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J133" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K133" s="4" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L133" s="4" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:361</x:v>
+      </x:c>
+      <x:c r="M133" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N133" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" ht="72" customHeight="1">
+      <x:c r="A134" s="9" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B134" s="9" t="str">
+        <x:v>TC-TM002-SECURITY-01#SWITCH_DURING_REFRESH</x:v>
+      </x:c>
+      <x:c r="C134" s="9" t="str">
+        <x:v>renderer 不能传任意路径 · 变体</x:v>
+      </x:c>
+      <x:c r="D134" s="9" t="str">
+        <x:v>TASK-TM002-ACCESS</x:v>
+      </x:c>
+      <x:c r="E134" s="9" t="str">
+        <x:v>安全单元</x:v>
+      </x:c>
+      <x:c r="F134" s="9" t="str">
+        <x:v>Alice 已确认 A true/false；首个 A 元数据读取后/提交前停住，切 Bob 后释放。</x:v>
+      </x:c>
+      <x:c r="G134" s="9" t="str">
+        <x:v>Bob 不得见旧 Alice 候选或得到来源；切换后 A/B 后续零访问；Bob 请求 Alice 来源 ID 被拒绝。</x:v>
+      </x:c>
+      <x:c r="H134" s="9" t="str">
+        <x:v>准备：七变体各自 R 与独立 A/B/profile；仅内存主进程 handler、受控异步屏障和隔离文件；无服务/DB，SQL 不适用。四恶意参数安全拒绝，三竞态过期结果不提交。
+变化：不适用：辅助检查不写服务业务库。
+核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
+      </x:c>
+      <x:c r="I134" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J134" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K134" s="9" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L134" s="9" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:361</x:v>
+      </x:c>
+      <x:c r="M134" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N134" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" ht="72" customHeight="1">
+      <x:c r="A135" s="4" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B135" s="4" t="str">
+        <x:v>TC-TM002-DATA-01</x:v>
+      </x:c>
+      <x:c r="C135" s="4" t="str">
+        <x:v>fixture 仅操作自有根</x:v>
+      </x:c>
+      <x:c r="D135" s="4" t="str">
+        <x:v>TASK-TM002-DATA</x:v>
+      </x:c>
+      <x:c r="E135" s="4" t="str">
+        <x:v>治理检查</x:v>
+      </x:c>
+      <x:c r="F135" s="4" t="str">
+        <x:v>新的 run_id、自有 0700 临时根；生成参数 seed=42、mtime=2026-10-01T00:00:00Z；另准备一个无 owner marker 的隔离拒绝样本，不在用户目录。</x:v>
+      </x:c>
+      <x:c r="G135" s="4" t="str">
+        <x:v>输出初始 A/B 文件集合、25/12 B 固定字节、28 B 新增文件配方、链接、mtime、owner marker、expected 与 SHA256；文件与目录模式符合合同，无网络/DB 操作。
+独立 stat 和拒读探针产生预定状态；B 与初始文件内容未改，无网络/DB 操作。
+拒绝样本不受生成器清理，用户根不被触碰；无网络/DB 操作。</x:v>
+      </x:c>
+      <x:c r="H135" s="4" t="str">
+        <x:v>准备：只写自有 fixture A/B 和 expected manifest；无服务/DB，SQL 不适用，因为数据是本地权限/文件状态。重置按 R，拒绝样本由测试自身单独清理。
+变化：不适用：辅助检查不写服务业务库。
+核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
+      </x:c>
+      <x:c r="I135" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J135" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K135" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L135" s="4" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:375</x:v>
+      </x:c>
+      <x:c r="M135" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N135" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" ht="117" customHeight="1">
+      <x:c r="A136" s="9" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B136" s="9" t="str">
+        <x:v>TC-TM002-CATALOG-01</x:v>
+      </x:c>
+      <x:c r="C136" s="9" t="str">
+        <x:v>各版本 TC 归属不能串线</x:v>
+      </x:c>
+      <x:c r="D136" s="9" t="str">
+        <x:v>TASK-TM002-CATALOG</x:v>
+      </x:c>
+      <x:c r="E136" s="9" t="str">
+        <x:v>治理检查</x:v>
+      </x:c>
+      <x:c r="F136" s="9" t="str">
+        <x:v>本例私有目录中的 catalog 临时复制品包含 TC-TM001-LOGIN-01（归属 v0.1.0-20260929T074814Z 的原 TASK）和 TC-TM002-SELECT-01（归属 v0.2.0-20261001T034118Z/TASK-TM002-PICKER）。固定变体 TC-TM002-CATALOG-01#VALID 保留这两个正确映射；TC-TM002-CATALOG-01#MISSING_TASK 只删除 TC-TM002-SELECT-01 的 task_ids 字段；TC-TM002-CATALOG-01#WRONG_RELEASE 只把 TC-TM002-SELECT-01 的 release_id 错误写成 v0.1.0-20260929T074814Z。每变体单独从原始有效样本复制，不叠加变更。</x:v>
+      </x:c>
+      <x:c r="G136" s="9" t="str">
+        <x:v>UI 不适用，原因是治理检查；无 App 文件访问、网络或 DB 操作。
+#VALID 退出码 0 且两个 TC 映射均正确；#MISSING_TASK 按 TC-TM002-SELECT-01 报缺 TASK 且非 0；#WRONG_RELEASE 按同 ID 报 release/TASK 归属冲突且非 0；无网络/DB 操作。
+核对源 catalog SHA 未变、没有 TC 被静默删除，分别保存命令、退出码和该变体原始输出；无网络/DB 操作。</x:v>
+      </x:c>
+      <x:c r="H136" s="9" t="str">
+        <x:v>准备：只改自有临时副本，不改源 catalog；无服务/DB，SQL 不适用。每变体按 owner marker 清理独立副本。
+变化：不适用：辅助检查不写服务业务库。
+核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
+      </x:c>
+      <x:c r="I136" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J136" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K136" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L136" s="9" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:386</x:v>
+      </x:c>
+      <x:c r="M136" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N136" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" ht="72" customHeight="1">
+      <x:c r="A137" s="4" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B137" s="4" t="str">
+        <x:v>TC-TM002-CATALOG-01#VALID</x:v>
+      </x:c>
+      <x:c r="C137" s="4" t="str">
+        <x:v>各版本 TC 归属不能串线 · 变体</x:v>
+      </x:c>
+      <x:c r="D137" s="4" t="str">
+        <x:v>TASK-TM002-CATALOG</x:v>
+      </x:c>
+      <x:c r="E137" s="4" t="str">
+        <x:v>治理检查</x:v>
+      </x:c>
+      <x:c r="F137" s="4" t="str">
+        <x:v>临时副本保留TM001/TM002正确映射。</x:v>
+      </x:c>
+      <x:c r="G137" s="4" t="str">
+        <x:v>治理检查退出0，两TC映射正确；源catalog SHA不变。</x:v>
+      </x:c>
+      <x:c r="H137" s="4" t="str">
+        <x:v>准备：只改自有临时副本，不改源 catalog；无服务/DB，SQL 不适用。每变体按 owner marker 清理独立副本。
+变化：不适用：辅助检查不写服务业务库。
+核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
+      </x:c>
+      <x:c r="I137" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J137" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K137" s="4" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L137" s="4" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:386</x:v>
+      </x:c>
+      <x:c r="M137" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N137" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" ht="72" customHeight="1">
+      <x:c r="A138" s="9" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B138" s="9" t="str">
+        <x:v>TC-TM002-CATALOG-01#MISSING_TASK</x:v>
+      </x:c>
+      <x:c r="C138" s="9" t="str">
+        <x:v>各版本 TC 归属不能串线 · 变体</x:v>
+      </x:c>
+      <x:c r="D138" s="9" t="str">
+        <x:v>TASK-TM002-CATALOG</x:v>
+      </x:c>
+      <x:c r="E138" s="9" t="str">
+        <x:v>治理检查</x:v>
+      </x:c>
+      <x:c r="F138" s="9" t="str">
+        <x:v>仅删除临时副本TC-TM002-SELECT-01的task_ids。</x:v>
+      </x:c>
+      <x:c r="G138" s="9" t="str">
+        <x:v>检查非0，按该TC报缺TASK；源catalog SHA不变。</x:v>
+      </x:c>
+      <x:c r="H138" s="9" t="str">
+        <x:v>准备：只改自有临时副本，不改源 catalog；无服务/DB，SQL 不适用。每变体按 owner marker 清理独立副本。
+变化：不适用：辅助检查不写服务业务库。
+核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
+      </x:c>
+      <x:c r="I138" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J138" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K138" s="9" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L138" s="9" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:386</x:v>
+      </x:c>
+      <x:c r="M138" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N138" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" ht="72" customHeight="1">
+      <x:c r="A139" s="4" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B139" s="4" t="str">
+        <x:v>TC-TM002-CATALOG-01#WRONG_RELEASE</x:v>
+      </x:c>
+      <x:c r="C139" s="4" t="str">
+        <x:v>各版本 TC 归属不能串线 · 变体</x:v>
+      </x:c>
+      <x:c r="D139" s="4" t="str">
+        <x:v>TASK-TM002-CATALOG</x:v>
+      </x:c>
+      <x:c r="E139" s="4" t="str">
+        <x:v>治理检查</x:v>
+      </x:c>
+      <x:c r="F139" s="4" t="str">
+        <x:v>仅把该TC的release_id改为v0.1.0-20260929T074814Z。</x:v>
+      </x:c>
+      <x:c r="G139" s="4" t="str">
+        <x:v>检查非0，按该TC报release/TASK归属冲突；源catalog SHA不变。</x:v>
+      </x:c>
+      <x:c r="H139" s="4" t="str">
+        <x:v>准备：只改自有临时副本，不改源 catalog；无服务/DB，SQL 不适用。每变体按 owner marker 清理独立副本。
+变化：不适用：辅助检查不写服务业务库。
+核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
+      </x:c>
+      <x:c r="I139" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J139" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K139" s="4" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L139" s="4" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:386</x:v>
+      </x:c>
+      <x:c r="M139" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N139" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" ht="132" customHeight="1">
+      <x:c r="A140" s="9" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B140" s="9" t="str">
+        <x:v>TC-TM002-EVIDENCE-01</x:v>
+      </x:c>
+      <x:c r="C140" s="9" t="str">
+        <x:v>缺原生/文件审计不得放行</x:v>
+      </x:c>
+      <x:c r="D140" s="9" t="str">
+        <x:v>TASK-TM002-RUNNER</x:v>
+      </x:c>
+      <x:c r="E140" s="9" t="str">
+        <x:v>治理检查</x:v>
+      </x:c>
+      <x:c r="F140" s="9" t="str">
+        <x:v>固定程序只在本例私有目录生成合成原始报告及隔离副本，绝不改真实产品报告。稳定变体 TC-TM002-EVIDENCE-01#COMPLETE 为结构完整的合成输入；TC-TM002-EVIDENCE-01#MISSING_STEP 只删除步骤 2 的逐步事件；TC-TM002-EVIDENCE-01#MISSING_PICKER 只删除唯一的真实面板事件；TC-TM002-EVIDENCE-01#MISSING_FS 只删除该 TC 的来源访问审计；TC-TM002-EVIDENCE-01#WRONG_PACKAGE 将 package manifest SHA256 改为 64 个字符 0；TC-TM002-EVIDENCE-01#FAILED_CLEANUP 将 cleanup.completed 改为 false。各变体从同一完整合成母版单独构造，不叠加。</x:v>
+      </x:c>
+      <x:c r="G140" s="9" t="str">
+        <x:v>UI 不适用，原因是证据复核；无 App 文件访问、网络或 DB 操作。
+#COMPLETE 仅结构核对通过且 release_eligible=false，不能签产品通行证；#MISSING_STEP、#MISSING_PICKER、#MISSING_FS、#WRONG_PACKAGE、#FAILED_CLEANUP 均分别返回非 PASS 与对应缺项原因，缺 FS 时 UI 无 B 不可补证；无网络/DB 操作。
+核对输入原件未覆盖、首次失败和复核输出按变体单独保留；无网络/DB 操作。</x:v>
+      </x:c>
+      <x:c r="H140" s="9" t="str">
+        <x:v>准备：只生成自有报告副本；无服务/DB，SQL 不适用。按 owner marker 独立清理，真实报告不可写。
+变化：不适用：辅助检查不写服务业务库。
+核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
+      </x:c>
+      <x:c r="I140" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J140" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K140" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L140" s="9" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:397</x:v>
+      </x:c>
+      <x:c r="M140" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N140" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" ht="72" customHeight="1">
+      <x:c r="A141" s="4" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B141" s="4" t="str">
+        <x:v>TC-TM002-EVIDENCE-01#COMPLETE</x:v>
+      </x:c>
+      <x:c r="C141" s="4" t="str">
+        <x:v>缺原生/文件审计不得放行 · 变体</x:v>
+      </x:c>
+      <x:c r="D141" s="4" t="str">
+        <x:v>TASK-TM002-RUNNER</x:v>
+      </x:c>
+      <x:c r="E141" s="4" t="str">
+        <x:v>治理检查</x:v>
+      </x:c>
+      <x:c r="F141" s="4" t="str">
+        <x:v>完整合成报告副本。</x:v>
+      </x:c>
+      <x:c r="G141" s="4" t="str">
+        <x:v>结构通过但release_eligible=false，不签产品通行证。</x:v>
+      </x:c>
+      <x:c r="H141" s="4" t="str">
+        <x:v>准备：只生成自有报告副本；无服务/DB，SQL 不适用。按 owner marker 独立清理，真实报告不可写。
+变化：不适用：辅助检查不写服务业务库。
+核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
+      </x:c>
+      <x:c r="I141" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J141" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K141" s="4" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L141" s="4" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:397</x:v>
+      </x:c>
+      <x:c r="M141" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N141" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142" ht="72" customHeight="1">
+      <x:c r="A142" s="9" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B142" s="9" t="str">
+        <x:v>TC-TM002-EVIDENCE-01#MISSING_STEP</x:v>
+      </x:c>
+      <x:c r="C142" s="9" t="str">
+        <x:v>缺原生/文件审计不得放行 · 变体</x:v>
+      </x:c>
+      <x:c r="D142" s="9" t="str">
+        <x:v>TASK-TM002-RUNNER</x:v>
+      </x:c>
+      <x:c r="E142" s="9" t="str">
+        <x:v>治理检查</x:v>
+      </x:c>
+      <x:c r="F142" s="9" t="str">
+        <x:v>只删步骤2逐步事件。</x:v>
+      </x:c>
+      <x:c r="G142" s="9" t="str">
+        <x:v>复核非PASS并指出缺步骤。</x:v>
+      </x:c>
+      <x:c r="H142" s="9" t="str">
+        <x:v>准备：只生成自有报告副本；无服务/DB，SQL 不适用。按 owner marker 独立清理，真实报告不可写。
+变化：不适用：辅助检查不写服务业务库。
+核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
+      </x:c>
+      <x:c r="I142" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J142" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K142" s="9" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L142" s="9" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:397</x:v>
+      </x:c>
+      <x:c r="M142" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N142" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" ht="72" customHeight="1">
+      <x:c r="A143" s="4" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B143" s="4" t="str">
+        <x:v>TC-TM002-EVIDENCE-01#MISSING_PICKER</x:v>
+      </x:c>
+      <x:c r="C143" s="4" t="str">
+        <x:v>缺原生/文件审计不得放行 · 变体</x:v>
+      </x:c>
+      <x:c r="D143" s="4" t="str">
+        <x:v>TASK-TM002-RUNNER</x:v>
+      </x:c>
+      <x:c r="E143" s="4" t="str">
+        <x:v>治理检查</x:v>
+      </x:c>
+      <x:c r="F143" s="4" t="str">
+        <x:v>只删唯一真实面板事件。</x:v>
+      </x:c>
+      <x:c r="G143" s="4" t="str">
+        <x:v>复核非PASS并指出缺原生面板证据。</x:v>
+      </x:c>
+      <x:c r="H143" s="4" t="str">
+        <x:v>准备：只生成自有报告副本；无服务/DB，SQL 不适用。按 owner marker 独立清理，真实报告不可写。
+变化：不适用：辅助检查不写服务业务库。
+核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
+      </x:c>
+      <x:c r="I143" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J143" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K143" s="4" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L143" s="4" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:397</x:v>
+      </x:c>
+      <x:c r="M143" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N143" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" ht="72" customHeight="1">
+      <x:c r="A144" s="9" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B144" s="9" t="str">
+        <x:v>TC-TM002-EVIDENCE-01#MISSING_FS</x:v>
+      </x:c>
+      <x:c r="C144" s="9" t="str">
+        <x:v>缺原生/文件审计不得放行 · 变体</x:v>
+      </x:c>
+      <x:c r="D144" s="9" t="str">
+        <x:v>TASK-TM002-RUNNER</x:v>
+      </x:c>
+      <x:c r="E144" s="9" t="str">
+        <x:v>治理检查</x:v>
+      </x:c>
+      <x:c r="F144" s="9" t="str">
+        <x:v>只删来源访问审计。</x:v>
+      </x:c>
+      <x:c r="G144" s="9" t="str">
+        <x:v>复核非PASS并指出缺文件审计；UI无B不可补证。</x:v>
+      </x:c>
+      <x:c r="H144" s="9" t="str">
+        <x:v>准备：只生成自有报告副本；无服务/DB，SQL 不适用。按 owner marker 独立清理，真实报告不可写。
+变化：不适用：辅助检查不写服务业务库。
+核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
+      </x:c>
+      <x:c r="I144" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J144" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K144" s="9" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L144" s="9" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:397</x:v>
+      </x:c>
+      <x:c r="M144" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N144" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" ht="72" customHeight="1">
+      <x:c r="A145" s="4" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B145" s="4" t="str">
+        <x:v>TC-TM002-EVIDENCE-01#WRONG_PACKAGE</x:v>
+      </x:c>
+      <x:c r="C145" s="4" t="str">
+        <x:v>缺原生/文件审计不得放行 · 变体</x:v>
+      </x:c>
+      <x:c r="D145" s="4" t="str">
+        <x:v>TASK-TM002-RUNNER</x:v>
+      </x:c>
+      <x:c r="E145" s="4" t="str">
+        <x:v>治理检查</x:v>
+      </x:c>
+      <x:c r="F145" s="4" t="str">
+        <x:v>只把package manifest SHA256改为64个0。</x:v>
+      </x:c>
+      <x:c r="G145" s="4" t="str">
+        <x:v>复核非PASS并指出包摘要不匹配。</x:v>
+      </x:c>
+      <x:c r="H145" s="4" t="str">
+        <x:v>准备：只生成自有报告副本；无服务/DB，SQL 不适用。按 owner marker 独立清理，真实报告不可写。
+变化：不适用：辅助检查不写服务业务库。
+核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
+      </x:c>
+      <x:c r="I145" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J145" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K145" s="4" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L145" s="4" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:397</x:v>
+      </x:c>
+      <x:c r="M145" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N145" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" ht="72" customHeight="1">
+      <x:c r="A146" s="9" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B146" s="9" t="str">
+        <x:v>TC-TM002-EVIDENCE-01#FAILED_CLEANUP</x:v>
+      </x:c>
+      <x:c r="C146" s="9" t="str">
+        <x:v>缺原生/文件审计不得放行 · 变体</x:v>
+      </x:c>
+      <x:c r="D146" s="9" t="str">
+        <x:v>TASK-TM002-RUNNER</x:v>
+      </x:c>
+      <x:c r="E146" s="9" t="str">
+        <x:v>治理检查</x:v>
+      </x:c>
+      <x:c r="F146" s="9" t="str">
+        <x:v>只把cleanup.completed改为false。</x:v>
+      </x:c>
+      <x:c r="G146" s="9" t="str">
+        <x:v>复核非PASS并指出清理未完成。</x:v>
+      </x:c>
+      <x:c r="H146" s="9" t="str">
+        <x:v>准备：只生成自有报告副本；无服务/DB，SQL 不适用。按 owner marker 独立清理，真实报告不可写。
+变化：不适用：辅助检查不写服务业务库。
+核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
+      </x:c>
+      <x:c r="I146" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J146" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K146" s="9" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L146" s="9" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:397</x:v>
+      </x:c>
+      <x:c r="M146" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N146" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" ht="132" customHeight="1">
+      <x:c r="A147" s="4" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B147" s="4" t="str">
+        <x:v>TC-TM002-DELIVERY-01</x:v>
+      </x:c>
+      <x:c r="C147" s="4" t="str">
+        <x:v>最终包、升级与全量回归门禁</x:v>
+      </x:c>
+      <x:c r="D147" s="4" t="str">
+        <x:v>TASK-TM002-DELIVERY</x:v>
+      </x:c>
+      <x:c r="E147" s="4" t="str">
+        <x:v>交付门禁</x:v>
+      </x:c>
+      <x:c r="F147" s="4" t="str">
+        <x:v>已锁定候选 SHA/tree、0.2.0 最终 DMG 原件/清单、上一0.1本机正式稳定DMG及其SOP-018通行证、SOP-020归档收据、来源里程碑SHA/tree、签名和原包摘要、同机隔离签名更新源与每例隔离服务；若没有这些前置或真实升级入口，本例为 BLOCKED，不能用开发/候选包、受控101或同源码测试高版冒充。远端源码登记与Tag可待最终统一办理。TM-001 全部已交付 TC 和 除本例外 TM-002 其余 27 条父 TC 与 35 个稳定变体的固定清单在运行前确定。</x:v>
+      </x:c>
+      <x:c r="G147" s="4" t="str">
+        <x:v>TM-001 全部已交付 TC、其他 27 条 TM-002 父 TC/35 变体的真实 UI、原生面板、服务与隔离 DB 由各自固定程序执行；原始记录各有唯一尝试和清理；本例结果此时仍为 BLOCKED。
+上一0.1本机稳定原包来源与通行证一致，App 自主升级；0.2显示新版本、保留TM-001合成账号/配置且 /v1/me 复核身份；来源初态 none，真实面板确认A后重启恢复本版密文来源；两端包签名、摘要和进程版本吻合。
+本例不自我依赖：只有 TM-001 全部、其他 27 条 TM-002 父 TC/35 变体及升级真实结果均 PASS，且本例自身包/升级/证据核验 PASS，才记本例 PASS 并由最终 gate 签发通行证；计算前为 BLOCKED；本步骤无业务 DB 写入。</x:v>
+      </x:c>
+      <x:c r="H147" s="4" t="str">
+        <x:v>准备：每个产品 TC 由共同 R 独立准备合成账号、隔离 SQLite 与来源；本门禁只读这些运行的原始摘要及 SQL/数据证据引用，并核对最终 DMG、升级源和候选 SHA/tree。 上一稳定0.1包须有SOP-018/020原件及来源里程碑身份，远端登记可待办。
+变化：本门禁自身无服务业务 SQL 写入；逐个产品 TC 的认证 sessions/audit 变化只按各自 NDA 与只读证据解释。
+核验：只读复核 TM-001 全部已交付 TC、其他 27 条 TM-002 父 TC/35 变体的隔离 DB/SQL 引用与原始逐步结果，并核对最终包、升级、清理和候选一致性；本例结果由这些原件派生，不连接生产库。 核对上一0.1稳定原包的通行证、归档、来源SHA/tree及真实升级链。</x:v>
+      </x:c>
+      <x:c r="I147" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J147" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K147" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L147" s="4" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:408</x:v>
+      </x:c>
+      <x:c r="M147" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N147" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" ht="72" customHeight="1">
+      <x:c r="A148" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B148" s="9" t="str">
+        <x:v>E2E-TM003-001</x:v>
+      </x:c>
+      <x:c r="C148" s="9" t="str">
+        <x:v>增量采集、重扫、重启和移动</x:v>
+      </x:c>
+      <x:c r="D148" s="9" t="str">
         <x:v>待拆解</x:v>
       </x:c>
-      <x:c r="E83" s="4" t="str">
+      <x:c r="E148" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F83" s="4" t="str">
-        <x:v>数据集 system_permissions；全新测试账号登录；专用临时根有待授权目录A与未授权目录B，分别含可识别的合成日志与唯一哨兵文件；不得使用真实 ~/.codex 或 ~/.claude。system_permissions 尚缺目录/授权状态生成及清理程序；相关原始日志须待TM-003/004确认版本后生成。</x:v>
-      </x:c>
-      <x:c r="G83" s="4" t="str">
-        <x:v>未确认前不得开始持续扫描；预览和后续读取范围均不包含B。重启保留A与真实同意状态。是否产生用量在采集版本另验，不能要求授权版本依赖尚未实现的解析器。</x:v>
-      </x:c>
-      <x:c r="H83" s="4" t="str">
+      <x:c r="F148" s="9" t="str">
+        <x:v>数据集 codex_raw；依赖TM-001/002；已授权隔离Codex目录。codex_raw 须声明真实支持的工具版本、字段语义和来源。规划三次调用A/B/C的独立增量分别为 input/output 100/10、200/20、300/30，缓存20/40/60为input子项；原始格式尚未绑定。</x:v>
+      </x:c>
+      <x:c r="G148" s="9" t="str">
+        <x:v>唯一事件=3，input=600、output=60、total=660、cached=120且不额外加到total。首次A为110，全部后为660；重扫、重启、移动后仍660。预期由给定增量手工相加，不能用产品解析器生成。</x:v>
+      </x:c>
+      <x:c r="H148" s="9" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
 变化：待具体任务及数据设计细化。
 核验：暂无可执行数据库核验绑定。</x:v>
       </x:c>
-      <x:c r="I83" s="4" t="str">
+      <x:c r="I148" s="9" t="str">
         <x:v>未来规划</x:v>
       </x:c>
-      <x:c r="J83" s="4" t="str">
+      <x:c r="J148" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K83" s="4" t="str">
+      <x:c r="K148" s="9" t="str">
         <x:v>未来概要</x:v>
       </x:c>
-      <x:c r="L83" s="4" t="str">
-        <x:v>docs/testing/cases/02-TM-002-permissions.md:11</x:v>
-      </x:c>
-      <x:c r="M83" s="4" t="str">
+      <x:c r="L148" s="9" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:11</x:v>
+      </x:c>
+      <x:c r="M148" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-    </x:row>
-    <x:row r="84" ht="57" customHeight="1">
-      <x:c r="A84" s="9" t="str">
-        <x:v>TM-002</x:v>
-      </x:c>
-      <x:c r="B84" s="9" t="str">
-        <x:v>E2E-TM002-002</x:v>
-      </x:c>
-      <x:c r="C84" s="9" t="str">
-        <x:v>拒绝、失效与重新授权</x:v>
-      </x:c>
-      <x:c r="D84" s="9" t="str">
+      <x:c r="N148" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" ht="72" customHeight="1">
+      <x:c r="A149" s="4" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B149" s="4" t="str">
+        <x:v>E2E-TM003-002</x:v>
+      </x:c>
+      <x:c r="C149" s="4" t="str">
+        <x:v>累计值、重复事件、分支和未知格式</x:v>
+      </x:c>
+      <x:c r="D149" s="4" t="str">
         <x:v>待拆解</x:v>
       </x:c>
-      <x:c r="E84" s="9" t="str">
+      <x:c r="E149" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F84" s="9" t="str">
-        <x:v>数据集 system_permissions；账号已登录；专用目录A。分别准备“从未授权”和“曾授权后权限失效”两个隔离状态，权限变更只作用于测试目录/测试域。system_permissions 生成/重置程序未实现。</x:v>
-      </x:c>
-      <x:c r="G84" s="9" t="str">
-        <x:v>拒绝不会崩溃或隐式授权；失效后停止读取，重新授权后恢复访问和持久授权。此例不证明已解析事件去重，恢复去重分别由TM-003-004/TM-004-004验证。</x:v>
-      </x:c>
-      <x:c r="H84" s="9" t="str">
+      <x:c r="F149" s="4" t="str">
+        <x:v>数据集 codex_raw；codex_raw 规划独立分组：累计input/output 100/10→150/15，重复最后一条；另开启有明确新会话身份的重置累计30/3；分支复制前序历史后新增20/2。再附一条未知结构与一条无法解释的累计回退。版本、事件/分支语义仍需实际fixture证实。</x:v>
+      </x:c>
+      <x:c r="G149" s="4" t="str">
+        <x:v>可确认的新用量为150/15+30/3+20/2，即input=200、output=20、total=220；重复累计和继承历史贡献0新增量。未知/无法核实回退须单独诊断，不作为0值成功事件，也不污染220可信总量。</x:v>
+      </x:c>
+      <x:c r="H149" s="4" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
 变化：待具体任务及数据设计细化。
 核验：暂无可执行数据库核验绑定。</x:v>
       </x:c>
-      <x:c r="I84" s="9" t="str">
+      <x:c r="I149" s="4" t="str">
         <x:v>未来规划</x:v>
       </x:c>
-      <x:c r="J84" s="9" t="str">
+      <x:c r="J149" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K84" s="9" t="str">
+      <x:c r="K149" s="4" t="str">
         <x:v>未来概要</x:v>
       </x:c>
-      <x:c r="L84" s="9" t="str">
-        <x:v>docs/testing/cases/02-TM-002-permissions.md:28</x:v>
-      </x:c>
-      <x:c r="M84" s="9" t="str">
+      <x:c r="L149" s="4" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:28</x:v>
+      </x:c>
+      <x:c r="M149" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-    </x:row>
-    <x:row r="85" ht="72" customHeight="1">
-      <x:c r="A85" s="4" t="str">
+      <x:c r="N149" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" ht="57" customHeight="1">
+      <x:c r="A150" s="9" t="str">
         <x:v>TM-003</x:v>
       </x:c>
-      <x:c r="B85" s="4" t="str">
-        <x:v>E2E-TM003-001</x:v>
-      </x:c>
-      <x:c r="C85" s="4" t="str">
-        <x:v>增量采集、重扫、重启和移动</x:v>
-      </x:c>
-      <x:c r="D85" s="4" t="str">
+      <x:c r="B150" s="9" t="str">
+        <x:v>E2E-TM003-003</x:v>
+      </x:c>
+      <x:c r="C150" s="9" t="str">
+        <x:v>半行完成与源日志清理</x:v>
+      </x:c>
+      <x:c r="D150" s="9" t="str">
         <x:v>待拆解</x:v>
       </x:c>
-      <x:c r="E85" s="4" t="str">
+      <x:c r="E150" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F85" s="4" t="str">
-        <x:v>数据集 codex_raw；依赖TM-001/002；已授权隔离Codex目录。codex_raw 须声明真实支持的工具版本、字段语义和来源。规划三次调用A/B/C的独立增量分别为 input/output 100/10、200/20、300/30，缓存20/40/60为input子项；原始格式尚未绑定。</x:v>
-      </x:c>
-      <x:c r="G85" s="4" t="str">
-        <x:v>唯一事件=3，input=600、output=60、total=660、cached=120且不额外加到total。首次A为110，全部后为660；重扫、重启、移动后仍660。预期由给定增量手工相加，不能用产品解析器生成。</x:v>
-      </x:c>
-      <x:c r="H85" s="4" t="str">
+      <x:c r="F150" s="9" t="str">
+        <x:v>数据集 codex_raw；codex_raw 规划完整调用A=100/10、待分两次写入调用B=50/5；当前已导入历史覆盖范围另有边界标记。原始字节拆分与文件清理程序未实现。</x:v>
+      </x:c>
+      <x:c r="G150" s="9" t="str">
+        <x:v>半行时只有A、total=110；补全后A+B共2条、total=165，重启不重计。源文件删除不删除已采集统计，早于可证明覆盖范围的历史显示缺失，不能以0表示。</x:v>
+      </x:c>
+      <x:c r="H150" s="9" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
 变化：待具体任务及数据设计细化。
 核验：暂无可执行数据库核验绑定。</x:v>
       </x:c>
-      <x:c r="I85" s="4" t="str">
+      <x:c r="I150" s="9" t="str">
         <x:v>未来规划</x:v>
       </x:c>
-      <x:c r="J85" s="4" t="str">
+      <x:c r="J150" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K85" s="4" t="str">
+      <x:c r="K150" s="9" t="str">
         <x:v>未来概要</x:v>
       </x:c>
-      <x:c r="L85" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:11</x:v>
-      </x:c>
-      <x:c r="M85" s="4" t="str">
+      <x:c r="L150" s="9" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:45</x:v>
+      </x:c>
+      <x:c r="M150" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-    </x:row>
-    <x:row r="86" ht="72" customHeight="1">
-      <x:c r="A86" s="9" t="str">
+      <x:c r="N150" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" ht="57" customHeight="1">
+      <x:c r="A151" s="4" t="str">
         <x:v>TM-003</x:v>
       </x:c>
-      <x:c r="B86" s="9" t="str">
-        <x:v>E2E-TM003-002</x:v>
-      </x:c>
-      <x:c r="C86" s="9" t="str">
-        <x:v>累计值、重复事件、分支和未知格式</x:v>
-      </x:c>
-      <x:c r="D86" s="9" t="str">
+      <x:c r="B151" s="4" t="str">
+        <x:v>E2E-TM003-004</x:v>
+      </x:c>
+      <x:c r="C151" s="4" t="str">
+        <x:v>重新授权后的去重</x:v>
+      </x:c>
+      <x:c r="D151" s="4" t="str">
         <x:v>待拆解</x:v>
       </x:c>
-      <x:c r="E86" s="9" t="str">
+      <x:c r="E151" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F86" s="9" t="str">
-        <x:v>数据集 codex_raw；codex_raw 规划独立分组：累计input/output 100/10→150/15，重复最后一条；另开启有明确新会话身份的重置累计30/3；分支复制前序历史后新增20/2。再附一条未知结构与一条无法解释的累计回退。版本、事件/分支语义仍需实际fixture证实。</x:v>
-      </x:c>
-      <x:c r="G86" s="9" t="str">
-        <x:v>可确认的新用量为150/15+30/3+20/2，即input=200、output=20、total=220；重复累计和继承历史贡献0新增量。未知/无法核实回退须单独诊断，不作为0值成功事件，也不污染220可信总量。</x:v>
-      </x:c>
-      <x:c r="H86" s="9" t="str">
+      <x:c r="F151" s="4" t="str">
+        <x:v>数据集 codex_raw；TM-002权限恢复已可运行；Codex目录含已采集A=100/10、B=200/20。撤销期间追加C=300/30，重新授权后还重放A。codex_raw 与system_permissions跨fixture绑定待实现。</x:v>
+      </x:c>
+      <x:c r="G151" s="4" t="str">
+        <x:v>撤销期间不读取；恢复前total=330，恢复后唯一A/B/C共3条、total=660；重放A贡献0；刷新和重启后保持660。</x:v>
+      </x:c>
+      <x:c r="H151" s="4" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
 变化：待具体任务及数据设计细化。
 核验：暂无可执行数据库核验绑定。</x:v>
       </x:c>
-      <x:c r="I86" s="9" t="str">
+      <x:c r="I151" s="4" t="str">
         <x:v>未来规划</x:v>
       </x:c>
-      <x:c r="J86" s="9" t="str">
+      <x:c r="J151" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K86" s="9" t="str">
+      <x:c r="K151" s="4" t="str">
         <x:v>未来概要</x:v>
       </x:c>
-      <x:c r="L86" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:28</x:v>
-      </x:c>
-      <x:c r="M86" s="9" t="str">
+      <x:c r="L151" s="4" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:62</x:v>
+      </x:c>
+      <x:c r="M151" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-    </x:row>
-    <x:row r="87" ht="57" customHeight="1">
-      <x:c r="A87" s="4" t="str">
-        <x:v>TM-003</x:v>
-      </x:c>
-      <x:c r="B87" s="4" t="str">
-        <x:v>E2E-TM003-003</x:v>
-      </x:c>
-      <x:c r="C87" s="4" t="str">
-        <x:v>半行完成与源日志清理</x:v>
-      </x:c>
-      <x:c r="D87" s="4" t="str">
+      <x:c r="N151" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" ht="57" customHeight="1">
+      <x:c r="A152" s="9" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="B152" s="9" t="str">
+        <x:v>E2E-TM004-001</x:v>
+      </x:c>
+      <x:c r="C152" s="9" t="str">
+        <x:v>主会话与子代理归属</x:v>
+      </x:c>
+      <x:c r="D152" s="9" t="str">
         <x:v>待拆解</x:v>
       </x:c>
-      <x:c r="E87" s="4" t="str">
+      <x:c r="E152" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F87" s="4" t="str">
-        <x:v>数据集 codex_raw；codex_raw 规划完整调用A=100/10、待分两次写入调用B=50/5；当前已导入历史覆盖范围另有边界标记。原始字节拆分与文件清理程序未实现。</x:v>
-      </x:c>
-      <x:c r="G87" s="4" t="str">
-        <x:v>半行时只有A、total=110；补全后A+B共2条、total=165，重启不重计。源文件删除不删除已采集统计，早于可证明覆盖范围的历史显示缺失，不能以0表示。</x:v>
-      </x:c>
-      <x:c r="H87" s="4" t="str">
+      <x:c r="F152" s="9" t="str">
+        <x:v>数据集 claude_raw；依赖TM-002/003；claude_raw 须注明已验证Claude Code版本。规划主调用M=100/10与子代理S=200/20，同属用户alice/项目A，具有明确父子关系且模型字段可不同。</x:v>
+      </x:c>
+      <x:c r="G152" s="9" t="str">
+        <x:v>M与S各入账一次，共input300、output30、total330；S计入正确父项目，不因主会话引用而再计一次。模型明细保留各自原始可识别模型。</x:v>
+      </x:c>
+      <x:c r="H152" s="9" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
 变化：待具体任务及数据设计细化。
 核验：暂无可执行数据库核验绑定。</x:v>
       </x:c>
-      <x:c r="I87" s="4" t="str">
+      <x:c r="I152" s="9" t="str">
         <x:v>未来规划</x:v>
       </x:c>
-      <x:c r="J87" s="4" t="str">
+      <x:c r="J152" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K87" s="4" t="str">
+      <x:c r="K152" s="9" t="str">
         <x:v>未来概要</x:v>
       </x:c>
-      <x:c r="L87" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:45</x:v>
-      </x:c>
-      <x:c r="M87" s="4" t="str">
+      <x:c r="L152" s="9" t="str">
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:11</x:v>
+      </x:c>
+      <x:c r="M152" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-    </x:row>
-    <x:row r="88" ht="57" customHeight="1">
-      <x:c r="A88" s="9" t="str">
-        <x:v>TM-003</x:v>
-      </x:c>
-      <x:c r="B88" s="9" t="str">
-        <x:v>E2E-TM003-004</x:v>
-      </x:c>
-      <x:c r="C88" s="9" t="str">
-        <x:v>重新授权后的去重</x:v>
-      </x:c>
-      <x:c r="D88" s="9" t="str">
+      <x:c r="N152" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" ht="57" customHeight="1">
+      <x:c r="A153" s="4" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="B153" s="4" t="str">
+        <x:v>E2E-TM004-002</x:v>
+      </x:c>
+      <x:c r="C153" s="4" t="str">
+        <x:v>fork历史、消息改写与半写入</x:v>
+      </x:c>
+      <x:c r="D153" s="4" t="str">
         <x:v>待拆解</x:v>
       </x:c>
-      <x:c r="E88" s="9" t="str">
+      <x:c r="E153" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F88" s="9" t="str">
-        <x:v>数据集 codex_raw；TM-002权限恢复已可运行；Codex目录含已采集A=100/10、B=200/20。撤销期间追加C=300/30，重新授权后还重放A。codex_raw 与system_permissions跨fixture绑定待实现。</x:v>
-      </x:c>
-      <x:c r="G88" s="9" t="str">
-        <x:v>撤销期间不读取；恢复前total=330，恢复后唯一A/B/C共3条、total=660；重放A贡献0；刷新和重启后保持660。</x:v>
-      </x:c>
-      <x:c r="H88" s="9" t="str">
+      <x:c r="F153" s="4" t="str">
+        <x:v>数据集 claude_raw；规划原会话M=100/10，fork继承M但消息ID变化；分支新增N=50/5，最后调用P=20/2分段写入；同一片段重复出现。实际继承识别字段需由版本化raw证据确认。</x:v>
+      </x:c>
+      <x:c r="G153" s="4" t="str">
+        <x:v>继承历史虽改消息ID仍不重复；M+N阶段total165，半写入不增加，完整P后total187，共3次实际调用；重启不再增加。不能只以消息ID相等作为去重预期。</x:v>
+      </x:c>
+      <x:c r="H153" s="4" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
 变化：待具体任务及数据设计细化。
 核验：暂无可执行数据库核验绑定。</x:v>
       </x:c>
-      <x:c r="I88" s="9" t="str">
+      <x:c r="I153" s="4" t="str">
         <x:v>未来规划</x:v>
       </x:c>
-      <x:c r="J88" s="9" t="str">
+      <x:c r="J153" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K88" s="9" t="str">
+      <x:c r="K153" s="4" t="str">
         <x:v>未来概要</x:v>
       </x:c>
-      <x:c r="L88" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:62</x:v>
-      </x:c>
-      <x:c r="M88" s="9" t="str">
+      <x:c r="L153" s="4" t="str">
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:28</x:v>
+      </x:c>
+      <x:c r="M153" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-    </x:row>
-    <x:row r="89" ht="57" customHeight="1">
-      <x:c r="A89" s="4" t="str">
+      <x:c r="N153" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" ht="57" customHeight="1">
+      <x:c r="A154" s="9" t="str">
         <x:v>TM-004</x:v>
       </x:c>
-      <x:c r="B89" s="4" t="str">
-        <x:v>E2E-TM004-001</x:v>
-      </x:c>
-      <x:c r="C89" s="4" t="str">
-        <x:v>主会话与子代理归属</x:v>
-      </x:c>
-      <x:c r="D89" s="4" t="str">
+      <x:c r="B154" s="9" t="str">
+        <x:v>E2E-TM004-003</x:v>
+      </x:c>
+      <x:c r="C154" s="9" t="str">
+        <x:v>支持版本与未知usage降级</x:v>
+      </x:c>
+      <x:c r="D154" s="9" t="str">
         <x:v>待拆解</x:v>
       </x:c>
-      <x:c r="E89" s="4" t="str">
+      <x:c r="E154" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F89" s="4" t="str">
-        <x:v>数据集 claude_raw；依赖TM-002/003；claude_raw 须注明已验证Claude Code版本。规划主调用M=100/10与子代理S=200/20，同属用户alice/项目A，具有明确父子关系且模型字段可不同。</x:v>
-      </x:c>
-      <x:c r="G89" s="4" t="str">
-        <x:v>M与S各入账一次，共input300、output30、total330；S计入正确父项目，不因主会话引用而再计一次。模型明细保留各自原始可识别模型。</x:v>
-      </x:c>
-      <x:c r="H89" s="4" t="str">
+      <x:c r="F154" s="9" t="str">
+        <x:v>数据集 claude_raw；为每个拟声明支持版本准备原生样例及独立expected，例如完整调用100/10；另准备未知结构版本和缺usage的事件，后两者不用0填充。当前无已验证版本样例。</x:v>
+      </x:c>
+      <x:c r="G154" s="9" t="str">
+        <x:v>支持版本各与其独立数字相等；未知版本/缺usage明确显示未识别或缺失，不能当作有效零用量，也不覆盖已知调用110。支持列表必须由真实结果决定。</x:v>
+      </x:c>
+      <x:c r="H154" s="9" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
 变化：待具体任务及数据设计细化。
 核验：暂无可执行数据库核验绑定。</x:v>
       </x:c>
-      <x:c r="I89" s="4" t="str">
+      <x:c r="I154" s="9" t="str">
         <x:v>未来规划</x:v>
       </x:c>
-      <x:c r="J89" s="4" t="str">
+      <x:c r="J154" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K89" s="4" t="str">
+      <x:c r="K154" s="9" t="str">
         <x:v>未来概要</x:v>
       </x:c>
-      <x:c r="L89" s="4" t="str">
-        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:11</x:v>
-      </x:c>
-      <x:c r="M89" s="4" t="str">
+      <x:c r="L154" s="9" t="str">
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:45</x:v>
+      </x:c>
+      <x:c r="M154" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-    </x:row>
-    <x:row r="90" ht="57" customHeight="1">
-      <x:c r="A90" s="9" t="str">
+      <x:c r="N154" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" ht="57" customHeight="1">
+      <x:c r="A155" s="4" t="str">
         <x:v>TM-004</x:v>
       </x:c>
-      <x:c r="B90" s="9" t="str">
-        <x:v>E2E-TM004-002</x:v>
-      </x:c>
-      <x:c r="C90" s="9" t="str">
-        <x:v>fork历史、消息改写与半写入</x:v>
-      </x:c>
-      <x:c r="D90" s="9" t="str">
+      <x:c r="B155" s="4" t="str">
+        <x:v>E2E-TM004-004</x:v>
+      </x:c>
+      <x:c r="C155" s="4" t="str">
+        <x:v>主/子代理重新授权去重</x:v>
+      </x:c>
+      <x:c r="D155" s="4" t="str">
         <x:v>待拆解</x:v>
       </x:c>
-      <x:c r="E90" s="9" t="str">
+      <x:c r="E155" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F90" s="9" t="str">
-        <x:v>数据集 claude_raw；规划原会话M=100/10，fork继承M但消息ID变化；分支新增N=50/5，最后调用P=20/2分段写入；同一片段重复出现。实际继承识别字段需由版本化raw证据确认。</x:v>
-      </x:c>
-      <x:c r="G90" s="9" t="str">
-        <x:v>继承历史虽改消息ID仍不重复；M+N阶段total165，半写入不增加，完整P后total187，共3次实际调用；重启不再增加。不能只以消息ID相等作为去重预期。</x:v>
-      </x:c>
-      <x:c r="H90" s="9" t="str">
+      <x:c r="F155" s="4" t="str">
+        <x:v>数据集 claude_raw；初始主M=100/10、子S=200/20及继承M的fork均已扫描；失权期间子代理追加N=50/5。claude_raw 和权限状态联合fixture尚未实现。</x:v>
+      </x:c>
+      <x:c r="G155" s="4" t="str">
+        <x:v>恢复前total330，恢复后唯一M/S/N共3调用、total385；继承M和复制S均不重复；读取失败期间不生成成功零值。</x:v>
+      </x:c>
+      <x:c r="H155" s="4" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
 变化：待具体任务及数据设计细化。
 核验：暂无可执行数据库核验绑定。</x:v>
       </x:c>
-      <x:c r="I90" s="9" t="str">
+      <x:c r="I155" s="4" t="str">
         <x:v>未来规划</x:v>
       </x:c>
-      <x:c r="J90" s="9" t="str">
+      <x:c r="J155" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K90" s="9" t="str">
+      <x:c r="K155" s="4" t="str">
         <x:v>未来概要</x:v>
       </x:c>
-      <x:c r="L90" s="9" t="str">
-        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:28</x:v>
-      </x:c>
-      <x:c r="M90" s="9" t="str">
+      <x:c r="L155" s="4" t="str">
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:62</x:v>
+      </x:c>
+      <x:c r="M155" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-    </x:row>
-    <x:row r="91" ht="57" customHeight="1">
-      <x:c r="A91" s="4" t="str">
-        <x:v>TM-004</x:v>
-      </x:c>
-      <x:c r="B91" s="4" t="str">
-        <x:v>E2E-TM004-003</x:v>
-      </x:c>
-      <x:c r="C91" s="4" t="str">
-        <x:v>支持版本与未知usage降级</x:v>
-      </x:c>
-      <x:c r="D91" s="4" t="str">
+      <x:c r="N155" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" ht="57" customHeight="1">
+      <x:c r="A156" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B156" s="9" t="str">
+        <x:v>E2E-TM005-001</x:v>
+      </x:c>
+      <x:c r="C156" s="9" t="str">
+        <x:v>日期筛选、趋势和明细</x:v>
+      </x:c>
+      <x:c r="D156" s="9" t="str">
         <x:v>待拆解</x:v>
       </x:c>
-      <x:c r="E91" s="4" t="str">
+      <x:c r="E156" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F91" s="4" t="str">
-        <x:v>数据集 claude_raw；为每个拟声明支持版本准备原生样例及独立expected，例如完整调用100/10；另准备未知结构版本和缺usage的事件，后两者不用0填充。当前无已验证版本样例。</x:v>
-      </x:c>
-      <x:c r="G91" s="4" t="str">
-        <x:v>支持版本各与其独立数字相等；未知版本/缺usage明确显示未识别或缺失，不能当作有效零用量，也不覆盖已知调用110。支持列表必须由真实结果决定。</x:v>
-      </x:c>
-      <x:c r="H91" s="4" t="str">
+      <x:c r="F156" s="9" t="str">
+        <x:v>数据集 date_ranges；date_ranges 已由 scripts/test_data.py 提供标准化语义样例，固定2026-09-29T04:00:00Z、Asia/Shanghai、seed42；13行含1重复、12唯一。需另有已验证raw输入映射和真实App导入流程，当前未实现。</x:v>
+      </x:c>
+      <x:c r="G156" s="9" t="str">
+        <x:v>独立expected中的total依次16500、110、17380、27830、31130；custom=2200。today共5条、input15000、output1500、cache1700、reasoning170，cache/reasoning不再相加；custom-start包含、custom-end排除。趋势点及明细按expected事件时间逐条核对。</x:v>
+      </x:c>
+      <x:c r="H156" s="9" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
 变化：待具体任务及数据设计细化。
 核验：暂无可执行数据库核验绑定。</x:v>
       </x:c>
-      <x:c r="I91" s="4" t="str">
+      <x:c r="I156" s="9" t="str">
         <x:v>未来规划</x:v>
       </x:c>
-      <x:c r="J91" s="4" t="str">
+      <x:c r="J156" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K91" s="4" t="str">
+      <x:c r="K156" s="9" t="str">
         <x:v>未来概要</x:v>
       </x:c>
-      <x:c r="L91" s="4" t="str">
-        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:45</x:v>
-      </x:c>
-      <x:c r="M91" s="4" t="str">
+      <x:c r="L156" s="9" t="str">
+        <x:v>docs/testing/cases/05-TM-005-usage-statistics.md:15</x:v>
+      </x:c>
+      <x:c r="M156" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-    </x:row>
-    <x:row r="92" ht="57" customHeight="1">
-      <x:c r="A92" s="9" t="str">
-        <x:v>TM-004</x:v>
-      </x:c>
-      <x:c r="B92" s="9" t="str">
-        <x:v>E2E-TM004-004</x:v>
-      </x:c>
-      <x:c r="C92" s="9" t="str">
-        <x:v>主/子代理重新授权去重</x:v>
-      </x:c>
-      <x:c r="D92" s="9" t="str">
+      <x:c r="N156" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" ht="57" customHeight="1">
+      <x:c r="A157" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B157" s="4" t="str">
+        <x:v>E2E-TM005-002</x:v>
+      </x:c>
+      <x:c r="C157" s="4" t="str">
+        <x:v>时区、月边界与缺失值</x:v>
+      </x:c>
+      <x:c r="D157" s="4" t="str">
         <x:v>待拆解</x:v>
       </x:c>
-      <x:c r="E92" s="9" t="str">
+      <x:c r="E157" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F92" s="9" t="str">
-        <x:v>数据集 claude_raw；初始主M=100/10、子S=200/20及继承M的fork均已扫描；失权期间子代理追加N=50/5。claude_raw 和权限状态联合fixture尚未实现。</x:v>
-      </x:c>
-      <x:c r="G92" s="9" t="str">
-        <x:v>恢复前total330，恢复后唯一M/S/N共3调用、total385；继承M和复制S均不重复；读取失败期间不生成成功零值。</x:v>
-      </x:c>
-      <x:c r="H92" s="9" t="str">
+      <x:c r="F157" s="4" t="str">
+        <x:v>数据集 date_ranges；复用date_ranges中的2026-09-28T15:59:59Z与16:00:00Z、2026-08-30T15:59:59Z与16:00:00Z边界。另需补充覆盖缺口、已覆盖零调用日、unknown字段三类状态；当前生成器未覆盖后面三类。</x:v>
+      </x:c>
+      <x:c r="G157" s="4" t="str">
+        <x:v>Shanghai下15:59:59Z仍属前日、16:00:00Z属次日；UTC下二者同属UTC日期。无覆盖显示缺失，真实零可显示0，unknown字段显示未知；不得互相代替。各范围expected须独立按当地日期边界列出，不调用产品查询生成。</x:v>
+      </x:c>
+      <x:c r="H157" s="4" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
 变化：待具体任务及数据设计细化。
 核验：暂无可执行数据库核验绑定。</x:v>
       </x:c>
-      <x:c r="I92" s="9" t="str">
+      <x:c r="I157" s="4" t="str">
         <x:v>未来规划</x:v>
       </x:c>
-      <x:c r="J92" s="9" t="str">
+      <x:c r="J157" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K92" s="9" t="str">
+      <x:c r="K157" s="4" t="str">
         <x:v>未来概要</x:v>
       </x:c>
-      <x:c r="L92" s="9" t="str">
-        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:62</x:v>
-      </x:c>
-      <x:c r="M92" s="9" t="str">
+      <x:c r="L157" s="4" t="str">
+        <x:v>docs/testing/cases/05-TM-005-usage-statistics.md:32</x:v>
+      </x:c>
+      <x:c r="M157" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-    </x:row>
-    <x:row r="93" ht="57" customHeight="1">
-      <x:c r="A93" s="4" t="str">
-        <x:v>TM-005</x:v>
-      </x:c>
-      <x:c r="B93" s="4" t="str">
-        <x:v>E2E-TM005-001</x:v>
-      </x:c>
-      <x:c r="C93" s="4" t="str">
-        <x:v>日期筛选、趋势和明细</x:v>
-      </x:c>
-      <x:c r="D93" s="4" t="str">
+      <x:c r="N157" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" ht="57" customHeight="1">
+      <x:c r="A158" s="9" t="str">
+        <x:v>TM-006</x:v>
+      </x:c>
+      <x:c r="B158" s="9" t="str">
+        <x:v>E2E-TM006-001</x:v>
+      </x:c>
+      <x:c r="C158" s="9" t="str">
+        <x:v>Token子项与基础费用</x:v>
+      </x:c>
+      <x:c r="D158" s="9" t="str">
         <x:v>待拆解</x:v>
       </x:c>
-      <x:c r="E93" s="4" t="str">
+      <x:c r="E158" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F93" s="4" t="str">
-        <x:v>数据集 date_ranges；date_ranges 已由 scripts/test_data.py 提供标准化语义样例，固定2026-09-29T04:00:00Z、Asia/Shanghai、seed42；13行含1重复、12唯一。需另有已验证raw输入映射和真实App导入流程，当前未实现。</x:v>
-      </x:c>
-      <x:c r="G93" s="4" t="str">
-        <x:v>独立expected中的total依次16500、110、17380、27830、31130；custom=2200。today共5条、input15000、output1500、cache1700、reasoning170，cache/reasoning不再相加；custom-start包含、custom-end排除。趋势点及明细按expected事件时间逐条核对。</x:v>
-      </x:c>
-      <x:c r="H93" s="4" t="str">
+      <x:c r="F158" s="9" t="str">
+        <x:v>数据集 pricing；pricing由scripts/test_data.py生成合成非计费价格。gpt-5每百万input/cache/output为USD2/0.2/8；today-gpt input1000含cache200、output100含reasoning20。价格不是厂商现价。</x:v>
+      </x:c>
+      <x:c r="G158" s="9" t="str">
+        <x:v>单调用total=1100；费用=(800×2+200×0.2+100×8)/1000000=USD0.002440，reasoning20不另加价。today已知费用USD0.015190且有1条无价格，alice今日USD0.010090。使用Decimal/十进制独立oracle，不以界面舍入反推底层精度。</x:v>
+      </x:c>
+      <x:c r="H158" s="9" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
 变化：待具体任务及数据设计细化。
 核验：暂无可执行数据库核验绑定。</x:v>
       </x:c>
-      <x:c r="I93" s="4" t="str">
+      <x:c r="I158" s="9" t="str">
         <x:v>未来规划</x:v>
       </x:c>
-      <x:c r="J93" s="4" t="str">
+      <x:c r="J158" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K93" s="4" t="str">
+      <x:c r="K158" s="9" t="str">
         <x:v>未来概要</x:v>
       </x:c>
-      <x:c r="L93" s="4" t="str">
-        <x:v>docs/testing/cases/05-TM-005-usage-statistics.md:15</x:v>
-      </x:c>
-      <x:c r="M93" s="4" t="str">
+      <x:c r="L158" s="9" t="str">
+        <x:v>docs/testing/cases/06-TM-006-cost-estimates.md:15</x:v>
+      </x:c>
+      <x:c r="M158" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-    </x:row>
-    <x:row r="94" ht="57" customHeight="1">
-      <x:c r="A94" s="9" t="str">
-        <x:v>TM-005</x:v>
-      </x:c>
-      <x:c r="B94" s="9" t="str">
-        <x:v>E2E-TM005-002</x:v>
-      </x:c>
-      <x:c r="C94" s="9" t="str">
-        <x:v>时区、月边界与缺失值</x:v>
-      </x:c>
-      <x:c r="D94" s="9" t="str">
+      <x:c r="N158" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" ht="57" customHeight="1">
+      <x:c r="A159" s="4" t="str">
+        <x:v>TM-006</x:v>
+      </x:c>
+      <x:c r="B159" s="4" t="str">
+        <x:v>E2E-TM006-002</x:v>
+      </x:c>
+      <x:c r="C159" s="4" t="str">
+        <x:v>历史价格、多币种和未知费用</x:v>
+      </x:c>
+      <x:c r="D159" s="4" t="str">
         <x:v>待拆解</x:v>
       </x:c>
-      <x:c r="E94" s="9" t="str">
+      <x:c r="E159" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F94" s="9" t="str">
-        <x:v>数据集 date_ranges；复用date_ranges中的2026-09-28T15:59:59Z与16:00:00Z、2026-08-30T15:59:59Z与16:00:00Z边界。另需补充覆盖缺口、已覆盖零调用日、unknown字段三类状态；当前生成器未覆盖后面三类。</x:v>
-      </x:c>
-      <x:c r="G94" s="9" t="str">
-        <x:v>Shanghai下15:59:59Z仍属前日、16:00:00Z属次日；UTC下二者同属UTC日期。无覆盖显示缺失，真实零可显示0，unknown字段显示未知；不得互相代替。各范围expected须独立按当地日期边界列出，不调用产品查询生成。</x:v>
-      </x:c>
-      <x:c r="H94" s="9" t="str">
+      <x:c r="F159" s="4" t="str">
+        <x:v>数据集 pricing_extended；pricing_extended planned：同模型在生效时点T前后各一调用，两个独立价格版本；另有USD/CNY各一模型、无价模型和订阅估算模型。必须提供价格/订阅分摊规则及手算expected后才能实现。</x:v>
+      </x:c>
+      <x:c r="G159" s="4" t="str">
+        <x:v>T前后依各自生效版本计算，历史结果不会悄悄换价；USD与CNY分组，未约定汇率不得相加；无价格显示未知而非0；订阅必须明确估算口径。具体金额oracle依待定义订阅/价格合同生成，当前不得手填PASS。</x:v>
+      </x:c>
+      <x:c r="H159" s="4" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
 变化：待具体任务及数据设计细化。
 核验：暂无可执行数据库核验绑定。</x:v>
       </x:c>
-      <x:c r="I94" s="9" t="str">
+      <x:c r="I159" s="4" t="str">
         <x:v>未来规划</x:v>
       </x:c>
-      <x:c r="J94" s="9" t="str">
+      <x:c r="J159" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K94" s="9" t="str">
+      <x:c r="K159" s="4" t="str">
         <x:v>未来概要</x:v>
       </x:c>
-      <x:c r="L94" s="9" t="str">
-        <x:v>docs/testing/cases/05-TM-005-usage-statistics.md:32</x:v>
-      </x:c>
-      <x:c r="M94" s="9" t="str">
+      <x:c r="L159" s="4" t="str">
+        <x:v>docs/testing/cases/06-TM-006-cost-estimates.md:32</x:v>
+      </x:c>
+      <x:c r="M159" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-    </x:row>
-    <x:row r="95" ht="57" customHeight="1">
-      <x:c r="A95" s="4" t="str">
-        <x:v>TM-006</x:v>
-      </x:c>
-      <x:c r="B95" s="4" t="str">
-        <x:v>E2E-TM006-001</x:v>
-      </x:c>
-      <x:c r="C95" s="4" t="str">
-        <x:v>Token子项与基础费用</x:v>
-      </x:c>
-      <x:c r="D95" s="4" t="str">
+      <x:c r="N159" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" ht="57" customHeight="1">
+      <x:c r="A160" s="9" t="str">
+        <x:v>TM-007</x:v>
+      </x:c>
+      <x:c r="B160" s="9" t="str">
+        <x:v>E2E-TM007-001</x:v>
+      </x:c>
+      <x:c r="C160" s="9" t="str">
+        <x:v>离线、重启和补传幂等</x:v>
+      </x:c>
+      <x:c r="D160" s="9" t="str">
         <x:v>待拆解</x:v>
       </x:c>
-      <x:c r="E95" s="4" t="str">
+      <x:c r="E160" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F95" s="4" t="str">
-        <x:v>数据集 pricing；pricing由scripts/test_data.py生成合成非计费价格。gpt-5每百万input/cache/output为USD2/0.2/8；today-gpt input1000含cache200、output100含reasoning20。价格不是厂商现价。</x:v>
-      </x:c>
-      <x:c r="G95" s="4" t="str">
-        <x:v>单调用total=1100；费用=(800×2+200×0.2+100×8)/1000000=USD0.002440，reasoning20不另加价。today已知费用USD0.015190且有1条无价格，alice今日USD0.010090。使用Decimal/十进制独立oracle，不以界面舍入反推底层精度。</x:v>
-      </x:c>
-      <x:c r="H95" s="4" t="str">
+      <x:c r="F160" s="9" t="str">
+        <x:v>数据集 sync_faults；sync_faults planned；alice两个隔离设备A/B，设备A调用100/10、B调用200/20；真实FastAPI/SQLite服务，可由外部fixture断网/恢复。账号继续用隔离测试fixture。</x:v>
+      </x:c>
+      <x:c r="G160" s="9" t="str">
+        <x:v>离线重启不丢队列；恢复后2唯一调用、input300/output30/total330；重复批次不再加量。客户端只在真实确认后标已同步，个人合计与对应团队子集一致。</x:v>
+      </x:c>
+      <x:c r="H160" s="9" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
 变化：待具体任务及数据设计细化。
 核验：暂无可执行数据库核验绑定。</x:v>
       </x:c>
-      <x:c r="I95" s="4" t="str">
+      <x:c r="I160" s="9" t="str">
         <x:v>未来规划</x:v>
       </x:c>
-      <x:c r="J95" s="4" t="str">
+      <x:c r="J160" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K95" s="4" t="str">
+      <x:c r="K160" s="9" t="str">
         <x:v>未来概要</x:v>
       </x:c>
-      <x:c r="L95" s="4" t="str">
-        <x:v>docs/testing/cases/06-TM-006-cost-estimates.md:15</x:v>
-      </x:c>
-      <x:c r="M95" s="4" t="str">
+      <x:c r="L160" s="9" t="str">
+        <x:v>docs/testing/cases/07-TM-007-team-sync.md:11</x:v>
+      </x:c>
+      <x:c r="M160" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-    </x:row>
-    <x:row r="96" ht="57" customHeight="1">
-      <x:c r="A96" s="9" t="str">
-        <x:v>TM-006</x:v>
-      </x:c>
-      <x:c r="B96" s="9" t="str">
-        <x:v>E2E-TM006-002</x:v>
-      </x:c>
-      <x:c r="C96" s="9" t="str">
-        <x:v>历史价格、多币种和未知费用</x:v>
-      </x:c>
-      <x:c r="D96" s="9" t="str">
+      <x:c r="N160" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" ht="57" customHeight="1">
+      <x:c r="A161" s="4" t="str">
+        <x:v>TM-007</x:v>
+      </x:c>
+      <x:c r="B161" s="4" t="str">
+        <x:v>E2E-TM007-002</x:v>
+      </x:c>
+      <x:c r="C161" s="4" t="str">
+        <x:v>部分确认、中断和账号切换</x:v>
+      </x:c>
+      <x:c r="D161" s="4" t="str">
         <x:v>待拆解</x:v>
       </x:c>
-      <x:c r="E96" s="9" t="str">
+      <x:c r="E161" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F96" s="9" t="str">
-        <x:v>数据集 pricing_extended；pricing_extended planned：同模型在生效时点T前后各一调用，两个独立价格版本；另有USD/CNY各一模型、无价模型和订阅估算模型。必须提供价格/订阅分摊规则及手算expected后才能实现。</x:v>
-      </x:c>
-      <x:c r="G96" s="9" t="str">
-        <x:v>T前后依各自生效版本计算，历史结果不会悄悄换价；USD与CNY分组，未约定汇率不得相加；无价格显示未知而非0；订阅必须明确估算口径。具体金额oracle依待定义订阅/价格合同生成，当前不得手填PASS。</x:v>
-      </x:c>
-      <x:c r="H96" s="9" t="str">
+      <x:c r="F161" s="4" t="str">
+        <x:v>数据集 sync_faults；准备alice的三条唯一事件A/B/C，总量各110/220/330；控制服务仅确认A后断开，B可能已提交但响应丢失，C未提交。另有bob账号。故障注入必须在真实服务外部或明确测试环境中完成，不能绕过认证。</x:v>
+      </x:c>
+      <x:c r="G161" s="4" t="str">
+        <x:v>最终alice的A/B/C各一次、total660；响应丢失不造成B重复；bob不能承接或篡改alice既有事件归属。切换时旧队列按已批准归属策略隔离，不能默认为新登录账号。</x:v>
+      </x:c>
+      <x:c r="H161" s="4" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
 变化：待具体任务及数据设计细化。
 核验：暂无可执行数据库核验绑定。</x:v>
       </x:c>
-      <x:c r="I96" s="9" t="str">
+      <x:c r="I161" s="4" t="str">
         <x:v>未来规划</x:v>
       </x:c>
-      <x:c r="J96" s="9" t="str">
+      <x:c r="J161" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K96" s="9" t="str">
+      <x:c r="K161" s="4" t="str">
         <x:v>未来概要</x:v>
       </x:c>
-      <x:c r="L96" s="9" t="str">
-        <x:v>docs/testing/cases/06-TM-006-cost-estimates.md:32</x:v>
-      </x:c>
-      <x:c r="M96" s="9" t="str">
+      <x:c r="L161" s="4" t="str">
+        <x:v>docs/testing/cases/07-TM-007-team-sync.md:28</x:v>
+      </x:c>
+      <x:c r="M161" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-    </x:row>
-    <x:row r="97" ht="57" customHeight="1">
-      <x:c r="A97" s="4" t="str">
+      <x:c r="N161" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" ht="57" customHeight="1">
+      <x:c r="A162" s="9" t="str">
         <x:v>TM-007</x:v>
       </x:c>
-      <x:c r="B97" s="4" t="str">
-        <x:v>E2E-TM007-001</x:v>
-      </x:c>
-      <x:c r="C97" s="4" t="str">
-        <x:v>离线、重启和补传幂等</x:v>
-      </x:c>
-      <x:c r="D97" s="4" t="str">
+      <x:c r="B162" s="9" t="str">
+        <x:v>E2E-TM007-003</x:v>
+      </x:c>
+      <x:c r="C162" s="9" t="str">
+        <x:v>上传白名单与项目映射</x:v>
+      </x:c>
+      <x:c r="D162" s="9" t="str">
         <x:v>待拆解</x:v>
       </x:c>
-      <x:c r="E97" s="4" t="str">
+      <x:c r="E162" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F97" s="4" t="str">
-        <x:v>数据集 sync_faults；sync_faults planned；alice两个隔离设备A/B，设备A调用100/10、B调用200/20；真实FastAPI/SQLite服务，可由外部fixture断网/恢复。账号继续用隔离测试fixture。</x:v>
-      </x:c>
-      <x:c r="G97" s="4" t="str">
-        <x:v>离线重启不丢队列；恢复后2唯一调用、input300/output30/total330；重复批次不再加量。客户端只在真实确认后标已同步，个人合计与对应团队子集一致。</x:v>
-      </x:c>
-      <x:c r="H97" s="4" t="str">
+      <x:c r="F162" s="9" t="str">
+        <x:v>数据集 sync_faults；合成日志包含唯一正文/代码/API-key/完整路径哨兵，以及合法用量/必要去重元数据；只用假值。准备已归属项目A和未归属事件B，待sync_faults生成。</x:v>
+      </x:c>
+      <x:c r="G162" s="9" t="str">
+        <x:v>网络载荷/持久服务数据均不得含正文、代码、key或完整本机路径；只有批准用量/去重字段。B可明确分配，分配不增加事件量、也不跨团队归属。</x:v>
+      </x:c>
+      <x:c r="H162" s="9" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
 变化：待具体任务及数据设计细化。
 核验：暂无可执行数据库核验绑定。</x:v>
       </x:c>
-      <x:c r="I97" s="4" t="str">
+      <x:c r="I162" s="9" t="str">
         <x:v>未来规划</x:v>
       </x:c>
-      <x:c r="J97" s="4" t="str">
+      <x:c r="J162" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K97" s="4" t="str">
+      <x:c r="K162" s="9" t="str">
         <x:v>未来概要</x:v>
       </x:c>
-      <x:c r="L97" s="4" t="str">
-        <x:v>docs/testing/cases/07-TM-007-team-sync.md:11</x:v>
-      </x:c>
-      <x:c r="M97" s="4" t="str">
+      <x:c r="L162" s="9" t="str">
+        <x:v>docs/testing/cases/07-TM-007-team-sync.md:45</x:v>
+      </x:c>
+      <x:c r="M162" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-    </x:row>
-    <x:row r="98" ht="57" customHeight="1">
-      <x:c r="A98" s="9" t="str">
+      <x:c r="N162" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" ht="57" customHeight="1">
+      <x:c r="A163" s="4" t="str">
         <x:v>TM-007</x:v>
       </x:c>
-      <x:c r="B98" s="9" t="str">
-        <x:v>E2E-TM007-002</x:v>
-      </x:c>
-      <x:c r="C98" s="9" t="str">
-        <x:v>部分确认、中断和账号切换</x:v>
-      </x:c>
-      <x:c r="D98" s="9" t="str">
+      <x:c r="B163" s="4" t="str">
+        <x:v>E2E-TM007-004</x:v>
+      </x:c>
+      <x:c r="C163" s="4" t="str">
+        <x:v>统计越权与停用后上传</x:v>
+      </x:c>
+      <x:c r="D163" s="4" t="str">
         <x:v>待拆解</x:v>
       </x:c>
-      <x:c r="E98" s="9" t="str">
+      <x:c r="E163" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F98" s="9" t="str">
-        <x:v>数据集 sync_faults；准备alice的三条唯一事件A/B/C，总量各110/220/330；控制服务仅确认A后断开，B可能已提交但响应丢失，C未提交。另有bob账号。故障注入必须在真实服务外部或明确测试环境中完成，不能绕过认证。</x:v>
-      </x:c>
-      <x:c r="G98" s="9" t="str">
-        <x:v>最终alice的A/B/C各一次、total660；响应丢失不造成B重复；bob不能承接或篡改alice既有事件归属。切换时旧队列按已批准归属策略隔离，不能默认为新登录账号。</x:v>
-      </x:c>
-      <x:c r="H98" s="9" t="str">
+      <x:c r="F163" s="4" t="str">
+        <x:v>数据集 sync_faults；alice项目A调用100/10，bob项目B调用200/20；成员alice与管理员独立会话；alice另有一条未确认调用C=50/5。sync_faults与可重建统计SQL尚未实现。</x:v>
+      </x:c>
+      <x:c r="G163" s="4" t="str">
+        <x:v>成员无权请求被服务端拒绝，UI不显示bob的220；停用后旧会话及上传拒绝，C不能标为已确认；合法历史不能被失败上传删除。此处补足TM-001仅身份/管理接口权限的范围。</x:v>
+      </x:c>
+      <x:c r="H163" s="4" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
 变化：待具体任务及数据设计细化。
 核验：暂无可执行数据库核验绑定。</x:v>
       </x:c>
-      <x:c r="I98" s="9" t="str">
+      <x:c r="I163" s="4" t="str">
         <x:v>未来规划</x:v>
       </x:c>
-      <x:c r="J98" s="9" t="str">
+      <x:c r="J163" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K98" s="9" t="str">
+      <x:c r="K163" s="4" t="str">
         <x:v>未来概要</x:v>
       </x:c>
-      <x:c r="L98" s="9" t="str">
-        <x:v>docs/testing/cases/07-TM-007-team-sync.md:28</x:v>
-      </x:c>
-      <x:c r="M98" s="9" t="str">
+      <x:c r="L163" s="4" t="str">
+        <x:v>docs/testing/cases/07-TM-007-team-sync.md:62</x:v>
+      </x:c>
+      <x:c r="M163" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-    </x:row>
-    <x:row r="99" ht="57" customHeight="1">
-      <x:c r="A99" s="4" t="str">
-        <x:v>TM-007</x:v>
-      </x:c>
-      <x:c r="B99" s="4" t="str">
-        <x:v>E2E-TM007-003</x:v>
-      </x:c>
-      <x:c r="C99" s="4" t="str">
-        <x:v>上传白名单与项目映射</x:v>
-      </x:c>
-      <x:c r="D99" s="4" t="str">
+      <x:c r="N163" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" ht="57" customHeight="1">
+      <x:c r="A164" s="9" t="str">
+        <x:v>TM-008</x:v>
+      </x:c>
+      <x:c r="B164" s="9" t="str">
+        <x:v>E2E-TM008-001</x:v>
+      </x:c>
+      <x:c r="C164" s="9" t="str">
+        <x:v>筛选一致的CSV导出</x:v>
+      </x:c>
+      <x:c r="D164" s="9" t="str">
         <x:v>待拆解</x:v>
       </x:c>
-      <x:c r="E99" s="4" t="str">
+      <x:c r="E164" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F99" s="4" t="str">
-        <x:v>数据集 sync_faults；合成日志包含唯一正文/代码/API-key/完整路径哨兵，以及合法用量/必要去重元数据；只用假值。准备已归属项目A和未归属事件B，待sync_faults生成。</x:v>
-      </x:c>
-      <x:c r="G99" s="4" t="str">
-        <x:v>网络载荷/持久服务数据均不得含正文、代码、key或完整本机路径；只有批准用量/去重字段。B可明确分配，分配不增加事件量、也不跨团队归属。</x:v>
-      </x:c>
-      <x:c r="H99" s="4" t="str">
+      <x:c r="F164" s="9" t="str">
+        <x:v>数据集 export_rows；export_rows planned；两成员、两个模型、时间范围内外各有事件，独立清单明确每条ID/字段/权限。先具备TM-005/007统计和授权。</x:v>
+      </x:c>
+      <x:c r="G164" s="9" t="str">
+        <x:v>每次CSV仅包含当次筛选且授权可见记录，行数/ID/汇总等于独立清单与界面；不混入旧筛选、其他成员或范围外记录。已知/未知费用语义一致。</x:v>
+      </x:c>
+      <x:c r="H164" s="9" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
 变化：待具体任务及数据设计细化。
 核验：暂无可执行数据库核验绑定。</x:v>
       </x:c>
-      <x:c r="I99" s="4" t="str">
+      <x:c r="I164" s="9" t="str">
         <x:v>未来规划</x:v>
       </x:c>
-      <x:c r="J99" s="4" t="str">
+      <x:c r="J164" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K99" s="4" t="str">
+      <x:c r="K164" s="9" t="str">
         <x:v>未来概要</x:v>
       </x:c>
-      <x:c r="L99" s="4" t="str">
-        <x:v>docs/testing/cases/07-TM-007-team-sync.md:45</x:v>
-      </x:c>
-      <x:c r="M99" s="4" t="str">
+      <x:c r="L164" s="9" t="str">
+        <x:v>docs/testing/cases/08-TM-008-csv-export.md:11</x:v>
+      </x:c>
+      <x:c r="M164" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-    </x:row>
-    <x:row r="100" ht="57" customHeight="1">
-      <x:c r="A100" s="9" t="str">
-        <x:v>TM-007</x:v>
-      </x:c>
-      <x:c r="B100" s="9" t="str">
-        <x:v>E2E-TM007-004</x:v>
-      </x:c>
-      <x:c r="C100" s="9" t="str">
-        <x:v>统计越权与停用后上传</x:v>
-      </x:c>
-      <x:c r="D100" s="9" t="str">
+      <x:c r="N164" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" ht="57" customHeight="1">
+      <x:c r="A165" s="4" t="str">
+        <x:v>TM-008</x:v>
+      </x:c>
+      <x:c r="B165" s="4" t="str">
+        <x:v>E2E-TM008-002</x:v>
+      </x:c>
+      <x:c r="C165" s="4" t="str">
+        <x:v>CSV转义、未知值及权限</x:v>
+      </x:c>
+      <x:c r="D165" s="4" t="str">
         <x:v>待拆解</x:v>
       </x:c>
-      <x:c r="E100" s="9" t="str">
+      <x:c r="E165" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F100" s="9" t="str">
-        <x:v>数据集 sync_faults；alice项目A调用100/10，bob项目B调用200/20；成员alice与管理员独立会话；alice另有一条未确认调用C=50/5。sync_faults与可重建统计SQL尚未实现。</x:v>
-      </x:c>
-      <x:c r="G100" s="9" t="str">
-        <x:v>成员无权请求被服务端拒绝，UI不显示bob的220；停用后旧会话及上传拒绝，C不能标为已确认；合法历史不能被失败上传删除。此处补足TM-001仅身份/管理接口权限的范围。</x:v>
-      </x:c>
-      <x:c r="H100" s="9" t="str">
+      <x:c r="F165" s="4" t="str">
+        <x:v>数据集 export_rows；export_rows需含字段 a,b、say "hi"、带实际换行的项目名、未知费用与非ASCII模型名；两成员各有可区分哨兵事件。只在隔离数据中使用。</x:v>
+      </x:c>
+      <x:c r="G165" s="4" t="str">
+        <x:v>逗号、双引号、嵌入换行均round-trip一致，Unicode不损坏；未知值不写成0；他人哨兵不出现在文件。若导出失败，不能留下看似完整的半文件。</x:v>
+      </x:c>
+      <x:c r="H165" s="4" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
 变化：待具体任务及数据设计细化。
 核验：暂无可执行数据库核验绑定。</x:v>
       </x:c>
-      <x:c r="I100" s="9" t="str">
+      <x:c r="I165" s="4" t="str">
         <x:v>未来规划</x:v>
       </x:c>
-      <x:c r="J100" s="9" t="str">
+      <x:c r="J165" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K100" s="9" t="str">
+      <x:c r="K165" s="4" t="str">
         <x:v>未来概要</x:v>
       </x:c>
-      <x:c r="L100" s="9" t="str">
-        <x:v>docs/testing/cases/07-TM-007-team-sync.md:62</x:v>
-      </x:c>
-      <x:c r="M100" s="9" t="str">
+      <x:c r="L165" s="4" t="str">
+        <x:v>docs/testing/cases/08-TM-008-csv-export.md:28</x:v>
+      </x:c>
+      <x:c r="M165" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-    </x:row>
-    <x:row r="101" ht="57" customHeight="1">
-      <x:c r="A101" s="4" t="str">
-        <x:v>TM-008</x:v>
-      </x:c>
-      <x:c r="B101" s="4" t="str">
-        <x:v>E2E-TM008-001</x:v>
-      </x:c>
-      <x:c r="C101" s="4" t="str">
-        <x:v>筛选一致的CSV导出</x:v>
-      </x:c>
-      <x:c r="D101" s="4" t="str">
+      <x:c r="N165" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" ht="57" customHeight="1">
+      <x:c r="A166" s="9" t="str">
+        <x:v>TM-009</x:v>
+      </x:c>
+      <x:c r="B166" s="9" t="str">
+        <x:v>E2E-TM009-001</x:v>
+      </x:c>
+      <x:c r="C166" s="9" t="str">
+        <x:v>80%/100%提醒幂等</x:v>
+      </x:c>
+      <x:c r="D166" s="9" t="str">
         <x:v>待拆解</x:v>
       </x:c>
-      <x:c r="E101" s="4" t="str">
+      <x:c r="E166" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F101" s="4" t="str">
-        <x:v>数据集 export_rows；export_rows planned；两成员、两个模型、时间范围内外各有事件，独立清单明确每条ID/字段/权限。先具备TM-005/007统计和授权。</x:v>
-      </x:c>
-      <x:c r="G101" s="4" t="str">
-        <x:v>每次CSV仅包含当次筛选且授权可见记录，行数/ID/汇总等于独立清单与界面；不混入旧筛选、其他成员或范围外记录。已知/未知费用语义一致。</x:v>
-      </x:c>
-      <x:c r="H101" s="4" t="str">
+      <x:c r="F166" s="9" t="str">
+        <x:v>数据集 budget_periods；budget_periods planned；独立个人、项目和团队预算分别100个合成USD单位，同周期使用量依次79→80→99→100；原始调用与价格要能精确形成这些费用。</x:v>
+      </x:c>
+      <x:c r="G166" s="9" t="str">
+        <x:v>每预算每周期80与100各最多一次，未达到不发；重扫/重启/重复上传不重发；预算仅提醒，不拦截模型调用。三层预算分别按其授权范围计算。</x:v>
+      </x:c>
+      <x:c r="H166" s="9" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
 变化：待具体任务及数据设计细化。
 核验：暂无可执行数据库核验绑定。</x:v>
       </x:c>
-      <x:c r="I101" s="4" t="str">
+      <x:c r="I166" s="9" t="str">
         <x:v>未来规划</x:v>
       </x:c>
-      <x:c r="J101" s="4" t="str">
+      <x:c r="J166" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K101" s="4" t="str">
+      <x:c r="K166" s="9" t="str">
         <x:v>未来概要</x:v>
       </x:c>
-      <x:c r="L101" s="4" t="str">
-        <x:v>docs/testing/cases/08-TM-008-csv-export.md:11</x:v>
-      </x:c>
-      <x:c r="M101" s="4" t="str">
+      <x:c r="L166" s="9" t="str">
+        <x:v>docs/testing/cases/09-TM-009-budget-alerts.md:11</x:v>
+      </x:c>
+      <x:c r="M166" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-    </x:row>
-    <x:row r="102" ht="57" customHeight="1">
-      <x:c r="A102" s="9" t="str">
-        <x:v>TM-008</x:v>
-      </x:c>
-      <x:c r="B102" s="9" t="str">
-        <x:v>E2E-TM008-002</x:v>
-      </x:c>
-      <x:c r="C102" s="9" t="str">
-        <x:v>CSV转义、未知值及权限</x:v>
-      </x:c>
-      <x:c r="D102" s="9" t="str">
+      <x:c r="N166" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" ht="57" customHeight="1">
+      <x:c r="A167" s="4" t="str">
+        <x:v>TM-009</x:v>
+      </x:c>
+      <x:c r="B167" s="4" t="str">
+        <x:v>E2E-TM009-002</x:v>
+      </x:c>
+      <x:c r="C167" s="4" t="str">
+        <x:v>新周期、币种与通知恢复</x:v>
+      </x:c>
+      <x:c r="D167" s="4" t="str">
         <x:v>待拆解</x:v>
       </x:c>
-      <x:c r="E102" s="9" t="str">
+      <x:c r="E167" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F102" s="9" t="str">
-        <x:v>数据集 export_rows；export_rows需含字段 a,b、say "hi"、带实际换行的项目名、未知费用与非ASCII模型名；两成员各有可区分哨兵事件。只在隔离数据中使用。</x:v>
-      </x:c>
-      <x:c r="G102" s="9" t="str">
-        <x:v>逗号、双引号、嵌入换行均round-trip一致，Unicode不损坏；未知值不写成0；他人哨兵不出现在文件。若导出失败，不能留下看似完整的半文件。</x:v>
-      </x:c>
-      <x:c r="H102" s="9" t="str">
+      <x:c r="F167" s="4" t="str">
+        <x:v>数据集 budget_periods；两个币种独立预算；旧周期已发80/100阈值，参考时钟可由产品支持的测试配置推进；测试通知权限可以拒绝及恢复，不能修改用户其他App授权。</x:v>
+      </x:c>
+      <x:c r="G167" s="4" t="str">
+        <x:v>系统拒绝不丢失应用内状态、不造成重试通知风暴；新周期独立重置，允许新一轮各阈值一次；币种分开计算。通知补发策略需在对应需求明确，不能由测试临时猜测。</x:v>
+      </x:c>
+      <x:c r="H167" s="4" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
 变化：待具体任务及数据设计细化。
 核验：暂无可执行数据库核验绑定。</x:v>
       </x:c>
-      <x:c r="I102" s="9" t="str">
+      <x:c r="I167" s="4" t="str">
         <x:v>未来规划</x:v>
       </x:c>
-      <x:c r="J102" s="9" t="str">
+      <x:c r="J167" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K102" s="9" t="str">
+      <x:c r="K167" s="4" t="str">
         <x:v>未来概要</x:v>
       </x:c>
-      <x:c r="L102" s="9" t="str">
-        <x:v>docs/testing/cases/08-TM-008-csv-export.md:28</x:v>
-      </x:c>
-      <x:c r="M102" s="9" t="str">
+      <x:c r="L167" s="4" t="str">
+        <x:v>docs/testing/cases/09-TM-009-budget-alerts.md:28</x:v>
+      </x:c>
+      <x:c r="M167" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-    </x:row>
-    <x:row r="103" ht="57" customHeight="1">
-      <x:c r="A103" s="4" t="str">
-        <x:v>TM-009</x:v>
-      </x:c>
-      <x:c r="B103" s="4" t="str">
-        <x:v>E2E-TM009-001</x:v>
-      </x:c>
-      <x:c r="C103" s="4" t="str">
-        <x:v>80%/100%提醒幂等</x:v>
-      </x:c>
-      <x:c r="D103" s="4" t="str">
+      <x:c r="N167" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" ht="72" customHeight="1">
+      <x:c r="A168" s="9" t="str">
+        <x:v>TM-010</x:v>
+      </x:c>
+      <x:c r="B168" s="9" t="str">
+        <x:v>E2E-TM010-001</x:v>
+      </x:c>
+      <x:c r="C168" s="9" t="str">
+        <x:v>稳定版发现更新与数据保留</x:v>
+      </x:c>
+      <x:c r="D168" s="9" t="str">
         <x:v>待拆解</x:v>
       </x:c>
-      <x:c r="E103" s="4" t="str">
+      <x:c r="E168" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F103" s="4" t="str">
-        <x:v>数据集 budget_periods；budget_periods planned；独立个人、项目和团队预算分别100个合成USD单位，同周期使用量依次79→80→99→100；原始调用与价格要能精确形成这些费用。</x:v>
-      </x:c>
-      <x:c r="G103" s="4" t="str">
-        <x:v>每预算每周期80与100各最多一次，未达到不发；重扫/重启/重复上传不重发；预算仅提醒，不拦截模型调用。三层预算分别按其授权范围计算。</x:v>
-      </x:c>
-      <x:c r="H103" s="4" t="str">
+      <x:c r="F168" s="9" t="str">
+        <x:v>数据集 update_packages；依赖TM-001/007；update_packages planned。需真实已分发稳定版、候选最终包及相同分发profile的签名/清单；旧版有账号设置、手动地址、统计/队列独立快照。首版无历史稳定版时使用SOP017规定的候选→受控高版，不伪称稳定升级。</x:v>
+      </x:c>
+      <x:c r="G168" s="9" t="str">
+        <x:v>更新频率和说明可用；只有声明候选被安装，Sparkle自主重启；更新前后账号/设置/统计与快照一致，队列不丢失不重复。完整更新体验仍为未来功能，TM-001-004通过只证明最小更新路径。</x:v>
+      </x:c>
+      <x:c r="H168" s="9" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
 变化：待具体任务及数据设计细化。
 核验：暂无可执行数据库核验绑定。</x:v>
       </x:c>
-      <x:c r="I103" s="4" t="str">
+      <x:c r="I168" s="9" t="str">
         <x:v>未来规划</x:v>
       </x:c>
-      <x:c r="J103" s="4" t="str">
+      <x:c r="J168" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K103" s="4" t="str">
+      <x:c r="K168" s="9" t="str">
         <x:v>未来概要</x:v>
       </x:c>
-      <x:c r="L103" s="4" t="str">
-        <x:v>docs/testing/cases/09-TM-009-budget-alerts.md:11</x:v>
-      </x:c>
-      <x:c r="M103" s="4" t="str">
+      <x:c r="L168" s="9" t="str">
+        <x:v>docs/testing/cases/10-TM-010-software-updates.md:11</x:v>
+      </x:c>
+      <x:c r="M168" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-    </x:row>
-    <x:row r="104" ht="57" customHeight="1">
-      <x:c r="A104" s="9" t="str">
-        <x:v>TM-009</x:v>
-      </x:c>
-      <x:c r="B104" s="9" t="str">
-        <x:v>E2E-TM009-002</x:v>
-      </x:c>
-      <x:c r="C104" s="9" t="str">
-        <x:v>新周期、币种与通知恢复</x:v>
-      </x:c>
-      <x:c r="D104" s="9" t="str">
+      <x:c r="N168" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" ht="57" customHeight="1">
+      <x:c r="A169" s="4" t="str">
+        <x:v>TM-010</x:v>
+      </x:c>
+      <x:c r="B169" s="4" t="str">
+        <x:v>E2E-TM010-002</x:v>
+      </x:c>
+      <x:c r="C169" s="4" t="str">
+        <x:v>签名、网络、空间和迁移失败恢复</x:v>
+      </x:c>
+      <x:c r="D169" s="4" t="str">
         <x:v>待拆解</x:v>
       </x:c>
-      <x:c r="E104" s="9" t="str">
+      <x:c r="E169" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F104" s="9" t="str">
-        <x:v>数据集 budget_periods；两个币种独立预算；旧周期已发80/100阈值，参考时钟可由产品支持的测试配置推进；测试通知权限可以拒绝及恢复，不能修改用户其他App授权。</x:v>
-      </x:c>
-      <x:c r="G104" s="9" t="str">
-        <x:v>系统拒绝不丢失应用内状态、不造成重试通知风暴；新周期独立重置，允许新一轮各阈值一次；币种分开计算。通知补发策略需在对应需求明确，不能由测试临时猜测。</x:v>
-      </x:c>
-      <x:c r="H104" s="9" t="str">
+      <x:c r="F169" s="4" t="str">
+        <x:v>数据集 update_packages；对同一干净旧版分别建立四个隔离子场景：坏签名包、下载中断、受限测试卷空间不足、受控迁移失败；每个保存旧版包/DB/配置摘要。故障不能作用用户系统盘/生产库。</x:v>
+      </x:c>
+      <x:c r="G169" s="4" t="str">
+        <x:v>每个失败均不能形成半更新；原账号/统计和包的可用状态可验证。网络恢复后的成功需要完整包校验；迁移失败恢复来源与摘要明确。四个子场景全部为本case必需，不能挑一项通过。</x:v>
+      </x:c>
+      <x:c r="H169" s="4" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
 变化：待具体任务及数据设计细化。
 核验：暂无可执行数据库核验绑定。</x:v>
       </x:c>
-      <x:c r="I104" s="9" t="str">
+      <x:c r="I169" s="4" t="str">
         <x:v>未来规划</x:v>
       </x:c>
-      <x:c r="J104" s="9" t="str">
+      <x:c r="J169" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K104" s="9" t="str">
+      <x:c r="K169" s="4" t="str">
         <x:v>未来概要</x:v>
       </x:c>
-      <x:c r="L104" s="9" t="str">
-        <x:v>docs/testing/cases/09-TM-009-budget-alerts.md:28</x:v>
-      </x:c>
-      <x:c r="M104" s="9" t="str">
+      <x:c r="L169" s="4" t="str">
+        <x:v>docs/testing/cases/10-TM-010-software-updates.md:28</x:v>
+      </x:c>
+      <x:c r="M169" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-    </x:row>
-    <x:row r="105" ht="72" customHeight="1">
-      <x:c r="A105" s="4" t="str">
+      <x:c r="N169" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" ht="57" customHeight="1">
+      <x:c r="A170" s="9" t="str">
         <x:v>TM-010</x:v>
       </x:c>
-      <x:c r="B105" s="4" t="str">
-        <x:v>E2E-TM010-001</x:v>
-      </x:c>
-      <x:c r="C105" s="4" t="str">
-        <x:v>稳定版发现更新与数据保留</x:v>
-      </x:c>
-      <x:c r="D105" s="4" t="str">
+      <x:c r="B170" s="9" t="str">
+        <x:v>E2E-TM010-003</x:v>
+      </x:c>
+      <x:c r="C170" s="9" t="str">
+        <x:v>升级默认地址和手动覆盖</x:v>
+      </x:c>
+      <x:c r="D170" s="9" t="str">
         <x:v>待拆解</x:v>
       </x:c>
-      <x:c r="E105" s="4" t="str">
+      <x:c r="E170" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F105" s="4" t="str">
-        <x:v>数据集 update_packages；依赖TM-001/007；update_packages planned。需真实已分发稳定版、候选最终包及相同分发profile的签名/清单；旧版有账号设置、手动地址、统计/队列独立快照。首版无历史稳定版时使用SOP017规定的候选→受控高版，不伪称稳定升级。</x:v>
-      </x:c>
-      <x:c r="G105" s="4" t="str">
-        <x:v>更新频率和说明可用；只有声明候选被安装，Sparkle自主重启；更新前后账号/设置/统计与快照一致，队列不丢失不重复。完整更新体验仍为未来功能，TM-001-004通过只证明最小更新路径。</x:v>
-      </x:c>
-      <x:c r="H105" s="4" t="str">
+      <x:c r="F170" s="9" t="str">
+        <x:v>数据集 server_default_migration；server_default_migration planned；两套旧安装A从未设置地址、B已手动设置；候选内置一个届时确定且测试可访问的生产HTTPS默认地址。两源有独立账号/数据/会话，公钥不可随URL编辑。</x:v>
+      </x:c>
+      <x:c r="G170" s="9" t="str">
+        <x:v>只有无手动覆盖安装跟随新版默认；显式覆盖即使恰好等于旧默认也应按已经确定的配置来源规则处理。改变origin需重新服务认证，旧token不能跨源复用。</x:v>
+      </x:c>
+      <x:c r="H170" s="9" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
 变化：待具体任务及数据设计细化。
 核验：暂无可执行数据库核验绑定。</x:v>
       </x:c>
-      <x:c r="I105" s="4" t="str">
+      <x:c r="I170" s="9" t="str">
         <x:v>未来规划</x:v>
       </x:c>
-      <x:c r="J105" s="4" t="str">
+      <x:c r="J170" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K105" s="4" t="str">
+      <x:c r="K170" s="9" t="str">
         <x:v>未来概要</x:v>
       </x:c>
-      <x:c r="L105" s="4" t="str">
-        <x:v>docs/testing/cases/10-TM-010-software-updates.md:11</x:v>
-      </x:c>
-      <x:c r="M105" s="4" t="str">
+      <x:c r="L170" s="9" t="str">
+        <x:v>docs/testing/cases/10-TM-010-software-updates.md:45</x:v>
+      </x:c>
+      <x:c r="M170" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-    </x:row>
-    <x:row r="106" ht="57" customHeight="1">
-      <x:c r="A106" s="9" t="str">
-        <x:v>TM-010</x:v>
-      </x:c>
-      <x:c r="B106" s="9" t="str">
-        <x:v>E2E-TM010-002</x:v>
-      </x:c>
-      <x:c r="C106" s="9" t="str">
-        <x:v>签名、网络、空间和迁移失败恢复</x:v>
-      </x:c>
-      <x:c r="D106" s="9" t="str">
+      <x:c r="N170" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" ht="57" customHeight="1">
+      <x:c r="A171" s="4" t="str">
+        <x:v>TM-011</x:v>
+      </x:c>
+      <x:c r="B171" s="4" t="str">
+        <x:v>E2E-TM011-001</x:v>
+      </x:c>
+      <x:c r="C171" s="4" t="str">
+        <x:v>SQLite迁移与中断恢复</x:v>
+      </x:c>
+      <x:c r="D171" s="4" t="str">
         <x:v>待拆解</x:v>
       </x:c>
-      <x:c r="E106" s="9" t="str">
+      <x:c r="E171" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F106" s="9" t="str">
-        <x:v>数据集 update_packages；对同一干净旧版分别建立四个隔离子场景：坏签名包、下载中断、受限测试卷空间不足、受控迁移失败；每个保存旧版包/DB/配置摘要。故障不能作用用户系统盘/生产库。</x:v>
-      </x:c>
-      <x:c r="G106" s="9" t="str">
-        <x:v>每个失败均不能形成半更新；原账号/统计和包的可用状态可验证。网络恢复后的成功需要完整包校验；迁移失败恢复来源与摘要明确。四个子场景全部为本case必需，不能挑一项通过。</x:v>
-      </x:c>
-      <x:c r="H106" s="9" t="str">
+      <x:c r="F171" s="4" t="str">
+        <x:v>数据集 migration_snapshots；migration_snapshots planned；旧schema副本含固定账号/事件/队列、预计算记录数/Token/金额；候选迁移版本和明确故障点。全部作用私有临时库。</x:v>
+      </x:c>
+      <x:c r="G171" s="4" t="str">
+        <x:v>成功迁移只改变设计允许的schema/数据；账号、记录数、Token、费用/队列归属不丢。失败恢复到可启动一致状态，重复启动不重复迁移数据。不能以文件存在作为恢复成功。</x:v>
+      </x:c>
+      <x:c r="H171" s="4" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
 变化：待具体任务及数据设计细化。
 核验：暂无可执行数据库核验绑定。</x:v>
       </x:c>
-      <x:c r="I106" s="9" t="str">
+      <x:c r="I171" s="4" t="str">
         <x:v>未来规划</x:v>
       </x:c>
-      <x:c r="J106" s="9" t="str">
+      <x:c r="J171" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K106" s="9" t="str">
+      <x:c r="K171" s="4" t="str">
         <x:v>未来概要</x:v>
       </x:c>
-      <x:c r="L106" s="9" t="str">
-        <x:v>docs/testing/cases/10-TM-010-software-updates.md:28</x:v>
-      </x:c>
-      <x:c r="M106" s="9" t="str">
+      <x:c r="L171" s="4" t="str">
+        <x:v>docs/testing/cases/11-TM-011-data-migration.md:11</x:v>
+      </x:c>
+      <x:c r="M171" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-    </x:row>
-    <x:row r="107" ht="57" customHeight="1">
-      <x:c r="A107" s="4" t="str">
-        <x:v>TM-010</x:v>
-      </x:c>
-      <x:c r="B107" s="4" t="str">
-        <x:v>E2E-TM010-003</x:v>
-      </x:c>
-      <x:c r="C107" s="4" t="str">
-        <x:v>升级默认地址和手动覆盖</x:v>
-      </x:c>
-      <x:c r="D107" s="4" t="str">
+      <x:c r="N171" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" ht="57" customHeight="1">
+      <x:c r="A172" s="9" t="str">
+        <x:v>TM-011</x:v>
+      </x:c>
+      <x:c r="B172" s="9" t="str">
+        <x:v>E2E-TM011-002</x:v>
+      </x:c>
+      <x:c r="C172" s="9" t="str">
+        <x:v>未来SQLite到MySQL迁移</x:v>
+      </x:c>
+      <x:c r="D172" s="9" t="str">
         <x:v>待拆解</x:v>
       </x:c>
-      <x:c r="E107" s="4" t="str">
+      <x:c r="E172" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F107" s="4" t="str">
-        <x:v>数据集 server_default_migration；server_default_migration planned；两套旧安装A从未设置地址、B已手动设置；候选内置一个届时确定且测试可访问的生产HTTPS默认地址。两源有独立账号/数据/会话，公钥不可随URL编辑。</x:v>
-      </x:c>
-      <x:c r="G107" s="4" t="str">
-        <x:v>只有无手动覆盖安装跟随新版默认；显式覆盖即使恰好等于旧默认也应按已经确定的配置来源规则处理。改变origin需重新服务认证，旧token不能跨源复用。</x:v>
-      </x:c>
-      <x:c r="H107" s="4" t="str">
+      <x:c r="F172" s="9" t="str">
+        <x:v>数据集 migration_snapshots；仅后续独立版本适用；用户已确定v0.1.0继续SQLite。需要隔离源SQLite、目标MySQL、固定多成员/多项目用量快照、字符/时间/Decimal边界和独立expected。</x:v>
+      </x:c>
+      <x:c r="G172" s="9" t="str">
+        <x:v>源/目标记录数、Token、Decimal金额及权限结果一致，ID和幂等语义保持；不重复历史且旧源未被破坏。MySQL版本、字符集和迁移范围须在对应版本指定。</x:v>
+      </x:c>
+      <x:c r="H172" s="9" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
 变化：待具体任务及数据设计细化。
 核验：暂无可执行数据库核验绑定。</x:v>
       </x:c>
-      <x:c r="I107" s="4" t="str">
+      <x:c r="I172" s="9" t="str">
         <x:v>未来规划</x:v>
       </x:c>
-      <x:c r="J107" s="4" t="str">
+      <x:c r="J172" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K107" s="4" t="str">
+      <x:c r="K172" s="9" t="str">
         <x:v>未来概要</x:v>
       </x:c>
-      <x:c r="L107" s="4" t="str">
-        <x:v>docs/testing/cases/10-TM-010-software-updates.md:45</x:v>
-      </x:c>
-      <x:c r="M107" s="4" t="str">
+      <x:c r="L172" s="9" t="str">
+        <x:v>docs/testing/cases/11-TM-011-data-migration.md:28</x:v>
+      </x:c>
+      <x:c r="M172" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-    </x:row>
-    <x:row r="108" ht="57" customHeight="1">
-      <x:c r="A108" s="9" t="str">
+      <x:c r="N172" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" ht="57" customHeight="1">
+      <x:c r="A173" s="4" t="str">
         <x:v>TM-011</x:v>
       </x:c>
-      <x:c r="B108" s="9" t="str">
-        <x:v>E2E-TM011-001</x:v>
-      </x:c>
-      <x:c r="C108" s="9" t="str">
-        <x:v>SQLite迁移与中断恢复</x:v>
-      </x:c>
-      <x:c r="D108" s="9" t="str">
+      <x:c r="B173" s="4" t="str">
+        <x:v>E2E-TM011-003</x:v>
+      </x:c>
+      <x:c r="C173" s="4" t="str">
+        <x:v>备份恢复与旧客户端补传</x:v>
+      </x:c>
+      <x:c r="D173" s="4" t="str">
         <x:v>待拆解</x:v>
       </x:c>
-      <x:c r="E108" s="9" t="str">
+      <x:c r="E173" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F108" s="9" t="str">
-        <x:v>数据集 migration_snapshots；migration_snapshots planned；旧schema副本含固定账号/事件/队列、预计算记录数/Token/金额；候选迁移版本和明确故障点。全部作用私有临时库。</x:v>
-      </x:c>
-      <x:c r="G108" s="9" t="str">
-        <x:v>成功迁移只改变设计允许的schema/数据；账号、记录数、Token、费用/队列归属不丢。失败恢复到可启动一致状态，重复启动不重复迁移数据。不能以文件存在作为恢复成功。</x:v>
-      </x:c>
-      <x:c r="H108" s="9" t="str">
+      <x:c r="F173" s="4" t="str">
+        <x:v>数据集 migration_snapshots；隔离服务已确认事件A/B与旧客户端未确认C；备份包含schema/数据/版本/摘要，另保存不在备份里的独立oracle。恢复目标必须为空且带测试标记。</x:v>
+      </x:c>
+      <x:c r="G173" s="4" t="str">
+        <x:v>备份能实际恢复而非只压缩成功；A/B不丢，重复补传不增加；C最终只出现一次，账号/权限符合恢复基线。队列与服务确认一致，旧客户端协议兼容。</x:v>
+      </x:c>
+      <x:c r="H173" s="4" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
 变化：待具体任务及数据设计细化。
 核验：暂无可执行数据库核验绑定。</x:v>
       </x:c>
-      <x:c r="I108" s="9" t="str">
+      <x:c r="I173" s="4" t="str">
         <x:v>未来规划</x:v>
       </x:c>
-      <x:c r="J108" s="9" t="str">
+      <x:c r="J173" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K108" s="9" t="str">
+      <x:c r="K173" s="4" t="str">
         <x:v>未来概要</x:v>
       </x:c>
-      <x:c r="L108" s="9" t="str">
-        <x:v>docs/testing/cases/11-TM-011-data-migration.md:11</x:v>
-      </x:c>
-      <x:c r="M108" s="9" t="str">
+      <x:c r="L173" s="4" t="str">
+        <x:v>docs/testing/cases/11-TM-011-data-migration.md:45</x:v>
+      </x:c>
+      <x:c r="M173" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-    </x:row>
-    <x:row r="109" ht="57" customHeight="1">
-      <x:c r="A109" s="4" t="str">
+      <x:c r="N173" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174" ht="57" customHeight="1">
+      <x:c r="A174" s="9" t="str">
         <x:v>TM-011</x:v>
       </x:c>
-      <x:c r="B109" s="4" t="str">
-        <x:v>E2E-TM011-002</x:v>
-      </x:c>
-      <x:c r="C109" s="4" t="str">
-        <x:v>未来SQLite到MySQL迁移</x:v>
-      </x:c>
-      <x:c r="D109" s="4" t="str">
+      <x:c r="B174" s="9" t="str">
+        <x:v>E2E-TM011-004</x:v>
+      </x:c>
+      <x:c r="C174" s="9" t="str">
+        <x:v>保留时间边界与未同步保护</x:v>
+      </x:c>
+      <x:c r="D174" s="9" t="str">
         <x:v>待拆解</x:v>
       </x:c>
-      <x:c r="E109" s="4" t="str">
+      <x:c r="E174" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F109" s="4" t="str">
-        <x:v>数据集 migration_snapshots；仅后续独立版本适用；用户已确定v0.1.0继续SQLite。需要隔离源SQLite、目标MySQL、固定多成员/多项目用量快照、字符/时间/Decimal边界和独立expected。</x:v>
-      </x:c>
-      <x:c r="G109" s="4" t="str">
-        <x:v>源/目标记录数、Token、Decimal金额及权限结果一致，ID和幂等语义保持；不重复历史且旧源未被破坏。MySQL版本、字符集和迁移范围须在对应版本指定。</x:v>
-      </x:c>
-      <x:c r="H109" s="4" t="str">
+      <x:c r="F174" s="9" t="str">
+        <x:v>数据集 migration_snapshots；固定参考时间和Asia/Shanghai；本地90天/服务端365天。分别生成保留首日00:00、前一秒、前一天的已确认事件，以及同样超龄但未同步事件；具备可控时钟与独立边界oracle。</x:v>
+      </x:c>
+      <x:c r="G174" s="9" t="str">
+        <x:v>保留首日00:00仍在，早一秒的已同步记录被清理；本地/服务按各自天数独立判定。未同步记录即使超龄仍保护，成功补传仅计一次；历史缺失不能显示真实0。</x:v>
+      </x:c>
+      <x:c r="H174" s="9" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
 变化：待具体任务及数据设计细化。
 核验：暂无可执行数据库核验绑定。</x:v>
       </x:c>
-      <x:c r="I109" s="4" t="str">
+      <x:c r="I174" s="9" t="str">
         <x:v>未来规划</x:v>
       </x:c>
-      <x:c r="J109" s="4" t="str">
+      <x:c r="J174" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K109" s="4" t="str">
+      <x:c r="K174" s="9" t="str">
         <x:v>未来概要</x:v>
       </x:c>
-      <x:c r="L109" s="4" t="str">
-        <x:v>docs/testing/cases/11-TM-011-data-migration.md:28</x:v>
-      </x:c>
-      <x:c r="M109" s="4" t="str">
+      <x:c r="L174" s="9" t="str">
+        <x:v>docs/testing/cases/11-TM-011-data-migration.md:62</x:v>
+      </x:c>
+      <x:c r="M174" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-    </x:row>
-    <x:row r="110" ht="57" customHeight="1">
-      <x:c r="A110" s="9" t="str">
-        <x:v>TM-011</x:v>
-      </x:c>
-      <x:c r="B110" s="9" t="str">
-        <x:v>E2E-TM011-003</x:v>
-      </x:c>
-      <x:c r="C110" s="9" t="str">
-        <x:v>备份恢复与旧客户端补传</x:v>
-      </x:c>
-      <x:c r="D110" s="9" t="str">
+      <x:c r="N174" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" ht="57" customHeight="1">
+      <x:c r="A175" s="4" t="str">
+        <x:v>TM-012</x:v>
+      </x:c>
+      <x:c r="B175" s="4" t="str">
+        <x:v>E2E-TM012-001</x:v>
+      </x:c>
+      <x:c r="C175" s="4" t="str">
+        <x:v>菜单栏摘要、暂停恢复与刷新</x:v>
+      </x:c>
+      <x:c r="D175" s="4" t="str">
         <x:v>待拆解</x:v>
       </x:c>
-      <x:c r="E110" s="9" t="str">
+      <x:c r="E175" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F110" s="9" t="str">
-        <x:v>数据集 migration_snapshots；隔离服务已确认事件A/B与旧客户端未确认C；备份包含schema/数据/版本/摘要，另保存不在备份里的独立oracle。恢复目标必须为空且带测试标记。</x:v>
-      </x:c>
-      <x:c r="G110" s="9" t="str">
-        <x:v>备份能实际恢复而非只压缩成功；A/B不丢，重复补传不增加；C最终只出现一次，账号/权限符合恢复基线。队列与服务确认一致，旧客户端协议兼容。</x:v>
-      </x:c>
-      <x:c r="H110" s="9" t="str">
+      <x:c r="F175" s="4" t="str">
+        <x:v>数据集 diagnostic_states；diagnostic_states planned；已采集A=100/10；暂停期间追加B=200/20并重放A。依赖实际采集、统计和同步功能，使用专用日志目录。</x:v>
+      </x:c>
+      <x:c r="G175" s="4" t="str">
+        <x:v>初始total110、暂停期间仍110，恢复后唯一A/B、total330；手动刷新与重启不重复。菜单栏与主窗口同一筛选口径；暂停状态不伪装成没有日志。</x:v>
+      </x:c>
+      <x:c r="H175" s="4" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
 变化：待具体任务及数据设计细化。
 核验：暂无可执行数据库核验绑定。</x:v>
       </x:c>
-      <x:c r="I110" s="9" t="str">
+      <x:c r="I175" s="4" t="str">
         <x:v>未来规划</x:v>
       </x:c>
-      <x:c r="J110" s="9" t="str">
+      <x:c r="J175" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K110" s="9" t="str">
+      <x:c r="K175" s="4" t="str">
         <x:v>未来概要</x:v>
       </x:c>
-      <x:c r="L110" s="9" t="str">
-        <x:v>docs/testing/cases/11-TM-011-data-migration.md:45</x:v>
-      </x:c>
-      <x:c r="M110" s="9" t="str">
+      <x:c r="L175" s="4" t="str">
+        <x:v>docs/testing/cases/12-TM-012-menu-diagnostics.md:11</x:v>
+      </x:c>
+      <x:c r="M175" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-    </x:row>
-    <x:row r="111" ht="57" customHeight="1">
-      <x:c r="A111" s="4" t="str">
-        <x:v>TM-011</x:v>
-      </x:c>
-      <x:c r="B111" s="4" t="str">
-        <x:v>E2E-TM011-004</x:v>
-      </x:c>
-      <x:c r="C111" s="4" t="str">
-        <x:v>保留时间边界与未同步保护</x:v>
-      </x:c>
-      <x:c r="D111" s="4" t="str">
+      <x:c r="N175" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176" ht="57" customHeight="1">
+      <x:c r="A176" s="9" t="str">
+        <x:v>TM-012</x:v>
+      </x:c>
+      <x:c r="B176" s="9" t="str">
+        <x:v>E2E-TM012-002</x:v>
+      </x:c>
+      <x:c r="C176" s="9" t="str">
+        <x:v>诊断状态、恢复和登录启动</x:v>
+      </x:c>
+      <x:c r="D176" s="9" t="str">
         <x:v>待拆解</x:v>
       </x:c>
-      <x:c r="E111" s="4" t="str">
+      <x:c r="E176" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F111" s="4" t="str">
-        <x:v>数据集 migration_snapshots；固定参考时间和Asia/Shanghai；本地90天/服务端365天。分别生成保留首日00:00、前一秒、前一天的已确认事件，以及同样超龄但未同步事件；具备可控时钟与独立边界oracle。</x:v>
-      </x:c>
-      <x:c r="G111" s="4" t="str">
-        <x:v>保留首日00:00仍在，早一秒的已同步记录被清理；本地/服务按各自天数独立判定。未同步记录即使超龄仍保护，成功补传仅计一次；历史缺失不能显示真实0。</x:v>
-      </x:c>
-      <x:c r="H111" s="4" t="str">
+      <x:c r="F176" s="9" t="str">
+        <x:v>数据集 diagnostic_states；独立子场景：已授权目录失效、真实服务不可达/恢复、测试App登录启动开关。故障作用测试目录/进程；使用已登录桌面与可自动检查的系统设置。</x:v>
+      </x:c>
+      <x:c r="G176" s="9" t="str">
+        <x:v>错误与真实目录/网络故障一致，不能用旧缓存一直显示健康；恢复后状态及时更新，未同步数据不丢。启动设置与OS登记/实际启动行为一致，测试结束恢复本次测试前状态。</x:v>
+      </x:c>
+      <x:c r="H176" s="9" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
 变化：待具体任务及数据设计细化。
 核验：暂无可执行数据库核验绑定。</x:v>
       </x:c>
-      <x:c r="I111" s="4" t="str">
+      <x:c r="I176" s="9" t="str">
         <x:v>未来规划</x:v>
       </x:c>
-      <x:c r="J111" s="4" t="str">
+      <x:c r="J176" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K111" s="4" t="str">
+      <x:c r="K176" s="9" t="str">
         <x:v>未来概要</x:v>
       </x:c>
-      <x:c r="L111" s="4" t="str">
-        <x:v>docs/testing/cases/11-TM-011-data-migration.md:62</x:v>
-      </x:c>
-      <x:c r="M111" s="4" t="str">
+      <x:c r="L176" s="9" t="str">
+        <x:v>docs/testing/cases/12-TM-012-menu-diagnostics.md:28</x:v>
+      </x:c>
+      <x:c r="M176" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-    </x:row>
-    <x:row r="112" ht="57" customHeight="1">
-      <x:c r="A112" s="9" t="str">
-        <x:v>TM-012</x:v>
-      </x:c>
-      <x:c r="B112" s="9" t="str">
-        <x:v>E2E-TM012-001</x:v>
-      </x:c>
-      <x:c r="C112" s="9" t="str">
-        <x:v>菜单栏摘要、暂停恢复与刷新</x:v>
-      </x:c>
-      <x:c r="D112" s="9" t="str">
-        <x:v>待拆解</x:v>
-      </x:c>
-      <x:c r="E112" s="9" t="str">
-        <x:v>产品E2E</x:v>
-      </x:c>
-      <x:c r="F112" s="9" t="str">
-        <x:v>数据集 diagnostic_states；diagnostic_states planned；已采集A=100/10；暂停期间追加B=200/20并重放A。依赖实际采集、统计和同步功能，使用专用日志目录。</x:v>
-      </x:c>
-      <x:c r="G112" s="9" t="str">
-        <x:v>初始total110、暂停期间仍110，恢复后唯一A/B、total330；手动刷新与重启不重复。菜单栏与主窗口同一筛选口径；暂停状态不伪装成没有日志。</x:v>
-      </x:c>
-      <x:c r="H112" s="9" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
-      </x:c>
-      <x:c r="I112" s="9" t="str">
-        <x:v>未来规划</x:v>
-      </x:c>
-      <x:c r="J112" s="9" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="K112" s="9" t="str">
-        <x:v>未来概要</x:v>
-      </x:c>
-      <x:c r="L112" s="9" t="str">
-        <x:v>docs/testing/cases/12-TM-012-menu-diagnostics.md:11</x:v>
-      </x:c>
-      <x:c r="M112" s="9" t="str">
-        <x:v>尚未执行</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="113" ht="57" customHeight="1">
-      <x:c r="A113" s="4" t="str">
-        <x:v>TM-012</x:v>
-      </x:c>
-      <x:c r="B113" s="4" t="str">
-        <x:v>E2E-TM012-002</x:v>
-      </x:c>
-      <x:c r="C113" s="4" t="str">
-        <x:v>诊断状态、恢复和登录启动</x:v>
-      </x:c>
-      <x:c r="D113" s="4" t="str">
-        <x:v>待拆解</x:v>
-      </x:c>
-      <x:c r="E113" s="4" t="str">
-        <x:v>产品E2E</x:v>
-      </x:c>
-      <x:c r="F113" s="4" t="str">
-        <x:v>数据集 diagnostic_states；独立子场景：已授权目录失效、真实服务不可达/恢复、测试App登录启动开关。故障作用测试目录/进程；使用已登录桌面与可自动检查的系统设置。</x:v>
-      </x:c>
-      <x:c r="G113" s="4" t="str">
-        <x:v>错误与真实目录/网络故障一致，不能用旧缓存一直显示健康；恢复后状态及时更新，未同步数据不丢。启动设置与OS登记/实际启动行为一致，测试结束恢复本次测试前状态。</x:v>
-      </x:c>
-      <x:c r="H113" s="4" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
-      </x:c>
-      <x:c r="I113" s="4" t="str">
-        <x:v>未来规划</x:v>
-      </x:c>
-      <x:c r="J113" s="4" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="K113" s="4" t="str">
-        <x:v>未来概要</x:v>
-      </x:c>
-      <x:c r="L113" s="4" t="str">
-        <x:v>docs/testing/cases/12-TM-012-menu-diagnostics.md:28</x:v>
-      </x:c>
-      <x:c r="M113" s="4" t="str">
-        <x:v>尚未执行</x:v>
+      <x:c r="N176" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G5:G113">
+  <x:conditionalFormatting sqref="G5:G176">
     <x:cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="I5:I113">
+  <x:conditionalFormatting sqref="I5:I176">
     <x:cfRule type="containsText" dxfId="15" priority="4" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="17" priority="6" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="J5:J113">
+  <x:conditionalFormatting sqref="J5:J176">
     <x:cfRule type="containsText" dxfId="18" priority="7" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="19" priority="8" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="20" priority="9" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="M5:M113">
+  <x:conditionalFormatting sqref="M5:M176">
     <x:cfRule type="containsText" dxfId="21" priority="10" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="22" priority="11" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="23" priority="12" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf492ea58d26548f4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a349a07c4ad4ae4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10912,7 +14910,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91e619ff28294f4c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf2738bc8d4d43e7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10934,6 +14932,7 @@
     <x:col min="11" max="11" width="85" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="85" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="85" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="85" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2">
@@ -10981,6 +14980,9 @@
       <x:c r="M4" s="8" t="str">
         <x:v>状态依据</x:v>
       </x:c>
+      <x:c r="N4" s="8" t="str">
+        <x:v>design_source</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="42" customHeight="1">
       <x:c r="A5" s="4" t="str">
@@ -11022,6 +15024,9 @@
       <x:c r="M5" s="4" t="str">
         <x:v>releases/v0.0.1-20260929T060944Z/06-iteration-record.md</x:v>
       </x:c>
+      <x:c r="N5" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="72" customHeight="1">
       <x:c r="A6" s="9" t="str">
@@ -11063,26 +15068,73 @@
       <x:c r="M6" s="9" t="str">
         <x:v>releases/v0.1.0-20260929T074814Z/06-iteration-record.md</x:v>
       </x:c>
+      <x:c r="N6" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="72" customHeight="1">
+      <x:c r="A7" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+      <x:c r="B7" s="4" t="str">
+        <x:v>0.2.0</x:v>
+      </x:c>
+      <x:c r="C7" s="16" t="n">
+        <x:v>46296.15368055556</x:v>
+      </x:c>
+      <x:c r="D7" s="4" t="str">
+        <x:v>产品功能</x:v>
+      </x:c>
+      <x:c r="E7" s="4" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="F7" s="4" t="str">
+        <x:v>未发布</x:v>
+      </x:c>
+      <x:c r="G7" s="4" t="str">
+        <x:v>internal</x:v>
+      </x:c>
+      <x:c r="H7" s="4" t="str">
+        <x:v>本机版本归档及 dmg/&lt;release_id&gt;/；当前无本版正式包</x:v>
+      </x:c>
+      <x:c r="I7" s="15" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J7" s="4" t="str">
+        <x:v>0.2设计草稿：3功能点/9 TASK、28父TC/35变体已编制，SOP-008基线与固定程序未完成；需上一实际本机稳定0.1原包。产品E2E NOT_RUN、未发布。</x:v>
+      </x:c>
+      <x:c r="K7" s="4" t="str">
+        <x:v>TM001独立候选d2门禁PASS；本地master整合树尚未完成同树门禁或SOP-020稳定归档，不能继承为0.2升级源；本版无实际产品运行。</x:v>
+      </x:c>
+      <x:c r="L7" s="4" t="str">
+        <x:v>releases/v0.2.0-20261001T034118Z/00-manifest.json</x:v>
+      </x:c>
+      <x:c r="M7" s="4" t="str">
+        <x:v>releases/v0.2.0-20261001T034118Z/06-iteration-record.md</x:v>
+      </x:c>
+      <x:c r="N7" s="4" t="str">
+        <x:v>releases/v0.2.0-20261001T034118Z/01-requirements.md:32</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="F5:F6">
+  <x:conditionalFormatting sqref="F5:F7">
     <x:cfRule type="containsText" dxfId="30" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="31" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="32" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="J5:J6">
+  <x:conditionalFormatting sqref="J5:J7">
     <x:cfRule type="containsText" dxfId="33" priority="4" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="34" priority="5" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="35" priority="6" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="M5:M6">
+  <x:conditionalFormatting sqref="M5:M7">
     <x:cfRule type="containsText" dxfId="36" priority="7" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="37" priority="8" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="38" priority="9" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5282f33019444cc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R330cfc4c7212448f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12169,7 +16221,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc07fa5317a0347a6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52eacc33365f495f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TokenMeter项目总表.xlsx
+++ b/TokenMeter项目总表.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R5bcf6af7c2824aeb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="R416d93558caa47ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R3eed2723341c4efe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R11eacf0c8a6847ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="Rd6c7c534ab26465b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R3c8710592e9c49c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R1b270a2dee4346ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R0a4b3a5aa47546dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Rf888855f751947d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R32cead9b86ec4dda"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R35c4bd608c694a0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="Rb4069f2fb21043b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Rf2621ab51edf4918"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="Rd0eded506b6f4e16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R5cc396c4723c4ea4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="Ra228ac68a0294779"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R63749ec98d05495f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R5dee996be0e14721"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="Rb6b6c6cf83be4879"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Ref2df82fe2b34886"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R8cd258111ab14bc2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R8f05ebc6ecf14392"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1251,7 +1251,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c8e4c6871c9448d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb073f7078ced4335"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1959,7 +1959,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02f8fd2b66bf4042"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc22714fd11ab424f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2108,7 +2108,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85c0fee1613347c3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1928780e08ea4590"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2543,7 +2543,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f0aa82aa5844cbf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbce28c71569f41b7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3590,7 +3590,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5407363040844d1a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ebaf172ae7842c4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4367,7 +4367,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R490ea09385ac40b6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb908851cdca0420f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6150,7 +6150,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R857f4be4041d474b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf5b7618679c74cdf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12970,7 +12970,7 @@
         <x:v>v0.2.0-20261001T034118Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="147" ht="132" customHeight="1">
+    <x:row r="147" ht="177" customHeight="1">
       <x:c r="A147" s="4" t="str">
         <x:v>TM-002</x:v>
       </x:c>
@@ -12987,17 +12987,17 @@
         <x:v>交付门禁</x:v>
       </x:c>
       <x:c r="F147" s="4" t="str">
-        <x:v>已锁定候选 SHA/tree、0.2.0 最终 DMG 原件/清单、上一0.1本机正式稳定DMG及其SOP-018通行证、SOP-020归档收据、来源里程碑SHA/tree、签名和原包摘要、同机隔离签名更新源与每例隔离服务；若没有这些前置或真实升级入口，本例为 BLOCKED，不能用开发/候选包、受控101或同源码测试高版冒充。远端源码登记与Tag可待最终统一办理。TM-001 全部已交付 TC 和 除本例外 TM-002 其余 27 条父 TC 与 35 个稳定变体的固定清单在运行前确定。</x:v>
+        <x:v>已锁定候选 SHA/tree、0.2.0 最终 DMG 原件/清单、上一0.1本机正式稳定DMG及其SOP-018通行证、SOP-020 schema 2 release-index.json（milestone_sha/tree、master_tip_sha、remote_source_state=PENDING、原DMG/manifest/passport摘要）、签名、同机隔离签名更新源与每例隔离服务；若没有这些前置或真实升级入口，本例为 BLOCKED，不能用开发/候选包、受控101或同源码测试高版冒充。远端源码登记与Tag可待最终统一办理。TM-001 全部已交付 TC 和 除本例外 TM-002 其余 27 条父 TC 与 35 个稳定变体的固定清单在运行前确定。</x:v>
       </x:c>
       <x:c r="G147" s="4" t="str">
         <x:v>TM-001 全部已交付 TC、其他 27 条 TM-002 父 TC/35 变体的真实 UI、原生面板、服务与隔离 DB 由各自固定程序执行；原始记录各有唯一尝试和清理；本例结果此时仍为 BLOCKED。
-上一0.1本机稳定原包来源与通行证一致，App 自主升级；0.2显示新版本、保留TM-001合成账号/配置且 /v1/me 复核身份；来源初态 none，真实面板确认A后重启恢复本版密文来源；两端包签名、摘要和进程版本吻合。
+上一0.1本机稳定原包schema 2归档、里程碑来源、通行证与实际摘要一致，负测按既定拒绝，App 自主升级；0.2显示新版本、保留TM-001合成账号/配置且 /v1/me 复核身份；来源初态 none，真实面板确认A后重启恢复本版密文来源；两端包签名、摘要和进程版本吻合。
 本例不自我依赖：只有 TM-001 全部、其他 27 条 TM-002 父 TC/35 变体及升级真实结果均 PASS，且本例自身包/升级/证据核验 PASS，才记本例 PASS 并由最终 gate 签发通行证；计算前为 BLOCKED；本步骤无业务 DB 写入。</x:v>
       </x:c>
       <x:c r="H147" s="4" t="str">
-        <x:v>准备：每个产品 TC 由共同 R 独立准备合成账号、隔离 SQLite 与来源；本门禁只读这些运行的原始摘要及 SQL/数据证据引用，并核对最终 DMG、升级源和候选 SHA/tree。 上一稳定0.1包须有SOP-018/020原件及来源里程碑身份，远端登记可待办。
+        <x:v>准备：每个产品 TC 由共同 R 独立准备合成账号、隔离 SQLite 与来源；本门禁只读这些运行的原始摘要及 SQL/数据证据引用，并核对最终 DMG、升级源和候选 SHA/tree。 上一稳定0.1包须有SOP-018/020原件及来源里程碑身份，远端登记可待办。 稳定升级源消费者还须有旧schema/候选包/错误里程碑和摘要的固定拒绝负测。
 变化：本门禁自身无服务业务 SQL 写入；逐个产品 TC 的认证 sessions/audit 变化只按各自 NDA 与只读证据解释。
-核验：只读复核 TM-001 全部已交付 TC、其他 27 条 TM-002 父 TC/35 变体的隔离 DB/SQL 引用与原始逐步结果，并核对最终包、升级、清理和候选一致性；本例结果由这些原件派生，不连接生产库。 核对上一0.1稳定原包的通行证、归档、来源SHA/tree及真实升级链。</x:v>
+核验：只读复核 TM-001 全部已交付 TC、其他 27 条 TM-002 父 TC/35 变体的隔离 DB/SQL 引用与原始逐步结果，并核对最终包、升级、清理和候选一致性；本例结果由这些原件派生，不连接生产库。 核对上一0.1稳定原包的通行证、归档、来源SHA/tree及真实升级链。 只读核对schema 2 release-index.json的milestone_sha/tree、master_tip_sha、remote_source_state及原件摘要。</x:v>
       </x:c>
       <x:c r="I147" s="4" t="str">
         <x:v>预期待明确</x:v>
@@ -14375,7 +14375,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a349a07c4ad4ae4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec35cff4aad5459b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14910,7 +14910,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf2738bc8d4d43e7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc77e3f313c004fe0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15072,7 +15072,7 @@
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="72" customHeight="1">
+    <x:row r="7" ht="117" customHeight="1">
       <x:c r="A7" s="4" t="str">
         <x:v>v0.2.0-20261001T034118Z</x:v>
       </x:c>
@@ -15101,7 +15101,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J7" s="4" t="str">
-        <x:v>0.2设计草稿：3功能点/9 TASK、28父TC/35变体已编制，SOP-008基线与固定程序未完成；需上一实际本机稳定0.1原包。产品E2E NOT_RUN、未发布。</x:v>
+        <x:v>0.2设计草稿：3功能点/9 TASK、28父TC/35变体已编制，SOP-008基线与固定程序未完成；需上一实际本机稳定0.1原包和schema 2归档消费者。最终包Keychain身份探针缺隔离测试账号或已实测独立命名空间，相关E2E BLOCKED；产品E2E NOT_RUN、未发布。</x:v>
       </x:c>
       <x:c r="K7" s="4" t="str">
         <x:v>TM001独立候选d2门禁PASS；本地master整合树尚未完成同树门禁或SOP-020稳定归档，不能继承为0.2升级源；本版无实际产品运行。</x:v>
@@ -15134,7 +15134,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R330cfc4c7212448f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34c190857069430d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16221,7 +16221,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52eacc33365f495f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R94073158d3cc4eaf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TokenMeter项目总表.xlsx
+++ b/TokenMeter项目总表.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="Rb5afe6a2586a4b5f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Re1dd4dec0fb749e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R1a2d21dd2008419e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R51a27e6f77db4e84"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R3ad0bb6e9b7445bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R56a9d7363c4d46e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R2b0b6fa53b8a4447"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R16e41df402164005"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="R2aa3611019d84305"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R11ad06b80a2f4356"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R60abb8dd0c3e4e3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="Ra702d9032419454f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="R3ccf785cff824031"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="Rc0e266b44e8e4387"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R2fe9df2ed8484af4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="Ra1d3832d77d44954"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R6b490de23f5b4254"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R73a9f7a1a4ff407e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R61d060e006c441d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="R91607a3954054080"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R18ffc2a61fbe4df2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="Ra9834d7a84304806"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -715,8 +715,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="TMTable4" displayName="TMTable4" ref="A4:J25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:J25"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="TMTable4" displayName="TMTable4" ref="A4:J35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:J35"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="功能编号"/>
     <x:tableColumn id="2" name="层级"/>
@@ -734,8 +734,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="TMTable5" displayName="TMTable5" ref="A4:L48" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:L48"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="TMTable5" displayName="TMTable5" ref="A4:L73" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:L73"/>
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="任务编号"/>
     <x:tableColumn id="2" name="层级"/>
@@ -755,8 +755,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TMTable6" displayName="TMTable6" ref="A4:N176" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:N176"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TMTable6" displayName="TMTable6" ref="A4:N264" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:N264"/>
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="功能编号"/>
     <x:tableColumn id="2" name="用例编号"/>
@@ -799,8 +799,8 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="TMTable8" displayName="TMTable8" ref="A4:R7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:R7"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="TMTable8" displayName="TMTable8" ref="A4:R10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:R10"/>
   <x:tableColumns count="18">
     <x:tableColumn id="1" name="发布编号"/>
     <x:tableColumn id="2" name="版本"/>
@@ -826,8 +826,8 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="TMTable9" displayName="TMTable9" ref="A4:H43" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:H43"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="TMTable9" displayName="TMTable9" ref="A4:H46" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:H46"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="复盘编号"/>
     <x:tableColumn id="2" name="名称"/>
@@ -1066,7 +1066,7 @@
         <x:v>当前版本</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
+        <x:v>v0.2.0-20261001T034118Z</x:v>
       </x:c>
       <x:c r="C5" s="4" t="str">
         <x:v>未发布；版本状态见07发布版本</x:v>
@@ -1101,8 +1101,8 @@
         <x:v>已登记用例</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:f>COUNTA('05测试用例'!B5:B176)</x:f>
-        <x:v>172</x:v>
+        <x:f>COUNTA('05测试用例'!B5:B264)</x:f>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C8" s="9" t="str">
         <x:v>父用例与具有稳定 ID 的变体各占一行；含未来概要场景</x:v>
@@ -1125,7 +1125,7 @@
         <x:v>细化产品用例</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>102</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C10" s="9" t="str">
         <x:v>逐条结果按运行批次记录；稳定变体独立列出</x:v>
@@ -1158,21 +1158,21 @@
         <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="B13" s="10" t="n">
-        <x:v>65</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C13" s="4" t="str">
         <x:v>在05测试用例筛选此状态</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="57" customHeight="1">
+    <x:row r="14" ht="32" customHeight="1">
       <x:c r="A14" s="9" t="str">
         <x:v>最近完整回归</x:v>
       </x:c>
       <x:c r="B14" s="11" t="str">
-        <x:v>FAIL</x:v>
+        <x:v>未执行</x:v>
       </x:c>
       <x:c r="C14" s="9" t="str">
-        <x:v>固定本地master候选门禁FAIL；原始116项91 PASS/14 FAIL/11 BLOCKED，UPDATE-05父项与13变体缺签名输入。逐例模型78父TC 66 PASS/1 FAIL/11 BLOCKED，38变体25 PASS/13 FAIL；无正式稳定包。</x:v>
+        <x:v>尚无完整运行记录</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="42" customHeight="1">
@@ -1255,7 +1255,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde61e33f213f43c0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c3c3941a6734fa6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1455,7 +1455,7 @@
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G10" s="9" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H10" s="9" t="str">
         <x:v>sop/SOP-005-development-plan.md</x:v>
@@ -1481,7 +1481,7 @@
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G11" s="4" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H11" s="4" t="str">
         <x:v>sop/SOP-006-test-plan.md</x:v>
@@ -1507,13 +1507,13 @@
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G12" s="9" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H12" s="9" t="str">
         <x:v>sop/SOP-007-release-plan.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="87" customHeight="1">
+    <x:row r="13" ht="162" customHeight="1">
       <x:c r="A13" s="4" t="str">
         <x:v>SOP-008</x:v>
       </x:c>
@@ -1521,19 +1521,19 @@
         <x:v>SOP-008 基线检查</x:v>
       </x:c>
       <x:c r="C13" s="4" t="str">
-        <x:v>SOP-001–007 的版本计划全部完成、文档/SOP 迁移整合后，或已建基线发生影响实现的变化。单份草稿编制按 SOP-024 检查后返回原步骤。</x:v>
+        <x:v>SOP-001–007的版本计划全部完成、文档/SOP迁移整合后，或已建基线发生影响实现的变化；也可在整版仍draft时，为不依赖未决条件的明确TASK/TC子集建立开发切片。单份草稿编制按SOP-024检查后返回原步骤。</x:v>
       </x:c>
       <x:c r="D13" s="4" t="str">
-        <x:v>SOP-001–007 的档案和内容已齐全，必要元数据和 SOP 已登记；状态为 draft 的内容先解决实际缺项，经内容核对后登记为 baselined。不能为通过检查将未完成内容提前改为 baselined。</x:v>
+        <x:v>整版基线要求SOP-001–007档案和内容齐全，必要元数据和SOP已登记；draft内容先解决实际缺项，不能提前改成baselined。开发切片要求具体TASK/TC的需求、设计、数据、步骤、逐步预期、依赖和非目标均已固定且可独立验证；任何baseline_pending决定若可能改变该切片的预期、身份/权限、安全边界、接口或数据口径，该切片仍BLOCKED。切片不改变整版draft与其他TC的pending状态。</x:v>
       </x:c>
       <x:c r="E13" s="4" t="str">
-        <x:v>结构校验结果、语义一致性记录、完整文档基线或明确未决清单。</x:v>
+        <x:v>结构校验结果、语义一致性记录、整版文档基线或明确未决清单；可选的独立开发切片就绪记录，仍保留整版draft与未决TC。</x:v>
       </x:c>
       <x:c r="F13" s="4" t="str">
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G13" s="4" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H13" s="4" t="str">
         <x:v>sop/SOP-008-baseline-check.md</x:v>
@@ -1611,13 +1611,13 @@
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G16" s="9" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H16" s="9" t="str">
         <x:v>sop/SOP-011-test-implementation.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="132" customHeight="1">
+    <x:row r="17" ht="162" customHeight="1">
       <x:c r="A17" s="4" t="str">
         <x:v>SOP-012</x:v>
       </x:c>
@@ -1628,7 +1628,7 @@
         <x:v>数据和测试准备完成后实施目标业务；或按基线计划推进不依赖当前运行阻塞、具有独立验证条件的子任务。首个工程骨架由 SOP-009 建立。</x:v>
       </x:c>
       <x:c r="D17" s="4" t="str">
-        <x:v>SOP-008 基线有效，文件所有权和现有用户修改已确认。完整业务路径按 SOP-009→010→011 获得可运行骨架、数据/测试绑定和真实行为失败证据后实现。缺工具链时，可先执行开发计划中具有独立验证条件的源码子任务；已编写数据/测试绑定须真实存在，缺失的红测及产品验收保持 BLOCKED，不能凭源码完成关闭这些依赖。</x:v>
+        <x:v>SOP-008整版基线或仅覆盖本TASK/TC且不依赖未决项的开发切片就绪记录有效，文件所有权和现有用户修改已确认。完整业务路径按SOP-009→010→011获得可运行骨架、数据/测试绑定和真实行为失败证据后实现。缺工具链时，可先执行开发计划中具有独立验证条件的源码子任务；已编写数据/测试绑定须真实存在，缺失的红测及产品验收保持BLOCKED，不能凭源码完成关闭这些依赖。</x:v>
       </x:c>
       <x:c r="E17" s="4" t="str">
         <x:v>产品实现、真实测试与数据程序、同步文档和可构建候选变更。</x:v>
@@ -1637,13 +1637,13 @@
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G17" s="4" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H17" s="4" t="str">
         <x:v>sop/SOP-012-development.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="32" customHeight="1">
+    <x:row r="18" ht="42" customHeight="1">
       <x:c r="A18" s="9" t="str">
         <x:v>SOP-013</x:v>
       </x:c>
@@ -1651,7 +1651,7 @@
         <x:v>SOP-013 构建与检查</x:v>
       </x:c>
       <x:c r="C18" s="9" t="str">
-        <x:v>实现/依赖变化后、进入完整E2E前。</x:v>
+        <x:v>实现/依赖变化后、开发功能回归前；正式发布完整E2E前再次针对最终候选执行。</x:v>
       </x:c>
       <x:c r="D18" s="9" t="str">
         <x:v>012实现、009本机运行时和锁文件就绪。</x:v>
@@ -1663,7 +1663,7 @@
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G18" s="9" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H18" s="9" t="str">
         <x:v>sop/SOP-013-build-and-check.md</x:v>
@@ -1677,19 +1677,19 @@
         <x:v>SOP-014 自动 E2E</x:v>
       </x:c>
       <x:c r="C19" s="4" t="str">
-        <x:v>每次迭代、修复及发布候选。</x:v>
+        <x:v>每次功能完成或修复时执行对应固定TC回归；收到用户明确正式发布指令后执行最终候选完整回归。</x:v>
       </x:c>
       <x:c r="D19" s="4" t="str">
         <x:v>009–013、本机GUI、Electron/Playwright及真实服务/隔离DB。TM001 UPDATE-05受控签名变体另需SOP-009/010的显式私有签名输入及原包身份预检；缺前置只阻断依赖用例。</x:v>
       </x:c>
       <x:c r="E19" s="4" t="str">
-        <x:v>完整原始产品结果与清理、独立批次结果Excel，或真实FAIL/BLOCKED及缺失项。</x:v>
+        <x:v>开发阶段的本功能逐TC原始结果、清理和独立批次Excel；正式发布阶段的最终完整并集结果；或真实FAIL/BLOCKED/NOT_RUN及缺失项。</x:v>
       </x:c>
       <x:c r="F19" s="4" t="str">
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G19" s="4" t="n">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="H19" s="4" t="str">
         <x:v>sop/SOP-014-e2e.md</x:v>
@@ -1715,7 +1715,7 @@
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G20" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H20" s="9" t="str">
         <x:v>sop/SOP-015-bugfix.md</x:v>
@@ -1747,7 +1747,7 @@
         <x:v>sop/SOP-016-database-migration.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="102" customHeight="1">
+    <x:row r="22" ht="132" customHeight="1">
       <x:c r="A22" s="9" t="str">
         <x:v>SOP-017</x:v>
       </x:c>
@@ -1755,25 +1755,25 @@
         <x:v>SOP-017 安装包验证</x:v>
       </x:c>
       <x:c r="C22" s="9" t="str">
-        <x:v>内部本地版本准备发行或包/更新器变化。</x:v>
+        <x:v>开发需要可安装预览包，或用户明确启动正式对外发布；包/更新器变化时运行其固定功能TC。</x:v>
       </x:c>
       <x:c r="D22" s="9" t="str">
-        <x:v>007预案、013/014、SOP-019在本地master固定的本版本里程碑SHA/tree、真实本机GUI和稳定本地签名能力。首版验证自身受控高版更新；后续版本真实升级另须有上一版本按SOP-018/020形成、可独立复核的本机正式稳定DMG。</x:v>
+        <x:v>开发预览需007预案、013适用构建条件、可核对源码SHA/tree和受限签名能力；测试包的固定TC另需014所列本机GUI和隔离条件。正式发布另需用户明确指令、019固定最终本地候选SHA/tree、014完整并集，以及上一实际正式稳定包（如已存在）。没有上一稳定源而既定升级TC要求它时，先记BLOCKED并修订基线，不用开发包替代。</x:v>
       </x:c>
       <x:c r="E22" s="9" t="str">
-        <x:v>原始安装包及系统签名、安装/更新/E2E证据；根dmg/&lt;release_id&gt;/的未发布标记便捷副本及摘要核对。</x:v>
+        <x:v>开发阶段的未发布预览包、摘要和适用TC结果；正式发布阶段的最终原包、系统签名、安装/更新/完整E2E证据。</x:v>
       </x:c>
       <x:c r="F22" s="9" t="str">
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G22" s="9" t="n">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H22" s="9" t="str">
         <x:v>sop/SOP-017-package-validation.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="117" customHeight="1">
+    <x:row r="23" ht="162" customHeight="1">
       <x:c r="A23" s="4" t="str">
         <x:v>SOP-018</x:v>
       </x:c>
@@ -1781,25 +1781,25 @@
         <x:v>SOP-018 发布门禁</x:v>
       </x:c>
       <x:c r="C23" s="4" t="str">
-        <x:v>固定最终候选准备内部本地发行。</x:v>
+        <x:v>用户另行明确要求正式对外发布，且最终候选准备发行；开发阶段不启动本门禁。</x:v>
       </x:c>
       <x:c r="D23" s="4" t="str">
-        <x:v>013/014/017真实执行、SOP-019固定的本地master版本里程碑与其干净候选、原始产物齐全。TM001 UPDATE-05依赖的显式签名输入预检及全部真实App变体须分别有原始证据；后续版本的上一实际稳定包及真实升级证据须按SOP-017齐全。远端统一源码推送不是本机门禁的前置。</x:v>
+        <x:v>用户明确的正式发布指令、针对最终候选重新执行并通过的013/014完整跨需求并集与017、SOP-019固定的本地master最终SHA/tree和干净候选、原始产物齐全。TM001 UPDATE-05依赖的显式签名输入预检及全部真实App变体须分别有原始证据；适用的上一实际稳定包及真实升级证据须按SOP-017齐全。开发阶段逐功能回归和远端源码读回不能替代这些前置；远端源码已否登记不决定本机门禁。</x:v>
       </x:c>
       <x:c r="E23" s="4" t="str">
-        <x:v>PASS通行证或明确FAIL/BLOCKED，原始证据保持本地。</x:v>
+        <x:v>正式发布的PASS通行证或明确FAIL/BLOCKED，原始证据保持本地；未启动时记NOT_RUN、无通行证。</x:v>
       </x:c>
       <x:c r="F23" s="4" t="str">
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G23" s="4" t="n">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H23" s="4" t="str">
         <x:v>sop/SOP-018-release-gate.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="327" customHeight="1">
+    <x:row r="24" ht="282" customHeight="1">
       <x:c r="A24" s="9" t="str">
         <x:v>SOP-019</x:v>
       </x:c>
@@ -1807,25 +1807,25 @@
         <x:v>SOP-019 Git 版本追踪</x:v>
       </x:c>
       <x:c r="C24" s="9" t="str">
-        <x:v>开发会话产生需要保存的WIP/候选源码提交；总控完成一个本地整合里程碑并需要远端源码镜像；或全部目标版本完成、需要统一远端master与正式Tag登记。PR只在远端策略要求时作为受控路径。</x:v>
+        <x:v>开发会话产生需要保存的WIP/候选源码提交；总控完成一个本地整合里程碑并需要远端源码镜像；全部目标版本源码完成，需要统一登记远端master；或正式发布PASS后需要登记正式Tag。PR只在远端策略要求时作为受控路径。</x:v>
       </x:c>
       <x:c r="D24" s="9" t="str">
-        <x:v>用户已授权远端Git承担源码版本管理，产品开发、全量测试、打包及发行在本机完成；2026-10-01新增明确要求允许在最终远端master整合前，把可核对源码检查点快进保存到远端功能分支或单一整合镜像分支。每个需求有自己的worktree、codex/&lt;release_id&gt;/&lt;功能名&gt;分支、明确负责人和输入基线；远端推送只针对对应分支，master仍由总控最后统一办理。待推送的源码须有已完成提交、干净工作树、真实检查状态与可核对SHA/tree；WIP允许尚未通过产品测试，但必须如实标记。被测产品版本仍须在**本地master固定里程碑提交**上由固定程序完成本轮与此前已交付功能的完整E2E、SOP-017/018最终包门禁，再按SOP-020形成本机稳定包；远端检查点、PR或Actions结果均不能替代。正式Tag须本机通行证、稳定包归档和最终远端读回。仅规范分支可在结构、基线和治理检查后先行本地整合，记录release_eligible=false。未提交的用户改动不得带入其他会话工作树或整合。</x:v>
+        <x:v>用户已授权远端Git承担源码版本管理，产品开发、测试、打包及发行在本机完成；2026-10-01最新指令将开发阶段限于各功能已基线固定TC回归，全量跨需求E2E及正式发行待用户另行启动。每个需求有自己的worktree、codex/&lt;release_id&gt;/&lt;功能名&gt;分支、明确负责人和输入基线；远端同名分支与单一integration镜像可先保存源码检查点，master由总控最后统一办理。待推送源码须有已完成提交、干净工作树、真实检查状态与可核对SHA/tree；WIP及未通过功能回归均如实标记，不称功能验收或发布PASS。开发里程碑及远端源码登记不以逐版完整E2E、SOP-018通行证或SOP-020稳定包为前置。正式Tag须用户发布指令、最终候选完整门禁PASS、稳定包归档和远端读回。未提交的用户改动不得带入其他会话工作树或整合。</x:v>
       </x:c>
       <x:c r="E24" s="9" t="str">
-        <x:v>各会话独立worktree和已读回的远端源码检查点、可选整合镜像；逐版本地master里程碑及本机门禁/稳定包记录；最终远端master和逐版源码Tag映射。本地索引分别显示“代码已保存”“本机产品/发行状态”“远端master/Tag状态”。</x:v>
+        <x:v>各会话独立worktree和已读回的远端源码检查点、可选整合镜像；逐版本地master开发里程碑及真实功能TC状态；最终远端master源码读回。正式发布另产生最终候选门禁/稳定包和该正式版本Tag映射。本地索引分别显示“代码已保存”“功能回归状态”“正式发行状态”“远端master/Tag状态”。</x:v>
       </x:c>
       <x:c r="F24" s="9" t="str">
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G24" s="9" t="n">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H24" s="9" t="str">
         <x:v>sop/SOP-019-git-release.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="72" customHeight="1">
+    <x:row r="25" ht="87" customHeight="1">
       <x:c r="A25" s="4" t="str">
         <x:v>SOP-020</x:v>
       </x:c>
@@ -1833,10 +1833,10 @@
         <x:v>SOP-020 本地发行归档</x:v>
       </x:c>
       <x:c r="C25" s="4" t="str">
-        <x:v>本机018 PASS，且SOP-019已固定该版本在本地master的不可变SHA/tree与来源追踪；远端master读回和正式Tag可保持待办，不冒充已完成。</x:v>
+        <x:v>用户明确要求正式发布、本机018 PASS，且SOP-019已固定最终候选在本地master的不可变SHA/tree与来源追踪；远端master可能已登记源码，正式Tag仍待本步完成。</x:v>
       </x:c>
       <x:c r="D25" s="4" t="str">
-        <x:v>有效通行证、同一候选原包、本地版本里程碑、独立新目标目录和恢复预案。上一版本尚无正式稳定包时，下一版本依赖真实升级的门禁继续BLOCKED。</x:v>
+        <x:v>有效通行证、同一最终候选原包、本地版本里程碑、独立新目标目录和恢复预案。开发阶段无通行证时本步NOT_RUN；既定升级用例缺上一实际稳定包时正式门禁BLOCKED，不在本步补造。</x:v>
       </x:c>
       <x:c r="E25" s="4" t="str">
         <x:v>本地版本归档、原件校验和、根dmg/&lt;release_id&gt;/正式稳定安装入口、来源SHA/tree及远端待办/后续登记收据。</x:v>
@@ -1845,7 +1845,7 @@
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G25" s="4" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H25" s="4" t="str">
         <x:v>sop/SOP-020-deployment.md</x:v>
@@ -1963,7 +1963,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd45cd8169a394bd3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R966c6dcd4d42499a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2112,7 +2112,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8270c6fe1df14abf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97878ac8d0cc498c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2305,7 +2305,7 @@
         <x:v>用量统计</x:v>
       </x:c>
       <x:c r="D9" s="4" t="str">
-        <x:v>今天/昨天/近 7、15、30 天/自定义、趋势、明细、模型维度、缺失提示</x:v>
+        <x:v>Codex 与 Claude Code 双来源原生日志用量统计；日期范围、趋势、明细、模型、身份去重与缺失/零/未知三态</x:v>
       </x:c>
       <x:c r="E9" s="4" t="str">
         <x:v>AC-TM005-001
@@ -2315,10 +2315,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="G9" s="4" t="str">
-        <x:v>规划中</x:v>
+        <x:v>design_in_progress</x:v>
       </x:c>
       <x:c r="H9" s="4" t="str">
-        <x:v>docs/product/README.md:22</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/01-requirements.md</x:v>
       </x:c>
       <x:c r="I9" s="4" t="str">
         <x:v>未提供</x:v>
@@ -2547,7 +2547,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac6c21fbeb0342e2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b83207a825a41b6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3594,7 +3594,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95ac8888b10f438b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd029f162ac214e85"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3783,10 +3783,10 @@
         <x:v>0.4.0</x:v>
       </x:c>
       <x:c r="H8" s="9" t="str">
-        <x:v>规划中</x:v>
+        <x:v>开发中</x:v>
       </x:c>
       <x:c r="I8" s="9" t="str">
-        <x:v>docs/product/README.md:21</x:v>
+        <x:v>releases/v0.4.0-20261001T040433Z/02-breakdown.md</x:v>
       </x:c>
       <x:c r="J8" s="9" t="str">
         <x:v>未提供</x:v>
@@ -3806,7 +3806,7 @@
         <x:v>用量统计</x:v>
       </x:c>
       <x:c r="E9" s="4" t="str">
-        <x:v>今天/昨天/近 7、15、30 天/自定义、趋势、明细、模型维度、缺失提示</x:v>
+        <x:v>双来源可信事件、IANA 日界统计、三态覆盖及真实桌面验收</x:v>
       </x:c>
       <x:c r="F9" s="4" t="str">
         <x:v>AC-TM005-001
@@ -3816,10 +3816,10 @@
         <x:v>0.5.0</x:v>
       </x:c>
       <x:c r="H9" s="4" t="str">
-        <x:v>规划中</x:v>
+        <x:v>design_in_progress</x:v>
       </x:c>
       <x:c r="I9" s="4" t="str">
-        <x:v>docs/product/README.md:22</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/02-breakdown.md:10</x:v>
       </x:c>
       <x:c r="J9" s="4" t="str">
         <x:v>未提供</x:v>
@@ -4363,15 +4363,345 @@
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
+    <x:row r="26" ht="42" customHeight="1">
+      <x:c r="A26" s="9" t="str">
+        <x:v>FP-TM003-01</x:v>
+      </x:c>
+      <x:c r="B26" s="9" t="str">
+        <x:v>本轮功能点</x:v>
+      </x:c>
+      <x:c r="C26" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="D26" s="9" t="str">
+        <x:v>Codex 原生来源识别</x:v>
+      </x:c>
+      <x:c r="E26" s="9" t="str">
+        <x:v>只接受经核验的原生记录结构，未知结构可见</x:v>
+      </x:c>
+      <x:c r="F26" s="9" t="str">
+        <x:v>AC-TM003-001
+AC-TM003-002</x:v>
+      </x:c>
+      <x:c r="G26" s="9" t="str">
+        <x:v>0.3.0</x:v>
+      </x:c>
+      <x:c r="H26" s="9" t="str">
+        <x:v>规划中</x:v>
+      </x:c>
+      <x:c r="I26" s="9" t="str">
+        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:11</x:v>
+      </x:c>
+      <x:c r="J26" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="57" customHeight="1">
+      <x:c r="A27" s="4" t="str">
+        <x:v>FP-TM003-02</x:v>
+      </x:c>
+      <x:c r="B27" s="4" t="str">
+        <x:v>本轮功能点</x:v>
+      </x:c>
+      <x:c r="C27" s="4" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="D27" s="4" t="str">
+        <x:v>本地持久采集与去重</x:v>
+      </x:c>
+      <x:c r="E27" s="4" t="str">
+        <x:v>完整行游标、响应身份、累计核对、重启/移动/分支不重计</x:v>
+      </x:c>
+      <x:c r="F27" s="4" t="str">
+        <x:v>AC-TM003-001
+AC-TM003-002
+AC-TM003-003</x:v>
+      </x:c>
+      <x:c r="G27" s="4" t="str">
+        <x:v>0.3.0</x:v>
+      </x:c>
+      <x:c r="H27" s="4" t="str">
+        <x:v>规划中</x:v>
+      </x:c>
+      <x:c r="I27" s="4" t="str">
+        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:12</x:v>
+      </x:c>
+      <x:c r="J27" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="42" customHeight="1">
+      <x:c r="A28" s="9" t="str">
+        <x:v>FP-TM003-03</x:v>
+      </x:c>
+      <x:c r="B28" s="9" t="str">
+        <x:v>本轮功能点</x:v>
+      </x:c>
+      <x:c r="C28" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="D28" s="9" t="str">
+        <x:v>权限和状态</x:v>
+      </x:c>
+      <x:c r="E28" s="9" t="str">
+        <x:v>已确认授权根才读取，失效即停，重新授权后补扫</x:v>
+      </x:c>
+      <x:c r="F28" s="9" t="str">
+        <x:v>AC-TM003-001
+AC-TM003-004</x:v>
+      </x:c>
+      <x:c r="G28" s="9" t="str">
+        <x:v>0.3.0</x:v>
+      </x:c>
+      <x:c r="H28" s="9" t="str">
+        <x:v>规划中</x:v>
+      </x:c>
+      <x:c r="I28" s="9" t="str">
+        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:13</x:v>
+      </x:c>
+      <x:c r="J28" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="72" customHeight="1">
+      <x:c r="A29" s="4" t="str">
+        <x:v>FP-TM003-04</x:v>
+      </x:c>
+      <x:c r="B29" s="4" t="str">
+        <x:v>本轮功能点</x:v>
+      </x:c>
+      <x:c r="C29" s="4" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="D29" s="4" t="str">
+        <x:v>自动验证与交付</x:v>
+      </x:c>
+      <x:c r="E29" s="4" t="str">
+        <x:v>固定数据、逐 TC 产品 E2E、同候选全回归与可追踪档案</x:v>
+      </x:c>
+      <x:c r="F29" s="4" t="str">
+        <x:v>AC-TM003-001
+AC-TM003-002
+AC-TM003-003
+AC-TM003-004</x:v>
+      </x:c>
+      <x:c r="G29" s="4" t="str">
+        <x:v>0.3.0</x:v>
+      </x:c>
+      <x:c r="H29" s="4" t="str">
+        <x:v>规划中</x:v>
+      </x:c>
+      <x:c r="I29" s="4" t="str">
+        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:14</x:v>
+      </x:c>
+      <x:c r="J29" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="42" customHeight="1">
+      <x:c r="A30" s="9" t="str">
+        <x:v>FP-TM005-01</x:v>
+      </x:c>
+      <x:c r="B30" s="9" t="str">
+        <x:v>sub_feature</x:v>
+      </x:c>
+      <x:c r="C30" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="D30" s="9" t="str">
+        <x:v>可信事件</x:v>
+      </x:c>
+      <x:c r="E30" s="9" t="str">
+        <x:v>两来源不可变事件身份、用量子项和冲突诊断</x:v>
+      </x:c>
+      <x:c r="F30" s="9" t="str">
+        <x:v>AC-TM005-001
+AC-TM005-002</x:v>
+      </x:c>
+      <x:c r="G30" s="9" t="str">
+        <x:v>0.5.0</x:v>
+      </x:c>
+      <x:c r="H30" s="9" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="I30" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/02-breakdown.md:10</x:v>
+      </x:c>
+      <x:c r="J30" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="32" customHeight="1">
+      <x:c r="A31" s="4" t="str">
+        <x:v>FP-TM005-02</x:v>
+      </x:c>
+      <x:c r="B31" s="4" t="str">
+        <x:v>sub_feature</x:v>
+      </x:c>
+      <x:c r="C31" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="D31" s="4" t="str">
+        <x:v>范围和汇总</x:v>
+      </x:c>
+      <x:c r="E31" s="4" t="str">
+        <x:v>IANA当地日期、半开UTC范围、汇总/趋势/明细/模型</x:v>
+      </x:c>
+      <x:c r="F31" s="4" t="str">
+        <x:v>AC-TM005-001</x:v>
+      </x:c>
+      <x:c r="G31" s="4" t="str">
+        <x:v>0.5.0</x:v>
+      </x:c>
+      <x:c r="H31" s="4" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="I31" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/02-breakdown.md:11</x:v>
+      </x:c>
+      <x:c r="J31" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="32" customHeight="1">
+      <x:c r="A32" s="9" t="str">
+        <x:v>FP-TM005-03</x:v>
+      </x:c>
+      <x:c r="B32" s="9" t="str">
+        <x:v>sub_feature</x:v>
+      </x:c>
+      <x:c r="C32" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="D32" s="9" t="str">
+        <x:v>三态覆盖</x:v>
+      </x:c>
+      <x:c r="E32" s="9" t="str">
+        <x:v>两来源覆盖证明与缺失、真实零、未知状态</x:v>
+      </x:c>
+      <x:c r="F32" s="9" t="str">
+        <x:v>AC-TM005-002</x:v>
+      </x:c>
+      <x:c r="G32" s="9" t="str">
+        <x:v>0.5.0</x:v>
+      </x:c>
+      <x:c r="H32" s="9" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="I32" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/02-breakdown.md:12</x:v>
+      </x:c>
+      <x:c r="J32" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="32" customHeight="1">
+      <x:c r="A33" s="4" t="str">
+        <x:v>FP-TM005-04</x:v>
+      </x:c>
+      <x:c r="B33" s="4" t="str">
+        <x:v>sub_feature</x:v>
+      </x:c>
+      <x:c r="C33" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="D33" s="4" t="str">
+        <x:v>统计界面</x:v>
+      </x:c>
+      <x:c r="E33" s="4" t="str">
+        <x:v>真实IPC、筛选表单、统计卡片、趋势、明细和模型分组</x:v>
+      </x:c>
+      <x:c r="F33" s="4" t="str">
+        <x:v>AC-TM005-001</x:v>
+      </x:c>
+      <x:c r="G33" s="4" t="str">
+        <x:v>0.5.0</x:v>
+      </x:c>
+      <x:c r="H33" s="4" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="I33" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/02-breakdown.md:13</x:v>
+      </x:c>
+      <x:c r="J33" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="42" customHeight="1">
+      <x:c r="A34" s="9" t="str">
+        <x:v>FP-TM005-05</x:v>
+      </x:c>
+      <x:c r="B34" s="9" t="str">
+        <x:v>sub_feature</x:v>
+      </x:c>
+      <x:c r="C34" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="D34" s="9" t="str">
+        <x:v>原生数据与独立预期</x:v>
+      </x:c>
+      <x:c r="E34" s="9" t="str">
+        <x:v>seed42、受支持原生日志、独立oracle和隔离重置</x:v>
+      </x:c>
+      <x:c r="F34" s="9" t="str">
+        <x:v>AC-TM005-001
+AC-TM005-002</x:v>
+      </x:c>
+      <x:c r="G34" s="9" t="str">
+        <x:v>0.5.0</x:v>
+      </x:c>
+      <x:c r="H34" s="9" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="I34" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/02-breakdown.md:14</x:v>
+      </x:c>
+      <x:c r="J34" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="42" customHeight="1">
+      <x:c r="A35" s="4" t="str">
+        <x:v>FP-TM005-06</x:v>
+      </x:c>
+      <x:c r="B35" s="4" t="str">
+        <x:v>sub_feature</x:v>
+      </x:c>
+      <x:c r="C35" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="D35" s="4" t="str">
+        <x:v>产品用例与门禁</x:v>
+      </x:c>
+      <x:c r="E35" s="4" t="str">
+        <x:v>逐TC固定桌面E2E、原件复核和最终包门禁</x:v>
+      </x:c>
+      <x:c r="F35" s="4" t="str">
+        <x:v>AC-TM005-001
+AC-TM005-002</x:v>
+      </x:c>
+      <x:c r="G35" s="4" t="str">
+        <x:v>0.5.0</x:v>
+      </x:c>
+      <x:c r="H35" s="4" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="I35" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/02-breakdown.md:15</x:v>
+      </x:c>
+      <x:c r="J35" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="H5:H25">
+  <x:conditionalFormatting sqref="H5:H35">
     <x:cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="8" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2bda9dc0360d4d45"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39a6e7bac47e4ea0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5880,115 +6210,121 @@
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" ht="32" customHeight="1">
+    <x:row r="42" ht="87" customHeight="1">
       <x:c r="A42" s="9" t="str">
-        <x:v>TASK-TM001-PLAN</x:v>
+        <x:v>TASK-TM003-SOURCE</x:v>
       </x:c>
       <x:c r="B42" s="9" t="str">
-        <x:v>历史分组</x:v>
+        <x:v>具体任务</x:v>
       </x:c>
       <x:c r="C42" s="9" t="str">
+        <x:v>FP-TM003-01</x:v>
+      </x:c>
+      <x:c r="D42" s="9" t="str">
+        <x:v>REQ-TM003</x:v>
+      </x:c>
+      <x:c r="E42" s="9" t="str">
+        <x:v>AC-TM003-001
+AC-TM003-002</x:v>
+      </x:c>
+      <x:c r="F42" s="9" t="str">
+        <x:v>官方协议/rollout 来源、受控 Codex CLI 样例；独立</x:v>
+      </x:c>
+      <x:c r="G42" s="9" t="str">
+        <x:v>产物：固定支持版本、原生字段/来源/分支语义清单；样例只在本轮隔离根的 sessions/YYYY/MM/DD/*.jsonl；TM-002 元数据预览不当格式证明；不读真实用户日志
+完成条件：每个宣称支持的版本都有原生结构、字段摘要和复现来源；缺证据保持不支持</x:v>
+      </x:c>
+      <x:c r="H42" s="9" t="str">
+        <x:v>官方协议/rollout 来源、受控 Codex CLI 样例；独立</x:v>
+      </x:c>
+      <x:c r="I42" s="9" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="D42" s="9" t="str">
-        <x:v>REQ-TM001</x:v>
-      </x:c>
-      <x:c r="E42" s="9" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="F42" s="9" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="G42" s="9" t="str">
-        <x:v>六文档、完整追踪、SOP 修正、基线通过</x:v>
-      </x:c>
-      <x:c r="H42" s="9" t="str">
-        <x:v>需求</x:v>
-      </x:c>
-      <x:c r="I42" s="9" t="str">
-        <x:v>TEST-TM001-GOVERNANCE</x:v>
-      </x:c>
       <x:c r="J42" s="9" t="str">
-        <x:v>historical_group_not_minimal_task</x:v>
+        <x:v>规划中</x:v>
       </x:c>
       <x:c r="K42" s="9" t="str">
-        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:9</x:v>
+        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:20</x:v>
       </x:c>
       <x:c r="L42" s="9" t="str">
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" ht="42" customHeight="1">
+    <x:row r="43" ht="87" customHeight="1">
       <x:c r="A43" s="4" t="str">
-        <x:v>TASK-TM001-SERVER</x:v>
+        <x:v>TASK-TM003-FIXTURE</x:v>
       </x:c>
       <x:c r="B43" s="4" t="str">
-        <x:v>历史分组</x:v>
+        <x:v>具体任务</x:v>
       </x:c>
       <x:c r="C43" s="4" t="str">
+        <x:v>FP-TM003-01</x:v>
+      </x:c>
+      <x:c r="D43" s="4" t="str">
+        <x:v>REQ-TM003</x:v>
+      </x:c>
+      <x:c r="E43" s="4" t="str">
+        <x:v>AC-TM003-001
+AC-TM003-003</x:v>
+      </x:c>
+      <x:c r="F43" s="4" t="str">
+        <x:v>SOURCE、SOP-010；独立</x:v>
+      </x:c>
+      <x:c r="G43" s="4" t="str">
+        <x:v>产物：codex_raw 生成/重置程序，在 TM-002 深度/数量上限内造嵌套 .jsonl、同层越界 symlink、半行、重复、冲突、fork、失效组合；独立 expected 与归属清理
+完成条件：固定种子重建同字节输入和 110/660/220/165 等预期，不插入用量表，不触碰真实目录</x:v>
+      </x:c>
+      <x:c r="H43" s="4" t="str">
+        <x:v>SOURCE、SOP-010；独立</x:v>
+      </x:c>
+      <x:c r="I43" s="4" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="D43" s="4" t="str">
-        <x:v>REQ-TM001</x:v>
-      </x:c>
-      <x:c r="E43" s="4" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="F43" s="4" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="G43" s="4" t="str">
-        <x:v>FastAPI/SQLAlchemy/Alembic 工程、真实认证/权限/审计 API；随机可撤销 token 固定30天到期、不滑动，改密/重置/停用撤销旧会话</x:v>
-      </x:c>
-      <x:c r="H43" s="4" t="str">
-        <x:v>计划、数据/测试</x:v>
-      </x:c>
-      <x:c r="I43" s="4" t="str">
-        <x:v>E2E-TM001-001、E2E-TM001-002、E2E-TM001-003</x:v>
-      </x:c>
       <x:c r="J43" s="4" t="str">
-        <x:v>historical_group_not_minimal_task</x:v>
+        <x:v>规划中</x:v>
       </x:c>
       <x:c r="K43" s="4" t="str">
-        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:10</x:v>
+        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:21</x:v>
       </x:c>
       <x:c r="L43" s="4" t="str">
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" ht="42" customHeight="1">
+    <x:row r="44" ht="72" customHeight="1">
       <x:c r="A44" s="9" t="str">
-        <x:v>TASK-TM001-DATA</x:v>
+        <x:v>TASK-TM003-STORE</x:v>
       </x:c>
       <x:c r="B44" s="9" t="str">
-        <x:v>历史分组</x:v>
+        <x:v>具体任务</x:v>
       </x:c>
       <x:c r="C44" s="9" t="str">
+        <x:v>FP-TM003-02</x:v>
+      </x:c>
+      <x:c r="D44" s="9" t="str">
+        <x:v>REQ-TM003</x:v>
+      </x:c>
+      <x:c r="E44" s="9" t="str">
+        <x:v>AC-TM003-001
+AC-TM003-002</x:v>
+      </x:c>
+      <x:c r="F44" s="9" t="str">
+        <x:v>已基线 schema/隐私；依赖 TM-001 Electron 主进程基线</x:v>
+      </x:c>
+      <x:c r="G44" s="9" t="str">
+        <x:v>产物：客户端 SQLite 的事件、游标、诊断、覆盖范围表及事务入口；仅保留白名单字段
+完成条件：来源域内调用键唯一约束、事件+游标原子提交、重启可读、无原文/完整路径</x:v>
+      </x:c>
+      <x:c r="H44" s="9" t="str">
+        <x:v>已基线 schema/隐私；依赖 TM-001 Electron 主进程基线</x:v>
+      </x:c>
+      <x:c r="I44" s="9" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="D44" s="9" t="str">
-        <x:v>REQ-TM001</x:v>
-      </x:c>
-      <x:c r="E44" s="9" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="F44" s="9" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="G44" s="9" t="str">
-        <x:v>独立测试/生产 SQLite 文件、可执行造数 SQL、生产首建管理员、回归账号/独立预期及安全重置；已有生产密码不可被重建覆盖</x:v>
-      </x:c>
-      <x:c r="H44" s="9" t="str">
-        <x:v>计划、工程骨架</x:v>
-      </x:c>
-      <x:c r="I44" s="9" t="str">
-        <x:v>TEST-TM001-SERVER、E2E-TM001-001、E2E-TM001-005</x:v>
-      </x:c>
       <x:c r="J44" s="9" t="str">
-        <x:v>historical_group_not_minimal_task</x:v>
+        <x:v>规划中</x:v>
       </x:c>
       <x:c r="K44" s="9" t="str">
-        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:11</x:v>
+        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:22</x:v>
       </x:c>
       <x:c r="L44" s="9" t="str">
         <x:v>未提供</x:v>
@@ -5996,165 +6332,1161 @@
     </x:row>
     <x:row r="45" ht="72" customHeight="1">
       <x:c r="A45" s="4" t="str">
-        <x:v>TASK-TM001-MAC</x:v>
+        <x:v>TASK-TM003-PARSE</x:v>
       </x:c>
       <x:c r="B45" s="4" t="str">
-        <x:v>历史分组</x:v>
+        <x:v>具体任务</x:v>
       </x:c>
       <x:c r="C45" s="4" t="str">
+        <x:v>FP-TM003-01</x:v>
+      </x:c>
+      <x:c r="D45" s="4" t="str">
+        <x:v>REQ-TM003</x:v>
+      </x:c>
+      <x:c r="E45" s="4" t="str">
+        <x:v>AC-TM003-001
+AC-TM003-002</x:v>
+      </x:c>
+      <x:c r="F45" s="4" t="str">
+        <x:v>SOURCE、FIXTURE；可先独立源码准备</x:v>
+      </x:c>
+      <x:c r="G45" s="4" t="str">
+        <x:v>产物：将完整原生 JSONL 行转换为只含白名单字段的候选用量；检验非负数、子项、UTC、版本、模型
+完成条件：增量、累计、未知/损坏及未知模型分别有确定结果；不从累计字段重复算量</x:v>
+      </x:c>
+      <x:c r="H45" s="4" t="str">
+        <x:v>SOURCE、FIXTURE；可先独立源码准备</x:v>
+      </x:c>
+      <x:c r="I45" s="4" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="D45" s="4" t="str">
-        <x:v>REQ-TM001</x:v>
-      </x:c>
-      <x:c r="E45" s="4" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="F45" s="4" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="G45" s="4" t="str">
-        <x:v>Electron React/TypeScript 登录/改密/主页/管理、默认本机 API/更新源地址与配置管理页的用户覆盖持久化；默认开启可关闭的设备自动登录、按规范化 origin 隔离的受保护凭据文件与内存会话、稳定 UI 标识、Playwright Electron工程</x:v>
-      </x:c>
-      <x:c r="H45" s="4" t="str">
-        <x:v>API 合同、工程骨架</x:v>
-      </x:c>
-      <x:c r="I45" s="4" t="str">
-        <x:v>E2E-TM001-001、E2E-TM001-002、E2E-TM001-003、E2E-TM001-004、E2E-TM001-005、E2E-TM001-006</x:v>
-      </x:c>
       <x:c r="J45" s="4" t="str">
-        <x:v>historical_group_not_minimal_task</x:v>
+        <x:v>规划中</x:v>
       </x:c>
       <x:c r="K45" s="4" t="str">
-        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:12</x:v>
+        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:23</x:v>
       </x:c>
       <x:c r="L45" s="4" t="str">
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" ht="57" customHeight="1">
+    <x:row r="46" ht="72" customHeight="1">
       <x:c r="A46" s="9" t="str">
-        <x:v>TASK-TM001-UPDATE</x:v>
+        <x:v>TASK-TM003-IDENTITY</x:v>
       </x:c>
       <x:c r="B46" s="9" t="str">
-        <x:v>历史分组</x:v>
+        <x:v>具体任务</x:v>
       </x:c>
       <x:c r="C46" s="9" t="str">
+        <x:v>FP-TM003-02</x:v>
+      </x:c>
+      <x:c r="D46" s="9" t="str">
+        <x:v>REQ-TM003</x:v>
+      </x:c>
+      <x:c r="E46" s="9" t="str">
+        <x:v>AC-TM003-002</x:v>
+      </x:c>
+      <x:c r="F46" s="9" t="str">
+        <x:v>PARSE、STORE；独立于 UI</x:v>
+      </x:c>
+      <x:c r="G46" s="9" t="str">
+        <x:v>产物：版本固定的来源域+原生调用 ID 本机 HMAC、同 ID 冲突/不明重用诊断、fork 继承边界与重放处理；共享事件字段与 TM-004 合同一致
+完成条件：同来源同 ID 重放计一次，跨来源同字面 ID 不冲突；无可证实的跨 Agent/会话重用标覆盖不完整；方案升级不能使旧日志双计</x:v>
+      </x:c>
+      <x:c r="H46" s="9" t="str">
+        <x:v>PARSE、STORE；独立于 UI</x:v>
+      </x:c>
+      <x:c r="I46" s="9" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="D46" s="9" t="str">
-        <x:v>REQ-TM001</x:v>
-      </x:c>
-      <x:c r="E46" s="9" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="F46" s="9" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="G46" s="9" t="str">
-        <x:v>固定 Ed25519 公钥、同机回环更新源/签名测试包/失败包及真实更新用例；默认49177配置、URL安全校验与升级时锁定更新设置；两构建沿用经校验的同一隔离profile，升级后服务验证自动登录</x:v>
-      </x:c>
-      <x:c r="H46" s="9" t="str">
-        <x:v>Mac 工程</x:v>
-      </x:c>
-      <x:c r="I46" s="9" t="str">
-        <x:v>E2E-TM001-004</x:v>
-      </x:c>
       <x:c r="J46" s="9" t="str">
-        <x:v>historical_group_not_minimal_task</x:v>
+        <x:v>规划中</x:v>
       </x:c>
       <x:c r="K46" s="9" t="str">
-        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:13</x:v>
+        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:24</x:v>
       </x:c>
       <x:c r="L46" s="9" t="str">
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="47" ht="57" customHeight="1">
+    <x:row r="47" ht="87" customHeight="1">
       <x:c r="A47" s="4" t="str">
-        <x:v>TASK-TM001-RUNNER</x:v>
+        <x:v>TASK-TM003-SCAN</x:v>
       </x:c>
       <x:c r="B47" s="4" t="str">
-        <x:v>历史分组</x:v>
+        <x:v>具体任务</x:v>
       </x:c>
       <x:c r="C47" s="4" t="str">
+        <x:v>FP-TM003-02</x:v>
+      </x:c>
+      <x:c r="D47" s="4" t="str">
+        <x:v>REQ-TM003</x:v>
+      </x:c>
+      <x:c r="E47" s="4" t="str">
+        <x:v>AC-TM003-001
+AC-TM003-003
+AC-TM003-004</x:v>
+      </x:c>
+      <x:c r="F47" s="4" t="str">
+        <x:v>PARSE、IDENTITY、STORE、AUTH</x:v>
+      </x:c>
+      <x:c r="G47" s="4" t="str">
+        <x:v>产物：限定授权根的可续扫内部分页枚举、完成/截断/取消状态、完整行游标、文件变化/30 秒补扫/手动刷新、移动/截断恢复；不把 UI 预览上限当全量
+完成条件：半行不前进、补全一次入库；超预览上限后仍能读到授权根末端用量并仅在全量完成时清除不完整提示；移动/重启/截断不重计，目录外与越界符号链接不可读</x:v>
+      </x:c>
+      <x:c r="H47" s="4" t="str">
+        <x:v>PARSE、IDENTITY、STORE、AUTH</x:v>
+      </x:c>
+      <x:c r="I47" s="4" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="D47" s="4" t="str">
-        <x:v>REQ-TM001</x:v>
-      </x:c>
-      <x:c r="E47" s="4" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="F47" s="4" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="G47" s="4" t="str">
-        <x:v>本机Playwright从最终DMG安装App执行全部六例，原始JSON/trace/fixtureSQL/包摘要、父门禁复核；默认值与动态独占端口隔离测试；真实Squirrel自重启及profile、身份恢复</x:v>
-      </x:c>
-      <x:c r="H47" s="4" t="str">
-        <x:v>数据/桌面工程</x:v>
-      </x:c>
-      <x:c r="I47" s="4" t="str">
-        <x:v>E2E-TM001-001、E2E-TM001-002、E2E-TM001-003、E2E-TM001-004、E2E-TM001-005、E2E-TM001-006</x:v>
-      </x:c>
       <x:c r="J47" s="4" t="str">
-        <x:v>historical_group_not_minimal_task</x:v>
+        <x:v>规划中</x:v>
       </x:c>
       <x:c r="K47" s="4" t="str">
-        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:14</x:v>
+        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:25</x:v>
       </x:c>
       <x:c r="L47" s="4" t="str">
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" ht="32" customHeight="1">
+    <x:row r="48" ht="72" customHeight="1">
       <x:c r="A48" s="9" t="str">
-        <x:v>TASK-TM001-REVIEW</x:v>
+        <x:v>TASK-TM003-AUTH</x:v>
       </x:c>
       <x:c r="B48" s="9" t="str">
-        <x:v>历史分组</x:v>
+        <x:v>具体任务</x:v>
       </x:c>
       <x:c r="C48" s="9" t="str">
+        <x:v>FP-TM003-03</x:v>
+      </x:c>
+      <x:c r="D48" s="9" t="str">
+        <x:v>REQ-TM003</x:v>
+      </x:c>
+      <x:c r="E48" s="9" t="str">
+        <x:v>AC-TM003-004</x:v>
+      </x:c>
+      <x:c r="F48" s="9" t="str">
+        <x:v>TM-002 稳定提交及接口，**BLOCKED**</x:v>
+      </x:c>
+      <x:c r="G48" s="9" t="str">
+        <x:v>产物：经 TM-002 可替换只读能力获取确认来源及已验证 origin+account.id，接收失效/撤销/身份切换通知；仅主进程读日志
+完成条件：确认前/失效/身份切换时无旧能力读取；不同主体事件与游标隔离，重新确认后仅本主体补扫</x:v>
+      </x:c>
+      <x:c r="H48" s="9" t="str">
+        <x:v>TM-002 稳定提交及接口，**BLOCKED**</x:v>
+      </x:c>
+      <x:c r="I48" s="9" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="D48" s="9" t="str">
-        <x:v>REQ-TM001</x:v>
-      </x:c>
-      <x:c r="E48" s="9" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="F48" s="9" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="G48" s="9" t="str">
-        <x:v>完整回归、流程复盘、PR 与合并判定、发布阻塞记录</x:v>
-      </x:c>
-      <x:c r="H48" s="9" t="str">
-        <x:v>全部实现任务</x:v>
-      </x:c>
-      <x:c r="I48" s="9" t="str">
-        <x:v>TEST-TM001-GOVERNANCE</x:v>
-      </x:c>
       <x:c r="J48" s="9" t="str">
-        <x:v>historical_group_not_minimal_task</x:v>
+        <x:v>规划中</x:v>
       </x:c>
       <x:c r="K48" s="9" t="str">
-        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:15</x:v>
+        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:26</x:v>
       </x:c>
       <x:c r="L48" s="9" t="str">
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
+    <x:row r="49" ht="57" customHeight="1">
+      <x:c r="A49" s="4" t="str">
+        <x:v>TASK-TM003-UI</x:v>
+      </x:c>
+      <x:c r="B49" s="4" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C49" s="4" t="str">
+        <x:v>FP-TM003-03</x:v>
+      </x:c>
+      <x:c r="D49" s="4" t="str">
+        <x:v>REQ-TM003</x:v>
+      </x:c>
+      <x:c r="E49" s="4" t="str">
+        <x:v>AC-TM003-001
+AC-TM003-003</x:v>
+      </x:c>
+      <x:c r="F49" s="4" t="str">
+        <x:v>STORE、SCAN、AUTH，**BLOCKED**</x:v>
+      </x:c>
+      <x:c r="G49" s="4" t="str">
+        <x:v>产物：React 最小采集卡片与诊断，受限 preload/IPC，无任意路径参数
+完成条件：显示可信总量、cached 子项、覆盖起点、未知/失效/最后采集；UI 手动刷新真实驱动主进程</x:v>
+      </x:c>
+      <x:c r="H49" s="4" t="str">
+        <x:v>STORE、SCAN、AUTH，**BLOCKED**</x:v>
+      </x:c>
+      <x:c r="I49" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J49" s="4" t="str">
+        <x:v>规划中</x:v>
+      </x:c>
+      <x:c r="K49" s="4" t="str">
+        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:27</x:v>
+      </x:c>
+      <x:c r="L49" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="57" customHeight="1">
+      <x:c r="A50" s="9" t="str">
+        <x:v>TASK-TM003-MIGRATE</x:v>
+      </x:c>
+      <x:c r="B50" s="9" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C50" s="9" t="str">
+        <x:v>FP-TM003-02</x:v>
+      </x:c>
+      <x:c r="D50" s="9" t="str">
+        <x:v>REQ-TM003</x:v>
+      </x:c>
+      <x:c r="E50" s="9" t="str">
+        <x:v>AC-TM003-001
+AC-TM003-003</x:v>
+      </x:c>
+      <x:c r="F50" s="9" t="str">
+        <x:v>STORE、TM-001 已分发稳定包状态，**BLOCKED**</x:v>
+      </x:c>
+      <x:c r="G50" s="9" t="str">
+        <x:v>产物：新客户端 SQLite schema 的事务迁移、备份/恢复和旧版启动兼容
+完成条件：源/目标 schema、聚合和中断恢复由 SOP-016 在隔离库验证；无稳定旧包时记录该事实</x:v>
+      </x:c>
+      <x:c r="H50" s="9" t="str">
+        <x:v>STORE、TM-001 已分发稳定包状态，**BLOCKED**</x:v>
+      </x:c>
+      <x:c r="I50" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J50" s="9" t="str">
+        <x:v>规划中</x:v>
+      </x:c>
+      <x:c r="K50" s="9" t="str">
+        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:28</x:v>
+      </x:c>
+      <x:c r="L50" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="72" customHeight="1">
+      <x:c r="A51" s="4" t="str">
+        <x:v>TASK-TM003-E2E</x:v>
+      </x:c>
+      <x:c r="B51" s="4" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C51" s="4" t="str">
+        <x:v>FP-TM003-04</x:v>
+      </x:c>
+      <x:c r="D51" s="4" t="str">
+        <x:v>REQ-TM003</x:v>
+      </x:c>
+      <x:c r="E51" s="4" t="str">
+        <x:v>AC-TM003-001
+AC-TM003-002
+AC-TM003-003
+AC-TM003-004</x:v>
+      </x:c>
+      <x:c r="F51" s="4" t="str">
+        <x:v>FIXTURE、UI、TM-001/002 稳定产品与隔离 GUI 资源，**BLOCKED**</x:v>
+      </x:c>
+      <x:c r="G51" s="4" t="str">
+        <x:v>产物：扩展当前仅 TM-001 的 runner、逐 TC Playwright Electron 测试、每步原件与跨版本完整集合机器门禁；四场景组作补充
+完成条件：每条本版 TC 可独立调用；门禁拒绝缺任一本版/历史 TC、变体或步骤的原件；最终 DMG 安装后真实 UI/IPC/SQLite 与全部历史功能同批完整通过</x:v>
+      </x:c>
+      <x:c r="H51" s="4" t="str">
+        <x:v>FIXTURE、UI、TM-001/002 稳定产品与隔离 GUI 资源，**BLOCKED**</x:v>
+      </x:c>
+      <x:c r="I51" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J51" s="4" t="str">
+        <x:v>规划中</x:v>
+      </x:c>
+      <x:c r="K51" s="4" t="str">
+        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:29</x:v>
+      </x:c>
+      <x:c r="L51" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="72" customHeight="1">
+      <x:c r="A52" s="9" t="str">
+        <x:v>TASK-TM003-RELEASE</x:v>
+      </x:c>
+      <x:c r="B52" s="9" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C52" s="9" t="str">
+        <x:v>FP-TM003-04</x:v>
+      </x:c>
+      <x:c r="D52" s="9" t="str">
+        <x:v>REQ-TM003</x:v>
+      </x:c>
+      <x:c r="E52" s="9" t="str">
+        <x:v>AC-TM003-001
+AC-TM003-002
+AC-TM003-003
+AC-TM003-004</x:v>
+      </x:c>
+      <x:c r="F52" s="9" t="str">
+        <x:v>全部任务、SOP-013/014/017/018</x:v>
+      </x:c>
+      <x:c r="G52" s="9" t="str">
+        <x:v>产物：本版文档、总表、Changelog、源码交接、候选与本机档案
+完成条件：清单/Excel回读、实际结果和候选一致；门禁 PASS 才正式 tag/DMG，否则准确 BLOCKED</x:v>
+      </x:c>
+      <x:c r="H52" s="9" t="str">
+        <x:v>全部任务、SOP-013/014/017/018</x:v>
+      </x:c>
+      <x:c r="I52" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J52" s="9" t="str">
+        <x:v>规划中</x:v>
+      </x:c>
+      <x:c r="K52" s="9" t="str">
+        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:30</x:v>
+      </x:c>
+      <x:c r="L52" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="72" customHeight="1">
+      <x:c r="A53" s="4" t="str">
+        <x:v>TASK-TM004-SOURCE</x:v>
+      </x:c>
+      <x:c r="B53" s="4" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C53" s="4" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="D53" s="4" t="str">
+        <x:v>REQ-TM004</x:v>
+      </x:c>
+      <x:c r="E53" s="4" t="str">
+        <x:v>AC-TM004-001
+AC-TM004-002
+AC-TM004-003
+AC-TM004-004</x:v>
+      </x:c>
+      <x:c r="F53" s="4" t="str">
+        <x:v>TM-002授权句柄、项目目录</x:v>
+      </x:c>
+      <x:c r="G53" s="4" t="str">
+        <x:v>只遍历授权根下已确认的主/子日志；失权停扫、重授补扫；越界拒绝；预览与采集分别判定</x:v>
+      </x:c>
+      <x:c r="H53" s="4" t="str">
+        <x:v>TM-002授权接口及可续扫合同</x:v>
+      </x:c>
+      <x:c r="I53" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J53" s="4" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="K53" s="4" t="str">
+        <x:v>releases/v0.4.0-20261001T040433Z/02-breakdown.md</x:v>
+      </x:c>
+      <x:c r="L53" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="72" customHeight="1">
+      <x:c r="A54" s="9" t="str">
+        <x:v>TASK-TM004-PARSER</x:v>
+      </x:c>
+      <x:c r="B54" s="9" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C54" s="9" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="D54" s="9" t="str">
+        <x:v>REQ-TM004</x:v>
+      </x:c>
+      <x:c r="E54" s="9" t="str">
+        <x:v>AC-TM004-001
+AC-TM004-002
+AC-TM004-003
+AC-TM004-004</x:v>
+      </x:c>
+      <x:c r="F54" s="9" t="str">
+        <x:v>版本来源明确的完整原始行</x:v>
+      </x:c>
+      <x:c r="G54" s="9" t="str">
+        <x:v>抽取usage、模型、UTC时间、主/子标志及来源标识；不保留正文</x:v>
+      </x:c>
+      <x:c r="H54" s="9" t="str">
+        <x:v>raw样本、TM-003事件合同</x:v>
+      </x:c>
+      <x:c r="I54" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J54" s="9" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="K54" s="9" t="str">
+        <x:v>releases/v0.4.0-20261001T040433Z/02-breakdown.md</x:v>
+      </x:c>
+      <x:c r="L54" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="72" customHeight="1">
+      <x:c r="A55" s="4" t="str">
+        <x:v>TASK-TM004-LINEAGE</x:v>
+      </x:c>
+      <x:c r="B55" s="4" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C55" s="4" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="D55" s="4" t="str">
+        <x:v>REQ-TM004</x:v>
+      </x:c>
+      <x:c r="E55" s="4" t="str">
+        <x:v>AC-TM004-001
+AC-TM004-002
+AC-TM004-003
+AC-TM004-004</x:v>
+      </x:c>
+      <x:c r="F55" s="4" t="str">
+        <x:v>父子与fork来源证据</x:v>
+      </x:c>
+      <x:c r="G55" s="4" t="str">
+        <x:v>证实父子关系时正确归属；证实继承历史时跨会话去重；歧义诊断且不污染可信量</x:v>
+      </x:c>
+      <x:c r="H55" s="4" t="str">
+        <x:v>raw父子/fork样本、PARSER</x:v>
+      </x:c>
+      <x:c r="I55" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J55" s="4" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="K55" s="4" t="str">
+        <x:v>releases/v0.4.0-20261001T040433Z/02-breakdown.md</x:v>
+      </x:c>
+      <x:c r="L55" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="72" customHeight="1">
+      <x:c r="A56" s="9" t="str">
+        <x:v>TASK-TM004-INCREMENTAL</x:v>
+      </x:c>
+      <x:c r="B56" s="9" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C56" s="9" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="D56" s="9" t="str">
+        <x:v>REQ-TM004</x:v>
+      </x:c>
+      <x:c r="E56" s="9" t="str">
+        <x:v>AC-TM004-001
+AC-TM004-002
+AC-TM004-003
+AC-TM004-004</x:v>
+      </x:c>
+      <x:c r="F56" s="9" t="str">
+        <x:v>追加、半行、重复片段、跨来源ID、重启</x:v>
+      </x:c>
+      <x:c r="G56" s="9" t="str">
+        <x:v>持久游标、唯一键及事务；完整行才提交；跨来源不误去重；重扫幂等</x:v>
+      </x:c>
+      <x:c r="H56" s="9" t="str">
+        <x:v>TM-003 SQLite身份合同、PARSER</x:v>
+      </x:c>
+      <x:c r="I56" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J56" s="9" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="K56" s="9" t="str">
+        <x:v>releases/v0.4.0-20261001T040433Z/02-breakdown.md</x:v>
+      </x:c>
+      <x:c r="L56" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="72" customHeight="1">
+      <x:c r="A57" s="4" t="str">
+        <x:v>TASK-TM004-DIAGNOSTIC</x:v>
+      </x:c>
+      <x:c r="B57" s="4" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C57" s="4" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="D57" s="4" t="str">
+        <x:v>REQ-TM004</x:v>
+      </x:c>
+      <x:c r="E57" s="4" t="str">
+        <x:v>AC-TM004-001
+AC-TM004-002
+AC-TM004-003
+AC-TM004-004</x:v>
+      </x:c>
+      <x:c r="F57" s="4" t="str">
+        <x:v>缺usage、未知格式、读取失败</x:v>
+      </x:c>
+      <x:c r="G57" s="4" t="str">
+        <x:v>UI区分可信零、未知、缺失、无授权；诊断不泄露正文或完整路径</x:v>
+      </x:c>
+      <x:c r="H57" s="4" t="str">
+        <x:v>TM-003诊断接口、PARSER</x:v>
+      </x:c>
+      <x:c r="I57" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J57" s="4" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="K57" s="4" t="str">
+        <x:v>releases/v0.4.0-20261001T040433Z/02-breakdown.md</x:v>
+      </x:c>
+      <x:c r="L57" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="72" customHeight="1">
+      <x:c r="A58" s="9" t="str">
+        <x:v>TASK-TM004-DATA</x:v>
+      </x:c>
+      <x:c r="B58" s="9" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C58" s="9" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="D58" s="9" t="str">
+        <x:v>REQ-TM004</x:v>
+      </x:c>
+      <x:c r="E58" s="9" t="str">
+        <x:v>AC-TM004-001
+AC-TM004-002
+AC-TM004-003
+AC-TM004-004</x:v>
+      </x:c>
+      <x:c r="F58" s="9" t="str">
+        <x:v>隔离Claude Code 2.1.126原生投影与合成反例</x:v>
+      </x:c>
+      <x:c r="G58" s="9" t="str">
+        <x:v>版本化fixture生成、追加/半行/撤权程序、独立expected及SQLite只读检查</x:v>
+      </x:c>
+      <x:c r="H58" s="9" t="str">
+        <x:v>raw来源、TM-002/003数据合同</x:v>
+      </x:c>
+      <x:c r="I58" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J58" s="9" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="K58" s="9" t="str">
+        <x:v>releases/v0.4.0-20261001T040433Z/02-breakdown.md</x:v>
+      </x:c>
+      <x:c r="L58" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="72" customHeight="1">
+      <x:c r="A59" s="4" t="str">
+        <x:v>TASK-TM004-E2E</x:v>
+      </x:c>
+      <x:c r="B59" s="4" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C59" s="4" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="D59" s="4" t="str">
+        <x:v>REQ-TM004</x:v>
+      </x:c>
+      <x:c r="E59" s="4" t="str">
+        <x:v>AC-TM004-001
+AC-TM004-002
+AC-TM004-003
+AC-TM004-004</x:v>
+      </x:c>
+      <x:c r="F59" s="4" t="str">
+        <x:v>最终安装App、真实服务、隔离SQLite</x:v>
+      </x:c>
+      <x:c r="G59" s="4" t="str">
+        <x:v>全部细TC绑定固定Playwright Electron测试；逐步原始记录及历史功能全量回归</x:v>
+      </x:c>
+      <x:c r="H59" s="4" t="str">
+        <x:v>SOURCE→DATA、TM-001包执行器</x:v>
+      </x:c>
+      <x:c r="I59" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J59" s="4" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="K59" s="4" t="str">
+        <x:v>releases/v0.4.0-20261001T040433Z/02-breakdown.md</x:v>
+      </x:c>
+      <x:c r="L59" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="72" customHeight="1">
+      <x:c r="A60" s="9" t="str">
+        <x:v>TASK-TM004-RELEASE</x:v>
+      </x:c>
+      <x:c r="B60" s="9" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C60" s="9" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="D60" s="9" t="str">
+        <x:v>REQ-TM004</x:v>
+      </x:c>
+      <x:c r="E60" s="9" t="str">
+        <x:v>AC-TM004-001
+AC-TM004-002
+AC-TM004-003
+AC-TM004-004</x:v>
+      </x:c>
+      <x:c r="F60" s="9" t="str">
+        <x:v>完整候选</x:v>
+      </x:c>
+      <x:c r="G60" s="9" t="str">
+        <x:v>文档、矩阵、总表、Changelog同步；DMG安装门禁；交总控集成</x:v>
+      </x:c>
+      <x:c r="H60" s="9" t="str">
+        <x:v>E2E与此前版本全回归</x:v>
+      </x:c>
+      <x:c r="I60" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J60" s="9" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="K60" s="9" t="str">
+        <x:v>releases/v0.4.0-20261001T040433Z/02-breakdown.md</x:v>
+      </x:c>
+      <x:c r="L60" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="42" customHeight="1">
+      <x:c r="A61" s="4" t="str">
+        <x:v>TASK-TM005-EVENT-CONTRACT</x:v>
+      </x:c>
+      <x:c r="B61" s="4" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C61" s="4" t="str">
+        <x:v>FP-TM005-01</x:v>
+      </x:c>
+      <x:c r="D61" s="4" t="str">
+        <x:v>REQ-TM005</x:v>
+      </x:c>
+      <x:c r="E61" s="4" t="str">
+        <x:v>AC-TM005-001
+AC-TM005-002</x:v>
+      </x:c>
+      <x:c r="F61" s="4" t="str">
+        <x:v>TM-003/004稳定事件schema与诊断</x:v>
+      </x:c>
+      <x:c r="G61" s="4" t="str">
+        <x:v>本账号可信事件集合；重复不入账、冲突不静默完成</x:v>
+      </x:c>
+      <x:c r="H61" s="4" t="str">
+        <x:v>TM-003/004 schema与原生版本</x:v>
+      </x:c>
+      <x:c r="I61" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J61" s="4" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="K61" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/02-breakdown.md:10</x:v>
+      </x:c>
+      <x:c r="L61" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="32" customHeight="1">
+      <x:c r="A62" s="9" t="str">
+        <x:v>TASK-TM005-RANGE-QUERY</x:v>
+      </x:c>
+      <x:c r="B62" s="9" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C62" s="9" t="str">
+        <x:v>FP-TM005-02</x:v>
+      </x:c>
+      <x:c r="D62" s="9" t="str">
+        <x:v>REQ-TM005</x:v>
+      </x:c>
+      <x:c r="E62" s="9" t="str">
+        <x:v>AC-TM005-001</x:v>
+      </x:c>
+      <x:c r="F62" s="9" t="str">
+        <x:v>可信事件、当地日期与IANA时区</x:v>
+      </x:c>
+      <x:c r="G62" s="9" t="str">
+        <x:v>同一只读事务的汇总、逐日点、明细与模型分组；DST日界正确</x:v>
+      </x:c>
+      <x:c r="H62" s="9" t="str">
+        <x:v>稳定事件表</x:v>
+      </x:c>
+      <x:c r="I62" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J62" s="9" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="K62" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/02-breakdown.md:11</x:v>
+      </x:c>
+      <x:c r="L62" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="32" customHeight="1">
+      <x:c r="A63" s="4" t="str">
+        <x:v>TASK-TM005-COVERAGE</x:v>
+      </x:c>
+      <x:c r="B63" s="4" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C63" s="4" t="str">
+        <x:v>FP-TM005-03</x:v>
+      </x:c>
+      <x:c r="D63" s="4" t="str">
+        <x:v>REQ-TM005</x:v>
+      </x:c>
+      <x:c r="E63" s="4" t="str">
+        <x:v>AC-TM005-002</x:v>
+      </x:c>
+      <x:c r="F63" s="4" t="str">
+        <x:v>来源覆盖证明、诊断和未知字段</x:v>
+      </x:c>
+      <x:c r="G63" s="4" t="str">
+        <x:v>缺失、零、未知三态；无覆盖不能判零</x:v>
+      </x:c>
+      <x:c r="H63" s="4" t="str">
+        <x:v>TM-003/004覆盖合同</x:v>
+      </x:c>
+      <x:c r="I63" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J63" s="4" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="K63" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/02-breakdown.md:12</x:v>
+      </x:c>
+      <x:c r="L63" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="32" customHeight="1">
+      <x:c r="A64" s="9" t="str">
+        <x:v>TASK-TM005-UI</x:v>
+      </x:c>
+      <x:c r="B64" s="9" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C64" s="9" t="str">
+        <x:v>FP-TM005-04</x:v>
+      </x:c>
+      <x:c r="D64" s="9" t="str">
+        <x:v>REQ-TM005</x:v>
+      </x:c>
+      <x:c r="E64" s="9" t="str">
+        <x:v>AC-TM005-001</x:v>
+      </x:c>
+      <x:c r="F64" s="9" t="str">
+        <x:v>受限统计IPC结果</x:v>
+      </x:c>
+      <x:c r="G64" s="9" t="str">
+        <x:v>真实桌面统计视图；空/倒置日期拒绝、重启保持</x:v>
+      </x:c>
+      <x:c r="H64" s="9" t="str">
+        <x:v>真实IPC/客户端SQLite</x:v>
+      </x:c>
+      <x:c r="I64" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J64" s="9" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="K64" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/02-breakdown.md:13</x:v>
+      </x:c>
+      <x:c r="L64" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="42" customHeight="1">
+      <x:c r="A65" s="4" t="str">
+        <x:v>TASK-TM005-DATA</x:v>
+      </x:c>
+      <x:c r="B65" s="4" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C65" s="4" t="str">
+        <x:v>FP-TM005-05</x:v>
+      </x:c>
+      <x:c r="D65" s="4" t="str">
+        <x:v>REQ-TM005</x:v>
+      </x:c>
+      <x:c r="E65" s="4" t="str">
+        <x:v>AC-TM005-001
+AC-TM005-002</x:v>
+      </x:c>
+      <x:c r="F65" s="4" t="str">
+        <x:v>seed42、参考时钟与两来源已验证原生日志</x:v>
+      </x:c>
+      <x:c r="G65" s="4" t="str">
+        <x:v>独立expected及隔离账号/库/目录重置；不直接SQL灌统计事件</x:v>
+      </x:c>
+      <x:c r="H65" s="4" t="str">
+        <x:v>TM-003/004 raw样例</x:v>
+      </x:c>
+      <x:c r="I65" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J65" s="4" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="K65" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/02-breakdown.md:14</x:v>
+      </x:c>
+      <x:c r="L65" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="42" customHeight="1">
+      <x:c r="A66" s="9" t="str">
+        <x:v>TASK-TM005-E2E</x:v>
+      </x:c>
+      <x:c r="B66" s="9" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C66" s="9" t="str">
+        <x:v>FP-TM005-06</x:v>
+      </x:c>
+      <x:c r="D66" s="9" t="str">
+        <x:v>REQ-TM005</x:v>
+      </x:c>
+      <x:c r="E66" s="9" t="str">
+        <x:v>AC-TM005-001
+AC-TM005-002</x:v>
+      </x:c>
+      <x:c r="F66" s="9" t="str">
+        <x:v>固定候选SHA、最终DMG、全部必测TC与已交付功能</x:v>
+      </x:c>
+      <x:c r="G66" s="9" t="str">
+        <x:v>逐TC原始步骤与完整回归；仅机器门禁PASS可发布</x:v>
+      </x:c>
+      <x:c r="H66" s="9" t="str">
+        <x:v>TM-001–004适用回归与产品数据</x:v>
+      </x:c>
+      <x:c r="I66" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J66" s="9" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="K66" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/02-breakdown.md:15</x:v>
+      </x:c>
+      <x:c r="L66" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="32" customHeight="1">
+      <x:c r="A67" s="4" t="str">
+        <x:v>TASK-TM001-PLAN</x:v>
+      </x:c>
+      <x:c r="B67" s="4" t="str">
+        <x:v>历史分组</x:v>
+      </x:c>
+      <x:c r="C67" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="D67" s="4" t="str">
+        <x:v>REQ-TM001</x:v>
+      </x:c>
+      <x:c r="E67" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="F67" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="G67" s="4" t="str">
+        <x:v>六文档、完整追踪、SOP 修正、基线通过</x:v>
+      </x:c>
+      <x:c r="H67" s="4" t="str">
+        <x:v>需求</x:v>
+      </x:c>
+      <x:c r="I67" s="4" t="str">
+        <x:v>TEST-TM001-GOVERNANCE</x:v>
+      </x:c>
+      <x:c r="J67" s="4" t="str">
+        <x:v>historical_group_not_minimal_task</x:v>
+      </x:c>
+      <x:c r="K67" s="4" t="str">
+        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:9</x:v>
+      </x:c>
+      <x:c r="L67" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="42" customHeight="1">
+      <x:c r="A68" s="9" t="str">
+        <x:v>TASK-TM001-SERVER</x:v>
+      </x:c>
+      <x:c r="B68" s="9" t="str">
+        <x:v>历史分组</x:v>
+      </x:c>
+      <x:c r="C68" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="D68" s="9" t="str">
+        <x:v>REQ-TM001</x:v>
+      </x:c>
+      <x:c r="E68" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="F68" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="G68" s="9" t="str">
+        <x:v>FastAPI/SQLAlchemy/Alembic 工程、真实认证/权限/审计 API；随机可撤销 token 固定30天到期、不滑动，改密/重置/停用撤销旧会话</x:v>
+      </x:c>
+      <x:c r="H68" s="9" t="str">
+        <x:v>计划、数据/测试</x:v>
+      </x:c>
+      <x:c r="I68" s="9" t="str">
+        <x:v>E2E-TM001-001、E2E-TM001-002、E2E-TM001-003</x:v>
+      </x:c>
+      <x:c r="J68" s="9" t="str">
+        <x:v>historical_group_not_minimal_task</x:v>
+      </x:c>
+      <x:c r="K68" s="9" t="str">
+        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:10</x:v>
+      </x:c>
+      <x:c r="L68" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="42" customHeight="1">
+      <x:c r="A69" s="4" t="str">
+        <x:v>TASK-TM001-DATA</x:v>
+      </x:c>
+      <x:c r="B69" s="4" t="str">
+        <x:v>历史分组</x:v>
+      </x:c>
+      <x:c r="C69" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="D69" s="4" t="str">
+        <x:v>REQ-TM001</x:v>
+      </x:c>
+      <x:c r="E69" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="F69" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="G69" s="4" t="str">
+        <x:v>独立测试/生产 SQLite 文件、可执行造数 SQL、生产首建管理员、回归账号/独立预期及安全重置；已有生产密码不可被重建覆盖</x:v>
+      </x:c>
+      <x:c r="H69" s="4" t="str">
+        <x:v>计划、工程骨架</x:v>
+      </x:c>
+      <x:c r="I69" s="4" t="str">
+        <x:v>TEST-TM001-SERVER、E2E-TM001-001、E2E-TM001-005</x:v>
+      </x:c>
+      <x:c r="J69" s="4" t="str">
+        <x:v>historical_group_not_minimal_task</x:v>
+      </x:c>
+      <x:c r="K69" s="4" t="str">
+        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:11</x:v>
+      </x:c>
+      <x:c r="L69" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="72" customHeight="1">
+      <x:c r="A70" s="9" t="str">
+        <x:v>TASK-TM001-MAC</x:v>
+      </x:c>
+      <x:c r="B70" s="9" t="str">
+        <x:v>历史分组</x:v>
+      </x:c>
+      <x:c r="C70" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="D70" s="9" t="str">
+        <x:v>REQ-TM001</x:v>
+      </x:c>
+      <x:c r="E70" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="F70" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="G70" s="9" t="str">
+        <x:v>Electron React/TypeScript 登录/改密/主页/管理、默认本机 API/更新源地址与配置管理页的用户覆盖持久化；默认开启可关闭的设备自动登录、按规范化 origin 隔离的受保护凭据文件与内存会话、稳定 UI 标识、Playwright Electron工程</x:v>
+      </x:c>
+      <x:c r="H70" s="9" t="str">
+        <x:v>API 合同、工程骨架</x:v>
+      </x:c>
+      <x:c r="I70" s="9" t="str">
+        <x:v>E2E-TM001-001、E2E-TM001-002、E2E-TM001-003、E2E-TM001-004、E2E-TM001-005、E2E-TM001-006</x:v>
+      </x:c>
+      <x:c r="J70" s="9" t="str">
+        <x:v>historical_group_not_minimal_task</x:v>
+      </x:c>
+      <x:c r="K70" s="9" t="str">
+        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:12</x:v>
+      </x:c>
+      <x:c r="L70" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="57" customHeight="1">
+      <x:c r="A71" s="4" t="str">
+        <x:v>TASK-TM001-UPDATE</x:v>
+      </x:c>
+      <x:c r="B71" s="4" t="str">
+        <x:v>历史分组</x:v>
+      </x:c>
+      <x:c r="C71" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="D71" s="4" t="str">
+        <x:v>REQ-TM001</x:v>
+      </x:c>
+      <x:c r="E71" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="F71" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="G71" s="4" t="str">
+        <x:v>固定 Ed25519 公钥、同机回环更新源/签名测试包/失败包及真实更新用例；默认49177配置、URL安全校验与升级时锁定更新设置；两构建沿用经校验的同一隔离profile，升级后服务验证自动登录</x:v>
+      </x:c>
+      <x:c r="H71" s="4" t="str">
+        <x:v>Mac 工程</x:v>
+      </x:c>
+      <x:c r="I71" s="4" t="str">
+        <x:v>E2E-TM001-004</x:v>
+      </x:c>
+      <x:c r="J71" s="4" t="str">
+        <x:v>historical_group_not_minimal_task</x:v>
+      </x:c>
+      <x:c r="K71" s="4" t="str">
+        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:13</x:v>
+      </x:c>
+      <x:c r="L71" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="57" customHeight="1">
+      <x:c r="A72" s="9" t="str">
+        <x:v>TASK-TM001-RUNNER</x:v>
+      </x:c>
+      <x:c r="B72" s="9" t="str">
+        <x:v>历史分组</x:v>
+      </x:c>
+      <x:c r="C72" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="D72" s="9" t="str">
+        <x:v>REQ-TM001</x:v>
+      </x:c>
+      <x:c r="E72" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="F72" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="G72" s="9" t="str">
+        <x:v>本机Playwright从最终DMG安装App执行全部六例，原始JSON/trace/fixtureSQL/包摘要、父门禁复核；默认值与动态独占端口隔离测试；真实Squirrel自重启及profile、身份恢复</x:v>
+      </x:c>
+      <x:c r="H72" s="9" t="str">
+        <x:v>数据/桌面工程</x:v>
+      </x:c>
+      <x:c r="I72" s="9" t="str">
+        <x:v>E2E-TM001-001、E2E-TM001-002、E2E-TM001-003、E2E-TM001-004、E2E-TM001-005、E2E-TM001-006</x:v>
+      </x:c>
+      <x:c r="J72" s="9" t="str">
+        <x:v>historical_group_not_minimal_task</x:v>
+      </x:c>
+      <x:c r="K72" s="9" t="str">
+        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:14</x:v>
+      </x:c>
+      <x:c r="L72" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="32" customHeight="1">
+      <x:c r="A73" s="4" t="str">
+        <x:v>TASK-TM001-REVIEW</x:v>
+      </x:c>
+      <x:c r="B73" s="4" t="str">
+        <x:v>历史分组</x:v>
+      </x:c>
+      <x:c r="C73" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="D73" s="4" t="str">
+        <x:v>REQ-TM001</x:v>
+      </x:c>
+      <x:c r="E73" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="F73" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="G73" s="4" t="str">
+        <x:v>完整回归、流程复盘、PR 与合并判定、发布阻塞记录</x:v>
+      </x:c>
+      <x:c r="H73" s="4" t="str">
+        <x:v>全部实现任务</x:v>
+      </x:c>
+      <x:c r="I73" s="4" t="str">
+        <x:v>TEST-TM001-GOVERNANCE</x:v>
+      </x:c>
+      <x:c r="J73" s="4" t="str">
+        <x:v>historical_group_not_minimal_task</x:v>
+      </x:c>
+      <x:c r="K73" s="4" t="str">
+        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:15</x:v>
+      </x:c>
+      <x:c r="L73" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="J5:J48">
+  <x:conditionalFormatting sqref="J5:J73">
     <x:cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="10" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="11" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6fcc64b2616749e2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec70bb3810934e65"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9998,7 +11330,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I83" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J83" s="4" t="str">
         <x:v>未执行</x:v>
@@ -10045,7 +11377,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I84" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J84" s="9" t="str">
         <x:v>未执行</x:v>
@@ -10093,7 +11425,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I85" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J85" s="4" t="str">
         <x:v>未执行</x:v>
@@ -10141,7 +11473,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit、网络 ND0/NDA、本例私有来源密文摘要与 A/B 根身份。#REPLACE_CONFIRMED 另按原子提交时间比较旧 A 停读和新 B 唯一候选；不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I86" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J86" s="9" t="str">
         <x:v>未执行</x:v>
@@ -10187,7 +11519,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit、网络 ND0/NDA、本例私有来源密文摘要与 A/B 根身份。#REPLACE_CONFIRMED 另按原子提交时间比较旧 A 停读和新 B 唯一候选；不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I87" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J87" s="4" t="str">
         <x:v>未执行</x:v>
@@ -10233,7 +11565,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit、网络 ND0/NDA、本例私有来源密文摘要与 A/B 根身份。#REPLACE_CONFIRMED 另按原子提交时间比较旧 A 停读和新 B 唯一候选；不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I88" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J88" s="9" t="str">
         <x:v>未执行</x:v>
@@ -10279,7 +11611,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit、网络 ND0/NDA、本例私有来源密文摘要与 A/B 根身份。#REPLACE_CONFIRMED 另按原子提交时间比较旧 A 停读和新 B 唯一候选；不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I89" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J89" s="4" t="str">
         <x:v>未执行</x:v>
@@ -10331,7 +11663,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I90" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J90" s="9" t="str">
         <x:v>未执行</x:v>
@@ -10379,7 +11711,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I91" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J91" s="4" t="str">
         <x:v>未执行</x:v>
@@ -10427,7 +11759,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I92" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J92" s="9" t="str">
         <x:v>未执行</x:v>
@@ -10475,7 +11807,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I93" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J93" s="4" t="str">
         <x:v>未执行</x:v>
@@ -10523,7 +11855,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I94" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J94" s="9" t="str">
         <x:v>未执行</x:v>
@@ -10569,7 +11901,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I95" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J95" s="4" t="str">
         <x:v>未执行</x:v>
@@ -10615,7 +11947,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I96" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J96" s="9" t="str">
         <x:v>未执行</x:v>
@@ -10661,7 +11993,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I97" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J97" s="4" t="str">
         <x:v>未执行</x:v>
@@ -10709,7 +12041,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I98" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J98" s="9" t="str">
         <x:v>未执行</x:v>
@@ -10757,7 +12089,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I99" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J99" s="4" t="str">
         <x:v>未执行</x:v>
@@ -10805,7 +12137,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I100" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J100" s="9" t="str">
         <x:v>未执行</x:v>
@@ -10851,7 +12183,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I101" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J101" s="4" t="str">
         <x:v>未执行</x:v>
@@ -10897,7 +12229,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I102" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J102" s="9" t="str">
         <x:v>未执行</x:v>
@@ -10945,7 +12277,7 @@
 核验：先执行 Q-TM002-USERS；对照 sessions/audit、网络 ND0/NDA 与本例私有记录的完整布尔对、根身份/密文摘要。#TURN_COLLECT_OFF_ON 另核对旧扫描代际失效和恢复后仅 A；不向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I103" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J103" s="4" t="str">
         <x:v>未执行</x:v>
@@ -10991,7 +12323,7 @@
 核验：先执行 Q-TM002-USERS；对照 sessions/audit、网络 ND0/NDA 与本例私有记录的完整布尔对、根身份/密文摘要。#TURN_COLLECT_OFF_ON 另核对旧扫描代际失效和恢复后仅 A；不向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I104" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J104" s="9" t="str">
         <x:v>未执行</x:v>
@@ -11037,7 +12369,7 @@
 核验：先执行 Q-TM002-USERS；对照 sessions/audit、网络 ND0/NDA 与本例私有记录的完整布尔对、根身份/密文摘要。#TURN_COLLECT_OFF_ON 另核对旧扫描代际失效和恢复后仅 A；不向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I105" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J105" s="4" t="str">
         <x:v>未执行</x:v>
@@ -11083,7 +12415,7 @@
 核验：先执行 Q-TM002-USERS；对照 sessions/audit、网络 ND0/NDA 与本例私有记录的完整布尔对、根身份/密文摘要。#TURN_COLLECT_OFF_ON 另核对旧扫描代际失效和恢复后仅 A；不向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I106" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J106" s="9" t="str">
         <x:v>未执行</x:v>
@@ -11131,7 +12463,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 与真实 /v1/me、网络 NDA、本例私有记录前后摘要和 A/B 文件访问审计；损坏注入不修改服务 DB。</x:v>
       </x:c>
       <x:c r="I107" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J107" s="4" t="str">
         <x:v>未执行</x:v>
@@ -11177,7 +12509,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 与真实 /v1/me、网络 NDA、本例私有记录前后摘要和 A/B 文件访问审计；损坏注入不修改服务 DB。</x:v>
       </x:c>
       <x:c r="I108" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J108" s="9" t="str">
         <x:v>未执行</x:v>
@@ -11223,7 +12555,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 与真实 /v1/me、网络 NDA、本例私有记录前后摘要和 A/B 文件访问审计；损坏注入不修改服务 DB。</x:v>
       </x:c>
       <x:c r="I109" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J109" s="4" t="str">
         <x:v>未执行</x:v>
@@ -11271,7 +12603,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I110" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J110" s="9" t="str">
         <x:v>未执行</x:v>
@@ -11319,7 +12651,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I111" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J111" s="4" t="str">
         <x:v>未执行</x:v>
@@ -11367,7 +12699,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I112" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J112" s="9" t="str">
         <x:v>未执行</x:v>
@@ -11415,7 +12747,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I113" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J113" s="4" t="str">
         <x:v>未执行</x:v>
@@ -11463,7 +12795,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I114" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J114" s="9" t="str">
         <x:v>未执行</x:v>
@@ -11511,7 +12843,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I115" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J115" s="4" t="str">
         <x:v>未执行</x:v>
@@ -11559,7 +12891,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I116" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J116" s="9" t="str">
         <x:v>未执行</x:v>
@@ -11608,7 +12940,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I117" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J117" s="4" t="str">
         <x:v>未执行</x:v>
@@ -11656,7 +12988,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I118" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J118" s="9" t="str">
         <x:v>未执行</x:v>
@@ -11704,7 +13036,7 @@
 核验：不适用：无 DB 连接或 SQL；核对 sources 0600/密文摘要、状态与 A/B 审计。#WRITE_FAIL_KEEP_OLD 核对 B 加密已成功、故障仅在私有写入阶段、失败临时文件不可恢复，随后旧 A 再刷新 A1/A2，原记录字节 SHA 不变。</x:v>
       </x:c>
       <x:c r="I119" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J119" s="4" t="str">
         <x:v>未执行</x:v>
@@ -11750,7 +13082,7 @@
 核验：不适用：无 DB 连接或 SQL；核对 sources 0600/密文摘要、状态与 A/B 审计。#WRITE_FAIL_KEEP_OLD 核对 B 加密已成功、故障仅在私有写入阶段、失败临时文件不可恢复，随后旧 A 再刷新 A1/A2，原记录字节 SHA 不变。</x:v>
       </x:c>
       <x:c r="I120" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J120" s="9" t="str">
         <x:v>未执行</x:v>
@@ -11796,7 +13128,7 @@
 核验：不适用：无 DB 连接或 SQL；核对 sources 0600/密文摘要、状态与 A/B 审计。#WRITE_FAIL_KEEP_OLD 核对 B 加密已成功、故障仅在私有写入阶段、失败临时文件不可恢复，随后旧 A 再刷新 A1/A2，原记录字节 SHA 不变。</x:v>
       </x:c>
       <x:c r="I121" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J121" s="4" t="str">
         <x:v>未执行</x:v>
@@ -11842,7 +13174,7 @@
 核验：不适用：无 DB 连接或 SQL；核对 sources 0600/密文摘要、状态与 A/B 审计。#WRITE_FAIL_KEEP_OLD 核对 B 加密已成功、故障仅在私有写入阶段、失败临时文件不可恢复，随后旧 A 再刷新 A1/A2，原记录字节 SHA 不变。</x:v>
       </x:c>
       <x:c r="I122" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J122" s="9" t="str">
         <x:v>未执行</x:v>
@@ -11890,7 +13222,7 @@
 核验：不适用：无 DB 连接或 SQL；以固定完整相对路径清单比较每页、游标、complete 与 A/B 审计。旧树必须 a.jsonl 先于 a/x.jsonl，后接 p-0000…p-1198，页边界 256/256/256/256/177。#TREE_CHANGED 旧游标 invalid/incomplete；新扫描五页 256/256/256/256/178、1202 名无重漏、p-0000a 总序第 4；只据真实目录和生产 helper/主进程判断。</x:v>
       </x:c>
       <x:c r="I123" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J123" s="4" t="str">
         <x:v>未执行</x:v>
@@ -11936,7 +13268,7 @@
 核验：不适用：无 DB 连接或 SQL；以固定完整相对路径清单比较每页、游标、complete 与 A/B 审计。旧树必须 a.jsonl 先于 a/x.jsonl，后接 p-0000…p-1198，页边界 256/256/256/256/177。#TREE_CHANGED 旧游标 invalid/incomplete；新扫描五页 256/256/256/256/178、1202 名无重漏、p-0000a 总序第 4；只据真实目录和生产 helper/主进程判断。</x:v>
       </x:c>
       <x:c r="I124" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J124" s="9" t="str">
         <x:v>未执行</x:v>
@@ -11982,7 +13314,7 @@
 核验：不适用：无 DB 连接或 SQL；以固定完整相对路径清单比较每页、游标、complete 与 A/B 审计。旧树必须 a.jsonl 先于 a/x.jsonl，后接 p-0000…p-1198，页边界 256/256/256/256/177。#TREE_CHANGED 旧游标 invalid/incomplete；新扫描五页 256/256/256/256/178、1202 名无重漏、p-0000a 总序第 4；只据真实目录和生产 helper/主进程判断。</x:v>
       </x:c>
       <x:c r="I125" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J125" s="4" t="str">
         <x:v>未执行</x:v>
@@ -12028,7 +13360,7 @@
 核验：不适用：无 DB 连接或 SQL；以固定完整相对路径清单比较每页、游标、complete 与 A/B 审计。旧树必须 a.jsonl 先于 a/x.jsonl，后接 p-0000…p-1198，页边界 256/256/256/256/177。#TREE_CHANGED 旧游标 invalid/incomplete；新扫描五页 256/256/256/256/178、1202 名无重漏、p-0000a 总序第 4；只据真实目录和生产 helper/主进程判断。</x:v>
       </x:c>
       <x:c r="I126" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J126" s="9" t="str">
         <x:v>未执行</x:v>
@@ -12076,7 +13408,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I127" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J127" s="4" t="str">
         <x:v>未执行</x:v>
@@ -12122,7 +13454,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I128" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J128" s="9" t="str">
         <x:v>未执行</x:v>
@@ -12168,7 +13500,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I129" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J129" s="4" t="str">
         <x:v>未执行</x:v>
@@ -12214,7 +13546,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I130" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J130" s="9" t="str">
         <x:v>未执行</x:v>
@@ -12260,7 +13592,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I131" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J131" s="4" t="str">
         <x:v>未执行</x:v>
@@ -12306,7 +13638,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I132" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J132" s="9" t="str">
         <x:v>未执行</x:v>
@@ -12352,7 +13684,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I133" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J133" s="4" t="str">
         <x:v>未执行</x:v>
@@ -12398,7 +13730,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I134" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J134" s="9" t="str">
         <x:v>未执行</x:v>
@@ -12446,7 +13778,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I135" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J135" s="4" t="str">
         <x:v>未执行</x:v>
@@ -12494,7 +13826,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I136" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J136" s="9" t="str">
         <x:v>未执行</x:v>
@@ -12540,7 +13872,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I137" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J137" s="4" t="str">
         <x:v>未执行</x:v>
@@ -12586,7 +13918,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I138" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J138" s="9" t="str">
         <x:v>未执行</x:v>
@@ -12632,7 +13964,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I139" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J139" s="4" t="str">
         <x:v>未执行</x:v>
@@ -12680,7 +14012,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I140" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J140" s="9" t="str">
         <x:v>未执行</x:v>
@@ -12726,7 +14058,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I141" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J141" s="4" t="str">
         <x:v>未执行</x:v>
@@ -12772,7 +14104,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I142" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J142" s="9" t="str">
         <x:v>未执行</x:v>
@@ -12818,7 +14150,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I143" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J143" s="4" t="str">
         <x:v>未执行</x:v>
@@ -12864,7 +14196,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I144" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J144" s="9" t="str">
         <x:v>未执行</x:v>
@@ -12910,7 +14242,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I145" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J145" s="4" t="str">
         <x:v>未执行</x:v>
@@ -12956,7 +14288,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I146" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J146" s="9" t="str">
         <x:v>未执行</x:v>
@@ -13004,7 +14336,7 @@
 核验：只读复核 TM-001 全部已交付 TC、其他 27 条 TM-002 父 TC/35 变体的隔离 DB/SQL 引用与原始逐步结果，并核对最终包、升级、清理和候选一致性；本例结果由这些原件派生，不连接生产库。 核对上一0.1稳定原包的通行证、归档、来源SHA/tree及真实升级链。 只读核对schema 2 release-index.json的milestone_sha/tree、master_tip_sha、remote_source_state及原件摘要。</x:v>
       </x:c>
       <x:c r="I147" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J147" s="4" t="str">
         <x:v>未执行</x:v>
@@ -13030,7 +14362,7 @@
         <x:v>E2E-TM003-001</x:v>
       </x:c>
       <x:c r="C148" s="9" t="str">
-        <x:v>增量采集、重扫、重启和移动</x:v>
+        <x:v>增量、重扫、重启及移动</x:v>
       </x:c>
       <x:c r="D148" s="9" t="str">
         <x:v>待拆解</x:v>
@@ -13059,13 +14391,13 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L148" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:11</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:14</x:v>
       </x:c>
       <x:c r="M148" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N148" s="9" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
+        <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="72" customHeight="1">
@@ -13076,7 +14408,7 @@
         <x:v>E2E-TM003-002</x:v>
       </x:c>
       <x:c r="C149" s="4" t="str">
-        <x:v>累计值、重复事件、分支和未知格式</x:v>
+        <x:v>累计、重复、分支及未知</x:v>
       </x:c>
       <x:c r="D149" s="4" t="str">
         <x:v>待拆解</x:v>
@@ -13105,13 +14437,13 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L149" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:28</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:38</x:v>
       </x:c>
       <x:c r="M149" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N149" s="4" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
+        <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="57" customHeight="1">
@@ -13122,7 +14454,7 @@
         <x:v>E2E-TM003-003</x:v>
       </x:c>
       <x:c r="C150" s="9" t="str">
-        <x:v>半行完成与源日志清理</x:v>
+        <x:v>半行、源清理与历史覆盖</x:v>
       </x:c>
       <x:c r="D150" s="9" t="str">
         <x:v>待拆解</x:v>
@@ -13151,13 +14483,13 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L150" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:45</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:63</x:v>
       </x:c>
       <x:c r="M150" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N150" s="9" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
+        <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="57" customHeight="1">
@@ -13168,7 +14500,7 @@
         <x:v>E2E-TM003-004</x:v>
       </x:c>
       <x:c r="C151" s="4" t="str">
-        <x:v>重新授权后的去重</x:v>
+        <x:v>权限边界与重新授权</x:v>
       </x:c>
       <x:c r="D151" s="4" t="str">
         <x:v>待拆解</x:v>
@@ -13197,13 +14529,13 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L151" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:62</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:87</x:v>
       </x:c>
       <x:c r="M151" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N151" s="4" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
+        <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
     <x:row r="152" ht="57" customHeight="1">
@@ -13249,7 +14581,7 @@
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N152" s="9" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
+        <x:v>v0.2.0-20261001T034118Z</x:v>
       </x:c>
     </x:row>
     <x:row r="153" ht="57" customHeight="1">
@@ -13295,7 +14627,7 @@
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N153" s="4" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
+        <x:v>v0.2.0-20261001T034118Z</x:v>
       </x:c>
     </x:row>
     <x:row r="154" ht="57" customHeight="1">
@@ -13341,7 +14673,7 @@
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N154" s="9" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
+        <x:v>v0.2.0-20261001T034118Z</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="57" customHeight="1">
@@ -13387,938 +14719,994 @@
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N155" s="4" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="156" ht="57" customHeight="1">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" ht="72" customHeight="1">
       <x:c r="A156" s="9" t="str">
-        <x:v>TM-005</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B156" s="9" t="str">
-        <x:v>E2E-TM005-001</x:v>
+        <x:v>TC-TM004-SOURCE-01</x:v>
       </x:c>
       <x:c r="C156" s="9" t="str">
-        <x:v>日期筛选、趋势和明细</x:v>
+        <x:v>授权根限定（TASK-TM004-SOURCE，AC-001，E2E-001）</x:v>
       </x:c>
       <x:c r="D156" s="9" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-SOURCE</x:v>
       </x:c>
       <x:c r="E156" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F156" s="9" t="str">
-        <x:v>数据集 date_ranges；date_ranges 已由 scripts/test_data.py 提供标准化语义样例，固定2026-09-29T04:00:00Z、Asia/Shanghai、seed42；13行含1重复、12唯一。需另有已验证raw输入映射和真实App导入流程，当前未实现。</x:v>
+        <x:v>用户经 TM-002 UI 只选择隔离项目A目录；目录内有 M=100/10 完整原始行，旁边未授权目录有 X=999/99。</x:v>
       </x:c>
       <x:c r="G156" s="9" t="str">
-        <x:v>独立expected中的total依次16500、110、17380、27830、31130；custom=2200。today共5条、input15000、output1500、cache1700、reasoning170，cache/reasoning不再相加；custom-start包含、custom-end排除。趋势点及明细按expected事件时间逐条核对。</x:v>
+        <x:v>UI 显示待确认，事件表无新增
+UI 显示1次 M、total110，SQLite只读见唯一M
+调用数仍1、total110
+无X读取请求且事件表无X</x:v>
       </x:c>
       <x:c r="H156" s="9" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读按来源/项目统计 M 行数与 token，总数1/110；检查 X 键不存在；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I156" s="9" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J156" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K156" s="9" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L156" s="9" t="str">
-        <x:v>docs/testing/cases/05-TM-005-usage-statistics.md:15</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:87</x:v>
       </x:c>
       <x:c r="M156" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N156" s="9" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="157" ht="57" customHeight="1">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" ht="72" customHeight="1">
       <x:c r="A157" s="4" t="str">
-        <x:v>TM-005</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B157" s="4" t="str">
-        <x:v>E2E-TM005-002</x:v>
+        <x:v>TC-TM004-SOURCE-02</x:v>
       </x:c>
       <x:c r="C157" s="4" t="str">
-        <x:v>时区、月边界与缺失值</x:v>
+        <x:v>撤权和重新授权（TASK-TM004-SOURCE，AC-004，E2E-004）</x:v>
       </x:c>
       <x:c r="D157" s="4" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-SOURCE</x:v>
       </x:c>
       <x:c r="E157" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F157" s="4" t="str">
-        <x:v>数据集 date_ranges；复用date_ranges中的2026-09-28T15:59:59Z与16:00:00Z、2026-08-30T15:59:59Z与16:00:00Z边界。另需补充覆盖缺口、已覆盖零调用日、unknown字段三类状态；当前生成器未覆盖后面三类。</x:v>
+        <x:v>已扫描 M=100/10、S=200/20；撤权期间子代理新增 N=50/5。</x:v>
       </x:c>
       <x:c r="G157" s="4" t="str">
-        <x:v>Shanghai下15:59:59Z仍属前日、16:00:00Z属次日；UTC下二者同属UTC日期。无覆盖显示缺失，真实零可显示0，unknown字段显示未知；不得互相代替。各范围expected须独立按当地日期边界列出，不调用产品查询生成。</x:v>
+        <x:v>状态显示不可读且保留total330
+仍330且诊断为读取受阻
+唯一 M/S/N、total385
+M/S/N仍为三次且total385</x:v>
       </x:c>
       <x:c r="H157" s="4" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读唯一键数3与 token总385，撤权阶段无N。重置同共用配方；TM-002失权模拟与子目录绑定待补；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I157" s="4" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J157" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K157" s="4" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L157" s="4" t="str">
-        <x:v>docs/testing/cases/05-TM-005-usage-statistics.md:32</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:91</x:v>
       </x:c>
       <x:c r="M157" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N157" s="4" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="158" ht="57" customHeight="1">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" ht="72" customHeight="1">
       <x:c r="A158" s="9" t="str">
-        <x:v>TM-006</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B158" s="9" t="str">
-        <x:v>E2E-TM006-001</x:v>
+        <x:v>TC-TM004-PARSER-01</x:v>
       </x:c>
       <x:c r="C158" s="9" t="str">
-        <x:v>Token子项与基础费用</x:v>
+        <x:v>主/子实际调用（TASK-TM004-PARSER，AC-001，E2E-001）</x:v>
       </x:c>
       <x:c r="D158" s="9" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-PARSER</x:v>
       </x:c>
       <x:c r="E158" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F158" s="9" t="str">
-        <x:v>数据集 pricing；pricing由scripts/test_data.py生成合成非计费价格。gpt-5每百万input/cache/output为USD2/0.2/8；today-gpt input1000含cache200、output100含reasoning20。价格不是厂商现价。</x:v>
+        <x:v>同一项目原始主M100/10与子S200/20，模型各自保留，父关系有原始证据。</x:v>
       </x:c>
       <x:c r="G158" s="9" t="str">
-        <x:v>单调用total=1100；费用=(800×2+200×0.2+100×8)/1000000=USD0.002440，reasoning20不另加价。today已知费用USD0.015190且有1条无价格，alice今日USD0.010090。使用Decimal/十进制独立oracle，不以界面舍入反推底层精度。</x:v>
+        <x:v>可信total110
+可信input300/output30/total330
+仍2次调用/330</x:v>
       </x:c>
       <x:c r="H158" s="9" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读两条唯一事件和模型/父项目归属；不读取正文。版本化raw和模型字段待补；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I158" s="9" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J158" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K158" s="9" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L158" s="9" t="str">
-        <x:v>docs/testing/cases/06-TM-006-cost-estimates.md:15</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:95</x:v>
       </x:c>
       <x:c r="M158" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N158" s="9" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="159" ht="57" customHeight="1">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" ht="102" customHeight="1">
       <x:c r="A159" s="4" t="str">
-        <x:v>TM-006</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B159" s="4" t="str">
-        <x:v>E2E-TM006-002</x:v>
+        <x:v>TC-TM004-PARSER-02</x:v>
       </x:c>
       <x:c r="C159" s="4" t="str">
-        <x:v>历史价格、多币种和未知费用</x:v>
+        <x:v>未知结构/缺字段（TASK-TM004-PARSER，AC-003，E2E-003）</x:v>
       </x:c>
       <x:c r="D159" s="4" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-PARSER</x:v>
       </x:c>
       <x:c r="E159" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F159" s="4" t="str">
-        <x:v>数据集 pricing_extended；pricing_extended planned：同模型在生效时点T前后各一调用，两个独立价格版本；另有USD/CNY各一模型、无价模型和订阅估算模型。必须提供价格/订阅分摊规则及手算expected后才能实现。</x:v>
+        <x:v>已支持版本完整 M100/10、未知结构 U、JSONL 原始行真正缺 usage 的 Q。</x:v>
       </x:c>
       <x:c r="G159" s="4" t="str">
-        <x:v>T前后依各自生效版本计算，历史结果不会悄悄换价；USD与CNY分组，未约定汇率不得相加；无价格显示未知而非0；订阅必须明确估算口径。具体金额oracle依待定义订阅/价格合同生成，当前不得手填PASS。</x:v>
+        <x:v>可信total110
+可信仍110且出现未知结构诊断
+可信仍110、缺usage诊断新增
+诊断可见且不显示 U/Q 为零调用</x:v>
       </x:c>
       <x:c r="H159" s="4" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读可信事件1条/110，诊断各1条；具体版本标识、缺字段schema和SQL待补。隔离负测中 API SSE 省略 usage 后 CLI 仍在原生 JSONL 写0/0，**不是** Q 的原生缺字段样本；Q 需另证来源或标明故障注入，不得把0/0回填解释成已知零；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I159" s="4" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J159" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K159" s="4" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L159" s="4" t="str">
-        <x:v>docs/testing/cases/06-TM-006-cost-estimates.md:32</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:99</x:v>
       </x:c>
       <x:c r="M159" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N159" s="4" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="160" ht="57" customHeight="1">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" ht="72" customHeight="1">
       <x:c r="A160" s="9" t="str">
-        <x:v>TM-007</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B160" s="9" t="str">
-        <x:v>E2E-TM007-001</x:v>
+        <x:v>TC-TM004-LINEAGE-01</x:v>
       </x:c>
       <x:c r="C160" s="9" t="str">
-        <x:v>离线、重启和补传幂等</x:v>
+        <x:v>子代理父项目（TASK-TM004-LINEAGE，AC-001，E2E-001）</x:v>
       </x:c>
       <x:c r="D160" s="9" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-LINEAGE</x:v>
       </x:c>
       <x:c r="E160" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F160" s="9" t="str">
-        <x:v>数据集 sync_faults；sync_faults planned；alice两个隔离设备A/B，设备A调用100/10、B调用200/20；真实FastAPI/SQLite服务，可由外部fixture断网/恢复。账号继续用隔离测试fixture。</x:v>
+        <x:v>项目A主M100/10、子S200/20，另有项目B同名会话标识但无父关系。</x:v>
       </x:c>
       <x:c r="G160" s="9" t="str">
-        <x:v>离线重启不丢队列；恢复后2唯一调用、input300/output30/total330；重复批次不再加量。客户端只在真实确认后标已同步，个人合计与对应团队子集一致。</x:v>
+        <x:v>A=110
+A=330、B=0
+A仍330
+S标为子代理且使用原模型</x:v>
       </x:c>
       <x:c r="H160" s="9" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读S的父项目键为A、事件数2；原始父链线索缺失时不得假称通过；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I160" s="9" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J160" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K160" s="9" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L160" s="9" t="str">
-        <x:v>docs/testing/cases/07-TM-007-team-sync.md:11</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:103</x:v>
       </x:c>
       <x:c r="M160" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N160" s="9" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="161" ht="57" customHeight="1">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" ht="72" customHeight="1">
       <x:c r="A161" s="4" t="str">
-        <x:v>TM-007</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B161" s="4" t="str">
-        <x:v>E2E-TM007-002</x:v>
+        <x:v>TC-TM004-LINEAGE-02</x:v>
       </x:c>
       <x:c r="C161" s="4" t="str">
-        <x:v>部分确认、中断和账号切换</x:v>
+        <x:v>fork继承和ID改写（TASK-TM004-LINEAGE，AC-002，E2E-002）</x:v>
       </x:c>
       <x:c r="D161" s="4" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-LINEAGE</x:v>
       </x:c>
       <x:c r="E161" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F161" s="4" t="str">
-        <x:v>数据集 sync_faults；准备alice的三条唯一事件A/B/C，总量各110/220/330；控制服务仅确认A后断开，B可能已提交但响应丢失，C未提交。另有bob账号。故障注入必须在真实服务外部或明确测试环境中完成，不能绕过认证。</x:v>
+        <x:v>原M100/10、fork复制或引用M但消息ID改写、fork新N50/5。</x:v>
       </x:c>
       <x:c r="G161" s="4" t="str">
-        <x:v>最终alice的A/B/C各一次、total660；响应丢失不造成B重复；bob不能承接或篡改alice既有事件归属。切换时旧队列按已批准归属策略隔离，不能默认为新登录账号。</x:v>
+        <x:v>M仅入账一次且total110
+仍110
+total165且调用数2
+仍165</x:v>
       </x:c>
       <x:c r="H161" s="4" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读可信唯一调用2/165及继承诊断/关系；待schema确定；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I161" s="4" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J161" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K161" s="4" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L161" s="4" t="str">
-        <x:v>docs/testing/cases/07-TM-007-team-sync.md:28</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:107</x:v>
       </x:c>
       <x:c r="M161" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N161" s="4" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="162" ht="57" customHeight="1">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" ht="72" customHeight="1">
       <x:c r="A162" s="9" t="str">
-        <x:v>TM-007</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B162" s="9" t="str">
-        <x:v>E2E-TM007-003</x:v>
+        <x:v>TC-TM004-INCREMENTAL-01</x:v>
       </x:c>
       <x:c r="C162" s="9" t="str">
-        <x:v>上传白名单与项目映射</x:v>
+        <x:v>半行完成（TASK-TM004-INCREMENTAL，AC-002，E2E-002）</x:v>
       </x:c>
       <x:c r="D162" s="9" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-INCREMENTAL</x:v>
       </x:c>
       <x:c r="E162" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F162" s="9" t="str">
-        <x:v>数据集 sync_faults；合成日志包含唯一正文/代码/API-key/完整路径哨兵，以及合法用量/必要去重元数据；只用假值。准备已归属项目A和未归属事件B，待sync_faults生成。</x:v>
+        <x:v>已计M+N total165，P=20/2 原始JSONL行分成两次写入。</x:v>
       </x:c>
       <x:c r="G162" s="9" t="str">
-        <x:v>网络载荷/持久服务数据均不得含正文、代码、key或完整本机路径；只有批准用量/去重字段。B可明确分配，分配不增加事件量、也不跨团队归属。</x:v>
+        <x:v>扫描后仍165、读取游标未越过半行
+扫描后total187、调用数3
+P仅入账一次且total187</x:v>
       </x:c>
       <x:c r="H162" s="9" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读P只一条，可信事件3/187，游标处于完整行末；具体游标schema待补；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I162" s="9" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J162" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K162" s="9" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L162" s="9" t="str">
-        <x:v>docs/testing/cases/07-TM-007-team-sync.md:45</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:111</x:v>
       </x:c>
       <x:c r="M162" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N162" s="9" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="163" ht="57" customHeight="1">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" ht="72" customHeight="1">
       <x:c r="A163" s="4" t="str">
-        <x:v>TM-007</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B163" s="4" t="str">
-        <x:v>E2E-TM007-004</x:v>
+        <x:v>TC-TM004-INCREMENTAL-02</x:v>
       </x:c>
       <x:c r="C163" s="4" t="str">
-        <x:v>统计越权与停用后上传</x:v>
+        <x:v>重复与事务恢复（TASK-TM004-INCREMENTAL，AC-002/004，E2E-002/004）</x:v>
       </x:c>
       <x:c r="D163" s="4" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-INCREMENTAL</x:v>
       </x:c>
       <x:c r="E163" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F163" s="4" t="str">
-        <x:v>数据集 sync_faults；alice项目A调用100/10，bob项目B调用200/20；成员alice与管理员独立会话；alice另有一条未确认调用C=50/5。sync_faults与可重建统计SQL尚未实现。</x:v>
+        <x:v>完整M100/10、重复相同片段及移动/复制文件；在扫描提交边界中断App。</x:v>
       </x:c>
       <x:c r="G163" s="4" t="str">
-        <x:v>成员无权请求被服务端拒绝，UI不显示bob的220；停用后旧会话及上传拒绝，C不能标为已确认；合法历史不能被失败上传删除。此处补足TM-001仅身份/管理接口权限的范围。</x:v>
+        <x:v>M仅入账一次且total110
+仍110
+仍唯一M/110
+total165</x:v>
       </x:c>
       <x:c r="H163" s="4" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读唯一键数2/165且游标一致；故障注入不得绕过产品事务。TM-003事务接口待补；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I163" s="4" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J163" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K163" s="4" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L163" s="4" t="str">
-        <x:v>docs/testing/cases/07-TM-007-team-sync.md:62</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:115</x:v>
       </x:c>
       <x:c r="M163" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N163" s="4" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="164" ht="57" customHeight="1">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" ht="87" customHeight="1">
       <x:c r="A164" s="9" t="str">
-        <x:v>TM-008</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B164" s="9" t="str">
-        <x:v>E2E-TM008-001</x:v>
+        <x:v>TC-TM004-DIAG-01</x:v>
       </x:c>
       <x:c r="C164" s="9" t="str">
-        <x:v>筛选一致的CSV导出</x:v>
+        <x:v>未知值不是零（TASK-TM004-DIAGNOSTIC，AC-003，E2E-003）</x:v>
       </x:c>
       <x:c r="D164" s="9" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-DIAGNOSTIC</x:v>
       </x:c>
       <x:c r="E164" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F164" s="9" t="str">
-        <x:v>数据集 export_rows；export_rows planned；两成员、两个模型、时间范围内外各有事件，独立清单明确每条ID/字段/权限。先具备TM-005/007统计和授权。</x:v>
+        <x:v>可信M100/10、U未知格式、Q的JSONL原始行缺usage，以及另有独立来源证明的有效零usage记录Z。</x:v>
       </x:c>
       <x:c r="G164" s="9" t="str">
-        <x:v>每次CSV仅包含当次筛选且授权可见记录，行数/ID/汇总等于独立清单与界面；不混入旧筛选、其他成员或范围外记录。已知/未知费用语义一致。</x:v>
+        <x:v>显示110
+显示可信110和两个不同未覆盖提示
+零值记录可见但总量仍110
+三种状态不混淆</x:v>
       </x:c>
       <x:c r="H164" s="9" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读可信M和已证实的Z，U/Q仅诊断，不以0写入；Z的原始有效性仍 baseline_pending。2.1.126 遇到畸形合成 API 缺usage会自己写0/0，不能拿该行充当Z；未经额外证据不能由0/0 raw推断上游已知零；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I164" s="9" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J164" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K164" s="9" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L164" s="9" t="str">
-        <x:v>docs/testing/cases/08-TM-008-csv-export.md:11</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:119</x:v>
       </x:c>
       <x:c r="M164" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N164" s="9" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="165" ht="57" customHeight="1">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" ht="72" customHeight="1">
       <x:c r="A165" s="4" t="str">
-        <x:v>TM-008</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B165" s="4" t="str">
-        <x:v>E2E-TM008-002</x:v>
+        <x:v>TC-TM004-DIAG-02</x:v>
       </x:c>
       <x:c r="C165" s="4" t="str">
-        <x:v>CSV转义、未知值及权限</x:v>
+        <x:v>失权提示及隐私（TASK-TM004-DIAGNOSTIC，AC-004，E2E-004）</x:v>
       </x:c>
       <x:c r="D165" s="4" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-DIAGNOSTIC</x:v>
       </x:c>
       <x:c r="E165" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F165" s="4" t="str">
-        <x:v>数据集 export_rows；export_rows需含字段 a,b、say "hi"、带实际换行的项目名、未知费用与非ASCII模型名；两成员各有可区分哨兵事件。只在隔离数据中使用。</x:v>
+        <x:v>M已入账，撤权目录含合成 prompt、代码和密钥哨兵字符串。</x:v>
       </x:c>
       <x:c r="G165" s="4" t="str">
-        <x:v>逗号、双引号、嵌入换行均round-trip一致，Unicode不损坏；未知值不写成0；他人哨兵不出现在文件。若导出失败，不能留下看似完整的半文件。</x:v>
+        <x:v>UI显示读取受阻而非零用量，保留110
+无哨兵文本及完整源路径
+受阻提示消除且M不重计</x:v>
       </x:c>
       <x:c r="H165" s="4" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读事件1/110、诊断状态与仅白名单字段；隐私哨兵由固定生成器构造，不使用真实秘密；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I165" s="4" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J165" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K165" s="4" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L165" s="4" t="str">
-        <x:v>docs/testing/cases/08-TM-008-csv-export.md:28</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:123</x:v>
       </x:c>
       <x:c r="M165" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N165" s="4" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="166" ht="57" customHeight="1">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" ht="72" customHeight="1">
       <x:c r="A166" s="9" t="str">
-        <x:v>TM-009</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B166" s="9" t="str">
-        <x:v>E2E-TM009-001</x:v>
+        <x:v>TC-TM004-DATA-01</x:v>
       </x:c>
       <x:c r="C166" s="9" t="str">
-        <x:v>80%/100%提醒幂等</x:v>
+        <x:v>原始fixture和独立oracle（TASK-TM004-DATA，AC-001–004，E2E-003）</x:v>
       </x:c>
       <x:c r="D166" s="9" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-DATA</x:v>
       </x:c>
       <x:c r="E166" s="9" t="str">
-        <x:v>产品E2E</x:v>
+        <x:v>data_fixture</x:v>
       </x:c>
       <x:c r="F166" s="9" t="str">
-        <x:v>数据集 budget_periods；budget_periods planned；独立个人、项目和团队预算分别100个合成USD单位，同周期使用量依次79→80→99→100；原始调用与价格要能精确形成这些费用。</x:v>
+        <x:v>固定版本 CLI/公开来源、隔离 CLAUDE_CONFIG_DIR、固定合成任务；禁止访问真实 ~/.claude。</x:v>
       </x:c>
       <x:c r="G166" s="9" t="str">
-        <x:v>每预算每周期80与100各最多一次，未达到不发；重扫/重启/重复上传不重发；预算仅提醒，不拦截模型调用。三层预算分别按其授权范围计算。</x:v>
+        <x:v>版本、来源、原始SHA及父子/fork证据有原件
+M/S/N/P的330、165、187、385在运行前记录
+SHA一致且SQL初态只有合成账号与零事件
+仅删除本次拥有目录且保留原始报告</x:v>
       </x:c>
       <x:c r="H166" s="9" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：本例不直接写入产品用量表；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I166" s="9" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J166" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K166" s="9" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L166" s="9" t="str">
-        <x:v>docs/testing/cases/09-TM-009-budget-alerts.md:11</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:127</x:v>
       </x:c>
       <x:c r="M166" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N166" s="9" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="167" ht="57" customHeight="1">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" ht="72" customHeight="1">
       <x:c r="A167" s="4" t="str">
-        <x:v>TM-009</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B167" s="4" t="str">
-        <x:v>E2E-TM009-002</x:v>
+        <x:v>TC-TM004-E2E-01</x:v>
       </x:c>
       <x:c r="C167" s="4" t="str">
-        <x:v>新周期、币种与通知恢复</x:v>
+        <x:v>安装包真实链路（TASK-TM004-E2E，AC-001–004，E2E-001/004）</x:v>
       </x:c>
       <x:c r="D167" s="4" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-E2E</x:v>
       </x:c>
       <x:c r="E167" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F167" s="4" t="str">
-        <x:v>数据集 budget_periods；两个币种独立预算；旧周期已发80/100阈值，参考时钟可由产品支持的测试配置推进；测试通知权限可以拒绝及恢复，不能修改用户其他App授权。</x:v>
+        <x:v>本版固定候选SHA、原DMG、TM-001–004完整必测TC清单。</x:v>
       </x:c>
       <x:c r="G167" s="4" t="str">
-        <x:v>系统拒绝不丢失应用内状态、不造成重试通知风暴；新周期独立重置，允许新一轮各阈值一次；币种分开计算。通知补发策略需在对应需求明确，不能由测试临时猜测。</x:v>
+        <x:v>仅连接本次独占服务和隔离授权根
+逐步断言UI、IPC后果和只读SQLite
+目标及历史已交付TC全部执行且无跳过/重试/失败
+结果与候选包一致且本次资源清理完成</x:v>
       </x:c>
       <x:c r="H167" s="4" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：本例不直接写入产品用量表；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I167" s="4" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J167" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K167" s="4" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L167" s="4" t="str">
-        <x:v>docs/testing/cases/09-TM-009-budget-alerts.md:28</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:131</x:v>
       </x:c>
       <x:c r="M167" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N167" s="4" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
+        <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="72" customHeight="1">
       <x:c r="A168" s="9" t="str">
-        <x:v>TM-010</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B168" s="9" t="str">
-        <x:v>E2E-TM010-001</x:v>
+        <x:v>TC-TM004-RELEASE-01</x:v>
       </x:c>
       <x:c r="C168" s="9" t="str">
-        <x:v>稳定版发现更新与数据保留</x:v>
+        <x:v>候选与证据一致（TASK-TM004-RELEASE，AC-001–004，E2E-004）</x:v>
       </x:c>
       <x:c r="D168" s="9" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-RELEASE</x:v>
       </x:c>
       <x:c r="E168" s="9" t="str">
-        <x:v>产品E2E</x:v>
+        <x:v>release_gate</x:v>
       </x:c>
       <x:c r="F168" s="9" t="str">
-        <x:v>数据集 update_packages；依赖TM-001/007；update_packages planned。需真实已分发稳定版、候选最终包及相同分发profile的签名/清单；旧版有账号设置、手动地址、统计/队列独立快照。首版无历史稳定版时使用SOP017规定的候选→受控高版，不伪称稳定升级。</x:v>
+        <x:v>同一已提交SHA/tree、DMG摘要、完整TM-001–004结果。</x:v>
       </x:c>
       <x:c r="G168" s="9" t="str">
-        <x:v>更新频率和说明可用；只有声明候选被安装，Sparkle自主重启；更新前后账号/设置/统计与快照一致，队列不丢失不重复。完整更新体验仍为未来功能，TM-001-004通过只证明最小更新路径。</x:v>
+        <x:v>SHA/tree和DMG摘要一致
+完整集合逐例PASS且清理完成，否则阻断
+Excel行和源摘要一致
+SOP-018真实PASS才进入SOP-019</x:v>
       </x:c>
       <x:c r="H168" s="9" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：本例不直接写入产品用量表；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I168" s="9" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J168" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K168" s="9" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L168" s="9" t="str">
-        <x:v>docs/testing/cases/10-TM-010-software-updates.md:11</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:135</x:v>
       </x:c>
       <x:c r="M168" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N168" s="9" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="169" ht="57" customHeight="1">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" ht="72" customHeight="1">
       <x:c r="A169" s="4" t="str">
-        <x:v>TM-010</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B169" s="4" t="str">
-        <x:v>E2E-TM010-002</x:v>
+        <x:v>TC-TM004-SOURCE-03</x:v>
       </x:c>
       <x:c r="C169" s="4" t="str">
-        <x:v>签名、网络、空间和迁移失败恢复</x:v>
+        <x:v>嵌套子代理目录（TASK-TM004-SOURCE，AC-001，E2E-001）</x:v>
       </x:c>
       <x:c r="D169" s="4" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-SOURCE</x:v>
       </x:c>
       <x:c r="E169" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F169" s="4" t="str">
-        <x:v>数据集 update_packages；对同一干净旧版分别建立四个隔离子场景：坏签名包、下载中断、受限测试卷空间不足、受控迁移失败；每个保存旧版包/DB/配置摘要。故障不能作用用户系统盘/生产库。</x:v>
+        <x:v>2.1.126 已安装二进制显示子代理路径可在 subagents/ 下继续嵌套；确切层级与父链由待取得的原始样本决定。固定数据应含项目A主M100/10、一级子S200/20、嵌套子T=50/5，以及授权根外同名文件X=999/99。</x:v>
       </x:c>
       <x:c r="G169" s="4" t="str">
-        <x:v>每个失败均不能形成半更新；原账号/统计和包的可用状态可验证。网络恢复后的成功需要完整包校验；迁移失败恢复来源与摘要明确。四个子场景全部为本case必需，不能挑一项通过。</x:v>
+        <x:v>项目A可信total385/3次调用
+不读取X
+总量和归属不变
+不猜A</x:v>
       </x:c>
       <x:c r="H169" s="4" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读事件唯一键、父项目与总量3/385；缺链变体的T不得纳入A可信聚合；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I169" s="4" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J169" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K169" s="4" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L169" s="4" t="str">
-        <x:v>docs/testing/cases/10-TM-010-software-updates.md:28</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:139</x:v>
       </x:c>
       <x:c r="M169" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N169" s="4" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="170" ht="57" customHeight="1">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" ht="72" customHeight="1">
       <x:c r="A170" s="9" t="str">
-        <x:v>TM-010</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B170" s="9" t="str">
-        <x:v>E2E-TM010-003</x:v>
+        <x:v>TC-TM004-PARSER-03</x:v>
       </x:c>
       <x:c r="C170" s="9" t="str">
-        <x:v>升级默认地址和手动覆盖</x:v>
+        <x:v>同一消息多内容块和 Agent 摘要（TASK-TM004-PARSER，AC-001，E2E-001）</x:v>
       </x:c>
       <x:c r="D170" s="9" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-PARSER</x:v>
       </x:c>
       <x:c r="E170" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F170" s="9" t="str">
-        <x:v>数据集 server_default_migration；server_default_migration planned；两套旧安装A从未设置地址、B已手动设置；候选内置一个届时确定且测试可访问的生产HTTPS默认地址。两源有独立账号/数据/会话，公钥不可随URL编辑。</x:v>
+        <x:v>同一次主调用M100/10拆为至少两个带相同 message.id 与 usage 的 assistant 内容块，另有 Agent 工具结果的 totalTokens/usage 摘要与子S200/20原始调用；本机独立结构探针已实际生成31/9双块，CLI 写两行相同 ID 和完整 usage，子代理19/6的父工具结果出现 total_tokens: 25。</x:v>
       </x:c>
       <x:c r="G170" s="9" t="str">
-        <x:v>只有无手动覆盖安装跟随新版默认；显式覆盖即使恰好等于旧默认也应按已经确定的配置来源规则处理。改变origin需重新服务认证，旧token不能跨源复用。</x:v>
+        <x:v>UI/SQLite为1次调用、total110
+可信为M+S两次、total330
+仍330</x:v>
       </x:c>
       <x:c r="H170" s="9" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读源消息调用键2个/330，父Agent汇总不能额外成为第三次调用；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I170" s="9" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J170" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K170" s="9" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L170" s="9" t="str">
-        <x:v>docs/testing/cases/10-TM-010-software-updates.md:45</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:143</x:v>
       </x:c>
       <x:c r="M170" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N170" s="9" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="171" ht="57" customHeight="1">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" ht="72" customHeight="1">
       <x:c r="A171" s="4" t="str">
-        <x:v>TM-011</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B171" s="4" t="str">
-        <x:v>E2E-TM011-001</x:v>
+        <x:v>TC-TM004-LINEAGE-03</x:v>
       </x:c>
       <x:c r="C171" s="4" t="str">
-        <x:v>SQLite迁移与中断恢复</x:v>
+        <x:v>forkedFrom 复制与改写 UUID（TASK-TM004-LINEAGE，AC-002，E2E-002）</x:v>
       </x:c>
       <x:c r="D171" s="4" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-LINEAGE</x:v>
       </x:c>
       <x:c r="E171" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F171" s="4" t="str">
-        <x:v>数据集 migration_snapshots；migration_snapshots planned；旧schema副本含固定账号/事件/队列、预计算记录数/Token/金额；候选迁移版本和明确故障点。全部作用私有临时库。</x:v>
+        <x:v>已计M100/10；分别用2.1.126真实生成的 fork 复制记录（保留 UUID）和改写 UUID 记录，依据实际 raw 的跨文件调用身份/父链判定，不能假定两者都含 forkedFrom；再追加真正新N50/5。</x:v>
       </x:c>
       <x:c r="G171" s="4" t="str">
-        <x:v>成功迁移只改变设计允许的schema/数据；账号、记录数、Token、费用/队列归属不丢。失败恢复到可启动一致状态，重复启动不重复迁移数据。不能以文件存在作为恢复成功。</x:v>
+        <x:v>M仅计一次且total110
+均仍110并在诊断/关系中可追溯原M
+total165/2次
+仍两次可信调用且total165</x:v>
       </x:c>
       <x:c r="H171" s="4" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读可信调用键2个、继承引用指向M；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I171" s="4" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J171" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K171" s="4" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L171" s="4" t="str">
-        <x:v>docs/testing/cases/11-TM-011-data-migration.md:11</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:147</x:v>
       </x:c>
       <x:c r="M171" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N171" s="4" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="172" ht="57" customHeight="1">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" ht="72" customHeight="1">
       <x:c r="A172" s="9" t="str">
-        <x:v>TM-011</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B172" s="9" t="str">
-        <x:v>E2E-TM011-002</x:v>
+        <x:v>TC-TM004-LINEAGE-04</x:v>
       </x:c>
       <x:c r="C172" s="9" t="str">
-        <x:v>未来SQLite到MySQL迁移</x:v>
+        <x:v>fork-context-ref 父链（TASK-TM004-LINEAGE，AC-002，E2E-002）</x:v>
       </x:c>
       <x:c r="D172" s="9" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-LINEAGE</x:v>
       </x:c>
       <x:c r="E172" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F172" s="9" t="str">
-        <x:v>数据集 migration_snapshots；仅后续独立版本适用；用户已确定v0.1.0继续SQLite。需要隔离源SQLite、目标MySQL、固定多成员/多项目用量快照、字符/时间/Decimal边界和独立expected。</x:v>
+        <x:v>2.1.126真实子代理 fork 记录中带 agentId,parentSessionId,parentLastUuid,contextLength；父会话存在M100/10，子代理仅新增S200/20。</x:v>
       </x:c>
       <x:c r="G172" s="9" t="str">
-        <x:v>源/目标记录数、Token、Decimal金额及权限结果一致，ID和幂等语义保持；不重复历史且旧源未被破坏。MySQL版本、字符集和迁移范围须在对应版本指定。</x:v>
+        <x:v>可信110
+可信330/2次而非440
+可信M/S两次且total330
+引用解析到M的既有调用键</x:v>
       </x:c>
       <x:c r="H172" s="9" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读M/S各一条及引用，total330；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I172" s="9" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J172" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K172" s="9" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L172" s="9" t="str">
-        <x:v>docs/testing/cases/11-TM-011-data-migration.md:28</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:151</x:v>
       </x:c>
       <x:c r="M172" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N172" s="9" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="173" ht="57" customHeight="1">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" ht="72" customHeight="1">
       <x:c r="A173" s="4" t="str">
-        <x:v>TM-011</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B173" s="4" t="str">
-        <x:v>E2E-TM011-003</x:v>
+        <x:v>TC-TM004-LINEAGE-05</x:v>
       </x:c>
       <x:c r="C173" s="4" t="str">
-        <x:v>备份恢复与旧客户端补传</x:v>
+        <x:v>缺失或矛盾父链（TASK-TM004-LINEAGE，AC-002/003，E2E-002/003）</x:v>
       </x:c>
       <x:c r="D173" s="4" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-LINEAGE</x:v>
       </x:c>
       <x:c r="E173" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F173" s="4" t="str">
-        <x:v>数据集 migration_snapshots；隔离服务已确认事件A/B与旧客户端未确认C；备份包含schema/数据/版本/摘要，另保存不在备份里的独立oracle。恢复目标必须为空且带测试标记。</x:v>
+        <x:v>在上一例的合成同构目录中分别移除引用父文件、指向不存在的 parentLastUuid、或提供无 forkedFrom 但UUID改写的复制历史；这些是测试故障注入，不能标为厂商实际输出。</x:v>
       </x:c>
       <x:c r="G173" s="4" t="str">
-        <x:v>备份能实际恢复而非只压缩成功；A/B不丢，重复补传不增加；C最终只出现一次，账号/权限符合恢复基线。队列与服务确认一致，旧客户端协议兼容。</x:v>
+        <x:v>M仅计一次且total110
+App显示未确定来源诊断，可信总量仍110、不能把不明副本计为新调用或有效零
+若真实新增S200/20可独立识别则总量330
+可信总量保持且诊断随恢复更新</x:v>
       </x:c>
       <x:c r="H173" s="4" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读未确定记录与可信M/S计数，不能借SQL灌成功；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I173" s="4" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J173" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K173" s="4" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L173" s="4" t="str">
-        <x:v>docs/testing/cases/11-TM-011-data-migration.md:45</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:155</x:v>
       </x:c>
       <x:c r="M173" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N173" s="4" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="174" ht="57" customHeight="1">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174" ht="102" customHeight="1">
       <x:c r="A174" s="9" t="str">
-        <x:v>TM-011</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B174" s="9" t="str">
-        <x:v>E2E-TM011-004</x:v>
+        <x:v>TC-TM004-SOURCE-04</x:v>
       </x:c>
       <x:c r="C174" s="9" t="str">
-        <x:v>保留时间边界与未同步保护</x:v>
+        <x:v>预览截断后的可续扫覆盖（TASK-TM004-SOURCE，AC-001/004，E2E-001/004）</x:v>
       </x:c>
       <x:c r="D174" s="9" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-SOURCE</x:v>
       </x:c>
       <x:c r="E174" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F174" s="9" t="str">
-        <x:v>数据集 migration_snapshots；固定参考时间和Asia/Shanghai；本地90天/服务端365天。分别生成保留首日00:00、前一秒、前一天的已确认事件，以及同样超龄但未同步事件；具备可控时钟与独立边界oracle。</x:v>
+        <x:v>本例独占授权根，固定程序按 TM-002 已提交枚举顺序生成至少1025个普通 .jsonl 文件及足够目录项；前段有主M100/10，预览截断范围外且至少第五个256项采集页的深层 subagents/ 文件有子S50/5，其余文件没有可计量调用。另备可控制的页间撤权/恢复点。</x:v>
       </x:c>
       <x:c r="G174" s="9" t="str">
-        <x:v>保留首日00:00仍在，早一秒的已同步记录被清理；本地/服务按各自天数独立判定。未同步记录即使超龄仍保护，成功补传仅计一次；历史缺失不能显示真实0。</x:v>
+        <x:v>1000文件预览显示被截断，不声称全量
+UI 可显示已见M110，但 TM-003 coverage.scan_incomplete=1
+使用 openCandidateReadOnly(candidateToken) 读原始行；在另一次固定变体于页间撤权，下一页或打开须拒绝，cancelScan 后 scan_incomplete=1，重授后以新授权世代续扫
+可信 M+S 两调用、input150/output15/total165，scan_incomplete=0 才可显示本次覆盖完成；重启重扫总量不变</x:v>
       </x:c>
       <x:c r="H174" s="9" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读各来源事件键、聚合 (2,150,15)、游标及 coverage.scan_incomplete；中途必须为1；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I174" s="9" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J174" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K174" s="9" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L174" s="9" t="str">
-        <x:v>docs/testing/cases/11-TM-011-data-migration.md:62</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:159</x:v>
       </x:c>
       <x:c r="M174" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N174" s="9" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="175" ht="57" customHeight="1">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" ht="102" customHeight="1">
       <x:c r="A175" s="4" t="str">
-        <x:v>TM-012</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B175" s="4" t="str">
-        <x:v>E2E-TM012-001</x:v>
+        <x:v>TC-TM004-INCREMENTAL-03</x:v>
       </x:c>
       <x:c r="C175" s="4" t="str">
-        <x:v>菜单栏摘要、暂停恢复与刷新</x:v>
+        <x:v>跨工具同 ID 与 Claude 复制历史（TASK-TM004-INCREMENTAL，AC-001/002，E2E-001/002）</x:v>
       </x:c>
       <x:c r="D175" s="4" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-INCREMENTAL</x:v>
       </x:c>
       <x:c r="E175" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F175" s="4" t="str">
-        <x:v>数据集 diagnostic_states；diagnostic_states planned；已采集A=100/10；暂停期间追加B=200/20并重放A。依赖实际采集、统计和同步功能，使用专用日志目录。</x:v>
+        <x:v>同一合成主体、各自经 UI 授权的 Codex 与 Claude 隔离根。固定本地响应使 Codex 原生 payload.response_id 与 Claude 主 assistant.message.id 字面均为 shared-call-01，分别有 C=11/1 与 M=100/10；Claude 原生 --fork-session 复制M，再有独立 Agent 子调用S=200/20（新 message.id、与父同 sessionId 但带 agentId）。另以明确标记的衍生故障数据令同一 Claude message.id 出现矛盾101/10，该行不冒称 CLI 原件。</x:v>
       </x:c>
       <x:c r="G175" s="4" t="str">
-        <x:v>初始total110、暂停期间仍110，恢复后唯一A/B、total330；手动刷新与重启不重复。菜单栏与主窗口同一筛选口径；暂停状态不伪装成没有日志。</x:v>
+        <x:v>可信1次/total12
+可信2次/input111/output11/total122，跨工具同字面 ID 不冲突
+可信3次/input311/output31/total342
+可信仍3次/342，出现 identity_conflict 与覆盖不完整</x:v>
       </x:c>
       <x:c r="H175" s="4" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读同一 principal_key 下 source=codex 与 source=claude_code 各自事件数1/2、source_event_key 不同，Agent source_scope_key 与主来源可区分，复制M不多行，冲突不覆写原M；键与归属均不得存原生ID/完整路径；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I175" s="4" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J175" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K175" s="4" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L175" s="4" t="str">
-        <x:v>docs/testing/cases/12-TM-012-menu-diagnostics.md:11</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:163</x:v>
       </x:c>
       <x:c r="M175" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N175" s="4" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
+        <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
     </x:row>
     <x:row r="176" ht="57" customHeight="1">
       <x:c r="A176" s="9" t="str">
-        <x:v>TM-012</x:v>
+        <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B176" s="9" t="str">
-        <x:v>E2E-TM012-002</x:v>
+        <x:v>E2E-TM005-001</x:v>
       </x:c>
       <x:c r="C176" s="9" t="str">
-        <x:v>诊断状态、恢复和登录启动</x:v>
+        <x:v>日期筛选、趋势和明细</x:v>
       </x:c>
       <x:c r="D176" s="9" t="str">
         <x:v>待拆解</x:v>
@@ -14327,10 +15715,10 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F176" s="9" t="str">
-        <x:v>数据集 diagnostic_states；独立子场景：已授权目录失效、真实服务不可达/恢复、测试App登录启动开关。故障作用测试目录/进程；使用已登录桌面与可自动检查的系统设置。</x:v>
+        <x:v>数据集 date_ranges；date_ranges 已由 scripts/test_data.py 提供标准化语义样例，固定2026-09-29T04:00:00Z、Asia/Shanghai、seed42；13行含1重复、12唯一。需另有已验证raw输入映射和真实App导入流程，当前未实现。</x:v>
       </x:c>
       <x:c r="G176" s="9" t="str">
-        <x:v>错误与真实目录/网络故障一致，不能用旧缓存一直显示健康；恢复后状态及时更新，未同步数据不丢。启动设置与OS登记/实际启动行为一致，测试结束恢复本次测试前状态。</x:v>
+        <x:v>独立expected中的total依次16500、110、17380、27830、31130；custom=2200。today共5条、input15000、output1500、cache1700、reasoning170，cache/reasoning不再相加；custom-start包含、custom-end排除。趋势点及明细按expected事件时间逐条核对。</x:v>
       </x:c>
       <x:c r="H176" s="9" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
@@ -14347,39 +15735,4210 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L176" s="9" t="str">
-        <x:v>docs/testing/cases/12-TM-012-menu-diagnostics.md:28</x:v>
+        <x:v>docs/testing/cases/05-TM-005-usage-statistics.md:19</x:v>
       </x:c>
       <x:c r="M176" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N176" s="9" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177" ht="57" customHeight="1">
+      <x:c r="A177" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B177" s="4" t="str">
+        <x:v>E2E-TM005-002</x:v>
+      </x:c>
+      <x:c r="C177" s="4" t="str">
+        <x:v>时区、月边界与缺失值</x:v>
+      </x:c>
+      <x:c r="D177" s="4" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E177" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F177" s="4" t="str">
+        <x:v>数据集 date_ranges；复用date_ranges中的2026-09-28T15:59:59Z与16:00:00Z、2026-08-30T15:59:59Z与16:00:00Z边界。另需补充覆盖缺口、已覆盖零调用日、unknown字段三类状态；当前生成器未覆盖后面三类。</x:v>
+      </x:c>
+      <x:c r="G177" s="4" t="str">
+        <x:v>Shanghai下15:59:59Z仍属前日、16:00:00Z属次日；UTC下二者同属UTC日期。无覆盖显示缺失，真实零可显示0，unknown字段显示未知；不得互相代替。各范围expected须独立按当地日期边界列出，不调用产品查询生成。</x:v>
+      </x:c>
+      <x:c r="H177" s="4" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I177" s="4" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J177" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K177" s="4" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L177" s="4" t="str">
+        <x:v>docs/testing/cases/05-TM-005-usage-statistics.md:36</x:v>
+      </x:c>
+      <x:c r="M177" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N177" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178" ht="102" customHeight="1">
+      <x:c r="A178" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B178" s="9" t="str">
+        <x:v>TC-TM005-CONTRACT-01</x:v>
+      </x:c>
+      <x:c r="C178" s="9" t="str">
+        <x:v>两来源重复事件不增量</x:v>
+      </x:c>
+      <x:c r="D178" s="9" t="str">
+        <x:v>TASK-TM005-EVENT-CONTRACT</x:v>
+      </x:c>
+      <x:c r="E178" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F178" s="9" t="str">
+        <x:v>seed42 事件中 Codex today-gpt 和 Claude Code today-sonnet 各一原生事件，另各有同源重复读取；全部绑定同一合成账号</x:v>
+      </x:c>
+      <x:c r="G178" s="9" t="str">
+        <x:v>1. 从空客户端库在 App 授权两目录并等待采集；UI 应显示两个来源已读取，DB 只读记录应有两条可信事件，总量 3300。
+2. 复制/重放两条原生事件并在 App 点刷新；UI 总量仍 3300，DB 的唯一来源事件身份仍为两条，诊断不能误报新用量。
+3. 退出并由同一已安装 App 重启后再刷新；总量和身份仍不变。只清理由本例创建的文件与进程。</x:v>
+      </x:c>
+      <x:c r="H178" s="9" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I178" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J178" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K178" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L178" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:19</x:v>
+      </x:c>
+      <x:c r="M178" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N178" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" ht="102" customHeight="1">
+      <x:c r="A179" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B179" s="4" t="str">
+        <x:v>TC-TM005-CONTRACT-02</x:v>
+      </x:c>
+      <x:c r="C179" s="4" t="str">
+        <x:v>未知字段不伪造零</x:v>
+      </x:c>
+      <x:c r="D179" s="4" t="str">
+        <x:v>TASK-TM005-EVENT-CONTRACT</x:v>
+      </x:c>
+      <x:c r="E179" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F179" s="4" t="str">
+        <x:v>一条 Codex 缺 output、另一条 Claude Code 缺 input 的受支持原生记录，另有两条可信调用各 110 token</x:v>
+      </x:c>
+      <x:c r="G179" s="4" t="str">
+        <x:v>1. 从空库经 App 采集两条可信调用；卡片显示已知总量 220，DB 有两条可信事件。
+2. 追加两条缺字段记录并刷新；UI 显示相应未知诊断，完整总量不能把未知字段当 0。可信 220 不被覆盖，DB 的 unknown 状态与来源可只读辨认。
+3. 重扫与重启；可信 220 和两条未知状态保持，不能变成成功零用量。</x:v>
+      </x:c>
+      <x:c r="H179" s="4" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I179" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J179" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K179" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L179" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:29</x:v>
+      </x:c>
+      <x:c r="M179" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N179" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180" ht="102" customHeight="1">
+      <x:c r="A180" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B180" s="9" t="str">
+        <x:v>TC-TM005-CONTRACT-03</x:v>
+      </x:c>
+      <x:c r="C180" s="9" t="str">
+        <x:v>Claude fork 复制历史与新增调用</x:v>
+      </x:c>
+      <x:c r="D180" s="9" t="str">
+        <x:v>TASK-TM005-EVENT-CONTRACT</x:v>
+      </x:c>
+      <x:c r="E180" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F180" s="9" t="str">
+        <x:v>使用 TM-004 最终锁定的 Claude Code 2.1.126 自写原始 fork fixture：父会话可信调用 M=100/10，fork 文件复制父历史并新增可信调用 N=50/5；已固定的来源样本复制父 UUID、message.id、usage，却没有 forkedFrom</x:v>
+      </x:c>
+      <x:c r="G180" s="9" t="str">
+        <x:v>1. 在 App 授权本例 Claude 根并采集父会话 M；统计明细仅 M 一次，总量 110，DB 有一个可信来源调用身份。
+2. 由已验证 CLI 操作生成/写入上述固定 fork 原生日志后经 App 刷新；UI/DB 恰有 M、N 两个可信调用，total=165。复制的父历史不另入账，缺 forkedFrom 本身不构成新调用证明。
+3. 重扫 fork/父文件并重启 App；可信事件身份及 165 保持。若最终来源合同不能证明本例固定 fixture 的复制和新增关系，本例在运行前保持 BLOCKED，不能临场改写为另一预期或手填 PASS。</x:v>
+      </x:c>
+      <x:c r="H180" s="9" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I180" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J180" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K180" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L180" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:39</x:v>
+      </x:c>
+      <x:c r="M180" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N180" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181" ht="102" customHeight="1">
+      <x:c r="A181" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B181" s="4" t="str">
+        <x:v>TC-TM005-CONTRACT-04</x:v>
+      </x:c>
+      <x:c r="C181" s="4" t="str">
+        <x:v>Claude 父会话与子代理独立用量</x:v>
+      </x:c>
+      <x:c r="D181" s="4" t="str">
+        <x:v>TASK-TM005-EVENT-CONTRACT</x:v>
+      </x:c>
+      <x:c r="E181" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F181" s="4" t="str">
+        <x:v>TM-004 最终锁定的 Claude Code 2.1.126 自写主会话与 subagents/agent-*.jsonl fixture；设计数字为父调用 M=100/10、子代理调用 S=200/20，两者各有独立 usage。已固定的来源样本中子文件带 agentId、isSidechain=true，与父文件同 sessionId</x:v>
+      </x:c>
+      <x:c r="G181" s="4" t="str">
+        <x:v>1. App 授权本例 Claude 根并采集父会话；只有父调用 M 入账，UI/DB 显示可信 110 及父来源身份。
+2. 子代理原生日志完整写入并由 App 采集；UI/DB 恰有 M、S 两个可信调用，total=330。父会话对子代理的引用不能另加 220；父子同 sessionId 也不能把子代理的真实调用消掉。
+3. 重扫主/子文件、刷新并重启；两个唯一身份与 330 保持，模型维度分别保留实际模型标识。若最终 raw 无法证明该父子关系或独立调用，本例在运行前保持 BLOCKED，不临场更换结果判据。</x:v>
+      </x:c>
+      <x:c r="H181" s="4" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I181" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J181" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K181" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L181" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:49</x:v>
+      </x:c>
+      <x:c r="M181" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N181" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182" ht="102" customHeight="1">
+      <x:c r="A182" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B182" s="9" t="str">
+        <x:v>TC-TM005-CONTRACT-05</x:v>
+      </x:c>
+      <x:c r="C182" s="9" t="str">
+        <x:v>Codex 逐响应与缓存子项</x:v>
+      </x:c>
+      <x:c r="D182" s="9" t="str">
+        <x:v>TASK-TM005-EVENT-CONTRACT</x:v>
+      </x:c>
+      <x:c r="E182" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F182" s="9" t="str">
+        <x:v>TM-003 阶段隔离原生 Codex 0.158.0-alpha.2.1 rollout 形状：一条 token_usage_record，response_id=tm003-native-probe-response-1，input100、cached read20、cache write0、output10、reasoning2、total110；原始 JSONL SHA-256 3b30cfa81c0c29a80f1bfc1de5bf823db01a9a85636e41ec58dfdd00f0436d08</x:v>
+      </x:c>
+      <x:c r="G182" s="9" t="str">
+        <x:v>1. 由 TM-003 最终固定数据程序在本例拥有的 Codex 根生成受支持原生日志，从安装后的 App 授权并采集；UI 和只读 DB 恰有一个可信逐响应身份，input100、output10、total110。
+2. UI 缓存读20、缓存写0、推理输出2作为已知子项分别显示，不再加到 total；同一 rollout 内 turn/thread 累计快照不能生成第二个 110 调用。
+3. 重扫、刷新、重启后仍为一个身份/110；原生日志原件或派生 fixture 的摘要与运行记录一致。</x:v>
+      </x:c>
+      <x:c r="H182" s="9" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I182" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J182" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K182" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L182" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:59</x:v>
+      </x:c>
+      <x:c r="M182" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N182" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183" ht="102" customHeight="1">
+      <x:c r="A183" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B183" s="4" t="str">
+        <x:v>TC-TM005-CONTRACT-06</x:v>
+      </x:c>
+      <x:c r="C183" s="4" t="str">
+        <x:v>Codex fork 的累计快照不当增量</x:v>
+      </x:c>
+      <x:c r="D183" s="4" t="str">
+        <x:v>TASK-TM005-EVENT-CONTRACT</x:v>
+      </x:c>
+      <x:c r="E183" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F183" s="4" t="str">
+        <x:v>上游最终固定的 Codex exec fork 原生日志；设计数字为父响应 A=100/10、B=200/20，fork 新文件仅新响应 C=300/30，C 行的 thread_token_usage 为 A+B+C 累计 660</x:v>
+      </x:c>
+      <x:c r="G183" s="4" t="str">
+        <x:v>1. App 采集父日志 A/B；UI 与 DB 应有两个可信响应身份，total 330。
+2. App 读取仅含 C 的 fork 新文件；可信身份增至三个，total 660。C 的逐响应 330 只加一次，thread_token_usage=660 不另加为第四个调用或在本步加 660。
+3. 重扫父/fork 文件并重启；仍三个身份/660。若上游 fork 身份/解析证据不完整，记录未确定诊断，不按累计值补造事件。</x:v>
+      </x:c>
+      <x:c r="H183" s="4" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I183" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J183" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K183" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L183" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:69</x:v>
+      </x:c>
+      <x:c r="M183" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N183" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184" ht="102" customHeight="1">
+      <x:c r="A184" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B184" s="9" t="str">
+        <x:v>TC-TM005-CONTRACT-07</x:v>
+      </x:c>
+      <x:c r="C184" s="9" t="str">
+        <x:v>Claude 同消息多行不重复</x:v>
+      </x:c>
+      <x:c r="D184" s="9" t="str">
+        <x:v>TASK-TM005-EVENT-CONTRACT</x:v>
+      </x:c>
+      <x:c r="E184" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F184" s="9" t="str">
+        <x:v>TM-004 提交 dda5ccb 所记录的 Claude Code 2.1.126 原生日志形状：一个 API 消息的双 text 块对应两条 assistant JSONL，message.id 相同且每行都带完整 usage input31/output9</x:v>
+      </x:c>
+      <x:c r="G184" s="9" t="str">
+        <x:v>1. App 采集该消息；UI/DB 只出现一个可信调用身份，input31/output9/total40，而不是两行求和的 80。
+2. 刷新、重扫并重启；仍一个调用/40，明细不出现第二个相同消息。</x:v>
+      </x:c>
+      <x:c r="H184" s="9" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I184" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J184" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K184" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L184" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:79</x:v>
+      </x:c>
+      <x:c r="M184" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N184" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185" ht="102" customHeight="1">
+      <x:c r="A185" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B185" s="4" t="str">
+        <x:v>TC-TM005-CONTRACT-08</x:v>
+      </x:c>
+      <x:c r="C185" s="4" t="str">
+        <x:v>两来源原生 ID 碰撞与同源重放</x:v>
+      </x:c>
+      <x:c r="D185" s="4" t="str">
+        <x:v>TASK-TM005-EVENT-CONTRACT</x:v>
+      </x:c>
+      <x:c r="E185" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F185" s="4" t="str">
+        <x:v>隔离 Codex 与 Claude 原生日志各有不同的真实调用，却故意使其来源原生调用 ID 同为 shared-native-id-1；设计用量 Codex A=100/10、Claude B=200/20。再重放 Claude B 的相同原生记录</x:v>
+      </x:c>
+      <x:c r="G185" s="4" t="str">
+        <x:v>1. App 经两授权根先采集 Codex A；UI/只读 SQLite 有一个可信调用，total 110，记录 source=codex 与 source_event_key 的不泄露表示。
+2. App 再采集同原生 ID 的 Claude B；UI/SQLite 应有两个不同来源的可信调用，total 330。不能因跨来源 ID 碰撞压掉 B，也不能把 A 改写为 B。
+3. 重放 B 并刷新/重启；仍两个可信调用/330，同一 Claude 调用未重复。SQLite 旁证须同时检查两个来源身份、各自 token 和唯一键，而非仅检查总量。</x:v>
+      </x:c>
+      <x:c r="H185" s="4" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I185" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J185" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K185" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L185" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:88</x:v>
+      </x:c>
+      <x:c r="M185" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N185" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186" ht="102" customHeight="1">
+      <x:c r="A186" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B186" s="9" t="str">
+        <x:v>TC-TM005-CONTRACT-09</x:v>
+      </x:c>
+      <x:c r="C186" s="9" t="str">
+        <x:v>Claude 同 ID 继承关系无法证明</x:v>
+      </x:c>
+      <x:c r="D186" s="9" t="str">
+        <x:v>TASK-TM005-EVENT-CONTRACT</x:v>
+      </x:c>
+      <x:c r="E186" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F186" s="9" t="str">
+        <x:v>同一合成账号下两条 Claude Agent/会话原始记录都用 assistant.message.id=shared-claude-id-1、相同模型和 input100/output10；首调用 A 已可信，第二条 B 位于另一 Agent/会话，缺少能证明复制或独立新调用的父链/来源证据。相同用量/模型使本例只检验继承不确定性，不与 identity_conflict 混合</x:v>
+      </x:c>
+      <x:c r="G186" s="9" t="str">
+        <x:v>1. App 采集 A；UI/SQLite 有一个可信 Claude 调用，已知部分 110。
+2. 追加 B 并刷新；不能静默把 B 视为 A 的已证复制，也不能武断另加 110。UI 显示统计不完整、已知部分仍 110；诊断 unverified_inheritance，覆盖状态不完整。SQLite 保留 A 的可信键/值及不含原始 ID/完整路径的诊断代码、数量和来源归属旁证，不要求持久化 B 原文。
+3. 重扫/重启后诊断与已知部分保持；若 TM-004 最终合同找到可证复制/独立身份，先修本用例输入与预期并重新基线，不在运行时临时选答案。</x:v>
+      </x:c>
+      <x:c r="H186" s="9" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I186" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J186" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K186" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L186" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:98</x:v>
+      </x:c>
+      <x:c r="M186" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N186" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" ht="102" customHeight="1">
+      <x:c r="A187" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B187" s="4" t="str">
+        <x:v>TC-TM005-CONTRACT-10</x:v>
+      </x:c>
+      <x:c r="C187" s="4" t="str">
+        <x:v>同 ID 用量或模型冲突</x:v>
+      </x:c>
+      <x:c r="D187" s="4" t="str">
+        <x:v>TASK-TM005-EVENT-CONTRACT</x:v>
+      </x:c>
+      <x:c r="E187" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F187" s="4" t="str">
+        <x:v>Claude 同 assistant.message.id=conflict-claude-id-1 的首可信调用 A=100/10、模型 model-a；两个稳定变体 TC-TM005-CONTRACT-10#USAGE（后续同 ID usage 改为 200/20）与 TC-TM005-CONTRACT-10#MODEL（后续同 ID 用量仍 100/10、模型改为 model-b）</x:v>
+      </x:c>
+      <x:c r="G187" s="4" t="str">
+        <x:v>1. 每个变体从独立空客户端库采集 A；UI/SQLite 为一个可信事件、total110、模型 model-a。
+2. 追加对应矛盾行并刷新；identity_conflict 诊断出现，A 的用量和模型保持，已知部分 110，不新增/覆盖可信事件，不把统计标为完整。
+3. 重扫/重启；冲突诊断和首可信值保持。两个变体分别保存原始结果；不得用一个变体通过覆盖另一变体。</x:v>
+      </x:c>
+      <x:c r="H187" s="4" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I187" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J187" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K187" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L187" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:108</x:v>
+      </x:c>
+      <x:c r="M187" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N187" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188" ht="102" customHeight="1">
+      <x:c r="A188" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B188" s="9" t="str">
+        <x:v>TC-TM005-CONTRACT-10#USAGE</x:v>
+      </x:c>
+      <x:c r="C188" s="9" t="str">
+        <x:v>同 ID 用量或模型冲突 · 变体</x:v>
+      </x:c>
+      <x:c r="D188" s="9" t="str">
+        <x:v>TASK-TM005-EVENT-CONTRACT</x:v>
+      </x:c>
+      <x:c r="E188" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F188" s="9" t="str">
+        <x:v>从独立空库导入 A，再导入同 ID、同模型但 200/20 的行</x:v>
+      </x:c>
+      <x:c r="G188" s="9" t="str">
+        <x:v>identity_conflict，可信统计仍为 A 的 110。</x:v>
+      </x:c>
+      <x:c r="H188" s="9" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I188" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J188" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K188" s="9" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L188" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:108</x:v>
+      </x:c>
+      <x:c r="M188" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N188" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189" ht="102" customHeight="1">
+      <x:c r="A189" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B189" s="4" t="str">
+        <x:v>TC-TM005-CONTRACT-10#MODEL</x:v>
+      </x:c>
+      <x:c r="C189" s="4" t="str">
+        <x:v>同 ID 用量或模型冲突 · 变体</x:v>
+      </x:c>
+      <x:c r="D189" s="4" t="str">
+        <x:v>TASK-TM005-EVENT-CONTRACT</x:v>
+      </x:c>
+      <x:c r="E189" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F189" s="4" t="str">
+        <x:v>从独立空库导入 A，再导入同 ID、100/10 但模型为 model-b 的行</x:v>
+      </x:c>
+      <x:c r="G189" s="4" t="str">
+        <x:v>identity_conflict，可信统计仍为 A 的 110 且模型为 model-a。</x:v>
+      </x:c>
+      <x:c r="H189" s="4" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I189" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J189" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K189" s="4" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L189" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:108</x:v>
+      </x:c>
+      <x:c r="M189" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N189" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190" ht="102" customHeight="1">
+      <x:c r="A190" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B190" s="9" t="str">
+        <x:v>TC-TM005-RANGE-01</x:v>
+      </x:c>
+      <x:c r="C190" s="9" t="str">
+        <x:v>今天</x:v>
+      </x:c>
+      <x:c r="D190" s="9" t="str">
+        <x:v>TASK-TM005-RANGE-QUERY
+TASK-TM005-UI</x:v>
+      </x:c>
+      <x:c r="E190" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F190" s="9" t="str">
+        <x:v>seed42 全部 13 行映射为两来源原生事件，1 行为 today-gpt 原样重复；上海日锚点与运行日一致</x:v>
+      </x:c>
+      <x:c r="G190" s="9" t="str">
+        <x:v>1. 经 App 采集后选“今天”；卡片应显示唯一 5 次、input 15000、output 1500、total 16500、cached read 1700、reasoning 170，子项不再加到 total。规范化语义样例没有 cache write 字段；若最终 raw 映射也没有可核实字段，该子项应显示未知而非 0。
+2. 检查趋势今天点为 16500，明细 ID 集合恰为 today-gpt/sonnet/qwen/glm/unknown 的五项；每条来源、模型、UTC 时间与原生日志对应，不显示重复行。
+3. 只读 DB 核对今天半开 UTC 范围内五个唯一可信身份及各字段合计；源集合、UI、DB 相同。</x:v>
+      </x:c>
+      <x:c r="H190" s="9" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I190" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J190" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K190" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L190" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:121</x:v>
+      </x:c>
+      <x:c r="M190" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N190" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191" ht="102" customHeight="1">
+      <x:c r="A191" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B191" s="4" t="str">
+        <x:v>TC-TM005-RANGE-02</x:v>
+      </x:c>
+      <x:c r="C191" s="4" t="str">
+        <x:v>昨天</x:v>
+      </x:c>
+      <x:c r="D191" s="4" t="str">
+        <x:v>TASK-TM005-RANGE-QUERY</x:v>
+      </x:c>
+      <x:c r="E191" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F191" s="4" t="str">
+        <x:v>同一批原生数据；yesterday 在上海日界前 1 秒</x:v>
+      </x:c>
+      <x:c r="G191" s="4" t="str">
+        <x:v>1. 选“昨天”；卡片仅 1 次，input 100、output 10、total 110，cache 20、reasoning 2。
+2. 趋势该日点 110、明细仅 yesterday；today-gpt 的上海 00:00 边界事件不能出现在此日。
+3. 只读 DB 查询该当地日换算的 UTC 半开区间，仅返回 yesterday；确认筛选没有写用量表。</x:v>
+      </x:c>
+      <x:c r="H191" s="4" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I191" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J191" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K191" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L191" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:131</x:v>
+      </x:c>
+      <x:c r="M191" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N191" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192" ht="102" customHeight="1">
+      <x:c r="A192" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B192" s="9" t="str">
+        <x:v>TC-TM005-RANGE-03</x:v>
+      </x:c>
+      <x:c r="C192" s="9" t="str">
+        <x:v>近 7 天</x:v>
+      </x:c>
+      <x:c r="D192" s="9" t="str">
+        <x:v>TASK-TM005-RANGE-QUERY</x:v>
+      </x:c>
+      <x:c r="E192" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F192" s="9" t="str">
+        <x:v>上海当地 09-23 至 29 日语义窗口整体平移到运行日</x:v>
+      </x:c>
+      <x:c r="G192" s="9" t="str">
+        <x:v>1. 选“近 7 天”；卡片 7 次、total 17380，左边界 day7 包含。
+2. 趋势非空日仅为窗口内 day7=770、yesterday=110、today=16500；明细恰为今天五项加 yesterday/day7。其余日期的显示状态按覆盖证明判，不从缺事件推断 0。
+3. 只读 DB 对比 7 个唯一事件身份及 17380；重复 today-gpt 不入账。</x:v>
+      </x:c>
+      <x:c r="H192" s="9" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I192" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J192" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K192" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L192" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:139</x:v>
+      </x:c>
+      <x:c r="M192" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N192" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193" ht="102" customHeight="1">
+      <x:c r="A193" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B193" s="4" t="str">
+        <x:v>TC-TM005-RANGE-04</x:v>
+      </x:c>
+      <x:c r="C193" s="4" t="str">
+        <x:v>近 15 天</x:v>
+      </x:c>
+      <x:c r="D193" s="4" t="str">
+        <x:v>TASK-TM005-RANGE-QUERY</x:v>
+      </x:c>
+      <x:c r="E193" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F193" s="4" t="str">
+        <x:v>上海当地 09-15 至 29 日语义窗口</x:v>
+      </x:c>
+      <x:c r="G193" s="4" t="str">
+        <x:v>1. 选“近 15 天”；卡片 10 次、total 27830，day15 在左边界包含。
+2. 趋势非空日为 day15=1650、custom-start=2200、custom-end=6600、day7=770、yesterday=110、today=16500；明细为这 10 个唯一事件。
+3. 只读 DB 核对半开区间/10 个身份/27830；不把 day30 提前包含。</x:v>
+      </x:c>
+      <x:c r="H193" s="4" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I193" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J193" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K193" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L193" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:147</x:v>
+      </x:c>
+      <x:c r="M193" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N193" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194" ht="102" customHeight="1">
+      <x:c r="A194" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B194" s="9" t="str">
+        <x:v>TC-TM005-RANGE-05</x:v>
+      </x:c>
+      <x:c r="C194" s="9" t="str">
+        <x:v>近 30 天</x:v>
+      </x:c>
+      <x:c r="D194" s="9" t="str">
+        <x:v>TASK-TM005-RANGE-QUERY</x:v>
+      </x:c>
+      <x:c r="E194" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F194" s="9" t="str">
+        <x:v>上海当地 08-31 至 09-29 日语义窗口</x:v>
+      </x:c>
+      <x:c r="G194" s="9" t="str">
+        <x:v>1. 选“近 30 天”；卡片 11 次、total 31130，day30 在左边界包含，前 1 秒的 outside30 排除。
+2. 趋势增加 day30=3300 点；明细为近 15 天十项加 day30，没有 outside30。
+3. 只读 DB 核对 11 个身份/31130；刷新后仍一致。</x:v>
+      </x:c>
+      <x:c r="H194" s="9" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I194" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J194" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K194" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L194" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:155</x:v>
+      </x:c>
+      <x:c r="M194" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N194" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195" ht="102" customHeight="1">
+      <x:c r="A195" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B195" s="4" t="str">
+        <x:v>TC-TM005-RANGE-06</x:v>
+      </x:c>
+      <x:c r="C195" s="4" t="str">
+        <x:v>自定义半开日期</x:v>
+      </x:c>
+      <x:c r="D195" s="4" t="str">
+        <x:v>TASK-TM005-RANGE-QUERY</x:v>
+      </x:c>
+      <x:c r="E195" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F195" s="4" t="str">
+        <x:v>上海当地 09-20 至 21 日语义窗口，结束上界为 09-22 00:00</x:v>
+      </x:c>
+      <x:c r="G195" s="4" t="str">
+        <x:v>1. 在 UI 输入整体平移后的起止日并应用；卡片 1 次、input 2000、output 200、total 2200。
+2. 趋势只有 custom-start=2200 非空点，明细仅该事件；custom-end 在排除上界，不能出现。
+3. DB 只读查询 [start,end)；预期仅返回唯一 custom-start，查询不写入用量。</x:v>
+      </x:c>
+      <x:c r="H195" s="4" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I195" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J195" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K195" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L195" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:163</x:v>
+      </x:c>
+      <x:c r="M195" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N195" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196" ht="102" customHeight="1">
+      <x:c r="A196" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B196" s="9" t="str">
+        <x:v>TC-TM005-RANGE-09</x:v>
+      </x:c>
+      <x:c r="C196" s="9" t="str">
+        <x:v>起日大于止日</x:v>
+      </x:c>
+      <x:c r="D196" s="9" t="str">
+        <x:v>TASK-TM005-RANGE-QUERY</x:v>
+      </x:c>
+      <x:c r="E196" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F196" s="9" t="str">
+        <x:v>上海语义锚点平移后的起日 09-22、止日 09-20；此前已选“今天”显示 16500</x:v>
+      </x:c>
+      <x:c r="G196" s="9" t="str">
+        <x:v>1. 在自定义日期表单输入倒置范围并应用；UI 显示可识别的日期范围错误，不发起新查询，原卡片/趋势/明细仍对应今天 16500/五项。
+2. 只读 DB 核对用量与设置，再恢复有效范围查询；预期倒置范围没有写入，有效范围仍显示 2200，前次错误不污染状态。</x:v>
+      </x:c>
+      <x:c r="H196" s="9" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I196" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J196" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K196" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L196" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:171</x:v>
+      </x:c>
+      <x:c r="M196" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N196" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197" ht="102" customHeight="1">
+      <x:c r="A197" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B197" s="4" t="str">
+        <x:v>TC-TM005-RANGE-10</x:v>
+      </x:c>
+      <x:c r="C197" s="4" t="str">
+        <x:v>空起日与空止日</x:v>
+      </x:c>
+      <x:c r="D197" s="4" t="str">
+        <x:v>TASK-TM005-RANGE-QUERY</x:v>
+      </x:c>
+      <x:c r="E197" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F197" s="4" t="str">
+        <x:v>两个独立变体 TC-TM005-RANGE-10#START_EMPTY（起日空、止日 09-21）和 TC-TM005-RANGE-10#END_EMPTY（起日 09-20、止日空）；此前已选今天 16500</x:v>
+      </x:c>
+      <x:c r="G197" s="4" t="str">
+        <x:v>1. 每个变体独立从今天结果开始，清空指定字段并应用；表单拒绝，保留原卡片 16500、今天趋势和五条明细。
+2. 分别核对没有发起查询或写 DB；补齐字段后自定义有效窗口显示 2200。两个变体分别记录原始结果，不以其中一个通过代替另一个。</x:v>
+      </x:c>
+      <x:c r="H197" s="4" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I197" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J197" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K197" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L197" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:180</x:v>
+      </x:c>
+      <x:c r="M197" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N197" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198" ht="102" customHeight="1">
+      <x:c r="A198" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B198" s="9" t="str">
+        <x:v>TC-TM005-RANGE-10#START_EMPTY</x:v>
+      </x:c>
+      <x:c r="C198" s="9" t="str">
+        <x:v>空起日与空止日 · 变体</x:v>
+      </x:c>
+      <x:c r="D198" s="9" t="str">
+        <x:v>TASK-TM005-RANGE-QUERY</x:v>
+      </x:c>
+      <x:c r="E198" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F198" s="9" t="str">
+        <x:v>保持止日 09-21，清空起日并应用</x:v>
+      </x:c>
+      <x:c r="G198" s="9" t="str">
+        <x:v>拒绝查询，今天卡片仍为 16500、五条明细不变。</x:v>
+      </x:c>
+      <x:c r="H198" s="9" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I198" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J198" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K198" s="9" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L198" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:180</x:v>
+      </x:c>
+      <x:c r="M198" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N198" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199" ht="102" customHeight="1">
+      <x:c r="A199" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B199" s="4" t="str">
+        <x:v>TC-TM005-RANGE-10#END_EMPTY</x:v>
+      </x:c>
+      <x:c r="C199" s="4" t="str">
+        <x:v>空起日与空止日 · 变体</x:v>
+      </x:c>
+      <x:c r="D199" s="4" t="str">
+        <x:v>TASK-TM005-RANGE-QUERY</x:v>
+      </x:c>
+      <x:c r="E199" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F199" s="4" t="str">
+        <x:v>保持起日 09-20，清空止日并应用</x:v>
+      </x:c>
+      <x:c r="G199" s="4" t="str">
+        <x:v>拒绝查询，今天卡片仍为 16500、五条明细不变。</x:v>
+      </x:c>
+      <x:c r="H199" s="4" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I199" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J199" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K199" s="4" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L199" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:180</x:v>
+      </x:c>
+      <x:c r="M199" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N199" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200" ht="102" customHeight="1">
+      <x:c r="A200" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B200" s="9" t="str">
+        <x:v>TC-TM005-RANGE-08</x:v>
+      </x:c>
+      <x:c r="C200" s="9" t="str">
+        <x:v>刷新重启保持</x:v>
+      </x:c>
+      <x:c r="D200" s="9" t="str">
+        <x:v>TASK-TM005-RANGE-QUERY
+TASK-TM005-UI</x:v>
+      </x:c>
+      <x:c r="E200" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F200" s="9" t="str">
+        <x:v>seed42 双来源全量与近 30 天选择</x:v>
+      </x:c>
+      <x:c r="G200" s="9" t="str">
+        <x:v>1. 选择近 30 天并记录 UI/DB 初态；预期明细 11 项、total 31130，来源身份和覆盖状态与本例原始输入一致。
+2. App 内刷新并重扫两个来源；UI 与 DB 均不增量，仍 11 项/31130。
+3. 退出、重启安装后的同一 App/profile 并恢复筛选；UI 与 DB 仍 11 项/31130，授权状态和账号身份未串换。</x:v>
+      </x:c>
+      <x:c r="H200" s="9" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I200" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J200" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K200" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L200" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:192</x:v>
+      </x:c>
+      <x:c r="M200" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N200" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201" ht="102" customHeight="1">
+      <x:c r="A201" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B201" s="4" t="str">
+        <x:v>TC-TM005-MODEL-01</x:v>
+      </x:c>
+      <x:c r="C201" s="4" t="str">
+        <x:v>模型维度</x:v>
+      </x:c>
+      <x:c r="D201" s="4" t="str">
+        <x:v>TASK-TM005-UI</x:v>
+      </x:c>
+      <x:c r="E201" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F201" s="4" t="str">
+        <x:v>今天五项，两个来源至少各一项，模型名保持来源可识别标识</x:v>
+      </x:c>
+      <x:c r="G201" s="4" t="str">
+        <x:v>1. 选今天和模型维度；行值应为 gpt-5=1100、sonnet-test=2200、qwen-test=3300、glm-test=4400、unknown-model=5500，合计 16500。
+2. 选 unknown-model；明细只含 today-unknown，Token 5500 有效，价格未知不显示为免费或 0 用量。
+3. 刷新并重启 App 后再次查询模型维度；预期分组与明细仍与来源身份及只读 DB 一致。</x:v>
+      </x:c>
+      <x:c r="H201" s="4" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I201" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J201" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K201" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L201" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:200</x:v>
+      </x:c>
+      <x:c r="M201" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N201" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202" ht="102" customHeight="1">
+      <x:c r="A202" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B202" s="9" t="str">
+        <x:v>TC-TM005-MODEL-02</x:v>
+      </x:c>
+      <x:c r="C202" s="9" t="str">
+        <x:v>真实未知模型仍计用量</x:v>
+      </x:c>
+      <x:c r="D202" s="9" t="str">
+        <x:v>TASK-TM005-UI
+TASK-TM005-EVENT-CONTRACT</x:v>
+      </x:c>
+      <x:c r="E202" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F202" s="9" t="str">
+        <x:v>以 2026-09-29 上海当地日为语义锚点并随运行日整体平移的两条独立可信调用：Codex A 于锚点 2026-09-29T01:00:00Z，input100/output10，无法从同一 turn 核实模型，规范事件 model_id=null；Claude B 于 2026-09-29T02:00:00Z，input200/output20、模型 sonnet-test。这与 MODEL-01 中字面名称为 unknown-model 的已知模型不同</x:v>
+      </x:c>
+      <x:c r="G202" s="9" t="str">
+        <x:v>1. App 从两类已验证原生日志采集 A/B 后选该日；卡片显示两次、已知 total330，明细分别保留来源与用量，A 不因模型未知而丢失。
+2. 模型分组出现“未知模型”110 与 sonnet-test220，两组合计330；只读 SQLite 核对同一快照两条可信身份、A 的 model_id IS NULL、B 的模型及各自 input/output。
+3. 刷新并重启 App 后查询同一日期；预期仍为两次/330，未知模型不被擅自改为最近一行模型，也不被标成零费用或零用量。</x:v>
+      </x:c>
+      <x:c r="H202" s="9" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I202" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J202" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K202" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L202" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:208</x:v>
+      </x:c>
+      <x:c r="M202" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N202" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203" ht="102" customHeight="1">
+      <x:c r="A203" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B203" s="4" t="str">
+        <x:v>TC-TM005-RANGE-07</x:v>
+      </x:c>
+      <x:c r="C203" s="4" t="str">
+        <x:v>时区与月界</x:v>
+      </x:c>
+      <x:c r="D203" s="4" t="str">
+        <x:v>TASK-TM005-RANGE-QUERY</x:v>
+      </x:c>
+      <x:c r="E203" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F203" s="4" t="str">
+        <x:v>上海 09-28 15:59:59Z/16:00:00Z 与 UTC 08-30 15:59:59Z/16:00:00Z 四个语义边界事件，整体平移整数天</x:v>
+      </x:c>
+      <x:c r="G203" s="4" t="str">
+        <x:v>1. 团队时区为 Asia/Shanghai 时，上海昨天仅 yesterday=110，今天含 today-gpt=1100；近 30 天含 day30=3300，排除 outside30=11000。
+2. 经真实时区设置 UI 改为 UTC，用明确自定义 UTC 日期查询边界；09-28 UTC 同含 yesterday 与 today-gpt，total 1210；08-30 UTC 同含 outside30/day30，total 14300。事件 UTC 时间及 DB 源身份不变。
+3. 重启后 UTC 设置保留；再查询 UTC 近 30 天对应自定义窗口，total 27830，两个 08-30 事件均排除。只有显示分桶变动，DB 事件数仍 12 唯一。</x:v>
+      </x:c>
+      <x:c r="H203" s="4" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I203" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J203" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K203" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L203" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:220</x:v>
+      </x:c>
+      <x:c r="M203" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N203" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204" ht="147" customHeight="1">
+      <x:c r="A204" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B204" s="9" t="str">
+        <x:v>TC-TM005-RANGE-11</x:v>
+      </x:c>
+      <x:c r="C204" s="9" t="str">
+        <x:v>夏令时当地日长度</x:v>
+      </x:c>
+      <x:c r="D204" s="9" t="str">
+        <x:v>TASK-TM005-RANGE-QUERY</x:v>
+      </x:c>
+      <x:c r="E204" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F204" s="9" t="str">
+        <x:v>两个独立稳定变体 TC-TM005-RANGE-11#SPRING 与 TC-TM005-RANGE-11#FALL，团队时区经真实 UI 设为 America/New_York。春季 2026-03-08 的 UTC 半开界为 [2026-03-08T05:00:00Z,2026-03-09T04:00:00Z)；四个固定事件为边界前 S0（04:59:59Z，Codex 5/1）、起界 S1（05:00:00Z，Codex 9/1）、末界前 S2（次日03:59:59Z，Claude 18/2）、排除上界 S3（次日04:00:00Z，Claude 27/3）。秋季 2026-11-01 的界为 [2026-11-01T04:00:00Z,2026-11-02T05:00:00Z)；四个固定事件为 F0（03:59:59Z，Codex 5/1）、F1（04:00:00Z，Codex 36/4）、F2（次日04:59:59Z，Claude 45/5）、F3（次日05:00:00Z，Claude 54/6）。数值均为 input/output Token</x:v>
+      </x:c>
+      <x:c r="G204" s="9" t="str">
+        <x:v>1. 各变体从独立空库、已验证双来源原生日志和相同登录身份开始；UI 选对应自定义当地日，春季仅 S1/S2 两次/30，秋季仅 F1/F2 两次/90，S0/S3/F0/F3 不在对应当日明细或趋势点。
+2. 只读 SQLite 以明确 UTC 半开界核对两个源事件身份及 input+output 合计；春季窗口为 23 小时、秋季为 25 小时，不能使用固定 86400 秒上界。
+3. 重启后时区与两变体结果分别保持；每个变体单独报告，不以其中一个结果覆盖另一个。</x:v>
+      </x:c>
+      <x:c r="H204" s="9" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I204" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J204" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K204" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L204" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:230</x:v>
+      </x:c>
+      <x:c r="M204" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N204" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205" ht="102" customHeight="1">
+      <x:c r="A205" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B205" s="4" t="str">
+        <x:v>TC-TM005-RANGE-11#SPRING</x:v>
+      </x:c>
+      <x:c r="C205" s="4" t="str">
+        <x:v>夏令时当地日长度 · 变体</x:v>
+      </x:c>
+      <x:c r="D205" s="4" t="str">
+        <x:v>TASK-TM005-RANGE-QUERY</x:v>
+      </x:c>
+      <x:c r="E205" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F205" s="4" t="str">
+        <x:v>以纽约 2026-03-08 为当地日，导入 S0–S3</x:v>
+      </x:c>
+      <x:c r="G205" s="4" t="str">
+        <x:v>仅含 S1/S2 两次、合计 30 Token，UTC 窗口长 23 小时。</x:v>
+      </x:c>
+      <x:c r="H205" s="4" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I205" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J205" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K205" s="4" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L205" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:230</x:v>
+      </x:c>
+      <x:c r="M205" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N205" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206" ht="102" customHeight="1">
+      <x:c r="A206" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B206" s="9" t="str">
+        <x:v>TC-TM005-RANGE-11#FALL</x:v>
+      </x:c>
+      <x:c r="C206" s="9" t="str">
+        <x:v>夏令时当地日长度 · 变体</x:v>
+      </x:c>
+      <x:c r="D206" s="9" t="str">
+        <x:v>TASK-TM005-RANGE-QUERY</x:v>
+      </x:c>
+      <x:c r="E206" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F206" s="9" t="str">
+        <x:v>以纽约 2026-11-01 为当地日，导入 F0–F3</x:v>
+      </x:c>
+      <x:c r="G206" s="9" t="str">
+        <x:v>仅含 F1/F2 两次、合计 90 Token，UTC 窗口长 25 小时。</x:v>
+      </x:c>
+      <x:c r="H206" s="9" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I206" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J206" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K206" s="9" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L206" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:230</x:v>
+      </x:c>
+      <x:c r="M206" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N206" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207" ht="102" customHeight="1">
+      <x:c r="A207" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B207" s="4" t="str">
+        <x:v>TC-TM005-STATE-01</x:v>
+      </x:c>
+      <x:c r="C207" s="4" t="str">
+        <x:v>无覆盖是缺失</x:v>
+      </x:c>
+      <x:c r="D207" s="4" t="str">
+        <x:v>TASK-TM005-COVERAGE</x:v>
+      </x:c>
+      <x:c r="E207" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F207" s="4" t="str">
+        <x:v>两来源均没有可证明覆盖的指定历史日，且没有可信事件</x:v>
+      </x:c>
+      <x:c r="G207" s="4" t="str">
+        <x:v>1. 从本例隔离库经 App 授权仅含近期日志的目录，打开早于已证实覆盖起点的自定义历史日；预期进入该日查询但尚不能凭空明细推断完整 0，DB 不新增用量事件。
+2. UI 显示缺失/不可确认，不能显示完整 0；趋势点/明细状态与卡片一致。DB 只读证明没有该日可信事件，且覆盖记录并未声称完整。
+3. 刷新后仍为缺失；空结果不能生成新零用量事件。</x:v>
+      </x:c>
+      <x:c r="H207" s="4" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I207" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J207" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K207" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L207" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:243</x:v>
+      </x:c>
+      <x:c r="M207" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N207" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208" ht="102" customHeight="1">
+      <x:c r="A208" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B208" s="9" t="str">
+        <x:v>TC-TM005-STATE-02</x:v>
+      </x:c>
+      <x:c r="C208" s="9" t="str">
+        <x:v>已覆盖零调用</x:v>
+      </x:c>
+      <x:c r="D208" s="9" t="str">
+        <x:v>TASK-TM005-COVERAGE</x:v>
+      </x:c>
+      <x:c r="E208" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F208" s="9" t="str">
+        <x:v>两来源对某完整当地日均有可核实、连续成功的覆盖证明，实际无调用</x:v>
+      </x:c>
+      <x:c r="G208" s="9" t="str">
+        <x:v>1. 在隔离 App 取得并核验两来源覆盖证明后选该日；UI 明确 0 次、0 Token，趋势该日为真实 0，明细为空。
+2. DB 只读核对覆盖区间完整、事件数 0；无任何合成“零调用事件”。重启后状态仍为已覆盖零。</x:v>
+      </x:c>
+      <x:c r="H208" s="9" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I208" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J208" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K208" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L208" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:251</x:v>
+      </x:c>
+      <x:c r="M208" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N208" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209" ht="102" customHeight="1">
+      <x:c r="A209" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B209" s="4" t="str">
+        <x:v>TC-TM005-STATE-03</x:v>
+      </x:c>
+      <x:c r="C209" s="4" t="str">
+        <x:v>字段未知</x:v>
+      </x:c>
+      <x:c r="D209" s="4" t="str">
+        <x:v>TASK-TM005-COVERAGE</x:v>
+      </x:c>
+      <x:c r="E209" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F209" s="4" t="str">
+        <x:v>一条受支持原生会话有时间/模型但缺可信 usage，另有正常可信调用 110</x:v>
+      </x:c>
+      <x:c r="G209" s="4" t="str">
+        <x:v>1. App 先采集正常调用；预期 UI 与 DB 显示已知 110。
+2. 追加缺 usage 原生事件并刷新；UI 显示不完整/未知诊断，不能把它当作 0 或把合计称为完整 110；DB 记录 unknown 原因且原正常事件不变。
+3. 重扫并重启 App；预期未知诊断仍在，未因去重而被隐藏。</x:v>
+      </x:c>
+      <x:c r="H209" s="4" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I209" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J209" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K209" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L209" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:260</x:v>
+      </x:c>
+      <x:c r="M209" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N209" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210" ht="102" customHeight="1">
+      <x:c r="A210" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B210" s="9" t="str">
+        <x:v>TC-TM005-STATE-04</x:v>
+      </x:c>
+      <x:c r="C210" s="9" t="str">
+        <x:v>三态持久化</x:v>
+      </x:c>
+      <x:c r="D210" s="9" t="str">
+        <x:v>TASK-TM005-COVERAGE</x:v>
+      </x:c>
+      <x:c r="E210" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F210" s="9" t="str">
+        <x:v>分别预置上述无覆盖、完整空日、未知字段三种可核实源状态</x:v>
+      </x:c>
+      <x:c r="G210" s="9" t="str">
+        <x:v>1. 在 App 依次选择三日；每个日期分别显示缺失、0、未知，保存 UI/只读 DB 的各自状态。
+2. 退出重启并改变团队时区后按新当地日重查；覆盖按 UTC 区间换算，三种状态不能互换或丢失。</x:v>
+      </x:c>
+      <x:c r="H210" s="9" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I210" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J210" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K210" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L210" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:268</x:v>
+      </x:c>
+      <x:c r="M210" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N210" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211" ht="102" customHeight="1">
+      <x:c r="A211" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B211" s="4" t="str">
+        <x:v>TC-TM005-STATE-05</x:v>
+      </x:c>
+      <x:c r="C211" s="4" t="str">
+        <x:v>Claude 数值零与上游缺 usage 的歧义</x:v>
+      </x:c>
+      <x:c r="D211" s="4" t="str">
+        <x:v>TASK-TM005-COVERAGE</x:v>
+      </x:c>
+      <x:c r="E211" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F211" s="4" t="str">
+        <x:v>TM-004 的两种受控 API 响应设计：显式报告零 usage 与整体省略 usage；Claude Code 2.1.126 原生阶段探针已发现后一种仍使 CLI 写出数值 0/0 usage</x:v>
+      </x:c>
+      <x:c r="G211" s="4" t="str">
+        <x:v>1. 分别由最终固定的原生数据程序生成两类日志，记录原始字节摘要与可观察字段；若两类 raw 不能区分，测试应把区别判据标为 BLOCKED，不能凭 API fixture 的隐藏输入让 App “识别”日志看不到的状态。
+2. App 读取省略 usage 所得数值零日志；没有额外可核实证据时 UI/DB 应保持未知或未确定，不能显示“已证明完整零用量”。已知可信事件的合计不被该 0 改成完整。
+3. 只有 TM-004 最终合同证明可区分显式零时，才对该变体单独断言真实零；重扫/重启不能把未知提升为零。</x:v>
+      </x:c>
+      <x:c r="H211" s="4" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I211" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J211" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K211" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L211" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:275</x:v>
+      </x:c>
+      <x:c r="M211" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N211" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212" ht="117" customHeight="1">
+      <x:c r="A212" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B212" s="9" t="str">
+        <x:v>TC-TM005-STATE-06</x:v>
+      </x:c>
+      <x:c r="C212" s="9" t="str">
+        <x:v>全量扫描分页与撤权时的覆盖</x:v>
+      </x:c>
+      <x:c r="D212" s="9" t="str">
+        <x:v>TASK-TM005-COVERAGE</x:v>
+      </x:c>
+      <x:c r="E212" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F212" s="9" t="str">
+        <x:v>本例拥有的 Claude 授权根含至少 1025 个候选文件、跨至少 5 个计划中的采集页；第一页含可信调用 A=100/10，后页另含可信调用 B=200/20。另有预览截断、页间撤权两个独立稳定变体</x:v>
+      </x:c>
+      <x:c r="G212" s="9" t="str">
+        <x:v>1. 从已安装 App 经 TM-002 真实 UI 授权根；预览即使只列前 1000 文件也不能使 TM-005 宣称全量覆盖。采集分页未完成时，UI 仅显示已知部分（A 若已被可信采集则为 110）及 history_incomplete，不显示完整 110 或空日 0；SQLite 只读旁证记录 continuation/诊断和已提交可信事件。
+2. 正常变体继续到所有页面、必要深度与完整行/游标提交；若 TM-004 最终合同确认全部可信，UI/DB 合计 A+B=330，覆盖状态按真实证明更新，不遗漏第 1025 个及后续文件。
+3. 撤权变体在两页之间撤销本例授权；扫描立刻停止，后页 B 不得读取，UI 保持已知部分 110 与不完整/失权提示，SQLite 不写完整覆盖或成功零。重授权后的补扫单独执行，最终值仍须 TM-004 身份/分页合同核定。</x:v>
+      </x:c>
+      <x:c r="H212" s="9" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I212" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J212" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K212" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L212" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:285</x:v>
+      </x:c>
+      <x:c r="M212" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N212" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="213" ht="102" customHeight="1">
+      <x:c r="A213" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B213" s="4" t="str">
+        <x:v>TC-TM005-DATA-01</x:v>
+      </x:c>
+      <x:c r="C213" s="4" t="str">
+        <x:v>生成/重置可复现</x:v>
+      </x:c>
+      <x:c r="D213" s="4" t="str">
+        <x:v>TASK-TM005-DATA</x:v>
+      </x:c>
+      <x:c r="E213" s="4" t="str">
+        <x:v>governance</x:v>
+      </x:c>
+      <x:c r="F213" s="4" t="str">
+        <x:v>同 seed42、同日锚点及两来源已验证版本，两个独立 run_id</x:v>
+      </x:c>
+      <x:c r="G213" s="4" t="str">
+        <x:v>1. 调用计划中的 raw 生成器两次，核对受支持格式、事件身份、原始字节摘要与独立 expected 相同（run_id 标记可不同）；不得读取真实 ~/.codex 或 ~/.claude。
+2. 只在已核对 owner marker、目录成员和摘要后调用重置；两个本例私有目录被清理，外部文件不动。程序不存在时为 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="H213" s="4" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I213" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J213" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K213" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L213" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:297</x:v>
+      </x:c>
+      <x:c r="M213" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N213" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214" ht="102" customHeight="1">
+      <x:c r="A214" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B214" s="9" t="str">
+        <x:v>TC-TM005-DATA-02</x:v>
+      </x:c>
+      <x:c r="C214" s="9" t="str">
+        <x:v>独立预期与边界</x:v>
+      </x:c>
+      <x:c r="D214" s="9" t="str">
+        <x:v>TASK-TM005-DATA</x:v>
+      </x:c>
+      <x:c r="E214" s="9" t="str">
+        <x:v>governance</x:v>
+      </x:c>
+      <x:c r="F214" s="9" t="str">
+        <x:v>语义 oracle tests/fixtures/tm005-semantic-expected.json和最终 raw 映射计划</x:v>
+      </x:c>
+      <x:c r="G214" s="9" t="str">
+        <x:v>1. 在产品启动前运行固定语义 oracle 检查；预期 seed42 语义样例 13 行/12 唯一，双来源事件集合及平移后的上海/UTC半开区间与预存摘要一致；原生映射未就绪时本例仍 BLOCKED。
+2. 对照原始字节与独立预期中的模型/字段、覆盖与 unknown 状态；缺原生日志/覆盖样例不得标可执行。该检查不能代替产品查询。</x:v>
+      </x:c>
+      <x:c r="H214" s="9" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I214" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J214" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K214" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L214" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:304</x:v>
+      </x:c>
+      <x:c r="M214" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N214" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215" ht="102" customHeight="1">
+      <x:c r="A215" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B215" s="4" t="str">
+        <x:v>TC-TM005-E2E-01</x:v>
+      </x:c>
+      <x:c r="C215" s="4" t="str">
+        <x:v>精确集合与最终安装包</x:v>
+      </x:c>
+      <x:c r="D215" s="4" t="str">
+        <x:v>TASK-TM005-E2E</x:v>
+      </x:c>
+      <x:c r="E215" s="4" t="str">
+        <x:v>governance_gate</x:v>
+      </x:c>
+      <x:c r="F215" s="4" t="str">
+        <x:v>固定候选 SHA、最终 DMG 与上述所有 TC 及此前已交付功能集合</x:v>
+      </x:c>
+      <x:c r="G215" s="4" t="str">
+        <x:v>1. 门禁从 DMG 安装的正式 App 逐 TC 运行，核对实际安装包摘要、独立输入/预期、原始结果与全部清理；任一 FAIL/BLOCKED/零例/跳过/重试取绿均阻断。
+2. 核对 TM-001→TM-004 的适用完整 E2E 及迁移/升级结果；只有本机机器门禁原始复核 PASS 才可签发本版通行证。当前无程序/包/原件，状态 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="H215" s="4" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I215" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J215" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K215" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L215" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:311</x:v>
+      </x:c>
+      <x:c r="M215" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N215" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216" ht="57" customHeight="1">
+      <x:c r="A216" s="9" t="str">
+        <x:v>TM-006</x:v>
+      </x:c>
+      <x:c r="B216" s="9" t="str">
+        <x:v>E2E-TM006-001</x:v>
+      </x:c>
+      <x:c r="C216" s="9" t="str">
+        <x:v>Token子项与基础费用</x:v>
+      </x:c>
+      <x:c r="D216" s="9" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E216" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F216" s="9" t="str">
+        <x:v>数据集 pricing；pricing由scripts/test_data.py生成合成非计费价格。gpt-5每百万input/cache/output为USD2/0.2/8；today-gpt input1000含cache200、output100含reasoning20。价格不是厂商现价。</x:v>
+      </x:c>
+      <x:c r="G216" s="9" t="str">
+        <x:v>单调用total=1100；费用=(800×2+200×0.2+100×8)/1000000=USD0.002440，reasoning20不另加价。today已知费用USD0.015190且有1条无价格，alice今日USD0.010090。使用Decimal/十进制独立oracle，不以界面舍入反推底层精度。</x:v>
+      </x:c>
+      <x:c r="H216" s="9" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I216" s="9" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J216" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K216" s="9" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L216" s="9" t="str">
+        <x:v>docs/testing/cases/06-TM-006-cost-estimates.md:15</x:v>
+      </x:c>
+      <x:c r="M216" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N216" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217" ht="57" customHeight="1">
+      <x:c r="A217" s="4" t="str">
+        <x:v>TM-006</x:v>
+      </x:c>
+      <x:c r="B217" s="4" t="str">
+        <x:v>E2E-TM006-002</x:v>
+      </x:c>
+      <x:c r="C217" s="4" t="str">
+        <x:v>历史价格、多币种和未知费用</x:v>
+      </x:c>
+      <x:c r="D217" s="4" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E217" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F217" s="4" t="str">
+        <x:v>数据集 pricing_extended；pricing_extended planned：同模型在生效时点T前后各一调用，两个独立价格版本；另有USD/CNY各一模型、无价模型和订阅估算模型。必须提供价格/订阅分摊规则及手算expected后才能实现。</x:v>
+      </x:c>
+      <x:c r="G217" s="4" t="str">
+        <x:v>T前后依各自生效版本计算，历史结果不会悄悄换价；USD与CNY分组，未约定汇率不得相加；无价格显示未知而非0；订阅必须明确估算口径。具体金额oracle依待定义订阅/价格合同生成，当前不得手填PASS。</x:v>
+      </x:c>
+      <x:c r="H217" s="4" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I217" s="4" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J217" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K217" s="4" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L217" s="4" t="str">
+        <x:v>docs/testing/cases/06-TM-006-cost-estimates.md:32</x:v>
+      </x:c>
+      <x:c r="M217" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N217" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="218" ht="57" customHeight="1">
+      <x:c r="A218" s="9" t="str">
+        <x:v>TM-007</x:v>
+      </x:c>
+      <x:c r="B218" s="9" t="str">
+        <x:v>E2E-TM007-001</x:v>
+      </x:c>
+      <x:c r="C218" s="9" t="str">
+        <x:v>离线、重启和补传幂等</x:v>
+      </x:c>
+      <x:c r="D218" s="9" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E218" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F218" s="9" t="str">
+        <x:v>数据集 sync_faults；sync_faults planned；alice两个隔离设备A/B，设备A调用100/10、B调用200/20；真实FastAPI/SQLite服务，可由外部fixture断网/恢复。账号继续用隔离测试fixture。</x:v>
+      </x:c>
+      <x:c r="G218" s="9" t="str">
+        <x:v>离线重启不丢队列；恢复后2唯一调用、input300/output30/total330；重复批次不再加量。客户端只在真实确认后标已同步，个人合计与对应团队子集一致。</x:v>
+      </x:c>
+      <x:c r="H218" s="9" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I218" s="9" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J218" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K218" s="9" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L218" s="9" t="str">
+        <x:v>docs/testing/cases/07-TM-007-team-sync.md:11</x:v>
+      </x:c>
+      <x:c r="M218" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N218" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="219" ht="57" customHeight="1">
+      <x:c r="A219" s="4" t="str">
+        <x:v>TM-007</x:v>
+      </x:c>
+      <x:c r="B219" s="4" t="str">
+        <x:v>E2E-TM007-002</x:v>
+      </x:c>
+      <x:c r="C219" s="4" t="str">
+        <x:v>部分确认、中断和账号切换</x:v>
+      </x:c>
+      <x:c r="D219" s="4" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E219" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F219" s="4" t="str">
+        <x:v>数据集 sync_faults；准备alice的三条唯一事件A/B/C，总量各110/220/330；控制服务仅确认A后断开，B可能已提交但响应丢失，C未提交。另有bob账号。故障注入必须在真实服务外部或明确测试环境中完成，不能绕过认证。</x:v>
+      </x:c>
+      <x:c r="G219" s="4" t="str">
+        <x:v>最终alice的A/B/C各一次、total660；响应丢失不造成B重复；bob不能承接或篡改alice既有事件归属。切换时旧队列按已批准归属策略隔离，不能默认为新登录账号。</x:v>
+      </x:c>
+      <x:c r="H219" s="4" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I219" s="4" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J219" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K219" s="4" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L219" s="4" t="str">
+        <x:v>docs/testing/cases/07-TM-007-team-sync.md:28</x:v>
+      </x:c>
+      <x:c r="M219" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N219" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="220" ht="57" customHeight="1">
+      <x:c r="A220" s="9" t="str">
+        <x:v>TM-007</x:v>
+      </x:c>
+      <x:c r="B220" s="9" t="str">
+        <x:v>E2E-TM007-003</x:v>
+      </x:c>
+      <x:c r="C220" s="9" t="str">
+        <x:v>上传白名单与项目映射</x:v>
+      </x:c>
+      <x:c r="D220" s="9" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E220" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F220" s="9" t="str">
+        <x:v>数据集 sync_faults；合成日志包含唯一正文/代码/API-key/完整路径哨兵，以及合法用量/必要去重元数据；只用假值。准备已归属项目A和未归属事件B，待sync_faults生成。</x:v>
+      </x:c>
+      <x:c r="G220" s="9" t="str">
+        <x:v>网络载荷/持久服务数据均不得含正文、代码、key或完整本机路径；只有批准用量/去重字段。B可明确分配，分配不增加事件量、也不跨团队归属。</x:v>
+      </x:c>
+      <x:c r="H220" s="9" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I220" s="9" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J220" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K220" s="9" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L220" s="9" t="str">
+        <x:v>docs/testing/cases/07-TM-007-team-sync.md:45</x:v>
+      </x:c>
+      <x:c r="M220" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N220" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221" ht="57" customHeight="1">
+      <x:c r="A221" s="4" t="str">
+        <x:v>TM-007</x:v>
+      </x:c>
+      <x:c r="B221" s="4" t="str">
+        <x:v>E2E-TM007-004</x:v>
+      </x:c>
+      <x:c r="C221" s="4" t="str">
+        <x:v>统计越权与停用后上传</x:v>
+      </x:c>
+      <x:c r="D221" s="4" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E221" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F221" s="4" t="str">
+        <x:v>数据集 sync_faults；alice项目A调用100/10，bob项目B调用200/20；成员alice与管理员独立会话；alice另有一条未确认调用C=50/5。sync_faults与可重建统计SQL尚未实现。</x:v>
+      </x:c>
+      <x:c r="G221" s="4" t="str">
+        <x:v>成员无权请求被服务端拒绝，UI不显示bob的220；停用后旧会话及上传拒绝，C不能标为已确认；合法历史不能被失败上传删除。此处补足TM-001仅身份/管理接口权限的范围。</x:v>
+      </x:c>
+      <x:c r="H221" s="4" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I221" s="4" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J221" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K221" s="4" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L221" s="4" t="str">
+        <x:v>docs/testing/cases/07-TM-007-team-sync.md:62</x:v>
+      </x:c>
+      <x:c r="M221" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N221" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="222" ht="57" customHeight="1">
+      <x:c r="A222" s="9" t="str">
+        <x:v>TM-008</x:v>
+      </x:c>
+      <x:c r="B222" s="9" t="str">
+        <x:v>E2E-TM008-001</x:v>
+      </x:c>
+      <x:c r="C222" s="9" t="str">
+        <x:v>筛选一致的CSV导出</x:v>
+      </x:c>
+      <x:c r="D222" s="9" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E222" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F222" s="9" t="str">
+        <x:v>数据集 export_rows；export_rows planned；两成员、两个模型、时间范围内外各有事件，独立清单明确每条ID/字段/权限。先具备TM-005/007统计和授权。</x:v>
+      </x:c>
+      <x:c r="G222" s="9" t="str">
+        <x:v>每次CSV仅包含当次筛选且授权可见记录，行数/ID/汇总等于独立清单与界面；不混入旧筛选、其他成员或范围外记录。已知/未知费用语义一致。</x:v>
+      </x:c>
+      <x:c r="H222" s="9" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I222" s="9" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J222" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K222" s="9" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L222" s="9" t="str">
+        <x:v>docs/testing/cases/08-TM-008-csv-export.md:11</x:v>
+      </x:c>
+      <x:c r="M222" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N222" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="223" ht="57" customHeight="1">
+      <x:c r="A223" s="4" t="str">
+        <x:v>TM-008</x:v>
+      </x:c>
+      <x:c r="B223" s="4" t="str">
+        <x:v>E2E-TM008-002</x:v>
+      </x:c>
+      <x:c r="C223" s="4" t="str">
+        <x:v>CSV转义、未知值及权限</x:v>
+      </x:c>
+      <x:c r="D223" s="4" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E223" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F223" s="4" t="str">
+        <x:v>数据集 export_rows；export_rows需含字段 a,b、say "hi"、带实际换行的项目名、未知费用与非ASCII模型名；两成员各有可区分哨兵事件。只在隔离数据中使用。</x:v>
+      </x:c>
+      <x:c r="G223" s="4" t="str">
+        <x:v>逗号、双引号、嵌入换行均round-trip一致，Unicode不损坏；未知值不写成0；他人哨兵不出现在文件。若导出失败，不能留下看似完整的半文件。</x:v>
+      </x:c>
+      <x:c r="H223" s="4" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I223" s="4" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J223" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K223" s="4" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L223" s="4" t="str">
+        <x:v>docs/testing/cases/08-TM-008-csv-export.md:28</x:v>
+      </x:c>
+      <x:c r="M223" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N223" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224" ht="57" customHeight="1">
+      <x:c r="A224" s="9" t="str">
+        <x:v>TM-009</x:v>
+      </x:c>
+      <x:c r="B224" s="9" t="str">
+        <x:v>E2E-TM009-001</x:v>
+      </x:c>
+      <x:c r="C224" s="9" t="str">
+        <x:v>80%/100%提醒幂等</x:v>
+      </x:c>
+      <x:c r="D224" s="9" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E224" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F224" s="9" t="str">
+        <x:v>数据集 budget_periods；budget_periods planned；独立个人、项目和团队预算分别100个合成USD单位，同周期使用量依次79→80→99→100；原始调用与价格要能精确形成这些费用。</x:v>
+      </x:c>
+      <x:c r="G224" s="9" t="str">
+        <x:v>每预算每周期80与100各最多一次，未达到不发；重扫/重启/重复上传不重发；预算仅提醒，不拦截模型调用。三层预算分别按其授权范围计算。</x:v>
+      </x:c>
+      <x:c r="H224" s="9" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I224" s="9" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J224" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K224" s="9" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L224" s="9" t="str">
+        <x:v>docs/testing/cases/09-TM-009-budget-alerts.md:11</x:v>
+      </x:c>
+      <x:c r="M224" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N224" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="225" ht="57" customHeight="1">
+      <x:c r="A225" s="4" t="str">
+        <x:v>TM-009</x:v>
+      </x:c>
+      <x:c r="B225" s="4" t="str">
+        <x:v>E2E-TM009-002</x:v>
+      </x:c>
+      <x:c r="C225" s="4" t="str">
+        <x:v>新周期、币种与通知恢复</x:v>
+      </x:c>
+      <x:c r="D225" s="4" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E225" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F225" s="4" t="str">
+        <x:v>数据集 budget_periods；两个币种独立预算；旧周期已发80/100阈值，参考时钟可由产品支持的测试配置推进；测试通知权限可以拒绝及恢复，不能修改用户其他App授权。</x:v>
+      </x:c>
+      <x:c r="G225" s="4" t="str">
+        <x:v>系统拒绝不丢失应用内状态、不造成重试通知风暴；新周期独立重置，允许新一轮各阈值一次；币种分开计算。通知补发策略需在对应需求明确，不能由测试临时猜测。</x:v>
+      </x:c>
+      <x:c r="H225" s="4" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I225" s="4" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J225" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K225" s="4" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L225" s="4" t="str">
+        <x:v>docs/testing/cases/09-TM-009-budget-alerts.md:28</x:v>
+      </x:c>
+      <x:c r="M225" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N225" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="226" ht="72" customHeight="1">
+      <x:c r="A226" s="9" t="str">
+        <x:v>TM-010</x:v>
+      </x:c>
+      <x:c r="B226" s="9" t="str">
+        <x:v>E2E-TM010-001</x:v>
+      </x:c>
+      <x:c r="C226" s="9" t="str">
+        <x:v>稳定版发现更新与数据保留</x:v>
+      </x:c>
+      <x:c r="D226" s="9" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E226" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F226" s="9" t="str">
+        <x:v>数据集 update_packages；依赖TM-001/007；update_packages planned。需真实已分发稳定版、候选最终包及相同分发profile的签名/清单；旧版有账号设置、手动地址、统计/队列独立快照。首版无历史稳定版时使用SOP017规定的候选→受控高版，不伪称稳定升级。</x:v>
+      </x:c>
+      <x:c r="G226" s="9" t="str">
+        <x:v>更新频率和说明可用；只有声明候选被安装，Sparkle自主重启；更新前后账号/设置/统计与快照一致，队列不丢失不重复。完整更新体验仍为未来功能，TM-001-004通过只证明最小更新路径。</x:v>
+      </x:c>
+      <x:c r="H226" s="9" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I226" s="9" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J226" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K226" s="9" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L226" s="9" t="str">
+        <x:v>docs/testing/cases/10-TM-010-software-updates.md:11</x:v>
+      </x:c>
+      <x:c r="M226" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N226" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="227" ht="57" customHeight="1">
+      <x:c r="A227" s="4" t="str">
+        <x:v>TM-010</x:v>
+      </x:c>
+      <x:c r="B227" s="4" t="str">
+        <x:v>E2E-TM010-002</x:v>
+      </x:c>
+      <x:c r="C227" s="4" t="str">
+        <x:v>签名、网络、空间和迁移失败恢复</x:v>
+      </x:c>
+      <x:c r="D227" s="4" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E227" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F227" s="4" t="str">
+        <x:v>数据集 update_packages；对同一干净旧版分别建立四个隔离子场景：坏签名包、下载中断、受限测试卷空间不足、受控迁移失败；每个保存旧版包/DB/配置摘要。故障不能作用用户系统盘/生产库。</x:v>
+      </x:c>
+      <x:c r="G227" s="4" t="str">
+        <x:v>每个失败均不能形成半更新；原账号/统计和包的可用状态可验证。网络恢复后的成功需要完整包校验；迁移失败恢复来源与摘要明确。四个子场景全部为本case必需，不能挑一项通过。</x:v>
+      </x:c>
+      <x:c r="H227" s="4" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I227" s="4" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J227" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K227" s="4" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L227" s="4" t="str">
+        <x:v>docs/testing/cases/10-TM-010-software-updates.md:28</x:v>
+      </x:c>
+      <x:c r="M227" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N227" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="228" ht="57" customHeight="1">
+      <x:c r="A228" s="9" t="str">
+        <x:v>TM-010</x:v>
+      </x:c>
+      <x:c r="B228" s="9" t="str">
+        <x:v>E2E-TM010-003</x:v>
+      </x:c>
+      <x:c r="C228" s="9" t="str">
+        <x:v>升级默认地址和手动覆盖</x:v>
+      </x:c>
+      <x:c r="D228" s="9" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E228" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F228" s="9" t="str">
+        <x:v>数据集 server_default_migration；server_default_migration planned；两套旧安装A从未设置地址、B已手动设置；候选内置一个届时确定且测试可访问的生产HTTPS默认地址。两源有独立账号/数据/会话，公钥不可随URL编辑。</x:v>
+      </x:c>
+      <x:c r="G228" s="9" t="str">
+        <x:v>只有无手动覆盖安装跟随新版默认；显式覆盖即使恰好等于旧默认也应按已经确定的配置来源规则处理。改变origin需重新服务认证，旧token不能跨源复用。</x:v>
+      </x:c>
+      <x:c r="H228" s="9" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I228" s="9" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J228" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K228" s="9" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L228" s="9" t="str">
+        <x:v>docs/testing/cases/10-TM-010-software-updates.md:45</x:v>
+      </x:c>
+      <x:c r="M228" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N228" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="229" ht="57" customHeight="1">
+      <x:c r="A229" s="4" t="str">
+        <x:v>TM-011</x:v>
+      </x:c>
+      <x:c r="B229" s="4" t="str">
+        <x:v>E2E-TM011-001</x:v>
+      </x:c>
+      <x:c r="C229" s="4" t="str">
+        <x:v>SQLite迁移与中断恢复</x:v>
+      </x:c>
+      <x:c r="D229" s="4" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E229" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F229" s="4" t="str">
+        <x:v>数据集 migration_snapshots；migration_snapshots planned；旧schema副本含固定账号/事件/队列、预计算记录数/Token/金额；候选迁移版本和明确故障点。全部作用私有临时库。</x:v>
+      </x:c>
+      <x:c r="G229" s="4" t="str">
+        <x:v>成功迁移只改变设计允许的schema/数据；账号、记录数、Token、费用/队列归属不丢。失败恢复到可启动一致状态，重复启动不重复迁移数据。不能以文件存在作为恢复成功。</x:v>
+      </x:c>
+      <x:c r="H229" s="4" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I229" s="4" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J229" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K229" s="4" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L229" s="4" t="str">
+        <x:v>docs/testing/cases/11-TM-011-data-migration.md:11</x:v>
+      </x:c>
+      <x:c r="M229" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N229" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="230" ht="57" customHeight="1">
+      <x:c r="A230" s="9" t="str">
+        <x:v>TM-011</x:v>
+      </x:c>
+      <x:c r="B230" s="9" t="str">
+        <x:v>E2E-TM011-002</x:v>
+      </x:c>
+      <x:c r="C230" s="9" t="str">
+        <x:v>未来SQLite到MySQL迁移</x:v>
+      </x:c>
+      <x:c r="D230" s="9" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E230" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F230" s="9" t="str">
+        <x:v>数据集 migration_snapshots；仅后续独立版本适用；用户已确定v0.1.0继续SQLite。需要隔离源SQLite、目标MySQL、固定多成员/多项目用量快照、字符/时间/Decimal边界和独立expected。</x:v>
+      </x:c>
+      <x:c r="G230" s="9" t="str">
+        <x:v>源/目标记录数、Token、Decimal金额及权限结果一致，ID和幂等语义保持；不重复历史且旧源未被破坏。MySQL版本、字符集和迁移范围须在对应版本指定。</x:v>
+      </x:c>
+      <x:c r="H230" s="9" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I230" s="9" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J230" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K230" s="9" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L230" s="9" t="str">
+        <x:v>docs/testing/cases/11-TM-011-data-migration.md:28</x:v>
+      </x:c>
+      <x:c r="M230" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N230" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="231" ht="57" customHeight="1">
+      <x:c r="A231" s="4" t="str">
+        <x:v>TM-011</x:v>
+      </x:c>
+      <x:c r="B231" s="4" t="str">
+        <x:v>E2E-TM011-003</x:v>
+      </x:c>
+      <x:c r="C231" s="4" t="str">
+        <x:v>备份恢复与旧客户端补传</x:v>
+      </x:c>
+      <x:c r="D231" s="4" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E231" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F231" s="4" t="str">
+        <x:v>数据集 migration_snapshots；隔离服务已确认事件A/B与旧客户端未确认C；备份包含schema/数据/版本/摘要，另保存不在备份里的独立oracle。恢复目标必须为空且带测试标记。</x:v>
+      </x:c>
+      <x:c r="G231" s="4" t="str">
+        <x:v>备份能实际恢复而非只压缩成功；A/B不丢，重复补传不增加；C最终只出现一次，账号/权限符合恢复基线。队列与服务确认一致，旧客户端协议兼容。</x:v>
+      </x:c>
+      <x:c r="H231" s="4" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I231" s="4" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J231" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K231" s="4" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L231" s="4" t="str">
+        <x:v>docs/testing/cases/11-TM-011-data-migration.md:45</x:v>
+      </x:c>
+      <x:c r="M231" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N231" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="232" ht="57" customHeight="1">
+      <x:c r="A232" s="9" t="str">
+        <x:v>TM-011</x:v>
+      </x:c>
+      <x:c r="B232" s="9" t="str">
+        <x:v>E2E-TM011-004</x:v>
+      </x:c>
+      <x:c r="C232" s="9" t="str">
+        <x:v>保留时间边界与未同步保护</x:v>
+      </x:c>
+      <x:c r="D232" s="9" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E232" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F232" s="9" t="str">
+        <x:v>数据集 migration_snapshots；固定参考时间和Asia/Shanghai；本地90天/服务端365天。分别生成保留首日00:00、前一秒、前一天的已确认事件，以及同样超龄但未同步事件；具备可控时钟与独立边界oracle。</x:v>
+      </x:c>
+      <x:c r="G232" s="9" t="str">
+        <x:v>保留首日00:00仍在，早一秒的已同步记录被清理；本地/服务按各自天数独立判定。未同步记录即使超龄仍保护，成功补传仅计一次；历史缺失不能显示真实0。</x:v>
+      </x:c>
+      <x:c r="H232" s="9" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I232" s="9" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J232" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K232" s="9" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L232" s="9" t="str">
+        <x:v>docs/testing/cases/11-TM-011-data-migration.md:62</x:v>
+      </x:c>
+      <x:c r="M232" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N232" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="233" ht="57" customHeight="1">
+      <x:c r="A233" s="4" t="str">
+        <x:v>TM-012</x:v>
+      </x:c>
+      <x:c r="B233" s="4" t="str">
+        <x:v>E2E-TM012-001</x:v>
+      </x:c>
+      <x:c r="C233" s="4" t="str">
+        <x:v>菜单栏摘要、暂停恢复与刷新</x:v>
+      </x:c>
+      <x:c r="D233" s="4" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E233" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F233" s="4" t="str">
+        <x:v>数据集 diagnostic_states；diagnostic_states planned；已采集A=100/10；暂停期间追加B=200/20并重放A。依赖实际采集、统计和同步功能，使用专用日志目录。</x:v>
+      </x:c>
+      <x:c r="G233" s="4" t="str">
+        <x:v>初始total110、暂停期间仍110，恢复后唯一A/B、total330；手动刷新与重启不重复。菜单栏与主窗口同一筛选口径；暂停状态不伪装成没有日志。</x:v>
+      </x:c>
+      <x:c r="H233" s="4" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I233" s="4" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J233" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K233" s="4" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L233" s="4" t="str">
+        <x:v>docs/testing/cases/12-TM-012-menu-diagnostics.md:11</x:v>
+      </x:c>
+      <x:c r="M233" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N233" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="234" ht="57" customHeight="1">
+      <x:c r="A234" s="9" t="str">
+        <x:v>TM-012</x:v>
+      </x:c>
+      <x:c r="B234" s="9" t="str">
+        <x:v>E2E-TM012-002</x:v>
+      </x:c>
+      <x:c r="C234" s="9" t="str">
+        <x:v>诊断状态、恢复和登录启动</x:v>
+      </x:c>
+      <x:c r="D234" s="9" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E234" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F234" s="9" t="str">
+        <x:v>数据集 diagnostic_states；独立子场景：已授权目录失效、真实服务不可达/恢复、测试App登录启动开关。故障作用测试目录/进程；使用已登录桌面与可自动检查的系统设置。</x:v>
+      </x:c>
+      <x:c r="G234" s="9" t="str">
+        <x:v>错误与真实目录/网络故障一致，不能用旧缓存一直显示健康；恢复后状态及时更新，未同步数据不丢。启动设置与OS登记/实际启动行为一致，测试结束恢复本次测试前状态。</x:v>
+      </x:c>
+      <x:c r="H234" s="9" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I234" s="9" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J234" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K234" s="9" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L234" s="9" t="str">
+        <x:v>docs/testing/cases/12-TM-012-menu-diagnostics.md:28</x:v>
+      </x:c>
+      <x:c r="M234" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N234" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="235" ht="72" customHeight="1">
+      <x:c r="A235" s="4" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B235" s="4" t="str">
+        <x:v>TC-TM003-SOURCE-01</x:v>
+      </x:c>
+      <x:c r="C235" s="4" t="str">
+        <x:v>受控版本来源与字段核验</x:v>
+      </x:c>
+      <x:c r="D235" s="4" t="str">
+        <x:v>TASK-TM003-SOURCE</x:v>
+      </x:c>
+      <x:c r="E235" s="4" t="str">
+        <x:v>source_check</x:v>
+      </x:c>
+      <x:c r="F235" s="4" t="str">
+        <x:v>1. 对照本版声明的 CLI build、官方结构与 sessions/YYYY/MM/DD/*.jsonl 受控原生样例→样例有 session_meta.id、token_usage_record.payload.response_id/usage，版本和 SHA 有记录。2. 换一个未声明 build→该 build 不列为已支持，显示 unsupported_source_version。</x:v>
+      </x:c>
+      <x:c r="G235" s="4" t="str">
+        <x:v>候选元数据与超限“不完整”不被标为支持或历史覆盖证明；经独立核实的原生样例有 session_meta.id、token_usage_record.payload.response_id/usage，版本与 SHA 留证
+该 build 不列为已支持，显示 unsupported_source_version</x:v>
+      </x:c>
+      <x:c r="H235" s="4" t="str">
+        <x:v>准备：无 DB 写入
+变化：不适用；见本用例具体数据库观察面。
+核验：无 DB 写入；核对来源清单版本、摘要与私有样例归属。数据：受控来源样例；每次新隔离根重建。</x:v>
+      </x:c>
+      <x:c r="I235" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J235" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K235" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L235" s="4" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:207</x:v>
+      </x:c>
+      <x:c r="M235" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N235" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="236" ht="72" customHeight="1">
+      <x:c r="A236" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B236" s="9" t="str">
+        <x:v>TC-TM003-DATA-01</x:v>
+      </x:c>
+      <x:c r="C236" s="9" t="str">
+        <x:v>固定原生形状数据与独立预期</x:v>
+      </x:c>
+      <x:c r="D236" s="9" t="str">
+        <x:v>TASK-TM003-FIXTURE</x:v>
+      </x:c>
+      <x:c r="E236" s="9" t="str">
+        <x:v>data_check</x:v>
+      </x:c>
+      <x:c r="F236" s="9" t="str">
+        <x:v>1. 在 sessions/YYYY/MM/DD/*.jsonl 以 seed303 与本次已记录的 T0 生成 A/B/C 原生形状记录→同一 seed+T0 重建时字节摘要固定且三 ID 不同。2. 独立读取 expected 文件→A=110、A+B+C=660、cached=120，第二配方=220；没有调用产品解析器。</x:v>
+      </x:c>
+      <x:c r="G236" s="9" t="str">
+        <x:v>两份相对位置和字节摘要相同，A/B/C 三响应 ID 互异；四层子目录在 TM-002 草稿8层上限内、文件/目录项未达1000/5000；owner/expected 记录 T0
+A=110、A+B+C=660、cached=120，第二配方=220；没有调用产品解析器</x:v>
+      </x:c>
+      <x:c r="H236" s="9" t="str">
+        <x:v>准备：准备新私有根，不写用量表
+变化：不适用；见本用例具体数据库观察面。
+核验：不写用量表；只核对嵌套来源相对位置、元数据上限、两份源 SHA、独立 expected 和 owner；仅删除本例拥有的根。</x:v>
+      </x:c>
+      <x:c r="I236" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J236" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K236" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L236" s="9" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:211</x:v>
+      </x:c>
+      <x:c r="M236" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N236" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="237" ht="72" customHeight="1">
+      <x:c r="A237" s="4" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B237" s="4" t="str">
+        <x:v>TC-TM003-PARSE-01</x:v>
+      </x:c>
+      <x:c r="C237" s="4" t="str">
+        <x:v>三响应与缓存子项计量</x:v>
+      </x:c>
+      <x:c r="D237" s="4" t="str">
+        <x:v>TASK-TM003-PARSE</x:v>
+      </x:c>
+      <x:c r="E237" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F237" s="4" t="str">
+        <x:v>R-BASE。1. 仅追加 A 完整行并从 UI 刷新→卡片 input100/output10/total110/cached read20/cache write5/reasoning3、唯一1。2. 追加 B/C 后刷新→input600/output60/total660/cached read120/cache write30/reasoning18、唯一3；累计字段不额外加。</x:v>
+      </x:c>
+      <x:c r="G237" s="4" t="str">
+        <x:v>卡片 input100/output10/total110/cached read20/cache write5/reasoning3、唯一1
+input600/output60/total660/cached read120/cache write30/reasoning18、唯一3；累计字段不额外加</x:v>
+      </x:c>
+      <x:c r="H237" s="4" t="str">
+        <x:v>准备：空客户端库
+变化：插入 A 后1行，再插 B/C 后3行
+核验：空客户端库→插入 A 后1行，再插 B/C 后3行；Q_SUM=(3,600,60,120)，Q_SUB=(30,18)、Q_NULL=0；重置私有库。</x:v>
+      </x:c>
+      <x:c r="I237" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J237" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K237" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L237" s="4" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:215</x:v>
+      </x:c>
+      <x:c r="M237" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N237" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="238" ht="72" customHeight="1">
+      <x:c r="A238" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B238" s="9" t="str">
+        <x:v>TC-TM003-SCAN-01</x:v>
+      </x:c>
+      <x:c r="C238" s="9" t="str">
+        <x:v>追加补扫重启移动去重</x:v>
+      </x:c>
+      <x:c r="D238" s="9" t="str">
+        <x:v>TASK-TM003-SCAN</x:v>
+      </x:c>
+      <x:c r="E238" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F238" s="9" t="str">
+        <x:v>R-BASE、A/B/C。1. 三次分批追加并等 watcher 或30秒补扫→每批总量110/330/660。2. 手动刷新同文件并重启 App→仍660。3. 同一授权根内移动文件并刷新→仍唯一3、660。</x:v>
+      </x:c>
+      <x:c r="G238" s="9" t="str">
+        <x:v>每批总量110/330/660
+仍660
+仍唯一3、660</x:v>
+      </x:c>
+      <x:c r="H238" s="9" t="str">
+        <x:v>准备：空库
+变化：只增加3事件
+核验：空库→只增加3事件；每步 Q_SUM 为 (1,100,10,20)、(2,300,30,60)、(3,600,60,120)，重扫/重启/移动不变；核对 Q_CURSOR 完整行字节边界。</x:v>
+      </x:c>
+      <x:c r="I238" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J238" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K238" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L238" s="9" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:219</x:v>
+      </x:c>
+      <x:c r="M238" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N238" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="239" ht="117" customHeight="1">
+      <x:c r="A239" s="4" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B239" s="4" t="str">
+        <x:v>TC-TM003-STORE-01</x:v>
+      </x:c>
+      <x:c r="C239" s="4" t="str">
+        <x:v>事件与游标持久化</x:v>
+      </x:c>
+      <x:c r="D239" s="4" t="str">
+        <x:v>TASK-TM003-STORE</x:v>
+      </x:c>
+      <x:c r="E239" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F239" s="4" t="str">
+        <x:v>R-BASE、A/B；本例拥有的私有 profile 身份密钥和隔离客户端库。1. 完整 A 刷新→110。2. 本例进程退出/重启→110。3. 追加同 ID 同用量 A→仍110。4. 仅使本例 profile 的 usage 身份密钥不可读取，再追加 B=200/20/cached40 并刷新→保持110、停采集。5. 恢复原密钥后重启/刷新→A 不重计、B 入库，total330。密钥原文不进入报告。</x:v>
+      </x:c>
+      <x:c r="G239" s="4" t="str">
+        <x:v>110
+UI 恢复110
+仍110；无第二事件
+密钥不可用时停采集，不生成新键重扫旧日志或把 B 入库
+恢复原密钥后只补入 B，既有 A 不重计</x:v>
+      </x:c>
+      <x:c r="H239" s="4" t="str">
+        <x:v>准备：本例私有空库、受控 A/B 原生形状数据和隔离 usage 身份密钥；仅本例 fixture 可暂时使该密钥不可读取并恢复原件；不直接向事件表造数
+变化：A 一事件及游标原子提交；密钥不可用时事件/游标不变且覆盖不完整；恢复原密钥后 B 一事件提交、A 键不变
+核验：只读 Q_SUM 依次 (1,100,10,20)、同值、同值、同值、(2,300,30,60)；逐步检查 Q_CURSOR 与 coverage；原 A source_event_key 在恢复后不变，绝不让新密钥重扫成第二份 A</x:v>
+      </x:c>
+      <x:c r="I239" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J239" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K239" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L239" s="4" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:223</x:v>
+      </x:c>
+      <x:c r="M239" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N239" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="240" ht="87" customHeight="1">
+      <x:c r="A240" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B240" s="9" t="str">
+        <x:v>TC-TM003-UI-01</x:v>
+      </x:c>
+      <x:c r="C240" s="9" t="str">
+        <x:v>可信总量与未知来源展示</x:v>
+      </x:c>
+      <x:c r="D240" s="9" t="str">
+        <x:v>TASK-TM003-UI</x:v>
+      </x:c>
+      <x:c r="E240" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F240" s="9" t="str">
+        <x:v>R-BASE、A/B/C。1. 采集前查看卡片→显示尚无可证明历史/等待采集，不能显示已知0。2. 采集后→可信 input600、output60、total660、cached read120、cache write30、reasoning output18、唯一3、UTC最后采集时间。3. 插入一个缺 cached_input_tokens 的非 0.158 完整行→可信总量仍660，显示缺字段诊断，不把未知 cached 当0。</x:v>
+      </x:c>
+      <x:c r="G240" s="9" t="str">
+        <x:v>显示尚无可证明历史/等待采集，不能显示已知0
+可信 input600、output60、total660、cached read120、cache write30、reasoning output18、唯一3、UTC最后采集时间
+可信总量仍660，显示缺字段诊断，不把未知 cached 当0</x:v>
+      </x:c>
+      <x:c r="H240" s="9" t="str">
+        <x:v>准备：空库
+变化：前三条 Q_SUM=(3,600,60,120)
+核验：空库→前三条 Q_SUM=(3,600,60,120)；无新事件，Q_SUM保持三条；Q_DIAG出现缺字段，UI 区分未知来源。</x:v>
+      </x:c>
+      <x:c r="I240" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J240" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K240" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L240" s="9" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:227</x:v>
+      </x:c>
+      <x:c r="M240" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N240" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="241" ht="72" customHeight="1">
+      <x:c r="A241" s="4" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B241" s="4" t="str">
+        <x:v>TC-TM003-SOURCE-02</x:v>
+      </x:c>
+      <x:c r="C241" s="4" t="str">
+        <x:v>无响应身份累计记录降级</x:v>
+      </x:c>
+      <x:c r="D241" s="4" t="str">
+        <x:v>TASK-TM003-SOURCE</x:v>
+      </x:c>
+      <x:c r="E241" s="4" t="str">
+        <x:v>source_check</x:v>
+      </x:c>
+      <x:c r="F241" s="4" t="str">
+        <x:v>1. 输入只有 event_msg.token_count.info.total_token_usage=100/10 且无 response_id→诊断 unverified_cumulative、可信事件0。2. 加 rate-limit-only 的 info=null→诊断 missing_usage，不生成0值用量事件。</x:v>
+      </x:c>
+      <x:c r="G241" s="4" t="str">
+        <x:v>诊断 unverified_cumulative、可信事件0
+诊断 missing_usage，不生成0值用量事件</x:v>
+      </x:c>
+      <x:c r="H241" s="4" t="str">
+        <x:v>准备：新库
+变化：Q_SUM无事件
+核验：新库→Q_SUM无事件；Q_DIAG分别含 unverified_cumulative 与 missing_usage；仅测试拥有根。</x:v>
+      </x:c>
+      <x:c r="I241" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J241" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K241" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L241" s="4" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:231</x:v>
+      </x:c>
+      <x:c r="M241" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N241" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="242" ht="57" customHeight="1">
+      <x:c r="A242" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B242" s="9" t="str">
+        <x:v>TC-TM003-PARSE-02</x:v>
+      </x:c>
+      <x:c r="C242" s="9" t="str">
+        <x:v>损坏及缺字段记录隔离</x:v>
+      </x:c>
+      <x:c r="D242" s="9" t="str">
+        <x:v>TASK-TM003-PARSE</x:v>
+      </x:c>
+      <x:c r="E242" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F242" s="9" t="str">
+        <x:v>R-BASE。1. 完整合法 100/10 行→110。2. 依次追加缺 usage、负 input、cached 111&gt;input100、矛盾 total111 四个不同 ID 完整行→UI 可信总量仍110，每项显示独立诊断，不能作为0值成功事件。</x:v>
+      </x:c>
+      <x:c r="G242" s="9" t="str">
+        <x:v>110
+UI 可信总量仍110，每项显示独立诊断，不能作为0值成功事件</x:v>
+      </x:c>
+      <x:c r="H242" s="9" t="str">
+        <x:v>准备：空库
+变化：仅合法1行
+核验：空库→仅合法1行；Q_SUM=(1,100,10,20)；Q_DIAG四种错误各≥1；重置私有库。</x:v>
+      </x:c>
+      <x:c r="I242" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J242" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K242" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L242" s="9" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:235</x:v>
+      </x:c>
+      <x:c r="M242" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N242" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="243" ht="87" customHeight="1">
+      <x:c r="A243" s="4" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B243" s="4" t="str">
+        <x:v>TC-TM003-MODEL-01</x:v>
+      </x:c>
+      <x:c r="C243" s="4" t="str">
+        <x:v>模型标识与未知模型保留</x:v>
+      </x:c>
+      <x:c r="D243" s="4" t="str">
+        <x:v>TASK-TM003-PARSE</x:v>
+      </x:c>
+      <x:c r="E243" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F243" s="4" t="str">
+        <x:v>R-BASE。1. 在有同一 turn_id 的原生 turn_context 声明 gpt-6-sol 并追加 ID-m 10/1→UI 总量11，DB模型为 gpt-6-sol。2. 对新 turn 声明来源未知但实际原样标识 model-x 并追加 ID-n 10/1→UI 总量22，DB保留 model-x，不得改成0或空字符串。3. 追加找不到同 turn 上下文的 ID-o 10/1→UI 总量33，DB模型为 NULL 且显示模型未知诊断。</x:v>
+      </x:c>
+      <x:c r="G243" s="4" t="str">
+        <x:v>UI 总量11，DB模型为 gpt-6-sol
+UI 总量22，DB保留 model-x，不得改成0或空字符串
+UI 总量33，DB模型为 NULL 且显示模型未知诊断</x:v>
+      </x:c>
+      <x:c r="H243" s="4" t="str">
+        <x:v>准备：空库
+变化：最终 Q_IO=(3,30,3)
+核验：空库→最终 Q_IO=(3,30,3)；只读查询三个模型字段依次为 gpt-6-sol、model-x、NULL；不插入模型维度造数。</x:v>
+      </x:c>
+      <x:c r="I243" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J243" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K243" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L243" s="4" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:239</x:v>
+      </x:c>
+      <x:c r="M243" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N243" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="244" ht="72" customHeight="1">
+      <x:c r="A244" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B244" s="9" t="str">
+        <x:v>TC-TM003-DEDUP-01</x:v>
+      </x:c>
+      <x:c r="C244" s="9" t="str">
+        <x:v>相同响应重放和身份冲突</x:v>
+      </x:c>
+      <x:c r="D244" s="9" t="str">
+        <x:v>TASK-TM003-IDENTITY</x:v>
+      </x:c>
+      <x:c r="E244" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F244" s="9" t="str">
+        <x:v>R-BASE。1. 追加 ID-a 100/10→110。2. 重放 ID-a 完全相同记录→仍110。3. 追加 ID-b 同样100/10→220且唯一2。4. 再写 ID-a 999/99→仍220并有 identity_conflict。</x:v>
+      </x:c>
+      <x:c r="G244" s="9" t="str">
+        <x:v>110
+仍110
+220且唯一2
+仍220并有 identity_conflict</x:v>
+      </x:c>
+      <x:c r="H244" s="9" t="str">
+        <x:v>准备：空库
+变化：最终 Q_SUM=(2,200,20,40)
+核验：空库→最终 Q_SUM=(2,200,20,40)；冲突不覆盖原行；读 Q_DIAG。</x:v>
+      </x:c>
+      <x:c r="I244" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J244" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K244" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L244" s="9" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:243</x:v>
+      </x:c>
+      <x:c r="M244" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N244" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="245" ht="87" customHeight="1">
+      <x:c r="A245" s="4" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B245" s="4" t="str">
+        <x:v>TC-TM003-BRANCH-01</x:v>
+      </x:c>
+      <x:c r="C245" s="4" t="str">
+        <x:v>累计快照新会话与分支</x:v>
+      </x:c>
+      <x:c r="D245" s="4" t="str">
+        <x:v>TASK-TM003-IDENTITY</x:v>
+      </x:c>
+      <x:c r="E245" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F245" s="4" t="str">
+        <x:v>R-BASE。1. 主会话按 usage 写 100/10、50/5，而累计快照从100/10到150/15→可信165。2. 新会话写30/3→198。3. 普通 CLI fork 子文件带 forked_from_id，只有新响应20/2、thread 累计170/17；另从独立文件重放父 A→可信220、唯一4，重放不新增事件。4. 写无响应身份的累计回退和未知结构→仍220，显示 unverified_cumulative / unknown_format。</x:v>
+      </x:c>
+      <x:c r="G245" s="4" t="str">
+        <x:v>可信165
+198
+可信220、唯一4
+仍220，显示 unverified_cumulative / unknown_format</x:v>
+      </x:c>
+      <x:c r="H245" s="4" t="str">
+        <x:v>准备：空库
+变化：最终 Q_IO=(4,200,20)
+核验：空库→最终 Q_IO=(4,200,20)；output20、total220；cached 按固定各项另核；Q_DIAG有两类，继承不新增事件。</x:v>
+      </x:c>
+      <x:c r="I245" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J245" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K245" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L245" s="4" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:247</x:v>
+      </x:c>
+      <x:c r="M245" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N245" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="246" ht="102" customHeight="1">
+      <x:c r="A246" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B246" s="9" t="str">
+        <x:v>TC-TM003-NAMESPACE-01</x:v>
+      </x:c>
+      <x:c r="C246" s="9" t="str">
+        <x:v>跨来源事件身份和不明继承</x:v>
+      </x:c>
+      <x:c r="D246" s="9" t="str">
+        <x:v>TASK-TM003-IDENTITY</x:v>
+      </x:c>
+      <x:c r="E246" s="9" t="str">
+        <x:v>source_check</x:v>
+      </x:c>
+      <x:c r="F246" s="9" t="str">
+        <x:v>本例私有 schema 与tests/fixtures/tm004/identity-v1-vectors.json 中的公开测试 HMAC key（仅固定向量，绝不进入产品 profile）；标准事件 Codex provider-response/shared-call-01=100/10/cached20，Claude provider-message/shared-call-01=30/3/cached0；随后同 Codex 事件重放、另一 Agent 无复制链同 Claude ID 重用、同 Codex ID 但用量或模型冲突。</x:v>
+      </x:c>
+      <x:c r="G246" s="9" t="str">
+        <x:v>两条可信事件 total143，显式来源域防止跨工具误合并
+键相同且不新增事件
+不能把未证明同一调用的重用计为新事件，Agent 归属不进入唯一键
+首条可信事件不覆写，仍两条 total143</x:v>
+      </x:c>
+      <x:c r="H246" s="9" t="str">
+        <x:v>准备：本例拥有的全新私有 schema；使用已提交公开32字节测试 key 与标准事件作为纯身份入口固定 oracle，真实产品 profile 自行生成私密随机 key；不直接向事件表造数
+变化：正式身份/存储入口只接受2事件；重复和冲突不新增或覆写
+核验：只读 Q_SUM=(2,130,13,20)，按 source 核对两键精确等于 afd67bd0cad0227b3e7b5ac132bb9b3ed492073983b9c16a0c9cc24dd3008051 和 bf222a85ab2209f72ff82c21b7172c9315448b3e1d5bf4503a3c76b30c46cad1，再核对身份冲突与不明继承诊断、coverage 不完整</x:v>
+      </x:c>
+      <x:c r="I246" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J246" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K246" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L246" s="9" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:251</x:v>
+      </x:c>
+      <x:c r="M246" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N246" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="247" ht="57" customHeight="1">
+      <x:c r="A247" s="4" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B247" s="4" t="str">
+        <x:v>TC-TM003-PRIVACY-01</x:v>
+      </x:c>
+      <x:c r="C247" s="4" t="str">
+        <x:v>原文哨兵不得入库和报告</x:v>
+      </x:c>
+      <x:c r="D247" s="4" t="str">
+        <x:v>TASK-TM003-STORE</x:v>
+      </x:c>
+      <x:c r="E247" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F247" s="4" t="str">
+        <x:v>R-BASE 中只放合法 A=100/10/cached20；在 A 的非用量文本字段加入固定合成哨兵、代码片段和合成绝对路径，然后退出 App 检查仅本例拥有的 SQLite/WAL/采集报告。</x:v>
+      </x:c>
+      <x:c r="G247" s="4" t="str">
+        <x:v>有效用量仍只按 usage 计
+均不含哨兵/原始路径/原始 JSONL</x:v>
+      </x:c>
+      <x:c r="H247" s="4" t="str">
+        <x:v>准备：新库
+变化：仅白名单事件字段、HMAC 身份
+核验：新库→仅白名单事件字段、HMAC 身份；Q_SUM与合法用量一致；重置私有根。</x:v>
+      </x:c>
+      <x:c r="I247" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J247" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K247" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L247" s="4" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:255</x:v>
+      </x:c>
+      <x:c r="M247" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N247" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="248" ht="57" customHeight="1">
+      <x:c r="A248" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B248" s="9" t="str">
+        <x:v>TC-TM003-DATA-02</x:v>
+      </x:c>
+      <x:c r="C248" s="9" t="str">
+        <x:v>半行字节数据与归属清理</x:v>
+      </x:c>
+      <x:c r="D248" s="9" t="str">
+        <x:v>TASK-TM003-FIXTURE</x:v>
+      </x:c>
+      <x:c r="E248" s="9" t="str">
+        <x:v>data_check</x:v>
+      </x:c>
+      <x:c r="F248" s="9" t="str">
+        <x:v>1. 数据程序向拥有的文件只写 B JSONL 前半字节且无 LF→文件确实不含完整 B 行。2. 同程序补写余字节与 LF→恰好一条完整 B。3. 清理仅 owner 收据中的源文件→其他根、App 和服务不受影响。</x:v>
+      </x:c>
+      <x:c r="G248" s="9" t="str">
+        <x:v>文件确实不含完整 B 行
+恰好一条完整 B
+其他根、App 和服务不受影响</x:v>
+      </x:c>
+      <x:c r="H248" s="9" t="str">
+        <x:v>准备：无产品库写入
+变化：不适用；见本用例具体数据库观察面。
+核验：无产品库写入；按字节摘要、LF 数和 owner 核对；重置只删本例根。</x:v>
+      </x:c>
+      <x:c r="I248" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J248" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K248" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L248" s="9" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:259</x:v>
+      </x:c>
+      <x:c r="M248" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N248" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="249" ht="72" customHeight="1">
+      <x:c r="A249" s="4" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B249" s="4" t="str">
+        <x:v>TC-TM003-SCAN-02</x:v>
+      </x:c>
+      <x:c r="C249" s="4" t="str">
+        <x:v>半行补全后只计一次</x:v>
+      </x:c>
+      <x:c r="D249" s="4" t="str">
+        <x:v>TASK-TM003-SCAN</x:v>
+      </x:c>
+      <x:c r="E249" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F249" s="4" t="str">
+        <x:v>R-BASE。1. 完整 A=100/10 后刷新→total110、唯一1。2. 只追加 B=50/5 半行并刷新→仍110、游标停在 A 的 LF 后。3. 补齐 B 和 LF 后刷新，再重启→total165、唯一2，B 只计一次。</x:v>
+      </x:c>
+      <x:c r="G249" s="4" t="str">
+        <x:v>total110、唯一1
+仍110、游标停在 A 的 LF 后
+total165、唯一2，B 只计一次</x:v>
+      </x:c>
+      <x:c r="H249" s="4" t="str">
+        <x:v>准备：空库
+变化：Q_SUM=(1,100,10,20)，半行时同值，补全后 Q_IO=(2,150,15)
+核验：空库→Q_SUM=(1,100,10,20)，半行时同值，补全后 Q_IO=(2,150,15)；Q_CURSOR先停于 A 完整字节，再到 B 完整字节。</x:v>
+      </x:c>
+      <x:c r="I249" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J249" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K249" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L249" s="4" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:263</x:v>
+      </x:c>
+      <x:c r="M249" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N249" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="250" ht="72" customHeight="1">
+      <x:c r="A250" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B250" s="9" t="str">
+        <x:v>TC-TM003-SCAN-03</x:v>
+      </x:c>
+      <x:c r="C250" s="9" t="str">
+        <x:v>截断后的重读与新事件</x:v>
+      </x:c>
+      <x:c r="D250" s="9" t="str">
+        <x:v>TASK-TM003-SCAN</x:v>
+      </x:c>
+      <x:c r="E250" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F250" s="9" t="str">
+        <x:v>R-BASE。1. 完整 A=100/10 与 B=50/5 入库→total165、唯一2。2. 仅对本例源文件截断为完整 A 并刷新→已采集 B 不丢，仍165，游标重置到当前 A 的 LF。3. 追加新 ID-C=300/30 完整行并刷新、重启→total495、唯一3，A不重计。</x:v>
+      </x:c>
+      <x:c r="G250" s="9" t="str">
+        <x:v>total165、唯一2
+已采集 B 不丢，仍165，游标重置到当前 A 的 LF
+total495、唯一3，A不重计</x:v>
+      </x:c>
+      <x:c r="H250" s="9" t="str">
+        <x:v>准备：空库
+变化：Q_IO 先 (2,150,15)，截断后不变，最后 (3,450,45)
+核验：空库→Q_IO 先 (2,150,15)，截断后不变，最后 (3,450,45)；Q_CURSOR按新文件完整字节更新，不越过未闭合行。</x:v>
+      </x:c>
+      <x:c r="I250" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J250" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K250" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L250" s="9" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:267</x:v>
+      </x:c>
+      <x:c r="M250" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N250" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="251" ht="72" customHeight="1">
+      <x:c r="A251" s="4" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B251" s="4" t="str">
+        <x:v>TC-TM003-WINDOW-01</x:v>
+      </x:c>
+      <x:c r="C251" s="4" t="str">
+        <x:v>首次30天UTC采集窗口</x:v>
+      </x:c>
+      <x:c r="D251" s="4" t="str">
+        <x:v>TASK-TM003-SCAN</x:v>
+      </x:c>
+      <x:c r="E251" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F251" s="4" t="str">
+        <x:v>固定程序于运行准备阶段记录 T0 UTC 秒；授权前在本例根写完整 ID-old=T0-31天 900/90、ID-new=T0-29天 100/10；授权后追加 ID-next=T0-1天 50/5、ID-bad=无效 UTC 时间 200/20。</x:v>
+      </x:c>
+      <x:c r="G251" s="4" t="str">
+        <x:v>T0-31天的记录不计，T0-29天的记录计入
+新增 50/5 只计一次
+无效时间不得生成可信事件</x:v>
+      </x:c>
+      <x:c r="H251" s="4" t="str">
+        <x:v>准备：本例全新客户端库；只经真实 UI 授权并扫描原生形状测试文件，不直接写产品库
+变化：先插入 ID-new，再插入 ID-next；ID-old 和 ID-bad 都不入事件表
+核验：初次 Q_SUM=(1,100,10,20)，追加后 Q_IO=(2,150,15)，无效时间后同值；Q_DIAG 有 invalid_time；按响应键只读验证 old/bad 不在库</x:v>
+      </x:c>
+      <x:c r="I251" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J251" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K251" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L251" s="4" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:271</x:v>
+      </x:c>
+      <x:c r="M251" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N251" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="252" ht="117" customHeight="1">
+      <x:c r="A252" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B252" s="9" t="str">
+        <x:v>TC-TM003-COVERAGE-OVERFLOW-01</x:v>
+      </x:c>
+      <x:c r="C252" s="9" t="str">
+        <x:v>超预览上限的授权内部分页、撤销与目录变动</x:v>
+      </x:c>
+      <x:c r="D252" s="9" t="str">
+        <x:v>TASK-TM003-SCAN</x:v>
+      </x:c>
+      <x:c r="E252" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F252" s="9" t="str">
+        <x:v>本例私有 0700 授权根含1001个可排序的 sessions/YYYY/MM/DD/*.jsonl，前1000个无可信用量，最后一个 A=100/10/cached20；另有未授权根 B=900/90。预览上限1000，内部分页每页最多256。</x:v>
+      </x:c>
+      <x:c r="G252" s="9" t="str">
+        <x:v>预览不是全量扫描完成证明
+暂停状态不得提交完整覆盖
+末端第1001个 A 计一次
+撤销使旧授权能力失效，不跨根读 B
+跨页目录变动废弃全部暂定页，既有已提交 A 保留，不能续扫旧页或仅凭 complete 判正文完整</x:v>
+      </x:c>
+      <x:c r="H252" s="9" t="str">
+        <x:v>准备：本例拥有的全新客户端库、0700 双根和1001个合成 JSONL；通过真实 UI 确认根；不直接写事件表
+变化：预览/暂停零事件，完成后 A 一事件，撤销后保留 A 且覆盖不完整；目录变动废弃新一轮暂存页，已提交 A 不变
+核验：只读 Q_SUM 依次无事件、无事件、(1,100,10,20)、同值；核对 scan_incomplete 依次1、1、0、1及旧能力拒绝；第5步旧 generation 拒绝、暂存游标回滚，Q_SUM 保持(1,100,10,20)，新 generation 从头开始</x:v>
+      </x:c>
+      <x:c r="I252" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J252" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K252" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L252" s="9" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:275</x:v>
+      </x:c>
+      <x:c r="M252" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N252" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="253" ht="72" customHeight="1">
+      <x:c r="A253" s="4" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B253" s="4" t="str">
+        <x:v>TC-TM003-UI-02</x:v>
+      </x:c>
+      <x:c r="C253" s="4" t="str">
+        <x:v>源清理后的覆盖缺口</x:v>
+      </x:c>
+      <x:c r="D253" s="4" t="str">
+        <x:v>TASK-TM003-UI</x:v>
+      </x:c>
+      <x:c r="E253" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F253" s="4" t="str">
+        <x:v>R-BASE、完整 A/B。1. 导入后→UI total165 且覆盖起点为最早可信事件时间。2. 删除仅本例拥有的源文件后刷新/重启→仍165；源缺失与更早历史不可证明的提示可见，不能显示历史0。</x:v>
+      </x:c>
+      <x:c r="G253" s="4" t="str">
+        <x:v>UI total165 且覆盖起点为最早可信事件时间
+仍165；源缺失与更早历史不可证明的提示可见，不能显示历史0</x:v>
+      </x:c>
+      <x:c r="H253" s="4" t="str">
+        <x:v>准备：空库
+变化：保留2事件、Q_IO=(2,150,15)
+核验：空库→保留2事件、Q_IO=(2,150,15)；coverage.missing_before=1 或等价状态；不删事件。</x:v>
+      </x:c>
+      <x:c r="I253" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J253" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K253" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L253" s="4" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:279</x:v>
+      </x:c>
+      <x:c r="M253" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N253" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="254" ht="57" customHeight="1">
+      <x:c r="A254" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B254" s="9" t="str">
+        <x:v>TC-TM003-BOUNDARY-01</x:v>
+      </x:c>
+      <x:c r="C254" s="9" t="str">
+        <x:v>未授权根和越界链接拒绝</x:v>
+      </x:c>
+      <x:c r="D254" s="9" t="str">
+        <x:v>TASK-TM003-SCAN</x:v>
+      </x:c>
+      <x:c r="E254" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F254" s="9" t="str">
+        <x:v>测试拥有 A/B，B 内有 ID-x=900/90，A 的 sessions/YYYY/MM/DD/ 同层有 symlink escape.jsonl 指向 B。1. 仅通过真实 UI 选 A 并确认→A 的可信事件可读。2. 手动刷新与30秒补扫→B 和越界 symlink 不被读，UI 无 x 用量。</x:v>
+      </x:c>
+      <x:c r="G254" s="9" t="str">
+        <x:v>A 的可信事件可读
+B 与同层越界 symlink 均不被读，UI 无 x 用量，B 的文件摘要不变</x:v>
+      </x:c>
+      <x:c r="H254" s="9" t="str">
+        <x:v>准备：空库
+变化：只出现 A 的 response key
+核验：空库→只出现 A 的 response key；Q_SUM不含990；B 的文件摘要前后不变。</x:v>
+      </x:c>
+      <x:c r="I254" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J254" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K254" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L254" s="9" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:283</x:v>
+      </x:c>
+      <x:c r="M254" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N254" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="255" ht="57" customHeight="1">
+      <x:c r="A255" s="4" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B255" s="4" t="str">
+        <x:v>TC-TM003-AUTH-01</x:v>
+      </x:c>
+      <x:c r="C255" s="4" t="str">
+        <x:v>确认前与失效时停读</x:v>
+      </x:c>
+      <x:c r="D255" s="4" t="str">
+        <x:v>TASK-TM003-AUTH</x:v>
+      </x:c>
+      <x:c r="E255" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F255" s="4" t="str">
+        <x:v>A 含 A=100/10。1. 打开授权预览但不确认→持续扫描不启动、客户端无事件。2. 确认后→110。3. TM-002 fixture 仅使 A 授权失效，再追加 B=200/20 并刷新→卡片显示需重新授权，仍110，A 不被继续读取。</x:v>
+      </x:c>
+      <x:c r="G255" s="4" t="str">
+        <x:v>持续扫描不启动、客户端无事件
+110
+卡片显示需重新授权，仍110，A 不被继续读取</x:v>
+      </x:c>
+      <x:c r="H255" s="4" t="str">
+        <x:v>准备：新库
+变化：确认前0事件
+核验：新库→确认前0事件；确认后 Q_SUM=(1,100,10,20)；失效后不变，游标不前进。</x:v>
+      </x:c>
+      <x:c r="I255" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J255" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K255" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L255" s="4" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:287</x:v>
+      </x:c>
+      <x:c r="M255" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N255" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="256" ht="72" customHeight="1">
+      <x:c r="A256" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B256" s="9" t="str">
+        <x:v>TC-TM003-AUTH-02</x:v>
+      </x:c>
+      <x:c r="C256" s="9" t="str">
+        <x:v>重新授权后的去重补扫</x:v>
+      </x:c>
+      <x:c r="D256" s="9" t="str">
+        <x:v>TASK-TM003-AUTH</x:v>
+      </x:c>
+      <x:c r="E256" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F256" s="9" t="str">
+        <x:v>A 已通过真实 UI 授权且含 A=100/10、B=200/20。1. 采集后→330、唯一2。2. 失效期间追加 C=300/30 与重放 A→仍330。3. 从真实 UI 重新授权同根并确认→660、唯一3。4. 刷新并重启→仍660。</x:v>
+      </x:c>
+      <x:c r="G256" s="9" t="str">
+        <x:v>330、唯一2
+仍330
+660、唯一3
+仍660</x:v>
+      </x:c>
+      <x:c r="H256" s="9" t="str">
+        <x:v>准备：空库
+变化：Q_SUM依次 (2,300,30,60)、同值、(3,600,60,120)、同值
+核验：空库→Q_SUM依次 (2,300,30,60)、同值、(3,600,60,120)、同值；重复 A 不插入。</x:v>
+      </x:c>
+      <x:c r="I256" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J256" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K256" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L256" s="9" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:291</x:v>
+      </x:c>
+      <x:c r="M256" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N256" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="257" ht="87" customHeight="1">
+      <x:c r="A257" s="4" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B257" s="4" t="str">
+        <x:v>TC-TM003-ISOLATION-01</x:v>
+      </x:c>
+      <x:c r="C257" s="4" t="str">
+        <x:v>已验证主体切换时来源和采集状态隔离</x:v>
+      </x:c>
+      <x:c r="D257" s="4" t="str">
+        <x:v>TASK-TM003-AUTH</x:v>
+      </x:c>
+      <x:c r="E257" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F257" s="4" t="str">
+        <x:v>两隔离真实服务 O1/O2；O1 成员 U1/U2，O2 成员 U1b（ID与U1相同）；本例根 A 含固定 ID-a=100/10；各主体通过真实 UI 分别确认来源。</x:v>
+      </x:c>
+      <x:c r="G257" s="4" t="str">
+        <x:v>只有 P1 来源能力被使用
+旧主体读取已停止
+相同响应在不同已确认主体各自计一次
+规范化 origin 是主体键的一部分
+恢复旧主体不重计，也不读取其他主体来源</x:v>
+      </x:c>
+      <x:c r="H257" s="4" t="str">
+        <x:v>准备：只经真实服务创建合成 U1/U2/U1b，客户端新库，隔离根 A；不向 usage_event 造数
+变化：P1/P2 各自一条事件与独立游标，P3 无事件或游标；身份切换不删除旧主体记录
+核验：按 HMAC(O1,U1)、HMAC(O1,U2)、HMAC(O2,U1b) 的不可逆主体键分别查询 Q_SUM 和 source_cursor；原路径、账号凭据与原始日志不入库</x:v>
+      </x:c>
+      <x:c r="I257" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J257" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K257" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L257" s="4" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:295</x:v>
+      </x:c>
+      <x:c r="M257" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N257" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="258" ht="117" customHeight="1">
+      <x:c r="A258" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B258" s="9" t="str">
+        <x:v>TC-TM003-MIGRATE-01</x:v>
+      </x:c>
+      <x:c r="C258" s="9" t="str">
+        <x:v>客户端库迁移和恢复</x:v>
+      </x:c>
+      <x:c r="D258" s="9" t="str">
+        <x:v>TASK-TM003-MIGRATE</x:v>
+      </x:c>
+      <x:c r="E258" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F258" s="9" t="str">
+        <x:v>上一实际稳定版 TM-002 私有 profile，包含合成账号、已确认授权根与原有 schema；该版尚无采集事件，若无稳定版包则 BLOCKED。1. 在本轮隔离根备份并验证可恢复→旧 schema、账号/授权状态有摘要且无 usage_event。2. 经 App 内真实更新到候选→新 schema 建立，账号/授权保留，卡片显示尚无可信历史；向已授权根追加固定 A=100/10 后刷新→唯一1、total110。3. 在另一拥有副本注入迁移中断并重试→中断可检测，恢复旧 profile 后重试可得相同账号/授权与唯一 A，不重复计。</x:v>
+      </x:c>
+      <x:c r="G258" s="9" t="str">
+        <x:v>备份副本可打开且还原原状态
+真实更新与首次采集成功，未制造旧版不存在的历史用量
+中断可检测，恢复与重试后聚合不变</x:v>
+      </x:c>
+      <x:c r="H258" s="9" t="str">
+        <x:v>准备：从上一实际稳定 TM-002 包生成本例私有 profile，备份并验证可恢复；源版无 usage_event
+变化：候选创建目标 schema，首次 A 采集写入唯一一条事件；中断副本恢复后同一事件不重计
+核验：只在隔离副本造旧状态；源库只读核对旧 schema、账号/授权记录与无用量表；更新后 Q_SCHEMA 为目标版本、Q_SUM 先无行、采集 A 后为 (1,100,10,20)，账号/授权记录不变；不接触生产库。</x:v>
+      </x:c>
+      <x:c r="I258" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J258" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K258" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L258" s="9" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:299</x:v>
+      </x:c>
+      <x:c r="M258" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N258" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="259" ht="87" customHeight="1">
+      <x:c r="A259" s="4" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B259" s="4" t="str">
+        <x:v>TC-TM003-E2E-01</x:v>
+      </x:c>
+      <x:c r="C259" s="4" t="str">
+        <x:v>固定逐项入口和证据审计</x:v>
+      </x:c>
+      <x:c r="D259" s="4" t="str">
+        <x:v>TASK-TM003-E2E</x:v>
+      </x:c>
+      <x:c r="E259" s="4" t="str">
+        <x:v>governance</x:v>
+      </x:c>
+      <x:c r="F259" s="4" t="str">
+        <x:v>1. 固定单例入口指定一条 TM-003 TC→新 run_id、逐步原件和 SQL/源摘要。2. 对 TM-001 已交付集合加 TM-003 全部目标 TC/四组补充运行→每例/变体/组有原件，零缺例/跳过/重试。3. 移除副本报告一步→审计 BLOCKED。4. 在副本移除一条 TM-003 TC 或将变体 release 改成 TM-001→跨版本门禁拒绝，不签通行证。</x:v>
+      </x:c>
+      <x:c r="G259" s="4" t="str">
+        <x:v>新 run_id，逐步原件和 SQL/源摘要齐全
+逐 TC/变体与场景组均有独立原件、零缺例/跳过/重试；门禁集合不再固定只含 TM-001
+审计判 BLOCKED
+跨版本门禁拒绝该副本，不生成通行证</x:v>
+      </x:c>
+      <x:c r="H259" s="4" t="str">
+        <x:v>准备：使用测试拥有的独立库，审计只读原件
+变化：不适用；见本用例具体数据库观察面。
+核验：使用测试拥有的独立库，审计只读原件；不生成假 PASS。</x:v>
+      </x:c>
+      <x:c r="I259" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J259" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K259" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L259" s="4" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:303</x:v>
+      </x:c>
+      <x:c r="M259" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N259" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="260" ht="72" customHeight="1">
+      <x:c r="A260" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B260" s="9" t="str">
+        <x:v>TC-TM003-E2E-02</x:v>
+      </x:c>
+      <x:c r="C260" s="9" t="str">
+        <x:v>最终DMG真实链路和清理</x:v>
+      </x:c>
+      <x:c r="D260" s="9" t="str">
+        <x:v>TASK-TM003-E2E</x:v>
+      </x:c>
+      <x:c r="E260" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F260" s="9" t="str">
+        <x:v>1. 从最终候选 DMG 复制并安装 App→记录原件/安装路径与哈希。2. 用 Playwright executablePath 启动→真实 UI/IPC/采集/服务/SQLite 全链且 TM-001/002/003 应测集合精确相等。3. 退出并按 owner 清理→无遗留进程/端口/私有目录。</x:v>
+      </x:c>
+      <x:c r="G260" s="9" t="str">
+        <x:v>记录原件/安装路径与哈希
+真实 UI/IPC/采集/服务/SQLite 全链且 TM-001/002/003 应测集合精确相等
+无遗留进程/端口/私有目录</x:v>
+      </x:c>
+      <x:c r="H260" s="9" t="str">
+        <x:v>准备：每例隔离客户端/服务库
+变化：不适用；见本用例具体数据库观察面。
+核验：每例隔离客户端/服务库；最终 DB 与逐 TC 预期相符；包、源码、测试摘要一致。</x:v>
+      </x:c>
+      <x:c r="I260" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J260" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K260" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L260" s="9" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:307</x:v>
+      </x:c>
+      <x:c r="M260" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N260" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="261" ht="57" customHeight="1">
+      <x:c r="A261" s="4" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B261" s="4" t="str">
+        <x:v>TC-TM003-GOV-01</x:v>
+      </x:c>
+      <x:c r="C261" s="4" t="str">
+        <x:v>追踪总表与门禁拒绝</x:v>
+      </x:c>
+      <x:c r="D261" s="4" t="str">
+        <x:v>TASK-TM003-RELEASE</x:v>
+      </x:c>
+      <x:c r="E261" s="4" t="str">
+        <x:v>governance</x:v>
+      </x:c>
+      <x:c r="F261" s="4" t="str">
+        <x:v>1. 核对 manifest/需求→TASK→TC/AC、数据能力、Changelog、总表→零孤立或空预期。2. 运行 structure/baseline/quality 与总表回读→全部真实返回0才记录文档基线。3. 用候选原始报告门禁→任一 FAIL/BLOCKED 拒绝通行证。</x:v>
+      </x:c>
+      <x:c r="G261" s="4" t="str">
+        <x:v>TASK→TC/AC、数据能力、Changelog、总表→零孤立或空预期
+全部真实返回0才记录文档基线
+任一 FAIL/BLOCKED 拒绝通行证</x:v>
+      </x:c>
+      <x:c r="H261" s="4" t="str">
+        <x:v>准备：对数据库不适用
+变化：不适用；见本用例具体数据库观察面。
+核验：对数据库不适用；使用机器清单、结果 Excel 与原件摘要，不代写产品库。</x:v>
+      </x:c>
+      <x:c r="I261" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J261" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K261" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L261" s="4" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:311</x:v>
+      </x:c>
+      <x:c r="M261" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N261" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="262" ht="72" customHeight="1">
+      <x:c r="A262" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B262" s="9" t="str">
+        <x:v>TC-TM003-CORE-01</x:v>
+      </x:c>
+      <x:c r="C262" s="9" t="str">
+        <x:v>完整LF增量与累计快照解析</x:v>
+      </x:c>
+      <x:c r="D262" s="9" t="str">
+        <x:v>TASK-TM003-PARSE</x:v>
+      </x:c>
+      <x:c r="E262" s="9" t="str">
+        <x:v>source_check</x:v>
+      </x:c>
+      <x:c r="F262" s="9" t="str">
+        <x:v>原生形状完整A=100/10/cached20；B=200/20/cached40半行后补LF；C=300/30/cached60完整行及累计快照；固定种子和T0。</x:v>
+      </x:c>
+      <x:c r="G262" s="9" t="str">
+        <x:v>仅A一事件，input100/output10/total110/cached20，完成偏移恰在A的LF后
+仍仅A，完成偏移不跨半行
+仅A/B/C三事件，input600/output60/total660/cached120；累计快照和复扫不增量；完成偏移在累计快照行的LF后</x:v>
+      </x:c>
+      <x:c r="H262" s="9" t="str">
+        <x:v>准备：无产品DB写入；每例新私有根
+变化：不适用；纯解析返回事件与完成字节偏移
+核验：按源文件字节摘要、长度、完整LF边界和解析事件字段逐步比对；仅清理本例owner根</x:v>
+      </x:c>
+      <x:c r="I262" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J262" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K262" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L262" s="9" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:315</x:v>
+      </x:c>
+      <x:c r="M262" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N262" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="263" ht="72" customHeight="1">
+      <x:c r="A263" s="4" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B263" s="4" t="str">
+        <x:v>TC-TM003-CORE-02</x:v>
+      </x:c>
+      <x:c r="C263" s="4" t="str">
+        <x:v>累计空值及非法用量诊断</x:v>
+      </x:c>
+      <x:c r="D263" s="4" t="str">
+        <x:v>TASK-TM003-SOURCE
+TASK-TM003-PARSE</x:v>
+      </x:c>
+      <x:c r="E263" s="4" t="str">
+        <x:v>source_check</x:v>
+      </x:c>
+      <x:c r="F263" s="4" t="str">
+        <x:v>无ID累计100/10和rate-limit info=null；合法A；缺usage、负input、cached111&gt;input100、total111四条不同ID完整LF行；未知build。</x:v>
+      </x:c>
+      <x:c r="G263" s="4" t="str">
+        <x:v>零可信事件；分别诊断unverified_cumulative、missing_usage，不生成零值事件
+只有A=110一事件；四条负例依次诊断missing_usage、negative_input、invalid_cached、invalid_total；不覆写A
+零新增事件，诊断unsupported_source_version</x:v>
+      </x:c>
+      <x:c r="H263" s="4" t="str">
+        <x:v>准备：无产品DB写入；每例新私有根
+变化：不适用；仅模块事件/诊断返回值
+核验：独立枚举返回的事件数量、数值、诊断代码和数量；仅清理本例owner根</x:v>
+      </x:c>
+      <x:c r="I263" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J263" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K263" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L263" s="4" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:319</x:v>
+      </x:c>
+      <x:c r="M263" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N263" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="264" ht="72" customHeight="1">
+      <x:c r="A264" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B264" s="9" t="str">
+        <x:v>TC-TM003-CORE-03</x:v>
+      </x:c>
+      <x:c r="C264" s="9" t="str">
+        <x:v>公开向量身份去重与冲突</x:v>
+      </x:c>
+      <x:c r="D264" s="9" t="str">
+        <x:v>TASK-TM003-IDENTITY</x:v>
+      </x:c>
+      <x:c r="E264" s="9" t="str">
+        <x:v>source_check</x:v>
+      </x:c>
+      <x:c r="F264" s="9" t="str">
+        <x:v>公开identity-v1测试key；codex/provider-response/shared-call-01的A=100/10/cached20；同ID重放；shared-call-02同usage；shared-call-01冲突999/99；claude_code/provider-message/shared-call-01仅求键。</x:v>
+      </x:c>
+      <x:c r="G264" s="9" t="str">
+        <x:v>一事件total110；键精确为afd67bd0cad0227b3e7b5ac132bb9b3ed492073983b9c16a0c9cc24dd3008051
+重放仍一事件；新ID后两事件，input200/output20/cached40/total220
+首事件不变，诊断identity_conflict；Claude键精确为bf222a85ab2209f72ff82c21b7172c9315448b3e1d5bf4503a3c76b30c46cad1且不向本例产品库添加Claude事件</x:v>
+      </x:c>
+      <x:c r="H264" s="9" t="str">
+        <x:v>准备：创建本例拥有的空临时SQLite；不访问产品profile/Keychain
+变化：仅通过正式模块API插入两条Codex事件与一条冲突诊断
+核验：只读核对来源域唯一约束、两行总量、首行未覆写和诊断；只清理本例owner DB</x:v>
+      </x:c>
+      <x:c r="I264" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J264" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K264" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L264" s="9" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:323</x:v>
+      </x:c>
+      <x:c r="M264" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N264" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G5:G176">
+  <x:conditionalFormatting sqref="G5:G264">
     <x:cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="I5:I176">
+  <x:conditionalFormatting sqref="I5:I264">
     <x:cfRule type="containsText" dxfId="15" priority="4" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="17" priority="6" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="J5:J176">
+  <x:conditionalFormatting sqref="J5:J264">
     <x:cfRule type="containsText" dxfId="18" priority="7" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="19" priority="8" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="20" priority="9" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="M5:M176">
+  <x:conditionalFormatting sqref="M5:M264">
     <x:cfRule type="containsText" dxfId="21" priority="10" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="22" priority="11" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="23" priority="12" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb73f0eb8104442b9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f9309e62ac44ebc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14952,7 +20511,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R105b9c20d4354a21"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0297172083574cbe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15098,7 +20657,7 @@
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="87" customHeight="1">
+    <x:row r="6" ht="117" customHeight="1">
       <x:c r="A6" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
       </x:c>
@@ -15127,7 +20686,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J6" s="9" t="str">
-        <x:v>独立候选 d2db551 门禁 PASS 仅为历史；本地 master 固定 c2911bc 首次最终包门禁 FAIL，精细116项91 PASS/14 FAIL/11 BLOCKED，UPDATE-05签名输入缺失；无正式稳定包，未发布。</x:v>
+        <x:v>开发中，未发布。c291本地master最终包门禁FAIL：116项91 PASS/14 FAIL/11 BLOCKED；9f06cb1修复私有签名输入后开发检查PASS，但新定向App仍FAIL/BLOCKED并有ENOSPC，功能回归未完成。旧d2db551独立候选PASS不转用于新候选。正式发行完整门禁NOT_RUN，无稳定0.1原包。</x:v>
       </x:c>
       <x:c r="K6" s="9" t="str">
         <x:v>旧SwiftUI PR #2 已合并、历史双平台六例PASS；不继承给Electron</x:v>
@@ -15154,7 +20713,7 @@
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="117" customHeight="1">
+    <x:row r="7" ht="192" customHeight="1">
       <x:c r="A7" s="4" t="str">
         <x:v>v0.2.0-20261001T034118Z</x:v>
       </x:c>
@@ -15183,10 +20742,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J7" s="4" t="str">
-        <x:v>0.2设计草稿：3功能点/9 TASK、28父TC/35变体已编制，SOP-008基线与固定程序未完成；需上一实际本机稳定0.1原包；c291本地master首次门禁FAIL和schema 2归档消费者。最终包Keychain身份探针缺隔离测试账号或已实测独立命名空间，相关E2E BLOCKED；产品E2E NOT_RUN、未发布。</x:v>
+        <x:v>设计基线已完成：3功能点、9 TASK、28父TC、35变体。开发工作树已有原生目录面板、加密locator、根FD受限读取、React授权UI及33个固定E2E叶入口（28可执行、5场景摘要）；报告单元59/59、治理473/473、构建PASS。产品E2E因AX trusted=false及隔离标准测试账号不可用BLOCKED，Keychain最终包隔离未证实。本独立文档树未合该代码，机器绑定仍planned；正式发行完整门禁NOT_RUN、未发布。0.2公开配置为version0.2.0/build200及测试高版0.2.1/build201，实际0.2包尚未证明。</x:v>
       </x:c>
       <x:c r="K7" s="4" t="str">
-        <x:v>TM001独立候选d2门禁PASS；本地master整合树尚未完成同树门禁或SOP-020稳定归档，不能继承为0.2升级源；本版无实际产品运行。</x:v>
+        <x:v>TM001独立候选d2门禁PASS只属历史；本地master c2911bc首次最终包门禁FAIL、无SOP-020稳定原包，不能作为0.2升级源；本版无实际产品运行。</x:v>
       </x:c>
       <x:c r="L7" s="4" t="str">
         <x:v>releases/v0.2.0-20261001T034118Z/00-manifest.json</x:v>
@@ -15198,7 +20757,7 @@
         <x:v>未核实同名功能分支SHA/tree读回</x:v>
       </x:c>
       <x:c r="O7" s="4" t="str">
-        <x:v>未来设计草稿；产品E2E未执行，本机稳定包未归档；0.1上游c291门禁FAIL</x:v>
+        <x:v>产品E2E未执行；本机稳定包未归档</x:v>
       </x:c>
       <x:c r="P7" s="4" t="str">
         <x:v>本轮五版稳定后一次受保护PR；待办</x:v>
@@ -15210,25 +20769,193 @@
         <x:v>releases/v0.2.0-20261001T034118Z/01-requirements.md:32</x:v>
       </x:c>
     </x:row>
+    <x:row r="8" ht="117" customHeight="1">
+      <x:c r="A8" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+      <x:c r="B8" s="9" t="str">
+        <x:v>0.3.0</x:v>
+      </x:c>
+      <x:c r="C8" s="17" t="n">
+        <x:v>46296.157546296294</x:v>
+      </x:c>
+      <x:c r="D8" s="9" t="str">
+        <x:v>产品功能</x:v>
+      </x:c>
+      <x:c r="E8" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="F8" s="9" t="str">
+        <x:v>未发布</x:v>
+      </x:c>
+      <x:c r="G8" s="9" t="str">
+        <x:v>internal</x:v>
+      </x:c>
+      <x:c r="H8" s="9" t="str">
+        <x:v>dmg/&lt;release_id&gt;/：正式包仅在本机门禁 PASS 后保存</x:v>
+      </x:c>
+      <x:c r="I8" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J8" s="9" t="str">
+        <x:v>整版draft、未发布。原27条目标TC与3条无授权CORE辅助TC设计固定但程序绑定和运行未完成；CORE切片文档检查PASS，Git提交SHA因主对象库不可见而缺，development_slice_ready仍BLOCKED。TM002授权与产品Keychain依赖未齐，产品E2E未执行；正式发行完整门禁NOT_RUN。</x:v>
+      </x:c>
+      <x:c r="K8" s="9" t="str">
+        <x:v>TM-001 干净源码候选为技术基底；其产品门禁不继承给TM-003</x:v>
+      </x:c>
+      <x:c r="L8" s="9" t="str">
+        <x:v>releases/v0.3.0-20261001T034652Z/00-manifest.json</x:v>
+      </x:c>
+      <x:c r="M8" s="9" t="str">
+        <x:v>releases/v0.3.0-20261001T034652Z/06-iteration-record.md</x:v>
+      </x:c>
+      <x:c r="N8" s="9" t="str">
+        <x:v>未核实同名功能分支SHA/tree读回</x:v>
+      </x:c>
+      <x:c r="O8" s="9" t="str">
+        <x:v>产品E2E未执行；本机稳定包未归档</x:v>
+      </x:c>
+      <x:c r="P8" s="9" t="str">
+        <x:v>本轮五版稳定后一次受保护PR；待办</x:v>
+      </x:c>
+      <x:c r="Q8" s="9" t="str">
+        <x:v>本轮五版稳定及远端master读回后逐版登记；待办</x:v>
+      </x:c>
+      <x:c r="R8" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="132" customHeight="1">
+      <x:c r="A9" s="4" t="str">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+      <x:c r="B9" s="4" t="str">
+        <x:v>0.4.0</x:v>
+      </x:c>
+      <x:c r="C9" s="16" t="n">
+        <x:v>46296.16982638889</x:v>
+      </x:c>
+      <x:c r="D9" s="4" t="str">
+        <x:v>产品功能</x:v>
+      </x:c>
+      <x:c r="E9" s="4" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="F9" s="4" t="str">
+        <x:v>未发布</x:v>
+      </x:c>
+      <x:c r="G9" s="4" t="str">
+        <x:v>internal</x:v>
+      </x:c>
+      <x:c r="H9" s="4" t="str">
+        <x:v>dmg/&lt;release_id&gt;/：仅门禁PASS后放正式DMG</x:v>
+      </x:c>
+      <x:c r="I9" s="15" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J9" s="4" t="str">
+        <x:v>整版draft、未发布。8 TASK、20细TC及四组摘要已登记；纯内存Claude 2.1.126解析器f2c3972覆盖已验证主会话、复制fork、同ID双块及可核实单层Agent，单元36/36、治理452/452PASS。改写UUID、fork-context-ref、嵌套Agent、有效零及授权/身份/SQLite仍缺证据或集成；20条产品TC未执行，正式发行完整门禁NOT_RUN。</x:v>
+      </x:c>
+      <x:c r="K9" s="4" t="str">
+        <x:v>TM004源分支原生零/缺失与nested Agent定向探针仅为研究证据；0.3及此前稳定原包尚未形成，真实升级BLOCKED。</x:v>
+      </x:c>
+      <x:c r="L9" s="4" t="str">
+        <x:v>releases/v0.4.0-20261001T040433Z/00-manifest.json</x:v>
+      </x:c>
+      <x:c r="M9" s="4" t="str">
+        <x:v>releases/v0.4.0-20261001T040433Z/06-iteration-record.md</x:v>
+      </x:c>
+      <x:c r="N9" s="4" t="str">
+        <x:v>未核实同名远端功能分支SHA/tree</x:v>
+      </x:c>
+      <x:c r="O9" s="4" t="str">
+        <x:v>最终包产品E2E未执行；本机稳定包未归档</x:v>
+      </x:c>
+      <x:c r="P9" s="4" t="str">
+        <x:v>全部目标版本稳定后待办</x:v>
+      </x:c>
+      <x:c r="Q9" s="4" t="str">
+        <x:v>远端master读回后逐版待办</x:v>
+      </x:c>
+      <x:c r="R9" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="102" customHeight="1">
+      <x:c r="A10" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+      <x:c r="B10" s="9" t="str">
+        <x:v>0.5.0</x:v>
+      </x:c>
+      <x:c r="C10" s="17" t="n">
+        <x:v>46296.15797453704</x:v>
+      </x:c>
+      <x:c r="D10" s="9" t="str">
+        <x:v>产品功能</x:v>
+      </x:c>
+      <x:c r="E10" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="F10" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="G10" s="9" t="str">
+        <x:v>internal</x:v>
+      </x:c>
+      <x:c r="H10" s="9" t="str">
+        <x:v>dmg/&lt;release_id&gt;/：仅门禁PASS后放正式原名包</x:v>
+      </x:c>
+      <x:c r="I10" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J10" s="9" t="str">
+        <x:v>整版draft、未发布。6 TASK、32父TC、6稳定变体及两组摘要已登记；纯统计语义oracle仅可验证算术/覆盖合同，不证明双来源真实采集。固定产品数据、SQLite/IPC、安装App逐TC绑定未完成；正式发行完整门禁NOT_RUN。</x:v>
+      </x:c>
+      <x:c r="K10" s="9" t="str">
+        <x:v>TM005语义oracle只验证规范化样例；0.4及此前稳定原包尚未形成，真实升级BLOCKED。</x:v>
+      </x:c>
+      <x:c r="L10" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/00-manifest.json</x:v>
+      </x:c>
+      <x:c r="M10" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/06-iteration-record.md</x:v>
+      </x:c>
+      <x:c r="N10" s="9" t="str">
+        <x:v>未核实同名远端功能分支SHA/tree</x:v>
+      </x:c>
+      <x:c r="O10" s="9" t="str">
+        <x:v>最终包产品E2E未执行；本机稳定包未归档</x:v>
+      </x:c>
+      <x:c r="P10" s="9" t="str">
+        <x:v>全部目标版本稳定后待办</x:v>
+      </x:c>
+      <x:c r="Q10" s="9" t="str">
+        <x:v>远端master读回后逐版待办</x:v>
+      </x:c>
+      <x:c r="R10" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="F5:F7">
+  <x:conditionalFormatting sqref="F5:F10">
     <x:cfRule type="containsText" dxfId="30" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="31" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="32" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="J5:J7">
+  <x:conditionalFormatting sqref="J5:J10">
     <x:cfRule type="containsText" dxfId="33" priority="4" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="34" priority="5" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="35" priority="6" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="M5:M7">
+  <x:conditionalFormatting sqref="M5:M10">
     <x:cfRule type="containsText" dxfId="36" priority="7" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="37" priority="8" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="38" priority="9" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra250272c05624546"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d04cecde8da4866"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16307,15 +22034,93 @@
         <x:v>docs/retrospectives/2026-10-01-development-and-governance.md:77</x:v>
       </x:c>
     </x:row>
+    <x:row r="44" ht="132" customHeight="1">
+      <x:c r="A44" s="9" t="str">
+        <x:v>RET-039</x:v>
+      </x:c>
+      <x:c r="B44" s="9" t="str">
+        <x:v>切换当前版本暴露历史用例隐式归属</x:v>
+      </x:c>
+      <x:c r="C44" s="9" t="str">
+        <x:v>TM-002 独立文档分支切到当前 0.2 后，78 条未写 release_id 的 TM-001 历史父用例默认落入 0.2 manifest；补归属后 45 条早期 source.heading 仅存 ID，与原详细文档完整标题不一致。</x:v>
+      </x:c>
+      <x:c r="D44" s="9" t="str">
+        <x:v>核对导出失败清单、0.1/0.2 manifest、用例功能与原文行号；认定为追踪元数据问题，保留 TM-001 既定动作、预期和原始测试结果。</x:v>
+      </x:c>
+      <x:c r="E44" s="9" t="str">
+        <x:v>78 条 TM-001 父用例显式登记来源 0.1 release_id；逐行核对并补齐 45 条精确原文标题；重生用例表并执行导出、文档基线和语义映射检查。</x:v>
+      </x:c>
+      <x:c r="F44" s="9" t="str">
+        <x:v>0.2 分支用例导出 CURRENT（137 父记录/437 父步骤），structure/baseline/quality PASS，TM-002 28 父 TC/35 变体获设计基线；完整治理回归452项中9项旧TM001程序跨版本ERROR，原始检查在 .local/docs-checks/20261001-tm002-baseline/，修复交开发会话。本版产品E2E未执行、未发布。</x:v>
+      </x:c>
+      <x:c r="G44" s="9" t="str">
+        <x:v>跨版本共用机器用例目录要为历史用例显式写来源版本，标题精确回链；切换当前版本时必须实测追踪合同。</x:v>
+      </x:c>
+      <x:c r="H44" s="9" t="str">
+        <x:v>docs/retrospectives/2026-10-01-development-and-governance.md:89</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="72" customHeight="1">
+      <x:c r="A45" s="4" t="str">
+        <x:v>RET-040</x:v>
+      </x:c>
+      <x:c r="B45" s="4" t="str">
+        <x:v>历史用例显式来源与旧治理程序冲突</x:v>
+      </x:c>
+      <x:c r="C45" s="4" t="str">
+        <x:v>切换0.2当前版本后，完整治理452项中9项ERROR；旧程序仍以顶层0.2判定历史TM001变体来源。</x:v>
+      </x:c>
+      <x:c r="D45" s="4" t="str">
+        <x:v>保留首次失败原件，由TM002开发会话修固定程序和负测，文档树拣选后完整重跑。</x:v>
+      </x:c>
+      <x:c r="E45" s="4" t="str">
+        <x:v>ca0c43b按父TC/变体显式release_id校验历史来源并拒绝混合/未来来源；本树拣选为dcf215f。</x:v>
+      </x:c>
+      <x:c r="F45" s="4" t="str">
+        <x:v>完整治理457/457 PASS，日志.local/docs-checks/20261001-remote-checkpoint-docs/governance-after-ca0.log；TM002产品E2E未执行。</x:v>
+      </x:c>
+      <x:c r="G45" s="4" t="str">
+        <x:v>元数据改为显式来源后，所有消费程序都要按该字段校验，当前版本切换须纳入回归。</x:v>
+      </x:c>
+      <x:c r="H45" s="4" t="str">
+        <x:v>docs/retrospectives/2026-10-01-development-and-governance.md:101</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="87" customHeight="1">
+      <x:c r="A46" s="9" t="str">
+        <x:v>RET-041</x:v>
+      </x:c>
+      <x:c r="B46" s="9" t="str">
+        <x:v>0.1本地master首次最终包门禁缺签名输入</x:v>
+      </x:c>
+      <x:c r="C46" s="9" t="str">
+        <x:v>c2911bc最终包门禁FAIL：116原始项91 PASS/14 FAIL/11 BLOCKED，UPDATE-05父项和13变体缺签名输入，0.1稳定原包无法归档。</x:v>
+      </x:c>
+      <x:c r="D46" s="9" t="str">
+        <x:v>核对固定SHA/tree和原件，保留FAIL，不借用独立d2db551候选PASS；交TM001按SOP015修复。</x:v>
+      </x:c>
+      <x:c r="E46" s="9" t="str">
+        <x:v>针对新候选补签名输入与固定回归并完整重跑；文档会话为失败run新建逐例Excel并登记根总表。</x:v>
+      </x:c>
+      <x:c r="F46" s="9" t="str">
+        <x:v>原件在总控整合树.local/gates/tm001-master-gate-c2911bc-20261001T113036Z/；独立结果Excel回读PASS但产品FAIL，78父TC 66 PASS/1 FAIL/11 BLOCKED、38变体25 PASS/13 FAIL；无稳定包。</x:v>
+      </x:c>
+      <x:c r="G46" s="9" t="str">
+        <x:v>独立候选PASS不能移给最终整合树；最终包签名输入须在运行前可用且由机器验证。</x:v>
+      </x:c>
+      <x:c r="H46" s="9" t="str">
+        <x:v>docs/retrospectives/2026-10-01-development-and-governance.md:113</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="F5:F43">
+  <x:conditionalFormatting sqref="F5:F46">
     <x:cfRule type="containsText" dxfId="39" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="40" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="41" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfed032a9b53a4532"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ff906f63aba4039"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TokenMeter项目总表.xlsx
+++ b/TokenMeter项目总表.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="Ra702d9032419454f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="R3ccf785cff824031"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="Rc0e266b44e8e4387"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R2fe9df2ed8484af4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="Ra1d3832d77d44954"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R6b490de23f5b4254"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R73a9f7a1a4ff407e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R61d060e006c441d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="R91607a3954054080"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R18ffc2a61fbe4df2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="Ra9834d7a84304806"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R04a09d8054e24439"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Ra8b6d438e10e4cc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R6744e6d3400e4dbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R2ba2051075b449cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="Rde15358f574c431e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R828cd351cd3f4a6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R9c2d956194f14733"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R1b84a2ea719747e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Ra3337ccae59b4978"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R8b1eb842c9be4df6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R9db3c10219b94070"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1255,7 +1255,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c3c3941a6734fa6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad2356804e564194"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1963,7 +1963,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R966c6dcd4d42499a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c6ce5ad2d3f4c4e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2112,7 +2112,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97878ac8d0cc498c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbabee8887f5246c6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2547,7 +2547,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b83207a825a41b6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb60bcb58940a449d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3594,7 +3594,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd029f162ac214e85"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd30be25a417f4e6e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4701,7 +4701,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39a6e7bac47e4ea0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9ab17abf0d0427a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7486,7 +7486,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec70bb3810934e65"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf769948b070a4b80"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19938,7 +19938,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f9309e62ac44ebc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R912ecfc95f1a4378"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20511,7 +20511,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0297172083574cbe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d8dfb9ad96d493c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20769,7 +20769,7 @@
         <x:v>releases/v0.2.0-20261001T034118Z/01-requirements.md:32</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="117" customHeight="1">
+    <x:row r="8" ht="132" customHeight="1">
       <x:c r="A8" s="9" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
@@ -20798,7 +20798,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J8" s="9" t="str">
-        <x:v>整版draft、未发布。原27条目标TC与3条无授权CORE辅助TC设计固定但程序绑定和运行未完成；CORE切片文档检查PASS，Git提交SHA因主对象库不可见而缺，development_slice_ready仍BLOCKED。TM002授权与产品Keychain依赖未齐，产品E2E未执行；正式发行完整门禁NOT_RUN。</x:v>
+        <x:v>整版draft、未发布。原27条目标TC保留，新增3条无授权CORE辅助TC在恢复新仓库候选7d77d63按SOP-008独立切片判为development_slice_ready；固定程序绑定与实际运行仍缺，30条TM003目标/辅助TC均未获得产品PASS。授权/真实App/服务/Keychain及产品E2E仍BLOCKED，0.3整版baseline和正式发行完整门禁NOT_RUN。</x:v>
       </x:c>
       <x:c r="K8" s="9" t="str">
         <x:v>TM-001 干净源码候选为技术基底；其产品门禁不继承给TM-003</x:v>
@@ -20955,7 +20955,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d04cecde8da4866"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc08e1a26493946c2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22120,7 +22120,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ff906f63aba4039"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra38b2a0da86e45e9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TokenMeter项目总表.xlsx
+++ b/TokenMeter项目总表.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="Rb5afe6a2586a4b5f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Re1dd4dec0fb749e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R1a2d21dd2008419e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R51a27e6f77db4e84"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R3ad0bb6e9b7445bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R56a9d7363c4d46e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R2b0b6fa53b8a4447"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R16e41df402164005"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="R2aa3611019d84305"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R11ad06b80a2f4356"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R60abb8dd0c3e4e3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R04a09d8054e24439"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Ra8b6d438e10e4cc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R6744e6d3400e4dbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R2ba2051075b449cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="Rde15358f574c431e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R828cd351cd3f4a6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R9c2d956194f14733"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R1b84a2ea719747e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Ra3337ccae59b4978"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R8b1eb842c9be4df6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R9db3c10219b94070"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -715,8 +715,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="TMTable4" displayName="TMTable4" ref="A4:J25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:J25"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="TMTable4" displayName="TMTable4" ref="A4:J35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:J35"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="功能编号"/>
     <x:tableColumn id="2" name="层级"/>
@@ -734,8 +734,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="TMTable5" displayName="TMTable5" ref="A4:L48" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:L48"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="TMTable5" displayName="TMTable5" ref="A4:L73" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:L73"/>
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="任务编号"/>
     <x:tableColumn id="2" name="层级"/>
@@ -755,8 +755,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TMTable6" displayName="TMTable6" ref="A4:N176" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:N176"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TMTable6" displayName="TMTable6" ref="A4:N264" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:N264"/>
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="功能编号"/>
     <x:tableColumn id="2" name="用例编号"/>
@@ -799,8 +799,8 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="TMTable8" displayName="TMTable8" ref="A4:R7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:R7"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="TMTable8" displayName="TMTable8" ref="A4:R10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:R10"/>
   <x:tableColumns count="18">
     <x:tableColumn id="1" name="发布编号"/>
     <x:tableColumn id="2" name="版本"/>
@@ -826,8 +826,8 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="TMTable9" displayName="TMTable9" ref="A4:H43" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:H43"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="TMTable9" displayName="TMTable9" ref="A4:H46" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:H46"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="复盘编号"/>
     <x:tableColumn id="2" name="名称"/>
@@ -1066,7 +1066,7 @@
         <x:v>当前版本</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
+        <x:v>v0.2.0-20261001T034118Z</x:v>
       </x:c>
       <x:c r="C5" s="4" t="str">
         <x:v>未发布；版本状态见07发布版本</x:v>
@@ -1101,8 +1101,8 @@
         <x:v>已登记用例</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:f>COUNTA('05测试用例'!B5:B176)</x:f>
-        <x:v>172</x:v>
+        <x:f>COUNTA('05测试用例'!B5:B264)</x:f>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C8" s="9" t="str">
         <x:v>父用例与具有稳定 ID 的变体各占一行；含未来概要场景</x:v>
@@ -1125,7 +1125,7 @@
         <x:v>细化产品用例</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>102</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C10" s="9" t="str">
         <x:v>逐条结果按运行批次记录；稳定变体独立列出</x:v>
@@ -1158,21 +1158,21 @@
         <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="B13" s="10" t="n">
-        <x:v>65</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C13" s="4" t="str">
         <x:v>在05测试用例筛选此状态</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="57" customHeight="1">
+    <x:row r="14" ht="32" customHeight="1">
       <x:c r="A14" s="9" t="str">
         <x:v>最近完整回归</x:v>
       </x:c>
       <x:c r="B14" s="11" t="str">
-        <x:v>FAIL</x:v>
+        <x:v>未执行</x:v>
       </x:c>
       <x:c r="C14" s="9" t="str">
-        <x:v>固定本地master候选门禁FAIL；原始116项91 PASS/14 FAIL/11 BLOCKED，UPDATE-05父项与13变体缺签名输入。逐例模型78父TC 66 PASS/1 FAIL/11 BLOCKED，38变体25 PASS/13 FAIL；无正式稳定包。</x:v>
+        <x:v>尚无完整运行记录</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="42" customHeight="1">
@@ -1255,7 +1255,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde61e33f213f43c0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad2356804e564194"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1455,7 +1455,7 @@
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G10" s="9" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H10" s="9" t="str">
         <x:v>sop/SOP-005-development-plan.md</x:v>
@@ -1481,7 +1481,7 @@
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G11" s="4" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H11" s="4" t="str">
         <x:v>sop/SOP-006-test-plan.md</x:v>
@@ -1507,13 +1507,13 @@
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G12" s="9" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H12" s="9" t="str">
         <x:v>sop/SOP-007-release-plan.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="87" customHeight="1">
+    <x:row r="13" ht="162" customHeight="1">
       <x:c r="A13" s="4" t="str">
         <x:v>SOP-008</x:v>
       </x:c>
@@ -1521,19 +1521,19 @@
         <x:v>SOP-008 基线检查</x:v>
       </x:c>
       <x:c r="C13" s="4" t="str">
-        <x:v>SOP-001–007 的版本计划全部完成、文档/SOP 迁移整合后，或已建基线发生影响实现的变化。单份草稿编制按 SOP-024 检查后返回原步骤。</x:v>
+        <x:v>SOP-001–007的版本计划全部完成、文档/SOP迁移整合后，或已建基线发生影响实现的变化；也可在整版仍draft时，为不依赖未决条件的明确TASK/TC子集建立开发切片。单份草稿编制按SOP-024检查后返回原步骤。</x:v>
       </x:c>
       <x:c r="D13" s="4" t="str">
-        <x:v>SOP-001–007 的档案和内容已齐全，必要元数据和 SOP 已登记；状态为 draft 的内容先解决实际缺项，经内容核对后登记为 baselined。不能为通过检查将未完成内容提前改为 baselined。</x:v>
+        <x:v>整版基线要求SOP-001–007档案和内容齐全，必要元数据和SOP已登记；draft内容先解决实际缺项，不能提前改成baselined。开发切片要求具体TASK/TC的需求、设计、数据、步骤、逐步预期、依赖和非目标均已固定且可独立验证；任何baseline_pending决定若可能改变该切片的预期、身份/权限、安全边界、接口或数据口径，该切片仍BLOCKED。切片不改变整版draft与其他TC的pending状态。</x:v>
       </x:c>
       <x:c r="E13" s="4" t="str">
-        <x:v>结构校验结果、语义一致性记录、完整文档基线或明确未决清单。</x:v>
+        <x:v>结构校验结果、语义一致性记录、整版文档基线或明确未决清单；可选的独立开发切片就绪记录，仍保留整版draft与未决TC。</x:v>
       </x:c>
       <x:c r="F13" s="4" t="str">
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G13" s="4" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H13" s="4" t="str">
         <x:v>sop/SOP-008-baseline-check.md</x:v>
@@ -1611,13 +1611,13 @@
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G16" s="9" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H16" s="9" t="str">
         <x:v>sop/SOP-011-test-implementation.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="132" customHeight="1">
+    <x:row r="17" ht="162" customHeight="1">
       <x:c r="A17" s="4" t="str">
         <x:v>SOP-012</x:v>
       </x:c>
@@ -1628,7 +1628,7 @@
         <x:v>数据和测试准备完成后实施目标业务；或按基线计划推进不依赖当前运行阻塞、具有独立验证条件的子任务。首个工程骨架由 SOP-009 建立。</x:v>
       </x:c>
       <x:c r="D17" s="4" t="str">
-        <x:v>SOP-008 基线有效，文件所有权和现有用户修改已确认。完整业务路径按 SOP-009→010→011 获得可运行骨架、数据/测试绑定和真实行为失败证据后实现。缺工具链时，可先执行开发计划中具有独立验证条件的源码子任务；已编写数据/测试绑定须真实存在，缺失的红测及产品验收保持 BLOCKED，不能凭源码完成关闭这些依赖。</x:v>
+        <x:v>SOP-008整版基线或仅覆盖本TASK/TC且不依赖未决项的开发切片就绪记录有效，文件所有权和现有用户修改已确认。完整业务路径按SOP-009→010→011获得可运行骨架、数据/测试绑定和真实行为失败证据后实现。缺工具链时，可先执行开发计划中具有独立验证条件的源码子任务；已编写数据/测试绑定须真实存在，缺失的红测及产品验收保持BLOCKED，不能凭源码完成关闭这些依赖。</x:v>
       </x:c>
       <x:c r="E17" s="4" t="str">
         <x:v>产品实现、真实测试与数据程序、同步文档和可构建候选变更。</x:v>
@@ -1637,13 +1637,13 @@
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G17" s="4" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H17" s="4" t="str">
         <x:v>sop/SOP-012-development.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="32" customHeight="1">
+    <x:row r="18" ht="42" customHeight="1">
       <x:c r="A18" s="9" t="str">
         <x:v>SOP-013</x:v>
       </x:c>
@@ -1651,7 +1651,7 @@
         <x:v>SOP-013 构建与检查</x:v>
       </x:c>
       <x:c r="C18" s="9" t="str">
-        <x:v>实现/依赖变化后、进入完整E2E前。</x:v>
+        <x:v>实现/依赖变化后、开发功能回归前；正式发布完整E2E前再次针对最终候选执行。</x:v>
       </x:c>
       <x:c r="D18" s="9" t="str">
         <x:v>012实现、009本机运行时和锁文件就绪。</x:v>
@@ -1663,7 +1663,7 @@
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G18" s="9" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H18" s="9" t="str">
         <x:v>sop/SOP-013-build-and-check.md</x:v>
@@ -1677,19 +1677,19 @@
         <x:v>SOP-014 自动 E2E</x:v>
       </x:c>
       <x:c r="C19" s="4" t="str">
-        <x:v>每次迭代、修复及发布候选。</x:v>
+        <x:v>每次功能完成或修复时执行对应固定TC回归；收到用户明确正式发布指令后执行最终候选完整回归。</x:v>
       </x:c>
       <x:c r="D19" s="4" t="str">
         <x:v>009–013、本机GUI、Electron/Playwright及真实服务/隔离DB。TM001 UPDATE-05受控签名变体另需SOP-009/010的显式私有签名输入及原包身份预检；缺前置只阻断依赖用例。</x:v>
       </x:c>
       <x:c r="E19" s="4" t="str">
-        <x:v>完整原始产品结果与清理、独立批次结果Excel，或真实FAIL/BLOCKED及缺失项。</x:v>
+        <x:v>开发阶段的本功能逐TC原始结果、清理和独立批次Excel；正式发布阶段的最终完整并集结果；或真实FAIL/BLOCKED/NOT_RUN及缺失项。</x:v>
       </x:c>
       <x:c r="F19" s="4" t="str">
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G19" s="4" t="n">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="H19" s="4" t="str">
         <x:v>sop/SOP-014-e2e.md</x:v>
@@ -1715,7 +1715,7 @@
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G20" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H20" s="9" t="str">
         <x:v>sop/SOP-015-bugfix.md</x:v>
@@ -1747,7 +1747,7 @@
         <x:v>sop/SOP-016-database-migration.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="102" customHeight="1">
+    <x:row r="22" ht="132" customHeight="1">
       <x:c r="A22" s="9" t="str">
         <x:v>SOP-017</x:v>
       </x:c>
@@ -1755,25 +1755,25 @@
         <x:v>SOP-017 安装包验证</x:v>
       </x:c>
       <x:c r="C22" s="9" t="str">
-        <x:v>内部本地版本准备发行或包/更新器变化。</x:v>
+        <x:v>开发需要可安装预览包，或用户明确启动正式对外发布；包/更新器变化时运行其固定功能TC。</x:v>
       </x:c>
       <x:c r="D22" s="9" t="str">
-        <x:v>007预案、013/014、SOP-019在本地master固定的本版本里程碑SHA/tree、真实本机GUI和稳定本地签名能力。首版验证自身受控高版更新；后续版本真实升级另须有上一版本按SOP-018/020形成、可独立复核的本机正式稳定DMG。</x:v>
+        <x:v>开发预览需007预案、013适用构建条件、可核对源码SHA/tree和受限签名能力；测试包的固定TC另需014所列本机GUI和隔离条件。正式发布另需用户明确指令、019固定最终本地候选SHA/tree、014完整并集，以及上一实际正式稳定包（如已存在）。没有上一稳定源而既定升级TC要求它时，先记BLOCKED并修订基线，不用开发包替代。</x:v>
       </x:c>
       <x:c r="E22" s="9" t="str">
-        <x:v>原始安装包及系统签名、安装/更新/E2E证据；根dmg/&lt;release_id&gt;/的未发布标记便捷副本及摘要核对。</x:v>
+        <x:v>开发阶段的未发布预览包、摘要和适用TC结果；正式发布阶段的最终原包、系统签名、安装/更新/完整E2E证据。</x:v>
       </x:c>
       <x:c r="F22" s="9" t="str">
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G22" s="9" t="n">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H22" s="9" t="str">
         <x:v>sop/SOP-017-package-validation.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="117" customHeight="1">
+    <x:row r="23" ht="162" customHeight="1">
       <x:c r="A23" s="4" t="str">
         <x:v>SOP-018</x:v>
       </x:c>
@@ -1781,25 +1781,25 @@
         <x:v>SOP-018 发布门禁</x:v>
       </x:c>
       <x:c r="C23" s="4" t="str">
-        <x:v>固定最终候选准备内部本地发行。</x:v>
+        <x:v>用户另行明确要求正式对外发布，且最终候选准备发行；开发阶段不启动本门禁。</x:v>
       </x:c>
       <x:c r="D23" s="4" t="str">
-        <x:v>013/014/017真实执行、SOP-019固定的本地master版本里程碑与其干净候选、原始产物齐全。TM001 UPDATE-05依赖的显式签名输入预检及全部真实App变体须分别有原始证据；后续版本的上一实际稳定包及真实升级证据须按SOP-017齐全。远端统一源码推送不是本机门禁的前置。</x:v>
+        <x:v>用户明确的正式发布指令、针对最终候选重新执行并通过的013/014完整跨需求并集与017、SOP-019固定的本地master最终SHA/tree和干净候选、原始产物齐全。TM001 UPDATE-05依赖的显式签名输入预检及全部真实App变体须分别有原始证据；适用的上一实际稳定包及真实升级证据须按SOP-017齐全。开发阶段逐功能回归和远端源码读回不能替代这些前置；远端源码已否登记不决定本机门禁。</x:v>
       </x:c>
       <x:c r="E23" s="4" t="str">
-        <x:v>PASS通行证或明确FAIL/BLOCKED，原始证据保持本地。</x:v>
+        <x:v>正式发布的PASS通行证或明确FAIL/BLOCKED，原始证据保持本地；未启动时记NOT_RUN、无通行证。</x:v>
       </x:c>
       <x:c r="F23" s="4" t="str">
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G23" s="4" t="n">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H23" s="4" t="str">
         <x:v>sop/SOP-018-release-gate.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="327" customHeight="1">
+    <x:row r="24" ht="282" customHeight="1">
       <x:c r="A24" s="9" t="str">
         <x:v>SOP-019</x:v>
       </x:c>
@@ -1807,25 +1807,25 @@
         <x:v>SOP-019 Git 版本追踪</x:v>
       </x:c>
       <x:c r="C24" s="9" t="str">
-        <x:v>开发会话产生需要保存的WIP/候选源码提交；总控完成一个本地整合里程碑并需要远端源码镜像；或全部目标版本完成、需要统一远端master与正式Tag登记。PR只在远端策略要求时作为受控路径。</x:v>
+        <x:v>开发会话产生需要保存的WIP/候选源码提交；总控完成一个本地整合里程碑并需要远端源码镜像；全部目标版本源码完成，需要统一登记远端master；或正式发布PASS后需要登记正式Tag。PR只在远端策略要求时作为受控路径。</x:v>
       </x:c>
       <x:c r="D24" s="9" t="str">
-        <x:v>用户已授权远端Git承担源码版本管理，产品开发、全量测试、打包及发行在本机完成；2026-10-01新增明确要求允许在最终远端master整合前，把可核对源码检查点快进保存到远端功能分支或单一整合镜像分支。每个需求有自己的worktree、codex/&lt;release_id&gt;/&lt;功能名&gt;分支、明确负责人和输入基线；远端推送只针对对应分支，master仍由总控最后统一办理。待推送的源码须有已完成提交、干净工作树、真实检查状态与可核对SHA/tree；WIP允许尚未通过产品测试，但必须如实标记。被测产品版本仍须在**本地master固定里程碑提交**上由固定程序完成本轮与此前已交付功能的完整E2E、SOP-017/018最终包门禁，再按SOP-020形成本机稳定包；远端检查点、PR或Actions结果均不能替代。正式Tag须本机通行证、稳定包归档和最终远端读回。仅规范分支可在结构、基线和治理检查后先行本地整合，记录release_eligible=false。未提交的用户改动不得带入其他会话工作树或整合。</x:v>
+        <x:v>用户已授权远端Git承担源码版本管理，产品开发、测试、打包及发行在本机完成；2026-10-01最新指令将开发阶段限于各功能已基线固定TC回归，全量跨需求E2E及正式发行待用户另行启动。每个需求有自己的worktree、codex/&lt;release_id&gt;/&lt;功能名&gt;分支、明确负责人和输入基线；远端同名分支与单一integration镜像可先保存源码检查点，master由总控最后统一办理。待推送源码须有已完成提交、干净工作树、真实检查状态与可核对SHA/tree；WIP及未通过功能回归均如实标记，不称功能验收或发布PASS。开发里程碑及远端源码登记不以逐版完整E2E、SOP-018通行证或SOP-020稳定包为前置。正式Tag须用户发布指令、最终候选完整门禁PASS、稳定包归档和远端读回。未提交的用户改动不得带入其他会话工作树或整合。</x:v>
       </x:c>
       <x:c r="E24" s="9" t="str">
-        <x:v>各会话独立worktree和已读回的远端源码检查点、可选整合镜像；逐版本地master里程碑及本机门禁/稳定包记录；最终远端master和逐版源码Tag映射。本地索引分别显示“代码已保存”“本机产品/发行状态”“远端master/Tag状态”。</x:v>
+        <x:v>各会话独立worktree和已读回的远端源码检查点、可选整合镜像；逐版本地master开发里程碑及真实功能TC状态；最终远端master源码读回。正式发布另产生最终候选门禁/稳定包和该正式版本Tag映射。本地索引分别显示“代码已保存”“功能回归状态”“正式发行状态”“远端master/Tag状态”。</x:v>
       </x:c>
       <x:c r="F24" s="9" t="str">
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G24" s="9" t="n">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H24" s="9" t="str">
         <x:v>sop/SOP-019-git-release.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="72" customHeight="1">
+    <x:row r="25" ht="87" customHeight="1">
       <x:c r="A25" s="4" t="str">
         <x:v>SOP-020</x:v>
       </x:c>
@@ -1833,10 +1833,10 @@
         <x:v>SOP-020 本地发行归档</x:v>
       </x:c>
       <x:c r="C25" s="4" t="str">
-        <x:v>本机018 PASS，且SOP-019已固定该版本在本地master的不可变SHA/tree与来源追踪；远端master读回和正式Tag可保持待办，不冒充已完成。</x:v>
+        <x:v>用户明确要求正式发布、本机018 PASS，且SOP-019已固定最终候选在本地master的不可变SHA/tree与来源追踪；远端master可能已登记源码，正式Tag仍待本步完成。</x:v>
       </x:c>
       <x:c r="D25" s="4" t="str">
-        <x:v>有效通行证、同一候选原包、本地版本里程碑、独立新目标目录和恢复预案。上一版本尚无正式稳定包时，下一版本依赖真实升级的门禁继续BLOCKED。</x:v>
+        <x:v>有效通行证、同一最终候选原包、本地版本里程碑、独立新目标目录和恢复预案。开发阶段无通行证时本步NOT_RUN；既定升级用例缺上一实际稳定包时正式门禁BLOCKED，不在本步补造。</x:v>
       </x:c>
       <x:c r="E25" s="4" t="str">
         <x:v>本地版本归档、原件校验和、根dmg/&lt;release_id&gt;/正式稳定安装入口、来源SHA/tree及远端待办/后续登记收据。</x:v>
@@ -1845,7 +1845,7 @@
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G25" s="4" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H25" s="4" t="str">
         <x:v>sop/SOP-020-deployment.md</x:v>
@@ -1963,7 +1963,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd45cd8169a394bd3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c6ce5ad2d3f4c4e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2112,7 +2112,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8270c6fe1df14abf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbabee8887f5246c6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2305,7 +2305,7 @@
         <x:v>用量统计</x:v>
       </x:c>
       <x:c r="D9" s="4" t="str">
-        <x:v>今天/昨天/近 7、15、30 天/自定义、趋势、明细、模型维度、缺失提示</x:v>
+        <x:v>Codex 与 Claude Code 双来源原生日志用量统计；日期范围、趋势、明细、模型、身份去重与缺失/零/未知三态</x:v>
       </x:c>
       <x:c r="E9" s="4" t="str">
         <x:v>AC-TM005-001
@@ -2315,10 +2315,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="G9" s="4" t="str">
-        <x:v>规划中</x:v>
+        <x:v>design_in_progress</x:v>
       </x:c>
       <x:c r="H9" s="4" t="str">
-        <x:v>docs/product/README.md:22</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/01-requirements.md</x:v>
       </x:c>
       <x:c r="I9" s="4" t="str">
         <x:v>未提供</x:v>
@@ -2547,7 +2547,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac6c21fbeb0342e2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb60bcb58940a449d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3594,7 +3594,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95ac8888b10f438b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd30be25a417f4e6e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3783,10 +3783,10 @@
         <x:v>0.4.0</x:v>
       </x:c>
       <x:c r="H8" s="9" t="str">
-        <x:v>规划中</x:v>
+        <x:v>开发中</x:v>
       </x:c>
       <x:c r="I8" s="9" t="str">
-        <x:v>docs/product/README.md:21</x:v>
+        <x:v>releases/v0.4.0-20261001T040433Z/02-breakdown.md</x:v>
       </x:c>
       <x:c r="J8" s="9" t="str">
         <x:v>未提供</x:v>
@@ -3806,7 +3806,7 @@
         <x:v>用量统计</x:v>
       </x:c>
       <x:c r="E9" s="4" t="str">
-        <x:v>今天/昨天/近 7、15、30 天/自定义、趋势、明细、模型维度、缺失提示</x:v>
+        <x:v>双来源可信事件、IANA 日界统计、三态覆盖及真实桌面验收</x:v>
       </x:c>
       <x:c r="F9" s="4" t="str">
         <x:v>AC-TM005-001
@@ -3816,10 +3816,10 @@
         <x:v>0.5.0</x:v>
       </x:c>
       <x:c r="H9" s="4" t="str">
-        <x:v>规划中</x:v>
+        <x:v>design_in_progress</x:v>
       </x:c>
       <x:c r="I9" s="4" t="str">
-        <x:v>docs/product/README.md:22</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/02-breakdown.md:10</x:v>
       </x:c>
       <x:c r="J9" s="4" t="str">
         <x:v>未提供</x:v>
@@ -4363,15 +4363,345 @@
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
+    <x:row r="26" ht="42" customHeight="1">
+      <x:c r="A26" s="9" t="str">
+        <x:v>FP-TM003-01</x:v>
+      </x:c>
+      <x:c r="B26" s="9" t="str">
+        <x:v>本轮功能点</x:v>
+      </x:c>
+      <x:c r="C26" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="D26" s="9" t="str">
+        <x:v>Codex 原生来源识别</x:v>
+      </x:c>
+      <x:c r="E26" s="9" t="str">
+        <x:v>只接受经核验的原生记录结构，未知结构可见</x:v>
+      </x:c>
+      <x:c r="F26" s="9" t="str">
+        <x:v>AC-TM003-001
+AC-TM003-002</x:v>
+      </x:c>
+      <x:c r="G26" s="9" t="str">
+        <x:v>0.3.0</x:v>
+      </x:c>
+      <x:c r="H26" s="9" t="str">
+        <x:v>规划中</x:v>
+      </x:c>
+      <x:c r="I26" s="9" t="str">
+        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:11</x:v>
+      </x:c>
+      <x:c r="J26" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="57" customHeight="1">
+      <x:c r="A27" s="4" t="str">
+        <x:v>FP-TM003-02</x:v>
+      </x:c>
+      <x:c r="B27" s="4" t="str">
+        <x:v>本轮功能点</x:v>
+      </x:c>
+      <x:c r="C27" s="4" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="D27" s="4" t="str">
+        <x:v>本地持久采集与去重</x:v>
+      </x:c>
+      <x:c r="E27" s="4" t="str">
+        <x:v>完整行游标、响应身份、累计核对、重启/移动/分支不重计</x:v>
+      </x:c>
+      <x:c r="F27" s="4" t="str">
+        <x:v>AC-TM003-001
+AC-TM003-002
+AC-TM003-003</x:v>
+      </x:c>
+      <x:c r="G27" s="4" t="str">
+        <x:v>0.3.0</x:v>
+      </x:c>
+      <x:c r="H27" s="4" t="str">
+        <x:v>规划中</x:v>
+      </x:c>
+      <x:c r="I27" s="4" t="str">
+        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:12</x:v>
+      </x:c>
+      <x:c r="J27" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="42" customHeight="1">
+      <x:c r="A28" s="9" t="str">
+        <x:v>FP-TM003-03</x:v>
+      </x:c>
+      <x:c r="B28" s="9" t="str">
+        <x:v>本轮功能点</x:v>
+      </x:c>
+      <x:c r="C28" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="D28" s="9" t="str">
+        <x:v>权限和状态</x:v>
+      </x:c>
+      <x:c r="E28" s="9" t="str">
+        <x:v>已确认授权根才读取，失效即停，重新授权后补扫</x:v>
+      </x:c>
+      <x:c r="F28" s="9" t="str">
+        <x:v>AC-TM003-001
+AC-TM003-004</x:v>
+      </x:c>
+      <x:c r="G28" s="9" t="str">
+        <x:v>0.3.0</x:v>
+      </x:c>
+      <x:c r="H28" s="9" t="str">
+        <x:v>规划中</x:v>
+      </x:c>
+      <x:c r="I28" s="9" t="str">
+        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:13</x:v>
+      </x:c>
+      <x:c r="J28" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="72" customHeight="1">
+      <x:c r="A29" s="4" t="str">
+        <x:v>FP-TM003-04</x:v>
+      </x:c>
+      <x:c r="B29" s="4" t="str">
+        <x:v>本轮功能点</x:v>
+      </x:c>
+      <x:c r="C29" s="4" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="D29" s="4" t="str">
+        <x:v>自动验证与交付</x:v>
+      </x:c>
+      <x:c r="E29" s="4" t="str">
+        <x:v>固定数据、逐 TC 产品 E2E、同候选全回归与可追踪档案</x:v>
+      </x:c>
+      <x:c r="F29" s="4" t="str">
+        <x:v>AC-TM003-001
+AC-TM003-002
+AC-TM003-003
+AC-TM003-004</x:v>
+      </x:c>
+      <x:c r="G29" s="4" t="str">
+        <x:v>0.3.0</x:v>
+      </x:c>
+      <x:c r="H29" s="4" t="str">
+        <x:v>规划中</x:v>
+      </x:c>
+      <x:c r="I29" s="4" t="str">
+        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:14</x:v>
+      </x:c>
+      <x:c r="J29" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="42" customHeight="1">
+      <x:c r="A30" s="9" t="str">
+        <x:v>FP-TM005-01</x:v>
+      </x:c>
+      <x:c r="B30" s="9" t="str">
+        <x:v>sub_feature</x:v>
+      </x:c>
+      <x:c r="C30" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="D30" s="9" t="str">
+        <x:v>可信事件</x:v>
+      </x:c>
+      <x:c r="E30" s="9" t="str">
+        <x:v>两来源不可变事件身份、用量子项和冲突诊断</x:v>
+      </x:c>
+      <x:c r="F30" s="9" t="str">
+        <x:v>AC-TM005-001
+AC-TM005-002</x:v>
+      </x:c>
+      <x:c r="G30" s="9" t="str">
+        <x:v>0.5.0</x:v>
+      </x:c>
+      <x:c r="H30" s="9" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="I30" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/02-breakdown.md:10</x:v>
+      </x:c>
+      <x:c r="J30" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="32" customHeight="1">
+      <x:c r="A31" s="4" t="str">
+        <x:v>FP-TM005-02</x:v>
+      </x:c>
+      <x:c r="B31" s="4" t="str">
+        <x:v>sub_feature</x:v>
+      </x:c>
+      <x:c r="C31" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="D31" s="4" t="str">
+        <x:v>范围和汇总</x:v>
+      </x:c>
+      <x:c r="E31" s="4" t="str">
+        <x:v>IANA当地日期、半开UTC范围、汇总/趋势/明细/模型</x:v>
+      </x:c>
+      <x:c r="F31" s="4" t="str">
+        <x:v>AC-TM005-001</x:v>
+      </x:c>
+      <x:c r="G31" s="4" t="str">
+        <x:v>0.5.0</x:v>
+      </x:c>
+      <x:c r="H31" s="4" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="I31" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/02-breakdown.md:11</x:v>
+      </x:c>
+      <x:c r="J31" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="32" customHeight="1">
+      <x:c r="A32" s="9" t="str">
+        <x:v>FP-TM005-03</x:v>
+      </x:c>
+      <x:c r="B32" s="9" t="str">
+        <x:v>sub_feature</x:v>
+      </x:c>
+      <x:c r="C32" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="D32" s="9" t="str">
+        <x:v>三态覆盖</x:v>
+      </x:c>
+      <x:c r="E32" s="9" t="str">
+        <x:v>两来源覆盖证明与缺失、真实零、未知状态</x:v>
+      </x:c>
+      <x:c r="F32" s="9" t="str">
+        <x:v>AC-TM005-002</x:v>
+      </x:c>
+      <x:c r="G32" s="9" t="str">
+        <x:v>0.5.0</x:v>
+      </x:c>
+      <x:c r="H32" s="9" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="I32" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/02-breakdown.md:12</x:v>
+      </x:c>
+      <x:c r="J32" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="32" customHeight="1">
+      <x:c r="A33" s="4" t="str">
+        <x:v>FP-TM005-04</x:v>
+      </x:c>
+      <x:c r="B33" s="4" t="str">
+        <x:v>sub_feature</x:v>
+      </x:c>
+      <x:c r="C33" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="D33" s="4" t="str">
+        <x:v>统计界面</x:v>
+      </x:c>
+      <x:c r="E33" s="4" t="str">
+        <x:v>真实IPC、筛选表单、统计卡片、趋势、明细和模型分组</x:v>
+      </x:c>
+      <x:c r="F33" s="4" t="str">
+        <x:v>AC-TM005-001</x:v>
+      </x:c>
+      <x:c r="G33" s="4" t="str">
+        <x:v>0.5.0</x:v>
+      </x:c>
+      <x:c r="H33" s="4" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="I33" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/02-breakdown.md:13</x:v>
+      </x:c>
+      <x:c r="J33" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="42" customHeight="1">
+      <x:c r="A34" s="9" t="str">
+        <x:v>FP-TM005-05</x:v>
+      </x:c>
+      <x:c r="B34" s="9" t="str">
+        <x:v>sub_feature</x:v>
+      </x:c>
+      <x:c r="C34" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="D34" s="9" t="str">
+        <x:v>原生数据与独立预期</x:v>
+      </x:c>
+      <x:c r="E34" s="9" t="str">
+        <x:v>seed42、受支持原生日志、独立oracle和隔离重置</x:v>
+      </x:c>
+      <x:c r="F34" s="9" t="str">
+        <x:v>AC-TM005-001
+AC-TM005-002</x:v>
+      </x:c>
+      <x:c r="G34" s="9" t="str">
+        <x:v>0.5.0</x:v>
+      </x:c>
+      <x:c r="H34" s="9" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="I34" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/02-breakdown.md:14</x:v>
+      </x:c>
+      <x:c r="J34" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="42" customHeight="1">
+      <x:c r="A35" s="4" t="str">
+        <x:v>FP-TM005-06</x:v>
+      </x:c>
+      <x:c r="B35" s="4" t="str">
+        <x:v>sub_feature</x:v>
+      </x:c>
+      <x:c r="C35" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="D35" s="4" t="str">
+        <x:v>产品用例与门禁</x:v>
+      </x:c>
+      <x:c r="E35" s="4" t="str">
+        <x:v>逐TC固定桌面E2E、原件复核和最终包门禁</x:v>
+      </x:c>
+      <x:c r="F35" s="4" t="str">
+        <x:v>AC-TM005-001
+AC-TM005-002</x:v>
+      </x:c>
+      <x:c r="G35" s="4" t="str">
+        <x:v>0.5.0</x:v>
+      </x:c>
+      <x:c r="H35" s="4" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="I35" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/02-breakdown.md:15</x:v>
+      </x:c>
+      <x:c r="J35" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="H5:H25">
+  <x:conditionalFormatting sqref="H5:H35">
     <x:cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="8" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2bda9dc0360d4d45"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9ab17abf0d0427a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5880,115 +6210,121 @@
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" ht="32" customHeight="1">
+    <x:row r="42" ht="87" customHeight="1">
       <x:c r="A42" s="9" t="str">
-        <x:v>TASK-TM001-PLAN</x:v>
+        <x:v>TASK-TM003-SOURCE</x:v>
       </x:c>
       <x:c r="B42" s="9" t="str">
-        <x:v>历史分组</x:v>
+        <x:v>具体任务</x:v>
       </x:c>
       <x:c r="C42" s="9" t="str">
+        <x:v>FP-TM003-01</x:v>
+      </x:c>
+      <x:c r="D42" s="9" t="str">
+        <x:v>REQ-TM003</x:v>
+      </x:c>
+      <x:c r="E42" s="9" t="str">
+        <x:v>AC-TM003-001
+AC-TM003-002</x:v>
+      </x:c>
+      <x:c r="F42" s="9" t="str">
+        <x:v>官方协议/rollout 来源、受控 Codex CLI 样例；独立</x:v>
+      </x:c>
+      <x:c r="G42" s="9" t="str">
+        <x:v>产物：固定支持版本、原生字段/来源/分支语义清单；样例只在本轮隔离根的 sessions/YYYY/MM/DD/*.jsonl；TM-002 元数据预览不当格式证明；不读真实用户日志
+完成条件：每个宣称支持的版本都有原生结构、字段摘要和复现来源；缺证据保持不支持</x:v>
+      </x:c>
+      <x:c r="H42" s="9" t="str">
+        <x:v>官方协议/rollout 来源、受控 Codex CLI 样例；独立</x:v>
+      </x:c>
+      <x:c r="I42" s="9" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="D42" s="9" t="str">
-        <x:v>REQ-TM001</x:v>
-      </x:c>
-      <x:c r="E42" s="9" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="F42" s="9" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="G42" s="9" t="str">
-        <x:v>六文档、完整追踪、SOP 修正、基线通过</x:v>
-      </x:c>
-      <x:c r="H42" s="9" t="str">
-        <x:v>需求</x:v>
-      </x:c>
-      <x:c r="I42" s="9" t="str">
-        <x:v>TEST-TM001-GOVERNANCE</x:v>
-      </x:c>
       <x:c r="J42" s="9" t="str">
-        <x:v>historical_group_not_minimal_task</x:v>
+        <x:v>规划中</x:v>
       </x:c>
       <x:c r="K42" s="9" t="str">
-        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:9</x:v>
+        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:20</x:v>
       </x:c>
       <x:c r="L42" s="9" t="str">
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" ht="42" customHeight="1">
+    <x:row r="43" ht="87" customHeight="1">
       <x:c r="A43" s="4" t="str">
-        <x:v>TASK-TM001-SERVER</x:v>
+        <x:v>TASK-TM003-FIXTURE</x:v>
       </x:c>
       <x:c r="B43" s="4" t="str">
-        <x:v>历史分组</x:v>
+        <x:v>具体任务</x:v>
       </x:c>
       <x:c r="C43" s="4" t="str">
+        <x:v>FP-TM003-01</x:v>
+      </x:c>
+      <x:c r="D43" s="4" t="str">
+        <x:v>REQ-TM003</x:v>
+      </x:c>
+      <x:c r="E43" s="4" t="str">
+        <x:v>AC-TM003-001
+AC-TM003-003</x:v>
+      </x:c>
+      <x:c r="F43" s="4" t="str">
+        <x:v>SOURCE、SOP-010；独立</x:v>
+      </x:c>
+      <x:c r="G43" s="4" t="str">
+        <x:v>产物：codex_raw 生成/重置程序，在 TM-002 深度/数量上限内造嵌套 .jsonl、同层越界 symlink、半行、重复、冲突、fork、失效组合；独立 expected 与归属清理
+完成条件：固定种子重建同字节输入和 110/660/220/165 等预期，不插入用量表，不触碰真实目录</x:v>
+      </x:c>
+      <x:c r="H43" s="4" t="str">
+        <x:v>SOURCE、SOP-010；独立</x:v>
+      </x:c>
+      <x:c r="I43" s="4" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="D43" s="4" t="str">
-        <x:v>REQ-TM001</x:v>
-      </x:c>
-      <x:c r="E43" s="4" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="F43" s="4" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="G43" s="4" t="str">
-        <x:v>FastAPI/SQLAlchemy/Alembic 工程、真实认证/权限/审计 API；随机可撤销 token 固定30天到期、不滑动，改密/重置/停用撤销旧会话</x:v>
-      </x:c>
-      <x:c r="H43" s="4" t="str">
-        <x:v>计划、数据/测试</x:v>
-      </x:c>
-      <x:c r="I43" s="4" t="str">
-        <x:v>E2E-TM001-001、E2E-TM001-002、E2E-TM001-003</x:v>
-      </x:c>
       <x:c r="J43" s="4" t="str">
-        <x:v>historical_group_not_minimal_task</x:v>
+        <x:v>规划中</x:v>
       </x:c>
       <x:c r="K43" s="4" t="str">
-        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:10</x:v>
+        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:21</x:v>
       </x:c>
       <x:c r="L43" s="4" t="str">
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" ht="42" customHeight="1">
+    <x:row r="44" ht="72" customHeight="1">
       <x:c r="A44" s="9" t="str">
-        <x:v>TASK-TM001-DATA</x:v>
+        <x:v>TASK-TM003-STORE</x:v>
       </x:c>
       <x:c r="B44" s="9" t="str">
-        <x:v>历史分组</x:v>
+        <x:v>具体任务</x:v>
       </x:c>
       <x:c r="C44" s="9" t="str">
+        <x:v>FP-TM003-02</x:v>
+      </x:c>
+      <x:c r="D44" s="9" t="str">
+        <x:v>REQ-TM003</x:v>
+      </x:c>
+      <x:c r="E44" s="9" t="str">
+        <x:v>AC-TM003-001
+AC-TM003-002</x:v>
+      </x:c>
+      <x:c r="F44" s="9" t="str">
+        <x:v>已基线 schema/隐私；依赖 TM-001 Electron 主进程基线</x:v>
+      </x:c>
+      <x:c r="G44" s="9" t="str">
+        <x:v>产物：客户端 SQLite 的事件、游标、诊断、覆盖范围表及事务入口；仅保留白名单字段
+完成条件：来源域内调用键唯一约束、事件+游标原子提交、重启可读、无原文/完整路径</x:v>
+      </x:c>
+      <x:c r="H44" s="9" t="str">
+        <x:v>已基线 schema/隐私；依赖 TM-001 Electron 主进程基线</x:v>
+      </x:c>
+      <x:c r="I44" s="9" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="D44" s="9" t="str">
-        <x:v>REQ-TM001</x:v>
-      </x:c>
-      <x:c r="E44" s="9" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="F44" s="9" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="G44" s="9" t="str">
-        <x:v>独立测试/生产 SQLite 文件、可执行造数 SQL、生产首建管理员、回归账号/独立预期及安全重置；已有生产密码不可被重建覆盖</x:v>
-      </x:c>
-      <x:c r="H44" s="9" t="str">
-        <x:v>计划、工程骨架</x:v>
-      </x:c>
-      <x:c r="I44" s="9" t="str">
-        <x:v>TEST-TM001-SERVER、E2E-TM001-001、E2E-TM001-005</x:v>
-      </x:c>
       <x:c r="J44" s="9" t="str">
-        <x:v>historical_group_not_minimal_task</x:v>
+        <x:v>规划中</x:v>
       </x:c>
       <x:c r="K44" s="9" t="str">
-        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:11</x:v>
+        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:22</x:v>
       </x:c>
       <x:c r="L44" s="9" t="str">
         <x:v>未提供</x:v>
@@ -5996,165 +6332,1161 @@
     </x:row>
     <x:row r="45" ht="72" customHeight="1">
       <x:c r="A45" s="4" t="str">
-        <x:v>TASK-TM001-MAC</x:v>
+        <x:v>TASK-TM003-PARSE</x:v>
       </x:c>
       <x:c r="B45" s="4" t="str">
-        <x:v>历史分组</x:v>
+        <x:v>具体任务</x:v>
       </x:c>
       <x:c r="C45" s="4" t="str">
+        <x:v>FP-TM003-01</x:v>
+      </x:c>
+      <x:c r="D45" s="4" t="str">
+        <x:v>REQ-TM003</x:v>
+      </x:c>
+      <x:c r="E45" s="4" t="str">
+        <x:v>AC-TM003-001
+AC-TM003-002</x:v>
+      </x:c>
+      <x:c r="F45" s="4" t="str">
+        <x:v>SOURCE、FIXTURE；可先独立源码准备</x:v>
+      </x:c>
+      <x:c r="G45" s="4" t="str">
+        <x:v>产物：将完整原生 JSONL 行转换为只含白名单字段的候选用量；检验非负数、子项、UTC、版本、模型
+完成条件：增量、累计、未知/损坏及未知模型分别有确定结果；不从累计字段重复算量</x:v>
+      </x:c>
+      <x:c r="H45" s="4" t="str">
+        <x:v>SOURCE、FIXTURE；可先独立源码准备</x:v>
+      </x:c>
+      <x:c r="I45" s="4" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="D45" s="4" t="str">
-        <x:v>REQ-TM001</x:v>
-      </x:c>
-      <x:c r="E45" s="4" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="F45" s="4" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="G45" s="4" t="str">
-        <x:v>Electron React/TypeScript 登录/改密/主页/管理、默认本机 API/更新源地址与配置管理页的用户覆盖持久化；默认开启可关闭的设备自动登录、按规范化 origin 隔离的受保护凭据文件与内存会话、稳定 UI 标识、Playwright Electron工程</x:v>
-      </x:c>
-      <x:c r="H45" s="4" t="str">
-        <x:v>API 合同、工程骨架</x:v>
-      </x:c>
-      <x:c r="I45" s="4" t="str">
-        <x:v>E2E-TM001-001、E2E-TM001-002、E2E-TM001-003、E2E-TM001-004、E2E-TM001-005、E2E-TM001-006</x:v>
-      </x:c>
       <x:c r="J45" s="4" t="str">
-        <x:v>historical_group_not_minimal_task</x:v>
+        <x:v>规划中</x:v>
       </x:c>
       <x:c r="K45" s="4" t="str">
-        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:12</x:v>
+        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:23</x:v>
       </x:c>
       <x:c r="L45" s="4" t="str">
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" ht="57" customHeight="1">
+    <x:row r="46" ht="72" customHeight="1">
       <x:c r="A46" s="9" t="str">
-        <x:v>TASK-TM001-UPDATE</x:v>
+        <x:v>TASK-TM003-IDENTITY</x:v>
       </x:c>
       <x:c r="B46" s="9" t="str">
-        <x:v>历史分组</x:v>
+        <x:v>具体任务</x:v>
       </x:c>
       <x:c r="C46" s="9" t="str">
+        <x:v>FP-TM003-02</x:v>
+      </x:c>
+      <x:c r="D46" s="9" t="str">
+        <x:v>REQ-TM003</x:v>
+      </x:c>
+      <x:c r="E46" s="9" t="str">
+        <x:v>AC-TM003-002</x:v>
+      </x:c>
+      <x:c r="F46" s="9" t="str">
+        <x:v>PARSE、STORE；独立于 UI</x:v>
+      </x:c>
+      <x:c r="G46" s="9" t="str">
+        <x:v>产物：版本固定的来源域+原生调用 ID 本机 HMAC、同 ID 冲突/不明重用诊断、fork 继承边界与重放处理；共享事件字段与 TM-004 合同一致
+完成条件：同来源同 ID 重放计一次，跨来源同字面 ID 不冲突；无可证实的跨 Agent/会话重用标覆盖不完整；方案升级不能使旧日志双计</x:v>
+      </x:c>
+      <x:c r="H46" s="9" t="str">
+        <x:v>PARSE、STORE；独立于 UI</x:v>
+      </x:c>
+      <x:c r="I46" s="9" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="D46" s="9" t="str">
-        <x:v>REQ-TM001</x:v>
-      </x:c>
-      <x:c r="E46" s="9" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="F46" s="9" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="G46" s="9" t="str">
-        <x:v>固定 Ed25519 公钥、同机回环更新源/签名测试包/失败包及真实更新用例；默认49177配置、URL安全校验与升级时锁定更新设置；两构建沿用经校验的同一隔离profile，升级后服务验证自动登录</x:v>
-      </x:c>
-      <x:c r="H46" s="9" t="str">
-        <x:v>Mac 工程</x:v>
-      </x:c>
-      <x:c r="I46" s="9" t="str">
-        <x:v>E2E-TM001-004</x:v>
-      </x:c>
       <x:c r="J46" s="9" t="str">
-        <x:v>historical_group_not_minimal_task</x:v>
+        <x:v>规划中</x:v>
       </x:c>
       <x:c r="K46" s="9" t="str">
-        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:13</x:v>
+        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:24</x:v>
       </x:c>
       <x:c r="L46" s="9" t="str">
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="47" ht="57" customHeight="1">
+    <x:row r="47" ht="87" customHeight="1">
       <x:c r="A47" s="4" t="str">
-        <x:v>TASK-TM001-RUNNER</x:v>
+        <x:v>TASK-TM003-SCAN</x:v>
       </x:c>
       <x:c r="B47" s="4" t="str">
-        <x:v>历史分组</x:v>
+        <x:v>具体任务</x:v>
       </x:c>
       <x:c r="C47" s="4" t="str">
+        <x:v>FP-TM003-02</x:v>
+      </x:c>
+      <x:c r="D47" s="4" t="str">
+        <x:v>REQ-TM003</x:v>
+      </x:c>
+      <x:c r="E47" s="4" t="str">
+        <x:v>AC-TM003-001
+AC-TM003-003
+AC-TM003-004</x:v>
+      </x:c>
+      <x:c r="F47" s="4" t="str">
+        <x:v>PARSE、IDENTITY、STORE、AUTH</x:v>
+      </x:c>
+      <x:c r="G47" s="4" t="str">
+        <x:v>产物：限定授权根的可续扫内部分页枚举、完成/截断/取消状态、完整行游标、文件变化/30 秒补扫/手动刷新、移动/截断恢复；不把 UI 预览上限当全量
+完成条件：半行不前进、补全一次入库；超预览上限后仍能读到授权根末端用量并仅在全量完成时清除不完整提示；移动/重启/截断不重计，目录外与越界符号链接不可读</x:v>
+      </x:c>
+      <x:c r="H47" s="4" t="str">
+        <x:v>PARSE、IDENTITY、STORE、AUTH</x:v>
+      </x:c>
+      <x:c r="I47" s="4" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="D47" s="4" t="str">
-        <x:v>REQ-TM001</x:v>
-      </x:c>
-      <x:c r="E47" s="4" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="F47" s="4" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="G47" s="4" t="str">
-        <x:v>本机Playwright从最终DMG安装App执行全部六例，原始JSON/trace/fixtureSQL/包摘要、父门禁复核；默认值与动态独占端口隔离测试；真实Squirrel自重启及profile、身份恢复</x:v>
-      </x:c>
-      <x:c r="H47" s="4" t="str">
-        <x:v>数据/桌面工程</x:v>
-      </x:c>
-      <x:c r="I47" s="4" t="str">
-        <x:v>E2E-TM001-001、E2E-TM001-002、E2E-TM001-003、E2E-TM001-004、E2E-TM001-005、E2E-TM001-006</x:v>
-      </x:c>
       <x:c r="J47" s="4" t="str">
-        <x:v>historical_group_not_minimal_task</x:v>
+        <x:v>规划中</x:v>
       </x:c>
       <x:c r="K47" s="4" t="str">
-        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:14</x:v>
+        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:25</x:v>
       </x:c>
       <x:c r="L47" s="4" t="str">
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" ht="32" customHeight="1">
+    <x:row r="48" ht="72" customHeight="1">
       <x:c r="A48" s="9" t="str">
-        <x:v>TASK-TM001-REVIEW</x:v>
+        <x:v>TASK-TM003-AUTH</x:v>
       </x:c>
       <x:c r="B48" s="9" t="str">
-        <x:v>历史分组</x:v>
+        <x:v>具体任务</x:v>
       </x:c>
       <x:c r="C48" s="9" t="str">
+        <x:v>FP-TM003-03</x:v>
+      </x:c>
+      <x:c r="D48" s="9" t="str">
+        <x:v>REQ-TM003</x:v>
+      </x:c>
+      <x:c r="E48" s="9" t="str">
+        <x:v>AC-TM003-004</x:v>
+      </x:c>
+      <x:c r="F48" s="9" t="str">
+        <x:v>TM-002 稳定提交及接口，**BLOCKED**</x:v>
+      </x:c>
+      <x:c r="G48" s="9" t="str">
+        <x:v>产物：经 TM-002 可替换只读能力获取确认来源及已验证 origin+account.id，接收失效/撤销/身份切换通知；仅主进程读日志
+完成条件：确认前/失效/身份切换时无旧能力读取；不同主体事件与游标隔离，重新确认后仅本主体补扫</x:v>
+      </x:c>
+      <x:c r="H48" s="9" t="str">
+        <x:v>TM-002 稳定提交及接口，**BLOCKED**</x:v>
+      </x:c>
+      <x:c r="I48" s="9" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="D48" s="9" t="str">
-        <x:v>REQ-TM001</x:v>
-      </x:c>
-      <x:c r="E48" s="9" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="F48" s="9" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="G48" s="9" t="str">
-        <x:v>完整回归、流程复盘、PR 与合并判定、发布阻塞记录</x:v>
-      </x:c>
-      <x:c r="H48" s="9" t="str">
-        <x:v>全部实现任务</x:v>
-      </x:c>
-      <x:c r="I48" s="9" t="str">
-        <x:v>TEST-TM001-GOVERNANCE</x:v>
-      </x:c>
       <x:c r="J48" s="9" t="str">
-        <x:v>historical_group_not_minimal_task</x:v>
+        <x:v>规划中</x:v>
       </x:c>
       <x:c r="K48" s="9" t="str">
-        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:15</x:v>
+        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:26</x:v>
       </x:c>
       <x:c r="L48" s="9" t="str">
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
+    <x:row r="49" ht="57" customHeight="1">
+      <x:c r="A49" s="4" t="str">
+        <x:v>TASK-TM003-UI</x:v>
+      </x:c>
+      <x:c r="B49" s="4" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C49" s="4" t="str">
+        <x:v>FP-TM003-03</x:v>
+      </x:c>
+      <x:c r="D49" s="4" t="str">
+        <x:v>REQ-TM003</x:v>
+      </x:c>
+      <x:c r="E49" s="4" t="str">
+        <x:v>AC-TM003-001
+AC-TM003-003</x:v>
+      </x:c>
+      <x:c r="F49" s="4" t="str">
+        <x:v>STORE、SCAN、AUTH，**BLOCKED**</x:v>
+      </x:c>
+      <x:c r="G49" s="4" t="str">
+        <x:v>产物：React 最小采集卡片与诊断，受限 preload/IPC，无任意路径参数
+完成条件：显示可信总量、cached 子项、覆盖起点、未知/失效/最后采集；UI 手动刷新真实驱动主进程</x:v>
+      </x:c>
+      <x:c r="H49" s="4" t="str">
+        <x:v>STORE、SCAN、AUTH，**BLOCKED**</x:v>
+      </x:c>
+      <x:c r="I49" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J49" s="4" t="str">
+        <x:v>规划中</x:v>
+      </x:c>
+      <x:c r="K49" s="4" t="str">
+        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:27</x:v>
+      </x:c>
+      <x:c r="L49" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="57" customHeight="1">
+      <x:c r="A50" s="9" t="str">
+        <x:v>TASK-TM003-MIGRATE</x:v>
+      </x:c>
+      <x:c r="B50" s="9" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C50" s="9" t="str">
+        <x:v>FP-TM003-02</x:v>
+      </x:c>
+      <x:c r="D50" s="9" t="str">
+        <x:v>REQ-TM003</x:v>
+      </x:c>
+      <x:c r="E50" s="9" t="str">
+        <x:v>AC-TM003-001
+AC-TM003-003</x:v>
+      </x:c>
+      <x:c r="F50" s="9" t="str">
+        <x:v>STORE、TM-001 已分发稳定包状态，**BLOCKED**</x:v>
+      </x:c>
+      <x:c r="G50" s="9" t="str">
+        <x:v>产物：新客户端 SQLite schema 的事务迁移、备份/恢复和旧版启动兼容
+完成条件：源/目标 schema、聚合和中断恢复由 SOP-016 在隔离库验证；无稳定旧包时记录该事实</x:v>
+      </x:c>
+      <x:c r="H50" s="9" t="str">
+        <x:v>STORE、TM-001 已分发稳定包状态，**BLOCKED**</x:v>
+      </x:c>
+      <x:c r="I50" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J50" s="9" t="str">
+        <x:v>规划中</x:v>
+      </x:c>
+      <x:c r="K50" s="9" t="str">
+        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:28</x:v>
+      </x:c>
+      <x:c r="L50" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="72" customHeight="1">
+      <x:c r="A51" s="4" t="str">
+        <x:v>TASK-TM003-E2E</x:v>
+      </x:c>
+      <x:c r="B51" s="4" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C51" s="4" t="str">
+        <x:v>FP-TM003-04</x:v>
+      </x:c>
+      <x:c r="D51" s="4" t="str">
+        <x:v>REQ-TM003</x:v>
+      </x:c>
+      <x:c r="E51" s="4" t="str">
+        <x:v>AC-TM003-001
+AC-TM003-002
+AC-TM003-003
+AC-TM003-004</x:v>
+      </x:c>
+      <x:c r="F51" s="4" t="str">
+        <x:v>FIXTURE、UI、TM-001/002 稳定产品与隔离 GUI 资源，**BLOCKED**</x:v>
+      </x:c>
+      <x:c r="G51" s="4" t="str">
+        <x:v>产物：扩展当前仅 TM-001 的 runner、逐 TC Playwright Electron 测试、每步原件与跨版本完整集合机器门禁；四场景组作补充
+完成条件：每条本版 TC 可独立调用；门禁拒绝缺任一本版/历史 TC、变体或步骤的原件；最终 DMG 安装后真实 UI/IPC/SQLite 与全部历史功能同批完整通过</x:v>
+      </x:c>
+      <x:c r="H51" s="4" t="str">
+        <x:v>FIXTURE、UI、TM-001/002 稳定产品与隔离 GUI 资源，**BLOCKED**</x:v>
+      </x:c>
+      <x:c r="I51" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J51" s="4" t="str">
+        <x:v>规划中</x:v>
+      </x:c>
+      <x:c r="K51" s="4" t="str">
+        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:29</x:v>
+      </x:c>
+      <x:c r="L51" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="72" customHeight="1">
+      <x:c r="A52" s="9" t="str">
+        <x:v>TASK-TM003-RELEASE</x:v>
+      </x:c>
+      <x:c r="B52" s="9" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C52" s="9" t="str">
+        <x:v>FP-TM003-04</x:v>
+      </x:c>
+      <x:c r="D52" s="9" t="str">
+        <x:v>REQ-TM003</x:v>
+      </x:c>
+      <x:c r="E52" s="9" t="str">
+        <x:v>AC-TM003-001
+AC-TM003-002
+AC-TM003-003
+AC-TM003-004</x:v>
+      </x:c>
+      <x:c r="F52" s="9" t="str">
+        <x:v>全部任务、SOP-013/014/017/018</x:v>
+      </x:c>
+      <x:c r="G52" s="9" t="str">
+        <x:v>产物：本版文档、总表、Changelog、源码交接、候选与本机档案
+完成条件：清单/Excel回读、实际结果和候选一致；门禁 PASS 才正式 tag/DMG，否则准确 BLOCKED</x:v>
+      </x:c>
+      <x:c r="H52" s="9" t="str">
+        <x:v>全部任务、SOP-013/014/017/018</x:v>
+      </x:c>
+      <x:c r="I52" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J52" s="9" t="str">
+        <x:v>规划中</x:v>
+      </x:c>
+      <x:c r="K52" s="9" t="str">
+        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:30</x:v>
+      </x:c>
+      <x:c r="L52" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="72" customHeight="1">
+      <x:c r="A53" s="4" t="str">
+        <x:v>TASK-TM004-SOURCE</x:v>
+      </x:c>
+      <x:c r="B53" s="4" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C53" s="4" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="D53" s="4" t="str">
+        <x:v>REQ-TM004</x:v>
+      </x:c>
+      <x:c r="E53" s="4" t="str">
+        <x:v>AC-TM004-001
+AC-TM004-002
+AC-TM004-003
+AC-TM004-004</x:v>
+      </x:c>
+      <x:c r="F53" s="4" t="str">
+        <x:v>TM-002授权句柄、项目目录</x:v>
+      </x:c>
+      <x:c r="G53" s="4" t="str">
+        <x:v>只遍历授权根下已确认的主/子日志；失权停扫、重授补扫；越界拒绝；预览与采集分别判定</x:v>
+      </x:c>
+      <x:c r="H53" s="4" t="str">
+        <x:v>TM-002授权接口及可续扫合同</x:v>
+      </x:c>
+      <x:c r="I53" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J53" s="4" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="K53" s="4" t="str">
+        <x:v>releases/v0.4.0-20261001T040433Z/02-breakdown.md</x:v>
+      </x:c>
+      <x:c r="L53" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="72" customHeight="1">
+      <x:c r="A54" s="9" t="str">
+        <x:v>TASK-TM004-PARSER</x:v>
+      </x:c>
+      <x:c r="B54" s="9" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C54" s="9" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="D54" s="9" t="str">
+        <x:v>REQ-TM004</x:v>
+      </x:c>
+      <x:c r="E54" s="9" t="str">
+        <x:v>AC-TM004-001
+AC-TM004-002
+AC-TM004-003
+AC-TM004-004</x:v>
+      </x:c>
+      <x:c r="F54" s="9" t="str">
+        <x:v>版本来源明确的完整原始行</x:v>
+      </x:c>
+      <x:c r="G54" s="9" t="str">
+        <x:v>抽取usage、模型、UTC时间、主/子标志及来源标识；不保留正文</x:v>
+      </x:c>
+      <x:c r="H54" s="9" t="str">
+        <x:v>raw样本、TM-003事件合同</x:v>
+      </x:c>
+      <x:c r="I54" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J54" s="9" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="K54" s="9" t="str">
+        <x:v>releases/v0.4.0-20261001T040433Z/02-breakdown.md</x:v>
+      </x:c>
+      <x:c r="L54" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="72" customHeight="1">
+      <x:c r="A55" s="4" t="str">
+        <x:v>TASK-TM004-LINEAGE</x:v>
+      </x:c>
+      <x:c r="B55" s="4" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C55" s="4" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="D55" s="4" t="str">
+        <x:v>REQ-TM004</x:v>
+      </x:c>
+      <x:c r="E55" s="4" t="str">
+        <x:v>AC-TM004-001
+AC-TM004-002
+AC-TM004-003
+AC-TM004-004</x:v>
+      </x:c>
+      <x:c r="F55" s="4" t="str">
+        <x:v>父子与fork来源证据</x:v>
+      </x:c>
+      <x:c r="G55" s="4" t="str">
+        <x:v>证实父子关系时正确归属；证实继承历史时跨会话去重；歧义诊断且不污染可信量</x:v>
+      </x:c>
+      <x:c r="H55" s="4" t="str">
+        <x:v>raw父子/fork样本、PARSER</x:v>
+      </x:c>
+      <x:c r="I55" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J55" s="4" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="K55" s="4" t="str">
+        <x:v>releases/v0.4.0-20261001T040433Z/02-breakdown.md</x:v>
+      </x:c>
+      <x:c r="L55" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="72" customHeight="1">
+      <x:c r="A56" s="9" t="str">
+        <x:v>TASK-TM004-INCREMENTAL</x:v>
+      </x:c>
+      <x:c r="B56" s="9" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C56" s="9" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="D56" s="9" t="str">
+        <x:v>REQ-TM004</x:v>
+      </x:c>
+      <x:c r="E56" s="9" t="str">
+        <x:v>AC-TM004-001
+AC-TM004-002
+AC-TM004-003
+AC-TM004-004</x:v>
+      </x:c>
+      <x:c r="F56" s="9" t="str">
+        <x:v>追加、半行、重复片段、跨来源ID、重启</x:v>
+      </x:c>
+      <x:c r="G56" s="9" t="str">
+        <x:v>持久游标、唯一键及事务；完整行才提交；跨来源不误去重；重扫幂等</x:v>
+      </x:c>
+      <x:c r="H56" s="9" t="str">
+        <x:v>TM-003 SQLite身份合同、PARSER</x:v>
+      </x:c>
+      <x:c r="I56" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J56" s="9" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="K56" s="9" t="str">
+        <x:v>releases/v0.4.0-20261001T040433Z/02-breakdown.md</x:v>
+      </x:c>
+      <x:c r="L56" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="72" customHeight="1">
+      <x:c r="A57" s="4" t="str">
+        <x:v>TASK-TM004-DIAGNOSTIC</x:v>
+      </x:c>
+      <x:c r="B57" s="4" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C57" s="4" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="D57" s="4" t="str">
+        <x:v>REQ-TM004</x:v>
+      </x:c>
+      <x:c r="E57" s="4" t="str">
+        <x:v>AC-TM004-001
+AC-TM004-002
+AC-TM004-003
+AC-TM004-004</x:v>
+      </x:c>
+      <x:c r="F57" s="4" t="str">
+        <x:v>缺usage、未知格式、读取失败</x:v>
+      </x:c>
+      <x:c r="G57" s="4" t="str">
+        <x:v>UI区分可信零、未知、缺失、无授权；诊断不泄露正文或完整路径</x:v>
+      </x:c>
+      <x:c r="H57" s="4" t="str">
+        <x:v>TM-003诊断接口、PARSER</x:v>
+      </x:c>
+      <x:c r="I57" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J57" s="4" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="K57" s="4" t="str">
+        <x:v>releases/v0.4.0-20261001T040433Z/02-breakdown.md</x:v>
+      </x:c>
+      <x:c r="L57" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="72" customHeight="1">
+      <x:c r="A58" s="9" t="str">
+        <x:v>TASK-TM004-DATA</x:v>
+      </x:c>
+      <x:c r="B58" s="9" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C58" s="9" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="D58" s="9" t="str">
+        <x:v>REQ-TM004</x:v>
+      </x:c>
+      <x:c r="E58" s="9" t="str">
+        <x:v>AC-TM004-001
+AC-TM004-002
+AC-TM004-003
+AC-TM004-004</x:v>
+      </x:c>
+      <x:c r="F58" s="9" t="str">
+        <x:v>隔离Claude Code 2.1.126原生投影与合成反例</x:v>
+      </x:c>
+      <x:c r="G58" s="9" t="str">
+        <x:v>版本化fixture生成、追加/半行/撤权程序、独立expected及SQLite只读检查</x:v>
+      </x:c>
+      <x:c r="H58" s="9" t="str">
+        <x:v>raw来源、TM-002/003数据合同</x:v>
+      </x:c>
+      <x:c r="I58" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J58" s="9" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="K58" s="9" t="str">
+        <x:v>releases/v0.4.0-20261001T040433Z/02-breakdown.md</x:v>
+      </x:c>
+      <x:c r="L58" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="72" customHeight="1">
+      <x:c r="A59" s="4" t="str">
+        <x:v>TASK-TM004-E2E</x:v>
+      </x:c>
+      <x:c r="B59" s="4" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C59" s="4" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="D59" s="4" t="str">
+        <x:v>REQ-TM004</x:v>
+      </x:c>
+      <x:c r="E59" s="4" t="str">
+        <x:v>AC-TM004-001
+AC-TM004-002
+AC-TM004-003
+AC-TM004-004</x:v>
+      </x:c>
+      <x:c r="F59" s="4" t="str">
+        <x:v>最终安装App、真实服务、隔离SQLite</x:v>
+      </x:c>
+      <x:c r="G59" s="4" t="str">
+        <x:v>全部细TC绑定固定Playwright Electron测试；逐步原始记录及历史功能全量回归</x:v>
+      </x:c>
+      <x:c r="H59" s="4" t="str">
+        <x:v>SOURCE→DATA、TM-001包执行器</x:v>
+      </x:c>
+      <x:c r="I59" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J59" s="4" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="K59" s="4" t="str">
+        <x:v>releases/v0.4.0-20261001T040433Z/02-breakdown.md</x:v>
+      </x:c>
+      <x:c r="L59" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="72" customHeight="1">
+      <x:c r="A60" s="9" t="str">
+        <x:v>TASK-TM004-RELEASE</x:v>
+      </x:c>
+      <x:c r="B60" s="9" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C60" s="9" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="D60" s="9" t="str">
+        <x:v>REQ-TM004</x:v>
+      </x:c>
+      <x:c r="E60" s="9" t="str">
+        <x:v>AC-TM004-001
+AC-TM004-002
+AC-TM004-003
+AC-TM004-004</x:v>
+      </x:c>
+      <x:c r="F60" s="9" t="str">
+        <x:v>完整候选</x:v>
+      </x:c>
+      <x:c r="G60" s="9" t="str">
+        <x:v>文档、矩阵、总表、Changelog同步；DMG安装门禁；交总控集成</x:v>
+      </x:c>
+      <x:c r="H60" s="9" t="str">
+        <x:v>E2E与此前版本全回归</x:v>
+      </x:c>
+      <x:c r="I60" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J60" s="9" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="K60" s="9" t="str">
+        <x:v>releases/v0.4.0-20261001T040433Z/02-breakdown.md</x:v>
+      </x:c>
+      <x:c r="L60" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="42" customHeight="1">
+      <x:c r="A61" s="4" t="str">
+        <x:v>TASK-TM005-EVENT-CONTRACT</x:v>
+      </x:c>
+      <x:c r="B61" s="4" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C61" s="4" t="str">
+        <x:v>FP-TM005-01</x:v>
+      </x:c>
+      <x:c r="D61" s="4" t="str">
+        <x:v>REQ-TM005</x:v>
+      </x:c>
+      <x:c r="E61" s="4" t="str">
+        <x:v>AC-TM005-001
+AC-TM005-002</x:v>
+      </x:c>
+      <x:c r="F61" s="4" t="str">
+        <x:v>TM-003/004稳定事件schema与诊断</x:v>
+      </x:c>
+      <x:c r="G61" s="4" t="str">
+        <x:v>本账号可信事件集合；重复不入账、冲突不静默完成</x:v>
+      </x:c>
+      <x:c r="H61" s="4" t="str">
+        <x:v>TM-003/004 schema与原生版本</x:v>
+      </x:c>
+      <x:c r="I61" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J61" s="4" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="K61" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/02-breakdown.md:10</x:v>
+      </x:c>
+      <x:c r="L61" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="32" customHeight="1">
+      <x:c r="A62" s="9" t="str">
+        <x:v>TASK-TM005-RANGE-QUERY</x:v>
+      </x:c>
+      <x:c r="B62" s="9" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C62" s="9" t="str">
+        <x:v>FP-TM005-02</x:v>
+      </x:c>
+      <x:c r="D62" s="9" t="str">
+        <x:v>REQ-TM005</x:v>
+      </x:c>
+      <x:c r="E62" s="9" t="str">
+        <x:v>AC-TM005-001</x:v>
+      </x:c>
+      <x:c r="F62" s="9" t="str">
+        <x:v>可信事件、当地日期与IANA时区</x:v>
+      </x:c>
+      <x:c r="G62" s="9" t="str">
+        <x:v>同一只读事务的汇总、逐日点、明细与模型分组；DST日界正确</x:v>
+      </x:c>
+      <x:c r="H62" s="9" t="str">
+        <x:v>稳定事件表</x:v>
+      </x:c>
+      <x:c r="I62" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J62" s="9" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="K62" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/02-breakdown.md:11</x:v>
+      </x:c>
+      <x:c r="L62" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="32" customHeight="1">
+      <x:c r="A63" s="4" t="str">
+        <x:v>TASK-TM005-COVERAGE</x:v>
+      </x:c>
+      <x:c r="B63" s="4" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C63" s="4" t="str">
+        <x:v>FP-TM005-03</x:v>
+      </x:c>
+      <x:c r="D63" s="4" t="str">
+        <x:v>REQ-TM005</x:v>
+      </x:c>
+      <x:c r="E63" s="4" t="str">
+        <x:v>AC-TM005-002</x:v>
+      </x:c>
+      <x:c r="F63" s="4" t="str">
+        <x:v>来源覆盖证明、诊断和未知字段</x:v>
+      </x:c>
+      <x:c r="G63" s="4" t="str">
+        <x:v>缺失、零、未知三态；无覆盖不能判零</x:v>
+      </x:c>
+      <x:c r="H63" s="4" t="str">
+        <x:v>TM-003/004覆盖合同</x:v>
+      </x:c>
+      <x:c r="I63" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J63" s="4" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="K63" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/02-breakdown.md:12</x:v>
+      </x:c>
+      <x:c r="L63" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="32" customHeight="1">
+      <x:c r="A64" s="9" t="str">
+        <x:v>TASK-TM005-UI</x:v>
+      </x:c>
+      <x:c r="B64" s="9" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C64" s="9" t="str">
+        <x:v>FP-TM005-04</x:v>
+      </x:c>
+      <x:c r="D64" s="9" t="str">
+        <x:v>REQ-TM005</x:v>
+      </x:c>
+      <x:c r="E64" s="9" t="str">
+        <x:v>AC-TM005-001</x:v>
+      </x:c>
+      <x:c r="F64" s="9" t="str">
+        <x:v>受限统计IPC结果</x:v>
+      </x:c>
+      <x:c r="G64" s="9" t="str">
+        <x:v>真实桌面统计视图；空/倒置日期拒绝、重启保持</x:v>
+      </x:c>
+      <x:c r="H64" s="9" t="str">
+        <x:v>真实IPC/客户端SQLite</x:v>
+      </x:c>
+      <x:c r="I64" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J64" s="9" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="K64" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/02-breakdown.md:13</x:v>
+      </x:c>
+      <x:c r="L64" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="42" customHeight="1">
+      <x:c r="A65" s="4" t="str">
+        <x:v>TASK-TM005-DATA</x:v>
+      </x:c>
+      <x:c r="B65" s="4" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C65" s="4" t="str">
+        <x:v>FP-TM005-05</x:v>
+      </x:c>
+      <x:c r="D65" s="4" t="str">
+        <x:v>REQ-TM005</x:v>
+      </x:c>
+      <x:c r="E65" s="4" t="str">
+        <x:v>AC-TM005-001
+AC-TM005-002</x:v>
+      </x:c>
+      <x:c r="F65" s="4" t="str">
+        <x:v>seed42、参考时钟与两来源已验证原生日志</x:v>
+      </x:c>
+      <x:c r="G65" s="4" t="str">
+        <x:v>独立expected及隔离账号/库/目录重置；不直接SQL灌统计事件</x:v>
+      </x:c>
+      <x:c r="H65" s="4" t="str">
+        <x:v>TM-003/004 raw样例</x:v>
+      </x:c>
+      <x:c r="I65" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J65" s="4" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="K65" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/02-breakdown.md:14</x:v>
+      </x:c>
+      <x:c r="L65" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="42" customHeight="1">
+      <x:c r="A66" s="9" t="str">
+        <x:v>TASK-TM005-E2E</x:v>
+      </x:c>
+      <x:c r="B66" s="9" t="str">
+        <x:v>具体任务</x:v>
+      </x:c>
+      <x:c r="C66" s="9" t="str">
+        <x:v>FP-TM005-06</x:v>
+      </x:c>
+      <x:c r="D66" s="9" t="str">
+        <x:v>REQ-TM005</x:v>
+      </x:c>
+      <x:c r="E66" s="9" t="str">
+        <x:v>AC-TM005-001
+AC-TM005-002</x:v>
+      </x:c>
+      <x:c r="F66" s="9" t="str">
+        <x:v>固定候选SHA、最终DMG、全部必测TC与已交付功能</x:v>
+      </x:c>
+      <x:c r="G66" s="9" t="str">
+        <x:v>逐TC原始步骤与完整回归；仅机器门禁PASS可发布</x:v>
+      </x:c>
+      <x:c r="H66" s="9" t="str">
+        <x:v>TM-001–004适用回归与产品数据</x:v>
+      </x:c>
+      <x:c r="I66" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="J66" s="9" t="str">
+        <x:v>baseline_pending</x:v>
+      </x:c>
+      <x:c r="K66" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/02-breakdown.md:15</x:v>
+      </x:c>
+      <x:c r="L66" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="32" customHeight="1">
+      <x:c r="A67" s="4" t="str">
+        <x:v>TASK-TM001-PLAN</x:v>
+      </x:c>
+      <x:c r="B67" s="4" t="str">
+        <x:v>历史分组</x:v>
+      </x:c>
+      <x:c r="C67" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="D67" s="4" t="str">
+        <x:v>REQ-TM001</x:v>
+      </x:c>
+      <x:c r="E67" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="F67" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="G67" s="4" t="str">
+        <x:v>六文档、完整追踪、SOP 修正、基线通过</x:v>
+      </x:c>
+      <x:c r="H67" s="4" t="str">
+        <x:v>需求</x:v>
+      </x:c>
+      <x:c r="I67" s="4" t="str">
+        <x:v>TEST-TM001-GOVERNANCE</x:v>
+      </x:c>
+      <x:c r="J67" s="4" t="str">
+        <x:v>historical_group_not_minimal_task</x:v>
+      </x:c>
+      <x:c r="K67" s="4" t="str">
+        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:9</x:v>
+      </x:c>
+      <x:c r="L67" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="42" customHeight="1">
+      <x:c r="A68" s="9" t="str">
+        <x:v>TASK-TM001-SERVER</x:v>
+      </x:c>
+      <x:c r="B68" s="9" t="str">
+        <x:v>历史分组</x:v>
+      </x:c>
+      <x:c r="C68" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="D68" s="9" t="str">
+        <x:v>REQ-TM001</x:v>
+      </x:c>
+      <x:c r="E68" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="F68" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="G68" s="9" t="str">
+        <x:v>FastAPI/SQLAlchemy/Alembic 工程、真实认证/权限/审计 API；随机可撤销 token 固定30天到期、不滑动，改密/重置/停用撤销旧会话</x:v>
+      </x:c>
+      <x:c r="H68" s="9" t="str">
+        <x:v>计划、数据/测试</x:v>
+      </x:c>
+      <x:c r="I68" s="9" t="str">
+        <x:v>E2E-TM001-001、E2E-TM001-002、E2E-TM001-003</x:v>
+      </x:c>
+      <x:c r="J68" s="9" t="str">
+        <x:v>historical_group_not_minimal_task</x:v>
+      </x:c>
+      <x:c r="K68" s="9" t="str">
+        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:10</x:v>
+      </x:c>
+      <x:c r="L68" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="42" customHeight="1">
+      <x:c r="A69" s="4" t="str">
+        <x:v>TASK-TM001-DATA</x:v>
+      </x:c>
+      <x:c r="B69" s="4" t="str">
+        <x:v>历史分组</x:v>
+      </x:c>
+      <x:c r="C69" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="D69" s="4" t="str">
+        <x:v>REQ-TM001</x:v>
+      </x:c>
+      <x:c r="E69" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="F69" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="G69" s="4" t="str">
+        <x:v>独立测试/生产 SQLite 文件、可执行造数 SQL、生产首建管理员、回归账号/独立预期及安全重置；已有生产密码不可被重建覆盖</x:v>
+      </x:c>
+      <x:c r="H69" s="4" t="str">
+        <x:v>计划、工程骨架</x:v>
+      </x:c>
+      <x:c r="I69" s="4" t="str">
+        <x:v>TEST-TM001-SERVER、E2E-TM001-001、E2E-TM001-005</x:v>
+      </x:c>
+      <x:c r="J69" s="4" t="str">
+        <x:v>historical_group_not_minimal_task</x:v>
+      </x:c>
+      <x:c r="K69" s="4" t="str">
+        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:11</x:v>
+      </x:c>
+      <x:c r="L69" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="72" customHeight="1">
+      <x:c r="A70" s="9" t="str">
+        <x:v>TASK-TM001-MAC</x:v>
+      </x:c>
+      <x:c r="B70" s="9" t="str">
+        <x:v>历史分组</x:v>
+      </x:c>
+      <x:c r="C70" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="D70" s="9" t="str">
+        <x:v>REQ-TM001</x:v>
+      </x:c>
+      <x:c r="E70" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="F70" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="G70" s="9" t="str">
+        <x:v>Electron React/TypeScript 登录/改密/主页/管理、默认本机 API/更新源地址与配置管理页的用户覆盖持久化；默认开启可关闭的设备自动登录、按规范化 origin 隔离的受保护凭据文件与内存会话、稳定 UI 标识、Playwright Electron工程</x:v>
+      </x:c>
+      <x:c r="H70" s="9" t="str">
+        <x:v>API 合同、工程骨架</x:v>
+      </x:c>
+      <x:c r="I70" s="9" t="str">
+        <x:v>E2E-TM001-001、E2E-TM001-002、E2E-TM001-003、E2E-TM001-004、E2E-TM001-005、E2E-TM001-006</x:v>
+      </x:c>
+      <x:c r="J70" s="9" t="str">
+        <x:v>historical_group_not_minimal_task</x:v>
+      </x:c>
+      <x:c r="K70" s="9" t="str">
+        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:12</x:v>
+      </x:c>
+      <x:c r="L70" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="57" customHeight="1">
+      <x:c r="A71" s="4" t="str">
+        <x:v>TASK-TM001-UPDATE</x:v>
+      </x:c>
+      <x:c r="B71" s="4" t="str">
+        <x:v>历史分组</x:v>
+      </x:c>
+      <x:c r="C71" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="D71" s="4" t="str">
+        <x:v>REQ-TM001</x:v>
+      </x:c>
+      <x:c r="E71" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="F71" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="G71" s="4" t="str">
+        <x:v>固定 Ed25519 公钥、同机回环更新源/签名测试包/失败包及真实更新用例；默认49177配置、URL安全校验与升级时锁定更新设置；两构建沿用经校验的同一隔离profile，升级后服务验证自动登录</x:v>
+      </x:c>
+      <x:c r="H71" s="4" t="str">
+        <x:v>Mac 工程</x:v>
+      </x:c>
+      <x:c r="I71" s="4" t="str">
+        <x:v>E2E-TM001-004</x:v>
+      </x:c>
+      <x:c r="J71" s="4" t="str">
+        <x:v>historical_group_not_minimal_task</x:v>
+      </x:c>
+      <x:c r="K71" s="4" t="str">
+        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:13</x:v>
+      </x:c>
+      <x:c r="L71" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="57" customHeight="1">
+      <x:c r="A72" s="9" t="str">
+        <x:v>TASK-TM001-RUNNER</x:v>
+      </x:c>
+      <x:c r="B72" s="9" t="str">
+        <x:v>历史分组</x:v>
+      </x:c>
+      <x:c r="C72" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="D72" s="9" t="str">
+        <x:v>REQ-TM001</x:v>
+      </x:c>
+      <x:c r="E72" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="F72" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="G72" s="9" t="str">
+        <x:v>本机Playwright从最终DMG安装App执行全部六例，原始JSON/trace/fixtureSQL/包摘要、父门禁复核；默认值与动态独占端口隔离测试；真实Squirrel自重启及profile、身份恢复</x:v>
+      </x:c>
+      <x:c r="H72" s="9" t="str">
+        <x:v>数据/桌面工程</x:v>
+      </x:c>
+      <x:c r="I72" s="9" t="str">
+        <x:v>E2E-TM001-001、E2E-TM001-002、E2E-TM001-003、E2E-TM001-004、E2E-TM001-005、E2E-TM001-006</x:v>
+      </x:c>
+      <x:c r="J72" s="9" t="str">
+        <x:v>historical_group_not_minimal_task</x:v>
+      </x:c>
+      <x:c r="K72" s="9" t="str">
+        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:14</x:v>
+      </x:c>
+      <x:c r="L72" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="32" customHeight="1">
+      <x:c r="A73" s="4" t="str">
+        <x:v>TASK-TM001-REVIEW</x:v>
+      </x:c>
+      <x:c r="B73" s="4" t="str">
+        <x:v>历史分组</x:v>
+      </x:c>
+      <x:c r="C73" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="D73" s="4" t="str">
+        <x:v>REQ-TM001</x:v>
+      </x:c>
+      <x:c r="E73" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="F73" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="G73" s="4" t="str">
+        <x:v>完整回归、流程复盘、PR 与合并判定、发布阻塞记录</x:v>
+      </x:c>
+      <x:c r="H73" s="4" t="str">
+        <x:v>全部实现任务</x:v>
+      </x:c>
+      <x:c r="I73" s="4" t="str">
+        <x:v>TEST-TM001-GOVERNANCE</x:v>
+      </x:c>
+      <x:c r="J73" s="4" t="str">
+        <x:v>historical_group_not_minimal_task</x:v>
+      </x:c>
+      <x:c r="K73" s="4" t="str">
+        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:15</x:v>
+      </x:c>
+      <x:c r="L73" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="J5:J48">
+  <x:conditionalFormatting sqref="J5:J73">
     <x:cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="10" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="11" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6fcc64b2616749e2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf769948b070a4b80"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9998,7 +11330,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I83" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J83" s="4" t="str">
         <x:v>未执行</x:v>
@@ -10045,7 +11377,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I84" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J84" s="9" t="str">
         <x:v>未执行</x:v>
@@ -10093,7 +11425,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I85" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J85" s="4" t="str">
         <x:v>未执行</x:v>
@@ -10141,7 +11473,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit、网络 ND0/NDA、本例私有来源密文摘要与 A/B 根身份。#REPLACE_CONFIRMED 另按原子提交时间比较旧 A 停读和新 B 唯一候选；不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I86" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J86" s="9" t="str">
         <x:v>未执行</x:v>
@@ -10187,7 +11519,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit、网络 ND0/NDA、本例私有来源密文摘要与 A/B 根身份。#REPLACE_CONFIRMED 另按原子提交时间比较旧 A 停读和新 B 唯一候选；不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I87" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J87" s="4" t="str">
         <x:v>未执行</x:v>
@@ -10233,7 +11565,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit、网络 ND0/NDA、本例私有来源密文摘要与 A/B 根身份。#REPLACE_CONFIRMED 另按原子提交时间比较旧 A 停读和新 B 唯一候选；不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I88" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J88" s="9" t="str">
         <x:v>未执行</x:v>
@@ -10279,7 +11611,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit、网络 ND0/NDA、本例私有来源密文摘要与 A/B 根身份。#REPLACE_CONFIRMED 另按原子提交时间比较旧 A 停读和新 B 唯一候选；不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I89" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J89" s="4" t="str">
         <x:v>未执行</x:v>
@@ -10331,7 +11663,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I90" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J90" s="9" t="str">
         <x:v>未执行</x:v>
@@ -10379,7 +11711,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I91" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J91" s="4" t="str">
         <x:v>未执行</x:v>
@@ -10427,7 +11759,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I92" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J92" s="9" t="str">
         <x:v>未执行</x:v>
@@ -10475,7 +11807,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I93" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J93" s="4" t="str">
         <x:v>未执行</x:v>
@@ -10523,7 +11855,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I94" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J94" s="9" t="str">
         <x:v>未执行</x:v>
@@ -10569,7 +11901,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I95" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J95" s="4" t="str">
         <x:v>未执行</x:v>
@@ -10615,7 +11947,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I96" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J96" s="9" t="str">
         <x:v>未执行</x:v>
@@ -10661,7 +11993,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I97" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J97" s="4" t="str">
         <x:v>未执行</x:v>
@@ -10709,7 +12041,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I98" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J98" s="9" t="str">
         <x:v>未执行</x:v>
@@ -10757,7 +12089,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I99" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J99" s="4" t="str">
         <x:v>未执行</x:v>
@@ -10805,7 +12137,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I100" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J100" s="9" t="str">
         <x:v>未执行</x:v>
@@ -10851,7 +12183,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I101" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J101" s="4" t="str">
         <x:v>未执行</x:v>
@@ -10897,7 +12229,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I102" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J102" s="9" t="str">
         <x:v>未执行</x:v>
@@ -10945,7 +12277,7 @@
 核验：先执行 Q-TM002-USERS；对照 sessions/audit、网络 ND0/NDA 与本例私有记录的完整布尔对、根身份/密文摘要。#TURN_COLLECT_OFF_ON 另核对旧扫描代际失效和恢复后仅 A；不向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I103" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J103" s="4" t="str">
         <x:v>未执行</x:v>
@@ -10991,7 +12323,7 @@
 核验：先执行 Q-TM002-USERS；对照 sessions/audit、网络 ND0/NDA 与本例私有记录的完整布尔对、根身份/密文摘要。#TURN_COLLECT_OFF_ON 另核对旧扫描代际失效和恢复后仅 A；不向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I104" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J104" s="9" t="str">
         <x:v>未执行</x:v>
@@ -11037,7 +12369,7 @@
 核验：先执行 Q-TM002-USERS；对照 sessions/audit、网络 ND0/NDA 与本例私有记录的完整布尔对、根身份/密文摘要。#TURN_COLLECT_OFF_ON 另核对旧扫描代际失效和恢复后仅 A；不向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I105" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J105" s="4" t="str">
         <x:v>未执行</x:v>
@@ -11083,7 +12415,7 @@
 核验：先执行 Q-TM002-USERS；对照 sessions/audit、网络 ND0/NDA 与本例私有记录的完整布尔对、根身份/密文摘要。#TURN_COLLECT_OFF_ON 另核对旧扫描代际失效和恢复后仅 A；不向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I106" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J106" s="9" t="str">
         <x:v>未执行</x:v>
@@ -11131,7 +12463,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 与真实 /v1/me、网络 NDA、本例私有记录前后摘要和 A/B 文件访问审计；损坏注入不修改服务 DB。</x:v>
       </x:c>
       <x:c r="I107" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J107" s="4" t="str">
         <x:v>未执行</x:v>
@@ -11177,7 +12509,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 与真实 /v1/me、网络 NDA、本例私有记录前后摘要和 A/B 文件访问审计；损坏注入不修改服务 DB。</x:v>
       </x:c>
       <x:c r="I108" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J108" s="9" t="str">
         <x:v>未执行</x:v>
@@ -11223,7 +12555,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 与真实 /v1/me、网络 NDA、本例私有记录前后摘要和 A/B 文件访问审计；损坏注入不修改服务 DB。</x:v>
       </x:c>
       <x:c r="I109" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J109" s="4" t="str">
         <x:v>未执行</x:v>
@@ -11271,7 +12603,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I110" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J110" s="9" t="str">
         <x:v>未执行</x:v>
@@ -11319,7 +12651,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I111" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J111" s="4" t="str">
         <x:v>未执行</x:v>
@@ -11367,7 +12699,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I112" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J112" s="9" t="str">
         <x:v>未执行</x:v>
@@ -11415,7 +12747,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I113" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J113" s="4" t="str">
         <x:v>未执行</x:v>
@@ -11463,7 +12795,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I114" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J114" s="9" t="str">
         <x:v>未执行</x:v>
@@ -11511,7 +12843,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I115" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J115" s="4" t="str">
         <x:v>未执行</x:v>
@@ -11559,7 +12891,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I116" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J116" s="9" t="str">
         <x:v>未执行</x:v>
@@ -11608,7 +12940,7 @@
 核验：先执行 Q-TM002-USERS；只读比较 sessions/audit 初末快照、网络 ND0/NDA、私有来源摘要。TM-002 无业务造数 SQL，不直接向 DB 写来源状态。</x:v>
       </x:c>
       <x:c r="I117" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J117" s="4" t="str">
         <x:v>未执行</x:v>
@@ -11656,7 +12988,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I118" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J118" s="9" t="str">
         <x:v>未执行</x:v>
@@ -11704,7 +13036,7 @@
 核验：不适用：无 DB 连接或 SQL；核对 sources 0600/密文摘要、状态与 A/B 审计。#WRITE_FAIL_KEEP_OLD 核对 B 加密已成功、故障仅在私有写入阶段、失败临时文件不可恢复，随后旧 A 再刷新 A1/A2，原记录字节 SHA 不变。</x:v>
       </x:c>
       <x:c r="I119" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J119" s="4" t="str">
         <x:v>未执行</x:v>
@@ -11750,7 +13082,7 @@
 核验：不适用：无 DB 连接或 SQL；核对 sources 0600/密文摘要、状态与 A/B 审计。#WRITE_FAIL_KEEP_OLD 核对 B 加密已成功、故障仅在私有写入阶段、失败临时文件不可恢复，随后旧 A 再刷新 A1/A2，原记录字节 SHA 不变。</x:v>
       </x:c>
       <x:c r="I120" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J120" s="9" t="str">
         <x:v>未执行</x:v>
@@ -11796,7 +13128,7 @@
 核验：不适用：无 DB 连接或 SQL；核对 sources 0600/密文摘要、状态与 A/B 审计。#WRITE_FAIL_KEEP_OLD 核对 B 加密已成功、故障仅在私有写入阶段、失败临时文件不可恢复，随后旧 A 再刷新 A1/A2，原记录字节 SHA 不变。</x:v>
       </x:c>
       <x:c r="I121" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J121" s="4" t="str">
         <x:v>未执行</x:v>
@@ -11842,7 +13174,7 @@
 核验：不适用：无 DB 连接或 SQL；核对 sources 0600/密文摘要、状态与 A/B 审计。#WRITE_FAIL_KEEP_OLD 核对 B 加密已成功、故障仅在私有写入阶段、失败临时文件不可恢复，随后旧 A 再刷新 A1/A2，原记录字节 SHA 不变。</x:v>
       </x:c>
       <x:c r="I122" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J122" s="9" t="str">
         <x:v>未执行</x:v>
@@ -11890,7 +13222,7 @@
 核验：不适用：无 DB 连接或 SQL；以固定完整相对路径清单比较每页、游标、complete 与 A/B 审计。旧树必须 a.jsonl 先于 a/x.jsonl，后接 p-0000…p-1198，页边界 256/256/256/256/177。#TREE_CHANGED 旧游标 invalid/incomplete；新扫描五页 256/256/256/256/178、1202 名无重漏、p-0000a 总序第 4；只据真实目录和生产 helper/主进程判断。</x:v>
       </x:c>
       <x:c r="I123" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J123" s="4" t="str">
         <x:v>未执行</x:v>
@@ -11936,7 +13268,7 @@
 核验：不适用：无 DB 连接或 SQL；以固定完整相对路径清单比较每页、游标、complete 与 A/B 审计。旧树必须 a.jsonl 先于 a/x.jsonl，后接 p-0000…p-1198，页边界 256/256/256/256/177。#TREE_CHANGED 旧游标 invalid/incomplete；新扫描五页 256/256/256/256/178、1202 名无重漏、p-0000a 总序第 4；只据真实目录和生产 helper/主进程判断。</x:v>
       </x:c>
       <x:c r="I124" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J124" s="9" t="str">
         <x:v>未执行</x:v>
@@ -11982,7 +13314,7 @@
 核验：不适用：无 DB 连接或 SQL；以固定完整相对路径清单比较每页、游标、complete 与 A/B 审计。旧树必须 a.jsonl 先于 a/x.jsonl，后接 p-0000…p-1198，页边界 256/256/256/256/177。#TREE_CHANGED 旧游标 invalid/incomplete；新扫描五页 256/256/256/256/178、1202 名无重漏、p-0000a 总序第 4；只据真实目录和生产 helper/主进程判断。</x:v>
       </x:c>
       <x:c r="I125" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J125" s="4" t="str">
         <x:v>未执行</x:v>
@@ -12028,7 +13360,7 @@
 核验：不适用：无 DB 连接或 SQL；以固定完整相对路径清单比较每页、游标、complete 与 A/B 审计。旧树必须 a.jsonl 先于 a/x.jsonl，后接 p-0000…p-1198，页边界 256/256/256/256/177。#TREE_CHANGED 旧游标 invalid/incomplete；新扫描五页 256/256/256/256/178、1202 名无重漏、p-0000a 总序第 4；只据真实目录和生产 helper/主进程判断。</x:v>
       </x:c>
       <x:c r="I126" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J126" s="9" t="str">
         <x:v>未执行</x:v>
@@ -12076,7 +13408,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I127" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J127" s="4" t="str">
         <x:v>未执行</x:v>
@@ -12122,7 +13454,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I128" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J128" s="9" t="str">
         <x:v>未执行</x:v>
@@ -12168,7 +13500,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I129" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J129" s="4" t="str">
         <x:v>未执行</x:v>
@@ -12214,7 +13546,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I130" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J130" s="9" t="str">
         <x:v>未执行</x:v>
@@ -12260,7 +13592,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I131" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J131" s="4" t="str">
         <x:v>未执行</x:v>
@@ -12306,7 +13638,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I132" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J132" s="9" t="str">
         <x:v>未执行</x:v>
@@ -12352,7 +13684,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I133" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J133" s="4" t="str">
         <x:v>未执行</x:v>
@@ -12398,7 +13730,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I134" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J134" s="9" t="str">
         <x:v>未执行</x:v>
@@ -12446,7 +13778,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I135" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J135" s="4" t="str">
         <x:v>未执行</x:v>
@@ -12494,7 +13826,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I136" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J136" s="9" t="str">
         <x:v>未执行</x:v>
@@ -12540,7 +13872,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I137" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J137" s="4" t="str">
         <x:v>未执行</x:v>
@@ -12586,7 +13918,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I138" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J138" s="9" t="str">
         <x:v>未执行</x:v>
@@ -12632,7 +13964,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I139" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J139" s="4" t="str">
         <x:v>未执行</x:v>
@@ -12680,7 +14012,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I140" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J140" s="9" t="str">
         <x:v>未执行</x:v>
@@ -12726,7 +14058,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I141" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J141" s="4" t="str">
         <x:v>未执行</x:v>
@@ -12772,7 +14104,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I142" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J142" s="9" t="str">
         <x:v>未执行</x:v>
@@ -12818,7 +14150,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I143" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J143" s="4" t="str">
         <x:v>未执行</x:v>
@@ -12864,7 +14196,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I144" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J144" s="9" t="str">
         <x:v>未执行</x:v>
@@ -12910,7 +14242,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I145" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J145" s="4" t="str">
         <x:v>未执行</x:v>
@@ -12956,7 +14288,7 @@
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
       <x:c r="I146" s="9" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J146" s="9" t="str">
         <x:v>未执行</x:v>
@@ -13004,7 +14336,7 @@
 核验：只读复核 TM-001 全部已交付 TC、其他 27 条 TM-002 父 TC/35 变体的隔离 DB/SQL 引用与原始逐步结果，并核对最终包、升级、清理和候选一致性；本例结果由这些原件派生，不连接生产库。 核对上一0.1稳定原包的通行证、归档、来源SHA/tree及真实升级链。 只读核对schema 2 release-index.json的milestone_sha/tree、master_tip_sha、remote_source_state及原件摘要。</x:v>
       </x:c>
       <x:c r="I147" s="4" t="str">
-        <x:v>预期待明确</x:v>
+        <x:v>baselined</x:v>
       </x:c>
       <x:c r="J147" s="4" t="str">
         <x:v>未执行</x:v>
@@ -13030,7 +14362,7 @@
         <x:v>E2E-TM003-001</x:v>
       </x:c>
       <x:c r="C148" s="9" t="str">
-        <x:v>增量采集、重扫、重启和移动</x:v>
+        <x:v>增量、重扫、重启及移动</x:v>
       </x:c>
       <x:c r="D148" s="9" t="str">
         <x:v>待拆解</x:v>
@@ -13059,13 +14391,13 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L148" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:11</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:14</x:v>
       </x:c>
       <x:c r="M148" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N148" s="9" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
+        <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="72" customHeight="1">
@@ -13076,7 +14408,7 @@
         <x:v>E2E-TM003-002</x:v>
       </x:c>
       <x:c r="C149" s="4" t="str">
-        <x:v>累计值、重复事件、分支和未知格式</x:v>
+        <x:v>累计、重复、分支及未知</x:v>
       </x:c>
       <x:c r="D149" s="4" t="str">
         <x:v>待拆解</x:v>
@@ -13105,13 +14437,13 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L149" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:28</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:38</x:v>
       </x:c>
       <x:c r="M149" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N149" s="4" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
+        <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="57" customHeight="1">
@@ -13122,7 +14454,7 @@
         <x:v>E2E-TM003-003</x:v>
       </x:c>
       <x:c r="C150" s="9" t="str">
-        <x:v>半行完成与源日志清理</x:v>
+        <x:v>半行、源清理与历史覆盖</x:v>
       </x:c>
       <x:c r="D150" s="9" t="str">
         <x:v>待拆解</x:v>
@@ -13151,13 +14483,13 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L150" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:45</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:63</x:v>
       </x:c>
       <x:c r="M150" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N150" s="9" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
+        <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="57" customHeight="1">
@@ -13168,7 +14500,7 @@
         <x:v>E2E-TM003-004</x:v>
       </x:c>
       <x:c r="C151" s="4" t="str">
-        <x:v>重新授权后的去重</x:v>
+        <x:v>权限边界与重新授权</x:v>
       </x:c>
       <x:c r="D151" s="4" t="str">
         <x:v>待拆解</x:v>
@@ -13197,13 +14529,13 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L151" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:62</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:87</x:v>
       </x:c>
       <x:c r="M151" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N151" s="4" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
+        <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
     <x:row r="152" ht="57" customHeight="1">
@@ -13249,7 +14581,7 @@
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N152" s="9" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
+        <x:v>v0.2.0-20261001T034118Z</x:v>
       </x:c>
     </x:row>
     <x:row r="153" ht="57" customHeight="1">
@@ -13295,7 +14627,7 @@
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N153" s="4" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
+        <x:v>v0.2.0-20261001T034118Z</x:v>
       </x:c>
     </x:row>
     <x:row r="154" ht="57" customHeight="1">
@@ -13341,7 +14673,7 @@
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N154" s="9" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
+        <x:v>v0.2.0-20261001T034118Z</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="57" customHeight="1">
@@ -13387,938 +14719,994 @@
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N155" s="4" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="156" ht="57" customHeight="1">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" ht="72" customHeight="1">
       <x:c r="A156" s="9" t="str">
-        <x:v>TM-005</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B156" s="9" t="str">
-        <x:v>E2E-TM005-001</x:v>
+        <x:v>TC-TM004-SOURCE-01</x:v>
       </x:c>
       <x:c r="C156" s="9" t="str">
-        <x:v>日期筛选、趋势和明细</x:v>
+        <x:v>授权根限定（TASK-TM004-SOURCE，AC-001，E2E-001）</x:v>
       </x:c>
       <x:c r="D156" s="9" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-SOURCE</x:v>
       </x:c>
       <x:c r="E156" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F156" s="9" t="str">
-        <x:v>数据集 date_ranges；date_ranges 已由 scripts/test_data.py 提供标准化语义样例，固定2026-09-29T04:00:00Z、Asia/Shanghai、seed42；13行含1重复、12唯一。需另有已验证raw输入映射和真实App导入流程，当前未实现。</x:v>
+        <x:v>用户经 TM-002 UI 只选择隔离项目A目录；目录内有 M=100/10 完整原始行，旁边未授权目录有 X=999/99。</x:v>
       </x:c>
       <x:c r="G156" s="9" t="str">
-        <x:v>独立expected中的total依次16500、110、17380、27830、31130；custom=2200。today共5条、input15000、output1500、cache1700、reasoning170，cache/reasoning不再相加；custom-start包含、custom-end排除。趋势点及明细按expected事件时间逐条核对。</x:v>
+        <x:v>UI 显示待确认，事件表无新增
+UI 显示1次 M、total110，SQLite只读见唯一M
+调用数仍1、total110
+无X读取请求且事件表无X</x:v>
       </x:c>
       <x:c r="H156" s="9" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读按来源/项目统计 M 行数与 token，总数1/110；检查 X 键不存在；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I156" s="9" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J156" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K156" s="9" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L156" s="9" t="str">
-        <x:v>docs/testing/cases/05-TM-005-usage-statistics.md:15</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:87</x:v>
       </x:c>
       <x:c r="M156" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N156" s="9" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="157" ht="57" customHeight="1">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" ht="72" customHeight="1">
       <x:c r="A157" s="4" t="str">
-        <x:v>TM-005</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B157" s="4" t="str">
-        <x:v>E2E-TM005-002</x:v>
+        <x:v>TC-TM004-SOURCE-02</x:v>
       </x:c>
       <x:c r="C157" s="4" t="str">
-        <x:v>时区、月边界与缺失值</x:v>
+        <x:v>撤权和重新授权（TASK-TM004-SOURCE，AC-004，E2E-004）</x:v>
       </x:c>
       <x:c r="D157" s="4" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-SOURCE</x:v>
       </x:c>
       <x:c r="E157" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F157" s="4" t="str">
-        <x:v>数据集 date_ranges；复用date_ranges中的2026-09-28T15:59:59Z与16:00:00Z、2026-08-30T15:59:59Z与16:00:00Z边界。另需补充覆盖缺口、已覆盖零调用日、unknown字段三类状态；当前生成器未覆盖后面三类。</x:v>
+        <x:v>已扫描 M=100/10、S=200/20；撤权期间子代理新增 N=50/5。</x:v>
       </x:c>
       <x:c r="G157" s="4" t="str">
-        <x:v>Shanghai下15:59:59Z仍属前日、16:00:00Z属次日；UTC下二者同属UTC日期。无覆盖显示缺失，真实零可显示0，unknown字段显示未知；不得互相代替。各范围expected须独立按当地日期边界列出，不调用产品查询生成。</x:v>
+        <x:v>状态显示不可读且保留total330
+仍330且诊断为读取受阻
+唯一 M/S/N、total385
+M/S/N仍为三次且total385</x:v>
       </x:c>
       <x:c r="H157" s="4" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读唯一键数3与 token总385，撤权阶段无N。重置同共用配方；TM-002失权模拟与子目录绑定待补；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I157" s="4" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J157" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K157" s="4" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L157" s="4" t="str">
-        <x:v>docs/testing/cases/05-TM-005-usage-statistics.md:32</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:91</x:v>
       </x:c>
       <x:c r="M157" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N157" s="4" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="158" ht="57" customHeight="1">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" ht="72" customHeight="1">
       <x:c r="A158" s="9" t="str">
-        <x:v>TM-006</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B158" s="9" t="str">
-        <x:v>E2E-TM006-001</x:v>
+        <x:v>TC-TM004-PARSER-01</x:v>
       </x:c>
       <x:c r="C158" s="9" t="str">
-        <x:v>Token子项与基础费用</x:v>
+        <x:v>主/子实际调用（TASK-TM004-PARSER，AC-001，E2E-001）</x:v>
       </x:c>
       <x:c r="D158" s="9" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-PARSER</x:v>
       </x:c>
       <x:c r="E158" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F158" s="9" t="str">
-        <x:v>数据集 pricing；pricing由scripts/test_data.py生成合成非计费价格。gpt-5每百万input/cache/output为USD2/0.2/8；today-gpt input1000含cache200、output100含reasoning20。价格不是厂商现价。</x:v>
+        <x:v>同一项目原始主M100/10与子S200/20，模型各自保留，父关系有原始证据。</x:v>
       </x:c>
       <x:c r="G158" s="9" t="str">
-        <x:v>单调用total=1100；费用=(800×2+200×0.2+100×8)/1000000=USD0.002440，reasoning20不另加价。today已知费用USD0.015190且有1条无价格，alice今日USD0.010090。使用Decimal/十进制独立oracle，不以界面舍入反推底层精度。</x:v>
+        <x:v>可信total110
+可信input300/output30/total330
+仍2次调用/330</x:v>
       </x:c>
       <x:c r="H158" s="9" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读两条唯一事件和模型/父项目归属；不读取正文。版本化raw和模型字段待补；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I158" s="9" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J158" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K158" s="9" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L158" s="9" t="str">
-        <x:v>docs/testing/cases/06-TM-006-cost-estimates.md:15</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:95</x:v>
       </x:c>
       <x:c r="M158" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N158" s="9" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="159" ht="57" customHeight="1">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" ht="102" customHeight="1">
       <x:c r="A159" s="4" t="str">
-        <x:v>TM-006</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B159" s="4" t="str">
-        <x:v>E2E-TM006-002</x:v>
+        <x:v>TC-TM004-PARSER-02</x:v>
       </x:c>
       <x:c r="C159" s="4" t="str">
-        <x:v>历史价格、多币种和未知费用</x:v>
+        <x:v>未知结构/缺字段（TASK-TM004-PARSER，AC-003，E2E-003）</x:v>
       </x:c>
       <x:c r="D159" s="4" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-PARSER</x:v>
       </x:c>
       <x:c r="E159" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F159" s="4" t="str">
-        <x:v>数据集 pricing_extended；pricing_extended planned：同模型在生效时点T前后各一调用，两个独立价格版本；另有USD/CNY各一模型、无价模型和订阅估算模型。必须提供价格/订阅分摊规则及手算expected后才能实现。</x:v>
+        <x:v>已支持版本完整 M100/10、未知结构 U、JSONL 原始行真正缺 usage 的 Q。</x:v>
       </x:c>
       <x:c r="G159" s="4" t="str">
-        <x:v>T前后依各自生效版本计算，历史结果不会悄悄换价；USD与CNY分组，未约定汇率不得相加；无价格显示未知而非0；订阅必须明确估算口径。具体金额oracle依待定义订阅/价格合同生成，当前不得手填PASS。</x:v>
+        <x:v>可信total110
+可信仍110且出现未知结构诊断
+可信仍110、缺usage诊断新增
+诊断可见且不显示 U/Q 为零调用</x:v>
       </x:c>
       <x:c r="H159" s="4" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读可信事件1条/110，诊断各1条；具体版本标识、缺字段schema和SQL待补。隔离负测中 API SSE 省略 usage 后 CLI 仍在原生 JSONL 写0/0，**不是** Q 的原生缺字段样本；Q 需另证来源或标明故障注入，不得把0/0回填解释成已知零；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I159" s="4" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J159" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K159" s="4" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L159" s="4" t="str">
-        <x:v>docs/testing/cases/06-TM-006-cost-estimates.md:32</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:99</x:v>
       </x:c>
       <x:c r="M159" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N159" s="4" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="160" ht="57" customHeight="1">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" ht="72" customHeight="1">
       <x:c r="A160" s="9" t="str">
-        <x:v>TM-007</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B160" s="9" t="str">
-        <x:v>E2E-TM007-001</x:v>
+        <x:v>TC-TM004-LINEAGE-01</x:v>
       </x:c>
       <x:c r="C160" s="9" t="str">
-        <x:v>离线、重启和补传幂等</x:v>
+        <x:v>子代理父项目（TASK-TM004-LINEAGE，AC-001，E2E-001）</x:v>
       </x:c>
       <x:c r="D160" s="9" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-LINEAGE</x:v>
       </x:c>
       <x:c r="E160" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F160" s="9" t="str">
-        <x:v>数据集 sync_faults；sync_faults planned；alice两个隔离设备A/B，设备A调用100/10、B调用200/20；真实FastAPI/SQLite服务，可由外部fixture断网/恢复。账号继续用隔离测试fixture。</x:v>
+        <x:v>项目A主M100/10、子S200/20，另有项目B同名会话标识但无父关系。</x:v>
       </x:c>
       <x:c r="G160" s="9" t="str">
-        <x:v>离线重启不丢队列；恢复后2唯一调用、input300/output30/total330；重复批次不再加量。客户端只在真实确认后标已同步，个人合计与对应团队子集一致。</x:v>
+        <x:v>A=110
+A=330、B=0
+A仍330
+S标为子代理且使用原模型</x:v>
       </x:c>
       <x:c r="H160" s="9" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读S的父项目键为A、事件数2；原始父链线索缺失时不得假称通过；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I160" s="9" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J160" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K160" s="9" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L160" s="9" t="str">
-        <x:v>docs/testing/cases/07-TM-007-team-sync.md:11</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:103</x:v>
       </x:c>
       <x:c r="M160" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N160" s="9" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="161" ht="57" customHeight="1">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" ht="72" customHeight="1">
       <x:c r="A161" s="4" t="str">
-        <x:v>TM-007</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B161" s="4" t="str">
-        <x:v>E2E-TM007-002</x:v>
+        <x:v>TC-TM004-LINEAGE-02</x:v>
       </x:c>
       <x:c r="C161" s="4" t="str">
-        <x:v>部分确认、中断和账号切换</x:v>
+        <x:v>fork继承和ID改写（TASK-TM004-LINEAGE，AC-002，E2E-002）</x:v>
       </x:c>
       <x:c r="D161" s="4" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-LINEAGE</x:v>
       </x:c>
       <x:c r="E161" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F161" s="4" t="str">
-        <x:v>数据集 sync_faults；准备alice的三条唯一事件A/B/C，总量各110/220/330；控制服务仅确认A后断开，B可能已提交但响应丢失，C未提交。另有bob账号。故障注入必须在真实服务外部或明确测试环境中完成，不能绕过认证。</x:v>
+        <x:v>原M100/10、fork复制或引用M但消息ID改写、fork新N50/5。</x:v>
       </x:c>
       <x:c r="G161" s="4" t="str">
-        <x:v>最终alice的A/B/C各一次、total660；响应丢失不造成B重复；bob不能承接或篡改alice既有事件归属。切换时旧队列按已批准归属策略隔离，不能默认为新登录账号。</x:v>
+        <x:v>M仅入账一次且total110
+仍110
+total165且调用数2
+仍165</x:v>
       </x:c>
       <x:c r="H161" s="4" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读可信唯一调用2/165及继承诊断/关系；待schema确定；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I161" s="4" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J161" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K161" s="4" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L161" s="4" t="str">
-        <x:v>docs/testing/cases/07-TM-007-team-sync.md:28</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:107</x:v>
       </x:c>
       <x:c r="M161" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N161" s="4" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="162" ht="57" customHeight="1">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" ht="72" customHeight="1">
       <x:c r="A162" s="9" t="str">
-        <x:v>TM-007</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B162" s="9" t="str">
-        <x:v>E2E-TM007-003</x:v>
+        <x:v>TC-TM004-INCREMENTAL-01</x:v>
       </x:c>
       <x:c r="C162" s="9" t="str">
-        <x:v>上传白名单与项目映射</x:v>
+        <x:v>半行完成（TASK-TM004-INCREMENTAL，AC-002，E2E-002）</x:v>
       </x:c>
       <x:c r="D162" s="9" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-INCREMENTAL</x:v>
       </x:c>
       <x:c r="E162" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F162" s="9" t="str">
-        <x:v>数据集 sync_faults；合成日志包含唯一正文/代码/API-key/完整路径哨兵，以及合法用量/必要去重元数据；只用假值。准备已归属项目A和未归属事件B，待sync_faults生成。</x:v>
+        <x:v>已计M+N total165，P=20/2 原始JSONL行分成两次写入。</x:v>
       </x:c>
       <x:c r="G162" s="9" t="str">
-        <x:v>网络载荷/持久服务数据均不得含正文、代码、key或完整本机路径；只有批准用量/去重字段。B可明确分配，分配不增加事件量、也不跨团队归属。</x:v>
+        <x:v>扫描后仍165、读取游标未越过半行
+扫描后total187、调用数3
+P仅入账一次且total187</x:v>
       </x:c>
       <x:c r="H162" s="9" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读P只一条，可信事件3/187，游标处于完整行末；具体游标schema待补；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I162" s="9" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J162" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K162" s="9" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L162" s="9" t="str">
-        <x:v>docs/testing/cases/07-TM-007-team-sync.md:45</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:111</x:v>
       </x:c>
       <x:c r="M162" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N162" s="9" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="163" ht="57" customHeight="1">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" ht="72" customHeight="1">
       <x:c r="A163" s="4" t="str">
-        <x:v>TM-007</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B163" s="4" t="str">
-        <x:v>E2E-TM007-004</x:v>
+        <x:v>TC-TM004-INCREMENTAL-02</x:v>
       </x:c>
       <x:c r="C163" s="4" t="str">
-        <x:v>统计越权与停用后上传</x:v>
+        <x:v>重复与事务恢复（TASK-TM004-INCREMENTAL，AC-002/004，E2E-002/004）</x:v>
       </x:c>
       <x:c r="D163" s="4" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-INCREMENTAL</x:v>
       </x:c>
       <x:c r="E163" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F163" s="4" t="str">
-        <x:v>数据集 sync_faults；alice项目A调用100/10，bob项目B调用200/20；成员alice与管理员独立会话；alice另有一条未确认调用C=50/5。sync_faults与可重建统计SQL尚未实现。</x:v>
+        <x:v>完整M100/10、重复相同片段及移动/复制文件；在扫描提交边界中断App。</x:v>
       </x:c>
       <x:c r="G163" s="4" t="str">
-        <x:v>成员无权请求被服务端拒绝，UI不显示bob的220；停用后旧会话及上传拒绝，C不能标为已确认；合法历史不能被失败上传删除。此处补足TM-001仅身份/管理接口权限的范围。</x:v>
+        <x:v>M仅入账一次且total110
+仍110
+仍唯一M/110
+total165</x:v>
       </x:c>
       <x:c r="H163" s="4" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读唯一键数2/165且游标一致；故障注入不得绕过产品事务。TM-003事务接口待补；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I163" s="4" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J163" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K163" s="4" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L163" s="4" t="str">
-        <x:v>docs/testing/cases/07-TM-007-team-sync.md:62</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:115</x:v>
       </x:c>
       <x:c r="M163" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N163" s="4" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="164" ht="57" customHeight="1">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" ht="87" customHeight="1">
       <x:c r="A164" s="9" t="str">
-        <x:v>TM-008</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B164" s="9" t="str">
-        <x:v>E2E-TM008-001</x:v>
+        <x:v>TC-TM004-DIAG-01</x:v>
       </x:c>
       <x:c r="C164" s="9" t="str">
-        <x:v>筛选一致的CSV导出</x:v>
+        <x:v>未知值不是零（TASK-TM004-DIAGNOSTIC，AC-003，E2E-003）</x:v>
       </x:c>
       <x:c r="D164" s="9" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-DIAGNOSTIC</x:v>
       </x:c>
       <x:c r="E164" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F164" s="9" t="str">
-        <x:v>数据集 export_rows；export_rows planned；两成员、两个模型、时间范围内外各有事件，独立清单明确每条ID/字段/权限。先具备TM-005/007统计和授权。</x:v>
+        <x:v>可信M100/10、U未知格式、Q的JSONL原始行缺usage，以及另有独立来源证明的有效零usage记录Z。</x:v>
       </x:c>
       <x:c r="G164" s="9" t="str">
-        <x:v>每次CSV仅包含当次筛选且授权可见记录，行数/ID/汇总等于独立清单与界面；不混入旧筛选、其他成员或范围外记录。已知/未知费用语义一致。</x:v>
+        <x:v>显示110
+显示可信110和两个不同未覆盖提示
+零值记录可见但总量仍110
+三种状态不混淆</x:v>
       </x:c>
       <x:c r="H164" s="9" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读可信M和已证实的Z，U/Q仅诊断，不以0写入；Z的原始有效性仍 baseline_pending。2.1.126 遇到畸形合成 API 缺usage会自己写0/0，不能拿该行充当Z；未经额外证据不能由0/0 raw推断上游已知零；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I164" s="9" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J164" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K164" s="9" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L164" s="9" t="str">
-        <x:v>docs/testing/cases/08-TM-008-csv-export.md:11</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:119</x:v>
       </x:c>
       <x:c r="M164" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N164" s="9" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="165" ht="57" customHeight="1">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" ht="72" customHeight="1">
       <x:c r="A165" s="4" t="str">
-        <x:v>TM-008</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B165" s="4" t="str">
-        <x:v>E2E-TM008-002</x:v>
+        <x:v>TC-TM004-DIAG-02</x:v>
       </x:c>
       <x:c r="C165" s="4" t="str">
-        <x:v>CSV转义、未知值及权限</x:v>
+        <x:v>失权提示及隐私（TASK-TM004-DIAGNOSTIC，AC-004，E2E-004）</x:v>
       </x:c>
       <x:c r="D165" s="4" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-DIAGNOSTIC</x:v>
       </x:c>
       <x:c r="E165" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F165" s="4" t="str">
-        <x:v>数据集 export_rows；export_rows需含字段 a,b、say "hi"、带实际换行的项目名、未知费用与非ASCII模型名；两成员各有可区分哨兵事件。只在隔离数据中使用。</x:v>
+        <x:v>M已入账，撤权目录含合成 prompt、代码和密钥哨兵字符串。</x:v>
       </x:c>
       <x:c r="G165" s="4" t="str">
-        <x:v>逗号、双引号、嵌入换行均round-trip一致，Unicode不损坏；未知值不写成0；他人哨兵不出现在文件。若导出失败，不能留下看似完整的半文件。</x:v>
+        <x:v>UI显示读取受阻而非零用量，保留110
+无哨兵文本及完整源路径
+受阻提示消除且M不重计</x:v>
       </x:c>
       <x:c r="H165" s="4" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读事件1/110、诊断状态与仅白名单字段；隐私哨兵由固定生成器构造，不使用真实秘密；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I165" s="4" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J165" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K165" s="4" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L165" s="4" t="str">
-        <x:v>docs/testing/cases/08-TM-008-csv-export.md:28</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:123</x:v>
       </x:c>
       <x:c r="M165" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N165" s="4" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="166" ht="57" customHeight="1">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" ht="72" customHeight="1">
       <x:c r="A166" s="9" t="str">
-        <x:v>TM-009</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B166" s="9" t="str">
-        <x:v>E2E-TM009-001</x:v>
+        <x:v>TC-TM004-DATA-01</x:v>
       </x:c>
       <x:c r="C166" s="9" t="str">
-        <x:v>80%/100%提醒幂等</x:v>
+        <x:v>原始fixture和独立oracle（TASK-TM004-DATA，AC-001–004，E2E-003）</x:v>
       </x:c>
       <x:c r="D166" s="9" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-DATA</x:v>
       </x:c>
       <x:c r="E166" s="9" t="str">
-        <x:v>产品E2E</x:v>
+        <x:v>data_fixture</x:v>
       </x:c>
       <x:c r="F166" s="9" t="str">
-        <x:v>数据集 budget_periods；budget_periods planned；独立个人、项目和团队预算分别100个合成USD单位，同周期使用量依次79→80→99→100；原始调用与价格要能精确形成这些费用。</x:v>
+        <x:v>固定版本 CLI/公开来源、隔离 CLAUDE_CONFIG_DIR、固定合成任务；禁止访问真实 ~/.claude。</x:v>
       </x:c>
       <x:c r="G166" s="9" t="str">
-        <x:v>每预算每周期80与100各最多一次，未达到不发；重扫/重启/重复上传不重发；预算仅提醒，不拦截模型调用。三层预算分别按其授权范围计算。</x:v>
+        <x:v>版本、来源、原始SHA及父子/fork证据有原件
+M/S/N/P的330、165、187、385在运行前记录
+SHA一致且SQL初态只有合成账号与零事件
+仅删除本次拥有目录且保留原始报告</x:v>
       </x:c>
       <x:c r="H166" s="9" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：本例不直接写入产品用量表；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I166" s="9" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J166" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K166" s="9" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L166" s="9" t="str">
-        <x:v>docs/testing/cases/09-TM-009-budget-alerts.md:11</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:127</x:v>
       </x:c>
       <x:c r="M166" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N166" s="9" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="167" ht="57" customHeight="1">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" ht="72" customHeight="1">
       <x:c r="A167" s="4" t="str">
-        <x:v>TM-009</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B167" s="4" t="str">
-        <x:v>E2E-TM009-002</x:v>
+        <x:v>TC-TM004-E2E-01</x:v>
       </x:c>
       <x:c r="C167" s="4" t="str">
-        <x:v>新周期、币种与通知恢复</x:v>
+        <x:v>安装包真实链路（TASK-TM004-E2E，AC-001–004，E2E-001/004）</x:v>
       </x:c>
       <x:c r="D167" s="4" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-E2E</x:v>
       </x:c>
       <x:c r="E167" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F167" s="4" t="str">
-        <x:v>数据集 budget_periods；两个币种独立预算；旧周期已发80/100阈值，参考时钟可由产品支持的测试配置推进；测试通知权限可以拒绝及恢复，不能修改用户其他App授权。</x:v>
+        <x:v>本版固定候选SHA、原DMG、TM-001–004完整必测TC清单。</x:v>
       </x:c>
       <x:c r="G167" s="4" t="str">
-        <x:v>系统拒绝不丢失应用内状态、不造成重试通知风暴；新周期独立重置，允许新一轮各阈值一次；币种分开计算。通知补发策略需在对应需求明确，不能由测试临时猜测。</x:v>
+        <x:v>仅连接本次独占服务和隔离授权根
+逐步断言UI、IPC后果和只读SQLite
+目标及历史已交付TC全部执行且无跳过/重试/失败
+结果与候选包一致且本次资源清理完成</x:v>
       </x:c>
       <x:c r="H167" s="4" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：本例不直接写入产品用量表；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I167" s="4" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J167" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K167" s="4" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L167" s="4" t="str">
-        <x:v>docs/testing/cases/09-TM-009-budget-alerts.md:28</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:131</x:v>
       </x:c>
       <x:c r="M167" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N167" s="4" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
+        <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="72" customHeight="1">
       <x:c r="A168" s="9" t="str">
-        <x:v>TM-010</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B168" s="9" t="str">
-        <x:v>E2E-TM010-001</x:v>
+        <x:v>TC-TM004-RELEASE-01</x:v>
       </x:c>
       <x:c r="C168" s="9" t="str">
-        <x:v>稳定版发现更新与数据保留</x:v>
+        <x:v>候选与证据一致（TASK-TM004-RELEASE，AC-001–004，E2E-004）</x:v>
       </x:c>
       <x:c r="D168" s="9" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-RELEASE</x:v>
       </x:c>
       <x:c r="E168" s="9" t="str">
-        <x:v>产品E2E</x:v>
+        <x:v>release_gate</x:v>
       </x:c>
       <x:c r="F168" s="9" t="str">
-        <x:v>数据集 update_packages；依赖TM-001/007；update_packages planned。需真实已分发稳定版、候选最终包及相同分发profile的签名/清单；旧版有账号设置、手动地址、统计/队列独立快照。首版无历史稳定版时使用SOP017规定的候选→受控高版，不伪称稳定升级。</x:v>
+        <x:v>同一已提交SHA/tree、DMG摘要、完整TM-001–004结果。</x:v>
       </x:c>
       <x:c r="G168" s="9" t="str">
-        <x:v>更新频率和说明可用；只有声明候选被安装，Sparkle自主重启；更新前后账号/设置/统计与快照一致，队列不丢失不重复。完整更新体验仍为未来功能，TM-001-004通过只证明最小更新路径。</x:v>
+        <x:v>SHA/tree和DMG摘要一致
+完整集合逐例PASS且清理完成，否则阻断
+Excel行和源摘要一致
+SOP-018真实PASS才进入SOP-019</x:v>
       </x:c>
       <x:c r="H168" s="9" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：本例不直接写入产品用量表；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I168" s="9" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J168" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K168" s="9" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L168" s="9" t="str">
-        <x:v>docs/testing/cases/10-TM-010-software-updates.md:11</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:135</x:v>
       </x:c>
       <x:c r="M168" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N168" s="9" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="169" ht="57" customHeight="1">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" ht="72" customHeight="1">
       <x:c r="A169" s="4" t="str">
-        <x:v>TM-010</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B169" s="4" t="str">
-        <x:v>E2E-TM010-002</x:v>
+        <x:v>TC-TM004-SOURCE-03</x:v>
       </x:c>
       <x:c r="C169" s="4" t="str">
-        <x:v>签名、网络、空间和迁移失败恢复</x:v>
+        <x:v>嵌套子代理目录（TASK-TM004-SOURCE，AC-001，E2E-001）</x:v>
       </x:c>
       <x:c r="D169" s="4" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-SOURCE</x:v>
       </x:c>
       <x:c r="E169" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F169" s="4" t="str">
-        <x:v>数据集 update_packages；对同一干净旧版分别建立四个隔离子场景：坏签名包、下载中断、受限测试卷空间不足、受控迁移失败；每个保存旧版包/DB/配置摘要。故障不能作用用户系统盘/生产库。</x:v>
+        <x:v>2.1.126 已安装二进制显示子代理路径可在 subagents/ 下继续嵌套；确切层级与父链由待取得的原始样本决定。固定数据应含项目A主M100/10、一级子S200/20、嵌套子T=50/5，以及授权根外同名文件X=999/99。</x:v>
       </x:c>
       <x:c r="G169" s="4" t="str">
-        <x:v>每个失败均不能形成半更新；原账号/统计和包的可用状态可验证。网络恢复后的成功需要完整包校验；迁移失败恢复来源与摘要明确。四个子场景全部为本case必需，不能挑一项通过。</x:v>
+        <x:v>项目A可信total385/3次调用
+不读取X
+总量和归属不变
+不猜A</x:v>
       </x:c>
       <x:c r="H169" s="4" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读事件唯一键、父项目与总量3/385；缺链变体的T不得纳入A可信聚合；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I169" s="4" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J169" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K169" s="4" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L169" s="4" t="str">
-        <x:v>docs/testing/cases/10-TM-010-software-updates.md:28</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:139</x:v>
       </x:c>
       <x:c r="M169" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N169" s="4" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="170" ht="57" customHeight="1">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" ht="72" customHeight="1">
       <x:c r="A170" s="9" t="str">
-        <x:v>TM-010</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B170" s="9" t="str">
-        <x:v>E2E-TM010-003</x:v>
+        <x:v>TC-TM004-PARSER-03</x:v>
       </x:c>
       <x:c r="C170" s="9" t="str">
-        <x:v>升级默认地址和手动覆盖</x:v>
+        <x:v>同一消息多内容块和 Agent 摘要（TASK-TM004-PARSER，AC-001，E2E-001）</x:v>
       </x:c>
       <x:c r="D170" s="9" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-PARSER</x:v>
       </x:c>
       <x:c r="E170" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F170" s="9" t="str">
-        <x:v>数据集 server_default_migration；server_default_migration planned；两套旧安装A从未设置地址、B已手动设置；候选内置一个届时确定且测试可访问的生产HTTPS默认地址。两源有独立账号/数据/会话，公钥不可随URL编辑。</x:v>
+        <x:v>同一次主调用M100/10拆为至少两个带相同 message.id 与 usage 的 assistant 内容块，另有 Agent 工具结果的 totalTokens/usage 摘要与子S200/20原始调用；本机独立结构探针已实际生成31/9双块，CLI 写两行相同 ID 和完整 usage，子代理19/6的父工具结果出现 total_tokens: 25。</x:v>
       </x:c>
       <x:c r="G170" s="9" t="str">
-        <x:v>只有无手动覆盖安装跟随新版默认；显式覆盖即使恰好等于旧默认也应按已经确定的配置来源规则处理。改变origin需重新服务认证，旧token不能跨源复用。</x:v>
+        <x:v>UI/SQLite为1次调用、total110
+可信为M+S两次、total330
+仍330</x:v>
       </x:c>
       <x:c r="H170" s="9" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读源消息调用键2个/330，父Agent汇总不能额外成为第三次调用；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I170" s="9" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J170" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K170" s="9" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L170" s="9" t="str">
-        <x:v>docs/testing/cases/10-TM-010-software-updates.md:45</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:143</x:v>
       </x:c>
       <x:c r="M170" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N170" s="9" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="171" ht="57" customHeight="1">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" ht="72" customHeight="1">
       <x:c r="A171" s="4" t="str">
-        <x:v>TM-011</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B171" s="4" t="str">
-        <x:v>E2E-TM011-001</x:v>
+        <x:v>TC-TM004-LINEAGE-03</x:v>
       </x:c>
       <x:c r="C171" s="4" t="str">
-        <x:v>SQLite迁移与中断恢复</x:v>
+        <x:v>forkedFrom 复制与改写 UUID（TASK-TM004-LINEAGE，AC-002，E2E-002）</x:v>
       </x:c>
       <x:c r="D171" s="4" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-LINEAGE</x:v>
       </x:c>
       <x:c r="E171" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F171" s="4" t="str">
-        <x:v>数据集 migration_snapshots；migration_snapshots planned；旧schema副本含固定账号/事件/队列、预计算记录数/Token/金额；候选迁移版本和明确故障点。全部作用私有临时库。</x:v>
+        <x:v>已计M100/10；分别用2.1.126真实生成的 fork 复制记录（保留 UUID）和改写 UUID 记录，依据实际 raw 的跨文件调用身份/父链判定，不能假定两者都含 forkedFrom；再追加真正新N50/5。</x:v>
       </x:c>
       <x:c r="G171" s="4" t="str">
-        <x:v>成功迁移只改变设计允许的schema/数据；账号、记录数、Token、费用/队列归属不丢。失败恢复到可启动一致状态，重复启动不重复迁移数据。不能以文件存在作为恢复成功。</x:v>
+        <x:v>M仅计一次且total110
+均仍110并在诊断/关系中可追溯原M
+total165/2次
+仍两次可信调用且total165</x:v>
       </x:c>
       <x:c r="H171" s="4" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读可信调用键2个、继承引用指向M；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I171" s="4" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J171" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K171" s="4" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L171" s="4" t="str">
-        <x:v>docs/testing/cases/11-TM-011-data-migration.md:11</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:147</x:v>
       </x:c>
       <x:c r="M171" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N171" s="4" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="172" ht="57" customHeight="1">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" ht="72" customHeight="1">
       <x:c r="A172" s="9" t="str">
-        <x:v>TM-011</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B172" s="9" t="str">
-        <x:v>E2E-TM011-002</x:v>
+        <x:v>TC-TM004-LINEAGE-04</x:v>
       </x:c>
       <x:c r="C172" s="9" t="str">
-        <x:v>未来SQLite到MySQL迁移</x:v>
+        <x:v>fork-context-ref 父链（TASK-TM004-LINEAGE，AC-002，E2E-002）</x:v>
       </x:c>
       <x:c r="D172" s="9" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-LINEAGE</x:v>
       </x:c>
       <x:c r="E172" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F172" s="9" t="str">
-        <x:v>数据集 migration_snapshots；仅后续独立版本适用；用户已确定v0.1.0继续SQLite。需要隔离源SQLite、目标MySQL、固定多成员/多项目用量快照、字符/时间/Decimal边界和独立expected。</x:v>
+        <x:v>2.1.126真实子代理 fork 记录中带 agentId,parentSessionId,parentLastUuid,contextLength；父会话存在M100/10，子代理仅新增S200/20。</x:v>
       </x:c>
       <x:c r="G172" s="9" t="str">
-        <x:v>源/目标记录数、Token、Decimal金额及权限结果一致，ID和幂等语义保持；不重复历史且旧源未被破坏。MySQL版本、字符集和迁移范围须在对应版本指定。</x:v>
+        <x:v>可信110
+可信330/2次而非440
+可信M/S两次且total330
+引用解析到M的既有调用键</x:v>
       </x:c>
       <x:c r="H172" s="9" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读M/S各一条及引用，total330；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I172" s="9" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J172" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K172" s="9" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L172" s="9" t="str">
-        <x:v>docs/testing/cases/11-TM-011-data-migration.md:28</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:151</x:v>
       </x:c>
       <x:c r="M172" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N172" s="9" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="173" ht="57" customHeight="1">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" ht="72" customHeight="1">
       <x:c r="A173" s="4" t="str">
-        <x:v>TM-011</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B173" s="4" t="str">
-        <x:v>E2E-TM011-003</x:v>
+        <x:v>TC-TM004-LINEAGE-05</x:v>
       </x:c>
       <x:c r="C173" s="4" t="str">
-        <x:v>备份恢复与旧客户端补传</x:v>
+        <x:v>缺失或矛盾父链（TASK-TM004-LINEAGE，AC-002/003，E2E-002/003）</x:v>
       </x:c>
       <x:c r="D173" s="4" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-LINEAGE</x:v>
       </x:c>
       <x:c r="E173" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F173" s="4" t="str">
-        <x:v>数据集 migration_snapshots；隔离服务已确认事件A/B与旧客户端未确认C；备份包含schema/数据/版本/摘要，另保存不在备份里的独立oracle。恢复目标必须为空且带测试标记。</x:v>
+        <x:v>在上一例的合成同构目录中分别移除引用父文件、指向不存在的 parentLastUuid、或提供无 forkedFrom 但UUID改写的复制历史；这些是测试故障注入，不能标为厂商实际输出。</x:v>
       </x:c>
       <x:c r="G173" s="4" t="str">
-        <x:v>备份能实际恢复而非只压缩成功；A/B不丢，重复补传不增加；C最终只出现一次，账号/权限符合恢复基线。队列与服务确认一致，旧客户端协议兼容。</x:v>
+        <x:v>M仅计一次且total110
+App显示未确定来源诊断，可信总量仍110、不能把不明副本计为新调用或有效零
+若真实新增S200/20可独立识别则总量330
+可信总量保持且诊断随恢复更新</x:v>
       </x:c>
       <x:c r="H173" s="4" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读未确定记录与可信M/S计数，不能借SQL灌成功；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I173" s="4" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J173" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K173" s="4" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L173" s="4" t="str">
-        <x:v>docs/testing/cases/11-TM-011-data-migration.md:45</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:155</x:v>
       </x:c>
       <x:c r="M173" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N173" s="4" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="174" ht="57" customHeight="1">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174" ht="102" customHeight="1">
       <x:c r="A174" s="9" t="str">
-        <x:v>TM-011</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B174" s="9" t="str">
-        <x:v>E2E-TM011-004</x:v>
+        <x:v>TC-TM004-SOURCE-04</x:v>
       </x:c>
       <x:c r="C174" s="9" t="str">
-        <x:v>保留时间边界与未同步保护</x:v>
+        <x:v>预览截断后的可续扫覆盖（TASK-TM004-SOURCE，AC-001/004，E2E-001/004）</x:v>
       </x:c>
       <x:c r="D174" s="9" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-SOURCE</x:v>
       </x:c>
       <x:c r="E174" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F174" s="9" t="str">
-        <x:v>数据集 migration_snapshots；固定参考时间和Asia/Shanghai；本地90天/服务端365天。分别生成保留首日00:00、前一秒、前一天的已确认事件，以及同样超龄但未同步事件；具备可控时钟与独立边界oracle。</x:v>
+        <x:v>本例独占授权根，固定程序按 TM-002 已提交枚举顺序生成至少1025个普通 .jsonl 文件及足够目录项；前段有主M100/10，预览截断范围外且至少第五个256项采集页的深层 subagents/ 文件有子S50/5，其余文件没有可计量调用。另备可控制的页间撤权/恢复点。</x:v>
       </x:c>
       <x:c r="G174" s="9" t="str">
-        <x:v>保留首日00:00仍在，早一秒的已同步记录被清理；本地/服务按各自天数独立判定。未同步记录即使超龄仍保护，成功补传仅计一次；历史缺失不能显示真实0。</x:v>
+        <x:v>1000文件预览显示被截断，不声称全量
+UI 可显示已见M110，但 TM-003 coverage.scan_incomplete=1
+使用 openCandidateReadOnly(candidateToken) 读原始行；在另一次固定变体于页间撤权，下一页或打开须拒绝，cancelScan 后 scan_incomplete=1，重授后以新授权世代续扫
+可信 M+S 两调用、input150/output15/total165，scan_incomplete=0 才可显示本次覆盖完成；重启重扫总量不变</x:v>
       </x:c>
       <x:c r="H174" s="9" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读各来源事件键、聚合 (2,150,15)、游标及 coverage.scan_incomplete；中途必须为1；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I174" s="9" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J174" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K174" s="9" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L174" s="9" t="str">
-        <x:v>docs/testing/cases/11-TM-011-data-migration.md:62</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:159</x:v>
       </x:c>
       <x:c r="M174" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N174" s="9" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="175" ht="57" customHeight="1">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" ht="102" customHeight="1">
       <x:c r="A175" s="4" t="str">
-        <x:v>TM-012</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B175" s="4" t="str">
-        <x:v>E2E-TM012-001</x:v>
+        <x:v>TC-TM004-INCREMENTAL-03</x:v>
       </x:c>
       <x:c r="C175" s="4" t="str">
-        <x:v>菜单栏摘要、暂停恢复与刷新</x:v>
+        <x:v>跨工具同 ID 与 Claude 复制历史（TASK-TM004-INCREMENTAL，AC-001/002，E2E-001/002）</x:v>
       </x:c>
       <x:c r="D175" s="4" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM004-INCREMENTAL</x:v>
       </x:c>
       <x:c r="E175" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F175" s="4" t="str">
-        <x:v>数据集 diagnostic_states；diagnostic_states planned；已采集A=100/10；暂停期间追加B=200/20并重放A。依赖实际采集、统计和同步功能，使用专用日志目录。</x:v>
+        <x:v>同一合成主体、各自经 UI 授权的 Codex 与 Claude 隔离根。固定本地响应使 Codex 原生 payload.response_id 与 Claude 主 assistant.message.id 字面均为 shared-call-01，分别有 C=11/1 与 M=100/10；Claude 原生 --fork-session 复制M，再有独立 Agent 子调用S=200/20（新 message.id、与父同 sessionId 但带 agentId）。另以明确标记的衍生故障数据令同一 Claude message.id 出现矛盾101/10，该行不冒称 CLI 原件。</x:v>
       </x:c>
       <x:c r="G175" s="4" t="str">
-        <x:v>初始total110、暂停期间仍110，恢复后唯一A/B、total330；手动刷新与重启不重复。菜单栏与主窗口同一筛选口径；暂停状态不伪装成没有日志。</x:v>
+        <x:v>可信1次/total12
+可信2次/input111/output11/total122，跨工具同字面 ID 不冲突
+可信3次/input311/output31/total342
+可信仍3次/342，出现 identity_conflict 与覆盖不完整</x:v>
       </x:c>
       <x:c r="H175" s="4" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
+变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
+核验：规划只读核对：只读同一 principal_key 下 source=codex 与 source=claude_code 各自事件数1/2、source_event_key 不同，Agent source_scope_key 与主来源可区分，复制M不多行，冲突不覆写原M；键与归属均不得存原生ID/完整路径；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
       <x:c r="I175" s="4" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J175" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K175" s="4" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L175" s="4" t="str">
-        <x:v>docs/testing/cases/12-TM-012-menu-diagnostics.md:11</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:163</x:v>
       </x:c>
       <x:c r="M175" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N175" s="4" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
+        <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
     </x:row>
     <x:row r="176" ht="57" customHeight="1">
       <x:c r="A176" s="9" t="str">
-        <x:v>TM-012</x:v>
+        <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B176" s="9" t="str">
-        <x:v>E2E-TM012-002</x:v>
+        <x:v>E2E-TM005-001</x:v>
       </x:c>
       <x:c r="C176" s="9" t="str">
-        <x:v>诊断状态、恢复和登录启动</x:v>
+        <x:v>日期筛选、趋势和明细</x:v>
       </x:c>
       <x:c r="D176" s="9" t="str">
         <x:v>待拆解</x:v>
@@ -14327,10 +15715,10 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F176" s="9" t="str">
-        <x:v>数据集 diagnostic_states；独立子场景：已授权目录失效、真实服务不可达/恢复、测试App登录启动开关。故障作用测试目录/进程；使用已登录桌面与可自动检查的系统设置。</x:v>
+        <x:v>数据集 date_ranges；date_ranges 已由 scripts/test_data.py 提供标准化语义样例，固定2026-09-29T04:00:00Z、Asia/Shanghai、seed42；13行含1重复、12唯一。需另有已验证raw输入映射和真实App导入流程，当前未实现。</x:v>
       </x:c>
       <x:c r="G176" s="9" t="str">
-        <x:v>错误与真实目录/网络故障一致，不能用旧缓存一直显示健康；恢复后状态及时更新，未同步数据不丢。启动设置与OS登记/实际启动行为一致，测试结束恢复本次测试前状态。</x:v>
+        <x:v>独立expected中的total依次16500、110、17380、27830、31130；custom=2200。today共5条、input15000、output1500、cache1700、reasoning170，cache/reasoning不再相加；custom-start包含、custom-end排除。趋势点及明细按expected事件时间逐条核对。</x:v>
       </x:c>
       <x:c r="H176" s="9" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
@@ -14347,39 +15735,4210 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L176" s="9" t="str">
-        <x:v>docs/testing/cases/12-TM-012-menu-diagnostics.md:28</x:v>
+        <x:v>docs/testing/cases/05-TM-005-usage-statistics.md:19</x:v>
       </x:c>
       <x:c r="M176" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N176" s="9" t="str">
-        <x:v>v0.1.0-20260929T074814Z</x:v>
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177" ht="57" customHeight="1">
+      <x:c r="A177" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B177" s="4" t="str">
+        <x:v>E2E-TM005-002</x:v>
+      </x:c>
+      <x:c r="C177" s="4" t="str">
+        <x:v>时区、月边界与缺失值</x:v>
+      </x:c>
+      <x:c r="D177" s="4" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E177" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F177" s="4" t="str">
+        <x:v>数据集 date_ranges；复用date_ranges中的2026-09-28T15:59:59Z与16:00:00Z、2026-08-30T15:59:59Z与16:00:00Z边界。另需补充覆盖缺口、已覆盖零调用日、unknown字段三类状态；当前生成器未覆盖后面三类。</x:v>
+      </x:c>
+      <x:c r="G177" s="4" t="str">
+        <x:v>Shanghai下15:59:59Z仍属前日、16:00:00Z属次日；UTC下二者同属UTC日期。无覆盖显示缺失，真实零可显示0，unknown字段显示未知；不得互相代替。各范围expected须独立按当地日期边界列出，不调用产品查询生成。</x:v>
+      </x:c>
+      <x:c r="H177" s="4" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I177" s="4" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J177" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K177" s="4" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L177" s="4" t="str">
+        <x:v>docs/testing/cases/05-TM-005-usage-statistics.md:36</x:v>
+      </x:c>
+      <x:c r="M177" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N177" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178" ht="102" customHeight="1">
+      <x:c r="A178" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B178" s="9" t="str">
+        <x:v>TC-TM005-CONTRACT-01</x:v>
+      </x:c>
+      <x:c r="C178" s="9" t="str">
+        <x:v>两来源重复事件不增量</x:v>
+      </x:c>
+      <x:c r="D178" s="9" t="str">
+        <x:v>TASK-TM005-EVENT-CONTRACT</x:v>
+      </x:c>
+      <x:c r="E178" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F178" s="9" t="str">
+        <x:v>seed42 事件中 Codex today-gpt 和 Claude Code today-sonnet 各一原生事件，另各有同源重复读取；全部绑定同一合成账号</x:v>
+      </x:c>
+      <x:c r="G178" s="9" t="str">
+        <x:v>1. 从空客户端库在 App 授权两目录并等待采集；UI 应显示两个来源已读取，DB 只读记录应有两条可信事件，总量 3300。
+2. 复制/重放两条原生事件并在 App 点刷新；UI 总量仍 3300，DB 的唯一来源事件身份仍为两条，诊断不能误报新用量。
+3. 退出并由同一已安装 App 重启后再刷新；总量和身份仍不变。只清理由本例创建的文件与进程。</x:v>
+      </x:c>
+      <x:c r="H178" s="9" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I178" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J178" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K178" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L178" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:19</x:v>
+      </x:c>
+      <x:c r="M178" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N178" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" ht="102" customHeight="1">
+      <x:c r="A179" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B179" s="4" t="str">
+        <x:v>TC-TM005-CONTRACT-02</x:v>
+      </x:c>
+      <x:c r="C179" s="4" t="str">
+        <x:v>未知字段不伪造零</x:v>
+      </x:c>
+      <x:c r="D179" s="4" t="str">
+        <x:v>TASK-TM005-EVENT-CONTRACT</x:v>
+      </x:c>
+      <x:c r="E179" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F179" s="4" t="str">
+        <x:v>一条 Codex 缺 output、另一条 Claude Code 缺 input 的受支持原生记录，另有两条可信调用各 110 token</x:v>
+      </x:c>
+      <x:c r="G179" s="4" t="str">
+        <x:v>1. 从空库经 App 采集两条可信调用；卡片显示已知总量 220，DB 有两条可信事件。
+2. 追加两条缺字段记录并刷新；UI 显示相应未知诊断，完整总量不能把未知字段当 0。可信 220 不被覆盖，DB 的 unknown 状态与来源可只读辨认。
+3. 重扫与重启；可信 220 和两条未知状态保持，不能变成成功零用量。</x:v>
+      </x:c>
+      <x:c r="H179" s="4" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I179" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J179" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K179" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L179" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:29</x:v>
+      </x:c>
+      <x:c r="M179" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N179" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180" ht="102" customHeight="1">
+      <x:c r="A180" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B180" s="9" t="str">
+        <x:v>TC-TM005-CONTRACT-03</x:v>
+      </x:c>
+      <x:c r="C180" s="9" t="str">
+        <x:v>Claude fork 复制历史与新增调用</x:v>
+      </x:c>
+      <x:c r="D180" s="9" t="str">
+        <x:v>TASK-TM005-EVENT-CONTRACT</x:v>
+      </x:c>
+      <x:c r="E180" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F180" s="9" t="str">
+        <x:v>使用 TM-004 最终锁定的 Claude Code 2.1.126 自写原始 fork fixture：父会话可信调用 M=100/10，fork 文件复制父历史并新增可信调用 N=50/5；已固定的来源样本复制父 UUID、message.id、usage，却没有 forkedFrom</x:v>
+      </x:c>
+      <x:c r="G180" s="9" t="str">
+        <x:v>1. 在 App 授权本例 Claude 根并采集父会话 M；统计明细仅 M 一次，总量 110，DB 有一个可信来源调用身份。
+2. 由已验证 CLI 操作生成/写入上述固定 fork 原生日志后经 App 刷新；UI/DB 恰有 M、N 两个可信调用，total=165。复制的父历史不另入账，缺 forkedFrom 本身不构成新调用证明。
+3. 重扫 fork/父文件并重启 App；可信事件身份及 165 保持。若最终来源合同不能证明本例固定 fixture 的复制和新增关系，本例在运行前保持 BLOCKED，不能临场改写为另一预期或手填 PASS。</x:v>
+      </x:c>
+      <x:c r="H180" s="9" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I180" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J180" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K180" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L180" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:39</x:v>
+      </x:c>
+      <x:c r="M180" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N180" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181" ht="102" customHeight="1">
+      <x:c r="A181" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B181" s="4" t="str">
+        <x:v>TC-TM005-CONTRACT-04</x:v>
+      </x:c>
+      <x:c r="C181" s="4" t="str">
+        <x:v>Claude 父会话与子代理独立用量</x:v>
+      </x:c>
+      <x:c r="D181" s="4" t="str">
+        <x:v>TASK-TM005-EVENT-CONTRACT</x:v>
+      </x:c>
+      <x:c r="E181" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F181" s="4" t="str">
+        <x:v>TM-004 最终锁定的 Claude Code 2.1.126 自写主会话与 subagents/agent-*.jsonl fixture；设计数字为父调用 M=100/10、子代理调用 S=200/20，两者各有独立 usage。已固定的来源样本中子文件带 agentId、isSidechain=true，与父文件同 sessionId</x:v>
+      </x:c>
+      <x:c r="G181" s="4" t="str">
+        <x:v>1. App 授权本例 Claude 根并采集父会话；只有父调用 M 入账，UI/DB 显示可信 110 及父来源身份。
+2. 子代理原生日志完整写入并由 App 采集；UI/DB 恰有 M、S 两个可信调用，total=330。父会话对子代理的引用不能另加 220；父子同 sessionId 也不能把子代理的真实调用消掉。
+3. 重扫主/子文件、刷新并重启；两个唯一身份与 330 保持，模型维度分别保留实际模型标识。若最终 raw 无法证明该父子关系或独立调用，本例在运行前保持 BLOCKED，不临场更换结果判据。</x:v>
+      </x:c>
+      <x:c r="H181" s="4" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I181" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J181" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K181" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L181" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:49</x:v>
+      </x:c>
+      <x:c r="M181" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N181" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182" ht="102" customHeight="1">
+      <x:c r="A182" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B182" s="9" t="str">
+        <x:v>TC-TM005-CONTRACT-05</x:v>
+      </x:c>
+      <x:c r="C182" s="9" t="str">
+        <x:v>Codex 逐响应与缓存子项</x:v>
+      </x:c>
+      <x:c r="D182" s="9" t="str">
+        <x:v>TASK-TM005-EVENT-CONTRACT</x:v>
+      </x:c>
+      <x:c r="E182" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F182" s="9" t="str">
+        <x:v>TM-003 阶段隔离原生 Codex 0.158.0-alpha.2.1 rollout 形状：一条 token_usage_record，response_id=tm003-native-probe-response-1，input100、cached read20、cache write0、output10、reasoning2、total110；原始 JSONL SHA-256 3b30cfa81c0c29a80f1bfc1de5bf823db01a9a85636e41ec58dfdd00f0436d08</x:v>
+      </x:c>
+      <x:c r="G182" s="9" t="str">
+        <x:v>1. 由 TM-003 最终固定数据程序在本例拥有的 Codex 根生成受支持原生日志，从安装后的 App 授权并采集；UI 和只读 DB 恰有一个可信逐响应身份，input100、output10、total110。
+2. UI 缓存读20、缓存写0、推理输出2作为已知子项分别显示，不再加到 total；同一 rollout 内 turn/thread 累计快照不能生成第二个 110 调用。
+3. 重扫、刷新、重启后仍为一个身份/110；原生日志原件或派生 fixture 的摘要与运行记录一致。</x:v>
+      </x:c>
+      <x:c r="H182" s="9" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I182" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J182" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K182" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L182" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:59</x:v>
+      </x:c>
+      <x:c r="M182" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N182" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183" ht="102" customHeight="1">
+      <x:c r="A183" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B183" s="4" t="str">
+        <x:v>TC-TM005-CONTRACT-06</x:v>
+      </x:c>
+      <x:c r="C183" s="4" t="str">
+        <x:v>Codex fork 的累计快照不当增量</x:v>
+      </x:c>
+      <x:c r="D183" s="4" t="str">
+        <x:v>TASK-TM005-EVENT-CONTRACT</x:v>
+      </x:c>
+      <x:c r="E183" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F183" s="4" t="str">
+        <x:v>上游最终固定的 Codex exec fork 原生日志；设计数字为父响应 A=100/10、B=200/20，fork 新文件仅新响应 C=300/30，C 行的 thread_token_usage 为 A+B+C 累计 660</x:v>
+      </x:c>
+      <x:c r="G183" s="4" t="str">
+        <x:v>1. App 采集父日志 A/B；UI 与 DB 应有两个可信响应身份，total 330。
+2. App 读取仅含 C 的 fork 新文件；可信身份增至三个，total 660。C 的逐响应 330 只加一次，thread_token_usage=660 不另加为第四个调用或在本步加 660。
+3. 重扫父/fork 文件并重启；仍三个身份/660。若上游 fork 身份/解析证据不完整，记录未确定诊断，不按累计值补造事件。</x:v>
+      </x:c>
+      <x:c r="H183" s="4" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I183" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J183" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K183" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L183" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:69</x:v>
+      </x:c>
+      <x:c r="M183" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N183" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184" ht="102" customHeight="1">
+      <x:c r="A184" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B184" s="9" t="str">
+        <x:v>TC-TM005-CONTRACT-07</x:v>
+      </x:c>
+      <x:c r="C184" s="9" t="str">
+        <x:v>Claude 同消息多行不重复</x:v>
+      </x:c>
+      <x:c r="D184" s="9" t="str">
+        <x:v>TASK-TM005-EVENT-CONTRACT</x:v>
+      </x:c>
+      <x:c r="E184" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F184" s="9" t="str">
+        <x:v>TM-004 提交 dda5ccb 所记录的 Claude Code 2.1.126 原生日志形状：一个 API 消息的双 text 块对应两条 assistant JSONL，message.id 相同且每行都带完整 usage input31/output9</x:v>
+      </x:c>
+      <x:c r="G184" s="9" t="str">
+        <x:v>1. App 采集该消息；UI/DB 只出现一个可信调用身份，input31/output9/total40，而不是两行求和的 80。
+2. 刷新、重扫并重启；仍一个调用/40，明细不出现第二个相同消息。</x:v>
+      </x:c>
+      <x:c r="H184" s="9" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I184" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J184" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K184" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L184" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:79</x:v>
+      </x:c>
+      <x:c r="M184" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N184" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185" ht="102" customHeight="1">
+      <x:c r="A185" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B185" s="4" t="str">
+        <x:v>TC-TM005-CONTRACT-08</x:v>
+      </x:c>
+      <x:c r="C185" s="4" t="str">
+        <x:v>两来源原生 ID 碰撞与同源重放</x:v>
+      </x:c>
+      <x:c r="D185" s="4" t="str">
+        <x:v>TASK-TM005-EVENT-CONTRACT</x:v>
+      </x:c>
+      <x:c r="E185" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F185" s="4" t="str">
+        <x:v>隔离 Codex 与 Claude 原生日志各有不同的真实调用，却故意使其来源原生调用 ID 同为 shared-native-id-1；设计用量 Codex A=100/10、Claude B=200/20。再重放 Claude B 的相同原生记录</x:v>
+      </x:c>
+      <x:c r="G185" s="4" t="str">
+        <x:v>1. App 经两授权根先采集 Codex A；UI/只读 SQLite 有一个可信调用，total 110，记录 source=codex 与 source_event_key 的不泄露表示。
+2. App 再采集同原生 ID 的 Claude B；UI/SQLite 应有两个不同来源的可信调用，total 330。不能因跨来源 ID 碰撞压掉 B，也不能把 A 改写为 B。
+3. 重放 B 并刷新/重启；仍两个可信调用/330，同一 Claude 调用未重复。SQLite 旁证须同时检查两个来源身份、各自 token 和唯一键，而非仅检查总量。</x:v>
+      </x:c>
+      <x:c r="H185" s="4" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I185" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J185" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K185" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L185" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:88</x:v>
+      </x:c>
+      <x:c r="M185" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N185" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186" ht="102" customHeight="1">
+      <x:c r="A186" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B186" s="9" t="str">
+        <x:v>TC-TM005-CONTRACT-09</x:v>
+      </x:c>
+      <x:c r="C186" s="9" t="str">
+        <x:v>Claude 同 ID 继承关系无法证明</x:v>
+      </x:c>
+      <x:c r="D186" s="9" t="str">
+        <x:v>TASK-TM005-EVENT-CONTRACT</x:v>
+      </x:c>
+      <x:c r="E186" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F186" s="9" t="str">
+        <x:v>同一合成账号下两条 Claude Agent/会话原始记录都用 assistant.message.id=shared-claude-id-1、相同模型和 input100/output10；首调用 A 已可信，第二条 B 位于另一 Agent/会话，缺少能证明复制或独立新调用的父链/来源证据。相同用量/模型使本例只检验继承不确定性，不与 identity_conflict 混合</x:v>
+      </x:c>
+      <x:c r="G186" s="9" t="str">
+        <x:v>1. App 采集 A；UI/SQLite 有一个可信 Claude 调用，已知部分 110。
+2. 追加 B 并刷新；不能静默把 B 视为 A 的已证复制，也不能武断另加 110。UI 显示统计不完整、已知部分仍 110；诊断 unverified_inheritance，覆盖状态不完整。SQLite 保留 A 的可信键/值及不含原始 ID/完整路径的诊断代码、数量和来源归属旁证，不要求持久化 B 原文。
+3. 重扫/重启后诊断与已知部分保持；若 TM-004 最终合同找到可证复制/独立身份，先修本用例输入与预期并重新基线，不在运行时临时选答案。</x:v>
+      </x:c>
+      <x:c r="H186" s="9" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I186" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J186" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K186" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L186" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:98</x:v>
+      </x:c>
+      <x:c r="M186" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N186" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" ht="102" customHeight="1">
+      <x:c r="A187" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B187" s="4" t="str">
+        <x:v>TC-TM005-CONTRACT-10</x:v>
+      </x:c>
+      <x:c r="C187" s="4" t="str">
+        <x:v>同 ID 用量或模型冲突</x:v>
+      </x:c>
+      <x:c r="D187" s="4" t="str">
+        <x:v>TASK-TM005-EVENT-CONTRACT</x:v>
+      </x:c>
+      <x:c r="E187" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F187" s="4" t="str">
+        <x:v>Claude 同 assistant.message.id=conflict-claude-id-1 的首可信调用 A=100/10、模型 model-a；两个稳定变体 TC-TM005-CONTRACT-10#USAGE（后续同 ID usage 改为 200/20）与 TC-TM005-CONTRACT-10#MODEL（后续同 ID 用量仍 100/10、模型改为 model-b）</x:v>
+      </x:c>
+      <x:c r="G187" s="4" t="str">
+        <x:v>1. 每个变体从独立空客户端库采集 A；UI/SQLite 为一个可信事件、total110、模型 model-a。
+2. 追加对应矛盾行并刷新；identity_conflict 诊断出现，A 的用量和模型保持，已知部分 110，不新增/覆盖可信事件，不把统计标为完整。
+3. 重扫/重启；冲突诊断和首可信值保持。两个变体分别保存原始结果；不得用一个变体通过覆盖另一变体。</x:v>
+      </x:c>
+      <x:c r="H187" s="4" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I187" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J187" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K187" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L187" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:108</x:v>
+      </x:c>
+      <x:c r="M187" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N187" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188" ht="102" customHeight="1">
+      <x:c r="A188" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B188" s="9" t="str">
+        <x:v>TC-TM005-CONTRACT-10#USAGE</x:v>
+      </x:c>
+      <x:c r="C188" s="9" t="str">
+        <x:v>同 ID 用量或模型冲突 · 变体</x:v>
+      </x:c>
+      <x:c r="D188" s="9" t="str">
+        <x:v>TASK-TM005-EVENT-CONTRACT</x:v>
+      </x:c>
+      <x:c r="E188" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F188" s="9" t="str">
+        <x:v>从独立空库导入 A，再导入同 ID、同模型但 200/20 的行</x:v>
+      </x:c>
+      <x:c r="G188" s="9" t="str">
+        <x:v>identity_conflict，可信统计仍为 A 的 110。</x:v>
+      </x:c>
+      <x:c r="H188" s="9" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I188" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J188" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K188" s="9" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L188" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:108</x:v>
+      </x:c>
+      <x:c r="M188" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N188" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189" ht="102" customHeight="1">
+      <x:c r="A189" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B189" s="4" t="str">
+        <x:v>TC-TM005-CONTRACT-10#MODEL</x:v>
+      </x:c>
+      <x:c r="C189" s="4" t="str">
+        <x:v>同 ID 用量或模型冲突 · 变体</x:v>
+      </x:c>
+      <x:c r="D189" s="4" t="str">
+        <x:v>TASK-TM005-EVENT-CONTRACT</x:v>
+      </x:c>
+      <x:c r="E189" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F189" s="4" t="str">
+        <x:v>从独立空库导入 A，再导入同 ID、100/10 但模型为 model-b 的行</x:v>
+      </x:c>
+      <x:c r="G189" s="4" t="str">
+        <x:v>identity_conflict，可信统计仍为 A 的 110 且模型为 model-a。</x:v>
+      </x:c>
+      <x:c r="H189" s="4" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I189" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J189" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K189" s="4" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L189" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:108</x:v>
+      </x:c>
+      <x:c r="M189" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N189" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190" ht="102" customHeight="1">
+      <x:c r="A190" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B190" s="9" t="str">
+        <x:v>TC-TM005-RANGE-01</x:v>
+      </x:c>
+      <x:c r="C190" s="9" t="str">
+        <x:v>今天</x:v>
+      </x:c>
+      <x:c r="D190" s="9" t="str">
+        <x:v>TASK-TM005-RANGE-QUERY
+TASK-TM005-UI</x:v>
+      </x:c>
+      <x:c r="E190" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F190" s="9" t="str">
+        <x:v>seed42 全部 13 行映射为两来源原生事件，1 行为 today-gpt 原样重复；上海日锚点与运行日一致</x:v>
+      </x:c>
+      <x:c r="G190" s="9" t="str">
+        <x:v>1. 经 App 采集后选“今天”；卡片应显示唯一 5 次、input 15000、output 1500、total 16500、cached read 1700、reasoning 170，子项不再加到 total。规范化语义样例没有 cache write 字段；若最终 raw 映射也没有可核实字段，该子项应显示未知而非 0。
+2. 检查趋势今天点为 16500，明细 ID 集合恰为 today-gpt/sonnet/qwen/glm/unknown 的五项；每条来源、模型、UTC 时间与原生日志对应，不显示重复行。
+3. 只读 DB 核对今天半开 UTC 范围内五个唯一可信身份及各字段合计；源集合、UI、DB 相同。</x:v>
+      </x:c>
+      <x:c r="H190" s="9" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I190" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J190" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K190" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L190" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:121</x:v>
+      </x:c>
+      <x:c r="M190" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N190" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191" ht="102" customHeight="1">
+      <x:c r="A191" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B191" s="4" t="str">
+        <x:v>TC-TM005-RANGE-02</x:v>
+      </x:c>
+      <x:c r="C191" s="4" t="str">
+        <x:v>昨天</x:v>
+      </x:c>
+      <x:c r="D191" s="4" t="str">
+        <x:v>TASK-TM005-RANGE-QUERY</x:v>
+      </x:c>
+      <x:c r="E191" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F191" s="4" t="str">
+        <x:v>同一批原生数据；yesterday 在上海日界前 1 秒</x:v>
+      </x:c>
+      <x:c r="G191" s="4" t="str">
+        <x:v>1. 选“昨天”；卡片仅 1 次，input 100、output 10、total 110，cache 20、reasoning 2。
+2. 趋势该日点 110、明细仅 yesterday；today-gpt 的上海 00:00 边界事件不能出现在此日。
+3. 只读 DB 查询该当地日换算的 UTC 半开区间，仅返回 yesterday；确认筛选没有写用量表。</x:v>
+      </x:c>
+      <x:c r="H191" s="4" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I191" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J191" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K191" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L191" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:131</x:v>
+      </x:c>
+      <x:c r="M191" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N191" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192" ht="102" customHeight="1">
+      <x:c r="A192" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B192" s="9" t="str">
+        <x:v>TC-TM005-RANGE-03</x:v>
+      </x:c>
+      <x:c r="C192" s="9" t="str">
+        <x:v>近 7 天</x:v>
+      </x:c>
+      <x:c r="D192" s="9" t="str">
+        <x:v>TASK-TM005-RANGE-QUERY</x:v>
+      </x:c>
+      <x:c r="E192" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F192" s="9" t="str">
+        <x:v>上海当地 09-23 至 29 日语义窗口整体平移到运行日</x:v>
+      </x:c>
+      <x:c r="G192" s="9" t="str">
+        <x:v>1. 选“近 7 天”；卡片 7 次、total 17380，左边界 day7 包含。
+2. 趋势非空日仅为窗口内 day7=770、yesterday=110、today=16500；明细恰为今天五项加 yesterday/day7。其余日期的显示状态按覆盖证明判，不从缺事件推断 0。
+3. 只读 DB 对比 7 个唯一事件身份及 17380；重复 today-gpt 不入账。</x:v>
+      </x:c>
+      <x:c r="H192" s="9" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I192" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J192" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K192" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L192" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:139</x:v>
+      </x:c>
+      <x:c r="M192" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N192" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193" ht="102" customHeight="1">
+      <x:c r="A193" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B193" s="4" t="str">
+        <x:v>TC-TM005-RANGE-04</x:v>
+      </x:c>
+      <x:c r="C193" s="4" t="str">
+        <x:v>近 15 天</x:v>
+      </x:c>
+      <x:c r="D193" s="4" t="str">
+        <x:v>TASK-TM005-RANGE-QUERY</x:v>
+      </x:c>
+      <x:c r="E193" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F193" s="4" t="str">
+        <x:v>上海当地 09-15 至 29 日语义窗口</x:v>
+      </x:c>
+      <x:c r="G193" s="4" t="str">
+        <x:v>1. 选“近 15 天”；卡片 10 次、total 27830，day15 在左边界包含。
+2. 趋势非空日为 day15=1650、custom-start=2200、custom-end=6600、day7=770、yesterday=110、today=16500；明细为这 10 个唯一事件。
+3. 只读 DB 核对半开区间/10 个身份/27830；不把 day30 提前包含。</x:v>
+      </x:c>
+      <x:c r="H193" s="4" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I193" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J193" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K193" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L193" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:147</x:v>
+      </x:c>
+      <x:c r="M193" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N193" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194" ht="102" customHeight="1">
+      <x:c r="A194" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B194" s="9" t="str">
+        <x:v>TC-TM005-RANGE-05</x:v>
+      </x:c>
+      <x:c r="C194" s="9" t="str">
+        <x:v>近 30 天</x:v>
+      </x:c>
+      <x:c r="D194" s="9" t="str">
+        <x:v>TASK-TM005-RANGE-QUERY</x:v>
+      </x:c>
+      <x:c r="E194" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F194" s="9" t="str">
+        <x:v>上海当地 08-31 至 09-29 日语义窗口</x:v>
+      </x:c>
+      <x:c r="G194" s="9" t="str">
+        <x:v>1. 选“近 30 天”；卡片 11 次、total 31130，day30 在左边界包含，前 1 秒的 outside30 排除。
+2. 趋势增加 day30=3300 点；明细为近 15 天十项加 day30，没有 outside30。
+3. 只读 DB 核对 11 个身份/31130；刷新后仍一致。</x:v>
+      </x:c>
+      <x:c r="H194" s="9" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I194" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J194" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K194" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L194" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:155</x:v>
+      </x:c>
+      <x:c r="M194" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N194" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195" ht="102" customHeight="1">
+      <x:c r="A195" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B195" s="4" t="str">
+        <x:v>TC-TM005-RANGE-06</x:v>
+      </x:c>
+      <x:c r="C195" s="4" t="str">
+        <x:v>自定义半开日期</x:v>
+      </x:c>
+      <x:c r="D195" s="4" t="str">
+        <x:v>TASK-TM005-RANGE-QUERY</x:v>
+      </x:c>
+      <x:c r="E195" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F195" s="4" t="str">
+        <x:v>上海当地 09-20 至 21 日语义窗口，结束上界为 09-22 00:00</x:v>
+      </x:c>
+      <x:c r="G195" s="4" t="str">
+        <x:v>1. 在 UI 输入整体平移后的起止日并应用；卡片 1 次、input 2000、output 200、total 2200。
+2. 趋势只有 custom-start=2200 非空点，明细仅该事件；custom-end 在排除上界，不能出现。
+3. DB 只读查询 [start,end)；预期仅返回唯一 custom-start，查询不写入用量。</x:v>
+      </x:c>
+      <x:c r="H195" s="4" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I195" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J195" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K195" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L195" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:163</x:v>
+      </x:c>
+      <x:c r="M195" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N195" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196" ht="102" customHeight="1">
+      <x:c r="A196" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B196" s="9" t="str">
+        <x:v>TC-TM005-RANGE-09</x:v>
+      </x:c>
+      <x:c r="C196" s="9" t="str">
+        <x:v>起日大于止日</x:v>
+      </x:c>
+      <x:c r="D196" s="9" t="str">
+        <x:v>TASK-TM005-RANGE-QUERY</x:v>
+      </x:c>
+      <x:c r="E196" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F196" s="9" t="str">
+        <x:v>上海语义锚点平移后的起日 09-22、止日 09-20；此前已选“今天”显示 16500</x:v>
+      </x:c>
+      <x:c r="G196" s="9" t="str">
+        <x:v>1. 在自定义日期表单输入倒置范围并应用；UI 显示可识别的日期范围错误，不发起新查询，原卡片/趋势/明细仍对应今天 16500/五项。
+2. 只读 DB 核对用量与设置，再恢复有效范围查询；预期倒置范围没有写入，有效范围仍显示 2200，前次错误不污染状态。</x:v>
+      </x:c>
+      <x:c r="H196" s="9" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I196" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J196" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K196" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L196" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:171</x:v>
+      </x:c>
+      <x:c r="M196" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N196" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197" ht="102" customHeight="1">
+      <x:c r="A197" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B197" s="4" t="str">
+        <x:v>TC-TM005-RANGE-10</x:v>
+      </x:c>
+      <x:c r="C197" s="4" t="str">
+        <x:v>空起日与空止日</x:v>
+      </x:c>
+      <x:c r="D197" s="4" t="str">
+        <x:v>TASK-TM005-RANGE-QUERY</x:v>
+      </x:c>
+      <x:c r="E197" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F197" s="4" t="str">
+        <x:v>两个独立变体 TC-TM005-RANGE-10#START_EMPTY（起日空、止日 09-21）和 TC-TM005-RANGE-10#END_EMPTY（起日 09-20、止日空）；此前已选今天 16500</x:v>
+      </x:c>
+      <x:c r="G197" s="4" t="str">
+        <x:v>1. 每个变体独立从今天结果开始，清空指定字段并应用；表单拒绝，保留原卡片 16500、今天趋势和五条明细。
+2. 分别核对没有发起查询或写 DB；补齐字段后自定义有效窗口显示 2200。两个变体分别记录原始结果，不以其中一个通过代替另一个。</x:v>
+      </x:c>
+      <x:c r="H197" s="4" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I197" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J197" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K197" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L197" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:180</x:v>
+      </x:c>
+      <x:c r="M197" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N197" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198" ht="102" customHeight="1">
+      <x:c r="A198" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B198" s="9" t="str">
+        <x:v>TC-TM005-RANGE-10#START_EMPTY</x:v>
+      </x:c>
+      <x:c r="C198" s="9" t="str">
+        <x:v>空起日与空止日 · 变体</x:v>
+      </x:c>
+      <x:c r="D198" s="9" t="str">
+        <x:v>TASK-TM005-RANGE-QUERY</x:v>
+      </x:c>
+      <x:c r="E198" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F198" s="9" t="str">
+        <x:v>保持止日 09-21，清空起日并应用</x:v>
+      </x:c>
+      <x:c r="G198" s="9" t="str">
+        <x:v>拒绝查询，今天卡片仍为 16500、五条明细不变。</x:v>
+      </x:c>
+      <x:c r="H198" s="9" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I198" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J198" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K198" s="9" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L198" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:180</x:v>
+      </x:c>
+      <x:c r="M198" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N198" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199" ht="102" customHeight="1">
+      <x:c r="A199" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B199" s="4" t="str">
+        <x:v>TC-TM005-RANGE-10#END_EMPTY</x:v>
+      </x:c>
+      <x:c r="C199" s="4" t="str">
+        <x:v>空起日与空止日 · 变体</x:v>
+      </x:c>
+      <x:c r="D199" s="4" t="str">
+        <x:v>TASK-TM005-RANGE-QUERY</x:v>
+      </x:c>
+      <x:c r="E199" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F199" s="4" t="str">
+        <x:v>保持起日 09-20，清空止日并应用</x:v>
+      </x:c>
+      <x:c r="G199" s="4" t="str">
+        <x:v>拒绝查询，今天卡片仍为 16500、五条明细不变。</x:v>
+      </x:c>
+      <x:c r="H199" s="4" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I199" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J199" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K199" s="4" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L199" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:180</x:v>
+      </x:c>
+      <x:c r="M199" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N199" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200" ht="102" customHeight="1">
+      <x:c r="A200" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B200" s="9" t="str">
+        <x:v>TC-TM005-RANGE-08</x:v>
+      </x:c>
+      <x:c r="C200" s="9" t="str">
+        <x:v>刷新重启保持</x:v>
+      </x:c>
+      <x:c r="D200" s="9" t="str">
+        <x:v>TASK-TM005-RANGE-QUERY
+TASK-TM005-UI</x:v>
+      </x:c>
+      <x:c r="E200" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F200" s="9" t="str">
+        <x:v>seed42 双来源全量与近 30 天选择</x:v>
+      </x:c>
+      <x:c r="G200" s="9" t="str">
+        <x:v>1. 选择近 30 天并记录 UI/DB 初态；预期明细 11 项、total 31130，来源身份和覆盖状态与本例原始输入一致。
+2. App 内刷新并重扫两个来源；UI 与 DB 均不增量，仍 11 项/31130。
+3. 退出、重启安装后的同一 App/profile 并恢复筛选；UI 与 DB 仍 11 项/31130，授权状态和账号身份未串换。</x:v>
+      </x:c>
+      <x:c r="H200" s="9" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I200" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J200" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K200" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L200" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:192</x:v>
+      </x:c>
+      <x:c r="M200" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N200" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201" ht="102" customHeight="1">
+      <x:c r="A201" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B201" s="4" t="str">
+        <x:v>TC-TM005-MODEL-01</x:v>
+      </x:c>
+      <x:c r="C201" s="4" t="str">
+        <x:v>模型维度</x:v>
+      </x:c>
+      <x:c r="D201" s="4" t="str">
+        <x:v>TASK-TM005-UI</x:v>
+      </x:c>
+      <x:c r="E201" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F201" s="4" t="str">
+        <x:v>今天五项，两个来源至少各一项，模型名保持来源可识别标识</x:v>
+      </x:c>
+      <x:c r="G201" s="4" t="str">
+        <x:v>1. 选今天和模型维度；行值应为 gpt-5=1100、sonnet-test=2200、qwen-test=3300、glm-test=4400、unknown-model=5500，合计 16500。
+2. 选 unknown-model；明细只含 today-unknown，Token 5500 有效，价格未知不显示为免费或 0 用量。
+3. 刷新并重启 App 后再次查询模型维度；预期分组与明细仍与来源身份及只读 DB 一致。</x:v>
+      </x:c>
+      <x:c r="H201" s="4" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I201" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J201" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K201" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L201" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:200</x:v>
+      </x:c>
+      <x:c r="M201" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N201" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202" ht="102" customHeight="1">
+      <x:c r="A202" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B202" s="9" t="str">
+        <x:v>TC-TM005-MODEL-02</x:v>
+      </x:c>
+      <x:c r="C202" s="9" t="str">
+        <x:v>真实未知模型仍计用量</x:v>
+      </x:c>
+      <x:c r="D202" s="9" t="str">
+        <x:v>TASK-TM005-UI
+TASK-TM005-EVENT-CONTRACT</x:v>
+      </x:c>
+      <x:c r="E202" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F202" s="9" t="str">
+        <x:v>以 2026-09-29 上海当地日为语义锚点并随运行日整体平移的两条独立可信调用：Codex A 于锚点 2026-09-29T01:00:00Z，input100/output10，无法从同一 turn 核实模型，规范事件 model_id=null；Claude B 于 2026-09-29T02:00:00Z，input200/output20、模型 sonnet-test。这与 MODEL-01 中字面名称为 unknown-model 的已知模型不同</x:v>
+      </x:c>
+      <x:c r="G202" s="9" t="str">
+        <x:v>1. App 从两类已验证原生日志采集 A/B 后选该日；卡片显示两次、已知 total330，明细分别保留来源与用量，A 不因模型未知而丢失。
+2. 模型分组出现“未知模型”110 与 sonnet-test220，两组合计330；只读 SQLite 核对同一快照两条可信身份、A 的 model_id IS NULL、B 的模型及各自 input/output。
+3. 刷新并重启 App 后查询同一日期；预期仍为两次/330，未知模型不被擅自改为最近一行模型，也不被标成零费用或零用量。</x:v>
+      </x:c>
+      <x:c r="H202" s="9" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I202" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J202" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K202" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L202" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:208</x:v>
+      </x:c>
+      <x:c r="M202" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N202" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203" ht="102" customHeight="1">
+      <x:c r="A203" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B203" s="4" t="str">
+        <x:v>TC-TM005-RANGE-07</x:v>
+      </x:c>
+      <x:c r="C203" s="4" t="str">
+        <x:v>时区与月界</x:v>
+      </x:c>
+      <x:c r="D203" s="4" t="str">
+        <x:v>TASK-TM005-RANGE-QUERY</x:v>
+      </x:c>
+      <x:c r="E203" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F203" s="4" t="str">
+        <x:v>上海 09-28 15:59:59Z/16:00:00Z 与 UTC 08-30 15:59:59Z/16:00:00Z 四个语义边界事件，整体平移整数天</x:v>
+      </x:c>
+      <x:c r="G203" s="4" t="str">
+        <x:v>1. 团队时区为 Asia/Shanghai 时，上海昨天仅 yesterday=110，今天含 today-gpt=1100；近 30 天含 day30=3300，排除 outside30=11000。
+2. 经真实时区设置 UI 改为 UTC，用明确自定义 UTC 日期查询边界；09-28 UTC 同含 yesterday 与 today-gpt，total 1210；08-30 UTC 同含 outside30/day30，total 14300。事件 UTC 时间及 DB 源身份不变。
+3. 重启后 UTC 设置保留；再查询 UTC 近 30 天对应自定义窗口，total 27830，两个 08-30 事件均排除。只有显示分桶变动，DB 事件数仍 12 唯一。</x:v>
+      </x:c>
+      <x:c r="H203" s="4" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I203" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J203" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K203" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L203" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:220</x:v>
+      </x:c>
+      <x:c r="M203" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N203" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204" ht="147" customHeight="1">
+      <x:c r="A204" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B204" s="9" t="str">
+        <x:v>TC-TM005-RANGE-11</x:v>
+      </x:c>
+      <x:c r="C204" s="9" t="str">
+        <x:v>夏令时当地日长度</x:v>
+      </x:c>
+      <x:c r="D204" s="9" t="str">
+        <x:v>TASK-TM005-RANGE-QUERY</x:v>
+      </x:c>
+      <x:c r="E204" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F204" s="9" t="str">
+        <x:v>两个独立稳定变体 TC-TM005-RANGE-11#SPRING 与 TC-TM005-RANGE-11#FALL，团队时区经真实 UI 设为 America/New_York。春季 2026-03-08 的 UTC 半开界为 [2026-03-08T05:00:00Z,2026-03-09T04:00:00Z)；四个固定事件为边界前 S0（04:59:59Z，Codex 5/1）、起界 S1（05:00:00Z，Codex 9/1）、末界前 S2（次日03:59:59Z，Claude 18/2）、排除上界 S3（次日04:00:00Z，Claude 27/3）。秋季 2026-11-01 的界为 [2026-11-01T04:00:00Z,2026-11-02T05:00:00Z)；四个固定事件为 F0（03:59:59Z，Codex 5/1）、F1（04:00:00Z，Codex 36/4）、F2（次日04:59:59Z，Claude 45/5）、F3（次日05:00:00Z，Claude 54/6）。数值均为 input/output Token</x:v>
+      </x:c>
+      <x:c r="G204" s="9" t="str">
+        <x:v>1. 各变体从独立空库、已验证双来源原生日志和相同登录身份开始；UI 选对应自定义当地日，春季仅 S1/S2 两次/30，秋季仅 F1/F2 两次/90，S0/S3/F0/F3 不在对应当日明细或趋势点。
+2. 只读 SQLite 以明确 UTC 半开界核对两个源事件身份及 input+output 合计；春季窗口为 23 小时、秋季为 25 小时，不能使用固定 86400 秒上界。
+3. 重启后时区与两变体结果分别保持；每个变体单独报告，不以其中一个结果覆盖另一个。</x:v>
+      </x:c>
+      <x:c r="H204" s="9" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I204" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J204" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K204" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L204" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:230</x:v>
+      </x:c>
+      <x:c r="M204" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N204" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205" ht="102" customHeight="1">
+      <x:c r="A205" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B205" s="4" t="str">
+        <x:v>TC-TM005-RANGE-11#SPRING</x:v>
+      </x:c>
+      <x:c r="C205" s="4" t="str">
+        <x:v>夏令时当地日长度 · 变体</x:v>
+      </x:c>
+      <x:c r="D205" s="4" t="str">
+        <x:v>TASK-TM005-RANGE-QUERY</x:v>
+      </x:c>
+      <x:c r="E205" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F205" s="4" t="str">
+        <x:v>以纽约 2026-03-08 为当地日，导入 S0–S3</x:v>
+      </x:c>
+      <x:c r="G205" s="4" t="str">
+        <x:v>仅含 S1/S2 两次、合计 30 Token，UTC 窗口长 23 小时。</x:v>
+      </x:c>
+      <x:c r="H205" s="4" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I205" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J205" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K205" s="4" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L205" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:230</x:v>
+      </x:c>
+      <x:c r="M205" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N205" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206" ht="102" customHeight="1">
+      <x:c r="A206" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B206" s="9" t="str">
+        <x:v>TC-TM005-RANGE-11#FALL</x:v>
+      </x:c>
+      <x:c r="C206" s="9" t="str">
+        <x:v>夏令时当地日长度 · 变体</x:v>
+      </x:c>
+      <x:c r="D206" s="9" t="str">
+        <x:v>TASK-TM005-RANGE-QUERY</x:v>
+      </x:c>
+      <x:c r="E206" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F206" s="9" t="str">
+        <x:v>以纽约 2026-11-01 为当地日，导入 F0–F3</x:v>
+      </x:c>
+      <x:c r="G206" s="9" t="str">
+        <x:v>仅含 F1/F2 两次、合计 90 Token，UTC 窗口长 25 小时。</x:v>
+      </x:c>
+      <x:c r="H206" s="9" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I206" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J206" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K206" s="9" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L206" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:230</x:v>
+      </x:c>
+      <x:c r="M206" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N206" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207" ht="102" customHeight="1">
+      <x:c r="A207" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B207" s="4" t="str">
+        <x:v>TC-TM005-STATE-01</x:v>
+      </x:c>
+      <x:c r="C207" s="4" t="str">
+        <x:v>无覆盖是缺失</x:v>
+      </x:c>
+      <x:c r="D207" s="4" t="str">
+        <x:v>TASK-TM005-COVERAGE</x:v>
+      </x:c>
+      <x:c r="E207" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F207" s="4" t="str">
+        <x:v>两来源均没有可证明覆盖的指定历史日，且没有可信事件</x:v>
+      </x:c>
+      <x:c r="G207" s="4" t="str">
+        <x:v>1. 从本例隔离库经 App 授权仅含近期日志的目录，打开早于已证实覆盖起点的自定义历史日；预期进入该日查询但尚不能凭空明细推断完整 0，DB 不新增用量事件。
+2. UI 显示缺失/不可确认，不能显示完整 0；趋势点/明细状态与卡片一致。DB 只读证明没有该日可信事件，且覆盖记录并未声称完整。
+3. 刷新后仍为缺失；空结果不能生成新零用量事件。</x:v>
+      </x:c>
+      <x:c r="H207" s="4" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I207" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J207" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K207" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L207" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:243</x:v>
+      </x:c>
+      <x:c r="M207" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N207" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208" ht="102" customHeight="1">
+      <x:c r="A208" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B208" s="9" t="str">
+        <x:v>TC-TM005-STATE-02</x:v>
+      </x:c>
+      <x:c r="C208" s="9" t="str">
+        <x:v>已覆盖零调用</x:v>
+      </x:c>
+      <x:c r="D208" s="9" t="str">
+        <x:v>TASK-TM005-COVERAGE</x:v>
+      </x:c>
+      <x:c r="E208" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F208" s="9" t="str">
+        <x:v>两来源对某完整当地日均有可核实、连续成功的覆盖证明，实际无调用</x:v>
+      </x:c>
+      <x:c r="G208" s="9" t="str">
+        <x:v>1. 在隔离 App 取得并核验两来源覆盖证明后选该日；UI 明确 0 次、0 Token，趋势该日为真实 0，明细为空。
+2. DB 只读核对覆盖区间完整、事件数 0；无任何合成“零调用事件”。重启后状态仍为已覆盖零。</x:v>
+      </x:c>
+      <x:c r="H208" s="9" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I208" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J208" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K208" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L208" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:251</x:v>
+      </x:c>
+      <x:c r="M208" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N208" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209" ht="102" customHeight="1">
+      <x:c r="A209" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B209" s="4" t="str">
+        <x:v>TC-TM005-STATE-03</x:v>
+      </x:c>
+      <x:c r="C209" s="4" t="str">
+        <x:v>字段未知</x:v>
+      </x:c>
+      <x:c r="D209" s="4" t="str">
+        <x:v>TASK-TM005-COVERAGE</x:v>
+      </x:c>
+      <x:c r="E209" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F209" s="4" t="str">
+        <x:v>一条受支持原生会话有时间/模型但缺可信 usage，另有正常可信调用 110</x:v>
+      </x:c>
+      <x:c r="G209" s="4" t="str">
+        <x:v>1. App 先采集正常调用；预期 UI 与 DB 显示已知 110。
+2. 追加缺 usage 原生事件并刷新；UI 显示不完整/未知诊断，不能把它当作 0 或把合计称为完整 110；DB 记录 unknown 原因且原正常事件不变。
+3. 重扫并重启 App；预期未知诊断仍在，未因去重而被隐藏。</x:v>
+      </x:c>
+      <x:c r="H209" s="4" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I209" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J209" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K209" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L209" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:260</x:v>
+      </x:c>
+      <x:c r="M209" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N209" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210" ht="102" customHeight="1">
+      <x:c r="A210" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B210" s="9" t="str">
+        <x:v>TC-TM005-STATE-04</x:v>
+      </x:c>
+      <x:c r="C210" s="9" t="str">
+        <x:v>三态持久化</x:v>
+      </x:c>
+      <x:c r="D210" s="9" t="str">
+        <x:v>TASK-TM005-COVERAGE</x:v>
+      </x:c>
+      <x:c r="E210" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F210" s="9" t="str">
+        <x:v>分别预置上述无覆盖、完整空日、未知字段三种可核实源状态</x:v>
+      </x:c>
+      <x:c r="G210" s="9" t="str">
+        <x:v>1. 在 App 依次选择三日；每个日期分别显示缺失、0、未知，保存 UI/只读 DB 的各自状态。
+2. 退出重启并改变团队时区后按新当地日重查；覆盖按 UTC 区间换算，三种状态不能互换或丢失。</x:v>
+      </x:c>
+      <x:c r="H210" s="9" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I210" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J210" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K210" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L210" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:268</x:v>
+      </x:c>
+      <x:c r="M210" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N210" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211" ht="102" customHeight="1">
+      <x:c r="A211" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B211" s="4" t="str">
+        <x:v>TC-TM005-STATE-05</x:v>
+      </x:c>
+      <x:c r="C211" s="4" t="str">
+        <x:v>Claude 数值零与上游缺 usage 的歧义</x:v>
+      </x:c>
+      <x:c r="D211" s="4" t="str">
+        <x:v>TASK-TM005-COVERAGE</x:v>
+      </x:c>
+      <x:c r="E211" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F211" s="4" t="str">
+        <x:v>TM-004 的两种受控 API 响应设计：显式报告零 usage 与整体省略 usage；Claude Code 2.1.126 原生阶段探针已发现后一种仍使 CLI 写出数值 0/0 usage</x:v>
+      </x:c>
+      <x:c r="G211" s="4" t="str">
+        <x:v>1. 分别由最终固定的原生数据程序生成两类日志，记录原始字节摘要与可观察字段；若两类 raw 不能区分，测试应把区别判据标为 BLOCKED，不能凭 API fixture 的隐藏输入让 App “识别”日志看不到的状态。
+2. App 读取省略 usage 所得数值零日志；没有额外可核实证据时 UI/DB 应保持未知或未确定，不能显示“已证明完整零用量”。已知可信事件的合计不被该 0 改成完整。
+3. 只有 TM-004 最终合同证明可区分显式零时，才对该变体单独断言真实零；重扫/重启不能把未知提升为零。</x:v>
+      </x:c>
+      <x:c r="H211" s="4" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I211" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J211" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K211" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L211" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:275</x:v>
+      </x:c>
+      <x:c r="M211" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N211" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212" ht="117" customHeight="1">
+      <x:c r="A212" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B212" s="9" t="str">
+        <x:v>TC-TM005-STATE-06</x:v>
+      </x:c>
+      <x:c r="C212" s="9" t="str">
+        <x:v>全量扫描分页与撤权时的覆盖</x:v>
+      </x:c>
+      <x:c r="D212" s="9" t="str">
+        <x:v>TASK-TM005-COVERAGE</x:v>
+      </x:c>
+      <x:c r="E212" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F212" s="9" t="str">
+        <x:v>本例拥有的 Claude 授权根含至少 1025 个候选文件、跨至少 5 个计划中的采集页；第一页含可信调用 A=100/10，后页另含可信调用 B=200/20。另有预览截断、页间撤权两个独立稳定变体</x:v>
+      </x:c>
+      <x:c r="G212" s="9" t="str">
+        <x:v>1. 从已安装 App 经 TM-002 真实 UI 授权根；预览即使只列前 1000 文件也不能使 TM-005 宣称全量覆盖。采集分页未完成时，UI 仅显示已知部分（A 若已被可信采集则为 110）及 history_incomplete，不显示完整 110 或空日 0；SQLite 只读旁证记录 continuation/诊断和已提交可信事件。
+2. 正常变体继续到所有页面、必要深度与完整行/游标提交；若 TM-004 最终合同确认全部可信，UI/DB 合计 A+B=330，覆盖状态按真实证明更新，不遗漏第 1025 个及后续文件。
+3. 撤权变体在两页之间撤销本例授权；扫描立刻停止，后页 B 不得读取，UI 保持已知部分 110 与不完整/失权提示，SQLite 不写完整覆盖或成功零。重授权后的补扫单独执行，最终值仍须 TM-004 身份/分页合同核定。</x:v>
+      </x:c>
+      <x:c r="H212" s="9" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I212" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J212" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K212" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L212" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:285</x:v>
+      </x:c>
+      <x:c r="M212" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N212" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="213" ht="102" customHeight="1">
+      <x:c r="A213" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B213" s="4" t="str">
+        <x:v>TC-TM005-DATA-01</x:v>
+      </x:c>
+      <x:c r="C213" s="4" t="str">
+        <x:v>生成/重置可复现</x:v>
+      </x:c>
+      <x:c r="D213" s="4" t="str">
+        <x:v>TASK-TM005-DATA</x:v>
+      </x:c>
+      <x:c r="E213" s="4" t="str">
+        <x:v>governance</x:v>
+      </x:c>
+      <x:c r="F213" s="4" t="str">
+        <x:v>同 seed42、同日锚点及两来源已验证版本，两个独立 run_id</x:v>
+      </x:c>
+      <x:c r="G213" s="4" t="str">
+        <x:v>1. 调用计划中的 raw 生成器两次，核对受支持格式、事件身份、原始字节摘要与独立 expected 相同（run_id 标记可不同）；不得读取真实 ~/.codex 或 ~/.claude。
+2. 只在已核对 owner marker、目录成员和摘要后调用重置；两个本例私有目录被清理，外部文件不动。程序不存在时为 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="H213" s="4" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I213" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J213" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K213" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L213" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:297</x:v>
+      </x:c>
+      <x:c r="M213" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N213" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214" ht="102" customHeight="1">
+      <x:c r="A214" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B214" s="9" t="str">
+        <x:v>TC-TM005-DATA-02</x:v>
+      </x:c>
+      <x:c r="C214" s="9" t="str">
+        <x:v>独立预期与边界</x:v>
+      </x:c>
+      <x:c r="D214" s="9" t="str">
+        <x:v>TASK-TM005-DATA</x:v>
+      </x:c>
+      <x:c r="E214" s="9" t="str">
+        <x:v>governance</x:v>
+      </x:c>
+      <x:c r="F214" s="9" t="str">
+        <x:v>语义 oracle tests/fixtures/tm005-semantic-expected.json和最终 raw 映射计划</x:v>
+      </x:c>
+      <x:c r="G214" s="9" t="str">
+        <x:v>1. 在产品启动前运行固定语义 oracle 检查；预期 seed42 语义样例 13 行/12 唯一，双来源事件集合及平移后的上海/UTC半开区间与预存摘要一致；原生映射未就绪时本例仍 BLOCKED。
+2. 对照原始字节与独立预期中的模型/字段、覆盖与 unknown 状态；缺原生日志/覆盖样例不得标可执行。该检查不能代替产品查询。</x:v>
+      </x:c>
+      <x:c r="H214" s="9" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I214" s="9" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J214" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K214" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L214" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:304</x:v>
+      </x:c>
+      <x:c r="M214" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N214" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215" ht="102" customHeight="1">
+      <x:c r="A215" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B215" s="4" t="str">
+        <x:v>TC-TM005-E2E-01</x:v>
+      </x:c>
+      <x:c r="C215" s="4" t="str">
+        <x:v>精确集合与最终安装包</x:v>
+      </x:c>
+      <x:c r="D215" s="4" t="str">
+        <x:v>TASK-TM005-E2E</x:v>
+      </x:c>
+      <x:c r="E215" s="4" t="str">
+        <x:v>governance_gate</x:v>
+      </x:c>
+      <x:c r="F215" s="4" t="str">
+        <x:v>固定候选 SHA、最终 DMG 与上述所有 TC 及此前已交付功能集合</x:v>
+      </x:c>
+      <x:c r="G215" s="4" t="str">
+        <x:v>1. 门禁从 DMG 安装的正式 App 逐 TC 运行，核对实际安装包摘要、独立输入/预期、原始结果与全部清理；任一 FAIL/BLOCKED/零例/跳过/重试取绿均阻断。
+2. 核对 TM-001→TM-004 的适用完整 E2E 及迁移/升级结果；只有本机机器门禁原始复核 PASS 才可签发本版通行证。当前无程序/包/原件，状态 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="H215" s="4" t="str">
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
+      </x:c>
+      <x:c r="I215" s="4" t="str">
+        <x:v>预期待明确</x:v>
+      </x:c>
+      <x:c r="J215" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K215" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L215" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:311</x:v>
+      </x:c>
+      <x:c r="M215" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N215" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216" ht="57" customHeight="1">
+      <x:c r="A216" s="9" t="str">
+        <x:v>TM-006</x:v>
+      </x:c>
+      <x:c r="B216" s="9" t="str">
+        <x:v>E2E-TM006-001</x:v>
+      </x:c>
+      <x:c r="C216" s="9" t="str">
+        <x:v>Token子项与基础费用</x:v>
+      </x:c>
+      <x:c r="D216" s="9" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E216" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F216" s="9" t="str">
+        <x:v>数据集 pricing；pricing由scripts/test_data.py生成合成非计费价格。gpt-5每百万input/cache/output为USD2/0.2/8；today-gpt input1000含cache200、output100含reasoning20。价格不是厂商现价。</x:v>
+      </x:c>
+      <x:c r="G216" s="9" t="str">
+        <x:v>单调用total=1100；费用=(800×2+200×0.2+100×8)/1000000=USD0.002440，reasoning20不另加价。today已知费用USD0.015190且有1条无价格，alice今日USD0.010090。使用Decimal/十进制独立oracle，不以界面舍入反推底层精度。</x:v>
+      </x:c>
+      <x:c r="H216" s="9" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I216" s="9" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J216" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K216" s="9" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L216" s="9" t="str">
+        <x:v>docs/testing/cases/06-TM-006-cost-estimates.md:15</x:v>
+      </x:c>
+      <x:c r="M216" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N216" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217" ht="57" customHeight="1">
+      <x:c r="A217" s="4" t="str">
+        <x:v>TM-006</x:v>
+      </x:c>
+      <x:c r="B217" s="4" t="str">
+        <x:v>E2E-TM006-002</x:v>
+      </x:c>
+      <x:c r="C217" s="4" t="str">
+        <x:v>历史价格、多币种和未知费用</x:v>
+      </x:c>
+      <x:c r="D217" s="4" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E217" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F217" s="4" t="str">
+        <x:v>数据集 pricing_extended；pricing_extended planned：同模型在生效时点T前后各一调用，两个独立价格版本；另有USD/CNY各一模型、无价模型和订阅估算模型。必须提供价格/订阅分摊规则及手算expected后才能实现。</x:v>
+      </x:c>
+      <x:c r="G217" s="4" t="str">
+        <x:v>T前后依各自生效版本计算，历史结果不会悄悄换价；USD与CNY分组，未约定汇率不得相加；无价格显示未知而非0；订阅必须明确估算口径。具体金额oracle依待定义订阅/价格合同生成，当前不得手填PASS。</x:v>
+      </x:c>
+      <x:c r="H217" s="4" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I217" s="4" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J217" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K217" s="4" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L217" s="4" t="str">
+        <x:v>docs/testing/cases/06-TM-006-cost-estimates.md:32</x:v>
+      </x:c>
+      <x:c r="M217" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N217" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="218" ht="57" customHeight="1">
+      <x:c r="A218" s="9" t="str">
+        <x:v>TM-007</x:v>
+      </x:c>
+      <x:c r="B218" s="9" t="str">
+        <x:v>E2E-TM007-001</x:v>
+      </x:c>
+      <x:c r="C218" s="9" t="str">
+        <x:v>离线、重启和补传幂等</x:v>
+      </x:c>
+      <x:c r="D218" s="9" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E218" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F218" s="9" t="str">
+        <x:v>数据集 sync_faults；sync_faults planned；alice两个隔离设备A/B，设备A调用100/10、B调用200/20；真实FastAPI/SQLite服务，可由外部fixture断网/恢复。账号继续用隔离测试fixture。</x:v>
+      </x:c>
+      <x:c r="G218" s="9" t="str">
+        <x:v>离线重启不丢队列；恢复后2唯一调用、input300/output30/total330；重复批次不再加量。客户端只在真实确认后标已同步，个人合计与对应团队子集一致。</x:v>
+      </x:c>
+      <x:c r="H218" s="9" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I218" s="9" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J218" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K218" s="9" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L218" s="9" t="str">
+        <x:v>docs/testing/cases/07-TM-007-team-sync.md:11</x:v>
+      </x:c>
+      <x:c r="M218" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N218" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="219" ht="57" customHeight="1">
+      <x:c r="A219" s="4" t="str">
+        <x:v>TM-007</x:v>
+      </x:c>
+      <x:c r="B219" s="4" t="str">
+        <x:v>E2E-TM007-002</x:v>
+      </x:c>
+      <x:c r="C219" s="4" t="str">
+        <x:v>部分确认、中断和账号切换</x:v>
+      </x:c>
+      <x:c r="D219" s="4" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E219" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F219" s="4" t="str">
+        <x:v>数据集 sync_faults；准备alice的三条唯一事件A/B/C，总量各110/220/330；控制服务仅确认A后断开，B可能已提交但响应丢失，C未提交。另有bob账号。故障注入必须在真实服务外部或明确测试环境中完成，不能绕过认证。</x:v>
+      </x:c>
+      <x:c r="G219" s="4" t="str">
+        <x:v>最终alice的A/B/C各一次、total660；响应丢失不造成B重复；bob不能承接或篡改alice既有事件归属。切换时旧队列按已批准归属策略隔离，不能默认为新登录账号。</x:v>
+      </x:c>
+      <x:c r="H219" s="4" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I219" s="4" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J219" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K219" s="4" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L219" s="4" t="str">
+        <x:v>docs/testing/cases/07-TM-007-team-sync.md:28</x:v>
+      </x:c>
+      <x:c r="M219" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N219" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="220" ht="57" customHeight="1">
+      <x:c r="A220" s="9" t="str">
+        <x:v>TM-007</x:v>
+      </x:c>
+      <x:c r="B220" s="9" t="str">
+        <x:v>E2E-TM007-003</x:v>
+      </x:c>
+      <x:c r="C220" s="9" t="str">
+        <x:v>上传白名单与项目映射</x:v>
+      </x:c>
+      <x:c r="D220" s="9" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E220" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F220" s="9" t="str">
+        <x:v>数据集 sync_faults；合成日志包含唯一正文/代码/API-key/完整路径哨兵，以及合法用量/必要去重元数据；只用假值。准备已归属项目A和未归属事件B，待sync_faults生成。</x:v>
+      </x:c>
+      <x:c r="G220" s="9" t="str">
+        <x:v>网络载荷/持久服务数据均不得含正文、代码、key或完整本机路径；只有批准用量/去重字段。B可明确分配，分配不增加事件量、也不跨团队归属。</x:v>
+      </x:c>
+      <x:c r="H220" s="9" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I220" s="9" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J220" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K220" s="9" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L220" s="9" t="str">
+        <x:v>docs/testing/cases/07-TM-007-team-sync.md:45</x:v>
+      </x:c>
+      <x:c r="M220" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N220" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221" ht="57" customHeight="1">
+      <x:c r="A221" s="4" t="str">
+        <x:v>TM-007</x:v>
+      </x:c>
+      <x:c r="B221" s="4" t="str">
+        <x:v>E2E-TM007-004</x:v>
+      </x:c>
+      <x:c r="C221" s="4" t="str">
+        <x:v>统计越权与停用后上传</x:v>
+      </x:c>
+      <x:c r="D221" s="4" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E221" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F221" s="4" t="str">
+        <x:v>数据集 sync_faults；alice项目A调用100/10，bob项目B调用200/20；成员alice与管理员独立会话；alice另有一条未确认调用C=50/5。sync_faults与可重建统计SQL尚未实现。</x:v>
+      </x:c>
+      <x:c r="G221" s="4" t="str">
+        <x:v>成员无权请求被服务端拒绝，UI不显示bob的220；停用后旧会话及上传拒绝，C不能标为已确认；合法历史不能被失败上传删除。此处补足TM-001仅身份/管理接口权限的范围。</x:v>
+      </x:c>
+      <x:c r="H221" s="4" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I221" s="4" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J221" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K221" s="4" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L221" s="4" t="str">
+        <x:v>docs/testing/cases/07-TM-007-team-sync.md:62</x:v>
+      </x:c>
+      <x:c r="M221" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N221" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="222" ht="57" customHeight="1">
+      <x:c r="A222" s="9" t="str">
+        <x:v>TM-008</x:v>
+      </x:c>
+      <x:c r="B222" s="9" t="str">
+        <x:v>E2E-TM008-001</x:v>
+      </x:c>
+      <x:c r="C222" s="9" t="str">
+        <x:v>筛选一致的CSV导出</x:v>
+      </x:c>
+      <x:c r="D222" s="9" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E222" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F222" s="9" t="str">
+        <x:v>数据集 export_rows；export_rows planned；两成员、两个模型、时间范围内外各有事件，独立清单明确每条ID/字段/权限。先具备TM-005/007统计和授权。</x:v>
+      </x:c>
+      <x:c r="G222" s="9" t="str">
+        <x:v>每次CSV仅包含当次筛选且授权可见记录，行数/ID/汇总等于独立清单与界面；不混入旧筛选、其他成员或范围外记录。已知/未知费用语义一致。</x:v>
+      </x:c>
+      <x:c r="H222" s="9" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I222" s="9" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J222" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K222" s="9" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L222" s="9" t="str">
+        <x:v>docs/testing/cases/08-TM-008-csv-export.md:11</x:v>
+      </x:c>
+      <x:c r="M222" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N222" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="223" ht="57" customHeight="1">
+      <x:c r="A223" s="4" t="str">
+        <x:v>TM-008</x:v>
+      </x:c>
+      <x:c r="B223" s="4" t="str">
+        <x:v>E2E-TM008-002</x:v>
+      </x:c>
+      <x:c r="C223" s="4" t="str">
+        <x:v>CSV转义、未知值及权限</x:v>
+      </x:c>
+      <x:c r="D223" s="4" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E223" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F223" s="4" t="str">
+        <x:v>数据集 export_rows；export_rows需含字段 a,b、say "hi"、带实际换行的项目名、未知费用与非ASCII模型名；两成员各有可区分哨兵事件。只在隔离数据中使用。</x:v>
+      </x:c>
+      <x:c r="G223" s="4" t="str">
+        <x:v>逗号、双引号、嵌入换行均round-trip一致，Unicode不损坏；未知值不写成0；他人哨兵不出现在文件。若导出失败，不能留下看似完整的半文件。</x:v>
+      </x:c>
+      <x:c r="H223" s="4" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I223" s="4" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J223" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K223" s="4" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L223" s="4" t="str">
+        <x:v>docs/testing/cases/08-TM-008-csv-export.md:28</x:v>
+      </x:c>
+      <x:c r="M223" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N223" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224" ht="57" customHeight="1">
+      <x:c r="A224" s="9" t="str">
+        <x:v>TM-009</x:v>
+      </x:c>
+      <x:c r="B224" s="9" t="str">
+        <x:v>E2E-TM009-001</x:v>
+      </x:c>
+      <x:c r="C224" s="9" t="str">
+        <x:v>80%/100%提醒幂等</x:v>
+      </x:c>
+      <x:c r="D224" s="9" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E224" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F224" s="9" t="str">
+        <x:v>数据集 budget_periods；budget_periods planned；独立个人、项目和团队预算分别100个合成USD单位，同周期使用量依次79→80→99→100；原始调用与价格要能精确形成这些费用。</x:v>
+      </x:c>
+      <x:c r="G224" s="9" t="str">
+        <x:v>每预算每周期80与100各最多一次，未达到不发；重扫/重启/重复上传不重发；预算仅提醒，不拦截模型调用。三层预算分别按其授权范围计算。</x:v>
+      </x:c>
+      <x:c r="H224" s="9" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I224" s="9" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J224" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K224" s="9" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L224" s="9" t="str">
+        <x:v>docs/testing/cases/09-TM-009-budget-alerts.md:11</x:v>
+      </x:c>
+      <x:c r="M224" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N224" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="225" ht="57" customHeight="1">
+      <x:c r="A225" s="4" t="str">
+        <x:v>TM-009</x:v>
+      </x:c>
+      <x:c r="B225" s="4" t="str">
+        <x:v>E2E-TM009-002</x:v>
+      </x:c>
+      <x:c r="C225" s="4" t="str">
+        <x:v>新周期、币种与通知恢复</x:v>
+      </x:c>
+      <x:c r="D225" s="4" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E225" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F225" s="4" t="str">
+        <x:v>数据集 budget_periods；两个币种独立预算；旧周期已发80/100阈值，参考时钟可由产品支持的测试配置推进；测试通知权限可以拒绝及恢复，不能修改用户其他App授权。</x:v>
+      </x:c>
+      <x:c r="G225" s="4" t="str">
+        <x:v>系统拒绝不丢失应用内状态、不造成重试通知风暴；新周期独立重置，允许新一轮各阈值一次；币种分开计算。通知补发策略需在对应需求明确，不能由测试临时猜测。</x:v>
+      </x:c>
+      <x:c r="H225" s="4" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I225" s="4" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J225" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K225" s="4" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L225" s="4" t="str">
+        <x:v>docs/testing/cases/09-TM-009-budget-alerts.md:28</x:v>
+      </x:c>
+      <x:c r="M225" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N225" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="226" ht="72" customHeight="1">
+      <x:c r="A226" s="9" t="str">
+        <x:v>TM-010</x:v>
+      </x:c>
+      <x:c r="B226" s="9" t="str">
+        <x:v>E2E-TM010-001</x:v>
+      </x:c>
+      <x:c r="C226" s="9" t="str">
+        <x:v>稳定版发现更新与数据保留</x:v>
+      </x:c>
+      <x:c r="D226" s="9" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E226" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F226" s="9" t="str">
+        <x:v>数据集 update_packages；依赖TM-001/007；update_packages planned。需真实已分发稳定版、候选最终包及相同分发profile的签名/清单；旧版有账号设置、手动地址、统计/队列独立快照。首版无历史稳定版时使用SOP017规定的候选→受控高版，不伪称稳定升级。</x:v>
+      </x:c>
+      <x:c r="G226" s="9" t="str">
+        <x:v>更新频率和说明可用；只有声明候选被安装，Sparkle自主重启；更新前后账号/设置/统计与快照一致，队列不丢失不重复。完整更新体验仍为未来功能，TM-001-004通过只证明最小更新路径。</x:v>
+      </x:c>
+      <x:c r="H226" s="9" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I226" s="9" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J226" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K226" s="9" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L226" s="9" t="str">
+        <x:v>docs/testing/cases/10-TM-010-software-updates.md:11</x:v>
+      </x:c>
+      <x:c r="M226" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N226" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="227" ht="57" customHeight="1">
+      <x:c r="A227" s="4" t="str">
+        <x:v>TM-010</x:v>
+      </x:c>
+      <x:c r="B227" s="4" t="str">
+        <x:v>E2E-TM010-002</x:v>
+      </x:c>
+      <x:c r="C227" s="4" t="str">
+        <x:v>签名、网络、空间和迁移失败恢复</x:v>
+      </x:c>
+      <x:c r="D227" s="4" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E227" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F227" s="4" t="str">
+        <x:v>数据集 update_packages；对同一干净旧版分别建立四个隔离子场景：坏签名包、下载中断、受限测试卷空间不足、受控迁移失败；每个保存旧版包/DB/配置摘要。故障不能作用用户系统盘/生产库。</x:v>
+      </x:c>
+      <x:c r="G227" s="4" t="str">
+        <x:v>每个失败均不能形成半更新；原账号/统计和包的可用状态可验证。网络恢复后的成功需要完整包校验；迁移失败恢复来源与摘要明确。四个子场景全部为本case必需，不能挑一项通过。</x:v>
+      </x:c>
+      <x:c r="H227" s="4" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I227" s="4" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J227" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K227" s="4" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L227" s="4" t="str">
+        <x:v>docs/testing/cases/10-TM-010-software-updates.md:28</x:v>
+      </x:c>
+      <x:c r="M227" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N227" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="228" ht="57" customHeight="1">
+      <x:c r="A228" s="9" t="str">
+        <x:v>TM-010</x:v>
+      </x:c>
+      <x:c r="B228" s="9" t="str">
+        <x:v>E2E-TM010-003</x:v>
+      </x:c>
+      <x:c r="C228" s="9" t="str">
+        <x:v>升级默认地址和手动覆盖</x:v>
+      </x:c>
+      <x:c r="D228" s="9" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E228" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F228" s="9" t="str">
+        <x:v>数据集 server_default_migration；server_default_migration planned；两套旧安装A从未设置地址、B已手动设置；候选内置一个届时确定且测试可访问的生产HTTPS默认地址。两源有独立账号/数据/会话，公钥不可随URL编辑。</x:v>
+      </x:c>
+      <x:c r="G228" s="9" t="str">
+        <x:v>只有无手动覆盖安装跟随新版默认；显式覆盖即使恰好等于旧默认也应按已经确定的配置来源规则处理。改变origin需重新服务认证，旧token不能跨源复用。</x:v>
+      </x:c>
+      <x:c r="H228" s="9" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I228" s="9" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J228" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K228" s="9" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L228" s="9" t="str">
+        <x:v>docs/testing/cases/10-TM-010-software-updates.md:45</x:v>
+      </x:c>
+      <x:c r="M228" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N228" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="229" ht="57" customHeight="1">
+      <x:c r="A229" s="4" t="str">
+        <x:v>TM-011</x:v>
+      </x:c>
+      <x:c r="B229" s="4" t="str">
+        <x:v>E2E-TM011-001</x:v>
+      </x:c>
+      <x:c r="C229" s="4" t="str">
+        <x:v>SQLite迁移与中断恢复</x:v>
+      </x:c>
+      <x:c r="D229" s="4" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E229" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F229" s="4" t="str">
+        <x:v>数据集 migration_snapshots；migration_snapshots planned；旧schema副本含固定账号/事件/队列、预计算记录数/Token/金额；候选迁移版本和明确故障点。全部作用私有临时库。</x:v>
+      </x:c>
+      <x:c r="G229" s="4" t="str">
+        <x:v>成功迁移只改变设计允许的schema/数据；账号、记录数、Token、费用/队列归属不丢。失败恢复到可启动一致状态，重复启动不重复迁移数据。不能以文件存在作为恢复成功。</x:v>
+      </x:c>
+      <x:c r="H229" s="4" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I229" s="4" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J229" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K229" s="4" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L229" s="4" t="str">
+        <x:v>docs/testing/cases/11-TM-011-data-migration.md:11</x:v>
+      </x:c>
+      <x:c r="M229" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N229" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="230" ht="57" customHeight="1">
+      <x:c r="A230" s="9" t="str">
+        <x:v>TM-011</x:v>
+      </x:c>
+      <x:c r="B230" s="9" t="str">
+        <x:v>E2E-TM011-002</x:v>
+      </x:c>
+      <x:c r="C230" s="9" t="str">
+        <x:v>未来SQLite到MySQL迁移</x:v>
+      </x:c>
+      <x:c r="D230" s="9" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E230" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F230" s="9" t="str">
+        <x:v>数据集 migration_snapshots；仅后续独立版本适用；用户已确定v0.1.0继续SQLite。需要隔离源SQLite、目标MySQL、固定多成员/多项目用量快照、字符/时间/Decimal边界和独立expected。</x:v>
+      </x:c>
+      <x:c r="G230" s="9" t="str">
+        <x:v>源/目标记录数、Token、Decimal金额及权限结果一致，ID和幂等语义保持；不重复历史且旧源未被破坏。MySQL版本、字符集和迁移范围须在对应版本指定。</x:v>
+      </x:c>
+      <x:c r="H230" s="9" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I230" s="9" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J230" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K230" s="9" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L230" s="9" t="str">
+        <x:v>docs/testing/cases/11-TM-011-data-migration.md:28</x:v>
+      </x:c>
+      <x:c r="M230" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N230" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="231" ht="57" customHeight="1">
+      <x:c r="A231" s="4" t="str">
+        <x:v>TM-011</x:v>
+      </x:c>
+      <x:c r="B231" s="4" t="str">
+        <x:v>E2E-TM011-003</x:v>
+      </x:c>
+      <x:c r="C231" s="4" t="str">
+        <x:v>备份恢复与旧客户端补传</x:v>
+      </x:c>
+      <x:c r="D231" s="4" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E231" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F231" s="4" t="str">
+        <x:v>数据集 migration_snapshots；隔离服务已确认事件A/B与旧客户端未确认C；备份包含schema/数据/版本/摘要，另保存不在备份里的独立oracle。恢复目标必须为空且带测试标记。</x:v>
+      </x:c>
+      <x:c r="G231" s="4" t="str">
+        <x:v>备份能实际恢复而非只压缩成功；A/B不丢，重复补传不增加；C最终只出现一次，账号/权限符合恢复基线。队列与服务确认一致，旧客户端协议兼容。</x:v>
+      </x:c>
+      <x:c r="H231" s="4" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I231" s="4" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J231" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K231" s="4" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L231" s="4" t="str">
+        <x:v>docs/testing/cases/11-TM-011-data-migration.md:45</x:v>
+      </x:c>
+      <x:c r="M231" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N231" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="232" ht="57" customHeight="1">
+      <x:c r="A232" s="9" t="str">
+        <x:v>TM-011</x:v>
+      </x:c>
+      <x:c r="B232" s="9" t="str">
+        <x:v>E2E-TM011-004</x:v>
+      </x:c>
+      <x:c r="C232" s="9" t="str">
+        <x:v>保留时间边界与未同步保护</x:v>
+      </x:c>
+      <x:c r="D232" s="9" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E232" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F232" s="9" t="str">
+        <x:v>数据集 migration_snapshots；固定参考时间和Asia/Shanghai；本地90天/服务端365天。分别生成保留首日00:00、前一秒、前一天的已确认事件，以及同样超龄但未同步事件；具备可控时钟与独立边界oracle。</x:v>
+      </x:c>
+      <x:c r="G232" s="9" t="str">
+        <x:v>保留首日00:00仍在，早一秒的已同步记录被清理；本地/服务按各自天数独立判定。未同步记录即使超龄仍保护，成功补传仅计一次；历史缺失不能显示真实0。</x:v>
+      </x:c>
+      <x:c r="H232" s="9" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I232" s="9" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J232" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K232" s="9" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L232" s="9" t="str">
+        <x:v>docs/testing/cases/11-TM-011-data-migration.md:62</x:v>
+      </x:c>
+      <x:c r="M232" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N232" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="233" ht="57" customHeight="1">
+      <x:c r="A233" s="4" t="str">
+        <x:v>TM-012</x:v>
+      </x:c>
+      <x:c r="B233" s="4" t="str">
+        <x:v>E2E-TM012-001</x:v>
+      </x:c>
+      <x:c r="C233" s="4" t="str">
+        <x:v>菜单栏摘要、暂停恢复与刷新</x:v>
+      </x:c>
+      <x:c r="D233" s="4" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E233" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F233" s="4" t="str">
+        <x:v>数据集 diagnostic_states；diagnostic_states planned；已采集A=100/10；暂停期间追加B=200/20并重放A。依赖实际采集、统计和同步功能，使用专用日志目录。</x:v>
+      </x:c>
+      <x:c r="G233" s="4" t="str">
+        <x:v>初始total110、暂停期间仍110，恢复后唯一A/B、total330；手动刷新与重启不重复。菜单栏与主窗口同一筛选口径；暂停状态不伪装成没有日志。</x:v>
+      </x:c>
+      <x:c r="H233" s="4" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I233" s="4" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J233" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K233" s="4" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L233" s="4" t="str">
+        <x:v>docs/testing/cases/12-TM-012-menu-diagnostics.md:11</x:v>
+      </x:c>
+      <x:c r="M233" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N233" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="234" ht="57" customHeight="1">
+      <x:c r="A234" s="9" t="str">
+        <x:v>TM-012</x:v>
+      </x:c>
+      <x:c r="B234" s="9" t="str">
+        <x:v>E2E-TM012-002</x:v>
+      </x:c>
+      <x:c r="C234" s="9" t="str">
+        <x:v>诊断状态、恢复和登录启动</x:v>
+      </x:c>
+      <x:c r="D234" s="9" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E234" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F234" s="9" t="str">
+        <x:v>数据集 diagnostic_states；独立子场景：已授权目录失效、真实服务不可达/恢复、测试App登录启动开关。故障作用测试目录/进程；使用已登录桌面与可自动检查的系统设置。</x:v>
+      </x:c>
+      <x:c r="G234" s="9" t="str">
+        <x:v>错误与真实目录/网络故障一致，不能用旧缓存一直显示健康；恢复后状态及时更新，未同步数据不丢。启动设置与OS登记/实际启动行为一致，测试结束恢复本次测试前状态。</x:v>
+      </x:c>
+      <x:c r="H234" s="9" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I234" s="9" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J234" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K234" s="9" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L234" s="9" t="str">
+        <x:v>docs/testing/cases/12-TM-012-menu-diagnostics.md:28</x:v>
+      </x:c>
+      <x:c r="M234" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N234" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="235" ht="72" customHeight="1">
+      <x:c r="A235" s="4" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B235" s="4" t="str">
+        <x:v>TC-TM003-SOURCE-01</x:v>
+      </x:c>
+      <x:c r="C235" s="4" t="str">
+        <x:v>受控版本来源与字段核验</x:v>
+      </x:c>
+      <x:c r="D235" s="4" t="str">
+        <x:v>TASK-TM003-SOURCE</x:v>
+      </x:c>
+      <x:c r="E235" s="4" t="str">
+        <x:v>source_check</x:v>
+      </x:c>
+      <x:c r="F235" s="4" t="str">
+        <x:v>1. 对照本版声明的 CLI build、官方结构与 sessions/YYYY/MM/DD/*.jsonl 受控原生样例→样例有 session_meta.id、token_usage_record.payload.response_id/usage，版本和 SHA 有记录。2. 换一个未声明 build→该 build 不列为已支持，显示 unsupported_source_version。</x:v>
+      </x:c>
+      <x:c r="G235" s="4" t="str">
+        <x:v>候选元数据与超限“不完整”不被标为支持或历史覆盖证明；经独立核实的原生样例有 session_meta.id、token_usage_record.payload.response_id/usage，版本与 SHA 留证
+该 build 不列为已支持，显示 unsupported_source_version</x:v>
+      </x:c>
+      <x:c r="H235" s="4" t="str">
+        <x:v>准备：无 DB 写入
+变化：不适用；见本用例具体数据库观察面。
+核验：无 DB 写入；核对来源清单版本、摘要与私有样例归属。数据：受控来源样例；每次新隔离根重建。</x:v>
+      </x:c>
+      <x:c r="I235" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J235" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K235" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L235" s="4" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:207</x:v>
+      </x:c>
+      <x:c r="M235" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N235" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="236" ht="72" customHeight="1">
+      <x:c r="A236" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B236" s="9" t="str">
+        <x:v>TC-TM003-DATA-01</x:v>
+      </x:c>
+      <x:c r="C236" s="9" t="str">
+        <x:v>固定原生形状数据与独立预期</x:v>
+      </x:c>
+      <x:c r="D236" s="9" t="str">
+        <x:v>TASK-TM003-FIXTURE</x:v>
+      </x:c>
+      <x:c r="E236" s="9" t="str">
+        <x:v>data_check</x:v>
+      </x:c>
+      <x:c r="F236" s="9" t="str">
+        <x:v>1. 在 sessions/YYYY/MM/DD/*.jsonl 以 seed303 与本次已记录的 T0 生成 A/B/C 原生形状记录→同一 seed+T0 重建时字节摘要固定且三 ID 不同。2. 独立读取 expected 文件→A=110、A+B+C=660、cached=120，第二配方=220；没有调用产品解析器。</x:v>
+      </x:c>
+      <x:c r="G236" s="9" t="str">
+        <x:v>两份相对位置和字节摘要相同，A/B/C 三响应 ID 互异；四层子目录在 TM-002 草稿8层上限内、文件/目录项未达1000/5000；owner/expected 记录 T0
+A=110、A+B+C=660、cached=120，第二配方=220；没有调用产品解析器</x:v>
+      </x:c>
+      <x:c r="H236" s="9" t="str">
+        <x:v>准备：准备新私有根，不写用量表
+变化：不适用；见本用例具体数据库观察面。
+核验：不写用量表；只核对嵌套来源相对位置、元数据上限、两份源 SHA、独立 expected 和 owner；仅删除本例拥有的根。</x:v>
+      </x:c>
+      <x:c r="I236" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J236" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K236" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L236" s="9" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:211</x:v>
+      </x:c>
+      <x:c r="M236" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N236" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="237" ht="72" customHeight="1">
+      <x:c r="A237" s="4" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B237" s="4" t="str">
+        <x:v>TC-TM003-PARSE-01</x:v>
+      </x:c>
+      <x:c r="C237" s="4" t="str">
+        <x:v>三响应与缓存子项计量</x:v>
+      </x:c>
+      <x:c r="D237" s="4" t="str">
+        <x:v>TASK-TM003-PARSE</x:v>
+      </x:c>
+      <x:c r="E237" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F237" s="4" t="str">
+        <x:v>R-BASE。1. 仅追加 A 完整行并从 UI 刷新→卡片 input100/output10/total110/cached read20/cache write5/reasoning3、唯一1。2. 追加 B/C 后刷新→input600/output60/total660/cached read120/cache write30/reasoning18、唯一3；累计字段不额外加。</x:v>
+      </x:c>
+      <x:c r="G237" s="4" t="str">
+        <x:v>卡片 input100/output10/total110/cached read20/cache write5/reasoning3、唯一1
+input600/output60/total660/cached read120/cache write30/reasoning18、唯一3；累计字段不额外加</x:v>
+      </x:c>
+      <x:c r="H237" s="4" t="str">
+        <x:v>准备：空客户端库
+变化：插入 A 后1行，再插 B/C 后3行
+核验：空客户端库→插入 A 后1行，再插 B/C 后3行；Q_SUM=(3,600,60,120)，Q_SUB=(30,18)、Q_NULL=0；重置私有库。</x:v>
+      </x:c>
+      <x:c r="I237" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J237" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K237" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L237" s="4" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:215</x:v>
+      </x:c>
+      <x:c r="M237" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N237" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="238" ht="72" customHeight="1">
+      <x:c r="A238" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B238" s="9" t="str">
+        <x:v>TC-TM003-SCAN-01</x:v>
+      </x:c>
+      <x:c r="C238" s="9" t="str">
+        <x:v>追加补扫重启移动去重</x:v>
+      </x:c>
+      <x:c r="D238" s="9" t="str">
+        <x:v>TASK-TM003-SCAN</x:v>
+      </x:c>
+      <x:c r="E238" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F238" s="9" t="str">
+        <x:v>R-BASE、A/B/C。1. 三次分批追加并等 watcher 或30秒补扫→每批总量110/330/660。2. 手动刷新同文件并重启 App→仍660。3. 同一授权根内移动文件并刷新→仍唯一3、660。</x:v>
+      </x:c>
+      <x:c r="G238" s="9" t="str">
+        <x:v>每批总量110/330/660
+仍660
+仍唯一3、660</x:v>
+      </x:c>
+      <x:c r="H238" s="9" t="str">
+        <x:v>准备：空库
+变化：只增加3事件
+核验：空库→只增加3事件；每步 Q_SUM 为 (1,100,10,20)、(2,300,30,60)、(3,600,60,120)，重扫/重启/移动不变；核对 Q_CURSOR 完整行字节边界。</x:v>
+      </x:c>
+      <x:c r="I238" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J238" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K238" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L238" s="9" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:219</x:v>
+      </x:c>
+      <x:c r="M238" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N238" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="239" ht="117" customHeight="1">
+      <x:c r="A239" s="4" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B239" s="4" t="str">
+        <x:v>TC-TM003-STORE-01</x:v>
+      </x:c>
+      <x:c r="C239" s="4" t="str">
+        <x:v>事件与游标持久化</x:v>
+      </x:c>
+      <x:c r="D239" s="4" t="str">
+        <x:v>TASK-TM003-STORE</x:v>
+      </x:c>
+      <x:c r="E239" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F239" s="4" t="str">
+        <x:v>R-BASE、A/B；本例拥有的私有 profile 身份密钥和隔离客户端库。1. 完整 A 刷新→110。2. 本例进程退出/重启→110。3. 追加同 ID 同用量 A→仍110。4. 仅使本例 profile 的 usage 身份密钥不可读取，再追加 B=200/20/cached40 并刷新→保持110、停采集。5. 恢复原密钥后重启/刷新→A 不重计、B 入库，total330。密钥原文不进入报告。</x:v>
+      </x:c>
+      <x:c r="G239" s="4" t="str">
+        <x:v>110
+UI 恢复110
+仍110；无第二事件
+密钥不可用时停采集，不生成新键重扫旧日志或把 B 入库
+恢复原密钥后只补入 B，既有 A 不重计</x:v>
+      </x:c>
+      <x:c r="H239" s="4" t="str">
+        <x:v>准备：本例私有空库、受控 A/B 原生形状数据和隔离 usage 身份密钥；仅本例 fixture 可暂时使该密钥不可读取并恢复原件；不直接向事件表造数
+变化：A 一事件及游标原子提交；密钥不可用时事件/游标不变且覆盖不完整；恢复原密钥后 B 一事件提交、A 键不变
+核验：只读 Q_SUM 依次 (1,100,10,20)、同值、同值、同值、(2,300,30,60)；逐步检查 Q_CURSOR 与 coverage；原 A source_event_key 在恢复后不变，绝不让新密钥重扫成第二份 A</x:v>
+      </x:c>
+      <x:c r="I239" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J239" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K239" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L239" s="4" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:223</x:v>
+      </x:c>
+      <x:c r="M239" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N239" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="240" ht="87" customHeight="1">
+      <x:c r="A240" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B240" s="9" t="str">
+        <x:v>TC-TM003-UI-01</x:v>
+      </x:c>
+      <x:c r="C240" s="9" t="str">
+        <x:v>可信总量与未知来源展示</x:v>
+      </x:c>
+      <x:c r="D240" s="9" t="str">
+        <x:v>TASK-TM003-UI</x:v>
+      </x:c>
+      <x:c r="E240" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F240" s="9" t="str">
+        <x:v>R-BASE、A/B/C。1. 采集前查看卡片→显示尚无可证明历史/等待采集，不能显示已知0。2. 采集后→可信 input600、output60、total660、cached read120、cache write30、reasoning output18、唯一3、UTC最后采集时间。3. 插入一个缺 cached_input_tokens 的非 0.158 完整行→可信总量仍660，显示缺字段诊断，不把未知 cached 当0。</x:v>
+      </x:c>
+      <x:c r="G240" s="9" t="str">
+        <x:v>显示尚无可证明历史/等待采集，不能显示已知0
+可信 input600、output60、total660、cached read120、cache write30、reasoning output18、唯一3、UTC最后采集时间
+可信总量仍660，显示缺字段诊断，不把未知 cached 当0</x:v>
+      </x:c>
+      <x:c r="H240" s="9" t="str">
+        <x:v>准备：空库
+变化：前三条 Q_SUM=(3,600,60,120)
+核验：空库→前三条 Q_SUM=(3,600,60,120)；无新事件，Q_SUM保持三条；Q_DIAG出现缺字段，UI 区分未知来源。</x:v>
+      </x:c>
+      <x:c r="I240" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J240" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K240" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L240" s="9" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:227</x:v>
+      </x:c>
+      <x:c r="M240" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N240" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="241" ht="72" customHeight="1">
+      <x:c r="A241" s="4" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B241" s="4" t="str">
+        <x:v>TC-TM003-SOURCE-02</x:v>
+      </x:c>
+      <x:c r="C241" s="4" t="str">
+        <x:v>无响应身份累计记录降级</x:v>
+      </x:c>
+      <x:c r="D241" s="4" t="str">
+        <x:v>TASK-TM003-SOURCE</x:v>
+      </x:c>
+      <x:c r="E241" s="4" t="str">
+        <x:v>source_check</x:v>
+      </x:c>
+      <x:c r="F241" s="4" t="str">
+        <x:v>1. 输入只有 event_msg.token_count.info.total_token_usage=100/10 且无 response_id→诊断 unverified_cumulative、可信事件0。2. 加 rate-limit-only 的 info=null→诊断 missing_usage，不生成0值用量事件。</x:v>
+      </x:c>
+      <x:c r="G241" s="4" t="str">
+        <x:v>诊断 unverified_cumulative、可信事件0
+诊断 missing_usage，不生成0值用量事件</x:v>
+      </x:c>
+      <x:c r="H241" s="4" t="str">
+        <x:v>准备：新库
+变化：Q_SUM无事件
+核验：新库→Q_SUM无事件；Q_DIAG分别含 unverified_cumulative 与 missing_usage；仅测试拥有根。</x:v>
+      </x:c>
+      <x:c r="I241" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J241" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K241" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L241" s="4" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:231</x:v>
+      </x:c>
+      <x:c r="M241" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N241" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="242" ht="57" customHeight="1">
+      <x:c r="A242" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B242" s="9" t="str">
+        <x:v>TC-TM003-PARSE-02</x:v>
+      </x:c>
+      <x:c r="C242" s="9" t="str">
+        <x:v>损坏及缺字段记录隔离</x:v>
+      </x:c>
+      <x:c r="D242" s="9" t="str">
+        <x:v>TASK-TM003-PARSE</x:v>
+      </x:c>
+      <x:c r="E242" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F242" s="9" t="str">
+        <x:v>R-BASE。1. 完整合法 100/10 行→110。2. 依次追加缺 usage、负 input、cached 111&gt;input100、矛盾 total111 四个不同 ID 完整行→UI 可信总量仍110，每项显示独立诊断，不能作为0值成功事件。</x:v>
+      </x:c>
+      <x:c r="G242" s="9" t="str">
+        <x:v>110
+UI 可信总量仍110，每项显示独立诊断，不能作为0值成功事件</x:v>
+      </x:c>
+      <x:c r="H242" s="9" t="str">
+        <x:v>准备：空库
+变化：仅合法1行
+核验：空库→仅合法1行；Q_SUM=(1,100,10,20)；Q_DIAG四种错误各≥1；重置私有库。</x:v>
+      </x:c>
+      <x:c r="I242" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J242" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K242" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L242" s="9" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:235</x:v>
+      </x:c>
+      <x:c r="M242" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N242" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="243" ht="87" customHeight="1">
+      <x:c r="A243" s="4" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B243" s="4" t="str">
+        <x:v>TC-TM003-MODEL-01</x:v>
+      </x:c>
+      <x:c r="C243" s="4" t="str">
+        <x:v>模型标识与未知模型保留</x:v>
+      </x:c>
+      <x:c r="D243" s="4" t="str">
+        <x:v>TASK-TM003-PARSE</x:v>
+      </x:c>
+      <x:c r="E243" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F243" s="4" t="str">
+        <x:v>R-BASE。1. 在有同一 turn_id 的原生 turn_context 声明 gpt-6-sol 并追加 ID-m 10/1→UI 总量11，DB模型为 gpt-6-sol。2. 对新 turn 声明来源未知但实际原样标识 model-x 并追加 ID-n 10/1→UI 总量22，DB保留 model-x，不得改成0或空字符串。3. 追加找不到同 turn 上下文的 ID-o 10/1→UI 总量33，DB模型为 NULL 且显示模型未知诊断。</x:v>
+      </x:c>
+      <x:c r="G243" s="4" t="str">
+        <x:v>UI 总量11，DB模型为 gpt-6-sol
+UI 总量22，DB保留 model-x，不得改成0或空字符串
+UI 总量33，DB模型为 NULL 且显示模型未知诊断</x:v>
+      </x:c>
+      <x:c r="H243" s="4" t="str">
+        <x:v>准备：空库
+变化：最终 Q_IO=(3,30,3)
+核验：空库→最终 Q_IO=(3,30,3)；只读查询三个模型字段依次为 gpt-6-sol、model-x、NULL；不插入模型维度造数。</x:v>
+      </x:c>
+      <x:c r="I243" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J243" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K243" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L243" s="4" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:239</x:v>
+      </x:c>
+      <x:c r="M243" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N243" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="244" ht="72" customHeight="1">
+      <x:c r="A244" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B244" s="9" t="str">
+        <x:v>TC-TM003-DEDUP-01</x:v>
+      </x:c>
+      <x:c r="C244" s="9" t="str">
+        <x:v>相同响应重放和身份冲突</x:v>
+      </x:c>
+      <x:c r="D244" s="9" t="str">
+        <x:v>TASK-TM003-IDENTITY</x:v>
+      </x:c>
+      <x:c r="E244" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F244" s="9" t="str">
+        <x:v>R-BASE。1. 追加 ID-a 100/10→110。2. 重放 ID-a 完全相同记录→仍110。3. 追加 ID-b 同样100/10→220且唯一2。4. 再写 ID-a 999/99→仍220并有 identity_conflict。</x:v>
+      </x:c>
+      <x:c r="G244" s="9" t="str">
+        <x:v>110
+仍110
+220且唯一2
+仍220并有 identity_conflict</x:v>
+      </x:c>
+      <x:c r="H244" s="9" t="str">
+        <x:v>准备：空库
+变化：最终 Q_SUM=(2,200,20,40)
+核验：空库→最终 Q_SUM=(2,200,20,40)；冲突不覆盖原行；读 Q_DIAG。</x:v>
+      </x:c>
+      <x:c r="I244" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J244" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K244" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L244" s="9" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:243</x:v>
+      </x:c>
+      <x:c r="M244" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N244" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="245" ht="87" customHeight="1">
+      <x:c r="A245" s="4" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B245" s="4" t="str">
+        <x:v>TC-TM003-BRANCH-01</x:v>
+      </x:c>
+      <x:c r="C245" s="4" t="str">
+        <x:v>累计快照新会话与分支</x:v>
+      </x:c>
+      <x:c r="D245" s="4" t="str">
+        <x:v>TASK-TM003-IDENTITY</x:v>
+      </x:c>
+      <x:c r="E245" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F245" s="4" t="str">
+        <x:v>R-BASE。1. 主会话按 usage 写 100/10、50/5，而累计快照从100/10到150/15→可信165。2. 新会话写30/3→198。3. 普通 CLI fork 子文件带 forked_from_id，只有新响应20/2、thread 累计170/17；另从独立文件重放父 A→可信220、唯一4，重放不新增事件。4. 写无响应身份的累计回退和未知结构→仍220，显示 unverified_cumulative / unknown_format。</x:v>
+      </x:c>
+      <x:c r="G245" s="4" t="str">
+        <x:v>可信165
+198
+可信220、唯一4
+仍220，显示 unverified_cumulative / unknown_format</x:v>
+      </x:c>
+      <x:c r="H245" s="4" t="str">
+        <x:v>准备：空库
+变化：最终 Q_IO=(4,200,20)
+核验：空库→最终 Q_IO=(4,200,20)；output20、total220；cached 按固定各项另核；Q_DIAG有两类，继承不新增事件。</x:v>
+      </x:c>
+      <x:c r="I245" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J245" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K245" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L245" s="4" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:247</x:v>
+      </x:c>
+      <x:c r="M245" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N245" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="246" ht="102" customHeight="1">
+      <x:c r="A246" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B246" s="9" t="str">
+        <x:v>TC-TM003-NAMESPACE-01</x:v>
+      </x:c>
+      <x:c r="C246" s="9" t="str">
+        <x:v>跨来源事件身份和不明继承</x:v>
+      </x:c>
+      <x:c r="D246" s="9" t="str">
+        <x:v>TASK-TM003-IDENTITY</x:v>
+      </x:c>
+      <x:c r="E246" s="9" t="str">
+        <x:v>source_check</x:v>
+      </x:c>
+      <x:c r="F246" s="9" t="str">
+        <x:v>本例私有 schema 与tests/fixtures/tm004/identity-v1-vectors.json 中的公开测试 HMAC key（仅固定向量，绝不进入产品 profile）；标准事件 Codex provider-response/shared-call-01=100/10/cached20，Claude provider-message/shared-call-01=30/3/cached0；随后同 Codex 事件重放、另一 Agent 无复制链同 Claude ID 重用、同 Codex ID 但用量或模型冲突。</x:v>
+      </x:c>
+      <x:c r="G246" s="9" t="str">
+        <x:v>两条可信事件 total143，显式来源域防止跨工具误合并
+键相同且不新增事件
+不能把未证明同一调用的重用计为新事件，Agent 归属不进入唯一键
+首条可信事件不覆写，仍两条 total143</x:v>
+      </x:c>
+      <x:c r="H246" s="9" t="str">
+        <x:v>准备：本例拥有的全新私有 schema；使用已提交公开32字节测试 key 与标准事件作为纯身份入口固定 oracle，真实产品 profile 自行生成私密随机 key；不直接向事件表造数
+变化：正式身份/存储入口只接受2事件；重复和冲突不新增或覆写
+核验：只读 Q_SUM=(2,130,13,20)，按 source 核对两键精确等于 afd67bd0cad0227b3e7b5ac132bb9b3ed492073983b9c16a0c9cc24dd3008051 和 bf222a85ab2209f72ff82c21b7172c9315448b3e1d5bf4503a3c76b30c46cad1，再核对身份冲突与不明继承诊断、coverage 不完整</x:v>
+      </x:c>
+      <x:c r="I246" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J246" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K246" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L246" s="9" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:251</x:v>
+      </x:c>
+      <x:c r="M246" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N246" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="247" ht="57" customHeight="1">
+      <x:c r="A247" s="4" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B247" s="4" t="str">
+        <x:v>TC-TM003-PRIVACY-01</x:v>
+      </x:c>
+      <x:c r="C247" s="4" t="str">
+        <x:v>原文哨兵不得入库和报告</x:v>
+      </x:c>
+      <x:c r="D247" s="4" t="str">
+        <x:v>TASK-TM003-STORE</x:v>
+      </x:c>
+      <x:c r="E247" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F247" s="4" t="str">
+        <x:v>R-BASE 中只放合法 A=100/10/cached20；在 A 的非用量文本字段加入固定合成哨兵、代码片段和合成绝对路径，然后退出 App 检查仅本例拥有的 SQLite/WAL/采集报告。</x:v>
+      </x:c>
+      <x:c r="G247" s="4" t="str">
+        <x:v>有效用量仍只按 usage 计
+均不含哨兵/原始路径/原始 JSONL</x:v>
+      </x:c>
+      <x:c r="H247" s="4" t="str">
+        <x:v>准备：新库
+变化：仅白名单事件字段、HMAC 身份
+核验：新库→仅白名单事件字段、HMAC 身份；Q_SUM与合法用量一致；重置私有根。</x:v>
+      </x:c>
+      <x:c r="I247" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J247" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K247" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L247" s="4" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:255</x:v>
+      </x:c>
+      <x:c r="M247" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N247" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="248" ht="57" customHeight="1">
+      <x:c r="A248" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B248" s="9" t="str">
+        <x:v>TC-TM003-DATA-02</x:v>
+      </x:c>
+      <x:c r="C248" s="9" t="str">
+        <x:v>半行字节数据与归属清理</x:v>
+      </x:c>
+      <x:c r="D248" s="9" t="str">
+        <x:v>TASK-TM003-FIXTURE</x:v>
+      </x:c>
+      <x:c r="E248" s="9" t="str">
+        <x:v>data_check</x:v>
+      </x:c>
+      <x:c r="F248" s="9" t="str">
+        <x:v>1. 数据程序向拥有的文件只写 B JSONL 前半字节且无 LF→文件确实不含完整 B 行。2. 同程序补写余字节与 LF→恰好一条完整 B。3. 清理仅 owner 收据中的源文件→其他根、App 和服务不受影响。</x:v>
+      </x:c>
+      <x:c r="G248" s="9" t="str">
+        <x:v>文件确实不含完整 B 行
+恰好一条完整 B
+其他根、App 和服务不受影响</x:v>
+      </x:c>
+      <x:c r="H248" s="9" t="str">
+        <x:v>准备：无产品库写入
+变化：不适用；见本用例具体数据库观察面。
+核验：无产品库写入；按字节摘要、LF 数和 owner 核对；重置只删本例根。</x:v>
+      </x:c>
+      <x:c r="I248" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J248" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K248" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L248" s="9" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:259</x:v>
+      </x:c>
+      <x:c r="M248" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N248" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="249" ht="72" customHeight="1">
+      <x:c r="A249" s="4" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B249" s="4" t="str">
+        <x:v>TC-TM003-SCAN-02</x:v>
+      </x:c>
+      <x:c r="C249" s="4" t="str">
+        <x:v>半行补全后只计一次</x:v>
+      </x:c>
+      <x:c r="D249" s="4" t="str">
+        <x:v>TASK-TM003-SCAN</x:v>
+      </x:c>
+      <x:c r="E249" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F249" s="4" t="str">
+        <x:v>R-BASE。1. 完整 A=100/10 后刷新→total110、唯一1。2. 只追加 B=50/5 半行并刷新→仍110、游标停在 A 的 LF 后。3. 补齐 B 和 LF 后刷新，再重启→total165、唯一2，B 只计一次。</x:v>
+      </x:c>
+      <x:c r="G249" s="4" t="str">
+        <x:v>total110、唯一1
+仍110、游标停在 A 的 LF 后
+total165、唯一2，B 只计一次</x:v>
+      </x:c>
+      <x:c r="H249" s="4" t="str">
+        <x:v>准备：空库
+变化：Q_SUM=(1,100,10,20)，半行时同值，补全后 Q_IO=(2,150,15)
+核验：空库→Q_SUM=(1,100,10,20)，半行时同值，补全后 Q_IO=(2,150,15)；Q_CURSOR先停于 A 完整字节，再到 B 完整字节。</x:v>
+      </x:c>
+      <x:c r="I249" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J249" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K249" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L249" s="4" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:263</x:v>
+      </x:c>
+      <x:c r="M249" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N249" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="250" ht="72" customHeight="1">
+      <x:c r="A250" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B250" s="9" t="str">
+        <x:v>TC-TM003-SCAN-03</x:v>
+      </x:c>
+      <x:c r="C250" s="9" t="str">
+        <x:v>截断后的重读与新事件</x:v>
+      </x:c>
+      <x:c r="D250" s="9" t="str">
+        <x:v>TASK-TM003-SCAN</x:v>
+      </x:c>
+      <x:c r="E250" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F250" s="9" t="str">
+        <x:v>R-BASE。1. 完整 A=100/10 与 B=50/5 入库→total165、唯一2。2. 仅对本例源文件截断为完整 A 并刷新→已采集 B 不丢，仍165，游标重置到当前 A 的 LF。3. 追加新 ID-C=300/30 完整行并刷新、重启→total495、唯一3，A不重计。</x:v>
+      </x:c>
+      <x:c r="G250" s="9" t="str">
+        <x:v>total165、唯一2
+已采集 B 不丢，仍165，游标重置到当前 A 的 LF
+total495、唯一3，A不重计</x:v>
+      </x:c>
+      <x:c r="H250" s="9" t="str">
+        <x:v>准备：空库
+变化：Q_IO 先 (2,150,15)，截断后不变，最后 (3,450,45)
+核验：空库→Q_IO 先 (2,150,15)，截断后不变，最后 (3,450,45)；Q_CURSOR按新文件完整字节更新，不越过未闭合行。</x:v>
+      </x:c>
+      <x:c r="I250" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J250" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K250" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L250" s="9" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:267</x:v>
+      </x:c>
+      <x:c r="M250" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N250" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="251" ht="72" customHeight="1">
+      <x:c r="A251" s="4" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B251" s="4" t="str">
+        <x:v>TC-TM003-WINDOW-01</x:v>
+      </x:c>
+      <x:c r="C251" s="4" t="str">
+        <x:v>首次30天UTC采集窗口</x:v>
+      </x:c>
+      <x:c r="D251" s="4" t="str">
+        <x:v>TASK-TM003-SCAN</x:v>
+      </x:c>
+      <x:c r="E251" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F251" s="4" t="str">
+        <x:v>固定程序于运行准备阶段记录 T0 UTC 秒；授权前在本例根写完整 ID-old=T0-31天 900/90、ID-new=T0-29天 100/10；授权后追加 ID-next=T0-1天 50/5、ID-bad=无效 UTC 时间 200/20。</x:v>
+      </x:c>
+      <x:c r="G251" s="4" t="str">
+        <x:v>T0-31天的记录不计，T0-29天的记录计入
+新增 50/5 只计一次
+无效时间不得生成可信事件</x:v>
+      </x:c>
+      <x:c r="H251" s="4" t="str">
+        <x:v>准备：本例全新客户端库；只经真实 UI 授权并扫描原生形状测试文件，不直接写产品库
+变化：先插入 ID-new，再插入 ID-next；ID-old 和 ID-bad 都不入事件表
+核验：初次 Q_SUM=(1,100,10,20)，追加后 Q_IO=(2,150,15)，无效时间后同值；Q_DIAG 有 invalid_time；按响应键只读验证 old/bad 不在库</x:v>
+      </x:c>
+      <x:c r="I251" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J251" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K251" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L251" s="4" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:271</x:v>
+      </x:c>
+      <x:c r="M251" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N251" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="252" ht="117" customHeight="1">
+      <x:c r="A252" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B252" s="9" t="str">
+        <x:v>TC-TM003-COVERAGE-OVERFLOW-01</x:v>
+      </x:c>
+      <x:c r="C252" s="9" t="str">
+        <x:v>超预览上限的授权内部分页、撤销与目录变动</x:v>
+      </x:c>
+      <x:c r="D252" s="9" t="str">
+        <x:v>TASK-TM003-SCAN</x:v>
+      </x:c>
+      <x:c r="E252" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F252" s="9" t="str">
+        <x:v>本例私有 0700 授权根含1001个可排序的 sessions/YYYY/MM/DD/*.jsonl，前1000个无可信用量，最后一个 A=100/10/cached20；另有未授权根 B=900/90。预览上限1000，内部分页每页最多256。</x:v>
+      </x:c>
+      <x:c r="G252" s="9" t="str">
+        <x:v>预览不是全量扫描完成证明
+暂停状态不得提交完整覆盖
+末端第1001个 A 计一次
+撤销使旧授权能力失效，不跨根读 B
+跨页目录变动废弃全部暂定页，既有已提交 A 保留，不能续扫旧页或仅凭 complete 判正文完整</x:v>
+      </x:c>
+      <x:c r="H252" s="9" t="str">
+        <x:v>准备：本例拥有的全新客户端库、0700 双根和1001个合成 JSONL；通过真实 UI 确认根；不直接写事件表
+变化：预览/暂停零事件，完成后 A 一事件，撤销后保留 A 且覆盖不完整；目录变动废弃新一轮暂存页，已提交 A 不变
+核验：只读 Q_SUM 依次无事件、无事件、(1,100,10,20)、同值；核对 scan_incomplete 依次1、1、0、1及旧能力拒绝；第5步旧 generation 拒绝、暂存游标回滚，Q_SUM 保持(1,100,10,20)，新 generation 从头开始</x:v>
+      </x:c>
+      <x:c r="I252" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J252" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K252" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L252" s="9" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:275</x:v>
+      </x:c>
+      <x:c r="M252" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N252" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="253" ht="72" customHeight="1">
+      <x:c r="A253" s="4" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B253" s="4" t="str">
+        <x:v>TC-TM003-UI-02</x:v>
+      </x:c>
+      <x:c r="C253" s="4" t="str">
+        <x:v>源清理后的覆盖缺口</x:v>
+      </x:c>
+      <x:c r="D253" s="4" t="str">
+        <x:v>TASK-TM003-UI</x:v>
+      </x:c>
+      <x:c r="E253" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F253" s="4" t="str">
+        <x:v>R-BASE、完整 A/B。1. 导入后→UI total165 且覆盖起点为最早可信事件时间。2. 删除仅本例拥有的源文件后刷新/重启→仍165；源缺失与更早历史不可证明的提示可见，不能显示历史0。</x:v>
+      </x:c>
+      <x:c r="G253" s="4" t="str">
+        <x:v>UI total165 且覆盖起点为最早可信事件时间
+仍165；源缺失与更早历史不可证明的提示可见，不能显示历史0</x:v>
+      </x:c>
+      <x:c r="H253" s="4" t="str">
+        <x:v>准备：空库
+变化：保留2事件、Q_IO=(2,150,15)
+核验：空库→保留2事件、Q_IO=(2,150,15)；coverage.missing_before=1 或等价状态；不删事件。</x:v>
+      </x:c>
+      <x:c r="I253" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J253" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K253" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L253" s="4" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:279</x:v>
+      </x:c>
+      <x:c r="M253" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N253" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="254" ht="57" customHeight="1">
+      <x:c r="A254" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B254" s="9" t="str">
+        <x:v>TC-TM003-BOUNDARY-01</x:v>
+      </x:c>
+      <x:c r="C254" s="9" t="str">
+        <x:v>未授权根和越界链接拒绝</x:v>
+      </x:c>
+      <x:c r="D254" s="9" t="str">
+        <x:v>TASK-TM003-SCAN</x:v>
+      </x:c>
+      <x:c r="E254" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F254" s="9" t="str">
+        <x:v>测试拥有 A/B，B 内有 ID-x=900/90，A 的 sessions/YYYY/MM/DD/ 同层有 symlink escape.jsonl 指向 B。1. 仅通过真实 UI 选 A 并确认→A 的可信事件可读。2. 手动刷新与30秒补扫→B 和越界 symlink 不被读，UI 无 x 用量。</x:v>
+      </x:c>
+      <x:c r="G254" s="9" t="str">
+        <x:v>A 的可信事件可读
+B 与同层越界 symlink 均不被读，UI 无 x 用量，B 的文件摘要不变</x:v>
+      </x:c>
+      <x:c r="H254" s="9" t="str">
+        <x:v>准备：空库
+变化：只出现 A 的 response key
+核验：空库→只出现 A 的 response key；Q_SUM不含990；B 的文件摘要前后不变。</x:v>
+      </x:c>
+      <x:c r="I254" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J254" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K254" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L254" s="9" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:283</x:v>
+      </x:c>
+      <x:c r="M254" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N254" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="255" ht="57" customHeight="1">
+      <x:c r="A255" s="4" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B255" s="4" t="str">
+        <x:v>TC-TM003-AUTH-01</x:v>
+      </x:c>
+      <x:c r="C255" s="4" t="str">
+        <x:v>确认前与失效时停读</x:v>
+      </x:c>
+      <x:c r="D255" s="4" t="str">
+        <x:v>TASK-TM003-AUTH</x:v>
+      </x:c>
+      <x:c r="E255" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F255" s="4" t="str">
+        <x:v>A 含 A=100/10。1. 打开授权预览但不确认→持续扫描不启动、客户端无事件。2. 确认后→110。3. TM-002 fixture 仅使 A 授权失效，再追加 B=200/20 并刷新→卡片显示需重新授权，仍110，A 不被继续读取。</x:v>
+      </x:c>
+      <x:c r="G255" s="4" t="str">
+        <x:v>持续扫描不启动、客户端无事件
+110
+卡片显示需重新授权，仍110，A 不被继续读取</x:v>
+      </x:c>
+      <x:c r="H255" s="4" t="str">
+        <x:v>准备：新库
+变化：确认前0事件
+核验：新库→确认前0事件；确认后 Q_SUM=(1,100,10,20)；失效后不变，游标不前进。</x:v>
+      </x:c>
+      <x:c r="I255" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J255" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K255" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L255" s="4" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:287</x:v>
+      </x:c>
+      <x:c r="M255" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N255" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="256" ht="72" customHeight="1">
+      <x:c r="A256" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B256" s="9" t="str">
+        <x:v>TC-TM003-AUTH-02</x:v>
+      </x:c>
+      <x:c r="C256" s="9" t="str">
+        <x:v>重新授权后的去重补扫</x:v>
+      </x:c>
+      <x:c r="D256" s="9" t="str">
+        <x:v>TASK-TM003-AUTH</x:v>
+      </x:c>
+      <x:c r="E256" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F256" s="9" t="str">
+        <x:v>A 已通过真实 UI 授权且含 A=100/10、B=200/20。1. 采集后→330、唯一2。2. 失效期间追加 C=300/30 与重放 A→仍330。3. 从真实 UI 重新授权同根并确认→660、唯一3。4. 刷新并重启→仍660。</x:v>
+      </x:c>
+      <x:c r="G256" s="9" t="str">
+        <x:v>330、唯一2
+仍330
+660、唯一3
+仍660</x:v>
+      </x:c>
+      <x:c r="H256" s="9" t="str">
+        <x:v>准备：空库
+变化：Q_SUM依次 (2,300,30,60)、同值、(3,600,60,120)、同值
+核验：空库→Q_SUM依次 (2,300,30,60)、同值、(3,600,60,120)、同值；重复 A 不插入。</x:v>
+      </x:c>
+      <x:c r="I256" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J256" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K256" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L256" s="9" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:291</x:v>
+      </x:c>
+      <x:c r="M256" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N256" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="257" ht="87" customHeight="1">
+      <x:c r="A257" s="4" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B257" s="4" t="str">
+        <x:v>TC-TM003-ISOLATION-01</x:v>
+      </x:c>
+      <x:c r="C257" s="4" t="str">
+        <x:v>已验证主体切换时来源和采集状态隔离</x:v>
+      </x:c>
+      <x:c r="D257" s="4" t="str">
+        <x:v>TASK-TM003-AUTH</x:v>
+      </x:c>
+      <x:c r="E257" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F257" s="4" t="str">
+        <x:v>两隔离真实服务 O1/O2；O1 成员 U1/U2，O2 成员 U1b（ID与U1相同）；本例根 A 含固定 ID-a=100/10；各主体通过真实 UI 分别确认来源。</x:v>
+      </x:c>
+      <x:c r="G257" s="4" t="str">
+        <x:v>只有 P1 来源能力被使用
+旧主体读取已停止
+相同响应在不同已确认主体各自计一次
+规范化 origin 是主体键的一部分
+恢复旧主体不重计，也不读取其他主体来源</x:v>
+      </x:c>
+      <x:c r="H257" s="4" t="str">
+        <x:v>准备：只经真实服务创建合成 U1/U2/U1b，客户端新库，隔离根 A；不向 usage_event 造数
+变化：P1/P2 各自一条事件与独立游标，P3 无事件或游标；身份切换不删除旧主体记录
+核验：按 HMAC(O1,U1)、HMAC(O1,U2)、HMAC(O2,U1b) 的不可逆主体键分别查询 Q_SUM 和 source_cursor；原路径、账号凭据与原始日志不入库</x:v>
+      </x:c>
+      <x:c r="I257" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J257" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K257" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L257" s="4" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:295</x:v>
+      </x:c>
+      <x:c r="M257" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N257" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="258" ht="117" customHeight="1">
+      <x:c r="A258" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B258" s="9" t="str">
+        <x:v>TC-TM003-MIGRATE-01</x:v>
+      </x:c>
+      <x:c r="C258" s="9" t="str">
+        <x:v>客户端库迁移和恢复</x:v>
+      </x:c>
+      <x:c r="D258" s="9" t="str">
+        <x:v>TASK-TM003-MIGRATE</x:v>
+      </x:c>
+      <x:c r="E258" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F258" s="9" t="str">
+        <x:v>上一实际稳定版 TM-002 私有 profile，包含合成账号、已确认授权根与原有 schema；该版尚无采集事件，若无稳定版包则 BLOCKED。1. 在本轮隔离根备份并验证可恢复→旧 schema、账号/授权状态有摘要且无 usage_event。2. 经 App 内真实更新到候选→新 schema 建立，账号/授权保留，卡片显示尚无可信历史；向已授权根追加固定 A=100/10 后刷新→唯一1、total110。3. 在另一拥有副本注入迁移中断并重试→中断可检测，恢复旧 profile 后重试可得相同账号/授权与唯一 A，不重复计。</x:v>
+      </x:c>
+      <x:c r="G258" s="9" t="str">
+        <x:v>备份副本可打开且还原原状态
+真实更新与首次采集成功，未制造旧版不存在的历史用量
+中断可检测，恢复与重试后聚合不变</x:v>
+      </x:c>
+      <x:c r="H258" s="9" t="str">
+        <x:v>准备：从上一实际稳定 TM-002 包生成本例私有 profile，备份并验证可恢复；源版无 usage_event
+变化：候选创建目标 schema，首次 A 采集写入唯一一条事件；中断副本恢复后同一事件不重计
+核验：只在隔离副本造旧状态；源库只读核对旧 schema、账号/授权记录与无用量表；更新后 Q_SCHEMA 为目标版本、Q_SUM 先无行、采集 A 后为 (1,100,10,20)，账号/授权记录不变；不接触生产库。</x:v>
+      </x:c>
+      <x:c r="I258" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J258" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K258" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L258" s="9" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:299</x:v>
+      </x:c>
+      <x:c r="M258" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N258" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="259" ht="87" customHeight="1">
+      <x:c r="A259" s="4" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B259" s="4" t="str">
+        <x:v>TC-TM003-E2E-01</x:v>
+      </x:c>
+      <x:c r="C259" s="4" t="str">
+        <x:v>固定逐项入口和证据审计</x:v>
+      </x:c>
+      <x:c r="D259" s="4" t="str">
+        <x:v>TASK-TM003-E2E</x:v>
+      </x:c>
+      <x:c r="E259" s="4" t="str">
+        <x:v>governance</x:v>
+      </x:c>
+      <x:c r="F259" s="4" t="str">
+        <x:v>1. 固定单例入口指定一条 TM-003 TC→新 run_id、逐步原件和 SQL/源摘要。2. 对 TM-001 已交付集合加 TM-003 全部目标 TC/四组补充运行→每例/变体/组有原件，零缺例/跳过/重试。3. 移除副本报告一步→审计 BLOCKED。4. 在副本移除一条 TM-003 TC 或将变体 release 改成 TM-001→跨版本门禁拒绝，不签通行证。</x:v>
+      </x:c>
+      <x:c r="G259" s="4" t="str">
+        <x:v>新 run_id，逐步原件和 SQL/源摘要齐全
+逐 TC/变体与场景组均有独立原件、零缺例/跳过/重试；门禁集合不再固定只含 TM-001
+审计判 BLOCKED
+跨版本门禁拒绝该副本，不生成通行证</x:v>
+      </x:c>
+      <x:c r="H259" s="4" t="str">
+        <x:v>准备：使用测试拥有的独立库，审计只读原件
+变化：不适用；见本用例具体数据库观察面。
+核验：使用测试拥有的独立库，审计只读原件；不生成假 PASS。</x:v>
+      </x:c>
+      <x:c r="I259" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J259" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K259" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L259" s="4" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:303</x:v>
+      </x:c>
+      <x:c r="M259" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N259" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="260" ht="72" customHeight="1">
+      <x:c r="A260" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B260" s="9" t="str">
+        <x:v>TC-TM003-E2E-02</x:v>
+      </x:c>
+      <x:c r="C260" s="9" t="str">
+        <x:v>最终DMG真实链路和清理</x:v>
+      </x:c>
+      <x:c r="D260" s="9" t="str">
+        <x:v>TASK-TM003-E2E</x:v>
+      </x:c>
+      <x:c r="E260" s="9" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F260" s="9" t="str">
+        <x:v>1. 从最终候选 DMG 复制并安装 App→记录原件/安装路径与哈希。2. 用 Playwright executablePath 启动→真实 UI/IPC/采集/服务/SQLite 全链且 TM-001/002/003 应测集合精确相等。3. 退出并按 owner 清理→无遗留进程/端口/私有目录。</x:v>
+      </x:c>
+      <x:c r="G260" s="9" t="str">
+        <x:v>记录原件/安装路径与哈希
+真实 UI/IPC/采集/服务/SQLite 全链且 TM-001/002/003 应测集合精确相等
+无遗留进程/端口/私有目录</x:v>
+      </x:c>
+      <x:c r="H260" s="9" t="str">
+        <x:v>准备：每例隔离客户端/服务库
+变化：不适用；见本用例具体数据库观察面。
+核验：每例隔离客户端/服务库；最终 DB 与逐 TC 预期相符；包、源码、测试摘要一致。</x:v>
+      </x:c>
+      <x:c r="I260" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J260" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K260" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L260" s="9" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:307</x:v>
+      </x:c>
+      <x:c r="M260" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N260" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="261" ht="57" customHeight="1">
+      <x:c r="A261" s="4" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B261" s="4" t="str">
+        <x:v>TC-TM003-GOV-01</x:v>
+      </x:c>
+      <x:c r="C261" s="4" t="str">
+        <x:v>追踪总表与门禁拒绝</x:v>
+      </x:c>
+      <x:c r="D261" s="4" t="str">
+        <x:v>TASK-TM003-RELEASE</x:v>
+      </x:c>
+      <x:c r="E261" s="4" t="str">
+        <x:v>governance</x:v>
+      </x:c>
+      <x:c r="F261" s="4" t="str">
+        <x:v>1. 核对 manifest/需求→TASK→TC/AC、数据能力、Changelog、总表→零孤立或空预期。2. 运行 structure/baseline/quality 与总表回读→全部真实返回0才记录文档基线。3. 用候选原始报告门禁→任一 FAIL/BLOCKED 拒绝通行证。</x:v>
+      </x:c>
+      <x:c r="G261" s="4" t="str">
+        <x:v>TASK→TC/AC、数据能力、Changelog、总表→零孤立或空预期
+全部真实返回0才记录文档基线
+任一 FAIL/BLOCKED 拒绝通行证</x:v>
+      </x:c>
+      <x:c r="H261" s="4" t="str">
+        <x:v>准备：对数据库不适用
+变化：不适用；见本用例具体数据库观察面。
+核验：对数据库不适用；使用机器清单、结果 Excel 与原件摘要，不代写产品库。</x:v>
+      </x:c>
+      <x:c r="I261" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J261" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K261" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L261" s="4" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:311</x:v>
+      </x:c>
+      <x:c r="M261" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N261" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="262" ht="72" customHeight="1">
+      <x:c r="A262" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B262" s="9" t="str">
+        <x:v>TC-TM003-CORE-01</x:v>
+      </x:c>
+      <x:c r="C262" s="9" t="str">
+        <x:v>完整LF增量与累计快照解析</x:v>
+      </x:c>
+      <x:c r="D262" s="9" t="str">
+        <x:v>TASK-TM003-PARSE</x:v>
+      </x:c>
+      <x:c r="E262" s="9" t="str">
+        <x:v>source_check</x:v>
+      </x:c>
+      <x:c r="F262" s="9" t="str">
+        <x:v>原生形状完整A=100/10/cached20；B=200/20/cached40半行后补LF；C=300/30/cached60完整行及累计快照；固定种子和T0。</x:v>
+      </x:c>
+      <x:c r="G262" s="9" t="str">
+        <x:v>仅A一事件，input100/output10/total110/cached20，完成偏移恰在A的LF后
+仍仅A，完成偏移不跨半行
+仅A/B/C三事件，input600/output60/total660/cached120；累计快照和复扫不增量；完成偏移在累计快照行的LF后</x:v>
+      </x:c>
+      <x:c r="H262" s="9" t="str">
+        <x:v>准备：无产品DB写入；每例新私有根
+变化：不适用；纯解析返回事件与完成字节偏移
+核验：按源文件字节摘要、长度、完整LF边界和解析事件字段逐步比对；仅清理本例owner根</x:v>
+      </x:c>
+      <x:c r="I262" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J262" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K262" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L262" s="9" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:315</x:v>
+      </x:c>
+      <x:c r="M262" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N262" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="263" ht="72" customHeight="1">
+      <x:c r="A263" s="4" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B263" s="4" t="str">
+        <x:v>TC-TM003-CORE-02</x:v>
+      </x:c>
+      <x:c r="C263" s="4" t="str">
+        <x:v>累计空值及非法用量诊断</x:v>
+      </x:c>
+      <x:c r="D263" s="4" t="str">
+        <x:v>TASK-TM003-SOURCE
+TASK-TM003-PARSE</x:v>
+      </x:c>
+      <x:c r="E263" s="4" t="str">
+        <x:v>source_check</x:v>
+      </x:c>
+      <x:c r="F263" s="4" t="str">
+        <x:v>无ID累计100/10和rate-limit info=null；合法A；缺usage、负input、cached111&gt;input100、total111四条不同ID完整LF行；未知build。</x:v>
+      </x:c>
+      <x:c r="G263" s="4" t="str">
+        <x:v>零可信事件；分别诊断unverified_cumulative、missing_usage，不生成零值事件
+只有A=110一事件；四条负例依次诊断missing_usage、negative_input、invalid_cached、invalid_total；不覆写A
+零新增事件，诊断unsupported_source_version</x:v>
+      </x:c>
+      <x:c r="H263" s="4" t="str">
+        <x:v>准备：无产品DB写入；每例新私有根
+变化：不适用；仅模块事件/诊断返回值
+核验：独立枚举返回的事件数量、数值、诊断代码和数量；仅清理本例owner根</x:v>
+      </x:c>
+      <x:c r="I263" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J263" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K263" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L263" s="4" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:319</x:v>
+      </x:c>
+      <x:c r="M263" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N263" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="264" ht="72" customHeight="1">
+      <x:c r="A264" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B264" s="9" t="str">
+        <x:v>TC-TM003-CORE-03</x:v>
+      </x:c>
+      <x:c r="C264" s="9" t="str">
+        <x:v>公开向量身份去重与冲突</x:v>
+      </x:c>
+      <x:c r="D264" s="9" t="str">
+        <x:v>TASK-TM003-IDENTITY</x:v>
+      </x:c>
+      <x:c r="E264" s="9" t="str">
+        <x:v>source_check</x:v>
+      </x:c>
+      <x:c r="F264" s="9" t="str">
+        <x:v>公开identity-v1测试key；codex/provider-response/shared-call-01的A=100/10/cached20；同ID重放；shared-call-02同usage；shared-call-01冲突999/99；claude_code/provider-message/shared-call-01仅求键。</x:v>
+      </x:c>
+      <x:c r="G264" s="9" t="str">
+        <x:v>一事件total110；键精确为afd67bd0cad0227b3e7b5ac132bb9b3ed492073983b9c16a0c9cc24dd3008051
+重放仍一事件；新ID后两事件，input200/output20/cached40/total220
+首事件不变，诊断identity_conflict；Claude键精确为bf222a85ab2209f72ff82c21b7172c9315448b3e1d5bf4503a3c76b30c46cad1且不向本例产品库添加Claude事件</x:v>
+      </x:c>
+      <x:c r="H264" s="9" t="str">
+        <x:v>准备：创建本例拥有的空临时SQLite；不访问产品profile/Keychain
+变化：仅通过正式模块API插入两条Codex事件与一条冲突诊断
+核验：只读核对来源域唯一约束、两行总量、首行未覆写和诊断；只清理本例owner DB</x:v>
+      </x:c>
+      <x:c r="I264" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J264" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K264" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L264" s="9" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:323</x:v>
+      </x:c>
+      <x:c r="M264" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N264" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G5:G176">
+  <x:conditionalFormatting sqref="G5:G264">
     <x:cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="I5:I176">
+  <x:conditionalFormatting sqref="I5:I264">
     <x:cfRule type="containsText" dxfId="15" priority="4" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="17" priority="6" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="J5:J176">
+  <x:conditionalFormatting sqref="J5:J264">
     <x:cfRule type="containsText" dxfId="18" priority="7" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="19" priority="8" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="20" priority="9" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="M5:M176">
+  <x:conditionalFormatting sqref="M5:M264">
     <x:cfRule type="containsText" dxfId="21" priority="10" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="22" priority="11" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="23" priority="12" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb73f0eb8104442b9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R912ecfc95f1a4378"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14952,7 +20511,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R105b9c20d4354a21"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d8dfb9ad96d493c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15098,7 +20657,7 @@
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="87" customHeight="1">
+    <x:row r="6" ht="117" customHeight="1">
       <x:c r="A6" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
       </x:c>
@@ -15127,7 +20686,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J6" s="9" t="str">
-        <x:v>独立候选 d2db551 门禁 PASS 仅为历史；本地 master 固定 c2911bc 首次最终包门禁 FAIL，精细116项91 PASS/14 FAIL/11 BLOCKED，UPDATE-05签名输入缺失；无正式稳定包，未发布。</x:v>
+        <x:v>开发中，未发布。c291本地master最终包门禁FAIL：116项91 PASS/14 FAIL/11 BLOCKED；9f06cb1修复私有签名输入后开发检查PASS，但新定向App仍FAIL/BLOCKED并有ENOSPC，功能回归未完成。旧d2db551独立候选PASS不转用于新候选。正式发行完整门禁NOT_RUN，无稳定0.1原包。</x:v>
       </x:c>
       <x:c r="K6" s="9" t="str">
         <x:v>旧SwiftUI PR #2 已合并、历史双平台六例PASS；不继承给Electron</x:v>
@@ -15154,7 +20713,7 @@
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="117" customHeight="1">
+    <x:row r="7" ht="192" customHeight="1">
       <x:c r="A7" s="4" t="str">
         <x:v>v0.2.0-20261001T034118Z</x:v>
       </x:c>
@@ -15183,10 +20742,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J7" s="4" t="str">
-        <x:v>0.2设计草稿：3功能点/9 TASK、28父TC/35变体已编制，SOP-008基线与固定程序未完成；需上一实际本机稳定0.1原包；c291本地master首次门禁FAIL和schema 2归档消费者。最终包Keychain身份探针缺隔离测试账号或已实测独立命名空间，相关E2E BLOCKED；产品E2E NOT_RUN、未发布。</x:v>
+        <x:v>设计基线已完成：3功能点、9 TASK、28父TC、35变体。开发工作树已有原生目录面板、加密locator、根FD受限读取、React授权UI及33个固定E2E叶入口（28可执行、5场景摘要）；报告单元59/59、治理473/473、构建PASS。产品E2E因AX trusted=false及隔离标准测试账号不可用BLOCKED，Keychain最终包隔离未证实。本独立文档树未合该代码，机器绑定仍planned；正式发行完整门禁NOT_RUN、未发布。0.2公开配置为version0.2.0/build200及测试高版0.2.1/build201，实际0.2包尚未证明。</x:v>
       </x:c>
       <x:c r="K7" s="4" t="str">
-        <x:v>TM001独立候选d2门禁PASS；本地master整合树尚未完成同树门禁或SOP-020稳定归档，不能继承为0.2升级源；本版无实际产品运行。</x:v>
+        <x:v>TM001独立候选d2门禁PASS只属历史；本地master c2911bc首次最终包门禁FAIL、无SOP-020稳定原包，不能作为0.2升级源；本版无实际产品运行。</x:v>
       </x:c>
       <x:c r="L7" s="4" t="str">
         <x:v>releases/v0.2.0-20261001T034118Z/00-manifest.json</x:v>
@@ -15198,7 +20757,7 @@
         <x:v>未核实同名功能分支SHA/tree读回</x:v>
       </x:c>
       <x:c r="O7" s="4" t="str">
-        <x:v>未来设计草稿；产品E2E未执行，本机稳定包未归档；0.1上游c291门禁FAIL</x:v>
+        <x:v>产品E2E未执行；本机稳定包未归档</x:v>
       </x:c>
       <x:c r="P7" s="4" t="str">
         <x:v>本轮五版稳定后一次受保护PR；待办</x:v>
@@ -15210,25 +20769,193 @@
         <x:v>releases/v0.2.0-20261001T034118Z/01-requirements.md:32</x:v>
       </x:c>
     </x:row>
+    <x:row r="8" ht="132" customHeight="1">
+      <x:c r="A8" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+      <x:c r="B8" s="9" t="str">
+        <x:v>0.3.0</x:v>
+      </x:c>
+      <x:c r="C8" s="17" t="n">
+        <x:v>46296.157546296294</x:v>
+      </x:c>
+      <x:c r="D8" s="9" t="str">
+        <x:v>产品功能</x:v>
+      </x:c>
+      <x:c r="E8" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="F8" s="9" t="str">
+        <x:v>未发布</x:v>
+      </x:c>
+      <x:c r="G8" s="9" t="str">
+        <x:v>internal</x:v>
+      </x:c>
+      <x:c r="H8" s="9" t="str">
+        <x:v>dmg/&lt;release_id&gt;/：正式包仅在本机门禁 PASS 后保存</x:v>
+      </x:c>
+      <x:c r="I8" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J8" s="9" t="str">
+        <x:v>整版draft、未发布。原27条目标TC保留，新增3条无授权CORE辅助TC在恢复新仓库候选7d77d63按SOP-008独立切片判为development_slice_ready；固定程序绑定与实际运行仍缺，30条TM003目标/辅助TC均未获得产品PASS。授权/真实App/服务/Keychain及产品E2E仍BLOCKED，0.3整版baseline和正式发行完整门禁NOT_RUN。</x:v>
+      </x:c>
+      <x:c r="K8" s="9" t="str">
+        <x:v>TM-001 干净源码候选为技术基底；其产品门禁不继承给TM-003</x:v>
+      </x:c>
+      <x:c r="L8" s="9" t="str">
+        <x:v>releases/v0.3.0-20261001T034652Z/00-manifest.json</x:v>
+      </x:c>
+      <x:c r="M8" s="9" t="str">
+        <x:v>releases/v0.3.0-20261001T034652Z/06-iteration-record.md</x:v>
+      </x:c>
+      <x:c r="N8" s="9" t="str">
+        <x:v>未核实同名功能分支SHA/tree读回</x:v>
+      </x:c>
+      <x:c r="O8" s="9" t="str">
+        <x:v>产品E2E未执行；本机稳定包未归档</x:v>
+      </x:c>
+      <x:c r="P8" s="9" t="str">
+        <x:v>本轮五版稳定后一次受保护PR；待办</x:v>
+      </x:c>
+      <x:c r="Q8" s="9" t="str">
+        <x:v>本轮五版稳定及远端master读回后逐版登记；待办</x:v>
+      </x:c>
+      <x:c r="R8" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="132" customHeight="1">
+      <x:c r="A9" s="4" t="str">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+      <x:c r="B9" s="4" t="str">
+        <x:v>0.4.0</x:v>
+      </x:c>
+      <x:c r="C9" s="16" t="n">
+        <x:v>46296.16982638889</x:v>
+      </x:c>
+      <x:c r="D9" s="4" t="str">
+        <x:v>产品功能</x:v>
+      </x:c>
+      <x:c r="E9" s="4" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="F9" s="4" t="str">
+        <x:v>未发布</x:v>
+      </x:c>
+      <x:c r="G9" s="4" t="str">
+        <x:v>internal</x:v>
+      </x:c>
+      <x:c r="H9" s="4" t="str">
+        <x:v>dmg/&lt;release_id&gt;/：仅门禁PASS后放正式DMG</x:v>
+      </x:c>
+      <x:c r="I9" s="15" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J9" s="4" t="str">
+        <x:v>整版draft、未发布。8 TASK、20细TC及四组摘要已登记；纯内存Claude 2.1.126解析器f2c3972覆盖已验证主会话、复制fork、同ID双块及可核实单层Agent，单元36/36、治理452/452PASS。改写UUID、fork-context-ref、嵌套Agent、有效零及授权/身份/SQLite仍缺证据或集成；20条产品TC未执行，正式发行完整门禁NOT_RUN。</x:v>
+      </x:c>
+      <x:c r="K9" s="4" t="str">
+        <x:v>TM004源分支原生零/缺失与nested Agent定向探针仅为研究证据；0.3及此前稳定原包尚未形成，真实升级BLOCKED。</x:v>
+      </x:c>
+      <x:c r="L9" s="4" t="str">
+        <x:v>releases/v0.4.0-20261001T040433Z/00-manifest.json</x:v>
+      </x:c>
+      <x:c r="M9" s="4" t="str">
+        <x:v>releases/v0.4.0-20261001T040433Z/06-iteration-record.md</x:v>
+      </x:c>
+      <x:c r="N9" s="4" t="str">
+        <x:v>未核实同名远端功能分支SHA/tree</x:v>
+      </x:c>
+      <x:c r="O9" s="4" t="str">
+        <x:v>最终包产品E2E未执行；本机稳定包未归档</x:v>
+      </x:c>
+      <x:c r="P9" s="4" t="str">
+        <x:v>全部目标版本稳定后待办</x:v>
+      </x:c>
+      <x:c r="Q9" s="4" t="str">
+        <x:v>远端master读回后逐版待办</x:v>
+      </x:c>
+      <x:c r="R9" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="102" customHeight="1">
+      <x:c r="A10" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+      <x:c r="B10" s="9" t="str">
+        <x:v>0.5.0</x:v>
+      </x:c>
+      <x:c r="C10" s="17" t="n">
+        <x:v>46296.15797453704</x:v>
+      </x:c>
+      <x:c r="D10" s="9" t="str">
+        <x:v>产品功能</x:v>
+      </x:c>
+      <x:c r="E10" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="F10" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="G10" s="9" t="str">
+        <x:v>internal</x:v>
+      </x:c>
+      <x:c r="H10" s="9" t="str">
+        <x:v>dmg/&lt;release_id&gt;/：仅门禁PASS后放正式原名包</x:v>
+      </x:c>
+      <x:c r="I10" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J10" s="9" t="str">
+        <x:v>整版draft、未发布。6 TASK、32父TC、6稳定变体及两组摘要已登记；纯统计语义oracle仅可验证算术/覆盖合同，不证明双来源真实采集。固定产品数据、SQLite/IPC、安装App逐TC绑定未完成；正式发行完整门禁NOT_RUN。</x:v>
+      </x:c>
+      <x:c r="K10" s="9" t="str">
+        <x:v>TM005语义oracle只验证规范化样例；0.4及此前稳定原包尚未形成，真实升级BLOCKED。</x:v>
+      </x:c>
+      <x:c r="L10" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/00-manifest.json</x:v>
+      </x:c>
+      <x:c r="M10" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/06-iteration-record.md</x:v>
+      </x:c>
+      <x:c r="N10" s="9" t="str">
+        <x:v>未核实同名远端功能分支SHA/tree</x:v>
+      </x:c>
+      <x:c r="O10" s="9" t="str">
+        <x:v>最终包产品E2E未执行；本机稳定包未归档</x:v>
+      </x:c>
+      <x:c r="P10" s="9" t="str">
+        <x:v>全部目标版本稳定后待办</x:v>
+      </x:c>
+      <x:c r="Q10" s="9" t="str">
+        <x:v>远端master读回后逐版待办</x:v>
+      </x:c>
+      <x:c r="R10" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="F5:F7">
+  <x:conditionalFormatting sqref="F5:F10">
     <x:cfRule type="containsText" dxfId="30" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="31" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="32" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="J5:J7">
+  <x:conditionalFormatting sqref="J5:J10">
     <x:cfRule type="containsText" dxfId="33" priority="4" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="34" priority="5" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="35" priority="6" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="M5:M7">
+  <x:conditionalFormatting sqref="M5:M10">
     <x:cfRule type="containsText" dxfId="36" priority="7" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="37" priority="8" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="38" priority="9" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra250272c05624546"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc08e1a26493946c2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16307,15 +22034,93 @@
         <x:v>docs/retrospectives/2026-10-01-development-and-governance.md:77</x:v>
       </x:c>
     </x:row>
+    <x:row r="44" ht="132" customHeight="1">
+      <x:c r="A44" s="9" t="str">
+        <x:v>RET-039</x:v>
+      </x:c>
+      <x:c r="B44" s="9" t="str">
+        <x:v>切换当前版本暴露历史用例隐式归属</x:v>
+      </x:c>
+      <x:c r="C44" s="9" t="str">
+        <x:v>TM-002 独立文档分支切到当前 0.2 后，78 条未写 release_id 的 TM-001 历史父用例默认落入 0.2 manifest；补归属后 45 条早期 source.heading 仅存 ID，与原详细文档完整标题不一致。</x:v>
+      </x:c>
+      <x:c r="D44" s="9" t="str">
+        <x:v>核对导出失败清单、0.1/0.2 manifest、用例功能与原文行号；认定为追踪元数据问题，保留 TM-001 既定动作、预期和原始测试结果。</x:v>
+      </x:c>
+      <x:c r="E44" s="9" t="str">
+        <x:v>78 条 TM-001 父用例显式登记来源 0.1 release_id；逐行核对并补齐 45 条精确原文标题；重生用例表并执行导出、文档基线和语义映射检查。</x:v>
+      </x:c>
+      <x:c r="F44" s="9" t="str">
+        <x:v>0.2 分支用例导出 CURRENT（137 父记录/437 父步骤），structure/baseline/quality PASS，TM-002 28 父 TC/35 变体获设计基线；完整治理回归452项中9项旧TM001程序跨版本ERROR，原始检查在 .local/docs-checks/20261001-tm002-baseline/，修复交开发会话。本版产品E2E未执行、未发布。</x:v>
+      </x:c>
+      <x:c r="G44" s="9" t="str">
+        <x:v>跨版本共用机器用例目录要为历史用例显式写来源版本，标题精确回链；切换当前版本时必须实测追踪合同。</x:v>
+      </x:c>
+      <x:c r="H44" s="9" t="str">
+        <x:v>docs/retrospectives/2026-10-01-development-and-governance.md:89</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="72" customHeight="1">
+      <x:c r="A45" s="4" t="str">
+        <x:v>RET-040</x:v>
+      </x:c>
+      <x:c r="B45" s="4" t="str">
+        <x:v>历史用例显式来源与旧治理程序冲突</x:v>
+      </x:c>
+      <x:c r="C45" s="4" t="str">
+        <x:v>切换0.2当前版本后，完整治理452项中9项ERROR；旧程序仍以顶层0.2判定历史TM001变体来源。</x:v>
+      </x:c>
+      <x:c r="D45" s="4" t="str">
+        <x:v>保留首次失败原件，由TM002开发会话修固定程序和负测，文档树拣选后完整重跑。</x:v>
+      </x:c>
+      <x:c r="E45" s="4" t="str">
+        <x:v>ca0c43b按父TC/变体显式release_id校验历史来源并拒绝混合/未来来源；本树拣选为dcf215f。</x:v>
+      </x:c>
+      <x:c r="F45" s="4" t="str">
+        <x:v>完整治理457/457 PASS，日志.local/docs-checks/20261001-remote-checkpoint-docs/governance-after-ca0.log；TM002产品E2E未执行。</x:v>
+      </x:c>
+      <x:c r="G45" s="4" t="str">
+        <x:v>元数据改为显式来源后，所有消费程序都要按该字段校验，当前版本切换须纳入回归。</x:v>
+      </x:c>
+      <x:c r="H45" s="4" t="str">
+        <x:v>docs/retrospectives/2026-10-01-development-and-governance.md:101</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="87" customHeight="1">
+      <x:c r="A46" s="9" t="str">
+        <x:v>RET-041</x:v>
+      </x:c>
+      <x:c r="B46" s="9" t="str">
+        <x:v>0.1本地master首次最终包门禁缺签名输入</x:v>
+      </x:c>
+      <x:c r="C46" s="9" t="str">
+        <x:v>c2911bc最终包门禁FAIL：116原始项91 PASS/14 FAIL/11 BLOCKED，UPDATE-05父项和13变体缺签名输入，0.1稳定原包无法归档。</x:v>
+      </x:c>
+      <x:c r="D46" s="9" t="str">
+        <x:v>核对固定SHA/tree和原件，保留FAIL，不借用独立d2db551候选PASS；交TM001按SOP015修复。</x:v>
+      </x:c>
+      <x:c r="E46" s="9" t="str">
+        <x:v>针对新候选补签名输入与固定回归并完整重跑；文档会话为失败run新建逐例Excel并登记根总表。</x:v>
+      </x:c>
+      <x:c r="F46" s="9" t="str">
+        <x:v>原件在总控整合树.local/gates/tm001-master-gate-c2911bc-20261001T113036Z/；独立结果Excel回读PASS但产品FAIL，78父TC 66 PASS/1 FAIL/11 BLOCKED、38变体25 PASS/13 FAIL；无稳定包。</x:v>
+      </x:c>
+      <x:c r="G46" s="9" t="str">
+        <x:v>独立候选PASS不能移给最终整合树；最终包签名输入须在运行前可用且由机器验证。</x:v>
+      </x:c>
+      <x:c r="H46" s="9" t="str">
+        <x:v>docs/retrospectives/2026-10-01-development-and-governance.md:113</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="F5:F43">
+  <x:conditionalFormatting sqref="F5:F46">
     <x:cfRule type="containsText" dxfId="39" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="40" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="41" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfed032a9b53a4532"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra38b2a0da86e45e9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TokenMeter项目总表.xlsx
+++ b/TokenMeter项目总表.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R04a09d8054e24439"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Ra8b6d438e10e4cc8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R6744e6d3400e4dbf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R2ba2051075b449cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="Rde15358f574c431e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R828cd351cd3f4a6b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R9c2d956194f14733"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R1b84a2ea719747e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Ra3337ccae59b4978"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R8b1eb842c9be4df6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R9db3c10219b94070"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R49697d2c441d464b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="R5d12880f2ce24702"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R60e45e41e1234871"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="Rf8797fb3cdf7496a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R82b1eb0351634d5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R95cfb4f1d6ac42bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="Rabfd9323da1c4b9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R1d58ab70850b4c19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Rdd0b166202e346e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="Rd589207889cc4343"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="Rd07e33eea4e84bed"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -755,8 +755,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TMTable6" displayName="TMTable6" ref="A4:N264" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:N264"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TMTable6" displayName="TMTable6" ref="A4:N267" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:N267"/>
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="功能编号"/>
     <x:tableColumn id="2" name="用例编号"/>
@@ -1101,8 +1101,8 @@
         <x:v>已登记用例</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:f>COUNTA('05测试用例'!B5:B264)</x:f>
-        <x:v>260</x:v>
+        <x:f>COUNTA('05测试用例'!B5:B267)</x:f>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="C8" s="9" t="str">
         <x:v>父用例与具有稳定 ID 的变体各占一行；含未来概要场景</x:v>
@@ -1125,7 +1125,7 @@
         <x:v>细化产品用例</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>190</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C10" s="9" t="str">
         <x:v>逐条结果按运行批次记录；稳定变体独立列出</x:v>
@@ -1255,7 +1255,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad2356804e564194"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa21f6bd2e694056"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1963,7 +1963,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c6ce5ad2d3f4c4e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc2f0e39e73241d3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2112,7 +2112,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbabee8887f5246c6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17a35b4f5f0d417e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2547,7 +2547,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb60bcb58940a449d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R961caa3c423e4d07"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3594,7 +3594,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd30be25a417f4e6e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93b416a951454bb2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4701,7 +4701,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9ab17abf0d0427a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd1338d444aef4cb7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7486,7 +7486,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf769948b070a4b80"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R961f62463f854144"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19915,30 +19915,176 @@
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
+    <x:row r="265" ht="72" customHeight="1">
+      <x:c r="A265" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B265" s="4" t="str">
+        <x:v>TC-TM005-CORE-01</x:v>
+      </x:c>
+      <x:c r="C265" s="4" t="str">
+        <x:v>双来源可信事件与半开日汇总</x:v>
+      </x:c>
+      <x:c r="D265" s="4" t="str">
+        <x:v>TASK-TM005-EVENT-CONTRACT
+TASK-TM005-RANGE-QUERY</x:v>
+      </x:c>
+      <x:c r="E265" s="4" t="str">
+        <x:v>source_check</x:v>
+      </x:c>
+      <x:c r="F265" s="4" t="str">
+        <x:v>fixture的A/B、跨主体C、界外D/E；synthetic-p1、Asia/Shanghai当地日2026-09-29</x:v>
+      </x:c>
+      <x:c r="G265" s="4" t="str">
+        <x:v>1. 按固定主体/当地日查询纯统计函数；仅A/B被选、C/D/E排除；输入数组和键不变
+2. 核对来源、模型、Token和三个子项；input300/output30/total330；Codex110/Claude220；未知模型110/sonnet-test220；缓存读20但部分未知、缓存写未知、推理2但部分未知，子项不加总
+3. 逐个输入非法来源、负数、超范围缓存和坏UTC；各自被拒绝，无完整零或有效汇总输出；原fixture不变</x:v>
+      </x:c>
+      <x:c r="H265" s="4" t="str">
+        <x:v>准备：无产品DB写入；每例从新内存输入开始
+变化：不适用；纯统计返回值与输入未变
+核验：固定fixture摘要、事件筛选、各字段与状态逐步核对；无SQL</x:v>
+      </x:c>
+      <x:c r="I265" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J265" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K265" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L265" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:326</x:v>
+      </x:c>
+      <x:c r="M265" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N265" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="266" ht="57" customHeight="1">
+      <x:c r="A266" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B266" s="9" t="str">
+        <x:v>TC-TM005-CORE-02</x:v>
+      </x:c>
+      <x:c r="C266" s="9" t="str">
+        <x:v>未知用量诊断不补零</x:v>
+      </x:c>
+      <x:c r="D266" s="9" t="str">
+        <x:v>TASK-TM005-EVENT-CONTRACT
+TASK-TM005-COVERAGE</x:v>
+      </x:c>
+      <x:c r="E266" s="9" t="str">
+        <x:v>source_check</x:v>
+      </x:c>
+      <x:c r="F266" s="9" t="str">
+        <x:v>fixture A/B及同范围Claude missing_usage诊断；双来源complete仅为模块合成覆盖假设</x:v>
+      </x:c>
+      <x:c r="G266" s="9" t="str">
+        <x:v>1. 先仅统计A/B；已知330，未知模型110保留，来源Codex110/Claude220
+2. 加入诊断重新统计；partial、known_tokens330、total_tokens=null；诊断不增调用或零Token
+3. 移除A/B仅保留诊断；unknown、known_tokens0、total_tokens=null，不能写已确认零</x:v>
+      </x:c>
+      <x:c r="H266" s="9" t="str">
+        <x:v>准备：无产品DB写入；每例从新内存输入开始
+变化：不适用；纯统计返回值与输入未变
+核验：固定fixture摘要、事件筛选、各字段与状态逐步核对；无SQL</x:v>
+      </x:c>
+      <x:c r="I266" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J266" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K266" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L266" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:334</x:v>
+      </x:c>
+      <x:c r="M266" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N266" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="267" ht="87" customHeight="1">
+      <x:c r="A267" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B267" s="4" t="str">
+        <x:v>TC-TM005-CORE-03</x:v>
+      </x:c>
+      <x:c r="C267" s="4" t="str">
+        <x:v>声明式覆盖状态代数</x:v>
+      </x:c>
+      <x:c r="D267" s="4" t="str">
+        <x:v>TASK-TM005-COVERAGE</x:v>
+      </x:c>
+      <x:c r="E267" s="4" t="str">
+        <x:v>source_check</x:v>
+      </x:c>
+      <x:c r="F267" s="4" t="str">
+        <x:v>fixture五行coverage_algebra；complete仅为模块合成输入，product_coverage_proven=false</x:v>
+      </x:c>
+      <x:c r="G267" s="4" t="str">
+        <x:v>1. 两来源complete且无事件、随后移除覆盖事实；前者complete/known0/total0；后者不得自行推断complete
+2. 一来源missing，分别给空事件与可信110；空事件missing/known0/total null；可信110为partial/known110/total null
+3. 两来源complete，分别给可信110+未知诊断、仅未知诊断；前者partial/known110/total null；后者unknown/known0/total null</x:v>
+      </x:c>
+      <x:c r="H267" s="4" t="str">
+        <x:v>准备：无产品DB写入；每例从新内存输入开始
+变化：不适用；纯统计返回值与输入未变
+核验：固定fixture摘要、事件筛选、各字段与状态逐步核对；无SQL</x:v>
+      </x:c>
+      <x:c r="I267" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J267" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K267" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L267" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:342</x:v>
+      </x:c>
+      <x:c r="M267" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N267" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G5:G264">
+  <x:conditionalFormatting sqref="G5:G267">
     <x:cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="I5:I264">
+  <x:conditionalFormatting sqref="I5:I267">
     <x:cfRule type="containsText" dxfId="15" priority="4" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="17" priority="6" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="J5:J264">
+  <x:conditionalFormatting sqref="J5:J267">
     <x:cfRule type="containsText" dxfId="18" priority="7" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="19" priority="8" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="20" priority="9" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="M5:M264">
+  <x:conditionalFormatting sqref="M5:M267">
     <x:cfRule type="containsText" dxfId="21" priority="10" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="22" priority="11" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="23" priority="12" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R912ecfc95f1a4378"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73e815c9d86a4064"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20511,7 +20657,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d8dfb9ad96d493c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d75d2e9f55f4cfc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20798,7 +20944,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J8" s="9" t="str">
-        <x:v>整版draft、未发布。原27条目标TC保留，新增3条无授权CORE辅助TC在恢复新仓库候选7d77d63按SOP-008独立切片判为development_slice_ready；固定程序绑定与实际运行仍缺，30条TM003目标/辅助TC均未获得产品PASS。授权/真实App/服务/Keychain及产品E2E仍BLOCKED，0.3整版baseline和正式发行完整门禁NOT_RUN。</x:v>
+        <x:v>整版draft、未发布。27条产品TC未执行；3条CORE辅助TC已在文档提交48ca089独立切片就绪，在开发分支311deedf运行模块3/3 PASS，原始receipt在该分支.local/ci/tm003-core-20261001/。代码尚未合入本文档树，机器绑定保持空；模块报告不能作为产品E2E或发行门禁，结果Excel规范待SOP修订。</x:v>
       </x:c>
       <x:c r="K8" s="9" t="str">
         <x:v>TM-001 干净源码候选为技术基底；其产品门禁不继承给TM-003</x:v>
@@ -20813,7 +20959,7 @@
         <x:v>未核实同名功能分支SHA/tree读回</x:v>
       </x:c>
       <x:c r="O8" s="9" t="str">
-        <x:v>产品E2E未执行；本机稳定包未归档</x:v>
+        <x:v>CORE模块3/3只在独立开发分支PASS；真实安装App产品E2E未运行；本机稳定包未归档</x:v>
       </x:c>
       <x:c r="P8" s="9" t="str">
         <x:v>本轮五版稳定后一次受保护PR；待办</x:v>
@@ -20881,7 +21027,7 @@
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="102" customHeight="1">
+    <x:row r="10" ht="117" customHeight="1">
       <x:c r="A10" s="9" t="str">
         <x:v>v0.5.0-20261001T034729Z</x:v>
       </x:c>
@@ -20910,7 +21056,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J10" s="9" t="str">
-        <x:v>整版draft、未发布。6 TASK、32父TC、6稳定变体及两组摘要已登记；纯统计语义oracle仅可验证算术/覆盖合同，不证明双来源真实采集。固定产品数据、SQLite/IPC、安装App逐TC绑定未完成；正式发行完整门禁NOT_RUN。</x:v>
+        <x:v>整版draft、未发布。原32条产品父TC、6稳定变体和两组摘要保留；新增3条纯统计CORE辅助TC，合成fixture与逐步预期已冻结，切片核对尚在进行。静态oracle不证明真实双来源采集或产品E2E；固定产品数据、SQLite/IPC、安装App逐TC绑定未完成，正式发行完整门禁NOT_RUN。</x:v>
       </x:c>
       <x:c r="K10" s="9" t="str">
         <x:v>TM005语义oracle只验证规范化样例；0.4及此前稳定原包尚未形成，真实升级BLOCKED。</x:v>
@@ -20955,7 +21101,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc08e1a26493946c2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7977dad8fd6645e6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22120,7 +22266,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra38b2a0da86e45e9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf611e281df2443f1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TokenMeter项目总表.xlsx
+++ b/TokenMeter项目总表.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R49697d2c441d464b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="R5d12880f2ce24702"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R60e45e41e1234871"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="Rf8797fb3cdf7496a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R82b1eb0351634d5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R95cfb4f1d6ac42bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="Rabfd9323da1c4b9e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R1d58ab70850b4c19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Rdd0b166202e346e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="Rd589207889cc4343"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="Rd07e33eea4e84bed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="Ra34cb97649fe4064"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Ra70c794b2e164466"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="Rfb3048600da248a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R7e5a4ada29ae4937"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="Re2b75bfe9fed4bc0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="Rb81226098b1e4536"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="Re24460cc44ea476b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R18122656c3bd40c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="R93ce1a3f21084943"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="Rbacb2c3887dc4b14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R363d3736582d4f08"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1255,7 +1255,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa21f6bd2e694056"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e400cb931d046ee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1963,7 +1963,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc2f0e39e73241d3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re66a8b0da047414e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2112,7 +2112,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17a35b4f5f0d417e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref49158206c0495c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2547,7 +2547,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R961caa3c423e4d07"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b318a29ab9c4d3d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3594,7 +3594,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93b416a951454bb2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37d2691052f64f9a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4701,7 +4701,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd1338d444aef4cb7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ff245d7da434fbd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7486,7 +7486,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R961f62463f854144"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd75cc4e2fd4745e8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20084,7 +20084,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73e815c9d86a4064"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8f0538f57bf4f6c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20657,7 +20657,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d75d2e9f55f4cfc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55c211e1a3b04821"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21027,7 +21027,7 @@
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="117" customHeight="1">
+    <x:row r="10" ht="162" customHeight="1">
       <x:c r="A10" s="9" t="str">
         <x:v>v0.5.0-20261001T034729Z</x:v>
       </x:c>
@@ -21056,7 +21056,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J10" s="9" t="str">
-        <x:v>整版draft、未发布。原32条产品父TC、6稳定变体和两组摘要保留；新增3条纯统计CORE辅助TC，合成fixture与逐步预期已冻结，切片核对尚在进行。静态oracle不证明真实双来源采集或产品E2E；固定产品数据、SQLite/IPC、安装App逐TC绑定未完成，正式发行完整门禁NOT_RUN。</x:v>
+        <x:v>整版draft、未发布。原32条产品父TC、6稳定变体和两组摘要保留；纯统计CORE-01/02/03辅助TC在输入提交061c759后，经SOP-008内容核对及结构/治理457项PASS，独立切片development_slice_ready，程序绑定仍为空、模块实际运行unexecuted。静态oracle与切片就绪不证明真实双来源采集或产品E2E；固定产品数据、SQLite/IPC、安装App逐TC绑定未完成，正式发行完整门禁NOT_RUN。</x:v>
       </x:c>
       <x:c r="K10" s="9" t="str">
         <x:v>TM005语义oracle只验证规范化样例；0.4及此前稳定原包尚未形成，真实升级BLOCKED。</x:v>
@@ -21101,7 +21101,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7977dad8fd6645e6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra17d60bf792243b7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22266,7 +22266,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf611e281df2443f1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R110a0b1237ef4333"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TokenMeter项目总表.xlsx
+++ b/TokenMeter项目总表.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="Ra34cb97649fe4064"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Ra70c794b2e164466"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="Rfb3048600da248a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R7e5a4ada29ae4937"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="Re2b75bfe9fed4bc0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="Rb81226098b1e4536"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="Re24460cc44ea476b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R18122656c3bd40c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="R93ce1a3f21084943"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="Rbacb2c3887dc4b14"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R363d3736582d4f08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R37ace6a3945f47b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Rceed6940fe764674"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R84b4961f62504997"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R6a82d18c33fc49e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R7bc52af645e44234"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R6c9210257dd648a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R9f2c216a24f34eba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="Rd412b793cfec432a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="R5eba53e2586c47e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R539ced6782444afc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="Rc0c3595293ea42bc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -755,8 +755,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TMTable6" displayName="TMTable6" ref="A4:N267" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:N267"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TMTable6" displayName="TMTable6" ref="A4:N270" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:N270"/>
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="功能编号"/>
     <x:tableColumn id="2" name="用例编号"/>
@@ -1101,8 +1101,8 @@
         <x:v>已登记用例</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:f>COUNTA('05测试用例'!B5:B267)</x:f>
-        <x:v>263</x:v>
+        <x:f>COUNTA('05测试用例'!B5:B270)</x:f>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="C8" s="9" t="str">
         <x:v>父用例与具有稳定 ID 的变体各占一行；含未来概要场景</x:v>
@@ -1125,7 +1125,7 @@
         <x:v>细化产品用例</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>193</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="C10" s="9" t="str">
         <x:v>逐条结果按运行批次记录；稳定变体独立列出</x:v>
@@ -1255,7 +1255,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e400cb931d046ee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc08057c18b414774"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1963,7 +1963,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re66a8b0da047414e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7630e691777f4a17"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2112,7 +2112,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref49158206c0495c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R595d16cdd3e04f9f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2547,7 +2547,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b318a29ab9c4d3d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9b039b9e42a452e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3594,7 +3594,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37d2691052f64f9a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc7e50be55244892"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4701,7 +4701,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ff245d7da434fbd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9144ed7a373426b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7486,7 +7486,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd75cc4e2fd4745e8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76db2900f6da4213"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15735,7 +15735,7 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L176" s="9" t="str">
-        <x:v>docs/testing/cases/05-TM-005-usage-statistics.md:19</x:v>
+        <x:v>docs/testing/cases/05-TM-005-usage-statistics.md:21</x:v>
       </x:c>
       <x:c r="M176" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -15781,7 +15781,7 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L177" s="4" t="str">
-        <x:v>docs/testing/cases/05-TM-005-usage-statistics.md:36</x:v>
+        <x:v>docs/testing/cases/05-TM-005-usage-statistics.md:38</x:v>
       </x:c>
       <x:c r="M177" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -20061,30 +20061,175 @@
         <x:v>v0.5.0-20261001T034729Z</x:v>
       </x:c>
     </x:row>
+    <x:row r="268" ht="72" customHeight="1">
+      <x:c r="A268" s="9" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="B268" s="9" t="str">
+        <x:v>TC-TM004-CORE-01</x:v>
+      </x:c>
+      <x:c r="C268" s="9" t="str">
+        <x:v>完整LF、半行与限额续读</x:v>
+      </x:c>
+      <x:c r="D268" s="9" t="str">
+        <x:v>TASK-TM004-INCREMENTAL</x:v>
+      </x:c>
+      <x:c r="E268" s="9" t="str">
+        <x:v>source_check</x:v>
+      </x:c>
+      <x:c r="F268" s="9" t="str">
+        <x:v>固定746字节13/7 assistant行、前半字节、两条不同ID完整行、首读上限754字节</x:v>
+      </x:c>
+      <x:c r="G268" s="9" t="str">
+        <x:v>1. 读未写完的前半行；调用0、偏移0、scanIncomplete=true，不作可信零结论
+2. 补齐LF、重复读取；补齐后一次13/7=20、偏移746、前缀MAC匹配；重复读取0调用且游标不变
+3. 两完整行首读754字节后续读；首读只第一条、偏移746、read_limit且未完成；续读只第二条、偏移为总字节长、完成</x:v>
+      </x:c>
+      <x:c r="H268" s="9" t="str">
+        <x:v>准备：无产品DB；每例新建自有临时文件
+变化：不适用；只返回模块调用、诊断与游标
+核验：固定fixture/行摘要和逐步返回值、前缀MAC及失败时无新游标；无SQL</x:v>
+      </x:c>
+      <x:c r="I268" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J268" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K268" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L268" s="9" t="str">
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:170</x:v>
+      </x:c>
+      <x:c r="M268" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N268" s="9" t="str">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="269" ht="72" customHeight="1">
+      <x:c r="A269" s="4" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="B269" s="4" t="str">
+        <x:v>TC-TM004-CORE-02</x:v>
+      </x:c>
+      <x:c r="C269" s="4" t="str">
+        <x:v>前缀MAC、变更和密钥失败</x:v>
+      </x:c>
+      <x:c r="D269" s="4" t="str">
+        <x:v>TASK-TM004-INCREMENTAL</x:v>
+      </x:c>
+      <x:c r="E269" s="4" t="str">
+        <x:v>source_check</x:v>
+      </x:c>
+      <x:c r="F269" s="4" t="str">
+        <x:v>已提交首行，追加不同ID第二行、同长度ID改写并复原mtime、截短、身份改变、秘密缺失或错误</x:v>
+      </x:c>
+      <x:c r="G269" s="4" t="str">
+        <x:v>1. 首行后追加第二完整行；快照digest变化但稳定身份/前缀MAC相同，续读只第二调用，无cursor_reset
+2. 同长度前缀改写、截短及稳定身份变更；分别报cursor_reset并从0重扫；同inode/size/mtime也不能忽略MAC不符
+3. 秘密无效或读中源变化；拒绝且没有可提交新游标/可信调用/成功零；输出不含路径正文秘密</x:v>
+      </x:c>
+      <x:c r="H269" s="4" t="str">
+        <x:v>准备：无产品DB；每例新建自有临时文件
+变化：不适用；只返回模块调用、诊断与游标
+核验：固定fixture/行摘要和逐步返回值、前缀MAC及失败时无新游标；无SQL</x:v>
+      </x:c>
+      <x:c r="I269" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J269" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K269" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L269" s="4" t="str">
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:178</x:v>
+      </x:c>
+      <x:c r="M269" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N269" s="4" t="str">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="270" ht="57" customHeight="1">
+      <x:c r="A270" s="9" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="B270" s="9" t="str">
+        <x:v>TC-TM004-CORE-03</x:v>
+      </x:c>
+      <x:c r="C270" s="9" t="str">
+        <x:v>损坏完整行与未知结构</x:v>
+      </x:c>
+      <x:c r="D270" s="9" t="str">
+        <x:v>TASK-TM004-PARSER
+TASK-TM004-INCREMENTAL</x:v>
+      </x:c>
+      <x:c r="E270" s="9" t="str">
+        <x:v>source_check</x:v>
+      </x:c>
+      <x:c r="F270" s="9" t="str">
+        <x:v>固定13/7行前置非法UTF8完整行和版本2.1.127完整行，尾部再追加无LF坏字节</x:v>
+      </x:c>
+      <x:c r="G270" s="9" t="str">
+        <x:v>1. 读三条完整LF行；仅合法2.1.126一条调用13/7=20；invalid_utf8及unsupported_version各一次
+2. 核对游标、重复读取及隐私；游标到三行LF末，MAC匹配且完成；重复读取0；输出无路径、正文、秘密
+3. 追加无LF坏字节再补LF；未补LF前偏移不动且未完成；补LF后仅诊断推进，无伪调用</x:v>
+      </x:c>
+      <x:c r="H270" s="9" t="str">
+        <x:v>准备：无产品DB；每例新建自有临时文件
+变化：不适用；只返回模块调用、诊断与游标
+核验：固定fixture/行摘要和逐步返回值、前缀MAC及失败时无新游标；无SQL</x:v>
+      </x:c>
+      <x:c r="I270" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J270" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K270" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L270" s="9" t="str">
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:186</x:v>
+      </x:c>
+      <x:c r="M270" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N270" s="9" t="str">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G5:G267">
+  <x:conditionalFormatting sqref="G5:G270">
     <x:cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="I5:I267">
+  <x:conditionalFormatting sqref="I5:I270">
     <x:cfRule type="containsText" dxfId="15" priority="4" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="17" priority="6" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="J5:J267">
+  <x:conditionalFormatting sqref="J5:J270">
     <x:cfRule type="containsText" dxfId="18" priority="7" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="19" priority="8" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="20" priority="9" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="M5:M267">
+  <x:conditionalFormatting sqref="M5:M270">
     <x:cfRule type="containsText" dxfId="21" priority="10" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="22" priority="11" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="23" priority="12" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8f0538f57bf4f6c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf20fbd45b564c07"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20657,7 +20802,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55c211e1a3b04821"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad61b66a93d64781"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21000,7 +21145,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J9" s="4" t="str">
-        <x:v>整版draft、未发布。8 TASK、20细TC及四组摘要已登记；纯内存Claude 2.1.126解析器f2c3972覆盖已验证主会话、复制fork、同ID双块及可核实单层Agent，单元36/36、治理452/452PASS。改写UUID、fork-context-ref、嵌套Agent、有效零及授权/身份/SQLite仍缺证据或集成；20条产品TC未执行，正式发行完整门禁NOT_RUN。</x:v>
+        <x:v>整版draft、未发布。原20产品细TC及四组摘要保留，新增3条已打开只读句柄的reader CORE辅助TC，固定LF、前缀MAC/重扫和损坏行输入，切片检查未完成。开发树模块红0/3与绿3/3仅是交接证据，且代码未形成干净提交；产品授权、稳定文件身份、SQLite原子事务、IPC/App E2E未验证，正式发行门禁NOT_RUN。</x:v>
       </x:c>
       <x:c r="K9" s="4" t="str">
         <x:v>TM004源分支原生零/缺失与nested Agent定向探针仅为研究证据；0.3及此前稳定原包尚未形成，真实升级BLOCKED。</x:v>
@@ -21101,7 +21246,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra17d60bf792243b7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c2f4c5085bc46f9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22266,7 +22411,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R110a0b1237ef4333"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73a7e994b1c249cd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TokenMeter项目总表.xlsx
+++ b/TokenMeter项目总表.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R37ace6a3945f47b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Rceed6940fe764674"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R84b4961f62504997"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R6a82d18c33fc49e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R7bc52af645e44234"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R6c9210257dd648a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R9f2c216a24f34eba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="Rd412b793cfec432a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="R5eba53e2586c47e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R539ced6782444afc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="Rc0c3595293ea42bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="Ra6f210bcb0454295"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="R79f1b1bb8c7d4c88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R169ebc8165914139"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="Rcdd98965e7164734"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R670eb371060f4511"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R216314e6083e425e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R50b9ebef16624a75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R8ac6150839b04d13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Rbb98a582fe514638"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R50d19ea48f5644bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R64aaf28c83be4b22"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1255,7 +1255,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc08057c18b414774"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re175f6a10d684b84"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1611,7 +1611,7 @@
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G16" s="9" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H16" s="9" t="str">
         <x:v>sop/SOP-011-test-implementation.md</x:v>
@@ -1657,13 +1657,13 @@
         <x:v>012实现、009本机运行时和锁文件就绪。</x:v>
       </x:c>
       <x:c r="E18" s="9" t="str">
-        <x:v>构建物和基础原始结果或精确缺项。</x:v>
+        <x:v>构建物、基础及固定模块TC原始结果、独立批次Excel和导出收据，或精确缺项。</x:v>
       </x:c>
       <x:c r="F18" s="9" t="str">
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G18" s="9" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H18" s="9" t="str">
         <x:v>sop/SOP-013-build-and-check.md</x:v>
@@ -1689,7 +1689,7 @@
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G19" s="4" t="n">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="H19" s="4" t="str">
         <x:v>sop/SOP-014-e2e.md</x:v>
@@ -1949,7 +1949,7 @@
         <x:v>已基线</x:v>
       </x:c>
       <x:c r="G29" s="4" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H29" s="4" t="str">
         <x:v>sop/SOP-024-document-change.md</x:v>
@@ -1963,7 +1963,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7630e691777f4a17"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01d20f25691a4d3c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2112,7 +2112,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R595d16cdd3e04f9f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d4100c370ca43ef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2547,7 +2547,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9b039b9e42a452e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58ce105b0ad34683"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3594,7 +3594,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc7e50be55244892"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcea4c46319904a25"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4701,7 +4701,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9144ed7a373426b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57f6c1e9dfc540fa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7486,7 +7486,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76db2900f6da4213"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R865e9e7bfd724203"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20229,7 +20229,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf20fbd45b564c07"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rafe0914c2e5f4e3d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20802,7 +20802,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad61b66a93d64781"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a1d865dd2024f4f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21060,7 +21060,7 @@
         <x:v>releases/v0.2.0-20261001T034118Z/01-requirements.md:32</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="132" customHeight="1">
+    <x:row r="8" ht="192" customHeight="1">
       <x:c r="A8" s="9" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
@@ -21089,7 +21089,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J8" s="9" t="str">
-        <x:v>整版draft、未发布。27条产品TC未执行；3条CORE辅助TC已在文档提交48ca089独立切片就绪，在开发分支311deedf运行模块3/3 PASS，原始receipt在该分支.local/ci/tm003-core-20261001/。代码尚未合入本文档树，机器绑定保持空；模块报告不能作为产品E2E或发行门禁，结果Excel规范待SOP修订。</x:v>
+        <x:v>整版draft、未发布。27条产品TC未执行；3条CORE辅助TC已在文档提交48ca089独立切片就绪，在开发分支311deedf运行模块3/3 PASS，原始receipt在该分支.local/ci/tm003-core-20261001/。代码尚未合入本文档树，机器绑定保持空；模块报告不能作为产品E2E或发行门禁，结果Excel规范待SOP修订。 2026-10-02新代码候选44379e6已有逐步模块3/3与桌面29/29/typecheck/build原件；source_check独立Excel导出程序仍缺，批次登记BLOCKED，产品E2E仍NOT_RUN。</x:v>
       </x:c>
       <x:c r="K8" s="9" t="str">
         <x:v>TM-001 干净源码候选为技术基底；其产品门禁不继承给TM-003</x:v>
@@ -21172,7 +21172,7 @@
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="162" customHeight="1">
+    <x:row r="10" ht="237" customHeight="1">
       <x:c r="A10" s="9" t="str">
         <x:v>v0.5.0-20261001T034729Z</x:v>
       </x:c>
@@ -21201,7 +21201,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J10" s="9" t="str">
-        <x:v>整版draft、未发布。原32条产品父TC、6稳定变体和两组摘要保留；纯统计CORE-01/02/03辅助TC在输入提交061c759后，经SOP-008内容核对及结构/治理457项PASS，独立切片development_slice_ready，程序绑定仍为空、模块实际运行unexecuted。静态oracle与切片就绪不证明真实双来源采集或产品E2E；固定产品数据、SQLite/IPC、安装App逐TC绑定未完成，正式发行完整门禁NOT_RUN。</x:v>
+        <x:v>整版draft、未发布。原32条产品父TC、6稳定变体和两组摘要保留；纯统计CORE-01/02/03辅助TC在输入提交061c759后，经SOP-008内容核对及结构/治理457项PASS，独立切片development_slice_ready，程序绑定仍为空、模块实际运行unexecuted。静态oracle与切片就绪不证明真实双来源采集或产品E2E；固定产品数据、SQLite/IPC、安装App逐TC绑定未完成，正式发行完整门禁NOT_RUN。 独立代码提交6a0f6f的source_check CORE3/3、桌面29/29、build PASS，原件在TM005工作树.local/tm005-core-postcommit-20261001T162401Z；程序尚未进入本文档树、模块Excel导出/批次登记BLOCKED，产品E2E仍NOT_RUN。</x:v>
       </x:c>
       <x:c r="K10" s="9" t="str">
         <x:v>TM005语义oracle只验证规范化样例；0.4及此前稳定原包尚未形成，真实升级BLOCKED。</x:v>
@@ -21246,7 +21246,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c2f4c5085bc46f9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raad3cfddeeb34401"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22411,7 +22411,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73a7e994b1c249cd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31d38ae98c06435d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TokenMeter项目总表.xlsx
+++ b/TokenMeter项目总表.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="Ra6f210bcb0454295"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="R79f1b1bb8c7d4c88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R169ebc8165914139"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="Rcdd98965e7164734"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R670eb371060f4511"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R216314e6083e425e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R50b9ebef16624a75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R8ac6150839b04d13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Rbb98a582fe514638"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R50d19ea48f5644bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R64aaf28c83be4b22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="Rbf12aa18b3554001"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="R0df86ad125c847cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="Rb1d655ac537243bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R02ea4983c9c44775"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="Rcf6a862be63b4235"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R2503d345bbf645c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="Rb9fac209113c41ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R929989622c2e47b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Rabd4aa5c6f0f4350"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R63d60e02ad764d31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R79b31b47b30a4cc3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -152,7 +152,38 @@
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="45">
+  <x:dxfs count="48">
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9A201B"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFDE8E7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF754E00"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF2CD"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF754E00"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF6DF"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
     <x:dxf>
       <x:font>
         <x:b/>
@@ -778,21 +809,23 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TMTable7" displayName="TMTable7" ref="A4:L17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:L17"/>
-  <x:tableColumns count="12">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TMTable7" displayName="TMTable7" ref="A4:N19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:N19"/>
+  <x:tableColumns count="14">
     <x:tableColumn id="1" name="运行批次"/>
     <x:tableColumn id="2" name="版本"/>
-    <x:tableColumn id="3" name="范围"/>
-    <x:tableColumn id="4" name="结果"/>
-    <x:tableColumn id="5" name="父用例/场景数"/>
-    <x:tableColumn id="6" name="通过数"/>
-    <x:tableColumn id="7" name="失败数"/>
-    <x:tableColumn id="8" name="阻塞数"/>
-    <x:tableColumn id="9" name="候选提交"/>
-    <x:tableColumn id="10" name="发布资格"/>
-    <x:tableColumn id="11" name="批次摘要"/>
-    <x:tableColumn id="12" name="独立结果Excel（本机）"/>
+    <x:tableColumn id="3" name="执行类型"/>
+    <x:tableColumn id="4" name="范围"/>
+    <x:tableColumn id="5" name="结果"/>
+    <x:tableColumn id="6" name="父用例/场景数"/>
+    <x:tableColumn id="7" name="通过数"/>
+    <x:tableColumn id="8" name="失败数"/>
+    <x:tableColumn id="9" name="阻塞数"/>
+    <x:tableColumn id="10" name="候选提交"/>
+    <x:tableColumn id="11" name="发布资格"/>
+    <x:tableColumn id="12" name="批次摘要"/>
+    <x:tableColumn id="13" name="独立结果Excel（本机）"/>
+    <x:tableColumn id="14" name="产品E2E状态"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -1113,8 +1146,8 @@
         <x:v>测试批次</x:v>
       </x:c>
       <x:c r="B9" s="10" t="n">
-        <x:f>COUNTA('06测试批次'!A5:A17)</x:f>
-        <x:v>13</x:v>
+        <x:f>COUNTA('06测试批次'!A5:A19)</x:f>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C9" s="4" t="str">
         <x:v>06测试批次，每次运行一行，记录独立结果Excel位置</x:v>
@@ -1125,7 +1158,7 @@
         <x:v>细化产品用例</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>196</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C10" s="9" t="str">
         <x:v>逐条结果按运行批次记录；稳定变体独立列出</x:v>
@@ -1136,7 +1169,7 @@
         <x:v>界面与治理检查</x:v>
       </x:c>
       <x:c r="B11" s="10" t="n">
-        <x:v>41</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C11" s="4" t="str">
         <x:v>辅助检查不能替代产品E2E；稳定变体独立列出</x:v>
@@ -1235,10 +1268,10 @@
         <x:v>最近登记批次</x:v>
       </x:c>
       <x:c r="B20" s="9" t="str">
-        <x:v>FAIL</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="C20" s="9" t="str">
-        <x:v>本地master固定候选最终包首次精细门禁：固定本地master候选门禁FAIL；原始116项91 PASS/14 FAIL/11 BLOCKED，UPDATE-05父项与13变体缺签名输入。逐例模型78父TC 66 PASS/1 FAIL/11 BLOCKED，38变体25 PASS/13 FAIL；无正式稳定包。；是否覆盖完整回归以批次范围和原始证据为准。</x:v>
+        <x:v>source_check · TM-003 CORE-01/02/03 固定模块验证；非产品E2E：共享source_check清理合同扩展后的新候选：CORE固定3/3、九步PASS，owned_root清理逐例PASS；独立Excel/verification回读PASS。旧ea6b187批次保留；原27条产品TC与正式发行仍NOT_RUN。；是否覆盖完整产品回归以批次范围和原始证据为准。</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="32" customHeight="1">
@@ -1255,7 +1288,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re175f6a10d684b84"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25d759ba0397462f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1957,13 +1990,13 @@
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="F5:F29">
-    <x:cfRule type="containsText" dxfId="42" priority="1" operator="containsText" text="FAIL"/>
-    <x:cfRule type="containsText" dxfId="43" priority="2" operator="containsText" text="预期待明确"/>
-    <x:cfRule type="containsText" dxfId="44" priority="3" operator="containsText" text="未执行"/>
+    <x:cfRule type="containsText" dxfId="45" priority="1" operator="containsText" text="FAIL"/>
+    <x:cfRule type="containsText" dxfId="46" priority="2" operator="containsText" text="预期待明确"/>
+    <x:cfRule type="containsText" dxfId="47" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01d20f25691a4d3c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R569059b8ca0b4736"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2112,7 +2145,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d4100c370ca43ef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6025bfdd02894eb7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2547,7 +2580,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58ce105b0ad34683"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf28121b6afbb43f9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3594,7 +3627,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcea4c46319904a25"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9e3695a17444599"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4701,7 +4734,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57f6c1e9dfc540fa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89bf59096c52401f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7486,7 +7519,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R865e9e7bfd724203"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf24b92a7a9c4ba9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13395,15 +13428,13 @@
         <x:v>安全单元</x:v>
       </x:c>
       <x:c r="F127" s="4" t="str">
-        <x:v>七个独立变体：四个恶意 IPC 参数分别为 B 绝对路径、B 的 file:// URL、../B/sessions/2026/10/01/b-01.jsonl、伪造 selectionId 00000000-0000-4000-8000-000000000099；三个受控竞态为过期选择、撤销期间刷新、切换账号期间刷新。全部只用自有 A/B 与同一主进程业务代码。</x:v>
+        <x:v>七个独立变体：B路径攻击使用独占短根R=/tmp/t2-&lt;8位十六进制&gt;、R/A/a.jsonl与R/B/b.jsonl；ABSOLUTE/FILE_URL/DOTDOT分别调用tokenmeter:invoke(previewSource,{selectionId:B绝对路径/file URL/../B/b.jsonl})，TOKEN调用同method并传未签发UUID；三竞态保持原输入。路径字串事前断言≤64，仅本例拥有A/B。</x:v>
       </x:c>
       <x:c r="G127" s="4" t="str">
-        <x:v>测试 UI 不适用，原因是本例为主进程参数安全层；A/B 文件未被读取，无网络/DB 操作。
-主进程返回安全错误码，不返回内容、绝对路径或 locator；不存在 renderer 任意文件读取 API，A/B open/read=0、B 元数据访问=0；无网络/DB 操作。
-四个恶意参数变体均未确认来源、未修改 A/B 字节；分别保存脱敏错误码和文件审计，不记录路径或 token；无网络/DB 操作。</x:v>
+        <x:v>ABSOLUTE/FILE_URL/DOTDOT/TOKEN均调用previewSource.selectionId，返回snapshot.error=invalid_selection且不打开A/B、无来源状态变化；竞态变体沿既定屏障判据。</x:v>
       </x:c>
       <x:c r="H127" s="4" t="str">
-        <x:v>准备：七变体各自 R 与独立 A/B/profile；仅内存主进程 handler、受控异步屏障和隔离文件；无服务/DB，SQL 不适用。四恶意参数安全拒绝，三竞态过期结果不提交。
+        <x:v>准备：七变体各自短根R=/tmp/t2-&lt;8位十六进制&gt;、A/B/profile及owner marker；恶意字串≤64，实际业务previewSource IPC、受控异步屏障和隔离文件；无服务/DB，SQL不适用。
 变化：不适用：辅助检查不写服务业务库。
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
@@ -13443,13 +13474,13 @@
         <x:v>安全单元</x:v>
       </x:c>
       <x:c r="F128" s="9" t="str">
-        <x:v>renderer传B绝对路径</x:v>
+        <x:v>tokenmeter:invoke('previewSource',{selectionId:R+'/B/b.jsonl'})；R=/tmp/t2-&lt;8位十六进制&gt;独占短根，输入≤64字符</x:v>
       </x:c>
       <x:c r="G128" s="9" t="str">
-        <x:v>主进程安全拒绝，不返回内容、绝对路径或 locator；B 元数据/open/read=0，sources 无确认记录。</x:v>
+        <x:v>snapshot.error=invalid_selection；无pending/confirmed变化，不返回路径/locator/正文；A/B open/read=0、B metadata=0</x:v>
       </x:c>
       <x:c r="H128" s="9" t="str">
-        <x:v>准备：七变体各自 R 与独立 A/B/profile；仅内存主进程 handler、受控异步屏障和隔离文件；无服务/DB，SQL 不适用。四恶意参数安全拒绝，三竞态过期结果不提交。
+        <x:v>准备：七变体各自短根R=/tmp/t2-&lt;8位十六进制&gt;、A/B/profile及owner marker；恶意字串≤64，实际业务previewSource IPC、受控异步屏障和隔离文件；无服务/DB，SQL不适用。
 变化：不适用：辅助检查不写服务业务库。
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
@@ -13489,13 +13520,13 @@
         <x:v>安全单元</x:v>
       </x:c>
       <x:c r="F129" s="4" t="str">
-        <x:v>renderer传指向B的file:// URL</x:v>
+        <x:v>tokenmeter:invoke('previewSource',{selectionId:pathToFileURL(R+'/B/b.jsonl').href})；R=/tmp/t2-&lt;8位十六进制&gt;独占短根，输入≤64字符</x:v>
       </x:c>
       <x:c r="G129" s="4" t="str">
-        <x:v>主进程安全拒绝，不返回内容、绝对路径或 locator；B 元数据/open/read=0，sources 无确认记录。</x:v>
+        <x:v>snapshot.error=invalid_selection；无pending/confirmed变化，不返回路径/locator/正文；A/B open/read=0、B metadata=0</x:v>
       </x:c>
       <x:c r="H129" s="4" t="str">
-        <x:v>准备：七变体各自 R 与独立 A/B/profile；仅内存主进程 handler、受控异步屏障和隔离文件；无服务/DB，SQL 不适用。四恶意参数安全拒绝，三竞态过期结果不提交。
+        <x:v>准备：七变体各自短根R=/tmp/t2-&lt;8位十六进制&gt;、A/B/profile及owner marker；恶意字串≤64，实际业务previewSource IPC、受控异步屏障和隔离文件；无服务/DB，SQL不适用。
 变化：不适用：辅助检查不写服务业务库。
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
@@ -13535,13 +13566,13 @@
         <x:v>安全单元</x:v>
       </x:c>
       <x:c r="F130" s="9" t="str">
-        <x:v>renderer传../B/sessions/2026/10/01/b-01.jsonl</x:v>
+        <x:v>tokenmeter:invoke('previewSource',{selectionId:'../B/b.jsonl'})；R=/tmp/t2-&lt;8位十六进制&gt;独占短根，输入≤64字符</x:v>
       </x:c>
       <x:c r="G130" s="9" t="str">
-        <x:v>主进程安全拒绝，不返回内容、绝对路径或 locator；B 元数据/open/read=0，sources 无确认记录。</x:v>
+        <x:v>snapshot.error=invalid_selection；无pending/confirmed变化，不返回路径/locator/正文；A/B open/read=0、B metadata=0</x:v>
       </x:c>
       <x:c r="H130" s="9" t="str">
-        <x:v>准备：七变体各自 R 与独立 A/B/profile；仅内存主进程 handler、受控异步屏障和隔离文件；无服务/DB，SQL 不适用。四恶意参数安全拒绝，三竞态过期结果不提交。
+        <x:v>准备：七变体各自短根R=/tmp/t2-&lt;8位十六进制&gt;、A/B/profile及owner marker；恶意字串≤64，实际业务previewSource IPC、受控异步屏障和隔离文件；无服务/DB，SQL不适用。
 变化：不适用：辅助检查不写服务业务库。
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
@@ -13587,7 +13618,7 @@
         <x:v>主进程安全拒绝，不返回内容、绝对路径或 locator；B 元数据/open/read=0，sources 无确认记录。</x:v>
       </x:c>
       <x:c r="H131" s="4" t="str">
-        <x:v>准备：七变体各自 R 与独立 A/B/profile；仅内存主进程 handler、受控异步屏障和隔离文件；无服务/DB，SQL 不适用。四恶意参数安全拒绝，三竞态过期结果不提交。
+        <x:v>准备：七变体各自短根R=/tmp/t2-&lt;8位十六进制&gt;、A/B/profile及owner marker；恶意字串≤64，实际业务previewSource IPC、受控异步屏障和隔离文件；无服务/DB，SQL不适用。
 变化：不适用：辅助检查不写服务业务库。
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
@@ -13633,7 +13664,7 @@
         <x:v>旧 Alice 结果拒绝，Bob 不得建暂选/确认 A；Alice/Bob 无新增来源，A/B 零读取。</x:v>
       </x:c>
       <x:c r="H132" s="9" t="str">
-        <x:v>准备：七变体各自 R 与独立 A/B/profile；仅内存主进程 handler、受控异步屏障和隔离文件；无服务/DB，SQL 不适用。四恶意参数安全拒绝，三竞态过期结果不提交。
+        <x:v>准备：七变体各自短根R=/tmp/t2-&lt;8位十六进制&gt;、A/B/profile及owner marker；恶意字串≤64，实际业务previewSource IPC、受控异步屏障和隔离文件；无服务/DB，SQL不适用。
 变化：不适用：辅助检查不写服务业务库。
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
@@ -13679,7 +13710,7 @@
         <x:v>撤销删密文和读取能力，旧 Promise 不提交候选或 complete=true；撤销后 A/B 后续操作为零。</x:v>
       </x:c>
       <x:c r="H133" s="4" t="str">
-        <x:v>准备：七变体各自 R 与独立 A/B/profile；仅内存主进程 handler、受控异步屏障和隔离文件；无服务/DB，SQL 不适用。四恶意参数安全拒绝，三竞态过期结果不提交。
+        <x:v>准备：七变体各自短根R=/tmp/t2-&lt;8位十六进制&gt;、A/B/profile及owner marker；恶意字串≤64，实际业务previewSource IPC、受控异步屏障和隔离文件；无服务/DB，SQL不适用。
 变化：不适用：辅助检查不写服务业务库。
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
@@ -13725,7 +13756,7 @@
         <x:v>Bob 不得见旧 Alice 候选或得到来源；切换后 A/B 后续零访问；Bob 请求 Alice 来源 ID 被拒绝。</x:v>
       </x:c>
       <x:c r="H134" s="9" t="str">
-        <x:v>准备：七变体各自 R 与独立 A/B/profile；仅内存主进程 handler、受控异步屏障和隔离文件；无服务/DB，SQL 不适用。四恶意参数安全拒绝，三竞态过期结果不提交。
+        <x:v>准备：七变体各自短根R=/tmp/t2-&lt;8位十六进制&gt;、A/B/profile及owner marker；恶意字串≤64，实际业务previewSource IPC、受控异步屏障和隔离文件；无服务/DB，SQL不适用。
 变化：不适用：辅助检查不写服务业务库。
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
@@ -18485,7 +18516,7 @@
         <x:v>TASK-TM003-SOURCE</x:v>
       </x:c>
       <x:c r="E235" s="4" t="str">
-        <x:v>source_check</x:v>
+        <x:v>模块检查</x:v>
       </x:c>
       <x:c r="F235" s="4" t="str">
         <x:v>1. 对照本版声明的 CLI build、官方结构与 sessions/YYYY/MM/DD/*.jsonl 受控原生样例→样例有 session_meta.id、token_usage_record.payload.response_id/usage，版本和 SHA 有记录。2. 换一个未声明 build→该 build 不列为已支持，显示 unsupported_source_version。</x:v>
@@ -18772,7 +18803,7 @@
         <x:v>TASK-TM003-SOURCE</x:v>
       </x:c>
       <x:c r="E241" s="4" t="str">
-        <x:v>source_check</x:v>
+        <x:v>模块检查</x:v>
       </x:c>
       <x:c r="F241" s="4" t="str">
         <x:v>1. 输入只有 event_msg.token_count.info.total_token_usage=100/10 且无 response_id→诊断 unverified_cumulative、可信事件0。2. 加 rate-limit-only 的 info=null→诊断 missing_usage，不生成0值用量事件。</x:v>
@@ -19012,7 +19043,7 @@
         <x:v>TASK-TM003-IDENTITY</x:v>
       </x:c>
       <x:c r="E246" s="9" t="str">
-        <x:v>source_check</x:v>
+        <x:v>模块检查</x:v>
       </x:c>
       <x:c r="F246" s="9" t="str">
         <x:v>本例私有 schema 与tests/fixtures/tm004/identity-v1-vectors.json 中的公开测试 HMAC key（仅固定向量，绝不进入产品 profile）；标准事件 Codex provider-response/shared-call-01=100/10/cached20，Claude provider-message/shared-call-01=30/3/cached0；随后同 Codex 事件重放、另一 Agent 无复制链同 Claude ID 重用、同 Codex ID 但用量或模型冲突。</x:v>
@@ -19784,7 +19815,7 @@
         <x:v>TASK-TM003-PARSE</x:v>
       </x:c>
       <x:c r="E262" s="9" t="str">
-        <x:v>source_check</x:v>
+        <x:v>模块检查</x:v>
       </x:c>
       <x:c r="F262" s="9" t="str">
         <x:v>原生形状完整A=100/10/cached20；B=200/20/cached40半行后补LF；C=300/30/cached60完整行及累计快照；固定种子和T0。</x:v>
@@ -19803,7 +19834,7 @@
         <x:v>draft</x:v>
       </x:c>
       <x:c r="J262" s="9" t="str">
-        <x:v>未执行</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="K262" s="9" t="str">
         <x:v>细化用例</x:v>
@@ -19812,7 +19843,7 @@
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:315</x:v>
       </x:c>
       <x:c r="M262" s="9" t="str">
-        <x:v>尚未执行</x:v>
+        <x:v>tm003-core-20261001T165439Z (source_check；产品E2E未运行)</x:v>
       </x:c>
       <x:c r="N262" s="9" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
@@ -19833,7 +19864,7 @@
 TASK-TM003-PARSE</x:v>
       </x:c>
       <x:c r="E263" s="4" t="str">
-        <x:v>source_check</x:v>
+        <x:v>模块检查</x:v>
       </x:c>
       <x:c r="F263" s="4" t="str">
         <x:v>无ID累计100/10和rate-limit info=null；合法A；缺usage、负input、cached111&gt;input100、total111四条不同ID完整LF行；未知build。</x:v>
@@ -19852,7 +19883,7 @@
         <x:v>draft</x:v>
       </x:c>
       <x:c r="J263" s="4" t="str">
-        <x:v>未执行</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="K263" s="4" t="str">
         <x:v>细化用例</x:v>
@@ -19861,7 +19892,7 @@
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:319</x:v>
       </x:c>
       <x:c r="M263" s="4" t="str">
-        <x:v>尚未执行</x:v>
+        <x:v>tm003-core-20261001T165439Z (source_check；产品E2E未运行)</x:v>
       </x:c>
       <x:c r="N263" s="4" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
@@ -19881,7 +19912,7 @@
         <x:v>TASK-TM003-IDENTITY</x:v>
       </x:c>
       <x:c r="E264" s="9" t="str">
-        <x:v>source_check</x:v>
+        <x:v>模块检查</x:v>
       </x:c>
       <x:c r="F264" s="9" t="str">
         <x:v>公开identity-v1测试key；codex/provider-response/shared-call-01的A=100/10/cached20；同ID重放；shared-call-02同usage；shared-call-01冲突999/99；claude_code/provider-message/shared-call-01仅求键。</x:v>
@@ -19900,7 +19931,7 @@
         <x:v>draft</x:v>
       </x:c>
       <x:c r="J264" s="9" t="str">
-        <x:v>未执行</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="K264" s="9" t="str">
         <x:v>细化用例</x:v>
@@ -19909,13 +19940,13 @@
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:323</x:v>
       </x:c>
       <x:c r="M264" s="9" t="str">
-        <x:v>尚未执行</x:v>
+        <x:v>tm003-core-20261001T165439Z (source_check；产品E2E未运行)</x:v>
       </x:c>
       <x:c r="N264" s="9" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="265" ht="72" customHeight="1">
+    <x:row r="265" ht="87" customHeight="1">
       <x:c r="A265" s="4" t="str">
         <x:v>TM-005</x:v>
       </x:c>
@@ -19930,13 +19961,13 @@
 TASK-TM005-RANGE-QUERY</x:v>
       </x:c>
       <x:c r="E265" s="4" t="str">
-        <x:v>source_check</x:v>
+        <x:v>模块检查</x:v>
       </x:c>
       <x:c r="F265" s="4" t="str">
         <x:v>fixture的A/B、跨主体C、界外D/E；synthetic-p1、Asia/Shanghai当地日2026-09-29</x:v>
       </x:c>
       <x:c r="G265" s="4" t="str">
-        <x:v>1. 按固定主体/当地日查询纯统计函数；仅A/B被选、C/D/E排除；输入数组和键不变
+        <x:v>1. 按固定主体和fixture固定UTC半开界查询纯统计函数，不做IANA日期换算；仅A/B被选、C/D/E排除；输入数组和键不变
 2. 核对来源、模型、Token和三个子项；input300/output30/total330；Codex110/Claude220；未知模型110/sonnet-test220；缓存读20但部分未知、缓存写未知、推理2但部分未知，子项不加总
 3. 逐个输入非法来源、负数、超范围缓存和坏UTC；各自被拒绝，无完整零或有效汇总输出；原fixture不变</x:v>
       </x:c>
@@ -19979,7 +20010,7 @@
 TASK-TM005-COVERAGE</x:v>
       </x:c>
       <x:c r="E266" s="9" t="str">
-        <x:v>source_check</x:v>
+        <x:v>模块检查</x:v>
       </x:c>
       <x:c r="F266" s="9" t="str">
         <x:v>fixture A/B及同范围Claude missing_usage诊断；双来源complete仅为模块合成覆盖假设</x:v>
@@ -20027,7 +20058,7 @@
         <x:v>TASK-TM005-COVERAGE</x:v>
       </x:c>
       <x:c r="E267" s="4" t="str">
-        <x:v>source_check</x:v>
+        <x:v>模块检查</x:v>
       </x:c>
       <x:c r="F267" s="4" t="str">
         <x:v>fixture五行coverage_algebra；complete仅为模块合成输入，product_coverage_proven=false</x:v>
@@ -20075,7 +20106,7 @@
         <x:v>TASK-TM004-INCREMENTAL</x:v>
       </x:c>
       <x:c r="E268" s="9" t="str">
-        <x:v>source_check</x:v>
+        <x:v>模块检查</x:v>
       </x:c>
       <x:c r="F268" s="9" t="str">
         <x:v>固定746字节13/7 assistant行、前半字节、两条不同ID完整行、首读上限754字节</x:v>
@@ -20123,7 +20154,7 @@
         <x:v>TASK-TM004-INCREMENTAL</x:v>
       </x:c>
       <x:c r="E269" s="4" t="str">
-        <x:v>source_check</x:v>
+        <x:v>模块检查</x:v>
       </x:c>
       <x:c r="F269" s="4" t="str">
         <x:v>已提交首行，追加不同ID第二行、同长度ID改写并复原mtime、截短、身份改变、秘密缺失或错误</x:v>
@@ -20172,7 +20203,7 @@
 TASK-TM004-INCREMENTAL</x:v>
       </x:c>
       <x:c r="E270" s="9" t="str">
-        <x:v>source_check</x:v>
+        <x:v>模块检查</x:v>
       </x:c>
       <x:c r="F270" s="9" t="str">
         <x:v>固定13/7行前置非法UTF8完整行和版本2.1.127完整行，尾部再追加无LF坏字节</x:v>
@@ -20229,7 +20260,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rafe0914c2e5f4e3d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53d132cdb12b4b3f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20240,21 +20271,23 @@
   <x:cols>
     <x:col min="1" max="1" width="55" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="52" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="43" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="55" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="95" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="55" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="95" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="95" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2">
       <x:c r="A2" s="1" t="str">
-        <x:v>测试批次索引 · 详细结果单独保存</x:v>
+        <x:v>测试批次索引 · 模块与产品结果分别计数</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="32" customHeight="1">
@@ -20265,34 +20298,40 @@
         <x:v>版本</x:v>
       </x:c>
       <x:c r="C4" s="8" t="str">
+        <x:v>执行类型</x:v>
+      </x:c>
+      <x:c r="D4" s="8" t="str">
         <x:v>范围</x:v>
       </x:c>
-      <x:c r="D4" s="8" t="str">
+      <x:c r="E4" s="8" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="E4" s="8" t="str">
+      <x:c r="F4" s="8" t="str">
         <x:v>父用例/场景数</x:v>
       </x:c>
-      <x:c r="F4" s="8" t="str">
+      <x:c r="G4" s="8" t="str">
         <x:v>通过数</x:v>
       </x:c>
-      <x:c r="G4" s="8" t="str">
+      <x:c r="H4" s="8" t="str">
         <x:v>失败数</x:v>
       </x:c>
-      <x:c r="H4" s="8" t="str">
+      <x:c r="I4" s="8" t="str">
         <x:v>阻塞数</x:v>
       </x:c>
-      <x:c r="I4" s="8" t="str">
+      <x:c r="J4" s="8" t="str">
         <x:v>候选提交</x:v>
       </x:c>
-      <x:c r="J4" s="8" t="str">
+      <x:c r="K4" s="8" t="str">
         <x:v>发布资格</x:v>
       </x:c>
-      <x:c r="K4" s="8" t="str">
+      <x:c r="L4" s="8" t="str">
         <x:v>批次摘要</x:v>
       </x:c>
-      <x:c r="L4" s="8" t="str">
+      <x:c r="M4" s="8" t="str">
         <x:v>独立结果Excel（本机）</x:v>
+      </x:c>
+      <x:c r="N4" s="8" t="str">
+        <x:v>产品E2E状态</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="42" customHeight="1">
@@ -20303,34 +20342,40 @@
         <x:v>v0.1.0-20260929T074814Z</x:v>
       </x:c>
       <x:c r="C5" s="4" t="str">
+        <x:v>product_e2e</x:v>
+      </x:c>
+      <x:c r="D5" s="4" t="str">
         <x:v>开发包诊断 / dirty</x:v>
       </x:c>
-      <x:c r="D5" s="4" t="str">
+      <x:c r="E5" s="4" t="str">
         <x:v>FAIL</x:v>
       </x:c>
-      <x:c r="E5" s="4" t="n">
+      <x:c r="F5" s="4" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F5" s="4" t="n">
+      <x:c r="G5" s="4" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G5" s="4" t="n">
+      <x:c r="H5" s="4" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H5" s="4" t="n">
+      <x:c r="I5" s="4" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I5" s="4" t="str">
+      <x:c r="J5" s="4" t="str">
         <x:v>6e80dd12d60ee5dad641bca030445a2153a269c9</x:v>
       </x:c>
-      <x:c r="J5" s="4" t="str">
+      <x:c r="K5" s="4" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="K5" s="4" t="str">
+      <x:c r="L5" s="4" t="str">
         <x:v>六个历史聚合场景，升级004失败；不回填新增TC。结果表修订02修正时间显示，原表和测试证据保留；未新增测试运行。</x:v>
       </x:c>
-      <x:c r="L5" s="4" t="str">
+      <x:c r="M5" s="4" t="str">
         <x:v>.local/test-results/local-a1b2c3d4e5f60718293a4b5c6d7e8f94/revisions/02/TokenMeter测试结果-local-a1b2c3d4e5f60718293a4b5c6d7e8f94.xlsx</x:v>
+      </x:c>
+      <x:c r="N5" s="4" t="str">
+        <x:v>FAIL</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="42" customHeight="1">
@@ -20341,34 +20386,40 @@
         <x:v>v0.1.0-20260929T074814Z</x:v>
       </x:c>
       <x:c r="C6" s="9" t="str">
+        <x:v>product_e2e</x:v>
+      </x:c>
+      <x:c r="D6" s="9" t="str">
         <x:v>精细开发包回归（测试造数中断）</x:v>
       </x:c>
-      <x:c r="D6" s="9" t="str">
+      <x:c r="E6" s="9" t="str">
         <x:v>BLOCKED</x:v>
       </x:c>
-      <x:c r="E6" s="9" t="n">
+      <x:c r="F6" s="9" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="F6" s="9" t="n">
+      <x:c r="G6" s="9" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="G6" s="9" t="n">
+      <x:c r="H6" s="9" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H6" s="9" t="n">
+      <x:c r="I6" s="9" t="n">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="I6" s="9" t="str">
+      <x:c r="J6" s="9" t="str">
         <x:v>6e80dd12d60ee5dad641bca030445a2153a269c9</x:v>
       </x:c>
-      <x:c r="J6" s="9" t="str">
+      <x:c r="K6" s="9" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="K6" s="9" t="str">
+      <x:c r="L6" s="9" t="str">
         <x:v>前16条登录实际PASS；第17条参数路径中的#被SQLite URI截断，准备阶段中断。78父TC为16 PASS/62 BLOCKED；31变体未完成。清理全真，缺项未以旧场景通过代替。</x:v>
       </x:c>
-      <x:c r="L6" s="9" t="str">
+      <x:c r="M6" s="9" t="str">
         <x:v>.local/test-results/local-7feea03dd72e4eddba0651cede8fd23d-frozen/TokenMeter测试结果-local-7feea03dd72e4eddba0651cede8fd23d.xlsx</x:v>
+      </x:c>
+      <x:c r="N6" s="9" t="str">
+        <x:v>BLOCKED</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="57" customHeight="1">
@@ -20379,34 +20430,40 @@
         <x:v>v0.1.0-20260929T074814Z</x:v>
       </x:c>
       <x:c r="C7" s="4" t="str">
+        <x:v>product_e2e</x:v>
+      </x:c>
+      <x:c r="D7" s="4" t="str">
         <x:v>完整精细回归及同候选辅助检查</x:v>
       </x:c>
-      <x:c r="D7" s="4" t="str">
+      <x:c r="E7" s="4" t="str">
         <x:v>FAIL</x:v>
       </x:c>
-      <x:c r="E7" s="4" t="n">
+      <x:c r="F7" s="4" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="F7" s="4" t="n">
+      <x:c r="G7" s="4" t="n">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="G7" s="4" t="n">
+      <x:c r="H7" s="4" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="H7" s="4" t="n">
+      <x:c r="I7" s="4" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="4" t="str">
+      <x:c r="J7" s="4" t="str">
         <x:v>6e80dd12d60ee5dad641bca030445a2153a269c9</x:v>
       </x:c>
-      <x:c r="J7" s="4" t="str">
+      <x:c r="K7" s="4" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="K7" s="4" t="str">
+      <x:c r="L7" s="4" t="str">
         <x:v>78父用例：62 PASS、9 FAIL、7 BLOCKED；38参数变体：31 PASS、7 FAIL（不与父用例相加）。真实产品95个执行入口，另11条辅助检查。独立代码复核保留原始失败，证据不足降BLOCKED。含3,397条证据链接和12张截图。</x:v>
       </x:c>
-      <x:c r="L7" s="4" t="str">
+      <x:c r="M7" s="4" t="str">
         <x:v>.local/test-results/local-343e54113b0b442383e80f137013014b-reviewed/TokenMeter测试结果-local-343e54113b0b442383e80f137013014b.xlsx</x:v>
+      </x:c>
+      <x:c r="N7" s="4" t="str">
+        <x:v>FAIL</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="57" customHeight="1">
@@ -20417,34 +20474,40 @@
         <x:v>v0.1.0-20260929T074814Z</x:v>
       </x:c>
       <x:c r="C8" s="9" t="str">
+        <x:v>product_e2e</x:v>
+      </x:c>
+      <x:c r="D8" s="9" t="str">
         <x:v>PASSWORD05/ADMIN03/UPDATE05脚本修复后定向验证</x:v>
       </x:c>
-      <x:c r="D8" s="9" t="str">
+      <x:c r="E8" s="9" t="str">
         <x:v>FAIL</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="n">
+      <x:c r="F8" s="9" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F8" s="9" t="n">
+      <x:c r="G8" s="9" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G8" s="9" t="n">
+      <x:c r="H8" s="9" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H8" s="9" t="n">
+      <x:c r="I8" s="9" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="str">
+      <x:c r="J8" s="9" t="str">
         <x:v>6e80dd12d60ee5dad641bca030445a2153a269c9</x:v>
       </x:c>
-      <x:c r="J8" s="9" t="str">
+      <x:c r="K8" s="9" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="K8" s="9" t="str">
+      <x:c r="L8" s="9" t="str">
         <x:v>15个实际Playwright入口；3父用例2 PASS/1 FAIL，13变体8 PASS/5 FAIL。PASSWORD05独立peer与ADMIN03收尾脚本修复验证通过；UPDATE05五个解压身份场景20秒后仍有临时目录残留。其余75父用例范围外。原全量失败保留，本次不构成全量发布回归。</x:v>
       </x:c>
-      <x:c r="L8" s="9" t="str">
+      <x:c r="M8" s="9" t="str">
         <x:v>.local/test-results/local-877830fb340a4d12b4e29cf76fa422ed-reviewed/TokenMeter测试结果-local-877830fb340a4d12b4e29cf76fa422ed.xlsx</x:v>
+      </x:c>
+      <x:c r="N8" s="9" t="str">
+        <x:v>FAIL</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="57" customHeight="1">
@@ -20455,34 +20518,40 @@
         <x:v>v0.1.0-20260929T074814Z</x:v>
       </x:c>
       <x:c r="C9" s="4" t="str">
+        <x:v>product_e2e</x:v>
+      </x:c>
+      <x:c r="D9" s="4" t="str">
         <x:v>UI01颜色检查脚本修复后单例验证</x:v>
       </x:c>
-      <x:c r="D9" s="4" t="str">
+      <x:c r="E9" s="4" t="str">
         <x:v>PASS</x:v>
-      </x:c>
-      <x:c r="E9" s="4" t="n">
-        <x:v>1</x:v>
       </x:c>
       <x:c r="F9" s="4" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G9" s="4" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H9" s="4" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I9" s="4" t="str">
+      <x:c r="I9" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J9" s="4" t="str">
         <x:v>6e80dd12d60ee5dad641bca030445a2153a269c9</x:v>
       </x:c>
-      <x:c r="J9" s="4" t="str">
+      <x:c r="K9" s="4" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="K9" s="4" t="str">
+      <x:c r="L9" s="4" t="str">
         <x:v>仅UI01一条PASS，77条TM001不在本次范围。修复#fff缩写颜色解析后，程序测得浅色对比度16.235、深色12.513，6页无溢出。7张截图、53条证据链接；不覆盖首次FAIL，不代表完整产品回归通过。</x:v>
       </x:c>
-      <x:c r="L9" s="4" t="str">
+      <x:c r="M9" s="4" t="str">
         <x:v>.local/test-results/aux-ui01-local-343e54113b0b442383e80f137013014b-02-reviewed/TokenMeter测试结果-aux-ui01-local-343e54113b0b442383e80f137013014b-02.xlsx</x:v>
+      </x:c>
+      <x:c r="N9" s="4" t="str">
+        <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="57" customHeight="1">
@@ -20493,34 +20562,40 @@
         <x:v>v0.1.0-20260929T074814Z</x:v>
       </x:c>
       <x:c r="C10" s="9" t="str">
+        <x:v>product_e2e</x:v>
+      </x:c>
+      <x:c r="D10" s="9" t="str">
         <x:v>完整精细主回归（辅助11项未绑定）</x:v>
       </x:c>
-      <x:c r="D10" s="9" t="str">
+      <x:c r="E10" s="9" t="str">
         <x:v>FAIL</x:v>
       </x:c>
-      <x:c r="E10" s="9" t="n">
+      <x:c r="F10" s="9" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="F10" s="9" t="n">
+      <x:c r="G10" s="9" t="n">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="G10" s="9" t="n">
+      <x:c r="H10" s="9" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H10" s="9" t="n">
+      <x:c r="I10" s="9" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="I10" s="9" t="str">
+      <x:c r="J10" s="9" t="str">
         <x:v>6e80dd12d60ee5dad641bca030445a2153a269c9</x:v>
       </x:c>
-      <x:c r="J10" s="9" t="str">
+      <x:c r="K10" s="9" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="K10" s="9" t="str">
+      <x:c r="L10" s="9" t="str">
         <x:v>78父TC：66 PASS、1 FAIL（SESSION-09）、11辅助占位BLOCKED；38参数变体全部PASS。原始运行FAIL，清理完成；独立审计PASS只证明被审计旁证，不改变产品结论。 参数变体另计：38 PASS、0 FAIL、0 BLOCKED。</x:v>
       </x:c>
-      <x:c r="L10" s="9" t="str">
+      <x:c r="M10" s="9" t="str">
         <x:v>.local/test-results/local-571dd63bfe5b4d90a95ed9c70d80de07-reviewed/TokenMeter测试结果-local-571dd63bfe5b4d90a95ed9c70d80de07.xlsx</x:v>
+      </x:c>
+      <x:c r="N10" s="9" t="str">
+        <x:v>FAIL</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="42" customHeight="1">
@@ -20531,34 +20606,40 @@
         <x:v>v0.1.0-20260929T074814Z</x:v>
       </x:c>
       <x:c r="C11" s="4" t="str">
+        <x:v>product_e2e</x:v>
+      </x:c>
+      <x:c r="D11" s="4" t="str">
         <x:v>SESSION-09脚本修正后单例定向验证</x:v>
       </x:c>
-      <x:c r="D11" s="4" t="str">
+      <x:c r="E11" s="4" t="str">
         <x:v>PASS</x:v>
-      </x:c>
-      <x:c r="E11" s="4" t="n">
-        <x:v>1</x:v>
       </x:c>
       <x:c r="F11" s="4" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G11" s="4" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H11" s="4" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I11" s="4" t="str">
+      <x:c r="I11" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J11" s="4" t="str">
         <x:v>6e80dd12d60ee5dad641bca030445a2153a269c9</x:v>
       </x:c>
-      <x:c r="J11" s="4" t="str">
+      <x:c r="K11" s="4" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="K11" s="4" t="str">
+      <x:c r="L11" s="4" t="str">
         <x:v>SESSION-09一例PASS、清理完成；其余77父TC范围外。仅定位前次禁用按钮点击失败，不覆盖完整回归FAIL。</x:v>
       </x:c>
-      <x:c r="L11" s="4" t="str">
+      <x:c r="M11" s="4" t="str">
         <x:v>.local/test-results/local-4a8815e9d61e4b4bbdd41f7a2f897c52-reviewed/TokenMeter测试结果-local-4a8815e9d61e4b4bbdd41f7a2f897c52.xlsx</x:v>
+      </x:c>
+      <x:c r="N11" s="4" t="str">
+        <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="57" customHeight="1">
@@ -20569,34 +20650,40 @@
         <x:v>v0.1.0-20260929T074814Z</x:v>
       </x:c>
       <x:c r="C12" s="9" t="str">
+        <x:v>product_e2e</x:v>
+      </x:c>
+      <x:c r="D12" s="9" t="str">
         <x:v>完整精细主回归（升级清理失败）</x:v>
       </x:c>
-      <x:c r="D12" s="9" t="str">
+      <x:c r="E12" s="9" t="str">
         <x:v>FAIL</x:v>
       </x:c>
-      <x:c r="E12" s="9" t="n">
+      <x:c r="F12" s="9" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="F12" s="9" t="n">
+      <x:c r="G12" s="9" t="n">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="G12" s="9" t="n">
+      <x:c r="H12" s="9" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H12" s="9" t="n">
+      <x:c r="I12" s="9" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="I12" s="9" t="str">
+      <x:c r="J12" s="9" t="str">
         <x:v>6e80dd12d60ee5dad641bca030445a2153a269c9</x:v>
       </x:c>
-      <x:c r="J12" s="9" t="str">
+      <x:c r="K12" s="9" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="K12" s="9" t="str">
+      <x:c r="L12" s="9" t="str">
         <x:v>78父TC：65 PASS、1 FAIL（UPDATE-07清理不完整）、12 BLOCKED（UPDATE-08及11辅助占位）；38参数变体全部PASS。原始运行FAIL、cleanup_completed=false；不能放行。 参数变体另计：38 PASS、0 FAIL、0 BLOCKED。</x:v>
       </x:c>
-      <x:c r="L12" s="9" t="str">
+      <x:c r="M12" s="9" t="str">
         <x:v>.local/test-results/local-f47f8257607c48458cc52b886d281d70-reviewed/TokenMeter测试结果-local-f47f8257607c48458cc52b886d281d70.xlsx</x:v>
+      </x:c>
+      <x:c r="N12" s="9" t="str">
+        <x:v>FAIL</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="42" customHeight="1">
@@ -20607,34 +20694,40 @@
         <x:v>v0.1.0-20260929T074814Z</x:v>
       </x:c>
       <x:c r="C13" s="4" t="str">
+        <x:v>product_e2e</x:v>
+      </x:c>
+      <x:c r="D13" s="4" t="str">
         <x:v>UPDATE-07/08清理问题定向复现</x:v>
       </x:c>
-      <x:c r="D13" s="4" t="str">
+      <x:c r="E13" s="4" t="str">
         <x:v>FAIL</x:v>
       </x:c>
-      <x:c r="E13" s="4" t="n">
+      <x:c r="F13" s="4" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F13" s="4" t="n">
+      <x:c r="G13" s="4" t="n">
         <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="4" t="n">
-        <x:v>1</x:v>
       </x:c>
       <x:c r="H13" s="4" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I13" s="4" t="str">
+      <x:c r="I13" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J13" s="4" t="str">
         <x:v>6e80dd12d60ee5dad641bca030445a2153a269c9</x:v>
       </x:c>
-      <x:c r="J13" s="4" t="str">
+      <x:c r="K13" s="4" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="K13" s="4" t="str">
+      <x:c r="L13" s="4" t="str">
         <x:v>UPDATE-07因本轮拥有资源未完全清理而FAIL，UPDATE-08为避免接管残留而BLOCKED；cleanup_completed=false。其余76父TC范围外，原始失败保留。</x:v>
       </x:c>
-      <x:c r="L13" s="4" t="str">
+      <x:c r="M13" s="4" t="str">
         <x:v>.local/test-results/local-c8e31657d5e4428584a6f316936113e1-reviewed/TokenMeter测试结果-local-c8e31657d5e4428584a6f316936113e1.xlsx</x:v>
+      </x:c>
+      <x:c r="N13" s="4" t="str">
+        <x:v>FAIL</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="42" customHeight="1">
@@ -20645,34 +20738,40 @@
         <x:v>v0.1.0-20260929T074814Z</x:v>
       </x:c>
       <x:c r="C14" s="9" t="str">
+        <x:v>product_e2e</x:v>
+      </x:c>
+      <x:c r="D14" s="9" t="str">
         <x:v>UPDATE-07/08测试环境阻断定向批次</x:v>
       </x:c>
-      <x:c r="D14" s="9" t="str">
+      <x:c r="E14" s="9" t="str">
         <x:v>BLOCKED</x:v>
       </x:c>
-      <x:c r="E14" s="9" t="n">
+      <x:c r="F14" s="9" t="n">
         <x:v>2</x:v>
-      </x:c>
-      <x:c r="F14" s="9" t="n">
-        <x:v>0</x:v>
       </x:c>
       <x:c r="G14" s="9" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H14" s="9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I14" s="9" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="I14" s="9" t="str">
+      <x:c r="J14" s="9" t="str">
         <x:v>6e80dd12d60ee5dad641bca030445a2153a269c9</x:v>
       </x:c>
-      <x:c r="J14" s="9" t="str">
+      <x:c r="K14" s="9" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="K14" s="9" t="str">
+      <x:c r="L14" s="9" t="str">
         <x:v>启动时使用系统Python，缺少alembic；UPDATE-07/08均在准备阶段BLOCKED，实际执行0例。原始BLOCKED及环境原因保留，清理完成。</x:v>
       </x:c>
-      <x:c r="L14" s="9" t="str">
+      <x:c r="M14" s="9" t="str">
         <x:v>.local/test-results/local-70e531d3092c4cbea30160117c379287-reviewed/TokenMeter测试结果-local-70e531d3092c4cbea30160117c379287.xlsx</x:v>
+      </x:c>
+      <x:c r="N14" s="9" t="str">
+        <x:v>BLOCKED</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="42" customHeight="1">
@@ -20683,34 +20782,40 @@
         <x:v>v0.1.0-20260929T074814Z</x:v>
       </x:c>
       <x:c r="C15" s="4" t="str">
+        <x:v>product_e2e</x:v>
+      </x:c>
+      <x:c r="D15" s="4" t="str">
         <x:v>UPDATE-07/08隔离环境定向验证</x:v>
       </x:c>
-      <x:c r="D15" s="4" t="str">
+      <x:c r="E15" s="4" t="str">
         <x:v>PASS</x:v>
-      </x:c>
-      <x:c r="E15" s="4" t="n">
-        <x:v>2</x:v>
       </x:c>
       <x:c r="F15" s="4" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G15" s="4" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H15" s="4" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I15" s="4" t="str">
+      <x:c r="I15" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J15" s="4" t="str">
         <x:v>6e80dd12d60ee5dad641bca030445a2153a269c9</x:v>
       </x:c>
-      <x:c r="J15" s="4" t="str">
+      <x:c r="K15" s="4" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="K15" s="4" t="str">
+      <x:c r="L15" s="4" t="str">
         <x:v>使用项目venv执行UPDATE-07/08，2例PASS、清理完成；UPDATE-07独立旁证审计PASS。其余76父TC范围外，不覆盖此前完整回归FAIL。</x:v>
       </x:c>
-      <x:c r="L15" s="4" t="str">
+      <x:c r="M15" s="4" t="str">
         <x:v>.local/test-results/local-b6627e4379c64386bfc1a535fb432c16-reviewed/TokenMeter测试结果-local-b6627e4379c64386bfc1a535fb432c16.xlsx</x:v>
+      </x:c>
+      <x:c r="N15" s="4" t="str">
+        <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="57" customHeight="1">
@@ -20721,34 +20826,40 @@
         <x:v>v0.1.0-20260929T074814Z</x:v>
       </x:c>
       <x:c r="C16" s="9" t="str">
+        <x:v>product_e2e</x:v>
+      </x:c>
+      <x:c r="D16" s="9" t="str">
         <x:v>同候选完整联合复核（本机开发包）</x:v>
       </x:c>
-      <x:c r="D16" s="9" t="str">
+      <x:c r="E16" s="9" t="str">
         <x:v>PASS</x:v>
-      </x:c>
-      <x:c r="E16" s="9" t="n">
-        <x:v>78</x:v>
       </x:c>
       <x:c r="F16" s="9" t="n">
         <x:v>78</x:v>
       </x:c>
       <x:c r="G16" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="H16" s="9" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I16" s="9" t="str">
+      <x:c r="I16" s="9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J16" s="9" t="str">
         <x:v>6e80dd12d60ee5dad641bca030445a2153a269c9</x:v>
       </x:c>
-      <x:c r="J16" s="9" t="str">
+      <x:c r="K16" s="9" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="K16" s="9" t="str">
+      <x:c r="L16" s="9" t="str">
         <x:v>主原始BLOCKED：67产品父TC与38参数变体PASS，11辅助仅占位BLOCKED。独立辅助11/11 PASS并绑定同候选，六组6/6 PASS，审计v2 12/12 PASS；联合审核后78父TC和38变体全PASS。原件未改，开发包与dirty源码不具发布资格。</x:v>
       </x:c>
-      <x:c r="L16" s="9" t="str">
+      <x:c r="M16" s="9" t="str">
         <x:v>.local/test-results/local-534748ff47cb44229183a6bd878c1674-reviewed/TokenMeter测试结果-local-534748ff47cb44229183a6bd878c1674.xlsx</x:v>
+      </x:c>
+      <x:c r="N16" s="9" t="str">
+        <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="57" customHeight="1">
@@ -20759,50 +20870,149 @@
         <x:v>v0.1.0-20260929T074814Z</x:v>
       </x:c>
       <x:c r="C17" s="4" t="str">
+        <x:v>product_e2e</x:v>
+      </x:c>
+      <x:c r="D17" s="4" t="str">
         <x:v>本地master固定候选最终包首次精细门禁</x:v>
       </x:c>
-      <x:c r="D17" s="4" t="str">
+      <x:c r="E17" s="4" t="str">
         <x:v>FAIL</x:v>
       </x:c>
-      <x:c r="E17" s="4" t="n">
+      <x:c r="F17" s="4" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="F17" s="4" t="n">
+      <x:c r="G17" s="4" t="n">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="G17" s="4" t="n">
+      <x:c r="H17" s="4" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H17" s="4" t="n">
+      <x:c r="I17" s="4" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="I17" s="4" t="str">
+      <x:c r="J17" s="4" t="str">
         <x:v>c2911bc65d55579fcf71e5ba11db87357a01a5e4</x:v>
       </x:c>
-      <x:c r="J17" s="4" t="str">
+      <x:c r="K17" s="4" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="K17" s="4" t="str">
+      <x:c r="L17" s="4" t="str">
         <x:v>固定本地master候选门禁FAIL；原始116项91 PASS/14 FAIL/11 BLOCKED，UPDATE-05父项与13变体缺签名输入。逐例模型78父TC 66 PASS/1 FAIL/11 BLOCKED，38变体25 PASS/13 FAIL；无正式稳定包。</x:v>
       </x:c>
-      <x:c r="L17" s="4" t="str">
+      <x:c r="M17" s="4" t="str">
         <x:v>.local/test-results/local-0512d4fc44544eba97f9d1ae79cbfc37-reviewed/TokenMeter测试结果-local-0512d4fc44544eba97f9d1ae79cbfc37.xlsx</x:v>
       </x:c>
+      <x:c r="N17" s="4" t="str">
+        <x:v>FAIL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="42" customHeight="1">
+      <x:c r="A18" s="9" t="str">
+        <x:v>tm003-core-20261001T163807Z</x:v>
+      </x:c>
+      <x:c r="B18" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+      <x:c r="C18" s="9" t="str">
+        <x:v>source_check</x:v>
+      </x:c>
+      <x:c r="D18" s="9" t="str">
+        <x:v>TM-003 CORE-01/02/03 固定模块验证；非产品E2E</x:v>
+      </x:c>
+      <x:c r="E18" s="9" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F18" s="9" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G18" s="9" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H18" s="9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I18" s="9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J18" s="9" t="str">
+        <x:v>ea6b18765ce63a5b32b7de0488de5d2a4647de94</x:v>
+      </x:c>
+      <x:c r="K18" s="9" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="L18" s="9" t="str">
+        <x:v>source_check固定3条/9步骤PASS，逐例清理PASS；独立结果Excel/verification回读PASS。仅模块，不覆盖TM003原27条产品TC；产品E2E和发行门禁NOT_RUN。</x:v>
+      </x:c>
+      <x:c r="M18" s="9" t="str">
+        <x:v>.local/test-results/tm003-core-20261001T163807Z/TokenMeter测试结果-tm003-core-20261001T163807Z.xlsx</x:v>
+      </x:c>
+      <x:c r="N18" s="9" t="str">
+        <x:v>NOT_RUN</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="57" customHeight="1">
+      <x:c r="A19" s="4" t="str">
+        <x:v>tm003-core-20261001T165439Z</x:v>
+      </x:c>
+      <x:c r="B19" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+      <x:c r="C19" s="4" t="str">
+        <x:v>source_check</x:v>
+      </x:c>
+      <x:c r="D19" s="4" t="str">
+        <x:v>TM-003 CORE-01/02/03 固定模块验证；非产品E2E</x:v>
+      </x:c>
+      <x:c r="E19" s="4" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F19" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G19" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H19" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I19" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J19" s="4" t="str">
+        <x:v>d7c3d39ac0a007f0e16f55bbb3cfc9b15fd9fe34</x:v>
+      </x:c>
+      <x:c r="K19" s="4" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="L19" s="4" t="str">
+        <x:v>共享source_check清理合同扩展后的新候选：CORE固定3/3、九步PASS，owned_root清理逐例PASS；独立Excel/verification回读PASS。旧ea6b187批次保留；原27条产品TC与正式发行仍NOT_RUN。</x:v>
+      </x:c>
+      <x:c r="M19" s="4" t="str">
+        <x:v>.local/test-results/tm003-core-20261001T165439Z/TokenMeter测试结果-tm003-core-20261001T165439Z.xlsx</x:v>
+      </x:c>
+      <x:c r="N19" s="4" t="str">
+        <x:v>NOT_RUN</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="D5:D17">
+  <x:conditionalFormatting sqref="E5:E19">
     <x:cfRule type="containsText" dxfId="24" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="25" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="26" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="L5:L17">
+  <x:conditionalFormatting sqref="M5:M19">
     <x:cfRule type="containsText" dxfId="27" priority="4" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="28" priority="5" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="29" priority="6" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="N5:N19">
+    <x:cfRule type="containsText" dxfId="30" priority="7" operator="containsText" text="FAIL"/>
+    <x:cfRule type="containsText" dxfId="31" priority="8" operator="containsText" text="预期待明确"/>
+    <x:cfRule type="containsText" dxfId="32" priority="9" operator="containsText" text="未执行"/>
+  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a1d865dd2024f4f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf5d2095136964585"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21004,7 +21214,7 @@
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="192" customHeight="1">
+    <x:row r="7" ht="237" customHeight="1">
       <x:c r="A7" s="4" t="str">
         <x:v>v0.2.0-20261001T034118Z</x:v>
       </x:c>
@@ -21033,7 +21243,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J7" s="4" t="str">
-        <x:v>设计基线已完成：3功能点、9 TASK、28父TC、35变体。开发工作树已有原生目录面板、加密locator、根FD受限读取、React授权UI及33个固定E2E叶入口（28可执行、5场景摘要）；报告单元59/59、治理473/473、构建PASS。产品E2E因AX trusted=false及隔离标准测试账号不可用BLOCKED，Keychain最终包隔离未证实。本独立文档树未合该代码，机器绑定仍planned；正式发行完整门禁NOT_RUN、未发布。0.2公开配置为version0.2.0/build200及测试高版0.2.1/build201，实际0.2包尚未证明。</x:v>
+        <x:v>设计基线已完成：3功能点、9 TASK、28父TC、35变体。开发工作树已有原生目录面板、加密locator、根FD受限读取、React授权UI及33个固定E2E叶入口（28可执行、5场景摘要）；报告单元59/59、治理473/473、构建PASS。产品E2E因AX trusted=false及隔离标准测试账号不可用BLOCKED，Keychain最终包隔离未证实。本独立文档树未合该代码，机器绑定仍planned；正式发行完整门禁NOT_RUN、未发布。0.2公开配置为version0.2.0/build200及测试高版0.2.1/build201，实际0.2包尚未证明。 2026-10-02修订SECURITY-01三个恶意字串变体的固定IPC method/字段/错误码，产品状态不变；需在整合候选重核基线及固定程序。</x:v>
       </x:c>
       <x:c r="K7" s="4" t="str">
         <x:v>TM001独立候选d2门禁PASS只属历史；本地master c2911bc首次最终包门禁FAIL、无SOP-020稳定原包，不能作为0.2升级源；本版无实际产品运行。</x:v>
@@ -21060,7 +21270,7 @@
         <x:v>releases/v0.2.0-20261001T034118Z/01-requirements.md:32</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="192" customHeight="1">
+    <x:row r="8" ht="297" customHeight="1">
       <x:c r="A8" s="9" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
@@ -21089,7 +21299,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J8" s="9" t="str">
-        <x:v>整版draft、未发布。27条产品TC未执行；3条CORE辅助TC已在文档提交48ca089独立切片就绪，在开发分支311deedf运行模块3/3 PASS，原始receipt在该分支.local/ci/tm003-core-20261001/。代码尚未合入本文档树，机器绑定保持空；模块报告不能作为产品E2E或发行门禁，结果Excel规范待SOP修订。 2026-10-02新代码候选44379e6已有逐步模块3/3与桌面29/29/typecheck/build原件；source_check独立Excel导出程序仍缺，批次登记BLOCKED，产品E2E仍NOT_RUN。</x:v>
+        <x:v>整版draft、未发布。27条产品TC未执行；3条CORE辅助TC已在文档提交48ca089独立切片就绪，在开发分支311deedf运行模块3/3 PASS，原始receipt在该分支.local/ci/tm003-core-20261001/。代码尚未合入本文档树，机器绑定保持空；模块报告不能作为产品E2E或发行门禁，结果Excel规范待SOP修订。 2026-10-02新代码候选44379e6已有逐步模块3/3与桌面29/29/typecheck/build原件；source_check独立Excel导出程序仍缺，批次登记BLOCKED，产品E2E仍NOT_RUN。 固定导出器新run tm003-core-20261001T163807Z在ea6b187候选生成3/3/9步source_check独立Excel并回读PASS，现已按被测SHA登记模块批次；原27条产品TC与发行仍NOT_RUN。 新清理合同候选d7c3d39的独立run tm003-core-20261001T165439Z亦3/3/9步及Excel回读PASS，作为最新模块批次；旧ea6批次保留。</x:v>
       </x:c>
       <x:c r="K8" s="9" t="str">
         <x:v>TM-001 干净源码候选为技术基底；其产品门禁不继承给TM-003</x:v>
@@ -21116,7 +21326,7 @@
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="132" customHeight="1">
+    <x:row r="9" ht="162" customHeight="1">
       <x:c r="A9" s="4" t="str">
         <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
@@ -21145,7 +21355,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J9" s="4" t="str">
-        <x:v>整版draft、未发布。原20产品细TC及四组摘要保留，新增3条已打开只读句柄的reader CORE辅助TC，固定LF、前缀MAC/重扫和损坏行输入，切片检查未完成。开发树模块红0/3与绿3/3仅是交接证据，且代码未形成干净提交；产品授权、稳定文件身份、SQLite原子事务、IPC/App E2E未验证，正式发行门禁NOT_RUN。</x:v>
+        <x:v>整版draft、未发布。原20产品细TC及四组摘要保留，3条reader CORE辅助TC在输入提交fea41fe/同步SOP后的干净候选ebbcfd0上按SOP-008独立判为development_slice_ready；程序绑定仍空。本版代码分支e52b62e报告reader目标9/9、桌面49/49和build PASS，仅为模块原件，Excel/总表批次尚无固定导出器。产品授权、稳定文件身份最终接口、SQLite原子事务、IPC/App E2E未验证，正式发行门禁NOT_RUN。</x:v>
       </x:c>
       <x:c r="K9" s="4" t="str">
         <x:v>TM004源分支原生零/缺失与nested Agent定向探针仅为研究证据；0.3及此前稳定原包尚未形成，真实升级BLOCKED。</x:v>
@@ -21172,7 +21382,7 @@
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="237" customHeight="1">
+    <x:row r="10" ht="267" customHeight="1">
       <x:c r="A10" s="9" t="str">
         <x:v>v0.5.0-20261001T034729Z</x:v>
       </x:c>
@@ -21201,7 +21411,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J10" s="9" t="str">
-        <x:v>整版draft、未发布。原32条产品父TC、6稳定变体和两组摘要保留；纯统计CORE-01/02/03辅助TC在输入提交061c759后，经SOP-008内容核对及结构/治理457项PASS，独立切片development_slice_ready，程序绑定仍为空、模块实际运行unexecuted。静态oracle与切片就绪不证明真实双来源采集或产品E2E；固定产品数据、SQLite/IPC、安装App逐TC绑定未完成，正式发行完整门禁NOT_RUN。 独立代码提交6a0f6f的source_check CORE3/3、桌面29/29、build PASS，原件在TM005工作树.local/tm005-core-postcommit-20261001T162401Z；程序尚未进入本文档树、模块Excel导出/批次登记BLOCKED，产品E2E仍NOT_RUN。</x:v>
+        <x:v>整版draft、未发布。原32条产品父TC、6稳定变体和两组摘要保留；纯统计CORE-01/02/03辅助TC在输入提交061c759后，经SOP-008内容核对及结构/治理457项PASS，独立切片development_slice_ready，程序绑定仍为空、模块实际运行unexecuted。静态oracle与切片就绪不证明真实双来源采集或产品E2E；固定产品数据、SQLite/IPC、安装App逐TC绑定未完成，正式发行完整门禁NOT_RUN。 独立代码提交6a0f6f的source_check CORE3/3、桌面29/29、build PASS，原件在TM005工作树.local/tm005-core-postcommit-20261001T162401Z；程序尚未进入本文档树、模块Excel导出/批次登记BLOCKED，产品E2E仍NOT_RUN。 CORE-01仅验证已给UTC半开界聚合，不验证IANA日期换算；该单独辅助TC待固定。</x:v>
       </x:c>
       <x:c r="K10" s="9" t="str">
         <x:v>TM005语义oracle只验证规范化样例；0.4及此前稳定原包尚未形成，真实升级BLOCKED。</x:v>
@@ -21230,23 +21440,23 @@
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="F5:F10">
-    <x:cfRule type="containsText" dxfId="30" priority="1" operator="containsText" text="FAIL"/>
-    <x:cfRule type="containsText" dxfId="31" priority="2" operator="containsText" text="预期待明确"/>
-    <x:cfRule type="containsText" dxfId="32" priority="3" operator="containsText" text="未执行"/>
+    <x:cfRule type="containsText" dxfId="33" priority="1" operator="containsText" text="FAIL"/>
+    <x:cfRule type="containsText" dxfId="34" priority="2" operator="containsText" text="预期待明确"/>
+    <x:cfRule type="containsText" dxfId="35" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="J5:J10">
-    <x:cfRule type="containsText" dxfId="33" priority="4" operator="containsText" text="FAIL"/>
-    <x:cfRule type="containsText" dxfId="34" priority="5" operator="containsText" text="预期待明确"/>
-    <x:cfRule type="containsText" dxfId="35" priority="6" operator="containsText" text="未执行"/>
+    <x:cfRule type="containsText" dxfId="36" priority="4" operator="containsText" text="FAIL"/>
+    <x:cfRule type="containsText" dxfId="37" priority="5" operator="containsText" text="预期待明确"/>
+    <x:cfRule type="containsText" dxfId="38" priority="6" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="M5:M10">
-    <x:cfRule type="containsText" dxfId="36" priority="7" operator="containsText" text="FAIL"/>
-    <x:cfRule type="containsText" dxfId="37" priority="8" operator="containsText" text="预期待明确"/>
-    <x:cfRule type="containsText" dxfId="38" priority="9" operator="containsText" text="未执行"/>
+    <x:cfRule type="containsText" dxfId="39" priority="7" operator="containsText" text="FAIL"/>
+    <x:cfRule type="containsText" dxfId="40" priority="8" operator="containsText" text="预期待明确"/>
+    <x:cfRule type="containsText" dxfId="41" priority="9" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raad3cfddeeb34401"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22babf438e234005"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22405,13 +22615,13 @@
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="F5:F46">
-    <x:cfRule type="containsText" dxfId="39" priority="1" operator="containsText" text="FAIL"/>
-    <x:cfRule type="containsText" dxfId="40" priority="2" operator="containsText" text="预期待明确"/>
-    <x:cfRule type="containsText" dxfId="41" priority="3" operator="containsText" text="未执行"/>
+    <x:cfRule type="containsText" dxfId="42" priority="1" operator="containsText" text="FAIL"/>
+    <x:cfRule type="containsText" dxfId="43" priority="2" operator="containsText" text="预期待明确"/>
+    <x:cfRule type="containsText" dxfId="44" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31d38ae98c06435d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3f8606679304557"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TokenMeter项目总表.xlsx
+++ b/TokenMeter项目总表.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="Rbf12aa18b3554001"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="R0df86ad125c847cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="Rb1d655ac537243bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R02ea4983c9c44775"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="Rcf6a862be63b4235"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R2503d345bbf645c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="Rb9fac209113c41ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R929989622c2e47b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Rabd4aa5c6f0f4350"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R63d60e02ad764d31"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R79b31b47b30a4cc3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R7bcf00d865dd4eb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="R156bab950efc4f5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="Rc9c5081c5e674fc5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="Rf6b5cfbd3ec349c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R85fc27840feb49b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R4a1341aeefab4aac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="Rd777e0187db64e0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R4a3ebf10cd5f4340"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="R7016dc8cac4844f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R999fe6c93ae14b6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="Rdeebd0e96c5f4903"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -786,8 +786,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TMTable6" displayName="TMTable6" ref="A4:N270" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:N270"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TMTable6" displayName="TMTable6" ref="A4:N272" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:N272"/>
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="功能编号"/>
     <x:tableColumn id="2" name="用例编号"/>
@@ -1134,8 +1134,8 @@
         <x:v>已登记用例</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:f>COUNTA('05测试用例'!B5:B270)</x:f>
-        <x:v>266</x:v>
+        <x:f>COUNTA('05测试用例'!B5:B272)</x:f>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C8" s="9" t="str">
         <x:v>父用例与具有稳定 ID 的变体各占一行；含未来概要场景</x:v>
@@ -1169,7 +1169,7 @@
         <x:v>界面与治理检查</x:v>
       </x:c>
       <x:c r="B11" s="10" t="n">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C11" s="4" t="str">
         <x:v>辅助检查不能替代产品E2E；稳定变体独立列出</x:v>
@@ -1288,7 +1288,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25d759ba0397462f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45392368bbda4a2d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1996,7 +1996,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R569059b8ca0b4736"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19b2f7e0dda74ebc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2145,7 +2145,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6025bfdd02894eb7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6300d3a562d543fa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2580,7 +2580,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf28121b6afbb43f9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8eb61670ecc40d7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3627,7 +3627,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9e3695a17444599"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra55d6dc8b0a34b63"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4734,7 +4734,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89bf59096c52401f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd5e4f1c98b7d43cb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7519,7 +7519,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf24b92a7a9c4ba9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R168a1387b8454b44"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18540,7 +18540,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L235" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:207</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:238</x:v>
       </x:c>
       <x:c r="M235" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -18587,7 +18587,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L236" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:211</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:242</x:v>
       </x:c>
       <x:c r="M236" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -18634,7 +18634,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L237" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:215</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:246</x:v>
       </x:c>
       <x:c r="M237" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -18682,7 +18682,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L238" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:219</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:250</x:v>
       </x:c>
       <x:c r="M238" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -18732,7 +18732,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L239" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:223</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:254</x:v>
       </x:c>
       <x:c r="M239" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -18780,7 +18780,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L240" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:227</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:258</x:v>
       </x:c>
       <x:c r="M240" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -18827,7 +18827,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L241" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:231</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:262</x:v>
       </x:c>
       <x:c r="M241" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -18874,7 +18874,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L242" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:235</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:266</x:v>
       </x:c>
       <x:c r="M242" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -18922,7 +18922,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L243" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:239</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:270</x:v>
       </x:c>
       <x:c r="M243" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -18971,7 +18971,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L244" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:243</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:274</x:v>
       </x:c>
       <x:c r="M244" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19020,7 +19020,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L245" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:247</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:278</x:v>
       </x:c>
       <x:c r="M245" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19069,7 +19069,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L246" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:251</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:282</x:v>
       </x:c>
       <x:c r="M246" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19116,7 +19116,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L247" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:255</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:286</x:v>
       </x:c>
       <x:c r="M247" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19164,7 +19164,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L248" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:259</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:290</x:v>
       </x:c>
       <x:c r="M248" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19212,7 +19212,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L249" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:263</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:294</x:v>
       </x:c>
       <x:c r="M249" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19260,7 +19260,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L250" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:267</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:298</x:v>
       </x:c>
       <x:c r="M250" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19308,7 +19308,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L251" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:271</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:302</x:v>
       </x:c>
       <x:c r="M251" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19358,7 +19358,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L252" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:275</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:306</x:v>
       </x:c>
       <x:c r="M252" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19405,7 +19405,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L253" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:279</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:310</x:v>
       </x:c>
       <x:c r="M253" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19452,7 +19452,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L254" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:283</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:314</x:v>
       </x:c>
       <x:c r="M254" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19500,7 +19500,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L255" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:287</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:318</x:v>
       </x:c>
       <x:c r="M255" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19549,7 +19549,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L256" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:291</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:322</x:v>
       </x:c>
       <x:c r="M256" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19599,7 +19599,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L257" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:295</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:326</x:v>
       </x:c>
       <x:c r="M257" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19647,7 +19647,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L258" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:299</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:330</x:v>
       </x:c>
       <x:c r="M258" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19696,7 +19696,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L259" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:303</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:334</x:v>
       </x:c>
       <x:c r="M259" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19744,7 +19744,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L260" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:307</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:338</x:v>
       </x:c>
       <x:c r="M260" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19792,7 +19792,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L261" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:311</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:342</x:v>
       </x:c>
       <x:c r="M261" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19840,7 +19840,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L262" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:315</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:346</x:v>
       </x:c>
       <x:c r="M262" s="9" t="str">
         <x:v>tm003-core-20261001T165439Z (source_check；产品E2E未运行)</x:v>
@@ -19889,7 +19889,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L263" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:319</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:350</x:v>
       </x:c>
       <x:c r="M263" s="4" t="str">
         <x:v>tm003-core-20261001T165439Z (source_check；产品E2E未运行)</x:v>
@@ -19937,7 +19937,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L264" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:323</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:354</x:v>
       </x:c>
       <x:c r="M264" s="9" t="str">
         <x:v>tm003-core-20261001T165439Z (source_check；产品E2E未运行)</x:v>
@@ -19946,127 +19946,130 @@
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="265" ht="87" customHeight="1">
+    <x:row r="265" ht="117" customHeight="1">
       <x:c r="A265" s="4" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B265" s="4" t="str">
+        <x:v>TC-TM003-CORE-04</x:v>
+      </x:c>
+      <x:c r="C265" s="4" t="str">
+        <x:v>同步批次原子提交与密钥标记</x:v>
+      </x:c>
+      <x:c r="D265" s="4" t="str">
+        <x:v>TASK-TM003-STORE</x:v>
+      </x:c>
+      <x:c r="E265" s="4" t="str">
+        <x:v>模块检查</x:v>
+      </x:c>
+      <x:c r="F265" s="4" t="str">
+        <x:v>header+A=410字节、补B=750字节；A100/10/cached20、B200/20/cached40；公开key1=00..1f及不同有效key2=20..3f；owner SQLite上的INSERT和UPDATE失败触发器</x:v>
+      </x:c>
+      <x:c r="G265" s="4" t="str">
+        <x:v>一行A，(count,input,output,cached)=(1,100,10,20)，total110，诊断0，cursor410，key1标记，scan_incomplete=1；重开不变
+批次失败且全回滚；仍仅A/total110/诊断0/cursor410/原MAC/key1标记/scan_incomplete=1；重开仍相同
+B仅新增一次；(2,300,30,60)、total330、invalid_record诊断1、cursor750及新MAC、scan_incomplete=0；重开不重计
+明确密钥标记不匹配并停采集；A/B两行/total330/诊断1/cursor750/覆盖/key1标记均不变，无key2重键或已知零</x:v>
+      </x:c>
+      <x:c r="H265" s="4" t="str">
+        <x:v>准备：新建本例owner SQLite；业务行只由模块API插入；步骤2在本例库创建两条失败触发器
+变化：步骤1 A+cursor/coverage/key标记原子提交；步骤2全回滚；步骤3 B+一诊断+cursor/coverage原子提交；步骤4不变
+核验：每步只读usage_event数量与SUM、collection_diagnostic代码数、source_cursor offset/prefix_mac、coverage.scan_incomplete、identity_key_state.key_marker；关闭重开复查；仅清理owner库</x:v>
+      </x:c>
+      <x:c r="I265" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J265" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K265" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L265" s="4" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:203</x:v>
+      </x:c>
+      <x:c r="M265" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N265" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="266" ht="117" customHeight="1">
+      <x:c r="A266" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B266" s="9" t="str">
+        <x:v>TC-TM003-CORE-05</x:v>
+      </x:c>
+      <x:c r="C266" s="9" t="str">
+        <x:v>追加、半行、前缀改写与截短游标</x:v>
+      </x:c>
+      <x:c r="D266" s="9" t="str">
+        <x:v>TASK-TM003-SCAN
+TASK-TM003-STORE</x:v>
+      </x:c>
+      <x:c r="E266" s="9" t="str">
+        <x:v>模块检查</x:v>
+      </x:c>
+      <x:c r="F266" s="9" t="str">
+        <x:v>fixture header+A410、+B750、+C1090；B半行；A.padding 0→1同长度原地改写且mtime不变；合成稳定文件身份恒定，可变快照digest随修改；公开key1</x:v>
+      </x:c>
+      <x:c r="G266" s="9" t="str">
+        <x:v>A一行total110，cursor410，保存对410字节prefixMAC及稳定身份，输出不含路径/正文/密钥
+B不提交；A一行total110，cursor410，前缀MAC相同，无cursor_reset
+只消费B/C；(count,input,output,cached)=(3,600,60,120)，total660，cursor1090，A不重计，无cursor_reset
+fixture新旧SHA不同；prefixMAC不符，cursor_reset且从0重扫；A/B/C唯一三行、total660、旧行不删，coverage.missing_before=1
+长度小于游标而从0重扫；历史A/B/C三行与total660保留；cursor410，coverage缺口为真，B/C不填零不删除</x:v>
+      </x:c>
+      <x:c r="H266" s="9" t="str">
+        <x:v>准备：新建owner文件/空SQLite；模块读取固定原始行；不访问TM-002目录能力
+变化：A/B/C仅通过正式模块API入库；追加推进完整LF游标；改写/截短重扫仅改变游标和覆盖缺口、不删可信旧行
+核验：只读按(principal_key,source,source_event_key)核对唯一三行及SUM、source_cursor offset/prefix_mac、coverage.missing_before、cursor_reset诊断；比较fixture新旧SHA/长度/mtime；结束仅清理owner资源</x:v>
+      </x:c>
+      <x:c r="I266" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J266" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K266" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L266" s="9" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:216</x:v>
+      </x:c>
+      <x:c r="M266" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N266" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="267" ht="87" customHeight="1">
+      <x:c r="A267" s="4" t="str">
         <x:v>TM-005</x:v>
       </x:c>
-      <x:c r="B265" s="4" t="str">
+      <x:c r="B267" s="4" t="str">
         <x:v>TC-TM005-CORE-01</x:v>
       </x:c>
-      <x:c r="C265" s="4" t="str">
+      <x:c r="C267" s="4" t="str">
         <x:v>双来源可信事件与半开日汇总</x:v>
       </x:c>
-      <x:c r="D265" s="4" t="str">
+      <x:c r="D267" s="4" t="str">
         <x:v>TASK-TM005-EVENT-CONTRACT
 TASK-TM005-RANGE-QUERY</x:v>
       </x:c>
-      <x:c r="E265" s="4" t="str">
+      <x:c r="E267" s="4" t="str">
         <x:v>模块检查</x:v>
       </x:c>
-      <x:c r="F265" s="4" t="str">
+      <x:c r="F267" s="4" t="str">
         <x:v>fixture的A/B、跨主体C、界外D/E；synthetic-p1、Asia/Shanghai当地日2026-09-29</x:v>
       </x:c>
-      <x:c r="G265" s="4" t="str">
+      <x:c r="G267" s="4" t="str">
         <x:v>1. 按固定主体和fixture固定UTC半开界查询纯统计函数，不做IANA日期换算；仅A/B被选、C/D/E排除；输入数组和键不变
 2. 核对来源、模型、Token和三个子项；input300/output30/total330；Codex110/Claude220；未知模型110/sonnet-test220；缓存读20但部分未知、缓存写未知、推理2但部分未知，子项不加总
 3. 逐个输入非法来源、负数、超范围缓存和坏UTC；各自被拒绝，无完整零或有效汇总输出；原fixture不变</x:v>
-      </x:c>
-      <x:c r="H265" s="4" t="str">
-        <x:v>准备：无产品DB写入；每例从新内存输入开始
-变化：不适用；纯统计返回值与输入未变
-核验：固定fixture摘要、事件筛选、各字段与状态逐步核对；无SQL</x:v>
-      </x:c>
-      <x:c r="I265" s="4" t="str">
-        <x:v>draft</x:v>
-      </x:c>
-      <x:c r="J265" s="4" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="K265" s="4" t="str">
-        <x:v>细化用例</x:v>
-      </x:c>
-      <x:c r="L265" s="4" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:326</x:v>
-      </x:c>
-      <x:c r="M265" s="4" t="str">
-        <x:v>尚未执行</x:v>
-      </x:c>
-      <x:c r="N265" s="4" t="str">
-        <x:v>v0.5.0-20261001T034729Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="266" ht="57" customHeight="1">
-      <x:c r="A266" s="9" t="str">
-        <x:v>TM-005</x:v>
-      </x:c>
-      <x:c r="B266" s="9" t="str">
-        <x:v>TC-TM005-CORE-02</x:v>
-      </x:c>
-      <x:c r="C266" s="9" t="str">
-        <x:v>未知用量诊断不补零</x:v>
-      </x:c>
-      <x:c r="D266" s="9" t="str">
-        <x:v>TASK-TM005-EVENT-CONTRACT
-TASK-TM005-COVERAGE</x:v>
-      </x:c>
-      <x:c r="E266" s="9" t="str">
-        <x:v>模块检查</x:v>
-      </x:c>
-      <x:c r="F266" s="9" t="str">
-        <x:v>fixture A/B及同范围Claude missing_usage诊断；双来源complete仅为模块合成覆盖假设</x:v>
-      </x:c>
-      <x:c r="G266" s="9" t="str">
-        <x:v>1. 先仅统计A/B；已知330，未知模型110保留，来源Codex110/Claude220
-2. 加入诊断重新统计；partial、known_tokens330、total_tokens=null；诊断不增调用或零Token
-3. 移除A/B仅保留诊断；unknown、known_tokens0、total_tokens=null，不能写已确认零</x:v>
-      </x:c>
-      <x:c r="H266" s="9" t="str">
-        <x:v>准备：无产品DB写入；每例从新内存输入开始
-变化：不适用；纯统计返回值与输入未变
-核验：固定fixture摘要、事件筛选、各字段与状态逐步核对；无SQL</x:v>
-      </x:c>
-      <x:c r="I266" s="9" t="str">
-        <x:v>draft</x:v>
-      </x:c>
-      <x:c r="J266" s="9" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="K266" s="9" t="str">
-        <x:v>细化用例</x:v>
-      </x:c>
-      <x:c r="L266" s="9" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:334</x:v>
-      </x:c>
-      <x:c r="M266" s="9" t="str">
-        <x:v>尚未执行</x:v>
-      </x:c>
-      <x:c r="N266" s="9" t="str">
-        <x:v>v0.5.0-20261001T034729Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="267" ht="87" customHeight="1">
-      <x:c r="A267" s="4" t="str">
-        <x:v>TM-005</x:v>
-      </x:c>
-      <x:c r="B267" s="4" t="str">
-        <x:v>TC-TM005-CORE-03</x:v>
-      </x:c>
-      <x:c r="C267" s="4" t="str">
-        <x:v>声明式覆盖状态代数</x:v>
-      </x:c>
-      <x:c r="D267" s="4" t="str">
-        <x:v>TASK-TM005-COVERAGE</x:v>
-      </x:c>
-      <x:c r="E267" s="4" t="str">
-        <x:v>模块检查</x:v>
-      </x:c>
-      <x:c r="F267" s="4" t="str">
-        <x:v>fixture五行coverage_algebra；complete仅为模块合成输入，product_coverage_proven=false</x:v>
-      </x:c>
-      <x:c r="G267" s="4" t="str">
-        <x:v>1. 两来源complete且无事件、随后移除覆盖事实；前者complete/known0/total0；后者不得自行推断complete
-2. 一来源missing，分别给空事件与可信110；空事件missing/known0/total null；可信110为partial/known110/total null
-3. 两来源complete，分别给可信110+未知诊断、仅未知诊断；前者partial/known110/total null；后者unknown/known0/total null</x:v>
       </x:c>
       <x:c r="H267" s="4" t="str">
         <x:v>准备：无产品DB写入；每例从新内存输入开始
@@ -20083,7 +20086,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L267" s="4" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:342</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:326</x:v>
       </x:c>
       <x:c r="M267" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -20092,126 +20095,126 @@
         <x:v>v0.5.0-20261001T034729Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="268" ht="72" customHeight="1">
+    <x:row r="268" ht="57" customHeight="1">
       <x:c r="A268" s="9" t="str">
-        <x:v>TM-004</x:v>
+        <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B268" s="9" t="str">
-        <x:v>TC-TM004-CORE-01</x:v>
+        <x:v>TC-TM005-CORE-02</x:v>
       </x:c>
       <x:c r="C268" s="9" t="str">
-        <x:v>完整LF、半行与限额续读</x:v>
+        <x:v>未知用量诊断不补零</x:v>
       </x:c>
       <x:c r="D268" s="9" t="str">
-        <x:v>TASK-TM004-INCREMENTAL</x:v>
+        <x:v>TASK-TM005-EVENT-CONTRACT
+TASK-TM005-COVERAGE</x:v>
       </x:c>
       <x:c r="E268" s="9" t="str">
         <x:v>模块检查</x:v>
       </x:c>
       <x:c r="F268" s="9" t="str">
+        <x:v>fixture A/B及同范围Claude missing_usage诊断；双来源complete仅为模块合成覆盖假设</x:v>
+      </x:c>
+      <x:c r="G268" s="9" t="str">
+        <x:v>1. 先仅统计A/B；已知330，未知模型110保留，来源Codex110/Claude220
+2. 加入诊断重新统计；partial、known_tokens330、total_tokens=null；诊断不增调用或零Token
+3. 移除A/B仅保留诊断；unknown、known_tokens0、total_tokens=null，不能写已确认零</x:v>
+      </x:c>
+      <x:c r="H268" s="9" t="str">
+        <x:v>准备：无产品DB写入；每例从新内存输入开始
+变化：不适用；纯统计返回值与输入未变
+核验：固定fixture摘要、事件筛选、各字段与状态逐步核对；无SQL</x:v>
+      </x:c>
+      <x:c r="I268" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J268" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K268" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L268" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:334</x:v>
+      </x:c>
+      <x:c r="M268" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N268" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="269" ht="87" customHeight="1">
+      <x:c r="A269" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B269" s="4" t="str">
+        <x:v>TC-TM005-CORE-03</x:v>
+      </x:c>
+      <x:c r="C269" s="4" t="str">
+        <x:v>声明式覆盖状态代数</x:v>
+      </x:c>
+      <x:c r="D269" s="4" t="str">
+        <x:v>TASK-TM005-COVERAGE</x:v>
+      </x:c>
+      <x:c r="E269" s="4" t="str">
+        <x:v>模块检查</x:v>
+      </x:c>
+      <x:c r="F269" s="4" t="str">
+        <x:v>fixture五行coverage_algebra；complete仅为模块合成输入，product_coverage_proven=false</x:v>
+      </x:c>
+      <x:c r="G269" s="4" t="str">
+        <x:v>1. 两来源complete且无事件、随后移除覆盖事实；前者complete/known0/total0；后者不得自行推断complete
+2. 一来源missing，分别给空事件与可信110；空事件missing/known0/total null；可信110为partial/known110/total null
+3. 两来源complete，分别给可信110+未知诊断、仅未知诊断；前者partial/known110/total null；后者unknown/known0/total null</x:v>
+      </x:c>
+      <x:c r="H269" s="4" t="str">
+        <x:v>准备：无产品DB写入；每例从新内存输入开始
+变化：不适用；纯统计返回值与输入未变
+核验：固定fixture摘要、事件筛选、各字段与状态逐步核对；无SQL</x:v>
+      </x:c>
+      <x:c r="I269" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J269" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K269" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L269" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:342</x:v>
+      </x:c>
+      <x:c r="M269" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N269" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="270" ht="72" customHeight="1">
+      <x:c r="A270" s="9" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="B270" s="9" t="str">
+        <x:v>TC-TM004-CORE-01</x:v>
+      </x:c>
+      <x:c r="C270" s="9" t="str">
+        <x:v>完整LF、半行与限额续读</x:v>
+      </x:c>
+      <x:c r="D270" s="9" t="str">
+        <x:v>TASK-TM004-INCREMENTAL</x:v>
+      </x:c>
+      <x:c r="E270" s="9" t="str">
+        <x:v>模块检查</x:v>
+      </x:c>
+      <x:c r="F270" s="9" t="str">
         <x:v>固定746字节13/7 assistant行、前半字节、两条不同ID完整行、首读上限754字节</x:v>
       </x:c>
-      <x:c r="G268" s="9" t="str">
+      <x:c r="G270" s="9" t="str">
         <x:v>1. 读未写完的前半行；调用0、偏移0、scanIncomplete=true，不作可信零结论
 2. 补齐LF、重复读取；补齐后一次13/7=20、偏移746、前缀MAC匹配；重复读取0调用且游标不变
 3. 两完整行首读754字节后续读；首读只第一条、偏移746、read_limit且未完成；续读只第二条、偏移为总字节长、完成</x:v>
-      </x:c>
-      <x:c r="H268" s="9" t="str">
-        <x:v>准备：无产品DB；每例新建自有临时文件
-变化：不适用；只返回模块调用、诊断与游标
-核验：固定fixture/行摘要和逐步返回值、前缀MAC及失败时无新游标；无SQL</x:v>
-      </x:c>
-      <x:c r="I268" s="9" t="str">
-        <x:v>draft</x:v>
-      </x:c>
-      <x:c r="J268" s="9" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="K268" s="9" t="str">
-        <x:v>细化用例</x:v>
-      </x:c>
-      <x:c r="L268" s="9" t="str">
-        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:170</x:v>
-      </x:c>
-      <x:c r="M268" s="9" t="str">
-        <x:v>尚未执行</x:v>
-      </x:c>
-      <x:c r="N268" s="9" t="str">
-        <x:v>v0.4.0-20261001T040433Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="269" ht="72" customHeight="1">
-      <x:c r="A269" s="4" t="str">
-        <x:v>TM-004</x:v>
-      </x:c>
-      <x:c r="B269" s="4" t="str">
-        <x:v>TC-TM004-CORE-02</x:v>
-      </x:c>
-      <x:c r="C269" s="4" t="str">
-        <x:v>前缀MAC、变更和密钥失败</x:v>
-      </x:c>
-      <x:c r="D269" s="4" t="str">
-        <x:v>TASK-TM004-INCREMENTAL</x:v>
-      </x:c>
-      <x:c r="E269" s="4" t="str">
-        <x:v>模块检查</x:v>
-      </x:c>
-      <x:c r="F269" s="4" t="str">
-        <x:v>已提交首行，追加不同ID第二行、同长度ID改写并复原mtime、截短、身份改变、秘密缺失或错误</x:v>
-      </x:c>
-      <x:c r="G269" s="4" t="str">
-        <x:v>1. 首行后追加第二完整行；快照digest变化但稳定身份/前缀MAC相同，续读只第二调用，无cursor_reset
-2. 同长度前缀改写、截短及稳定身份变更；分别报cursor_reset并从0重扫；同inode/size/mtime也不能忽略MAC不符
-3. 秘密无效或读中源变化；拒绝且没有可提交新游标/可信调用/成功零；输出不含路径正文秘密</x:v>
-      </x:c>
-      <x:c r="H269" s="4" t="str">
-        <x:v>准备：无产品DB；每例新建自有临时文件
-变化：不适用；只返回模块调用、诊断与游标
-核验：固定fixture/行摘要和逐步返回值、前缀MAC及失败时无新游标；无SQL</x:v>
-      </x:c>
-      <x:c r="I269" s="4" t="str">
-        <x:v>draft</x:v>
-      </x:c>
-      <x:c r="J269" s="4" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="K269" s="4" t="str">
-        <x:v>细化用例</x:v>
-      </x:c>
-      <x:c r="L269" s="4" t="str">
-        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:178</x:v>
-      </x:c>
-      <x:c r="M269" s="4" t="str">
-        <x:v>尚未执行</x:v>
-      </x:c>
-      <x:c r="N269" s="4" t="str">
-        <x:v>v0.4.0-20261001T040433Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="270" ht="57" customHeight="1">
-      <x:c r="A270" s="9" t="str">
-        <x:v>TM-004</x:v>
-      </x:c>
-      <x:c r="B270" s="9" t="str">
-        <x:v>TC-TM004-CORE-03</x:v>
-      </x:c>
-      <x:c r="C270" s="9" t="str">
-        <x:v>损坏完整行与未知结构</x:v>
-      </x:c>
-      <x:c r="D270" s="9" t="str">
-        <x:v>TASK-TM004-PARSER
-TASK-TM004-INCREMENTAL</x:v>
-      </x:c>
-      <x:c r="E270" s="9" t="str">
-        <x:v>模块检查</x:v>
-      </x:c>
-      <x:c r="F270" s="9" t="str">
-        <x:v>固定13/7行前置非法UTF8完整行和版本2.1.127完整行，尾部再追加无LF坏字节</x:v>
-      </x:c>
-      <x:c r="G270" s="9" t="str">
-        <x:v>1. 读三条完整LF行；仅合法2.1.126一条调用13/7=20；invalid_utf8及unsupported_version各一次
-2. 核对游标、重复读取及隐私；游标到三行LF末，MAC匹配且完成；重复读取0；输出无路径、正文、秘密
-3. 追加无LF坏字节再补LF；未补LF前偏移不动且未完成；补LF后仅诊断推进，无伪调用</x:v>
       </x:c>
       <x:c r="H270" s="9" t="str">
         <x:v>准备：无产品DB；每例新建自有临时文件
@@ -20228,7 +20231,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L270" s="9" t="str">
-        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:186</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:170</x:v>
       </x:c>
       <x:c r="M270" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -20237,30 +20240,127 @@
         <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
     </x:row>
+    <x:row r="271" ht="72" customHeight="1">
+      <x:c r="A271" s="4" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="B271" s="4" t="str">
+        <x:v>TC-TM004-CORE-02</x:v>
+      </x:c>
+      <x:c r="C271" s="4" t="str">
+        <x:v>前缀MAC、变更和密钥失败</x:v>
+      </x:c>
+      <x:c r="D271" s="4" t="str">
+        <x:v>TASK-TM004-INCREMENTAL</x:v>
+      </x:c>
+      <x:c r="E271" s="4" t="str">
+        <x:v>模块检查</x:v>
+      </x:c>
+      <x:c r="F271" s="4" t="str">
+        <x:v>已提交首行，追加不同ID第二行、同长度ID改写并复原mtime、截短、身份改变、秘密缺失或错误</x:v>
+      </x:c>
+      <x:c r="G271" s="4" t="str">
+        <x:v>1. 首行后追加第二完整行；快照digest变化但稳定身份/前缀MAC相同，续读只第二调用，无cursor_reset
+2. 同长度前缀改写、截短及稳定身份变更；分别报cursor_reset并从0重扫；同inode/size/mtime也不能忽略MAC不符
+3. 秘密无效或读中源变化；拒绝且没有可提交新游标/可信调用/成功零；输出不含路径正文秘密</x:v>
+      </x:c>
+      <x:c r="H271" s="4" t="str">
+        <x:v>准备：无产品DB；每例新建自有临时文件
+变化：不适用；只返回模块调用、诊断与游标
+核验：固定fixture/行摘要和逐步返回值、前缀MAC及失败时无新游标；无SQL</x:v>
+      </x:c>
+      <x:c r="I271" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J271" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K271" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L271" s="4" t="str">
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:178</x:v>
+      </x:c>
+      <x:c r="M271" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N271" s="4" t="str">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="272" ht="57" customHeight="1">
+      <x:c r="A272" s="9" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="B272" s="9" t="str">
+        <x:v>TC-TM004-CORE-03</x:v>
+      </x:c>
+      <x:c r="C272" s="9" t="str">
+        <x:v>损坏完整行与未知结构</x:v>
+      </x:c>
+      <x:c r="D272" s="9" t="str">
+        <x:v>TASK-TM004-PARSER
+TASK-TM004-INCREMENTAL</x:v>
+      </x:c>
+      <x:c r="E272" s="9" t="str">
+        <x:v>模块检查</x:v>
+      </x:c>
+      <x:c r="F272" s="9" t="str">
+        <x:v>固定13/7行前置非法UTF8完整行和版本2.1.127完整行，尾部再追加无LF坏字节</x:v>
+      </x:c>
+      <x:c r="G272" s="9" t="str">
+        <x:v>1. 读三条完整LF行；仅合法2.1.126一条调用13/7=20；invalid_utf8及unsupported_version各一次
+2. 核对游标、重复读取及隐私；游标到三行LF末，MAC匹配且完成；重复读取0；输出无路径、正文、秘密
+3. 追加无LF坏字节再补LF；未补LF前偏移不动且未完成；补LF后仅诊断推进，无伪调用</x:v>
+      </x:c>
+      <x:c r="H272" s="9" t="str">
+        <x:v>准备：无产品DB；每例新建自有临时文件
+变化：不适用；只返回模块调用、诊断与游标
+核验：固定fixture/行摘要和逐步返回值、前缀MAC及失败时无新游标；无SQL</x:v>
+      </x:c>
+      <x:c r="I272" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J272" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K272" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L272" s="9" t="str">
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:186</x:v>
+      </x:c>
+      <x:c r="M272" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N272" s="9" t="str">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G5:G270">
+  <x:conditionalFormatting sqref="G5:G272">
     <x:cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="I5:I270">
+  <x:conditionalFormatting sqref="I5:I272">
     <x:cfRule type="containsText" dxfId="15" priority="4" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="17" priority="6" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="J5:J270">
+  <x:conditionalFormatting sqref="J5:J272">
     <x:cfRule type="containsText" dxfId="18" priority="7" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="19" priority="8" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="20" priority="9" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="M5:M270">
+  <x:conditionalFormatting sqref="M5:M272">
     <x:cfRule type="containsText" dxfId="21" priority="10" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="22" priority="11" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="23" priority="12" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53d132cdb12b4b3f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b5bad41f7cb43fa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21012,7 +21112,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf5d2095136964585"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1c226c53dd74dcc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21270,7 +21370,7 @@
         <x:v>releases/v0.2.0-20261001T034118Z/01-requirements.md:32</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="297" customHeight="1">
+    <x:row r="8" ht="342" customHeight="1">
       <x:c r="A8" s="9" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
@@ -21299,7 +21399,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J8" s="9" t="str">
-        <x:v>整版draft、未发布。27条产品TC未执行；3条CORE辅助TC已在文档提交48ca089独立切片就绪，在开发分支311deedf运行模块3/3 PASS，原始receipt在该分支.local/ci/tm003-core-20261001/。代码尚未合入本文档树，机器绑定保持空；模块报告不能作为产品E2E或发行门禁，结果Excel规范待SOP修订。 2026-10-02新代码候选44379e6已有逐步模块3/3与桌面29/29/typecheck/build原件；source_check独立Excel导出程序仍缺，批次登记BLOCKED，产品E2E仍NOT_RUN。 固定导出器新run tm003-core-20261001T163807Z在ea6b187候选生成3/3/9步source_check独立Excel并回读PASS，现已按被测SHA登记模块批次；原27条产品TC与发行仍NOT_RUN。 新清理合同候选d7c3d39的独立run tm003-core-20261001T165439Z亦3/3/9步及Excel回读PASS，作为最新模块批次；旧ea6批次保留。</x:v>
+        <x:v>整版draft、未发布。27条产品TC未执行；3条CORE辅助TC已在文档提交48ca089独立切片就绪，在开发分支311deedf运行模块3/3 PASS，原始receipt在该分支.local/ci/tm003-core-20261001/。代码尚未合入本文档树，机器绑定保持空；模块报告不能作为产品E2E或发行门禁，结果Excel规范待SOP修订。 2026-10-02新代码候选44379e6已有逐步模块3/3与桌面29/29/typecheck/build原件；source_check独立Excel导出程序仍缺，批次登记BLOCKED，产品E2E仍NOT_RUN。 固定导出器新run tm003-core-20261001T163807Z在ea6b187候选生成3/3/9步source_check独立Excel并回读PASS，现已按被测SHA登记模块批次；原27条产品TC与发行仍NOT_RUN。 新清理合同候选d7c3d39的独立run tm003-core-20261001T165439Z亦3/3/9步及Excel回读PASS，作为最新模块批次；旧ea6批次保留。 后续CORE-04/05的测试输入已编制，程序未绑定、未执行；独立SOP-008切片复核待文档干净提交。</x:v>
       </x:c>
       <x:c r="K8" s="9" t="str">
         <x:v>TM-001 干净源码候选为技术基底；其产品门禁不继承给TM-003</x:v>
@@ -21456,7 +21556,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22babf438e234005"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4158954b7951482d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22621,7 +22721,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3f8606679304557"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf359d27351742cf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TokenMeter项目总表.xlsx
+++ b/TokenMeter项目总表.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R7bcf00d865dd4eb0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="R156bab950efc4f5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="Rc9c5081c5e674fc5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="Rf6b5cfbd3ec349c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R85fc27840feb49b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R4a1341aeefab4aac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="Rd777e0187db64e0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R4a3ebf10cd5f4340"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="R7016dc8cac4844f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R999fe6c93ae14b6c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="Rdeebd0e96c5f4903"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R0af57b27871f4093"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Rc785ec2bd08349ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R9da2d755809c4ca2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="Rf609cc11a3c14d1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R6bf838a9f9584f80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R379f8348e51344d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R3518c44d508c4867"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R29618a27bc994739"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Rff51e22708124cb7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="Rd9e1c0f3ca2f432e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R36c8450f06cd4cc9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -809,8 +809,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TMTable7" displayName="TMTable7" ref="A4:N19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:N19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TMTable7" displayName="TMTable7" ref="A4:N20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:N20"/>
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="运行批次"/>
     <x:tableColumn id="2" name="版本"/>
@@ -1146,8 +1146,8 @@
         <x:v>测试批次</x:v>
       </x:c>
       <x:c r="B9" s="10" t="n">
-        <x:f>COUNTA('06测试批次'!A5:A19)</x:f>
-        <x:v>15</x:v>
+        <x:f>COUNTA('06测试批次'!A5:A20)</x:f>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C9" s="4" t="str">
         <x:v>06测试批次，每次运行一行，记录独立结果Excel位置</x:v>
@@ -1271,7 +1271,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="C20" s="9" t="str">
-        <x:v>source_check · TM-003 CORE-01/02/03 固定模块验证；非产品E2E：共享source_check清理合同扩展后的新候选：CORE固定3/3、九步PASS，owned_root清理逐例PASS；独立Excel/verification回读PASS。旧ea6b187批次保留；原27条产品TC与正式发行仍NOT_RUN。；是否覆盖完整产品回归以批次范围和原始证据为准。</x:v>
+        <x:v>product_e2e · granular_targeted_probe；仅TC-TM001-UPDATE-05父例及13固定变体：UPDATE-05父例1 PASS、13固定变体13 PASS、26逐步记录，77条TM001父例范围外；清理完成。仅709d候选定向探针，不覆盖旧c291完整门禁FAIL或授予发行资格；Excel为后置de081a6导出修复从原报告生成，非重跑App。；是否覆盖完整产品回归以批次范围和原始证据为准。</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="32" customHeight="1">
@@ -1288,7 +1288,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45392368bbda4a2d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb45b5bde48c74523"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1996,7 +1996,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19b2f7e0dda74ebc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06bc7c770cc6441a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2145,7 +2145,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6300d3a562d543fa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R897949901cd54d89"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2580,7 +2580,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8eb61670ecc40d7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra14f9d99992246ea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3627,7 +3627,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra55d6dc8b0a34b63"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2770688113524adb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4734,7 +4734,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd5e4f1c98b7d43cb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d1f5a873b2c4094"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7519,7 +7519,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R168a1387b8454b44"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57f30b7f7d394d9c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10661,7 +10661,7 @@
         <x:v>已设计</x:v>
       </x:c>
       <x:c r="J68" s="9" t="str">
-        <x:v>FAIL</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="K68" s="9" t="str">
         <x:v>细化用例</x:v>
@@ -10670,7 +10670,7 @@
         <x:v>docs/testing/cases/01b-TM-001-session-admin-release-scenarios.md:609</x:v>
       </x:c>
       <x:c r="M68" s="9" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-65796d0033704e3988cd7174dec93c81 (仅定向探针；完整门禁仍FAIL)</x:v>
       </x:c>
       <x:c r="N68" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -20360,7 +20360,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b5bad41f7cb43fa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15026631cc374e50"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21094,25 +21094,69 @@
         <x:v>NOT_RUN</x:v>
       </x:c>
     </x:row>
+    <x:row r="20" ht="57" customHeight="1">
+      <x:c r="A20" s="9" t="str">
+        <x:v>local-65796d0033704e3988cd7174dec93c81</x:v>
+      </x:c>
+      <x:c r="B20" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+      <x:c r="C20" s="9" t="str">
+        <x:v>product_e2e</x:v>
+      </x:c>
+      <x:c r="D20" s="9" t="str">
+        <x:v>granular_targeted_probe；仅TC-TM001-UPDATE-05父例及13固定变体</x:v>
+      </x:c>
+      <x:c r="E20" s="9" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F20" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G20" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H20" s="9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I20" s="9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J20" s="9" t="str">
+        <x:v>709d21253a0f88bc703a431cbf3adba3df17e508</x:v>
+      </x:c>
+      <x:c r="K20" s="9" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="L20" s="9" t="str">
+        <x:v>UPDATE-05父例1 PASS、13固定变体13 PASS、26逐步记录，77条TM001父例范围外；清理完成。仅709d候选定向探针，不覆盖旧c291完整门禁FAIL或授予发行资格；Excel为后置de081a6导出修复从原报告生成，非重跑App。</x:v>
+      </x:c>
+      <x:c r="M20" s="9" t="str">
+        <x:v>.local/test-results/local-65796d0033704e3988cd7174dec93c81/TokenMeter测试结果-local-65796d0033704e3988cd7174dec93c81.xlsx</x:v>
+      </x:c>
+      <x:c r="N20" s="9" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="E5:E19">
+  <x:conditionalFormatting sqref="E5:E20">
     <x:cfRule type="containsText" dxfId="24" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="25" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="26" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="M5:M19">
+  <x:conditionalFormatting sqref="M5:M20">
     <x:cfRule type="containsText" dxfId="27" priority="4" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="28" priority="5" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="29" priority="6" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="N5:N19">
+  <x:conditionalFormatting sqref="N5:N20">
     <x:cfRule type="containsText" dxfId="30" priority="7" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="31" priority="8" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="32" priority="9" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1c226c53dd74dcc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46c847e7fec346f4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21258,7 +21302,7 @@
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="117" customHeight="1">
+    <x:row r="6" ht="177" customHeight="1">
       <x:c r="A6" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
       </x:c>
@@ -21287,7 +21331,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J6" s="9" t="str">
-        <x:v>开发中，未发布。c291本地master最终包门禁FAIL：116项91 PASS/14 FAIL/11 BLOCKED；9f06cb1修复私有签名输入后开发检查PASS，但新定向App仍FAIL/BLOCKED并有ENOSPC，功能回归未完成。旧d2db551独立候选PASS不转用于新候选。正式发行完整门禁NOT_RUN，无稳定0.1原包。</x:v>
+        <x:v>开发中，未发布。c291本地master最终包门禁FAIL：116项91 PASS/14 FAIL/11 BLOCKED；9f06cb1修复私有签名输入后开发检查PASS，但新定向App仍FAIL/BLOCKED并有ENOSPC，功能回归未完成。旧d2db551独立候选PASS不转用于新候选。正式发行完整门禁NOT_RUN，无稳定0.1原包。 709d UPDATE-05定向父1+变体13 PASS，后置de081a6导出Excel回读PASS；仅定向，77父TC范围外，旧c291完整门禁FAIL及未发行不变。</x:v>
       </x:c>
       <x:c r="K6" s="9" t="str">
         <x:v>旧SwiftUI PR #2 已合并、历史双平台六例PASS；不继承给Electron</x:v>
@@ -21556,7 +21600,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4158954b7951482d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6453414550ec48c7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22721,7 +22765,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf359d27351742cf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra37c7c299a6c4c35"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TokenMeter项目总表.xlsx
+++ b/TokenMeter项目总表.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R0af57b27871f4093"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Rc785ec2bd08349ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R9da2d755809c4ca2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="Rf609cc11a3c14d1d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R6bf838a9f9584f80"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R379f8348e51344d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R3518c44d508c4867"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R29618a27bc994739"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Rff51e22708124cb7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="Rd9e1c0f3ca2f432e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R36c8450f06cd4cc9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="Rbde94a1a5ca34e1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="R284aa9f88a2e4034"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="Rc25a6238ae194d71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="Rcc997e240d914aa6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R08667b0399ca47da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R48cbdec366684311"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="Rf5c7c974eace4aa0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="Rf8cb85b19dcf4653"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="R50a4e122758c41f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R57a9fa2ad59a4f1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R0b814b45870a4298"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -786,8 +786,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TMTable6" displayName="TMTable6" ref="A4:N272" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:N272"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TMTable6" displayName="TMTable6" ref="A4:N273" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:N273"/>
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="功能编号"/>
     <x:tableColumn id="2" name="用例编号"/>
@@ -1134,8 +1134,8 @@
         <x:v>已登记用例</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:f>COUNTA('05测试用例'!B5:B272)</x:f>
-        <x:v>268</x:v>
+        <x:f>COUNTA('05测试用例'!B5:B273)</x:f>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C8" s="9" t="str">
         <x:v>父用例与具有稳定 ID 的变体各占一行；含未来概要场景</x:v>
@@ -1169,7 +1169,7 @@
         <x:v>界面与治理检查</x:v>
       </x:c>
       <x:c r="B11" s="10" t="n">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C11" s="4" t="str">
         <x:v>辅助检查不能替代产品E2E；稳定变体独立列出</x:v>
@@ -1288,7 +1288,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb45b5bde48c74523"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6034ed23f6dd49f9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1996,7 +1996,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06bc7c770cc6441a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8da03928fcd14244"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2145,7 +2145,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R897949901cd54d89"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9c873e73bb3444f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2580,7 +2580,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra14f9d99992246ea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76cc21639a444669"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3627,7 +3627,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2770688113524adb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc99b01a21c74a59"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4734,7 +4734,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d1f5a873b2c4094"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48b80fb90b69440a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7519,7 +7519,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57f30b7f7d394d9c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3fc4ce55b6b4ada"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13434,7 +13434,7 @@
         <x:v>ABSOLUTE/FILE_URL/DOTDOT/TOKEN均调用previewSource.selectionId，返回snapshot.error=invalid_selection且不打开A/B、无来源状态变化；竞态变体沿既定屏障判据。</x:v>
       </x:c>
       <x:c r="H127" s="4" t="str">
-        <x:v>准备：七变体各自短根R=/tmp/t2-&lt;8位十六进制&gt;、A/B/profile及owner marker；恶意字串≤64，实际业务previewSource IPC、受控异步屏障和隔离文件；无服务/DB，SQL不适用。
+        <x:v>准备：七变体各自短根R=/tmp/t2-&lt;8位十六进制&gt;、R只放A/B；profile在独立realpath化的用户私有0700临时目录；owner marker；恶意字串≤64，实际业务previewSource IPC、受控异步屏障和隔离文件；无服务/DB，SQL不适用。
 变化：不适用：辅助检查不写服务业务库。
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
@@ -13457,7 +13457,7 @@
         <x:v>v0.2.0-20261001T034118Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="128" ht="72" customHeight="1">
+    <x:row r="128" ht="87" customHeight="1">
       <x:c r="A128" s="9" t="str">
         <x:v>TM-002</x:v>
       </x:c>
@@ -13480,7 +13480,7 @@
         <x:v>snapshot.error=invalid_selection；无pending/confirmed变化，不返回路径/locator/正文；A/B open/read=0、B metadata=0</x:v>
       </x:c>
       <x:c r="H128" s="9" t="str">
-        <x:v>准备：七变体各自短根R=/tmp/t2-&lt;8位十六进制&gt;、A/B/profile及owner marker；恶意字串≤64，实际业务previewSource IPC、受控异步屏障和隔离文件；无服务/DB，SQL不适用。
+        <x:v>准备：七变体各自短根R=/tmp/t2-&lt;8位十六进制&gt;、R只放A/B；profile在独立realpath化的用户私有0700临时目录；owner marker；恶意字串≤64，实际业务previewSource IPC、受控异步屏障和隔离文件；无服务/DB，SQL不适用。
 变化：不适用：辅助检查不写服务业务库。
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
@@ -13503,7 +13503,7 @@
         <x:v>v0.2.0-20261001T034118Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="129" ht="72" customHeight="1">
+    <x:row r="129" ht="87" customHeight="1">
       <x:c r="A129" s="4" t="str">
         <x:v>TM-002</x:v>
       </x:c>
@@ -13526,7 +13526,7 @@
         <x:v>snapshot.error=invalid_selection；无pending/confirmed变化，不返回路径/locator/正文；A/B open/read=0、B metadata=0</x:v>
       </x:c>
       <x:c r="H129" s="4" t="str">
-        <x:v>准备：七变体各自短根R=/tmp/t2-&lt;8位十六进制&gt;、A/B/profile及owner marker；恶意字串≤64，实际业务previewSource IPC、受控异步屏障和隔离文件；无服务/DB，SQL不适用。
+        <x:v>准备：七变体各自短根R=/tmp/t2-&lt;8位十六进制&gt;、R只放A/B；profile在独立realpath化的用户私有0700临时目录；owner marker；恶意字串≤64，实际业务previewSource IPC、受控异步屏障和隔离文件；无服务/DB，SQL不适用。
 变化：不适用：辅助检查不写服务业务库。
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
@@ -13549,7 +13549,7 @@
         <x:v>v0.2.0-20261001T034118Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="130" ht="72" customHeight="1">
+    <x:row r="130" ht="87" customHeight="1">
       <x:c r="A130" s="9" t="str">
         <x:v>TM-002</x:v>
       </x:c>
@@ -13572,7 +13572,7 @@
         <x:v>snapshot.error=invalid_selection；无pending/confirmed变化，不返回路径/locator/正文；A/B open/read=0、B metadata=0</x:v>
       </x:c>
       <x:c r="H130" s="9" t="str">
-        <x:v>准备：七变体各自短根R=/tmp/t2-&lt;8位十六进制&gt;、A/B/profile及owner marker；恶意字串≤64，实际业务previewSource IPC、受控异步屏障和隔离文件；无服务/DB，SQL不适用。
+        <x:v>准备：七变体各自短根R=/tmp/t2-&lt;8位十六进制&gt;、R只放A/B；profile在独立realpath化的用户私有0700临时目录；owner marker；恶意字串≤64，实际业务previewSource IPC、受控异步屏障和隔离文件；无服务/DB，SQL不适用。
 变化：不适用：辅助检查不写服务业务库。
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
@@ -13595,7 +13595,7 @@
         <x:v>v0.2.0-20261001T034118Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="131" ht="72" customHeight="1">
+    <x:row r="131" ht="87" customHeight="1">
       <x:c r="A131" s="4" t="str">
         <x:v>TM-002</x:v>
       </x:c>
@@ -13618,7 +13618,7 @@
         <x:v>主进程安全拒绝，不返回内容、绝对路径或 locator；B 元数据/open/read=0，sources 无确认记录。</x:v>
       </x:c>
       <x:c r="H131" s="4" t="str">
-        <x:v>准备：七变体各自短根R=/tmp/t2-&lt;8位十六进制&gt;、A/B/profile及owner marker；恶意字串≤64，实际业务previewSource IPC、受控异步屏障和隔离文件；无服务/DB，SQL不适用。
+        <x:v>准备：七变体各自短根R=/tmp/t2-&lt;8位十六进制&gt;、R只放A/B；profile在独立realpath化的用户私有0700临时目录；owner marker；恶意字串≤64，实际业务previewSource IPC、受控异步屏障和隔离文件；无服务/DB，SQL不适用。
 变化：不适用：辅助检查不写服务业务库。
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
@@ -13641,7 +13641,7 @@
         <x:v>v0.2.0-20261001T034118Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="132" ht="72" customHeight="1">
+    <x:row r="132" ht="87" customHeight="1">
       <x:c r="A132" s="9" t="str">
         <x:v>TM-002</x:v>
       </x:c>
@@ -13664,7 +13664,7 @@
         <x:v>旧 Alice 结果拒绝，Bob 不得建暂选/确认 A；Alice/Bob 无新增来源，A/B 零读取。</x:v>
       </x:c>
       <x:c r="H132" s="9" t="str">
-        <x:v>准备：七变体各自短根R=/tmp/t2-&lt;8位十六进制&gt;、A/B/profile及owner marker；恶意字串≤64，实际业务previewSource IPC、受控异步屏障和隔离文件；无服务/DB，SQL不适用。
+        <x:v>准备：七变体各自短根R=/tmp/t2-&lt;8位十六进制&gt;、R只放A/B；profile在独立realpath化的用户私有0700临时目录；owner marker；恶意字串≤64，实际业务previewSource IPC、受控异步屏障和隔离文件；无服务/DB，SQL不适用。
 变化：不适用：辅助检查不写服务业务库。
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
@@ -13687,7 +13687,7 @@
         <x:v>v0.2.0-20261001T034118Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="133" ht="72" customHeight="1">
+    <x:row r="133" ht="87" customHeight="1">
       <x:c r="A133" s="4" t="str">
         <x:v>TM-002</x:v>
       </x:c>
@@ -13710,7 +13710,7 @@
         <x:v>撤销删密文和读取能力，旧 Promise 不提交候选或 complete=true；撤销后 A/B 后续操作为零。</x:v>
       </x:c>
       <x:c r="H133" s="4" t="str">
-        <x:v>准备：七变体各自短根R=/tmp/t2-&lt;8位十六进制&gt;、A/B/profile及owner marker；恶意字串≤64，实际业务previewSource IPC、受控异步屏障和隔离文件；无服务/DB，SQL不适用。
+        <x:v>准备：七变体各自短根R=/tmp/t2-&lt;8位十六进制&gt;、R只放A/B；profile在独立realpath化的用户私有0700临时目录；owner marker；恶意字串≤64，实际业务previewSource IPC、受控异步屏障和隔离文件；无服务/DB，SQL不适用。
 变化：不适用：辅助检查不写服务业务库。
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
@@ -13733,7 +13733,7 @@
         <x:v>v0.2.0-20261001T034118Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="134" ht="72" customHeight="1">
+    <x:row r="134" ht="87" customHeight="1">
       <x:c r="A134" s="9" t="str">
         <x:v>TM-002</x:v>
       </x:c>
@@ -13756,7 +13756,7 @@
         <x:v>Bob 不得见旧 Alice 候选或得到来源；切换后 A/B 后续零访问；Bob 请求 Alice 来源 ID 被拒绝。</x:v>
       </x:c>
       <x:c r="H134" s="9" t="str">
-        <x:v>准备：七变体各自短根R=/tmp/t2-&lt;8位十六进制&gt;、A/B/profile及owner marker；恶意字串≤64，实际业务previewSource IPC、受控异步屏障和隔离文件；无服务/DB，SQL不适用。
+        <x:v>准备：七变体各自短根R=/tmp/t2-&lt;8位十六进制&gt;、R只放A/B；profile在独立realpath化的用户私有0700临时目录；owner marker；恶意字串≤64，实际业务previewSource IPC、受控异步屏障和隔离文件；无服务/DB，SQL不适用。
 变化：不适用：辅助检查不写服务业务库。
 核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
       </x:c>
@@ -14013,7 +14013,7 @@
         <x:v>v0.2.0-20261001T034118Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="140" ht="132" customHeight="1">
+    <x:row r="140" ht="162" customHeight="1">
       <x:c r="A140" s="9" t="str">
         <x:v>TM-002</x:v>
       </x:c>
@@ -14030,11 +14030,11 @@
         <x:v>治理检查</x:v>
       </x:c>
       <x:c r="F140" s="9" t="str">
-        <x:v>固定程序只在本例私有目录生成合成原始报告及隔离副本，绝不改真实产品报告。稳定变体 TC-TM002-EVIDENCE-01#COMPLETE 为结构完整的合成输入；TC-TM002-EVIDENCE-01#MISSING_STEP 只删除步骤 2 的逐步事件；TC-TM002-EVIDENCE-01#MISSING_PICKER 只删除唯一的真实面板事件；TC-TM002-EVIDENCE-01#MISSING_FS 只删除该 TC 的来源访问审计；TC-TM002-EVIDENCE-01#WRONG_PACKAGE 将 package manifest SHA256 改为 64 个字符 0；TC-TM002-EVIDENCE-01#FAILED_CLEANUP 将 cleanup.completed 改为 false。各变体从同一完整合成母版单独构造，不叠加。</x:v>
+        <x:v>固定程序只在本例私有目录生成合成原始报告及隔离副本，绝不改真实产品报告。稳定变体 TC-TM002-EVIDENCE-01#COMPLETE 为结构完整的合成输入；TC-TM002-EVIDENCE-01#MISSING_STEP 只删除步骤 2 的逐步事件；TC-TM002-EVIDENCE-01#MISSING_PICKER 只删除唯一的真实面板事件；TC-TM002-EVIDENCE-01#MISSING_CHOOSER_WITNESS仅从picker-01.json删除chooser_confirm_button并更新该旁证摘要、其它原报告字段不变；TC-TM002-EVIDENCE-01#MISSING_FS 只删除该 TC 的来源访问审计；TC-TM002-EVIDENCE-01#WRONG_PACKAGE 将 package manifest SHA256 改为 64 个字符 0；TC-TM002-EVIDENCE-01#FAILED_CLEANUP 将 cleanup.completed 改为 false。各变体从同一完整合成母版单独构造，不叠加。</x:v>
       </x:c>
       <x:c r="G140" s="9" t="str">
         <x:v>UI 不适用，原因是证据复核；无 App 文件访问、网络或 DB 操作。
-#COMPLETE 仅结构核对通过且 release_eligible=false，不能签产品通行证；#MISSING_STEP、#MISSING_PICKER、#MISSING_FS、#WRONG_PACKAGE、#FAILED_CLEANUP 均分别返回非 PASS 与对应缺项原因，缺 FS 时 UI 无 B 不可补证；无网络/DB 操作。
+#COMPLETE 仅结构核对通过且 release_eligible=false，不能签产品通行证；#MISSING_STEP、#MISSING_PICKER、#MISSING_CHOOSER_WITNESS、#MISSING_FS、#WRONG_PACKAGE、#FAILED_CLEANUP 均分别返回非 PASS 与对应缺项原因，缺 FS 时 UI 无 B 不可补证；无网络/DB 操作。；缺chooser见证时独立复核器须非零退出/FAIL并指出native picker event不可信，通用面板事件不能补证。
 核对输入原件未覆盖、首次失败和复核输出按变体单独保留；无网络/DB 操作。</x:v>
       </x:c>
       <x:c r="H140" s="9" t="str">
@@ -14204,7 +14204,7 @@
         <x:v>TM-002</x:v>
       </x:c>
       <x:c r="B144" s="9" t="str">
-        <x:v>TC-TM002-EVIDENCE-01#MISSING_FS</x:v>
+        <x:v>TC-TM002-EVIDENCE-01#MISSING_CHOOSER_WITNESS</x:v>
       </x:c>
       <x:c r="C144" s="9" t="str">
         <x:v>缺原生/文件审计不得放行 · 变体</x:v>
@@ -14216,10 +14216,10 @@
         <x:v>治理检查</x:v>
       </x:c>
       <x:c r="F144" s="9" t="str">
-        <x:v>只删来源访问审计。</x:v>
+        <x:v>完整合成母版独立副本中仅删除picker-01.json的chooser_confirm_button，重算该picker_events旁证描述摘要；其余原报告/步骤/事件保持。</x:v>
       </x:c>
       <x:c r="G144" s="9" t="str">
-        <x:v>复核非PASS并指出缺文件审计；UI无B不可补证。</x:v>
+        <x:v>独立verify_tm002_evidence非零退出且FAIL，错误指出native picker event不可信；不因通用面板事件而通过。</x:v>
       </x:c>
       <x:c r="H144" s="9" t="str">
         <x:v>准备：只生成自有报告副本；无服务/DB，SQL 不适用。按 owner marker 独立清理，真实报告不可写。
@@ -14250,7 +14250,7 @@
         <x:v>TM-002</x:v>
       </x:c>
       <x:c r="B145" s="4" t="str">
-        <x:v>TC-TM002-EVIDENCE-01#WRONG_PACKAGE</x:v>
+        <x:v>TC-TM002-EVIDENCE-01#MISSING_FS</x:v>
       </x:c>
       <x:c r="C145" s="4" t="str">
         <x:v>缺原生/文件审计不得放行 · 变体</x:v>
@@ -14262,10 +14262,10 @@
         <x:v>治理检查</x:v>
       </x:c>
       <x:c r="F145" s="4" t="str">
-        <x:v>只把package manifest SHA256改为64个0。</x:v>
+        <x:v>只删来源访问审计。</x:v>
       </x:c>
       <x:c r="G145" s="4" t="str">
-        <x:v>复核非PASS并指出包摘要不匹配。</x:v>
+        <x:v>复核非PASS并指出缺文件审计；UI无B不可补证。</x:v>
       </x:c>
       <x:c r="H145" s="4" t="str">
         <x:v>准备：只生成自有报告副本；无服务/DB，SQL 不适用。按 owner marker 独立清理，真实报告不可写。
@@ -14296,7 +14296,7 @@
         <x:v>TM-002</x:v>
       </x:c>
       <x:c r="B146" s="9" t="str">
-        <x:v>TC-TM002-EVIDENCE-01#FAILED_CLEANUP</x:v>
+        <x:v>TC-TM002-EVIDENCE-01#WRONG_PACKAGE</x:v>
       </x:c>
       <x:c r="C146" s="9" t="str">
         <x:v>缺原生/文件审计不得放行 · 变体</x:v>
@@ -14308,10 +14308,10 @@
         <x:v>治理检查</x:v>
       </x:c>
       <x:c r="F146" s="9" t="str">
-        <x:v>只把cleanup.completed改为false。</x:v>
+        <x:v>只把package manifest SHA256改为64个0。</x:v>
       </x:c>
       <x:c r="G146" s="9" t="str">
-        <x:v>复核非PASS并指出清理未完成。</x:v>
+        <x:v>复核非PASS并指出包摘要不匹配。</x:v>
       </x:c>
       <x:c r="H146" s="9" t="str">
         <x:v>准备：只生成自有报告副本；无服务/DB，SQL 不适用。按 owner marker 独立清理，真实报告不可写。
@@ -14337,98 +14337,98 @@
         <x:v>v0.2.0-20261001T034118Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="147" ht="177" customHeight="1">
+    <x:row r="147" ht="72" customHeight="1">
       <x:c r="A147" s="4" t="str">
         <x:v>TM-002</x:v>
       </x:c>
       <x:c r="B147" s="4" t="str">
+        <x:v>TC-TM002-EVIDENCE-01#FAILED_CLEANUP</x:v>
+      </x:c>
+      <x:c r="C147" s="4" t="str">
+        <x:v>缺原生/文件审计不得放行 · 变体</x:v>
+      </x:c>
+      <x:c r="D147" s="4" t="str">
+        <x:v>TASK-TM002-RUNNER</x:v>
+      </x:c>
+      <x:c r="E147" s="4" t="str">
+        <x:v>治理检查</x:v>
+      </x:c>
+      <x:c r="F147" s="4" t="str">
+        <x:v>只把cleanup.completed改为false。</x:v>
+      </x:c>
+      <x:c r="G147" s="4" t="str">
+        <x:v>复核非PASS并指出清理未完成。</x:v>
+      </x:c>
+      <x:c r="H147" s="4" t="str">
+        <x:v>准备：只生成自有报告副本；无服务/DB，SQL 不适用。按 owner marker 独立清理，真实报告不可写。
+变化：不适用：辅助检查不写服务业务库。
+核验：不适用：本例按内存输入、自有副本或原始结果核验，没有 DB 连接或 SQL。</x:v>
+      </x:c>
+      <x:c r="I147" s="4" t="str">
+        <x:v>baselined</x:v>
+      </x:c>
+      <x:c r="J147" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K147" s="4" t="str">
+        <x:v>细化变体</x:v>
+      </x:c>
+      <x:c r="L147" s="4" t="str">
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:397</x:v>
+      </x:c>
+      <x:c r="M147" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N147" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" ht="177" customHeight="1">
+      <x:c r="A148" s="9" t="str">
+        <x:v>TM-002</x:v>
+      </x:c>
+      <x:c r="B148" s="9" t="str">
         <x:v>TC-TM002-DELIVERY-01</x:v>
       </x:c>
-      <x:c r="C147" s="4" t="str">
+      <x:c r="C148" s="9" t="str">
         <x:v>最终包、升级与全量回归门禁</x:v>
       </x:c>
-      <x:c r="D147" s="4" t="str">
+      <x:c r="D148" s="9" t="str">
         <x:v>TASK-TM002-DELIVERY</x:v>
       </x:c>
-      <x:c r="E147" s="4" t="str">
+      <x:c r="E148" s="9" t="str">
         <x:v>交付门禁</x:v>
       </x:c>
-      <x:c r="F147" s="4" t="str">
+      <x:c r="F148" s="9" t="str">
         <x:v>已锁定候选 SHA/tree、0.2.0 最终 DMG 原件/清单、上一0.1本机正式稳定DMG及其SOP-018通行证、SOP-020 schema 2 release-index.json（milestone_sha/tree、master_tip_sha、remote_source_state=PENDING、原DMG/manifest/passport摘要）、签名、同机隔离签名更新源与每例隔离服务；若没有这些前置或真实升级入口，本例为 BLOCKED，不能用开发/候选包、受控101或同源码测试高版冒充。远端源码登记与Tag可待最终统一办理。TM-001 全部已交付 TC 和 除本例外 TM-002 其余 27 条父 TC 与 35 个稳定变体的固定清单在运行前确定。</x:v>
       </x:c>
-      <x:c r="G147" s="4" t="str">
+      <x:c r="G148" s="9" t="str">
         <x:v>TM-001 全部已交付 TC、其他 27 条 TM-002 父 TC/35 变体的真实 UI、原生面板、服务与隔离 DB 由各自固定程序执行；原始记录各有唯一尝试和清理；本例结果此时仍为 BLOCKED。
 上一0.1本机稳定原包schema 2归档、里程碑来源、通行证与实际摘要一致，负测按既定拒绝，App 自主升级；0.2显示新版本、保留TM-001合成账号/配置且 /v1/me 复核身份；来源初态 none，真实面板确认A后重启恢复本版密文来源；两端包签名、摘要和进程版本吻合。
 本例不自我依赖：只有 TM-001 全部、其他 27 条 TM-002 父 TC/35 变体及升级真实结果均 PASS，且本例自身包/升级/证据核验 PASS，才记本例 PASS 并由最终 gate 签发通行证；计算前为 BLOCKED；本步骤无业务 DB 写入。</x:v>
       </x:c>
-      <x:c r="H147" s="4" t="str">
+      <x:c r="H148" s="9" t="str">
         <x:v>准备：每个产品 TC 由共同 R 独立准备合成账号、隔离 SQLite 与来源；本门禁只读这些运行的原始摘要及 SQL/数据证据引用，并核对最终 DMG、升级源和候选 SHA/tree。 上一稳定0.1包须有SOP-018/020原件及来源里程碑身份，远端登记可待办。 稳定升级源消费者还须有旧schema/候选包/错误里程碑和摘要的固定拒绝负测。
 变化：本门禁自身无服务业务 SQL 写入；逐个产品 TC 的认证 sessions/audit 变化只按各自 NDA 与只读证据解释。
 核验：只读复核 TM-001 全部已交付 TC、其他 27 条 TM-002 父 TC/35 变体的隔离 DB/SQL 引用与原始逐步结果，并核对最终包、升级、清理和候选一致性；本例结果由这些原件派生，不连接生产库。 核对上一0.1稳定原包的通行证、归档、来源SHA/tree及真实升级链。 只读核对schema 2 release-index.json的milestone_sha/tree、master_tip_sha、remote_source_state及原件摘要。</x:v>
       </x:c>
-      <x:c r="I147" s="4" t="str">
+      <x:c r="I148" s="9" t="str">
         <x:v>baselined</x:v>
-      </x:c>
-      <x:c r="J147" s="4" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="K147" s="4" t="str">
-        <x:v>细化用例</x:v>
-      </x:c>
-      <x:c r="L147" s="4" t="str">
-        <x:v>docs/testing/cases/02-TM-002-permissions.md:408</x:v>
-      </x:c>
-      <x:c r="M147" s="4" t="str">
-        <x:v>尚未执行</x:v>
-      </x:c>
-      <x:c r="N147" s="4" t="str">
-        <x:v>v0.2.0-20261001T034118Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="148" ht="72" customHeight="1">
-      <x:c r="A148" s="9" t="str">
-        <x:v>TM-003</x:v>
-      </x:c>
-      <x:c r="B148" s="9" t="str">
-        <x:v>E2E-TM003-001</x:v>
-      </x:c>
-      <x:c r="C148" s="9" t="str">
-        <x:v>增量、重扫、重启及移动</x:v>
-      </x:c>
-      <x:c r="D148" s="9" t="str">
-        <x:v>待拆解</x:v>
-      </x:c>
-      <x:c r="E148" s="9" t="str">
-        <x:v>产品E2E</x:v>
-      </x:c>
-      <x:c r="F148" s="9" t="str">
-        <x:v>数据集 codex_raw；依赖TM-001/002；已授权隔离Codex目录。codex_raw 须声明真实支持的工具版本、字段语义和来源。规划三次调用A/B/C的独立增量分别为 input/output 100/10、200/20、300/30，缓存20/40/60为input子项；原始格式尚未绑定。</x:v>
-      </x:c>
-      <x:c r="G148" s="9" t="str">
-        <x:v>唯一事件=3，input=600、output=60、total=660、cached=120且不额外加到total。首次A为110，全部后为660；重扫、重启、移动后仍660。预期由给定增量手工相加，不能用产品解析器生成。</x:v>
-      </x:c>
-      <x:c r="H148" s="9" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
-      </x:c>
-      <x:c r="I148" s="9" t="str">
-        <x:v>未来规划</x:v>
       </x:c>
       <x:c r="J148" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K148" s="9" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L148" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:14</x:v>
+        <x:v>docs/testing/cases/02-TM-002-permissions.md:408</x:v>
       </x:c>
       <x:c r="M148" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N148" s="9" t="str">
-        <x:v>v0.3.0-20261001T034652Z</x:v>
+        <x:v>v0.2.0-20261001T034118Z</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="72" customHeight="1">
@@ -14436,10 +14436,10 @@
         <x:v>TM-003</x:v>
       </x:c>
       <x:c r="B149" s="4" t="str">
-        <x:v>E2E-TM003-002</x:v>
+        <x:v>E2E-TM003-001</x:v>
       </x:c>
       <x:c r="C149" s="4" t="str">
-        <x:v>累计、重复、分支及未知</x:v>
+        <x:v>增量、重扫、重启及移动</x:v>
       </x:c>
       <x:c r="D149" s="4" t="str">
         <x:v>待拆解</x:v>
@@ -14448,10 +14448,10 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F149" s="4" t="str">
-        <x:v>数据集 codex_raw；codex_raw 规划独立分组：累计input/output 100/10→150/15，重复最后一条；另开启有明确新会话身份的重置累计30/3；分支复制前序历史后新增20/2。再附一条未知结构与一条无法解释的累计回退。版本、事件/分支语义仍需实际fixture证实。</x:v>
+        <x:v>数据集 codex_raw；依赖TM-001/002；已授权隔离Codex目录。codex_raw 须声明真实支持的工具版本、字段语义和来源。规划三次调用A/B/C的独立增量分别为 input/output 100/10、200/20、300/30，缓存20/40/60为input子项；原始格式尚未绑定。</x:v>
       </x:c>
       <x:c r="G149" s="4" t="str">
-        <x:v>可确认的新用量为150/15+30/3+20/2，即input=200、output=20、total=220；重复累计和继承历史贡献0新增量。未知/无法核实回退须单独诊断，不作为0值成功事件，也不污染220可信总量。</x:v>
+        <x:v>唯一事件=3，input=600、output=60、total=660、cached=120且不额外加到total。首次A为110，全部后为660；重扫、重启、移动后仍660。预期由给定增量手工相加，不能用产品解析器生成。</x:v>
       </x:c>
       <x:c r="H149" s="4" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
@@ -14468,7 +14468,7 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L149" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:38</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:14</x:v>
       </x:c>
       <x:c r="M149" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -14477,15 +14477,15 @@
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="150" ht="57" customHeight="1">
+    <x:row r="150" ht="72" customHeight="1">
       <x:c r="A150" s="9" t="str">
         <x:v>TM-003</x:v>
       </x:c>
       <x:c r="B150" s="9" t="str">
-        <x:v>E2E-TM003-003</x:v>
+        <x:v>E2E-TM003-002</x:v>
       </x:c>
       <x:c r="C150" s="9" t="str">
-        <x:v>半行、源清理与历史覆盖</x:v>
+        <x:v>累计、重复、分支及未知</x:v>
       </x:c>
       <x:c r="D150" s="9" t="str">
         <x:v>待拆解</x:v>
@@ -14494,10 +14494,10 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F150" s="9" t="str">
-        <x:v>数据集 codex_raw；codex_raw 规划完整调用A=100/10、待分两次写入调用B=50/5；当前已导入历史覆盖范围另有边界标记。原始字节拆分与文件清理程序未实现。</x:v>
+        <x:v>数据集 codex_raw；codex_raw 规划独立分组：累计input/output 100/10→150/15，重复最后一条；另开启有明确新会话身份的重置累计30/3；分支复制前序历史后新增20/2。再附一条未知结构与一条无法解释的累计回退。版本、事件/分支语义仍需实际fixture证实。</x:v>
       </x:c>
       <x:c r="G150" s="9" t="str">
-        <x:v>半行时只有A、total=110；补全后A+B共2条、total=165，重启不重计。源文件删除不删除已采集统计，早于可证明覆盖范围的历史显示缺失，不能以0表示。</x:v>
+        <x:v>可确认的新用量为150/15+30/3+20/2，即input=200、output=20、total=220；重复累计和继承历史贡献0新增量。未知/无法核实回退须单独诊断，不作为0值成功事件，也不污染220可信总量。</x:v>
       </x:c>
       <x:c r="H150" s="9" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
@@ -14514,7 +14514,7 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L150" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:63</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:38</x:v>
       </x:c>
       <x:c r="M150" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -14528,10 +14528,10 @@
         <x:v>TM-003</x:v>
       </x:c>
       <x:c r="B151" s="4" t="str">
-        <x:v>E2E-TM003-004</x:v>
+        <x:v>E2E-TM003-003</x:v>
       </x:c>
       <x:c r="C151" s="4" t="str">
-        <x:v>权限边界与重新授权</x:v>
+        <x:v>半行、源清理与历史覆盖</x:v>
       </x:c>
       <x:c r="D151" s="4" t="str">
         <x:v>待拆解</x:v>
@@ -14540,10 +14540,10 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F151" s="4" t="str">
-        <x:v>数据集 codex_raw；TM-002权限恢复已可运行；Codex目录含已采集A=100/10、B=200/20。撤销期间追加C=300/30，重新授权后还重放A。codex_raw 与system_permissions跨fixture绑定待实现。</x:v>
+        <x:v>数据集 codex_raw；codex_raw 规划完整调用A=100/10、待分两次写入调用B=50/5；当前已导入历史覆盖范围另有边界标记。原始字节拆分与文件清理程序未实现。</x:v>
       </x:c>
       <x:c r="G151" s="4" t="str">
-        <x:v>撤销期间不读取；恢复前total=330，恢复后唯一A/B/C共3条、total=660；重放A贡献0；刷新和重启后保持660。</x:v>
+        <x:v>半行时只有A、total=110；补全后A+B共2条、total=165，重启不重计。源文件删除不删除已采集统计，早于可证明覆盖范围的历史显示缺失，不能以0表示。</x:v>
       </x:c>
       <x:c r="H151" s="4" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
@@ -14560,7 +14560,7 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L151" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:87</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:63</x:v>
       </x:c>
       <x:c r="M151" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -14571,13 +14571,13 @@
     </x:row>
     <x:row r="152" ht="57" customHeight="1">
       <x:c r="A152" s="9" t="str">
-        <x:v>TM-004</x:v>
+        <x:v>TM-003</x:v>
       </x:c>
       <x:c r="B152" s="9" t="str">
-        <x:v>E2E-TM004-001</x:v>
+        <x:v>E2E-TM003-004</x:v>
       </x:c>
       <x:c r="C152" s="9" t="str">
-        <x:v>主会话与子代理归属</x:v>
+        <x:v>权限边界与重新授权</x:v>
       </x:c>
       <x:c r="D152" s="9" t="str">
         <x:v>待拆解</x:v>
@@ -14586,10 +14586,10 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F152" s="9" t="str">
-        <x:v>数据集 claude_raw；依赖TM-002/003；claude_raw 须注明已验证Claude Code版本。规划主调用M=100/10与子代理S=200/20，同属用户alice/项目A，具有明确父子关系且模型字段可不同。</x:v>
+        <x:v>数据集 codex_raw；TM-002权限恢复已可运行；Codex目录含已采集A=100/10、B=200/20。撤销期间追加C=300/30，重新授权后还重放A。codex_raw 与system_permissions跨fixture绑定待实现。</x:v>
       </x:c>
       <x:c r="G152" s="9" t="str">
-        <x:v>M与S各入账一次，共input300、output30、total330；S计入正确父项目，不因主会话引用而再计一次。模型明细保留各自原始可识别模型。</x:v>
+        <x:v>撤销期间不读取；恢复前total=330，恢复后唯一A/B/C共3条、total=660；重放A贡献0；刷新和重启后保持660。</x:v>
       </x:c>
       <x:c r="H152" s="9" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
@@ -14606,13 +14606,13 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L152" s="9" t="str">
-        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:11</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:87</x:v>
       </x:c>
       <x:c r="M152" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N152" s="9" t="str">
-        <x:v>v0.2.0-20261001T034118Z</x:v>
+        <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
     <x:row r="153" ht="57" customHeight="1">
@@ -14620,10 +14620,10 @@
         <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B153" s="4" t="str">
-        <x:v>E2E-TM004-002</x:v>
+        <x:v>E2E-TM004-001</x:v>
       </x:c>
       <x:c r="C153" s="4" t="str">
-        <x:v>fork历史、消息改写与半写入</x:v>
+        <x:v>主会话与子代理归属</x:v>
       </x:c>
       <x:c r="D153" s="4" t="str">
         <x:v>待拆解</x:v>
@@ -14632,10 +14632,10 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F153" s="4" t="str">
-        <x:v>数据集 claude_raw；规划原会话M=100/10，fork继承M但消息ID变化；分支新增N=50/5，最后调用P=20/2分段写入；同一片段重复出现。实际继承识别字段需由版本化raw证据确认。</x:v>
+        <x:v>数据集 claude_raw；依赖TM-002/003；claude_raw 须注明已验证Claude Code版本。规划主调用M=100/10与子代理S=200/20，同属用户alice/项目A，具有明确父子关系且模型字段可不同。</x:v>
       </x:c>
       <x:c r="G153" s="4" t="str">
-        <x:v>继承历史虽改消息ID仍不重复；M+N阶段total165，半写入不增加，完整P后total187，共3次实际调用；重启不再增加。不能只以消息ID相等作为去重预期。</x:v>
+        <x:v>M与S各入账一次，共input300、output30、total330；S计入正确父项目，不因主会话引用而再计一次。模型明细保留各自原始可识别模型。</x:v>
       </x:c>
       <x:c r="H153" s="4" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
@@ -14652,7 +14652,7 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L153" s="4" t="str">
-        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:28</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:11</x:v>
       </x:c>
       <x:c r="M153" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -14666,10 +14666,10 @@
         <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B154" s="9" t="str">
-        <x:v>E2E-TM004-003</x:v>
+        <x:v>E2E-TM004-002</x:v>
       </x:c>
       <x:c r="C154" s="9" t="str">
-        <x:v>支持版本与未知usage降级</x:v>
+        <x:v>fork历史、消息改写与半写入</x:v>
       </x:c>
       <x:c r="D154" s="9" t="str">
         <x:v>待拆解</x:v>
@@ -14678,10 +14678,10 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F154" s="9" t="str">
-        <x:v>数据集 claude_raw；为每个拟声明支持版本准备原生样例及独立expected，例如完整调用100/10；另准备未知结构版本和缺usage的事件，后两者不用0填充。当前无已验证版本样例。</x:v>
+        <x:v>数据集 claude_raw；规划原会话M=100/10，fork继承M但消息ID变化；分支新增N=50/5，最后调用P=20/2分段写入；同一片段重复出现。实际继承识别字段需由版本化raw证据确认。</x:v>
       </x:c>
       <x:c r="G154" s="9" t="str">
-        <x:v>支持版本各与其独立数字相等；未知版本/缺usage明确显示未识别或缺失，不能当作有效零用量，也不覆盖已知调用110。支持列表必须由真实结果决定。</x:v>
+        <x:v>继承历史虽改消息ID仍不重复；M+N阶段total165，半写入不增加，完整P后total187，共3次实际调用；重启不再增加。不能只以消息ID相等作为去重预期。</x:v>
       </x:c>
       <x:c r="H154" s="9" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
@@ -14698,7 +14698,7 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L154" s="9" t="str">
-        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:45</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:28</x:v>
       </x:c>
       <x:c r="M154" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -14712,10 +14712,10 @@
         <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B155" s="4" t="str">
-        <x:v>E2E-TM004-004</x:v>
+        <x:v>E2E-TM004-003</x:v>
       </x:c>
       <x:c r="C155" s="4" t="str">
-        <x:v>主/子代理重新授权去重</x:v>
+        <x:v>支持版本与未知usage降级</x:v>
       </x:c>
       <x:c r="D155" s="4" t="str">
         <x:v>待拆解</x:v>
@@ -14724,10 +14724,10 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F155" s="4" t="str">
-        <x:v>数据集 claude_raw；初始主M=100/10、子S=200/20及继承M的fork均已扫描；失权期间子代理追加N=50/5。claude_raw 和权限状态联合fixture尚未实现。</x:v>
+        <x:v>数据集 claude_raw；为每个拟声明支持版本准备原生样例及独立expected，例如完整调用100/10；另准备未知结构版本和缺usage的事件，后两者不用0填充。当前无已验证版本样例。</x:v>
       </x:c>
       <x:c r="G155" s="4" t="str">
-        <x:v>恢复前total330，恢复后唯一M/S/N共3调用、total385；继承M和复制S均不重复；读取失败期间不生成成功零值。</x:v>
+        <x:v>支持版本各与其独立数字相等；未知版本/缺usage明确显示未识别或缺失，不能当作有效零用量，也不覆盖已知调用110。支持列表必须由真实结果决定。</x:v>
       </x:c>
       <x:c r="H155" s="4" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
@@ -14744,7 +14744,7 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L155" s="4" t="str">
-        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:62</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:45</x:v>
       </x:c>
       <x:c r="M155" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -14753,1026 +14753,1026 @@
         <x:v>v0.2.0-20261001T034118Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="156" ht="72" customHeight="1">
+    <x:row r="156" ht="57" customHeight="1">
       <x:c r="A156" s="9" t="str">
         <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B156" s="9" t="str">
-        <x:v>TC-TM004-SOURCE-01</x:v>
+        <x:v>E2E-TM004-004</x:v>
       </x:c>
       <x:c r="C156" s="9" t="str">
-        <x:v>授权根限定（TASK-TM004-SOURCE，AC-001，E2E-001）</x:v>
+        <x:v>主/子代理重新授权去重</x:v>
       </x:c>
       <x:c r="D156" s="9" t="str">
-        <x:v>TASK-TM004-SOURCE</x:v>
+        <x:v>待拆解</x:v>
       </x:c>
       <x:c r="E156" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F156" s="9" t="str">
+        <x:v>数据集 claude_raw；初始主M=100/10、子S=200/20及继承M的fork均已扫描；失权期间子代理追加N=50/5。claude_raw 和权限状态联合fixture尚未实现。</x:v>
+      </x:c>
+      <x:c r="G156" s="9" t="str">
+        <x:v>恢复前total330，恢复后唯一M/S/N共3调用、total385；继承M和复制S均不重复；读取失败期间不生成成功零值。</x:v>
+      </x:c>
+      <x:c r="H156" s="9" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I156" s="9" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J156" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K156" s="9" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L156" s="9" t="str">
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:62</x:v>
+      </x:c>
+      <x:c r="M156" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N156" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" ht="72" customHeight="1">
+      <x:c r="A157" s="4" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="B157" s="4" t="str">
+        <x:v>TC-TM004-SOURCE-01</x:v>
+      </x:c>
+      <x:c r="C157" s="4" t="str">
+        <x:v>授权根限定（TASK-TM004-SOURCE，AC-001，E2E-001）</x:v>
+      </x:c>
+      <x:c r="D157" s="4" t="str">
+        <x:v>TASK-TM004-SOURCE</x:v>
+      </x:c>
+      <x:c r="E157" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F157" s="4" t="str">
         <x:v>用户经 TM-002 UI 只选择隔离项目A目录；目录内有 M=100/10 完整原始行，旁边未授权目录有 X=999/99。</x:v>
       </x:c>
-      <x:c r="G156" s="9" t="str">
+      <x:c r="G157" s="4" t="str">
         <x:v>UI 显示待确认，事件表无新增
 UI 显示1次 M、total110，SQLite只读见唯一M
 调用数仍1、total110
 无X读取请求且事件表无X</x:v>
       </x:c>
-      <x:c r="H156" s="9" t="str">
+      <x:c r="H157" s="4" t="str">
         <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
 变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
 核验：规划只读核对：只读按来源/项目统计 M 行数与 token，总数1/110；检查 X 键不存在；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
-      <x:c r="I156" s="9" t="str">
+      <x:c r="I157" s="4" t="str">
         <x:v>预期待明确</x:v>
       </x:c>
-      <x:c r="J156" s="9" t="str">
+      <x:c r="J157" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K156" s="9" t="str">
+      <x:c r="K157" s="4" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L156" s="9" t="str">
+      <x:c r="L157" s="4" t="str">
         <x:v>docs/testing/cases/04-TM-004-claude-collection.md:87</x:v>
       </x:c>
-      <x:c r="M156" s="9" t="str">
+      <x:c r="M157" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N156" s="9" t="str">
+      <x:c r="N157" s="4" t="str">
         <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="157" ht="72" customHeight="1">
-      <x:c r="A157" s="4" t="str">
+    <x:row r="158" ht="72" customHeight="1">
+      <x:c r="A158" s="9" t="str">
         <x:v>TM-004</x:v>
       </x:c>
-      <x:c r="B157" s="4" t="str">
+      <x:c r="B158" s="9" t="str">
         <x:v>TC-TM004-SOURCE-02</x:v>
       </x:c>
-      <x:c r="C157" s="4" t="str">
+      <x:c r="C158" s="9" t="str">
         <x:v>撤权和重新授权（TASK-TM004-SOURCE，AC-004，E2E-004）</x:v>
       </x:c>
-      <x:c r="D157" s="4" t="str">
+      <x:c r="D158" s="9" t="str">
         <x:v>TASK-TM004-SOURCE</x:v>
       </x:c>
-      <x:c r="E157" s="4" t="str">
+      <x:c r="E158" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F157" s="4" t="str">
+      <x:c r="F158" s="9" t="str">
         <x:v>已扫描 M=100/10、S=200/20；撤权期间子代理新增 N=50/5。</x:v>
       </x:c>
-      <x:c r="G157" s="4" t="str">
+      <x:c r="G158" s="9" t="str">
         <x:v>状态显示不可读且保留total330
 仍330且诊断为读取受阻
 唯一 M/S/N、total385
 M/S/N仍为三次且total385</x:v>
       </x:c>
-      <x:c r="H157" s="4" t="str">
+      <x:c r="H158" s="9" t="str">
         <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
 变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
 核验：规划只读核对：只读唯一键数3与 token总385，撤权阶段无N。重置同共用配方；TM-002失权模拟与子目录绑定待补；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
-      <x:c r="I157" s="4" t="str">
+      <x:c r="I158" s="9" t="str">
         <x:v>预期待明确</x:v>
       </x:c>
-      <x:c r="J157" s="4" t="str">
+      <x:c r="J158" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K157" s="4" t="str">
+      <x:c r="K158" s="9" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L157" s="4" t="str">
+      <x:c r="L158" s="9" t="str">
         <x:v>docs/testing/cases/04-TM-004-claude-collection.md:91</x:v>
       </x:c>
-      <x:c r="M157" s="4" t="str">
+      <x:c r="M158" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N157" s="4" t="str">
+      <x:c r="N158" s="9" t="str">
         <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="158" ht="72" customHeight="1">
-      <x:c r="A158" s="9" t="str">
+    <x:row r="159" ht="72" customHeight="1">
+      <x:c r="A159" s="4" t="str">
         <x:v>TM-004</x:v>
       </x:c>
-      <x:c r="B158" s="9" t="str">
+      <x:c r="B159" s="4" t="str">
         <x:v>TC-TM004-PARSER-01</x:v>
       </x:c>
-      <x:c r="C158" s="9" t="str">
+      <x:c r="C159" s="4" t="str">
         <x:v>主/子实际调用（TASK-TM004-PARSER，AC-001，E2E-001）</x:v>
       </x:c>
-      <x:c r="D158" s="9" t="str">
+      <x:c r="D159" s="4" t="str">
         <x:v>TASK-TM004-PARSER</x:v>
       </x:c>
-      <x:c r="E158" s="9" t="str">
+      <x:c r="E159" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F158" s="9" t="str">
+      <x:c r="F159" s="4" t="str">
         <x:v>同一项目原始主M100/10与子S200/20，模型各自保留，父关系有原始证据。</x:v>
       </x:c>
-      <x:c r="G158" s="9" t="str">
+      <x:c r="G159" s="4" t="str">
         <x:v>可信total110
 可信input300/output30/total330
 仍2次调用/330</x:v>
       </x:c>
-      <x:c r="H158" s="9" t="str">
+      <x:c r="H159" s="4" t="str">
         <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
 变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
 核验：规划只读核对：只读两条唯一事件和模型/父项目归属；不读取正文。版本化raw和模型字段待补；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
-      <x:c r="I158" s="9" t="str">
+      <x:c r="I159" s="4" t="str">
         <x:v>预期待明确</x:v>
       </x:c>
-      <x:c r="J158" s="9" t="str">
+      <x:c r="J159" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K158" s="9" t="str">
+      <x:c r="K159" s="4" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L158" s="9" t="str">
+      <x:c r="L159" s="4" t="str">
         <x:v>docs/testing/cases/04-TM-004-claude-collection.md:95</x:v>
       </x:c>
-      <x:c r="M158" s="9" t="str">
+      <x:c r="M159" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N158" s="9" t="str">
+      <x:c r="N159" s="4" t="str">
         <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="159" ht="102" customHeight="1">
-      <x:c r="A159" s="4" t="str">
+    <x:row r="160" ht="102" customHeight="1">
+      <x:c r="A160" s="9" t="str">
         <x:v>TM-004</x:v>
       </x:c>
-      <x:c r="B159" s="4" t="str">
+      <x:c r="B160" s="9" t="str">
         <x:v>TC-TM004-PARSER-02</x:v>
       </x:c>
-      <x:c r="C159" s="4" t="str">
+      <x:c r="C160" s="9" t="str">
         <x:v>未知结构/缺字段（TASK-TM004-PARSER，AC-003，E2E-003）</x:v>
       </x:c>
-      <x:c r="D159" s="4" t="str">
+      <x:c r="D160" s="9" t="str">
         <x:v>TASK-TM004-PARSER</x:v>
       </x:c>
-      <x:c r="E159" s="4" t="str">
+      <x:c r="E160" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F159" s="4" t="str">
+      <x:c r="F160" s="9" t="str">
         <x:v>已支持版本完整 M100/10、未知结构 U、JSONL 原始行真正缺 usage 的 Q。</x:v>
       </x:c>
-      <x:c r="G159" s="4" t="str">
+      <x:c r="G160" s="9" t="str">
         <x:v>可信total110
 可信仍110且出现未知结构诊断
 可信仍110、缺usage诊断新增
 诊断可见且不显示 U/Q 为零调用</x:v>
       </x:c>
-      <x:c r="H159" s="4" t="str">
+      <x:c r="H160" s="9" t="str">
         <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
 变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
 核验：规划只读核对：只读可信事件1条/110，诊断各1条；具体版本标识、缺字段schema和SQL待补。隔离负测中 API SSE 省略 usage 后 CLI 仍在原生 JSONL 写0/0，**不是** Q 的原生缺字段样本；Q 需另证来源或标明故障注入，不得把0/0回填解释成已知零；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
-      <x:c r="I159" s="4" t="str">
+      <x:c r="I160" s="9" t="str">
         <x:v>预期待明确</x:v>
       </x:c>
-      <x:c r="J159" s="4" t="str">
+      <x:c r="J160" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K159" s="4" t="str">
+      <x:c r="K160" s="9" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L159" s="4" t="str">
+      <x:c r="L160" s="9" t="str">
         <x:v>docs/testing/cases/04-TM-004-claude-collection.md:99</x:v>
       </x:c>
-      <x:c r="M159" s="4" t="str">
+      <x:c r="M160" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N159" s="4" t="str">
+      <x:c r="N160" s="9" t="str">
         <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="160" ht="72" customHeight="1">
-      <x:c r="A160" s="9" t="str">
+    <x:row r="161" ht="72" customHeight="1">
+      <x:c r="A161" s="4" t="str">
         <x:v>TM-004</x:v>
       </x:c>
-      <x:c r="B160" s="9" t="str">
+      <x:c r="B161" s="4" t="str">
         <x:v>TC-TM004-LINEAGE-01</x:v>
       </x:c>
-      <x:c r="C160" s="9" t="str">
+      <x:c r="C161" s="4" t="str">
         <x:v>子代理父项目（TASK-TM004-LINEAGE，AC-001，E2E-001）</x:v>
       </x:c>
-      <x:c r="D160" s="9" t="str">
+      <x:c r="D161" s="4" t="str">
         <x:v>TASK-TM004-LINEAGE</x:v>
       </x:c>
-      <x:c r="E160" s="9" t="str">
+      <x:c r="E161" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F160" s="9" t="str">
+      <x:c r="F161" s="4" t="str">
         <x:v>项目A主M100/10、子S200/20，另有项目B同名会话标识但无父关系。</x:v>
       </x:c>
-      <x:c r="G160" s="9" t="str">
+      <x:c r="G161" s="4" t="str">
         <x:v>A=110
 A=330、B=0
 A仍330
 S标为子代理且使用原模型</x:v>
       </x:c>
-      <x:c r="H160" s="9" t="str">
+      <x:c r="H161" s="4" t="str">
         <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
 变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
 核验：规划只读核对：只读S的父项目键为A、事件数2；原始父链线索缺失时不得假称通过；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
-      <x:c r="I160" s="9" t="str">
+      <x:c r="I161" s="4" t="str">
         <x:v>预期待明确</x:v>
       </x:c>
-      <x:c r="J160" s="9" t="str">
+      <x:c r="J161" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K160" s="9" t="str">
+      <x:c r="K161" s="4" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L160" s="9" t="str">
+      <x:c r="L161" s="4" t="str">
         <x:v>docs/testing/cases/04-TM-004-claude-collection.md:103</x:v>
       </x:c>
-      <x:c r="M160" s="9" t="str">
+      <x:c r="M161" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N160" s="9" t="str">
+      <x:c r="N161" s="4" t="str">
         <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="161" ht="72" customHeight="1">
-      <x:c r="A161" s="4" t="str">
+    <x:row r="162" ht="72" customHeight="1">
+      <x:c r="A162" s="9" t="str">
         <x:v>TM-004</x:v>
       </x:c>
-      <x:c r="B161" s="4" t="str">
+      <x:c r="B162" s="9" t="str">
         <x:v>TC-TM004-LINEAGE-02</x:v>
       </x:c>
-      <x:c r="C161" s="4" t="str">
+      <x:c r="C162" s="9" t="str">
         <x:v>fork继承和ID改写（TASK-TM004-LINEAGE，AC-002，E2E-002）</x:v>
       </x:c>
-      <x:c r="D161" s="4" t="str">
+      <x:c r="D162" s="9" t="str">
         <x:v>TASK-TM004-LINEAGE</x:v>
       </x:c>
-      <x:c r="E161" s="4" t="str">
+      <x:c r="E162" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F161" s="4" t="str">
+      <x:c r="F162" s="9" t="str">
         <x:v>原M100/10、fork复制或引用M但消息ID改写、fork新N50/5。</x:v>
       </x:c>
-      <x:c r="G161" s="4" t="str">
+      <x:c r="G162" s="9" t="str">
         <x:v>M仅入账一次且total110
 仍110
 total165且调用数2
 仍165</x:v>
       </x:c>
-      <x:c r="H161" s="4" t="str">
+      <x:c r="H162" s="9" t="str">
         <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
 变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
 核验：规划只读核对：只读可信唯一调用2/165及继承诊断/关系；待schema确定；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
-      <x:c r="I161" s="4" t="str">
+      <x:c r="I162" s="9" t="str">
         <x:v>预期待明确</x:v>
       </x:c>
-      <x:c r="J161" s="4" t="str">
+      <x:c r="J162" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K161" s="4" t="str">
+      <x:c r="K162" s="9" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L161" s="4" t="str">
+      <x:c r="L162" s="9" t="str">
         <x:v>docs/testing/cases/04-TM-004-claude-collection.md:107</x:v>
       </x:c>
-      <x:c r="M161" s="4" t="str">
+      <x:c r="M162" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N161" s="4" t="str">
+      <x:c r="N162" s="9" t="str">
         <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="162" ht="72" customHeight="1">
-      <x:c r="A162" s="9" t="str">
+    <x:row r="163" ht="72" customHeight="1">
+      <x:c r="A163" s="4" t="str">
         <x:v>TM-004</x:v>
       </x:c>
-      <x:c r="B162" s="9" t="str">
+      <x:c r="B163" s="4" t="str">
         <x:v>TC-TM004-INCREMENTAL-01</x:v>
       </x:c>
-      <x:c r="C162" s="9" t="str">
+      <x:c r="C163" s="4" t="str">
         <x:v>半行完成（TASK-TM004-INCREMENTAL，AC-002，E2E-002）</x:v>
       </x:c>
-      <x:c r="D162" s="9" t="str">
+      <x:c r="D163" s="4" t="str">
         <x:v>TASK-TM004-INCREMENTAL</x:v>
       </x:c>
-      <x:c r="E162" s="9" t="str">
+      <x:c r="E163" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F162" s="9" t="str">
+      <x:c r="F163" s="4" t="str">
         <x:v>已计M+N total165，P=20/2 原始JSONL行分成两次写入。</x:v>
       </x:c>
-      <x:c r="G162" s="9" t="str">
+      <x:c r="G163" s="4" t="str">
         <x:v>扫描后仍165、读取游标未越过半行
 扫描后total187、调用数3
 P仅入账一次且total187</x:v>
       </x:c>
-      <x:c r="H162" s="9" t="str">
+      <x:c r="H163" s="4" t="str">
         <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
 变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
 核验：规划只读核对：只读P只一条，可信事件3/187，游标处于完整行末；具体游标schema待补；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
-      <x:c r="I162" s="9" t="str">
+      <x:c r="I163" s="4" t="str">
         <x:v>预期待明确</x:v>
       </x:c>
-      <x:c r="J162" s="9" t="str">
+      <x:c r="J163" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K162" s="9" t="str">
+      <x:c r="K163" s="4" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L162" s="9" t="str">
+      <x:c r="L163" s="4" t="str">
         <x:v>docs/testing/cases/04-TM-004-claude-collection.md:111</x:v>
       </x:c>
-      <x:c r="M162" s="9" t="str">
+      <x:c r="M163" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N162" s="9" t="str">
+      <x:c r="N163" s="4" t="str">
         <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="163" ht="72" customHeight="1">
-      <x:c r="A163" s="4" t="str">
+    <x:row r="164" ht="72" customHeight="1">
+      <x:c r="A164" s="9" t="str">
         <x:v>TM-004</x:v>
       </x:c>
-      <x:c r="B163" s="4" t="str">
+      <x:c r="B164" s="9" t="str">
         <x:v>TC-TM004-INCREMENTAL-02</x:v>
       </x:c>
-      <x:c r="C163" s="4" t="str">
+      <x:c r="C164" s="9" t="str">
         <x:v>重复与事务恢复（TASK-TM004-INCREMENTAL，AC-002/004，E2E-002/004）</x:v>
       </x:c>
-      <x:c r="D163" s="4" t="str">
+      <x:c r="D164" s="9" t="str">
         <x:v>TASK-TM004-INCREMENTAL</x:v>
       </x:c>
-      <x:c r="E163" s="4" t="str">
+      <x:c r="E164" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F163" s="4" t="str">
+      <x:c r="F164" s="9" t="str">
         <x:v>完整M100/10、重复相同片段及移动/复制文件；在扫描提交边界中断App。</x:v>
       </x:c>
-      <x:c r="G163" s="4" t="str">
+      <x:c r="G164" s="9" t="str">
         <x:v>M仅入账一次且total110
 仍110
 仍唯一M/110
 total165</x:v>
       </x:c>
-      <x:c r="H163" s="4" t="str">
+      <x:c r="H164" s="9" t="str">
         <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
 变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
 核验：规划只读核对：只读唯一键数2/165且游标一致；故障注入不得绕过产品事务。TM-003事务接口待补；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
-      <x:c r="I163" s="4" t="str">
+      <x:c r="I164" s="9" t="str">
         <x:v>预期待明确</x:v>
       </x:c>
-      <x:c r="J163" s="4" t="str">
+      <x:c r="J164" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K163" s="4" t="str">
+      <x:c r="K164" s="9" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L163" s="4" t="str">
+      <x:c r="L164" s="9" t="str">
         <x:v>docs/testing/cases/04-TM-004-claude-collection.md:115</x:v>
       </x:c>
-      <x:c r="M163" s="4" t="str">
+      <x:c r="M164" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N163" s="4" t="str">
+      <x:c r="N164" s="9" t="str">
         <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="164" ht="87" customHeight="1">
-      <x:c r="A164" s="9" t="str">
+    <x:row r="165" ht="87" customHeight="1">
+      <x:c r="A165" s="4" t="str">
         <x:v>TM-004</x:v>
       </x:c>
-      <x:c r="B164" s="9" t="str">
+      <x:c r="B165" s="4" t="str">
         <x:v>TC-TM004-DIAG-01</x:v>
       </x:c>
-      <x:c r="C164" s="9" t="str">
+      <x:c r="C165" s="4" t="str">
         <x:v>未知值不是零（TASK-TM004-DIAGNOSTIC，AC-003，E2E-003）</x:v>
       </x:c>
-      <x:c r="D164" s="9" t="str">
+      <x:c r="D165" s="4" t="str">
         <x:v>TASK-TM004-DIAGNOSTIC</x:v>
       </x:c>
-      <x:c r="E164" s="9" t="str">
+      <x:c r="E165" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F164" s="9" t="str">
+      <x:c r="F165" s="4" t="str">
         <x:v>可信M100/10、U未知格式、Q的JSONL原始行缺usage，以及另有独立来源证明的有效零usage记录Z。</x:v>
       </x:c>
-      <x:c r="G164" s="9" t="str">
+      <x:c r="G165" s="4" t="str">
         <x:v>显示110
 显示可信110和两个不同未覆盖提示
 零值记录可见但总量仍110
 三种状态不混淆</x:v>
       </x:c>
-      <x:c r="H164" s="9" t="str">
+      <x:c r="H165" s="4" t="str">
         <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
 变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
 核验：规划只读核对：只读可信M和已证实的Z，U/Q仅诊断，不以0写入；Z的原始有效性仍 baseline_pending。2.1.126 遇到畸形合成 API 缺usage会自己写0/0，不能拿该行充当Z；未经额外证据不能由0/0 raw推断上游已知零；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
-      <x:c r="I164" s="9" t="str">
+      <x:c r="I165" s="4" t="str">
         <x:v>预期待明确</x:v>
       </x:c>
-      <x:c r="J164" s="9" t="str">
+      <x:c r="J165" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K164" s="9" t="str">
+      <x:c r="K165" s="4" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L164" s="9" t="str">
+      <x:c r="L165" s="4" t="str">
         <x:v>docs/testing/cases/04-TM-004-claude-collection.md:119</x:v>
       </x:c>
-      <x:c r="M164" s="9" t="str">
+      <x:c r="M165" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N164" s="9" t="str">
+      <x:c r="N165" s="4" t="str">
         <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="165" ht="72" customHeight="1">
-      <x:c r="A165" s="4" t="str">
+    <x:row r="166" ht="72" customHeight="1">
+      <x:c r="A166" s="9" t="str">
         <x:v>TM-004</x:v>
       </x:c>
-      <x:c r="B165" s="4" t="str">
+      <x:c r="B166" s="9" t="str">
         <x:v>TC-TM004-DIAG-02</x:v>
       </x:c>
-      <x:c r="C165" s="4" t="str">
+      <x:c r="C166" s="9" t="str">
         <x:v>失权提示及隐私（TASK-TM004-DIAGNOSTIC，AC-004，E2E-004）</x:v>
       </x:c>
-      <x:c r="D165" s="4" t="str">
+      <x:c r="D166" s="9" t="str">
         <x:v>TASK-TM004-DIAGNOSTIC</x:v>
       </x:c>
-      <x:c r="E165" s="4" t="str">
+      <x:c r="E166" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F165" s="4" t="str">
+      <x:c r="F166" s="9" t="str">
         <x:v>M已入账，撤权目录含合成 prompt、代码和密钥哨兵字符串。</x:v>
       </x:c>
-      <x:c r="G165" s="4" t="str">
+      <x:c r="G166" s="9" t="str">
         <x:v>UI显示读取受阻而非零用量，保留110
 无哨兵文本及完整源路径
 受阻提示消除且M不重计</x:v>
       </x:c>
-      <x:c r="H165" s="4" t="str">
+      <x:c r="H166" s="9" t="str">
         <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
 变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
 核验：规划只读核对：只读事件1/110、诊断状态与仅白名单字段；隐私哨兵由固定生成器构造，不使用真实秘密；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
-      <x:c r="I165" s="4" t="str">
+      <x:c r="I166" s="9" t="str">
         <x:v>预期待明确</x:v>
       </x:c>
-      <x:c r="J165" s="4" t="str">
+      <x:c r="J166" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K165" s="4" t="str">
+      <x:c r="K166" s="9" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L165" s="4" t="str">
+      <x:c r="L166" s="9" t="str">
         <x:v>docs/testing/cases/04-TM-004-claude-collection.md:123</x:v>
       </x:c>
-      <x:c r="M165" s="4" t="str">
+      <x:c r="M166" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N165" s="4" t="str">
+      <x:c r="N166" s="9" t="str">
         <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="166" ht="72" customHeight="1">
-      <x:c r="A166" s="9" t="str">
+    <x:row r="167" ht="72" customHeight="1">
+      <x:c r="A167" s="4" t="str">
         <x:v>TM-004</x:v>
       </x:c>
-      <x:c r="B166" s="9" t="str">
+      <x:c r="B167" s="4" t="str">
         <x:v>TC-TM004-DATA-01</x:v>
       </x:c>
-      <x:c r="C166" s="9" t="str">
+      <x:c r="C167" s="4" t="str">
         <x:v>原始fixture和独立oracle（TASK-TM004-DATA，AC-001–004，E2E-003）</x:v>
       </x:c>
-      <x:c r="D166" s="9" t="str">
+      <x:c r="D167" s="4" t="str">
         <x:v>TASK-TM004-DATA</x:v>
       </x:c>
-      <x:c r="E166" s="9" t="str">
+      <x:c r="E167" s="4" t="str">
         <x:v>data_fixture</x:v>
       </x:c>
-      <x:c r="F166" s="9" t="str">
+      <x:c r="F167" s="4" t="str">
         <x:v>固定版本 CLI/公开来源、隔离 CLAUDE_CONFIG_DIR、固定合成任务；禁止访问真实 ~/.claude。</x:v>
       </x:c>
-      <x:c r="G166" s="9" t="str">
+      <x:c r="G167" s="4" t="str">
         <x:v>版本、来源、原始SHA及父子/fork证据有原件
 M/S/N/P的330、165、187、385在运行前记录
 SHA一致且SQL初态只有合成账号与零事件
 仅删除本次拥有目录且保留原始报告</x:v>
       </x:c>
-      <x:c r="H166" s="9" t="str">
+      <x:c r="H167" s="4" t="str">
         <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
 变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
 核验：规划只读核对：本例不直接写入产品用量表；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
-      <x:c r="I166" s="9" t="str">
+      <x:c r="I167" s="4" t="str">
         <x:v>预期待明确</x:v>
       </x:c>
-      <x:c r="J166" s="9" t="str">
+      <x:c r="J167" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K166" s="9" t="str">
+      <x:c r="K167" s="4" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L166" s="9" t="str">
+      <x:c r="L167" s="4" t="str">
         <x:v>docs/testing/cases/04-TM-004-claude-collection.md:127</x:v>
       </x:c>
-      <x:c r="M166" s="9" t="str">
+      <x:c r="M167" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N166" s="9" t="str">
+      <x:c r="N167" s="4" t="str">
         <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="167" ht="72" customHeight="1">
-      <x:c r="A167" s="4" t="str">
+    <x:row r="168" ht="72" customHeight="1">
+      <x:c r="A168" s="9" t="str">
         <x:v>TM-004</x:v>
       </x:c>
-      <x:c r="B167" s="4" t="str">
+      <x:c r="B168" s="9" t="str">
         <x:v>TC-TM004-E2E-01</x:v>
       </x:c>
-      <x:c r="C167" s="4" t="str">
+      <x:c r="C168" s="9" t="str">
         <x:v>安装包真实链路（TASK-TM004-E2E，AC-001–004，E2E-001/004）</x:v>
       </x:c>
-      <x:c r="D167" s="4" t="str">
+      <x:c r="D168" s="9" t="str">
         <x:v>TASK-TM004-E2E</x:v>
       </x:c>
-      <x:c r="E167" s="4" t="str">
+      <x:c r="E168" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F167" s="4" t="str">
+      <x:c r="F168" s="9" t="str">
         <x:v>本版固定候选SHA、原DMG、TM-001–004完整必测TC清单。</x:v>
       </x:c>
-      <x:c r="G167" s="4" t="str">
+      <x:c r="G168" s="9" t="str">
         <x:v>仅连接本次独占服务和隔离授权根
 逐步断言UI、IPC后果和只读SQLite
 目标及历史已交付TC全部执行且无跳过/重试/失败
 结果与候选包一致且本次资源清理完成</x:v>
       </x:c>
-      <x:c r="H167" s="4" t="str">
+      <x:c r="H168" s="9" t="str">
         <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
 变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
 核验：规划只读核对：本例不直接写入产品用量表；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
-      <x:c r="I167" s="4" t="str">
+      <x:c r="I168" s="9" t="str">
         <x:v>预期待明确</x:v>
       </x:c>
-      <x:c r="J167" s="4" t="str">
+      <x:c r="J168" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K167" s="4" t="str">
+      <x:c r="K168" s="9" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L167" s="4" t="str">
+      <x:c r="L168" s="9" t="str">
         <x:v>docs/testing/cases/04-TM-004-claude-collection.md:131</x:v>
       </x:c>
-      <x:c r="M167" s="4" t="str">
+      <x:c r="M168" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N167" s="4" t="str">
+      <x:c r="N168" s="9" t="str">
         <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="168" ht="72" customHeight="1">
-      <x:c r="A168" s="9" t="str">
+    <x:row r="169" ht="72" customHeight="1">
+      <x:c r="A169" s="4" t="str">
         <x:v>TM-004</x:v>
       </x:c>
-      <x:c r="B168" s="9" t="str">
+      <x:c r="B169" s="4" t="str">
         <x:v>TC-TM004-RELEASE-01</x:v>
       </x:c>
-      <x:c r="C168" s="9" t="str">
+      <x:c r="C169" s="4" t="str">
         <x:v>候选与证据一致（TASK-TM004-RELEASE，AC-001–004，E2E-004）</x:v>
       </x:c>
-      <x:c r="D168" s="9" t="str">
+      <x:c r="D169" s="4" t="str">
         <x:v>TASK-TM004-RELEASE</x:v>
       </x:c>
-      <x:c r="E168" s="9" t="str">
+      <x:c r="E169" s="4" t="str">
         <x:v>release_gate</x:v>
       </x:c>
-      <x:c r="F168" s="9" t="str">
+      <x:c r="F169" s="4" t="str">
         <x:v>同一已提交SHA/tree、DMG摘要、完整TM-001–004结果。</x:v>
       </x:c>
-      <x:c r="G168" s="9" t="str">
+      <x:c r="G169" s="4" t="str">
         <x:v>SHA/tree和DMG摘要一致
 完整集合逐例PASS且清理完成，否则阻断
 Excel行和源摘要一致
 SOP-018真实PASS才进入SOP-019</x:v>
       </x:c>
-      <x:c r="H168" s="9" t="str">
+      <x:c r="H169" s="4" t="str">
         <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
 变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
 核验：规划只读核对：本例不直接写入产品用量表；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
-      <x:c r="I168" s="9" t="str">
+      <x:c r="I169" s="4" t="str">
         <x:v>预期待明确</x:v>
       </x:c>
-      <x:c r="J168" s="9" t="str">
+      <x:c r="J169" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K168" s="9" t="str">
+      <x:c r="K169" s="4" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L168" s="9" t="str">
+      <x:c r="L169" s="4" t="str">
         <x:v>docs/testing/cases/04-TM-004-claude-collection.md:135</x:v>
       </x:c>
-      <x:c r="M168" s="9" t="str">
+      <x:c r="M169" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N168" s="9" t="str">
+      <x:c r="N169" s="4" t="str">
         <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="169" ht="72" customHeight="1">
-      <x:c r="A169" s="4" t="str">
+    <x:row r="170" ht="72" customHeight="1">
+      <x:c r="A170" s="9" t="str">
         <x:v>TM-004</x:v>
       </x:c>
-      <x:c r="B169" s="4" t="str">
+      <x:c r="B170" s="9" t="str">
         <x:v>TC-TM004-SOURCE-03</x:v>
       </x:c>
-      <x:c r="C169" s="4" t="str">
+      <x:c r="C170" s="9" t="str">
         <x:v>嵌套子代理目录（TASK-TM004-SOURCE，AC-001，E2E-001）</x:v>
       </x:c>
-      <x:c r="D169" s="4" t="str">
+      <x:c r="D170" s="9" t="str">
         <x:v>TASK-TM004-SOURCE</x:v>
       </x:c>
-      <x:c r="E169" s="4" t="str">
+      <x:c r="E170" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F169" s="4" t="str">
+      <x:c r="F170" s="9" t="str">
         <x:v>2.1.126 已安装二进制显示子代理路径可在 subagents/ 下继续嵌套；确切层级与父链由待取得的原始样本决定。固定数据应含项目A主M100/10、一级子S200/20、嵌套子T=50/5，以及授权根外同名文件X=999/99。</x:v>
       </x:c>
-      <x:c r="G169" s="4" t="str">
+      <x:c r="G170" s="9" t="str">
         <x:v>项目A可信total385/3次调用
 不读取X
 总量和归属不变
 不猜A</x:v>
       </x:c>
-      <x:c r="H169" s="4" t="str">
+      <x:c r="H170" s="9" t="str">
         <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
 变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
 核验：规划只读核对：只读事件唯一键、父项目与总量3/385；缺链变体的T不得纳入A可信聚合；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
-      <x:c r="I169" s="4" t="str">
+      <x:c r="I170" s="9" t="str">
         <x:v>预期待明确</x:v>
       </x:c>
-      <x:c r="J169" s="4" t="str">
+      <x:c r="J170" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K169" s="4" t="str">
+      <x:c r="K170" s="9" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L169" s="4" t="str">
+      <x:c r="L170" s="9" t="str">
         <x:v>docs/testing/cases/04-TM-004-claude-collection.md:139</x:v>
       </x:c>
-      <x:c r="M169" s="4" t="str">
+      <x:c r="M170" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N169" s="4" t="str">
+      <x:c r="N170" s="9" t="str">
         <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="170" ht="72" customHeight="1">
-      <x:c r="A170" s="9" t="str">
+    <x:row r="171" ht="72" customHeight="1">
+      <x:c r="A171" s="4" t="str">
         <x:v>TM-004</x:v>
       </x:c>
-      <x:c r="B170" s="9" t="str">
+      <x:c r="B171" s="4" t="str">
         <x:v>TC-TM004-PARSER-03</x:v>
       </x:c>
-      <x:c r="C170" s="9" t="str">
+      <x:c r="C171" s="4" t="str">
         <x:v>同一消息多内容块和 Agent 摘要（TASK-TM004-PARSER，AC-001，E2E-001）</x:v>
       </x:c>
-      <x:c r="D170" s="9" t="str">
+      <x:c r="D171" s="4" t="str">
         <x:v>TASK-TM004-PARSER</x:v>
       </x:c>
-      <x:c r="E170" s="9" t="str">
+      <x:c r="E171" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F170" s="9" t="str">
+      <x:c r="F171" s="4" t="str">
         <x:v>同一次主调用M100/10拆为至少两个带相同 message.id 与 usage 的 assistant 内容块，另有 Agent 工具结果的 totalTokens/usage 摘要与子S200/20原始调用；本机独立结构探针已实际生成31/9双块，CLI 写两行相同 ID 和完整 usage，子代理19/6的父工具结果出现 total_tokens: 25。</x:v>
       </x:c>
-      <x:c r="G170" s="9" t="str">
+      <x:c r="G171" s="4" t="str">
         <x:v>UI/SQLite为1次调用、total110
 可信为M+S两次、total330
 仍330</x:v>
       </x:c>
-      <x:c r="H170" s="9" t="str">
+      <x:c r="H171" s="4" t="str">
         <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
 变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
 核验：规划只读核对：只读源消息调用键2个/330，父Agent汇总不能额外成为第三次调用；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
-      <x:c r="I170" s="9" t="str">
+      <x:c r="I171" s="4" t="str">
         <x:v>预期待明确</x:v>
       </x:c>
-      <x:c r="J170" s="9" t="str">
+      <x:c r="J171" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K170" s="9" t="str">
+      <x:c r="K171" s="4" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L170" s="9" t="str">
+      <x:c r="L171" s="4" t="str">
         <x:v>docs/testing/cases/04-TM-004-claude-collection.md:143</x:v>
       </x:c>
-      <x:c r="M170" s="9" t="str">
+      <x:c r="M171" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N170" s="9" t="str">
+      <x:c r="N171" s="4" t="str">
         <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="171" ht="72" customHeight="1">
-      <x:c r="A171" s="4" t="str">
+    <x:row r="172" ht="72" customHeight="1">
+      <x:c r="A172" s="9" t="str">
         <x:v>TM-004</x:v>
       </x:c>
-      <x:c r="B171" s="4" t="str">
+      <x:c r="B172" s="9" t="str">
         <x:v>TC-TM004-LINEAGE-03</x:v>
       </x:c>
-      <x:c r="C171" s="4" t="str">
+      <x:c r="C172" s="9" t="str">
         <x:v>forkedFrom 复制与改写 UUID（TASK-TM004-LINEAGE，AC-002，E2E-002）</x:v>
       </x:c>
-      <x:c r="D171" s="4" t="str">
+      <x:c r="D172" s="9" t="str">
         <x:v>TASK-TM004-LINEAGE</x:v>
       </x:c>
-      <x:c r="E171" s="4" t="str">
+      <x:c r="E172" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F171" s="4" t="str">
+      <x:c r="F172" s="9" t="str">
         <x:v>已计M100/10；分别用2.1.126真实生成的 fork 复制记录（保留 UUID）和改写 UUID 记录，依据实际 raw 的跨文件调用身份/父链判定，不能假定两者都含 forkedFrom；再追加真正新N50/5。</x:v>
       </x:c>
-      <x:c r="G171" s="4" t="str">
+      <x:c r="G172" s="9" t="str">
         <x:v>M仅计一次且total110
 均仍110并在诊断/关系中可追溯原M
 total165/2次
 仍两次可信调用且total165</x:v>
       </x:c>
-      <x:c r="H171" s="4" t="str">
+      <x:c r="H172" s="9" t="str">
         <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
 变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
 核验：规划只读核对：只读可信调用键2个、继承引用指向M；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
-      <x:c r="I171" s="4" t="str">
+      <x:c r="I172" s="9" t="str">
         <x:v>预期待明确</x:v>
       </x:c>
-      <x:c r="J171" s="4" t="str">
+      <x:c r="J172" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K171" s="4" t="str">
+      <x:c r="K172" s="9" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L171" s="4" t="str">
+      <x:c r="L172" s="9" t="str">
         <x:v>docs/testing/cases/04-TM-004-claude-collection.md:147</x:v>
       </x:c>
-      <x:c r="M171" s="4" t="str">
+      <x:c r="M172" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N171" s="4" t="str">
+      <x:c r="N172" s="9" t="str">
         <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="172" ht="72" customHeight="1">
-      <x:c r="A172" s="9" t="str">
+    <x:row r="173" ht="72" customHeight="1">
+      <x:c r="A173" s="4" t="str">
         <x:v>TM-004</x:v>
       </x:c>
-      <x:c r="B172" s="9" t="str">
+      <x:c r="B173" s="4" t="str">
         <x:v>TC-TM004-LINEAGE-04</x:v>
       </x:c>
-      <x:c r="C172" s="9" t="str">
+      <x:c r="C173" s="4" t="str">
         <x:v>fork-context-ref 父链（TASK-TM004-LINEAGE，AC-002，E2E-002）</x:v>
       </x:c>
-      <x:c r="D172" s="9" t="str">
+      <x:c r="D173" s="4" t="str">
         <x:v>TASK-TM004-LINEAGE</x:v>
       </x:c>
-      <x:c r="E172" s="9" t="str">
+      <x:c r="E173" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F172" s="9" t="str">
+      <x:c r="F173" s="4" t="str">
         <x:v>2.1.126真实子代理 fork 记录中带 agentId,parentSessionId,parentLastUuid,contextLength；父会话存在M100/10，子代理仅新增S200/20。</x:v>
       </x:c>
-      <x:c r="G172" s="9" t="str">
+      <x:c r="G173" s="4" t="str">
         <x:v>可信110
 可信330/2次而非440
 可信M/S两次且total330
 引用解析到M的既有调用键</x:v>
       </x:c>
-      <x:c r="H172" s="9" t="str">
+      <x:c r="H173" s="4" t="str">
         <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
 变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
 核验：规划只读核对：只读M/S各一条及引用，total330；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
-      <x:c r="I172" s="9" t="str">
+      <x:c r="I173" s="4" t="str">
         <x:v>预期待明确</x:v>
       </x:c>
-      <x:c r="J172" s="9" t="str">
+      <x:c r="J173" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K172" s="9" t="str">
+      <x:c r="K173" s="4" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L172" s="9" t="str">
+      <x:c r="L173" s="4" t="str">
         <x:v>docs/testing/cases/04-TM-004-claude-collection.md:151</x:v>
       </x:c>
-      <x:c r="M172" s="9" t="str">
+      <x:c r="M173" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N172" s="9" t="str">
+      <x:c r="N173" s="4" t="str">
         <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="173" ht="72" customHeight="1">
-      <x:c r="A173" s="4" t="str">
+    <x:row r="174" ht="72" customHeight="1">
+      <x:c r="A174" s="9" t="str">
         <x:v>TM-004</x:v>
       </x:c>
-      <x:c r="B173" s="4" t="str">
+      <x:c r="B174" s="9" t="str">
         <x:v>TC-TM004-LINEAGE-05</x:v>
       </x:c>
-      <x:c r="C173" s="4" t="str">
+      <x:c r="C174" s="9" t="str">
         <x:v>缺失或矛盾父链（TASK-TM004-LINEAGE，AC-002/003，E2E-002/003）</x:v>
       </x:c>
-      <x:c r="D173" s="4" t="str">
+      <x:c r="D174" s="9" t="str">
         <x:v>TASK-TM004-LINEAGE</x:v>
       </x:c>
-      <x:c r="E173" s="4" t="str">
+      <x:c r="E174" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F173" s="4" t="str">
+      <x:c r="F174" s="9" t="str">
         <x:v>在上一例的合成同构目录中分别移除引用父文件、指向不存在的 parentLastUuid、或提供无 forkedFrom 但UUID改写的复制历史；这些是测试故障注入，不能标为厂商实际输出。</x:v>
       </x:c>
-      <x:c r="G173" s="4" t="str">
+      <x:c r="G174" s="9" t="str">
         <x:v>M仅计一次且total110
 App显示未确定来源诊断，可信总量仍110、不能把不明副本计为新调用或有效零
 若真实新增S200/20可独立识别则总量330
 可信总量保持且诊断随恢复更新</x:v>
       </x:c>
-      <x:c r="H173" s="4" t="str">
+      <x:c r="H174" s="9" t="str">
         <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
 变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
 核验：规划只读核对：只读未确定记录与可信M/S计数，不能借SQL灌成功；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
-      <x:c r="I173" s="4" t="str">
+      <x:c r="I174" s="9" t="str">
         <x:v>预期待明确</x:v>
       </x:c>
-      <x:c r="J173" s="4" t="str">
+      <x:c r="J174" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K173" s="4" t="str">
+      <x:c r="K174" s="9" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L173" s="4" t="str">
+      <x:c r="L174" s="9" t="str">
         <x:v>docs/testing/cases/04-TM-004-claude-collection.md:155</x:v>
       </x:c>
-      <x:c r="M173" s="4" t="str">
+      <x:c r="M174" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N173" s="4" t="str">
+      <x:c r="N174" s="9" t="str">
         <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="174" ht="102" customHeight="1">
-      <x:c r="A174" s="9" t="str">
+    <x:row r="175" ht="102" customHeight="1">
+      <x:c r="A175" s="4" t="str">
         <x:v>TM-004</x:v>
       </x:c>
-      <x:c r="B174" s="9" t="str">
+      <x:c r="B175" s="4" t="str">
         <x:v>TC-TM004-SOURCE-04</x:v>
       </x:c>
-      <x:c r="C174" s="9" t="str">
+      <x:c r="C175" s="4" t="str">
         <x:v>预览截断后的可续扫覆盖（TASK-TM004-SOURCE，AC-001/004，E2E-001/004）</x:v>
       </x:c>
-      <x:c r="D174" s="9" t="str">
+      <x:c r="D175" s="4" t="str">
         <x:v>TASK-TM004-SOURCE</x:v>
       </x:c>
-      <x:c r="E174" s="9" t="str">
+      <x:c r="E175" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F174" s="9" t="str">
+      <x:c r="F175" s="4" t="str">
         <x:v>本例独占授权根，固定程序按 TM-002 已提交枚举顺序生成至少1025个普通 .jsonl 文件及足够目录项；前段有主M100/10，预览截断范围外且至少第五个256项采集页的深层 subagents/ 文件有子S50/5，其余文件没有可计量调用。另备可控制的页间撤权/恢复点。</x:v>
       </x:c>
-      <x:c r="G174" s="9" t="str">
+      <x:c r="G175" s="4" t="str">
         <x:v>1000文件预览显示被截断，不声称全量
 UI 可显示已见M110，但 TM-003 coverage.scan_incomplete=1
 使用 openCandidateReadOnly(candidateToken) 读原始行；在另一次固定变体于页间撤权，下一页或打开须拒绝，cancelScan 后 scan_incomplete=1，重授后以新授权世代续扫
 可信 M+S 两调用、input150/output15/total165，scan_incomplete=0 才可显示本次覆盖完成；重启重扫总量不变</x:v>
       </x:c>
-      <x:c r="H174" s="9" t="str">
+      <x:c r="H175" s="4" t="str">
         <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
 变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
 核验：规划只读核对：只读各来源事件键、聚合 (2,150,15)、游标及 coverage.scan_incomplete；中途必须为1；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
-      <x:c r="I174" s="9" t="str">
+      <x:c r="I175" s="4" t="str">
         <x:v>预期待明确</x:v>
       </x:c>
-      <x:c r="J174" s="9" t="str">
+      <x:c r="J175" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K174" s="9" t="str">
+      <x:c r="K175" s="4" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L174" s="9" t="str">
+      <x:c r="L175" s="4" t="str">
         <x:v>docs/testing/cases/04-TM-004-claude-collection.md:159</x:v>
       </x:c>
-      <x:c r="M174" s="9" t="str">
+      <x:c r="M175" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N174" s="9" t="str">
+      <x:c r="N175" s="4" t="str">
         <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="175" ht="102" customHeight="1">
-      <x:c r="A175" s="4" t="str">
+    <x:row r="176" ht="102" customHeight="1">
+      <x:c r="A176" s="9" t="str">
         <x:v>TM-004</x:v>
       </x:c>
-      <x:c r="B175" s="4" t="str">
+      <x:c r="B176" s="9" t="str">
         <x:v>TC-TM004-INCREMENTAL-03</x:v>
       </x:c>
-      <x:c r="C175" s="4" t="str">
+      <x:c r="C176" s="9" t="str">
         <x:v>跨工具同 ID 与 Claude 复制历史（TASK-TM004-INCREMENTAL，AC-001/002，E2E-001/002）</x:v>
       </x:c>
-      <x:c r="D175" s="4" t="str">
+      <x:c r="D176" s="9" t="str">
         <x:v>TASK-TM004-INCREMENTAL</x:v>
       </x:c>
-      <x:c r="E175" s="4" t="str">
+      <x:c r="E176" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F175" s="4" t="str">
+      <x:c r="F176" s="9" t="str">
         <x:v>同一合成主体、各自经 UI 授权的 Codex 与 Claude 隔离根。固定本地响应使 Codex 原生 payload.response_id 与 Claude 主 assistant.message.id 字面均为 shared-call-01，分别有 C=11/1 与 M=100/10；Claude 原生 --fork-session 复制M，再有独立 Agent 子调用S=200/20（新 message.id、与父同 sessionId 但带 agentId）。另以明确标记的衍生故障数据令同一 Claude message.id 出现矛盾101/10，该行不冒称 CLI 原件。</x:v>
       </x:c>
-      <x:c r="G175" s="4" t="str">
+      <x:c r="G176" s="9" t="str">
         <x:v>可信1次/total12
 可信2次/input111/output11/total122，跨工具同字面 ID 不冲突
 可信3次/input311/output31/total342
 可信仍3次/342，出现 identity_conflict 与覆盖不完整</x:v>
       </x:c>
-      <x:c r="H175" s="4" t="str">
+      <x:c r="H176" s="9" t="str">
         <x:v>准备：按SOP-010新建隔离账号与SQLite；不得SQL直灌规范化成功事件
 变化：仅由真实App读取受控原始日志后按步骤产生事件或诊断；当前未执行
 核验：规划只读核对：只读同一 principal_key 下 source=codex 与 source=claude_code 各自事件数1/2、source_event_key 不同，Agent source_scope_key 与主来源可区分，复制M不多行，冲突不覆写原M；键与归属均不得存原生ID/完整路径；确切可执行SQL待TM-003稳定schema</x:v>
       </x:c>
-      <x:c r="I175" s="4" t="str">
+      <x:c r="I176" s="9" t="str">
         <x:v>预期待明确</x:v>
-      </x:c>
-      <x:c r="J175" s="4" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="K175" s="4" t="str">
-        <x:v>细化用例</x:v>
-      </x:c>
-      <x:c r="L175" s="4" t="str">
-        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:163</x:v>
-      </x:c>
-      <x:c r="M175" s="4" t="str">
-        <x:v>尚未执行</x:v>
-      </x:c>
-      <x:c r="N175" s="4" t="str">
-        <x:v>v0.4.0-20261001T040433Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="176" ht="57" customHeight="1">
-      <x:c r="A176" s="9" t="str">
-        <x:v>TM-005</x:v>
-      </x:c>
-      <x:c r="B176" s="9" t="str">
-        <x:v>E2E-TM005-001</x:v>
-      </x:c>
-      <x:c r="C176" s="9" t="str">
-        <x:v>日期筛选、趋势和明细</x:v>
-      </x:c>
-      <x:c r="D176" s="9" t="str">
-        <x:v>待拆解</x:v>
-      </x:c>
-      <x:c r="E176" s="9" t="str">
-        <x:v>产品E2E</x:v>
-      </x:c>
-      <x:c r="F176" s="9" t="str">
-        <x:v>数据集 date_ranges；date_ranges 已由 scripts/test_data.py 提供标准化语义样例，固定2026-09-29T04:00:00Z、Asia/Shanghai、seed42；13行含1重复、12唯一。需另有已验证raw输入映射和真实App导入流程，当前未实现。</x:v>
-      </x:c>
-      <x:c r="G176" s="9" t="str">
-        <x:v>独立expected中的total依次16500、110、17380、27830、31130；custom=2200。today共5条、input15000、output1500、cache1700、reasoning170，cache/reasoning不再相加；custom-start包含、custom-end排除。趋势点及明细按expected事件时间逐条核对。</x:v>
-      </x:c>
-      <x:c r="H176" s="9" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
-      </x:c>
-      <x:c r="I176" s="9" t="str">
-        <x:v>未来规划</x:v>
       </x:c>
       <x:c r="J176" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K176" s="9" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L176" s="9" t="str">
-        <x:v>docs/testing/cases/05-TM-005-usage-statistics.md:21</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:163</x:v>
       </x:c>
       <x:c r="M176" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N176" s="9" t="str">
-        <x:v>v0.2.0-20261001T034118Z</x:v>
+        <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
     </x:row>
     <x:row r="177" ht="57" customHeight="1">
@@ -15780,10 +15780,10 @@
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B177" s="4" t="str">
-        <x:v>E2E-TM005-002</x:v>
+        <x:v>E2E-TM005-001</x:v>
       </x:c>
       <x:c r="C177" s="4" t="str">
-        <x:v>时区、月边界与缺失值</x:v>
+        <x:v>日期筛选、趋势和明细</x:v>
       </x:c>
       <x:c r="D177" s="4" t="str">
         <x:v>待拆解</x:v>
@@ -15792,10 +15792,10 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F177" s="4" t="str">
-        <x:v>数据集 date_ranges；复用date_ranges中的2026-09-28T15:59:59Z与16:00:00Z、2026-08-30T15:59:59Z与16:00:00Z边界。另需补充覆盖缺口、已覆盖零调用日、unknown字段三类状态；当前生成器未覆盖后面三类。</x:v>
+        <x:v>数据集 date_ranges；date_ranges 已由 scripts/test_data.py 提供标准化语义样例，固定2026-09-29T04:00:00Z、Asia/Shanghai、seed42；13行含1重复、12唯一。需另有已验证raw输入映射和真实App导入流程，当前未实现。</x:v>
       </x:c>
       <x:c r="G177" s="4" t="str">
-        <x:v>Shanghai下15:59:59Z仍属前日、16:00:00Z属次日；UTC下二者同属UTC日期。无覆盖显示缺失，真实零可显示0，unknown字段显示未知；不得互相代替。各范围expected须独立按当地日期边界列出，不调用产品查询生成。</x:v>
+        <x:v>独立expected中的total依次16500、110、17380、27830、31130；custom=2200。today共5条、input15000、output1500、cache1700、reasoning170，cache/reasoning不再相加；custom-start包含、custom-end排除。趋势点及明细按expected事件时间逐条核对。</x:v>
       </x:c>
       <x:c r="H177" s="4" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
@@ -15812,7 +15812,7 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L177" s="4" t="str">
-        <x:v>docs/testing/cases/05-TM-005-usage-statistics.md:38</x:v>
+        <x:v>docs/testing/cases/05-TM-005-usage-statistics.md:21</x:v>
       </x:c>
       <x:c r="M177" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -15821,77 +15821,75 @@
         <x:v>v0.2.0-20261001T034118Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="178" ht="102" customHeight="1">
+    <x:row r="178" ht="57" customHeight="1">
       <x:c r="A178" s="9" t="str">
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B178" s="9" t="str">
-        <x:v>TC-TM005-CONTRACT-01</x:v>
+        <x:v>E2E-TM005-002</x:v>
       </x:c>
       <x:c r="C178" s="9" t="str">
-        <x:v>两来源重复事件不增量</x:v>
+        <x:v>时区、月边界与缺失值</x:v>
       </x:c>
       <x:c r="D178" s="9" t="str">
-        <x:v>TASK-TM005-EVENT-CONTRACT</x:v>
+        <x:v>待拆解</x:v>
       </x:c>
       <x:c r="E178" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F178" s="9" t="str">
+        <x:v>数据集 date_ranges；复用date_ranges中的2026-09-28T15:59:59Z与16:00:00Z、2026-08-30T15:59:59Z与16:00:00Z边界。另需补充覆盖缺口、已覆盖零调用日、unknown字段三类状态；当前生成器未覆盖后面三类。</x:v>
+      </x:c>
+      <x:c r="G178" s="9" t="str">
+        <x:v>Shanghai下15:59:59Z仍属前日、16:00:00Z属次日；UTC下二者同属UTC日期。无覆盖显示缺失，真实零可显示0，unknown字段显示未知；不得互相代替。各范围expected须独立按当地日期边界列出，不调用产品查询生成。</x:v>
+      </x:c>
+      <x:c r="H178" s="9" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I178" s="9" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J178" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K178" s="9" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L178" s="9" t="str">
+        <x:v>docs/testing/cases/05-TM-005-usage-statistics.md:38</x:v>
+      </x:c>
+      <x:c r="M178" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N178" s="9" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" ht="102" customHeight="1">
+      <x:c r="A179" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B179" s="4" t="str">
+        <x:v>TC-TM005-CONTRACT-01</x:v>
+      </x:c>
+      <x:c r="C179" s="4" t="str">
+        <x:v>两来源重复事件不增量</x:v>
+      </x:c>
+      <x:c r="D179" s="4" t="str">
+        <x:v>TASK-TM005-EVENT-CONTRACT</x:v>
+      </x:c>
+      <x:c r="E179" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F179" s="4" t="str">
         <x:v>seed42 事件中 Codex today-gpt 和 Claude Code today-sonnet 各一原生事件，另各有同源重复读取；全部绑定同一合成账号</x:v>
       </x:c>
-      <x:c r="G178" s="9" t="str">
+      <x:c r="G179" s="4" t="str">
         <x:v>1. 从空客户端库在 App 授权两目录并等待采集；UI 应显示两个来源已读取，DB 只读记录应有两条可信事件，总量 3300。
 2. 复制/重放两条原生事件并在 App 点刷新；UI 总量仍 3300，DB 的唯一来源事件身份仍为两条，诊断不能误报新用量。
 3. 退出并由同一已安装 App 重启后再刷新；总量和身份仍不变。只清理由本例创建的文件与进程。</x:v>
-      </x:c>
-      <x:c r="H178" s="9" t="str">
-        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
-变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
-核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
-      </x:c>
-      <x:c r="I178" s="9" t="str">
-        <x:v>预期待明确</x:v>
-      </x:c>
-      <x:c r="J178" s="9" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="K178" s="9" t="str">
-        <x:v>细化用例</x:v>
-      </x:c>
-      <x:c r="L178" s="9" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:19</x:v>
-      </x:c>
-      <x:c r="M178" s="9" t="str">
-        <x:v>尚未执行</x:v>
-      </x:c>
-      <x:c r="N178" s="9" t="str">
-        <x:v>v0.5.0-20261001T034729Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="179" ht="102" customHeight="1">
-      <x:c r="A179" s="4" t="str">
-        <x:v>TM-005</x:v>
-      </x:c>
-      <x:c r="B179" s="4" t="str">
-        <x:v>TC-TM005-CONTRACT-02</x:v>
-      </x:c>
-      <x:c r="C179" s="4" t="str">
-        <x:v>未知字段不伪造零</x:v>
-      </x:c>
-      <x:c r="D179" s="4" t="str">
-        <x:v>TASK-TM005-EVENT-CONTRACT</x:v>
-      </x:c>
-      <x:c r="E179" s="4" t="str">
-        <x:v>产品E2E</x:v>
-      </x:c>
-      <x:c r="F179" s="4" t="str">
-        <x:v>一条 Codex 缺 output、另一条 Claude Code 缺 input 的受支持原生记录，另有两条可信调用各 110 token</x:v>
-      </x:c>
-      <x:c r="G179" s="4" t="str">
-        <x:v>1. 从空库经 App 采集两条可信调用；卡片显示已知总量 220，DB 有两条可信事件。
-2. 追加两条缺字段记录并刷新；UI 显示相应未知诊断，完整总量不能把未知字段当 0。可信 220 不被覆盖，DB 的 unknown 状态与来源可只读辨认。
-3. 重扫与重启；可信 220 和两条未知状态保持，不能变成成功零用量。</x:v>
       </x:c>
       <x:c r="H179" s="4" t="str">
         <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
@@ -15908,7 +15906,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L179" s="4" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:29</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:19</x:v>
       </x:c>
       <x:c r="M179" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -15922,10 +15920,10 @@
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B180" s="9" t="str">
-        <x:v>TC-TM005-CONTRACT-03</x:v>
+        <x:v>TC-TM005-CONTRACT-02</x:v>
       </x:c>
       <x:c r="C180" s="9" t="str">
-        <x:v>Claude fork 复制历史与新增调用</x:v>
+        <x:v>未知字段不伪造零</x:v>
       </x:c>
       <x:c r="D180" s="9" t="str">
         <x:v>TASK-TM005-EVENT-CONTRACT</x:v>
@@ -15934,12 +15932,12 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F180" s="9" t="str">
-        <x:v>使用 TM-004 最终锁定的 Claude Code 2.1.126 自写原始 fork fixture：父会话可信调用 M=100/10，fork 文件复制父历史并新增可信调用 N=50/5；已固定的来源样本复制父 UUID、message.id、usage，却没有 forkedFrom</x:v>
+        <x:v>一条 Codex 缺 output、另一条 Claude Code 缺 input 的受支持原生记录，另有两条可信调用各 110 token</x:v>
       </x:c>
       <x:c r="G180" s="9" t="str">
-        <x:v>1. 在 App 授权本例 Claude 根并采集父会话 M；统计明细仅 M 一次，总量 110，DB 有一个可信来源调用身份。
-2. 由已验证 CLI 操作生成/写入上述固定 fork 原生日志后经 App 刷新；UI/DB 恰有 M、N 两个可信调用，total=165。复制的父历史不另入账，缺 forkedFrom 本身不构成新调用证明。
-3. 重扫 fork/父文件并重启 App；可信事件身份及 165 保持。若最终来源合同不能证明本例固定 fixture 的复制和新增关系，本例在运行前保持 BLOCKED，不能临场改写为另一预期或手填 PASS。</x:v>
+        <x:v>1. 从空库经 App 采集两条可信调用；卡片显示已知总量 220，DB 有两条可信事件。
+2. 追加两条缺字段记录并刷新；UI 显示相应未知诊断，完整总量不能把未知字段当 0。可信 220 不被覆盖，DB 的 unknown 状态与来源可只读辨认。
+3. 重扫与重启；可信 220 和两条未知状态保持，不能变成成功零用量。</x:v>
       </x:c>
       <x:c r="H180" s="9" t="str">
         <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
@@ -15956,7 +15954,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L180" s="9" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:39</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:29</x:v>
       </x:c>
       <x:c r="M180" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -15970,10 +15968,10 @@
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B181" s="4" t="str">
-        <x:v>TC-TM005-CONTRACT-04</x:v>
+        <x:v>TC-TM005-CONTRACT-03</x:v>
       </x:c>
       <x:c r="C181" s="4" t="str">
-        <x:v>Claude 父会话与子代理独立用量</x:v>
+        <x:v>Claude fork 复制历史与新增调用</x:v>
       </x:c>
       <x:c r="D181" s="4" t="str">
         <x:v>TASK-TM005-EVENT-CONTRACT</x:v>
@@ -15982,12 +15980,12 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F181" s="4" t="str">
-        <x:v>TM-004 最终锁定的 Claude Code 2.1.126 自写主会话与 subagents/agent-*.jsonl fixture；设计数字为父调用 M=100/10、子代理调用 S=200/20，两者各有独立 usage。已固定的来源样本中子文件带 agentId、isSidechain=true，与父文件同 sessionId</x:v>
+        <x:v>使用 TM-004 最终锁定的 Claude Code 2.1.126 自写原始 fork fixture：父会话可信调用 M=100/10，fork 文件复制父历史并新增可信调用 N=50/5；已固定的来源样本复制父 UUID、message.id、usage，却没有 forkedFrom</x:v>
       </x:c>
       <x:c r="G181" s="4" t="str">
-        <x:v>1. App 授权本例 Claude 根并采集父会话；只有父调用 M 入账，UI/DB 显示可信 110 及父来源身份。
-2. 子代理原生日志完整写入并由 App 采集；UI/DB 恰有 M、S 两个可信调用，total=330。父会话对子代理的引用不能另加 220；父子同 sessionId 也不能把子代理的真实调用消掉。
-3. 重扫主/子文件、刷新并重启；两个唯一身份与 330 保持，模型维度分别保留实际模型标识。若最终 raw 无法证明该父子关系或独立调用，本例在运行前保持 BLOCKED，不临场更换结果判据。</x:v>
+        <x:v>1. 在 App 授权本例 Claude 根并采集父会话 M；统计明细仅 M 一次，总量 110，DB 有一个可信来源调用身份。
+2. 由已验证 CLI 操作生成/写入上述固定 fork 原生日志后经 App 刷新；UI/DB 恰有 M、N 两个可信调用，total=165。复制的父历史不另入账，缺 forkedFrom 本身不构成新调用证明。
+3. 重扫 fork/父文件并重启 App；可信事件身份及 165 保持。若最终来源合同不能证明本例固定 fixture 的复制和新增关系，本例在运行前保持 BLOCKED，不能临场改写为另一预期或手填 PASS。</x:v>
       </x:c>
       <x:c r="H181" s="4" t="str">
         <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
@@ -16004,7 +16002,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L181" s="4" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:49</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:39</x:v>
       </x:c>
       <x:c r="M181" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -16018,10 +16016,10 @@
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B182" s="9" t="str">
-        <x:v>TC-TM005-CONTRACT-05</x:v>
+        <x:v>TC-TM005-CONTRACT-04</x:v>
       </x:c>
       <x:c r="C182" s="9" t="str">
-        <x:v>Codex 逐响应与缓存子项</x:v>
+        <x:v>Claude 父会话与子代理独立用量</x:v>
       </x:c>
       <x:c r="D182" s="9" t="str">
         <x:v>TASK-TM005-EVENT-CONTRACT</x:v>
@@ -16030,12 +16028,12 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F182" s="9" t="str">
-        <x:v>TM-003 阶段隔离原生 Codex 0.158.0-alpha.2.1 rollout 形状：一条 token_usage_record，response_id=tm003-native-probe-response-1，input100、cached read20、cache write0、output10、reasoning2、total110；原始 JSONL SHA-256 3b30cfa81c0c29a80f1bfc1de5bf823db01a9a85636e41ec58dfdd00f0436d08</x:v>
+        <x:v>TM-004 最终锁定的 Claude Code 2.1.126 自写主会话与 subagents/agent-*.jsonl fixture；设计数字为父调用 M=100/10、子代理调用 S=200/20，两者各有独立 usage。已固定的来源样本中子文件带 agentId、isSidechain=true，与父文件同 sessionId</x:v>
       </x:c>
       <x:c r="G182" s="9" t="str">
-        <x:v>1. 由 TM-003 最终固定数据程序在本例拥有的 Codex 根生成受支持原生日志，从安装后的 App 授权并采集；UI 和只读 DB 恰有一个可信逐响应身份，input100、output10、total110。
-2. UI 缓存读20、缓存写0、推理输出2作为已知子项分别显示，不再加到 total；同一 rollout 内 turn/thread 累计快照不能生成第二个 110 调用。
-3. 重扫、刷新、重启后仍为一个身份/110；原生日志原件或派生 fixture 的摘要与运行记录一致。</x:v>
+        <x:v>1. App 授权本例 Claude 根并采集父会话；只有父调用 M 入账，UI/DB 显示可信 110 及父来源身份。
+2. 子代理原生日志完整写入并由 App 采集；UI/DB 恰有 M、S 两个可信调用，total=330。父会话对子代理的引用不能另加 220；父子同 sessionId 也不能把子代理的真实调用消掉。
+3. 重扫主/子文件、刷新并重启；两个唯一身份与 330 保持，模型维度分别保留实际模型标识。若最终 raw 无法证明该父子关系或独立调用，本例在运行前保持 BLOCKED，不临场更换结果判据。</x:v>
       </x:c>
       <x:c r="H182" s="9" t="str">
         <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
@@ -16052,7 +16050,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L182" s="9" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:59</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:49</x:v>
       </x:c>
       <x:c r="M182" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -16066,10 +16064,10 @@
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B183" s="4" t="str">
-        <x:v>TC-TM005-CONTRACT-06</x:v>
+        <x:v>TC-TM005-CONTRACT-05</x:v>
       </x:c>
       <x:c r="C183" s="4" t="str">
-        <x:v>Codex fork 的累计快照不当增量</x:v>
+        <x:v>Codex 逐响应与缓存子项</x:v>
       </x:c>
       <x:c r="D183" s="4" t="str">
         <x:v>TASK-TM005-EVENT-CONTRACT</x:v>
@@ -16078,12 +16076,12 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F183" s="4" t="str">
-        <x:v>上游最终固定的 Codex exec fork 原生日志；设计数字为父响应 A=100/10、B=200/20，fork 新文件仅新响应 C=300/30，C 行的 thread_token_usage 为 A+B+C 累计 660</x:v>
+        <x:v>TM-003 阶段隔离原生 Codex 0.158.0-alpha.2.1 rollout 形状：一条 token_usage_record，response_id=tm003-native-probe-response-1，input100、cached read20、cache write0、output10、reasoning2、total110；原始 JSONL SHA-256 3b30cfa81c0c29a80f1bfc1de5bf823db01a9a85636e41ec58dfdd00f0436d08</x:v>
       </x:c>
       <x:c r="G183" s="4" t="str">
-        <x:v>1. App 采集父日志 A/B；UI 与 DB 应有两个可信响应身份，total 330。
-2. App 读取仅含 C 的 fork 新文件；可信身份增至三个，total 660。C 的逐响应 330 只加一次，thread_token_usage=660 不另加为第四个调用或在本步加 660。
-3. 重扫父/fork 文件并重启；仍三个身份/660。若上游 fork 身份/解析证据不完整，记录未确定诊断，不按累计值补造事件。</x:v>
+        <x:v>1. 由 TM-003 最终固定数据程序在本例拥有的 Codex 根生成受支持原生日志，从安装后的 App 授权并采集；UI 和只读 DB 恰有一个可信逐响应身份，input100、output10、total110。
+2. UI 缓存读20、缓存写0、推理输出2作为已知子项分别显示，不再加到 total；同一 rollout 内 turn/thread 累计快照不能生成第二个 110 调用。
+3. 重扫、刷新、重启后仍为一个身份/110；原生日志原件或派生 fixture 的摘要与运行记录一致。</x:v>
       </x:c>
       <x:c r="H183" s="4" t="str">
         <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
@@ -16100,7 +16098,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L183" s="4" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:69</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:59</x:v>
       </x:c>
       <x:c r="M183" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -16114,10 +16112,10 @@
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B184" s="9" t="str">
-        <x:v>TC-TM005-CONTRACT-07</x:v>
+        <x:v>TC-TM005-CONTRACT-06</x:v>
       </x:c>
       <x:c r="C184" s="9" t="str">
-        <x:v>Claude 同消息多行不重复</x:v>
+        <x:v>Codex fork 的累计快照不当增量</x:v>
       </x:c>
       <x:c r="D184" s="9" t="str">
         <x:v>TASK-TM005-EVENT-CONTRACT</x:v>
@@ -16126,11 +16124,12 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F184" s="9" t="str">
-        <x:v>TM-004 提交 dda5ccb 所记录的 Claude Code 2.1.126 原生日志形状：一个 API 消息的双 text 块对应两条 assistant JSONL，message.id 相同且每行都带完整 usage input31/output9</x:v>
+        <x:v>上游最终固定的 Codex exec fork 原生日志；设计数字为父响应 A=100/10、B=200/20，fork 新文件仅新响应 C=300/30，C 行的 thread_token_usage 为 A+B+C 累计 660</x:v>
       </x:c>
       <x:c r="G184" s="9" t="str">
-        <x:v>1. App 采集该消息；UI/DB 只出现一个可信调用身份，input31/output9/total40，而不是两行求和的 80。
-2. 刷新、重扫并重启；仍一个调用/40，明细不出现第二个相同消息。</x:v>
+        <x:v>1. App 采集父日志 A/B；UI 与 DB 应有两个可信响应身份，total 330。
+2. App 读取仅含 C 的 fork 新文件；可信身份增至三个，total 660。C 的逐响应 330 只加一次，thread_token_usage=660 不另加为第四个调用或在本步加 660。
+3. 重扫父/fork 文件并重启；仍三个身份/660。若上游 fork 身份/解析证据不完整，记录未确定诊断，不按累计值补造事件。</x:v>
       </x:c>
       <x:c r="H184" s="9" t="str">
         <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
@@ -16147,7 +16146,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L184" s="9" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:79</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:69</x:v>
       </x:c>
       <x:c r="M184" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -16161,10 +16160,10 @@
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B185" s="4" t="str">
-        <x:v>TC-TM005-CONTRACT-08</x:v>
+        <x:v>TC-TM005-CONTRACT-07</x:v>
       </x:c>
       <x:c r="C185" s="4" t="str">
-        <x:v>两来源原生 ID 碰撞与同源重放</x:v>
+        <x:v>Claude 同消息多行不重复</x:v>
       </x:c>
       <x:c r="D185" s="4" t="str">
         <x:v>TASK-TM005-EVENT-CONTRACT</x:v>
@@ -16173,12 +16172,11 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F185" s="4" t="str">
-        <x:v>隔离 Codex 与 Claude 原生日志各有不同的真实调用，却故意使其来源原生调用 ID 同为 shared-native-id-1；设计用量 Codex A=100/10、Claude B=200/20。再重放 Claude B 的相同原生记录</x:v>
+        <x:v>TM-004 提交 dda5ccb 所记录的 Claude Code 2.1.126 原生日志形状：一个 API 消息的双 text 块对应两条 assistant JSONL，message.id 相同且每行都带完整 usage input31/output9</x:v>
       </x:c>
       <x:c r="G185" s="4" t="str">
-        <x:v>1. App 经两授权根先采集 Codex A；UI/只读 SQLite 有一个可信调用，total 110，记录 source=codex 与 source_event_key 的不泄露表示。
-2. App 再采集同原生 ID 的 Claude B；UI/SQLite 应有两个不同来源的可信调用，total 330。不能因跨来源 ID 碰撞压掉 B，也不能把 A 改写为 B。
-3. 重放 B 并刷新/重启；仍两个可信调用/330，同一 Claude 调用未重复。SQLite 旁证须同时检查两个来源身份、各自 token 和唯一键，而非仅检查总量。</x:v>
+        <x:v>1. App 采集该消息；UI/DB 只出现一个可信调用身份，input31/output9/total40，而不是两行求和的 80。
+2. 刷新、重扫并重启；仍一个调用/40，明细不出现第二个相同消息。</x:v>
       </x:c>
       <x:c r="H185" s="4" t="str">
         <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
@@ -16195,7 +16193,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L185" s="4" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:88</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:79</x:v>
       </x:c>
       <x:c r="M185" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -16209,10 +16207,10 @@
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B186" s="9" t="str">
-        <x:v>TC-TM005-CONTRACT-09</x:v>
+        <x:v>TC-TM005-CONTRACT-08</x:v>
       </x:c>
       <x:c r="C186" s="9" t="str">
-        <x:v>Claude 同 ID 继承关系无法证明</x:v>
+        <x:v>两来源原生 ID 碰撞与同源重放</x:v>
       </x:c>
       <x:c r="D186" s="9" t="str">
         <x:v>TASK-TM005-EVENT-CONTRACT</x:v>
@@ -16221,12 +16219,12 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F186" s="9" t="str">
-        <x:v>同一合成账号下两条 Claude Agent/会话原始记录都用 assistant.message.id=shared-claude-id-1、相同模型和 input100/output10；首调用 A 已可信，第二条 B 位于另一 Agent/会话，缺少能证明复制或独立新调用的父链/来源证据。相同用量/模型使本例只检验继承不确定性，不与 identity_conflict 混合</x:v>
+        <x:v>隔离 Codex 与 Claude 原生日志各有不同的真实调用，却故意使其来源原生调用 ID 同为 shared-native-id-1；设计用量 Codex A=100/10、Claude B=200/20。再重放 Claude B 的相同原生记录</x:v>
       </x:c>
       <x:c r="G186" s="9" t="str">
-        <x:v>1. App 采集 A；UI/SQLite 有一个可信 Claude 调用，已知部分 110。
-2. 追加 B 并刷新；不能静默把 B 视为 A 的已证复制，也不能武断另加 110。UI 显示统计不完整、已知部分仍 110；诊断 unverified_inheritance，覆盖状态不完整。SQLite 保留 A 的可信键/值及不含原始 ID/完整路径的诊断代码、数量和来源归属旁证，不要求持久化 B 原文。
-3. 重扫/重启后诊断与已知部分保持；若 TM-004 最终合同找到可证复制/独立身份，先修本用例输入与预期并重新基线，不在运行时临时选答案。</x:v>
+        <x:v>1. App 经两授权根先采集 Codex A；UI/只读 SQLite 有一个可信调用，total 110，记录 source=codex 与 source_event_key 的不泄露表示。
+2. App 再采集同原生 ID 的 Claude B；UI/SQLite 应有两个不同来源的可信调用，total 330。不能因跨来源 ID 碰撞压掉 B，也不能把 A 改写为 B。
+3. 重放 B 并刷新/重启；仍两个可信调用/330，同一 Claude 调用未重复。SQLite 旁证须同时检查两个来源身份、各自 token 和唯一键，而非仅检查总量。</x:v>
       </x:c>
       <x:c r="H186" s="9" t="str">
         <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
@@ -16243,7 +16241,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L186" s="9" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:98</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:88</x:v>
       </x:c>
       <x:c r="M186" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -16257,10 +16255,10 @@
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B187" s="4" t="str">
-        <x:v>TC-TM005-CONTRACT-10</x:v>
+        <x:v>TC-TM005-CONTRACT-09</x:v>
       </x:c>
       <x:c r="C187" s="4" t="str">
-        <x:v>同 ID 用量或模型冲突</x:v>
+        <x:v>Claude 同 ID 继承关系无法证明</x:v>
       </x:c>
       <x:c r="D187" s="4" t="str">
         <x:v>TASK-TM005-EVENT-CONTRACT</x:v>
@@ -16269,12 +16267,12 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F187" s="4" t="str">
-        <x:v>Claude 同 assistant.message.id=conflict-claude-id-1 的首可信调用 A=100/10、模型 model-a；两个稳定变体 TC-TM005-CONTRACT-10#USAGE（后续同 ID usage 改为 200/20）与 TC-TM005-CONTRACT-10#MODEL（后续同 ID 用量仍 100/10、模型改为 model-b）</x:v>
+        <x:v>同一合成账号下两条 Claude Agent/会话原始记录都用 assistant.message.id=shared-claude-id-1、相同模型和 input100/output10；首调用 A 已可信，第二条 B 位于另一 Agent/会话，缺少能证明复制或独立新调用的父链/来源证据。相同用量/模型使本例只检验继承不确定性，不与 identity_conflict 混合</x:v>
       </x:c>
       <x:c r="G187" s="4" t="str">
-        <x:v>1. 每个变体从独立空客户端库采集 A；UI/SQLite 为一个可信事件、total110、模型 model-a。
-2. 追加对应矛盾行并刷新；identity_conflict 诊断出现，A 的用量和模型保持，已知部分 110，不新增/覆盖可信事件，不把统计标为完整。
-3. 重扫/重启；冲突诊断和首可信值保持。两个变体分别保存原始结果；不得用一个变体通过覆盖另一变体。</x:v>
+        <x:v>1. App 采集 A；UI/SQLite 有一个可信 Claude 调用，已知部分 110。
+2. 追加 B 并刷新；不能静默把 B 视为 A 的已证复制，也不能武断另加 110。UI 显示统计不完整、已知部分仍 110；诊断 unverified_inheritance，覆盖状态不完整。SQLite 保留 A 的可信键/值及不含原始 ID/完整路径的诊断代码、数量和来源归属旁证，不要求持久化 B 原文。
+3. 重扫/重启后诊断与已知部分保持；若 TM-004 最终合同找到可证复制/独立身份，先修本用例输入与预期并重新基线，不在运行时临时选答案。</x:v>
       </x:c>
       <x:c r="H187" s="4" t="str">
         <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
@@ -16291,7 +16289,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L187" s="4" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:108</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:98</x:v>
       </x:c>
       <x:c r="M187" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -16305,10 +16303,10 @@
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B188" s="9" t="str">
-        <x:v>TC-TM005-CONTRACT-10#USAGE</x:v>
+        <x:v>TC-TM005-CONTRACT-10</x:v>
       </x:c>
       <x:c r="C188" s="9" t="str">
-        <x:v>同 ID 用量或模型冲突 · 变体</x:v>
+        <x:v>同 ID 用量或模型冲突</x:v>
       </x:c>
       <x:c r="D188" s="9" t="str">
         <x:v>TASK-TM005-EVENT-CONTRACT</x:v>
@@ -16317,10 +16315,12 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F188" s="9" t="str">
-        <x:v>从独立空库导入 A，再导入同 ID、同模型但 200/20 的行</x:v>
+        <x:v>Claude 同 assistant.message.id=conflict-claude-id-1 的首可信调用 A=100/10、模型 model-a；两个稳定变体 TC-TM005-CONTRACT-10#USAGE（后续同 ID usage 改为 200/20）与 TC-TM005-CONTRACT-10#MODEL（后续同 ID 用量仍 100/10、模型改为 model-b）</x:v>
       </x:c>
       <x:c r="G188" s="9" t="str">
-        <x:v>identity_conflict，可信统计仍为 A 的 110。</x:v>
+        <x:v>1. 每个变体从独立空客户端库采集 A；UI/SQLite 为一个可信事件、total110、模型 model-a。
+2. 追加对应矛盾行并刷新；identity_conflict 诊断出现，A 的用量和模型保持，已知部分 110，不新增/覆盖可信事件，不把统计标为完整。
+3. 重扫/重启；冲突诊断和首可信值保持。两个变体分别保存原始结果；不得用一个变体通过覆盖另一变体。</x:v>
       </x:c>
       <x:c r="H188" s="9" t="str">
         <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
@@ -16334,7 +16334,7 @@
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K188" s="9" t="str">
-        <x:v>细化变体</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L188" s="9" t="str">
         <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:108</x:v>
@@ -16351,7 +16351,7 @@
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B189" s="4" t="str">
-        <x:v>TC-TM005-CONTRACT-10#MODEL</x:v>
+        <x:v>TC-TM005-CONTRACT-10#USAGE</x:v>
       </x:c>
       <x:c r="C189" s="4" t="str">
         <x:v>同 ID 用量或模型冲突 · 变体</x:v>
@@ -16363,10 +16363,10 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F189" s="4" t="str">
-        <x:v>从独立空库导入 A，再导入同 ID、100/10 但模型为 model-b 的行</x:v>
+        <x:v>从独立空库导入 A，再导入同 ID、同模型但 200/20 的行</x:v>
       </x:c>
       <x:c r="G189" s="4" t="str">
-        <x:v>identity_conflict，可信统计仍为 A 的 110 且模型为 model-a。</x:v>
+        <x:v>identity_conflict，可信统计仍为 A 的 110。</x:v>
       </x:c>
       <x:c r="H189" s="4" t="str">
         <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
@@ -16397,25 +16397,22 @@
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B190" s="9" t="str">
-        <x:v>TC-TM005-RANGE-01</x:v>
+        <x:v>TC-TM005-CONTRACT-10#MODEL</x:v>
       </x:c>
       <x:c r="C190" s="9" t="str">
-        <x:v>今天</x:v>
+        <x:v>同 ID 用量或模型冲突 · 变体</x:v>
       </x:c>
       <x:c r="D190" s="9" t="str">
-        <x:v>TASK-TM005-RANGE-QUERY
-TASK-TM005-UI</x:v>
+        <x:v>TASK-TM005-EVENT-CONTRACT</x:v>
       </x:c>
       <x:c r="E190" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F190" s="9" t="str">
-        <x:v>seed42 全部 13 行映射为两来源原生事件，1 行为 today-gpt 原样重复；上海日锚点与运行日一致</x:v>
+        <x:v>从独立空库导入 A，再导入同 ID、100/10 但模型为 model-b 的行</x:v>
       </x:c>
       <x:c r="G190" s="9" t="str">
-        <x:v>1. 经 App 采集后选“今天”；卡片应显示唯一 5 次、input 15000、output 1500、total 16500、cached read 1700、reasoning 170，子项不再加到 total。规范化语义样例没有 cache write 字段；若最终 raw 映射也没有可核实字段，该子项应显示未知而非 0。
-2. 检查趋势今天点为 16500，明细 ID 集合恰为 today-gpt/sonnet/qwen/glm/unknown 的五项；每条来源、模型、UTC 时间与原生日志对应，不显示重复行。
-3. 只读 DB 核对今天半开 UTC 范围内五个唯一可信身份及各字段合计；源集合、UI、DB 相同。</x:v>
+        <x:v>identity_conflict，可信统计仍为 A 的 110 且模型为 model-a。</x:v>
       </x:c>
       <x:c r="H190" s="9" t="str">
         <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
@@ -16429,10 +16426,10 @@
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K190" s="9" t="str">
-        <x:v>细化用例</x:v>
+        <x:v>细化变体</x:v>
       </x:c>
       <x:c r="L190" s="9" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:121</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:108</x:v>
       </x:c>
       <x:c r="M190" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -16446,24 +16443,25 @@
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B191" s="4" t="str">
-        <x:v>TC-TM005-RANGE-02</x:v>
+        <x:v>TC-TM005-RANGE-01</x:v>
       </x:c>
       <x:c r="C191" s="4" t="str">
-        <x:v>昨天</x:v>
+        <x:v>今天</x:v>
       </x:c>
       <x:c r="D191" s="4" t="str">
-        <x:v>TASK-TM005-RANGE-QUERY</x:v>
+        <x:v>TASK-TM005-RANGE-QUERY
+TASK-TM005-UI</x:v>
       </x:c>
       <x:c r="E191" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F191" s="4" t="str">
-        <x:v>同一批原生数据；yesterday 在上海日界前 1 秒</x:v>
+        <x:v>seed42 全部 13 行映射为两来源原生事件，1 行为 today-gpt 原样重复；上海日锚点与运行日一致</x:v>
       </x:c>
       <x:c r="G191" s="4" t="str">
-        <x:v>1. 选“昨天”；卡片仅 1 次，input 100、output 10、total 110，cache 20、reasoning 2。
-2. 趋势该日点 110、明细仅 yesterday；today-gpt 的上海 00:00 边界事件不能出现在此日。
-3. 只读 DB 查询该当地日换算的 UTC 半开区间，仅返回 yesterday；确认筛选没有写用量表。</x:v>
+        <x:v>1. 经 App 采集后选“今天”；卡片应显示唯一 5 次、input 15000、output 1500、total 16500、cached read 1700、reasoning 170，子项不再加到 total。规范化语义样例没有 cache write 字段；若最终 raw 映射也没有可核实字段，该子项应显示未知而非 0。
+2. 检查趋势今天点为 16500，明细 ID 集合恰为 today-gpt/sonnet/qwen/glm/unknown 的五项；每条来源、模型、UTC 时间与原生日志对应，不显示重复行。
+3. 只读 DB 核对今天半开 UTC 范围内五个唯一可信身份及各字段合计；源集合、UI、DB 相同。</x:v>
       </x:c>
       <x:c r="H191" s="4" t="str">
         <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
@@ -16480,7 +16478,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L191" s="4" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:131</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:121</x:v>
       </x:c>
       <x:c r="M191" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -16494,10 +16492,10 @@
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B192" s="9" t="str">
-        <x:v>TC-TM005-RANGE-03</x:v>
+        <x:v>TC-TM005-RANGE-02</x:v>
       </x:c>
       <x:c r="C192" s="9" t="str">
-        <x:v>近 7 天</x:v>
+        <x:v>昨天</x:v>
       </x:c>
       <x:c r="D192" s="9" t="str">
         <x:v>TASK-TM005-RANGE-QUERY</x:v>
@@ -16506,12 +16504,12 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F192" s="9" t="str">
-        <x:v>上海当地 09-23 至 29 日语义窗口整体平移到运行日</x:v>
+        <x:v>同一批原生数据；yesterday 在上海日界前 1 秒</x:v>
       </x:c>
       <x:c r="G192" s="9" t="str">
-        <x:v>1. 选“近 7 天”；卡片 7 次、total 17380，左边界 day7 包含。
-2. 趋势非空日仅为窗口内 day7=770、yesterday=110、today=16500；明细恰为今天五项加 yesterday/day7。其余日期的显示状态按覆盖证明判，不从缺事件推断 0。
-3. 只读 DB 对比 7 个唯一事件身份及 17380；重复 today-gpt 不入账。</x:v>
+        <x:v>1. 选“昨天”；卡片仅 1 次，input 100、output 10、total 110，cache 20、reasoning 2。
+2. 趋势该日点 110、明细仅 yesterday；today-gpt 的上海 00:00 边界事件不能出现在此日。
+3. 只读 DB 查询该当地日换算的 UTC 半开区间，仅返回 yesterday；确认筛选没有写用量表。</x:v>
       </x:c>
       <x:c r="H192" s="9" t="str">
         <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
@@ -16528,7 +16526,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L192" s="9" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:139</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:131</x:v>
       </x:c>
       <x:c r="M192" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -16542,10 +16540,10 @@
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B193" s="4" t="str">
-        <x:v>TC-TM005-RANGE-04</x:v>
+        <x:v>TC-TM005-RANGE-03</x:v>
       </x:c>
       <x:c r="C193" s="4" t="str">
-        <x:v>近 15 天</x:v>
+        <x:v>近 7 天</x:v>
       </x:c>
       <x:c r="D193" s="4" t="str">
         <x:v>TASK-TM005-RANGE-QUERY</x:v>
@@ -16554,12 +16552,12 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F193" s="4" t="str">
-        <x:v>上海当地 09-15 至 29 日语义窗口</x:v>
+        <x:v>上海当地 09-23 至 29 日语义窗口整体平移到运行日</x:v>
       </x:c>
       <x:c r="G193" s="4" t="str">
-        <x:v>1. 选“近 15 天”；卡片 10 次、total 27830，day15 在左边界包含。
-2. 趋势非空日为 day15=1650、custom-start=2200、custom-end=6600、day7=770、yesterday=110、today=16500；明细为这 10 个唯一事件。
-3. 只读 DB 核对半开区间/10 个身份/27830；不把 day30 提前包含。</x:v>
+        <x:v>1. 选“近 7 天”；卡片 7 次、total 17380，左边界 day7 包含。
+2. 趋势非空日仅为窗口内 day7=770、yesterday=110、today=16500；明细恰为今天五项加 yesterday/day7。其余日期的显示状态按覆盖证明判，不从缺事件推断 0。
+3. 只读 DB 对比 7 个唯一事件身份及 17380；重复 today-gpt 不入账。</x:v>
       </x:c>
       <x:c r="H193" s="4" t="str">
         <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
@@ -16576,7 +16574,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L193" s="4" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:147</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:139</x:v>
       </x:c>
       <x:c r="M193" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -16590,10 +16588,10 @@
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B194" s="9" t="str">
-        <x:v>TC-TM005-RANGE-05</x:v>
+        <x:v>TC-TM005-RANGE-04</x:v>
       </x:c>
       <x:c r="C194" s="9" t="str">
-        <x:v>近 30 天</x:v>
+        <x:v>近 15 天</x:v>
       </x:c>
       <x:c r="D194" s="9" t="str">
         <x:v>TASK-TM005-RANGE-QUERY</x:v>
@@ -16602,12 +16600,12 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F194" s="9" t="str">
-        <x:v>上海当地 08-31 至 09-29 日语义窗口</x:v>
+        <x:v>上海当地 09-15 至 29 日语义窗口</x:v>
       </x:c>
       <x:c r="G194" s="9" t="str">
-        <x:v>1. 选“近 30 天”；卡片 11 次、total 31130，day30 在左边界包含，前 1 秒的 outside30 排除。
-2. 趋势增加 day30=3300 点；明细为近 15 天十项加 day30，没有 outside30。
-3. 只读 DB 核对 11 个身份/31130；刷新后仍一致。</x:v>
+        <x:v>1. 选“近 15 天”；卡片 10 次、total 27830，day15 在左边界包含。
+2. 趋势非空日为 day15=1650、custom-start=2200、custom-end=6600、day7=770、yesterday=110、today=16500；明细为这 10 个唯一事件。
+3. 只读 DB 核对半开区间/10 个身份/27830；不把 day30 提前包含。</x:v>
       </x:c>
       <x:c r="H194" s="9" t="str">
         <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
@@ -16624,7 +16622,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L194" s="9" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:155</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:147</x:v>
       </x:c>
       <x:c r="M194" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -16638,10 +16636,10 @@
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B195" s="4" t="str">
-        <x:v>TC-TM005-RANGE-06</x:v>
+        <x:v>TC-TM005-RANGE-05</x:v>
       </x:c>
       <x:c r="C195" s="4" t="str">
-        <x:v>自定义半开日期</x:v>
+        <x:v>近 30 天</x:v>
       </x:c>
       <x:c r="D195" s="4" t="str">
         <x:v>TASK-TM005-RANGE-QUERY</x:v>
@@ -16650,12 +16648,12 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F195" s="4" t="str">
-        <x:v>上海当地 09-20 至 21 日语义窗口，结束上界为 09-22 00:00</x:v>
+        <x:v>上海当地 08-31 至 09-29 日语义窗口</x:v>
       </x:c>
       <x:c r="G195" s="4" t="str">
-        <x:v>1. 在 UI 输入整体平移后的起止日并应用；卡片 1 次、input 2000、output 200、total 2200。
-2. 趋势只有 custom-start=2200 非空点，明细仅该事件；custom-end 在排除上界，不能出现。
-3. DB 只读查询 [start,end)；预期仅返回唯一 custom-start，查询不写入用量。</x:v>
+        <x:v>1. 选“近 30 天”；卡片 11 次、total 31130，day30 在左边界包含，前 1 秒的 outside30 排除。
+2. 趋势增加 day30=3300 点；明细为近 15 天十项加 day30，没有 outside30。
+3. 只读 DB 核对 11 个身份/31130；刷新后仍一致。</x:v>
       </x:c>
       <x:c r="H195" s="4" t="str">
         <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
@@ -16672,7 +16670,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L195" s="4" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:163</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:155</x:v>
       </x:c>
       <x:c r="M195" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -16686,10 +16684,10 @@
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B196" s="9" t="str">
-        <x:v>TC-TM005-RANGE-09</x:v>
+        <x:v>TC-TM005-RANGE-06</x:v>
       </x:c>
       <x:c r="C196" s="9" t="str">
-        <x:v>起日大于止日</x:v>
+        <x:v>自定义半开日期</x:v>
       </x:c>
       <x:c r="D196" s="9" t="str">
         <x:v>TASK-TM005-RANGE-QUERY</x:v>
@@ -16698,11 +16696,12 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F196" s="9" t="str">
-        <x:v>上海语义锚点平移后的起日 09-22、止日 09-20；此前已选“今天”显示 16500</x:v>
+        <x:v>上海当地 09-20 至 21 日语义窗口，结束上界为 09-22 00:00</x:v>
       </x:c>
       <x:c r="G196" s="9" t="str">
-        <x:v>1. 在自定义日期表单输入倒置范围并应用；UI 显示可识别的日期范围错误，不发起新查询，原卡片/趋势/明细仍对应今天 16500/五项。
-2. 只读 DB 核对用量与设置，再恢复有效范围查询；预期倒置范围没有写入，有效范围仍显示 2200，前次错误不污染状态。</x:v>
+        <x:v>1. 在 UI 输入整体平移后的起止日并应用；卡片 1 次、input 2000、output 200、total 2200。
+2. 趋势只有 custom-start=2200 非空点，明细仅该事件；custom-end 在排除上界，不能出现。
+3. DB 只读查询 [start,end)；预期仅返回唯一 custom-start，查询不写入用量。</x:v>
       </x:c>
       <x:c r="H196" s="9" t="str">
         <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
@@ -16719,7 +16718,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L196" s="9" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:171</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:163</x:v>
       </x:c>
       <x:c r="M196" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -16733,10 +16732,10 @@
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B197" s="4" t="str">
-        <x:v>TC-TM005-RANGE-10</x:v>
+        <x:v>TC-TM005-RANGE-09</x:v>
       </x:c>
       <x:c r="C197" s="4" t="str">
-        <x:v>空起日与空止日</x:v>
+        <x:v>起日大于止日</x:v>
       </x:c>
       <x:c r="D197" s="4" t="str">
         <x:v>TASK-TM005-RANGE-QUERY</x:v>
@@ -16745,11 +16744,11 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F197" s="4" t="str">
-        <x:v>两个独立变体 TC-TM005-RANGE-10#START_EMPTY（起日空、止日 09-21）和 TC-TM005-RANGE-10#END_EMPTY（起日 09-20、止日空）；此前已选今天 16500</x:v>
+        <x:v>上海语义锚点平移后的起日 09-22、止日 09-20；此前已选“今天”显示 16500</x:v>
       </x:c>
       <x:c r="G197" s="4" t="str">
-        <x:v>1. 每个变体独立从今天结果开始，清空指定字段并应用；表单拒绝，保留原卡片 16500、今天趋势和五条明细。
-2. 分别核对没有发起查询或写 DB；补齐字段后自定义有效窗口显示 2200。两个变体分别记录原始结果，不以其中一个通过代替另一个。</x:v>
+        <x:v>1. 在自定义日期表单输入倒置范围并应用；UI 显示可识别的日期范围错误，不发起新查询，原卡片/趋势/明细仍对应今天 16500/五项。
+2. 只读 DB 核对用量与设置，再恢复有效范围查询；预期倒置范围没有写入，有效范围仍显示 2200，前次错误不污染状态。</x:v>
       </x:c>
       <x:c r="H197" s="4" t="str">
         <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
@@ -16766,7 +16765,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L197" s="4" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:180</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:171</x:v>
       </x:c>
       <x:c r="M197" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -16780,10 +16779,10 @@
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B198" s="9" t="str">
-        <x:v>TC-TM005-RANGE-10#START_EMPTY</x:v>
+        <x:v>TC-TM005-RANGE-10</x:v>
       </x:c>
       <x:c r="C198" s="9" t="str">
-        <x:v>空起日与空止日 · 变体</x:v>
+        <x:v>空起日与空止日</x:v>
       </x:c>
       <x:c r="D198" s="9" t="str">
         <x:v>TASK-TM005-RANGE-QUERY</x:v>
@@ -16792,10 +16791,11 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F198" s="9" t="str">
-        <x:v>保持止日 09-21，清空起日并应用</x:v>
+        <x:v>两个独立变体 TC-TM005-RANGE-10#START_EMPTY（起日空、止日 09-21）和 TC-TM005-RANGE-10#END_EMPTY（起日 09-20、止日空）；此前已选今天 16500</x:v>
       </x:c>
       <x:c r="G198" s="9" t="str">
-        <x:v>拒绝查询，今天卡片仍为 16500、五条明细不变。</x:v>
+        <x:v>1. 每个变体独立从今天结果开始，清空指定字段并应用；表单拒绝，保留原卡片 16500、今天趋势和五条明细。
+2. 分别核对没有发起查询或写 DB；补齐字段后自定义有效窗口显示 2200。两个变体分别记录原始结果，不以其中一个通过代替另一个。</x:v>
       </x:c>
       <x:c r="H198" s="9" t="str">
         <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
@@ -16809,7 +16809,7 @@
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K198" s="9" t="str">
-        <x:v>细化变体</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L198" s="9" t="str">
         <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:180</x:v>
@@ -16826,7 +16826,7 @@
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B199" s="4" t="str">
-        <x:v>TC-TM005-RANGE-10#END_EMPTY</x:v>
+        <x:v>TC-TM005-RANGE-10#START_EMPTY</x:v>
       </x:c>
       <x:c r="C199" s="4" t="str">
         <x:v>空起日与空止日 · 变体</x:v>
@@ -16838,7 +16838,7 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F199" s="4" t="str">
-        <x:v>保持起日 09-20，清空止日并应用</x:v>
+        <x:v>保持止日 09-21，清空起日并应用</x:v>
       </x:c>
       <x:c r="G199" s="4" t="str">
         <x:v>拒绝查询，今天卡片仍为 16500、五条明细不变。</x:v>
@@ -16872,25 +16872,22 @@
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B200" s="9" t="str">
-        <x:v>TC-TM005-RANGE-08</x:v>
+        <x:v>TC-TM005-RANGE-10#END_EMPTY</x:v>
       </x:c>
       <x:c r="C200" s="9" t="str">
-        <x:v>刷新重启保持</x:v>
+        <x:v>空起日与空止日 · 变体</x:v>
       </x:c>
       <x:c r="D200" s="9" t="str">
-        <x:v>TASK-TM005-RANGE-QUERY
-TASK-TM005-UI</x:v>
+        <x:v>TASK-TM005-RANGE-QUERY</x:v>
       </x:c>
       <x:c r="E200" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F200" s="9" t="str">
-        <x:v>seed42 双来源全量与近 30 天选择</x:v>
+        <x:v>保持起日 09-20，清空止日并应用</x:v>
       </x:c>
       <x:c r="G200" s="9" t="str">
-        <x:v>1. 选择近 30 天并记录 UI/DB 初态；预期明细 11 项、total 31130，来源身份和覆盖状态与本例原始输入一致。
-2. App 内刷新并重扫两个来源；UI 与 DB 均不增量，仍 11 项/31130。
-3. 退出、重启安装后的同一 App/profile 并恢复筛选；UI 与 DB 仍 11 项/31130，授权状态和账号身份未串换。</x:v>
+        <x:v>拒绝查询，今天卡片仍为 16500、五条明细不变。</x:v>
       </x:c>
       <x:c r="H200" s="9" t="str">
         <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
@@ -16904,10 +16901,10 @@
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K200" s="9" t="str">
-        <x:v>细化用例</x:v>
+        <x:v>细化变体</x:v>
       </x:c>
       <x:c r="L200" s="9" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:192</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:180</x:v>
       </x:c>
       <x:c r="M200" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -16921,24 +16918,25 @@
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B201" s="4" t="str">
-        <x:v>TC-TM005-MODEL-01</x:v>
+        <x:v>TC-TM005-RANGE-08</x:v>
       </x:c>
       <x:c r="C201" s="4" t="str">
-        <x:v>模型维度</x:v>
+        <x:v>刷新重启保持</x:v>
       </x:c>
       <x:c r="D201" s="4" t="str">
-        <x:v>TASK-TM005-UI</x:v>
+        <x:v>TASK-TM005-RANGE-QUERY
+TASK-TM005-UI</x:v>
       </x:c>
       <x:c r="E201" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F201" s="4" t="str">
-        <x:v>今天五项，两个来源至少各一项，模型名保持来源可识别标识</x:v>
+        <x:v>seed42 双来源全量与近 30 天选择</x:v>
       </x:c>
       <x:c r="G201" s="4" t="str">
-        <x:v>1. 选今天和模型维度；行值应为 gpt-5=1100、sonnet-test=2200、qwen-test=3300、glm-test=4400、unknown-model=5500，合计 16500。
-2. 选 unknown-model；明细只含 today-unknown，Token 5500 有效，价格未知不显示为免费或 0 用量。
-3. 刷新并重启 App 后再次查询模型维度；预期分组与明细仍与来源身份及只读 DB 一致。</x:v>
+        <x:v>1. 选择近 30 天并记录 UI/DB 初态；预期明细 11 项、total 31130，来源身份和覆盖状态与本例原始输入一致。
+2. App 内刷新并重扫两个来源；UI 与 DB 均不增量，仍 11 项/31130。
+3. 退出、重启安装后的同一 App/profile 并恢复筛选；UI 与 DB 仍 11 项/31130，授权状态和账号身份未串换。</x:v>
       </x:c>
       <x:c r="H201" s="4" t="str">
         <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
@@ -16955,7 +16953,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L201" s="4" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:200</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:192</x:v>
       </x:c>
       <x:c r="M201" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -16969,25 +16967,24 @@
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B202" s="9" t="str">
-        <x:v>TC-TM005-MODEL-02</x:v>
+        <x:v>TC-TM005-MODEL-01</x:v>
       </x:c>
       <x:c r="C202" s="9" t="str">
-        <x:v>真实未知模型仍计用量</x:v>
+        <x:v>模型维度</x:v>
       </x:c>
       <x:c r="D202" s="9" t="str">
-        <x:v>TASK-TM005-UI
-TASK-TM005-EVENT-CONTRACT</x:v>
+        <x:v>TASK-TM005-UI</x:v>
       </x:c>
       <x:c r="E202" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F202" s="9" t="str">
-        <x:v>以 2026-09-29 上海当地日为语义锚点并随运行日整体平移的两条独立可信调用：Codex A 于锚点 2026-09-29T01:00:00Z，input100/output10，无法从同一 turn 核实模型，规范事件 model_id=null；Claude B 于 2026-09-29T02:00:00Z，input200/output20、模型 sonnet-test。这与 MODEL-01 中字面名称为 unknown-model 的已知模型不同</x:v>
+        <x:v>今天五项，两个来源至少各一项，模型名保持来源可识别标识</x:v>
       </x:c>
       <x:c r="G202" s="9" t="str">
-        <x:v>1. App 从两类已验证原生日志采集 A/B 后选该日；卡片显示两次、已知 total330，明细分别保留来源与用量，A 不因模型未知而丢失。
-2. 模型分组出现“未知模型”110 与 sonnet-test220，两组合计330；只读 SQLite 核对同一快照两条可信身份、A 的 model_id IS NULL、B 的模型及各自 input/output。
-3. 刷新并重启 App 后查询同一日期；预期仍为两次/330，未知模型不被擅自改为最近一行模型，也不被标成零费用或零用量。</x:v>
+        <x:v>1. 选今天和模型维度；行值应为 gpt-5=1100、sonnet-test=2200、qwen-test=3300、glm-test=4400、unknown-model=5500，合计 16500。
+2. 选 unknown-model；明细只含 today-unknown，Token 5500 有效，价格未知不显示为免费或 0 用量。
+3. 刷新并重启 App 后再次查询模型维度；预期分组与明细仍与来源身份及只读 DB 一致。</x:v>
       </x:c>
       <x:c r="H202" s="9" t="str">
         <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
@@ -17004,7 +17001,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L202" s="9" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:208</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:200</x:v>
       </x:c>
       <x:c r="M202" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -17018,24 +17015,25 @@
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B203" s="4" t="str">
-        <x:v>TC-TM005-RANGE-07</x:v>
+        <x:v>TC-TM005-MODEL-02</x:v>
       </x:c>
       <x:c r="C203" s="4" t="str">
-        <x:v>时区与月界</x:v>
+        <x:v>真实未知模型仍计用量</x:v>
       </x:c>
       <x:c r="D203" s="4" t="str">
-        <x:v>TASK-TM005-RANGE-QUERY</x:v>
+        <x:v>TASK-TM005-UI
+TASK-TM005-EVENT-CONTRACT</x:v>
       </x:c>
       <x:c r="E203" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F203" s="4" t="str">
-        <x:v>上海 09-28 15:59:59Z/16:00:00Z 与 UTC 08-30 15:59:59Z/16:00:00Z 四个语义边界事件，整体平移整数天</x:v>
+        <x:v>以 2026-09-29 上海当地日为语义锚点并随运行日整体平移的两条独立可信调用：Codex A 于锚点 2026-09-29T01:00:00Z，input100/output10，无法从同一 turn 核实模型，规范事件 model_id=null；Claude B 于 2026-09-29T02:00:00Z，input200/output20、模型 sonnet-test。这与 MODEL-01 中字面名称为 unknown-model 的已知模型不同</x:v>
       </x:c>
       <x:c r="G203" s="4" t="str">
-        <x:v>1. 团队时区为 Asia/Shanghai 时，上海昨天仅 yesterday=110，今天含 today-gpt=1100；近 30 天含 day30=3300，排除 outside30=11000。
-2. 经真实时区设置 UI 改为 UTC，用明确自定义 UTC 日期查询边界；09-28 UTC 同含 yesterday 与 today-gpt，total 1210；08-30 UTC 同含 outside30/day30，total 14300。事件 UTC 时间及 DB 源身份不变。
-3. 重启后 UTC 设置保留；再查询 UTC 近 30 天对应自定义窗口，total 27830，两个 08-30 事件均排除。只有显示分桶变动，DB 事件数仍 12 唯一。</x:v>
+        <x:v>1. App 从两类已验证原生日志采集 A/B 后选该日；卡片显示两次、已知 total330，明细分别保留来源与用量，A 不因模型未知而丢失。
+2. 模型分组出现“未知模型”110 与 sonnet-test220，两组合计330；只读 SQLite 核对同一快照两条可信身份、A 的 model_id IS NULL、B 的模型及各自 input/output。
+3. 刷新并重启 App 后查询同一日期；预期仍为两次/330，未知模型不被擅自改为最近一行模型，也不被标成零费用或零用量。</x:v>
       </x:c>
       <x:c r="H203" s="4" t="str">
         <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
@@ -17052,7 +17050,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L203" s="4" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:220</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:208</x:v>
       </x:c>
       <x:c r="M203" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -17061,15 +17059,15 @@
         <x:v>v0.5.0-20261001T034729Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="204" ht="147" customHeight="1">
+    <x:row r="204" ht="102" customHeight="1">
       <x:c r="A204" s="9" t="str">
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B204" s="9" t="str">
-        <x:v>TC-TM005-RANGE-11</x:v>
+        <x:v>TC-TM005-RANGE-07</x:v>
       </x:c>
       <x:c r="C204" s="9" t="str">
-        <x:v>夏令时当地日长度</x:v>
+        <x:v>时区与月界</x:v>
       </x:c>
       <x:c r="D204" s="9" t="str">
         <x:v>TASK-TM005-RANGE-QUERY</x:v>
@@ -17078,12 +17076,12 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F204" s="9" t="str">
-        <x:v>两个独立稳定变体 TC-TM005-RANGE-11#SPRING 与 TC-TM005-RANGE-11#FALL，团队时区经真实 UI 设为 America/New_York。春季 2026-03-08 的 UTC 半开界为 [2026-03-08T05:00:00Z,2026-03-09T04:00:00Z)；四个固定事件为边界前 S0（04:59:59Z，Codex 5/1）、起界 S1（05:00:00Z，Codex 9/1）、末界前 S2（次日03:59:59Z，Claude 18/2）、排除上界 S3（次日04:00:00Z，Claude 27/3）。秋季 2026-11-01 的界为 [2026-11-01T04:00:00Z,2026-11-02T05:00:00Z)；四个固定事件为 F0（03:59:59Z，Codex 5/1）、F1（04:00:00Z，Codex 36/4）、F2（次日04:59:59Z，Claude 45/5）、F3（次日05:00:00Z，Claude 54/6）。数值均为 input/output Token</x:v>
+        <x:v>上海 09-28 15:59:59Z/16:00:00Z 与 UTC 08-30 15:59:59Z/16:00:00Z 四个语义边界事件，整体平移整数天</x:v>
       </x:c>
       <x:c r="G204" s="9" t="str">
-        <x:v>1. 各变体从独立空库、已验证双来源原生日志和相同登录身份开始；UI 选对应自定义当地日，春季仅 S1/S2 两次/30，秋季仅 F1/F2 两次/90，S0/S3/F0/F3 不在对应当日明细或趋势点。
-2. 只读 SQLite 以明确 UTC 半开界核对两个源事件身份及 input+output 合计；春季窗口为 23 小时、秋季为 25 小时，不能使用固定 86400 秒上界。
-3. 重启后时区与两变体结果分别保持；每个变体单独报告，不以其中一个结果覆盖另一个。</x:v>
+        <x:v>1. 团队时区为 Asia/Shanghai 时，上海昨天仅 yesterday=110，今天含 today-gpt=1100；近 30 天含 day30=3300，排除 outside30=11000。
+2. 经真实时区设置 UI 改为 UTC，用明确自定义 UTC 日期查询边界；09-28 UTC 同含 yesterday 与 today-gpt，total 1210；08-30 UTC 同含 outside30/day30，total 14300。事件 UTC 时间及 DB 源身份不变。
+3. 重启后 UTC 设置保留；再查询 UTC 近 30 天对应自定义窗口，total 27830，两个 08-30 事件均排除。只有显示分桶变动，DB 事件数仍 12 唯一。</x:v>
       </x:c>
       <x:c r="H204" s="9" t="str">
         <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
@@ -17100,7 +17098,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L204" s="9" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:230</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:220</x:v>
       </x:c>
       <x:c r="M204" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -17109,15 +17107,15 @@
         <x:v>v0.5.0-20261001T034729Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="205" ht="102" customHeight="1">
+    <x:row r="205" ht="147" customHeight="1">
       <x:c r="A205" s="4" t="str">
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B205" s="4" t="str">
-        <x:v>TC-TM005-RANGE-11#SPRING</x:v>
+        <x:v>TC-TM005-RANGE-11</x:v>
       </x:c>
       <x:c r="C205" s="4" t="str">
-        <x:v>夏令时当地日长度 · 变体</x:v>
+        <x:v>夏令时当地日长度</x:v>
       </x:c>
       <x:c r="D205" s="4" t="str">
         <x:v>TASK-TM005-RANGE-QUERY</x:v>
@@ -17126,10 +17124,12 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F205" s="4" t="str">
-        <x:v>以纽约 2026-03-08 为当地日，导入 S0–S3</x:v>
+        <x:v>两个独立稳定变体 TC-TM005-RANGE-11#SPRING 与 TC-TM005-RANGE-11#FALL，团队时区经真实 UI 设为 America/New_York。春季 2026-03-08 的 UTC 半开界为 [2026-03-08T05:00:00Z,2026-03-09T04:00:00Z)；四个固定事件为边界前 S0（04:59:59Z，Codex 5/1）、起界 S1（05:00:00Z，Codex 9/1）、末界前 S2（次日03:59:59Z，Claude 18/2）、排除上界 S3（次日04:00:00Z，Claude 27/3）。秋季 2026-11-01 的界为 [2026-11-01T04:00:00Z,2026-11-02T05:00:00Z)；四个固定事件为 F0（03:59:59Z，Codex 5/1）、F1（04:00:00Z，Codex 36/4）、F2（次日04:59:59Z，Claude 45/5）、F3（次日05:00:00Z，Claude 54/6）。数值均为 input/output Token</x:v>
       </x:c>
       <x:c r="G205" s="4" t="str">
-        <x:v>仅含 S1/S2 两次、合计 30 Token，UTC 窗口长 23 小时。</x:v>
+        <x:v>1. 各变体从独立空库、已验证双来源原生日志和相同登录身份开始；UI 选对应自定义当地日，春季仅 S1/S2 两次/30，秋季仅 F1/F2 两次/90，S0/S3/F0/F3 不在对应当日明细或趋势点。
+2. 只读 SQLite 以明确 UTC 半开界核对两个源事件身份及 input+output 合计；春季窗口为 23 小时、秋季为 25 小时，不能使用固定 86400 秒上界。
+3. 重启后时区与两变体结果分别保持；每个变体单独报告，不以其中一个结果覆盖另一个。</x:v>
       </x:c>
       <x:c r="H205" s="4" t="str">
         <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
@@ -17143,7 +17143,7 @@
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K205" s="4" t="str">
-        <x:v>细化变体</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L205" s="4" t="str">
         <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:230</x:v>
@@ -17160,7 +17160,7 @@
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B206" s="9" t="str">
-        <x:v>TC-TM005-RANGE-11#FALL</x:v>
+        <x:v>TC-TM005-RANGE-11#SPRING</x:v>
       </x:c>
       <x:c r="C206" s="9" t="str">
         <x:v>夏令时当地日长度 · 变体</x:v>
@@ -17172,10 +17172,10 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F206" s="9" t="str">
-        <x:v>以纽约 2026-11-01 为当地日，导入 F0–F3</x:v>
+        <x:v>以纽约 2026-03-08 为当地日，导入 S0–S3</x:v>
       </x:c>
       <x:c r="G206" s="9" t="str">
-        <x:v>仅含 F1/F2 两次、合计 90 Token，UTC 窗口长 25 小时。</x:v>
+        <x:v>仅含 S1/S2 两次、合计 30 Token，UTC 窗口长 23 小时。</x:v>
       </x:c>
       <x:c r="H206" s="9" t="str">
         <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
@@ -17206,24 +17206,22 @@
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B207" s="4" t="str">
-        <x:v>TC-TM005-STATE-01</x:v>
+        <x:v>TC-TM005-RANGE-11#FALL</x:v>
       </x:c>
       <x:c r="C207" s="4" t="str">
-        <x:v>无覆盖是缺失</x:v>
+        <x:v>夏令时当地日长度 · 变体</x:v>
       </x:c>
       <x:c r="D207" s="4" t="str">
-        <x:v>TASK-TM005-COVERAGE</x:v>
+        <x:v>TASK-TM005-RANGE-QUERY</x:v>
       </x:c>
       <x:c r="E207" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F207" s="4" t="str">
-        <x:v>两来源均没有可证明覆盖的指定历史日，且没有可信事件</x:v>
+        <x:v>以纽约 2026-11-01 为当地日，导入 F0–F3</x:v>
       </x:c>
       <x:c r="G207" s="4" t="str">
-        <x:v>1. 从本例隔离库经 App 授权仅含近期日志的目录，打开早于已证实覆盖起点的自定义历史日；预期进入该日查询但尚不能凭空明细推断完整 0，DB 不新增用量事件。
-2. UI 显示缺失/不可确认，不能显示完整 0；趋势点/明细状态与卡片一致。DB 只读证明没有该日可信事件，且覆盖记录并未声称完整。
-3. 刷新后仍为缺失；空结果不能生成新零用量事件。</x:v>
+        <x:v>仅含 F1/F2 两次、合计 90 Token，UTC 窗口长 25 小时。</x:v>
       </x:c>
       <x:c r="H207" s="4" t="str">
         <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
@@ -17237,10 +17235,10 @@
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K207" s="4" t="str">
-        <x:v>细化用例</x:v>
+        <x:v>细化变体</x:v>
       </x:c>
       <x:c r="L207" s="4" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:243</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:230</x:v>
       </x:c>
       <x:c r="M207" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -17254,10 +17252,10 @@
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B208" s="9" t="str">
-        <x:v>TC-TM005-STATE-02</x:v>
+        <x:v>TC-TM005-STATE-01</x:v>
       </x:c>
       <x:c r="C208" s="9" t="str">
-        <x:v>已覆盖零调用</x:v>
+        <x:v>无覆盖是缺失</x:v>
       </x:c>
       <x:c r="D208" s="9" t="str">
         <x:v>TASK-TM005-COVERAGE</x:v>
@@ -17266,11 +17264,12 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F208" s="9" t="str">
-        <x:v>两来源对某完整当地日均有可核实、连续成功的覆盖证明，实际无调用</x:v>
+        <x:v>两来源均没有可证明覆盖的指定历史日，且没有可信事件</x:v>
       </x:c>
       <x:c r="G208" s="9" t="str">
-        <x:v>1. 在隔离 App 取得并核验两来源覆盖证明后选该日；UI 明确 0 次、0 Token，趋势该日为真实 0，明细为空。
-2. DB 只读核对覆盖区间完整、事件数 0；无任何合成“零调用事件”。重启后状态仍为已覆盖零。</x:v>
+        <x:v>1. 从本例隔离库经 App 授权仅含近期日志的目录，打开早于已证实覆盖起点的自定义历史日；预期进入该日查询但尚不能凭空明细推断完整 0，DB 不新增用量事件。
+2. UI 显示缺失/不可确认，不能显示完整 0；趋势点/明细状态与卡片一致。DB 只读证明没有该日可信事件，且覆盖记录并未声称完整。
+3. 刷新后仍为缺失；空结果不能生成新零用量事件。</x:v>
       </x:c>
       <x:c r="H208" s="9" t="str">
         <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
@@ -17287,7 +17286,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L208" s="9" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:251</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:243</x:v>
       </x:c>
       <x:c r="M208" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -17301,10 +17300,10 @@
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B209" s="4" t="str">
-        <x:v>TC-TM005-STATE-03</x:v>
+        <x:v>TC-TM005-STATE-02</x:v>
       </x:c>
       <x:c r="C209" s="4" t="str">
-        <x:v>字段未知</x:v>
+        <x:v>已覆盖零调用</x:v>
       </x:c>
       <x:c r="D209" s="4" t="str">
         <x:v>TASK-TM005-COVERAGE</x:v>
@@ -17313,12 +17312,11 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F209" s="4" t="str">
-        <x:v>一条受支持原生会话有时间/模型但缺可信 usage，另有正常可信调用 110</x:v>
+        <x:v>两来源对某完整当地日均有可核实、连续成功的覆盖证明，实际无调用</x:v>
       </x:c>
       <x:c r="G209" s="4" t="str">
-        <x:v>1. App 先采集正常调用；预期 UI 与 DB 显示已知 110。
-2. 追加缺 usage 原生事件并刷新；UI 显示不完整/未知诊断，不能把它当作 0 或把合计称为完整 110；DB 记录 unknown 原因且原正常事件不变。
-3. 重扫并重启 App；预期未知诊断仍在，未因去重而被隐藏。</x:v>
+        <x:v>1. 在隔离 App 取得并核验两来源覆盖证明后选该日；UI 明确 0 次、0 Token，趋势该日为真实 0，明细为空。
+2. DB 只读核对覆盖区间完整、事件数 0；无任何合成“零调用事件”。重启后状态仍为已覆盖零。</x:v>
       </x:c>
       <x:c r="H209" s="4" t="str">
         <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
@@ -17335,7 +17333,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L209" s="4" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:260</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:251</x:v>
       </x:c>
       <x:c r="M209" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -17349,10 +17347,10 @@
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B210" s="9" t="str">
-        <x:v>TC-TM005-STATE-04</x:v>
+        <x:v>TC-TM005-STATE-03</x:v>
       </x:c>
       <x:c r="C210" s="9" t="str">
-        <x:v>三态持久化</x:v>
+        <x:v>字段未知</x:v>
       </x:c>
       <x:c r="D210" s="9" t="str">
         <x:v>TASK-TM005-COVERAGE</x:v>
@@ -17361,11 +17359,12 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F210" s="9" t="str">
-        <x:v>分别预置上述无覆盖、完整空日、未知字段三种可核实源状态</x:v>
+        <x:v>一条受支持原生会话有时间/模型但缺可信 usage，另有正常可信调用 110</x:v>
       </x:c>
       <x:c r="G210" s="9" t="str">
-        <x:v>1. 在 App 依次选择三日；每个日期分别显示缺失、0、未知，保存 UI/只读 DB 的各自状态。
-2. 退出重启并改变团队时区后按新当地日重查；覆盖按 UTC 区间换算，三种状态不能互换或丢失。</x:v>
+        <x:v>1. App 先采集正常调用；预期 UI 与 DB 显示已知 110。
+2. 追加缺 usage 原生事件并刷新；UI 显示不完整/未知诊断，不能把它当作 0 或把合计称为完整 110；DB 记录 unknown 原因且原正常事件不变。
+3. 重扫并重启 App；预期未知诊断仍在，未因去重而被隐藏。</x:v>
       </x:c>
       <x:c r="H210" s="9" t="str">
         <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
@@ -17382,7 +17381,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L210" s="9" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:268</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:260</x:v>
       </x:c>
       <x:c r="M210" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -17396,10 +17395,10 @@
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B211" s="4" t="str">
-        <x:v>TC-TM005-STATE-05</x:v>
+        <x:v>TC-TM005-STATE-04</x:v>
       </x:c>
       <x:c r="C211" s="4" t="str">
-        <x:v>Claude 数值零与上游缺 usage 的歧义</x:v>
+        <x:v>三态持久化</x:v>
       </x:c>
       <x:c r="D211" s="4" t="str">
         <x:v>TASK-TM005-COVERAGE</x:v>
@@ -17408,12 +17407,11 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F211" s="4" t="str">
-        <x:v>TM-004 的两种受控 API 响应设计：显式报告零 usage 与整体省略 usage；Claude Code 2.1.126 原生阶段探针已发现后一种仍使 CLI 写出数值 0/0 usage</x:v>
+        <x:v>分别预置上述无覆盖、完整空日、未知字段三种可核实源状态</x:v>
       </x:c>
       <x:c r="G211" s="4" t="str">
-        <x:v>1. 分别由最终固定的原生数据程序生成两类日志，记录原始字节摘要与可观察字段；若两类 raw 不能区分，测试应把区别判据标为 BLOCKED，不能凭 API fixture 的隐藏输入让 App “识别”日志看不到的状态。
-2. App 读取省略 usage 所得数值零日志；没有额外可核实证据时 UI/DB 应保持未知或未确定，不能显示“已证明完整零用量”。已知可信事件的合计不被该 0 改成完整。
-3. 只有 TM-004 最终合同证明可区分显式零时，才对该变体单独断言真实零；重扫/重启不能把未知提升为零。</x:v>
+        <x:v>1. 在 App 依次选择三日；每个日期分别显示缺失、0、未知，保存 UI/只读 DB 的各自状态。
+2. 退出重启并改变团队时区后按新当地日重查；覆盖按 UTC 区间换算，三种状态不能互换或丢失。</x:v>
       </x:c>
       <x:c r="H211" s="4" t="str">
         <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
@@ -17430,7 +17428,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L211" s="4" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:275</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:268</x:v>
       </x:c>
       <x:c r="M211" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -17439,15 +17437,15 @@
         <x:v>v0.5.0-20261001T034729Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="212" ht="117" customHeight="1">
+    <x:row r="212" ht="102" customHeight="1">
       <x:c r="A212" s="9" t="str">
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B212" s="9" t="str">
-        <x:v>TC-TM005-STATE-06</x:v>
+        <x:v>TC-TM005-STATE-05</x:v>
       </x:c>
       <x:c r="C212" s="9" t="str">
-        <x:v>全量扫描分页与撤权时的覆盖</x:v>
+        <x:v>Claude 数值零与上游缺 usage 的歧义</x:v>
       </x:c>
       <x:c r="D212" s="9" t="str">
         <x:v>TASK-TM005-COVERAGE</x:v>
@@ -17456,12 +17454,12 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F212" s="9" t="str">
-        <x:v>本例拥有的 Claude 授权根含至少 1025 个候选文件、跨至少 5 个计划中的采集页；第一页含可信调用 A=100/10，后页另含可信调用 B=200/20。另有预览截断、页间撤权两个独立稳定变体</x:v>
+        <x:v>TM-004 的两种受控 API 响应设计：显式报告零 usage 与整体省略 usage；Claude Code 2.1.126 原生阶段探针已发现后一种仍使 CLI 写出数值 0/0 usage</x:v>
       </x:c>
       <x:c r="G212" s="9" t="str">
-        <x:v>1. 从已安装 App 经 TM-002 真实 UI 授权根；预览即使只列前 1000 文件也不能使 TM-005 宣称全量覆盖。采集分页未完成时，UI 仅显示已知部分（A 若已被可信采集则为 110）及 history_incomplete，不显示完整 110 或空日 0；SQLite 只读旁证记录 continuation/诊断和已提交可信事件。
-2. 正常变体继续到所有页面、必要深度与完整行/游标提交；若 TM-004 最终合同确认全部可信，UI/DB 合计 A+B=330，覆盖状态按真实证明更新，不遗漏第 1025 个及后续文件。
-3. 撤权变体在两页之间撤销本例授权；扫描立刻停止，后页 B 不得读取，UI 保持已知部分 110 与不完整/失权提示，SQLite 不写完整覆盖或成功零。重授权后的补扫单独执行，最终值仍须 TM-004 身份/分页合同核定。</x:v>
+        <x:v>1. 分别由最终固定的原生数据程序生成两类日志，记录原始字节摘要与可观察字段；若两类 raw 不能区分，测试应把区别判据标为 BLOCKED，不能凭 API fixture 的隐藏输入让 App “识别”日志看不到的状态。
+2. App 读取省略 usage 所得数值零日志；没有额外可核实证据时 UI/DB 应保持未知或未确定，不能显示“已证明完整零用量”。已知可信事件的合计不被该 0 改成完整。
+3. 只有 TM-004 最终合同证明可区分显式零时，才对该变体单独断言真实零；重扫/重启不能把未知提升为零。</x:v>
       </x:c>
       <x:c r="H212" s="9" t="str">
         <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
@@ -17478,7 +17476,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L212" s="9" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:285</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:275</x:v>
       </x:c>
       <x:c r="M212" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -17487,28 +17485,29 @@
         <x:v>v0.5.0-20261001T034729Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="213" ht="102" customHeight="1">
+    <x:row r="213" ht="117" customHeight="1">
       <x:c r="A213" s="4" t="str">
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B213" s="4" t="str">
-        <x:v>TC-TM005-DATA-01</x:v>
+        <x:v>TC-TM005-STATE-06</x:v>
       </x:c>
       <x:c r="C213" s="4" t="str">
-        <x:v>生成/重置可复现</x:v>
+        <x:v>全量扫描分页与撤权时的覆盖</x:v>
       </x:c>
       <x:c r="D213" s="4" t="str">
-        <x:v>TASK-TM005-DATA</x:v>
+        <x:v>TASK-TM005-COVERAGE</x:v>
       </x:c>
       <x:c r="E213" s="4" t="str">
-        <x:v>governance</x:v>
+        <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F213" s="4" t="str">
-        <x:v>同 seed42、同日锚点及两来源已验证版本，两个独立 run_id</x:v>
+        <x:v>本例拥有的 Claude 授权根含至少 1025 个候选文件、跨至少 5 个计划中的采集页；第一页含可信调用 A=100/10，后页另含可信调用 B=200/20。另有预览截断、页间撤权两个独立稳定变体</x:v>
       </x:c>
       <x:c r="G213" s="4" t="str">
-        <x:v>1. 调用计划中的 raw 生成器两次，核对受支持格式、事件身份、原始字节摘要与独立 expected 相同（run_id 标记可不同）；不得读取真实 ~/.codex 或 ~/.claude。
-2. 只在已核对 owner marker、目录成员和摘要后调用重置；两个本例私有目录被清理，外部文件不动。程序不存在时为 BLOCKED。</x:v>
+        <x:v>1. 从已安装 App 经 TM-002 真实 UI 授权根；预览即使只列前 1000 文件也不能使 TM-005 宣称全量覆盖。采集分页未完成时，UI 仅显示已知部分（A 若已被可信采集则为 110）及 history_incomplete，不显示完整 110 或空日 0；SQLite 只读旁证记录 continuation/诊断和已提交可信事件。
+2. 正常变体继续到所有页面、必要深度与完整行/游标提交；若 TM-004 最终合同确认全部可信，UI/DB 合计 A+B=330，覆盖状态按真实证明更新，不遗漏第 1025 个及后续文件。
+3. 撤权变体在两页之间撤销本例授权；扫描立刻停止，后页 B 不得读取，UI 保持已知部分 110 与不完整/失权提示，SQLite 不写完整覆盖或成功零。重授权后的补扫单独执行，最终值仍须 TM-004 身份/分页合同核定。</x:v>
       </x:c>
       <x:c r="H213" s="4" t="str">
         <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
@@ -17525,7 +17524,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L213" s="4" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:297</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:285</x:v>
       </x:c>
       <x:c r="M213" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -17539,10 +17538,10 @@
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B214" s="9" t="str">
-        <x:v>TC-TM005-DATA-02</x:v>
+        <x:v>TC-TM005-DATA-01</x:v>
       </x:c>
       <x:c r="C214" s="9" t="str">
-        <x:v>独立预期与边界</x:v>
+        <x:v>生成/重置可复现</x:v>
       </x:c>
       <x:c r="D214" s="9" t="str">
         <x:v>TASK-TM005-DATA</x:v>
@@ -17551,11 +17550,11 @@
         <x:v>governance</x:v>
       </x:c>
       <x:c r="F214" s="9" t="str">
-        <x:v>语义 oracle tests/fixtures/tm005-semantic-expected.json和最终 raw 映射计划</x:v>
+        <x:v>同 seed42、同日锚点及两来源已验证版本，两个独立 run_id</x:v>
       </x:c>
       <x:c r="G214" s="9" t="str">
-        <x:v>1. 在产品启动前运行固定语义 oracle 检查；预期 seed42 语义样例 13 行/12 唯一，双来源事件集合及平移后的上海/UTC半开区间与预存摘要一致；原生映射未就绪时本例仍 BLOCKED。
-2. 对照原始字节与独立预期中的模型/字段、覆盖与 unknown 状态；缺原生日志/覆盖样例不得标可执行。该检查不能代替产品查询。</x:v>
+        <x:v>1. 调用计划中的 raw 生成器两次，核对受支持格式、事件身份、原始字节摘要与独立 expected 相同（run_id 标记可不同）；不得读取真实 ~/.codex 或 ~/.claude。
+2. 只在已核对 owner marker、目录成员和摘要后调用重置；两个本例私有目录被清理，外部文件不动。程序不存在时为 BLOCKED。</x:v>
       </x:c>
       <x:c r="H214" s="9" t="str">
         <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
@@ -17572,7 +17571,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L214" s="9" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:304</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:297</x:v>
       </x:c>
       <x:c r="M214" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -17586,23 +17585,23 @@
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B215" s="4" t="str">
-        <x:v>TC-TM005-E2E-01</x:v>
+        <x:v>TC-TM005-DATA-02</x:v>
       </x:c>
       <x:c r="C215" s="4" t="str">
-        <x:v>精确集合与最终安装包</x:v>
+        <x:v>独立预期与边界</x:v>
       </x:c>
       <x:c r="D215" s="4" t="str">
-        <x:v>TASK-TM005-E2E</x:v>
+        <x:v>TASK-TM005-DATA</x:v>
       </x:c>
       <x:c r="E215" s="4" t="str">
-        <x:v>governance_gate</x:v>
+        <x:v>governance</x:v>
       </x:c>
       <x:c r="F215" s="4" t="str">
-        <x:v>固定候选 SHA、最终 DMG 与上述所有 TC 及此前已交付功能集合</x:v>
+        <x:v>语义 oracle tests/fixtures/tm005-semantic-expected.json和最终 raw 映射计划</x:v>
       </x:c>
       <x:c r="G215" s="4" t="str">
-        <x:v>1. 门禁从 DMG 安装的正式 App 逐 TC 运行，核对实际安装包摘要、独立输入/预期、原始结果与全部清理；任一 FAIL/BLOCKED/零例/跳过/重试取绿均阻断。
-2. 核对 TM-001→TM-004 的适用完整 E2E 及迁移/升级结果；只有本机机器门禁原始复核 PASS 才可签发本版通行证。当前无程序/包/原件，状态 BLOCKED。</x:v>
+        <x:v>1. 在产品启动前运行固定语义 oracle 检查；预期 seed42 语义样例 13 行/12 唯一，双来源事件集合及平移后的上海/UTC半开区间与预存摘要一致；原生映射未就绪时本例仍 BLOCKED。
+2. 对照原始字节与独立预期中的模型/字段、覆盖与 unknown 状态；缺原生日志/覆盖样例不得标可执行。该检查不能代替产品查询。</x:v>
       </x:c>
       <x:c r="H215" s="4" t="str">
         <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
@@ -17619,7 +17618,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L215" s="4" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:311</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:304</x:v>
       </x:c>
       <x:c r="M215" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -17628,50 +17627,51 @@
         <x:v>v0.5.0-20261001T034729Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="216" ht="57" customHeight="1">
+    <x:row r="216" ht="102" customHeight="1">
       <x:c r="A216" s="9" t="str">
-        <x:v>TM-006</x:v>
+        <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B216" s="9" t="str">
-        <x:v>E2E-TM006-001</x:v>
+        <x:v>TC-TM005-E2E-01</x:v>
       </x:c>
       <x:c r="C216" s="9" t="str">
-        <x:v>Token子项与基础费用</x:v>
+        <x:v>精确集合与最终安装包</x:v>
       </x:c>
       <x:c r="D216" s="9" t="str">
-        <x:v>待拆解</x:v>
+        <x:v>TASK-TM005-E2E</x:v>
       </x:c>
       <x:c r="E216" s="9" t="str">
-        <x:v>产品E2E</x:v>
+        <x:v>governance_gate</x:v>
       </x:c>
       <x:c r="F216" s="9" t="str">
-        <x:v>数据集 pricing；pricing由scripts/test_data.py生成合成非计费价格。gpt-5每百万input/cache/output为USD2/0.2/8；today-gpt input1000含cache200、output100含reasoning20。价格不是厂商现价。</x:v>
+        <x:v>固定候选 SHA、最终 DMG 与上述所有 TC 及此前已交付功能集合</x:v>
       </x:c>
       <x:c r="G216" s="9" t="str">
-        <x:v>单调用total=1100；费用=(800×2+200×0.2+100×8)/1000000=USD0.002440，reasoning20不另加价。today已知费用USD0.015190且有1条无价格，alice今日USD0.010090。使用Decimal/十进制独立oracle，不以界面舍入反推底层精度。</x:v>
+        <x:v>1. 门禁从 DMG 安装的正式 App 逐 TC 运行，核对实际安装包摘要、独立输入/预期、原始结果与全部清理；任一 FAIL/BLOCKED/零例/跳过/重试取绿均阻断。
+2. 核对 TM-001→TM-004 的适用完整 E2E 及迁移/升级结果；只有本机机器门禁原始复核 PASS 才可签发本版通行证。当前无程序/包/原件，状态 BLOCKED。</x:v>
       </x:c>
       <x:c r="H216" s="9" t="str">
-        <x:v>准备：待该功能的数据程序/SQL方案确定。
-变化：待具体任务及数据设计细化。
-核验：暂无可执行数据库核验绑定。</x:v>
+        <x:v>准备：本例独立空客户端 SQLite 和隔离服务 SQLite；只能由固定的两来源原生日志经 App 采集，不能直接向产品库 SQL 造统计数据。
+变化：事件、诊断与覆盖状态须与本例逐步设计预期一致；具体表和迁移由 TM-003/004 稳定合同确定。
+核验：只读 SQLite 对照来源、稳定身份、UTC 时间、Token、覆盖和诊断；具体列名与 SQL 尚未绑定，执行前 BLOCKED。</x:v>
       </x:c>
       <x:c r="I216" s="9" t="str">
-        <x:v>未来规划</x:v>
+        <x:v>预期待明确</x:v>
       </x:c>
       <x:c r="J216" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K216" s="9" t="str">
-        <x:v>未来概要</x:v>
+        <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L216" s="9" t="str">
-        <x:v>docs/testing/cases/06-TM-006-cost-estimates.md:15</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:311</x:v>
       </x:c>
       <x:c r="M216" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
       <x:c r="N216" s="9" t="str">
-        <x:v>v0.2.0-20261001T034118Z</x:v>
+        <x:v>v0.5.0-20261001T034729Z</x:v>
       </x:c>
     </x:row>
     <x:row r="217" ht="57" customHeight="1">
@@ -17679,10 +17679,10 @@
         <x:v>TM-006</x:v>
       </x:c>
       <x:c r="B217" s="4" t="str">
-        <x:v>E2E-TM006-002</x:v>
+        <x:v>E2E-TM006-001</x:v>
       </x:c>
       <x:c r="C217" s="4" t="str">
-        <x:v>历史价格、多币种和未知费用</x:v>
+        <x:v>Token子项与基础费用</x:v>
       </x:c>
       <x:c r="D217" s="4" t="str">
         <x:v>待拆解</x:v>
@@ -17691,10 +17691,10 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F217" s="4" t="str">
-        <x:v>数据集 pricing_extended；pricing_extended planned：同模型在生效时点T前后各一调用，两个独立价格版本；另有USD/CNY各一模型、无价模型和订阅估算模型。必须提供价格/订阅分摊规则及手算expected后才能实现。</x:v>
+        <x:v>数据集 pricing；pricing由scripts/test_data.py生成合成非计费价格。gpt-5每百万input/cache/output为USD2/0.2/8；today-gpt input1000含cache200、output100含reasoning20。价格不是厂商现价。</x:v>
       </x:c>
       <x:c r="G217" s="4" t="str">
-        <x:v>T前后依各自生效版本计算，历史结果不会悄悄换价；USD与CNY分组，未约定汇率不得相加；无价格显示未知而非0；订阅必须明确估算口径。具体金额oracle依待定义订阅/价格合同生成，当前不得手填PASS。</x:v>
+        <x:v>单调用total=1100；费用=(800×2+200×0.2+100×8)/1000000=USD0.002440，reasoning20不另加价。today已知费用USD0.015190且有1条无价格，alice今日USD0.010090。使用Decimal/十进制独立oracle，不以界面舍入反推底层精度。</x:v>
       </x:c>
       <x:c r="H217" s="4" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
@@ -17711,7 +17711,7 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L217" s="4" t="str">
-        <x:v>docs/testing/cases/06-TM-006-cost-estimates.md:32</x:v>
+        <x:v>docs/testing/cases/06-TM-006-cost-estimates.md:15</x:v>
       </x:c>
       <x:c r="M217" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -17722,13 +17722,13 @@
     </x:row>
     <x:row r="218" ht="57" customHeight="1">
       <x:c r="A218" s="9" t="str">
-        <x:v>TM-007</x:v>
+        <x:v>TM-006</x:v>
       </x:c>
       <x:c r="B218" s="9" t="str">
-        <x:v>E2E-TM007-001</x:v>
+        <x:v>E2E-TM006-002</x:v>
       </x:c>
       <x:c r="C218" s="9" t="str">
-        <x:v>离线、重启和补传幂等</x:v>
+        <x:v>历史价格、多币种和未知费用</x:v>
       </x:c>
       <x:c r="D218" s="9" t="str">
         <x:v>待拆解</x:v>
@@ -17737,10 +17737,10 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F218" s="9" t="str">
-        <x:v>数据集 sync_faults；sync_faults planned；alice两个隔离设备A/B，设备A调用100/10、B调用200/20；真实FastAPI/SQLite服务，可由外部fixture断网/恢复。账号继续用隔离测试fixture。</x:v>
+        <x:v>数据集 pricing_extended；pricing_extended planned：同模型在生效时点T前后各一调用，两个独立价格版本；另有USD/CNY各一模型、无价模型和订阅估算模型。必须提供价格/订阅分摊规则及手算expected后才能实现。</x:v>
       </x:c>
       <x:c r="G218" s="9" t="str">
-        <x:v>离线重启不丢队列；恢复后2唯一调用、input300/output30/total330；重复批次不再加量。客户端只在真实确认后标已同步，个人合计与对应团队子集一致。</x:v>
+        <x:v>T前后依各自生效版本计算，历史结果不会悄悄换价；USD与CNY分组，未约定汇率不得相加；无价格显示未知而非0；订阅必须明确估算口径。具体金额oracle依待定义订阅/价格合同生成，当前不得手填PASS。</x:v>
       </x:c>
       <x:c r="H218" s="9" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
@@ -17757,7 +17757,7 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L218" s="9" t="str">
-        <x:v>docs/testing/cases/07-TM-007-team-sync.md:11</x:v>
+        <x:v>docs/testing/cases/06-TM-006-cost-estimates.md:32</x:v>
       </x:c>
       <x:c r="M218" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -17771,10 +17771,10 @@
         <x:v>TM-007</x:v>
       </x:c>
       <x:c r="B219" s="4" t="str">
-        <x:v>E2E-TM007-002</x:v>
+        <x:v>E2E-TM007-001</x:v>
       </x:c>
       <x:c r="C219" s="4" t="str">
-        <x:v>部分确认、中断和账号切换</x:v>
+        <x:v>离线、重启和补传幂等</x:v>
       </x:c>
       <x:c r="D219" s="4" t="str">
         <x:v>待拆解</x:v>
@@ -17783,10 +17783,10 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F219" s="4" t="str">
-        <x:v>数据集 sync_faults；准备alice的三条唯一事件A/B/C，总量各110/220/330；控制服务仅确认A后断开，B可能已提交但响应丢失，C未提交。另有bob账号。故障注入必须在真实服务外部或明确测试环境中完成，不能绕过认证。</x:v>
+        <x:v>数据集 sync_faults；sync_faults planned；alice两个隔离设备A/B，设备A调用100/10、B调用200/20；真实FastAPI/SQLite服务，可由外部fixture断网/恢复。账号继续用隔离测试fixture。</x:v>
       </x:c>
       <x:c r="G219" s="4" t="str">
-        <x:v>最终alice的A/B/C各一次、total660；响应丢失不造成B重复；bob不能承接或篡改alice既有事件归属。切换时旧队列按已批准归属策略隔离，不能默认为新登录账号。</x:v>
+        <x:v>离线重启不丢队列；恢复后2唯一调用、input300/output30/total330；重复批次不再加量。客户端只在真实确认后标已同步，个人合计与对应团队子集一致。</x:v>
       </x:c>
       <x:c r="H219" s="4" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
@@ -17803,7 +17803,7 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L219" s="4" t="str">
-        <x:v>docs/testing/cases/07-TM-007-team-sync.md:28</x:v>
+        <x:v>docs/testing/cases/07-TM-007-team-sync.md:11</x:v>
       </x:c>
       <x:c r="M219" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -17817,10 +17817,10 @@
         <x:v>TM-007</x:v>
       </x:c>
       <x:c r="B220" s="9" t="str">
-        <x:v>E2E-TM007-003</x:v>
+        <x:v>E2E-TM007-002</x:v>
       </x:c>
       <x:c r="C220" s="9" t="str">
-        <x:v>上传白名单与项目映射</x:v>
+        <x:v>部分确认、中断和账号切换</x:v>
       </x:c>
       <x:c r="D220" s="9" t="str">
         <x:v>待拆解</x:v>
@@ -17829,10 +17829,10 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F220" s="9" t="str">
-        <x:v>数据集 sync_faults；合成日志包含唯一正文/代码/API-key/完整路径哨兵，以及合法用量/必要去重元数据；只用假值。准备已归属项目A和未归属事件B，待sync_faults生成。</x:v>
+        <x:v>数据集 sync_faults；准备alice的三条唯一事件A/B/C，总量各110/220/330；控制服务仅确认A后断开，B可能已提交但响应丢失，C未提交。另有bob账号。故障注入必须在真实服务外部或明确测试环境中完成，不能绕过认证。</x:v>
       </x:c>
       <x:c r="G220" s="9" t="str">
-        <x:v>网络载荷/持久服务数据均不得含正文、代码、key或完整本机路径；只有批准用量/去重字段。B可明确分配，分配不增加事件量、也不跨团队归属。</x:v>
+        <x:v>最终alice的A/B/C各一次、total660；响应丢失不造成B重复；bob不能承接或篡改alice既有事件归属。切换时旧队列按已批准归属策略隔离，不能默认为新登录账号。</x:v>
       </x:c>
       <x:c r="H220" s="9" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
@@ -17849,7 +17849,7 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L220" s="9" t="str">
-        <x:v>docs/testing/cases/07-TM-007-team-sync.md:45</x:v>
+        <x:v>docs/testing/cases/07-TM-007-team-sync.md:28</x:v>
       </x:c>
       <x:c r="M220" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -17863,10 +17863,10 @@
         <x:v>TM-007</x:v>
       </x:c>
       <x:c r="B221" s="4" t="str">
-        <x:v>E2E-TM007-004</x:v>
+        <x:v>E2E-TM007-003</x:v>
       </x:c>
       <x:c r="C221" s="4" t="str">
-        <x:v>统计越权与停用后上传</x:v>
+        <x:v>上传白名单与项目映射</x:v>
       </x:c>
       <x:c r="D221" s="4" t="str">
         <x:v>待拆解</x:v>
@@ -17875,10 +17875,10 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F221" s="4" t="str">
-        <x:v>数据集 sync_faults；alice项目A调用100/10，bob项目B调用200/20；成员alice与管理员独立会话；alice另有一条未确认调用C=50/5。sync_faults与可重建统计SQL尚未实现。</x:v>
+        <x:v>数据集 sync_faults；合成日志包含唯一正文/代码/API-key/完整路径哨兵，以及合法用量/必要去重元数据；只用假值。准备已归属项目A和未归属事件B，待sync_faults生成。</x:v>
       </x:c>
       <x:c r="G221" s="4" t="str">
-        <x:v>成员无权请求被服务端拒绝，UI不显示bob的220；停用后旧会话及上传拒绝，C不能标为已确认；合法历史不能被失败上传删除。此处补足TM-001仅身份/管理接口权限的范围。</x:v>
+        <x:v>网络载荷/持久服务数据均不得含正文、代码、key或完整本机路径；只有批准用量/去重字段。B可明确分配，分配不增加事件量、也不跨团队归属。</x:v>
       </x:c>
       <x:c r="H221" s="4" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
@@ -17895,7 +17895,7 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L221" s="4" t="str">
-        <x:v>docs/testing/cases/07-TM-007-team-sync.md:62</x:v>
+        <x:v>docs/testing/cases/07-TM-007-team-sync.md:45</x:v>
       </x:c>
       <x:c r="M221" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -17906,13 +17906,13 @@
     </x:row>
     <x:row r="222" ht="57" customHeight="1">
       <x:c r="A222" s="9" t="str">
-        <x:v>TM-008</x:v>
+        <x:v>TM-007</x:v>
       </x:c>
       <x:c r="B222" s="9" t="str">
-        <x:v>E2E-TM008-001</x:v>
+        <x:v>E2E-TM007-004</x:v>
       </x:c>
       <x:c r="C222" s="9" t="str">
-        <x:v>筛选一致的CSV导出</x:v>
+        <x:v>统计越权与停用后上传</x:v>
       </x:c>
       <x:c r="D222" s="9" t="str">
         <x:v>待拆解</x:v>
@@ -17921,10 +17921,10 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F222" s="9" t="str">
-        <x:v>数据集 export_rows；export_rows planned；两成员、两个模型、时间范围内外各有事件，独立清单明确每条ID/字段/权限。先具备TM-005/007统计和授权。</x:v>
+        <x:v>数据集 sync_faults；alice项目A调用100/10，bob项目B调用200/20；成员alice与管理员独立会话；alice另有一条未确认调用C=50/5。sync_faults与可重建统计SQL尚未实现。</x:v>
       </x:c>
       <x:c r="G222" s="9" t="str">
-        <x:v>每次CSV仅包含当次筛选且授权可见记录，行数/ID/汇总等于独立清单与界面；不混入旧筛选、其他成员或范围外记录。已知/未知费用语义一致。</x:v>
+        <x:v>成员无权请求被服务端拒绝，UI不显示bob的220；停用后旧会话及上传拒绝，C不能标为已确认；合法历史不能被失败上传删除。此处补足TM-001仅身份/管理接口权限的范围。</x:v>
       </x:c>
       <x:c r="H222" s="9" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
@@ -17941,7 +17941,7 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L222" s="9" t="str">
-        <x:v>docs/testing/cases/08-TM-008-csv-export.md:11</x:v>
+        <x:v>docs/testing/cases/07-TM-007-team-sync.md:62</x:v>
       </x:c>
       <x:c r="M222" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -17955,10 +17955,10 @@
         <x:v>TM-008</x:v>
       </x:c>
       <x:c r="B223" s="4" t="str">
-        <x:v>E2E-TM008-002</x:v>
+        <x:v>E2E-TM008-001</x:v>
       </x:c>
       <x:c r="C223" s="4" t="str">
-        <x:v>CSV转义、未知值及权限</x:v>
+        <x:v>筛选一致的CSV导出</x:v>
       </x:c>
       <x:c r="D223" s="4" t="str">
         <x:v>待拆解</x:v>
@@ -17967,10 +17967,10 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F223" s="4" t="str">
-        <x:v>数据集 export_rows；export_rows需含字段 a,b、say "hi"、带实际换行的项目名、未知费用与非ASCII模型名；两成员各有可区分哨兵事件。只在隔离数据中使用。</x:v>
+        <x:v>数据集 export_rows；export_rows planned；两成员、两个模型、时间范围内外各有事件，独立清单明确每条ID/字段/权限。先具备TM-005/007统计和授权。</x:v>
       </x:c>
       <x:c r="G223" s="4" t="str">
-        <x:v>逗号、双引号、嵌入换行均round-trip一致，Unicode不损坏；未知值不写成0；他人哨兵不出现在文件。若导出失败，不能留下看似完整的半文件。</x:v>
+        <x:v>每次CSV仅包含当次筛选且授权可见记录，行数/ID/汇总等于独立清单与界面；不混入旧筛选、其他成员或范围外记录。已知/未知费用语义一致。</x:v>
       </x:c>
       <x:c r="H223" s="4" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
@@ -17987,7 +17987,7 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L223" s="4" t="str">
-        <x:v>docs/testing/cases/08-TM-008-csv-export.md:28</x:v>
+        <x:v>docs/testing/cases/08-TM-008-csv-export.md:11</x:v>
       </x:c>
       <x:c r="M223" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -17998,13 +17998,13 @@
     </x:row>
     <x:row r="224" ht="57" customHeight="1">
       <x:c r="A224" s="9" t="str">
-        <x:v>TM-009</x:v>
+        <x:v>TM-008</x:v>
       </x:c>
       <x:c r="B224" s="9" t="str">
-        <x:v>E2E-TM009-001</x:v>
+        <x:v>E2E-TM008-002</x:v>
       </x:c>
       <x:c r="C224" s="9" t="str">
-        <x:v>80%/100%提醒幂等</x:v>
+        <x:v>CSV转义、未知值及权限</x:v>
       </x:c>
       <x:c r="D224" s="9" t="str">
         <x:v>待拆解</x:v>
@@ -18013,10 +18013,10 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F224" s="9" t="str">
-        <x:v>数据集 budget_periods；budget_periods planned；独立个人、项目和团队预算分别100个合成USD单位，同周期使用量依次79→80→99→100；原始调用与价格要能精确形成这些费用。</x:v>
+        <x:v>数据集 export_rows；export_rows需含字段 a,b、say "hi"、带实际换行的项目名、未知费用与非ASCII模型名；两成员各有可区分哨兵事件。只在隔离数据中使用。</x:v>
       </x:c>
       <x:c r="G224" s="9" t="str">
-        <x:v>每预算每周期80与100各最多一次，未达到不发；重扫/重启/重复上传不重发；预算仅提醒，不拦截模型调用。三层预算分别按其授权范围计算。</x:v>
+        <x:v>逗号、双引号、嵌入换行均round-trip一致，Unicode不损坏；未知值不写成0；他人哨兵不出现在文件。若导出失败，不能留下看似完整的半文件。</x:v>
       </x:c>
       <x:c r="H224" s="9" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
@@ -18033,7 +18033,7 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L224" s="9" t="str">
-        <x:v>docs/testing/cases/09-TM-009-budget-alerts.md:11</x:v>
+        <x:v>docs/testing/cases/08-TM-008-csv-export.md:28</x:v>
       </x:c>
       <x:c r="M224" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -18047,10 +18047,10 @@
         <x:v>TM-009</x:v>
       </x:c>
       <x:c r="B225" s="4" t="str">
-        <x:v>E2E-TM009-002</x:v>
+        <x:v>E2E-TM009-001</x:v>
       </x:c>
       <x:c r="C225" s="4" t="str">
-        <x:v>新周期、币种与通知恢复</x:v>
+        <x:v>80%/100%提醒幂等</x:v>
       </x:c>
       <x:c r="D225" s="4" t="str">
         <x:v>待拆解</x:v>
@@ -18059,10 +18059,10 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F225" s="4" t="str">
-        <x:v>数据集 budget_periods；两个币种独立预算；旧周期已发80/100阈值，参考时钟可由产品支持的测试配置推进；测试通知权限可以拒绝及恢复，不能修改用户其他App授权。</x:v>
+        <x:v>数据集 budget_periods；budget_periods planned；独立个人、项目和团队预算分别100个合成USD单位，同周期使用量依次79→80→99→100；原始调用与价格要能精确形成这些费用。</x:v>
       </x:c>
       <x:c r="G225" s="4" t="str">
-        <x:v>系统拒绝不丢失应用内状态、不造成重试通知风暴；新周期独立重置，允许新一轮各阈值一次；币种分开计算。通知补发策略需在对应需求明确，不能由测试临时猜测。</x:v>
+        <x:v>每预算每周期80与100各最多一次，未达到不发；重扫/重启/重复上传不重发；预算仅提醒，不拦截模型调用。三层预算分别按其授权范围计算。</x:v>
       </x:c>
       <x:c r="H225" s="4" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
@@ -18079,7 +18079,7 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L225" s="4" t="str">
-        <x:v>docs/testing/cases/09-TM-009-budget-alerts.md:28</x:v>
+        <x:v>docs/testing/cases/09-TM-009-budget-alerts.md:11</x:v>
       </x:c>
       <x:c r="M225" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -18088,15 +18088,15 @@
         <x:v>v0.2.0-20261001T034118Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="226" ht="72" customHeight="1">
+    <x:row r="226" ht="57" customHeight="1">
       <x:c r="A226" s="9" t="str">
-        <x:v>TM-010</x:v>
+        <x:v>TM-009</x:v>
       </x:c>
       <x:c r="B226" s="9" t="str">
-        <x:v>E2E-TM010-001</x:v>
+        <x:v>E2E-TM009-002</x:v>
       </x:c>
       <x:c r="C226" s="9" t="str">
-        <x:v>稳定版发现更新与数据保留</x:v>
+        <x:v>新周期、币种与通知恢复</x:v>
       </x:c>
       <x:c r="D226" s="9" t="str">
         <x:v>待拆解</x:v>
@@ -18105,10 +18105,10 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F226" s="9" t="str">
-        <x:v>数据集 update_packages；依赖TM-001/007；update_packages planned。需真实已分发稳定版、候选最终包及相同分发profile的签名/清单；旧版有账号设置、手动地址、统计/队列独立快照。首版无历史稳定版时使用SOP017规定的候选→受控高版，不伪称稳定升级。</x:v>
+        <x:v>数据集 budget_periods；两个币种独立预算；旧周期已发80/100阈值，参考时钟可由产品支持的测试配置推进；测试通知权限可以拒绝及恢复，不能修改用户其他App授权。</x:v>
       </x:c>
       <x:c r="G226" s="9" t="str">
-        <x:v>更新频率和说明可用；只有声明候选被安装，Sparkle自主重启；更新前后账号/设置/统计与快照一致，队列不丢失不重复。完整更新体验仍为未来功能，TM-001-004通过只证明最小更新路径。</x:v>
+        <x:v>系统拒绝不丢失应用内状态、不造成重试通知风暴；新周期独立重置，允许新一轮各阈值一次；币种分开计算。通知补发策略需在对应需求明确，不能由测试临时猜测。</x:v>
       </x:c>
       <x:c r="H226" s="9" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
@@ -18125,7 +18125,7 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L226" s="9" t="str">
-        <x:v>docs/testing/cases/10-TM-010-software-updates.md:11</x:v>
+        <x:v>docs/testing/cases/09-TM-009-budget-alerts.md:28</x:v>
       </x:c>
       <x:c r="M226" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -18134,15 +18134,15 @@
         <x:v>v0.2.0-20261001T034118Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="227" ht="57" customHeight="1">
+    <x:row r="227" ht="72" customHeight="1">
       <x:c r="A227" s="4" t="str">
         <x:v>TM-010</x:v>
       </x:c>
       <x:c r="B227" s="4" t="str">
-        <x:v>E2E-TM010-002</x:v>
+        <x:v>E2E-TM010-001</x:v>
       </x:c>
       <x:c r="C227" s="4" t="str">
-        <x:v>签名、网络、空间和迁移失败恢复</x:v>
+        <x:v>稳定版发现更新与数据保留</x:v>
       </x:c>
       <x:c r="D227" s="4" t="str">
         <x:v>待拆解</x:v>
@@ -18151,10 +18151,10 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F227" s="4" t="str">
-        <x:v>数据集 update_packages；对同一干净旧版分别建立四个隔离子场景：坏签名包、下载中断、受限测试卷空间不足、受控迁移失败；每个保存旧版包/DB/配置摘要。故障不能作用用户系统盘/生产库。</x:v>
+        <x:v>数据集 update_packages；依赖TM-001/007；update_packages planned。需真实已分发稳定版、候选最终包及相同分发profile的签名/清单；旧版有账号设置、手动地址、统计/队列独立快照。首版无历史稳定版时使用SOP017规定的候选→受控高版，不伪称稳定升级。</x:v>
       </x:c>
       <x:c r="G227" s="4" t="str">
-        <x:v>每个失败均不能形成半更新；原账号/统计和包的可用状态可验证。网络恢复后的成功需要完整包校验；迁移失败恢复来源与摘要明确。四个子场景全部为本case必需，不能挑一项通过。</x:v>
+        <x:v>更新频率和说明可用；只有声明候选被安装，Sparkle自主重启；更新前后账号/设置/统计与快照一致，队列不丢失不重复。完整更新体验仍为未来功能，TM-001-004通过只证明最小更新路径。</x:v>
       </x:c>
       <x:c r="H227" s="4" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
@@ -18171,7 +18171,7 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L227" s="4" t="str">
-        <x:v>docs/testing/cases/10-TM-010-software-updates.md:28</x:v>
+        <x:v>docs/testing/cases/10-TM-010-software-updates.md:11</x:v>
       </x:c>
       <x:c r="M227" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -18185,10 +18185,10 @@
         <x:v>TM-010</x:v>
       </x:c>
       <x:c r="B228" s="9" t="str">
-        <x:v>E2E-TM010-003</x:v>
+        <x:v>E2E-TM010-002</x:v>
       </x:c>
       <x:c r="C228" s="9" t="str">
-        <x:v>升级默认地址和手动覆盖</x:v>
+        <x:v>签名、网络、空间和迁移失败恢复</x:v>
       </x:c>
       <x:c r="D228" s="9" t="str">
         <x:v>待拆解</x:v>
@@ -18197,10 +18197,10 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F228" s="9" t="str">
-        <x:v>数据集 server_default_migration；server_default_migration planned；两套旧安装A从未设置地址、B已手动设置；候选内置一个届时确定且测试可访问的生产HTTPS默认地址。两源有独立账号/数据/会话，公钥不可随URL编辑。</x:v>
+        <x:v>数据集 update_packages；对同一干净旧版分别建立四个隔离子场景：坏签名包、下载中断、受限测试卷空间不足、受控迁移失败；每个保存旧版包/DB/配置摘要。故障不能作用用户系统盘/生产库。</x:v>
       </x:c>
       <x:c r="G228" s="9" t="str">
-        <x:v>只有无手动覆盖安装跟随新版默认；显式覆盖即使恰好等于旧默认也应按已经确定的配置来源规则处理。改变origin需重新服务认证，旧token不能跨源复用。</x:v>
+        <x:v>每个失败均不能形成半更新；原账号/统计和包的可用状态可验证。网络恢复后的成功需要完整包校验；迁移失败恢复来源与摘要明确。四个子场景全部为本case必需，不能挑一项通过。</x:v>
       </x:c>
       <x:c r="H228" s="9" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
@@ -18217,7 +18217,7 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L228" s="9" t="str">
-        <x:v>docs/testing/cases/10-TM-010-software-updates.md:45</x:v>
+        <x:v>docs/testing/cases/10-TM-010-software-updates.md:28</x:v>
       </x:c>
       <x:c r="M228" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -18228,13 +18228,13 @@
     </x:row>
     <x:row r="229" ht="57" customHeight="1">
       <x:c r="A229" s="4" t="str">
-        <x:v>TM-011</x:v>
+        <x:v>TM-010</x:v>
       </x:c>
       <x:c r="B229" s="4" t="str">
-        <x:v>E2E-TM011-001</x:v>
+        <x:v>E2E-TM010-003</x:v>
       </x:c>
       <x:c r="C229" s="4" t="str">
-        <x:v>SQLite迁移与中断恢复</x:v>
+        <x:v>升级默认地址和手动覆盖</x:v>
       </x:c>
       <x:c r="D229" s="4" t="str">
         <x:v>待拆解</x:v>
@@ -18243,10 +18243,10 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F229" s="4" t="str">
-        <x:v>数据集 migration_snapshots；migration_snapshots planned；旧schema副本含固定账号/事件/队列、预计算记录数/Token/金额；候选迁移版本和明确故障点。全部作用私有临时库。</x:v>
+        <x:v>数据集 server_default_migration；server_default_migration planned；两套旧安装A从未设置地址、B已手动设置；候选内置一个届时确定且测试可访问的生产HTTPS默认地址。两源有独立账号/数据/会话，公钥不可随URL编辑。</x:v>
       </x:c>
       <x:c r="G229" s="4" t="str">
-        <x:v>成功迁移只改变设计允许的schema/数据；账号、记录数、Token、费用/队列归属不丢。失败恢复到可启动一致状态，重复启动不重复迁移数据。不能以文件存在作为恢复成功。</x:v>
+        <x:v>只有无手动覆盖安装跟随新版默认；显式覆盖即使恰好等于旧默认也应按已经确定的配置来源规则处理。改变origin需重新服务认证，旧token不能跨源复用。</x:v>
       </x:c>
       <x:c r="H229" s="4" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
@@ -18263,7 +18263,7 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L229" s="4" t="str">
-        <x:v>docs/testing/cases/11-TM-011-data-migration.md:11</x:v>
+        <x:v>docs/testing/cases/10-TM-010-software-updates.md:45</x:v>
       </x:c>
       <x:c r="M229" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -18277,10 +18277,10 @@
         <x:v>TM-011</x:v>
       </x:c>
       <x:c r="B230" s="9" t="str">
-        <x:v>E2E-TM011-002</x:v>
+        <x:v>E2E-TM011-001</x:v>
       </x:c>
       <x:c r="C230" s="9" t="str">
-        <x:v>未来SQLite到MySQL迁移</x:v>
+        <x:v>SQLite迁移与中断恢复</x:v>
       </x:c>
       <x:c r="D230" s="9" t="str">
         <x:v>待拆解</x:v>
@@ -18289,10 +18289,10 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F230" s="9" t="str">
-        <x:v>数据集 migration_snapshots；仅后续独立版本适用；用户已确定v0.1.0继续SQLite。需要隔离源SQLite、目标MySQL、固定多成员/多项目用量快照、字符/时间/Decimal边界和独立expected。</x:v>
+        <x:v>数据集 migration_snapshots；migration_snapshots planned；旧schema副本含固定账号/事件/队列、预计算记录数/Token/金额；候选迁移版本和明确故障点。全部作用私有临时库。</x:v>
       </x:c>
       <x:c r="G230" s="9" t="str">
-        <x:v>源/目标记录数、Token、Decimal金额及权限结果一致，ID和幂等语义保持；不重复历史且旧源未被破坏。MySQL版本、字符集和迁移范围须在对应版本指定。</x:v>
+        <x:v>成功迁移只改变设计允许的schema/数据；账号、记录数、Token、费用/队列归属不丢。失败恢复到可启动一致状态，重复启动不重复迁移数据。不能以文件存在作为恢复成功。</x:v>
       </x:c>
       <x:c r="H230" s="9" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
@@ -18309,7 +18309,7 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L230" s="9" t="str">
-        <x:v>docs/testing/cases/11-TM-011-data-migration.md:28</x:v>
+        <x:v>docs/testing/cases/11-TM-011-data-migration.md:11</x:v>
       </x:c>
       <x:c r="M230" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -18323,10 +18323,10 @@
         <x:v>TM-011</x:v>
       </x:c>
       <x:c r="B231" s="4" t="str">
-        <x:v>E2E-TM011-003</x:v>
+        <x:v>E2E-TM011-002</x:v>
       </x:c>
       <x:c r="C231" s="4" t="str">
-        <x:v>备份恢复与旧客户端补传</x:v>
+        <x:v>未来SQLite到MySQL迁移</x:v>
       </x:c>
       <x:c r="D231" s="4" t="str">
         <x:v>待拆解</x:v>
@@ -18335,10 +18335,10 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F231" s="4" t="str">
-        <x:v>数据集 migration_snapshots；隔离服务已确认事件A/B与旧客户端未确认C；备份包含schema/数据/版本/摘要，另保存不在备份里的独立oracle。恢复目标必须为空且带测试标记。</x:v>
+        <x:v>数据集 migration_snapshots；仅后续独立版本适用；用户已确定v0.1.0继续SQLite。需要隔离源SQLite、目标MySQL、固定多成员/多项目用量快照、字符/时间/Decimal边界和独立expected。</x:v>
       </x:c>
       <x:c r="G231" s="4" t="str">
-        <x:v>备份能实际恢复而非只压缩成功；A/B不丢，重复补传不增加；C最终只出现一次，账号/权限符合恢复基线。队列与服务确认一致，旧客户端协议兼容。</x:v>
+        <x:v>源/目标记录数、Token、Decimal金额及权限结果一致，ID和幂等语义保持；不重复历史且旧源未被破坏。MySQL版本、字符集和迁移范围须在对应版本指定。</x:v>
       </x:c>
       <x:c r="H231" s="4" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
@@ -18355,7 +18355,7 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L231" s="4" t="str">
-        <x:v>docs/testing/cases/11-TM-011-data-migration.md:45</x:v>
+        <x:v>docs/testing/cases/11-TM-011-data-migration.md:28</x:v>
       </x:c>
       <x:c r="M231" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -18369,10 +18369,10 @@
         <x:v>TM-011</x:v>
       </x:c>
       <x:c r="B232" s="9" t="str">
-        <x:v>E2E-TM011-004</x:v>
+        <x:v>E2E-TM011-003</x:v>
       </x:c>
       <x:c r="C232" s="9" t="str">
-        <x:v>保留时间边界与未同步保护</x:v>
+        <x:v>备份恢复与旧客户端补传</x:v>
       </x:c>
       <x:c r="D232" s="9" t="str">
         <x:v>待拆解</x:v>
@@ -18381,10 +18381,10 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F232" s="9" t="str">
-        <x:v>数据集 migration_snapshots；固定参考时间和Asia/Shanghai；本地90天/服务端365天。分别生成保留首日00:00、前一秒、前一天的已确认事件，以及同样超龄但未同步事件；具备可控时钟与独立边界oracle。</x:v>
+        <x:v>数据集 migration_snapshots；隔离服务已确认事件A/B与旧客户端未确认C；备份包含schema/数据/版本/摘要，另保存不在备份里的独立oracle。恢复目标必须为空且带测试标记。</x:v>
       </x:c>
       <x:c r="G232" s="9" t="str">
-        <x:v>保留首日00:00仍在，早一秒的已同步记录被清理；本地/服务按各自天数独立判定。未同步记录即使超龄仍保护，成功补传仅计一次；历史缺失不能显示真实0。</x:v>
+        <x:v>备份能实际恢复而非只压缩成功；A/B不丢，重复补传不增加；C最终只出现一次，账号/权限符合恢复基线。队列与服务确认一致，旧客户端协议兼容。</x:v>
       </x:c>
       <x:c r="H232" s="9" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
@@ -18401,7 +18401,7 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L232" s="9" t="str">
-        <x:v>docs/testing/cases/11-TM-011-data-migration.md:62</x:v>
+        <x:v>docs/testing/cases/11-TM-011-data-migration.md:45</x:v>
       </x:c>
       <x:c r="M232" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -18412,13 +18412,13 @@
     </x:row>
     <x:row r="233" ht="57" customHeight="1">
       <x:c r="A233" s="4" t="str">
-        <x:v>TM-012</x:v>
+        <x:v>TM-011</x:v>
       </x:c>
       <x:c r="B233" s="4" t="str">
-        <x:v>E2E-TM012-001</x:v>
+        <x:v>E2E-TM011-004</x:v>
       </x:c>
       <x:c r="C233" s="4" t="str">
-        <x:v>菜单栏摘要、暂停恢复与刷新</x:v>
+        <x:v>保留时间边界与未同步保护</x:v>
       </x:c>
       <x:c r="D233" s="4" t="str">
         <x:v>待拆解</x:v>
@@ -18427,10 +18427,10 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F233" s="4" t="str">
-        <x:v>数据集 diagnostic_states；diagnostic_states planned；已采集A=100/10；暂停期间追加B=200/20并重放A。依赖实际采集、统计和同步功能，使用专用日志目录。</x:v>
+        <x:v>数据集 migration_snapshots；固定参考时间和Asia/Shanghai；本地90天/服务端365天。分别生成保留首日00:00、前一秒、前一天的已确认事件，以及同样超龄但未同步事件；具备可控时钟与独立边界oracle。</x:v>
       </x:c>
       <x:c r="G233" s="4" t="str">
-        <x:v>初始total110、暂停期间仍110，恢复后唯一A/B、total330；手动刷新与重启不重复。菜单栏与主窗口同一筛选口径；暂停状态不伪装成没有日志。</x:v>
+        <x:v>保留首日00:00仍在，早一秒的已同步记录被清理；本地/服务按各自天数独立判定。未同步记录即使超龄仍保护，成功补传仅计一次；历史缺失不能显示真实0。</x:v>
       </x:c>
       <x:c r="H233" s="4" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
@@ -18447,7 +18447,7 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L233" s="4" t="str">
-        <x:v>docs/testing/cases/12-TM-012-menu-diagnostics.md:11</x:v>
+        <x:v>docs/testing/cases/11-TM-011-data-migration.md:62</x:v>
       </x:c>
       <x:c r="M233" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -18461,10 +18461,10 @@
         <x:v>TM-012</x:v>
       </x:c>
       <x:c r="B234" s="9" t="str">
-        <x:v>E2E-TM012-002</x:v>
+        <x:v>E2E-TM012-001</x:v>
       </x:c>
       <x:c r="C234" s="9" t="str">
-        <x:v>诊断状态、恢复和登录启动</x:v>
+        <x:v>菜单栏摘要、暂停恢复与刷新</x:v>
       </x:c>
       <x:c r="D234" s="9" t="str">
         <x:v>待拆解</x:v>
@@ -18473,10 +18473,10 @@
         <x:v>产品E2E</x:v>
       </x:c>
       <x:c r="F234" s="9" t="str">
-        <x:v>数据集 diagnostic_states；独立子场景：已授权目录失效、真实服务不可达/恢复、测试App登录启动开关。故障作用测试目录/进程；使用已登录桌面与可自动检查的系统设置。</x:v>
+        <x:v>数据集 diagnostic_states；diagnostic_states planned；已采集A=100/10；暂停期间追加B=200/20并重放A。依赖实际采集、统计和同步功能，使用专用日志目录。</x:v>
       </x:c>
       <x:c r="G234" s="9" t="str">
-        <x:v>错误与真实目录/网络故障一致，不能用旧缓存一直显示健康；恢复后状态及时更新，未同步数据不丢。启动设置与OS登记/实际启动行为一致，测试结束恢复本次测试前状态。</x:v>
+        <x:v>初始total110、暂停期间仍110，恢复后唯一A/B、total330；手动刷新与重启不重复。菜单栏与主窗口同一筛选口径；暂停状态不伪装成没有日志。</x:v>
       </x:c>
       <x:c r="H234" s="9" t="str">
         <x:v>准备：待该功能的数据程序/SQL方案确定。
@@ -18493,7 +18493,7 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L234" s="9" t="str">
-        <x:v>docs/testing/cases/12-TM-012-menu-diagnostics.md:28</x:v>
+        <x:v>docs/testing/cases/12-TM-012-menu-diagnostics.md:11</x:v>
       </x:c>
       <x:c r="M234" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -18502,1623 +18502,1620 @@
         <x:v>v0.2.0-20261001T034118Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="235" ht="72" customHeight="1">
+    <x:row r="235" ht="57" customHeight="1">
       <x:c r="A235" s="4" t="str">
+        <x:v>TM-012</x:v>
+      </x:c>
+      <x:c r="B235" s="4" t="str">
+        <x:v>E2E-TM012-002</x:v>
+      </x:c>
+      <x:c r="C235" s="4" t="str">
+        <x:v>诊断状态、恢复和登录启动</x:v>
+      </x:c>
+      <x:c r="D235" s="4" t="str">
+        <x:v>待拆解</x:v>
+      </x:c>
+      <x:c r="E235" s="4" t="str">
+        <x:v>产品E2E</x:v>
+      </x:c>
+      <x:c r="F235" s="4" t="str">
+        <x:v>数据集 diagnostic_states；独立子场景：已授权目录失效、真实服务不可达/恢复、测试App登录启动开关。故障作用测试目录/进程；使用已登录桌面与可自动检查的系统设置。</x:v>
+      </x:c>
+      <x:c r="G235" s="4" t="str">
+        <x:v>错误与真实目录/网络故障一致，不能用旧缓存一直显示健康；恢复后状态及时更新，未同步数据不丢。启动设置与OS登记/实际启动行为一致，测试结束恢复本次测试前状态。</x:v>
+      </x:c>
+      <x:c r="H235" s="4" t="str">
+        <x:v>准备：待该功能的数据程序/SQL方案确定。
+变化：待具体任务及数据设计细化。
+核验：暂无可执行数据库核验绑定。</x:v>
+      </x:c>
+      <x:c r="I235" s="4" t="str">
+        <x:v>未来规划</x:v>
+      </x:c>
+      <x:c r="J235" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K235" s="4" t="str">
+        <x:v>未来概要</x:v>
+      </x:c>
+      <x:c r="L235" s="4" t="str">
+        <x:v>docs/testing/cases/12-TM-012-menu-diagnostics.md:28</x:v>
+      </x:c>
+      <x:c r="M235" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N235" s="4" t="str">
+        <x:v>v0.2.0-20261001T034118Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="236" ht="72" customHeight="1">
+      <x:c r="A236" s="9" t="str">
         <x:v>TM-003</x:v>
       </x:c>
-      <x:c r="B235" s="4" t="str">
+      <x:c r="B236" s="9" t="str">
         <x:v>TC-TM003-SOURCE-01</x:v>
       </x:c>
-      <x:c r="C235" s="4" t="str">
+      <x:c r="C236" s="9" t="str">
         <x:v>受控版本来源与字段核验</x:v>
       </x:c>
-      <x:c r="D235" s="4" t="str">
+      <x:c r="D236" s="9" t="str">
         <x:v>TASK-TM003-SOURCE</x:v>
       </x:c>
-      <x:c r="E235" s="4" t="str">
+      <x:c r="E236" s="9" t="str">
         <x:v>模块检查</x:v>
       </x:c>
-      <x:c r="F235" s="4" t="str">
+      <x:c r="F236" s="9" t="str">
         <x:v>1. 对照本版声明的 CLI build、官方结构与 sessions/YYYY/MM/DD/*.jsonl 受控原生样例→样例有 session_meta.id、token_usage_record.payload.response_id/usage，版本和 SHA 有记录。2. 换一个未声明 build→该 build 不列为已支持，显示 unsupported_source_version。</x:v>
       </x:c>
-      <x:c r="G235" s="4" t="str">
+      <x:c r="G236" s="9" t="str">
         <x:v>候选元数据与超限“不完整”不被标为支持或历史覆盖证明；经独立核实的原生样例有 session_meta.id、token_usage_record.payload.response_id/usage，版本与 SHA 留证
 该 build 不列为已支持，显示 unsupported_source_version</x:v>
       </x:c>
-      <x:c r="H235" s="4" t="str">
+      <x:c r="H236" s="9" t="str">
         <x:v>准备：无 DB 写入
 变化：不适用；见本用例具体数据库观察面。
 核验：无 DB 写入；核对来源清单版本、摘要与私有样例归属。数据：受控来源样例；每次新隔离根重建。</x:v>
       </x:c>
-      <x:c r="I235" s="4" t="str">
+      <x:c r="I236" s="9" t="str">
         <x:v>draft</x:v>
       </x:c>
-      <x:c r="J235" s="4" t="str">
+      <x:c r="J236" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K235" s="4" t="str">
+      <x:c r="K236" s="9" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L235" s="4" t="str">
+      <x:c r="L236" s="9" t="str">
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:238</x:v>
       </x:c>
-      <x:c r="M235" s="4" t="str">
+      <x:c r="M236" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N235" s="4" t="str">
+      <x:c r="N236" s="9" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="236" ht="72" customHeight="1">
-      <x:c r="A236" s="9" t="str">
+    <x:row r="237" ht="72" customHeight="1">
+      <x:c r="A237" s="4" t="str">
         <x:v>TM-003</x:v>
       </x:c>
-      <x:c r="B236" s="9" t="str">
+      <x:c r="B237" s="4" t="str">
         <x:v>TC-TM003-DATA-01</x:v>
       </x:c>
-      <x:c r="C236" s="9" t="str">
+      <x:c r="C237" s="4" t="str">
         <x:v>固定原生形状数据与独立预期</x:v>
       </x:c>
-      <x:c r="D236" s="9" t="str">
+      <x:c r="D237" s="4" t="str">
         <x:v>TASK-TM003-FIXTURE</x:v>
       </x:c>
-      <x:c r="E236" s="9" t="str">
+      <x:c r="E237" s="4" t="str">
         <x:v>data_check</x:v>
       </x:c>
-      <x:c r="F236" s="9" t="str">
+      <x:c r="F237" s="4" t="str">
         <x:v>1. 在 sessions/YYYY/MM/DD/*.jsonl 以 seed303 与本次已记录的 T0 生成 A/B/C 原生形状记录→同一 seed+T0 重建时字节摘要固定且三 ID 不同。2. 独立读取 expected 文件→A=110、A+B+C=660、cached=120，第二配方=220；没有调用产品解析器。</x:v>
       </x:c>
-      <x:c r="G236" s="9" t="str">
+      <x:c r="G237" s="4" t="str">
         <x:v>两份相对位置和字节摘要相同，A/B/C 三响应 ID 互异；四层子目录在 TM-002 草稿8层上限内、文件/目录项未达1000/5000；owner/expected 记录 T0
 A=110、A+B+C=660、cached=120，第二配方=220；没有调用产品解析器</x:v>
       </x:c>
-      <x:c r="H236" s="9" t="str">
+      <x:c r="H237" s="4" t="str">
         <x:v>准备：准备新私有根，不写用量表
 变化：不适用；见本用例具体数据库观察面。
 核验：不写用量表；只核对嵌套来源相对位置、元数据上限、两份源 SHA、独立 expected 和 owner；仅删除本例拥有的根。</x:v>
       </x:c>
-      <x:c r="I236" s="9" t="str">
+      <x:c r="I237" s="4" t="str">
         <x:v>draft</x:v>
       </x:c>
-      <x:c r="J236" s="9" t="str">
+      <x:c r="J237" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K236" s="9" t="str">
+      <x:c r="K237" s="4" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L236" s="9" t="str">
+      <x:c r="L237" s="4" t="str">
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:242</x:v>
       </x:c>
-      <x:c r="M236" s="9" t="str">
+      <x:c r="M237" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N236" s="9" t="str">
+      <x:c r="N237" s="4" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="237" ht="72" customHeight="1">
-      <x:c r="A237" s="4" t="str">
+    <x:row r="238" ht="72" customHeight="1">
+      <x:c r="A238" s="9" t="str">
         <x:v>TM-003</x:v>
       </x:c>
-      <x:c r="B237" s="4" t="str">
+      <x:c r="B238" s="9" t="str">
         <x:v>TC-TM003-PARSE-01</x:v>
       </x:c>
-      <x:c r="C237" s="4" t="str">
+      <x:c r="C238" s="9" t="str">
         <x:v>三响应与缓存子项计量</x:v>
       </x:c>
-      <x:c r="D237" s="4" t="str">
+      <x:c r="D238" s="9" t="str">
         <x:v>TASK-TM003-PARSE</x:v>
       </x:c>
-      <x:c r="E237" s="4" t="str">
+      <x:c r="E238" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F237" s="4" t="str">
+      <x:c r="F238" s="9" t="str">
         <x:v>R-BASE。1. 仅追加 A 完整行并从 UI 刷新→卡片 input100/output10/total110/cached read20/cache write5/reasoning3、唯一1。2. 追加 B/C 后刷新→input600/output60/total660/cached read120/cache write30/reasoning18、唯一3；累计字段不额外加。</x:v>
       </x:c>
-      <x:c r="G237" s="4" t="str">
+      <x:c r="G238" s="9" t="str">
         <x:v>卡片 input100/output10/total110/cached read20/cache write5/reasoning3、唯一1
 input600/output60/total660/cached read120/cache write30/reasoning18、唯一3；累计字段不额外加</x:v>
       </x:c>
-      <x:c r="H237" s="4" t="str">
+      <x:c r="H238" s="9" t="str">
         <x:v>准备：空客户端库
 变化：插入 A 后1行，再插 B/C 后3行
 核验：空客户端库→插入 A 后1行，再插 B/C 后3行；Q_SUM=(3,600,60,120)，Q_SUB=(30,18)、Q_NULL=0；重置私有库。</x:v>
       </x:c>
-      <x:c r="I237" s="4" t="str">
+      <x:c r="I238" s="9" t="str">
         <x:v>draft</x:v>
       </x:c>
-      <x:c r="J237" s="4" t="str">
+      <x:c r="J238" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K237" s="4" t="str">
+      <x:c r="K238" s="9" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L237" s="4" t="str">
+      <x:c r="L238" s="9" t="str">
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:246</x:v>
       </x:c>
-      <x:c r="M237" s="4" t="str">
+      <x:c r="M238" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N237" s="4" t="str">
+      <x:c r="N238" s="9" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="238" ht="72" customHeight="1">
-      <x:c r="A238" s="9" t="str">
+    <x:row r="239" ht="72" customHeight="1">
+      <x:c r="A239" s="4" t="str">
         <x:v>TM-003</x:v>
       </x:c>
-      <x:c r="B238" s="9" t="str">
+      <x:c r="B239" s="4" t="str">
         <x:v>TC-TM003-SCAN-01</x:v>
       </x:c>
-      <x:c r="C238" s="9" t="str">
+      <x:c r="C239" s="4" t="str">
         <x:v>追加补扫重启移动去重</x:v>
       </x:c>
-      <x:c r="D238" s="9" t="str">
+      <x:c r="D239" s="4" t="str">
         <x:v>TASK-TM003-SCAN</x:v>
       </x:c>
-      <x:c r="E238" s="9" t="str">
+      <x:c r="E239" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F238" s="9" t="str">
+      <x:c r="F239" s="4" t="str">
         <x:v>R-BASE、A/B/C。1. 三次分批追加并等 watcher 或30秒补扫→每批总量110/330/660。2. 手动刷新同文件并重启 App→仍660。3. 同一授权根内移动文件并刷新→仍唯一3、660。</x:v>
       </x:c>
-      <x:c r="G238" s="9" t="str">
+      <x:c r="G239" s="4" t="str">
         <x:v>每批总量110/330/660
 仍660
 仍唯一3、660</x:v>
       </x:c>
-      <x:c r="H238" s="9" t="str">
+      <x:c r="H239" s="4" t="str">
         <x:v>准备：空库
 变化：只增加3事件
 核验：空库→只增加3事件；每步 Q_SUM 为 (1,100,10,20)、(2,300,30,60)、(3,600,60,120)，重扫/重启/移动不变；核对 Q_CURSOR 完整行字节边界。</x:v>
       </x:c>
-      <x:c r="I238" s="9" t="str">
+      <x:c r="I239" s="4" t="str">
         <x:v>draft</x:v>
       </x:c>
-      <x:c r="J238" s="9" t="str">
+      <x:c r="J239" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K238" s="9" t="str">
+      <x:c r="K239" s="4" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L238" s="9" t="str">
+      <x:c r="L239" s="4" t="str">
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:250</x:v>
       </x:c>
-      <x:c r="M238" s="9" t="str">
+      <x:c r="M239" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N238" s="9" t="str">
+      <x:c r="N239" s="4" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="239" ht="117" customHeight="1">
-      <x:c r="A239" s="4" t="str">
+    <x:row r="240" ht="117" customHeight="1">
+      <x:c r="A240" s="9" t="str">
         <x:v>TM-003</x:v>
       </x:c>
-      <x:c r="B239" s="4" t="str">
+      <x:c r="B240" s="9" t="str">
         <x:v>TC-TM003-STORE-01</x:v>
       </x:c>
-      <x:c r="C239" s="4" t="str">
+      <x:c r="C240" s="9" t="str">
         <x:v>事件与游标持久化</x:v>
       </x:c>
-      <x:c r="D239" s="4" t="str">
+      <x:c r="D240" s="9" t="str">
         <x:v>TASK-TM003-STORE</x:v>
       </x:c>
-      <x:c r="E239" s="4" t="str">
+      <x:c r="E240" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F239" s="4" t="str">
+      <x:c r="F240" s="9" t="str">
         <x:v>R-BASE、A/B；本例拥有的私有 profile 身份密钥和隔离客户端库。1. 完整 A 刷新→110。2. 本例进程退出/重启→110。3. 追加同 ID 同用量 A→仍110。4. 仅使本例 profile 的 usage 身份密钥不可读取，再追加 B=200/20/cached40 并刷新→保持110、停采集。5. 恢复原密钥后重启/刷新→A 不重计、B 入库，total330。密钥原文不进入报告。</x:v>
       </x:c>
-      <x:c r="G239" s="4" t="str">
+      <x:c r="G240" s="9" t="str">
         <x:v>110
 UI 恢复110
 仍110；无第二事件
 密钥不可用时停采集，不生成新键重扫旧日志或把 B 入库
 恢复原密钥后只补入 B，既有 A 不重计</x:v>
       </x:c>
-      <x:c r="H239" s="4" t="str">
+      <x:c r="H240" s="9" t="str">
         <x:v>准备：本例私有空库、受控 A/B 原生形状数据和隔离 usage 身份密钥；仅本例 fixture 可暂时使该密钥不可读取并恢复原件；不直接向事件表造数
 变化：A 一事件及游标原子提交；密钥不可用时事件/游标不变且覆盖不完整；恢复原密钥后 B 一事件提交、A 键不变
 核验：只读 Q_SUM 依次 (1,100,10,20)、同值、同值、同值、(2,300,30,60)；逐步检查 Q_CURSOR 与 coverage；原 A source_event_key 在恢复后不变，绝不让新密钥重扫成第二份 A</x:v>
       </x:c>
-      <x:c r="I239" s="4" t="str">
+      <x:c r="I240" s="9" t="str">
         <x:v>draft</x:v>
       </x:c>
-      <x:c r="J239" s="4" t="str">
+      <x:c r="J240" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K239" s="4" t="str">
+      <x:c r="K240" s="9" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L239" s="4" t="str">
+      <x:c r="L240" s="9" t="str">
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:254</x:v>
       </x:c>
-      <x:c r="M239" s="4" t="str">
+      <x:c r="M240" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N239" s="4" t="str">
+      <x:c r="N240" s="9" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="240" ht="87" customHeight="1">
-      <x:c r="A240" s="9" t="str">
+    <x:row r="241" ht="87" customHeight="1">
+      <x:c r="A241" s="4" t="str">
         <x:v>TM-003</x:v>
       </x:c>
-      <x:c r="B240" s="9" t="str">
+      <x:c r="B241" s="4" t="str">
         <x:v>TC-TM003-UI-01</x:v>
       </x:c>
-      <x:c r="C240" s="9" t="str">
+      <x:c r="C241" s="4" t="str">
         <x:v>可信总量与未知来源展示</x:v>
       </x:c>
-      <x:c r="D240" s="9" t="str">
+      <x:c r="D241" s="4" t="str">
         <x:v>TASK-TM003-UI</x:v>
       </x:c>
-      <x:c r="E240" s="9" t="str">
+      <x:c r="E241" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F240" s="9" t="str">
+      <x:c r="F241" s="4" t="str">
         <x:v>R-BASE、A/B/C。1. 采集前查看卡片→显示尚无可证明历史/等待采集，不能显示已知0。2. 采集后→可信 input600、output60、total660、cached read120、cache write30、reasoning output18、唯一3、UTC最后采集时间。3. 插入一个缺 cached_input_tokens 的非 0.158 完整行→可信总量仍660，显示缺字段诊断，不把未知 cached 当0。</x:v>
       </x:c>
-      <x:c r="G240" s="9" t="str">
+      <x:c r="G241" s="4" t="str">
         <x:v>显示尚无可证明历史/等待采集，不能显示已知0
 可信 input600、output60、total660、cached read120、cache write30、reasoning output18、唯一3、UTC最后采集时间
 可信总量仍660，显示缺字段诊断，不把未知 cached 当0</x:v>
       </x:c>
-      <x:c r="H240" s="9" t="str">
+      <x:c r="H241" s="4" t="str">
         <x:v>准备：空库
 变化：前三条 Q_SUM=(3,600,60,120)
 核验：空库→前三条 Q_SUM=(3,600,60,120)；无新事件，Q_SUM保持三条；Q_DIAG出现缺字段，UI 区分未知来源。</x:v>
       </x:c>
-      <x:c r="I240" s="9" t="str">
+      <x:c r="I241" s="4" t="str">
         <x:v>draft</x:v>
       </x:c>
-      <x:c r="J240" s="9" t="str">
+      <x:c r="J241" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K240" s="9" t="str">
+      <x:c r="K241" s="4" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L240" s="9" t="str">
+      <x:c r="L241" s="4" t="str">
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:258</x:v>
       </x:c>
-      <x:c r="M240" s="9" t="str">
+      <x:c r="M241" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N240" s="9" t="str">
+      <x:c r="N241" s="4" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="241" ht="72" customHeight="1">
-      <x:c r="A241" s="4" t="str">
+    <x:row r="242" ht="72" customHeight="1">
+      <x:c r="A242" s="9" t="str">
         <x:v>TM-003</x:v>
       </x:c>
-      <x:c r="B241" s="4" t="str">
+      <x:c r="B242" s="9" t="str">
         <x:v>TC-TM003-SOURCE-02</x:v>
       </x:c>
-      <x:c r="C241" s="4" t="str">
+      <x:c r="C242" s="9" t="str">
         <x:v>无响应身份累计记录降级</x:v>
       </x:c>
-      <x:c r="D241" s="4" t="str">
+      <x:c r="D242" s="9" t="str">
         <x:v>TASK-TM003-SOURCE</x:v>
       </x:c>
-      <x:c r="E241" s="4" t="str">
+      <x:c r="E242" s="9" t="str">
         <x:v>模块检查</x:v>
       </x:c>
-      <x:c r="F241" s="4" t="str">
+      <x:c r="F242" s="9" t="str">
         <x:v>1. 输入只有 event_msg.token_count.info.total_token_usage=100/10 且无 response_id→诊断 unverified_cumulative、可信事件0。2. 加 rate-limit-only 的 info=null→诊断 missing_usage，不生成0值用量事件。</x:v>
       </x:c>
-      <x:c r="G241" s="4" t="str">
+      <x:c r="G242" s="9" t="str">
         <x:v>诊断 unverified_cumulative、可信事件0
 诊断 missing_usage，不生成0值用量事件</x:v>
       </x:c>
-      <x:c r="H241" s="4" t="str">
+      <x:c r="H242" s="9" t="str">
         <x:v>准备：新库
 变化：Q_SUM无事件
 核验：新库→Q_SUM无事件；Q_DIAG分别含 unverified_cumulative 与 missing_usage；仅测试拥有根。</x:v>
       </x:c>
-      <x:c r="I241" s="4" t="str">
+      <x:c r="I242" s="9" t="str">
         <x:v>draft</x:v>
       </x:c>
-      <x:c r="J241" s="4" t="str">
+      <x:c r="J242" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K241" s="4" t="str">
+      <x:c r="K242" s="9" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L241" s="4" t="str">
+      <x:c r="L242" s="9" t="str">
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:262</x:v>
       </x:c>
-      <x:c r="M241" s="4" t="str">
+      <x:c r="M242" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N241" s="4" t="str">
+      <x:c r="N242" s="9" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="242" ht="57" customHeight="1">
-      <x:c r="A242" s="9" t="str">
+    <x:row r="243" ht="57" customHeight="1">
+      <x:c r="A243" s="4" t="str">
         <x:v>TM-003</x:v>
       </x:c>
-      <x:c r="B242" s="9" t="str">
+      <x:c r="B243" s="4" t="str">
         <x:v>TC-TM003-PARSE-02</x:v>
       </x:c>
-      <x:c r="C242" s="9" t="str">
+      <x:c r="C243" s="4" t="str">
         <x:v>损坏及缺字段记录隔离</x:v>
       </x:c>
-      <x:c r="D242" s="9" t="str">
+      <x:c r="D243" s="4" t="str">
         <x:v>TASK-TM003-PARSE</x:v>
       </x:c>
-      <x:c r="E242" s="9" t="str">
+      <x:c r="E243" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F242" s="9" t="str">
+      <x:c r="F243" s="4" t="str">
         <x:v>R-BASE。1. 完整合法 100/10 行→110。2. 依次追加缺 usage、负 input、cached 111&gt;input100、矛盾 total111 四个不同 ID 完整行→UI 可信总量仍110，每项显示独立诊断，不能作为0值成功事件。</x:v>
       </x:c>
-      <x:c r="G242" s="9" t="str">
+      <x:c r="G243" s="4" t="str">
         <x:v>110
 UI 可信总量仍110，每项显示独立诊断，不能作为0值成功事件</x:v>
       </x:c>
-      <x:c r="H242" s="9" t="str">
+      <x:c r="H243" s="4" t="str">
         <x:v>准备：空库
 变化：仅合法1行
 核验：空库→仅合法1行；Q_SUM=(1,100,10,20)；Q_DIAG四种错误各≥1；重置私有库。</x:v>
       </x:c>
-      <x:c r="I242" s="9" t="str">
+      <x:c r="I243" s="4" t="str">
         <x:v>draft</x:v>
       </x:c>
-      <x:c r="J242" s="9" t="str">
+      <x:c r="J243" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K242" s="9" t="str">
+      <x:c r="K243" s="4" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L242" s="9" t="str">
+      <x:c r="L243" s="4" t="str">
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:266</x:v>
       </x:c>
-      <x:c r="M242" s="9" t="str">
+      <x:c r="M243" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N242" s="9" t="str">
+      <x:c r="N243" s="4" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="243" ht="87" customHeight="1">
-      <x:c r="A243" s="4" t="str">
+    <x:row r="244" ht="87" customHeight="1">
+      <x:c r="A244" s="9" t="str">
         <x:v>TM-003</x:v>
       </x:c>
-      <x:c r="B243" s="4" t="str">
+      <x:c r="B244" s="9" t="str">
         <x:v>TC-TM003-MODEL-01</x:v>
       </x:c>
-      <x:c r="C243" s="4" t="str">
+      <x:c r="C244" s="9" t="str">
         <x:v>模型标识与未知模型保留</x:v>
       </x:c>
-      <x:c r="D243" s="4" t="str">
+      <x:c r="D244" s="9" t="str">
         <x:v>TASK-TM003-PARSE</x:v>
       </x:c>
-      <x:c r="E243" s="4" t="str">
+      <x:c r="E244" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F243" s="4" t="str">
+      <x:c r="F244" s="9" t="str">
         <x:v>R-BASE。1. 在有同一 turn_id 的原生 turn_context 声明 gpt-6-sol 并追加 ID-m 10/1→UI 总量11，DB模型为 gpt-6-sol。2. 对新 turn 声明来源未知但实际原样标识 model-x 并追加 ID-n 10/1→UI 总量22，DB保留 model-x，不得改成0或空字符串。3. 追加找不到同 turn 上下文的 ID-o 10/1→UI 总量33，DB模型为 NULL 且显示模型未知诊断。</x:v>
       </x:c>
-      <x:c r="G243" s="4" t="str">
+      <x:c r="G244" s="9" t="str">
         <x:v>UI 总量11，DB模型为 gpt-6-sol
 UI 总量22，DB保留 model-x，不得改成0或空字符串
 UI 总量33，DB模型为 NULL 且显示模型未知诊断</x:v>
       </x:c>
-      <x:c r="H243" s="4" t="str">
+      <x:c r="H244" s="9" t="str">
         <x:v>准备：空库
 变化：最终 Q_IO=(3,30,3)
 核验：空库→最终 Q_IO=(3,30,3)；只读查询三个模型字段依次为 gpt-6-sol、model-x、NULL；不插入模型维度造数。</x:v>
       </x:c>
-      <x:c r="I243" s="4" t="str">
+      <x:c r="I244" s="9" t="str">
         <x:v>draft</x:v>
       </x:c>
-      <x:c r="J243" s="4" t="str">
+      <x:c r="J244" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K243" s="4" t="str">
+      <x:c r="K244" s="9" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L243" s="4" t="str">
+      <x:c r="L244" s="9" t="str">
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:270</x:v>
       </x:c>
-      <x:c r="M243" s="4" t="str">
+      <x:c r="M244" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N243" s="4" t="str">
+      <x:c r="N244" s="9" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="244" ht="72" customHeight="1">
-      <x:c r="A244" s="9" t="str">
+    <x:row r="245" ht="72" customHeight="1">
+      <x:c r="A245" s="4" t="str">
         <x:v>TM-003</x:v>
       </x:c>
-      <x:c r="B244" s="9" t="str">
+      <x:c r="B245" s="4" t="str">
         <x:v>TC-TM003-DEDUP-01</x:v>
       </x:c>
-      <x:c r="C244" s="9" t="str">
+      <x:c r="C245" s="4" t="str">
         <x:v>相同响应重放和身份冲突</x:v>
       </x:c>
-      <x:c r="D244" s="9" t="str">
+      <x:c r="D245" s="4" t="str">
         <x:v>TASK-TM003-IDENTITY</x:v>
       </x:c>
-      <x:c r="E244" s="9" t="str">
+      <x:c r="E245" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F244" s="9" t="str">
+      <x:c r="F245" s="4" t="str">
         <x:v>R-BASE。1. 追加 ID-a 100/10→110。2. 重放 ID-a 完全相同记录→仍110。3. 追加 ID-b 同样100/10→220且唯一2。4. 再写 ID-a 999/99→仍220并有 identity_conflict。</x:v>
       </x:c>
-      <x:c r="G244" s="9" t="str">
+      <x:c r="G245" s="4" t="str">
         <x:v>110
 仍110
 220且唯一2
 仍220并有 identity_conflict</x:v>
       </x:c>
-      <x:c r="H244" s="9" t="str">
+      <x:c r="H245" s="4" t="str">
         <x:v>准备：空库
 变化：最终 Q_SUM=(2,200,20,40)
 核验：空库→最终 Q_SUM=(2,200,20,40)；冲突不覆盖原行；读 Q_DIAG。</x:v>
       </x:c>
-      <x:c r="I244" s="9" t="str">
+      <x:c r="I245" s="4" t="str">
         <x:v>draft</x:v>
       </x:c>
-      <x:c r="J244" s="9" t="str">
+      <x:c r="J245" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K244" s="9" t="str">
+      <x:c r="K245" s="4" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L244" s="9" t="str">
+      <x:c r="L245" s="4" t="str">
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:274</x:v>
       </x:c>
-      <x:c r="M244" s="9" t="str">
+      <x:c r="M245" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N244" s="9" t="str">
+      <x:c r="N245" s="4" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="245" ht="87" customHeight="1">
-      <x:c r="A245" s="4" t="str">
+    <x:row r="246" ht="87" customHeight="1">
+      <x:c r="A246" s="9" t="str">
         <x:v>TM-003</x:v>
       </x:c>
-      <x:c r="B245" s="4" t="str">
+      <x:c r="B246" s="9" t="str">
         <x:v>TC-TM003-BRANCH-01</x:v>
       </x:c>
-      <x:c r="C245" s="4" t="str">
+      <x:c r="C246" s="9" t="str">
         <x:v>累计快照新会话与分支</x:v>
       </x:c>
-      <x:c r="D245" s="4" t="str">
+      <x:c r="D246" s="9" t="str">
         <x:v>TASK-TM003-IDENTITY</x:v>
       </x:c>
-      <x:c r="E245" s="4" t="str">
+      <x:c r="E246" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F245" s="4" t="str">
+      <x:c r="F246" s="9" t="str">
         <x:v>R-BASE。1. 主会话按 usage 写 100/10、50/5，而累计快照从100/10到150/15→可信165。2. 新会话写30/3→198。3. 普通 CLI fork 子文件带 forked_from_id，只有新响应20/2、thread 累计170/17；另从独立文件重放父 A→可信220、唯一4，重放不新增事件。4. 写无响应身份的累计回退和未知结构→仍220，显示 unverified_cumulative / unknown_format。</x:v>
       </x:c>
-      <x:c r="G245" s="4" t="str">
+      <x:c r="G246" s="9" t="str">
         <x:v>可信165
 198
 可信220、唯一4
 仍220，显示 unverified_cumulative / unknown_format</x:v>
       </x:c>
-      <x:c r="H245" s="4" t="str">
+      <x:c r="H246" s="9" t="str">
         <x:v>准备：空库
 变化：最终 Q_IO=(4,200,20)
 核验：空库→最终 Q_IO=(4,200,20)；output20、total220；cached 按固定各项另核；Q_DIAG有两类，继承不新增事件。</x:v>
       </x:c>
-      <x:c r="I245" s="4" t="str">
+      <x:c r="I246" s="9" t="str">
         <x:v>draft</x:v>
       </x:c>
-      <x:c r="J245" s="4" t="str">
+      <x:c r="J246" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K245" s="4" t="str">
+      <x:c r="K246" s="9" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L245" s="4" t="str">
+      <x:c r="L246" s="9" t="str">
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:278</x:v>
       </x:c>
-      <x:c r="M245" s="4" t="str">
+      <x:c r="M246" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N245" s="4" t="str">
+      <x:c r="N246" s="9" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="246" ht="102" customHeight="1">
-      <x:c r="A246" s="9" t="str">
+    <x:row r="247" ht="102" customHeight="1">
+      <x:c r="A247" s="4" t="str">
         <x:v>TM-003</x:v>
       </x:c>
-      <x:c r="B246" s="9" t="str">
+      <x:c r="B247" s="4" t="str">
         <x:v>TC-TM003-NAMESPACE-01</x:v>
       </x:c>
-      <x:c r="C246" s="9" t="str">
+      <x:c r="C247" s="4" t="str">
         <x:v>跨来源事件身份和不明继承</x:v>
       </x:c>
-      <x:c r="D246" s="9" t="str">
+      <x:c r="D247" s="4" t="str">
         <x:v>TASK-TM003-IDENTITY</x:v>
       </x:c>
-      <x:c r="E246" s="9" t="str">
+      <x:c r="E247" s="4" t="str">
         <x:v>模块检查</x:v>
       </x:c>
-      <x:c r="F246" s="9" t="str">
+      <x:c r="F247" s="4" t="str">
         <x:v>本例私有 schema 与tests/fixtures/tm004/identity-v1-vectors.json 中的公开测试 HMAC key（仅固定向量，绝不进入产品 profile）；标准事件 Codex provider-response/shared-call-01=100/10/cached20，Claude provider-message/shared-call-01=30/3/cached0；随后同 Codex 事件重放、另一 Agent 无复制链同 Claude ID 重用、同 Codex ID 但用量或模型冲突。</x:v>
       </x:c>
-      <x:c r="G246" s="9" t="str">
+      <x:c r="G247" s="4" t="str">
         <x:v>两条可信事件 total143，显式来源域防止跨工具误合并
 键相同且不新增事件
 不能把未证明同一调用的重用计为新事件，Agent 归属不进入唯一键
 首条可信事件不覆写，仍两条 total143</x:v>
       </x:c>
-      <x:c r="H246" s="9" t="str">
+      <x:c r="H247" s="4" t="str">
         <x:v>准备：本例拥有的全新私有 schema；使用已提交公开32字节测试 key 与标准事件作为纯身份入口固定 oracle，真实产品 profile 自行生成私密随机 key；不直接向事件表造数
 变化：正式身份/存储入口只接受2事件；重复和冲突不新增或覆写
 核验：只读 Q_SUM=(2,130,13,20)，按 source 核对两键精确等于 afd67bd0cad0227b3e7b5ac132bb9b3ed492073983b9c16a0c9cc24dd3008051 和 bf222a85ab2209f72ff82c21b7172c9315448b3e1d5bf4503a3c76b30c46cad1，再核对身份冲突与不明继承诊断、coverage 不完整</x:v>
       </x:c>
-      <x:c r="I246" s="9" t="str">
+      <x:c r="I247" s="4" t="str">
         <x:v>draft</x:v>
       </x:c>
-      <x:c r="J246" s="9" t="str">
+      <x:c r="J247" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K246" s="9" t="str">
+      <x:c r="K247" s="4" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L246" s="9" t="str">
+      <x:c r="L247" s="4" t="str">
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:282</x:v>
       </x:c>
-      <x:c r="M246" s="9" t="str">
+      <x:c r="M247" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N246" s="9" t="str">
+      <x:c r="N247" s="4" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="247" ht="57" customHeight="1">
-      <x:c r="A247" s="4" t="str">
+    <x:row r="248" ht="57" customHeight="1">
+      <x:c r="A248" s="9" t="str">
         <x:v>TM-003</x:v>
       </x:c>
-      <x:c r="B247" s="4" t="str">
+      <x:c r="B248" s="9" t="str">
         <x:v>TC-TM003-PRIVACY-01</x:v>
       </x:c>
-      <x:c r="C247" s="4" t="str">
+      <x:c r="C248" s="9" t="str">
         <x:v>原文哨兵不得入库和报告</x:v>
       </x:c>
-      <x:c r="D247" s="4" t="str">
+      <x:c r="D248" s="9" t="str">
         <x:v>TASK-TM003-STORE</x:v>
       </x:c>
-      <x:c r="E247" s="4" t="str">
+      <x:c r="E248" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F247" s="4" t="str">
+      <x:c r="F248" s="9" t="str">
         <x:v>R-BASE 中只放合法 A=100/10/cached20；在 A 的非用量文本字段加入固定合成哨兵、代码片段和合成绝对路径，然后退出 App 检查仅本例拥有的 SQLite/WAL/采集报告。</x:v>
       </x:c>
-      <x:c r="G247" s="4" t="str">
+      <x:c r="G248" s="9" t="str">
         <x:v>有效用量仍只按 usage 计
 均不含哨兵/原始路径/原始 JSONL</x:v>
       </x:c>
-      <x:c r="H247" s="4" t="str">
+      <x:c r="H248" s="9" t="str">
         <x:v>准备：新库
 变化：仅白名单事件字段、HMAC 身份
 核验：新库→仅白名单事件字段、HMAC 身份；Q_SUM与合法用量一致；重置私有根。</x:v>
       </x:c>
-      <x:c r="I247" s="4" t="str">
+      <x:c r="I248" s="9" t="str">
         <x:v>draft</x:v>
       </x:c>
-      <x:c r="J247" s="4" t="str">
+      <x:c r="J248" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K247" s="4" t="str">
+      <x:c r="K248" s="9" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L247" s="4" t="str">
+      <x:c r="L248" s="9" t="str">
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:286</x:v>
       </x:c>
-      <x:c r="M247" s="4" t="str">
+      <x:c r="M248" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N247" s="4" t="str">
+      <x:c r="N248" s="9" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="248" ht="57" customHeight="1">
-      <x:c r="A248" s="9" t="str">
+    <x:row r="249" ht="57" customHeight="1">
+      <x:c r="A249" s="4" t="str">
         <x:v>TM-003</x:v>
       </x:c>
-      <x:c r="B248" s="9" t="str">
+      <x:c r="B249" s="4" t="str">
         <x:v>TC-TM003-DATA-02</x:v>
       </x:c>
-      <x:c r="C248" s="9" t="str">
+      <x:c r="C249" s="4" t="str">
         <x:v>半行字节数据与归属清理</x:v>
       </x:c>
-      <x:c r="D248" s="9" t="str">
+      <x:c r="D249" s="4" t="str">
         <x:v>TASK-TM003-FIXTURE</x:v>
       </x:c>
-      <x:c r="E248" s="9" t="str">
+      <x:c r="E249" s="4" t="str">
         <x:v>data_check</x:v>
       </x:c>
-      <x:c r="F248" s="9" t="str">
+      <x:c r="F249" s="4" t="str">
         <x:v>1. 数据程序向拥有的文件只写 B JSONL 前半字节且无 LF→文件确实不含完整 B 行。2. 同程序补写余字节与 LF→恰好一条完整 B。3. 清理仅 owner 收据中的源文件→其他根、App 和服务不受影响。</x:v>
       </x:c>
-      <x:c r="G248" s="9" t="str">
+      <x:c r="G249" s="4" t="str">
         <x:v>文件确实不含完整 B 行
 恰好一条完整 B
 其他根、App 和服务不受影响</x:v>
       </x:c>
-      <x:c r="H248" s="9" t="str">
+      <x:c r="H249" s="4" t="str">
         <x:v>准备：无产品库写入
 变化：不适用；见本用例具体数据库观察面。
 核验：无产品库写入；按字节摘要、LF 数和 owner 核对；重置只删本例根。</x:v>
       </x:c>
-      <x:c r="I248" s="9" t="str">
+      <x:c r="I249" s="4" t="str">
         <x:v>draft</x:v>
       </x:c>
-      <x:c r="J248" s="9" t="str">
+      <x:c r="J249" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K248" s="9" t="str">
+      <x:c r="K249" s="4" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L248" s="9" t="str">
+      <x:c r="L249" s="4" t="str">
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:290</x:v>
       </x:c>
-      <x:c r="M248" s="9" t="str">
+      <x:c r="M249" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N248" s="9" t="str">
+      <x:c r="N249" s="4" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="249" ht="72" customHeight="1">
-      <x:c r="A249" s="4" t="str">
+    <x:row r="250" ht="72" customHeight="1">
+      <x:c r="A250" s="9" t="str">
         <x:v>TM-003</x:v>
       </x:c>
-      <x:c r="B249" s="4" t="str">
+      <x:c r="B250" s="9" t="str">
         <x:v>TC-TM003-SCAN-02</x:v>
       </x:c>
-      <x:c r="C249" s="4" t="str">
+      <x:c r="C250" s="9" t="str">
         <x:v>半行补全后只计一次</x:v>
       </x:c>
-      <x:c r="D249" s="4" t="str">
+      <x:c r="D250" s="9" t="str">
         <x:v>TASK-TM003-SCAN</x:v>
       </x:c>
-      <x:c r="E249" s="4" t="str">
+      <x:c r="E250" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F249" s="4" t="str">
+      <x:c r="F250" s="9" t="str">
         <x:v>R-BASE。1. 完整 A=100/10 后刷新→total110、唯一1。2. 只追加 B=50/5 半行并刷新→仍110、游标停在 A 的 LF 后。3. 补齐 B 和 LF 后刷新，再重启→total165、唯一2，B 只计一次。</x:v>
       </x:c>
-      <x:c r="G249" s="4" t="str">
+      <x:c r="G250" s="9" t="str">
         <x:v>total110、唯一1
 仍110、游标停在 A 的 LF 后
 total165、唯一2，B 只计一次</x:v>
       </x:c>
-      <x:c r="H249" s="4" t="str">
+      <x:c r="H250" s="9" t="str">
         <x:v>准备：空库
 变化：Q_SUM=(1,100,10,20)，半行时同值，补全后 Q_IO=(2,150,15)
 核验：空库→Q_SUM=(1,100,10,20)，半行时同值，补全后 Q_IO=(2,150,15)；Q_CURSOR先停于 A 完整字节，再到 B 完整字节。</x:v>
       </x:c>
-      <x:c r="I249" s="4" t="str">
+      <x:c r="I250" s="9" t="str">
         <x:v>draft</x:v>
       </x:c>
-      <x:c r="J249" s="4" t="str">
+      <x:c r="J250" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K249" s="4" t="str">
+      <x:c r="K250" s="9" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L249" s="4" t="str">
+      <x:c r="L250" s="9" t="str">
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:294</x:v>
       </x:c>
-      <x:c r="M249" s="4" t="str">
+      <x:c r="M250" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N249" s="4" t="str">
+      <x:c r="N250" s="9" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="250" ht="72" customHeight="1">
-      <x:c r="A250" s="9" t="str">
+    <x:row r="251" ht="72" customHeight="1">
+      <x:c r="A251" s="4" t="str">
         <x:v>TM-003</x:v>
       </x:c>
-      <x:c r="B250" s="9" t="str">
+      <x:c r="B251" s="4" t="str">
         <x:v>TC-TM003-SCAN-03</x:v>
       </x:c>
-      <x:c r="C250" s="9" t="str">
+      <x:c r="C251" s="4" t="str">
         <x:v>截断后的重读与新事件</x:v>
       </x:c>
-      <x:c r="D250" s="9" t="str">
+      <x:c r="D251" s="4" t="str">
         <x:v>TASK-TM003-SCAN</x:v>
       </x:c>
-      <x:c r="E250" s="9" t="str">
+      <x:c r="E251" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F250" s="9" t="str">
+      <x:c r="F251" s="4" t="str">
         <x:v>R-BASE。1. 完整 A=100/10 与 B=50/5 入库→total165、唯一2。2. 仅对本例源文件截断为完整 A 并刷新→已采集 B 不丢，仍165，游标重置到当前 A 的 LF。3. 追加新 ID-C=300/30 完整行并刷新、重启→total495、唯一3，A不重计。</x:v>
       </x:c>
-      <x:c r="G250" s="9" t="str">
+      <x:c r="G251" s="4" t="str">
         <x:v>total165、唯一2
 已采集 B 不丢，仍165，游标重置到当前 A 的 LF
 total495、唯一3，A不重计</x:v>
       </x:c>
-      <x:c r="H250" s="9" t="str">
+      <x:c r="H251" s="4" t="str">
         <x:v>准备：空库
 变化：Q_IO 先 (2,150,15)，截断后不变，最后 (3,450,45)
 核验：空库→Q_IO 先 (2,150,15)，截断后不变，最后 (3,450,45)；Q_CURSOR按新文件完整字节更新，不越过未闭合行。</x:v>
       </x:c>
-      <x:c r="I250" s="9" t="str">
+      <x:c r="I251" s="4" t="str">
         <x:v>draft</x:v>
       </x:c>
-      <x:c r="J250" s="9" t="str">
+      <x:c r="J251" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K250" s="9" t="str">
+      <x:c r="K251" s="4" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L250" s="9" t="str">
+      <x:c r="L251" s="4" t="str">
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:298</x:v>
       </x:c>
-      <x:c r="M250" s="9" t="str">
+      <x:c r="M251" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N250" s="9" t="str">
+      <x:c r="N251" s="4" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="251" ht="72" customHeight="1">
-      <x:c r="A251" s="4" t="str">
+    <x:row r="252" ht="72" customHeight="1">
+      <x:c r="A252" s="9" t="str">
         <x:v>TM-003</x:v>
       </x:c>
-      <x:c r="B251" s="4" t="str">
+      <x:c r="B252" s="9" t="str">
         <x:v>TC-TM003-WINDOW-01</x:v>
       </x:c>
-      <x:c r="C251" s="4" t="str">
+      <x:c r="C252" s="9" t="str">
         <x:v>首次30天UTC采集窗口</x:v>
       </x:c>
-      <x:c r="D251" s="4" t="str">
+      <x:c r="D252" s="9" t="str">
         <x:v>TASK-TM003-SCAN</x:v>
       </x:c>
-      <x:c r="E251" s="4" t="str">
+      <x:c r="E252" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F251" s="4" t="str">
+      <x:c r="F252" s="9" t="str">
         <x:v>固定程序于运行准备阶段记录 T0 UTC 秒；授权前在本例根写完整 ID-old=T0-31天 900/90、ID-new=T0-29天 100/10；授权后追加 ID-next=T0-1天 50/5、ID-bad=无效 UTC 时间 200/20。</x:v>
       </x:c>
-      <x:c r="G251" s="4" t="str">
+      <x:c r="G252" s="9" t="str">
         <x:v>T0-31天的记录不计，T0-29天的记录计入
 新增 50/5 只计一次
 无效时间不得生成可信事件</x:v>
       </x:c>
-      <x:c r="H251" s="4" t="str">
+      <x:c r="H252" s="9" t="str">
         <x:v>准备：本例全新客户端库；只经真实 UI 授权并扫描原生形状测试文件，不直接写产品库
 变化：先插入 ID-new，再插入 ID-next；ID-old 和 ID-bad 都不入事件表
 核验：初次 Q_SUM=(1,100,10,20)，追加后 Q_IO=(2,150,15)，无效时间后同值；Q_DIAG 有 invalid_time；按响应键只读验证 old/bad 不在库</x:v>
       </x:c>
-      <x:c r="I251" s="4" t="str">
+      <x:c r="I252" s="9" t="str">
         <x:v>draft</x:v>
       </x:c>
-      <x:c r="J251" s="4" t="str">
+      <x:c r="J252" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K251" s="4" t="str">
+      <x:c r="K252" s="9" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L251" s="4" t="str">
+      <x:c r="L252" s="9" t="str">
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:302</x:v>
       </x:c>
-      <x:c r="M251" s="4" t="str">
+      <x:c r="M252" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N251" s="4" t="str">
+      <x:c r="N252" s="9" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="252" ht="117" customHeight="1">
-      <x:c r="A252" s="9" t="str">
+    <x:row r="253" ht="117" customHeight="1">
+      <x:c r="A253" s="4" t="str">
         <x:v>TM-003</x:v>
       </x:c>
-      <x:c r="B252" s="9" t="str">
+      <x:c r="B253" s="4" t="str">
         <x:v>TC-TM003-COVERAGE-OVERFLOW-01</x:v>
       </x:c>
-      <x:c r="C252" s="9" t="str">
+      <x:c r="C253" s="4" t="str">
         <x:v>超预览上限的授权内部分页、撤销与目录变动</x:v>
       </x:c>
-      <x:c r="D252" s="9" t="str">
+      <x:c r="D253" s="4" t="str">
         <x:v>TASK-TM003-SCAN</x:v>
       </x:c>
-      <x:c r="E252" s="9" t="str">
+      <x:c r="E253" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F252" s="9" t="str">
+      <x:c r="F253" s="4" t="str">
         <x:v>本例私有 0700 授权根含1001个可排序的 sessions/YYYY/MM/DD/*.jsonl，前1000个无可信用量，最后一个 A=100/10/cached20；另有未授权根 B=900/90。预览上限1000，内部分页每页最多256。</x:v>
       </x:c>
-      <x:c r="G252" s="9" t="str">
+      <x:c r="G253" s="4" t="str">
         <x:v>预览不是全量扫描完成证明
 暂停状态不得提交完整覆盖
 末端第1001个 A 计一次
 撤销使旧授权能力失效，不跨根读 B
 跨页目录变动废弃全部暂定页，既有已提交 A 保留，不能续扫旧页或仅凭 complete 判正文完整</x:v>
       </x:c>
-      <x:c r="H252" s="9" t="str">
+      <x:c r="H253" s="4" t="str">
         <x:v>准备：本例拥有的全新客户端库、0700 双根和1001个合成 JSONL；通过真实 UI 确认根；不直接写事件表
 变化：预览/暂停零事件，完成后 A 一事件，撤销后保留 A 且覆盖不完整；目录变动废弃新一轮暂存页，已提交 A 不变
 核验：只读 Q_SUM 依次无事件、无事件、(1,100,10,20)、同值；核对 scan_incomplete 依次1、1、0、1及旧能力拒绝；第5步旧 generation 拒绝、暂存游标回滚，Q_SUM 保持(1,100,10,20)，新 generation 从头开始</x:v>
       </x:c>
-      <x:c r="I252" s="9" t="str">
+      <x:c r="I253" s="4" t="str">
         <x:v>draft</x:v>
       </x:c>
-      <x:c r="J252" s="9" t="str">
+      <x:c r="J253" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K252" s="9" t="str">
+      <x:c r="K253" s="4" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L252" s="9" t="str">
+      <x:c r="L253" s="4" t="str">
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:306</x:v>
       </x:c>
-      <x:c r="M252" s="9" t="str">
+      <x:c r="M253" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N252" s="9" t="str">
+      <x:c r="N253" s="4" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="253" ht="72" customHeight="1">
-      <x:c r="A253" s="4" t="str">
+    <x:row r="254" ht="72" customHeight="1">
+      <x:c r="A254" s="9" t="str">
         <x:v>TM-003</x:v>
       </x:c>
-      <x:c r="B253" s="4" t="str">
+      <x:c r="B254" s="9" t="str">
         <x:v>TC-TM003-UI-02</x:v>
       </x:c>
-      <x:c r="C253" s="4" t="str">
+      <x:c r="C254" s="9" t="str">
         <x:v>源清理后的覆盖缺口</x:v>
       </x:c>
-      <x:c r="D253" s="4" t="str">
+      <x:c r="D254" s="9" t="str">
         <x:v>TASK-TM003-UI</x:v>
       </x:c>
-      <x:c r="E253" s="4" t="str">
+      <x:c r="E254" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F253" s="4" t="str">
+      <x:c r="F254" s="9" t="str">
         <x:v>R-BASE、完整 A/B。1. 导入后→UI total165 且覆盖起点为最早可信事件时间。2. 删除仅本例拥有的源文件后刷新/重启→仍165；源缺失与更早历史不可证明的提示可见，不能显示历史0。</x:v>
       </x:c>
-      <x:c r="G253" s="4" t="str">
+      <x:c r="G254" s="9" t="str">
         <x:v>UI total165 且覆盖起点为最早可信事件时间
 仍165；源缺失与更早历史不可证明的提示可见，不能显示历史0</x:v>
       </x:c>
-      <x:c r="H253" s="4" t="str">
+      <x:c r="H254" s="9" t="str">
         <x:v>准备：空库
 变化：保留2事件、Q_IO=(2,150,15)
 核验：空库→保留2事件、Q_IO=(2,150,15)；coverage.missing_before=1 或等价状态；不删事件。</x:v>
       </x:c>
-      <x:c r="I253" s="4" t="str">
+      <x:c r="I254" s="9" t="str">
         <x:v>draft</x:v>
       </x:c>
-      <x:c r="J253" s="4" t="str">
+      <x:c r="J254" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K253" s="4" t="str">
+      <x:c r="K254" s="9" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L253" s="4" t="str">
+      <x:c r="L254" s="9" t="str">
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:310</x:v>
       </x:c>
-      <x:c r="M253" s="4" t="str">
+      <x:c r="M254" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N253" s="4" t="str">
+      <x:c r="N254" s="9" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="254" ht="57" customHeight="1">
-      <x:c r="A254" s="9" t="str">
+    <x:row r="255" ht="57" customHeight="1">
+      <x:c r="A255" s="4" t="str">
         <x:v>TM-003</x:v>
       </x:c>
-      <x:c r="B254" s="9" t="str">
+      <x:c r="B255" s="4" t="str">
         <x:v>TC-TM003-BOUNDARY-01</x:v>
       </x:c>
-      <x:c r="C254" s="9" t="str">
+      <x:c r="C255" s="4" t="str">
         <x:v>未授权根和越界链接拒绝</x:v>
       </x:c>
-      <x:c r="D254" s="9" t="str">
+      <x:c r="D255" s="4" t="str">
         <x:v>TASK-TM003-SCAN</x:v>
       </x:c>
-      <x:c r="E254" s="9" t="str">
+      <x:c r="E255" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F254" s="9" t="str">
+      <x:c r="F255" s="4" t="str">
         <x:v>测试拥有 A/B，B 内有 ID-x=900/90，A 的 sessions/YYYY/MM/DD/ 同层有 symlink escape.jsonl 指向 B。1. 仅通过真实 UI 选 A 并确认→A 的可信事件可读。2. 手动刷新与30秒补扫→B 和越界 symlink 不被读，UI 无 x 用量。</x:v>
       </x:c>
-      <x:c r="G254" s="9" t="str">
+      <x:c r="G255" s="4" t="str">
         <x:v>A 的可信事件可读
 B 与同层越界 symlink 均不被读，UI 无 x 用量，B 的文件摘要不变</x:v>
       </x:c>
-      <x:c r="H254" s="9" t="str">
+      <x:c r="H255" s="4" t="str">
         <x:v>准备：空库
 变化：只出现 A 的 response key
 核验：空库→只出现 A 的 response key；Q_SUM不含990；B 的文件摘要前后不变。</x:v>
       </x:c>
-      <x:c r="I254" s="9" t="str">
+      <x:c r="I255" s="4" t="str">
         <x:v>draft</x:v>
       </x:c>
-      <x:c r="J254" s="9" t="str">
+      <x:c r="J255" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K254" s="9" t="str">
+      <x:c r="K255" s="4" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L254" s="9" t="str">
+      <x:c r="L255" s="4" t="str">
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:314</x:v>
       </x:c>
-      <x:c r="M254" s="9" t="str">
+      <x:c r="M255" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N254" s="9" t="str">
+      <x:c r="N255" s="4" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="255" ht="57" customHeight="1">
-      <x:c r="A255" s="4" t="str">
+    <x:row r="256" ht="57" customHeight="1">
+      <x:c r="A256" s="9" t="str">
         <x:v>TM-003</x:v>
       </x:c>
-      <x:c r="B255" s="4" t="str">
+      <x:c r="B256" s="9" t="str">
         <x:v>TC-TM003-AUTH-01</x:v>
       </x:c>
-      <x:c r="C255" s="4" t="str">
+      <x:c r="C256" s="9" t="str">
         <x:v>确认前与失效时停读</x:v>
       </x:c>
-      <x:c r="D255" s="4" t="str">
+      <x:c r="D256" s="9" t="str">
         <x:v>TASK-TM003-AUTH</x:v>
       </x:c>
-      <x:c r="E255" s="4" t="str">
+      <x:c r="E256" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F255" s="4" t="str">
+      <x:c r="F256" s="9" t="str">
         <x:v>A 含 A=100/10。1. 打开授权预览但不确认→持续扫描不启动、客户端无事件。2. 确认后→110。3. TM-002 fixture 仅使 A 授权失效，再追加 B=200/20 并刷新→卡片显示需重新授权，仍110，A 不被继续读取。</x:v>
       </x:c>
-      <x:c r="G255" s="4" t="str">
+      <x:c r="G256" s="9" t="str">
         <x:v>持续扫描不启动、客户端无事件
 110
 卡片显示需重新授权，仍110，A 不被继续读取</x:v>
       </x:c>
-      <x:c r="H255" s="4" t="str">
+      <x:c r="H256" s="9" t="str">
         <x:v>准备：新库
 变化：确认前0事件
 核验：新库→确认前0事件；确认后 Q_SUM=(1,100,10,20)；失效后不变，游标不前进。</x:v>
       </x:c>
-      <x:c r="I255" s="4" t="str">
+      <x:c r="I256" s="9" t="str">
         <x:v>draft</x:v>
       </x:c>
-      <x:c r="J255" s="4" t="str">
+      <x:c r="J256" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K255" s="4" t="str">
+      <x:c r="K256" s="9" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L255" s="4" t="str">
+      <x:c r="L256" s="9" t="str">
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:318</x:v>
       </x:c>
-      <x:c r="M255" s="4" t="str">
+      <x:c r="M256" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N255" s="4" t="str">
+      <x:c r="N256" s="9" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="256" ht="72" customHeight="1">
-      <x:c r="A256" s="9" t="str">
+    <x:row r="257" ht="72" customHeight="1">
+      <x:c r="A257" s="4" t="str">
         <x:v>TM-003</x:v>
       </x:c>
-      <x:c r="B256" s="9" t="str">
+      <x:c r="B257" s="4" t="str">
         <x:v>TC-TM003-AUTH-02</x:v>
       </x:c>
-      <x:c r="C256" s="9" t="str">
+      <x:c r="C257" s="4" t="str">
         <x:v>重新授权后的去重补扫</x:v>
       </x:c>
-      <x:c r="D256" s="9" t="str">
+      <x:c r="D257" s="4" t="str">
         <x:v>TASK-TM003-AUTH</x:v>
       </x:c>
-      <x:c r="E256" s="9" t="str">
+      <x:c r="E257" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F256" s="9" t="str">
+      <x:c r="F257" s="4" t="str">
         <x:v>A 已通过真实 UI 授权且含 A=100/10、B=200/20。1. 采集后→330、唯一2。2. 失效期间追加 C=300/30 与重放 A→仍330。3. 从真实 UI 重新授权同根并确认→660、唯一3。4. 刷新并重启→仍660。</x:v>
       </x:c>
-      <x:c r="G256" s="9" t="str">
+      <x:c r="G257" s="4" t="str">
         <x:v>330、唯一2
 仍330
 660、唯一3
 仍660</x:v>
       </x:c>
-      <x:c r="H256" s="9" t="str">
+      <x:c r="H257" s="4" t="str">
         <x:v>准备：空库
 变化：Q_SUM依次 (2,300,30,60)、同值、(3,600,60,120)、同值
 核验：空库→Q_SUM依次 (2,300,30,60)、同值、(3,600,60,120)、同值；重复 A 不插入。</x:v>
       </x:c>
-      <x:c r="I256" s="9" t="str">
+      <x:c r="I257" s="4" t="str">
         <x:v>draft</x:v>
       </x:c>
-      <x:c r="J256" s="9" t="str">
+      <x:c r="J257" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K256" s="9" t="str">
+      <x:c r="K257" s="4" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L256" s="9" t="str">
+      <x:c r="L257" s="4" t="str">
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:322</x:v>
       </x:c>
-      <x:c r="M256" s="9" t="str">
+      <x:c r="M257" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N256" s="9" t="str">
+      <x:c r="N257" s="4" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="257" ht="87" customHeight="1">
-      <x:c r="A257" s="4" t="str">
+    <x:row r="258" ht="87" customHeight="1">
+      <x:c r="A258" s="9" t="str">
         <x:v>TM-003</x:v>
       </x:c>
-      <x:c r="B257" s="4" t="str">
+      <x:c r="B258" s="9" t="str">
         <x:v>TC-TM003-ISOLATION-01</x:v>
       </x:c>
-      <x:c r="C257" s="4" t="str">
+      <x:c r="C258" s="9" t="str">
         <x:v>已验证主体切换时来源和采集状态隔离</x:v>
       </x:c>
-      <x:c r="D257" s="4" t="str">
+      <x:c r="D258" s="9" t="str">
         <x:v>TASK-TM003-AUTH</x:v>
       </x:c>
-      <x:c r="E257" s="4" t="str">
+      <x:c r="E258" s="9" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F257" s="4" t="str">
+      <x:c r="F258" s="9" t="str">
         <x:v>两隔离真实服务 O1/O2；O1 成员 U1/U2，O2 成员 U1b（ID与U1相同）；本例根 A 含固定 ID-a=100/10；各主体通过真实 UI 分别确认来源。</x:v>
       </x:c>
-      <x:c r="G257" s="4" t="str">
+      <x:c r="G258" s="9" t="str">
         <x:v>只有 P1 来源能力被使用
 旧主体读取已停止
 相同响应在不同已确认主体各自计一次
 规范化 origin 是主体键的一部分
 恢复旧主体不重计，也不读取其他主体来源</x:v>
       </x:c>
-      <x:c r="H257" s="4" t="str">
+      <x:c r="H258" s="9" t="str">
         <x:v>准备：只经真实服务创建合成 U1/U2/U1b，客户端新库，隔离根 A；不向 usage_event 造数
 变化：P1/P2 各自一条事件与独立游标，P3 无事件或游标；身份切换不删除旧主体记录
 核验：按 HMAC(O1,U1)、HMAC(O1,U2)、HMAC(O2,U1b) 的不可逆主体键分别查询 Q_SUM 和 source_cursor；原路径、账号凭据与原始日志不入库</x:v>
       </x:c>
-      <x:c r="I257" s="4" t="str">
+      <x:c r="I258" s="9" t="str">
         <x:v>draft</x:v>
       </x:c>
-      <x:c r="J257" s="4" t="str">
+      <x:c r="J258" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K257" s="4" t="str">
+      <x:c r="K258" s="9" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L257" s="4" t="str">
+      <x:c r="L258" s="9" t="str">
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:326</x:v>
       </x:c>
-      <x:c r="M257" s="4" t="str">
+      <x:c r="M258" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N257" s="4" t="str">
+      <x:c r="N258" s="9" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="258" ht="117" customHeight="1">
-      <x:c r="A258" s="9" t="str">
+    <x:row r="259" ht="117" customHeight="1">
+      <x:c r="A259" s="4" t="str">
         <x:v>TM-003</x:v>
       </x:c>
-      <x:c r="B258" s="9" t="str">
+      <x:c r="B259" s="4" t="str">
         <x:v>TC-TM003-MIGRATE-01</x:v>
       </x:c>
-      <x:c r="C258" s="9" t="str">
+      <x:c r="C259" s="4" t="str">
         <x:v>客户端库迁移和恢复</x:v>
       </x:c>
-      <x:c r="D258" s="9" t="str">
+      <x:c r="D259" s="4" t="str">
         <x:v>TASK-TM003-MIGRATE</x:v>
       </x:c>
-      <x:c r="E258" s="9" t="str">
+      <x:c r="E259" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F258" s="9" t="str">
+      <x:c r="F259" s="4" t="str">
         <x:v>上一实际稳定版 TM-002 私有 profile，包含合成账号、已确认授权根与原有 schema；该版尚无采集事件，若无稳定版包则 BLOCKED。1. 在本轮隔离根备份并验证可恢复→旧 schema、账号/授权状态有摘要且无 usage_event。2. 经 App 内真实更新到候选→新 schema 建立，账号/授权保留，卡片显示尚无可信历史；向已授权根追加固定 A=100/10 后刷新→唯一1、total110。3. 在另一拥有副本注入迁移中断并重试→中断可检测，恢复旧 profile 后重试可得相同账号/授权与唯一 A，不重复计。</x:v>
       </x:c>
-      <x:c r="G258" s="9" t="str">
+      <x:c r="G259" s="4" t="str">
         <x:v>备份副本可打开且还原原状态
 真实更新与首次采集成功，未制造旧版不存在的历史用量
 中断可检测，恢复与重试后聚合不变</x:v>
       </x:c>
-      <x:c r="H258" s="9" t="str">
+      <x:c r="H259" s="4" t="str">
         <x:v>准备：从上一实际稳定 TM-002 包生成本例私有 profile，备份并验证可恢复；源版无 usage_event
 变化：候选创建目标 schema，首次 A 采集写入唯一一条事件；中断副本恢复后同一事件不重计
 核验：只在隔离副本造旧状态；源库只读核对旧 schema、账号/授权记录与无用量表；更新后 Q_SCHEMA 为目标版本、Q_SUM 先无行、采集 A 后为 (1,100,10,20)，账号/授权记录不变；不接触生产库。</x:v>
       </x:c>
-      <x:c r="I258" s="9" t="str">
+      <x:c r="I259" s="4" t="str">
         <x:v>draft</x:v>
       </x:c>
-      <x:c r="J258" s="9" t="str">
+      <x:c r="J259" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K258" s="9" t="str">
+      <x:c r="K259" s="4" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L258" s="9" t="str">
+      <x:c r="L259" s="4" t="str">
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:330</x:v>
       </x:c>
-      <x:c r="M258" s="9" t="str">
+      <x:c r="M259" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N258" s="9" t="str">
+      <x:c r="N259" s="4" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="259" ht="87" customHeight="1">
-      <x:c r="A259" s="4" t="str">
+    <x:row r="260" ht="87" customHeight="1">
+      <x:c r="A260" s="9" t="str">
         <x:v>TM-003</x:v>
       </x:c>
-      <x:c r="B259" s="4" t="str">
+      <x:c r="B260" s="9" t="str">
         <x:v>TC-TM003-E2E-01</x:v>
       </x:c>
-      <x:c r="C259" s="4" t="str">
+      <x:c r="C260" s="9" t="str">
         <x:v>固定逐项入口和证据审计</x:v>
       </x:c>
-      <x:c r="D259" s="4" t="str">
+      <x:c r="D260" s="9" t="str">
         <x:v>TASK-TM003-E2E</x:v>
       </x:c>
-      <x:c r="E259" s="4" t="str">
+      <x:c r="E260" s="9" t="str">
         <x:v>governance</x:v>
       </x:c>
-      <x:c r="F259" s="4" t="str">
+      <x:c r="F260" s="9" t="str">
         <x:v>1. 固定单例入口指定一条 TM-003 TC→新 run_id、逐步原件和 SQL/源摘要。2. 对 TM-001 已交付集合加 TM-003 全部目标 TC/四组补充运行→每例/变体/组有原件，零缺例/跳过/重试。3. 移除副本报告一步→审计 BLOCKED。4. 在副本移除一条 TM-003 TC 或将变体 release 改成 TM-001→跨版本门禁拒绝，不签通行证。</x:v>
       </x:c>
-      <x:c r="G259" s="4" t="str">
+      <x:c r="G260" s="9" t="str">
         <x:v>新 run_id，逐步原件和 SQL/源摘要齐全
 逐 TC/变体与场景组均有独立原件、零缺例/跳过/重试；门禁集合不再固定只含 TM-001
 审计判 BLOCKED
 跨版本门禁拒绝该副本，不生成通行证</x:v>
       </x:c>
-      <x:c r="H259" s="4" t="str">
+      <x:c r="H260" s="9" t="str">
         <x:v>准备：使用测试拥有的独立库，审计只读原件
 变化：不适用；见本用例具体数据库观察面。
 核验：使用测试拥有的独立库，审计只读原件；不生成假 PASS。</x:v>
       </x:c>
-      <x:c r="I259" s="4" t="str">
+      <x:c r="I260" s="9" t="str">
         <x:v>draft</x:v>
       </x:c>
-      <x:c r="J259" s="4" t="str">
+      <x:c r="J260" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K259" s="4" t="str">
+      <x:c r="K260" s="9" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L259" s="4" t="str">
+      <x:c r="L260" s="9" t="str">
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:334</x:v>
       </x:c>
-      <x:c r="M259" s="4" t="str">
+      <x:c r="M260" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N259" s="4" t="str">
+      <x:c r="N260" s="9" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="260" ht="72" customHeight="1">
-      <x:c r="A260" s="9" t="str">
+    <x:row r="261" ht="72" customHeight="1">
+      <x:c r="A261" s="4" t="str">
         <x:v>TM-003</x:v>
       </x:c>
-      <x:c r="B260" s="9" t="str">
+      <x:c r="B261" s="4" t="str">
         <x:v>TC-TM003-E2E-02</x:v>
       </x:c>
-      <x:c r="C260" s="9" t="str">
+      <x:c r="C261" s="4" t="str">
         <x:v>最终DMG真实链路和清理</x:v>
       </x:c>
-      <x:c r="D260" s="9" t="str">
+      <x:c r="D261" s="4" t="str">
         <x:v>TASK-TM003-E2E</x:v>
       </x:c>
-      <x:c r="E260" s="9" t="str">
+      <x:c r="E261" s="4" t="str">
         <x:v>产品E2E</x:v>
       </x:c>
-      <x:c r="F260" s="9" t="str">
+      <x:c r="F261" s="4" t="str">
         <x:v>1. 从最终候选 DMG 复制并安装 App→记录原件/安装路径与哈希。2. 用 Playwright executablePath 启动→真实 UI/IPC/采集/服务/SQLite 全链且 TM-001/002/003 应测集合精确相等。3. 退出并按 owner 清理→无遗留进程/端口/私有目录。</x:v>
       </x:c>
-      <x:c r="G260" s="9" t="str">
+      <x:c r="G261" s="4" t="str">
         <x:v>记录原件/安装路径与哈希
 真实 UI/IPC/采集/服务/SQLite 全链且 TM-001/002/003 应测集合精确相等
 无遗留进程/端口/私有目录</x:v>
       </x:c>
-      <x:c r="H260" s="9" t="str">
+      <x:c r="H261" s="4" t="str">
         <x:v>准备：每例隔离客户端/服务库
 变化：不适用；见本用例具体数据库观察面。
 核验：每例隔离客户端/服务库；最终 DB 与逐 TC 预期相符；包、源码、测试摘要一致。</x:v>
       </x:c>
-      <x:c r="I260" s="9" t="str">
+      <x:c r="I261" s="4" t="str">
         <x:v>draft</x:v>
       </x:c>
-      <x:c r="J260" s="9" t="str">
+      <x:c r="J261" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K260" s="9" t="str">
+      <x:c r="K261" s="4" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L260" s="9" t="str">
+      <x:c r="L261" s="4" t="str">
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:338</x:v>
       </x:c>
-      <x:c r="M260" s="9" t="str">
+      <x:c r="M261" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N260" s="9" t="str">
+      <x:c r="N261" s="4" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="261" ht="57" customHeight="1">
-      <x:c r="A261" s="4" t="str">
+    <x:row r="262" ht="57" customHeight="1">
+      <x:c r="A262" s="9" t="str">
         <x:v>TM-003</x:v>
       </x:c>
-      <x:c r="B261" s="4" t="str">
+      <x:c r="B262" s="9" t="str">
         <x:v>TC-TM003-GOV-01</x:v>
       </x:c>
-      <x:c r="C261" s="4" t="str">
+      <x:c r="C262" s="9" t="str">
         <x:v>追踪总表与门禁拒绝</x:v>
       </x:c>
-      <x:c r="D261" s="4" t="str">
+      <x:c r="D262" s="9" t="str">
         <x:v>TASK-TM003-RELEASE</x:v>
       </x:c>
-      <x:c r="E261" s="4" t="str">
+      <x:c r="E262" s="9" t="str">
         <x:v>governance</x:v>
       </x:c>
-      <x:c r="F261" s="4" t="str">
+      <x:c r="F262" s="9" t="str">
         <x:v>1. 核对 manifest/需求→TASK→TC/AC、数据能力、Changelog、总表→零孤立或空预期。2. 运行 structure/baseline/quality 与总表回读→全部真实返回0才记录文档基线。3. 用候选原始报告门禁→任一 FAIL/BLOCKED 拒绝通行证。</x:v>
       </x:c>
-      <x:c r="G261" s="4" t="str">
+      <x:c r="G262" s="9" t="str">
         <x:v>TASK→TC/AC、数据能力、Changelog、总表→零孤立或空预期
 全部真实返回0才记录文档基线
 任一 FAIL/BLOCKED 拒绝通行证</x:v>
       </x:c>
-      <x:c r="H261" s="4" t="str">
+      <x:c r="H262" s="9" t="str">
         <x:v>准备：对数据库不适用
 变化：不适用；见本用例具体数据库观察面。
 核验：对数据库不适用；使用机器清单、结果 Excel 与原件摘要，不代写产品库。</x:v>
       </x:c>
-      <x:c r="I261" s="4" t="str">
+      <x:c r="I262" s="9" t="str">
         <x:v>draft</x:v>
       </x:c>
-      <x:c r="J261" s="4" t="str">
+      <x:c r="J262" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K261" s="4" t="str">
+      <x:c r="K262" s="9" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L261" s="4" t="str">
+      <x:c r="L262" s="9" t="str">
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:342</x:v>
       </x:c>
-      <x:c r="M261" s="4" t="str">
+      <x:c r="M262" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N261" s="4" t="str">
+      <x:c r="N262" s="9" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="262" ht="72" customHeight="1">
-      <x:c r="A262" s="9" t="str">
+    <x:row r="263" ht="72" customHeight="1">
+      <x:c r="A263" s="4" t="str">
         <x:v>TM-003</x:v>
       </x:c>
-      <x:c r="B262" s="9" t="str">
+      <x:c r="B263" s="4" t="str">
         <x:v>TC-TM003-CORE-01</x:v>
       </x:c>
-      <x:c r="C262" s="9" t="str">
+      <x:c r="C263" s="4" t="str">
         <x:v>完整LF增量与累计快照解析</x:v>
       </x:c>
-      <x:c r="D262" s="9" t="str">
+      <x:c r="D263" s="4" t="str">
         <x:v>TASK-TM003-PARSE</x:v>
       </x:c>
-      <x:c r="E262" s="9" t="str">
+      <x:c r="E263" s="4" t="str">
         <x:v>模块检查</x:v>
       </x:c>
-      <x:c r="F262" s="9" t="str">
+      <x:c r="F263" s="4" t="str">
         <x:v>原生形状完整A=100/10/cached20；B=200/20/cached40半行后补LF；C=300/30/cached60完整行及累计快照；固定种子和T0。</x:v>
       </x:c>
-      <x:c r="G262" s="9" t="str">
+      <x:c r="G263" s="4" t="str">
         <x:v>仅A一事件，input100/output10/total110/cached20，完成偏移恰在A的LF后
 仍仅A，完成偏移不跨半行
 仅A/B/C三事件，input600/output60/total660/cached120；累计快照和复扫不增量；完成偏移在累计快照行的LF后</x:v>
       </x:c>
-      <x:c r="H262" s="9" t="str">
+      <x:c r="H263" s="4" t="str">
         <x:v>准备：无产品DB写入；每例新私有根
 变化：不适用；纯解析返回事件与完成字节偏移
 核验：按源文件字节摘要、长度、完整LF边界和解析事件字段逐步比对；仅清理本例owner根</x:v>
       </x:c>
-      <x:c r="I262" s="9" t="str">
+      <x:c r="I263" s="4" t="str">
         <x:v>draft</x:v>
       </x:c>
-      <x:c r="J262" s="9" t="str">
+      <x:c r="J263" s="4" t="str">
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="K262" s="9" t="str">
+      <x:c r="K263" s="4" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L262" s="9" t="str">
+      <x:c r="L263" s="4" t="str">
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:346</x:v>
       </x:c>
-      <x:c r="M262" s="9" t="str">
+      <x:c r="M263" s="4" t="str">
         <x:v>tm003-core-20261001T165439Z (source_check；产品E2E未运行)</x:v>
       </x:c>
-      <x:c r="N262" s="9" t="str">
+      <x:c r="N263" s="4" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="263" ht="72" customHeight="1">
-      <x:c r="A263" s="4" t="str">
+    <x:row r="264" ht="72" customHeight="1">
+      <x:c r="A264" s="9" t="str">
         <x:v>TM-003</x:v>
       </x:c>
-      <x:c r="B263" s="4" t="str">
+      <x:c r="B264" s="9" t="str">
         <x:v>TC-TM003-CORE-02</x:v>
       </x:c>
-      <x:c r="C263" s="4" t="str">
+      <x:c r="C264" s="9" t="str">
         <x:v>累计空值及非法用量诊断</x:v>
       </x:c>
-      <x:c r="D263" s="4" t="str">
+      <x:c r="D264" s="9" t="str">
         <x:v>TASK-TM003-SOURCE
 TASK-TM003-PARSE</x:v>
       </x:c>
-      <x:c r="E263" s="4" t="str">
+      <x:c r="E264" s="9" t="str">
         <x:v>模块检查</x:v>
       </x:c>
-      <x:c r="F263" s="4" t="str">
+      <x:c r="F264" s="9" t="str">
         <x:v>无ID累计100/10和rate-limit info=null；合法A；缺usage、负input、cached111&gt;input100、total111四条不同ID完整LF行；未知build。</x:v>
       </x:c>
-      <x:c r="G263" s="4" t="str">
+      <x:c r="G264" s="9" t="str">
         <x:v>零可信事件；分别诊断unverified_cumulative、missing_usage，不生成零值事件
 只有A=110一事件；四条负例依次诊断missing_usage、negative_input、invalid_cached、invalid_total；不覆写A
 零新增事件，诊断unsupported_source_version</x:v>
       </x:c>
-      <x:c r="H263" s="4" t="str">
+      <x:c r="H264" s="9" t="str">
         <x:v>准备：无产品DB写入；每例新私有根
 变化：不适用；仅模块事件/诊断返回值
 核验：独立枚举返回的事件数量、数值、诊断代码和数量；仅清理本例owner根</x:v>
       </x:c>
-      <x:c r="I263" s="4" t="str">
+      <x:c r="I264" s="9" t="str">
         <x:v>draft</x:v>
       </x:c>
-      <x:c r="J263" s="4" t="str">
+      <x:c r="J264" s="9" t="str">
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="K263" s="4" t="str">
+      <x:c r="K264" s="9" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L263" s="4" t="str">
+      <x:c r="L264" s="9" t="str">
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:350</x:v>
       </x:c>
-      <x:c r="M263" s="4" t="str">
+      <x:c r="M264" s="9" t="str">
         <x:v>tm003-core-20261001T165439Z (source_check；产品E2E未运行)</x:v>
       </x:c>
-      <x:c r="N263" s="4" t="str">
+      <x:c r="N264" s="9" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="264" ht="72" customHeight="1">
-      <x:c r="A264" s="9" t="str">
+    <x:row r="265" ht="72" customHeight="1">
+      <x:c r="A265" s="4" t="str">
         <x:v>TM-003</x:v>
       </x:c>
-      <x:c r="B264" s="9" t="str">
+      <x:c r="B265" s="4" t="str">
         <x:v>TC-TM003-CORE-03</x:v>
       </x:c>
-      <x:c r="C264" s="9" t="str">
+      <x:c r="C265" s="4" t="str">
         <x:v>公开向量身份去重与冲突</x:v>
       </x:c>
-      <x:c r="D264" s="9" t="str">
+      <x:c r="D265" s="4" t="str">
         <x:v>TASK-TM003-IDENTITY</x:v>
       </x:c>
-      <x:c r="E264" s="9" t="str">
+      <x:c r="E265" s="4" t="str">
         <x:v>模块检查</x:v>
       </x:c>
-      <x:c r="F264" s="9" t="str">
+      <x:c r="F265" s="4" t="str">
         <x:v>公开identity-v1测试key；codex/provider-response/shared-call-01的A=100/10/cached20；同ID重放；shared-call-02同usage；shared-call-01冲突999/99；claude_code/provider-message/shared-call-01仅求键。</x:v>
       </x:c>
-      <x:c r="G264" s="9" t="str">
+      <x:c r="G265" s="4" t="str">
         <x:v>一事件total110；键精确为afd67bd0cad0227b3e7b5ac132bb9b3ed492073983b9c16a0c9cc24dd3008051
 重放仍一事件；新ID后两事件，input200/output20/cached40/total220
 首事件不变，诊断identity_conflict；Claude键精确为bf222a85ab2209f72ff82c21b7172c9315448b3e1d5bf4503a3c76b30c46cad1且不向本例产品库添加Claude事件</x:v>
       </x:c>
-      <x:c r="H264" s="9" t="str">
+      <x:c r="H265" s="4" t="str">
         <x:v>准备：创建本例拥有的空临时SQLite；不访问产品profile/Keychain
 变化：仅通过正式模块API插入两条Codex事件与一条冲突诊断
 核验：只读核对来源域唯一约束、两行总量、首行未覆写和诊断；只清理本例owner DB</x:v>
       </x:c>
-      <x:c r="I264" s="9" t="str">
+      <x:c r="I265" s="4" t="str">
         <x:v>draft</x:v>
       </x:c>
-      <x:c r="J264" s="9" t="str">
+      <x:c r="J265" s="4" t="str">
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="K264" s="9" t="str">
+      <x:c r="K265" s="4" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L264" s="9" t="str">
+      <x:c r="L265" s="4" t="str">
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:354</x:v>
       </x:c>
-      <x:c r="M264" s="9" t="str">
+      <x:c r="M265" s="4" t="str">
         <x:v>tm003-core-20261001T165439Z (source_check；产品E2E未运行)</x:v>
       </x:c>
-      <x:c r="N264" s="9" t="str">
+      <x:c r="N265" s="4" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="265" ht="117" customHeight="1">
-      <x:c r="A265" s="4" t="str">
+    <x:row r="266" ht="117" customHeight="1">
+      <x:c r="A266" s="9" t="str">
         <x:v>TM-003</x:v>
       </x:c>
-      <x:c r="B265" s="4" t="str">
+      <x:c r="B266" s="9" t="str">
         <x:v>TC-TM003-CORE-04</x:v>
       </x:c>
-      <x:c r="C265" s="4" t="str">
+      <x:c r="C266" s="9" t="str">
         <x:v>同步批次原子提交与密钥标记</x:v>
       </x:c>
-      <x:c r="D265" s="4" t="str">
+      <x:c r="D266" s="9" t="str">
         <x:v>TASK-TM003-STORE</x:v>
       </x:c>
-      <x:c r="E265" s="4" t="str">
+      <x:c r="E266" s="9" t="str">
         <x:v>模块检查</x:v>
       </x:c>
-      <x:c r="F265" s="4" t="str">
+      <x:c r="F266" s="9" t="str">
         <x:v>header+A=410字节、补B=750字节；A100/10/cached20、B200/20/cached40；公开key1=00..1f及不同有效key2=20..3f；owner SQLite上的INSERT和UPDATE失败触发器</x:v>
       </x:c>
-      <x:c r="G265" s="4" t="str">
+      <x:c r="G266" s="9" t="str">
         <x:v>一行A，(count,input,output,cached)=(1,100,10,20)，total110，诊断0，cursor410，key1标记，scan_incomplete=1；重开不变
 批次失败且全回滚；仍仅A/total110/诊断0/cursor410/原MAC/key1标记/scan_incomplete=1；重开仍相同
 B仅新增一次；(2,300,30,60)、total330、invalid_record诊断1、cursor750及新MAC、scan_incomplete=0；重开不重计
 明确密钥标记不匹配并停采集；A/B两行/total330/诊断1/cursor750/覆盖/key1标记均不变，无key2重键或已知零</x:v>
       </x:c>
-      <x:c r="H265" s="4" t="str">
+      <x:c r="H266" s="9" t="str">
         <x:v>准备：新建本例owner SQLite；业务行只由模块API插入；步骤2在本例库创建两条失败触发器
 变化：步骤1 A+cursor/coverage/key标记原子提交；步骤2全回滚；步骤3 B+一诊断+cursor/coverage原子提交；步骤4不变
 核验：每步只读usage_event数量与SUM、collection_diagnostic代码数、source_cursor offset/prefix_mac、coverage.scan_incomplete、identity_key_state.key_marker；关闭重开复查；仅清理owner库</x:v>
       </x:c>
-      <x:c r="I265" s="4" t="str">
+      <x:c r="I266" s="9" t="str">
         <x:v>draft</x:v>
       </x:c>
-      <x:c r="J265" s="4" t="str">
+      <x:c r="J266" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K265" s="4" t="str">
+      <x:c r="K266" s="9" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L265" s="4" t="str">
+      <x:c r="L266" s="9" t="str">
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:203</x:v>
       </x:c>
-      <x:c r="M265" s="4" t="str">
+      <x:c r="M266" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N265" s="4" t="str">
+      <x:c r="N266" s="9" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="266" ht="117" customHeight="1">
-      <x:c r="A266" s="9" t="str">
+    <x:row r="267" ht="117" customHeight="1">
+      <x:c r="A267" s="4" t="str">
         <x:v>TM-003</x:v>
       </x:c>
-      <x:c r="B266" s="9" t="str">
+      <x:c r="B267" s="4" t="str">
         <x:v>TC-TM003-CORE-05</x:v>
       </x:c>
-      <x:c r="C266" s="9" t="str">
+      <x:c r="C267" s="4" t="str">
         <x:v>追加、半行、前缀改写与截短游标</x:v>
       </x:c>
-      <x:c r="D266" s="9" t="str">
+      <x:c r="D267" s="4" t="str">
         <x:v>TASK-TM003-SCAN
 TASK-TM003-STORE</x:v>
       </x:c>
-      <x:c r="E266" s="9" t="str">
+      <x:c r="E267" s="4" t="str">
         <x:v>模块检查</x:v>
       </x:c>
-      <x:c r="F266" s="9" t="str">
+      <x:c r="F267" s="4" t="str">
         <x:v>fixture header+A410、+B750、+C1090；B半行；A.padding 0→1同长度原地改写且mtime不变；合成稳定文件身份恒定，可变快照digest随修改；公开key1</x:v>
       </x:c>
-      <x:c r="G266" s="9" t="str">
+      <x:c r="G267" s="4" t="str">
         <x:v>A一行total110，cursor410，保存对410字节prefixMAC及稳定身份，输出不含路径/正文/密钥
 B不提交；A一行total110，cursor410，前缀MAC相同，无cursor_reset
 只消费B/C；(count,input,output,cached)=(3,600,60,120)，total660，cursor1090，A不重计，无cursor_reset
 fixture新旧SHA不同；prefixMAC不符，cursor_reset且从0重扫；A/B/C唯一三行、total660、旧行不删，coverage.missing_before=1
 长度小于游标而从0重扫；历史A/B/C三行与total660保留；cursor410，coverage缺口为真，B/C不填零不删除</x:v>
       </x:c>
-      <x:c r="H266" s="9" t="str">
+      <x:c r="H267" s="4" t="str">
         <x:v>准备：新建owner文件/空SQLite；模块读取固定原始行；不访问TM-002目录能力
 变化：A/B/C仅通过正式模块API入库；追加推进完整LF游标；改写/截短重扫仅改变游标和覆盖缺口、不删可信旧行
 核验：只读按(principal_key,source,source_event_key)核对唯一三行及SUM、source_cursor offset/prefix_mac、coverage.missing_before、cursor_reset诊断；比较fixture新旧SHA/长度/mtime；结束仅清理owner资源</x:v>
       </x:c>
-      <x:c r="I266" s="9" t="str">
+      <x:c r="I267" s="4" t="str">
         <x:v>draft</x:v>
       </x:c>
-      <x:c r="J266" s="9" t="str">
+      <x:c r="J267" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K266" s="9" t="str">
+      <x:c r="K267" s="4" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L266" s="9" t="str">
+      <x:c r="L267" s="4" t="str">
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:216</x:v>
       </x:c>
-      <x:c r="M266" s="9" t="str">
+      <x:c r="M267" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N266" s="9" t="str">
+      <x:c r="N267" s="4" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="267" ht="87" customHeight="1">
-      <x:c r="A267" s="4" t="str">
+    <x:row r="268" ht="87" customHeight="1">
+      <x:c r="A268" s="9" t="str">
         <x:v>TM-005</x:v>
       </x:c>
-      <x:c r="B267" s="4" t="str">
+      <x:c r="B268" s="9" t="str">
         <x:v>TC-TM005-CORE-01</x:v>
       </x:c>
-      <x:c r="C267" s="4" t="str">
+      <x:c r="C268" s="9" t="str">
         <x:v>双来源可信事件与半开日汇总</x:v>
       </x:c>
-      <x:c r="D267" s="4" t="str">
+      <x:c r="D268" s="9" t="str">
         <x:v>TASK-TM005-EVENT-CONTRACT
 TASK-TM005-RANGE-QUERY</x:v>
       </x:c>
-      <x:c r="E267" s="4" t="str">
+      <x:c r="E268" s="9" t="str">
         <x:v>模块检查</x:v>
       </x:c>
-      <x:c r="F267" s="4" t="str">
+      <x:c r="F268" s="9" t="str">
         <x:v>fixture的A/B、跨主体C、界外D/E；synthetic-p1、Asia/Shanghai当地日2026-09-29</x:v>
       </x:c>
-      <x:c r="G267" s="4" t="str">
+      <x:c r="G268" s="9" t="str">
         <x:v>1. 按固定主体和fixture固定UTC半开界查询纯统计函数，不做IANA日期换算；仅A/B被选、C/D/E排除；输入数组和键不变
 2. 核对来源、模型、Token和三个子项；input300/output30/total330；Codex110/Claude220；未知模型110/sonnet-test220；缓存读20但部分未知、缓存写未知、推理2但部分未知，子项不加总
 3. 逐个输入非法来源、负数、超范围缓存和坏UTC；各自被拒绝，无完整零或有效汇总输出；原fixture不变</x:v>
-      </x:c>
-      <x:c r="H267" s="4" t="str">
-        <x:v>准备：无产品DB写入；每例从新内存输入开始
-变化：不适用；纯统计返回值与输入未变
-核验：固定fixture摘要、事件筛选、各字段与状态逐步核对；无SQL</x:v>
-      </x:c>
-      <x:c r="I267" s="4" t="str">
-        <x:v>draft</x:v>
-      </x:c>
-      <x:c r="J267" s="4" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="K267" s="4" t="str">
-        <x:v>细化用例</x:v>
-      </x:c>
-      <x:c r="L267" s="4" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:326</x:v>
-      </x:c>
-      <x:c r="M267" s="4" t="str">
-        <x:v>尚未执行</x:v>
-      </x:c>
-      <x:c r="N267" s="4" t="str">
-        <x:v>v0.5.0-20261001T034729Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="268" ht="57" customHeight="1">
-      <x:c r="A268" s="9" t="str">
-        <x:v>TM-005</x:v>
-      </x:c>
-      <x:c r="B268" s="9" t="str">
-        <x:v>TC-TM005-CORE-02</x:v>
-      </x:c>
-      <x:c r="C268" s="9" t="str">
-        <x:v>未知用量诊断不补零</x:v>
-      </x:c>
-      <x:c r="D268" s="9" t="str">
-        <x:v>TASK-TM005-EVENT-CONTRACT
-TASK-TM005-COVERAGE</x:v>
-      </x:c>
-      <x:c r="E268" s="9" t="str">
-        <x:v>模块检查</x:v>
-      </x:c>
-      <x:c r="F268" s="9" t="str">
-        <x:v>fixture A/B及同范围Claude missing_usage诊断；双来源complete仅为模块合成覆盖假设</x:v>
-      </x:c>
-      <x:c r="G268" s="9" t="str">
-        <x:v>1. 先仅统计A/B；已知330，未知模型110保留，来源Codex110/Claude220
-2. 加入诊断重新统计；partial、known_tokens330、total_tokens=null；诊断不增调用或零Token
-3. 移除A/B仅保留诊断；unknown、known_tokens0、total_tokens=null，不能写已确认零</x:v>
       </x:c>
       <x:c r="H268" s="9" t="str">
         <x:v>准备：无产品DB写入；每例从新内存输入开始
@@ -20135,7 +20132,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L268" s="9" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:334</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:326</x:v>
       </x:c>
       <x:c r="M268" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -20144,29 +20141,30 @@
         <x:v>v0.5.0-20261001T034729Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="269" ht="87" customHeight="1">
+    <x:row r="269" ht="57" customHeight="1">
       <x:c r="A269" s="4" t="str">
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B269" s="4" t="str">
-        <x:v>TC-TM005-CORE-03</x:v>
+        <x:v>TC-TM005-CORE-02</x:v>
       </x:c>
       <x:c r="C269" s="4" t="str">
-        <x:v>声明式覆盖状态代数</x:v>
+        <x:v>未知用量诊断不补零</x:v>
       </x:c>
       <x:c r="D269" s="4" t="str">
-        <x:v>TASK-TM005-COVERAGE</x:v>
+        <x:v>TASK-TM005-EVENT-CONTRACT
+TASK-TM005-COVERAGE</x:v>
       </x:c>
       <x:c r="E269" s="4" t="str">
         <x:v>模块检查</x:v>
       </x:c>
       <x:c r="F269" s="4" t="str">
-        <x:v>fixture五行coverage_algebra；complete仅为模块合成输入，product_coverage_proven=false</x:v>
+        <x:v>fixture A/B及同范围Claude missing_usage诊断；双来源complete仅为模块合成覆盖假设</x:v>
       </x:c>
       <x:c r="G269" s="4" t="str">
-        <x:v>1. 两来源complete且无事件、随后移除覆盖事实；前者complete/known0/total0；后者不得自行推断complete
-2. 一来源missing，分别给空事件与可信110；空事件missing/known0/total null；可信110为partial/known110/total null
-3. 两来源complete，分别给可信110+未知诊断、仅未知诊断；前者partial/known110/total null；后者unknown/known0/total null</x:v>
+        <x:v>1. 先仅统计A/B；已知330，未知模型110保留，来源Codex110/Claude220
+2. 加入诊断重新统计；partial、known_tokens330、total_tokens=null；诊断不增调用或零Token
+3. 移除A/B仅保留诊断；unknown、known_tokens0、total_tokens=null，不能写已确认零</x:v>
       </x:c>
       <x:c r="H269" s="4" t="str">
         <x:v>准备：无产品DB写入；每例从新内存输入开始
@@ -20183,7 +20181,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L269" s="4" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:342</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:334</x:v>
       </x:c>
       <x:c r="M269" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -20192,77 +20190,77 @@
         <x:v>v0.5.0-20261001T034729Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="270" ht="72" customHeight="1">
+    <x:row r="270" ht="87" customHeight="1">
       <x:c r="A270" s="9" t="str">
-        <x:v>TM-004</x:v>
+        <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B270" s="9" t="str">
-        <x:v>TC-TM004-CORE-01</x:v>
+        <x:v>TC-TM005-CORE-03</x:v>
       </x:c>
       <x:c r="C270" s="9" t="str">
-        <x:v>完整LF、半行与限额续读</x:v>
+        <x:v>声明式覆盖状态代数</x:v>
       </x:c>
       <x:c r="D270" s="9" t="str">
-        <x:v>TASK-TM004-INCREMENTAL</x:v>
+        <x:v>TASK-TM005-COVERAGE</x:v>
       </x:c>
       <x:c r="E270" s="9" t="str">
         <x:v>模块检查</x:v>
       </x:c>
       <x:c r="F270" s="9" t="str">
+        <x:v>fixture五行coverage_algebra；complete仅为模块合成输入，product_coverage_proven=false</x:v>
+      </x:c>
+      <x:c r="G270" s="9" t="str">
+        <x:v>1. 两来源complete且无事件、随后移除覆盖事实；前者complete/known0/total0；后者不得自行推断complete
+2. 一来源missing，分别给空事件与可信110；空事件missing/known0/total null；可信110为partial/known110/total null
+3. 两来源complete，分别给可信110+未知诊断、仅未知诊断；前者partial/known110/total null；后者unknown/known0/total null</x:v>
+      </x:c>
+      <x:c r="H270" s="9" t="str">
+        <x:v>准备：无产品DB写入；每例从新内存输入开始
+变化：不适用；纯统计返回值与输入未变
+核验：固定fixture摘要、事件筛选、各字段与状态逐步核对；无SQL</x:v>
+      </x:c>
+      <x:c r="I270" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J270" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K270" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L270" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:342</x:v>
+      </x:c>
+      <x:c r="M270" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N270" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="271" ht="72" customHeight="1">
+      <x:c r="A271" s="4" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="B271" s="4" t="str">
+        <x:v>TC-TM004-CORE-01</x:v>
+      </x:c>
+      <x:c r="C271" s="4" t="str">
+        <x:v>完整LF、半行与限额续读</x:v>
+      </x:c>
+      <x:c r="D271" s="4" t="str">
+        <x:v>TASK-TM004-INCREMENTAL</x:v>
+      </x:c>
+      <x:c r="E271" s="4" t="str">
+        <x:v>模块检查</x:v>
+      </x:c>
+      <x:c r="F271" s="4" t="str">
         <x:v>固定746字节13/7 assistant行、前半字节、两条不同ID完整行、首读上限754字节</x:v>
       </x:c>
-      <x:c r="G270" s="9" t="str">
+      <x:c r="G271" s="4" t="str">
         <x:v>1. 读未写完的前半行；调用0、偏移0、scanIncomplete=true，不作可信零结论
 2. 补齐LF、重复读取；补齐后一次13/7=20、偏移746、前缀MAC匹配；重复读取0调用且游标不变
 3. 两完整行首读754字节后续读；首读只第一条、偏移746、read_limit且未完成；续读只第二条、偏移为总字节长、完成</x:v>
-      </x:c>
-      <x:c r="H270" s="9" t="str">
-        <x:v>准备：无产品DB；每例新建自有临时文件
-变化：不适用；只返回模块调用、诊断与游标
-核验：固定fixture/行摘要和逐步返回值、前缀MAC及失败时无新游标；无SQL</x:v>
-      </x:c>
-      <x:c r="I270" s="9" t="str">
-        <x:v>draft</x:v>
-      </x:c>
-      <x:c r="J270" s="9" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="K270" s="9" t="str">
-        <x:v>细化用例</x:v>
-      </x:c>
-      <x:c r="L270" s="9" t="str">
-        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:170</x:v>
-      </x:c>
-      <x:c r="M270" s="9" t="str">
-        <x:v>尚未执行</x:v>
-      </x:c>
-      <x:c r="N270" s="9" t="str">
-        <x:v>v0.4.0-20261001T040433Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="271" ht="72" customHeight="1">
-      <x:c r="A271" s="4" t="str">
-        <x:v>TM-004</x:v>
-      </x:c>
-      <x:c r="B271" s="4" t="str">
-        <x:v>TC-TM004-CORE-02</x:v>
-      </x:c>
-      <x:c r="C271" s="4" t="str">
-        <x:v>前缀MAC、变更和密钥失败</x:v>
-      </x:c>
-      <x:c r="D271" s="4" t="str">
-        <x:v>TASK-TM004-INCREMENTAL</x:v>
-      </x:c>
-      <x:c r="E271" s="4" t="str">
-        <x:v>模块检查</x:v>
-      </x:c>
-      <x:c r="F271" s="4" t="str">
-        <x:v>已提交首行，追加不同ID第二行、同长度ID改写并复原mtime、截短、身份改变、秘密缺失或错误</x:v>
-      </x:c>
-      <x:c r="G271" s="4" t="str">
-        <x:v>1. 首行后追加第二完整行；快照digest变化但稳定身份/前缀MAC相同，续读只第二调用，无cursor_reset
-2. 同长度前缀改写、截短及稳定身份变更；分别报cursor_reset并从0重扫；同inode/size/mtime也不能忽略MAC不符
-3. 秘密无效或读中源变化；拒绝且没有可提交新游标/可信调用/成功零；输出不含路径正文秘密</x:v>
       </x:c>
       <x:c r="H271" s="4" t="str">
         <x:v>准备：无产品DB；每例新建自有临时文件
@@ -20279,7 +20277,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L271" s="4" t="str">
-        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:178</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:170</x:v>
       </x:c>
       <x:c r="M271" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -20288,30 +20286,29 @@
         <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="272" ht="57" customHeight="1">
+    <x:row r="272" ht="72" customHeight="1">
       <x:c r="A272" s="9" t="str">
         <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B272" s="9" t="str">
-        <x:v>TC-TM004-CORE-03</x:v>
+        <x:v>TC-TM004-CORE-02</x:v>
       </x:c>
       <x:c r="C272" s="9" t="str">
-        <x:v>损坏完整行与未知结构</x:v>
+        <x:v>前缀MAC、变更和密钥失败</x:v>
       </x:c>
       <x:c r="D272" s="9" t="str">
-        <x:v>TASK-TM004-PARSER
-TASK-TM004-INCREMENTAL</x:v>
+        <x:v>TASK-TM004-INCREMENTAL</x:v>
       </x:c>
       <x:c r="E272" s="9" t="str">
         <x:v>模块检查</x:v>
       </x:c>
       <x:c r="F272" s="9" t="str">
-        <x:v>固定13/7行前置非法UTF8完整行和版本2.1.127完整行，尾部再追加无LF坏字节</x:v>
+        <x:v>已提交首行，追加不同ID第二行、同长度ID改写并复原mtime、截短、身份改变、秘密缺失或错误</x:v>
       </x:c>
       <x:c r="G272" s="9" t="str">
-        <x:v>1. 读三条完整LF行；仅合法2.1.126一条调用13/7=20；invalid_utf8及unsupported_version各一次
-2. 核对游标、重复读取及隐私；游标到三行LF末，MAC匹配且完成；重复读取0；输出无路径、正文、秘密
-3. 追加无LF坏字节再补LF；未补LF前偏移不动且未完成；补LF后仅诊断推进，无伪调用</x:v>
+        <x:v>1. 首行后追加第二完整行；快照digest变化但稳定身份/前缀MAC相同，续读只第二调用，无cursor_reset
+2. 同长度前缀改写、截短及稳定身份变更；分别报cursor_reset并从0重扫；同inode/size/mtime也不能忽略MAC不符
+3. 秘密无效或读中源变化；拒绝且没有可提交新游标/可信调用/成功零；输出不含路径正文秘密</x:v>
       </x:c>
       <x:c r="H272" s="9" t="str">
         <x:v>准备：无产品DB；每例新建自有临时文件
@@ -20328,7 +20325,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L272" s="9" t="str">
-        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:186</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:178</x:v>
       </x:c>
       <x:c r="M272" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -20337,30 +20334,79 @@
         <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
     </x:row>
+    <x:row r="273" ht="57" customHeight="1">
+      <x:c r="A273" s="4" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="B273" s="4" t="str">
+        <x:v>TC-TM004-CORE-03</x:v>
+      </x:c>
+      <x:c r="C273" s="4" t="str">
+        <x:v>损坏完整行与未知结构</x:v>
+      </x:c>
+      <x:c r="D273" s="4" t="str">
+        <x:v>TASK-TM004-PARSER
+TASK-TM004-INCREMENTAL</x:v>
+      </x:c>
+      <x:c r="E273" s="4" t="str">
+        <x:v>模块检查</x:v>
+      </x:c>
+      <x:c r="F273" s="4" t="str">
+        <x:v>固定13/7行前置非法UTF8完整行和版本2.1.127完整行，尾部再追加无LF坏字节</x:v>
+      </x:c>
+      <x:c r="G273" s="4" t="str">
+        <x:v>1. 读三条完整LF行；仅合法2.1.126一条调用13/7=20；invalid_utf8及unsupported_version各一次
+2. 核对游标、重复读取及隐私；游标到三行LF末，MAC匹配且完成；重复读取0；输出无路径、正文、秘密
+3. 追加无LF坏字节再补LF；未补LF前偏移不动且未完成；补LF后仅诊断推进，无伪调用</x:v>
+      </x:c>
+      <x:c r="H273" s="4" t="str">
+        <x:v>准备：无产品DB；每例新建自有临时文件
+变化：不适用；只返回模块调用、诊断与游标
+核验：固定fixture/行摘要和逐步返回值、前缀MAC及失败时无新游标；无SQL</x:v>
+      </x:c>
+      <x:c r="I273" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J273" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K273" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L273" s="4" t="str">
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:186</x:v>
+      </x:c>
+      <x:c r="M273" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N273" s="4" t="str">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G5:G272">
+  <x:conditionalFormatting sqref="G5:G273">
     <x:cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="I5:I272">
+  <x:conditionalFormatting sqref="I5:I273">
     <x:cfRule type="containsText" dxfId="15" priority="4" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="17" priority="6" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="J5:J272">
+  <x:conditionalFormatting sqref="J5:J273">
     <x:cfRule type="containsText" dxfId="18" priority="7" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="19" priority="8" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="20" priority="9" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="M5:M272">
+  <x:conditionalFormatting sqref="M5:M273">
     <x:cfRule type="containsText" dxfId="21" priority="10" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="22" priority="11" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="23" priority="12" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15026631cc374e50"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad33f5b1dcfb4e67"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21156,7 +21202,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46c847e7fec346f4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e7a2a8d48c543ac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21358,7 +21404,7 @@
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="237" customHeight="1">
+    <x:row r="7" ht="282" customHeight="1">
       <x:c r="A7" s="4" t="str">
         <x:v>v0.2.0-20261001T034118Z</x:v>
       </x:c>
@@ -21387,7 +21433,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J7" s="4" t="str">
-        <x:v>设计基线已完成：3功能点、9 TASK、28父TC、35变体。开发工作树已有原生目录面板、加密locator、根FD受限读取、React授权UI及33个固定E2E叶入口（28可执行、5场景摘要）；报告单元59/59、治理473/473、构建PASS。产品E2E因AX trusted=false及隔离标准测试账号不可用BLOCKED，Keychain最终包隔离未证实。本独立文档树未合该代码，机器绑定仍planned；正式发行完整门禁NOT_RUN、未发布。0.2公开配置为version0.2.0/build200及测试高版0.2.1/build201，实际0.2包尚未证明。 2026-10-02修订SECURITY-01三个恶意字串变体的固定IPC method/字段/错误码，产品状态不变；需在整合候选重核基线及固定程序。</x:v>
+        <x:v>设计基线已完成：3功能点、9 TASK、28父TC、35变体。开发工作树已有原生目录面板、加密locator、根FD受限读取、React授权UI及33个固定E2E叶入口（28可执行、5场景摘要）；报告单元59/59、治理473/473、构建PASS。产品E2E因AX trusted=false及隔离标准测试账号不可用BLOCKED，Keychain最终包隔离未证实。本独立文档树未合该代码，机器绑定仍planned；正式发行完整门禁NOT_RUN、未发布。0.2公开配置为version0.2.0/build200及测试高版0.2.1/build201，实际0.2包尚未证明。 2026-10-02修订SECURITY-01三个恶意字串变体的固定IPC method/字段/错误码，产品状态不变；需在整合候选重核基线及固定程序。 EVIDENCE-01新增第七固定负例，本版36变体；SECURITY-01仅profile准备目录纠错。新输入未执行，产品E2E仍NOT_RUN。</x:v>
       </x:c>
       <x:c r="K7" s="4" t="str">
         <x:v>TM001独立候选d2门禁PASS只属历史；本地master c2911bc首次最终包门禁FAIL、无SOP-020稳定原包，不能作为0.2升级源；本版无实际产品运行。</x:v>
@@ -21600,7 +21646,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6453414550ec48c7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc5d10965c904b6d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22765,7 +22811,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra37c7c299a6c4c35"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e806a9fd13a4224"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TokenMeter项目总表.xlsx
+++ b/TokenMeter项目总表.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="Rbde94a1a5ca34e1d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="R284aa9f88a2e4034"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="Rc25a6238ae194d71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="Rcc997e240d914aa6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R08667b0399ca47da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R48cbdec366684311"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="Rf5c7c974eace4aa0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="Rf8cb85b19dcf4653"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="R50a4e122758c41f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R57a9fa2ad59a4f1a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R0b814b45870a4298"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R7215fc6f93a443cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="R742d88c8de894ce7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R12c572f106d8457a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R1044b23d2bc74f6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R323f0c37591644ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R9de02a0f67a4441b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R900b662389ba48b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="Ra5304fed28d54022"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Rda36ae4456dd4866"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R1c8d52062e24401f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="Rbae19fa2c4fb4f57"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -786,8 +786,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TMTable6" displayName="TMTable6" ref="A4:N273" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:N273"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TMTable6" displayName="TMTable6" ref="A4:N274" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:N274"/>
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="功能编号"/>
     <x:tableColumn id="2" name="用例编号"/>
@@ -809,8 +809,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TMTable7" displayName="TMTable7" ref="A4:N20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:N20"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TMTable7" displayName="TMTable7" ref="A4:N21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:N21"/>
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="运行批次"/>
     <x:tableColumn id="2" name="版本"/>
@@ -1134,8 +1134,8 @@
         <x:v>已登记用例</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:f>COUNTA('05测试用例'!B5:B273)</x:f>
-        <x:v>269</x:v>
+        <x:f>COUNTA('05测试用例'!B5:B274)</x:f>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="C8" s="9" t="str">
         <x:v>父用例与具有稳定 ID 的变体各占一行；含未来概要场景</x:v>
@@ -1146,8 +1146,8 @@
         <x:v>测试批次</x:v>
       </x:c>
       <x:c r="B9" s="10" t="n">
-        <x:f>COUNTA('06测试批次'!A5:A20)</x:f>
-        <x:v>16</x:v>
+        <x:f>COUNTA('06测试批次'!A5:A21)</x:f>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C9" s="4" t="str">
         <x:v>06测试批次，每次运行一行，记录独立结果Excel位置</x:v>
@@ -1169,7 +1169,7 @@
         <x:v>界面与治理检查</x:v>
       </x:c>
       <x:c r="B11" s="10" t="n">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C11" s="4" t="str">
         <x:v>辅助检查不能替代产品E2E；稳定变体独立列出</x:v>
@@ -1271,7 +1271,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="C20" s="9" t="str">
-        <x:v>product_e2e · granular_targeted_probe；仅TC-TM001-UPDATE-05父例及13固定变体：UPDATE-05父例1 PASS、13固定变体13 PASS、26逐步记录，77条TM001父例范围外；清理完成。仅709d候选定向探针，不覆盖旧c291完整门禁FAIL或授予发行资格；Excel为后置de081a6导出修复从原报告生成，非重跑App。；是否覆盖完整产品回归以批次范围和原始证据为准。</x:v>
+        <x:v>source_check · TM-003 CORE-04/05 固定模块事务与游标验证；非产品E2E：source_check固定CORE04/05 2/2、9步、各例owner清理PASS；独立Excel/verification回读PASS。仅模块，原27条产品TC未执行，正式发行NOT_RUN。；是否覆盖完整产品回归以批次范围和原始证据为准。</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="32" customHeight="1">
@@ -1288,7 +1288,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6034ed23f6dd49f9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9093cd2d7ca74824"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1996,7 +1996,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8da03928fcd14244"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R968100f766774b29"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2145,7 +2145,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9c873e73bb3444f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2973a4fdff544a29"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2580,7 +2580,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76cc21639a444669"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b8deead0e034697"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3627,7 +3627,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc99b01a21c74a59"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra90d29cb501c470c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4734,7 +4734,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48b80fb90b69440a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3377c092b5cb4c90"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7519,7 +7519,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3fc4ce55b6b4ada"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe889e98a7904ae5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18586,7 +18586,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L236" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:238</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:251</x:v>
       </x:c>
       <x:c r="M236" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -18633,7 +18633,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L237" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:242</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:255</x:v>
       </x:c>
       <x:c r="M237" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -18680,7 +18680,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L238" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:246</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:259</x:v>
       </x:c>
       <x:c r="M238" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -18728,7 +18728,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L239" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:250</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:263</x:v>
       </x:c>
       <x:c r="M239" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -18778,7 +18778,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L240" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:254</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:267</x:v>
       </x:c>
       <x:c r="M240" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -18826,7 +18826,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L241" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:258</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:271</x:v>
       </x:c>
       <x:c r="M241" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -18873,7 +18873,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L242" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:262</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:275</x:v>
       </x:c>
       <x:c r="M242" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -18920,7 +18920,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L243" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:266</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:279</x:v>
       </x:c>
       <x:c r="M243" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -18968,7 +18968,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L244" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:270</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:283</x:v>
       </x:c>
       <x:c r="M244" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19017,7 +19017,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L245" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:274</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:287</x:v>
       </x:c>
       <x:c r="M245" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19066,7 +19066,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L246" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:278</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:291</x:v>
       </x:c>
       <x:c r="M246" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19115,7 +19115,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L247" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:282</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:295</x:v>
       </x:c>
       <x:c r="M247" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19162,7 +19162,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L248" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:286</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:299</x:v>
       </x:c>
       <x:c r="M248" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19210,7 +19210,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L249" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:290</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:303</x:v>
       </x:c>
       <x:c r="M249" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19258,7 +19258,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L250" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:294</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:307</x:v>
       </x:c>
       <x:c r="M250" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19306,7 +19306,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L251" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:298</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:311</x:v>
       </x:c>
       <x:c r="M251" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19354,7 +19354,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L252" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:302</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:315</x:v>
       </x:c>
       <x:c r="M252" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19404,7 +19404,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L253" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:306</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:319</x:v>
       </x:c>
       <x:c r="M253" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19451,7 +19451,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L254" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:310</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:323</x:v>
       </x:c>
       <x:c r="M254" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19498,7 +19498,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L255" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:314</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:327</x:v>
       </x:c>
       <x:c r="M255" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19546,7 +19546,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L256" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:318</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:331</x:v>
       </x:c>
       <x:c r="M256" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19595,7 +19595,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L257" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:322</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:335</x:v>
       </x:c>
       <x:c r="M257" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19645,7 +19645,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L258" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:326</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:339</x:v>
       </x:c>
       <x:c r="M258" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19693,7 +19693,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L259" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:330</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:343</x:v>
       </x:c>
       <x:c r="M259" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19742,7 +19742,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L260" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:334</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:347</x:v>
       </x:c>
       <x:c r="M260" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19790,7 +19790,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L261" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:338</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:351</x:v>
       </x:c>
       <x:c r="M261" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19838,7 +19838,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L262" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:342</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:355</x:v>
       </x:c>
       <x:c r="M262" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19886,7 +19886,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L263" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:346</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:359</x:v>
       </x:c>
       <x:c r="M263" s="4" t="str">
         <x:v>tm003-core-20261001T165439Z (source_check；产品E2E未运行)</x:v>
@@ -19935,7 +19935,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L264" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:350</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:363</x:v>
       </x:c>
       <x:c r="M264" s="9" t="str">
         <x:v>tm003-core-20261001T165439Z (source_check；产品E2E未运行)</x:v>
@@ -19983,7 +19983,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L265" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:354</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:367</x:v>
       </x:c>
       <x:c r="M265" s="4" t="str">
         <x:v>tm003-core-20261001T165439Z (source_check；产品E2E未运行)</x:v>
@@ -20026,7 +20026,7 @@
         <x:v>draft</x:v>
       </x:c>
       <x:c r="J266" s="9" t="str">
-        <x:v>未执行</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="K266" s="9" t="str">
         <x:v>细化用例</x:v>
@@ -20035,7 +20035,7 @@
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:203</x:v>
       </x:c>
       <x:c r="M266" s="9" t="str">
-        <x:v>尚未执行</x:v>
+        <x:v>tm003-core45-20261001T175000Z (source_check；产品E2E未运行)</x:v>
       </x:c>
       <x:c r="N266" s="9" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
@@ -20077,7 +20077,7 @@
         <x:v>draft</x:v>
       </x:c>
       <x:c r="J267" s="4" t="str">
-        <x:v>未执行</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="K267" s="4" t="str">
         <x:v>细化用例</x:v>
@@ -20086,85 +20086,86 @@
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:216</x:v>
       </x:c>
       <x:c r="M267" s="4" t="str">
-        <x:v>尚未执行</x:v>
+        <x:v>tm003-core45-20261001T175000Z (source_check；产品E2E未运行)</x:v>
       </x:c>
       <x:c r="N267" s="4" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="268" ht="87" customHeight="1">
+    <x:row r="268" ht="117" customHeight="1">
       <x:c r="A268" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B268" s="9" t="str">
+        <x:v>TC-TM003-CORE-06</x:v>
+      </x:c>
+      <x:c r="C268" s="9" t="str">
+        <x:v>多文件代际一次提交与全回滚</x:v>
+      </x:c>
+      <x:c r="D268" s="9" t="str">
+        <x:v>TASK-TM003-SCAN
+TASK-TM003-STORE</x:v>
+      </x:c>
+      <x:c r="E268" s="9" t="str">
+        <x:v>模块检查</x:v>
+      </x:c>
+      <x:c r="F268" s="9" t="str">
+        <x:v>固定tm003-core-generation.json：同一generation两页file-a/file-b，各header+完整LF调用、各410字节；第1页complete=false，末页complete=true；owner空SQLite、公开key1、假scan capability/guard；四步各新空库。</x:v>
+      </x:c>
+      <x:c r="G268" s="9" t="str">
+        <x:v>A仅内存暂存；commitScanBatch调用0次，事件/游标/诊断/覆盖无本代际行，complete=false不称完整
+批次失败并全回滚：A/B事件、两个游标、诊断、覆盖、首次key标记均0或不存在；重开库仍空
+guard拒绝或取消，cancelScan调用1次，commitScanBatch调用0次；暂存清空，事件/两个游标/诊断/覆盖/密钥标记均未提交
+A/B唯一两行，(count,input,output,cached,total)=(2,300,30,60,330)；两游标各410及prefixMAC、coverage.scan_incomplete=0；重启不重复，不输出路径/正文/密钥</x:v>
+      </x:c>
+      <x:c r="H268" s="9" t="str">
+        <x:v>准备：每路径独立owner 0700根/0600空SQLite；事件只由正式模块API提交；步骤2仅创建本例游标失败触发器
+变化：未完成无提交；第二游标失败或guard撤权全代际回滚；完整稳定代际原子提交A/B两个事件、两个游标和覆盖
+核验：逐步只读usage_event唯一键/聚合、source_cursor数量及偏移/prefixMAC、collection_diagnostic、coverage和identity_key_state；重开验证失败仍空、成功不重计；owner清理</x:v>
+      </x:c>
+      <x:c r="I268" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J268" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K268" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L268" s="9" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:230</x:v>
+      </x:c>
+      <x:c r="M268" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N268" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="269" ht="87" customHeight="1">
+      <x:c r="A269" s="4" t="str">
         <x:v>TM-005</x:v>
       </x:c>
-      <x:c r="B268" s="9" t="str">
+      <x:c r="B269" s="4" t="str">
         <x:v>TC-TM005-CORE-01</x:v>
       </x:c>
-      <x:c r="C268" s="9" t="str">
+      <x:c r="C269" s="4" t="str">
         <x:v>双来源可信事件与半开日汇总</x:v>
       </x:c>
-      <x:c r="D268" s="9" t="str">
+      <x:c r="D269" s="4" t="str">
         <x:v>TASK-TM005-EVENT-CONTRACT
 TASK-TM005-RANGE-QUERY</x:v>
       </x:c>
-      <x:c r="E268" s="9" t="str">
+      <x:c r="E269" s="4" t="str">
         <x:v>模块检查</x:v>
       </x:c>
-      <x:c r="F268" s="9" t="str">
+      <x:c r="F269" s="4" t="str">
         <x:v>fixture的A/B、跨主体C、界外D/E；synthetic-p1、Asia/Shanghai当地日2026-09-29</x:v>
       </x:c>
-      <x:c r="G268" s="9" t="str">
+      <x:c r="G269" s="4" t="str">
         <x:v>1. 按固定主体和fixture固定UTC半开界查询纯统计函数，不做IANA日期换算；仅A/B被选、C/D/E排除；输入数组和键不变
 2. 核对来源、模型、Token和三个子项；input300/output30/total330；Codex110/Claude220；未知模型110/sonnet-test220；缓存读20但部分未知、缓存写未知、推理2但部分未知，子项不加总
 3. 逐个输入非法来源、负数、超范围缓存和坏UTC；各自被拒绝，无完整零或有效汇总输出；原fixture不变</x:v>
-      </x:c>
-      <x:c r="H268" s="9" t="str">
-        <x:v>准备：无产品DB写入；每例从新内存输入开始
-变化：不适用；纯统计返回值与输入未变
-核验：固定fixture摘要、事件筛选、各字段与状态逐步核对；无SQL</x:v>
-      </x:c>
-      <x:c r="I268" s="9" t="str">
-        <x:v>draft</x:v>
-      </x:c>
-      <x:c r="J268" s="9" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="K268" s="9" t="str">
-        <x:v>细化用例</x:v>
-      </x:c>
-      <x:c r="L268" s="9" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:326</x:v>
-      </x:c>
-      <x:c r="M268" s="9" t="str">
-        <x:v>尚未执行</x:v>
-      </x:c>
-      <x:c r="N268" s="9" t="str">
-        <x:v>v0.5.0-20261001T034729Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="269" ht="57" customHeight="1">
-      <x:c r="A269" s="4" t="str">
-        <x:v>TM-005</x:v>
-      </x:c>
-      <x:c r="B269" s="4" t="str">
-        <x:v>TC-TM005-CORE-02</x:v>
-      </x:c>
-      <x:c r="C269" s="4" t="str">
-        <x:v>未知用量诊断不补零</x:v>
-      </x:c>
-      <x:c r="D269" s="4" t="str">
-        <x:v>TASK-TM005-EVENT-CONTRACT
-TASK-TM005-COVERAGE</x:v>
-      </x:c>
-      <x:c r="E269" s="4" t="str">
-        <x:v>模块检查</x:v>
-      </x:c>
-      <x:c r="F269" s="4" t="str">
-        <x:v>fixture A/B及同范围Claude missing_usage诊断；双来源complete仅为模块合成覆盖假设</x:v>
-      </x:c>
-      <x:c r="G269" s="4" t="str">
-        <x:v>1. 先仅统计A/B；已知330，未知模型110保留，来源Codex110/Claude220
-2. 加入诊断重新统计；partial、known_tokens330、total_tokens=null；诊断不增调用或零Token
-3. 移除A/B仅保留诊断；unknown、known_tokens0、total_tokens=null，不能写已确认零</x:v>
       </x:c>
       <x:c r="H269" s="4" t="str">
         <x:v>准备：无产品DB写入；每例从新内存输入开始
@@ -20181,7 +20182,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L269" s="4" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:334</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:326</x:v>
       </x:c>
       <x:c r="M269" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -20190,29 +20191,30 @@
         <x:v>v0.5.0-20261001T034729Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="270" ht="87" customHeight="1">
+    <x:row r="270" ht="57" customHeight="1">
       <x:c r="A270" s="9" t="str">
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B270" s="9" t="str">
-        <x:v>TC-TM005-CORE-03</x:v>
+        <x:v>TC-TM005-CORE-02</x:v>
       </x:c>
       <x:c r="C270" s="9" t="str">
-        <x:v>声明式覆盖状态代数</x:v>
+        <x:v>未知用量诊断不补零</x:v>
       </x:c>
       <x:c r="D270" s="9" t="str">
-        <x:v>TASK-TM005-COVERAGE</x:v>
+        <x:v>TASK-TM005-EVENT-CONTRACT
+TASK-TM005-COVERAGE</x:v>
       </x:c>
       <x:c r="E270" s="9" t="str">
         <x:v>模块检查</x:v>
       </x:c>
       <x:c r="F270" s="9" t="str">
-        <x:v>fixture五行coverage_algebra；complete仅为模块合成输入，product_coverage_proven=false</x:v>
+        <x:v>fixture A/B及同范围Claude missing_usage诊断；双来源complete仅为模块合成覆盖假设</x:v>
       </x:c>
       <x:c r="G270" s="9" t="str">
-        <x:v>1. 两来源complete且无事件、随后移除覆盖事实；前者complete/known0/total0；后者不得自行推断complete
-2. 一来源missing，分别给空事件与可信110；空事件missing/known0/total null；可信110为partial/known110/total null
-3. 两来源complete，分别给可信110+未知诊断、仅未知诊断；前者partial/known110/total null；后者unknown/known0/total null</x:v>
+        <x:v>1. 先仅统计A/B；已知330，未知模型110保留，来源Codex110/Claude220
+2. 加入诊断重新统计；partial、known_tokens330、total_tokens=null；诊断不增调用或零Token
+3. 移除A/B仅保留诊断；unknown、known_tokens0、total_tokens=null，不能写已确认零</x:v>
       </x:c>
       <x:c r="H270" s="9" t="str">
         <x:v>准备：无产品DB写入；每例从新内存输入开始
@@ -20229,7 +20231,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L270" s="9" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:342</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:334</x:v>
       </x:c>
       <x:c r="M270" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -20238,77 +20240,77 @@
         <x:v>v0.5.0-20261001T034729Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="271" ht="72" customHeight="1">
+    <x:row r="271" ht="87" customHeight="1">
       <x:c r="A271" s="4" t="str">
-        <x:v>TM-004</x:v>
+        <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B271" s="4" t="str">
-        <x:v>TC-TM004-CORE-01</x:v>
+        <x:v>TC-TM005-CORE-03</x:v>
       </x:c>
       <x:c r="C271" s="4" t="str">
-        <x:v>完整LF、半行与限额续读</x:v>
+        <x:v>声明式覆盖状态代数</x:v>
       </x:c>
       <x:c r="D271" s="4" t="str">
-        <x:v>TASK-TM004-INCREMENTAL</x:v>
+        <x:v>TASK-TM005-COVERAGE</x:v>
       </x:c>
       <x:c r="E271" s="4" t="str">
         <x:v>模块检查</x:v>
       </x:c>
       <x:c r="F271" s="4" t="str">
+        <x:v>fixture五行coverage_algebra；complete仅为模块合成输入，product_coverage_proven=false</x:v>
+      </x:c>
+      <x:c r="G271" s="4" t="str">
+        <x:v>1. 两来源complete且无事件、随后移除覆盖事实；前者complete/known0/total0；后者不得自行推断complete
+2. 一来源missing，分别给空事件与可信110；空事件missing/known0/total null；可信110为partial/known110/total null
+3. 两来源complete，分别给可信110+未知诊断、仅未知诊断；前者partial/known110/total null；后者unknown/known0/total null</x:v>
+      </x:c>
+      <x:c r="H271" s="4" t="str">
+        <x:v>准备：无产品DB写入；每例从新内存输入开始
+变化：不适用；纯统计返回值与输入未变
+核验：固定fixture摘要、事件筛选、各字段与状态逐步核对；无SQL</x:v>
+      </x:c>
+      <x:c r="I271" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J271" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K271" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L271" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:342</x:v>
+      </x:c>
+      <x:c r="M271" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N271" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="272" ht="72" customHeight="1">
+      <x:c r="A272" s="9" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="B272" s="9" t="str">
+        <x:v>TC-TM004-CORE-01</x:v>
+      </x:c>
+      <x:c r="C272" s="9" t="str">
+        <x:v>完整LF、半行与限额续读</x:v>
+      </x:c>
+      <x:c r="D272" s="9" t="str">
+        <x:v>TASK-TM004-INCREMENTAL</x:v>
+      </x:c>
+      <x:c r="E272" s="9" t="str">
+        <x:v>模块检查</x:v>
+      </x:c>
+      <x:c r="F272" s="9" t="str">
         <x:v>固定746字节13/7 assistant行、前半字节、两条不同ID完整行、首读上限754字节</x:v>
       </x:c>
-      <x:c r="G271" s="4" t="str">
+      <x:c r="G272" s="9" t="str">
         <x:v>1. 读未写完的前半行；调用0、偏移0、scanIncomplete=true，不作可信零结论
 2. 补齐LF、重复读取；补齐后一次13/7=20、偏移746、前缀MAC匹配；重复读取0调用且游标不变
 3. 两完整行首读754字节后续读；首读只第一条、偏移746、read_limit且未完成；续读只第二条、偏移为总字节长、完成</x:v>
-      </x:c>
-      <x:c r="H271" s="4" t="str">
-        <x:v>准备：无产品DB；每例新建自有临时文件
-变化：不适用；只返回模块调用、诊断与游标
-核验：固定fixture/行摘要和逐步返回值、前缀MAC及失败时无新游标；无SQL</x:v>
-      </x:c>
-      <x:c r="I271" s="4" t="str">
-        <x:v>draft</x:v>
-      </x:c>
-      <x:c r="J271" s="4" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="K271" s="4" t="str">
-        <x:v>细化用例</x:v>
-      </x:c>
-      <x:c r="L271" s="4" t="str">
-        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:170</x:v>
-      </x:c>
-      <x:c r="M271" s="4" t="str">
-        <x:v>尚未执行</x:v>
-      </x:c>
-      <x:c r="N271" s="4" t="str">
-        <x:v>v0.4.0-20261001T040433Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="272" ht="72" customHeight="1">
-      <x:c r="A272" s="9" t="str">
-        <x:v>TM-004</x:v>
-      </x:c>
-      <x:c r="B272" s="9" t="str">
-        <x:v>TC-TM004-CORE-02</x:v>
-      </x:c>
-      <x:c r="C272" s="9" t="str">
-        <x:v>前缀MAC、变更和密钥失败</x:v>
-      </x:c>
-      <x:c r="D272" s="9" t="str">
-        <x:v>TASK-TM004-INCREMENTAL</x:v>
-      </x:c>
-      <x:c r="E272" s="9" t="str">
-        <x:v>模块检查</x:v>
-      </x:c>
-      <x:c r="F272" s="9" t="str">
-        <x:v>已提交首行，追加不同ID第二行、同长度ID改写并复原mtime、截短、身份改变、秘密缺失或错误</x:v>
-      </x:c>
-      <x:c r="G272" s="9" t="str">
-        <x:v>1. 首行后追加第二完整行；快照digest变化但稳定身份/前缀MAC相同，续读只第二调用，无cursor_reset
-2. 同长度前缀改写、截短及稳定身份变更；分别报cursor_reset并从0重扫；同inode/size/mtime也不能忽略MAC不符
-3. 秘密无效或读中源变化；拒绝且没有可提交新游标/可信调用/成功零；输出不含路径正文秘密</x:v>
       </x:c>
       <x:c r="H272" s="9" t="str">
         <x:v>准备：无产品DB；每例新建自有临时文件
@@ -20325,7 +20327,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L272" s="9" t="str">
-        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:178</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:170</x:v>
       </x:c>
       <x:c r="M272" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -20334,30 +20336,29 @@
         <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="273" ht="57" customHeight="1">
+    <x:row r="273" ht="72" customHeight="1">
       <x:c r="A273" s="4" t="str">
         <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B273" s="4" t="str">
-        <x:v>TC-TM004-CORE-03</x:v>
+        <x:v>TC-TM004-CORE-02</x:v>
       </x:c>
       <x:c r="C273" s="4" t="str">
-        <x:v>损坏完整行与未知结构</x:v>
+        <x:v>前缀MAC、变更和密钥失败</x:v>
       </x:c>
       <x:c r="D273" s="4" t="str">
-        <x:v>TASK-TM004-PARSER
-TASK-TM004-INCREMENTAL</x:v>
+        <x:v>TASK-TM004-INCREMENTAL</x:v>
       </x:c>
       <x:c r="E273" s="4" t="str">
         <x:v>模块检查</x:v>
       </x:c>
       <x:c r="F273" s="4" t="str">
-        <x:v>固定13/7行前置非法UTF8完整行和版本2.1.127完整行，尾部再追加无LF坏字节</x:v>
+        <x:v>已提交首行，追加不同ID第二行、同长度ID改写并复原mtime、截短、身份改变、秘密缺失或错误</x:v>
       </x:c>
       <x:c r="G273" s="4" t="str">
-        <x:v>1. 读三条完整LF行；仅合法2.1.126一条调用13/7=20；invalid_utf8及unsupported_version各一次
-2. 核对游标、重复读取及隐私；游标到三行LF末，MAC匹配且完成；重复读取0；输出无路径、正文、秘密
-3. 追加无LF坏字节再补LF；未补LF前偏移不动且未完成；补LF后仅诊断推进，无伪调用</x:v>
+        <x:v>1. 首行后追加第二完整行；快照digest变化但稳定身份/前缀MAC相同，续读只第二调用，无cursor_reset
+2. 同长度前缀改写、截短及稳定身份变更；分别报cursor_reset并从0重扫；同inode/size/mtime也不能忽略MAC不符
+3. 秘密无效或读中源变化；拒绝且没有可提交新游标/可信调用/成功零；输出不含路径正文秘密</x:v>
       </x:c>
       <x:c r="H273" s="4" t="str">
         <x:v>准备：无产品DB；每例新建自有临时文件
@@ -20374,7 +20375,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L273" s="4" t="str">
-        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:186</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:178</x:v>
       </x:c>
       <x:c r="M273" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -20383,30 +20384,79 @@
         <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
     </x:row>
+    <x:row r="274" ht="57" customHeight="1">
+      <x:c r="A274" s="9" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="B274" s="9" t="str">
+        <x:v>TC-TM004-CORE-03</x:v>
+      </x:c>
+      <x:c r="C274" s="9" t="str">
+        <x:v>损坏完整行与未知结构</x:v>
+      </x:c>
+      <x:c r="D274" s="9" t="str">
+        <x:v>TASK-TM004-PARSER
+TASK-TM004-INCREMENTAL</x:v>
+      </x:c>
+      <x:c r="E274" s="9" t="str">
+        <x:v>模块检查</x:v>
+      </x:c>
+      <x:c r="F274" s="9" t="str">
+        <x:v>固定13/7行前置非法UTF8完整行和版本2.1.127完整行，尾部再追加无LF坏字节</x:v>
+      </x:c>
+      <x:c r="G274" s="9" t="str">
+        <x:v>1. 读三条完整LF行；仅合法2.1.126一条调用13/7=20；invalid_utf8及unsupported_version各一次
+2. 核对游标、重复读取及隐私；游标到三行LF末，MAC匹配且完成；重复读取0；输出无路径、正文、秘密
+3. 追加无LF坏字节再补LF；未补LF前偏移不动且未完成；补LF后仅诊断推进，无伪调用</x:v>
+      </x:c>
+      <x:c r="H274" s="9" t="str">
+        <x:v>准备：无产品DB；每例新建自有临时文件
+变化：不适用；只返回模块调用、诊断与游标
+核验：固定fixture/行摘要和逐步返回值、前缀MAC及失败时无新游标；无SQL</x:v>
+      </x:c>
+      <x:c r="I274" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J274" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K274" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L274" s="9" t="str">
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:186</x:v>
+      </x:c>
+      <x:c r="M274" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N274" s="9" t="str">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G5:G273">
+  <x:conditionalFormatting sqref="G5:G274">
     <x:cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="I5:I273">
+  <x:conditionalFormatting sqref="I5:I274">
     <x:cfRule type="containsText" dxfId="15" priority="4" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="17" priority="6" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="J5:J273">
+  <x:conditionalFormatting sqref="J5:J274">
     <x:cfRule type="containsText" dxfId="18" priority="7" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="19" priority="8" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="20" priority="9" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="M5:M273">
+  <x:conditionalFormatting sqref="M5:M274">
     <x:cfRule type="containsText" dxfId="21" priority="10" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="22" priority="11" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="23" priority="12" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad33f5b1dcfb4e67"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfaad12eebafd4f06"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21184,25 +21234,69 @@
         <x:v>PASS</x:v>
       </x:c>
     </x:row>
+    <x:row r="21" ht="42" customHeight="1">
+      <x:c r="A21" s="4" t="str">
+        <x:v>tm003-core45-20261001T175000Z</x:v>
+      </x:c>
+      <x:c r="B21" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+      <x:c r="C21" s="4" t="str">
+        <x:v>source_check</x:v>
+      </x:c>
+      <x:c r="D21" s="4" t="str">
+        <x:v>TM-003 CORE-04/05 固定模块事务与游标验证；非产品E2E</x:v>
+      </x:c>
+      <x:c r="E21" s="4" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F21" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G21" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H21" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I21" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J21" s="4" t="str">
+        <x:v>9efc6fa9d8523f30dfc20f4cfb8282cc54f18dd0</x:v>
+      </x:c>
+      <x:c r="K21" s="4" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="L21" s="4" t="str">
+        <x:v>source_check固定CORE04/05 2/2、9步、各例owner清理PASS；独立Excel/verification回读PASS。仅模块，原27条产品TC未执行，正式发行NOT_RUN。</x:v>
+      </x:c>
+      <x:c r="M21" s="4" t="str">
+        <x:v>.local/test-results/tm003-core45-20261001T175000Z/TokenMeter测试结果-tm003-core45-20261001T175000Z.xlsx</x:v>
+      </x:c>
+      <x:c r="N21" s="4" t="str">
+        <x:v>NOT_RUN</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="E5:E20">
+  <x:conditionalFormatting sqref="E5:E21">
     <x:cfRule type="containsText" dxfId="24" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="25" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="26" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="M5:M20">
+  <x:conditionalFormatting sqref="M5:M21">
     <x:cfRule type="containsText" dxfId="27" priority="4" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="28" priority="5" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="29" priority="6" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="N5:N20">
+  <x:conditionalFormatting sqref="N5:N21">
     <x:cfRule type="containsText" dxfId="30" priority="7" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="31" priority="8" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="32" priority="9" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e7a2a8d48c543ac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f0916034fad42d2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21460,7 +21554,7 @@
         <x:v>releases/v0.2.0-20261001T034118Z/01-requirements.md:32</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="342" customHeight="1">
+    <x:row r="8" ht="387" customHeight="1">
       <x:c r="A8" s="9" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
@@ -21489,7 +21583,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J8" s="9" t="str">
-        <x:v>整版draft、未发布。27条产品TC未执行；3条CORE辅助TC已在文档提交48ca089独立切片就绪，在开发分支311deedf运行模块3/3 PASS，原始receipt在该分支.local/ci/tm003-core-20261001/。代码尚未合入本文档树，机器绑定保持空；模块报告不能作为产品E2E或发行门禁，结果Excel规范待SOP修订。 2026-10-02新代码候选44379e6已有逐步模块3/3与桌面29/29/typecheck/build原件；source_check独立Excel导出程序仍缺，批次登记BLOCKED，产品E2E仍NOT_RUN。 固定导出器新run tm003-core-20261001T163807Z在ea6b187候选生成3/3/9步source_check独立Excel并回读PASS，现已按被测SHA登记模块批次；原27条产品TC与发行仍NOT_RUN。 新清理合同候选d7c3d39的独立run tm003-core-20261001T165439Z亦3/3/9步及Excel回读PASS，作为最新模块批次；旧ea6批次保留。 后续CORE-04/05的测试输入已编制，程序未绑定、未执行；独立SOP-008切片复核待文档干净提交。</x:v>
+        <x:v>整版draft、未发布。27条产品TC未执行；3条CORE辅助TC已在文档提交48ca089独立切片就绪，在开发分支311deedf运行模块3/3 PASS，原始receipt在该分支.local/ci/tm003-core-20261001/。代码尚未合入本文档树，机器绑定保持空；模块报告不能作为产品E2E或发行门禁，结果Excel规范待SOP修订。 2026-10-02新代码候选44379e6已有逐步模块3/3与桌面29/29/typecheck/build原件；source_check独立Excel导出程序仍缺，批次登记BLOCKED，产品E2E仍NOT_RUN。 固定导出器新run tm003-core-20261001T163807Z在ea6b187候选生成3/3/9步source_check独立Excel并回读PASS，现已按被测SHA登记模块批次；原27条产品TC与发行仍NOT_RUN。 新清理合同候选d7c3d39的独立run tm003-core-20261001T165439Z亦3/3/9步及Excel回读PASS，作为最新模块批次；旧ea6批次保留。 后续CORE-04/05的测试输入已编制，程序未绑定、未执行；独立SOP-008切片复核待文档干净提交。 CORE04/05基于9efc6fa独立source_check 2/2、9步和Excel回读PASS，第17批次；CORE06新输入未执行，产品E2E NOT_RUN。</x:v>
       </x:c>
       <x:c r="K8" s="9" t="str">
         <x:v>TM-001 干净源码候选为技术基底；其产品门禁不继承给TM-003</x:v>
@@ -21646,7 +21740,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc5d10965c904b6d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4791341f513d4308"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22811,7 +22905,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e806a9fd13a4224"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52c4b647f49e45f5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TokenMeter项目总表.xlsx
+++ b/TokenMeter项目总表.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R7215fc6f93a443cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="R742d88c8de894ce7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R12c572f106d8457a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R1044b23d2bc74f6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R323f0c37591644ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R9de02a0f67a4441b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R900b662389ba48b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="Ra5304fed28d54022"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Rda36ae4456dd4866"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R1c8d52062e24401f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="Rbae19fa2c4fb4f57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="Rcb2e6197ef514bde"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="R3d396230446642d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R0b857d5ae06a45ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R586e9306229e404c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="Rf581f41391f54e9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="Rdfefec032dd34f3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="Rac338ac978374a73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="Rfea48e2e580f413c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Ra6d9dd69c3c940c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R032275ad43524de5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R6d66857b2eac4403"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -786,8 +786,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TMTable6" displayName="TMTable6" ref="A4:N274" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:N274"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TMTable6" displayName="TMTable6" ref="A4:N275" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:N275"/>
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="功能编号"/>
     <x:tableColumn id="2" name="用例编号"/>
@@ -1134,8 +1134,8 @@
         <x:v>已登记用例</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:f>COUNTA('05测试用例'!B5:B274)</x:f>
-        <x:v>270</x:v>
+        <x:f>COUNTA('05测试用例'!B5:B275)</x:f>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="C8" s="9" t="str">
         <x:v>父用例与具有稳定 ID 的变体各占一行；含未来概要场景</x:v>
@@ -1169,7 +1169,7 @@
         <x:v>界面与治理检查</x:v>
       </x:c>
       <x:c r="B11" s="10" t="n">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C11" s="4" t="str">
         <x:v>辅助检查不能替代产品E2E；稳定变体独立列出</x:v>
@@ -1288,7 +1288,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9093cd2d7ca74824"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf232f8d41fe34f5e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1996,7 +1996,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R968100f766774b29"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra712f0d0e8f24eb3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2145,7 +2145,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2973a4fdff544a29"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7511311acf0f4c69"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2580,7 +2580,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b8deead0e034697"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5b3683e4c874f2c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3627,7 +3627,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra90d29cb501c470c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55ac6f0a777c4164"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4734,7 +4734,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3377c092b5cb4c90"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b0b80079f74487c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7519,7 +7519,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe889e98a7904ae5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R526d9b71940b4a85"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20433,30 +20433,79 @@
         <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
     </x:row>
+    <x:row r="275" ht="87" customHeight="1">
+      <x:c r="A275" s="4" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="B275" s="4" t="str">
+        <x:v>TC-TM004-CORE-04</x:v>
+      </x:c>
+      <x:c r="C275" s="4" t="str">
+        <x:v>授权主体与扫描事务触发</x:v>
+      </x:c>
+      <x:c r="D275" s="4" t="str">
+        <x:v>TASK-TM004-SOURCE
+TASK-TM004-INCREMENTAL</x:v>
+      </x:c>
+      <x:c r="E275" s="4" t="str">
+        <x:v>模块检查</x:v>
+      </x:c>
+      <x:c r="F275" s="4" t="str">
+        <x:v>tests/fixtures/tm004-trigger-core-slice.json；固定UUID、M=100/10、无效路径/主体/来源、三种屏障事件</x:v>
+      </x:c>
+      <x:c r="G275" s="4" t="str">
+        <x:v>1. 拒绝路径字段、无效主体/来源和预先取消的请求；明确拒绝；beginCandidateScan=0，commitSync=0，无成功零值
+2. 扫描开始后在固定屏障分别换账号、撤权和取消；每次cancelScan被调用；commitSync=0；缓冲数据不外露
+3. 健康主体和授权世代扫描完整M并通过提交守卫；commitSync恰一次；返回1次调用、100/10/110、覆盖完整；无私密哨兵/原生标识</x:v>
+      </x:c>
+      <x:c r="H275" s="4" t="str">
+        <x:v>准备：无产品DB；每子变体新建假端口与计数器
+变化：无SQLite；只观察假同步提交次数及数值
+核验：逐步断言扫描、取消、守卫、提交次数与返回白名单；无SQL</x:v>
+      </x:c>
+      <x:c r="I275" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J275" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K275" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L275" s="4" t="str">
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:198</x:v>
+      </x:c>
+      <x:c r="M275" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N275" s="4" t="str">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G5:G274">
+  <x:conditionalFormatting sqref="G5:G275">
     <x:cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="I5:I274">
+  <x:conditionalFormatting sqref="I5:I275">
     <x:cfRule type="containsText" dxfId="15" priority="4" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="17" priority="6" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="J5:J274">
+  <x:conditionalFormatting sqref="J5:J275">
     <x:cfRule type="containsText" dxfId="18" priority="7" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="19" priority="8" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="20" priority="9" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="M5:M274">
+  <x:conditionalFormatting sqref="M5:M275">
     <x:cfRule type="containsText" dxfId="21" priority="10" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="22" priority="11" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="23" priority="12" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfaad12eebafd4f06"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R62b3220ccbf44a10"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21296,7 +21345,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f0916034fad42d2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0455fdbf79064229"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21740,7 +21789,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4791341f513d4308"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6603ff5ad4b1416a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22905,7 +22954,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52c4b647f49e45f5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7dfc65debf24da0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TokenMeter项目总表.xlsx
+++ b/TokenMeter项目总表.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="Rcb2e6197ef514bde"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="R3d396230446642d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R0b857d5ae06a45ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R586e9306229e404c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="Rf581f41391f54e9a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="Rdfefec032dd34f3d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="Rac338ac978374a73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="Rfea48e2e580f413c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Ra6d9dd69c3c940c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R032275ad43524de5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R6d66857b2eac4403"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="Rd2a6d09f77894779"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Rf4e156a1925645dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="Red0433e6efb741c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R86b940aabb4d473e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R9846e0924699427f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R87d79ff2e74b42de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="Rf30adb9bddbd4df5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R33be556776a34e79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="R1fac0a087b6e4e85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R7291e1ae66594553"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="Re295b36e23cc4b12"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -786,8 +786,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TMTable6" displayName="TMTable6" ref="A4:N275" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:N275"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TMTable6" displayName="TMTable6" ref="A4:N276" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:N276"/>
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="功能编号"/>
     <x:tableColumn id="2" name="用例编号"/>
@@ -809,8 +809,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TMTable7" displayName="TMTable7" ref="A4:N21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:N21"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TMTable7" displayName="TMTable7" ref="A4:N22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:N22"/>
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="运行批次"/>
     <x:tableColumn id="2" name="版本"/>
@@ -832,8 +832,8 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="TMTable8" displayName="TMTable8" ref="A4:R10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:R10"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="TMTable8" displayName="TMTable8" ref="A4:R11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:R11"/>
   <x:tableColumns count="18">
     <x:tableColumn id="1" name="发布编号"/>
     <x:tableColumn id="2" name="版本"/>
@@ -1134,8 +1134,8 @@
         <x:v>已登记用例</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:f>COUNTA('05测试用例'!B5:B275)</x:f>
-        <x:v>271</x:v>
+        <x:f>COUNTA('05测试用例'!B5:B276)</x:f>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="C8" s="9" t="str">
         <x:v>父用例与具有稳定 ID 的变体各占一行；含未来概要场景</x:v>
@@ -1146,8 +1146,8 @@
         <x:v>测试批次</x:v>
       </x:c>
       <x:c r="B9" s="10" t="n">
-        <x:f>COUNTA('06测试批次'!A5:A21)</x:f>
-        <x:v>17</x:v>
+        <x:f>COUNTA('06测试批次'!A5:A22)</x:f>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C9" s="4" t="str">
         <x:v>06测试批次，每次运行一行，记录独立结果Excel位置</x:v>
@@ -1169,7 +1169,7 @@
         <x:v>界面与治理检查</x:v>
       </x:c>
       <x:c r="B11" s="10" t="n">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C11" s="4" t="str">
         <x:v>辅助检查不能替代产品E2E；稳定变体独立列出</x:v>
@@ -1271,7 +1271,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="C20" s="9" t="str">
-        <x:v>source_check · TM-003 CORE-04/05 固定模块事务与游标验证；非产品E2E：source_check固定CORE04/05 2/2、9步、各例owner清理PASS；独立Excel/verification回读PASS。仅模块，原27条产品TC未执行，正式发行NOT_RUN。；是否覆盖完整产品回归以批次范围和原始证据为准。</x:v>
+        <x:v>source_check · TM-003 CORE-06 固定多文件代际提交与全回滚；非产品E2E：source_check固定CORE06 1/1、四步及owner清理PASS；此前408ebf8红测步骤2 FAIL保留。独立Excel/verification回读PASS。原27条产品TC、App E2E与发行均NOT_RUN。；是否覆盖完整产品回归以批次范围和原始证据为准。</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="32" customHeight="1">
@@ -1288,7 +1288,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf232f8d41fe34f5e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R112308681a85490a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1996,7 +1996,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra712f0d0e8f24eb3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b0d3089fa0541b6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2145,7 +2145,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7511311acf0f4c69"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc6b07d381f0c44e1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2580,7 +2580,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5b3683e4c874f2c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf01dd68b6584e30"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3627,7 +3627,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55ac6f0a777c4164"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc237592fa63497d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4734,7 +4734,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b0b80079f74487c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8580111f2c5649f5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7519,7 +7519,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R526d9b71940b4a85"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3aa2b3bcebe74fdd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20127,7 +20127,7 @@
         <x:v>draft</x:v>
       </x:c>
       <x:c r="J268" s="9" t="str">
-        <x:v>未执行</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="K268" s="9" t="str">
         <x:v>细化用例</x:v>
@@ -20136,7 +20136,7 @@
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:230</x:v>
       </x:c>
       <x:c r="M268" s="9" t="str">
-        <x:v>尚未执行</x:v>
+        <x:v>tm003-core06-20261001T182500Z (source_check；产品E2E未运行)</x:v>
       </x:c>
       <x:c r="N268" s="9" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
@@ -20336,7 +20336,7 @@
         <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="273" ht="72" customHeight="1">
+    <x:row r="273" ht="87" customHeight="1">
       <x:c r="A273" s="4" t="str">
         <x:v>TM-004</x:v>
       </x:c>
@@ -20356,7 +20356,7 @@
         <x:v>已提交首行，追加不同ID第二行、同长度ID改写并复原mtime、截短、身份改变、秘密缺失或错误</x:v>
       </x:c>
       <x:c r="G273" s="4" t="str">
-        <x:v>1. 首行后追加第二完整行；快照digest变化但稳定身份/前缀MAC相同，续读只第二调用，无cursor_reset
+        <x:v>1. 首行后追加第二完整行；size/mtime变化但TM-002 dev/ino摘要和前缀MAC相同，续读只第二调用，无cursor_reset
 2. 同长度前缀改写、截短及稳定身份变更；分别报cursor_reset并从0重扫；同inode/size/mtime也不能忽略MAC不符
 3. 秘密无效或读中源变化；拒绝且没有可提交新游标/可信调用/成功零；输出不含路径正文秘密</x:v>
       </x:c>
@@ -20433,7 +20433,7 @@
         <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="275" ht="87" customHeight="1">
+    <x:row r="275" ht="132" customHeight="1">
       <x:c r="A275" s="4" t="str">
         <x:v>TM-004</x:v>
       </x:c>
@@ -20451,12 +20451,12 @@
         <x:v>模块检查</x:v>
       </x:c>
       <x:c r="F275" s="4" t="str">
-        <x:v>tests/fixtures/tm004-trigger-core-slice.json；固定UUID、M=100/10、无效路径/主体/来源、三种屏障事件</x:v>
+        <x:v>tests/fixtures/tm004-trigger-core-slice.json；固定UUID、M=100/10、各错误码、三种屏障事件及成功返回形状</x:v>
       </x:c>
       <x:c r="G275" s="4" t="str">
-        <x:v>1. 拒绝路径字段、无效主体/来源和预先取消的请求；明确拒绝；beginCandidateScan=0，commitSync=0，无成功零值
-2. 扫描开始后在固定屏障分别换账号、撤权和取消；每次cancelScan被调用；commitSync=0；缓冲数据不外露
-3. 健康主体和授权世代扫描完整M并通过提交守卫；commitSync恰一次；返回1次调用、100/10/110、覆盖完整；无私密哨兵/原生标识</x:v>
+        <x:v>1. 拒绝路径字段、无效主体/来源和预先取消的请求；路径字段/坏UUID为invalid_collection_request；账号不可用为collection_unavailable；异主体来源为source_not_authorized；预先取消为collection_cancelled；均扫描0、提交0
+2. 扫描开始后在固定屏障分别换账号、撤权和取消；换账号/撤权为collection_stale，取消为collection_cancelled；每次cancelScan、commitSync=0、缓冲不外露
+3. 健康主体和授权世代扫描完整M并通过提交守卫；commitSync恰一次；返回summary{callCount:1,inputTokens:100,outputTokens:10,totalTokens:110,scanIncomplete:false},diagnostics:[]，无私密哨兵/原生标识</x:v>
       </x:c>
       <x:c r="H275" s="4" t="str">
         <x:v>准备：无产品DB；每子变体新建假端口与计数器
@@ -20482,30 +20482,80 @@
         <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
     </x:row>
+    <x:row r="276" ht="147" customHeight="1">
+      <x:c r="A276" s="9" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="B276" s="9" t="str">
+        <x:v>TC-TM004-CORE-05</x:v>
+      </x:c>
+      <x:c r="C276" s="9" t="str">
+        <x:v>多文件来源键与整代持久映射</x:v>
+      </x:c>
+      <x:c r="D276" s="9" t="str">
+        <x:v>TASK-TM004-INCREMENTAL
+TASK-TM004-LINEAGE</x:v>
+      </x:c>
+      <x:c r="E276" s="9" t="str">
+        <x:v>模块检查</x:v>
+      </x:c>
+      <x:c r="F276" s="9" t="str">
+        <x:v>tests/fixtures/tm004-storage-port-slice.json；合成M100/10、S200/20、Q50/5，三文件HMAC/游标/诊断与隔离SQLite；异常model_id哨兵与invalid_model_id诊断</x:v>
+      </x:c>
+      <x:c r="G276" s="9" t="str">
+        <x:v>1. 计算三个文件来源键、根键及换源/追加/替换向量；64hex键逐一等于fixture；普通追加键不变，换sourceId/文件摘要改变；数据库不收原摘要/相对名
+2. 构造完整三文件generation并核对文件归属与turnId代号；a/b/c各有自己的M/S/Q、游标和诊断；c异常model_id置null并增加invalid_model_id，SQLite/WAL无哨兵；turn代号仅进scope HMAC；未到末页/正文不稳零提交
+3. 分别在新库注入第二游标写失败与guard撤权；每次整代回滚或零开始，事件/游标/诊断/覆盖/密钥标记全空；取消并清缓冲
+4. 稳定末页通过guard后一次同步commitScanBatch并重扫；唯一3调用、input350/output35/total385、3游标/4诊断按文件归属、scan_incomplete=1；scope键匹配向量，重扫不增；SQLite/WAL无模型哨兵/原生标识</x:v>
+      </x:c>
+      <x:c r="H276" s="9" t="str">
+        <x:v>准备：每故障子场景新建本例空SQLite；故障注入只在本例库设置第二游标写入RAISE(ABORT)
+变化：成功一次事务新增三事件、三个游标、三诊断与根覆盖；失败和撤权零提交
+核验：只读查询usage_event、source_cursor、collection_diagnostic、coverage的数量/键/数值；核对源键和scope HMAC向量及无原生标识；关闭并核对SQLite/WAL无合成prompt/路径哨兵</x:v>
+      </x:c>
+      <x:c r="I276" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J276" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K276" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L276" s="9" t="str">
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:206</x:v>
+      </x:c>
+      <x:c r="M276" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N276" s="9" t="str">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G5:G275">
+  <x:conditionalFormatting sqref="G5:G276">
     <x:cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="I5:I275">
+  <x:conditionalFormatting sqref="I5:I276">
     <x:cfRule type="containsText" dxfId="15" priority="4" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="17" priority="6" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="J5:J275">
+  <x:conditionalFormatting sqref="J5:J276">
     <x:cfRule type="containsText" dxfId="18" priority="7" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="19" priority="8" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="20" priority="9" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="M5:M275">
+  <x:conditionalFormatting sqref="M5:M276">
     <x:cfRule type="containsText" dxfId="21" priority="10" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="22" priority="11" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="23" priority="12" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R62b3220ccbf44a10"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07055277d0114c75"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21327,25 +21377,69 @@
         <x:v>NOT_RUN</x:v>
       </x:c>
     </x:row>
+    <x:row r="22" ht="42" customHeight="1">
+      <x:c r="A22" s="9" t="str">
+        <x:v>tm003-core06-20261001T182500Z</x:v>
+      </x:c>
+      <x:c r="B22" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+      <x:c r="C22" s="9" t="str">
+        <x:v>source_check</x:v>
+      </x:c>
+      <x:c r="D22" s="9" t="str">
+        <x:v>TM-003 CORE-06 固定多文件代际提交与全回滚；非产品E2E</x:v>
+      </x:c>
+      <x:c r="E22" s="9" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F22" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G22" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H22" s="9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I22" s="9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J22" s="9" t="str">
+        <x:v>eef956b877ebe60f53e605db861f738533837f8b</x:v>
+      </x:c>
+      <x:c r="K22" s="9" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="L22" s="9" t="str">
+        <x:v>source_check固定CORE06 1/1、四步及owner清理PASS；此前408ebf8红测步骤2 FAIL保留。独立Excel/verification回读PASS。原27条产品TC、App E2E与发行均NOT_RUN。</x:v>
+      </x:c>
+      <x:c r="M22" s="9" t="str">
+        <x:v>.local/test-results/tm003-core06-20261001T182500Z/TokenMeter测试结果-tm003-core06-20261001T182500Z.xlsx</x:v>
+      </x:c>
+      <x:c r="N22" s="9" t="str">
+        <x:v>NOT_RUN</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="E5:E21">
+  <x:conditionalFormatting sqref="E5:E22">
     <x:cfRule type="containsText" dxfId="24" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="25" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="26" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="M5:M21">
+  <x:conditionalFormatting sqref="M5:M22">
     <x:cfRule type="containsText" dxfId="27" priority="4" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="28" priority="5" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="29" priority="6" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="N5:N21">
+  <x:conditionalFormatting sqref="N5:N22">
     <x:cfRule type="containsText" dxfId="30" priority="7" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="31" priority="8" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="32" priority="9" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0455fdbf79064229"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfef00fe67eeb4ddb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21632,7 +21726,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J8" s="9" t="str">
-        <x:v>整版draft、未发布。27条产品TC未执行；3条CORE辅助TC已在文档提交48ca089独立切片就绪，在开发分支311deedf运行模块3/3 PASS，原始receipt在该分支.local/ci/tm003-core-20261001/。代码尚未合入本文档树，机器绑定保持空；模块报告不能作为产品E2E或发行门禁，结果Excel规范待SOP修订。 2026-10-02新代码候选44379e6已有逐步模块3/3与桌面29/29/typecheck/build原件；source_check独立Excel导出程序仍缺，批次登记BLOCKED，产品E2E仍NOT_RUN。 固定导出器新run tm003-core-20261001T163807Z在ea6b187候选生成3/3/9步source_check独立Excel并回读PASS，现已按被测SHA登记模块批次；原27条产品TC与发行仍NOT_RUN。 新清理合同候选d7c3d39的独立run tm003-core-20261001T165439Z亦3/3/9步及Excel回读PASS，作为最新模块批次；旧ea6批次保留。 后续CORE-04/05的测试输入已编制，程序未绑定、未执行；独立SOP-008切片复核待文档干净提交。 CORE04/05基于9efc6fa独立source_check 2/2、9步和Excel回读PASS，第17批次；CORE06新输入未执行，产品E2E NOT_RUN。</x:v>
+        <x:v>整版draft、未发布。27条产品TC未执行；3条CORE辅助TC已在文档提交48ca089独立切片就绪，在开发分支311deedf运行模块3/3 PASS，原始receipt在该分支.local/ci/tm003-core-20261001/。代码尚未合入本文档树，机器绑定保持空；模块报告不能作为产品E2E或发行门禁，结果Excel规范待SOP修订。 2026-10-02新代码候选44379e6已有逐步模块3/3与桌面29/29/typecheck/build原件；source_check独立Excel导出程序仍缺，批次登记BLOCKED，产品E2E仍NOT_RUN。 固定导出器新run tm003-core-20261001T163807Z在ea6b187候选生成3/3/9步source_check独立Excel并回读PASS，现已按被测SHA登记模块批次；原27条产品TC与发行仍NOT_RUN。 新清理合同候选d7c3d39的独立run tm003-core-20261001T165439Z亦3/3/9步及Excel回读PASS，作为最新模块批次；旧ea6批次保留。 后续CORE-04/05的测试输入已编制，程序未绑定、未执行；独立SOP-008切片复核待文档干净提交。 CORE04/05基于9efc6fa独立source_check 2/2、9步和Excel回读PASS，第17批次；CORE06新输入未执行，产品E2E NOT_RUN。 CORE06在eef956b的固定</x:v>
       </x:c>
       <x:c r="K8" s="9" t="str">
         <x:v>TM-001 干净源码候选为技术基底；其产品门禁不继承给TM-003</x:v>
@@ -21659,101 +21753,69 @@
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="162" customHeight="1">
+    <x:row r="9" ht="72" customHeight="1">
       <x:c r="A9" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z（续1）</x:v>
+      </x:c>
+      <x:c r="B9" s="4" t="str"/>
+      <x:c r="C9" s="16" t="str"/>
+      <x:c r="D9" s="4" t="str"/>
+      <x:c r="E9" s="4" t="str"/>
+      <x:c r="F9" s="4" t="str"/>
+      <x:c r="G9" s="4" t="str"/>
+      <x:c r="H9" s="4" t="str"/>
+      <x:c r="I9" s="4" t="str"/>
+      <x:c r="J9" s="4" t="str">
+        <x:v>source_check 1/1、四步与清理PASS，独立Excel回读PASS，第18批次；此前408ebf8红测失败保留。仅多文件模块，原27条产品TC与正式发行NOT_RUN。</x:v>
+      </x:c>
+      <x:c r="K9" s="4" t="str"/>
+      <x:c r="L9" s="4" t="str"/>
+      <x:c r="M9" s="4" t="str"/>
+      <x:c r="N9" s="4" t="str"/>
+      <x:c r="O9" s="4" t="str"/>
+      <x:c r="P9" s="4" t="str"/>
+      <x:c r="Q9" s="4" t="str"/>
+      <x:c r="R9" s="4" t="str"/>
+    </x:row>
+    <x:row r="10" ht="237" customHeight="1">
+      <x:c r="A10" s="9" t="str">
         <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
-      <x:c r="B9" s="4" t="str">
+      <x:c r="B10" s="9" t="str">
         <x:v>0.4.0</x:v>
       </x:c>
-      <x:c r="C9" s="16" t="n">
+      <x:c r="C10" s="17" t="n">
         <x:v>46296.16982638889</x:v>
-      </x:c>
-      <x:c r="D9" s="4" t="str">
-        <x:v>产品功能</x:v>
-      </x:c>
-      <x:c r="E9" s="4" t="str">
-        <x:v>TM-004</x:v>
-      </x:c>
-      <x:c r="F9" s="4" t="str">
-        <x:v>未发布</x:v>
-      </x:c>
-      <x:c r="G9" s="4" t="str">
-        <x:v>internal</x:v>
-      </x:c>
-      <x:c r="H9" s="4" t="str">
-        <x:v>dmg/&lt;release_id&gt;/：仅门禁PASS后放正式DMG</x:v>
-      </x:c>
-      <x:c r="I9" s="15" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J9" s="4" t="str">
-        <x:v>整版draft、未发布。原20产品细TC及四组摘要保留，3条reader CORE辅助TC在输入提交fea41fe/同步SOP后的干净候选ebbcfd0上按SOP-008独立判为development_slice_ready；程序绑定仍空。本版代码分支e52b62e报告reader目标9/9、桌面49/49和build PASS，仅为模块原件，Excel/总表批次尚无固定导出器。产品授权、稳定文件身份最终接口、SQLite原子事务、IPC/App E2E未验证，正式发行门禁NOT_RUN。</x:v>
-      </x:c>
-      <x:c r="K9" s="4" t="str">
-        <x:v>TM004源分支原生零/缺失与nested Agent定向探针仅为研究证据；0.3及此前稳定原包尚未形成，真实升级BLOCKED。</x:v>
-      </x:c>
-      <x:c r="L9" s="4" t="str">
-        <x:v>releases/v0.4.0-20261001T040433Z/00-manifest.json</x:v>
-      </x:c>
-      <x:c r="M9" s="4" t="str">
-        <x:v>releases/v0.4.0-20261001T040433Z/06-iteration-record.md</x:v>
-      </x:c>
-      <x:c r="N9" s="4" t="str">
-        <x:v>未核实同名远端功能分支SHA/tree</x:v>
-      </x:c>
-      <x:c r="O9" s="4" t="str">
-        <x:v>最终包产品E2E未执行；本机稳定包未归档</x:v>
-      </x:c>
-      <x:c r="P9" s="4" t="str">
-        <x:v>全部目标版本稳定后待办</x:v>
-      </x:c>
-      <x:c r="Q9" s="4" t="str">
-        <x:v>远端master读回后逐版待办</x:v>
-      </x:c>
-      <x:c r="R9" s="4" t="str">
-        <x:v>未提供</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="267" customHeight="1">
-      <x:c r="A10" s="9" t="str">
-        <x:v>v0.5.0-20261001T034729Z</x:v>
-      </x:c>
-      <x:c r="B10" s="9" t="str">
-        <x:v>0.5.0</x:v>
-      </x:c>
-      <x:c r="C10" s="17" t="n">
-        <x:v>46296.15797453704</x:v>
       </x:c>
       <x:c r="D10" s="9" t="str">
         <x:v>产品功能</x:v>
       </x:c>
       <x:c r="E10" s="9" t="str">
-        <x:v>TM-005</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="F10" s="9" t="str">
-        <x:v>draft</x:v>
+        <x:v>未发布</x:v>
       </x:c>
       <x:c r="G10" s="9" t="str">
         <x:v>internal</x:v>
       </x:c>
       <x:c r="H10" s="9" t="str">
-        <x:v>dmg/&lt;release_id&gt;/：仅门禁PASS后放正式原名包</x:v>
+        <x:v>dmg/&lt;release_id&gt;/：仅门禁PASS后放正式DMG</x:v>
       </x:c>
       <x:c r="I10" s="18" t="b">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J10" s="9" t="str">
-        <x:v>整版draft、未发布。原32条产品父TC、6稳定变体和两组摘要保留；纯统计CORE-01/02/03辅助TC在输入提交061c759后，经SOP-008内容核对及结构/治理457项PASS，独立切片development_slice_ready，程序绑定仍为空、模块实际运行unexecuted。静态oracle与切片就绪不证明真实双来源采集或产品E2E；固定产品数据、SQLite/IPC、安装App逐TC绑定未完成，正式发行完整门禁NOT_RUN。 独立代码提交6a0f6f的source_check CORE3/3、桌面29/29、build PASS，原件在TM005工作树.local/tm005-core-postcommit-20261001T162401Z；程序尚未进入本文档树、模块Excel导出/批次登记BLOCKED，产品E2E仍NOT_RUN。 CORE-01仅验证已给UTC半开界聚合，不验证IANA日期换算；该单独辅助TC待固定。</x:v>
+        <x:v>整版draft、未发布。原20产品细TC及四组摘要保留，3条reader CORE辅助TC在输入提交fea41fe/同步SOP后的干净候选ebbcfd0上按SOP-008独立判为development_slice_ready；程序绑定仍空。本版代码分支e52b62e报告reader目标9/9、桌面49/49和build PASS，仅为模块原件，Excel/总表批次尚无固定导出器。产品授权、稳定文件身份最终接口、SQLite原子事务、IPC/App E2E未验证，正式发行门禁NOT_RUN。 新增CORE04/05合成主进程触发及三文件存储辅助输入：拒绝码、提交守卫、来源/根分域HMAC、scope代号、modelId哨兵与整代事务；两例程序未绑定/未运行，原20条产品TC与正式发行NOT_RUN。</x:v>
       </x:c>
       <x:c r="K10" s="9" t="str">
-        <x:v>TM005语义oracle只验证规范化样例；0.4及此前稳定原包尚未形成，真实升级BLOCKED。</x:v>
+        <x:v>TM004源分支原生零/缺失与nested Agent定向探针仅为研究证据；0.3及此前稳定原包尚未形成，真实升级BLOCKED。</x:v>
       </x:c>
       <x:c r="L10" s="9" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/00-manifest.json</x:v>
+        <x:v>releases/v0.4.0-20261001T040433Z/00-manifest.json</x:v>
       </x:c>
       <x:c r="M10" s="9" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/06-iteration-record.md</x:v>
+        <x:v>releases/v0.4.0-20261001T040433Z/06-iteration-record.md</x:v>
       </x:c>
       <x:c r="N10" s="9" t="str">
         <x:v>未核实同名远端功能分支SHA/tree</x:v>
@@ -21771,25 +21833,81 @@
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
+    <x:row r="11" ht="267" customHeight="1">
+      <x:c r="A11" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+      <x:c r="B11" s="4" t="str">
+        <x:v>0.5.0</x:v>
+      </x:c>
+      <x:c r="C11" s="16" t="n">
+        <x:v>46296.15797453704</x:v>
+      </x:c>
+      <x:c r="D11" s="4" t="str">
+        <x:v>产品功能</x:v>
+      </x:c>
+      <x:c r="E11" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="F11" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="G11" s="4" t="str">
+        <x:v>internal</x:v>
+      </x:c>
+      <x:c r="H11" s="4" t="str">
+        <x:v>dmg/&lt;release_id&gt;/：仅门禁PASS后放正式原名包</x:v>
+      </x:c>
+      <x:c r="I11" s="15" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J11" s="4" t="str">
+        <x:v>整版draft、未发布。原32条产品父TC、6稳定变体和两组摘要保留；纯统计CORE-01/02/03辅助TC在输入提交061c759后，经SOP-008内容核对及结构/治理457项PASS，独立切片development_slice_ready，程序绑定仍为空、模块实际运行unexecuted。静态oracle与切片就绪不证明真实双来源采集或产品E2E；固定产品数据、SQLite/IPC、安装App逐TC绑定未完成，正式发行完整门禁NOT_RUN。 独立代码提交6a0f6f的source_check CORE3/3、桌面29/29、build PASS，原件在TM005工作树.local/tm005-core-postcommit-20261001T162401Z；程序尚未进入本文档树、模块Excel导出/批次登记BLOCKED，产品E2E仍NOT_RUN。 CORE-01仅验证已给UTC半开界聚合，不验证IANA日期换算；该单独辅助TC待固定。</x:v>
+      </x:c>
+      <x:c r="K11" s="4" t="str">
+        <x:v>TM005语义oracle只验证规范化样例；0.4及此前稳定原包尚未形成，真实升级BLOCKED。</x:v>
+      </x:c>
+      <x:c r="L11" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/00-manifest.json</x:v>
+      </x:c>
+      <x:c r="M11" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/06-iteration-record.md</x:v>
+      </x:c>
+      <x:c r="N11" s="4" t="str">
+        <x:v>未核实同名远端功能分支SHA/tree</x:v>
+      </x:c>
+      <x:c r="O11" s="4" t="str">
+        <x:v>最终包产品E2E未执行；本机稳定包未归档</x:v>
+      </x:c>
+      <x:c r="P11" s="4" t="str">
+        <x:v>全部目标版本稳定后待办</x:v>
+      </x:c>
+      <x:c r="Q11" s="4" t="str">
+        <x:v>远端master读回后逐版待办</x:v>
+      </x:c>
+      <x:c r="R11" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="F5:F10">
+  <x:conditionalFormatting sqref="F5:F11">
     <x:cfRule type="containsText" dxfId="33" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="34" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="35" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="J5:J10">
+  <x:conditionalFormatting sqref="J5:J11">
     <x:cfRule type="containsText" dxfId="36" priority="4" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="37" priority="5" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="38" priority="6" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="M5:M10">
+  <x:conditionalFormatting sqref="M5:M11">
     <x:cfRule type="containsText" dxfId="39" priority="7" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="40" priority="8" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="41" priority="9" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6603ff5ad4b1416a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05ae6df2a6ec496f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22954,7 +23072,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7dfc65debf24da0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9fd0a65e9add4415"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TokenMeter项目总表.xlsx
+++ b/TokenMeter项目总表.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="Rd2a6d09f77894779"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Rf4e156a1925645dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="Red0433e6efb741c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R86b940aabb4d473e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R9846e0924699427f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R87d79ff2e74b42de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="Rf30adb9bddbd4df5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R33be556776a34e79"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="R1fac0a087b6e4e85"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R7291e1ae66594553"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="Re295b36e23cc4b12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R03da98a060ab4d87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Rc913b7e1ddc34fd9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R5be28f3e8f744c1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R5fb38f2805654721"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R59404c9513e44933"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="Rb1e39f2374b54239"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="Rb5d78ab00f3c4599"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="Rb1c69ee60a984249"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="R171637a30f9a4bbd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R57f8bb6c4f834705"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R4d4ccaff825d4813"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -786,8 +786,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TMTable6" displayName="TMTable6" ref="A4:N276" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:N276"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TMTable6" displayName="TMTable6" ref="A4:N278" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:N278"/>
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="功能编号"/>
     <x:tableColumn id="2" name="用例编号"/>
@@ -1134,8 +1134,8 @@
         <x:v>已登记用例</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:f>COUNTA('05测试用例'!B5:B276)</x:f>
-        <x:v>272</x:v>
+        <x:f>COUNTA('05测试用例'!B5:B278)</x:f>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C8" s="9" t="str">
         <x:v>父用例与具有稳定 ID 的变体各占一行；含未来概要场景</x:v>
@@ -1169,7 +1169,7 @@
         <x:v>界面与治理检查</x:v>
       </x:c>
       <x:c r="B11" s="10" t="n">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C11" s="4" t="str">
         <x:v>辅助检查不能替代产品E2E；稳定变体独立列出</x:v>
@@ -1288,7 +1288,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R112308681a85490a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f67fcf0e7364c95"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1996,7 +1996,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b0d3089fa0541b6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95f5f982d560437b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2145,7 +2145,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc6b07d381f0c44e1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R165491c43adf4f37"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2580,7 +2580,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf01dd68b6584e30"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R665d6ed9fa6a4dfe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3627,7 +3627,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc237592fa63497d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R68ffe26ec25d4c6d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4734,7 +4734,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8580111f2c5649f5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdaf1cb19a5694eb9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7519,7 +7519,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3aa2b3bcebe74fdd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf26d95603cd64ac9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15812,7 +15812,7 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L177" s="4" t="str">
-        <x:v>docs/testing/cases/05-TM-005-usage-statistics.md:21</x:v>
+        <x:v>docs/testing/cases/05-TM-005-usage-statistics.md:23</x:v>
       </x:c>
       <x:c r="M177" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -15858,7 +15858,7 @@
         <x:v>未来概要</x:v>
       </x:c>
       <x:c r="L178" s="9" t="str">
-        <x:v>docs/testing/cases/05-TM-005-usage-statistics.md:38</x:v>
+        <x:v>docs/testing/cases/05-TM-005-usage-statistics.md:40</x:v>
       </x:c>
       <x:c r="M178" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -20532,30 +20532,128 @@
         <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
     </x:row>
+    <x:row r="277" ht="87" customHeight="1">
+      <x:c r="A277" s="4" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B277" s="4" t="str">
+        <x:v>TC-TM005-CORE-04</x:v>
+      </x:c>
+      <x:c r="C277" s="4" t="str">
+        <x:v>IANA当地日半开UTC界</x:v>
+      </x:c>
+      <x:c r="D277" s="4" t="str">
+        <x:v>TASK-TM005-RANGE-QUERY</x:v>
+      </x:c>
+      <x:c r="E277" s="4" t="str">
+        <x:v>模块检查</x:v>
+      </x:c>
+      <x:c r="F277" s="4" t="str">
+        <x:v>tests/fixtures/tm005-iana-core-slice.json；上海/UTC与纽约春秋四日、三种无效输入</x:v>
+      </x:c>
+      <x:c r="G277" s="4" t="str">
+        <x:v>1. 转换上海与UTC固定当地日；分别得到fixture固定24小时UTC半开界，传入事件UTC时刻不变
+2. 转换纽约春秋DST当地日及四类边界时刻；春23小时/秋25小时；before/at_end排除，at_start/before_end纳入
+3. 分别提交无效时区、无效日和非规范日期；invalid_timezone或invalid_local_day；无默认UTC范围/成功零</x:v>
+      </x:c>
+      <x:c r="H277" s="4" t="str">
+        <x:v>准备：无DB
+变化：无DB或系统时间变化
+核验：固定IANA各日UTC半开界、23/25小时、边界包含关系及错误码；无SQL</x:v>
+      </x:c>
+      <x:c r="I277" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J277" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K277" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L277" s="4" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:354</x:v>
+      </x:c>
+      <x:c r="M277" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N277" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="278" ht="132" customHeight="1">
+      <x:c r="A278" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B278" s="9" t="str">
+        <x:v>TC-TM005-CORE-05</x:v>
+      </x:c>
+      <x:c r="C278" s="9" t="str">
+        <x:v>双来源隔离SQLite同窗只读快照</x:v>
+      </x:c>
+      <x:c r="D278" s="9" t="str">
+        <x:v>TASK-TM005-EVENT-CONTRACT
+TASK-TM005-RANGE-QUERY</x:v>
+      </x:c>
+      <x:c r="E278" s="9" t="str">
+        <x:v>模块检查</x:v>
+      </x:c>
+      <x:c r="F278" s="9" t="str">
+        <x:v>tests/fixtures/tm005-sqlite-snapshot-slice.json；A/B双来源330、C异主体、D/E界外、F并发后新快照+55</x:v>
+      </x:c>
+      <x:c r="G278" s="9" t="str">
+        <x:v>1. 固定插入A–E并开启同一读事务；选A/B两调用，input300/output30/total330；C/D/E分别被主体或半开界排除，查询零写
+2. 在同一读事务取来源、模型、明细与逐日点；Codex110/Claude220；未知模型110/sonnet-test220；明细A/B和日点330；缓存读known20+unknown1，子项不加总
+3. 另一连接提交F后复查旧快照，再开新快照；旧事务各视图仍A/B和330；新事务A/B/F三调用、input350/output35/total385、Codex165/Claude220
+4. 查询空日及隐私边界；现有coverage不证明当地空日完整，不能报产品零；库/WAL/输出无原生ID、路径、正文或秘密</x:v>
+      </x:c>
+      <x:c r="H278" s="9" t="str">
+        <x:v>准备：固定准备程序仅在本例owner SQLite经UsageStore.commitBatch提交A–E；启用WAL并记录前态
+变化：查询零写入；另一连接固定提交F后旧读事务仍330，新读事务385
+核验：只读usage_event按主体/source/UTC半开界核对事件、来源/模型/明细/日点与子项未知数；coverage不能证明完整空日</x:v>
+      </x:c>
+      <x:c r="I278" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J278" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K278" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L278" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:362</x:v>
+      </x:c>
+      <x:c r="M278" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N278" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G5:G276">
+  <x:conditionalFormatting sqref="G5:G278">
     <x:cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="I5:I276">
+  <x:conditionalFormatting sqref="I5:I278">
     <x:cfRule type="containsText" dxfId="15" priority="4" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="17" priority="6" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="J5:J276">
+  <x:conditionalFormatting sqref="J5:J278">
     <x:cfRule type="containsText" dxfId="18" priority="7" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="19" priority="8" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="20" priority="9" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="M5:M276">
+  <x:conditionalFormatting sqref="M5:M278">
     <x:cfRule type="containsText" dxfId="21" priority="10" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="22" priority="11" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="23" priority="12" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07055277d0114c75"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50ad1a979e9f49c5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21439,7 +21537,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfef00fe67eeb4ddb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2673db9b28934247"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21833,7 +21931,7 @@
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="267" customHeight="1">
+    <x:row r="11" ht="327" customHeight="1">
       <x:c r="A11" s="4" t="str">
         <x:v>v0.5.0-20261001T034729Z</x:v>
       </x:c>
@@ -21862,7 +21960,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J11" s="4" t="str">
-        <x:v>整版draft、未发布。原32条产品父TC、6稳定变体和两组摘要保留；纯统计CORE-01/02/03辅助TC在输入提交061c759后，经SOP-008内容核对及结构/治理457项PASS，独立切片development_slice_ready，程序绑定仍为空、模块实际运行unexecuted。静态oracle与切片就绪不证明真实双来源采集或产品E2E；固定产品数据、SQLite/IPC、安装App逐TC绑定未完成，正式发行完整门禁NOT_RUN。 独立代码提交6a0f6f的source_check CORE3/3、桌面29/29、build PASS，原件在TM005工作树.local/tm005-core-postcommit-20261001T162401Z；程序尚未进入本文档树、模块Excel导出/批次登记BLOCKED，产品E2E仍NOT_RUN。 CORE-01仅验证已给UTC半开界聚合，不验证IANA日期换算；该单独辅助TC待固定。</x:v>
+        <x:v>整版draft、未发布。原32条产品父TC、6稳定变体和两组摘要保留；纯统计CORE-01/02/03辅助TC在输入提交061c759后，经SOP-008内容核对及结构/治理457项PASS，独立切片development_slice_ready，程序绑定仍为空、模块实际运行unexecuted。静态oracle与切片就绪不证明真实双来源采集或产品E2E；固定产品数据、SQLite/IPC、安装App逐TC绑定未完成，正式发行完整门禁NOT_RUN。 独立代码提交6a0f6f的source_check CORE3/3、桌面29/29、build PASS，原件在TM005工作树.local/tm005-core-postcommit-20261001T162401Z；程序尚未进入本文档树、模块Excel导出/批次登记BLOCKED，产品E2E仍NOT_RUN。 CORE-01仅验证已给UTC半开界聚合，不验证IANA日期换算；该单独辅助TC待固定。 新增CORE04/05固定IANA当地日与合成双来源SQLite只读快照辅助TC，程序null/unexecuted；coverage表无连续空日证明，原32产品TC/6变体与发行仍BLOCKED/NOT_RUN。</x:v>
       </x:c>
       <x:c r="K11" s="4" t="str">
         <x:v>TM005语义oracle只验证规范化样例；0.4及此前稳定原包尚未形成，真实升级BLOCKED。</x:v>
@@ -21907,7 +22005,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05ae6df2a6ec496f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40c2610ef7584128"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23072,7 +23170,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9fd0a65e9add4415"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19dc7b9740c5447e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TokenMeter项目总表.xlsx
+++ b/TokenMeter项目总表.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R03da98a060ab4d87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Rc913b7e1ddc34fd9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R5be28f3e8f744c1d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R5fb38f2805654721"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R59404c9513e44933"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="Rb1e39f2374b54239"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="Rb5d78ab00f3c4599"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="Rb1c69ee60a984249"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="R171637a30f9a4bbd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R57f8bb6c4f834705"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R4d4ccaff825d4813"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="Rfe05154a975845bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Ra3b4b22b95ac43e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R7f533fc21dc34947"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="Rcbce82796618482d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R4acab15c44c645bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R439bef78c4784c60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="Rfb32810f08f8448a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R9d4b22d3f2c3492d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="R5fb85447064a443b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="Reecff22380fc45ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R18d2afb9c5d7434a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -809,8 +809,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TMTable7" displayName="TMTable7" ref="A4:N22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:N22"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TMTable7" displayName="TMTable7" ref="A4:N23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:N23"/>
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="运行批次"/>
     <x:tableColumn id="2" name="版本"/>
@@ -1146,8 +1146,8 @@
         <x:v>测试批次</x:v>
       </x:c>
       <x:c r="B9" s="10" t="n">
-        <x:f>COUNTA('06测试批次'!A5:A22)</x:f>
-        <x:v>18</x:v>
+        <x:f>COUNTA('06测试批次'!A5:A23)</x:f>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C9" s="4" t="str">
         <x:v>06测试批次，每次运行一行，记录独立结果Excel位置</x:v>
@@ -1263,7 +1263,7 @@
         <x:v>DMG及原始证据留本机；Git保存代码、文档和此工作簿</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="72" customHeight="1">
+    <x:row r="20" ht="87" customHeight="1">
       <x:c r="A20" s="9" t="str">
         <x:v>最近登记批次</x:v>
       </x:c>
@@ -1271,7 +1271,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="C20" s="9" t="str">
-        <x:v>source_check · TM-003 CORE-06 固定多文件代际提交与全回滚；非产品E2E：source_check固定CORE06 1/1、四步及owner清理PASS；此前408ebf8红测步骤2 FAIL保留。独立Excel/verification回读PASS。原27条产品TC、App E2E与发行均NOT_RUN。；是否覆盖完整产品回归以批次范围和原始证据为准。</x:v>
+        <x:v>product_e2e · TASK-TM001-LOGIN-AUTH；仅LOGIN-01/02/03/04/08五条固定父TC，安装原DMG的真实App定向回归：原始App定向run五条父TC、11步骤PASS，cleanup_completed=true；前置误加--development的独立run local-7ce07b71ca1240de93c16a437ab7e292在清单预检处5例BLOCKED且App未启动，保留原件不混入本批PASS。其余TM001父TC在709d未运行，旧c291完整门禁FAIL及正式发行NOT_RUN。；是否覆盖完整产品回归以批次范围和原始证据为准。</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="32" customHeight="1">
@@ -1288,7 +1288,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f67fcf0e7364c95"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2a6a9990ee74b4f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1996,7 +1996,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95f5f982d560437b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51fd4f6cad34451f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2145,7 +2145,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R165491c43adf4f37"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbbfdd2f932b9450c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2580,7 +2580,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R665d6ed9fa6a4dfe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3156454378504541"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3627,7 +3627,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R68ffe26ec25d4c6d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97ed798623cb46cd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4734,7 +4734,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdaf1cb19a5694eb9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b9e21e2ae78491c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7519,7 +7519,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf26d95603cd64ac9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59eb394ef4834d88"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7635,7 +7635,7 @@
         <x:v>docs/testing/cases/01a-TM-001-login-scenarios.md:76</x:v>
       </x:c>
       <x:c r="M5" s="4" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-2aa05fb7b2754289a1d77b9ef89bd321</x:v>
       </x:c>
       <x:c r="N5" s="4" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -7682,7 +7682,7 @@
         <x:v>docs/testing/cases/01a-TM-001-login-scenarios.md:92</x:v>
       </x:c>
       <x:c r="M6" s="9" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-2aa05fb7b2754289a1d77b9ef89bd321</x:v>
       </x:c>
       <x:c r="N6" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -7729,7 +7729,7 @@
         <x:v>docs/testing/cases/01a-TM-001-login-scenarios.md:107</x:v>
       </x:c>
       <x:c r="M7" s="4" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-2aa05fb7b2754289a1d77b9ef89bd321</x:v>
       </x:c>
       <x:c r="N7" s="4" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -7776,7 +7776,7 @@
         <x:v>docs/testing/cases/01a-TM-001-login-scenarios.md:122</x:v>
       </x:c>
       <x:c r="M8" s="9" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-2aa05fb7b2754289a1d77b9ef89bd321</x:v>
       </x:c>
       <x:c r="N8" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -7964,7 +7964,7 @@
         <x:v>docs/testing/cases/01a-TM-001-login-scenarios.md:182</x:v>
       </x:c>
       <x:c r="M12" s="9" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-2aa05fb7b2754289a1d77b9ef89bd321</x:v>
       </x:c>
       <x:c r="N12" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -10061,7 +10061,7 @@
 新成员及admin改后状态完整保留，首建不是每次启动清库</x:v>
       </x:c>
       <x:c r="H56" s="9" t="str">
-        <x:v>准备：D-PROD先真实改密；额外成员用批准provision输入，数据绑定待补
+        <x:v>准备：D-PROD先在真实UI改密；固定Playwright程序以离线provision向本例拥有的库添加尾0007的test-extra成员，再读回与重启核对；不接触用户生产库。
 变化：重启不重置散列/账号；重复初始化/错误seed事务拒绝且原行保留；123456仍失效
 只读核验：Q-OWNER、Q-SCHEMA、Q-USERS、Q-AUDIT、Q-INTEGRITY</x:v>
       </x:c>
@@ -20653,7 +20653,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50ad1a979e9f49c5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46bf37bcf6b24826"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21519,25 +21519,69 @@
         <x:v>NOT_RUN</x:v>
       </x:c>
     </x:row>
+    <x:row r="23" ht="72" customHeight="1">
+      <x:c r="A23" s="4" t="str">
+        <x:v>local-2aa05fb7b2754289a1d77b9ef89bd321</x:v>
+      </x:c>
+      <x:c r="B23" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+      <x:c r="C23" s="4" t="str">
+        <x:v>product_e2e</x:v>
+      </x:c>
+      <x:c r="D23" s="4" t="str">
+        <x:v>TASK-TM001-LOGIN-AUTH；仅LOGIN-01/02/03/04/08五条固定父TC，安装原DMG的真实App定向回归</x:v>
+      </x:c>
+      <x:c r="E23" s="4" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F23" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G23" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H23" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I23" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J23" s="4" t="str">
+        <x:v>709d21253a0f88bc703a431cbf3adba3df17e508</x:v>
+      </x:c>
+      <x:c r="K23" s="4" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="L23" s="4" t="str">
+        <x:v>原始App定向run五条父TC、11步骤PASS，cleanup_completed=true；前置误加--development的独立run local-7ce07b71ca1240de93c16a437ab7e292在清单预检处5例BLOCKED且App未启动，保留原件不混入本批PASS。其余TM001父TC在709d未运行，旧c291完整门禁FAIL及正式发行NOT_RUN。</x:v>
+      </x:c>
+      <x:c r="M23" s="4" t="str">
+        <x:v>.local/test-results/local-2aa05fb7b2754289a1d77b9ef89bd321/TokenMeter测试结果-local-2aa05fb7b2754289a1d77b9ef89bd321.xlsx</x:v>
+      </x:c>
+      <x:c r="N23" s="4" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="E5:E22">
+  <x:conditionalFormatting sqref="E5:E23">
     <x:cfRule type="containsText" dxfId="24" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="25" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="26" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="M5:M22">
+  <x:conditionalFormatting sqref="M5:M23">
     <x:cfRule type="containsText" dxfId="27" priority="4" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="28" priority="5" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="29" priority="6" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="N5:N22">
+  <x:conditionalFormatting sqref="N5:N23">
     <x:cfRule type="containsText" dxfId="30" priority="7" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="31" priority="8" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="32" priority="9" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2673db9b28934247"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b1053466448425a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21683,7 +21727,7 @@
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="177" customHeight="1">
+    <x:row r="6" ht="207" customHeight="1">
       <x:c r="A6" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
       </x:c>
@@ -21712,7 +21756,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J6" s="9" t="str">
-        <x:v>开发中，未发布。c291本地master最终包门禁FAIL：116项91 PASS/14 FAIL/11 BLOCKED；9f06cb1修复私有签名输入后开发检查PASS，但新定向App仍FAIL/BLOCKED并有ENOSPC，功能回归未完成。旧d2db551独立候选PASS不转用于新候选。正式发行完整门禁NOT_RUN，无稳定0.1原包。 709d UPDATE-05定向父1+变体13 PASS，后置de081a6导出Excel回读PASS；仅定向，77父TC范围外，旧c291完整门禁FAIL及未发行不变。</x:v>
+        <x:v>开发中，未发布。c291本地master最终包门禁FAIL：116项91 PASS/14 FAIL/11 BLOCKED；9f06cb1修复私有签名输入后开发检查PASS，但新定向App仍FAIL/BLOCKED并有ENOSPC，功能回归未完成。旧d2db551独立候选PASS不转用于新候选。正式发行完整门禁NOT_RUN，无稳定0.1原包。 709d UPDATE-05定向父1+变体13 PASS，后置de081a6导出Excel回读PASS；仅定向，77父TC范围外，旧c291完整门禁FAIL及未发行不变。 709d安装DMG的登录定向五父例/11步原始PASS，独立Excel回读PASS；仍非整版回归，旧c291完整门禁FAIL。</x:v>
       </x:c>
       <x:c r="K6" s="9" t="str">
         <x:v>旧SwiftUI PR #2 已合并、历史双平台六例PASS；不继承给Electron</x:v>
@@ -22005,7 +22049,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40c2610ef7584128"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde003fe1710f4bf0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23170,7 +23214,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19dc7b9740c5447e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8033685bd13348ed"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TokenMeter项目总表.xlsx
+++ b/TokenMeter项目总表.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="Rfe05154a975845bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Ra3b4b22b95ac43e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R7f533fc21dc34947"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="Rcbce82796618482d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R4acab15c44c645bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R439bef78c4784c60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="Rfb32810f08f8448a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R9d4b22d3f2c3492d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="R5fb85447064a443b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="Reecff22380fc45ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R18d2afb9c5d7434a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R40eec56730e94cb3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="R2d0243dab96f4272"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R4f7c2e65804d429e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R7432be5ea61948a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R62b52c4fd3d4449e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="Ra062c60b9f1f4b1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R5304bf93fcdc463c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R88d16b11c9c24d8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="R2033abd9b4934d9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="Raa7b5685110e4847"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R8f4259f914264c18"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -809,8 +809,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TMTable7" displayName="TMTable7" ref="A4:N23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:N23"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TMTable7" displayName="TMTable7" ref="A4:N24" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:N24"/>
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="运行批次"/>
     <x:tableColumn id="2" name="版本"/>
@@ -1146,8 +1146,8 @@
         <x:v>测试批次</x:v>
       </x:c>
       <x:c r="B9" s="10" t="n">
-        <x:f>COUNTA('06测试批次'!A5:A23)</x:f>
-        <x:v>19</x:v>
+        <x:f>COUNTA('06测试批次'!A5:A24)</x:f>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C9" s="4" t="str">
         <x:v>06测试批次，每次运行一行，记录独立结果Excel位置</x:v>
@@ -1263,7 +1263,7 @@
         <x:v>DMG及原始证据留本机；Git保存代码、文档和此工作簿</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="87" customHeight="1">
+    <x:row r="20" ht="72" customHeight="1">
       <x:c r="A20" s="9" t="str">
         <x:v>最近登记批次</x:v>
       </x:c>
@@ -1271,7 +1271,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="C20" s="9" t="str">
-        <x:v>product_e2e · TASK-TM001-LOGIN-AUTH；仅LOGIN-01/02/03/04/08五条固定父TC，安装原DMG的真实App定向回归：原始App定向run五条父TC、11步骤PASS，cleanup_completed=true；前置误加--development的独立run local-7ce07b71ca1240de93c16a437ab7e292在清单预检处5例BLOCKED且App未启动，保留原件不混入本批PASS。其余TM001父TC在709d未运行，旧c291完整门禁FAIL及正式发行NOT_RUN。；是否覆盖完整产品回归以批次范围和原始证据为准。</x:v>
+        <x:v>product_e2e · TASK-TM001-LOGIN-SESSION；仅LOGIN-10/11/12/13/14/15六条固定父TC，真实App定向回归：原始真实App定向run六条父TC、14步骤PASS，cleanup_completed=true；独立Excel/verification PASS。与LOGIN-AUTH为不同run，709d其余TM001父TC未运行；旧c291完整门禁FAIL及正式发行NOT_RUN。；是否覆盖完整产品回归以批次范围和原始证据为准。</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="32" customHeight="1">
@@ -1288,7 +1288,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2a6a9990ee74b4f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R723af0d63ca24a15"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1996,7 +1996,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51fd4f6cad34451f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R808cf99423ce413b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2145,7 +2145,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbbfdd2f932b9450c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1136ecb951694a09"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2580,7 +2580,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3156454378504541"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f769844bef445eb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3627,7 +3627,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97ed798623cb46cd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34b9211cc0704e14"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4734,7 +4734,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b9e21e2ae78491c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c3b6d4310d04cf4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7519,7 +7519,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59eb394ef4834d88"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reefe618ae2574f9e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8058,7 +8058,7 @@
         <x:v>docs/testing/cases/01a-TM-001-login-scenarios.md:212</x:v>
       </x:c>
       <x:c r="M14" s="9" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-1d7d9238f9fd4d389e27cad990a6cb97</x:v>
       </x:c>
       <x:c r="N14" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -8106,7 +8106,7 @@
         <x:v>docs/testing/cases/01a-TM-001-login-scenarios.md:227</x:v>
       </x:c>
       <x:c r="M15" s="4" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-1d7d9238f9fd4d389e27cad990a6cb97</x:v>
       </x:c>
       <x:c r="N15" s="4" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -8154,7 +8154,7 @@
         <x:v>docs/testing/cases/01a-TM-001-login-scenarios.md:243</x:v>
       </x:c>
       <x:c r="M16" s="9" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-1d7d9238f9fd4d389e27cad990a6cb97</x:v>
       </x:c>
       <x:c r="N16" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -8201,7 +8201,7 @@
         <x:v>docs/testing/cases/01a-TM-001-login-scenarios.md:259</x:v>
       </x:c>
       <x:c r="M17" s="4" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-1d7d9238f9fd4d389e27cad990a6cb97</x:v>
       </x:c>
       <x:c r="N17" s="4" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -8248,7 +8248,7 @@
         <x:v>docs/testing/cases/01a-TM-001-login-scenarios.md:274</x:v>
       </x:c>
       <x:c r="M18" s="9" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-1d7d9238f9fd4d389e27cad990a6cb97</x:v>
       </x:c>
       <x:c r="N18" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -8295,7 +8295,7 @@
         <x:v>docs/testing/cases/01a-TM-001-login-scenarios.md:289</x:v>
       </x:c>
       <x:c r="M19" s="4" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-1d7d9238f9fd4d389e27cad990a6cb97</x:v>
       </x:c>
       <x:c r="N19" s="4" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -20653,7 +20653,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46bf37bcf6b24826"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a6423fa3c604459"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21563,25 +21563,69 @@
         <x:v>PASS</x:v>
       </x:c>
     </x:row>
+    <x:row r="24" ht="57" customHeight="1">
+      <x:c r="A24" s="9" t="str">
+        <x:v>local-1d7d9238f9fd4d389e27cad990a6cb97</x:v>
+      </x:c>
+      <x:c r="B24" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+      <x:c r="C24" s="9" t="str">
+        <x:v>product_e2e</x:v>
+      </x:c>
+      <x:c r="D24" s="9" t="str">
+        <x:v>TASK-TM001-LOGIN-SESSION；仅LOGIN-10/11/12/13/14/15六条固定父TC，真实App定向回归</x:v>
+      </x:c>
+      <x:c r="E24" s="9" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F24" s="9" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G24" s="9" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H24" s="9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I24" s="9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J24" s="9" t="str">
+        <x:v>709d21253a0f88bc703a431cbf3adba3df17e508</x:v>
+      </x:c>
+      <x:c r="K24" s="9" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="L24" s="9" t="str">
+        <x:v>原始真实App定向run六条父TC、14步骤PASS，cleanup_completed=true；独立Excel/verification PASS。与LOGIN-AUTH为不同run，709d其余TM001父TC未运行；旧c291完整门禁FAIL及正式发行NOT_RUN。</x:v>
+      </x:c>
+      <x:c r="M24" s="9" t="str">
+        <x:v>.local/test-results/local-1d7d9238f9fd4d389e27cad990a6cb97/TokenMeter测试结果-local-1d7d9238f9fd4d389e27cad990a6cb97.xlsx</x:v>
+      </x:c>
+      <x:c r="N24" s="9" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="E5:E23">
+  <x:conditionalFormatting sqref="E5:E24">
     <x:cfRule type="containsText" dxfId="24" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="25" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="26" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="M5:M23">
+  <x:conditionalFormatting sqref="M5:M24">
     <x:cfRule type="containsText" dxfId="27" priority="4" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="28" priority="5" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="29" priority="6" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="N5:N23">
+  <x:conditionalFormatting sqref="N5:N24">
     <x:cfRule type="containsText" dxfId="30" priority="7" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="31" priority="8" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="32" priority="9" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b1053466448425a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06d2cb7561004b00"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21727,7 +21771,7 @@
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="207" customHeight="1">
+    <x:row r="6" ht="237" customHeight="1">
       <x:c r="A6" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
       </x:c>
@@ -21756,7 +21800,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J6" s="9" t="str">
-        <x:v>开发中，未发布。c291本地master最终包门禁FAIL：116项91 PASS/14 FAIL/11 BLOCKED；9f06cb1修复私有签名输入后开发检查PASS，但新定向App仍FAIL/BLOCKED并有ENOSPC，功能回归未完成。旧d2db551独立候选PASS不转用于新候选。正式发行完整门禁NOT_RUN，无稳定0.1原包。 709d UPDATE-05定向父1+变体13 PASS，后置de081a6导出Excel回读PASS；仅定向，77父TC范围外，旧c291完整门禁FAIL及未发行不变。 709d安装DMG的登录定向五父例/11步原始PASS，独立Excel回读PASS；仍非整版回归，旧c291完整门禁FAIL。</x:v>
+        <x:v>开发中，未发布。c291本地master最终包门禁FAIL：116项91 PASS/14 FAIL/11 BLOCKED；9f06cb1修复私有签名输入后开发检查PASS，但新定向App仍FAIL/BLOCKED并有ENOSPC，功能回归未完成。旧d2db551独立候选PASS不转用于新候选。正式发行完整门禁NOT_RUN，无稳定0.1原包。 709d UPDATE-05定向父1+变体13 PASS，后置de081a6导出Excel回读PASS；仅定向，77父TC范围外，旧c291完整门禁FAIL及未发行不变。 709d安装DMG的登录定向五父例/11步原始PASS，独立Excel回读PASS；仍非整版回归，旧c291完整门禁FAIL。 709d LOGIN-SESSION另六父例/14步原始PASS并单独导出Excel；未完成整版回归。</x:v>
       </x:c>
       <x:c r="K6" s="9" t="str">
         <x:v>旧SwiftUI PR #2 已合并、历史双平台六例PASS；不继承给Electron</x:v>
@@ -22049,7 +22093,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde003fe1710f4bf0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45b56c3c45a94b44"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23214,7 +23258,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8033685bd13348ed"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8fffb01a21df4546"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TokenMeter项目总表.xlsx
+++ b/TokenMeter项目总表.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R40eec56730e94cb3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="R2d0243dab96f4272"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R4f7c2e65804d429e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R7432be5ea61948a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R62b52c4fd3d4449e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="Ra062c60b9f1f4b1c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R5304bf93fcdc463c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R88d16b11c9c24d8e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="R2033abd9b4934d9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="Raa7b5685110e4847"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R8f4259f914264c18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R8cdafae5ccab484a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Rcb8f66cdc3514d53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R28ce7a812c584bb9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="Ra0fe381165cd4a19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R4533929afd8f4c9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="Rf65a19c6ff634f23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R7f4d35d8ac554b24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R84e315dc370e4a55"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="R73cb57d499cc4b22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="Re986d5fc29994387"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="Re668346564824b45"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1288,7 +1288,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R723af0d63ca24a15"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a2e04e222b54c30"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1996,7 +1996,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R808cf99423ce413b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R81c65f4b63f14b8f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2145,7 +2145,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1136ecb951694a09"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c51b6908a3a4dc2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2580,7 +2580,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f769844bef445eb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf58f71e53f784f76"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3627,7 +3627,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34b9211cc0704e14"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc659f5cd08f4353"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4734,7 +4734,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c3b6d4310d04cf4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc94bbc0bb40546f2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7519,7 +7519,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reefe618ae2574f9e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R931bb2c1ca274f7b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20653,7 +20653,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a6423fa3c604459"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc90cfc758c1542e4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21625,7 +21625,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06d2cb7561004b00"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c8c0c3c927249f8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21827,7 +21827,7 @@
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="282" customHeight="1">
+    <x:row r="7" ht="342" customHeight="1">
       <x:c r="A7" s="4" t="str">
         <x:v>v0.2.0-20261001T034118Z</x:v>
       </x:c>
@@ -21856,7 +21856,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J7" s="4" t="str">
-        <x:v>设计基线已完成：3功能点、9 TASK、28父TC、35变体。开发工作树已有原生目录面板、加密locator、根FD受限读取、React授权UI及33个固定E2E叶入口（28可执行、5场景摘要）；报告单元59/59、治理473/473、构建PASS。产品E2E因AX trusted=false及隔离标准测试账号不可用BLOCKED，Keychain最终包隔离未证实。本独立文档树未合该代码，机器绑定仍planned；正式发行完整门禁NOT_RUN、未发布。0.2公开配置为version0.2.0/build200及测试高版0.2.1/build201，实际0.2包尚未证明。 2026-10-02修订SECURITY-01三个恶意字串变体的固定IPC method/字段/错误码，产品状态不变；需在整合候选重核基线及固定程序。 EVIDENCE-01新增第七固定负例，本版36变体；SECURITY-01仅profile准备目录纠错。新输入未执行，产品E2E仍NOT_RUN。</x:v>
+        <x:v>设计基线已完成：3功能点、9 TASK、28父TC、35变体。开发工作树已有原生目录面板、加密locator、根FD受限读取、React授权UI及33个固定E2E叶入口（28可执行、5场景摘要）；报告单元59/59、治理473/473、构建PASS。产品E2E因AX trusted=false及隔离标准测试账号不可用BLOCKED，Keychain最终包隔离未证实。本独立文档树未合该代码，机器绑定仍planned；正式发行完整门禁NOT_RUN、未发布。0.2公开配置为version0.2.0/build200及测试高版0.2.1/build201，实际0.2包尚未证明。 2026-10-02修订SECURITY-01三个恶意字串变体的固定IPC method/字段/错误码，产品状态不变；需在整合候选重核基线及固定程序。 EVIDENCE-01新增第七固定负例，本版36变体；SECURITY-01仅profile准备目录纠错。新输入未执行，产品E2E仍NOT_RUN。 0cc4f3e候选包预检33条全BLOCKED、零产品步骤；缺显式独立test/excluded账号，App未启动；固定结果Excel缺失，根总表批次待登记。</x:v>
       </x:c>
       <x:c r="K7" s="4" t="str">
         <x:v>TM001独立候选d2门禁PASS只属历史；本地master c2911bc首次最终包门禁FAIL、无SOP-020稳定原包，不能作为0.2升级源；本版无实际产品运行。</x:v>
@@ -22093,7 +22093,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45b56c3c45a94b44"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ef5d7f22e44442b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23258,7 +23258,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8fffb01a21df4546"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8347536de86f4d49"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TokenMeter项目总表.xlsx
+++ b/TokenMeter项目总表.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R8cdafae5ccab484a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Rcb8f66cdc3514d53"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R28ce7a812c584bb9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="Ra0fe381165cd4a19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R4533929afd8f4c9d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="Rf65a19c6ff634f23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R7f4d35d8ac554b24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R84e315dc370e4a55"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="R73cb57d499cc4b22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="Re986d5fc29994387"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="Re668346564824b45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R6859e9789eaa4df4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="R4640075aba8a46ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R60a530bf23a54544"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R2359c002b9c04b97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R576e404900d24273"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R4abac05370484d31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R404411f10c8b4644"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R42b671ea6dee41d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Red5216beacbc41fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R980a7298878d4026"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R55e5b945aebc4eb0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -786,8 +786,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TMTable6" displayName="TMTable6" ref="A4:N278" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:N278"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TMTable6" displayName="TMTable6" ref="A4:N279" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:N279"/>
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="功能编号"/>
     <x:tableColumn id="2" name="用例编号"/>
@@ -1134,8 +1134,8 @@
         <x:v>已登记用例</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:f>COUNTA('05测试用例'!B5:B278)</x:f>
-        <x:v>274</x:v>
+        <x:f>COUNTA('05测试用例'!B5:B279)</x:f>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="C8" s="9" t="str">
         <x:v>父用例与具有稳定 ID 的变体各占一行；含未来概要场景</x:v>
@@ -1169,7 +1169,7 @@
         <x:v>界面与治理检查</x:v>
       </x:c>
       <x:c r="B11" s="10" t="n">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C11" s="4" t="str">
         <x:v>辅助检查不能替代产品E2E；稳定变体独立列出</x:v>
@@ -1288,7 +1288,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a2e04e222b54c30"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86fe8959df4e4996"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1996,7 +1996,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R81c65f4b63f14b8f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8261aaa075b24b03"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2145,7 +2145,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c51b6908a3a4dc2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6de93d56ad0c49f8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2580,7 +2580,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf58f71e53f784f76"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc67abf79e706473f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3627,7 +3627,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc659f5cd08f4353"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14b7815ba70e4401"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4734,7 +4734,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc94bbc0bb40546f2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc59ced9c7c9e4ae9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7519,7 +7519,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R931bb2c1ca274f7b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R417c62f167974b9f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18586,7 +18586,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L236" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:251</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:265</x:v>
       </x:c>
       <x:c r="M236" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -18633,7 +18633,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L237" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:255</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:269</x:v>
       </x:c>
       <x:c r="M237" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -18680,7 +18680,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L238" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:259</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:273</x:v>
       </x:c>
       <x:c r="M238" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -18728,7 +18728,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L239" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:263</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:277</x:v>
       </x:c>
       <x:c r="M239" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -18778,7 +18778,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L240" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:267</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:281</x:v>
       </x:c>
       <x:c r="M240" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -18826,7 +18826,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L241" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:271</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:285</x:v>
       </x:c>
       <x:c r="M241" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -18873,7 +18873,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L242" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:275</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:289</x:v>
       </x:c>
       <x:c r="M242" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -18920,7 +18920,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L243" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:279</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:293</x:v>
       </x:c>
       <x:c r="M243" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -18968,7 +18968,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L244" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:283</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:297</x:v>
       </x:c>
       <x:c r="M244" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19017,7 +19017,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L245" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:287</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:301</x:v>
       </x:c>
       <x:c r="M245" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19066,7 +19066,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L246" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:291</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:305</x:v>
       </x:c>
       <x:c r="M246" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19115,7 +19115,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L247" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:295</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:309</x:v>
       </x:c>
       <x:c r="M247" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19162,7 +19162,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L248" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:299</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:313</x:v>
       </x:c>
       <x:c r="M248" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19210,7 +19210,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L249" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:303</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:317</x:v>
       </x:c>
       <x:c r="M249" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19258,7 +19258,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L250" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:307</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:321</x:v>
       </x:c>
       <x:c r="M250" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19306,7 +19306,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L251" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:311</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:325</x:v>
       </x:c>
       <x:c r="M251" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19354,7 +19354,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L252" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:315</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:329</x:v>
       </x:c>
       <x:c r="M252" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19404,7 +19404,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L253" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:319</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:333</x:v>
       </x:c>
       <x:c r="M253" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19451,7 +19451,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L254" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:323</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:337</x:v>
       </x:c>
       <x:c r="M254" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19498,7 +19498,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L255" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:327</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:341</x:v>
       </x:c>
       <x:c r="M255" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19546,7 +19546,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L256" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:331</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:345</x:v>
       </x:c>
       <x:c r="M256" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19595,7 +19595,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L257" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:335</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:349</x:v>
       </x:c>
       <x:c r="M257" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19645,7 +19645,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L258" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:339</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:353</x:v>
       </x:c>
       <x:c r="M258" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19693,7 +19693,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L259" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:343</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:357</x:v>
       </x:c>
       <x:c r="M259" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19742,7 +19742,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L260" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:347</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:361</x:v>
       </x:c>
       <x:c r="M260" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19790,7 +19790,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L261" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:351</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:365</x:v>
       </x:c>
       <x:c r="M261" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19838,7 +19838,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L262" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:355</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:369</x:v>
       </x:c>
       <x:c r="M262" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19886,7 +19886,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L263" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:359</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:373</x:v>
       </x:c>
       <x:c r="M263" s="4" t="str">
         <x:v>tm003-core-20261001T165439Z (source_check；产品E2E未运行)</x:v>
@@ -19935,7 +19935,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L264" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:363</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:377</x:v>
       </x:c>
       <x:c r="M264" s="9" t="str">
         <x:v>tm003-core-20261001T165439Z (source_check；产品E2E未运行)</x:v>
@@ -19983,7 +19983,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L265" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:367</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:381</x:v>
       </x:c>
       <x:c r="M265" s="4" t="str">
         <x:v>tm003-core-20261001T165439Z (source_check；产品E2E未运行)</x:v>
@@ -20142,79 +20142,81 @@
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="269" ht="87" customHeight="1">
+    <x:row r="269" ht="117" customHeight="1">
       <x:c r="A269" s="4" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B269" s="4" t="str">
+        <x:v>TC-TM003-CORE-07</x:v>
+      </x:c>
+      <x:c r="C269" s="4" t="str">
+        <x:v>主进程采集编排与能力失效</x:v>
+      </x:c>
+      <x:c r="D269" s="4" t="str">
+        <x:v>TASK-TM003-SCAN
+TASK-TM003-STORE</x:v>
+      </x:c>
+      <x:c r="E269" s="4" t="str">
+        <x:v>模块检查</x:v>
+      </x:c>
+      <x:c r="F269" s="4" t="str">
+        <x:v>固定同代际两页file-a/file-b各410字节、假readCandidateChunk每次最多返128字节、65536请求上限、公开HMAC root/file键向量；坏sourceId/主体/采集授权、提前EOF/读异常/1025字节元数据对1024注入暂存预算、撤权/切换主体；五步。</x:v>
+      </x:c>
+      <x:c r="G269" s="4" t="str">
+        <x:v>扫描前拒绝；beginCandidateScan与commitScanBatch调用0次，不写事件/游标/覆盖，不接受renderer路径/账号/密钥
+第一页无落库；末页完整稳定后A/B两事件、input300/output30/cached60/total330，两游标各410、coverage.scan_incomplete=0，commitScanBatch1次，cancelScan1次且无私密哨兵
+三路径均取消、提交0次、四表无行；请求≤65536，超预算在完整Buffer分配前失败，不截断正文后提交
+守卫拒绝、cancelScan各1次、同步提交0次，旧主体暂存不写新主体
+根/文件HMAC键及调用身份稳定，A/B仍各一、total330、游标各410，重扫仍经守卫和关闭，不输出私密哨兵</x:v>
+      </x:c>
+      <x:c r="H269" s="4" t="str">
+        <x:v>准备：每个故障变体本例owner0700根/0600新SQLite；事件只经正式解析/UsageStore；公开测试key不进入产品profile
+变化：仅完整稳定且guard通过的两页代际一次事务入A/B；所有预检、读取、容量和失权故障零提交；重扫去重
+核验：逐步只读usage_event数量/聚合/HMAC键、source_cursor两个偏移/prefixMAC、collection_diagnostic、coverage和库/WAL私密哨兵；核fake端口调用顺序/次数及owner清理</x:v>
+      </x:c>
+      <x:c r="I269" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J269" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K269" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L269" s="4" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:243</x:v>
+      </x:c>
+      <x:c r="M269" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N269" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="270" ht="87" customHeight="1">
+      <x:c r="A270" s="9" t="str">
         <x:v>TM-005</x:v>
       </x:c>
-      <x:c r="B269" s="4" t="str">
+      <x:c r="B270" s="9" t="str">
         <x:v>TC-TM005-CORE-01</x:v>
       </x:c>
-      <x:c r="C269" s="4" t="str">
+      <x:c r="C270" s="9" t="str">
         <x:v>双来源可信事件与半开日汇总</x:v>
       </x:c>
-      <x:c r="D269" s="4" t="str">
+      <x:c r="D270" s="9" t="str">
         <x:v>TASK-TM005-EVENT-CONTRACT
 TASK-TM005-RANGE-QUERY</x:v>
       </x:c>
-      <x:c r="E269" s="4" t="str">
+      <x:c r="E270" s="9" t="str">
         <x:v>模块检查</x:v>
       </x:c>
-      <x:c r="F269" s="4" t="str">
+      <x:c r="F270" s="9" t="str">
         <x:v>fixture的A/B、跨主体C、界外D/E；synthetic-p1、Asia/Shanghai当地日2026-09-29</x:v>
       </x:c>
-      <x:c r="G269" s="4" t="str">
+      <x:c r="G270" s="9" t="str">
         <x:v>1. 按固定主体和fixture固定UTC半开界查询纯统计函数，不做IANA日期换算；仅A/B被选、C/D/E排除；输入数组和键不变
 2. 核对来源、模型、Token和三个子项；input300/output30/total330；Codex110/Claude220；未知模型110/sonnet-test220；缓存读20但部分未知、缓存写未知、推理2但部分未知，子项不加总
 3. 逐个输入非法来源、负数、超范围缓存和坏UTC；各自被拒绝，无完整零或有效汇总输出；原fixture不变</x:v>
-      </x:c>
-      <x:c r="H269" s="4" t="str">
-        <x:v>准备：无产品DB写入；每例从新内存输入开始
-变化：不适用；纯统计返回值与输入未变
-核验：固定fixture摘要、事件筛选、各字段与状态逐步核对；无SQL</x:v>
-      </x:c>
-      <x:c r="I269" s="4" t="str">
-        <x:v>draft</x:v>
-      </x:c>
-      <x:c r="J269" s="4" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="K269" s="4" t="str">
-        <x:v>细化用例</x:v>
-      </x:c>
-      <x:c r="L269" s="4" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:326</x:v>
-      </x:c>
-      <x:c r="M269" s="4" t="str">
-        <x:v>尚未执行</x:v>
-      </x:c>
-      <x:c r="N269" s="4" t="str">
-        <x:v>v0.5.0-20261001T034729Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="270" ht="57" customHeight="1">
-      <x:c r="A270" s="9" t="str">
-        <x:v>TM-005</x:v>
-      </x:c>
-      <x:c r="B270" s="9" t="str">
-        <x:v>TC-TM005-CORE-02</x:v>
-      </x:c>
-      <x:c r="C270" s="9" t="str">
-        <x:v>未知用量诊断不补零</x:v>
-      </x:c>
-      <x:c r="D270" s="9" t="str">
-        <x:v>TASK-TM005-EVENT-CONTRACT
-TASK-TM005-COVERAGE</x:v>
-      </x:c>
-      <x:c r="E270" s="9" t="str">
-        <x:v>模块检查</x:v>
-      </x:c>
-      <x:c r="F270" s="9" t="str">
-        <x:v>fixture A/B及同范围Claude missing_usage诊断；双来源complete仅为模块合成覆盖假设</x:v>
-      </x:c>
-      <x:c r="G270" s="9" t="str">
-        <x:v>1. 先仅统计A/B；已知330，未知模型110保留，来源Codex110/Claude220
-2. 加入诊断重新统计；partial、known_tokens330、total_tokens=null；诊断不增调用或零Token
-3. 移除A/B仅保留诊断；unknown、known_tokens0、total_tokens=null，不能写已确认零</x:v>
       </x:c>
       <x:c r="H270" s="9" t="str">
         <x:v>准备：无产品DB写入；每例从新内存输入开始
@@ -20231,7 +20233,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L270" s="9" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:334</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:326</x:v>
       </x:c>
       <x:c r="M270" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -20240,29 +20242,30 @@
         <x:v>v0.5.0-20261001T034729Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="271" ht="87" customHeight="1">
+    <x:row r="271" ht="57" customHeight="1">
       <x:c r="A271" s="4" t="str">
         <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B271" s="4" t="str">
-        <x:v>TC-TM005-CORE-03</x:v>
+        <x:v>TC-TM005-CORE-02</x:v>
       </x:c>
       <x:c r="C271" s="4" t="str">
-        <x:v>声明式覆盖状态代数</x:v>
+        <x:v>未知用量诊断不补零</x:v>
       </x:c>
       <x:c r="D271" s="4" t="str">
-        <x:v>TASK-TM005-COVERAGE</x:v>
+        <x:v>TASK-TM005-EVENT-CONTRACT
+TASK-TM005-COVERAGE</x:v>
       </x:c>
       <x:c r="E271" s="4" t="str">
         <x:v>模块检查</x:v>
       </x:c>
       <x:c r="F271" s="4" t="str">
-        <x:v>fixture五行coverage_algebra；complete仅为模块合成输入，product_coverage_proven=false</x:v>
+        <x:v>fixture A/B及同范围Claude missing_usage诊断；双来源complete仅为模块合成覆盖假设</x:v>
       </x:c>
       <x:c r="G271" s="4" t="str">
-        <x:v>1. 两来源complete且无事件、随后移除覆盖事实；前者complete/known0/total0；后者不得自行推断complete
-2. 一来源missing，分别给空事件与可信110；空事件missing/known0/total null；可信110为partial/known110/total null
-3. 两来源complete，分别给可信110+未知诊断、仅未知诊断；前者partial/known110/total null；后者unknown/known0/total null</x:v>
+        <x:v>1. 先仅统计A/B；已知330，未知模型110保留，来源Codex110/Claude220
+2. 加入诊断重新统计；partial、known_tokens330、total_tokens=null；诊断不增调用或零Token
+3. 移除A/B仅保留诊断；unknown、known_tokens0、total_tokens=null，不能写已确认零</x:v>
       </x:c>
       <x:c r="H271" s="4" t="str">
         <x:v>准备：无产品DB写入；每例从新内存输入开始
@@ -20279,7 +20282,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L271" s="4" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:342</x:v>
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:334</x:v>
       </x:c>
       <x:c r="M271" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -20288,77 +20291,77 @@
         <x:v>v0.5.0-20261001T034729Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="272" ht="72" customHeight="1">
+    <x:row r="272" ht="87" customHeight="1">
       <x:c r="A272" s="9" t="str">
-        <x:v>TM-004</x:v>
+        <x:v>TM-005</x:v>
       </x:c>
       <x:c r="B272" s="9" t="str">
-        <x:v>TC-TM004-CORE-01</x:v>
+        <x:v>TC-TM005-CORE-03</x:v>
       </x:c>
       <x:c r="C272" s="9" t="str">
-        <x:v>完整LF、半行与限额续读</x:v>
+        <x:v>声明式覆盖状态代数</x:v>
       </x:c>
       <x:c r="D272" s="9" t="str">
-        <x:v>TASK-TM004-INCREMENTAL</x:v>
+        <x:v>TASK-TM005-COVERAGE</x:v>
       </x:c>
       <x:c r="E272" s="9" t="str">
         <x:v>模块检查</x:v>
       </x:c>
       <x:c r="F272" s="9" t="str">
+        <x:v>fixture五行coverage_algebra；complete仅为模块合成输入，product_coverage_proven=false</x:v>
+      </x:c>
+      <x:c r="G272" s="9" t="str">
+        <x:v>1. 两来源complete且无事件、随后移除覆盖事实；前者complete/known0/total0；后者不得自行推断complete
+2. 一来源missing，分别给空事件与可信110；空事件missing/known0/total null；可信110为partial/known110/total null
+3. 两来源complete，分别给可信110+未知诊断、仅未知诊断；前者partial/known110/total null；后者unknown/known0/total null</x:v>
+      </x:c>
+      <x:c r="H272" s="9" t="str">
+        <x:v>准备：无产品DB写入；每例从新内存输入开始
+变化：不适用；纯统计返回值与输入未变
+核验：固定fixture摘要、事件筛选、各字段与状态逐步核对；无SQL</x:v>
+      </x:c>
+      <x:c r="I272" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J272" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K272" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L272" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:342</x:v>
+      </x:c>
+      <x:c r="M272" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N272" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="273" ht="72" customHeight="1">
+      <x:c r="A273" s="4" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="B273" s="4" t="str">
+        <x:v>TC-TM004-CORE-01</x:v>
+      </x:c>
+      <x:c r="C273" s="4" t="str">
+        <x:v>完整LF、半行与限额续读</x:v>
+      </x:c>
+      <x:c r="D273" s="4" t="str">
+        <x:v>TASK-TM004-INCREMENTAL</x:v>
+      </x:c>
+      <x:c r="E273" s="4" t="str">
+        <x:v>模块检查</x:v>
+      </x:c>
+      <x:c r="F273" s="4" t="str">
         <x:v>固定746字节13/7 assistant行、前半字节、两条不同ID完整行、首读上限754字节</x:v>
       </x:c>
-      <x:c r="G272" s="9" t="str">
+      <x:c r="G273" s="4" t="str">
         <x:v>1. 读未写完的前半行；调用0、偏移0、scanIncomplete=true，不作可信零结论
 2. 补齐LF、重复读取；补齐后一次13/7=20、偏移746、前缀MAC匹配；重复读取0调用且游标不变
 3. 两完整行首读754字节后续读；首读只第一条、偏移746、read_limit且未完成；续读只第二条、偏移为总字节长、完成</x:v>
-      </x:c>
-      <x:c r="H272" s="9" t="str">
-        <x:v>准备：无产品DB；每例新建自有临时文件
-变化：不适用；只返回模块调用、诊断与游标
-核验：固定fixture/行摘要和逐步返回值、前缀MAC及失败时无新游标；无SQL</x:v>
-      </x:c>
-      <x:c r="I272" s="9" t="str">
-        <x:v>draft</x:v>
-      </x:c>
-      <x:c r="J272" s="9" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="K272" s="9" t="str">
-        <x:v>细化用例</x:v>
-      </x:c>
-      <x:c r="L272" s="9" t="str">
-        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:170</x:v>
-      </x:c>
-      <x:c r="M272" s="9" t="str">
-        <x:v>尚未执行</x:v>
-      </x:c>
-      <x:c r="N272" s="9" t="str">
-        <x:v>v0.4.0-20261001T040433Z</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="273" ht="87" customHeight="1">
-      <x:c r="A273" s="4" t="str">
-        <x:v>TM-004</x:v>
-      </x:c>
-      <x:c r="B273" s="4" t="str">
-        <x:v>TC-TM004-CORE-02</x:v>
-      </x:c>
-      <x:c r="C273" s="4" t="str">
-        <x:v>前缀MAC、变更和密钥失败</x:v>
-      </x:c>
-      <x:c r="D273" s="4" t="str">
-        <x:v>TASK-TM004-INCREMENTAL</x:v>
-      </x:c>
-      <x:c r="E273" s="4" t="str">
-        <x:v>模块检查</x:v>
-      </x:c>
-      <x:c r="F273" s="4" t="str">
-        <x:v>已提交首行，追加不同ID第二行、同长度ID改写并复原mtime、截短、身份改变、秘密缺失或错误</x:v>
-      </x:c>
-      <x:c r="G273" s="4" t="str">
-        <x:v>1. 首行后追加第二完整行；size/mtime变化但TM-002 dev/ino摘要和前缀MAC相同，续读只第二调用，无cursor_reset
-2. 同长度前缀改写、截短及稳定身份变更；分别报cursor_reset并从0重扫；同inode/size/mtime也不能忽略MAC不符
-3. 秘密无效或读中源变化；拒绝且没有可提交新游标/可信调用/成功零；输出不含路径正文秘密</x:v>
       </x:c>
       <x:c r="H273" s="4" t="str">
         <x:v>准备：无产品DB；每例新建自有临时文件
@@ -20375,7 +20378,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L273" s="4" t="str">
-        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:178</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:170</x:v>
       </x:c>
       <x:c r="M273" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -20384,30 +20387,29 @@
         <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="274" ht="57" customHeight="1">
+    <x:row r="274" ht="87" customHeight="1">
       <x:c r="A274" s="9" t="str">
         <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B274" s="9" t="str">
-        <x:v>TC-TM004-CORE-03</x:v>
+        <x:v>TC-TM004-CORE-02</x:v>
       </x:c>
       <x:c r="C274" s="9" t="str">
-        <x:v>损坏完整行与未知结构</x:v>
+        <x:v>前缀MAC、变更和密钥失败</x:v>
       </x:c>
       <x:c r="D274" s="9" t="str">
-        <x:v>TASK-TM004-PARSER
-TASK-TM004-INCREMENTAL</x:v>
+        <x:v>TASK-TM004-INCREMENTAL</x:v>
       </x:c>
       <x:c r="E274" s="9" t="str">
         <x:v>模块检查</x:v>
       </x:c>
       <x:c r="F274" s="9" t="str">
-        <x:v>固定13/7行前置非法UTF8完整行和版本2.1.127完整行，尾部再追加无LF坏字节</x:v>
+        <x:v>已提交首行，追加不同ID第二行、同长度ID改写并复原mtime、截短、身份改变、秘密缺失或错误</x:v>
       </x:c>
       <x:c r="G274" s="9" t="str">
-        <x:v>1. 读三条完整LF行；仅合法2.1.126一条调用13/7=20；invalid_utf8及unsupported_version各一次
-2. 核对游标、重复读取及隐私；游标到三行LF末，MAC匹配且完成；重复读取0；输出无路径、正文、秘密
-3. 追加无LF坏字节再补LF；未补LF前偏移不动且未完成；补LF后仅诊断推进，无伪调用</x:v>
+        <x:v>1. 首行后追加第二完整行；size/mtime变化但TM-002 dev/ino摘要和前缀MAC相同，续读只第二调用，无cursor_reset
+2. 同长度前缀改写、截短及稳定身份变更；分别报cursor_reset并从0重扫；同inode/size/mtime也不能忽略MAC不符
+3. 秘密无效或读中源变化；拒绝且没有可提交新游标/可信调用/成功零；输出不含路径正文秘密</x:v>
       </x:c>
       <x:c r="H274" s="9" t="str">
         <x:v>准备：无产品DB；每例新建自有临时文件
@@ -20424,7 +20426,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L274" s="9" t="str">
-        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:186</x:v>
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:178</x:v>
       </x:c>
       <x:c r="M274" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -20433,227 +20435,276 @@
         <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="275" ht="132" customHeight="1">
+    <x:row r="275" ht="57" customHeight="1">
       <x:c r="A275" s="4" t="str">
         <x:v>TM-004</x:v>
       </x:c>
       <x:c r="B275" s="4" t="str">
+        <x:v>TC-TM004-CORE-03</x:v>
+      </x:c>
+      <x:c r="C275" s="4" t="str">
+        <x:v>损坏完整行与未知结构</x:v>
+      </x:c>
+      <x:c r="D275" s="4" t="str">
+        <x:v>TASK-TM004-PARSER
+TASK-TM004-INCREMENTAL</x:v>
+      </x:c>
+      <x:c r="E275" s="4" t="str">
+        <x:v>模块检查</x:v>
+      </x:c>
+      <x:c r="F275" s="4" t="str">
+        <x:v>固定13/7行前置非法UTF8完整行和版本2.1.127完整行，尾部再追加无LF坏字节</x:v>
+      </x:c>
+      <x:c r="G275" s="4" t="str">
+        <x:v>1. 读三条完整LF行；仅合法2.1.126一条调用13/7=20；invalid_utf8及unsupported_version各一次
+2. 核对游标、重复读取及隐私；游标到三行LF末，MAC匹配且完成；重复读取0；输出无路径、正文、秘密
+3. 追加无LF坏字节再补LF；未补LF前偏移不动且未完成；补LF后仅诊断推进，无伪调用</x:v>
+      </x:c>
+      <x:c r="H275" s="4" t="str">
+        <x:v>准备：无产品DB；每例新建自有临时文件
+变化：不适用；只返回模块调用、诊断与游标
+核验：固定fixture/行摘要和逐步返回值、前缀MAC及失败时无新游标；无SQL</x:v>
+      </x:c>
+      <x:c r="I275" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J275" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K275" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L275" s="4" t="str">
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:186</x:v>
+      </x:c>
+      <x:c r="M275" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N275" s="4" t="str">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="276" ht="132" customHeight="1">
+      <x:c r="A276" s="9" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="B276" s="9" t="str">
         <x:v>TC-TM004-CORE-04</x:v>
       </x:c>
-      <x:c r="C275" s="4" t="str">
+      <x:c r="C276" s="9" t="str">
         <x:v>授权主体与扫描事务触发</x:v>
       </x:c>
-      <x:c r="D275" s="4" t="str">
+      <x:c r="D276" s="9" t="str">
         <x:v>TASK-TM004-SOURCE
 TASK-TM004-INCREMENTAL</x:v>
       </x:c>
-      <x:c r="E275" s="4" t="str">
+      <x:c r="E276" s="9" t="str">
         <x:v>模块检查</x:v>
       </x:c>
-      <x:c r="F275" s="4" t="str">
+      <x:c r="F276" s="9" t="str">
         <x:v>tests/fixtures/tm004-trigger-core-slice.json；固定UUID、M=100/10、各错误码、三种屏障事件及成功返回形状</x:v>
       </x:c>
-      <x:c r="G275" s="4" t="str">
+      <x:c r="G276" s="9" t="str">
         <x:v>1. 拒绝路径字段、无效主体/来源和预先取消的请求；路径字段/坏UUID为invalid_collection_request；账号不可用为collection_unavailable；异主体来源为source_not_authorized；预先取消为collection_cancelled；均扫描0、提交0
 2. 扫描开始后在固定屏障分别换账号、撤权和取消；换账号/撤权为collection_stale，取消为collection_cancelled；每次cancelScan、commitSync=0、缓冲不外露
 3. 健康主体和授权世代扫描完整M并通过提交守卫；commitSync恰一次；返回summary{callCount:1,inputTokens:100,outputTokens:10,totalTokens:110,scanIncomplete:false},diagnostics:[]，无私密哨兵/原生标识</x:v>
       </x:c>
-      <x:c r="H275" s="4" t="str">
+      <x:c r="H276" s="9" t="str">
         <x:v>准备：无产品DB；每子变体新建假端口与计数器
 变化：无SQLite；只观察假同步提交次数及数值
 核验：逐步断言扫描、取消、守卫、提交次数与返回白名单；无SQL</x:v>
       </x:c>
-      <x:c r="I275" s="4" t="str">
+      <x:c r="I276" s="9" t="str">
         <x:v>draft</x:v>
       </x:c>
-      <x:c r="J275" s="4" t="str">
+      <x:c r="J276" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K275" s="4" t="str">
+      <x:c r="K276" s="9" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L275" s="4" t="str">
+      <x:c r="L276" s="9" t="str">
         <x:v>docs/testing/cases/04-TM-004-claude-collection.md:198</x:v>
       </x:c>
-      <x:c r="M275" s="4" t="str">
+      <x:c r="M276" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N275" s="4" t="str">
+      <x:c r="N276" s="9" t="str">
         <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="276" ht="147" customHeight="1">
-      <x:c r="A276" s="9" t="str">
+    <x:row r="277" ht="147" customHeight="1">
+      <x:c r="A277" s="4" t="str">
         <x:v>TM-004</x:v>
       </x:c>
-      <x:c r="B276" s="9" t="str">
+      <x:c r="B277" s="4" t="str">
         <x:v>TC-TM004-CORE-05</x:v>
       </x:c>
-      <x:c r="C276" s="9" t="str">
+      <x:c r="C277" s="4" t="str">
         <x:v>多文件来源键与整代持久映射</x:v>
       </x:c>
-      <x:c r="D276" s="9" t="str">
+      <x:c r="D277" s="4" t="str">
         <x:v>TASK-TM004-INCREMENTAL
 TASK-TM004-LINEAGE</x:v>
       </x:c>
-      <x:c r="E276" s="9" t="str">
+      <x:c r="E277" s="4" t="str">
         <x:v>模块检查</x:v>
       </x:c>
-      <x:c r="F276" s="9" t="str">
+      <x:c r="F277" s="4" t="str">
         <x:v>tests/fixtures/tm004-storage-port-slice.json；合成M100/10、S200/20、Q50/5，三文件HMAC/游标/诊断与隔离SQLite；异常model_id哨兵与invalid_model_id诊断</x:v>
       </x:c>
-      <x:c r="G276" s="9" t="str">
+      <x:c r="G277" s="4" t="str">
         <x:v>1. 计算三个文件来源键、根键及换源/追加/替换向量；64hex键逐一等于fixture；普通追加键不变，换sourceId/文件摘要改变；数据库不收原摘要/相对名
 2. 构造完整三文件generation并核对文件归属与turnId代号；a/b/c各有自己的M/S/Q、游标和诊断；c异常model_id置null并增加invalid_model_id，SQLite/WAL无哨兵；turn代号仅进scope HMAC；未到末页/正文不稳零提交
 3. 分别在新库注入第二游标写失败与guard撤权；每次整代回滚或零开始，事件/游标/诊断/覆盖/密钥标记全空；取消并清缓冲
 4. 稳定末页通过guard后一次同步commitScanBatch并重扫；唯一3调用、input350/output35/total385、3游标/4诊断按文件归属、scan_incomplete=1；scope键匹配向量，重扫不增；SQLite/WAL无模型哨兵/原生标识</x:v>
       </x:c>
-      <x:c r="H276" s="9" t="str">
+      <x:c r="H277" s="4" t="str">
         <x:v>准备：每故障子场景新建本例空SQLite；故障注入只在本例库设置第二游标写入RAISE(ABORT)
 变化：成功一次事务新增三事件、三个游标、三诊断与根覆盖；失败和撤权零提交
 核验：只读查询usage_event、source_cursor、collection_diagnostic、coverage的数量/键/数值；核对源键和scope HMAC向量及无原生标识；关闭并核对SQLite/WAL无合成prompt/路径哨兵</x:v>
       </x:c>
-      <x:c r="I276" s="9" t="str">
+      <x:c r="I277" s="4" t="str">
         <x:v>draft</x:v>
       </x:c>
-      <x:c r="J276" s="9" t="str">
+      <x:c r="J277" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K276" s="9" t="str">
+      <x:c r="K277" s="4" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L276" s="9" t="str">
+      <x:c r="L277" s="4" t="str">
         <x:v>docs/testing/cases/04-TM-004-claude-collection.md:206</x:v>
       </x:c>
-      <x:c r="M276" s="9" t="str">
+      <x:c r="M277" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N276" s="9" t="str">
+      <x:c r="N277" s="4" t="str">
         <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="277" ht="87" customHeight="1">
-      <x:c r="A277" s="4" t="str">
+    <x:row r="278" ht="87" customHeight="1">
+      <x:c r="A278" s="9" t="str">
         <x:v>TM-005</x:v>
       </x:c>
-      <x:c r="B277" s="4" t="str">
+      <x:c r="B278" s="9" t="str">
         <x:v>TC-TM005-CORE-04</x:v>
       </x:c>
-      <x:c r="C277" s="4" t="str">
+      <x:c r="C278" s="9" t="str">
         <x:v>IANA当地日半开UTC界</x:v>
       </x:c>
-      <x:c r="D277" s="4" t="str">
+      <x:c r="D278" s="9" t="str">
         <x:v>TASK-TM005-RANGE-QUERY</x:v>
       </x:c>
-      <x:c r="E277" s="4" t="str">
+      <x:c r="E278" s="9" t="str">
         <x:v>模块检查</x:v>
       </x:c>
-      <x:c r="F277" s="4" t="str">
+      <x:c r="F278" s="9" t="str">
         <x:v>tests/fixtures/tm005-iana-core-slice.json；上海/UTC与纽约春秋四日、三种无效输入</x:v>
       </x:c>
-      <x:c r="G277" s="4" t="str">
+      <x:c r="G278" s="9" t="str">
         <x:v>1. 转换上海与UTC固定当地日；分别得到fixture固定24小时UTC半开界，传入事件UTC时刻不变
 2. 转换纽约春秋DST当地日及四类边界时刻；春23小时/秋25小时；before/at_end排除，at_start/before_end纳入
 3. 分别提交无效时区、无效日和非规范日期；invalid_timezone或invalid_local_day；无默认UTC范围/成功零</x:v>
       </x:c>
-      <x:c r="H277" s="4" t="str">
+      <x:c r="H278" s="9" t="str">
         <x:v>准备：无DB
 变化：无DB或系统时间变化
 核验：固定IANA各日UTC半开界、23/25小时、边界包含关系及错误码；无SQL</x:v>
       </x:c>
-      <x:c r="I277" s="4" t="str">
+      <x:c r="I278" s="9" t="str">
         <x:v>draft</x:v>
       </x:c>
-      <x:c r="J277" s="4" t="str">
+      <x:c r="J278" s="9" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K277" s="4" t="str">
+      <x:c r="K278" s="9" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L277" s="4" t="str">
+      <x:c r="L278" s="9" t="str">
         <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:354</x:v>
       </x:c>
-      <x:c r="M277" s="4" t="str">
+      <x:c r="M278" s="9" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N277" s="4" t="str">
+      <x:c r="N278" s="9" t="str">
         <x:v>v0.5.0-20261001T034729Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="278" ht="132" customHeight="1">
-      <x:c r="A278" s="9" t="str">
+    <x:row r="279" ht="132" customHeight="1">
+      <x:c r="A279" s="4" t="str">
         <x:v>TM-005</x:v>
       </x:c>
-      <x:c r="B278" s="9" t="str">
+      <x:c r="B279" s="4" t="str">
         <x:v>TC-TM005-CORE-05</x:v>
       </x:c>
-      <x:c r="C278" s="9" t="str">
+      <x:c r="C279" s="4" t="str">
         <x:v>双来源隔离SQLite同窗只读快照</x:v>
       </x:c>
-      <x:c r="D278" s="9" t="str">
+      <x:c r="D279" s="4" t="str">
         <x:v>TASK-TM005-EVENT-CONTRACT
 TASK-TM005-RANGE-QUERY</x:v>
       </x:c>
-      <x:c r="E278" s="9" t="str">
+      <x:c r="E279" s="4" t="str">
         <x:v>模块检查</x:v>
       </x:c>
-      <x:c r="F278" s="9" t="str">
+      <x:c r="F279" s="4" t="str">
         <x:v>tests/fixtures/tm005-sqlite-snapshot-slice.json；A/B双来源330、C异主体、D/E界外、F并发后新快照+55</x:v>
       </x:c>
-      <x:c r="G278" s="9" t="str">
+      <x:c r="G279" s="4" t="str">
         <x:v>1. 固定插入A–E并开启同一读事务；选A/B两调用，input300/output30/total330；C/D/E分别被主体或半开界排除，查询零写
 2. 在同一读事务取来源、模型、明细与逐日点；Codex110/Claude220；未知模型110/sonnet-test220；明细A/B和日点330；缓存读known20+unknown1，子项不加总
 3. 另一连接提交F后复查旧快照，再开新快照；旧事务各视图仍A/B和330；新事务A/B/F三调用、input350/output35/total385、Codex165/Claude220
 4. 查询空日及隐私边界；现有coverage不证明当地空日完整，不能报产品零；库/WAL/输出无原生ID、路径、正文或秘密</x:v>
       </x:c>
-      <x:c r="H278" s="9" t="str">
+      <x:c r="H279" s="4" t="str">
         <x:v>准备：固定准备程序仅在本例owner SQLite经UsageStore.commitBatch提交A–E；启用WAL并记录前态
 变化：查询零写入；另一连接固定提交F后旧读事务仍330，新读事务385
 核验：只读usage_event按主体/source/UTC半开界核对事件、来源/模型/明细/日点与子项未知数；coverage不能证明完整空日</x:v>
       </x:c>
-      <x:c r="I278" s="9" t="str">
+      <x:c r="I279" s="4" t="str">
         <x:v>draft</x:v>
       </x:c>
-      <x:c r="J278" s="9" t="str">
+      <x:c r="J279" s="4" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="K278" s="9" t="str">
+      <x:c r="K279" s="4" t="str">
         <x:v>细化用例</x:v>
       </x:c>
-      <x:c r="L278" s="9" t="str">
+      <x:c r="L279" s="4" t="str">
         <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:362</x:v>
       </x:c>
-      <x:c r="M278" s="9" t="str">
+      <x:c r="M279" s="4" t="str">
         <x:v>尚未执行</x:v>
       </x:c>
-      <x:c r="N278" s="9" t="str">
+      <x:c r="N279" s="4" t="str">
         <x:v>v0.5.0-20261001T034729Z</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G5:G278">
+  <x:conditionalFormatting sqref="G5:G279">
     <x:cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="I5:I278">
+  <x:conditionalFormatting sqref="I5:I279">
     <x:cfRule type="containsText" dxfId="15" priority="4" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="17" priority="6" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="J5:J278">
+  <x:conditionalFormatting sqref="J5:J279">
     <x:cfRule type="containsText" dxfId="18" priority="7" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="19" priority="8" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="20" priority="9" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="M5:M278">
+  <x:conditionalFormatting sqref="M5:M279">
     <x:cfRule type="containsText" dxfId="21" priority="10" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="22" priority="11" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="23" priority="12" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc90cfc758c1542e4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R81f501feb0d642bf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21625,7 +21676,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c8c0c3c927249f8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc52d724d2194bf8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21939,7 +21990,7 @@
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="72" customHeight="1">
+    <x:row r="9" ht="87" customHeight="1">
       <x:c r="A9" s="4" t="str">
         <x:v>v0.3.0-20261001T034652Z（续1）</x:v>
       </x:c>
@@ -21952,7 +22003,7 @@
       <x:c r="H9" s="4" t="str"/>
       <x:c r="I9" s="4" t="str"/>
       <x:c r="J9" s="4" t="str">
-        <x:v>source_check 1/1、四步与清理PASS，独立Excel回读PASS，第18批次；此前408ebf8红测失败保留。仅多文件模块，原27条产品TC与正式发行NOT_RUN。</x:v>
+        <x:v>source_check 1/1、四步与清理PASS，独立Excel回读PASS，第18批次；此前408ebf8红测失败保留。仅多文件模块，原27条产品TC与正式发行NOT_RUN。 CORE07主进程编排辅助TC已固定输入，程序/运行尚无。</x:v>
       </x:c>
       <x:c r="K9" s="4" t="str"/>
       <x:c r="L9" s="4" t="str"/>
@@ -22093,7 +22144,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ef5d7f22e44442b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf4f9079097f4817"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23258,7 +23309,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8347536de86f4d49"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R442b04bb61294121"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TokenMeter项目总表.xlsx
+++ b/TokenMeter项目总表.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R6859e9789eaa4df4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="R4640075aba8a46ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R60a530bf23a54544"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R2359c002b9c04b97"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R576e404900d24273"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R4abac05370484d31"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R404411f10c8b4644"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R42b671ea6dee41d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Red5216beacbc41fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R980a7298878d4026"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R55e5b945aebc4eb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R5aecea853f344e4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Rd27d59f669ab4628"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R006185a588df401c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="Rbfa8d23de5ca4a85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R031e61913cdb4f14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R814e04723aca453d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R55cace14a1724ac2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R0b6eb7aff5a040cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Rf51350a9a644454b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="Rc67567e977c24aa8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R6136b15bd3a141c4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -809,8 +809,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TMTable7" displayName="TMTable7" ref="A4:N24" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:N24"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TMTable7" displayName="TMTable7" ref="A4:N28" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:N28"/>
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="运行批次"/>
     <x:tableColumn id="2" name="版本"/>
@@ -1146,8 +1146,8 @@
         <x:v>测试批次</x:v>
       </x:c>
       <x:c r="B9" s="10" t="n">
-        <x:f>COUNTA('06测试批次'!A5:A24)</x:f>
-        <x:v>20</x:v>
+        <x:f>COUNTA('06测试批次'!A5:A28)</x:f>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C9" s="4" t="str">
         <x:v>06测试批次，每次运行一行，记录独立结果Excel位置</x:v>
@@ -1271,7 +1271,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="C20" s="9" t="str">
-        <x:v>product_e2e · TASK-TM001-LOGIN-SESSION；仅LOGIN-10/11/12/13/14/15六条固定父TC，真实App定向回归：原始真实App定向run六条父TC、14步骤PASS，cleanup_completed=true；独立Excel/verification PASS。与LOGIN-AUTH为不同run，709d其余TM001父TC未运行；旧c291完整门禁FAIL及正式发行NOT_RUN。；是否覆盖完整产品回归以批次范围和原始证据为准。</x:v>
+        <x:v>source_check · TM-005 CORE05合成双来源SQLite同窗快照固定辅助模块；非产品E2E：CORE05固定1/1、四步与owned_root清理PASS，独立Excel/verification回读PASS；原先两次红测失败原件保留，真实App/双来源原生日志产品TC仍未执行。；是否覆盖完整产品回归以批次范围和原始证据为准。</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="32" customHeight="1">
@@ -1288,7 +1288,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86fe8959df4e4996"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7713b6ac60884355"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1996,7 +1996,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8261aaa075b24b03"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R228a800dc39a4473"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2145,7 +2145,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6de93d56ad0c49f8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf54ef2ef4ab8469b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2580,7 +2580,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc67abf79e706473f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5da135ac933f44c6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3627,7 +3627,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14b7815ba70e4401"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24261c2e1b6a4d0b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4734,7 +4734,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc59ced9c7c9e4ae9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb6d7bee66f884245"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7519,7 +7519,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R417c62f167974b9f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rafb3d6399e4a4a3e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7823,7 +7823,7 @@
         <x:v>docs/testing/cases/01a-TM-001-login-scenarios.md:137</x:v>
       </x:c>
       <x:c r="M9" s="4" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-5e076fa3d05b4d949877333a3b5339e0</x:v>
       </x:c>
       <x:c r="N9" s="4" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -7870,7 +7870,7 @@
         <x:v>docs/testing/cases/01a-TM-001-login-scenarios.md:152</x:v>
       </x:c>
       <x:c r="M10" s="9" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-5e076fa3d05b4d949877333a3b5339e0</x:v>
       </x:c>
       <x:c r="N10" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -7917,7 +7917,7 @@
         <x:v>docs/testing/cases/01a-TM-001-login-scenarios.md:167</x:v>
       </x:c>
       <x:c r="M11" s="4" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-5e076fa3d05b4d949877333a3b5339e0</x:v>
       </x:c>
       <x:c r="N11" s="4" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -8011,7 +8011,7 @@
         <x:v>docs/testing/cases/01a-TM-001-login-scenarios.md:197</x:v>
       </x:c>
       <x:c r="M13" s="4" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-5e076fa3d05b4d949877333a3b5339e0</x:v>
       </x:c>
       <x:c r="N13" s="4" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -8343,7 +8343,7 @@
         <x:v>docs/testing/cases/01a-TM-001-login-scenarios.md:304</x:v>
       </x:c>
       <x:c r="M20" s="9" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-09f2c4fd672848a9a68ba851a5d7b3c9</x:v>
       </x:c>
       <x:c r="N20" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -8390,7 +8390,7 @@
         <x:v>docs/testing/cases/01a-TM-001-login-scenarios.md:320</x:v>
       </x:c>
       <x:c r="M21" s="4" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-5e076fa3d05b4d949877333a3b5339e0</x:v>
       </x:c>
       <x:c r="N21" s="4" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -8437,7 +8437,7 @@
         <x:v>docs/testing/cases/01a-TM-001-login-scenarios.md:341</x:v>
       </x:c>
       <x:c r="M22" s="9" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-5e076fa3d05b4d949877333a3b5339e0</x:v>
       </x:c>
       <x:c r="N22" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -8484,7 +8484,7 @@
         <x:v>docs/testing/cases/01a-TM-001-login-scenarios.md:364</x:v>
       </x:c>
       <x:c r="M23" s="4" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-5e076fa3d05b4d949877333a3b5339e0</x:v>
       </x:c>
       <x:c r="N23" s="4" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -8531,7 +8531,7 @@
         <x:v>docs/testing/cases/01a-TM-001-login-scenarios.md:386</x:v>
       </x:c>
       <x:c r="M24" s="9" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-5e076fa3d05b4d949877333a3b5339e0</x:v>
       </x:c>
       <x:c r="N24" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -8578,7 +8578,7 @@
         <x:v>docs/testing/cases/01a-TM-001-login-scenarios.md:401</x:v>
       </x:c>
       <x:c r="M25" s="4" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-5e076fa3d05b4d949877333a3b5339e0</x:v>
       </x:c>
       <x:c r="N25" s="4" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -8625,7 +8625,7 @@
         <x:v>docs/testing/cases/01a-TM-001-login-scenarios.md:416</x:v>
       </x:c>
       <x:c r="M26" s="9" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-5e076fa3d05b4d949877333a3b5339e0</x:v>
       </x:c>
       <x:c r="N26" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -20616,7 +20616,7 @@
         <x:v>draft</x:v>
       </x:c>
       <x:c r="J278" s="9" t="str">
-        <x:v>未执行</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="K278" s="9" t="str">
         <x:v>细化用例</x:v>
@@ -20625,7 +20625,7 @@
         <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:354</x:v>
       </x:c>
       <x:c r="M278" s="9" t="str">
-        <x:v>尚未执行</x:v>
+        <x:v>tm005-core04-20261001T193346Z</x:v>
       </x:c>
       <x:c r="N278" s="9" t="str">
         <x:v>v0.5.0-20261001T034729Z</x:v>
@@ -20666,7 +20666,7 @@
         <x:v>draft</x:v>
       </x:c>
       <x:c r="J279" s="4" t="str">
-        <x:v>未执行</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="K279" s="4" t="str">
         <x:v>细化用例</x:v>
@@ -20675,7 +20675,7 @@
         <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:362</x:v>
       </x:c>
       <x:c r="M279" s="4" t="str">
-        <x:v>尚未执行</x:v>
+        <x:v>tm005-core05-20261001T193346Z</x:v>
       </x:c>
       <x:c r="N279" s="4" t="str">
         <x:v>v0.5.0-20261001T034729Z</x:v>
@@ -20704,7 +20704,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R81f501feb0d642bf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re36cdc3eb98e42dc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21658,25 +21658,201 @@
         <x:v>PASS</x:v>
       </x:c>
     </x:row>
+    <x:row r="25" ht="57" customHeight="1">
+      <x:c r="A25" s="4" t="str">
+        <x:v>local-5e076fa3d05b4d949877333a3b5339e0</x:v>
+      </x:c>
+      <x:c r="B25" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+      <x:c r="C25" s="4" t="str">
+        <x:v>product_e2e</x:v>
+      </x:c>
+      <x:c r="D25" s="4" t="str">
+        <x:v>TASK-TM001-LOGIN-VALIDATION；10父TC与12固定变体，18真实App执行加4父例派生</x:v>
+      </x:c>
+      <x:c r="E25" s="4" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F25" s="4" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G25" s="4" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H25" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I25" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J25" s="4" t="str">
+        <x:v>709d21253a0f88bc703a431cbf3adba3df17e508</x:v>
+      </x:c>
+      <x:c r="K25" s="4" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="L25" s="4" t="str">
+        <x:v>10父TC与12固定变体共22/22报告行PASS、36步骤、cleanup=true；四父例由变体派生、18个真实App执行。仅709d LOGIN-VALIDATION定向，其他TM001功能未通过；旧c291完整门禁FAIL。</x:v>
+      </x:c>
+      <x:c r="M25" s="4" t="str">
+        <x:v>.local/test-results/local-5e076fa3d05b4d949877333a3b5339e0/TokenMeter测试结果-local-5e076fa3d05b4d949877333a3b5339e0.xlsx</x:v>
+      </x:c>
+      <x:c r="N25" s="4" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="42" customHeight="1">
+      <x:c r="A26" s="9" t="str">
+        <x:v>local-09f2c4fd672848a9a68ba851a5d7b3c9</x:v>
+      </x:c>
+      <x:c r="B26" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+      <x:c r="C26" s="9" t="str">
+        <x:v>product_e2e</x:v>
+      </x:c>
+      <x:c r="D26" s="9" t="str">
+        <x:v>TASK-TM001-LOGIN-RATE；仅LOGIN-16固定父TC</x:v>
+      </x:c>
+      <x:c r="E26" s="9" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F26" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G26" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H26" s="9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I26" s="9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J26" s="9" t="str">
+        <x:v>709d21253a0f88bc703a431cbf3adba3df17e508</x:v>
+      </x:c>
+      <x:c r="K26" s="9" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="L26" s="9" t="str">
+        <x:v>LOGIN-16单例/3步真实App PASS、cleanup=true，独立Excel回读PASS；仅709d定向，其他TM001功能及完整发行门禁未通过。</x:v>
+      </x:c>
+      <x:c r="M26" s="9" t="str">
+        <x:v>.local/test-results/local-09f2c4fd672848a9a68ba851a5d7b3c9/TokenMeter测试结果-local-09f2c4fd672848a9a68ba851a5d7b3c9.xlsx</x:v>
+      </x:c>
+      <x:c r="N26" s="9" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="42" customHeight="1">
+      <x:c r="A27" s="4" t="str">
+        <x:v>tm005-core04-20261001T193346Z</x:v>
+      </x:c>
+      <x:c r="B27" s="4" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+      <x:c r="C27" s="4" t="str">
+        <x:v>source_check</x:v>
+      </x:c>
+      <x:c r="D27" s="4" t="str">
+        <x:v>TM-005 CORE04 IANA当地日/DST半开界固定辅助模块；非产品E2E</x:v>
+      </x:c>
+      <x:c r="E27" s="4" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F27" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G27" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H27" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I27" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J27" s="4" t="str">
+        <x:v>259cf7688691d472837d59a8c1ae50e14b591410</x:v>
+      </x:c>
+      <x:c r="K27" s="4" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="L27" s="4" t="str">
+        <x:v>CORE04固定1/1、三步与memory_only清理PASS，独立Excel/verification回读PASS；纽约23/25小时与非法输入模块判据通过，安装App产品TC仍未执行。</x:v>
+      </x:c>
+      <x:c r="M27" s="4" t="str">
+        <x:v>.local/test-results/tm005-core04-20261001T193346Z/TokenMeter测试结果-tm005-core04-20261001T193346Z.xlsx</x:v>
+      </x:c>
+      <x:c r="N27" s="4" t="str">
+        <x:v>NOT_RUN</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="42" customHeight="1">
+      <x:c r="A28" s="9" t="str">
+        <x:v>tm005-core05-20261001T193346Z</x:v>
+      </x:c>
+      <x:c r="B28" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+      <x:c r="C28" s="9" t="str">
+        <x:v>source_check</x:v>
+      </x:c>
+      <x:c r="D28" s="9" t="str">
+        <x:v>TM-005 CORE05合成双来源SQLite同窗快照固定辅助模块；非产品E2E</x:v>
+      </x:c>
+      <x:c r="E28" s="9" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F28" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G28" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H28" s="9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I28" s="9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J28" s="9" t="str">
+        <x:v>259cf7688691d472837d59a8c1ae50e14b591410</x:v>
+      </x:c>
+      <x:c r="K28" s="9" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="L28" s="9" t="str">
+        <x:v>CORE05固定1/1、四步与owned_root清理PASS，独立Excel/verification回读PASS；原先两次红测失败原件保留，真实App/双来源原生日志产品TC仍未执行。</x:v>
+      </x:c>
+      <x:c r="M28" s="9" t="str">
+        <x:v>.local/test-results/tm005-core05-20261001T193346Z/TokenMeter测试结果-tm005-core05-20261001T193346Z.xlsx</x:v>
+      </x:c>
+      <x:c r="N28" s="9" t="str">
+        <x:v>NOT_RUN</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="E5:E24">
+  <x:conditionalFormatting sqref="E5:E28">
     <x:cfRule type="containsText" dxfId="24" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="25" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="26" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="M5:M24">
+  <x:conditionalFormatting sqref="M5:M28">
     <x:cfRule type="containsText" dxfId="27" priority="4" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="28" priority="5" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="29" priority="6" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="N5:N24">
+  <x:conditionalFormatting sqref="N5:N28">
     <x:cfRule type="containsText" dxfId="30" priority="7" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="31" priority="8" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="32" priority="9" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc52d724d2194bf8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac60af8e9db848b3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21822,7 +21998,7 @@
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="237" customHeight="1">
+    <x:row r="6" ht="282" customHeight="1">
       <x:c r="A6" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
       </x:c>
@@ -21851,7 +22027,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J6" s="9" t="str">
-        <x:v>开发中，未发布。c291本地master最终包门禁FAIL：116项91 PASS/14 FAIL/11 BLOCKED；9f06cb1修复私有签名输入后开发检查PASS，但新定向App仍FAIL/BLOCKED并有ENOSPC，功能回归未完成。旧d2db551独立候选PASS不转用于新候选。正式发行完整门禁NOT_RUN，无稳定0.1原包。 709d UPDATE-05定向父1+变体13 PASS，后置de081a6导出Excel回读PASS；仅定向，77父TC范围外，旧c291完整门禁FAIL及未发行不变。 709d安装DMG的登录定向五父例/11步原始PASS，独立Excel回读PASS；仍非整版回归，旧c291完整门禁FAIL。 709d LOGIN-SESSION另六父例/14步原始PASS并单独导出Excel；未完成整版回归。</x:v>
+        <x:v>开发中，未发布。c291本地master最终包门禁FAIL：116项91 PASS/14 FAIL/11 BLOCKED；9f06cb1修复私有签名输入后开发检查PASS，但新定向App仍FAIL/BLOCKED并有ENOSPC，功能回归未完成。旧d2db551独立候选PASS不转用于新候选。正式发行完整门禁NOT_RUN，无稳定0.1原包。 709d UPDATE-05定向父1+变体13 PASS，后置de081a6导出Excel回读PASS；仅定向，77父TC范围外，旧c291完整门禁FAIL及未发行不变。 709d安装DMG的登录定向五父例/11步原始PASS，独立Excel回读PASS；仍非整版回归，旧c291完整门禁FAIL。 709d LOGIN-SESSION另六父例/14步原始PASS并单独导出Excel；未完成整版回归。 709d LOGIN-VALIDATION十父+十二变体及LOGIN-RATE一父另两次定向PASS/Excel；四批登录合计22父+12变体，但TM001其他功能未验收。</x:v>
       </x:c>
       <x:c r="K6" s="9" t="str">
         <x:v>旧SwiftUI PR #2 已合并、历史双平台六例PASS；不继承给Electron</x:v>
@@ -22070,7 +22246,7 @@
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="327" customHeight="1">
+    <x:row r="11" ht="372" customHeight="1">
       <x:c r="A11" s="4" t="str">
         <x:v>v0.5.0-20261001T034729Z</x:v>
       </x:c>
@@ -22099,7 +22275,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J11" s="4" t="str">
-        <x:v>整版draft、未发布。原32条产品父TC、6稳定变体和两组摘要保留；纯统计CORE-01/02/03辅助TC在输入提交061c759后，经SOP-008内容核对及结构/治理457项PASS，独立切片development_slice_ready，程序绑定仍为空、模块实际运行unexecuted。静态oracle与切片就绪不证明真实双来源采集或产品E2E；固定产品数据、SQLite/IPC、安装App逐TC绑定未完成，正式发行完整门禁NOT_RUN。 独立代码提交6a0f6f的source_check CORE3/3、桌面29/29、build PASS，原件在TM005工作树.local/tm005-core-postcommit-20261001T162401Z；程序尚未进入本文档树、模块Excel导出/批次登记BLOCKED，产品E2E仍NOT_RUN。 CORE-01仅验证已给UTC半开界聚合，不验证IANA日期换算；该单独辅助TC待固定。 新增CORE04/05固定IANA当地日与合成双来源SQLite只读快照辅助TC，程序null/unexecuted；coverage表无连续空日证明，原32产品TC/6变体与发行仍BLOCKED/NOT_RUN。</x:v>
+        <x:v>整版draft、未发布。原32条产品父TC、6稳定变体和两组摘要保留；纯统计CORE-01/02/03辅助TC在输入提交061c759后，经SOP-008内容核对及结构/治理457项PASS，独立切片development_slice_ready，程序绑定仍为空、模块实际运行unexecuted。静态oracle与切片就绪不证明真实双来源采集或产品E2E；固定产品数据、SQLite/IPC、安装App逐TC绑定未完成，正式发行完整门禁NOT_RUN。 独立代码提交6a0f6f的source_check CORE3/3、桌面29/29、build PASS，原件在TM005工作树.local/tm005-core-postcommit-20261001T162401Z；程序尚未进入本文档树、模块Excel导出/批次登记BLOCKED，产品E2E仍NOT_RUN。 CORE-01仅验证已给UTC半开界聚合，不验证IANA日期换算；该单独辅助TC待固定。 新增CORE04/05固定IANA当地日与合成双来源SQLite只读快照辅助TC，程序null/unexecuted；coverage表无连续空日证明，原32产品TC/6变体与发行仍BLOCKED/NOT_RUN。 CORE04/05在259cf768候选固定模块分别1/1三/四步PASS且Excel回读；0.5产品E2E未运行。</x:v>
       </x:c>
       <x:c r="K11" s="4" t="str">
         <x:v>TM005语义oracle只验证规范化样例；0.4及此前稳定原包尚未形成，真实升级BLOCKED。</x:v>
@@ -22144,7 +22320,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf4f9079097f4817"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ac3655b89ed4f67"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23309,7 +23485,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R442b04bb61294121"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R114798d510fb437f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TokenMeter项目总表.xlsx
+++ b/TokenMeter项目总表.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R5aecea853f344e4f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Rd27d59f669ab4628"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R006185a588df401c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="Rbfa8d23de5ca4a85"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R031e61913cdb4f14"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R814e04723aca453d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R55cace14a1724ac2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R0b6eb7aff5a040cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Rf51350a9a644454b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="Rc67567e977c24aa8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R6136b15bd3a141c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="Rfc64f14418c448ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Rfd9f18be1749452c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R8ea424d0070c422f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R04abb273637d463a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="Rf5033cbd0f8a42de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R15c38db7c1904d7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R70ac51186f364251"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R212e9aaae0c54718"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Ra867a50951b247b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R71b5e166c51e4a5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R08bedfcee6524d9f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -809,8 +809,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TMTable7" displayName="TMTable7" ref="A4:N28" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:N28"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TMTable7" displayName="TMTable7" ref="A4:N29" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:N29"/>
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="运行批次"/>
     <x:tableColumn id="2" name="版本"/>
@@ -1146,8 +1146,8 @@
         <x:v>测试批次</x:v>
       </x:c>
       <x:c r="B9" s="10" t="n">
-        <x:f>COUNTA('06测试批次'!A5:A28)</x:f>
-        <x:v>24</x:v>
+        <x:f>COUNTA('06测试批次'!A5:A29)</x:f>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C9" s="4" t="str">
         <x:v>06测试批次，每次运行一行，记录独立结果Excel位置</x:v>
@@ -1263,7 +1263,7 @@
         <x:v>DMG及原始证据留本机；Git保存代码、文档和此工作簿</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="72" customHeight="1">
+    <x:row r="20" ht="87" customHeight="1">
       <x:c r="A20" s="9" t="str">
         <x:v>最近登记批次</x:v>
       </x:c>
@@ -1271,7 +1271,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="C20" s="9" t="str">
-        <x:v>source_check · TM-005 CORE05合成双来源SQLite同窗快照固定辅助模块；非产品E2E：CORE05固定1/1、四步与owned_root清理PASS，独立Excel/verification回读PASS；原先两次红测失败原件保留，真实App/双来源原生日志产品TC仍未执行。；是否覆盖完整产品回归以批次范围和原始证据为准。</x:v>
+        <x:v>product_e2e · TASK-TM001-CHANGE-PASSWORD；PASSWORD-01..11十一父TC及09/11下六固定变体，15真实App执行加2父例派生：11父+6变体共17/17报告行PASS、32步、清理完成；15真实App执行/2父例派生。独立审计仅PASSWORD-05 PASS，不能称12项完整审计。仅709d改密功能定向，其他TM001功能、旧c291完整门禁FAIL及正式发行NOT_RUN。；是否覆盖完整产品回归以批次范围和原始证据为准。</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="32" customHeight="1">
@@ -1288,7 +1288,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7713b6ac60884355"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0419773e35fb422f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1996,7 +1996,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R228a800dc39a4473"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8ca3cfe84354731"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2145,7 +2145,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf54ef2ef4ab8469b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R825253bf40594eae"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2580,7 +2580,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5da135ac933f44c6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4ecde44711a4d8b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3627,7 +3627,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24261c2e1b6a4d0b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd490caae6c264530"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4734,7 +4734,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb6d7bee66f884245"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re39fae7d7d624a7f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7519,7 +7519,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rafb3d6399e4a4a3e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra394df7f4df24a47"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8672,7 +8672,7 @@
         <x:v>docs/testing/cases/01a-TM-001-login-scenarios.md:431</x:v>
       </x:c>
       <x:c r="M27" s="4" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-64cdbd1050d84763928c0b6a7f30e2c3</x:v>
       </x:c>
       <x:c r="N27" s="4" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -8719,7 +8719,7 @@
         <x:v>docs/testing/cases/01a-TM-001-login-scenarios.md:446</x:v>
       </x:c>
       <x:c r="M28" s="9" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-64cdbd1050d84763928c0b6a7f30e2c3</x:v>
       </x:c>
       <x:c r="N28" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -8766,7 +8766,7 @@
         <x:v>docs/testing/cases/01a-TM-001-login-scenarios.md:461</x:v>
       </x:c>
       <x:c r="M29" s="4" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-64cdbd1050d84763928c0b6a7f30e2c3</x:v>
       </x:c>
       <x:c r="N29" s="4" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -8813,7 +8813,7 @@
         <x:v>docs/testing/cases/01a-TM-001-login-scenarios.md:476</x:v>
       </x:c>
       <x:c r="M30" s="9" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-64cdbd1050d84763928c0b6a7f30e2c3</x:v>
       </x:c>
       <x:c r="N30" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -8862,7 +8862,7 @@
         <x:v>docs/testing/cases/01a-TM-001-login-scenarios.md:491</x:v>
       </x:c>
       <x:c r="M31" s="4" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-64cdbd1050d84763928c0b6a7f30e2c3</x:v>
       </x:c>
       <x:c r="N31" s="4" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -8909,7 +8909,7 @@
         <x:v>docs/testing/cases/01a-TM-001-login-scenarios.md:508</x:v>
       </x:c>
       <x:c r="M32" s="9" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-64cdbd1050d84763928c0b6a7f30e2c3</x:v>
       </x:c>
       <x:c r="N32" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -8956,7 +8956,7 @@
         <x:v>docs/testing/cases/01a-TM-001-login-scenarios.md:523</x:v>
       </x:c>
       <x:c r="M33" s="4" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-64cdbd1050d84763928c0b6a7f30e2c3</x:v>
       </x:c>
       <x:c r="N33" s="4" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -9003,7 +9003,7 @@
         <x:v>docs/testing/cases/01a-TM-001-login-scenarios.md:538</x:v>
       </x:c>
       <x:c r="M34" s="9" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-64cdbd1050d84763928c0b6a7f30e2c3</x:v>
       </x:c>
       <x:c r="N34" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -9050,7 +9050,7 @@
         <x:v>docs/testing/cases/01a-TM-001-login-scenarios.md:553</x:v>
       </x:c>
       <x:c r="M35" s="4" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-64cdbd1050d84763928c0b6a7f30e2c3</x:v>
       </x:c>
       <x:c r="N35" s="4" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -9097,7 +9097,7 @@
         <x:v>docs/testing/cases/01a-TM-001-login-scenarios.md:576</x:v>
       </x:c>
       <x:c r="M36" s="9" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-64cdbd1050d84763928c0b6a7f30e2c3</x:v>
       </x:c>
       <x:c r="N36" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -9144,7 +9144,7 @@
         <x:v>docs/testing/cases/01a-TM-001-login-scenarios.md:591</x:v>
       </x:c>
       <x:c r="M37" s="4" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-64cdbd1050d84763928c0b6a7f30e2c3</x:v>
       </x:c>
       <x:c r="N37" s="4" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -20704,7 +20704,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re36cdc3eb98e42dc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff907dc856434a68"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21834,25 +21834,69 @@
         <x:v>NOT_RUN</x:v>
       </x:c>
     </x:row>
+    <x:row r="29" ht="57" customHeight="1">
+      <x:c r="A29" s="4" t="str">
+        <x:v>local-64cdbd1050d84763928c0b6a7f30e2c3</x:v>
+      </x:c>
+      <x:c r="B29" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+      <x:c r="C29" s="4" t="str">
+        <x:v>product_e2e</x:v>
+      </x:c>
+      <x:c r="D29" s="4" t="str">
+        <x:v>TASK-TM001-CHANGE-PASSWORD；PASSWORD-01..11十一父TC及09/11下六固定变体，15真实App执行加2父例派生</x:v>
+      </x:c>
+      <x:c r="E29" s="4" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F29" s="4" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G29" s="4" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H29" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I29" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J29" s="4" t="str">
+        <x:v>709d21253a0f88bc703a431cbf3adba3df17e508</x:v>
+      </x:c>
+      <x:c r="K29" s="4" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="L29" s="4" t="str">
+        <x:v>11父+6变体共17/17报告行PASS、32步、清理完成；15真实App执行/2父例派生。独立审计仅PASSWORD-05 PASS，不能称12项完整审计。仅709d改密功能定向，其他TM001功能、旧c291完整门禁FAIL及正式发行NOT_RUN。</x:v>
+      </x:c>
+      <x:c r="M29" s="4" t="str">
+        <x:v>.local/test-results/local-64cdbd1050d84763928c0b6a7f30e2c3/TokenMeter测试结果-local-64cdbd1050d84763928c0b6a7f30e2c3.xlsx</x:v>
+      </x:c>
+      <x:c r="N29" s="4" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="E5:E28">
+  <x:conditionalFormatting sqref="E5:E29">
     <x:cfRule type="containsText" dxfId="24" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="25" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="26" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="M5:M28">
+  <x:conditionalFormatting sqref="M5:M29">
     <x:cfRule type="containsText" dxfId="27" priority="4" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="28" priority="5" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="29" priority="6" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="N5:N28">
+  <x:conditionalFormatting sqref="N5:N29">
     <x:cfRule type="containsText" dxfId="30" priority="7" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="31" priority="8" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="32" priority="9" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac60af8e9db848b3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R174618c912c44748"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21998,7 +22042,7 @@
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="282" customHeight="1">
+    <x:row r="6" ht="327" customHeight="1">
       <x:c r="A6" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
       </x:c>
@@ -22027,7 +22071,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J6" s="9" t="str">
-        <x:v>开发中，未发布。c291本地master最终包门禁FAIL：116项91 PASS/14 FAIL/11 BLOCKED；9f06cb1修复私有签名输入后开发检查PASS，但新定向App仍FAIL/BLOCKED并有ENOSPC，功能回归未完成。旧d2db551独立候选PASS不转用于新候选。正式发行完整门禁NOT_RUN，无稳定0.1原包。 709d UPDATE-05定向父1+变体13 PASS，后置de081a6导出Excel回读PASS；仅定向，77父TC范围外，旧c291完整门禁FAIL及未发行不变。 709d安装DMG的登录定向五父例/11步原始PASS，独立Excel回读PASS；仍非整版回归，旧c291完整门禁FAIL。 709d LOGIN-SESSION另六父例/14步原始PASS并单独导出Excel；未完成整版回归。 709d LOGIN-VALIDATION十父+十二变体及LOGIN-RATE一父另两次定向PASS/Excel；四批登录合计22父+12变体，但TM001其他功能未验收。</x:v>
+        <x:v>开发中，未发布。c291本地master最终包门禁FAIL：116项91 PASS/14 FAIL/11 BLOCKED；9f06cb1修复私有签名输入后开发检查PASS，但新定向App仍FAIL/BLOCKED并有ENOSPC，功能回归未完成。旧d2db551独立候选PASS不转用于新候选。正式发行完整门禁NOT_RUN，无稳定0.1原包。 709d UPDATE-05定向父1+变体13 PASS，后置de081a6导出Excel回读PASS；仅定向，77父TC范围外，旧c291完整门禁FAIL及未发行不变。 709d安装DMG的登录定向五父例/11步原始PASS，独立Excel回读PASS；仍非整版回归，旧c291完整门禁FAIL。 709d LOGIN-SESSION另六父例/14步原始PASS并单独导出Excel；未完成整版回归。 709d LOGIN-VALIDATION十父+十二变体及LOGIN-RATE一父另两次定向PASS/Excel；四批登录合计22父+12变体，但TM001其他功能未验收。 709d CHANGE-PASSWORD十一父+六变体17行/32步另批定向PASS，PASSWORD-05单项独立审计PASS；未完成整版/12项审计。</x:v>
       </x:c>
       <x:c r="K6" s="9" t="str">
         <x:v>旧SwiftUI PR #2 已合并、历史双平台六例PASS；不继承给Electron</x:v>
@@ -22320,7 +22364,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ac3655b89ed4f67"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b6d80f555ee4313"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23485,7 +23529,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R114798d510fb437f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R432645b548d94627"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TokenMeter项目总表.xlsx
+++ b/TokenMeter项目总表.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="Rfc64f14418c448ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Rfd9f18be1749452c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R8ea424d0070c422f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R04abb273637d463a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="Rf5033cbd0f8a42de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R15c38db7c1904d7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R70ac51186f364251"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R212e9aaae0c54718"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Ra867a50951b247b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R71b5e166c51e4a5c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R08bedfcee6524d9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R5b7e7fd9d8064136"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Rca13714ea2eb4bd0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R34fbcca2560341bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="Rbb59dd038c7e485d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R9304618290ec472c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="Ra929ac29ea8c4312"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R1a21b4122a13461a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="Rc4c3f614e89845c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="R93d6c4490af544fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R1ea074624c644246"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R3a96156b72bc4508"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -809,8 +809,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TMTable7" displayName="TMTable7" ref="A4:N29" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:N29"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TMTable7" displayName="TMTable7" ref="A4:N30" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:N30"/>
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="运行批次"/>
     <x:tableColumn id="2" name="版本"/>
@@ -1146,8 +1146,8 @@
         <x:v>测试批次</x:v>
       </x:c>
       <x:c r="B9" s="10" t="n">
-        <x:f>COUNTA('06测试批次'!A5:A29)</x:f>
-        <x:v>25</x:v>
+        <x:f>COUNTA('06测试批次'!A5:A30)</x:f>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C9" s="4" t="str">
         <x:v>06测试批次，每次运行一行，记录独立结果Excel位置</x:v>
@@ -1271,7 +1271,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="C20" s="9" t="str">
-        <x:v>product_e2e · TASK-TM001-CHANGE-PASSWORD；PASSWORD-01..11十一父TC及09/11下六固定变体，15真实App执行加2父例派生：11父+6变体共17/17报告行PASS、32步、清理完成；15真实App执行/2父例派生。独立审计仅PASSWORD-05 PASS，不能称12项完整审计。仅709d改密功能定向，其他TM001功能、旧c291完整门禁FAIL及正式发行NOT_RUN。；是否覆盖完整产品回归以批次范围和原始证据为准。</x:v>
+        <x:v>product_e2e · TASK-TM001-SESSION；SESSION-01..10十父TC及SESSION-05#RESET/#DISABLE两变体，11真实App执行加1父例派生：10父+2变体共12/12报告行PASS、44步、清理完成；SESSION-05父例由两变体派生。独立审计仅SESSION-04 PASS，非12项完整审计。仅709d会话功能定向，其他TM001功能、旧c291完整门禁FAIL及正式发行NOT_RUN。；是否覆盖完整产品回归以批次范围和原始证据为准。</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="32" customHeight="1">
@@ -1288,7 +1288,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0419773e35fb422f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0122596413d49e1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1996,7 +1996,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8ca3cfe84354731"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b959ecddd074e70"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2145,7 +2145,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R825253bf40594eae"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e5c7a429072496d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2580,7 +2580,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4ecde44711a4d8b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R978ff2256dcc47a5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3627,7 +3627,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd490caae6c264530"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42d9cd88455e4cde"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4734,7 +4734,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re39fae7d7d624a7f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84934c925f564adf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7519,7 +7519,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra394df7f4df24a47"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37f1853248c14e92"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9193,7 +9193,7 @@
         <x:v>docs/testing/cases/01b-TM-001-session-admin-release-scenarios.md:76</x:v>
       </x:c>
       <x:c r="M38" s="9" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-ff24478631134a96bd7d40f2bbc5e254</x:v>
       </x:c>
       <x:c r="N38" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -9242,7 +9242,7 @@
         <x:v>docs/testing/cases/01b-TM-001-session-admin-release-scenarios.md:93</x:v>
       </x:c>
       <x:c r="M39" s="4" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-ff24478631134a96bd7d40f2bbc5e254</x:v>
       </x:c>
       <x:c r="N39" s="4" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -9291,7 +9291,7 @@
         <x:v>docs/testing/cases/01b-TM-001-session-admin-release-scenarios.md:110</x:v>
       </x:c>
       <x:c r="M40" s="9" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-ff24478631134a96bd7d40f2bbc5e254</x:v>
       </x:c>
       <x:c r="N40" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -9340,7 +9340,7 @@
         <x:v>docs/testing/cases/01b-TM-001-session-admin-release-scenarios.md:127</x:v>
       </x:c>
       <x:c r="M41" s="4" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-ff24478631134a96bd7d40f2bbc5e254</x:v>
       </x:c>
       <x:c r="N41" s="4" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -9389,7 +9389,7 @@
         <x:v>docs/testing/cases/01b-TM-001-session-admin-release-scenarios.md:149</x:v>
       </x:c>
       <x:c r="M42" s="9" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-ff24478631134a96bd7d40f2bbc5e254</x:v>
       </x:c>
       <x:c r="N42" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -9438,7 +9438,7 @@
         <x:v>docs/testing/cases/01b-TM-001-session-admin-release-scenarios.md:166</x:v>
       </x:c>
       <x:c r="M43" s="4" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-ff24478631134a96bd7d40f2bbc5e254</x:v>
       </x:c>
       <x:c r="N43" s="4" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -9487,7 +9487,7 @@
         <x:v>docs/testing/cases/01b-TM-001-session-admin-release-scenarios.md:183</x:v>
       </x:c>
       <x:c r="M44" s="9" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-ff24478631134a96bd7d40f2bbc5e254</x:v>
       </x:c>
       <x:c r="N44" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -9536,7 +9536,7 @@
         <x:v>docs/testing/cases/01b-TM-001-session-admin-release-scenarios.md:200</x:v>
       </x:c>
       <x:c r="M45" s="4" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-ff24478631134a96bd7d40f2bbc5e254</x:v>
       </x:c>
       <x:c r="N45" s="4" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -9586,7 +9586,7 @@
         <x:v>docs/testing/cases/01b-TM-001-session-admin-release-scenarios.md:217</x:v>
       </x:c>
       <x:c r="M46" s="9" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-ff24478631134a96bd7d40f2bbc5e254</x:v>
       </x:c>
       <x:c r="N46" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -9635,7 +9635,7 @@
         <x:v>docs/testing/cases/01b-TM-001-session-admin-release-scenarios.md:234</x:v>
       </x:c>
       <x:c r="M47" s="4" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-ff24478631134a96bd7d40f2bbc5e254</x:v>
       </x:c>
       <x:c r="N47" s="4" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -20704,7 +20704,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff907dc856434a68"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcdb18eb57a8d40c5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21878,25 +21878,69 @@
         <x:v>PASS</x:v>
       </x:c>
     </x:row>
+    <x:row r="30" ht="57" customHeight="1">
+      <x:c r="A30" s="9" t="str">
+        <x:v>local-ff24478631134a96bd7d40f2bbc5e254</x:v>
+      </x:c>
+      <x:c r="B30" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+      <x:c r="C30" s="9" t="str">
+        <x:v>product_e2e</x:v>
+      </x:c>
+      <x:c r="D30" s="9" t="str">
+        <x:v>TASK-TM001-SESSION；SESSION-01..10十父TC及SESSION-05#RESET/#DISABLE两变体，11真实App执行加1父例派生</x:v>
+      </x:c>
+      <x:c r="E30" s="9" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F30" s="9" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G30" s="9" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H30" s="9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I30" s="9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J30" s="9" t="str">
+        <x:v>709d21253a0f88bc703a431cbf3adba3df17e508</x:v>
+      </x:c>
+      <x:c r="K30" s="9" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="L30" s="9" t="str">
+        <x:v>10父+2变体共12/12报告行PASS、44步、清理完成；SESSION-05父例由两变体派生。独立审计仅SESSION-04 PASS，非12项完整审计。仅709d会话功能定向，其他TM001功能、旧c291完整门禁FAIL及正式发行NOT_RUN。</x:v>
+      </x:c>
+      <x:c r="M30" s="9" t="str">
+        <x:v>.local/test-results/local-ff24478631134a96bd7d40f2bbc5e254/TokenMeter测试结果-local-ff24478631134a96bd7d40f2bbc5e254.xlsx</x:v>
+      </x:c>
+      <x:c r="N30" s="9" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="E5:E29">
+  <x:conditionalFormatting sqref="E5:E30">
     <x:cfRule type="containsText" dxfId="24" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="25" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="26" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="M5:M29">
+  <x:conditionalFormatting sqref="M5:M30">
     <x:cfRule type="containsText" dxfId="27" priority="4" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="28" priority="5" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="29" priority="6" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="N5:N29">
+  <x:conditionalFormatting sqref="N5:N30">
     <x:cfRule type="containsText" dxfId="30" priority="7" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="31" priority="8" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="32" priority="9" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R174618c912c44748"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R464573aeb46c403f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22042,7 +22086,7 @@
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="327" customHeight="1">
+    <x:row r="6" ht="372" customHeight="1">
       <x:c r="A6" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
       </x:c>
@@ -22071,7 +22115,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J6" s="9" t="str">
-        <x:v>开发中，未发布。c291本地master最终包门禁FAIL：116项91 PASS/14 FAIL/11 BLOCKED；9f06cb1修复私有签名输入后开发检查PASS，但新定向App仍FAIL/BLOCKED并有ENOSPC，功能回归未完成。旧d2db551独立候选PASS不转用于新候选。正式发行完整门禁NOT_RUN，无稳定0.1原包。 709d UPDATE-05定向父1+变体13 PASS，后置de081a6导出Excel回读PASS；仅定向，77父TC范围外，旧c291完整门禁FAIL及未发行不变。 709d安装DMG的登录定向五父例/11步原始PASS，独立Excel回读PASS；仍非整版回归，旧c291完整门禁FAIL。 709d LOGIN-SESSION另六父例/14步原始PASS并单独导出Excel；未完成整版回归。 709d LOGIN-VALIDATION十父+十二变体及LOGIN-RATE一父另两次定向PASS/Excel；四批登录合计22父+12变体，但TM001其他功能未验收。 709d CHANGE-PASSWORD十一父+六变体17行/32步另批定向PASS，PASSWORD-05单项独立审计PASS；未完成整版/12项审计。</x:v>
+        <x:v>开发中，未发布。c291本地master最终包门禁FAIL：116项91 PASS/14 FAIL/11 BLOCKED；9f06cb1修复私有签名输入后开发检查PASS，但新定向App仍FAIL/BLOCKED并有ENOSPC，功能回归未完成。旧d2db551独立候选PASS不转用于新候选。正式发行完整门禁NOT_RUN，无稳定0.1原包。 709d UPDATE-05定向父1+变体13 PASS，后置de081a6导出Excel回读PASS；仅定向，77父TC范围外，旧c291完整门禁FAIL及未发行不变。 709d安装DMG的登录定向五父例/11步原始PASS，独立Excel回读PASS；仍非整版回归，旧c291完整门禁FAIL。 709d LOGIN-SESSION另六父例/14步原始PASS并单独导出Excel；未完成整版回归。 709d LOGIN-VALIDATION十父+十二变体及LOGIN-RATE一父另两次定向PASS/Excel；四批登录合计22父+12变体，但TM001其他功能未验收。 709d CHANGE-PASSWORD十一父+六变体17行/32步另批定向PASS，PASSWORD-05单项独立审计PASS；未完成整版/12项审计。 709d SESSION十父+两变体12行/44步另批定向PASS，SESSION-04单项审计PASS；整版/完整审计仍未完成。</x:v>
       </x:c>
       <x:c r="K6" s="9" t="str">
         <x:v>旧SwiftUI PR #2 已合并、历史双平台六例PASS；不继承给Electron</x:v>
@@ -22364,7 +22408,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b6d80f555ee4313"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8be3a10686445f2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23529,7 +23573,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R432645b548d94627"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ae934e5fe044feb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TokenMeter项目总表.xlsx
+++ b/TokenMeter项目总表.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R5b7e7fd9d8064136"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Rca13714ea2eb4bd0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R34fbcca2560341bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="Rbb59dd038c7e485d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R9304618290ec472c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="Ra929ac29ea8c4312"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R1a21b4122a13461a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="Rc4c3f614e89845c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="R93d6c4490af544fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R1ea074624c644246"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R3a96156b72bc4508"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R6f80327e98dd4abb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Re718f9c052b241ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R1917b91e169745b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="Rf2599f419df64a22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="Rf9517697bb1447f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="Rb18197dead8e41ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R1bd9d683b0d34ffc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R47fa7220a8814f42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Rfa5f86ea44294dcb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="Recf318c6212c49e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R19e7cee4e06949b4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -809,8 +809,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TMTable7" displayName="TMTable7" ref="A4:N30" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:N30"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TMTable7" displayName="TMTable7" ref="A4:N31" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:N31"/>
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="运行批次"/>
     <x:tableColumn id="2" name="版本"/>
@@ -1146,8 +1146,8 @@
         <x:v>测试批次</x:v>
       </x:c>
       <x:c r="B9" s="10" t="n">
-        <x:f>COUNTA('06测试批次'!A5:A30)</x:f>
-        <x:v>26</x:v>
+        <x:f>COUNTA('06测试批次'!A5:A31)</x:f>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C9" s="4" t="str">
         <x:v>06测试批次，每次运行一行，记录独立结果Excel位置</x:v>
@@ -1271,7 +1271,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="C20" s="9" t="str">
-        <x:v>product_e2e · TASK-TM001-SESSION；SESSION-01..10十父TC及SESSION-05#RESET/#DISABLE两变体，11真实App执行加1父例派生：10父+2变体共12/12报告行PASS、44步、清理完成；SESSION-05父例由两变体派生。独立审计仅SESSION-04 PASS，非12项完整审计。仅709d会话功能定向，其他TM001功能、旧c291完整门禁FAIL及正式发行NOT_RUN。；是否覆盖完整产品回归以批次范围和原始证据为准。</x:v>
+        <x:v>source_check · TM-003 CORE07假TM002能力主进程编排与本例SQLite固定辅助模块；非产品E2E：CORE07固定1/1、五步与owner清理PASS；先前collector_not_implemented红测FAIL原件保留，独立Excel/verification回读PASS。仅fake能力+小文件/注入预算，真实App/IPC/Keychain、任意大文件及发行均NOT_RUN/BLOCKED。；是否覆盖完整产品回归以批次范围和原始证据为准。</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="32" customHeight="1">
@@ -1288,7 +1288,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0122596413d49e1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R389a0173571c46e3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1996,7 +1996,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b959ecddd074e70"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd76318df15e54cdf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2145,7 +2145,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e5c7a429072496d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3907da28b35f4cc3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2580,7 +2580,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R978ff2256dcc47a5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2fb35876a9d49ef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3627,7 +3627,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42d9cd88455e4cde"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3618c52efb834244"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4734,7 +4734,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84934c925f564adf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R283733861e4f4a78"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7519,7 +7519,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37f1853248c14e92"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c1851f2b3e14ea7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20178,7 +20178,7 @@
         <x:v>draft</x:v>
       </x:c>
       <x:c r="J269" s="4" t="str">
-        <x:v>未执行</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="K269" s="4" t="str">
         <x:v>细化用例</x:v>
@@ -20187,7 +20187,7 @@
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:243</x:v>
       </x:c>
       <x:c r="M269" s="4" t="str">
-        <x:v>尚未执行</x:v>
+        <x:v>tm003-core07-20261001T200438Z</x:v>
       </x:c>
       <x:c r="N269" s="4" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
@@ -20704,7 +20704,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcdb18eb57a8d40c5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7109505d2c164d93"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21922,25 +21922,69 @@
         <x:v>PASS</x:v>
       </x:c>
     </x:row>
+    <x:row r="31" ht="57" customHeight="1">
+      <x:c r="A31" s="4" t="str">
+        <x:v>tm003-core07-20261001T200438Z</x:v>
+      </x:c>
+      <x:c r="B31" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+      <x:c r="C31" s="4" t="str">
+        <x:v>source_check</x:v>
+      </x:c>
+      <x:c r="D31" s="4" t="str">
+        <x:v>TM-003 CORE07假TM002能力主进程编排与本例SQLite固定辅助模块；非产品E2E</x:v>
+      </x:c>
+      <x:c r="E31" s="4" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F31" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G31" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H31" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I31" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J31" s="4" t="str">
+        <x:v>33b1ee1636fc8e92ecba834856769df9f112c509</x:v>
+      </x:c>
+      <x:c r="K31" s="4" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="L31" s="4" t="str">
+        <x:v>CORE07固定1/1、五步与owner清理PASS；先前collector_not_implemented红测FAIL原件保留，独立Excel/verification回读PASS。仅fake能力+小文件/注入预算，真实App/IPC/Keychain、任意大文件及发行均NOT_RUN/BLOCKED。</x:v>
+      </x:c>
+      <x:c r="M31" s="4" t="str">
+        <x:v>.local/test-results/tm003-core07-20261001T200438Z/TokenMeter测试结果-tm003-core07-20261001T200438Z.xlsx</x:v>
+      </x:c>
+      <x:c r="N31" s="4" t="str">
+        <x:v>NOT_RUN</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="E5:E30">
+  <x:conditionalFormatting sqref="E5:E31">
     <x:cfRule type="containsText" dxfId="24" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="25" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="26" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="M5:M30">
+  <x:conditionalFormatting sqref="M5:M31">
     <x:cfRule type="containsText" dxfId="27" priority="4" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="28" priority="5" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="29" priority="6" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="N5:N30">
+  <x:conditionalFormatting sqref="N5:N31">
     <x:cfRule type="containsText" dxfId="30" priority="7" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="31" priority="8" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="32" priority="9" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R464573aeb46c403f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re6d089132e2b4a94"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22254,7 +22298,7 @@
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="87" customHeight="1">
+    <x:row r="9" ht="132" customHeight="1">
       <x:c r="A9" s="4" t="str">
         <x:v>v0.3.0-20261001T034652Z（续1）</x:v>
       </x:c>
@@ -22267,7 +22311,7 @@
       <x:c r="H9" s="4" t="str"/>
       <x:c r="I9" s="4" t="str"/>
       <x:c r="J9" s="4" t="str">
-        <x:v>source_check 1/1、四步与清理PASS，独立Excel回读PASS，第18批次；此前408ebf8红测失败保留。仅多文件模块，原27条产品TC与正式发行NOT_RUN。 CORE07主进程编排辅助TC已固定输入，程序/运行尚无。</x:v>
+        <x:v>source_check 1/1、四步与清理PASS，独立Excel回读PASS，第18批次；此前408ebf8红测失败保留。仅多文件模块，原27条产品TC与正式发行NOT_RUN。 CORE07主进程编排辅助TC已固定输入，程序/运行尚无。 CORE07在33b1ee1代码候选固定模块1/1五步PASS、Excel回读；真实App/大文件产品仍未验收。</x:v>
       </x:c>
       <x:c r="K9" s="4" t="str"/>
       <x:c r="L9" s="4" t="str"/>
@@ -22408,7 +22452,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8be3a10686445f2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89616e7d2e0e4eb1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23573,7 +23617,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ae934e5fe044feb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra20c7708a25d4ed0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TokenMeter项目总表.xlsx
+++ b/TokenMeter项目总表.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R6f80327e98dd4abb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Re718f9c052b241ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R1917b91e169745b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="Rf2599f419df64a22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="Rf9517697bb1447f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="Rb18197dead8e41ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R1bd9d683b0d34ffc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R47fa7220a8814f42"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Rfa5f86ea44294dcb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="Recf318c6212c49e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R19e7cee4e06949b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R1f7ef9a4ca614d99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="R62e780c2444344e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R60dae5e928114473"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R9308ab9f90f544f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="Re62843944cd844b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R0ff9868f11644f92"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R898bf95a4d9244fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="Rea61de4a51cd48f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="R1feb460eca984418"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="Ra29fb61db43d4d85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R796669df95fa49cb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -809,8 +809,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TMTable7" displayName="TMTable7" ref="A4:N31" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:N31"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TMTable7" displayName="TMTable7" ref="A4:N32" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:N32"/>
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="运行批次"/>
     <x:tableColumn id="2" name="版本"/>
@@ -832,8 +832,8 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="TMTable8" displayName="TMTable8" ref="A4:R11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:R11"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="TMTable8" displayName="TMTable8" ref="A4:R12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:R12"/>
   <x:tableColumns count="18">
     <x:tableColumn id="1" name="发布编号"/>
     <x:tableColumn id="2" name="版本"/>
@@ -1146,8 +1146,8 @@
         <x:v>测试批次</x:v>
       </x:c>
       <x:c r="B9" s="10" t="n">
-        <x:f>COUNTA('06测试批次'!A5:A31)</x:f>
-        <x:v>27</x:v>
+        <x:f>COUNTA('06测试批次'!A5:A32)</x:f>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C9" s="4" t="str">
         <x:v>06测试批次，每次运行一行，记录独立结果Excel位置</x:v>
@@ -1271,7 +1271,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="C20" s="9" t="str">
-        <x:v>source_check · TM-003 CORE07假TM002能力主进程编排与本例SQLite固定辅助模块；非产品E2E：CORE07固定1/1、五步与owner清理PASS；先前collector_not_implemented红测FAIL原件保留，独立Excel/verification回读PASS。仅fake能力+小文件/注入预算，真实App/IPC/Keychain、任意大文件及发行均NOT_RUN/BLOCKED。；是否覆盖完整产品回归以批次范围和原始证据为准。</x:v>
+        <x:v>product_e2e · TASK-TM001-ADMIN；ADMIN-01..06六父TC及ADMIN-02/05下五固定变体，九真实App执行加两父例派生：6父+5变体共11/11报告行PASS、33步、清理完成；ADMIN-02/05父例由变体派生。独立审计仅ADMIN-03 PASS，非12项完整审计。仅709d管理员功能定向，其他TM001功能、旧c291完整门禁FAIL及正式发行NOT_RUN。；是否覆盖完整产品回归以批次范围和原始证据为准。</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="32" customHeight="1">
@@ -1288,7 +1288,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R389a0173571c46e3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60d54a6ba0224a79"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1996,7 +1996,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd76318df15e54cdf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38fc160fbd0e4883"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2145,7 +2145,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3907da28b35f4cc3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R563a38c6851b4300"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2580,7 +2580,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2fb35876a9d49ef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d53b72e0f624a4a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3627,7 +3627,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3618c52efb834244"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R94b7439a0de84eb9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4734,7 +4734,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R283733861e4f4a78"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf81feecdfec4aec"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7519,7 +7519,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c1851f2b3e14ea7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra59ff02bbe264520"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9685,7 +9685,7 @@
         <x:v>docs/testing/cases/01b-TM-001-session-admin-release-scenarios.md:258</x:v>
       </x:c>
       <x:c r="M48" s="9" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-cd15a5fef2444f748088d1fcdd29fe0d</x:v>
       </x:c>
       <x:c r="N48" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -9734,7 +9734,7 @@
         <x:v>docs/testing/cases/01b-TM-001-session-admin-release-scenarios.md:276</x:v>
       </x:c>
       <x:c r="M49" s="4" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-cd15a5fef2444f748088d1fcdd29fe0d</x:v>
       </x:c>
       <x:c r="N49" s="4" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -9783,7 +9783,7 @@
         <x:v>docs/testing/cases/01b-TM-001-session-admin-release-scenarios.md:293</x:v>
       </x:c>
       <x:c r="M50" s="9" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-cd15a5fef2444f748088d1fcdd29fe0d</x:v>
       </x:c>
       <x:c r="N50" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -9832,7 +9832,7 @@
         <x:v>docs/testing/cases/01b-TM-001-session-admin-release-scenarios.md:310</x:v>
       </x:c>
       <x:c r="M51" s="4" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-cd15a5fef2444f748088d1fcdd29fe0d</x:v>
       </x:c>
       <x:c r="N51" s="4" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -9881,7 +9881,7 @@
         <x:v>docs/testing/cases/01b-TM-001-session-admin-release-scenarios.md:327</x:v>
       </x:c>
       <x:c r="M52" s="9" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-cd15a5fef2444f748088d1fcdd29fe0d</x:v>
       </x:c>
       <x:c r="N52" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -9930,7 +9930,7 @@
         <x:v>docs/testing/cases/01b-TM-001-session-admin-release-scenarios.md:344</x:v>
       </x:c>
       <x:c r="M53" s="4" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-cd15a5fef2444f748088d1fcdd29fe0d</x:v>
       </x:c>
       <x:c r="N53" s="4" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -20704,7 +20704,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7109505d2c164d93"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R295b2eb23bc04eaa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21966,25 +21966,69 @@
         <x:v>NOT_RUN</x:v>
       </x:c>
     </x:row>
+    <x:row r="32" ht="57" customHeight="1">
+      <x:c r="A32" s="9" t="str">
+        <x:v>local-cd15a5fef2444f748088d1fcdd29fe0d</x:v>
+      </x:c>
+      <x:c r="B32" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+      <x:c r="C32" s="9" t="str">
+        <x:v>product_e2e</x:v>
+      </x:c>
+      <x:c r="D32" s="9" t="str">
+        <x:v>TASK-TM001-ADMIN；ADMIN-01..06六父TC及ADMIN-02/05下五固定变体，九真实App执行加两父例派生</x:v>
+      </x:c>
+      <x:c r="E32" s="9" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F32" s="9" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G32" s="9" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H32" s="9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I32" s="9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J32" s="9" t="str">
+        <x:v>709d21253a0f88bc703a431cbf3adba3df17e508</x:v>
+      </x:c>
+      <x:c r="K32" s="9" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="L32" s="9" t="str">
+        <x:v>6父+5变体共11/11报告行PASS、33步、清理完成；ADMIN-02/05父例由变体派生。独立审计仅ADMIN-03 PASS，非12项完整审计。仅709d管理员功能定向，其他TM001功能、旧c291完整门禁FAIL及正式发行NOT_RUN。</x:v>
+      </x:c>
+      <x:c r="M32" s="9" t="str">
+        <x:v>.local/test-results/local-cd15a5fef2444f748088d1fcdd29fe0d/TokenMeter测试结果-local-cd15a5fef2444f748088d1fcdd29fe0d.xlsx</x:v>
+      </x:c>
+      <x:c r="N32" s="9" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="E5:E31">
+  <x:conditionalFormatting sqref="E5:E32">
     <x:cfRule type="containsText" dxfId="24" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="25" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="26" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="M5:M31">
+  <x:conditionalFormatting sqref="M5:M32">
     <x:cfRule type="containsText" dxfId="27" priority="4" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="28" priority="5" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="29" priority="6" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="N5:N31">
+  <x:conditionalFormatting sqref="N5:N32">
     <x:cfRule type="containsText" dxfId="30" priority="7" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="31" priority="8" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="32" priority="9" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re6d089132e2b4a94"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfefa159669d54fe7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22130,7 +22174,7 @@
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="372" customHeight="1">
+    <x:row r="6" ht="402" customHeight="1">
       <x:c r="A6" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
       </x:c>
@@ -22159,7 +22203,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J6" s="9" t="str">
-        <x:v>开发中，未发布。c291本地master最终包门禁FAIL：116项91 PASS/14 FAIL/11 BLOCKED；9f06cb1修复私有签名输入后开发检查PASS，但新定向App仍FAIL/BLOCKED并有ENOSPC，功能回归未完成。旧d2db551独立候选PASS不转用于新候选。正式发行完整门禁NOT_RUN，无稳定0.1原包。 709d UPDATE-05定向父1+变体13 PASS，后置de081a6导出Excel回读PASS；仅定向，77父TC范围外，旧c291完整门禁FAIL及未发行不变。 709d安装DMG的登录定向五父例/11步原始PASS，独立Excel回读PASS；仍非整版回归，旧c291完整门禁FAIL。 709d LOGIN-SESSION另六父例/14步原始PASS并单独导出Excel；未完成整版回归。 709d LOGIN-VALIDATION十父+十二变体及LOGIN-RATE一父另两次定向PASS/Excel；四批登录合计22父+12变体，但TM001其他功能未验收。 709d CHANGE-PASSWORD十一父+六变体17行/32步另批定向PASS，PASSWORD-05单项独立审计PASS；未完成整版/12项审计。 709d SESSION十父+两变体12行/44步另批定向PASS，SESSION-04单项审计PASS；整版/完整审计仍未完成。</x:v>
+        <x:v>开发中，未发布。c291本地master最终包门禁FAIL：116项91 PASS/14 FAIL/11 BLOCKED；9f06cb1修复私有签名输入后开发检查PASS，但新定向App仍FAIL/BLOCKED并有ENOSPC，功能回归未完成。旧d2db551独立候选PASS不转用于新候选。正式发行完整门禁NOT_RUN，无稳定0.1原包。 709d UPDATE-05定向父1+变体13 PASS，后置de081a6导出Excel回读PASS；仅定向，77父TC范围外，旧c291完整门禁FAIL及未发行不变。 709d安装DMG的登录定向五父例/11步原始PASS，独立Excel回读PASS；仍非整版回归，旧c291完整门禁FAIL。 709d LOGIN-SESSION另六父例/14步原始PASS并单独导出Excel；未完成整版回归。 709d LOGIN-VALIDATION十父+十二变体及LOGIN-RATE一父另两次定向PASS/Excel；四批登录合计22父+12变体，但TM001其他功能未验收。 709d CHANGE-PASSWORD十一父+六变体17行/32步另批定向PASS，PASSWORD-05单项独立审计PASS；未完成整版/12项审计。 709d SESSION十父+两变体12行/44步另批定向PASS，SESSION-04单项审计PASS；整版/完整审计仍未完成。 709d ADMIN六父+五变体11行/33步另批定向PASS，ADMIN-03单项审计</x:v>
       </x:c>
       <x:c r="K6" s="9" t="str">
         <x:v>旧SwiftUI PR #2 已合并、历史双平台六例PASS；不继承给Electron</x:v>
@@ -22186,77 +22230,45 @@
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="342" customHeight="1">
+    <x:row r="7" ht="32" customHeight="1">
       <x:c r="A7" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z（续1）</x:v>
+      </x:c>
+      <x:c r="B7" s="4" t="str"/>
+      <x:c r="C7" s="16" t="str"/>
+      <x:c r="D7" s="4" t="str"/>
+      <x:c r="E7" s="4" t="str"/>
+      <x:c r="F7" s="4" t="str"/>
+      <x:c r="G7" s="4" t="str"/>
+      <x:c r="H7" s="4" t="str"/>
+      <x:c r="I7" s="4" t="str"/>
+      <x:c r="J7" s="4" t="str">
+        <x:v>PASS；整版/完整审计仍未完成。</x:v>
+      </x:c>
+      <x:c r="K7" s="4" t="str"/>
+      <x:c r="L7" s="4" t="str"/>
+      <x:c r="M7" s="4" t="str"/>
+      <x:c r="N7" s="4" t="str"/>
+      <x:c r="O7" s="4" t="str"/>
+      <x:c r="P7" s="4" t="str"/>
+      <x:c r="Q7" s="4" t="str"/>
+      <x:c r="R7" s="4" t="str"/>
+    </x:row>
+    <x:row r="8" ht="342" customHeight="1">
+      <x:c r="A8" s="9" t="str">
         <x:v>v0.2.0-20261001T034118Z</x:v>
       </x:c>
-      <x:c r="B7" s="4" t="str">
+      <x:c r="B8" s="9" t="str">
         <x:v>0.2.0</x:v>
       </x:c>
-      <x:c r="C7" s="16" t="n">
+      <x:c r="C8" s="17" t="n">
         <x:v>46296.15368055556</x:v>
-      </x:c>
-      <x:c r="D7" s="4" t="str">
-        <x:v>产品功能</x:v>
-      </x:c>
-      <x:c r="E7" s="4" t="str">
-        <x:v>TM-002</x:v>
-      </x:c>
-      <x:c r="F7" s="4" t="str">
-        <x:v>未发布</x:v>
-      </x:c>
-      <x:c r="G7" s="4" t="str">
-        <x:v>internal</x:v>
-      </x:c>
-      <x:c r="H7" s="4" t="str">
-        <x:v>本机版本归档及 dmg/&lt;release_id&gt;/；当前无本版正式包</x:v>
-      </x:c>
-      <x:c r="I7" s="15" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J7" s="4" t="str">
-        <x:v>设计基线已完成：3功能点、9 TASK、28父TC、35变体。开发工作树已有原生目录面板、加密locator、根FD受限读取、React授权UI及33个固定E2E叶入口（28可执行、5场景摘要）；报告单元59/59、治理473/473、构建PASS。产品E2E因AX trusted=false及隔离标准测试账号不可用BLOCKED，Keychain最终包隔离未证实。本独立文档树未合该代码，机器绑定仍planned；正式发行完整门禁NOT_RUN、未发布。0.2公开配置为version0.2.0/build200及测试高版0.2.1/build201，实际0.2包尚未证明。 2026-10-02修订SECURITY-01三个恶意字串变体的固定IPC method/字段/错误码，产品状态不变；需在整合候选重核基线及固定程序。 EVIDENCE-01新增第七固定负例，本版36变体；SECURITY-01仅profile准备目录纠错。新输入未执行，产品E2E仍NOT_RUN。 0cc4f3e候选包预检33条全BLOCKED、零产品步骤；缺显式独立test/excluded账号，App未启动；固定结果Excel缺失，根总表批次待登记。</x:v>
-      </x:c>
-      <x:c r="K7" s="4" t="str">
-        <x:v>TM001独立候选d2门禁PASS只属历史；本地master c2911bc首次最终包门禁FAIL、无SOP-020稳定原包，不能作为0.2升级源；本版无实际产品运行。</x:v>
-      </x:c>
-      <x:c r="L7" s="4" t="str">
-        <x:v>releases/v0.2.0-20261001T034118Z/00-manifest.json</x:v>
-      </x:c>
-      <x:c r="M7" s="4" t="str">
-        <x:v>releases/v0.2.0-20261001T034118Z/06-iteration-record.md</x:v>
-      </x:c>
-      <x:c r="N7" s="4" t="str">
-        <x:v>未核实同名功能分支SHA/tree读回</x:v>
-      </x:c>
-      <x:c r="O7" s="4" t="str">
-        <x:v>产品E2E未执行；本机稳定包未归档</x:v>
-      </x:c>
-      <x:c r="P7" s="4" t="str">
-        <x:v>本轮五版稳定后一次受保护PR；待办</x:v>
-      </x:c>
-      <x:c r="Q7" s="4" t="str">
-        <x:v>本轮五版稳定及远端master读回后逐版登记；待办</x:v>
-      </x:c>
-      <x:c r="R7" s="4" t="str">
-        <x:v>releases/v0.2.0-20261001T034118Z/01-requirements.md:32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="387" customHeight="1">
-      <x:c r="A8" s="9" t="str">
-        <x:v>v0.3.0-20261001T034652Z</x:v>
-      </x:c>
-      <x:c r="B8" s="9" t="str">
-        <x:v>0.3.0</x:v>
-      </x:c>
-      <x:c r="C8" s="17" t="n">
-        <x:v>46296.157546296294</x:v>
       </x:c>
       <x:c r="D8" s="9" t="str">
         <x:v>产品功能</x:v>
       </x:c>
       <x:c r="E8" s="9" t="str">
-        <x:v>TM-003</x:v>
+        <x:v>TM-002</x:v>
       </x:c>
       <x:c r="F8" s="9" t="str">
         <x:v>未发布</x:v>
@@ -22265,28 +22277,28 @@
         <x:v>internal</x:v>
       </x:c>
       <x:c r="H8" s="9" t="str">
-        <x:v>dmg/&lt;release_id&gt;/：正式包仅在本机门禁 PASS 后保存</x:v>
+        <x:v>本机版本归档及 dmg/&lt;release_id&gt;/；当前无本版正式包</x:v>
       </x:c>
       <x:c r="I8" s="18" t="b">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J8" s="9" t="str">
-        <x:v>整版draft、未发布。27条产品TC未执行；3条CORE辅助TC已在文档提交48ca089独立切片就绪，在开发分支311deedf运行模块3/3 PASS，原始receipt在该分支.local/ci/tm003-core-20261001/。代码尚未合入本文档树，机器绑定保持空；模块报告不能作为产品E2E或发行门禁，结果Excel规范待SOP修订。 2026-10-02新代码候选44379e6已有逐步模块3/3与桌面29/29/typecheck/build原件；source_check独立Excel导出程序仍缺，批次登记BLOCKED，产品E2E仍NOT_RUN。 固定导出器新run tm003-core-20261001T163807Z在ea6b187候选生成3/3/9步source_check独立Excel并回读PASS，现已按被测SHA登记模块批次；原27条产品TC与发行仍NOT_RUN。 新清理合同候选d7c3d39的独立run tm003-core-20261001T165439Z亦3/3/9步及Excel回读PASS，作为最新模块批次；旧ea6批次保留。 后续CORE-04/05的测试输入已编制，程序未绑定、未执行；独立SOP-008切片复核待文档干净提交。 CORE04/05基于9efc6fa独立source_check 2/2、9步和Excel回读PASS，第17批次；CORE06新输入未执行，产品E2E NOT_RUN。 CORE06在eef956b的固定</x:v>
+        <x:v>设计基线已完成：3功能点、9 TASK、28父TC、35变体。开发工作树已有原生目录面板、加密locator、根FD受限读取、React授权UI及33个固定E2E叶入口（28可执行、5场景摘要）；报告单元59/59、治理473/473、构建PASS。产品E2E因AX trusted=false及隔离标准测试账号不可用BLOCKED，Keychain最终包隔离未证实。本独立文档树未合该代码，机器绑定仍planned；正式发行完整门禁NOT_RUN、未发布。0.2公开配置为version0.2.0/build200及测试高版0.2.1/build201，实际0.2包尚未证明。 2026-10-02修订SECURITY-01三个恶意字串变体的固定IPC method/字段/错误码，产品状态不变；需在整合候选重核基线及固定程序。 EVIDENCE-01新增第七固定负例，本版36变体；SECURITY-01仅profile准备目录纠错。新输入未执行，产品E2E仍NOT_RUN。 0cc4f3e候选包预检33条全BLOCKED、零产品步骤；缺显式独立test/excluded账号，App未启动；固定结果Excel缺失，根总表批次待登记。</x:v>
       </x:c>
       <x:c r="K8" s="9" t="str">
-        <x:v>TM-001 干净源码候选为技术基底；其产品门禁不继承给TM-003</x:v>
+        <x:v>TM001独立候选d2门禁PASS只属历史；本地master c2911bc首次最终包门禁FAIL、无SOP-020稳定原包，不能作为0.2升级源；本版无实际产品运行。</x:v>
       </x:c>
       <x:c r="L8" s="9" t="str">
-        <x:v>releases/v0.3.0-20261001T034652Z/00-manifest.json</x:v>
+        <x:v>releases/v0.2.0-20261001T034118Z/00-manifest.json</x:v>
       </x:c>
       <x:c r="M8" s="9" t="str">
-        <x:v>releases/v0.3.0-20261001T034652Z/06-iteration-record.md</x:v>
+        <x:v>releases/v0.2.0-20261001T034118Z/06-iteration-record.md</x:v>
       </x:c>
       <x:c r="N8" s="9" t="str">
         <x:v>未核实同名功能分支SHA/tree读回</x:v>
       </x:c>
       <x:c r="O8" s="9" t="str">
-        <x:v>CORE模块3/3只在独立开发分支PASS；真实安装App产品E2E未运行；本机稳定包未归档</x:v>
+        <x:v>产品E2E未执行；本机稳定包未归档</x:v>
       </x:c>
       <x:c r="P8" s="9" t="str">
         <x:v>本轮五版稳定后一次受保护PR；待办</x:v>
@@ -22295,128 +22307,128 @@
         <x:v>本轮五版稳定及远端master读回后逐版登记；待办</x:v>
       </x:c>
       <x:c r="R8" s="9" t="str">
+        <x:v>releases/v0.2.0-20261001T034118Z/01-requirements.md:32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="387" customHeight="1">
+      <x:c r="A9" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+      <x:c r="B9" s="4" t="str">
+        <x:v>0.3.0</x:v>
+      </x:c>
+      <x:c r="C9" s="16" t="n">
+        <x:v>46296.157546296294</x:v>
+      </x:c>
+      <x:c r="D9" s="4" t="str">
+        <x:v>产品功能</x:v>
+      </x:c>
+      <x:c r="E9" s="4" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="F9" s="4" t="str">
+        <x:v>未发布</x:v>
+      </x:c>
+      <x:c r="G9" s="4" t="str">
+        <x:v>internal</x:v>
+      </x:c>
+      <x:c r="H9" s="4" t="str">
+        <x:v>dmg/&lt;release_id&gt;/：正式包仅在本机门禁 PASS 后保存</x:v>
+      </x:c>
+      <x:c r="I9" s="15" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J9" s="4" t="str">
+        <x:v>整版draft、未发布。27条产品TC未执行；3条CORE辅助TC已在文档提交48ca089独立切片就绪，在开发分支311deedf运行模块3/3 PASS，原始receipt在该分支.local/ci/tm003-core-20261001/。代码尚未合入本文档树，机器绑定保持空；模块报告不能作为产品E2E或发行门禁，结果Excel规范待SOP修订。 2026-10-02新代码候选44379e6已有逐步模块3/3与桌面29/29/typecheck/build原件；source_check独立Excel导出程序仍缺，批次登记BLOCKED，产品E2E仍NOT_RUN。 固定导出器新run tm003-core-20261001T163807Z在ea6b187候选生成3/3/9步source_check独立Excel并回读PASS，现已按被测SHA登记模块批次；原27条产品TC与发行仍NOT_RUN。 新清理合同候选d7c3d39的独立run tm003-core-20261001T165439Z亦3/3/9步及Excel回读PASS，作为最新模块批次；旧ea6批次保留。 后续CORE-04/05的测试输入已编制，程序未绑定、未执行；独立SOP-008切片复核待文档干净提交。 CORE04/05基于9efc6fa独立source_check 2/2、9步和Excel回读PASS，第17批次；CORE06新输入未执行，产品E2E NOT_RUN。 CORE06在eef956b的固定</x:v>
+      </x:c>
+      <x:c r="K9" s="4" t="str">
+        <x:v>TM-001 干净源码候选为技术基底；其产品门禁不继承给TM-003</x:v>
+      </x:c>
+      <x:c r="L9" s="4" t="str">
+        <x:v>releases/v0.3.0-20261001T034652Z/00-manifest.json</x:v>
+      </x:c>
+      <x:c r="M9" s="4" t="str">
+        <x:v>releases/v0.3.0-20261001T034652Z/06-iteration-record.md</x:v>
+      </x:c>
+      <x:c r="N9" s="4" t="str">
+        <x:v>未核实同名功能分支SHA/tree读回</x:v>
+      </x:c>
+      <x:c r="O9" s="4" t="str">
+        <x:v>CORE模块3/3只在独立开发分支PASS；真实安装App产品E2E未运行；本机稳定包未归档</x:v>
+      </x:c>
+      <x:c r="P9" s="4" t="str">
+        <x:v>本轮五版稳定后一次受保护PR；待办</x:v>
+      </x:c>
+      <x:c r="Q9" s="4" t="str">
+        <x:v>本轮五版稳定及远端master读回后逐版登记；待办</x:v>
+      </x:c>
+      <x:c r="R9" s="4" t="str">
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="132" customHeight="1">
-      <x:c r="A9" s="4" t="str">
+    <x:row r="10" ht="132" customHeight="1">
+      <x:c r="A10" s="9" t="str">
         <x:v>v0.3.0-20261001T034652Z（续1）</x:v>
       </x:c>
-      <x:c r="B9" s="4" t="str"/>
-      <x:c r="C9" s="16" t="str"/>
-      <x:c r="D9" s="4" t="str"/>
-      <x:c r="E9" s="4" t="str"/>
-      <x:c r="F9" s="4" t="str"/>
-      <x:c r="G9" s="4" t="str"/>
-      <x:c r="H9" s="4" t="str"/>
-      <x:c r="I9" s="4" t="str"/>
-      <x:c r="J9" s="4" t="str">
+      <x:c r="B10" s="9" t="str"/>
+      <x:c r="C10" s="17" t="str"/>
+      <x:c r="D10" s="9" t="str"/>
+      <x:c r="E10" s="9" t="str"/>
+      <x:c r="F10" s="9" t="str"/>
+      <x:c r="G10" s="9" t="str"/>
+      <x:c r="H10" s="9" t="str"/>
+      <x:c r="I10" s="9" t="str"/>
+      <x:c r="J10" s="9" t="str">
         <x:v>source_check 1/1、四步与清理PASS，独立Excel回读PASS，第18批次；此前408ebf8红测失败保留。仅多文件模块，原27条产品TC与正式发行NOT_RUN。 CORE07主进程编排辅助TC已固定输入，程序/运行尚无。 CORE07在33b1ee1代码候选固定模块1/1五步PASS、Excel回读；真实App/大文件产品仍未验收。</x:v>
       </x:c>
-      <x:c r="K9" s="4" t="str"/>
-      <x:c r="L9" s="4" t="str"/>
-      <x:c r="M9" s="4" t="str"/>
-      <x:c r="N9" s="4" t="str"/>
-      <x:c r="O9" s="4" t="str"/>
-      <x:c r="P9" s="4" t="str"/>
-      <x:c r="Q9" s="4" t="str"/>
-      <x:c r="R9" s="4" t="str"/>
-    </x:row>
-    <x:row r="10" ht="237" customHeight="1">
-      <x:c r="A10" s="9" t="str">
+      <x:c r="K10" s="9" t="str"/>
+      <x:c r="L10" s="9" t="str"/>
+      <x:c r="M10" s="9" t="str"/>
+      <x:c r="N10" s="9" t="str"/>
+      <x:c r="O10" s="9" t="str"/>
+      <x:c r="P10" s="9" t="str"/>
+      <x:c r="Q10" s="9" t="str"/>
+      <x:c r="R10" s="9" t="str"/>
+    </x:row>
+    <x:row r="11" ht="237" customHeight="1">
+      <x:c r="A11" s="4" t="str">
         <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
-      <x:c r="B10" s="9" t="str">
+      <x:c r="B11" s="4" t="str">
         <x:v>0.4.0</x:v>
       </x:c>
-      <x:c r="C10" s="17" t="n">
+      <x:c r="C11" s="16" t="n">
         <x:v>46296.16982638889</x:v>
-      </x:c>
-      <x:c r="D10" s="9" t="str">
-        <x:v>产品功能</x:v>
-      </x:c>
-      <x:c r="E10" s="9" t="str">
-        <x:v>TM-004</x:v>
-      </x:c>
-      <x:c r="F10" s="9" t="str">
-        <x:v>未发布</x:v>
-      </x:c>
-      <x:c r="G10" s="9" t="str">
-        <x:v>internal</x:v>
-      </x:c>
-      <x:c r="H10" s="9" t="str">
-        <x:v>dmg/&lt;release_id&gt;/：仅门禁PASS后放正式DMG</x:v>
-      </x:c>
-      <x:c r="I10" s="18" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J10" s="9" t="str">
-        <x:v>整版draft、未发布。原20产品细TC及四组摘要保留，3条reader CORE辅助TC在输入提交fea41fe/同步SOP后的干净候选ebbcfd0上按SOP-008独立判为development_slice_ready；程序绑定仍空。本版代码分支e52b62e报告reader目标9/9、桌面49/49和build PASS，仅为模块原件，Excel/总表批次尚无固定导出器。产品授权、稳定文件身份最终接口、SQLite原子事务、IPC/App E2E未验证，正式发行门禁NOT_RUN。 新增CORE04/05合成主进程触发及三文件存储辅助输入：拒绝码、提交守卫、来源/根分域HMAC、scope代号、modelId哨兵与整代事务；两例程序未绑定/未运行，原20条产品TC与正式发行NOT_RUN。</x:v>
-      </x:c>
-      <x:c r="K10" s="9" t="str">
-        <x:v>TM004源分支原生零/缺失与nested Agent定向探针仅为研究证据；0.3及此前稳定原包尚未形成，真实升级BLOCKED。</x:v>
-      </x:c>
-      <x:c r="L10" s="9" t="str">
-        <x:v>releases/v0.4.0-20261001T040433Z/00-manifest.json</x:v>
-      </x:c>
-      <x:c r="M10" s="9" t="str">
-        <x:v>releases/v0.4.0-20261001T040433Z/06-iteration-record.md</x:v>
-      </x:c>
-      <x:c r="N10" s="9" t="str">
-        <x:v>未核实同名远端功能分支SHA/tree</x:v>
-      </x:c>
-      <x:c r="O10" s="9" t="str">
-        <x:v>最终包产品E2E未执行；本机稳定包未归档</x:v>
-      </x:c>
-      <x:c r="P10" s="9" t="str">
-        <x:v>全部目标版本稳定后待办</x:v>
-      </x:c>
-      <x:c r="Q10" s="9" t="str">
-        <x:v>远端master读回后逐版待办</x:v>
-      </x:c>
-      <x:c r="R10" s="9" t="str">
-        <x:v>未提供</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="372" customHeight="1">
-      <x:c r="A11" s="4" t="str">
-        <x:v>v0.5.0-20261001T034729Z</x:v>
-      </x:c>
-      <x:c r="B11" s="4" t="str">
-        <x:v>0.5.0</x:v>
-      </x:c>
-      <x:c r="C11" s="16" t="n">
-        <x:v>46296.15797453704</x:v>
       </x:c>
       <x:c r="D11" s="4" t="str">
         <x:v>产品功能</x:v>
       </x:c>
       <x:c r="E11" s="4" t="str">
-        <x:v>TM-005</x:v>
+        <x:v>TM-004</x:v>
       </x:c>
       <x:c r="F11" s="4" t="str">
-        <x:v>draft</x:v>
+        <x:v>未发布</x:v>
       </x:c>
       <x:c r="G11" s="4" t="str">
         <x:v>internal</x:v>
       </x:c>
       <x:c r="H11" s="4" t="str">
-        <x:v>dmg/&lt;release_id&gt;/：仅门禁PASS后放正式原名包</x:v>
+        <x:v>dmg/&lt;release_id&gt;/：仅门禁PASS后放正式DMG</x:v>
       </x:c>
       <x:c r="I11" s="15" t="b">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J11" s="4" t="str">
-        <x:v>整版draft、未发布。原32条产品父TC、6稳定变体和两组摘要保留；纯统计CORE-01/02/03辅助TC在输入提交061c759后，经SOP-008内容核对及结构/治理457项PASS，独立切片development_slice_ready，程序绑定仍为空、模块实际运行unexecuted。静态oracle与切片就绪不证明真实双来源采集或产品E2E；固定产品数据、SQLite/IPC、安装App逐TC绑定未完成，正式发行完整门禁NOT_RUN。 独立代码提交6a0f6f的source_check CORE3/3、桌面29/29、build PASS，原件在TM005工作树.local/tm005-core-postcommit-20261001T162401Z；程序尚未进入本文档树、模块Excel导出/批次登记BLOCKED，产品E2E仍NOT_RUN。 CORE-01仅验证已给UTC半开界聚合，不验证IANA日期换算；该单独辅助TC待固定。 新增CORE04/05固定IANA当地日与合成双来源SQLite只读快照辅助TC，程序null/unexecuted；coverage表无连续空日证明，原32产品TC/6变体与发行仍BLOCKED/NOT_RUN。 CORE04/05在259cf768候选固定模块分别1/1三/四步PASS且Excel回读；0.5产品E2E未运行。</x:v>
+        <x:v>整版draft、未发布。原20产品细TC及四组摘要保留，3条reader CORE辅助TC在输入提交fea41fe/同步SOP后的干净候选ebbcfd0上按SOP-008独立判为development_slice_ready；程序绑定仍空。本版代码分支e52b62e报告reader目标9/9、桌面49/49和build PASS，仅为模块原件，Excel/总表批次尚无固定导出器。产品授权、稳定文件身份最终接口、SQLite原子事务、IPC/App E2E未验证，正式发行门禁NOT_RUN。 新增CORE04/05合成主进程触发及三文件存储辅助输入：拒绝码、提交守卫、来源/根分域HMAC、scope代号、modelId哨兵与整代事务；两例程序未绑定/未运行，原20条产品TC与正式发行NOT_RUN。</x:v>
       </x:c>
       <x:c r="K11" s="4" t="str">
-        <x:v>TM005语义oracle只验证规范化样例；0.4及此前稳定原包尚未形成，真实升级BLOCKED。</x:v>
+        <x:v>TM004源分支原生零/缺失与nested Agent定向探针仅为研究证据；0.3及此前稳定原包尚未形成，真实升级BLOCKED。</x:v>
       </x:c>
       <x:c r="L11" s="4" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/00-manifest.json</x:v>
+        <x:v>releases/v0.4.0-20261001T040433Z/00-manifest.json</x:v>
       </x:c>
       <x:c r="M11" s="4" t="str">
-        <x:v>releases/v0.5.0-20261001T034729Z/06-iteration-record.md</x:v>
+        <x:v>releases/v0.4.0-20261001T040433Z/06-iteration-record.md</x:v>
       </x:c>
       <x:c r="N11" s="4" t="str">
         <x:v>未核实同名远端功能分支SHA/tree</x:v>
@@ -22434,25 +22446,81 @@
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
+    <x:row r="12" ht="372" customHeight="1">
+      <x:c r="A12" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+      <x:c r="B12" s="9" t="str">
+        <x:v>0.5.0</x:v>
+      </x:c>
+      <x:c r="C12" s="17" t="n">
+        <x:v>46296.15797453704</x:v>
+      </x:c>
+      <x:c r="D12" s="9" t="str">
+        <x:v>产品功能</x:v>
+      </x:c>
+      <x:c r="E12" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="F12" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="G12" s="9" t="str">
+        <x:v>internal</x:v>
+      </x:c>
+      <x:c r="H12" s="9" t="str">
+        <x:v>dmg/&lt;release_id&gt;/：仅门禁PASS后放正式原名包</x:v>
+      </x:c>
+      <x:c r="I12" s="18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J12" s="9" t="str">
+        <x:v>整版draft、未发布。原32条产品父TC、6稳定变体和两组摘要保留；纯统计CORE-01/02/03辅助TC在输入提交061c759后，经SOP-008内容核对及结构/治理457项PASS，独立切片development_slice_ready，程序绑定仍为空、模块实际运行unexecuted。静态oracle与切片就绪不证明真实双来源采集或产品E2E；固定产品数据、SQLite/IPC、安装App逐TC绑定未完成，正式发行完整门禁NOT_RUN。 独立代码提交6a0f6f的source_check CORE3/3、桌面29/29、build PASS，原件在TM005工作树.local/tm005-core-postcommit-20261001T162401Z；程序尚未进入本文档树、模块Excel导出/批次登记BLOCKED，产品E2E仍NOT_RUN。 CORE-01仅验证已给UTC半开界聚合，不验证IANA日期换算；该单独辅助TC待固定。 新增CORE04/05固定IANA当地日与合成双来源SQLite只读快照辅助TC，程序null/unexecuted；coverage表无连续空日证明，原32产品TC/6变体与发行仍BLOCKED/NOT_RUN。 CORE04/05在259cf768候选固定模块分别1/1三/四步PASS且Excel回读；0.5产品E2E未运行。</x:v>
+      </x:c>
+      <x:c r="K12" s="9" t="str">
+        <x:v>TM005语义oracle只验证规范化样例；0.4及此前稳定原包尚未形成，真实升级BLOCKED。</x:v>
+      </x:c>
+      <x:c r="L12" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/00-manifest.json</x:v>
+      </x:c>
+      <x:c r="M12" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/06-iteration-record.md</x:v>
+      </x:c>
+      <x:c r="N12" s="9" t="str">
+        <x:v>未核实同名远端功能分支SHA/tree</x:v>
+      </x:c>
+      <x:c r="O12" s="9" t="str">
+        <x:v>最终包产品E2E未执行；本机稳定包未归档</x:v>
+      </x:c>
+      <x:c r="P12" s="9" t="str">
+        <x:v>全部目标版本稳定后待办</x:v>
+      </x:c>
+      <x:c r="Q12" s="9" t="str">
+        <x:v>远端master读回后逐版待办</x:v>
+      </x:c>
+      <x:c r="R12" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="F5:F11">
+  <x:conditionalFormatting sqref="F5:F12">
     <x:cfRule type="containsText" dxfId="33" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="34" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="35" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="J5:J11">
+  <x:conditionalFormatting sqref="J5:J12">
     <x:cfRule type="containsText" dxfId="36" priority="4" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="37" priority="5" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="38" priority="6" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="M5:M11">
+  <x:conditionalFormatting sqref="M5:M12">
     <x:cfRule type="containsText" dxfId="39" priority="7" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="40" priority="8" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="41" priority="9" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89616e7d2e0e4eb1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2089892258904863"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23617,7 +23685,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra20c7708a25d4ed0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R404a1b5e6b9340bc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TokenMeter项目总表.xlsx
+++ b/TokenMeter项目总表.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R1f7ef9a4ca614d99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="R62e780c2444344e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R60dae5e928114473"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R9308ab9f90f544f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="Re62843944cd844b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R0ff9868f11644f92"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R898bf95a4d9244fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="Rea61de4a51cd48f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="R1feb460eca984418"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="Ra29fb61db43d4d85"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R796669df95fa49cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R973aa54391a44687"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="R4b282092e32c43aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="Re5467380387b4478"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R1a9ed1474af742ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R818f478a06e9428b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R4eb2b9217f744629"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="Rbeb17a9fa52442f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="Rb5b62cb9daf04f49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Rfcecf67b1b7b400d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="Rd322f63fd3ee45ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="Re9b54c41d0cc48b8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1288,7 +1288,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60d54a6ba0224a79"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf48705fa661a4a3f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1996,7 +1996,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38fc160fbd0e4883"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61c84bf56a834a1a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2145,7 +2145,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R563a38c6851b4300"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17a167dc21124505"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2580,7 +2580,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d53b72e0f624a4a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ddb6023d1a64466"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3627,7 +3627,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R94b7439a0de84eb9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8099e739fb554904"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4734,7 +4734,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf81feecdfec4aec"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8cdb253d7d7435b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7519,7 +7519,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra59ff02bbe264520"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R304ed94fc7994fdf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18586,7 +18586,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L236" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:265</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:267</x:v>
       </x:c>
       <x:c r="M236" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -18633,7 +18633,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L237" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:269</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:271</x:v>
       </x:c>
       <x:c r="M237" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -18680,7 +18680,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L238" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:273</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:275</x:v>
       </x:c>
       <x:c r="M238" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -18728,7 +18728,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L239" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:277</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:279</x:v>
       </x:c>
       <x:c r="M239" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -18778,7 +18778,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L240" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:281</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:283</x:v>
       </x:c>
       <x:c r="M240" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -18826,7 +18826,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L241" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:285</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:287</x:v>
       </x:c>
       <x:c r="M241" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -18873,7 +18873,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L242" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:289</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:291</x:v>
       </x:c>
       <x:c r="M242" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -18920,7 +18920,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L243" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:293</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:295</x:v>
       </x:c>
       <x:c r="M243" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -18968,7 +18968,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L244" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:297</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:299</x:v>
       </x:c>
       <x:c r="M244" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19017,7 +19017,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L245" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:301</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:303</x:v>
       </x:c>
       <x:c r="M245" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19066,7 +19066,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L246" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:305</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:307</x:v>
       </x:c>
       <x:c r="M246" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19115,7 +19115,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L247" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:309</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:311</x:v>
       </x:c>
       <x:c r="M247" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19162,7 +19162,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L248" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:313</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:315</x:v>
       </x:c>
       <x:c r="M248" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19210,7 +19210,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L249" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:317</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:319</x:v>
       </x:c>
       <x:c r="M249" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19258,7 +19258,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L250" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:321</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:323</x:v>
       </x:c>
       <x:c r="M250" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19306,7 +19306,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L251" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:325</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:327</x:v>
       </x:c>
       <x:c r="M251" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19354,7 +19354,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L252" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:329</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:331</x:v>
       </x:c>
       <x:c r="M252" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19404,7 +19404,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L253" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:333</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:335</x:v>
       </x:c>
       <x:c r="M253" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19451,7 +19451,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L254" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:337</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:339</x:v>
       </x:c>
       <x:c r="M254" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19498,7 +19498,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L255" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:341</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:343</x:v>
       </x:c>
       <x:c r="M255" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19546,7 +19546,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L256" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:345</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:347</x:v>
       </x:c>
       <x:c r="M256" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19595,7 +19595,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L257" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:349</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:351</x:v>
       </x:c>
       <x:c r="M257" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19645,7 +19645,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L258" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:353</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:355</x:v>
       </x:c>
       <x:c r="M258" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19693,7 +19693,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L259" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:357</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:359</x:v>
       </x:c>
       <x:c r="M259" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19742,7 +19742,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L260" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:361</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:363</x:v>
       </x:c>
       <x:c r="M260" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19790,7 +19790,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L261" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:365</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:367</x:v>
       </x:c>
       <x:c r="M261" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19838,7 +19838,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L262" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:369</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:371</x:v>
       </x:c>
       <x:c r="M262" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19886,7 +19886,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L263" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:373</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:375</x:v>
       </x:c>
       <x:c r="M263" s="4" t="str">
         <x:v>tm003-core-20261001T165439Z (source_check；产品E2E未运行)</x:v>
@@ -19935,7 +19935,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L264" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:377</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:379</x:v>
       </x:c>
       <x:c r="M264" s="9" t="str">
         <x:v>tm003-core-20261001T165439Z (source_check；产品E2E未运行)</x:v>
@@ -19983,7 +19983,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L265" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:381</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:383</x:v>
       </x:c>
       <x:c r="M265" s="4" t="str">
         <x:v>tm003-core-20261001T165439Z (source_check；产品E2E未运行)</x:v>
@@ -20184,7 +20184,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L269" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:243</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:245</x:v>
       </x:c>
       <x:c r="M269" s="4" t="str">
         <x:v>tm003-core07-20261001T200438Z</x:v>
@@ -20704,7 +20704,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R295b2eb23bc04eaa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd02653cdd09d44aa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22028,7 +22028,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfefa159669d54fe7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5886ec758ee247c3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22520,7 +22520,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2089892258904863"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9107288e920e4826"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23685,7 +23685,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R404a1b5e6b9340bc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R371e5cbd4c204476"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TokenMeter项目总表.xlsx
+++ b/TokenMeter项目总表.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R973aa54391a44687"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="R4b282092e32c43aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="Re5467380387b4478"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R1a9ed1474af742ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R818f478a06e9428b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R4eb2b9217f744629"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="Rbeb17a9fa52442f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="Rb5b62cb9daf04f49"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Rfcecf67b1b7b400d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="Rd322f63fd3ee45ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="Re9b54c41d0cc48b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R25c7ef4d21ef4fd4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="R5d7a18cf723244dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R845ee3a915ea440d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="Red87944f69614163"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="Rcafe748a060048ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R1f583954536444c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R34eb875fe06146a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="Ra5887627fa414360"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Re6430d6359494dd9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="Ra807e13620044663"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="Rc40f3b57de954f70"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -809,8 +809,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TMTable7" displayName="TMTable7" ref="A4:N32" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:N32"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TMTable7" displayName="TMTable7" ref="A4:N39" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:N39"/>
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="运行批次"/>
     <x:tableColumn id="2" name="版本"/>
@@ -1146,8 +1146,8 @@
         <x:v>测试批次</x:v>
       </x:c>
       <x:c r="B9" s="10" t="n">
-        <x:f>COUNTA('06测试批次'!A5:A32)</x:f>
-        <x:v>28</x:v>
+        <x:f>COUNTA('06测试批次'!A5:A39)</x:f>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C9" s="4" t="str">
         <x:v>06测试批次，每次运行一行，记录独立结果Excel位置</x:v>
@@ -1263,7 +1263,7 @@
         <x:v>DMG及原始证据留本机；Git保存代码、文档和此工作簿</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="87" customHeight="1">
+    <x:row r="20" ht="72" customHeight="1">
       <x:c r="A20" s="9" t="str">
         <x:v>最近登记批次</x:v>
       </x:c>
@@ -1271,7 +1271,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="C20" s="9" t="str">
-        <x:v>product_e2e · TASK-TM001-ADMIN；ADMIN-01..06六父TC及ADMIN-02/05下五固定变体，九真实App执行加两父例派生：6父+5变体共11/11报告行PASS、33步、清理完成；ADMIN-02/05父例由变体派生。独立审计仅ADMIN-03 PASS，非12项完整审计。仅709d管理员功能定向，其他TM001功能、旧c291完整门禁FAIL及正式发行NOT_RUN。；是否覆盖完整产品回归以批次范围和原始证据为准。</x:v>
+        <x:v>source_check · TM-003 tm003-core07整合候选固定辅助模块；非产品E2E：1/1固定TC、5步与owner清理PASS；固定source_check导出及verification回读PASS。仅本整合候选的模块合同，产品App/授权/Keychain及发行均NOT_RUN。；是否覆盖完整产品回归以批次范围和原始证据为准。</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="32" customHeight="1">
@@ -1288,7 +1288,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf48705fa661a4a3f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1fb220f0980b4fa0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1996,7 +1996,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61c84bf56a834a1a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R946b9d11108544ec"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2145,7 +2145,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17a167dc21124505"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4f8eb3da8f543fb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2580,7 +2580,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ddb6023d1a64466"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R617d7812655a4209"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3627,7 +3627,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8099e739fb554904"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59b954f88c1d42a2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4734,7 +4734,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8cdb253d7d7435b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8865092385ba41ea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7519,7 +7519,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R304ed94fc7994fdf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd10e713cd477473d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10177,7 +10177,7 @@
         <x:v>docs/testing/cases/01b-TM-001-session-admin-release-scenarios.md:435</x:v>
       </x:c>
       <x:c r="M58" s="9" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-a9e4d3d99b6f4997b2f5df32a8d95563</x:v>
       </x:c>
       <x:c r="N58" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -10226,7 +10226,7 @@
         <x:v>docs/testing/cases/01b-TM-001-session-admin-release-scenarios.md:452</x:v>
       </x:c>
       <x:c r="M59" s="4" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-a9e4d3d99b6f4997b2f5df32a8d95563</x:v>
       </x:c>
       <x:c r="N59" s="4" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -10276,7 +10276,7 @@
         <x:v>docs/testing/cases/01b-TM-001-session-admin-release-scenarios.md:469</x:v>
       </x:c>
       <x:c r="M60" s="9" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-a9e4d3d99b6f4997b2f5df32a8d95563</x:v>
       </x:c>
       <x:c r="N60" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -10325,7 +10325,7 @@
         <x:v>docs/testing/cases/01b-TM-001-session-admin-release-scenarios.md:487</x:v>
       </x:c>
       <x:c r="M61" s="4" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-a9e4d3d99b6f4997b2f5df32a8d95563</x:v>
       </x:c>
       <x:c r="N61" s="4" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -10375,7 +10375,7 @@
         <x:v>docs/testing/cases/01b-TM-001-session-admin-release-scenarios.md:504</x:v>
       </x:c>
       <x:c r="M62" s="9" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-a9e4d3d99b6f4997b2f5df32a8d95563</x:v>
       </x:c>
       <x:c r="N62" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -10425,7 +10425,7 @@
         <x:v>docs/testing/cases/01b-TM-001-session-admin-release-scenarios.md:522</x:v>
       </x:c>
       <x:c r="M63" s="4" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-a9e4d3d99b6f4997b2f5df32a8d95563</x:v>
       </x:c>
       <x:c r="N63" s="4" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -10474,7 +10474,7 @@
         <x:v>docs/testing/cases/01b-TM-001-session-admin-release-scenarios.md:542</x:v>
       </x:c>
       <x:c r="M64" s="9" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-6f929a978dc54f608824992e10d7ef1b</x:v>
       </x:c>
       <x:c r="N64" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -10522,7 +10522,7 @@
         <x:v>docs/testing/cases/01b-TM-001-session-admin-release-scenarios.md:559</x:v>
       </x:c>
       <x:c r="M65" s="4" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-6f929a978dc54f608824992e10d7ef1b</x:v>
       </x:c>
       <x:c r="N65" s="4" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -10571,7 +10571,7 @@
         <x:v>docs/testing/cases/01b-TM-001-session-admin-release-scenarios.md:575</x:v>
       </x:c>
       <x:c r="M66" s="9" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-6f929a978dc54f608824992e10d7ef1b</x:v>
       </x:c>
       <x:c r="N66" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -10620,7 +10620,7 @@
         <x:v>docs/testing/cases/01b-TM-001-session-admin-release-scenarios.md:592</x:v>
       </x:c>
       <x:c r="M67" s="4" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-6f929a978dc54f608824992e10d7ef1b</x:v>
       </x:c>
       <x:c r="N67" s="4" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -10720,7 +10720,7 @@
         <x:v>docs/testing/cases/01b-TM-001-session-admin-release-scenarios.md:632</x:v>
       </x:c>
       <x:c r="M69" s="4" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-8c8930fe7be44ef88bdf56a41b74900c</x:v>
       </x:c>
       <x:c r="N69" s="4" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -10770,7 +10770,7 @@
         <x:v>docs/testing/cases/01b-TM-001-session-admin-release-scenarios.md:650</x:v>
       </x:c>
       <x:c r="M70" s="9" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-8c8930fe7be44ef88bdf56a41b74900c</x:v>
       </x:c>
       <x:c r="N70" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -10820,7 +10820,7 @@
         <x:v>docs/testing/cases/01b-TM-001-session-admin-release-scenarios.md:668</x:v>
       </x:c>
       <x:c r="M71" s="4" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-8c8930fe7be44ef88bdf56a41b74900c</x:v>
       </x:c>
       <x:c r="N71" s="4" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -19889,7 +19889,7 @@
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:375</x:v>
       </x:c>
       <x:c r="M263" s="4" t="str">
-        <x:v>tm003-core-20261001T165439Z (source_check；产品E2E未运行)</x:v>
+        <x:v>tm003-core-20261001T203711Z</x:v>
       </x:c>
       <x:c r="N263" s="4" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
@@ -19938,7 +19938,7 @@
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:379</x:v>
       </x:c>
       <x:c r="M264" s="9" t="str">
-        <x:v>tm003-core-20261001T165439Z (source_check；产品E2E未运行)</x:v>
+        <x:v>tm003-core-20261001T203711Z</x:v>
       </x:c>
       <x:c r="N264" s="9" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
@@ -19986,7 +19986,7 @@
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:383</x:v>
       </x:c>
       <x:c r="M265" s="4" t="str">
-        <x:v>tm003-core-20261001T165439Z (source_check；产品E2E未运行)</x:v>
+        <x:v>tm003-core-20261001T203711Z</x:v>
       </x:c>
       <x:c r="N265" s="4" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
@@ -20035,7 +20035,7 @@
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:203</x:v>
       </x:c>
       <x:c r="M266" s="9" t="str">
-        <x:v>tm003-core45-20261001T175000Z (source_check；产品E2E未运行)</x:v>
+        <x:v>tm003-core45-20261001T203711Z</x:v>
       </x:c>
       <x:c r="N266" s="9" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
@@ -20086,7 +20086,7 @@
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:216</x:v>
       </x:c>
       <x:c r="M267" s="4" t="str">
-        <x:v>tm003-core45-20261001T175000Z (source_check；产品E2E未运行)</x:v>
+        <x:v>tm003-core45-20261001T203711Z</x:v>
       </x:c>
       <x:c r="N267" s="4" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
@@ -20136,7 +20136,7 @@
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:230</x:v>
       </x:c>
       <x:c r="M268" s="9" t="str">
-        <x:v>tm003-core06-20261001T182500Z (source_check；产品E2E未运行)</x:v>
+        <x:v>tm003-core06-20261001T203711Z</x:v>
       </x:c>
       <x:c r="N268" s="9" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
@@ -20187,7 +20187,7 @@
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:245</x:v>
       </x:c>
       <x:c r="M269" s="4" t="str">
-        <x:v>tm003-core07-20261001T200438Z</x:v>
+        <x:v>tm003-core07-20261001T203711Z</x:v>
       </x:c>
       <x:c r="N269" s="4" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
@@ -20704,7 +20704,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd02653cdd09d44aa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R159a1893198944d3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22010,25 +22010,333 @@
         <x:v>PASS</x:v>
       </x:c>
     </x:row>
+    <x:row r="33" ht="42" customHeight="1">
+      <x:c r="A33" s="4" t="str">
+        <x:v>local-a9e4d3d99b6f4997b2f5df32a8d95563</x:v>
+      </x:c>
+      <x:c r="B33" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+      <x:c r="C33" s="4" t="str">
+        <x:v>product_e2e</x:v>
+      </x:c>
+      <x:c r="D33" s="4" t="str">
+        <x:v>TASK-TM001-CONFIG；CONFIG-01..06六父TC真实App定向</x:v>
+      </x:c>
+      <x:c r="E33" s="4" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F33" s="4" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G33" s="4" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H33" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I33" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J33" s="4" t="str">
+        <x:v>709d21253a0f88bc703a431cbf3adba3df17e508</x:v>
+      </x:c>
+      <x:c r="K33" s="4" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="L33" s="4" t="str">
+        <x:v>6父6/6行、27步、清理PASS；六父例独立审计PASS。仅709d配置功能定向，其他TM001及正式门禁未通过。</x:v>
+      </x:c>
+      <x:c r="M33" s="4" t="str">
+        <x:v>.local/test-results/local-a9e4d3d99b6f4997b2f5df32a8d95563/TokenMeter测试结果-local-a9e4d3d99b6f4997b2f5df32a8d95563.xlsx</x:v>
+      </x:c>
+      <x:c r="N33" s="4" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="42" customHeight="1">
+      <x:c r="A34" s="9" t="str">
+        <x:v>local-6f929a978dc54f608824992e10d7ef1b</x:v>
+      </x:c>
+      <x:c r="B34" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+      <x:c r="C34" s="9" t="str">
+        <x:v>product_e2e</x:v>
+      </x:c>
+      <x:c r="D34" s="9" t="str">
+        <x:v>TASK-TM001-UPDATE；UPDATE-01..04四父TC真实App定向</x:v>
+      </x:c>
+      <x:c r="E34" s="9" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F34" s="9" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G34" s="9" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H34" s="9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I34" s="9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J34" s="9" t="str">
+        <x:v>709d21253a0f88bc703a431cbf3adba3df17e508</x:v>
+      </x:c>
+      <x:c r="K34" s="9" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="L34" s="9" t="str">
+        <x:v>4父4/4行、15步、清理PASS；仅UPDATE-01/04两项独立审计PASS。UPDATE-05另见第16批次，UPDATE-06..08另测；旧完整门禁FAIL不变。</x:v>
+      </x:c>
+      <x:c r="M34" s="9" t="str">
+        <x:v>.local/test-results/local-6f929a978dc54f608824992e10d7ef1b/TokenMeter测试结果-local-6f929a978dc54f608824992e10d7ef1b.xlsx</x:v>
+      </x:c>
+      <x:c r="N34" s="9" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="42" customHeight="1">
+      <x:c r="A35" s="4" t="str">
+        <x:v>local-8c8930fe7be44ef88bdf56a41b74900c</x:v>
+      </x:c>
+      <x:c r="B35" s="4" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+      <x:c r="C35" s="4" t="str">
+        <x:v>product_e2e</x:v>
+      </x:c>
+      <x:c r="D35" s="4" t="str">
+        <x:v>TASK-TM001-UPDATE；UPDATE-06..08三父TC真实App定向</x:v>
+      </x:c>
+      <x:c r="E35" s="4" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F35" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G35" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H35" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I35" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J35" s="4" t="str">
+        <x:v>709d21253a0f88bc703a431cbf3adba3df17e508</x:v>
+      </x:c>
+      <x:c r="K35" s="4" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="L35" s="4" t="str">
+        <x:v>3父3/3行、15步、清理PASS；仅UPDATE-07独立审计PASS。709d UPDATE父例及13变体分散于三个定向批次，不构成整体门禁。</x:v>
+      </x:c>
+      <x:c r="M35" s="4" t="str">
+        <x:v>.local/test-results/local-8c8930fe7be44ef88bdf56a41b74900c/TokenMeter测试结果-local-8c8930fe7be44ef88bdf56a41b74900c.xlsx</x:v>
+      </x:c>
+      <x:c r="N35" s="4" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="42" customHeight="1">
+      <x:c r="A36" s="9" t="str">
+        <x:v>tm003-core-20261001T203711Z</x:v>
+      </x:c>
+      <x:c r="B36" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+      <x:c r="C36" s="9" t="str">
+        <x:v>source_check</x:v>
+      </x:c>
+      <x:c r="D36" s="9" t="str">
+        <x:v>TM-003 tm003-core整合候选固定辅助模块；非产品E2E</x:v>
+      </x:c>
+      <x:c r="E36" s="9" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F36" s="9" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G36" s="9" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H36" s="9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I36" s="9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J36" s="9" t="str">
+        <x:v>23241734f7821ee7664e3dae5104d68699d990a4</x:v>
+      </x:c>
+      <x:c r="K36" s="9" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="L36" s="9" t="str">
+        <x:v>3/3固定TC、9步与owner清理PASS；固定source_check导出及verification回读PASS。仅本整合候选的模块合同，产品App/授权/Keychain及发行均NOT_RUN。</x:v>
+      </x:c>
+      <x:c r="M36" s="9" t="str">
+        <x:v>.local/test-results/tm003-core-20261001T203711Z/TokenMeter测试结果-tm003-core-20261001T203711Z.xlsx</x:v>
+      </x:c>
+      <x:c r="N36" s="9" t="str">
+        <x:v>NOT_RUN</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="42" customHeight="1">
+      <x:c r="A37" s="4" t="str">
+        <x:v>tm003-core45-20261001T203711Z</x:v>
+      </x:c>
+      <x:c r="B37" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+      <x:c r="C37" s="4" t="str">
+        <x:v>source_check</x:v>
+      </x:c>
+      <x:c r="D37" s="4" t="str">
+        <x:v>TM-003 tm003-core45整合候选固定辅助模块；非产品E2E</x:v>
+      </x:c>
+      <x:c r="E37" s="4" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F37" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G37" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H37" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I37" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J37" s="4" t="str">
+        <x:v>23241734f7821ee7664e3dae5104d68699d990a4</x:v>
+      </x:c>
+      <x:c r="K37" s="4" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="L37" s="4" t="str">
+        <x:v>2/2固定TC、9步与owner清理PASS；固定source_check导出及verification回读PASS。仅本整合候选的模块合同，产品App/授权/Keychain及发行均NOT_RUN。</x:v>
+      </x:c>
+      <x:c r="M37" s="4" t="str">
+        <x:v>.local/test-results/tm003-core45-20261001T203711Z/TokenMeter测试结果-tm003-core45-20261001T203711Z.xlsx</x:v>
+      </x:c>
+      <x:c r="N37" s="4" t="str">
+        <x:v>NOT_RUN</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="42" customHeight="1">
+      <x:c r="A38" s="9" t="str">
+        <x:v>tm003-core06-20261001T203711Z</x:v>
+      </x:c>
+      <x:c r="B38" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+      <x:c r="C38" s="9" t="str">
+        <x:v>source_check</x:v>
+      </x:c>
+      <x:c r="D38" s="9" t="str">
+        <x:v>TM-003 tm003-core06整合候选固定辅助模块；非产品E2E</x:v>
+      </x:c>
+      <x:c r="E38" s="9" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F38" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G38" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H38" s="9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I38" s="9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J38" s="9" t="str">
+        <x:v>23241734f7821ee7664e3dae5104d68699d990a4</x:v>
+      </x:c>
+      <x:c r="K38" s="9" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="L38" s="9" t="str">
+        <x:v>1/1固定TC、4步与owner清理PASS；固定source_check导出及verification回读PASS。仅本整合候选的模块合同，产品App/授权/Keychain及发行均NOT_RUN。</x:v>
+      </x:c>
+      <x:c r="M38" s="9" t="str">
+        <x:v>.local/test-results/tm003-core06-20261001T203711Z/TokenMeter测试结果-tm003-core06-20261001T203711Z.xlsx</x:v>
+      </x:c>
+      <x:c r="N38" s="9" t="str">
+        <x:v>NOT_RUN</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="42" customHeight="1">
+      <x:c r="A39" s="4" t="str">
+        <x:v>tm003-core07-20261001T203711Z</x:v>
+      </x:c>
+      <x:c r="B39" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+      <x:c r="C39" s="4" t="str">
+        <x:v>source_check</x:v>
+      </x:c>
+      <x:c r="D39" s="4" t="str">
+        <x:v>TM-003 tm003-core07整合候选固定辅助模块；非产品E2E</x:v>
+      </x:c>
+      <x:c r="E39" s="4" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F39" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G39" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H39" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I39" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J39" s="4" t="str">
+        <x:v>23241734f7821ee7664e3dae5104d68699d990a4</x:v>
+      </x:c>
+      <x:c r="K39" s="4" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="L39" s="4" t="str">
+        <x:v>1/1固定TC、5步与owner清理PASS；固定source_check导出及verification回读PASS。仅本整合候选的模块合同，产品App/授权/Keychain及发行均NOT_RUN。</x:v>
+      </x:c>
+      <x:c r="M39" s="4" t="str">
+        <x:v>.local/test-results/tm003-core07-20261001T203711Z/TokenMeter测试结果-tm003-core07-20261001T203711Z.xlsx</x:v>
+      </x:c>
+      <x:c r="N39" s="4" t="str">
+        <x:v>NOT_RUN</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="E5:E32">
+  <x:conditionalFormatting sqref="E5:E39">
     <x:cfRule type="containsText" dxfId="24" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="25" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="26" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="M5:M32">
+  <x:conditionalFormatting sqref="M5:M39">
     <x:cfRule type="containsText" dxfId="27" priority="4" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="28" priority="5" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="29" priority="6" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="N5:N32">
+  <x:conditionalFormatting sqref="N5:N39">
     <x:cfRule type="containsText" dxfId="30" priority="7" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="31" priority="8" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="32" priority="9" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5886ec758ee247c3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa546b87be274fd7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22520,7 +22828,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9107288e920e4826"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8172fa1e86d4ef5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23685,7 +23993,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R371e5cbd4c204476"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb53fa82bde54715"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TokenMeter项目总表.xlsx
+++ b/TokenMeter项目总表.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R25c7ef4d21ef4fd4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="R5d7a18cf723244dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R845ee3a915ea440d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="Red87944f69614163"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="Rcafe748a060048ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R1f583954536444c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R34eb875fe06146a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="Ra5887627fa414360"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Re6430d6359494dd9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="Ra807e13620044663"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="Rc40f3b57de954f70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R4d5e79bc3cf34b82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Rae8bfd785b544c9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R614371cc937644a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R95f19b7b2ae84d15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R12729d999cb247fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R7050cb4a43fc4fab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R0c70f567e13d4892"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R3d6767aa932b49ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Rf52d0edfcbbb4473"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="Raf81eb3f16d64d0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R1632fb0aa65e4b6c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1288,7 +1288,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1fb220f0980b4fa0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd30e9130706149f9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1996,7 +1996,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R946b9d11108544ec"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9cf139ab3904095"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2145,7 +2145,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4f8eb3da8f543fb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R30a108f2a98b4bed"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2580,7 +2580,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R617d7812655a4209"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56e8401ed4aa4a36"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3627,7 +3627,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59b954f88c1d42a2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7cfeb4e6c68e4845"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4734,7 +4734,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8865092385ba41ea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41a2e8da96a2445a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7519,7 +7519,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd10e713cd477473d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25043e0a708f4375"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20704,7 +20704,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R159a1893198944d3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3eb9cbcd99cc45a1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22336,7 +22336,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa546b87be274fd7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b08fedd6fef434d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22828,7 +22828,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8172fa1e86d4ef5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb0706c88ee02424c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23993,7 +23993,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb53fa82bde54715"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7fa1ec01202f4d85"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TokenMeter项目总表.xlsx
+++ b/TokenMeter项目总表.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R4d5e79bc3cf34b82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Rae8bfd785b544c9a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R614371cc937644a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R95f19b7b2ae84d15"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R12729d999cb247fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R7050cb4a43fc4fab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R0c70f567e13d4892"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R3d6767aa932b49ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Rf52d0edfcbbb4473"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="Raf81eb3f16d64d0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R1632fb0aa65e4b6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R3cb0d6bcdf5b4d60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Rc165cd0df46944a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="Rdd922679d5dc4e6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R200b34690b774c08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R803defdb9bef407a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="Rcc23deb0274f41c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R14ea53fc1d944102"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R79ce0cdc2a9b4f2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Rc84140b5b6f04fdb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R573be4995ee74c91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R61bd3827d3904eb5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -765,8 +765,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="TMTable5" displayName="TMTable5" ref="A4:L73" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:L73"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="TMTable5" displayName="TMTable5" ref="A4:L76" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:L76"/>
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="任务编号"/>
     <x:tableColumn id="2" name="层级"/>
@@ -786,8 +786,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TMTable6" displayName="TMTable6" ref="A4:N279" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:N279"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TMTable6" displayName="TMTable6" ref="A4:N282" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:N282"/>
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="功能编号"/>
     <x:tableColumn id="2" name="用例编号"/>
@@ -1134,8 +1134,8 @@
         <x:v>已登记用例</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:f>COUNTA('05测试用例'!B5:B279)</x:f>
-        <x:v>275</x:v>
+        <x:f>COUNTA('05测试用例'!B5:B282)</x:f>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="C8" s="9" t="str">
         <x:v>父用例与具有稳定 ID 的变体各占一行；含未来概要场景</x:v>
@@ -1169,7 +1169,7 @@
         <x:v>界面与治理检查</x:v>
       </x:c>
       <x:c r="B11" s="10" t="n">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C11" s="4" t="str">
         <x:v>辅助检查不能替代产品E2E；稳定变体独立列出</x:v>
@@ -1288,7 +1288,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd30e9130706149f9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R78890397488e4ca9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1996,7 +1996,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9cf139ab3904095"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59713f1f5768440e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2145,7 +2145,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R30a108f2a98b4bed"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64341a0fc6234bb4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2580,7 +2580,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56e8401ed4aa4a36"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e47d71ac7c345b3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3627,7 +3627,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7cfeb4e6c68e4845"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd30a4ebacc7468f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4734,7 +4734,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41a2e8da96a2445a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0db642e62fc64cc4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6516,7 +6516,7 @@
         <x:v>规划中</x:v>
       </x:c>
       <x:c r="K48" s="9" t="str">
-        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:26</x:v>
+        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:29</x:v>
       </x:c>
       <x:c r="L48" s="9" t="str">
         <x:v>未提供</x:v>
@@ -6556,7 +6556,7 @@
         <x:v>规划中</x:v>
       </x:c>
       <x:c r="K49" s="4" t="str">
-        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:27</x:v>
+        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:30</x:v>
       </x:c>
       <x:c r="L49" s="4" t="str">
         <x:v>未提供</x:v>
@@ -6596,7 +6596,7 @@
         <x:v>规划中</x:v>
       </x:c>
       <x:c r="K50" s="9" t="str">
-        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:28</x:v>
+        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:31</x:v>
       </x:c>
       <x:c r="L50" s="9" t="str">
         <x:v>未提供</x:v>
@@ -6638,7 +6638,7 @@
         <x:v>规划中</x:v>
       </x:c>
       <x:c r="K51" s="4" t="str">
-        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:29</x:v>
+        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:32</x:v>
       </x:c>
       <x:c r="L51" s="4" t="str">
         <x:v>未提供</x:v>
@@ -6680,7 +6680,7 @@
         <x:v>规划中</x:v>
       </x:c>
       <x:c r="K52" s="9" t="str">
-        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:30</x:v>
+        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:33</x:v>
       </x:c>
       <x:c r="L52" s="9" t="str">
         <x:v>未提供</x:v>
@@ -7245,123 +7245,130 @@
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="67" ht="32" customHeight="1">
+    <x:row r="67" ht="87" customHeight="1">
       <x:c r="A67" s="4" t="str">
-        <x:v>TASK-TM001-PLAN</x:v>
+        <x:v>TASK-TM003-SECRET</x:v>
       </x:c>
       <x:c r="B67" s="4" t="str">
-        <x:v>历史分组</x:v>
+        <x:v>具体任务</x:v>
       </x:c>
       <x:c r="C67" s="4" t="str">
+        <x:v>FP-TM003-02</x:v>
+      </x:c>
+      <x:c r="D67" s="4" t="str">
+        <x:v>REQ-TM003</x:v>
+      </x:c>
+      <x:c r="E67" s="4" t="str">
+        <x:v>AC-TM003-002
+AC-TM003-004</x:v>
+      </x:c>
+      <x:c r="F67" s="4" t="str">
+        <x:v>IDENTITY/STORE已定合同；可替换加密端口及本例私有profile，独立于真实Keychain产品验证</x:v>
+      </x:c>
+      <x:c r="G67" s="4" t="str">
+        <x:v>产物：TM-003独占私有32字节密钥生命周期、origin+account.id 的 usage-principal-v1 HMAC、0600密文、缺失/损坏/错键停采集；产品默认系统随机源与macOS系统密钥保护，无明文回退
+完成条件：固定公开向量、重启同键、不同主体隔离；既有库缺/坏密文零重键零改库，安全失败；只在owner根测试</x:v>
+      </x:c>
+      <x:c r="H67" s="4" t="str">
+        <x:v>IDENTITY/STORE已定合同；可替换加密端口及本例私有profile，独立于真实Keychain产品验证</x:v>
+      </x:c>
+      <x:c r="I67" s="4" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="D67" s="4" t="str">
-        <x:v>REQ-TM001</x:v>
-      </x:c>
-      <x:c r="E67" s="4" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="F67" s="4" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="G67" s="4" t="str">
-        <x:v>六文档、完整追踪、SOP 修正、基线通过</x:v>
-      </x:c>
-      <x:c r="H67" s="4" t="str">
-        <x:v>需求</x:v>
-      </x:c>
-      <x:c r="I67" s="4" t="str">
-        <x:v>TEST-TM001-GOVERNANCE</x:v>
-      </x:c>
       <x:c r="J67" s="4" t="str">
-        <x:v>historical_group_not_minimal_task</x:v>
+        <x:v>规划中</x:v>
       </x:c>
       <x:c r="K67" s="4" t="str">
-        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:9</x:v>
+        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:26</x:v>
       </x:c>
       <x:c r="L67" s="4" t="str">
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="68" ht="42" customHeight="1">
+    <x:row r="68" ht="72" customHeight="1">
       <x:c r="A68" s="9" t="str">
-        <x:v>TASK-TM001-SERVER</x:v>
+        <x:v>TASK-TM003-WIRING</x:v>
       </x:c>
       <x:c r="B68" s="9" t="str">
-        <x:v>历史分组</x:v>
+        <x:v>具体任务</x:v>
       </x:c>
       <x:c r="C68" s="9" t="str">
+        <x:v>FP-TM003-02</x:v>
+      </x:c>
+      <x:c r="D68" s="9" t="str">
+        <x:v>REQ-TM003</x:v>
+      </x:c>
+      <x:c r="E68" s="9" t="str">
+        <x:v>AC-TM003-001
+AC-TM003-003
+AC-TM003-004</x:v>
+      </x:c>
+      <x:c r="F68" s="9" t="str">
+        <x:v>CORE-07主进程编排、SECRET、TM-002现有SourceAccess可替换端口；真实OS选择/Keychain产品验收仍BLOCKED</x:v>
+      </x:c>
+      <x:c r="G68" s="9" t="str">
+        <x:v>产物：TM-003独占主进程来源到Codex collector/UsageStore适配；renderer只传已确认sourceId，完整代际守卫后写库
+完成条件：真实SourceAccess类+本例helper/SQLite下确认前零读、A/B=330、撤销零新提交、换主体无串读</x:v>
+      </x:c>
+      <x:c r="H68" s="9" t="str">
+        <x:v>CORE-07主进程编排、SECRET、TM-002现有SourceAccess可替换端口；真实OS选择/Keychain产品验收仍BLOCKED</x:v>
+      </x:c>
+      <x:c r="I68" s="9" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="D68" s="9" t="str">
-        <x:v>REQ-TM001</x:v>
-      </x:c>
-      <x:c r="E68" s="9" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="F68" s="9" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="G68" s="9" t="str">
-        <x:v>FastAPI/SQLAlchemy/Alembic 工程、真实认证/权限/审计 API；随机可撤销 token 固定30天到期、不滑动，改密/重置/停用撤销旧会话</x:v>
-      </x:c>
-      <x:c r="H68" s="9" t="str">
-        <x:v>计划、数据/测试</x:v>
-      </x:c>
-      <x:c r="I68" s="9" t="str">
-        <x:v>E2E-TM001-001、E2E-TM001-002、E2E-TM001-003</x:v>
-      </x:c>
       <x:c r="J68" s="9" t="str">
-        <x:v>historical_group_not_minimal_task</x:v>
+        <x:v>规划中</x:v>
       </x:c>
       <x:c r="K68" s="9" t="str">
-        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:10</x:v>
+        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:27</x:v>
       </x:c>
       <x:c r="L68" s="9" t="str">
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="69" ht="42" customHeight="1">
+    <x:row r="69" ht="87" customHeight="1">
       <x:c r="A69" s="4" t="str">
-        <x:v>TASK-TM001-DATA</x:v>
+        <x:v>TASK-TM003-IPC</x:v>
       </x:c>
       <x:c r="B69" s="4" t="str">
-        <x:v>历史分组</x:v>
+        <x:v>具体任务</x:v>
       </x:c>
       <x:c r="C69" s="4" t="str">
+        <x:v>FP-TM003-03</x:v>
+      </x:c>
+      <x:c r="D69" s="4" t="str">
+        <x:v>REQ-TM003</x:v>
+      </x:c>
+      <x:c r="E69" s="4" t="str">
+        <x:v>AC-TM003-001
+AC-TM003-004</x:v>
+      </x:c>
+      <x:c r="F69" s="4" t="str">
+        <x:v>WIRING及TM-001现有单窗口sender检查；不依赖真实Keychain产品结论</x:v>
+      </x:c>
+      <x:c r="G69" s="4" t="str">
+        <x:v>产物：TM-003独占 index.ts、受限collection handler、preload/共享Snapshot的采集状态；collection:getState无参数、collection:refresh仅sourceId
+完成条件：非主sender/子frame/额外路径或身份字段拒绝；有效刷新/重复/停读/换主体只返回本主体白名单状态</x:v>
+      </x:c>
+      <x:c r="H69" s="4" t="str">
+        <x:v>WIRING及TM-001现有单窗口sender检查；不依赖真实Keychain产品结论</x:v>
+      </x:c>
+      <x:c r="I69" s="4" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="D69" s="4" t="str">
-        <x:v>REQ-TM001</x:v>
-      </x:c>
-      <x:c r="E69" s="4" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="F69" s="4" t="str">
-        <x:v>不适用</x:v>
-      </x:c>
-      <x:c r="G69" s="4" t="str">
-        <x:v>独立测试/生产 SQLite 文件、可执行造数 SQL、生产首建管理员、回归账号/独立预期及安全重置；已有生产密码不可被重建覆盖</x:v>
-      </x:c>
-      <x:c r="H69" s="4" t="str">
-        <x:v>计划、工程骨架</x:v>
-      </x:c>
-      <x:c r="I69" s="4" t="str">
-        <x:v>TEST-TM001-SERVER、E2E-TM001-001、E2E-TM001-005</x:v>
-      </x:c>
       <x:c r="J69" s="4" t="str">
-        <x:v>historical_group_not_minimal_task</x:v>
+        <x:v>规划中</x:v>
       </x:c>
       <x:c r="K69" s="4" t="str">
-        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:11</x:v>
+        <x:v>releases/v0.3.0-20261001T034652Z/02-breakdown.md:28</x:v>
       </x:c>
       <x:c r="L69" s="4" t="str">
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="70" ht="72" customHeight="1">
+    <x:row r="70" ht="32" customHeight="1">
       <x:c r="A70" s="9" t="str">
-        <x:v>TASK-TM001-MAC</x:v>
+        <x:v>TASK-TM001-PLAN</x:v>
       </x:c>
       <x:c r="B70" s="9" t="str">
         <x:v>历史分组</x:v>
@@ -7379,27 +7386,27 @@
         <x:v>不适用</x:v>
       </x:c>
       <x:c r="G70" s="9" t="str">
-        <x:v>Electron React/TypeScript 登录/改密/主页/管理、默认本机 API/更新源地址与配置管理页的用户覆盖持久化；默认开启可关闭的设备自动登录、按规范化 origin 隔离的受保护凭据文件与内存会话、稳定 UI 标识、Playwright Electron工程</x:v>
+        <x:v>六文档、完整追踪、SOP 修正、基线通过</x:v>
       </x:c>
       <x:c r="H70" s="9" t="str">
-        <x:v>API 合同、工程骨架</x:v>
+        <x:v>需求</x:v>
       </x:c>
       <x:c r="I70" s="9" t="str">
-        <x:v>E2E-TM001-001、E2E-TM001-002、E2E-TM001-003、E2E-TM001-004、E2E-TM001-005、E2E-TM001-006</x:v>
+        <x:v>TEST-TM001-GOVERNANCE</x:v>
       </x:c>
       <x:c r="J70" s="9" t="str">
         <x:v>historical_group_not_minimal_task</x:v>
       </x:c>
       <x:c r="K70" s="9" t="str">
-        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:12</x:v>
+        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:9</x:v>
       </x:c>
       <x:c r="L70" s="9" t="str">
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="71" ht="57" customHeight="1">
+    <x:row r="71" ht="42" customHeight="1">
       <x:c r="A71" s="4" t="str">
-        <x:v>TASK-TM001-UPDATE</x:v>
+        <x:v>TASK-TM001-SERVER</x:v>
       </x:c>
       <x:c r="B71" s="4" t="str">
         <x:v>历史分组</x:v>
@@ -7417,27 +7424,27 @@
         <x:v>不适用</x:v>
       </x:c>
       <x:c r="G71" s="4" t="str">
-        <x:v>固定 Ed25519 公钥、同机回环更新源/签名测试包/失败包及真实更新用例；默认49177配置、URL安全校验与升级时锁定更新设置；两构建沿用经校验的同一隔离profile，升级后服务验证自动登录</x:v>
+        <x:v>FastAPI/SQLAlchemy/Alembic 工程、真实认证/权限/审计 API；随机可撤销 token 固定30天到期、不滑动，改密/重置/停用撤销旧会话</x:v>
       </x:c>
       <x:c r="H71" s="4" t="str">
-        <x:v>Mac 工程</x:v>
+        <x:v>计划、数据/测试</x:v>
       </x:c>
       <x:c r="I71" s="4" t="str">
-        <x:v>E2E-TM001-004</x:v>
+        <x:v>E2E-TM001-001、E2E-TM001-002、E2E-TM001-003</x:v>
       </x:c>
       <x:c r="J71" s="4" t="str">
         <x:v>historical_group_not_minimal_task</x:v>
       </x:c>
       <x:c r="K71" s="4" t="str">
-        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:13</x:v>
+        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:10</x:v>
       </x:c>
       <x:c r="L71" s="4" t="str">
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="72" ht="57" customHeight="1">
+    <x:row r="72" ht="42" customHeight="1">
       <x:c r="A72" s="9" t="str">
-        <x:v>TASK-TM001-RUNNER</x:v>
+        <x:v>TASK-TM001-DATA</x:v>
       </x:c>
       <x:c r="B72" s="9" t="str">
         <x:v>历史分组</x:v>
@@ -7455,27 +7462,27 @@
         <x:v>不适用</x:v>
       </x:c>
       <x:c r="G72" s="9" t="str">
-        <x:v>本机Playwright从最终DMG安装App执行全部六例，原始JSON/trace/fixtureSQL/包摘要、父门禁复核；默认值与动态独占端口隔离测试；真实Squirrel自重启及profile、身份恢复</x:v>
+        <x:v>独立测试/生产 SQLite 文件、可执行造数 SQL、生产首建管理员、回归账号/独立预期及安全重置；已有生产密码不可被重建覆盖</x:v>
       </x:c>
       <x:c r="H72" s="9" t="str">
-        <x:v>数据/桌面工程</x:v>
+        <x:v>计划、工程骨架</x:v>
       </x:c>
       <x:c r="I72" s="9" t="str">
-        <x:v>E2E-TM001-001、E2E-TM001-002、E2E-TM001-003、E2E-TM001-004、E2E-TM001-005、E2E-TM001-006</x:v>
+        <x:v>TEST-TM001-SERVER、E2E-TM001-001、E2E-TM001-005</x:v>
       </x:c>
       <x:c r="J72" s="9" t="str">
         <x:v>historical_group_not_minimal_task</x:v>
       </x:c>
       <x:c r="K72" s="9" t="str">
-        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:14</x:v>
+        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:11</x:v>
       </x:c>
       <x:c r="L72" s="9" t="str">
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
-    <x:row r="73" ht="32" customHeight="1">
+    <x:row r="73" ht="72" customHeight="1">
       <x:c r="A73" s="4" t="str">
-        <x:v>TASK-TM001-REVIEW</x:v>
+        <x:v>TASK-TM001-MAC</x:v>
       </x:c>
       <x:c r="B73" s="4" t="str">
         <x:v>历史分组</x:v>
@@ -7493,33 +7500,147 @@
         <x:v>不适用</x:v>
       </x:c>
       <x:c r="G73" s="4" t="str">
-        <x:v>完整回归、流程复盘、PR 与合并判定、发布阻塞记录</x:v>
+        <x:v>Electron React/TypeScript 登录/改密/主页/管理、默认本机 API/更新源地址与配置管理页的用户覆盖持久化；默认开启可关闭的设备自动登录、按规范化 origin 隔离的受保护凭据文件与内存会话、稳定 UI 标识、Playwright Electron工程</x:v>
       </x:c>
       <x:c r="H73" s="4" t="str">
-        <x:v>全部实现任务</x:v>
+        <x:v>API 合同、工程骨架</x:v>
       </x:c>
       <x:c r="I73" s="4" t="str">
-        <x:v>TEST-TM001-GOVERNANCE</x:v>
+        <x:v>E2E-TM001-001、E2E-TM001-002、E2E-TM001-003、E2E-TM001-004、E2E-TM001-005、E2E-TM001-006</x:v>
       </x:c>
       <x:c r="J73" s="4" t="str">
         <x:v>historical_group_not_minimal_task</x:v>
       </x:c>
       <x:c r="K73" s="4" t="str">
-        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:15</x:v>
+        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:12</x:v>
       </x:c>
       <x:c r="L73" s="4" t="str">
         <x:v>未提供</x:v>
       </x:c>
     </x:row>
+    <x:row r="74" ht="57" customHeight="1">
+      <x:c r="A74" s="9" t="str">
+        <x:v>TASK-TM001-UPDATE</x:v>
+      </x:c>
+      <x:c r="B74" s="9" t="str">
+        <x:v>历史分组</x:v>
+      </x:c>
+      <x:c r="C74" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="D74" s="9" t="str">
+        <x:v>REQ-TM001</x:v>
+      </x:c>
+      <x:c r="E74" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="F74" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="G74" s="9" t="str">
+        <x:v>固定 Ed25519 公钥、同机回环更新源/签名测试包/失败包及真实更新用例；默认49177配置、URL安全校验与升级时锁定更新设置；两构建沿用经校验的同一隔离profile，升级后服务验证自动登录</x:v>
+      </x:c>
+      <x:c r="H74" s="9" t="str">
+        <x:v>Mac 工程</x:v>
+      </x:c>
+      <x:c r="I74" s="9" t="str">
+        <x:v>E2E-TM001-004</x:v>
+      </x:c>
+      <x:c r="J74" s="9" t="str">
+        <x:v>historical_group_not_minimal_task</x:v>
+      </x:c>
+      <x:c r="K74" s="9" t="str">
+        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:13</x:v>
+      </x:c>
+      <x:c r="L74" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="57" customHeight="1">
+      <x:c r="A75" s="4" t="str">
+        <x:v>TASK-TM001-RUNNER</x:v>
+      </x:c>
+      <x:c r="B75" s="4" t="str">
+        <x:v>历史分组</x:v>
+      </x:c>
+      <x:c r="C75" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="D75" s="4" t="str">
+        <x:v>REQ-TM001</x:v>
+      </x:c>
+      <x:c r="E75" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="F75" s="4" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="G75" s="4" t="str">
+        <x:v>本机Playwright从最终DMG安装App执行全部六例，原始JSON/trace/fixtureSQL/包摘要、父门禁复核；默认值与动态独占端口隔离测试；真实Squirrel自重启及profile、身份恢复</x:v>
+      </x:c>
+      <x:c r="H75" s="4" t="str">
+        <x:v>数据/桌面工程</x:v>
+      </x:c>
+      <x:c r="I75" s="4" t="str">
+        <x:v>E2E-TM001-001、E2E-TM001-002、E2E-TM001-003、E2E-TM001-004、E2E-TM001-005、E2E-TM001-006</x:v>
+      </x:c>
+      <x:c r="J75" s="4" t="str">
+        <x:v>historical_group_not_minimal_task</x:v>
+      </x:c>
+      <x:c r="K75" s="4" t="str">
+        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:14</x:v>
+      </x:c>
+      <x:c r="L75" s="4" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="32" customHeight="1">
+      <x:c r="A76" s="9" t="str">
+        <x:v>TASK-TM001-REVIEW</x:v>
+      </x:c>
+      <x:c r="B76" s="9" t="str">
+        <x:v>历史分组</x:v>
+      </x:c>
+      <x:c r="C76" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="D76" s="9" t="str">
+        <x:v>REQ-TM001</x:v>
+      </x:c>
+      <x:c r="E76" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="F76" s="9" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="G76" s="9" t="str">
+        <x:v>完整回归、流程复盘、PR 与合并判定、发布阻塞记录</x:v>
+      </x:c>
+      <x:c r="H76" s="9" t="str">
+        <x:v>全部实现任务</x:v>
+      </x:c>
+      <x:c r="I76" s="9" t="str">
+        <x:v>TEST-TM001-GOVERNANCE</x:v>
+      </x:c>
+      <x:c r="J76" s="9" t="str">
+        <x:v>historical_group_not_minimal_task</x:v>
+      </x:c>
+      <x:c r="K76" s="9" t="str">
+        <x:v>releases/v0.1.0-20260929T074814Z/02-breakdown.md:15</x:v>
+      </x:c>
+      <x:c r="L76" s="9" t="str">
+        <x:v>未提供</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="J5:J73">
+  <x:conditionalFormatting sqref="J5:J76">
     <x:cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="10" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="11" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25043e0a708f4375"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R982c2708ca2b4bbe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18586,7 +18707,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L236" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:267</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:312</x:v>
       </x:c>
       <x:c r="M236" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -18633,7 +18754,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L237" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:271</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:316</x:v>
       </x:c>
       <x:c r="M237" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -18680,7 +18801,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L238" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:275</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:320</x:v>
       </x:c>
       <x:c r="M238" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -18728,7 +18849,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L239" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:279</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:324</x:v>
       </x:c>
       <x:c r="M239" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -18778,7 +18899,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L240" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:283</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:328</x:v>
       </x:c>
       <x:c r="M240" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -18826,7 +18947,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L241" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:287</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:332</x:v>
       </x:c>
       <x:c r="M241" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -18873,7 +18994,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L242" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:291</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:336</x:v>
       </x:c>
       <x:c r="M242" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -18920,7 +19041,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L243" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:295</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:340</x:v>
       </x:c>
       <x:c r="M243" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -18968,7 +19089,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L244" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:299</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:344</x:v>
       </x:c>
       <x:c r="M244" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19017,7 +19138,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L245" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:303</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:348</x:v>
       </x:c>
       <x:c r="M245" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19066,7 +19187,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L246" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:307</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:352</x:v>
       </x:c>
       <x:c r="M246" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19115,7 +19236,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L247" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:311</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:356</x:v>
       </x:c>
       <x:c r="M247" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19162,7 +19283,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L248" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:315</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:360</x:v>
       </x:c>
       <x:c r="M248" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19210,7 +19331,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L249" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:319</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:364</x:v>
       </x:c>
       <x:c r="M249" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19258,7 +19379,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L250" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:323</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:368</x:v>
       </x:c>
       <x:c r="M250" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19306,7 +19427,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L251" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:327</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:372</x:v>
       </x:c>
       <x:c r="M251" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19354,7 +19475,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L252" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:331</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:376</x:v>
       </x:c>
       <x:c r="M252" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19404,7 +19525,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L253" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:335</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:380</x:v>
       </x:c>
       <x:c r="M253" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19451,7 +19572,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L254" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:339</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:384</x:v>
       </x:c>
       <x:c r="M254" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19498,7 +19619,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L255" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:343</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:388</x:v>
       </x:c>
       <x:c r="M255" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19546,7 +19667,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L256" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:347</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:392</x:v>
       </x:c>
       <x:c r="M256" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19595,7 +19716,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L257" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:351</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:396</x:v>
       </x:c>
       <x:c r="M257" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19645,7 +19766,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L258" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:355</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:400</x:v>
       </x:c>
       <x:c r="M258" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19693,7 +19814,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L259" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:359</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:404</x:v>
       </x:c>
       <x:c r="M259" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19742,7 +19863,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L260" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:363</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:408</x:v>
       </x:c>
       <x:c r="M260" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19790,7 +19911,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L261" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:367</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:412</x:v>
       </x:c>
       <x:c r="M261" s="4" t="str">
         <x:v>尚未执行</x:v>
@@ -19838,7 +19959,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L262" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:371</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:416</x:v>
       </x:c>
       <x:c r="M262" s="9" t="str">
         <x:v>尚未执行</x:v>
@@ -19886,7 +20007,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L263" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:375</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:420</x:v>
       </x:c>
       <x:c r="M263" s="4" t="str">
         <x:v>tm003-core-20261001T203711Z</x:v>
@@ -19935,7 +20056,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L264" s="9" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:379</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:424</x:v>
       </x:c>
       <x:c r="M264" s="9" t="str">
         <x:v>tm003-core-20261001T203711Z</x:v>
@@ -19983,7 +20104,7 @@
         <x:v>细化用例</x:v>
       </x:c>
       <x:c r="L265" s="4" t="str">
-        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:383</x:v>
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:428</x:v>
       </x:c>
       <x:c r="M265" s="4" t="str">
         <x:v>tm003-core-20261001T203711Z</x:v>
@@ -20681,30 +20802,177 @@
         <x:v>v0.5.0-20261001T034729Z</x:v>
       </x:c>
     </x:row>
+    <x:row r="280" ht="177" customHeight="1">
+      <x:c r="A280" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B280" s="9" t="str">
+        <x:v>TC-TM003-CORE-08</x:v>
+      </x:c>
+      <x:c r="C280" s="9" t="str">
+        <x:v>私有身份密钥持久性与拒绝重键</x:v>
+      </x:c>
+      <x:c r="D280" s="9" t="str">
+        <x:v>TASK-TM003-SECRET</x:v>
+      </x:c>
+      <x:c r="E280" s="9" t="str">
+        <x:v>模块检查</x:v>
+      </x:c>
+      <x:c r="F280" s="9" t="str">
+        <x:v>tests/fixtures/tm003-product-loop-slice.json；0700私有profile/0600库，公开32字节注入随机源，假系统密钥端口与三组principal向量；真实产品必须系统随机+系统密钥加密</x:v>
+      </x:c>
+      <x:c r="G280" s="9" t="str">
+        <x:v>1. 在空 owner profile 中以可用加密端口初始化密钥，求三组 principal 键。；随机源仅调用一次、32字节密钥仅在内存；密文记录0600/目录0700，无明文 key。三键逐字节等于 fixture；同账号不同 origin 和同 origin 不同账号各有不同键。尚无事件/游标/覆盖写入。
+2. 用第一主体经正式 UsageStore 提交 fixture A=110，关闭密钥端口与库，再用同 profile 重开并重放 A。；重开只解密原密文、不生成新密钥；第一 principal 键和 identity_key_state 标记不变；usage_event 始终一行、total110、游标不重计，第二/第三主体只读零行但状态为未核实而非产品已知零。
+3. 分别在独立复制的本例已有事件库中删除密文记录和损坏密文，再初始化。；两者均返回固定 identity_secret_unavailable/identity_secret_corrupt 停采集，随机源零调用，不创建新密文、不改事件、游标、覆盖或密钥标记；旧 A 仍可由只读库核对。
+4. 恢复原密文后让加密端口不可用，再换成另一有效32字节密钥尝试打开原库。；密钥不可用时停采集，不能明文回退；不同有效密钥被 marker 拒绝，A仍一行/110，记录和报告无密钥、密文、完整路径或原生日志正文。</x:v>
+      </x:c>
+      <x:c r="H280" s="9" t="str">
+        <x:v>准备：仅经UsageStore提交A；故障变体各复制owner库
+变化：重启重放及缺/坏/错键不改旧事件、游标或密钥标记
+核验：只读usage_event/source_cursor/coverage/identity_key_state；检查密文文件0600、无明文key</x:v>
+      </x:c>
+      <x:c r="I280" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J280" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K280" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L280" s="9" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:263</x:v>
+      </x:c>
+      <x:c r="M280" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N280" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="281" ht="192" customHeight="1">
+      <x:c r="A281" s="4" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B281" s="4" t="str">
+        <x:v>TC-TM003-CORE-09</x:v>
+      </x:c>
+      <x:c r="C281" s="4" t="str">
+        <x:v>已确认来源到本机库的主进程适配</x:v>
+      </x:c>
+      <x:c r="D281" s="4" t="str">
+        <x:v>TASK-TM003-WIRING</x:v>
+      </x:c>
+      <x:c r="E281" s="4" t="str">
+        <x:v>模块检查</x:v>
+      </x:c>
+      <x:c r="F281" s="4" t="str">
+        <x:v>tests/fixtures/tm003-product-loop-slice.json；CORE08密钥、真实SourceAccess类/合成helper与CORE07两文件各410字节</x:v>
+      </x:c>
+      <x:c r="G281" s="4" t="str">
+        <x:v>1. 未经确认直接触发 Codex 采集，再通过 SourceAccess 的选择/预览/确认方法建立本例来源。；确认前 beginCandidateScan/readCandidateChunk/commitScanBatch 均0次、库空；确认记录只属第一主体，候选元数据不包含正文。
+2. 以已确认 sourceId 调用主进程适配器，读取两个完整文件并在末页守卫通过后落库；关闭重开库/来源后重扫。；完成前库空；完成后A/B两事件、input300/output30/cached60/total330、各游标410、覆盖仅在全代完成后标记；重启重扫仍两行/330，无原始路径/原生ID落库。
+3. 从独立成功库开始新代际，在 file-b 后由 SourceAccess 撤销来源再尝试提交。；旧代际被取消，守卫拒绝、提交0次；已提交A/B仍两行/330，原成功代际的coverage行保持原值，本次运行状态须标采集不可用/不完整且不能称新代际完成；旧 sourceId 不再可读。
+4. 切到 fixture 的第二主体后尝试旧 sourceId，再为第二主体确认独立来源并扫描。；旧 sourceId 在读取前拒绝、第一主体数据不出现在第二主体查询；第二主体成功扫描后各主体各两行/330，HMAC主体键不同，不能共享游标/来源能力。</x:v>
+      </x:c>
+      <x:c r="H281" s="4" t="str">
+        <x:v>准备：经正式SourceAccess和UsageStore操作；各故障路径新库
+变化：完整代际写A/B=330；撤销/换主体不增加旧主体事件
+核验：只读主体/来源唯一键、事件总量、游标、覆盖及提交次数</x:v>
+      </x:c>
+      <x:c r="I281" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J281" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K281" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L281" s="4" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:276</x:v>
+      </x:c>
+      <x:c r="M281" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N281" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="282" ht="147" customHeight="1">
+      <x:c r="A282" s="9" t="str">
+        <x:v>TM-003</x:v>
+      </x:c>
+      <x:c r="B282" s="9" t="str">
+        <x:v>TC-TM003-CORE-10</x:v>
+      </x:c>
+      <x:c r="C282" s="9" t="str">
+        <x:v>主窗口 IPC 与刷新状态隔离</x:v>
+      </x:c>
+      <x:c r="D282" s="9" t="str">
+        <x:v>TASK-TM003-IPC</x:v>
+      </x:c>
+      <x:c r="E282" s="9" t="str">
+        <x:v>模块检查</x:v>
+      </x:c>
+      <x:c r="F282" s="9" t="str">
+        <x:v>tests/fixtures/tm003-product-loop-slice.json；CORE09成功库、固定主窗口sender/frame端口及第二主体</x:v>
+      </x:c>
+      <x:c r="G282" s="9" t="str">
+        <x:v>1. 分别用非主窗口 sender、子 frame、路径/账号/密钥多余字段和未确认 sourceId 调用 handler。；全部拒绝，采集/DB调用0次；不接受任意路径或由 renderer 指定 principal/secret，不返回旧主体状态。
+2. 主窗口按固定 sourceId 刷新并取 state。；只触发第一主体 Codex 采集一次，返回两事件的 input300/output30/total330、cached已知60、覆盖与诊断代码/数量；库仍两行，序列化状态无密钥、密文、路径、原生ID或正文。
+3. 同主体再刷新并取 state，随后将来源暂停/撤销。；重扫仍两行/330；暂停/撤销后刷新拒绝、旧可信330只对第一主体保留可见且标采集不可用/覆盖不完整，不能报新已知零。
+4. 切换第二主体后由旧 sender/sourceId 取 state/刷新。；旧来源被拒绝，第二主体 state 为缺失/未核实且无第一主体330；第一主体持久事件不删除，按主体只读核对隔离。</x:v>
+      </x:c>
+      <x:c r="H282" s="9" t="str">
+        <x:v>准备：本例owner库只经handler/collector操作
+变化：合法刷新不重复；非法sender/输入/换主体零新写
+核验：只读usage_event/coverage与输出白名单、handler调用数</x:v>
+      </x:c>
+      <x:c r="I282" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J282" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K282" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L282" s="9" t="str">
+        <x:v>docs/testing/cases/03-TM-003-codex-collection.md:289</x:v>
+      </x:c>
+      <x:c r="M282" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N282" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G5:G279">
+  <x:conditionalFormatting sqref="G5:G282">
     <x:cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="I5:I279">
+  <x:conditionalFormatting sqref="I5:I282">
     <x:cfRule type="containsText" dxfId="15" priority="4" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="17" priority="6" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="J5:J279">
+  <x:conditionalFormatting sqref="J5:J282">
     <x:cfRule type="containsText" dxfId="18" priority="7" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="19" priority="8" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="20" priority="9" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="M5:M279">
+  <x:conditionalFormatting sqref="M5:M282">
     <x:cfRule type="containsText" dxfId="21" priority="10" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="22" priority="11" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="23" priority="12" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3eb9cbcd99cc45a1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R661ea45b277542f6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22336,7 +22604,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b08fedd6fef434d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a44701823754209"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22828,7 +23096,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb0706c88ee02424c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99c4afc143c44994"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23993,7 +24261,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7fa1ec01202f4d85"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R743c0e31b0624da0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TokenMeter项目总表.xlsx
+++ b/TokenMeter项目总表.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R3cb0d6bcdf5b4d60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Rc165cd0df46944a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="Rdd922679d5dc4e6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R200b34690b774c08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R803defdb9bef407a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="Rcc23deb0274f41c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R14ea53fc1d944102"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R79ce0cdc2a9b4f2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Rc84140b5b6f04fdb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R573be4995ee74c91"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R61bd3827d3904eb5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="Re582a623448b4c2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="R725aeafdf035426b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="Rdd8f5ee6505943d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R2bd640a59e9442de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R1d386a79530f40f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R3bae464479c54fff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R67ff4269af2f4ebd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R12deb8759fcb48c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="R81c00dc18e6a4950"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R40b4fc7871cf4cf7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="Rf143a7c129c94948"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -809,8 +809,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TMTable7" displayName="TMTable7" ref="A4:N39" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:N39"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TMTable7" displayName="TMTable7" ref="A4:N40" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:N40"/>
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="运行批次"/>
     <x:tableColumn id="2" name="版本"/>
@@ -1146,8 +1146,8 @@
         <x:v>测试批次</x:v>
       </x:c>
       <x:c r="B9" s="10" t="n">
-        <x:f>COUNTA('06测试批次'!A5:A39)</x:f>
-        <x:v>35</x:v>
+        <x:f>COUNTA('06测试批次'!A5:A40)</x:f>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C9" s="4" t="str">
         <x:v>06测试批次，每次运行一行，记录独立结果Excel位置</x:v>
@@ -1271,7 +1271,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="C20" s="9" t="str">
-        <x:v>source_check · TM-003 tm003-core07整合候选固定辅助模块；非产品E2E：1/1固定TC、5步与owner清理PASS；固定source_check导出及verification回读PASS。仅本整合候选的模块合同，产品App/授权/Keychain及发行均NOT_RUN。；是否覆盖完整产品回归以批次范围和原始证据为准。</x:v>
+        <x:v>product_e2e · TASK-TM001-BOOTSTRAP；BOOTSTRAP-01..04四父TC安装正式App定向：4父4/4、18步、清理PASS；12截图、独立Excel/verification回读PASS。仅709d首次建库/安装App定向，未做本批独立审计；其余TM001、完整门禁与发行未通过。；是否覆盖完整产品回归以批次范围和原始证据为准。</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="32" customHeight="1">
@@ -1288,7 +1288,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R78890397488e4ca9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b2b58b21d51413d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1996,7 +1996,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59713f1f5768440e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc68078ec838b4b39"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2145,7 +2145,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64341a0fc6234bb4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8675b0726f440ee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2580,7 +2580,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e47d71ac7c345b3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b5b7dc9f1da48e5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3627,7 +3627,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd30a4ebacc7468f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18906c0dc8794e7b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4734,7 +4734,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0db642e62fc64cc4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbffd9f49b54c4a0f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7640,7 +7640,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R982c2708ca2b4bbe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b7d5ea1d8cf4cc7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10100,7 +10100,7 @@
         <x:v>docs/testing/cases/01b-TM-001-session-admin-release-scenarios.md:363</x:v>
       </x:c>
       <x:c r="M54" s="9" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-3d36f9cbe62a4c1e889e8ea2fa476281</x:v>
       </x:c>
       <x:c r="N54" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -10150,7 +10150,7 @@
         <x:v>docs/testing/cases/01b-TM-001-session-admin-release-scenarios.md:380</x:v>
       </x:c>
       <x:c r="M55" s="4" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-3d36f9cbe62a4c1e889e8ea2fa476281</x:v>
       </x:c>
       <x:c r="N55" s="4" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -10199,7 +10199,7 @@
         <x:v>docs/testing/cases/01b-TM-001-session-admin-release-scenarios.md:398</x:v>
       </x:c>
       <x:c r="M56" s="9" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-3d36f9cbe62a4c1e889e8ea2fa476281</x:v>
       </x:c>
       <x:c r="N56" s="9" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -10249,7 +10249,7 @@
         <x:v>docs/testing/cases/01b-TM-001-session-admin-release-scenarios.md:415</x:v>
       </x:c>
       <x:c r="M57" s="4" t="str">
-        <x:v>local-0512d4fc44544eba97f9d1ae79cbfc37</x:v>
+        <x:v>local-3d36f9cbe62a4c1e889e8ea2fa476281</x:v>
       </x:c>
       <x:c r="N57" s="4" t="str">
         <x:v>v0.1.0-20260929T074814Z</x:v>
@@ -20972,7 +20972,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R661ea45b277542f6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0cef30b7ec90422b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22586,25 +22586,69 @@
         <x:v>NOT_RUN</x:v>
       </x:c>
     </x:row>
+    <x:row r="40" ht="42" customHeight="1">
+      <x:c r="A40" s="9" t="str">
+        <x:v>local-3d36f9cbe62a4c1e889e8ea2fa476281</x:v>
+      </x:c>
+      <x:c r="B40" s="9" t="str">
+        <x:v>v0.1.0-20260929T074814Z</x:v>
+      </x:c>
+      <x:c r="C40" s="9" t="str">
+        <x:v>product_e2e</x:v>
+      </x:c>
+      <x:c r="D40" s="9" t="str">
+        <x:v>TASK-TM001-BOOTSTRAP；BOOTSTRAP-01..04四父TC安装正式App定向</x:v>
+      </x:c>
+      <x:c r="E40" s="9" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F40" s="9" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G40" s="9" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H40" s="9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I40" s="9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J40" s="9" t="str">
+        <x:v>709d21253a0f88bc703a431cbf3adba3df17e508</x:v>
+      </x:c>
+      <x:c r="K40" s="9" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="L40" s="9" t="str">
+        <x:v>4父4/4、18步、清理PASS；12截图、独立Excel/verification回读PASS。仅709d首次建库/安装App定向，未做本批独立审计；其余TM001、完整门禁与发行未通过。</x:v>
+      </x:c>
+      <x:c r="M40" s="9" t="str">
+        <x:v>.local/test-results/local-3d36f9cbe62a4c1e889e8ea2fa476281/TokenMeter测试结果-local-3d36f9cbe62a4c1e889e8ea2fa476281.xlsx</x:v>
+      </x:c>
+      <x:c r="N40" s="9" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="E5:E39">
+  <x:conditionalFormatting sqref="E5:E40">
     <x:cfRule type="containsText" dxfId="24" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="25" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="26" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="M5:M39">
+  <x:conditionalFormatting sqref="M5:M40">
     <x:cfRule type="containsText" dxfId="27" priority="4" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="28" priority="5" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="29" priority="6" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="N5:N39">
+  <x:conditionalFormatting sqref="N5:N40">
     <x:cfRule type="containsText" dxfId="30" priority="7" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="31" priority="8" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="32" priority="9" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a44701823754209"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea61f4ea009d4c73"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23096,7 +23140,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99c4afc143c44994"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb32f3e554b5241a4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24261,7 +24305,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R743c0e31b0624da0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcea83dea6bf84594"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TokenMeter项目总表.xlsx
+++ b/TokenMeter项目总表.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="Re582a623448b4c2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="R725aeafdf035426b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="Rdd8f5ee6505943d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R2bd640a59e9442de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R1d386a79530f40f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R3bae464479c54fff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R67ff4269af2f4ebd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R12deb8759fcb48c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="R81c00dc18e6a4950"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R40b4fc7871cf4cf7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="Rf143a7c129c94948"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="Ra4f8d98df41041e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Rbb8e251916d04868"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="Rc5f805f200d242d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="Rf4d8d5c4fe134d49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R6991c6c045a445d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R55615561eeb249bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R240979b2f1af4851"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R82efc12112f34203"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Rbc131f664828428b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R1787dfe246cb409a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R3fd87e0127824051"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -809,8 +809,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TMTable7" displayName="TMTable7" ref="A4:N40" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:N40"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TMTable7" displayName="TMTable7" ref="A4:N43" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:N43"/>
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="运行批次"/>
     <x:tableColumn id="2" name="版本"/>
@@ -1146,8 +1146,8 @@
         <x:v>测试批次</x:v>
       </x:c>
       <x:c r="B9" s="10" t="n">
-        <x:f>COUNTA('06测试批次'!A5:A40)</x:f>
-        <x:v>36</x:v>
+        <x:f>COUNTA('06测试批次'!A5:A43)</x:f>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C9" s="4" t="str">
         <x:v>06测试批次，每次运行一行，记录独立结果Excel位置</x:v>
@@ -1271,7 +1271,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="C20" s="9" t="str">
-        <x:v>product_e2e · TASK-TM001-BOOTSTRAP；BOOTSTRAP-01..04四父TC安装正式App定向：4父4/4、18步、清理PASS；12截图、独立Excel/verification回读PASS。仅709d首次建库/安装App定向，未做本批独立审计；其余TM001、完整门禁与发行未通过。；是否覆盖完整产品回归以批次范围和原始证据为准。</x:v>
+        <x:v>source_check · TM-004 CORE05三文件持久映射整合候选固定辅助模块；非产品E2E：1/1固定TC、4步与逐例清理PASS；固定source_check导出及verification回读PASS。仅同树辅助模块合同，原20产品TC、App/授权/服务及发行均NOT_RUN。；是否覆盖完整产品回归以批次范围和原始证据为准。</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="32" customHeight="1">
@@ -1288,7 +1288,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b2b58b21d51413d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2829fb58b8e4e3b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1996,7 +1996,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc68078ec838b4b39"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a2cb8f825f94efe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2145,7 +2145,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8675b0726f440ee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55e74f6419664647"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2580,7 +2580,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b5b7dc9f1da48e5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e81fa3ce52243fe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3627,7 +3627,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18906c0dc8794e7b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc97a256db72846b6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4734,7 +4734,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbffd9f49b54c4a0f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R123bd72d4ae64368"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7640,7 +7640,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b7d5ea1d8cf4cc7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2cee48957f904f14"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20493,7 +20493,7 @@
         <x:v>draft</x:v>
       </x:c>
       <x:c r="J273" s="4" t="str">
-        <x:v>未执行</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="K273" s="4" t="str">
         <x:v>细化用例</x:v>
@@ -20502,7 +20502,7 @@
         <x:v>docs/testing/cases/04-TM-004-claude-collection.md:170</x:v>
       </x:c>
       <x:c r="M273" s="4" t="str">
-        <x:v>尚未执行</x:v>
+        <x:v>tm004-core-20261001T213019Z</x:v>
       </x:c>
       <x:c r="N273" s="4" t="str">
         <x:v>v0.4.0-20261001T040433Z</x:v>
@@ -20541,7 +20541,7 @@
         <x:v>draft</x:v>
       </x:c>
       <x:c r="J274" s="9" t="str">
-        <x:v>未执行</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="K274" s="9" t="str">
         <x:v>细化用例</x:v>
@@ -20550,7 +20550,7 @@
         <x:v>docs/testing/cases/04-TM-004-claude-collection.md:178</x:v>
       </x:c>
       <x:c r="M274" s="9" t="str">
-        <x:v>尚未执行</x:v>
+        <x:v>tm004-core-20261001T213019Z</x:v>
       </x:c>
       <x:c r="N274" s="9" t="str">
         <x:v>v0.4.0-20261001T040433Z</x:v>
@@ -20590,7 +20590,7 @@
         <x:v>draft</x:v>
       </x:c>
       <x:c r="J275" s="4" t="str">
-        <x:v>未执行</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="K275" s="4" t="str">
         <x:v>细化用例</x:v>
@@ -20599,7 +20599,7 @@
         <x:v>docs/testing/cases/04-TM-004-claude-collection.md:186</x:v>
       </x:c>
       <x:c r="M275" s="4" t="str">
-        <x:v>尚未执行</x:v>
+        <x:v>tm004-core-20261001T213019Z</x:v>
       </x:c>
       <x:c r="N275" s="4" t="str">
         <x:v>v0.4.0-20261001T040433Z</x:v>
@@ -20639,7 +20639,7 @@
         <x:v>draft</x:v>
       </x:c>
       <x:c r="J276" s="9" t="str">
-        <x:v>未执行</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="K276" s="9" t="str">
         <x:v>细化用例</x:v>
@@ -20648,7 +20648,7 @@
         <x:v>docs/testing/cases/04-TM-004-claude-collection.md:198</x:v>
       </x:c>
       <x:c r="M276" s="9" t="str">
-        <x:v>尚未执行</x:v>
+        <x:v>tm004-core04-20261001T213019Z</x:v>
       </x:c>
       <x:c r="N276" s="9" t="str">
         <x:v>v0.4.0-20261001T040433Z</x:v>
@@ -20689,7 +20689,7 @@
         <x:v>draft</x:v>
       </x:c>
       <x:c r="J277" s="4" t="str">
-        <x:v>未执行</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="K277" s="4" t="str">
         <x:v>细化用例</x:v>
@@ -20698,7 +20698,7 @@
         <x:v>docs/testing/cases/04-TM-004-claude-collection.md:206</x:v>
       </x:c>
       <x:c r="M277" s="4" t="str">
-        <x:v>尚未执行</x:v>
+        <x:v>tm004-core05-20261001T213019Z</x:v>
       </x:c>
       <x:c r="N277" s="4" t="str">
         <x:v>v0.4.0-20261001T040433Z</x:v>
@@ -20972,7 +20972,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0cef30b7ec90422b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49a48a6b66b24ce7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22630,25 +22630,157 @@
         <x:v>PASS</x:v>
       </x:c>
     </x:row>
+    <x:row r="41" ht="42" customHeight="1">
+      <x:c r="A41" s="4" t="str">
+        <x:v>tm004-core-20261001T213019Z</x:v>
+      </x:c>
+      <x:c r="B41" s="4" t="str">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+      <x:c r="C41" s="4" t="str">
+        <x:v>source_check</x:v>
+      </x:c>
+      <x:c r="D41" s="4" t="str">
+        <x:v>TM-004 CORE01–03解析器整合候选固定辅助模块；非产品E2E</x:v>
+      </x:c>
+      <x:c r="E41" s="4" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F41" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G41" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H41" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I41" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J41" s="4" t="str">
+        <x:v>08463b31c5eef5e6c90978cb8d6cd79e4aa76e1a</x:v>
+      </x:c>
+      <x:c r="K41" s="4" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="L41" s="4" t="str">
+        <x:v>3/3固定TC、9步与逐例清理PASS；固定source_check导出及verification回读PASS。仅同树辅助模块合同，原20产品TC、App/授权/服务及发行均NOT_RUN。</x:v>
+      </x:c>
+      <x:c r="M41" s="4" t="str">
+        <x:v>.local/test-results/tm004-core-20261001T213019Z/TokenMeter测试结果-tm004-core-20261001T213019Z.xlsx</x:v>
+      </x:c>
+      <x:c r="N41" s="4" t="str">
+        <x:v>NOT_RUN</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="42" customHeight="1">
+      <x:c r="A42" s="9" t="str">
+        <x:v>tm004-core04-20261001T213019Z</x:v>
+      </x:c>
+      <x:c r="B42" s="9" t="str">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+      <x:c r="C42" s="9" t="str">
+        <x:v>source_check</x:v>
+      </x:c>
+      <x:c r="D42" s="9" t="str">
+        <x:v>TM-004 CORE04主进程触发整合候选固定辅助模块；非产品E2E</x:v>
+      </x:c>
+      <x:c r="E42" s="9" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F42" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G42" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H42" s="9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I42" s="9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J42" s="9" t="str">
+        <x:v>08463b31c5eef5e6c90978cb8d6cd79e4aa76e1a</x:v>
+      </x:c>
+      <x:c r="K42" s="9" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="L42" s="9" t="str">
+        <x:v>1/1固定TC、3步与逐例清理PASS；固定source_check导出及verification回读PASS。仅同树辅助模块合同，原20产品TC、App/授权/服务及发行均NOT_RUN。</x:v>
+      </x:c>
+      <x:c r="M42" s="9" t="str">
+        <x:v>.local/test-results/tm004-core04-20261001T213019Z/TokenMeter测试结果-tm004-core04-20261001T213019Z.xlsx</x:v>
+      </x:c>
+      <x:c r="N42" s="9" t="str">
+        <x:v>NOT_RUN</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="42" customHeight="1">
+      <x:c r="A43" s="4" t="str">
+        <x:v>tm004-core05-20261001T213019Z</x:v>
+      </x:c>
+      <x:c r="B43" s="4" t="str">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+      <x:c r="C43" s="4" t="str">
+        <x:v>source_check</x:v>
+      </x:c>
+      <x:c r="D43" s="4" t="str">
+        <x:v>TM-004 CORE05三文件持久映射整合候选固定辅助模块；非产品E2E</x:v>
+      </x:c>
+      <x:c r="E43" s="4" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F43" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G43" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H43" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I43" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J43" s="4" t="str">
+        <x:v>08463b31c5eef5e6c90978cb8d6cd79e4aa76e1a</x:v>
+      </x:c>
+      <x:c r="K43" s="4" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="L43" s="4" t="str">
+        <x:v>1/1固定TC、4步与逐例清理PASS；固定source_check导出及verification回读PASS。仅同树辅助模块合同，原20产品TC、App/授权/服务及发行均NOT_RUN。</x:v>
+      </x:c>
+      <x:c r="M43" s="4" t="str">
+        <x:v>.local/test-results/tm004-core05-20261001T213019Z/TokenMeter测试结果-tm004-core05-20261001T213019Z.xlsx</x:v>
+      </x:c>
+      <x:c r="N43" s="4" t="str">
+        <x:v>NOT_RUN</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="E5:E40">
+  <x:conditionalFormatting sqref="E5:E43">
     <x:cfRule type="containsText" dxfId="24" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="25" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="26" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="M5:M40">
+  <x:conditionalFormatting sqref="M5:M43">
     <x:cfRule type="containsText" dxfId="27" priority="4" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="28" priority="5" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="29" priority="6" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="N5:N40">
+  <x:conditionalFormatting sqref="N5:N43">
     <x:cfRule type="containsText" dxfId="30" priority="7" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="31" priority="8" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="32" priority="9" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea61f4ea009d4c73"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4da937c8421542c5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23140,7 +23272,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb32f3e554b5241a4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd8c59834cad4a65"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24305,7 +24437,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcea83dea6bf84594"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5602c13daa24499e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TokenMeter项目总表.xlsx
+++ b/TokenMeter项目总表.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="Ra4f8d98df41041e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Rbb8e251916d04868"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="Rc5f805f200d242d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="Rf4d8d5c4fe134d49"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R6991c6c045a445d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R55615561eeb249bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R240979b2f1af4851"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R82efc12112f34203"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Rbc131f664828428b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R1787dfe246cb409a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R3fd87e0127824051"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R979e864ed88a421e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Rcf160d41b5c64d6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="Rb478feb582a44898"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R62f96965f18b4165"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="Rcaecb9c5edff4271"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R8d8137e30b4b4cff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="Re6bf7c7d10df4df3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R4c6c81e9f3c9435b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Rff99ac9c8ed14746"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R576c8065402c49d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R45024f3ea21449c5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1288,7 +1288,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2829fb58b8e4e3b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R167b8999760f4471"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1996,7 +1996,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a2cb8f825f94efe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e93a1ee773b42f2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2145,7 +2145,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55e74f6419664647"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08b8bec042dd4560"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2580,7 +2580,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e81fa3ce52243fe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0bbe512b04b747bb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3627,7 +3627,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc97a256db72846b6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64d2a756b88843b2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4734,7 +4734,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R123bd72d4ae64368"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8dc7ec0418ba4063"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7640,7 +7640,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2cee48957f904f14"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re852f6b6070746ef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20972,7 +20972,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49a48a6b66b24ce7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re068c2a390c849cc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22780,7 +22780,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4da937c8421542c5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Racb0587e60b74444"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23272,7 +23272,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd8c59834cad4a65"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3a5c29434f44e40"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24437,7 +24437,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5602c13daa24499e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0473e66b4554171"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TokenMeter项目总表.xlsx
+++ b/TokenMeter项目总表.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R979e864ed88a421e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Rcf160d41b5c64d6f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="Rb478feb582a44898"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R62f96965f18b4165"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="Rcaecb9c5edff4271"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R8d8137e30b4b4cff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="Re6bf7c7d10df4df3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R4c6c81e9f3c9435b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Rff99ac9c8ed14746"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R576c8065402c49d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R45024f3ea21449c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="Re60ad307bc624cba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="R869b52894da64148"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R276fb5c257d8442e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="Red79df0315d947c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="Re40804555259416f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="Rdff2e0925ebe44f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R2b84aff271f243dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="Rfcba6c88d3d44a78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="R8116b1164695443b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R9ce622b3025e476d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="Rce6d1578b4ad4f27"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -809,8 +809,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TMTable7" displayName="TMTable7" ref="A4:N43" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:N43"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TMTable7" displayName="TMTable7" ref="A4:N44" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:N44"/>
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="运行批次"/>
     <x:tableColumn id="2" name="版本"/>
@@ -1146,8 +1146,8 @@
         <x:v>测试批次</x:v>
       </x:c>
       <x:c r="B9" s="10" t="n">
-        <x:f>COUNTA('06测试批次'!A5:A43)</x:f>
-        <x:v>39</x:v>
+        <x:f>COUNTA('06测试批次'!A5:A44)</x:f>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C9" s="4" t="str">
         <x:v>06测试批次，每次运行一行，记录独立结果Excel位置</x:v>
@@ -1271,7 +1271,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="C20" s="9" t="str">
-        <x:v>source_check · TM-004 CORE05三文件持久映射整合候选固定辅助模块；非产品E2E：1/1固定TC、4步与逐例清理PASS；固定source_check导出及verification回读PASS。仅同树辅助模块合同，原20产品TC、App/授权/服务及发行均NOT_RUN。；是否覆盖完整产品回归以批次范围和原始证据为准。</x:v>
+        <x:v>source_check · TM-003 CORE08开发候选私有密钥生命周期固定辅助模块；非产品E2E：CORE08固定四步1/1与owner清理PASS；独立Excel/verification回读PASS。先前红测FAIL原件保留；仅代码候选辅助合同，产品App/真实Keychain及发行NOT_RUN。；是否覆盖完整产品回归以批次范围和原始证据为准。</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="32" customHeight="1">
@@ -1288,7 +1288,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R167b8999760f4471"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree166958d99d40c3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1996,7 +1996,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e93a1ee773b42f2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R258567ac30514228"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2145,7 +2145,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08b8bec042dd4560"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55c259f9a3eb4581"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2580,7 +2580,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0bbe512b04b747bb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd095365c43504e07"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3627,7 +3627,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64d2a756b88843b2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0856a692cdb04fcd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4734,7 +4734,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8dc7ec0418ba4063"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf41b0f5f112d4c4f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7640,7 +7640,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re852f6b6070746ef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a8319a5ae234689"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20836,7 +20836,7 @@
         <x:v>draft</x:v>
       </x:c>
       <x:c r="J280" s="9" t="str">
-        <x:v>未执行</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="K280" s="9" t="str">
         <x:v>细化用例</x:v>
@@ -20845,7 +20845,7 @@
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:263</x:v>
       </x:c>
       <x:c r="M280" s="9" t="str">
-        <x:v>尚未执行</x:v>
+        <x:v>tm003-core08-20261001T215000Z</x:v>
       </x:c>
       <x:c r="N280" s="9" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
@@ -20972,7 +20972,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re068c2a390c849cc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0901ff8db43b43d8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22762,25 +22762,69 @@
         <x:v>NOT_RUN</x:v>
       </x:c>
     </x:row>
+    <x:row r="44" ht="42" customHeight="1">
+      <x:c r="A44" s="9" t="str">
+        <x:v>tm003-core08-20261001T215000Z</x:v>
+      </x:c>
+      <x:c r="B44" s="9" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+      <x:c r="C44" s="9" t="str">
+        <x:v>source_check</x:v>
+      </x:c>
+      <x:c r="D44" s="9" t="str">
+        <x:v>TM-003 CORE08开发候选私有密钥生命周期固定辅助模块；非产品E2E</x:v>
+      </x:c>
+      <x:c r="E44" s="9" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F44" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G44" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H44" s="9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I44" s="9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J44" s="9" t="str">
+        <x:v>724732d77e2ff26dc8db8bd5607c7eec1ae1b800</x:v>
+      </x:c>
+      <x:c r="K44" s="9" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="L44" s="9" t="str">
+        <x:v>CORE08固定四步1/1与owner清理PASS；独立Excel/verification回读PASS。先前红测FAIL原件保留；仅代码候选辅助合同，产品App/真实Keychain及发行NOT_RUN。</x:v>
+      </x:c>
+      <x:c r="M44" s="9" t="str">
+        <x:v>.local/test-results/tm003-core08-20261001T215000Z/TokenMeter测试结果-tm003-core08-20261001T215000Z.xlsx</x:v>
+      </x:c>
+      <x:c r="N44" s="9" t="str">
+        <x:v>NOT_RUN</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="E5:E43">
+  <x:conditionalFormatting sqref="E5:E44">
     <x:cfRule type="containsText" dxfId="24" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="25" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="26" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="M5:M43">
+  <x:conditionalFormatting sqref="M5:M44">
     <x:cfRule type="containsText" dxfId="27" priority="4" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="28" priority="5" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="29" priority="6" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="N5:N43">
+  <x:conditionalFormatting sqref="N5:N44">
     <x:cfRule type="containsText" dxfId="30" priority="7" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="31" priority="8" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="32" priority="9" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Racb0587e60b74444"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ddc967f20134f20"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23272,7 +23316,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3a5c29434f44e40"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13f38179e5df46b4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24437,7 +24481,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0473e66b4554171"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5dc7f339cf84d85"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TokenMeter项目总表.xlsx
+++ b/TokenMeter项目总表.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="Re60ad307bc624cba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="R869b52894da64148"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R276fb5c257d8442e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="Red79df0315d947c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="Re40804555259416f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="Rdff2e0925ebe44f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R2b84aff271f243dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="Rfcba6c88d3d44a78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="R8116b1164695443b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R9ce622b3025e476d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="Rce6d1578b4ad4f27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R11c75e7501aa4a66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Rcd3395bbe05047c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R97521633a63f4ee4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="Rf3827660e9d147a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R7263d892a32a4ea1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R5f8da0600f4e4c6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R7eb3784ad5c347e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="Ra7afe048b4874971"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Rf1d918338b9f4722"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="Ra71b3e2eb1d143a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R8d8da5cb8ed14905"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -786,8 +786,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TMTable6" displayName="TMTable6" ref="A4:N282" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:N282"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TMTable6" displayName="TMTable6" ref="A4:N283" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:N283"/>
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="功能编号"/>
     <x:tableColumn id="2" name="用例编号"/>
@@ -1134,8 +1134,8 @@
         <x:v>已登记用例</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:f>COUNTA('05测试用例'!B5:B282)</x:f>
-        <x:v>278</x:v>
+        <x:f>COUNTA('05测试用例'!B5:B283)</x:f>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="C8" s="9" t="str">
         <x:v>父用例与具有稳定 ID 的变体各占一行；含未来概要场景</x:v>
@@ -1169,7 +1169,7 @@
         <x:v>界面与治理检查</x:v>
       </x:c>
       <x:c r="B11" s="10" t="n">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C11" s="4" t="str">
         <x:v>辅助检查不能替代产品E2E；稳定变体独立列出</x:v>
@@ -1288,7 +1288,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree166958d99d40c3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0051db329a5045c5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1996,7 +1996,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R258567ac30514228"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfbed2d8d073d4d9e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2145,7 +2145,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55c259f9a3eb4581"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb0d713258afa4f66"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2580,7 +2580,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd095365c43504e07"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re8cb2580f5bb4754"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3627,7 +3627,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0856a692cdb04fcd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb66f75821784020"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4734,7 +4734,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf41b0f5f112d4c4f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R815db8d424fd485f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7640,7 +7640,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a8319a5ae234689"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R431c2d98733447a9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20949,30 +20949,81 @@
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
+    <x:row r="283" ht="177" customHeight="1">
+      <x:c r="A283" s="4" t="str">
+        <x:v>TM-004</x:v>
+      </x:c>
+      <x:c r="B283" s="4" t="str">
+        <x:v>TC-TM004-CORE-06</x:v>
+      </x:c>
+      <x:c r="C283" s="4" t="str">
+        <x:v>真实SourceAccess到私有库的多文件贯通</x:v>
+      </x:c>
+      <x:c r="D283" s="4" t="str">
+        <x:v>TASK-TM004-SOURCE
+TASK-TM004-INCREMENTAL</x:v>
+      </x:c>
+      <x:c r="E283" s="4" t="str">
+        <x:v>模块检查</x:v>
+      </x:c>
+      <x:c r="F283" s="4" t="str">
+        <x:v>tests/fixtures/tm004-sourceaccess-store-slice.json；四个2.1.126原生来源去敏投影文件、独立合成追加行；两页2+2/97字节分块与固定HMAC向量</x:v>
+      </x:c>
+      <x:c r="G283" s="4" t="str">
+        <x:v>1. 未确认时扫描，再经真实SourceAccess选择/预览/确认并核对四文件/root键；确认前扫描/读取/库提交均0、库空；确认仅绑定第一主体和sourceId，四文件/root键等于fixture，不把路径/原摘要当库键
+2. 真实主进程采集按两页2+2及97字节片段读完四文件，末页守卫后提交；只一次同步commitScanBatch；M+fork新+Agent父/子共5唯一调用、input85/output32/total117，四游标到LF末、coverage.scan_incomplete=0，复制fork不重计、子父归属已核验，DB/WAL无原生标识或正文
+3. 关闭重开owner来源/库/helper，重扫相同四文件；主体/root/文件键不变、事件5行/117，四游标和覆盖稳定，零新增调用；不自动读取未经确认来源
+4. 向主文件仅追加固定合成50/5完整LF行，续扫并重扫；只新增一调用，6行、input135/output37/total172，主游标推进追加字节数，其余三游标不变，无cursor_reset，复制fork不重计
+5. 从成功库独立副本分别在第一页后撤权、换主体、子文件提前EOF；每次取消scan、commitScanBatch=0；旧6行/172、四游标/覆盖原值不变，新主体无旧事件，本轮不可用/不完整而非已知零；SQLite/WAL与owner清理核对</x:v>
+      </x:c>
+      <x:c r="H283" s="4" t="str">
+        <x:v>准备：每故障从本例成功owner库复制；无生产库；只经UsageStore写入
+变化：成功首次5行/117、追加后6行/172、四游标及覆盖；故障零新写
+核验：只读usage_event/source_cursor/coverage/identity_key_state与SQLite/WAL隐私扫描；逐代际表摘要比较</x:v>
+      </x:c>
+      <x:c r="I283" s="4" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J283" s="4" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K283" s="4" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L283" s="4" t="str">
+        <x:v>docs/testing/cases/04-TM-004-claude-collection.md:221</x:v>
+      </x:c>
+      <x:c r="M283" s="4" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N283" s="4" t="str">
+        <x:v>v0.4.0-20261001T040433Z</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G5:G282">
+  <x:conditionalFormatting sqref="G5:G283">
     <x:cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="I5:I282">
+  <x:conditionalFormatting sqref="I5:I283">
     <x:cfRule type="containsText" dxfId="15" priority="4" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="17" priority="6" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="J5:J282">
+  <x:conditionalFormatting sqref="J5:J283">
     <x:cfRule type="containsText" dxfId="18" priority="7" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="19" priority="8" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="20" priority="9" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="M5:M282">
+  <x:conditionalFormatting sqref="M5:M283">
     <x:cfRule type="containsText" dxfId="21" priority="10" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="22" priority="11" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="23" priority="12" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0901ff8db43b43d8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb9ed34bc6b194032"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22824,7 +22875,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ddc967f20134f20"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb1d38cc0b164ee5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23316,7 +23367,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13f38179e5df46b4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd349354a00ac4a68"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24481,7 +24532,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5dc7f339cf84d85"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R114ad88e1a934f07"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TokenMeter项目总表.xlsx
+++ b/TokenMeter项目总表.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R11c75e7501aa4a66"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Rcd3395bbe05047c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R97521633a63f4ee4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="Rf3827660e9d147a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="R7263d892a32a4ea1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R5f8da0600f4e4c6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R7eb3784ad5c347e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="Ra7afe048b4874971"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Rf1d918338b9f4722"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="Ra71b3e2eb1d143a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R8d8da5cb8ed14905"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R77a41ceb7e1d4eb4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Re90e5233cf324df1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="Rb3dba04077c2466f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R23c0a48c7a024d2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="Rd1467ec4d93f475f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R8b8439e4b95c43b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="Redcd7efcc1be4df9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R87136a7531ae4a7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Rd7591be5ae5a472b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R4aa101cd0367474c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R1fbdb36192e64380"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1288,7 +1288,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0051db329a5045c5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9529159d9c8449b7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1996,7 +1996,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfbed2d8d073d4d9e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85e279ca487f4777"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2145,7 +2145,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb0d713258afa4f66"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e3d5e78a6bb4298"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2580,7 +2580,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re8cb2580f5bb4754"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R522391434b6d4376"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3627,7 +3627,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb66f75821784020"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf314f7705274a05"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4734,7 +4734,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R815db8d424fd485f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6414fd99d1e45fd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7640,7 +7640,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R431c2d98733447a9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd84c01bca41647ba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20949,7 +20949,7 @@
         <x:v>v0.3.0-20261001T034652Z</x:v>
       </x:c>
     </x:row>
-    <x:row r="283" ht="177" customHeight="1">
+    <x:row r="283" ht="192" customHeight="1">
       <x:c r="A283" s="4" t="str">
         <x:v>TM-004</x:v>
       </x:c>
@@ -20967,12 +20967,12 @@
         <x:v>模块检查</x:v>
       </x:c>
       <x:c r="F283" s="4" t="str">
-        <x:v>tests/fixtures/tm004-sourceaccess-store-slice.json；四个2.1.126原生来源去敏投影文件、独立合成追加行；两页2+2/97字节分块与固定HMAC向量</x:v>
+        <x:v>tests/fixtures/tm004-sourceaccess-store-slice.json；四个2.1.126原生来源去敏投影文件、独立合成追加行；两页2+2/97字节分块与固定UUID参考向量及真实确认随机UUID的独立参考HMAC判据</x:v>
       </x:c>
       <x:c r="G283" s="4" t="str">
-        <x:v>1. 未确认时扫描，再经真实SourceAccess选择/预览/确认并核对四文件/root键；确认前扫描/读取/库提交均0、库空；确认仅绑定第一主体和sourceId，四文件/root键等于fixture，不把路径/原摘要当库键
+        <x:v>1. 未确认时扫描，再经真实SourceAccess选择/预览/确认并核对四文件/root键；确认前扫描/读取/库提交均0、库空；真实确认只绑定第一主体并生成随机UUID，不注入固定sourceId；fixture固定UUID的四文件/root向量核参考算法，实际UUID的键等于独立参考HMAC输出；不把路径/原摘要当库键
 2. 真实主进程采集按两页2+2及97字节片段读完四文件，末页守卫后提交；只一次同步commitScanBatch；M+fork新+Agent父/子共5唯一调用、input85/output32/total117，四游标到LF末、coverage.scan_incomplete=0，复制fork不重计、子父归属已核验，DB/WAL无原生标识或正文
-3. 关闭重开owner来源/库/helper，重扫相同四文件；主体/root/文件键不变、事件5行/117，四游标和覆盖稳定，零新增调用；不自动读取未经确认来源
+3. 关闭重开owner来源/库/helper，重扫相同四文件；本轮随机sourceId与主体/root/文件键不变、事件5行/117，四游标和覆盖稳定，零新增调用；不自动读取未经确认来源
 4. 向主文件仅追加固定合成50/5完整LF行，续扫并重扫；只新增一调用，6行、input135/output37/total172，主游标推进追加字节数，其余三游标不变，无cursor_reset，复制fork不重计
 5. 从成功库独立副本分别在第一页后撤权、换主体、子文件提前EOF；每次取消scan、commitScanBatch=0；旧6行/172、四游标/覆盖原值不变，新主体无旧事件，本轮不可用/不完整而非已知零；SQLite/WAL与owner清理核对</x:v>
       </x:c>
@@ -21023,7 +21023,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb9ed34bc6b194032"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4fa96ea4ab404d84"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22875,7 +22875,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb1d38cc0b164ee5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6601eb6dd0b94b41"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23367,7 +23367,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd349354a00ac4a68"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c41e605622d4d2e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24532,7 +24532,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R114ad88e1a934f07"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ca33cc787ed485f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TokenMeter项目总表.xlsx
+++ b/TokenMeter项目总表.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R77a41ceb7e1d4eb4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Re90e5233cf324df1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="Rb3dba04077c2466f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R23c0a48c7a024d2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="Rd1467ec4d93f475f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="R8b8439e4b95c43b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="Redcd7efcc1be4df9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R87136a7531ae4a7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Rd7591be5ae5a472b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R4aa101cd0367474c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R1fbdb36192e64380"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R4b8a303160f5400f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="R3dbd15b232e04066"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R46efc5047b764b33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R8dd1972c7c3e4d01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="Rf8394c7616484a88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="Rf6317604a1364bbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="Ra5a8cac4b33a4931"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R40d4e4b74585463b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="R4f58192d49164ab6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R050217ba2a5c4ec5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R5d42d572a2814a72"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -786,8 +786,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TMTable6" displayName="TMTable6" ref="A4:N283" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:N283"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TMTable6" displayName="TMTable6" ref="A4:N284" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:N284"/>
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="功能编号"/>
     <x:tableColumn id="2" name="用例编号"/>
@@ -1134,8 +1134,8 @@
         <x:v>已登记用例</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:f>COUNTA('05测试用例'!B5:B283)</x:f>
-        <x:v>279</x:v>
+        <x:f>COUNTA('05测试用例'!B5:B284)</x:f>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="C8" s="9" t="str">
         <x:v>父用例与具有稳定 ID 的变体各占一行；含未来概要场景</x:v>
@@ -1169,7 +1169,7 @@
         <x:v>界面与治理检查</x:v>
       </x:c>
       <x:c r="B11" s="10" t="n">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C11" s="4" t="str">
         <x:v>辅助检查不能替代产品E2E；稳定变体独立列出</x:v>
@@ -1288,7 +1288,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9529159d9c8449b7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3fed29b5aa264417"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1996,7 +1996,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85e279ca487f4777"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c3d33699d2c4545"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2145,7 +2145,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e3d5e78a6bb4298"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbbb5786e72754e88"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2580,7 +2580,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R522391434b6d4376"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R901e345719de4d1f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3627,7 +3627,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf314f7705274a05"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80f007a5ff5c43f9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4734,7 +4734,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6414fd99d1e45fd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb10df9d3590b4d26"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7640,7 +7640,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd84c01bca41647ba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R096d115e78054a86"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21000,30 +21000,80 @@
         <x:v>v0.4.0-20261001T040433Z</x:v>
       </x:c>
     </x:row>
+    <x:row r="284" ht="207" customHeight="1">
+      <x:c r="A284" s="9" t="str">
+        <x:v>TM-005</x:v>
+      </x:c>
+      <x:c r="B284" s="9" t="str">
+        <x:v>TC-TM005-CORE-06</x:v>
+      </x:c>
+      <x:c r="C284" s="9" t="str">
+        <x:v>同快照双来源查询视图与模型身份</x:v>
+      </x:c>
+      <x:c r="D284" s="9" t="str">
+        <x:v>TASK-TM005-RANGE-QUERY</x:v>
+      </x:c>
+      <x:c r="E284" s="9" t="str">
+        <x:v>模块检查</x:v>
+      </x:c>
+      <x:c r="F284" s="9" t="str">
+        <x:v>tests/fixtures/tm005-query-view-slice.json引用CORE05物理库种子；上海当地09-29半开UTC、A–H合成事件、字面unknown_model及99字符含冒号模型</x:v>
+      </x:c>
+      <x:c r="G284" s="9" t="str">
+        <x:v>1. A–E仅经真实UsageStore提交到owner库，再在上海09-29 UTC半开窗开启同一只读查询事务；仅A/B两行、calls2、input300/output30、known330；Codex110/Claude220；state partial、total null；C异主体、D界前、E上界排除，查询零写
+2. 同一事务读模型/明细/当地日趋势及三类未知子项；模型null110与sonnet-test220分离，明细A/B，趋势partial/known330/total null；cached read20/未知1、cache write0/未知2、reasoning2/未知1，不加总；输出白名单无原生标识或秘密
+3. 第一事务保持时另一连接写F50/5，再分别查旧事务与新事务；旧事务仍A/B330；新事务A/B/F三调用input350/output35/known385、Codex165/Claude220且partial/total null；WAL不可用则BLOCKED
+4. 独立A–E库经UsageStore增加字面unknown_model的G及99字符含冒号模型H，重查同一日；A/B/G/H四行input370/output37/known407、Codex110/Claude297；modelId null110、sonnet-test220、字面unknown_model33、长冒号模型44互异且原值保留；仍partial/total null
+5. 查询当地10-01无事件日并核对隐私、只读与owner清理；missing/known0/total null，绝不成功完整零；库/WAL与输出无原生ID/路径/正文/secret/密文，仅清理本例拥有目录</x:v>
+      </x:c>
+      <x:c r="H284" s="9" t="str">
+        <x:v>准备：真实UsageStore.commitBatch只写本例owner空库；并发、模型补充与空日各独立副本
+变化：查询零写；基础A/B已知330，F后新事务385，G/H独立分支407
+核验：只读usage_event集合/模型原值/来源/时间及SQLite/WAL隐私；事务前后表摘要与owner清理</x:v>
+      </x:c>
+      <x:c r="I284" s="9" t="str">
+        <x:v>draft</x:v>
+      </x:c>
+      <x:c r="J284" s="9" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K284" s="9" t="str">
+        <x:v>细化用例</x:v>
+      </x:c>
+      <x:c r="L284" s="9" t="str">
+        <x:v>releases/v0.5.0-20261001T034729Z/04a-test-cases.md:375</x:v>
+      </x:c>
+      <x:c r="M284" s="9" t="str">
+        <x:v>尚未执行</x:v>
+      </x:c>
+      <x:c r="N284" s="9" t="str">
+        <x:v>v0.5.0-20261001T034729Z</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G5:G283">
+  <x:conditionalFormatting sqref="G5:G284">
     <x:cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="I5:I283">
+  <x:conditionalFormatting sqref="I5:I284">
     <x:cfRule type="containsText" dxfId="15" priority="4" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="17" priority="6" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="J5:J283">
+  <x:conditionalFormatting sqref="J5:J284">
     <x:cfRule type="containsText" dxfId="18" priority="7" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="19" priority="8" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="20" priority="9" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="M5:M283">
+  <x:conditionalFormatting sqref="M5:M284">
     <x:cfRule type="containsText" dxfId="21" priority="10" operator="containsText" text="FAIL"/>
     <x:cfRule type="containsText" dxfId="22" priority="11" operator="containsText" text="预期待明确"/>
     <x:cfRule type="containsText" dxfId="23" priority="12" operator="containsText" text="未执行"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4fa96ea4ab404d84"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5e37fd6971d4f24"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22875,7 +22925,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6601eb6dd0b94b41"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red69b6cf9ea349bf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23367,7 +23417,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c41e605622d4d2e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc1c06ea376e14a32"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24532,7 +24582,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ca33cc787ed485f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R92d89f73c8be4cab"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TokenMeter项目总表.xlsx
+++ b/TokenMeter项目总表.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R4b8a303160f5400f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="R3dbd15b232e04066"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="R46efc5047b764b33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R8dd1972c7c3e4d01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="Rf8394c7616484a88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="Rf6317604a1364bbf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="Ra5a8cac4b33a4931"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R40d4e4b74585463b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="R4f58192d49164ab6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R050217ba2a5c4ec5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R5d42d572a2814a72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00项目总览" sheetId="1" r:id="R9a0aa274d76c4726"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01需求清单" sheetId="2" r:id="Rfdb325963c5945ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02验收条件" sheetId="3" r:id="Rb144adf4e7fc4b29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03功能点" sheetId="4" r:id="R5e7a0981a3e345ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04开发任务" sheetId="5" r:id="Rc388648c81fd4ccf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05测试用例" sheetId="6" r:id="Rb407bb5e288743e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06测试批次" sheetId="7" r:id="R617128a7b85d4040"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07发布版本" sheetId="8" r:id="R25c324dfd5a4437a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08问题复盘" sheetId="9" r:id="Rc8ec9f5767e849e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09执行SOP" sheetId="10" r:id="R87c6e3652fa249dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10项目约定" sheetId="11" r:id="R1918838afdf44649"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -809,8 +809,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TMTable7" displayName="TMTable7" ref="A4:N44" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:N44"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TMTable7" displayName="TMTable7" ref="A4:N53" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:N53"/>
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="运行批次"/>
     <x:tableColumn id="2" name="版本"/>
@@ -1146,8 +1146,8 @@
         <x:v>测试批次</x:v>
       </x:c>
       <x:c r="B9" s="10" t="n">
-        <x:f>COUNTA('06测试批次'!A5:A44)</x:f>
-        <x:v>40</x:v>
+        <x:f>COUNTA('06测试批次'!A5:A53)</x:f>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C9" s="4" t="str">
         <x:v>06测试批次，每次运行一行，记录独立结果Excel位置</x:v>
@@ -1271,7 +1271,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="C20" s="9" t="str">
-        <x:v>source_check · TM-003 CORE08开发候选私有密钥生命周期固定辅助模块；非产品E2E：CORE08固定四步1/1与owner清理PASS；独立Excel/verification回读PASS。先前红测FAIL原件保留；仅代码候选辅助合同，产品App/真实Keychain及发行NOT_RUN。；是否覆盖完整产品回归以批次范围和原始证据为准。</x:v>
+        <x:v>source_check · TM-003 tm003-core09旧代码候选固定辅助模块；非产品E2E：1/1固定TC、4步与逐例清理PASS；原始报告及独立Excel/verification回读一致。只属于所列旧代码候选；本次文档绑定后未据此声称当前候选PASS，产品App E2E及发行NOT_RUN。；是否覆盖完整产品回归以批次范围和原始证据为准。</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="32" customHeight="1">
@@ -1288,7 +1288,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3fed29b5aa264417"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd57e4d1c608d430a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1996,7 +1996,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c3d33699d2c4545"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3eb98c4c3e8249ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2145,7 +2145,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbbb5786e72754e88"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde09c7aff4b64aef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2580,7 +2580,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R901e345719de4d1f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R296ffe6bd6b64c7f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3627,7 +3627,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80f007a5ff5c43f9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c82bc0790c141fc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4734,7 +4734,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb10df9d3590b4d26"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe158d460f334dcd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7640,7 +7640,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R096d115e78054a86"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4ca7d295c1f24741"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20010,7 +20010,7 @@
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:420</x:v>
       </x:c>
       <x:c r="M263" s="4" t="str">
-        <x:v>tm003-core-20261001T203711Z</x:v>
+        <x:v>tm003-final-20261001T215242Z-tm003-core</x:v>
       </x:c>
       <x:c r="N263" s="4" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
@@ -20059,7 +20059,7 @@
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:424</x:v>
       </x:c>
       <x:c r="M264" s="9" t="str">
-        <x:v>tm003-core-20261001T203711Z</x:v>
+        <x:v>tm003-final-20261001T215242Z-tm003-core</x:v>
       </x:c>
       <x:c r="N264" s="9" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
@@ -20107,7 +20107,7 @@
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:428</x:v>
       </x:c>
       <x:c r="M265" s="4" t="str">
-        <x:v>tm003-core-20261001T203711Z</x:v>
+        <x:v>tm003-final-20261001T215242Z-tm003-core</x:v>
       </x:c>
       <x:c r="N265" s="4" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
@@ -20156,7 +20156,7 @@
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:203</x:v>
       </x:c>
       <x:c r="M266" s="9" t="str">
-        <x:v>tm003-core45-20261001T203711Z</x:v>
+        <x:v>tm003-final-20261001T215242Z-tm003-core45</x:v>
       </x:c>
       <x:c r="N266" s="9" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
@@ -20207,7 +20207,7 @@
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:216</x:v>
       </x:c>
       <x:c r="M267" s="4" t="str">
-        <x:v>tm003-core45-20261001T203711Z</x:v>
+        <x:v>tm003-final-20261001T215242Z-tm003-core45</x:v>
       </x:c>
       <x:c r="N267" s="4" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
@@ -20257,7 +20257,7 @@
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:230</x:v>
       </x:c>
       <x:c r="M268" s="9" t="str">
-        <x:v>tm003-core06-20261001T203711Z</x:v>
+        <x:v>tm003-final-20261001T215242Z-tm003-core06</x:v>
       </x:c>
       <x:c r="N268" s="9" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
@@ -20308,7 +20308,7 @@
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:245</x:v>
       </x:c>
       <x:c r="M269" s="4" t="str">
-        <x:v>tm003-core07-20261001T203711Z</x:v>
+        <x:v>tm003-final-20261001T215242Z-tm003-core07</x:v>
       </x:c>
       <x:c r="N269" s="4" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
@@ -20845,7 +20845,7 @@
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:263</x:v>
       </x:c>
       <x:c r="M280" s="9" t="str">
-        <x:v>tm003-core08-20261001T215000Z</x:v>
+        <x:v>tm003-core08-20261001T220500Z</x:v>
       </x:c>
       <x:c r="N280" s="9" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
@@ -20885,7 +20885,7 @@
         <x:v>draft</x:v>
       </x:c>
       <x:c r="J281" s="4" t="str">
-        <x:v>未执行</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="K281" s="4" t="str">
         <x:v>细化用例</x:v>
@@ -20894,7 +20894,7 @@
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:276</x:v>
       </x:c>
       <x:c r="M281" s="4" t="str">
-        <x:v>尚未执行</x:v>
+        <x:v>tm003-core09-20261001T220500Z</x:v>
       </x:c>
       <x:c r="N281" s="4" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
@@ -20934,7 +20934,7 @@
         <x:v>draft</x:v>
       </x:c>
       <x:c r="J282" s="9" t="str">
-        <x:v>未执行</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="K282" s="9" t="str">
         <x:v>细化用例</x:v>
@@ -20943,7 +20943,7 @@
         <x:v>docs/testing/cases/03-TM-003-codex-collection.md:289</x:v>
       </x:c>
       <x:c r="M282" s="9" t="str">
-        <x:v>尚未执行</x:v>
+        <x:v>tm003-final-20261001T215242Z-tm003-core10</x:v>
       </x:c>
       <x:c r="N282" s="9" t="str">
         <x:v>v0.3.0-20261001T034652Z</x:v>
@@ -21073,7 +21073,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5e37fd6971d4f24"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d69bda786a64f8e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22907,25 +22907,421 @@
         <x:v>NOT_RUN</x:v>
       </x:c>
     </x:row>
+    <x:row r="45" ht="57" customHeight="1">
+      <x:c r="A45" s="4" t="str">
+        <x:v>tm003-final-20261001T215242Z-tm003-core</x:v>
+      </x:c>
+      <x:c r="B45" s="4" t="str">
+        <x:v>v0.3.0-20261001T034652Z</x:v>
+      </x:c>
+      <x:c r="C45" s="4" t="str">
+        <x:v>source_check</x:v>
+      </x:c>
+      <x:c r="D45" s="4" t="str">
+        <x:v>TM-003 tm003-core旧代码候选固定辅助模块；非产品E2E</x:v>
+      </x:c>
+      <x:c r="E45" s="4" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x: